--- a/Results.xlsx
+++ b/Results.xlsx
@@ -545,7 +545,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.12915</v>
+        <v>0.075</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08779375</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1266666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +559,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1639</v>
+        <v>0.225</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.118985</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2125</v>
       </c>
     </row>
     <row r="7">
@@ -561,7 +573,13 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>0.475</v>
+        <v>0.6100200000000001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.06056666666666667</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3266666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -569,7 +587,13 @@
         <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7166714285714285</v>
+        <v>0.7785857142857143</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1436042553191489</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3875</v>
       </c>
     </row>
     <row r="9">
@@ -577,7 +601,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7976000000000001</v>
+        <v>0.8483200000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.08552941176470588</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4450000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -585,7 +615,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8361083333333335</v>
+        <v>0.8702428571428572</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1216777777777778</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.4800000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -593,7 +629,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8736166666666668</v>
+        <v>0.8870333333333333</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1350446428571428</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +643,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>0.893511111111111</v>
+        <v>0.9149999999999998</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.08978148148148149</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4977777777777778</v>
       </c>
     </row>
     <row r="13">
@@ -609,7 +657,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8991699999999999</v>
+        <v>0.9157444444444444</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.217124</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5036363636363637</v>
       </c>
     </row>
     <row r="14">
@@ -617,7 +671,13 @@
         <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9159181818181817</v>
+        <v>0.9259222222222221</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.232845</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5142857142857143</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +685,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="n">
-        <v>0.9189363636363637</v>
+        <v>0.91415</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2367758620689655</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5442857142857143</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +699,13 @@
         <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>0.9280363636363638</v>
+        <v>0.9197749999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.3819878787878788</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="17">
@@ -641,7 +713,13 @@
         <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9273375000000001</v>
+        <v>0.9333222222222223</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4928724999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5700000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -649,7 +727,13 @@
         <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9268555555555555</v>
+        <v>0.9564600000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4787352941176471</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5636363636363636</v>
       </c>
     </row>
     <row r="19">
@@ -657,7 +741,13 @@
         <v>15</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9388916666666667</v>
+        <v>0.9430583333333333</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5002756097560975</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5525</v>
       </c>
     </row>
     <row r="20">
@@ -665,7 +755,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9589000000000001</v>
+        <v>0.9484909090909092</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5714088888888889</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5811111111111111</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +769,13 @@
         <v>17</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9474999999999999</v>
+        <v>0.95938</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.577195744680851</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5844444444444445</v>
       </c>
     </row>
     <row r="22">
@@ -681,7 +783,13 @@
         <v>18</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9447875</v>
+        <v>0.9510444444444444</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5232863636363635</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.6044444444444443</v>
       </c>
     </row>
     <row r="23">
@@ -689,7 +797,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9585555555555556</v>
+        <v>0.9500125</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.6105828571428571</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.597</v>
       </c>
     </row>
     <row r="24">
@@ -697,7 +811,13 @@
         <v>20</v>
       </c>
       <c r="B24" t="n">
-        <v>0.95417</v>
+        <v>0.9601777777777777</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6879018518518519</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5700000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -705,7 +825,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>0.9551384615384615</v>
+        <v>0.9608200000000001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7213787234042554</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5999999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -713,7 +839,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="n">
-        <v>0.9608583333333333</v>
+        <v>0.9611875</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7606375</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6125</v>
       </c>
     </row>
     <row r="27">
@@ -721,7 +853,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="n">
-        <v>0.9555583333333334</v>
+        <v>0.968181818181818</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.778108</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5822222222222222</v>
       </c>
     </row>
     <row r="28">
@@ -729,7 +867,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="n">
-        <v>0.9625000000000002</v>
+        <v>0.9592142857142859</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7689625000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5890909090909091</v>
       </c>
     </row>
     <row r="29">
@@ -737,7 +881,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9678571428571429</v>
+        <v>0.9742999999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7580777777777779</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6055555555555556</v>
       </c>
     </row>
     <row r="30">
@@ -745,7 +895,13 @@
         <v>26</v>
       </c>
       <c r="B30" t="n">
-        <v>0.9658500000000001</v>
+        <v>0.972709090909091</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7292792452830189</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.59375</v>
       </c>
     </row>
     <row r="31">
@@ -753,7 +909,13 @@
         <v>27</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9734499999999999</v>
+        <v>0.9690777777777777</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8179044776119404</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6163636363636364</v>
       </c>
     </row>
     <row r="32">
@@ -761,7 +923,13 @@
         <v>28</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9683727272727273</v>
+        <v>0.9744222222222222</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8443666666666666</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6249999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -769,7 +937,13 @@
         <v>29</v>
       </c>
       <c r="B33" t="n">
-        <v>0.9782500000000002</v>
+        <v>0.9690124999999998</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7803826923076923</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.604</v>
       </c>
     </row>
     <row r="34">
@@ -777,7 +951,13 @@
         <v>30</v>
       </c>
       <c r="B34" t="n">
-        <v>0.965975</v>
+        <v>0.9675777777777778</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7298433333333333</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.638</v>
       </c>
     </row>
     <row r="35">
@@ -785,7 +965,13 @@
         <v>31</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9722444444444446</v>
+        <v>0.9657444444444444</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7477555555555555</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6285714285714286</v>
       </c>
     </row>
     <row r="36">
@@ -793,7 +979,13 @@
         <v>32</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9711181818181819</v>
+        <v>0.9699999999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8142999999999999</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.612</v>
       </c>
     </row>
     <row r="37">
@@ -801,7 +993,13 @@
         <v>33</v>
       </c>
       <c r="B37" t="n">
-        <v>0.96834</v>
+        <v>0.9766600000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7617730769230769</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.63625</v>
       </c>
     </row>
     <row r="38">
@@ -809,7 +1007,13 @@
         <v>34</v>
       </c>
       <c r="B38" t="n">
-        <v>0.9683300000000001</v>
+        <v>0.9699125000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7742342857142858</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.615</v>
       </c>
     </row>
     <row r="39">
@@ -817,7 +1021,13 @@
         <v>35</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9739625</v>
+        <v>0.978125</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.8164804347826088</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6054545454545454</v>
       </c>
     </row>
     <row r="40">
@@ -825,7 +1035,13 @@
         <v>36</v>
       </c>
       <c r="B40" t="n">
-        <v>0.9689454545454547</v>
+        <v>0.9750000000000002</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.8562509090909092</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.603</v>
       </c>
     </row>
     <row r="41">
@@ -833,7 +1049,13 @@
         <v>37</v>
       </c>
       <c r="B41" t="n">
-        <v>0.9720545454545455</v>
+        <v>0.9814888888888889</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.603</v>
       </c>
     </row>
     <row r="42">
@@ -841,7 +1063,13 @@
         <v>38</v>
       </c>
       <c r="B42" t="n">
-        <v>0.9741800000000002</v>
+        <v>0.9695666666666667</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.8326671428571429</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6416666666666667</v>
       </c>
     </row>
     <row r="43">
@@ -849,7 +1077,13 @@
         <v>39</v>
       </c>
       <c r="B43" t="n">
-        <v>0.9750000000000001</v>
+        <v>0.9711833333333332</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7716187499999999</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6218181818181818</v>
       </c>
     </row>
     <row r="44">
@@ -857,7 +1091,13 @@
         <v>40</v>
       </c>
       <c r="B44" t="n">
-        <v>0.9675875</v>
+        <v>0.9719636363636365</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.8240226415094338</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.629</v>
       </c>
     </row>
     <row r="45">
@@ -865,7 +1105,13 @@
         <v>41</v>
       </c>
       <c r="B45" t="n">
-        <v>0.9709444444444445</v>
+        <v>0.9725</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.7969972972972973</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6244444444444444</v>
       </c>
     </row>
     <row r="46">
@@ -873,7 +1119,13 @@
         <v>42</v>
       </c>
       <c r="B46" t="n">
-        <v>0.9750200000000001</v>
+        <v>0.9724999999999999</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8404666666666666</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6125</v>
       </c>
     </row>
     <row r="47">
@@ -881,7 +1133,13 @@
         <v>43</v>
       </c>
       <c r="B47" t="n">
-        <v>0.9750111111111112</v>
+        <v>0.9791625</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8620829787234043</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6258333333333332</v>
       </c>
     </row>
     <row r="48">
@@ -889,7 +1147,13 @@
         <v>44</v>
       </c>
       <c r="B48" t="n">
-        <v>0.9731555555555558</v>
+        <v>0.9758300000000001</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8625190476190476</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.5957142857142858</v>
       </c>
     </row>
     <row r="49">
@@ -897,7 +1161,13 @@
         <v>45</v>
       </c>
       <c r="B49" t="n">
-        <v>0.977075</v>
+        <v>0.9683166666666667</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8678454545454546</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6125</v>
       </c>
     </row>
     <row r="50">
@@ -905,7 +1175,13 @@
         <v>46</v>
       </c>
       <c r="B50" t="n">
-        <v>0.9687625</v>
+        <v>0.9730500000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8535750000000001</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.61875</v>
       </c>
     </row>
     <row r="51">
@@ -913,7 +1189,13 @@
         <v>47</v>
       </c>
       <c r="B51" t="n">
-        <v>0.9727363636363637</v>
+        <v>0.9757</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7888000000000001</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.62625</v>
       </c>
     </row>
     <row r="52">
@@ -921,267 +1203,741 @@
         <v>48</v>
       </c>
       <c r="B52" t="n">
-        <v>0.9686000000000001</v>
+        <v>0.9755375000000003</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8334408163265306</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
         <v>49</v>
       </c>
+      <c r="B53" t="n">
+        <v>0.9708249999999999</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8718388888888888</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6230769230769231</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="B54" t="n">
+        <v>0.9743083333333336</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8772466666666667</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.6163636363636363</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="B55" t="n">
+        <v>0.9722166666666667</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8258163636363636</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.6350000000000001</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>52</v>
       </c>
+      <c r="B56" t="n">
+        <v>0.9757545454545454</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8429017857142859</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.6599999999999998</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>53</v>
       </c>
+      <c r="B57" t="n">
+        <v>0.9777888888888889</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.8547931818181819</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.6525</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>54</v>
       </c>
+      <c r="B58" t="n">
+        <v>0.9814777777777778</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.8976375000000001</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.6236363636363635</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="B59" t="n">
+        <v>0.9759111111111111</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.8037679999999999</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.61625</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
         <v>56</v>
       </c>
+      <c r="B60" t="n">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.8682555555555557</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.6444444444444445</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
         <v>57</v>
       </c>
+      <c r="B61" t="n">
+        <v>0.9802</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.8926078431372549</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.6054545454545454</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>58</v>
       </c>
+      <c r="B62" t="n">
+        <v>0.9718666666666667</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.819167924528302</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.6518181818181819</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
         <v>59</v>
       </c>
+      <c r="B63" t="n">
+        <v>0.9781375000000002</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.8303045454545454</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.6255555555555556</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="B64" t="n">
+        <v>0.9841000000000001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.8741514705882354</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6288888888888888</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
         <v>61</v>
       </c>
+      <c r="B65" t="n">
+        <v>0.9789333333333332</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.8770400000000002</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.6285714285714286</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
         <v>62</v>
       </c>
+      <c r="B66" t="n">
+        <v>0.9845142857142856</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.8505622222222222</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.6560000000000001</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
         <v>63</v>
       </c>
+      <c r="B67" t="n">
+        <v>0.9814000000000002</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.8494515151515151</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.6315384615384616</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="B68" t="n">
+        <v>0.9764833333333335</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.8627947368421053</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.639090909090909</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="B69" t="n">
+        <v>0.9857285714285715</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.8541378378378379</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.61875</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="B70" t="n">
+        <v>0.9780545454545454</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.8497814814814816</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.6409090909090909</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="B71" t="n">
+        <v>0.9828166666666667</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.8404051282051281</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.636</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
         <v>68</v>
       </c>
+      <c r="B72" t="n">
+        <v>0.9763363636363636</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.8604098039215687</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6316666666666666</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
         <v>69</v>
       </c>
+      <c r="B73" t="n">
+        <v>0.9841599999999999</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.8842749999999999</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.645</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="B74" t="n">
+        <v>0.9776857142857144</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.8675236363636362</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.6375</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
         <v>71</v>
       </c>
+      <c r="B75" t="n">
+        <v>0.97697</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.8693981481481482</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="B76" t="n">
+        <v>0.9812714285714286</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.8614092592592593</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.6171428571428572</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
         <v>73</v>
       </c>
+      <c r="B77" t="n">
+        <v>0.97958</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.8722933333333335</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.6262500000000001</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
         <v>74</v>
       </c>
+      <c r="B78" t="n">
+        <v>0.9875100000000001</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.8827476190476191</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.6211111111111111</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
         <v>75</v>
       </c>
+      <c r="B79" t="n">
+        <v>0.9800100000000002</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.8432821428571428</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.60875</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
         <v>76</v>
       </c>
+      <c r="B80" t="n">
+        <v>0.9774444444444447</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.8110307692307692</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6277777777777777</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="B81" t="n">
+        <v>0.9818272727272728</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.8605732142857143</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.6230000000000001</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
         <v>78</v>
       </c>
+      <c r="B82" t="n">
+        <v>0.9766111111111111</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.8467230769230769</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.64375</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
         <v>79</v>
       </c>
+      <c r="B83" t="n">
+        <v>0.9851100000000002</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.8985394736842105</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
         <v>80</v>
       </c>
+      <c r="B84" t="n">
+        <v>0.9818583333333333</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.9103076923076923</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.6455555555555555</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
         <v>81</v>
       </c>
+      <c r="B85" t="n">
+        <v>0.9854249999999999</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.8777682539682541</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.6277777777777778</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
         <v>82</v>
       </c>
+      <c r="B86" t="n">
+        <v>0.9791</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.8578171874999999</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.6144444444444445</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
         <v>83</v>
       </c>
+      <c r="B87" t="n">
+        <v>0.981488888888889</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.8933650793650795</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.6183333333333334</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
         <v>84</v>
       </c>
+      <c r="B88" t="n">
+        <v>0.9768250000000001</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.8925027397260273</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.6274999999999999</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
         <v>85</v>
       </c>
+      <c r="B89" t="n">
+        <v>0.972925</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.8916511111111112</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.6133333333333334</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
         <v>86</v>
       </c>
+      <c r="B90" t="n">
+        <v>0.9861222222222222</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.8890960000000001</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.6259999999999999</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
         <v>87</v>
       </c>
+      <c r="B91" t="n">
+        <v>0.9677142857142859</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.8613071428571428</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.6683333333333334</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
         <v>88</v>
       </c>
+      <c r="B92" t="n">
+        <v>0.9773499999999999</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.6430000000000001</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
         <v>89</v>
       </c>
+      <c r="B93" t="n">
+        <v>0.9848545454545454</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.9126571428571428</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.6399999999999999</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="B94" t="n">
+        <v>0.978990909090909</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.8855859649122806</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.6327272727272727</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
         <v>91</v>
       </c>
+      <c r="B95" t="n">
+        <v>0.9818181818181818</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.8622162790697676</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.6757142857142858</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
         <v>92</v>
       </c>
+      <c r="B96" t="n">
+        <v>0.9736222222222222</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.8845298245614035</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.6366666666666666</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="B97" t="n">
+        <v>0.9733888888888891</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.9000344827586206</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
         <v>94</v>
       </c>
+      <c r="B98" t="n">
+        <v>0.9689777777777779</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.8868131578947367</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.6400000000000001</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="B99" t="n">
+        <v>0.9894090909090911</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.8887260869565218</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.6283333333333334</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
         <v>96</v>
       </c>
+      <c r="B100" t="n">
+        <v>0.9805666666666666</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.8966268656716417</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.6533333333333332</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
         <v>97</v>
       </c>
+      <c r="B101" t="n">
+        <v>0.9760624999999999</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.8949745098039215</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.6449999999999999</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
         <v>98</v>
       </c>
+      <c r="B102" t="n">
+        <v>0.9889000000000001</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.8798243243243243</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.6387499999999999</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
         <v>99</v>
       </c>
+      <c r="B103" t="n">
+        <v>0.9841000000000001</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.905635</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.628</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0.9783181818181821</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.9058384615384617</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.6683333333333333</v>
       </c>
     </row>
     <row r="106">
@@ -1205,6 +1961,12 @@
       <c r="B108" t="n">
         <v>1</v>
       </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -1213,6 +1975,12 @@
       <c r="B109" t="n">
         <v>1</v>
       </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -1221,6 +1989,12 @@
       <c r="B110" t="n">
         <v>1</v>
       </c>
+      <c r="C110" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -1229,6 +2003,12 @@
       <c r="B111" t="n">
         <v>1</v>
       </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -1237,6 +2017,12 @@
       <c r="B112" t="n">
         <v>1</v>
       </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -1245,6 +2031,12 @@
       <c r="B113" t="n">
         <v>1</v>
       </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -1253,6 +2045,12 @@
       <c r="B114" t="n">
         <v>1</v>
       </c>
+      <c r="C114" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -1261,6 +2059,12 @@
       <c r="B115" t="n">
         <v>1</v>
       </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -1269,6 +2073,12 @@
       <c r="B116" t="n">
         <v>1</v>
       </c>
+      <c r="C116" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -1277,13 +2087,25 @@
       <c r="B117" t="n">
         <v>1</v>
       </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B118" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -1293,6 +2115,12 @@
       <c r="B119" t="n">
         <v>1</v>
       </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -1301,12 +2129,24 @@
       <c r="B120" t="n">
         <v>1</v>
       </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B121" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1315,6 +2155,12 @@
         <v>15</v>
       </c>
       <c r="B122" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1323,6 +2169,12 @@
         <v>16</v>
       </c>
       <c r="B123" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1333,6 +2185,12 @@
       <c r="B124" t="n">
         <v>1</v>
       </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -1341,12 +2199,24 @@
       <c r="B125" t="n">
         <v>1</v>
       </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B126" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1355,6 +2225,12 @@
         <v>20</v>
       </c>
       <c r="B127" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1365,6 +2241,12 @@
       <c r="B128" t="n">
         <v>1</v>
       </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -1373,12 +2255,24 @@
       <c r="B129" t="n">
         <v>1</v>
       </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B130" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1389,12 +2283,24 @@
       <c r="B131" t="n">
         <v>1</v>
       </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B132" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1403,6 +2309,12 @@
         <v>26</v>
       </c>
       <c r="B133" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1411,6 +2323,12 @@
         <v>27</v>
       </c>
       <c r="B134" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1421,12 +2339,24 @@
       <c r="B135" t="n">
         <v>1</v>
       </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B136" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1437,6 +2367,12 @@
       <c r="B137" t="n">
         <v>1</v>
       </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -1445,12 +2381,24 @@
       <c r="B138" t="n">
         <v>1</v>
       </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
         <v>32</v>
       </c>
       <c r="B139" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1461,12 +2409,24 @@
       <c r="B140" t="n">
         <v>1</v>
       </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B141" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1475,6 +2435,12 @@
         <v>35</v>
       </c>
       <c r="B142" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1483,6 +2449,12 @@
         <v>36</v>
       </c>
       <c r="B143" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1491,6 +2463,12 @@
         <v>37</v>
       </c>
       <c r="B144" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1501,12 +2479,24 @@
       <c r="B145" t="n">
         <v>1</v>
       </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
         <v>39</v>
       </c>
       <c r="B146" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1515,6 +2505,12 @@
         <v>40</v>
       </c>
       <c r="B147" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1523,6 +2519,12 @@
         <v>41</v>
       </c>
       <c r="B148" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1533,6 +2535,12 @@
       <c r="B149" t="n">
         <v>1</v>
       </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -1541,6 +2549,12 @@
       <c r="B150" t="n">
         <v>1</v>
       </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -1549,6 +2563,12 @@
       <c r="B151" t="n">
         <v>1</v>
       </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -1557,12 +2577,24 @@
       <c r="B152" t="n">
         <v>1</v>
       </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
         <v>46</v>
       </c>
       <c r="B153" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1571,6 +2603,12 @@
         <v>47</v>
       </c>
       <c r="B154" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1581,12 +2619,24 @@
       <c r="B155" t="n">
         <v>1</v>
       </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
         <v>49</v>
       </c>
       <c r="B156" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1594,255 +2644,714 @@
       <c r="A157" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
         <v>52</v>
       </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
         <v>53</v>
       </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
         <v>54</v>
       </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="B162" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
         <v>56</v>
       </c>
+      <c r="B163" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
         <v>57</v>
       </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
         <v>58</v>
       </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
         <v>59</v>
       </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="B167" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
         <v>61</v>
       </c>
+      <c r="B168" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
         <v>62</v>
       </c>
+      <c r="B169" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
         <v>63</v>
       </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="B172" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="B174" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
         <v>68</v>
       </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
         <v>69</v>
       </c>
+      <c r="B176" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
         <v>71</v>
       </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="B179" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
         <v>73</v>
       </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
         <v>74</v>
       </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
         <v>75</v>
       </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
         <v>76</v>
       </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="B184" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
         <v>78</v>
       </c>
+      <c r="B185" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
         <v>79</v>
       </c>
+      <c r="B186" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
         <v>80</v>
       </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
         <v>81</v>
       </c>
+      <c r="B188" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
         <v>82</v>
       </c>
+      <c r="B189" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
         <v>83</v>
       </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
         <v>84</v>
       </c>
+      <c r="B191" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
         <v>85</v>
       </c>
+      <c r="B192" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
         <v>86</v>
       </c>
+      <c r="B193" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
         <v>87</v>
       </c>
+      <c r="B194" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
         <v>88</v>
       </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
         <v>89</v>
       </c>
+      <c r="B196" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="B197" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
         <v>91</v>
       </c>
+      <c r="B198" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
         <v>92</v>
       </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="B200" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
         <v>94</v>
       </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
         <v>96</v>
       </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
         <v>97</v>
       </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
         <v>98</v>
       </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
         <v>99</v>
       </c>
+      <c r="B206" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -1866,6 +3375,12 @@
       <c r="B212" t="n">
         <v>1</v>
       </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.9772000000000001</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -1874,6 +3389,12 @@
       <c r="B213" t="n">
         <v>1</v>
       </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.9673857142857142</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -1882,13 +3403,25 @@
       <c r="B214" t="n">
         <v>1</v>
       </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0.9743600000000001</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B215" t="n">
-        <v>0.9712</v>
+        <v>0.86335</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.1422666666666667</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.9819</v>
       </c>
     </row>
     <row r="216">
@@ -1896,7 +3429,13 @@
         <v>5</v>
       </c>
       <c r="B216" t="n">
-        <v>0.6861999999999999</v>
+        <v>0.59855</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0.9669666666666666</v>
       </c>
     </row>
     <row r="217">
@@ -1904,7 +3443,13 @@
         <v>6</v>
       </c>
       <c r="B217" t="n">
-        <v>0.56502</v>
+        <v>0.5038666666666667</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0.9683400000000001</v>
       </c>
     </row>
     <row r="218">
@@ -1912,7 +3457,13 @@
         <v>7</v>
       </c>
       <c r="B218" t="n">
-        <v>0.47515</v>
+        <v>0.4394428571428571</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.9669000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -1920,7 +3471,13 @@
         <v>8</v>
       </c>
       <c r="B219" t="n">
-        <v>0.4212142857142857</v>
+        <v>0.4006333333333333</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0.9687625</v>
       </c>
     </row>
     <row r="220">
@@ -1928,7 +3485,13 @@
         <v>9</v>
       </c>
       <c r="B220" t="n">
-        <v>0.3956</v>
+        <v>0.38996</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.06954444444444445</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0.9676</v>
       </c>
     </row>
     <row r="221">
@@ -1936,7 +3499,13 @@
         <v>10</v>
       </c>
       <c r="B221" t="n">
-        <v>0.3644</v>
+        <v>0.3386285714285714</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0.9676999999999999</v>
       </c>
     </row>
     <row r="222">
@@ -1944,7 +3513,13 @@
         <v>11</v>
       </c>
       <c r="B222" t="n">
-        <v>0.3629285714285714</v>
+        <v>0.35256</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0.9615285714285715</v>
       </c>
     </row>
     <row r="223">
@@ -1952,7 +3527,13 @@
         <v>12</v>
       </c>
       <c r="B223" t="n">
-        <v>0.339125</v>
+        <v>0.3218</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0.9644000000000001</v>
       </c>
     </row>
     <row r="224">
@@ -1960,7 +3541,13 @@
         <v>13</v>
       </c>
       <c r="B224" t="n">
-        <v>0.3403666666666667</v>
+        <v>0.31868</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0.9641999999999999</v>
       </c>
     </row>
     <row r="225">
@@ -1968,7 +3555,13 @@
         <v>14</v>
       </c>
       <c r="B225" t="n">
-        <v>0.31595</v>
+        <v>0.29882</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.03905714285714285</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0.9649666666666668</v>
       </c>
     </row>
     <row r="226">
@@ -1976,7 +3569,13 @@
         <v>15</v>
       </c>
       <c r="B226" t="n">
-        <v>0.3058166666666667</v>
+        <v>0.2854875</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.0001857142857142857</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0.9652200000000001</v>
       </c>
     </row>
     <row r="227">
@@ -1984,7 +3583,13 @@
         <v>16</v>
       </c>
       <c r="B227" t="n">
-        <v>0.30622</v>
+        <v>0.297275</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.002471428571428571</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.95095</v>
       </c>
     </row>
     <row r="228">
@@ -1992,7 +3597,13 @@
         <v>17</v>
       </c>
       <c r="B228" t="n">
-        <v>0.2895857142857143</v>
+        <v>0.2832285714285714</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.0018875</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.9593</v>
       </c>
     </row>
     <row r="229">
@@ -2000,7 +3611,13 @@
         <v>18</v>
       </c>
       <c r="B229" t="n">
-        <v>0.300575</v>
+        <v>0.2855571428571428</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.02157777777777778</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.9638285714285714</v>
       </c>
     </row>
     <row r="230">
@@ -2008,7 +3625,13 @@
         <v>19</v>
       </c>
       <c r="B230" t="n">
-        <v>0.2901142857142857</v>
+        <v>0.3038571428571428</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0.9687625000000001</v>
       </c>
     </row>
     <row r="231">
@@ -2016,7 +3639,13 @@
         <v>20</v>
       </c>
       <c r="B231" t="n">
-        <v>0.29308</v>
+        <v>0.2821833333333333</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.0154375</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.9601166666666666</v>
       </c>
     </row>
     <row r="232">
@@ -2024,7 +3653,13 @@
         <v>21</v>
       </c>
       <c r="B232" t="n">
-        <v>0.2775333333333334</v>
+        <v>0.2840428571428572</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.0192375</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0.9636222222222222</v>
       </c>
     </row>
     <row r="233">
@@ -2032,7 +3667,13 @@
         <v>22</v>
       </c>
       <c r="B233" t="n">
-        <v>0.2799714285714285</v>
+        <v>0.2996833333333334</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0.9546999999999999</v>
       </c>
     </row>
     <row r="234">
@@ -2040,7 +3681,13 @@
         <v>23</v>
       </c>
       <c r="B234" t="n">
-        <v>0.2827333333333333</v>
+        <v>0.2696333333333333</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.96022</v>
       </c>
     </row>
     <row r="235">
@@ -2048,7 +3695,13 @@
         <v>24</v>
       </c>
       <c r="B235" t="n">
-        <v>0.2799666666666666</v>
+        <v>0.29164</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.06626000000000001</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0.9564333333333331</v>
       </c>
     </row>
     <row r="236">
@@ -2056,7 +3709,13 @@
         <v>25</v>
       </c>
       <c r="B236" t="n">
-        <v>0.2811333333333333</v>
+        <v>0.2852333333333333</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.04455555555555556</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0.9619</v>
       </c>
     </row>
     <row r="237">
@@ -2064,7 +3723,13 @@
         <v>26</v>
       </c>
       <c r="B237" t="n">
-        <v>0.26224</v>
+        <v>0.27145</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.06140000000000001</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0.950325</v>
       </c>
     </row>
     <row r="238">
@@ -2072,7 +3737,13 @@
         <v>27</v>
       </c>
       <c r="B238" t="n">
-        <v>0.2692</v>
+        <v>0.2926</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.06131</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.9628</v>
       </c>
     </row>
     <row r="239">
@@ -2080,7 +3751,13 @@
         <v>28</v>
       </c>
       <c r="B239" t="n">
-        <v>0.2760857142857143</v>
+        <v>0.2846142857142857</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.06942222222222222</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0.95996</v>
       </c>
     </row>
     <row r="240">
@@ -2088,7 +3765,13 @@
         <v>29</v>
       </c>
       <c r="B240" t="n">
-        <v>0.2693428571428571</v>
+        <v>0.279325</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.04089999999999999</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.9742500000000001</v>
       </c>
     </row>
     <row r="241">
@@ -2096,7 +3779,13 @@
         <v>30</v>
       </c>
       <c r="B241" t="n">
-        <v>0.2622</v>
+        <v>0.3313571428571428</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.04338571428571429</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.964375</v>
       </c>
     </row>
     <row r="242">
@@ -2104,7 +3793,13 @@
         <v>31</v>
       </c>
       <c r="B242" t="n">
-        <v>0.2738</v>
+        <v>0.28066</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.04341111111111111</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.965025</v>
       </c>
     </row>
     <row r="243">
@@ -2112,7 +3807,13 @@
         <v>32</v>
       </c>
       <c r="B243" t="n">
-        <v>0.26368</v>
+        <v>0.30395</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0.9628666666666668</v>
       </c>
     </row>
     <row r="244">
@@ -2120,7 +3821,13 @@
         <v>33</v>
       </c>
       <c r="B244" t="n">
-        <v>0.2634571428571429</v>
+        <v>0.309525</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.07202222222222222</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0.9635499999999999</v>
       </c>
     </row>
     <row r="245">
@@ -2128,7 +3835,13 @@
         <v>34</v>
       </c>
       <c r="B245" t="n">
-        <v>0.2664625</v>
+        <v>0.31492</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.0725625</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.95785</v>
       </c>
     </row>
     <row r="246">
@@ -2136,7 +3849,13 @@
         <v>35</v>
       </c>
       <c r="B246" t="n">
-        <v>0.2585</v>
+        <v>0.3557833333333333</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0.9650444444444444</v>
       </c>
     </row>
     <row r="247">
@@ -2144,7 +3863,13 @@
         <v>36</v>
       </c>
       <c r="B247" t="n">
-        <v>0.253075</v>
+        <v>0.43475</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.0772375</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0.9617</v>
       </c>
     </row>
     <row r="248">
@@ -2152,7 +3877,13 @@
         <v>37</v>
       </c>
       <c r="B248" t="n">
-        <v>0.2735375</v>
+        <v>0.4515</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.0704125</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0.9598714285714287</v>
       </c>
     </row>
     <row r="249">
@@ -2160,7 +3891,13 @@
         <v>38</v>
       </c>
       <c r="B249" t="n">
-        <v>0.26024</v>
+        <v>0.4719375</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.0595625</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0.96745</v>
       </c>
     </row>
     <row r="250">
@@ -2168,7 +3905,13 @@
         <v>39</v>
       </c>
       <c r="B250" t="n">
-        <v>0.27382</v>
+        <v>0.5395</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.08852499999999999</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0.9658000000000001</v>
       </c>
     </row>
     <row r="251">
@@ -2176,7 +3919,13 @@
         <v>40</v>
       </c>
       <c r="B251" t="n">
-        <v>0.2621875</v>
+        <v>0.73798</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.06547142857142857</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.9679333333333333</v>
       </c>
     </row>
     <row r="252">
@@ -2184,7 +3933,13 @@
         <v>41</v>
       </c>
       <c r="B252" t="n">
-        <v>0.25056</v>
+        <v>0.6383</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.03972</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.9638285714285715</v>
       </c>
     </row>
     <row r="253">
@@ -2192,7 +3947,13 @@
         <v>42</v>
       </c>
       <c r="B253" t="n">
-        <v>0.2584428571428571</v>
+        <v>0.7238666666666665</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.06938571428571429</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0.9564333333333334</v>
       </c>
     </row>
     <row r="254">
@@ -2200,7 +3961,13 @@
         <v>43</v>
       </c>
       <c r="B254" t="n">
-        <v>0.2419125</v>
+        <v>0.8518499999999999</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.0516375</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0.9648499999999999</v>
       </c>
     </row>
     <row r="255">
@@ -2208,7 +3975,13 @@
         <v>44</v>
       </c>
       <c r="B255" t="n">
-        <v>0.25678</v>
+        <v>0.8441000000000001</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.07271999999999999</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0.9621875</v>
       </c>
     </row>
     <row r="256">
@@ -2216,7 +3989,13 @@
         <v>45</v>
       </c>
       <c r="B256" t="n">
-        <v>0.24985</v>
+        <v>0.7597333333333333</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.04641428571428571</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0.9553666666666666</v>
       </c>
     </row>
     <row r="257">
@@ -2224,7 +4003,13 @@
         <v>46</v>
       </c>
       <c r="B257" t="n">
-        <v>0.259</v>
+        <v>0.7519857142857144</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.09318333333333333</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0.9653999999999999</v>
       </c>
     </row>
     <row r="258">
@@ -2232,7 +4017,13 @@
         <v>47</v>
       </c>
       <c r="B258" t="n">
-        <v>0.261525</v>
+        <v>0.962475</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.06245000000000001</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.9633666666666666</v>
       </c>
     </row>
     <row r="259">
@@ -2240,7 +4031,13 @@
         <v>48</v>
       </c>
       <c r="B259" t="n">
-        <v>0.2598444444444444</v>
+        <v>0.9591999999999998</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.05246000000000001</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0.9670666666666666</v>
       </c>
     </row>
     <row r="260">
@@ -2248,262 +4045,727 @@
         <v>49</v>
       </c>
       <c r="B260" t="n">
-        <v>0.241125</v>
+        <v>0.964325</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.05988888888888889</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.9664</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="B261" t="n">
+        <v>0.9275399999999999</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0.9633799999999999</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="B262" t="n">
+        <v>0.9653166666666667</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.05334999999999999</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.968325</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
         <v>52</v>
       </c>
+      <c r="B263" t="n">
+        <v>0.96005</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.05070000000000001</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0.9642375</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
         <v>53</v>
       </c>
+      <c r="B264" t="n">
+        <v>0.955757142857143</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.06910000000000001</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.9686999999999999</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
         <v>54</v>
       </c>
+      <c r="B265" t="n">
+        <v>0.9303999999999999</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.06868333333333333</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.9644374999999999</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="B266" t="n">
+        <v>0.9620571428571428</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.05111250000000001</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.968075</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
         <v>56</v>
       </c>
+      <c r="B267" t="n">
+        <v>0.9572857142857142</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.06910999999999998</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.9668166666666665</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
         <v>57</v>
       </c>
+      <c r="B268" t="n">
+        <v>0.9866199999999999</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.04971428571428571</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0.9664</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
         <v>58</v>
       </c>
+      <c r="B269" t="n">
+        <v>0.9676</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.0684375</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.96395</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
         <v>59</v>
       </c>
+      <c r="B270" t="n">
+        <v>0.9726750000000001</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.06354444444444445</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0.9705428571428572</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="B271" t="n">
+        <v>0.9635428571428571</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.06415555555555556</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0.9693666666666667</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
         <v>61</v>
       </c>
+      <c r="B272" t="n">
+        <v>0.9633142857142858</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.04751250000000001</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0.9635166666666666</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
         <v>62</v>
       </c>
+      <c r="B273" t="n">
+        <v>0.9835000000000002</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.06792999999999999</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0.973325</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
         <v>63</v>
       </c>
+      <c r="B274" t="n">
+        <v>0.9725833333333332</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.07925714285714287</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.9641</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="B275" t="n">
+        <v>0.9744666666666668</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.06868571428571429</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.9616666666666668</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="B276" t="n">
+        <v>0.9744666666666667</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.0759</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.9686666666666667</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="B277" t="n">
+        <v>0.9754799999999999</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.08202857142857144</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.9633833333333333</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="B278" t="n">
+        <v>0.9847400000000001</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.07958333333333333</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.9729166666666668</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
         <v>68</v>
       </c>
+      <c r="B279" t="n">
+        <v>0.9802</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.05191666666666667</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.9715166666666667</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
         <v>69</v>
       </c>
+      <c r="B280" t="n">
+        <v>0.9826333333333334</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.07367142857142857</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.9588800000000001</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="B281" t="n">
+        <v>0.989725</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.0640125</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.9632714285714287</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
         <v>71</v>
       </c>
+      <c r="B282" t="n">
+        <v>0.98514</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.06746666666666666</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.9753399999999999</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="B283" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.0602</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0.9684250000000001</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
         <v>73</v>
       </c>
+      <c r="B284" t="n">
+        <v>0.9802</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.05590000000000001</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.96546</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
         <v>74</v>
       </c>
+      <c r="B285" t="n">
+        <v>0.9833714285714287</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.06083999999999999</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0.9726666666666667</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
         <v>75</v>
       </c>
+      <c r="B286" t="n">
+        <v>0.9794499999999999</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.06904000000000002</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.9741333333333334</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
         <v>76</v>
       </c>
+      <c r="B287" t="n">
+        <v>0.9681000000000001</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.07385</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0.9765</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="B288" t="n">
+        <v>0.9846125</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.0515625</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.9697249999999999</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
         <v>78</v>
       </c>
+      <c r="B289" t="n">
+        <v>0.9876999999999999</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.06046666666666667</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0.9720666666666666</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
         <v>79</v>
       </c>
+      <c r="B290" t="n">
+        <v>0.981625</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.06795</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0.9654428571428569</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
         <v>80</v>
       </c>
+      <c r="B291" t="n">
+        <v>0.9883333333333333</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0.9690199999999999</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
         <v>81</v>
       </c>
+      <c r="B292" t="n">
+        <v>0.9881599999999999</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.08726250000000001</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0.9711400000000001</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
         <v>82</v>
       </c>
+      <c r="B293" t="n">
+        <v>0.9818166666666667</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.06408571428571429</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0.974</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
         <v>83</v>
       </c>
+      <c r="B294" t="n">
+        <v>0.9905571428571428</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.06754444444444446</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.9732714285714287</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
         <v>84</v>
       </c>
+      <c r="B295" t="n">
+        <v>0.9775285714285713</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.066125</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0.96868</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
         <v>85</v>
       </c>
+      <c r="B296" t="n">
+        <v>0.9914375</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.9729142857142856</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
         <v>86</v>
       </c>
+      <c r="B297" t="n">
+        <v>0.9937571428571428</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.040475</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0.9695125</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
         <v>87</v>
       </c>
+      <c r="B298" t="n">
+        <v>0.99178</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.07001250000000001</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0.976625</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
         <v>88</v>
       </c>
+      <c r="B299" t="n">
+        <v>0.9896750000000001</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.08821428571428572</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0.9759</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
         <v>89</v>
       </c>
+      <c r="B300" t="n">
+        <v>0.9946666666666667</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.07955555555555555</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0.9629</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="B301" t="n">
+        <v>0.99222</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.07677777777777778</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0.9754000000000002</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
         <v>91</v>
       </c>
+      <c r="B302" t="n">
+        <v>0.9934166666666666</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.05825999999999999</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0.9681571428571428</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
         <v>92</v>
       </c>
+      <c r="B303" t="n">
+        <v>0.9918428571428571</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.07485714285714286</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0.9691249999999999</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="B304" t="n">
+        <v>0.9931875</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.06672</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0.9712666666666667</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
         <v>94</v>
       </c>
+      <c r="B305" t="n">
+        <v>0.9929249999999999</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.09228571428571429</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0.968</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="B306" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.0708125</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0.974075</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
         <v>96</v>
       </c>
+      <c r="B307" t="n">
+        <v>0.9890833333333333</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.09132222222222222</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0.97094</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
         <v>97</v>
       </c>
+      <c r="B308" t="n">
+        <v>0.991475</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.0773888888888889</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0.970175</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
         <v>98</v>
       </c>
+      <c r="B309" t="n">
+        <v>0.9940142857142857</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.07300999999999999</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.9758000000000001</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
         <v>99</v>
       </c>
+      <c r="B310" t="n">
+        <v>0.9950600000000002</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.06864285714285714</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0.9707333333333333</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="B311" t="n">
+        <v>0.995475</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.08885000000000001</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0.97026</v>
       </c>
     </row>
     <row r="314">
@@ -2527,13 +4789,25 @@
       <c r="B316" t="n">
         <v>0</v>
       </c>
+      <c r="C316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>0.0005</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B317" t="n">
-        <v>0.0365</v>
+        <v>0.2521</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0.0167</v>
       </c>
     </row>
     <row r="318">
@@ -2541,7 +4815,13 @@
         <v>3</v>
       </c>
       <c r="B318" t="n">
-        <v>0.1618</v>
+        <v>0.0819</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>0.0401</v>
       </c>
     </row>
     <row r="319">
@@ -2549,7 +4829,13 @@
         <v>4</v>
       </c>
       <c r="B319" t="n">
-        <v>0.1013</v>
+        <v>0.0959</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>0.0653</v>
       </c>
     </row>
     <row r="320">
@@ -2557,7 +4843,13 @@
         <v>5</v>
       </c>
       <c r="B320" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0.0764</v>
       </c>
     </row>
     <row r="321">
@@ -2565,7 +4857,13 @@
         <v>6</v>
       </c>
       <c r="B321" t="n">
-        <v>0.0935</v>
+        <v>0.1016</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>0.0892</v>
       </c>
     </row>
     <row r="322">
@@ -2573,7 +4871,13 @@
         <v>7</v>
       </c>
       <c r="B322" t="n">
-        <v>0.1003</v>
+        <v>0.1053</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="E322" t="n">
+        <v>0.0819</v>
       </c>
     </row>
     <row r="323">
@@ -2581,7 +4885,13 @@
         <v>8</v>
       </c>
       <c r="B323" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1016</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0.0917</v>
       </c>
     </row>
     <row r="324">
@@ -2589,7 +4899,13 @@
         <v>9</v>
       </c>
       <c r="B324" t="n">
-        <v>0.0989</v>
+        <v>0.1011</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="325">
@@ -2597,7 +4913,13 @@
         <v>10</v>
       </c>
       <c r="B325" t="n">
-        <v>0.1</v>
+        <v>0.1002</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>0.0858</v>
       </c>
     </row>
     <row r="326">
@@ -2605,7 +4927,13 @@
         <v>11</v>
       </c>
       <c r="B326" t="n">
-        <v>0.1059</v>
+        <v>0.1024</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0.103</v>
       </c>
     </row>
     <row r="327">
@@ -2613,7 +4941,13 @@
         <v>12</v>
       </c>
       <c r="B327" t="n">
-        <v>0.099</v>
+        <v>0.1014</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0.1025</v>
       </c>
     </row>
     <row r="328">
@@ -2621,7 +4955,13 @@
         <v>13</v>
       </c>
       <c r="B328" t="n">
-        <v>0.1025</v>
+        <v>0.1027</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>0.104</v>
       </c>
     </row>
     <row r="329">
@@ -2629,7 +4969,13 @@
         <v>14</v>
       </c>
       <c r="B329" t="n">
-        <v>0.1015</v>
+        <v>0.1064</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0.1027</v>
       </c>
     </row>
     <row r="330">
@@ -2637,6 +4983,12 @@
         <v>15</v>
       </c>
       <c r="B330" t="n">
+        <v>0.1066</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="E330" t="n">
         <v>0.0987</v>
       </c>
     </row>
@@ -2645,7 +4997,13 @@
         <v>16</v>
       </c>
       <c r="B331" t="n">
-        <v>0.099</v>
+        <v>0.1075</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="E331" t="n">
+        <v>0.0974</v>
       </c>
     </row>
     <row r="332">
@@ -2653,7 +5011,13 @@
         <v>17</v>
       </c>
       <c r="B332" t="n">
-        <v>0.0978</v>
+        <v>0.1027</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="E332" t="n">
+        <v>0.0927</v>
       </c>
     </row>
     <row r="333">
@@ -2661,7 +5025,13 @@
         <v>18</v>
       </c>
       <c r="B333" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.1011</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>0.1021</v>
       </c>
     </row>
     <row r="334">
@@ -2669,7 +5039,13 @@
         <v>19</v>
       </c>
       <c r="B334" t="n">
-        <v>0.1021</v>
+        <v>0.1059</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0.09669999999999999</v>
       </c>
     </row>
     <row r="335">
@@ -2677,7 +5053,13 @@
         <v>20</v>
       </c>
       <c r="B335" t="n">
-        <v>0.0993</v>
+        <v>0.1048</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="E335" t="n">
+        <v>0.0969</v>
       </c>
     </row>
     <row r="336">
@@ -2685,7 +5067,13 @@
         <v>21</v>
       </c>
       <c r="B336" t="n">
-        <v>0.1006</v>
+        <v>0.1013</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.0567</v>
+      </c>
+      <c r="E336" t="n">
+        <v>0.1058</v>
       </c>
     </row>
     <row r="337">
@@ -2693,7 +5081,13 @@
         <v>22</v>
       </c>
       <c r="B337" t="n">
-        <v>0.0984</v>
+        <v>0.1008</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="E337" t="n">
+        <v>0.0969</v>
       </c>
     </row>
     <row r="338">
@@ -2701,7 +5095,13 @@
         <v>23</v>
       </c>
       <c r="B338" t="n">
-        <v>0.0974</v>
+        <v>0.1044</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0.09909999999999999</v>
       </c>
     </row>
     <row r="339">
@@ -2709,7 +5109,13 @@
         <v>24</v>
       </c>
       <c r="B339" t="n">
-        <v>0.1007</v>
+        <v>0.0997</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="E339" t="n">
+        <v>0.1073</v>
       </c>
     </row>
     <row r="340">
@@ -2717,7 +5123,13 @@
         <v>25</v>
       </c>
       <c r="B340" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1029</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0.0997</v>
       </c>
     </row>
     <row r="341">
@@ -2725,7 +5137,13 @@
         <v>26</v>
       </c>
       <c r="B341" t="n">
-        <v>0.099</v>
+        <v>0.1048</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.1024</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0.0974</v>
       </c>
     </row>
     <row r="342">
@@ -2733,7 +5151,13 @@
         <v>27</v>
       </c>
       <c r="B342" t="n">
-        <v>0.099</v>
+        <v>0.1033</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0.1032</v>
       </c>
     </row>
     <row r="343">
@@ -2741,7 +5165,13 @@
         <v>28</v>
       </c>
       <c r="B343" t="n">
-        <v>0.0993</v>
+        <v>0.1019</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0.1013</v>
       </c>
     </row>
     <row r="344">
@@ -2749,7 +5179,13 @@
         <v>29</v>
       </c>
       <c r="B344" t="n">
-        <v>0.099</v>
+        <v>0.1018</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="E344" t="n">
+        <v>0.097</v>
       </c>
     </row>
     <row r="345">
@@ -2757,7 +5193,13 @@
         <v>30</v>
       </c>
       <c r="B345" t="n">
-        <v>0.0988</v>
+        <v>0.0997</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0.1054</v>
       </c>
     </row>
     <row r="346">
@@ -2765,7 +5207,13 @@
         <v>31</v>
       </c>
       <c r="B346" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.1234</v>
+      </c>
+      <c r="E346" t="n">
+        <v>0.1032</v>
       </c>
     </row>
     <row r="347">
@@ -2773,7 +5221,13 @@
         <v>32</v>
       </c>
       <c r="B347" t="n">
-        <v>0.0979</v>
+        <v>0.1045</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.1055</v>
+      </c>
+      <c r="E347" t="n">
+        <v>0.0975</v>
       </c>
     </row>
     <row r="348">
@@ -2781,7 +5235,13 @@
         <v>33</v>
       </c>
       <c r="B348" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0997</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0.1067</v>
       </c>
     </row>
     <row r="349">
@@ -2789,7 +5249,13 @@
         <v>34</v>
       </c>
       <c r="B349" t="n">
-        <v>0.0989</v>
+        <v>0.1021</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="E349" t="n">
+        <v>0.1022</v>
       </c>
     </row>
     <row r="350">
@@ -2797,7 +5263,13 @@
         <v>35</v>
       </c>
       <c r="B350" t="n">
-        <v>0.0992</v>
+        <v>0.1032</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="E350" t="n">
+        <v>0.1099</v>
       </c>
     </row>
     <row r="351">
@@ -2805,7 +5277,13 @@
         <v>36</v>
       </c>
       <c r="B351" t="n">
-        <v>0.1001</v>
+        <v>0.1029</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="E351" t="n">
+        <v>0.1114</v>
       </c>
     </row>
     <row r="352">
@@ -2813,7 +5291,13 @@
         <v>37</v>
       </c>
       <c r="B352" t="n">
-        <v>0.0989</v>
+        <v>0.1027</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0.1079</v>
       </c>
     </row>
     <row r="353">
@@ -2821,7 +5305,13 @@
         <v>38</v>
       </c>
       <c r="B353" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0992</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="E353" t="n">
+        <v>0.1074</v>
       </c>
     </row>
     <row r="354">
@@ -2829,7 +5319,13 @@
         <v>39</v>
       </c>
       <c r="B354" t="n">
-        <v>0.1004</v>
+        <v>0.1019</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="E354" t="n">
+        <v>0.1052</v>
       </c>
     </row>
     <row r="355">
@@ -2837,7 +5333,13 @@
         <v>40</v>
       </c>
       <c r="B355" t="n">
-        <v>0.0977</v>
+        <v>0.1035</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0.1123</v>
       </c>
     </row>
     <row r="356">
@@ -2845,7 +5347,13 @@
         <v>41</v>
       </c>
       <c r="B356" t="n">
-        <v>0.098</v>
+        <v>0.1019</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="E356" t="n">
+        <v>0.1185</v>
       </c>
     </row>
     <row r="357">
@@ -2853,7 +5361,13 @@
         <v>42</v>
       </c>
       <c r="B357" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1007</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="E357" t="n">
+        <v>0.1064</v>
       </c>
     </row>
     <row r="358">
@@ -2861,7 +5375,13 @@
         <v>43</v>
       </c>
       <c r="B358" t="n">
-        <v>0.0983</v>
+        <v>0.1017</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="E358" t="n">
+        <v>0.1019</v>
       </c>
     </row>
     <row r="359">
@@ -2869,7 +5389,13 @@
         <v>44</v>
       </c>
       <c r="B359" t="n">
-        <v>0.099</v>
+        <v>0.1001</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0.0893</v>
+      </c>
+      <c r="E359" t="n">
+        <v>0.0936</v>
       </c>
     </row>
     <row r="360">
@@ -2877,7 +5403,13 @@
         <v>45</v>
       </c>
       <c r="B360" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1012</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="E360" t="n">
+        <v>0.1005</v>
       </c>
     </row>
     <row r="361">
@@ -2885,7 +5417,13 @@
         <v>46</v>
       </c>
       <c r="B361" t="n">
-        <v>0.0998</v>
+        <v>0.1061</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0.1101</v>
+      </c>
+      <c r="E361" t="n">
+        <v>0.1096</v>
       </c>
     </row>
     <row r="362">
@@ -2893,7 +5431,13 @@
         <v>47</v>
       </c>
       <c r="B362" t="n">
-        <v>0.0988</v>
+        <v>0.1046</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0.1093</v>
       </c>
     </row>
     <row r="363">
@@ -2901,7 +5445,13 @@
         <v>48</v>
       </c>
       <c r="B363" t="n">
-        <v>0.0988</v>
+        <v>0.1021</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="E363" t="n">
+        <v>0.1122</v>
       </c>
     </row>
     <row r="364">
@@ -2909,262 +5459,727 @@
         <v>49</v>
       </c>
       <c r="B364" t="n">
-        <v>0.0988</v>
+        <v>0.1062</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="E364" t="n">
+        <v>0.111</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="B365" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="E365" t="n">
+        <v>0.109</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="B366" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0.0801</v>
+      </c>
+      <c r="E366" t="n">
+        <v>0.1148</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
         <v>52</v>
       </c>
+      <c r="B367" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="E367" t="n">
+        <v>0.09859999999999999</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
         <v>53</v>
       </c>
+      <c r="B368" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="E368" t="n">
+        <v>0.1026</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
         <v>54</v>
       </c>
+      <c r="B369" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="E369" t="n">
+        <v>0.0997</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="B370" t="n">
+        <v>0.1065</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="E370" t="n">
+        <v>0.0994</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
         <v>56</v>
       </c>
+      <c r="B371" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="E371" t="n">
+        <v>0.0959</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
         <v>57</v>
       </c>
+      <c r="B372" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="E372" t="n">
+        <v>0.1014</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
         <v>58</v>
       </c>
+      <c r="B373" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="E373" t="n">
+        <v>0.1063</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
         <v>59</v>
       </c>
+      <c r="B374" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E374" t="n">
+        <v>0.1075</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="B375" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="E375" t="n">
+        <v>0.1019</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>61</v>
       </c>
+      <c r="B376" t="n">
+        <v>0.1141</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0.09229999999999999</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0.1026</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
         <v>62</v>
       </c>
+      <c r="B377" t="n">
+        <v>0.1189</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="E377" t="n">
+        <v>0.1031</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
         <v>63</v>
       </c>
+      <c r="B378" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="E378" t="n">
+        <v>0.1023</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="B379" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="E379" t="n">
+        <v>0.1018</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="B380" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="E380" t="n">
+        <v>0.1065</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="B381" t="n">
+        <v>0.1174</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="E381" t="n">
+        <v>0.1096</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="B382" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E382" t="n">
+        <v>0.108</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
         <v>68</v>
       </c>
+      <c r="B383" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="C383" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="E383" t="n">
+        <v>0.1035</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
         <v>69</v>
       </c>
+      <c r="B384" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="C384" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="E384" t="n">
+        <v>0.0958</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="B385" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="E385" t="n">
+        <v>0.0989</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
         <v>71</v>
       </c>
+      <c r="B386" t="n">
+        <v>0.1238</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="E386" t="n">
+        <v>0.1073</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="B387" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="E387" t="n">
+        <v>0.1004</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
         <v>73</v>
       </c>
+      <c r="B388" t="n">
+        <v>0.1211</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="E388" t="n">
+        <v>0.1029</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
         <v>74</v>
       </c>
+      <c r="B389" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="C389" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="E389" t="n">
+        <v>0.1007</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
         <v>75</v>
       </c>
+      <c r="B390" t="n">
+        <v>0.1193</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="E390" t="n">
+        <v>0.1132</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
         <v>76</v>
       </c>
+      <c r="B391" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="C391" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E391" t="n">
+        <v>0.1057</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="B392" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="E392" t="n">
+        <v>0.1042</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
         <v>78</v>
       </c>
+      <c r="B393" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="C393" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="E393" t="n">
+        <v>0.1065</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
         <v>79</v>
       </c>
+      <c r="B394" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="C394" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="E394" t="n">
+        <v>0.1037</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
         <v>80</v>
       </c>
+      <c r="B395" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="E395" t="n">
+        <v>0.1036</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
         <v>81</v>
       </c>
+      <c r="B396" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="C396" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="E396" t="n">
+        <v>0.1061</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
         <v>82</v>
       </c>
+      <c r="B397" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0.1054</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
         <v>83</v>
       </c>
+      <c r="B398" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="C398" t="n">
+        <v>0.0919</v>
+      </c>
+      <c r="E398" t="n">
+        <v>0.1045</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
         <v>84</v>
       </c>
+      <c r="B399" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="C399" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="E399" t="n">
+        <v>0.1018</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
         <v>85</v>
       </c>
+      <c r="B400" t="n">
+        <v>0.2057</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="E400" t="n">
+        <v>0.09669999999999999</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
         <v>86</v>
       </c>
+      <c r="B401" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="E401" t="n">
+        <v>0.1057</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
         <v>87</v>
       </c>
+      <c r="B402" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="C402" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="E402" t="n">
+        <v>0.1004</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
         <v>88</v>
       </c>
+      <c r="B403" t="n">
+        <v>0.1963</v>
+      </c>
+      <c r="C403" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="E403" t="n">
+        <v>0.1053</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
         <v>89</v>
       </c>
+      <c r="B404" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="C404" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="E404" t="n">
+        <v>0.1045</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="B405" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="C405" t="n">
+        <v>0.0801</v>
+      </c>
+      <c r="E405" t="n">
+        <v>0.1094</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
         <v>91</v>
       </c>
+      <c r="B406" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="C406" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="E406" t="n">
+        <v>0.1035</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
         <v>92</v>
       </c>
+      <c r="B407" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="E407" t="n">
+        <v>0.0969</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="B408" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="C408" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E408" t="n">
+        <v>0.1065</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
         <v>94</v>
       </c>
+      <c r="B409" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="C409" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="E409" t="n">
+        <v>0.1041</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="B410" t="n">
+        <v>0.2483</v>
+      </c>
+      <c r="C410" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="E410" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
         <v>96</v>
       </c>
+      <c r="B411" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="C411" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="E411" t="n">
+        <v>0.1056</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
         <v>97</v>
       </c>
+      <c r="B412" t="n">
+        <v>0.2145</v>
+      </c>
+      <c r="C412" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="E412" t="n">
+        <v>0.1022</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
         <v>98</v>
       </c>
+      <c r="B413" t="n">
+        <v>0.2079</v>
+      </c>
+      <c r="C413" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="E413" t="n">
+        <v>0.0955</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
         <v>99</v>
       </c>
+      <c r="B414" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="C414" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="E414" t="n">
+        <v>0.1072</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="B415" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="C415" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="E415" t="n">
+        <v>0.102</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -553,6 +553,9 @@
       <c r="E5" t="n">
         <v>0.1266666666666666</v>
       </c>
+      <c r="F5" t="n">
+        <v>0.3418142857142857</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -567,6 +570,9 @@
       <c r="E6" t="n">
         <v>0.2125</v>
       </c>
+      <c r="F6" t="n">
+        <v>0.235752</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -581,6 +587,9 @@
       <c r="E7" t="n">
         <v>0.3266666666666667</v>
       </c>
+      <c r="F7" t="n">
+        <v>0.2077</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -595,6 +604,9 @@
       <c r="E8" t="n">
         <v>0.3875</v>
       </c>
+      <c r="F8" t="n">
+        <v>0.38389</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -609,6 +621,9 @@
       <c r="E9" t="n">
         <v>0.4450000000000001</v>
       </c>
+      <c r="F9" t="n">
+        <v>0.4694645833333333</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -623,6 +638,9 @@
       <c r="E10" t="n">
         <v>0.4800000000000001</v>
       </c>
+      <c r="F10" t="n">
+        <v>0.5047102564102564</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -637,6 +655,9 @@
       <c r="E11" t="n">
         <v>0.49</v>
       </c>
+      <c r="F11" t="n">
+        <v>0.6691864864864865</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -651,6 +672,9 @@
       <c r="E12" t="n">
         <v>0.4977777777777778</v>
       </c>
+      <c r="F12" t="n">
+        <v>0.6767138888888888</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -665,6 +689,9 @@
       <c r="E13" t="n">
         <v>0.5036363636363637</v>
       </c>
+      <c r="F13" t="n">
+        <v>0.7465107142857145</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -679,6 +706,9 @@
       <c r="E14" t="n">
         <v>0.5142857142857143</v>
       </c>
+      <c r="F14" t="n">
+        <v>0.7914458333333334</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -693,6 +723,9 @@
       <c r="E15" t="n">
         <v>0.5442857142857143</v>
       </c>
+      <c r="F15" t="n">
+        <v>0.8049900000000001</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -707,6 +740,9 @@
       <c r="E16" t="n">
         <v>0.53</v>
       </c>
+      <c r="F16" t="n">
+        <v>0.6947354838709677</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -721,6 +757,9 @@
       <c r="E17" t="n">
         <v>0.5700000000000001</v>
       </c>
+      <c r="F17" t="n">
+        <v>0.7497333333333335</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -735,6 +774,9 @@
       <c r="E18" t="n">
         <v>0.5636363636363636</v>
       </c>
+      <c r="F18" t="n">
+        <v>0.8129351351351352</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -749,6 +791,9 @@
       <c r="E19" t="n">
         <v>0.5525</v>
       </c>
+      <c r="F19" t="n">
+        <v>0.8194866666666666</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -763,6 +808,9 @@
       <c r="E20" t="n">
         <v>0.5811111111111111</v>
       </c>
+      <c r="F20" t="n">
+        <v>0.8191054054054056</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -777,6 +825,9 @@
       <c r="E21" t="n">
         <v>0.5844444444444445</v>
       </c>
+      <c r="F21" t="n">
+        <v>0.7800285714285715</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -791,6 +842,9 @@
       <c r="E22" t="n">
         <v>0.6044444444444443</v>
       </c>
+      <c r="F22" t="n">
+        <v>0.8187216216216218</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -805,6 +859,9 @@
       <c r="E23" t="n">
         <v>0.597</v>
       </c>
+      <c r="F23" t="n">
+        <v>0.7837027027027027</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -819,6 +876,9 @@
       <c r="E24" t="n">
         <v>0.5700000000000001</v>
       </c>
+      <c r="F24" t="n">
+        <v>0.8625966666666667</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -833,6 +893,9 @@
       <c r="E25" t="n">
         <v>0.5999999999999999</v>
       </c>
+      <c r="F25" t="n">
+        <v>0.7646535714285714</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -847,6 +910,9 @@
       <c r="E26" t="n">
         <v>0.6125</v>
       </c>
+      <c r="F26" t="n">
+        <v>0.8405956521739131</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -861,6 +927,9 @@
       <c r="E27" t="n">
         <v>0.5822222222222222</v>
       </c>
+      <c r="F27" t="n">
+        <v>0.8331363636363636</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -875,6 +944,9 @@
       <c r="E28" t="n">
         <v>0.5890909090909091</v>
       </c>
+      <c r="F28" t="n">
+        <v>0.8638500000000001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -889,6 +961,9 @@
       <c r="E29" t="n">
         <v>0.6055555555555556</v>
       </c>
+      <c r="F29" t="n">
+        <v>0.882014705882353</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -903,6 +978,9 @@
       <c r="E30" t="n">
         <v>0.59375</v>
       </c>
+      <c r="F30" t="n">
+        <v>0.8676586206896553</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -917,6 +995,9 @@
       <c r="E31" t="n">
         <v>0.6163636363636364</v>
       </c>
+      <c r="F31" t="n">
+        <v>0.8223791666666666</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -931,6 +1012,9 @@
       <c r="E32" t="n">
         <v>0.6249999999999999</v>
       </c>
+      <c r="F32" t="n">
+        <v>0.8733448275862068</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -945,6 +1029,9 @@
       <c r="E33" t="n">
         <v>0.604</v>
       </c>
+      <c r="F33" t="n">
+        <v>0.8673037037037036</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -959,6 +1046,9 @@
       <c r="E34" t="n">
         <v>0.638</v>
       </c>
+      <c r="F34" t="n">
+        <v>0.812031818181818</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -973,6 +1063,9 @@
       <c r="E35" t="n">
         <v>0.6285714285714286</v>
       </c>
+      <c r="F35" t="n">
+        <v>0.9114866666666667</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -987,6 +1080,9 @@
       <c r="E36" t="n">
         <v>0.612</v>
       </c>
+      <c r="F36" t="n">
+        <v>0.7856696969696969</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1001,6 +1097,9 @@
       <c r="E37" t="n">
         <v>0.63625</v>
       </c>
+      <c r="F37" t="n">
+        <v>0.90499</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1015,6 +1114,9 @@
       <c r="E38" t="n">
         <v>0.615</v>
       </c>
+      <c r="F38" t="n">
+        <v>0.8504357142857143</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1029,6 +1131,9 @@
       <c r="E39" t="n">
         <v>0.6054545454545454</v>
       </c>
+      <c r="F39" t="n">
+        <v>0.8648653846153846</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1043,6 +1148,9 @@
       <c r="E40" t="n">
         <v>0.603</v>
       </c>
+      <c r="F40" t="n">
+        <v>0.8815763157894738</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1057,6 +1165,9 @@
       <c r="E41" t="n">
         <v>0.603</v>
       </c>
+      <c r="F41" t="n">
+        <v>0.8993925925925926</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1071,6 +1182,9 @@
       <c r="E42" t="n">
         <v>0.6416666666666667</v>
       </c>
+      <c r="F42" t="n">
+        <v>0.8211357142857142</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1085,6 +1199,9 @@
       <c r="E43" t="n">
         <v>0.6218181818181818</v>
       </c>
+      <c r="F43" t="n">
+        <v>0.8808049999999998</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1099,6 +1216,9 @@
       <c r="E44" t="n">
         <v>0.629</v>
       </c>
+      <c r="F44" t="n">
+        <v>0.8756241379310343</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1113,6 +1233,9 @@
       <c r="E45" t="n">
         <v>0.6244444444444444</v>
       </c>
+      <c r="F45" t="n">
+        <v>0.9163051282051282</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1127,6 +1250,9 @@
       <c r="E46" t="n">
         <v>0.6125</v>
       </c>
+      <c r="F46" t="n">
+        <v>0.8803719999999999</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1141,6 +1267,9 @@
       <c r="E47" t="n">
         <v>0.6258333333333332</v>
       </c>
+      <c r="F47" t="n">
+        <v>0.8571673076923076</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1155,6 +1284,9 @@
       <c r="E48" t="n">
         <v>0.5957142857142858</v>
       </c>
+      <c r="F48" t="n">
+        <v>0.904270588235294</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -1169,6 +1301,9 @@
       <c r="E49" t="n">
         <v>0.6125</v>
       </c>
+      <c r="F49" t="n">
+        <v>0.8393065217391303</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1183,6 +1318,9 @@
       <c r="E50" t="n">
         <v>0.61875</v>
       </c>
+      <c r="F50" t="n">
+        <v>0.9170555555555556</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -1197,6 +1335,9 @@
       <c r="E51" t="n">
         <v>0.62625</v>
       </c>
+      <c r="F51" t="n">
+        <v>0.8938351351351351</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1211,6 +1352,9 @@
       <c r="E52" t="n">
         <v>0.6333333333333333</v>
       </c>
+      <c r="F52" t="n">
+        <v>0.8468594594594595</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1225,6 +1369,9 @@
       <c r="E53" t="n">
         <v>0.6230769230769231</v>
       </c>
+      <c r="F53" t="n">
+        <v>0.8281232558139534</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -1239,6 +1386,9 @@
       <c r="E54" t="n">
         <v>0.6163636363636363</v>
       </c>
+      <c r="F54" t="n">
+        <v>0.8645057142857142</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -1253,6 +1403,9 @@
       <c r="E55" t="n">
         <v>0.6350000000000001</v>
       </c>
+      <c r="F55" t="n">
+        <v>0.8539222222222222</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -1267,6 +1420,9 @@
       <c r="E56" t="n">
         <v>0.6599999999999998</v>
       </c>
+      <c r="F56" t="n">
+        <v>0.8740264705882352</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -1281,6 +1437,9 @@
       <c r="E57" t="n">
         <v>0.6525</v>
       </c>
+      <c r="F57" t="n">
+        <v>0.8819529411764705</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -1295,6 +1454,9 @@
       <c r="E58" t="n">
         <v>0.6236363636363635</v>
       </c>
+      <c r="F58" t="n">
+        <v>0.8562448275862069</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -1309,6 +1471,9 @@
       <c r="E59" t="n">
         <v>0.61625</v>
       </c>
+      <c r="F59" t="n">
+        <v>0.847936</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -1323,6 +1488,9 @@
       <c r="E60" t="n">
         <v>0.6444444444444445</v>
       </c>
+      <c r="F60" t="n">
+        <v>0.9019029411764706</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -1337,6 +1505,9 @@
       <c r="E61" t="n">
         <v>0.6054545454545454</v>
       </c>
+      <c r="F61" t="n">
+        <v>0.8902481481481481</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -1351,6 +1522,9 @@
       <c r="E62" t="n">
         <v>0.6518181818181819</v>
       </c>
+      <c r="F62" t="n">
+        <v>0.8931657142857142</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -1365,6 +1539,9 @@
       <c r="E63" t="n">
         <v>0.6255555555555556</v>
       </c>
+      <c r="F63" t="n">
+        <v>0.91276</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -1379,6 +1556,9 @@
       <c r="E64" t="n">
         <v>0.6288888888888888</v>
       </c>
+      <c r="F64" t="n">
+        <v>0.7533304347826086</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -1393,6 +1573,9 @@
       <c r="E65" t="n">
         <v>0.6285714285714286</v>
       </c>
+      <c r="F65" t="n">
+        <v>0.9080310344827587</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -1407,6 +1590,9 @@
       <c r="E66" t="n">
         <v>0.6560000000000001</v>
       </c>
+      <c r="F66" t="n">
+        <v>0.8927138888888888</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -1421,6 +1607,9 @@
       <c r="E67" t="n">
         <v>0.6315384615384616</v>
       </c>
+      <c r="F67" t="n">
+        <v>0.7663733333333335</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -1435,6 +1624,9 @@
       <c r="E68" t="n">
         <v>0.639090909090909</v>
       </c>
+      <c r="F68" t="n">
+        <v>0.8221499999999999</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -1449,6 +1641,9 @@
       <c r="E69" t="n">
         <v>0.61875</v>
       </c>
+      <c r="F69" t="n">
+        <v>0.8919038461538461</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -1463,6 +1658,9 @@
       <c r="E70" t="n">
         <v>0.6409090909090909</v>
       </c>
+      <c r="F70" t="n">
+        <v>0.7159842105263158</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -1477,6 +1675,9 @@
       <c r="E71" t="n">
         <v>0.636</v>
       </c>
+      <c r="F71" t="n">
+        <v>0.7999799999999999</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -1491,6 +1692,9 @@
       <c r="E72" t="n">
         <v>0.6316666666666666</v>
       </c>
+      <c r="F72" t="n">
+        <v>0.9072555555555556</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -1505,6 +1709,9 @@
       <c r="E73" t="n">
         <v>0.645</v>
       </c>
+      <c r="F73" t="n">
+        <v>0.85636</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -1519,6 +1726,9 @@
       <c r="E74" t="n">
         <v>0.6375</v>
       </c>
+      <c r="F74" t="n">
+        <v>0.8374382978723405</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -1533,6 +1743,9 @@
       <c r="E75" t="n">
         <v>0.63</v>
       </c>
+      <c r="F75" t="n">
+        <v>0.838796875</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -1547,6 +1760,9 @@
       <c r="E76" t="n">
         <v>0.6171428571428572</v>
       </c>
+      <c r="F76" t="n">
+        <v>0.8860222222222222</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -1561,6 +1777,9 @@
       <c r="E77" t="n">
         <v>0.6262500000000001</v>
       </c>
+      <c r="F77" t="n">
+        <v>0.8845644444444444</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -1575,6 +1794,9 @@
       <c r="E78" t="n">
         <v>0.6211111111111111</v>
       </c>
+      <c r="F78" t="n">
+        <v>0.9372291666666666</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -1589,6 +1811,9 @@
       <c r="E79" t="n">
         <v>0.60875</v>
       </c>
+      <c r="F79" t="n">
+        <v>0.9174399999999999</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -1603,6 +1828,9 @@
       <c r="E80" t="n">
         <v>0.6277777777777777</v>
       </c>
+      <c r="F80" t="n">
+        <v>0.8157241379310346</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -1617,6 +1845,9 @@
       <c r="E81" t="n">
         <v>0.6230000000000001</v>
       </c>
+      <c r="F81" t="n">
+        <v>0.8742297297297295</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -1631,6 +1862,9 @@
       <c r="E82" t="n">
         <v>0.64375</v>
       </c>
+      <c r="F82" t="n">
+        <v>0.8379069767441859</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -1645,6 +1879,9 @@
       <c r="E83" t="n">
         <v>0.63</v>
       </c>
+      <c r="F83" t="n">
+        <v>0.8912636363636364</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -1659,6 +1896,9 @@
       <c r="E84" t="n">
         <v>0.6455555555555555</v>
       </c>
+      <c r="F84" t="n">
+        <v>0.8858806451612903</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -1673,6 +1913,9 @@
       <c r="E85" t="n">
         <v>0.6277777777777778</v>
       </c>
+      <c r="F85" t="n">
+        <v>0.8768636363636363</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -1687,6 +1930,9 @@
       <c r="E86" t="n">
         <v>0.6144444444444445</v>
       </c>
+      <c r="F86" t="n">
+        <v>0.8638142857142856</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -1701,6 +1947,9 @@
       <c r="E87" t="n">
         <v>0.6183333333333334</v>
       </c>
+      <c r="F87" t="n">
+        <v>0.8505481481481481</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -1715,6 +1964,9 @@
       <c r="E88" t="n">
         <v>0.6274999999999999</v>
       </c>
+      <c r="F88" t="n">
+        <v>0.848174074074074</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -1729,6 +1981,9 @@
       <c r="E89" t="n">
         <v>0.6133333333333334</v>
       </c>
+      <c r="F89" t="n">
+        <v>0.9192357142857143</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -1743,6 +1998,9 @@
       <c r="E90" t="n">
         <v>0.6259999999999999</v>
       </c>
+      <c r="F90" t="n">
+        <v>0.8750633333333332</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -1757,6 +2015,9 @@
       <c r="E91" t="n">
         <v>0.6683333333333334</v>
       </c>
+      <c r="F91" t="n">
+        <v>0.8891636363636363</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -1771,6 +2032,9 @@
       <c r="E92" t="n">
         <v>0.6430000000000001</v>
       </c>
+      <c r="F92" t="n">
+        <v>0.9124399999999999</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -1785,6 +2049,9 @@
       <c r="E93" t="n">
         <v>0.6399999999999999</v>
       </c>
+      <c r="F93" t="n">
+        <v>0.7613214285714286</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -1799,6 +2066,9 @@
       <c r="E94" t="n">
         <v>0.6327272727272727</v>
       </c>
+      <c r="F94" t="n">
+        <v>0.8559541666666667</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -1813,6 +2083,9 @@
       <c r="E95" t="n">
         <v>0.6757142857142858</v>
       </c>
+      <c r="F95" t="n">
+        <v>0.7982575757575756</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -1827,6 +2100,9 @@
       <c r="E96" t="n">
         <v>0.6366666666666666</v>
       </c>
+      <c r="F96" t="n">
+        <v>0.7648874999999999</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -1841,6 +2117,9 @@
       <c r="E97" t="n">
         <v>0.64</v>
       </c>
+      <c r="F97" t="n">
+        <v>0.8764421052631579</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -1855,6 +2134,9 @@
       <c r="E98" t="n">
         <v>0.6400000000000001</v>
       </c>
+      <c r="F98" t="n">
+        <v>0.8944347826086958</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -1869,6 +2151,9 @@
       <c r="E99" t="n">
         <v>0.6283333333333334</v>
       </c>
+      <c r="F99" t="n">
+        <v>0.8851374999999999</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -1883,6 +2168,9 @@
       <c r="E100" t="n">
         <v>0.6533333333333332</v>
       </c>
+      <c r="F100" t="n">
+        <v>0.83385</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -1897,6 +2185,9 @@
       <c r="E101" t="n">
         <v>0.6449999999999999</v>
       </c>
+      <c r="F101" t="n">
+        <v>0.830009375</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -1911,6 +2202,9 @@
       <c r="E102" t="n">
         <v>0.6387499999999999</v>
       </c>
+      <c r="F102" t="n">
+        <v>0.8951272727272727</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -1925,6 +2219,9 @@
       <c r="E103" t="n">
         <v>0.628</v>
       </c>
+      <c r="F103" t="n">
+        <v>0.88224375</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -1938,6 +2235,9 @@
       </c>
       <c r="E104" t="n">
         <v>0.6683333333333333</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.8899888888888889</v>
       </c>
     </row>
     <row r="106">
@@ -1967,6 +2267,9 @@
       <c r="E108" t="n">
         <v>1</v>
       </c>
+      <c r="F108" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -1981,6 +2284,9 @@
       <c r="E109" t="n">
         <v>1</v>
       </c>
+      <c r="F109" t="n">
+        <v>0.8571428571428571</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -1995,6 +2301,9 @@
       <c r="E110" t="n">
         <v>1</v>
       </c>
+      <c r="F110" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -2009,6 +2318,9 @@
       <c r="E111" t="n">
         <v>1</v>
       </c>
+      <c r="F111" t="n">
+        <v>0.9230769230769231</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -2023,6 +2335,9 @@
       <c r="E112" t="n">
         <v>1</v>
       </c>
+      <c r="F112" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -2037,6 +2352,9 @@
       <c r="E113" t="n">
         <v>1</v>
       </c>
+      <c r="F113" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -2051,6 +2369,9 @@
       <c r="E114" t="n">
         <v>1</v>
       </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -2065,6 +2386,9 @@
       <c r="E115" t="n">
         <v>1</v>
       </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -2079,6 +2403,9 @@
       <c r="E116" t="n">
         <v>1</v>
       </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -2093,6 +2420,9 @@
       <c r="E117" t="n">
         <v>1</v>
       </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -2107,6 +2437,9 @@
       <c r="E118" t="n">
         <v>1</v>
       </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -2121,6 +2454,9 @@
       <c r="E119" t="n">
         <v>1</v>
       </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -2135,6 +2471,9 @@
       <c r="E120" t="n">
         <v>1</v>
       </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -2149,6 +2488,9 @@
       <c r="E121" t="n">
         <v>1</v>
       </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -2163,6 +2505,9 @@
       <c r="E122" t="n">
         <v>1</v>
       </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -2177,6 +2522,9 @@
       <c r="E123" t="n">
         <v>1</v>
       </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -2191,6 +2539,9 @@
       <c r="E124" t="n">
         <v>1</v>
       </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -2205,6 +2556,9 @@
       <c r="E125" t="n">
         <v>1</v>
       </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -2219,6 +2573,9 @@
       <c r="E126" t="n">
         <v>1</v>
       </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -2233,6 +2590,9 @@
       <c r="E127" t="n">
         <v>1</v>
       </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -2247,6 +2607,9 @@
       <c r="E128" t="n">
         <v>1</v>
       </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -2261,6 +2624,9 @@
       <c r="E129" t="n">
         <v>1</v>
       </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -2275,6 +2641,9 @@
       <c r="E130" t="n">
         <v>1</v>
       </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -2289,6 +2658,9 @@
       <c r="E131" t="n">
         <v>1</v>
       </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -2303,6 +2675,9 @@
       <c r="E132" t="n">
         <v>1</v>
       </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -2317,6 +2692,9 @@
       <c r="E133" t="n">
         <v>1</v>
       </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -2331,6 +2709,9 @@
       <c r="E134" t="n">
         <v>1</v>
       </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -2345,6 +2726,9 @@
       <c r="E135" t="n">
         <v>1</v>
       </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -2359,6 +2743,9 @@
       <c r="E136" t="n">
         <v>1</v>
       </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -2373,6 +2760,9 @@
       <c r="E137" t="n">
         <v>1</v>
       </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -2387,6 +2777,9 @@
       <c r="E138" t="n">
         <v>1</v>
       </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -2401,6 +2794,9 @@
       <c r="E139" t="n">
         <v>1</v>
       </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -2415,6 +2811,9 @@
       <c r="E140" t="n">
         <v>1</v>
       </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -2429,6 +2828,9 @@
       <c r="E141" t="n">
         <v>1</v>
       </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -2443,6 +2845,9 @@
       <c r="E142" t="n">
         <v>1</v>
       </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -2457,6 +2862,9 @@
       <c r="E143" t="n">
         <v>1</v>
       </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -2471,6 +2879,9 @@
       <c r="E144" t="n">
         <v>1</v>
       </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -2485,6 +2896,9 @@
       <c r="E145" t="n">
         <v>1</v>
       </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -2499,6 +2913,9 @@
       <c r="E146" t="n">
         <v>1</v>
       </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -2513,6 +2930,9 @@
       <c r="E147" t="n">
         <v>1</v>
       </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -2527,6 +2947,9 @@
       <c r="E148" t="n">
         <v>1</v>
       </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -2541,6 +2964,9 @@
       <c r="E149" t="n">
         <v>1</v>
       </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -2555,6 +2981,9 @@
       <c r="E150" t="n">
         <v>1</v>
       </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -2569,6 +2998,9 @@
       <c r="E151" t="n">
         <v>1</v>
       </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -2583,6 +3015,9 @@
       <c r="E152" t="n">
         <v>1</v>
       </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -2597,6 +3032,9 @@
       <c r="E153" t="n">
         <v>1</v>
       </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -2611,6 +3049,9 @@
       <c r="E154" t="n">
         <v>1</v>
       </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -2625,6 +3066,9 @@
       <c r="E155" t="n">
         <v>1</v>
       </c>
+      <c r="F155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -2639,6 +3083,9 @@
       <c r="E156" t="n">
         <v>1</v>
       </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -2653,6 +3100,9 @@
       <c r="E157" t="n">
         <v>1</v>
       </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -2667,6 +3117,9 @@
       <c r="E158" t="n">
         <v>1</v>
       </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -2681,6 +3134,9 @@
       <c r="E159" t="n">
         <v>1</v>
       </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -2695,6 +3151,9 @@
       <c r="E160" t="n">
         <v>1</v>
       </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -2709,6 +3168,9 @@
       <c r="E161" t="n">
         <v>1</v>
       </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -2723,6 +3185,9 @@
       <c r="E162" t="n">
         <v>1</v>
       </c>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -2737,6 +3202,9 @@
       <c r="E163" t="n">
         <v>1</v>
       </c>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -2751,6 +3219,9 @@
       <c r="E164" t="n">
         <v>1</v>
       </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -2765,6 +3236,9 @@
       <c r="E165" t="n">
         <v>1</v>
       </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -2779,6 +3253,9 @@
       <c r="E166" t="n">
         <v>1</v>
       </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -2793,6 +3270,9 @@
       <c r="E167" t="n">
         <v>1</v>
       </c>
+      <c r="F167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -2807,6 +3287,9 @@
       <c r="E168" t="n">
         <v>1</v>
       </c>
+      <c r="F168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -2821,6 +3304,9 @@
       <c r="E169" t="n">
         <v>1</v>
       </c>
+      <c r="F169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -2835,6 +3321,9 @@
       <c r="E170" t="n">
         <v>1</v>
       </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -2849,6 +3338,9 @@
       <c r="E171" t="n">
         <v>1</v>
       </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -2863,6 +3355,9 @@
       <c r="E172" t="n">
         <v>1</v>
       </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -2877,6 +3372,9 @@
       <c r="E173" t="n">
         <v>1</v>
       </c>
+      <c r="F173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -2891,6 +3389,9 @@
       <c r="E174" t="n">
         <v>1</v>
       </c>
+      <c r="F174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -2905,6 +3406,9 @@
       <c r="E175" t="n">
         <v>1</v>
       </c>
+      <c r="F175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -2919,6 +3423,9 @@
       <c r="E176" t="n">
         <v>1</v>
       </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -2933,6 +3440,9 @@
       <c r="E177" t="n">
         <v>1</v>
       </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -2947,6 +3457,9 @@
       <c r="E178" t="n">
         <v>1</v>
       </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -2961,6 +3474,9 @@
       <c r="E179" t="n">
         <v>1</v>
       </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -2975,6 +3491,9 @@
       <c r="E180" t="n">
         <v>1</v>
       </c>
+      <c r="F180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -2989,6 +3508,9 @@
       <c r="E181" t="n">
         <v>1</v>
       </c>
+      <c r="F181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -3003,6 +3525,9 @@
       <c r="E182" t="n">
         <v>1</v>
       </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -3017,6 +3542,9 @@
       <c r="E183" t="n">
         <v>1</v>
       </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -3031,6 +3559,9 @@
       <c r="E184" t="n">
         <v>1</v>
       </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -3045,6 +3576,9 @@
       <c r="E185" t="n">
         <v>1</v>
       </c>
+      <c r="F185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -3059,6 +3593,9 @@
       <c r="E186" t="n">
         <v>1</v>
       </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -3073,6 +3610,9 @@
       <c r="E187" t="n">
         <v>1</v>
       </c>
+      <c r="F187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -3087,6 +3627,9 @@
       <c r="E188" t="n">
         <v>1</v>
       </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -3101,6 +3644,9 @@
       <c r="E189" t="n">
         <v>1</v>
       </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -3115,6 +3661,9 @@
       <c r="E190" t="n">
         <v>1</v>
       </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -3129,6 +3678,9 @@
       <c r="E191" t="n">
         <v>1</v>
       </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -3143,6 +3695,9 @@
       <c r="E192" t="n">
         <v>1</v>
       </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -3157,6 +3712,9 @@
       <c r="E193" t="n">
         <v>1</v>
       </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -3171,6 +3729,9 @@
       <c r="E194" t="n">
         <v>1</v>
       </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -3185,6 +3746,9 @@
       <c r="E195" t="n">
         <v>1</v>
       </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -3199,6 +3763,9 @@
       <c r="E196" t="n">
         <v>1</v>
       </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -3213,6 +3780,9 @@
       <c r="E197" t="n">
         <v>1</v>
       </c>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -3227,6 +3797,9 @@
       <c r="E198" t="n">
         <v>1</v>
       </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -3241,6 +3814,9 @@
       <c r="E199" t="n">
         <v>1</v>
       </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -3255,6 +3831,9 @@
       <c r="E200" t="n">
         <v>1</v>
       </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -3269,6 +3848,9 @@
       <c r="E201" t="n">
         <v>1</v>
       </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -3283,6 +3865,9 @@
       <c r="E202" t="n">
         <v>1</v>
       </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -3297,6 +3882,9 @@
       <c r="E203" t="n">
         <v>1</v>
       </c>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -3311,6 +3899,9 @@
       <c r="E204" t="n">
         <v>1</v>
       </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -3325,6 +3916,9 @@
       <c r="E205" t="n">
         <v>1</v>
       </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -3339,6 +3933,9 @@
       <c r="E206" t="n">
         <v>1</v>
       </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -3351,6 +3948,9 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3381,6 +3981,9 @@
       <c r="E212" t="n">
         <v>0.9772000000000001</v>
       </c>
+      <c r="F212" t="n">
+        <v>0.02106666666666667</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -3395,6 +3998,9 @@
       <c r="E213" t="n">
         <v>0.9673857142857142</v>
       </c>
+      <c r="F213" t="n">
+        <v>0.002733333333333333</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -3409,6 +4015,9 @@
       <c r="E214" t="n">
         <v>0.9743600000000001</v>
       </c>
+      <c r="F214" t="n">
+        <v>0.04305555555555556</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -3423,6 +4032,9 @@
       <c r="E215" t="n">
         <v>0.9819</v>
       </c>
+      <c r="F215" t="n">
+        <v>0.0163</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -3437,6 +4049,9 @@
       <c r="E216" t="n">
         <v>0.9669666666666666</v>
       </c>
+      <c r="F216" t="n">
+        <v>0.037</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -3451,6 +4066,9 @@
       <c r="E217" t="n">
         <v>0.9683400000000001</v>
       </c>
+      <c r="F217" t="n">
+        <v>0.001985714285714286</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -3465,6 +4083,9 @@
       <c r="E218" t="n">
         <v>0.9669000000000001</v>
       </c>
+      <c r="F218" t="n">
+        <v>0.0314125</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -3479,6 +4100,9 @@
       <c r="E219" t="n">
         <v>0.9687625</v>
       </c>
+      <c r="F219" t="n">
+        <v>0.01878571428571429</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -3493,6 +4117,9 @@
       <c r="E220" t="n">
         <v>0.9676</v>
       </c>
+      <c r="F220" t="n">
+        <v>0.02518</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -3507,6 +4134,9 @@
       <c r="E221" t="n">
         <v>0.9676999999999999</v>
       </c>
+      <c r="F221" t="n">
+        <v>0.04571428571428571</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -3521,6 +4151,9 @@
       <c r="E222" t="n">
         <v>0.9615285714285715</v>
       </c>
+      <c r="F222" t="n">
+        <v>0.02573636363636363</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -3535,6 +4168,9 @@
       <c r="E223" t="n">
         <v>0.9644000000000001</v>
       </c>
+      <c r="F223" t="n">
+        <v>0.05474285714285715</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -3549,6 +4185,9 @@
       <c r="E224" t="n">
         <v>0.9641999999999999</v>
       </c>
+      <c r="F224" t="n">
+        <v>0.02765</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -3563,6 +4202,9 @@
       <c r="E225" t="n">
         <v>0.9649666666666668</v>
       </c>
+      <c r="F225" t="n">
+        <v>0.01644285714285714</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -3577,6 +4219,9 @@
       <c r="E226" t="n">
         <v>0.9652200000000001</v>
       </c>
+      <c r="F226" t="n">
+        <v>0.05056666666666666</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -3591,6 +4236,9 @@
       <c r="E227" t="n">
         <v>0.95095</v>
       </c>
+      <c r="F227" t="n">
+        <v>0.02306</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -3605,6 +4253,9 @@
       <c r="E228" t="n">
         <v>0.9593</v>
       </c>
+      <c r="F228" t="n">
+        <v>0.04318888888888888</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -3619,6 +4270,9 @@
       <c r="E229" t="n">
         <v>0.9638285714285714</v>
       </c>
+      <c r="F229" t="n">
+        <v>0.0427</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -3633,6 +4287,9 @@
       <c r="E230" t="n">
         <v>0.9687625000000001</v>
       </c>
+      <c r="F230" t="n">
+        <v>0.0212875</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -3647,6 +4304,9 @@
       <c r="E231" t="n">
         <v>0.9601166666666666</v>
       </c>
+      <c r="F231" t="n">
+        <v>0.05803333333333333</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -3661,6 +4321,9 @@
       <c r="E232" t="n">
         <v>0.9636222222222222</v>
       </c>
+      <c r="F232" t="n">
+        <v>0.04984285714285714</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -3675,6 +4338,9 @@
       <c r="E233" t="n">
         <v>0.9546999999999999</v>
       </c>
+      <c r="F233" t="n">
+        <v>0.0256</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -3689,6 +4355,9 @@
       <c r="E234" t="n">
         <v>0.96022</v>
       </c>
+      <c r="F234" t="n">
+        <v>0.03195</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -3703,6 +4372,9 @@
       <c r="E235" t="n">
         <v>0.9564333333333331</v>
       </c>
+      <c r="F235" t="n">
+        <v>0.05833333333333334</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -3717,6 +4389,9 @@
       <c r="E236" t="n">
         <v>0.9619</v>
       </c>
+      <c r="F236" t="n">
+        <v>0.048975</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -3731,6 +4406,9 @@
       <c r="E237" t="n">
         <v>0.950325</v>
       </c>
+      <c r="F237" t="n">
+        <v>0.03787692307692308</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -3745,6 +4423,9 @@
       <c r="E238" t="n">
         <v>0.9628</v>
       </c>
+      <c r="F238" t="n">
+        <v>0.02671428571428571</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -3759,6 +4440,9 @@
       <c r="E239" t="n">
         <v>0.95996</v>
       </c>
+      <c r="F239" t="n">
+        <v>0.03134285714285714</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -3773,6 +4457,9 @@
       <c r="E240" t="n">
         <v>0.9742500000000001</v>
       </c>
+      <c r="F240" t="n">
+        <v>0.03561428571428572</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -3787,6 +4474,9 @@
       <c r="E241" t="n">
         <v>0.964375</v>
       </c>
+      <c r="F241" t="n">
+        <v>0.0253</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -3801,6 +4491,9 @@
       <c r="E242" t="n">
         <v>0.965025</v>
       </c>
+      <c r="F242" t="n">
+        <v>0.02495</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -3815,6 +4508,9 @@
       <c r="E243" t="n">
         <v>0.9628666666666668</v>
       </c>
+      <c r="F243" t="n">
+        <v>0.01975</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -3829,6 +4525,9 @@
       <c r="E244" t="n">
         <v>0.9635499999999999</v>
       </c>
+      <c r="F244" t="n">
+        <v>0.043275</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -3843,6 +4542,9 @@
       <c r="E245" t="n">
         <v>0.95785</v>
       </c>
+      <c r="F245" t="n">
+        <v>0.03581428571428571</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -3857,6 +4559,9 @@
       <c r="E246" t="n">
         <v>0.9650444444444444</v>
       </c>
+      <c r="F246" t="n">
+        <v>0.02161666666666667</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -3871,6 +4576,9 @@
       <c r="E247" t="n">
         <v>0.9617</v>
       </c>
+      <c r="F247" t="n">
+        <v>0.02373333333333333</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -3885,6 +4593,9 @@
       <c r="E248" t="n">
         <v>0.9598714285714287</v>
       </c>
+      <c r="F248" t="n">
+        <v>0.05775555555555556</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -3899,6 +4610,9 @@
       <c r="E249" t="n">
         <v>0.96745</v>
       </c>
+      <c r="F249" t="n">
+        <v>0.05026363636363636</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -3913,6 +4627,9 @@
       <c r="E250" t="n">
         <v>0.9658000000000001</v>
       </c>
+      <c r="F250" t="n">
+        <v>0.01205</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -3927,6 +4644,9 @@
       <c r="E251" t="n">
         <v>0.9679333333333333</v>
       </c>
+      <c r="F251" t="n">
+        <v>0.008399999999999999</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -3941,6 +4661,9 @@
       <c r="E252" t="n">
         <v>0.9638285714285715</v>
       </c>
+      <c r="F252" t="n">
+        <v>0.04458181818181817</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -3955,6 +4678,9 @@
       <c r="E253" t="n">
         <v>0.9564333333333334</v>
       </c>
+      <c r="F253" t="n">
+        <v>0.03048</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -3969,6 +4695,9 @@
       <c r="E254" t="n">
         <v>0.9648499999999999</v>
       </c>
+      <c r="F254" t="n">
+        <v>0.05865999999999999</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -3983,6 +4712,9 @@
       <c r="E255" t="n">
         <v>0.9621875</v>
       </c>
+      <c r="F255" t="n">
+        <v>0.0121</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -3997,6 +4729,9 @@
       <c r="E256" t="n">
         <v>0.9553666666666666</v>
       </c>
+      <c r="F256" t="n">
+        <v>0.0292125</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -4011,6 +4746,9 @@
       <c r="E257" t="n">
         <v>0.9653999999999999</v>
       </c>
+      <c r="F257" t="n">
+        <v>0.02890000000000001</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -4025,6 +4763,9 @@
       <c r="E258" t="n">
         <v>0.9633666666666666</v>
       </c>
+      <c r="F258" t="n">
+        <v>0.0393</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -4039,6 +4780,9 @@
       <c r="E259" t="n">
         <v>0.9670666666666666</v>
       </c>
+      <c r="F259" t="n">
+        <v>0.02243333333333333</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -4053,6 +4797,9 @@
       <c r="E260" t="n">
         <v>0.9664</v>
       </c>
+      <c r="F260" t="n">
+        <v>0.03118</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -4067,6 +4814,9 @@
       <c r="E261" t="n">
         <v>0.9633799999999999</v>
       </c>
+      <c r="F261" t="n">
+        <v>0.04964444444444445</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -4081,6 +4831,9 @@
       <c r="E262" t="n">
         <v>0.968325</v>
       </c>
+      <c r="F262" t="n">
+        <v>0.008566666666666667</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -4095,6 +4848,9 @@
       <c r="E263" t="n">
         <v>0.9642375</v>
       </c>
+      <c r="F263" t="n">
+        <v>0.0161875</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -4109,6 +4865,9 @@
       <c r="E264" t="n">
         <v>0.9686999999999999</v>
       </c>
+      <c r="F264" t="n">
+        <v>0.038075</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -4123,6 +4882,9 @@
       <c r="E265" t="n">
         <v>0.9644374999999999</v>
       </c>
+      <c r="F265" t="n">
+        <v>0.0322375</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -4137,6 +4899,9 @@
       <c r="E266" t="n">
         <v>0.968075</v>
       </c>
+      <c r="F266" t="n">
+        <v>0.06200000000000001</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -4151,6 +4916,9 @@
       <c r="E267" t="n">
         <v>0.9668166666666665</v>
       </c>
+      <c r="F267" t="n">
+        <v>0.04434285714285714</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -4165,6 +4933,9 @@
       <c r="E268" t="n">
         <v>0.9664</v>
       </c>
+      <c r="F268" t="n">
+        <v>0.0155</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -4179,6 +4950,9 @@
       <c r="E269" t="n">
         <v>0.96395</v>
       </c>
+      <c r="F269" t="n">
+        <v>0.02214444444444445</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -4193,6 +4967,9 @@
       <c r="E270" t="n">
         <v>0.9705428571428572</v>
       </c>
+      <c r="F270" t="n">
+        <v>0.0153</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -4207,6 +4984,9 @@
       <c r="E271" t="n">
         <v>0.9693666666666667</v>
       </c>
+      <c r="F271" t="n">
+        <v>0.05061111111111112</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -4221,6 +5001,9 @@
       <c r="E272" t="n">
         <v>0.9635166666666666</v>
       </c>
+      <c r="F272" t="n">
+        <v>0.04574285714285715</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -4235,6 +5018,9 @@
       <c r="E273" t="n">
         <v>0.973325</v>
       </c>
+      <c r="F273" t="n">
+        <v>0.0643857142857143</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -4249,6 +5035,9 @@
       <c r="E274" t="n">
         <v>0.9641</v>
       </c>
+      <c r="F274" t="n">
+        <v>0.0247625</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -4263,6 +5052,9 @@
       <c r="E275" t="n">
         <v>0.9616666666666668</v>
       </c>
+      <c r="F275" t="n">
+        <v>0.02635</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -4277,6 +5069,9 @@
       <c r="E276" t="n">
         <v>0.9686666666666667</v>
       </c>
+      <c r="F276" t="n">
+        <v>0.03193</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -4291,6 +5086,9 @@
       <c r="E277" t="n">
         <v>0.9633833333333333</v>
       </c>
+      <c r="F277" t="n">
+        <v>0.01968571428571429</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -4305,6 +5103,9 @@
       <c r="E278" t="n">
         <v>0.9729166666666668</v>
       </c>
+      <c r="F278" t="n">
+        <v>0.01865714285714286</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -4319,6 +5120,9 @@
       <c r="E279" t="n">
         <v>0.9715166666666667</v>
       </c>
+      <c r="F279" t="n">
+        <v>0.0261</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -4333,6 +5137,9 @@
       <c r="E280" t="n">
         <v>0.9588800000000001</v>
       </c>
+      <c r="F280" t="n">
+        <v>0.02078888888888889</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -4347,6 +5154,9 @@
       <c r="E281" t="n">
         <v>0.9632714285714287</v>
       </c>
+      <c r="F281" t="n">
+        <v>0.06896666666666666</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -4361,6 +5171,9 @@
       <c r="E282" t="n">
         <v>0.9753399999999999</v>
       </c>
+      <c r="F282" t="n">
+        <v>0.0392</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -4375,6 +5188,9 @@
       <c r="E283" t="n">
         <v>0.9684250000000001</v>
       </c>
+      <c r="F283" t="n">
+        <v>0.02911111111111112</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -4389,6 +5205,9 @@
       <c r="E284" t="n">
         <v>0.96546</v>
       </c>
+      <c r="F284" t="n">
+        <v>0.0371</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -4403,6 +5222,9 @@
       <c r="E285" t="n">
         <v>0.9726666666666667</v>
       </c>
+      <c r="F285" t="n">
+        <v>0.0251625</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -4417,6 +5239,9 @@
       <c r="E286" t="n">
         <v>0.9741333333333334</v>
       </c>
+      <c r="F286" t="n">
+        <v>0.0394</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -4431,6 +5256,9 @@
       <c r="E287" t="n">
         <v>0.9765</v>
       </c>
+      <c r="F287" t="n">
+        <v>0.01861666666666667</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -4445,6 +5273,9 @@
       <c r="E288" t="n">
         <v>0.9697249999999999</v>
       </c>
+      <c r="F288" t="n">
+        <v>0.0280125</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -4459,6 +5290,9 @@
       <c r="E289" t="n">
         <v>0.9720666666666666</v>
       </c>
+      <c r="F289" t="n">
+        <v>0.04339999999999999</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -4473,6 +5307,9 @@
       <c r="E290" t="n">
         <v>0.9654428571428569</v>
       </c>
+      <c r="F290" t="n">
+        <v>0.03743333333333333</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -4487,6 +5324,9 @@
       <c r="E291" t="n">
         <v>0.9690199999999999</v>
       </c>
+      <c r="F291" t="n">
+        <v>0.03304444444444445</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -4501,6 +5341,9 @@
       <c r="E292" t="n">
         <v>0.9711400000000001</v>
       </c>
+      <c r="F292" t="n">
+        <v>0.03262222222222222</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -4515,6 +5358,9 @@
       <c r="E293" t="n">
         <v>0.974</v>
       </c>
+      <c r="F293" t="n">
+        <v>0.02096666666666667</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -4529,6 +5375,9 @@
       <c r="E294" t="n">
         <v>0.9732714285714287</v>
       </c>
+      <c r="F294" t="n">
+        <v>0.06054999999999999</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -4543,6 +5392,9 @@
       <c r="E295" t="n">
         <v>0.96868</v>
       </c>
+      <c r="F295" t="n">
+        <v>0.05488333333333334</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -4557,6 +5409,9 @@
       <c r="E296" t="n">
         <v>0.9729142857142856</v>
       </c>
+      <c r="F296" t="n">
+        <v>0.02487777777777778</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -4571,6 +5426,9 @@
       <c r="E297" t="n">
         <v>0.9695125</v>
       </c>
+      <c r="F297" t="n">
+        <v>0.0305</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -4585,6 +5443,9 @@
       <c r="E298" t="n">
         <v>0.976625</v>
       </c>
+      <c r="F298" t="n">
+        <v>0.0248875</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -4599,6 +5460,9 @@
       <c r="E299" t="n">
         <v>0.9759</v>
       </c>
+      <c r="F299" t="n">
+        <v>0.02158333333333333</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -4613,6 +5477,9 @@
       <c r="E300" t="n">
         <v>0.9629</v>
       </c>
+      <c r="F300" t="n">
+        <v>0.03964</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -4627,6 +5494,9 @@
       <c r="E301" t="n">
         <v>0.9754000000000002</v>
       </c>
+      <c r="F301" t="n">
+        <v>0.03575</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -4641,6 +5511,9 @@
       <c r="E302" t="n">
         <v>0.9681571428571428</v>
       </c>
+      <c r="F302" t="n">
+        <v>0.02567777777777778</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -4655,6 +5528,9 @@
       <c r="E303" t="n">
         <v>0.9691249999999999</v>
       </c>
+      <c r="F303" t="n">
+        <v>0.0301</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -4669,6 +5545,9 @@
       <c r="E304" t="n">
         <v>0.9712666666666667</v>
       </c>
+      <c r="F304" t="n">
+        <v>0.01468333333333333</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -4683,6 +5562,9 @@
       <c r="E305" t="n">
         <v>0.968</v>
       </c>
+      <c r="F305" t="n">
+        <v>0.04118333333333334</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -4697,6 +5579,9 @@
       <c r="E306" t="n">
         <v>0.974075</v>
       </c>
+      <c r="F306" t="n">
+        <v>0.04451428571428571</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -4711,6 +5596,9 @@
       <c r="E307" t="n">
         <v>0.97094</v>
       </c>
+      <c r="F307" t="n">
+        <v>0.04881249999999999</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -4725,6 +5613,9 @@
       <c r="E308" t="n">
         <v>0.970175</v>
       </c>
+      <c r="F308" t="n">
+        <v>0.0229375</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -4739,6 +5630,9 @@
       <c r="E309" t="n">
         <v>0.9758000000000001</v>
       </c>
+      <c r="F309" t="n">
+        <v>0.04191</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -4753,6 +5647,9 @@
       <c r="E310" t="n">
         <v>0.9707333333333333</v>
       </c>
+      <c r="F310" t="n">
+        <v>0.02802857142857143</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -4766,6 +5663,9 @@
       </c>
       <c r="E311" t="n">
         <v>0.97026</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0.02215714285714285</v>
       </c>
     </row>
     <row r="314">
@@ -4795,6 +5695,9 @@
       <c r="E316" t="n">
         <v>0.0005</v>
       </c>
+      <c r="F316" t="n">
+        <v>0.0064</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -4809,6 +5712,9 @@
       <c r="E317" t="n">
         <v>0.0167</v>
       </c>
+      <c r="F317" t="n">
+        <v>0.0399</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -4823,6 +5729,9 @@
       <c r="E318" t="n">
         <v>0.0401</v>
       </c>
+      <c r="F318" t="n">
+        <v>0.0209</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -4837,6 +5746,9 @@
       <c r="E319" t="n">
         <v>0.0653</v>
       </c>
+      <c r="F319" t="n">
+        <v>0.0419</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -4851,6 +5763,9 @@
       <c r="E320" t="n">
         <v>0.0764</v>
       </c>
+      <c r="F320" t="n">
+        <v>0.07240000000000001</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -4865,6 +5780,9 @@
       <c r="E321" t="n">
         <v>0.0892</v>
       </c>
+      <c r="F321" t="n">
+        <v>0.0914</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -4879,6 +5797,9 @@
       <c r="E322" t="n">
         <v>0.0819</v>
       </c>
+      <c r="F322" t="n">
+        <v>0.1222</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -4893,6 +5814,9 @@
       <c r="E323" t="n">
         <v>0.0917</v>
       </c>
+      <c r="F323" t="n">
+        <v>0.1093</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -4907,6 +5831,9 @@
       <c r="E324" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="F324" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -4921,6 +5848,9 @@
       <c r="E325" t="n">
         <v>0.0858</v>
       </c>
+      <c r="F325" t="n">
+        <v>0.09420000000000001</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -4935,6 +5865,9 @@
       <c r="E326" t="n">
         <v>0.103</v>
       </c>
+      <c r="F326" t="n">
+        <v>0.1315</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -4949,6 +5882,9 @@
       <c r="E327" t="n">
         <v>0.1025</v>
       </c>
+      <c r="F327" t="n">
+        <v>0.08550000000000001</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -4963,6 +5899,9 @@
       <c r="E328" t="n">
         <v>0.104</v>
       </c>
+      <c r="F328" t="n">
+        <v>0.1102</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -4977,6 +5916,9 @@
       <c r="E329" t="n">
         <v>0.1027</v>
       </c>
+      <c r="F329" t="n">
+        <v>0.1163</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -4991,6 +5933,9 @@
       <c r="E330" t="n">
         <v>0.0987</v>
       </c>
+      <c r="F330" t="n">
+        <v>0.124</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -5005,6 +5950,9 @@
       <c r="E331" t="n">
         <v>0.0974</v>
       </c>
+      <c r="F331" t="n">
+        <v>0.06610000000000001</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -5019,6 +5967,9 @@
       <c r="E332" t="n">
         <v>0.0927</v>
       </c>
+      <c r="F332" t="n">
+        <v>0.1293</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -5033,6 +5984,9 @@
       <c r="E333" t="n">
         <v>0.1021</v>
       </c>
+      <c r="F333" t="n">
+        <v>0.1531</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -5047,6 +6001,9 @@
       <c r="E334" t="n">
         <v>0.09669999999999999</v>
       </c>
+      <c r="F334" t="n">
+        <v>0.1056</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -5061,6 +6018,9 @@
       <c r="E335" t="n">
         <v>0.0969</v>
       </c>
+      <c r="F335" t="n">
+        <v>0.1149</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -5075,6 +6035,9 @@
       <c r="E336" t="n">
         <v>0.1058</v>
       </c>
+      <c r="F336" t="n">
+        <v>0.1093</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -5089,6 +6052,9 @@
       <c r="E337" t="n">
         <v>0.0969</v>
       </c>
+      <c r="F337" t="n">
+        <v>0.1044</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -5103,6 +6069,9 @@
       <c r="E338" t="n">
         <v>0.09909999999999999</v>
       </c>
+      <c r="F338" t="n">
+        <v>0.1285</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -5117,6 +6086,9 @@
       <c r="E339" t="n">
         <v>0.1073</v>
       </c>
+      <c r="F339" t="n">
+        <v>0.1221</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -5131,6 +6103,9 @@
       <c r="E340" t="n">
         <v>0.0997</v>
       </c>
+      <c r="F340" t="n">
+        <v>0.09379999999999999</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -5145,6 +6120,9 @@
       <c r="E341" t="n">
         <v>0.0974</v>
       </c>
+      <c r="F341" t="n">
+        <v>0.07140000000000001</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -5159,6 +6137,9 @@
       <c r="E342" t="n">
         <v>0.1032</v>
       </c>
+      <c r="F342" t="n">
+        <v>0.1055</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -5173,6 +6154,9 @@
       <c r="E343" t="n">
         <v>0.1013</v>
       </c>
+      <c r="F343" t="n">
+        <v>0.1222</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -5187,6 +6171,9 @@
       <c r="E344" t="n">
         <v>0.097</v>
       </c>
+      <c r="F344" t="n">
+        <v>0.102</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -5201,6 +6188,9 @@
       <c r="E345" t="n">
         <v>0.1054</v>
       </c>
+      <c r="F345" t="n">
+        <v>0.1099</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -5215,6 +6205,9 @@
       <c r="E346" t="n">
         <v>0.1032</v>
       </c>
+      <c r="F346" t="n">
+        <v>0.0828</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -5229,6 +6222,9 @@
       <c r="E347" t="n">
         <v>0.0975</v>
       </c>
+      <c r="F347" t="n">
+        <v>0.0891</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -5243,6 +6239,9 @@
       <c r="E348" t="n">
         <v>0.1067</v>
       </c>
+      <c r="F348" t="n">
+        <v>0.1184</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -5257,6 +6256,9 @@
       <c r="E349" t="n">
         <v>0.1022</v>
       </c>
+      <c r="F349" t="n">
+        <v>0.1137</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -5271,6 +6273,9 @@
       <c r="E350" t="n">
         <v>0.1099</v>
       </c>
+      <c r="F350" t="n">
+        <v>0.097</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -5285,6 +6290,9 @@
       <c r="E351" t="n">
         <v>0.1114</v>
       </c>
+      <c r="F351" t="n">
+        <v>0.1025</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -5299,6 +6307,9 @@
       <c r="E352" t="n">
         <v>0.1079</v>
       </c>
+      <c r="F352" t="n">
+        <v>0.1133</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -5313,6 +6324,9 @@
       <c r="E353" t="n">
         <v>0.1074</v>
       </c>
+      <c r="F353" t="n">
+        <v>0.1349</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -5327,6 +6341,9 @@
       <c r="E354" t="n">
         <v>0.1052</v>
       </c>
+      <c r="F354" t="n">
+        <v>0.1008</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -5341,6 +6358,9 @@
       <c r="E355" t="n">
         <v>0.1123</v>
       </c>
+      <c r="F355" t="n">
+        <v>0.0844</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -5355,6 +6375,9 @@
       <c r="E356" t="n">
         <v>0.1185</v>
       </c>
+      <c r="F356" t="n">
+        <v>0.0985</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -5369,6 +6392,9 @@
       <c r="E357" t="n">
         <v>0.1064</v>
       </c>
+      <c r="F357" t="n">
+        <v>0.1084</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -5383,6 +6409,9 @@
       <c r="E358" t="n">
         <v>0.1019</v>
       </c>
+      <c r="F358" t="n">
+        <v>0.0866</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -5397,6 +6426,9 @@
       <c r="E359" t="n">
         <v>0.0936</v>
       </c>
+      <c r="F359" t="n">
+        <v>0.0872</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -5411,6 +6443,9 @@
       <c r="E360" t="n">
         <v>0.1005</v>
       </c>
+      <c r="F360" t="n">
+        <v>0.0772</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -5425,6 +6460,9 @@
       <c r="E361" t="n">
         <v>0.1096</v>
       </c>
+      <c r="F361" t="n">
+        <v>0.08550000000000001</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -5439,6 +6477,9 @@
       <c r="E362" t="n">
         <v>0.1093</v>
       </c>
+      <c r="F362" t="n">
+        <v>0.081</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -5453,6 +6494,9 @@
       <c r="E363" t="n">
         <v>0.1122</v>
       </c>
+      <c r="F363" t="n">
+        <v>0.08500000000000001</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -5467,6 +6511,9 @@
       <c r="E364" t="n">
         <v>0.111</v>
       </c>
+      <c r="F364" t="n">
+        <v>0.081</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -5481,6 +6528,9 @@
       <c r="E365" t="n">
         <v>0.109</v>
       </c>
+      <c r="F365" t="n">
+        <v>0.1086</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -5495,6 +6545,9 @@
       <c r="E366" t="n">
         <v>0.1148</v>
       </c>
+      <c r="F366" t="n">
+        <v>0.08459999999999999</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -5509,6 +6562,9 @@
       <c r="E367" t="n">
         <v>0.09859999999999999</v>
       </c>
+      <c r="F367" t="n">
+        <v>0.0867</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -5523,6 +6579,9 @@
       <c r="E368" t="n">
         <v>0.1026</v>
       </c>
+      <c r="F368" t="n">
+        <v>0.1065</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -5537,6 +6596,9 @@
       <c r="E369" t="n">
         <v>0.0997</v>
       </c>
+      <c r="F369" t="n">
+        <v>0.1339</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -5551,6 +6613,9 @@
       <c r="E370" t="n">
         <v>0.0994</v>
       </c>
+      <c r="F370" t="n">
+        <v>0.1227</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -5565,6 +6630,9 @@
       <c r="E371" t="n">
         <v>0.0959</v>
       </c>
+      <c r="F371" t="n">
+        <v>0.1226</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -5579,6 +6647,9 @@
       <c r="E372" t="n">
         <v>0.1014</v>
       </c>
+      <c r="F372" t="n">
+        <v>0.1104</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -5593,6 +6664,9 @@
       <c r="E373" t="n">
         <v>0.1063</v>
       </c>
+      <c r="F373" t="n">
+        <v>0.1057</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -5607,6 +6681,9 @@
       <c r="E374" t="n">
         <v>0.1075</v>
       </c>
+      <c r="F374" t="n">
+        <v>0.1132</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -5621,6 +6698,9 @@
       <c r="E375" t="n">
         <v>0.1019</v>
       </c>
+      <c r="F375" t="n">
+        <v>0.1067</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -5635,6 +6715,9 @@
       <c r="E376" t="n">
         <v>0.1026</v>
       </c>
+      <c r="F376" t="n">
+        <v>0.102</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -5649,6 +6732,9 @@
       <c r="E377" t="n">
         <v>0.1031</v>
       </c>
+      <c r="F377" t="n">
+        <v>0.1198</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -5663,6 +6749,9 @@
       <c r="E378" t="n">
         <v>0.1023</v>
       </c>
+      <c r="F378" t="n">
+        <v>0.1128</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -5677,6 +6766,9 @@
       <c r="E379" t="n">
         <v>0.1018</v>
       </c>
+      <c r="F379" t="n">
+        <v>0.1109</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -5691,6 +6783,9 @@
       <c r="E380" t="n">
         <v>0.1065</v>
       </c>
+      <c r="F380" t="n">
+        <v>0.1049</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -5705,6 +6800,9 @@
       <c r="E381" t="n">
         <v>0.1096</v>
       </c>
+      <c r="F381" t="n">
+        <v>0.1014</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -5719,6 +6817,9 @@
       <c r="E382" t="n">
         <v>0.108</v>
       </c>
+      <c r="F382" t="n">
+        <v>0.0964</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -5733,6 +6834,9 @@
       <c r="E383" t="n">
         <v>0.1035</v>
       </c>
+      <c r="F383" t="n">
+        <v>0.1074</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -5747,6 +6851,9 @@
       <c r="E384" t="n">
         <v>0.0958</v>
       </c>
+      <c r="F384" t="n">
+        <v>0.1354</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -5761,6 +6868,9 @@
       <c r="E385" t="n">
         <v>0.0989</v>
       </c>
+      <c r="F385" t="n">
+        <v>0.1104</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -5775,6 +6885,9 @@
       <c r="E386" t="n">
         <v>0.1073</v>
       </c>
+      <c r="F386" t="n">
+        <v>0.1039</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -5789,6 +6902,9 @@
       <c r="E387" t="n">
         <v>0.1004</v>
       </c>
+      <c r="F387" t="n">
+        <v>0.1188</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -5803,6 +6919,9 @@
       <c r="E388" t="n">
         <v>0.1029</v>
       </c>
+      <c r="F388" t="n">
+        <v>0.1274</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -5817,6 +6936,9 @@
       <c r="E389" t="n">
         <v>0.1007</v>
       </c>
+      <c r="F389" t="n">
+        <v>0.1208</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -5831,6 +6953,9 @@
       <c r="E390" t="n">
         <v>0.1132</v>
       </c>
+      <c r="F390" t="n">
+        <v>0.0949</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -5845,6 +6970,9 @@
       <c r="E391" t="n">
         <v>0.1057</v>
       </c>
+      <c r="F391" t="n">
+        <v>0.1044</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -5859,6 +6987,9 @@
       <c r="E392" t="n">
         <v>0.1042</v>
       </c>
+      <c r="F392" t="n">
+        <v>0.117</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -5873,6 +7004,9 @@
       <c r="E393" t="n">
         <v>0.1065</v>
       </c>
+      <c r="F393" t="n">
+        <v>0.1107</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -5887,6 +7021,9 @@
       <c r="E394" t="n">
         <v>0.1037</v>
       </c>
+      <c r="F394" t="n">
+        <v>0.1005</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -5901,6 +7038,9 @@
       <c r="E395" t="n">
         <v>0.1036</v>
       </c>
+      <c r="F395" t="n">
+        <v>0.0959</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -5915,6 +7055,9 @@
       <c r="E396" t="n">
         <v>0.1061</v>
       </c>
+      <c r="F396" t="n">
+        <v>0.1038</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -5929,6 +7072,9 @@
       <c r="E397" t="n">
         <v>0.1054</v>
       </c>
+      <c r="F397" t="n">
+        <v>0.1075</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -5943,6 +7089,9 @@
       <c r="E398" t="n">
         <v>0.1045</v>
       </c>
+      <c r="F398" t="n">
+        <v>0.1118</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -5957,6 +7106,9 @@
       <c r="E399" t="n">
         <v>0.1018</v>
       </c>
+      <c r="F399" t="n">
+        <v>0.1224</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -5971,6 +7123,9 @@
       <c r="E400" t="n">
         <v>0.09669999999999999</v>
       </c>
+      <c r="F400" t="n">
+        <v>0.1226</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -5985,6 +7140,9 @@
       <c r="E401" t="n">
         <v>0.1057</v>
       </c>
+      <c r="F401" t="n">
+        <v>0.1127</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -5999,6 +7157,9 @@
       <c r="E402" t="n">
         <v>0.1004</v>
       </c>
+      <c r="F402" t="n">
+        <v>0.1004</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -6013,6 +7174,9 @@
       <c r="E403" t="n">
         <v>0.1053</v>
       </c>
+      <c r="F403" t="n">
+        <v>0.111</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -6027,6 +7191,9 @@
       <c r="E404" t="n">
         <v>0.1045</v>
       </c>
+      <c r="F404" t="n">
+        <v>0.099</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -6041,6 +7208,9 @@
       <c r="E405" t="n">
         <v>0.1094</v>
       </c>
+      <c r="F405" t="n">
+        <v>0.0985</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -6055,6 +7225,9 @@
       <c r="E406" t="n">
         <v>0.1035</v>
       </c>
+      <c r="F406" t="n">
+        <v>0.1043</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -6069,6 +7242,9 @@
       <c r="E407" t="n">
         <v>0.0969</v>
       </c>
+      <c r="F407" t="n">
+        <v>0.1165</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -6083,6 +7259,9 @@
       <c r="E408" t="n">
         <v>0.1065</v>
       </c>
+      <c r="F408" t="n">
+        <v>0.1173</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -6097,6 +7276,9 @@
       <c r="E409" t="n">
         <v>0.1041</v>
       </c>
+      <c r="F409" t="n">
+        <v>0.1049</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -6111,6 +7293,9 @@
       <c r="E410" t="n">
         <v>0.1</v>
       </c>
+      <c r="F410" t="n">
+        <v>0.1177</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -6125,6 +7310,9 @@
       <c r="E411" t="n">
         <v>0.1056</v>
       </c>
+      <c r="F411" t="n">
+        <v>0.1196</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -6139,6 +7327,9 @@
       <c r="E412" t="n">
         <v>0.1022</v>
       </c>
+      <c r="F412" t="n">
+        <v>0.1264</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -6153,6 +7344,9 @@
       <c r="E413" t="n">
         <v>0.0955</v>
       </c>
+      <c r="F413" t="n">
+        <v>0.09959999999999999</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -6167,6 +7361,9 @@
       <c r="E414" t="n">
         <v>0.1072</v>
       </c>
+      <c r="F414" t="n">
+        <v>0.0955</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -6180,6 +7377,9 @@
       </c>
       <c r="E415" t="n">
         <v>0.102</v>
+      </c>
+      <c r="F415" t="n">
+        <v>0.1057</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -599,6 +599,9 @@
       <c r="I5" t="n">
         <v>0.1466666666666667</v>
       </c>
+      <c r="J5" t="n">
+        <v>0.084325</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -622,6 +625,9 @@
       <c r="I6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J6" t="n">
+        <v>0.2527071428571429</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -645,6 +651,9 @@
       <c r="I7" t="n">
         <v>0.3585714285714285</v>
       </c>
+      <c r="J7" t="n">
+        <v>0.2572611111111111</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -668,6 +677,9 @@
       <c r="I8" t="n">
         <v>0.4255555555555556</v>
       </c>
+      <c r="J8" t="n">
+        <v>0.3903916666666667</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -691,6 +703,9 @@
       <c r="I9" t="n">
         <v>0.49</v>
       </c>
+      <c r="J9" t="n">
+        <v>0.4041571428571428</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -714,6 +729,9 @@
       <c r="I10" t="n">
         <v>0.456</v>
       </c>
+      <c r="J10" t="n">
+        <v>0.509775</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -737,6 +755,9 @@
       <c r="I11" t="n">
         <v>0.512</v>
       </c>
+      <c r="J11" t="n">
+        <v>0.5659884615384616</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -760,6 +781,9 @@
       <c r="I12" t="n">
         <v>0.4925</v>
       </c>
+      <c r="J12" t="n">
+        <v>0.6995205882352941</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -783,6 +807,9 @@
       <c r="I13" t="n">
         <v>0.5328571428571428</v>
       </c>
+      <c r="J13" t="n">
+        <v>0.646334375</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -806,6 +833,9 @@
       <c r="I14" t="n">
         <v>0.5477777777777777</v>
       </c>
+      <c r="J14" t="n">
+        <v>0.7051977272727273</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -829,6 +859,9 @@
       <c r="I15" t="n">
         <v>0.5416666666666666</v>
       </c>
+      <c r="J15" t="n">
+        <v>0.7101333333333334</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -852,6 +885,9 @@
       <c r="I16" t="n">
         <v>0.5587500000000001</v>
       </c>
+      <c r="J16" t="n">
+        <v>0.7276179487179487</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -875,6 +911,9 @@
       <c r="I17" t="n">
         <v>0.58</v>
       </c>
+      <c r="J17" t="n">
+        <v>0.7821196078431373</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -898,6 +937,9 @@
       <c r="I18" t="n">
         <v>0.5718181818181818</v>
       </c>
+      <c r="J18" t="n">
+        <v>0.8010444444444444</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -921,6 +963,9 @@
       <c r="I19" t="n">
         <v>0.5685714285714285</v>
       </c>
+      <c r="J19" t="n">
+        <v>0.777974358974359</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -944,6 +989,9 @@
       <c r="I20" t="n">
         <v>0.57875</v>
       </c>
+      <c r="J20" t="n">
+        <v>0.674482</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -967,6 +1015,9 @@
       <c r="I21" t="n">
         <v>0.5875</v>
       </c>
+      <c r="J21" t="n">
+        <v>0.6924926829268293</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -990,6 +1041,9 @@
       <c r="I22" t="n">
         <v>0.5639999999999999</v>
       </c>
+      <c r="J22" t="n">
+        <v>0.786239393939394</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1013,6 +1067,9 @@
       <c r="I23" t="n">
         <v>0.5909090909090909</v>
       </c>
+      <c r="J23" t="n">
+        <v>0.8290617647058824</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1036,6 +1093,9 @@
       <c r="I24" t="n">
         <v>0.5911111111111111</v>
       </c>
+      <c r="J24" t="n">
+        <v>0.7833928571428571</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1059,6 +1119,9 @@
       <c r="I25" t="n">
         <v>0.595</v>
       </c>
+      <c r="J25" t="n">
+        <v>0.7791833333333333</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1082,6 +1145,9 @@
       <c r="I26" t="n">
         <v>0.5988888888888889</v>
       </c>
+      <c r="J26" t="n">
+        <v>0.8023947368421053</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1105,6 +1171,9 @@
       <c r="I27" t="n">
         <v>0.5544444444444445</v>
       </c>
+      <c r="J27" t="n">
+        <v>0.794712</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1128,6 +1197,9 @@
       <c r="I28" t="n">
         <v>0.59</v>
       </c>
+      <c r="J28" t="n">
+        <v>0.8642666666666668</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1151,6 +1223,9 @@
       <c r="I29" t="n">
         <v>0.5972727272727272</v>
       </c>
+      <c r="J29" t="n">
+        <v>0.8025583333333333</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1174,6 +1249,9 @@
       <c r="I30" t="n">
         <v>0.5999999999999999</v>
       </c>
+      <c r="J30" t="n">
+        <v>0.841264864864865</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1197,6 +1275,9 @@
       <c r="I31" t="n">
         <v>0.5924999999999999</v>
       </c>
+      <c r="J31" t="n">
+        <v>0.8277212121212121</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1220,6 +1301,9 @@
       <c r="I32" t="n">
         <v>0.58</v>
       </c>
+      <c r="J32" t="n">
+        <v>0.8714515151515152</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1243,6 +1327,9 @@
       <c r="I33" t="n">
         <v>0.6259999999999999</v>
       </c>
+      <c r="J33" t="n">
+        <v>0.8257514285714286</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1266,6 +1353,9 @@
       <c r="I34" t="n">
         <v>0.594</v>
       </c>
+      <c r="J34" t="n">
+        <v>0.713465</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1289,6 +1379,9 @@
       <c r="I35" t="n">
         <v>0.601</v>
       </c>
+      <c r="J35" t="n">
+        <v>0.8098421052631579</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1312,6 +1405,9 @@
       <c r="I36" t="n">
         <v>0.5766666666666668</v>
       </c>
+      <c r="J36" t="n">
+        <v>0.8045666666666667</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1335,6 +1431,9 @@
       <c r="I37" t="n">
         <v>0.6174999999999999</v>
       </c>
+      <c r="J37" t="n">
+        <v>0.7566081081081082</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1358,6 +1457,9 @@
       <c r="I38" t="n">
         <v>0.5955555555555555</v>
       </c>
+      <c r="J38" t="n">
+        <v>0.8094117647058825</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1381,6 +1483,9 @@
       <c r="I39" t="n">
         <v>0.592</v>
       </c>
+      <c r="J39" t="n">
+        <v>0.857563043478261</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1404,6 +1509,9 @@
       <c r="I40" t="n">
         <v>0.5787500000000001</v>
       </c>
+      <c r="J40" t="n">
+        <v>0.8153321428571428</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1427,6 +1535,9 @@
       <c r="I41" t="n">
         <v>0.5912499999999999</v>
       </c>
+      <c r="J41" t="n">
+        <v>0.83691875</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1450,6 +1561,9 @@
       <c r="I42" t="n">
         <v>0.6022222222222222</v>
       </c>
+      <c r="J42" t="n">
+        <v>0.8283978260869567</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1473,6 +1587,9 @@
       <c r="I43" t="n">
         <v>0.611</v>
       </c>
+      <c r="J43" t="n">
+        <v>0.8282827586206897</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1496,6 +1613,9 @@
       <c r="I44" t="n">
         <v>0.6190000000000001</v>
       </c>
+      <c r="J44" t="n">
+        <v>0.8807318181818182</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1519,6 +1639,9 @@
       <c r="I45" t="n">
         <v>0.60625</v>
       </c>
+      <c r="J45" t="n">
+        <v>0.8044952380952382</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1542,6 +1665,9 @@
       <c r="I46" t="n">
         <v>0.6259999999999999</v>
       </c>
+      <c r="J46" t="n">
+        <v>0.8225977777777778</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1565,6 +1691,9 @@
       <c r="I47" t="n">
         <v>0.6299999999999999</v>
       </c>
+      <c r="J47" t="n">
+        <v>0.8230216216216216</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1588,6 +1717,9 @@
       <c r="I48" t="n">
         <v>0.6512499999999999</v>
       </c>
+      <c r="J48" t="n">
+        <v>0.8747666666666668</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -1611,6 +1743,9 @@
       <c r="I49" t="n">
         <v>0.616</v>
       </c>
+      <c r="J49" t="n">
+        <v>0.8695774193548389</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1634,6 +1769,9 @@
       <c r="I50" t="n">
         <v>0.633</v>
       </c>
+      <c r="J50" t="n">
+        <v>0.8196439024390245</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -1657,6 +1795,9 @@
       <c r="I51" t="n">
         <v>0.6511111111111111</v>
       </c>
+      <c r="J51" t="n">
+        <v>0.8887681818181818</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1680,6 +1821,9 @@
       <c r="I52" t="n">
         <v>0.621</v>
       </c>
+      <c r="J52" t="n">
+        <v>0.8855155555555555</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1703,6 +1847,9 @@
       <c r="I53" t="n">
         <v>0.6425</v>
       </c>
+      <c r="J53" t="n">
+        <v>0.76078</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -1726,6 +1873,9 @@
       <c r="I54" t="n">
         <v>0.625</v>
       </c>
+      <c r="J54" t="n">
+        <v>0.8361736842105261</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -1749,6 +1899,9 @@
       <c r="I55" t="n">
         <v>0.60125</v>
       </c>
+      <c r="J55" t="n">
+        <v>0.8737023809523811</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -1772,6 +1925,9 @@
       <c r="I56" t="n">
         <v>0.62</v>
       </c>
+      <c r="J56" t="n">
+        <v>0.9107047619047619</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -1795,6 +1951,9 @@
       <c r="I57" t="n">
         <v>0.6377777777777778</v>
       </c>
+      <c r="J57" t="n">
+        <v>0.8687533333333335</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -1818,6 +1977,9 @@
       <c r="I58" t="n">
         <v>0.62</v>
       </c>
+      <c r="J58" t="n">
+        <v>0.842967857142857</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -1841,6 +2003,9 @@
       <c r="I59" t="n">
         <v>0.6437499999999999</v>
       </c>
+      <c r="J59" t="n">
+        <v>0.8244981132075472</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -1864,6 +2029,9 @@
       <c r="I60" t="n">
         <v>0.65</v>
       </c>
+      <c r="J60" t="n">
+        <v>0.8236529411764707</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -1887,6 +2055,9 @@
       <c r="I61" t="n">
         <v>0.6150000000000001</v>
       </c>
+      <c r="J61" t="n">
+        <v>0.8588763157894738</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -1910,6 +2081,9 @@
       <c r="I62" t="n">
         <v>0.6275000000000001</v>
       </c>
+      <c r="J62" t="n">
+        <v>0.8965612903225807</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -1933,6 +2107,9 @@
       <c r="I63" t="n">
         <v>0.6116666666666667</v>
       </c>
+      <c r="J63" t="n">
+        <v>0.8717281250000001</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -1956,6 +2133,9 @@
       <c r="I64" t="n">
         <v>0.6357142857142856</v>
       </c>
+      <c r="J64" t="n">
+        <v>0.8515315789473685</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -1979,6 +2159,9 @@
       <c r="I65" t="n">
         <v>0.6266666666666666</v>
       </c>
+      <c r="J65" t="n">
+        <v>0.8058722222222223</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -2002,6 +2185,9 @@
       <c r="I66" t="n">
         <v>0.6233333333333333</v>
       </c>
+      <c r="J66" t="n">
+        <v>0.8136958333333334</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -2025,6 +2211,9 @@
       <c r="I67" t="n">
         <v>0.6422222222222224</v>
       </c>
+      <c r="J67" t="n">
+        <v>0.8007903225806452</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -2048,6 +2237,9 @@
       <c r="I68" t="n">
         <v>0.603</v>
       </c>
+      <c r="J68" t="n">
+        <v>0.8431424999999999</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -2071,6 +2263,9 @@
       <c r="I69" t="n">
         <v>0.65</v>
       </c>
+      <c r="J69" t="n">
+        <v>0.8015155172413793</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -2094,6 +2289,9 @@
       <c r="I70" t="n">
         <v>0.594</v>
       </c>
+      <c r="J70" t="n">
+        <v>0.8374625</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -2117,6 +2315,9 @@
       <c r="I71" t="n">
         <v>0.6033333333333333</v>
       </c>
+      <c r="J71" t="n">
+        <v>0.812629268292683</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -2140,6 +2341,9 @@
       <c r="I72" t="n">
         <v>0.6224999999999999</v>
       </c>
+      <c r="J72" t="n">
+        <v>0.8550695652173913</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -2163,6 +2367,9 @@
       <c r="I73" t="n">
         <v>0.626</v>
       </c>
+      <c r="J73" t="n">
+        <v>0.7988055555555555</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -2186,6 +2393,9 @@
       <c r="I74" t="n">
         <v>0.61</v>
       </c>
+      <c r="J74" t="n">
+        <v>0.8802259259259259</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -2209,6 +2419,9 @@
       <c r="I75" t="n">
         <v>0.6353846153846154</v>
       </c>
+      <c r="J75" t="n">
+        <v>0.8824487804878048</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -2232,6 +2445,9 @@
       <c r="I76" t="n">
         <v>0.626</v>
       </c>
+      <c r="J76" t="n">
+        <v>0.8494771428571427</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -2255,6 +2471,9 @@
       <c r="I77" t="n">
         <v>0.61</v>
       </c>
+      <c r="J77" t="n">
+        <v>0.8099722222222222</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -2278,6 +2497,9 @@
       <c r="I78" t="n">
         <v>0.6024999999999999</v>
       </c>
+      <c r="J78" t="n">
+        <v>0.8352948717948717</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -2301,6 +2523,9 @@
       <c r="I79" t="n">
         <v>0.6172727272727272</v>
       </c>
+      <c r="J79" t="n">
+        <v>0.7850076923076924</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -2324,6 +2549,9 @@
       <c r="I80" t="n">
         <v>0.6323076923076923</v>
       </c>
+      <c r="J80" t="n">
+        <v>0.8836761904761905</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -2347,6 +2575,9 @@
       <c r="I81" t="n">
         <v>0.6381818181818182</v>
       </c>
+      <c r="J81" t="n">
+        <v>0.7918697674418603</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -2370,6 +2601,9 @@
       <c r="I82" t="n">
         <v>0.6300000000000001</v>
       </c>
+      <c r="J82" t="n">
+        <v>0.8031800000000001</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -2393,6 +2627,9 @@
       <c r="I83" t="n">
         <v>0.6377777777777779</v>
       </c>
+      <c r="J83" t="n">
+        <v>0.8663222222222221</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -2416,6 +2653,9 @@
       <c r="I84" t="n">
         <v>0.6077777777777779</v>
       </c>
+      <c r="J84" t="n">
+        <v>0.8505545454545456</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -2439,6 +2679,9 @@
       <c r="I85" t="n">
         <v>0.6171428571428572</v>
       </c>
+      <c r="J85" t="n">
+        <v>0.8456575757575757</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -2462,6 +2705,9 @@
       <c r="I86" t="n">
         <v>0.636</v>
       </c>
+      <c r="J86" t="n">
+        <v>0.8337040816326531</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -2485,6 +2731,9 @@
       <c r="I87" t="n">
         <v>0.648</v>
       </c>
+      <c r="J87" t="n">
+        <v>0.8017185185185185</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -2508,6 +2757,9 @@
       <c r="I88" t="n">
         <v>0.6388888888888888</v>
       </c>
+      <c r="J88" t="n">
+        <v>0.8196030303030303</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -2531,6 +2783,9 @@
       <c r="I89" t="n">
         <v>0.6388888888888888</v>
       </c>
+      <c r="J89" t="n">
+        <v>0.8074947368421052</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -2554,6 +2809,9 @@
       <c r="I90" t="n">
         <v>0.6111111111111112</v>
       </c>
+      <c r="J90" t="n">
+        <v>0.781253125</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -2577,6 +2835,9 @@
       <c r="I91" t="n">
         <v>0.63</v>
       </c>
+      <c r="J91" t="n">
+        <v>0.8277413793103449</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -2600,6 +2861,9 @@
       <c r="I92" t="n">
         <v>0.632</v>
       </c>
+      <c r="J92" t="n">
+        <v>0.8489088888888888</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -2623,6 +2887,9 @@
       <c r="I93" t="n">
         <v>0.6325000000000001</v>
       </c>
+      <c r="J93" t="n">
+        <v>0.8572111111111111</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -2646,6 +2913,9 @@
       <c r="I94" t="n">
         <v>0.6055555555555556</v>
       </c>
+      <c r="J94" t="n">
+        <v>0.7635352941176471</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -2669,6 +2939,9 @@
       <c r="I95" t="n">
         <v>0.6</v>
       </c>
+      <c r="J95" t="n">
+        <v>0.8265319999999999</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -2692,6 +2965,9 @@
       <c r="I96" t="n">
         <v>0.623</v>
       </c>
+      <c r="J96" t="n">
+        <v>0.8006685714285714</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -2715,6 +2991,9 @@
       <c r="I97" t="n">
         <v>0.6466666666666666</v>
       </c>
+      <c r="J97" t="n">
+        <v>0.7916</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -2738,6 +3017,9 @@
       <c r="I98" t="n">
         <v>0.675</v>
       </c>
+      <c r="J98" t="n">
+        <v>0.8065529411764706</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -2761,6 +3043,9 @@
       <c r="I99" t="n">
         <v>0.65</v>
       </c>
+      <c r="J99" t="n">
+        <v>0.8485624999999999</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -2784,6 +3069,9 @@
       <c r="I100" t="n">
         <v>0.6011111111111112</v>
       </c>
+      <c r="J100" t="n">
+        <v>0.8383518518518519</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -2807,6 +3095,9 @@
       <c r="I101" t="n">
         <v>0.6466666666666667</v>
       </c>
+      <c r="J101" t="n">
+        <v>0.8121136363636364</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -2830,6 +3121,9 @@
       <c r="I102" t="n">
         <v>0.634</v>
       </c>
+      <c r="J102" t="n">
+        <v>0.8871957446808511</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -2853,6 +3147,9 @@
       <c r="I103" t="n">
         <v>0.6377777777777778</v>
       </c>
+      <c r="J103" t="n">
+        <v>0.8266685714285714</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -2875,6 +3172,9 @@
       </c>
       <c r="I104" t="n">
         <v>0.6518181818181819</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.8704032258064517</v>
       </c>
     </row>
     <row r="106">
@@ -2923,6 +3223,9 @@
       <c r="I108" t="n">
         <v>1</v>
       </c>
+      <c r="J108" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -2946,6 +3249,9 @@
       <c r="I109" t="n">
         <v>1</v>
       </c>
+      <c r="J109" t="n">
+        <v>0.7692307692307693</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -2969,6 +3275,9 @@
       <c r="I110" t="n">
         <v>1</v>
       </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -2992,6 +3301,9 @@
       <c r="I111" t="n">
         <v>1</v>
       </c>
+      <c r="J111" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -3015,6 +3327,9 @@
       <c r="I112" t="n">
         <v>1</v>
       </c>
+      <c r="J112" t="n">
+        <v>0.8571428571428571</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -3038,6 +3353,9 @@
       <c r="I113" t="n">
         <v>1</v>
       </c>
+      <c r="J113" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -3061,6 +3379,9 @@
       <c r="I114" t="n">
         <v>1</v>
       </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -3084,6 +3405,9 @@
       <c r="I115" t="n">
         <v>1</v>
       </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -3107,6 +3431,9 @@
       <c r="I116" t="n">
         <v>1</v>
       </c>
+      <c r="J116" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -3130,6 +3457,9 @@
       <c r="I117" t="n">
         <v>1</v>
       </c>
+      <c r="J117" t="n">
+        <v>0.8571428571428571</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -3153,6 +3483,9 @@
       <c r="I118" t="n">
         <v>1</v>
       </c>
+      <c r="J118" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -3176,6 +3509,9 @@
       <c r="I119" t="n">
         <v>1</v>
       </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -3199,6 +3535,9 @@
       <c r="I120" t="n">
         <v>1</v>
       </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -3222,6 +3561,9 @@
       <c r="I121" t="n">
         <v>1</v>
       </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -3245,6 +3587,9 @@
       <c r="I122" t="n">
         <v>1</v>
       </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -3268,6 +3613,9 @@
       <c r="I123" t="n">
         <v>1</v>
       </c>
+      <c r="J123" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -3291,6 +3639,9 @@
       <c r="I124" t="n">
         <v>1</v>
       </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -3314,6 +3665,9 @@
       <c r="I125" t="n">
         <v>1</v>
       </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -3337,6 +3691,9 @@
       <c r="I126" t="n">
         <v>1</v>
       </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -3360,6 +3717,9 @@
       <c r="I127" t="n">
         <v>1</v>
       </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -3383,6 +3743,9 @@
       <c r="I128" t="n">
         <v>1</v>
       </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -3406,6 +3769,9 @@
       <c r="I129" t="n">
         <v>1</v>
       </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -3429,6 +3795,9 @@
       <c r="I130" t="n">
         <v>1</v>
       </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -3452,6 +3821,9 @@
       <c r="I131" t="n">
         <v>1</v>
       </c>
+      <c r="J131" t="n">
+        <v>0.8571428571428571</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -3475,6 +3847,9 @@
       <c r="I132" t="n">
         <v>1</v>
       </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -3498,6 +3873,9 @@
       <c r="I133" t="n">
         <v>1</v>
       </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -3521,6 +3899,9 @@
       <c r="I134" t="n">
         <v>1</v>
       </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -3544,6 +3925,9 @@
       <c r="I135" t="n">
         <v>1</v>
       </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -3567,6 +3951,9 @@
       <c r="I136" t="n">
         <v>1</v>
       </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -3590,6 +3977,9 @@
       <c r="I137" t="n">
         <v>1</v>
       </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -3613,6 +4003,9 @@
       <c r="I138" t="n">
         <v>1</v>
       </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -3636,6 +4029,9 @@
       <c r="I139" t="n">
         <v>1</v>
       </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -3659,6 +4055,9 @@
       <c r="I140" t="n">
         <v>1</v>
       </c>
+      <c r="J140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -3682,6 +4081,9 @@
       <c r="I141" t="n">
         <v>1</v>
       </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -3705,6 +4107,9 @@
       <c r="I142" t="n">
         <v>1</v>
       </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -3728,6 +4133,9 @@
       <c r="I143" t="n">
         <v>1</v>
       </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -3751,6 +4159,9 @@
       <c r="I144" t="n">
         <v>1</v>
       </c>
+      <c r="J144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -3774,6 +4185,9 @@
       <c r="I145" t="n">
         <v>1</v>
       </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -3797,6 +4211,9 @@
       <c r="I146" t="n">
         <v>1</v>
       </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -3820,6 +4237,9 @@
       <c r="I147" t="n">
         <v>1</v>
       </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -3843,6 +4263,9 @@
       <c r="I148" t="n">
         <v>1</v>
       </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -3866,6 +4289,9 @@
       <c r="I149" t="n">
         <v>1</v>
       </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -3889,6 +4315,9 @@
       <c r="I150" t="n">
         <v>1</v>
       </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -3912,6 +4341,9 @@
       <c r="I151" t="n">
         <v>1</v>
       </c>
+      <c r="J151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -3935,6 +4367,9 @@
       <c r="I152" t="n">
         <v>1</v>
       </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -3958,6 +4393,9 @@
       <c r="I153" t="n">
         <v>1</v>
       </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -3981,6 +4419,9 @@
       <c r="I154" t="n">
         <v>1</v>
       </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -4004,6 +4445,9 @@
       <c r="I155" t="n">
         <v>1</v>
       </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -4027,6 +4471,9 @@
       <c r="I156" t="n">
         <v>1</v>
       </c>
+      <c r="J156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -4050,6 +4497,9 @@
       <c r="I157" t="n">
         <v>1</v>
       </c>
+      <c r="J157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -4073,6 +4523,9 @@
       <c r="I158" t="n">
         <v>1</v>
       </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -4096,6 +4549,9 @@
       <c r="I159" t="n">
         <v>1</v>
       </c>
+      <c r="J159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -4119,6 +4575,9 @@
       <c r="I160" t="n">
         <v>1</v>
       </c>
+      <c r="J160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -4142,6 +4601,9 @@
       <c r="I161" t="n">
         <v>1</v>
       </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -4165,6 +4627,9 @@
       <c r="I162" t="n">
         <v>1</v>
       </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -4188,6 +4653,9 @@
       <c r="I163" t="n">
         <v>1</v>
       </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -4211,6 +4679,9 @@
       <c r="I164" t="n">
         <v>1</v>
       </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -4234,6 +4705,9 @@
       <c r="I165" t="n">
         <v>1</v>
       </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -4257,6 +4731,9 @@
       <c r="I166" t="n">
         <v>1</v>
       </c>
+      <c r="J166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -4280,6 +4757,9 @@
       <c r="I167" t="n">
         <v>1</v>
       </c>
+      <c r="J167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -4303,6 +4783,9 @@
       <c r="I168" t="n">
         <v>1</v>
       </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -4326,6 +4809,9 @@
       <c r="I169" t="n">
         <v>1</v>
       </c>
+      <c r="J169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -4349,6 +4835,9 @@
       <c r="I170" t="n">
         <v>1</v>
       </c>
+      <c r="J170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -4372,6 +4861,9 @@
       <c r="I171" t="n">
         <v>1</v>
       </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -4395,6 +4887,9 @@
       <c r="I172" t="n">
         <v>1</v>
       </c>
+      <c r="J172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -4418,6 +4913,9 @@
       <c r="I173" t="n">
         <v>1</v>
       </c>
+      <c r="J173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -4441,6 +4939,9 @@
       <c r="I174" t="n">
         <v>1</v>
       </c>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -4464,6 +4965,9 @@
       <c r="I175" t="n">
         <v>1</v>
       </c>
+      <c r="J175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -4487,6 +4991,9 @@
       <c r="I176" t="n">
         <v>1</v>
       </c>
+      <c r="J176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -4510,6 +5017,9 @@
       <c r="I177" t="n">
         <v>1</v>
       </c>
+      <c r="J177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -4533,6 +5043,9 @@
       <c r="I178" t="n">
         <v>1</v>
       </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -4556,6 +5069,9 @@
       <c r="I179" t="n">
         <v>1</v>
       </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -4579,6 +5095,9 @@
       <c r="I180" t="n">
         <v>1</v>
       </c>
+      <c r="J180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -4602,6 +5121,9 @@
       <c r="I181" t="n">
         <v>1</v>
       </c>
+      <c r="J181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -4625,6 +5147,9 @@
       <c r="I182" t="n">
         <v>1</v>
       </c>
+      <c r="J182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -4648,6 +5173,9 @@
       <c r="I183" t="n">
         <v>1</v>
       </c>
+      <c r="J183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -4671,6 +5199,9 @@
       <c r="I184" t="n">
         <v>1</v>
       </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -4694,6 +5225,9 @@
       <c r="I185" t="n">
         <v>1</v>
       </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -4717,6 +5251,9 @@
       <c r="I186" t="n">
         <v>1</v>
       </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -4740,6 +5277,9 @@
       <c r="I187" t="n">
         <v>1</v>
       </c>
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -4763,6 +5303,9 @@
       <c r="I188" t="n">
         <v>1</v>
       </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -4786,6 +5329,9 @@
       <c r="I189" t="n">
         <v>1</v>
       </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -4809,6 +5355,9 @@
       <c r="I190" t="n">
         <v>1</v>
       </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -4832,6 +5381,9 @@
       <c r="I191" t="n">
         <v>1</v>
       </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -4855,6 +5407,9 @@
       <c r="I192" t="n">
         <v>1</v>
       </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -4878,6 +5433,9 @@
       <c r="I193" t="n">
         <v>1</v>
       </c>
+      <c r="J193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -4901,6 +5459,9 @@
       <c r="I194" t="n">
         <v>1</v>
       </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -4924,6 +5485,9 @@
       <c r="I195" t="n">
         <v>1</v>
       </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -4947,6 +5511,9 @@
       <c r="I196" t="n">
         <v>1</v>
       </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -4970,6 +5537,9 @@
       <c r="I197" t="n">
         <v>1</v>
       </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -4993,6 +5563,9 @@
       <c r="I198" t="n">
         <v>1</v>
       </c>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -5016,6 +5589,9 @@
       <c r="I199" t="n">
         <v>1</v>
       </c>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -5039,6 +5615,9 @@
       <c r="I200" t="n">
         <v>1</v>
       </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -5062,6 +5641,9 @@
       <c r="I201" t="n">
         <v>1</v>
       </c>
+      <c r="J201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -5085,6 +5667,9 @@
       <c r="I202" t="n">
         <v>1</v>
       </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -5108,6 +5693,9 @@
       <c r="I203" t="n">
         <v>1</v>
       </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -5131,6 +5719,9 @@
       <c r="I204" t="n">
         <v>1</v>
       </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -5154,6 +5745,9 @@
       <c r="I205" t="n">
         <v>1</v>
       </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -5177,6 +5771,9 @@
       <c r="I206" t="n">
         <v>1</v>
       </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -5198,6 +5795,9 @@
         <v>100</v>
       </c>
       <c r="I207" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5247,6 +5847,9 @@
       <c r="I212" t="n">
         <v>0.00765</v>
       </c>
+      <c r="J212" t="n">
+        <v>0.8452</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -5270,6 +5873,9 @@
       <c r="I213" t="n">
         <v>0.006675</v>
       </c>
+      <c r="J213" t="n">
+        <v>0.6774625000000001</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -5293,6 +5899,9 @@
       <c r="I214" t="n">
         <v>0.0070375</v>
       </c>
+      <c r="J214" t="n">
+        <v>0.7674111111111112</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -5316,6 +5925,9 @@
       <c r="I215" t="n">
         <v>0.009049999999999999</v>
       </c>
+      <c r="J215" t="n">
+        <v>0.7663500000000001</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -5339,6 +5951,9 @@
       <c r="I216" t="n">
         <v>0.007285714285714286</v>
       </c>
+      <c r="J216" t="n">
+        <v>0.6505777777777778</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -5362,6 +5977,9 @@
       <c r="I217" t="n">
         <v>0.006057142857142857</v>
       </c>
+      <c r="J217" t="n">
+        <v>0.6559818181818181</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -5385,6 +6003,9 @@
       <c r="I218" t="n">
         <v>0.01086</v>
       </c>
+      <c r="J218" t="n">
+        <v>0.4963333333333333</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -5408,6 +6029,9 @@
       <c r="I219" t="n">
         <v>0.0125</v>
       </c>
+      <c r="J219" t="n">
+        <v>0.5920555555555556</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -5431,6 +6055,9 @@
       <c r="I220" t="n">
         <v>0.00925</v>
       </c>
+      <c r="J220" t="n">
+        <v>0.5877</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -5454,6 +6081,9 @@
       <c r="I221" t="n">
         <v>0.0123625</v>
       </c>
+      <c r="J221" t="n">
+        <v>0.7752444444444444</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -5477,6 +6107,9 @@
       <c r="I222" t="n">
         <v>0.010725</v>
       </c>
+      <c r="J222" t="n">
+        <v>0.64361</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -5500,6 +6133,9 @@
       <c r="I223" t="n">
         <v>0.01165714285714286</v>
       </c>
+      <c r="J223" t="n">
+        <v>0.4885714285714285</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -5523,6 +6159,9 @@
       <c r="I224" t="n">
         <v>0.009600000000000001</v>
       </c>
+      <c r="J224" t="n">
+        <v>0.6527000000000001</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -5546,6 +6185,9 @@
       <c r="I225" t="n">
         <v>0.008685714285714286</v>
       </c>
+      <c r="J225" t="n">
+        <v>0.5255399999999999</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -5569,6 +6211,9 @@
       <c r="I226" t="n">
         <v>0.01212857142857143</v>
       </c>
+      <c r="J226" t="n">
+        <v>0.5496444444444444</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -5592,6 +6237,9 @@
       <c r="I227" t="n">
         <v>0.01584</v>
       </c>
+      <c r="J227" t="n">
+        <v>0.5828166666666666</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -5615,6 +6263,9 @@
       <c r="I228" t="n">
         <v>0.0123</v>
       </c>
+      <c r="J228" t="n">
+        <v>0.5203636363636363</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -5638,6 +6289,9 @@
       <c r="I229" t="n">
         <v>0.0112</v>
       </c>
+      <c r="J229" t="n">
+        <v>0.564888888888889</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -5661,6 +6315,9 @@
       <c r="I230" t="n">
         <v>0.01463333333333333</v>
       </c>
+      <c r="J230" t="n">
+        <v>0.5632777777777778</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -5684,6 +6341,9 @@
       <c r="I231" t="n">
         <v>0.01574</v>
       </c>
+      <c r="J231" t="n">
+        <v>0.5177875000000001</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -5707,6 +6367,9 @@
       <c r="I232" t="n">
         <v>0.01185</v>
       </c>
+      <c r="J232" t="n">
+        <v>0.5377307692307692</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -5730,6 +6393,9 @@
       <c r="I233" t="n">
         <v>0.01116666666666667</v>
       </c>
+      <c r="J233" t="n">
+        <v>0.5020625000000001</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -5753,6 +6419,9 @@
       <c r="I234" t="n">
         <v>0.01193333333333333</v>
       </c>
+      <c r="J234" t="n">
+        <v>0.6765333333333333</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -5776,6 +6445,9 @@
       <c r="I235" t="n">
         <v>0.01456666666666667</v>
       </c>
+      <c r="J235" t="n">
+        <v>0.5295375</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -5799,6 +6471,9 @@
       <c r="I236" t="n">
         <v>0.009285714285714286</v>
       </c>
+      <c r="J236" t="n">
+        <v>0.4566909090909091</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -5822,6 +6497,9 @@
       <c r="I237" t="n">
         <v>0.0114</v>
       </c>
+      <c r="J237" t="n">
+        <v>0.3461</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -5845,6 +6523,9 @@
       <c r="I238" t="n">
         <v>0.01131428571428571</v>
       </c>
+      <c r="J238" t="n">
+        <v>0.6089545454545454</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -5868,6 +6549,9 @@
       <c r="I239" t="n">
         <v>0.0132</v>
       </c>
+      <c r="J239" t="n">
+        <v>0.5529818181818181</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -5891,6 +6575,9 @@
       <c r="I240" t="n">
         <v>0.01398</v>
       </c>
+      <c r="J240" t="n">
+        <v>0.5207799999999999</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -5914,6 +6601,9 @@
       <c r="I241" t="n">
         <v>0.00485</v>
       </c>
+      <c r="J241" t="n">
+        <v>0.5360666666666666</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -5937,6 +6627,9 @@
       <c r="I242" t="n">
         <v>0.011225</v>
       </c>
+      <c r="J242" t="n">
+        <v>0.50887</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -5960,6 +6653,9 @@
       <c r="I243" t="n">
         <v>0.009550000000000001</v>
       </c>
+      <c r="J243" t="n">
+        <v>0.4766727272727273</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -5983,6 +6679,9 @@
       <c r="I244" t="n">
         <v>0.01535</v>
       </c>
+      <c r="J244" t="n">
+        <v>0.6740777777777778</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -6006,6 +6705,9 @@
       <c r="I245" t="n">
         <v>0.01466666666666667</v>
       </c>
+      <c r="J245" t="n">
+        <v>0.5428363636363636</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -6029,6 +6731,9 @@
       <c r="I246" t="n">
         <v>0.013525</v>
       </c>
+      <c r="J246" t="n">
+        <v>0.4670285714285715</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -6052,6 +6757,9 @@
       <c r="I247" t="n">
         <v>0.01741666666666667</v>
       </c>
+      <c r="J247" t="n">
+        <v>0.4177</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -6075,6 +6783,9 @@
       <c r="I248" t="n">
         <v>0.01104285714285714</v>
       </c>
+      <c r="J248" t="n">
+        <v>0.4193727272727273</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -6098,6 +6809,9 @@
       <c r="I249" t="n">
         <v>0.0127375</v>
       </c>
+      <c r="J249" t="n">
+        <v>0.3126111111111111</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -6121,6 +6835,9 @@
       <c r="I250" t="n">
         <v>0.0139</v>
       </c>
+      <c r="J250" t="n">
+        <v>0.52541</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -6144,6 +6861,9 @@
       <c r="I251" t="n">
         <v>0.0115125</v>
       </c>
+      <c r="J251" t="n">
+        <v>0.62101</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -6167,6 +6887,9 @@
       <c r="I252" t="n">
         <v>0.01378</v>
       </c>
+      <c r="J252" t="n">
+        <v>0.47405</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -6190,6 +6913,9 @@
       <c r="I253" t="n">
         <v>0.008075000000000001</v>
       </c>
+      <c r="J253" t="n">
+        <v>0.2976124999999999</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -6213,6 +6939,9 @@
       <c r="I254" t="n">
         <v>0.01317142857142857</v>
       </c>
+      <c r="J254" t="n">
+        <v>0.5305636363636363</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -6236,6 +6965,9 @@
       <c r="I255" t="n">
         <v>0.0109</v>
       </c>
+      <c r="J255" t="n">
+        <v>0.453675</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -6259,6 +6991,9 @@
       <c r="I256" t="n">
         <v>0.01064285714285714</v>
       </c>
+      <c r="J256" t="n">
+        <v>0.5264</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -6282,6 +7017,9 @@
       <c r="I257" t="n">
         <v>0.0134</v>
       </c>
+      <c r="J257" t="n">
+        <v>0.5061099999999999</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -6305,6 +7043,9 @@
       <c r="I258" t="n">
         <v>0.01263333333333333</v>
       </c>
+      <c r="J258" t="n">
+        <v>0.5704727272727272</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -6328,6 +7069,9 @@
       <c r="I259" t="n">
         <v>0.01704285714285714</v>
       </c>
+      <c r="J259" t="n">
+        <v>0.4940125</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -6351,6 +7095,9 @@
       <c r="I260" t="n">
         <v>0.01583333333333333</v>
       </c>
+      <c r="J260" t="n">
+        <v>0.49337</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -6374,6 +7121,9 @@
       <c r="I261" t="n">
         <v>0.008433333333333334</v>
       </c>
+      <c r="J261" t="n">
+        <v>0.4787125</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -6397,6 +7147,9 @@
       <c r="I262" t="n">
         <v>0.01156</v>
       </c>
+      <c r="J262" t="n">
+        <v>0.5332166666666667</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -6420,6 +7173,9 @@
       <c r="I263" t="n">
         <v>0.0126875</v>
       </c>
+      <c r="J263" t="n">
+        <v>0.4821777777777778</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -6443,6 +7199,9 @@
       <c r="I264" t="n">
         <v>0.01032857142857143</v>
       </c>
+      <c r="J264" t="n">
+        <v>0.2785666666666666</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -6466,6 +7225,9 @@
       <c r="I265" t="n">
         <v>0.01536666666666667</v>
       </c>
+      <c r="J265" t="n">
+        <v>0.37362</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -6489,6 +7251,9 @@
       <c r="I266" t="n">
         <v>0.01271666666666667</v>
       </c>
+      <c r="J266" t="n">
+        <v>0.5777333333333333</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -6512,6 +7277,9 @@
       <c r="I267" t="n">
         <v>0.009600000000000001</v>
       </c>
+      <c r="J267" t="n">
+        <v>0.4187555555555555</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -6535,6 +7303,9 @@
       <c r="I268" t="n">
         <v>0.008925000000000001</v>
       </c>
+      <c r="J268" t="n">
+        <v>0.4432923076923077</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -6558,6 +7329,9 @@
       <c r="I269" t="n">
         <v>0.0111</v>
       </c>
+      <c r="J269" t="n">
+        <v>0.3992545454545455</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -6581,6 +7355,9 @@
       <c r="I270" t="n">
         <v>0.015</v>
       </c>
+      <c r="J270" t="n">
+        <v>0.53024</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -6604,6 +7381,9 @@
       <c r="I271" t="n">
         <v>0.0132</v>
       </c>
+      <c r="J271" t="n">
+        <v>0.35245</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -6627,6 +7407,9 @@
       <c r="I272" t="n">
         <v>0.009800000000000001</v>
       </c>
+      <c r="J272" t="n">
+        <v>0.5364099999999999</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -6650,6 +7433,9 @@
       <c r="I273" t="n">
         <v>0.01216</v>
       </c>
+      <c r="J273" t="n">
+        <v>0.49046</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -6673,6 +7459,9 @@
       <c r="I274" t="n">
         <v>0.00855</v>
       </c>
+      <c r="J274" t="n">
+        <v>0.5271454545454546</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -6696,6 +7485,9 @@
       <c r="I275" t="n">
         <v>0.0118</v>
       </c>
+      <c r="J275" t="n">
+        <v>0.6258583333333333</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -6719,6 +7511,9 @@
       <c r="I276" t="n">
         <v>0.009800000000000001</v>
       </c>
+      <c r="J276" t="n">
+        <v>0.5662900000000001</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -6742,6 +7537,9 @@
       <c r="I277" t="n">
         <v>0.01072</v>
       </c>
+      <c r="J277" t="n">
+        <v>0.5481333333333334</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -6765,6 +7563,9 @@
       <c r="I278" t="n">
         <v>0.0097</v>
       </c>
+      <c r="J278" t="n">
+        <v>0.6872499999999999</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -6788,6 +7589,9 @@
       <c r="I279" t="n">
         <v>0.00992</v>
       </c>
+      <c r="J279" t="n">
+        <v>0.38228</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -6811,6 +7615,9 @@
       <c r="I280" t="n">
         <v>0.007571428571428571</v>
       </c>
+      <c r="J280" t="n">
+        <v>0.5379111111111111</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -6834,6 +7641,9 @@
       <c r="I281" t="n">
         <v>0.008585714285714285</v>
       </c>
+      <c r="J281" t="n">
+        <v>0.3585</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -6857,6 +7667,9 @@
       <c r="I282" t="n">
         <v>0.012675</v>
       </c>
+      <c r="J282" t="n">
+        <v>0.46475</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -6880,6 +7693,9 @@
       <c r="I283" t="n">
         <v>0.009524999999999999</v>
       </c>
+      <c r="J283" t="n">
+        <v>0.5285444444444445</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -6903,6 +7719,9 @@
       <c r="I284" t="n">
         <v>0.00856</v>
       </c>
+      <c r="J284" t="n">
+        <v>0.6937299999999998</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -6926,6 +7745,9 @@
       <c r="I285" t="n">
         <v>0.008714285714285714</v>
       </c>
+      <c r="J285" t="n">
+        <v>0.619257142857143</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -6949,6 +7771,9 @@
       <c r="I286" t="n">
         <v>0.0126</v>
       </c>
+      <c r="J286" t="n">
+        <v>0.4541099999999999</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -6972,6 +7797,9 @@
       <c r="I287" t="n">
         <v>0.009650000000000001</v>
       </c>
+      <c r="J287" t="n">
+        <v>0.36542</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -6995,6 +7823,9 @@
       <c r="I288" t="n">
         <v>0.007875</v>
       </c>
+      <c r="J288" t="n">
+        <v>0.4118777777777777</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -7018,6 +7849,9 @@
       <c r="I289" t="n">
         <v>0.009479999999999999</v>
       </c>
+      <c r="J289" t="n">
+        <v>0.4954363636363638</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -7041,6 +7875,9 @@
       <c r="I290" t="n">
         <v>0.009766666666666667</v>
       </c>
+      <c r="J290" t="n">
+        <v>0.5547111111111112</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -7064,6 +7901,9 @@
       <c r="I291" t="n">
         <v>0.01</v>
       </c>
+      <c r="J291" t="n">
+        <v>0.4500666666666667</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -7087,6 +7927,9 @@
       <c r="I292" t="n">
         <v>0.01084285714285714</v>
       </c>
+      <c r="J292" t="n">
+        <v>0.4856444444444444</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -7110,6 +7953,9 @@
       <c r="I293" t="n">
         <v>0.01038333333333333</v>
       </c>
+      <c r="J293" t="n">
+        <v>0.5432083333333333</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -7133,6 +7979,9 @@
       <c r="I294" t="n">
         <v>0.009942857142857142</v>
       </c>
+      <c r="J294" t="n">
+        <v>0.4857363636363636</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -7156,6 +8005,9 @@
       <c r="I295" t="n">
         <v>0.004549999999999999</v>
       </c>
+      <c r="J295" t="n">
+        <v>0.43847</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -7179,6 +8031,9 @@
       <c r="I296" t="n">
         <v>0.01044444444444444</v>
       </c>
+      <c r="J296" t="n">
+        <v>0.5291</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -7202,6 +8057,9 @@
       <c r="I297" t="n">
         <v>0.01418571428571429</v>
       </c>
+      <c r="J297" t="n">
+        <v>0.5162</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -7225,6 +8083,9 @@
       <c r="I298" t="n">
         <v>0.0051</v>
       </c>
+      <c r="J298" t="n">
+        <v>0.5041545454545454</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -7248,6 +8109,9 @@
       <c r="I299" t="n">
         <v>0.0095625</v>
       </c>
+      <c r="J299" t="n">
+        <v>0.401623076923077</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -7271,6 +8135,9 @@
       <c r="I300" t="n">
         <v>0.007180000000000001</v>
       </c>
+      <c r="J300" t="n">
+        <v>0.45561</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -7294,6 +8161,9 @@
       <c r="I301" t="n">
         <v>0.01045</v>
       </c>
+      <c r="J301" t="n">
+        <v>0.3771777777777778</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -7317,6 +8187,9 @@
       <c r="I302" t="n">
         <v>0.006874999999999999</v>
       </c>
+      <c r="J302" t="n">
+        <v>0.6104636363636364</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -7340,6 +8213,9 @@
       <c r="I303" t="n">
         <v>0.009299999999999999</v>
       </c>
+      <c r="J303" t="n">
+        <v>0.4274909090909091</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -7363,6 +8239,9 @@
       <c r="I304" t="n">
         <v>0.009949999999999999</v>
       </c>
+      <c r="J304" t="n">
+        <v>0.4839090909090908</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -7386,6 +8265,9 @@
       <c r="I305" t="n">
         <v>0.007266666666666667</v>
       </c>
+      <c r="J305" t="n">
+        <v>0.6493749999999999</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -7409,6 +8291,9 @@
       <c r="I306" t="n">
         <v>0.008333333333333333</v>
       </c>
+      <c r="J306" t="n">
+        <v>0.5018142857142857</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -7432,6 +8317,9 @@
       <c r="I307" t="n">
         <v>0.00865</v>
       </c>
+      <c r="J307" t="n">
+        <v>0.4604571428571429</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -7455,6 +8343,9 @@
       <c r="I308" t="n">
         <v>0.0086625</v>
       </c>
+      <c r="J308" t="n">
+        <v>0.4075545454545454</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -7478,6 +8369,9 @@
       <c r="I309" t="n">
         <v>0.009639999999999999</v>
       </c>
+      <c r="J309" t="n">
+        <v>0.6233666666666667</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -7501,6 +8395,9 @@
       <c r="I310" t="n">
         <v>0.01025</v>
       </c>
+      <c r="J310" t="n">
+        <v>0.5002555555555555</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -7523,6 +8420,9 @@
       </c>
       <c r="I311" t="n">
         <v>0.01208333333333333</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0.4580555555555555</v>
       </c>
     </row>
     <row r="314">
@@ -7571,6 +8471,9 @@
       <c r="I316" t="n">
         <v>0</v>
       </c>
+      <c r="J316" t="n">
+        <v>0.0002</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -7594,6 +8497,9 @@
       <c r="I317" t="n">
         <v>0.0055</v>
       </c>
+      <c r="J317" t="n">
+        <v>0.0526</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -7617,6 +8523,9 @@
       <c r="I318" t="n">
         <v>0.06370000000000001</v>
       </c>
+      <c r="J318" t="n">
+        <v>0.016</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -7640,6 +8549,9 @@
       <c r="I319" t="n">
         <v>0.0674</v>
       </c>
+      <c r="J319" t="n">
+        <v>0.015</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -7663,6 +8575,9 @@
       <c r="I320" t="n">
         <v>0.08749999999999999</v>
       </c>
+      <c r="J320" t="n">
+        <v>0.0237</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -7686,6 +8601,9 @@
       <c r="I321" t="n">
         <v>0.06950000000000001</v>
       </c>
+      <c r="J321" t="n">
+        <v>0.0725</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -7709,6 +8627,9 @@
       <c r="I322" t="n">
         <v>0.0859</v>
       </c>
+      <c r="J322" t="n">
+        <v>0.09470000000000001</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -7732,6 +8653,9 @@
       <c r="I323" t="n">
         <v>0.0862</v>
       </c>
+      <c r="J323" t="n">
+        <v>0.0693</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -7755,6 +8679,9 @@
       <c r="I324" t="n">
         <v>0.0916</v>
       </c>
+      <c r="J324" t="n">
+        <v>0.0493</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -7778,6 +8705,9 @@
       <c r="I325" t="n">
         <v>0.09520000000000001</v>
       </c>
+      <c r="J325" t="n">
+        <v>0.0482</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -7801,6 +8731,9 @@
       <c r="I326" t="n">
         <v>0.1071</v>
       </c>
+      <c r="J326" t="n">
+        <v>0.0401</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -7824,6 +8757,9 @@
       <c r="I327" t="n">
         <v>0.1038</v>
       </c>
+      <c r="J327" t="n">
+        <v>0.0561</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -7847,6 +8783,9 @@
       <c r="I328" t="n">
         <v>0.1017</v>
       </c>
+      <c r="J328" t="n">
+        <v>0.0392</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -7870,6 +8809,9 @@
       <c r="I329" t="n">
         <v>0.1002</v>
       </c>
+      <c r="J329" t="n">
+        <v>0.0558</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -7893,6 +8835,9 @@
       <c r="I330" t="n">
         <v>0.0965</v>
       </c>
+      <c r="J330" t="n">
+        <v>0.0553</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -7916,6 +8861,9 @@
       <c r="I331" t="n">
         <v>0.0999</v>
       </c>
+      <c r="J331" t="n">
+        <v>0.0285</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -7939,6 +8887,9 @@
       <c r="I332" t="n">
         <v>0.09660000000000001</v>
       </c>
+      <c r="J332" t="n">
+        <v>0.0508</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -7962,6 +8913,9 @@
       <c r="I333" t="n">
         <v>0.0914</v>
       </c>
+      <c r="J333" t="n">
+        <v>0.07140000000000001</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -7985,6 +8939,9 @@
       <c r="I334" t="n">
         <v>0.0992</v>
       </c>
+      <c r="J334" t="n">
+        <v>0.0398</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -8008,6 +8965,9 @@
       <c r="I335" t="n">
         <v>0.09669999999999999</v>
       </c>
+      <c r="J335" t="n">
+        <v>0.0322</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -8031,6 +8991,9 @@
       <c r="I336" t="n">
         <v>0.1047</v>
       </c>
+      <c r="J336" t="n">
+        <v>0.0294</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -8054,6 +9017,9 @@
       <c r="I337" t="n">
         <v>0.1067</v>
       </c>
+      <c r="J337" t="n">
+        <v>0.0354</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -8077,6 +9043,9 @@
       <c r="I338" t="n">
         <v>0.1036</v>
       </c>
+      <c r="J338" t="n">
+        <v>0.0385</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -8100,6 +9069,9 @@
       <c r="I339" t="n">
         <v>0.1094</v>
       </c>
+      <c r="J339" t="n">
+        <v>0.0335</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -8123,6 +9095,9 @@
       <c r="I340" t="n">
         <v>0.107</v>
       </c>
+      <c r="J340" t="n">
+        <v>0.0356</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -8146,6 +9121,9 @@
       <c r="I341" t="n">
         <v>0.1023</v>
       </c>
+      <c r="J341" t="n">
+        <v>0.0394</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -8169,6 +9147,9 @@
       <c r="I342" t="n">
         <v>0.1042</v>
       </c>
+      <c r="J342" t="n">
+        <v>0.042</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -8192,6 +9173,9 @@
       <c r="I343" t="n">
         <v>0.1042</v>
       </c>
+      <c r="J343" t="n">
+        <v>0.0272</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -8215,6 +9199,9 @@
       <c r="I344" t="n">
         <v>0.1025</v>
       </c>
+      <c r="J344" t="n">
+        <v>0.0345</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -8238,6 +9225,9 @@
       <c r="I345" t="n">
         <v>0.1064</v>
       </c>
+      <c r="J345" t="n">
+        <v>0.0417</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -8261,6 +9251,9 @@
       <c r="I346" t="n">
         <v>0.1087</v>
       </c>
+      <c r="J346" t="n">
+        <v>0.0375</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -8284,6 +9277,9 @@
       <c r="I347" t="n">
         <v>0.1025</v>
       </c>
+      <c r="J347" t="n">
+        <v>0.0414</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -8307,6 +9303,9 @@
       <c r="I348" t="n">
         <v>0.1041</v>
       </c>
+      <c r="J348" t="n">
+        <v>0.0342</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -8330,6 +9329,9 @@
       <c r="I349" t="n">
         <v>0.1087</v>
       </c>
+      <c r="J349" t="n">
+        <v>0.0432</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -8353,6 +9355,9 @@
       <c r="I350" t="n">
         <v>0.1041</v>
       </c>
+      <c r="J350" t="n">
+        <v>0.043</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -8376,6 +9381,9 @@
       <c r="I351" t="n">
         <v>0.1029</v>
       </c>
+      <c r="J351" t="n">
+        <v>0.0282</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -8399,6 +9407,9 @@
       <c r="I352" t="n">
         <v>0.1122</v>
       </c>
+      <c r="J352" t="n">
+        <v>0.0362</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -8422,6 +9433,9 @@
       <c r="I353" t="n">
         <v>0.1004</v>
       </c>
+      <c r="J353" t="n">
+        <v>0.0443</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -8445,6 +9459,9 @@
       <c r="I354" t="n">
         <v>0.1023</v>
       </c>
+      <c r="J354" t="n">
+        <v>0.0515</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -8468,6 +9485,9 @@
       <c r="I355" t="n">
         <v>0.1064</v>
       </c>
+      <c r="J355" t="n">
+        <v>0.0294</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -8491,6 +9511,9 @@
       <c r="I356" t="n">
         <v>0.107</v>
       </c>
+      <c r="J356" t="n">
+        <v>0.0305</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -8514,6 +9537,9 @@
       <c r="I357" t="n">
         <v>0.1093</v>
       </c>
+      <c r="J357" t="n">
+        <v>0.0321</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -8537,6 +9563,9 @@
       <c r="I358" t="n">
         <v>0.1152</v>
       </c>
+      <c r="J358" t="n">
+        <v>0.039</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -8560,6 +9589,9 @@
       <c r="I359" t="n">
         <v>0.1091</v>
       </c>
+      <c r="J359" t="n">
+        <v>0.0455</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -8583,6 +9615,9 @@
       <c r="I360" t="n">
         <v>0.1092</v>
       </c>
+      <c r="J360" t="n">
+        <v>0.032</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -8606,6 +9641,9 @@
       <c r="I361" t="n">
         <v>0.1062</v>
       </c>
+      <c r="J361" t="n">
+        <v>0.0382</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -8629,6 +9667,9 @@
       <c r="I362" t="n">
         <v>0.1017</v>
       </c>
+      <c r="J362" t="n">
+        <v>0.0446</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -8652,6 +9693,9 @@
       <c r="I363" t="n">
         <v>0.109</v>
       </c>
+      <c r="J363" t="n">
+        <v>0.0287</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -8675,6 +9719,9 @@
       <c r="I364" t="n">
         <v>0.1004</v>
       </c>
+      <c r="J364" t="n">
+        <v>0.0258</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -8698,6 +9745,9 @@
       <c r="I365" t="n">
         <v>0.1137</v>
       </c>
+      <c r="J365" t="n">
+        <v>0.0368</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -8721,6 +9771,9 @@
       <c r="I366" t="n">
         <v>0.1098</v>
       </c>
+      <c r="J366" t="n">
+        <v>0.0369</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -8744,6 +9797,9 @@
       <c r="I367" t="n">
         <v>0.1129</v>
       </c>
+      <c r="J367" t="n">
+        <v>0.0319</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -8767,6 +9823,9 @@
       <c r="I368" t="n">
         <v>0.1094</v>
       </c>
+      <c r="J368" t="n">
+        <v>0.0326</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -8790,6 +9849,9 @@
       <c r="I369" t="n">
         <v>0.109</v>
       </c>
+      <c r="J369" t="n">
+        <v>0.0381</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -8813,6 +9875,9 @@
       <c r="I370" t="n">
         <v>0.1095</v>
       </c>
+      <c r="J370" t="n">
+        <v>0.0297</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -8836,6 +9901,9 @@
       <c r="I371" t="n">
         <v>0.1062</v>
       </c>
+      <c r="J371" t="n">
+        <v>0.027</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -8859,6 +9927,9 @@
       <c r="I372" t="n">
         <v>0.1038</v>
       </c>
+      <c r="J372" t="n">
+        <v>0.0266</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -8882,6 +9953,9 @@
       <c r="I373" t="n">
         <v>0.1075</v>
       </c>
+      <c r="J373" t="n">
+        <v>0.0433</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -8905,6 +9979,9 @@
       <c r="I374" t="n">
         <v>0.1102</v>
       </c>
+      <c r="J374" t="n">
+        <v>0.0389</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -8928,6 +10005,9 @@
       <c r="I375" t="n">
         <v>0.1013</v>
       </c>
+      <c r="J375" t="n">
+        <v>0.0271</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -8951,6 +10031,9 @@
       <c r="I376" t="n">
         <v>0.105</v>
       </c>
+      <c r="J376" t="n">
+        <v>0.0274</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -8974,6 +10057,9 @@
       <c r="I377" t="n">
         <v>0.1024</v>
       </c>
+      <c r="J377" t="n">
+        <v>0.032</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -8997,6 +10083,9 @@
       <c r="I378" t="n">
         <v>0.1017</v>
       </c>
+      <c r="J378" t="n">
+        <v>0.0393</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -9020,6 +10109,9 @@
       <c r="I379" t="n">
         <v>0.1078</v>
       </c>
+      <c r="J379" t="n">
+        <v>0.0429</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -9043,6 +10135,9 @@
       <c r="I380" t="n">
         <v>0.1036</v>
       </c>
+      <c r="J380" t="n">
+        <v>0.0336</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -9066,6 +10161,9 @@
       <c r="I381" t="n">
         <v>0.1055</v>
       </c>
+      <c r="J381" t="n">
+        <v>0.0257</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -9089,6 +10187,9 @@
       <c r="I382" t="n">
         <v>0.1053</v>
       </c>
+      <c r="J382" t="n">
+        <v>0.0257</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -9112,6 +10213,9 @@
       <c r="I383" t="n">
         <v>0.1031</v>
       </c>
+      <c r="J383" t="n">
+        <v>0.0262</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -9135,6 +10239,9 @@
       <c r="I384" t="n">
         <v>0.1075</v>
       </c>
+      <c r="J384" t="n">
+        <v>0.0275</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -9158,6 +10265,9 @@
       <c r="I385" t="n">
         <v>0.1096</v>
       </c>
+      <c r="J385" t="n">
+        <v>0.0242</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -9181,6 +10291,9 @@
       <c r="I386" t="n">
         <v>0.1143</v>
       </c>
+      <c r="J386" t="n">
+        <v>0.028</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -9204,6 +10317,9 @@
       <c r="I387" t="n">
         <v>0.1039</v>
       </c>
+      <c r="J387" t="n">
+        <v>0.0338</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -9227,6 +10343,9 @@
       <c r="I388" t="n">
         <v>0.1091</v>
       </c>
+      <c r="J388" t="n">
+        <v>0.0229</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -9250,6 +10369,9 @@
       <c r="I389" t="n">
         <v>0.1013</v>
       </c>
+      <c r="J389" t="n">
+        <v>0.0264</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -9273,6 +10395,9 @@
       <c r="I390" t="n">
         <v>0.1079</v>
       </c>
+      <c r="J390" t="n">
+        <v>0.027</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -9296,6 +10421,9 @@
       <c r="I391" t="n">
         <v>0.0989</v>
       </c>
+      <c r="J391" t="n">
+        <v>0.0313</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -9319,6 +10447,9 @@
       <c r="I392" t="n">
         <v>0.1047</v>
       </c>
+      <c r="J392" t="n">
+        <v>0.0238</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -9342,6 +10473,9 @@
       <c r="I393" t="n">
         <v>0.1025</v>
       </c>
+      <c r="J393" t="n">
+        <v>0.0217</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -9365,6 +10499,9 @@
       <c r="I394" t="n">
         <v>0.1004</v>
       </c>
+      <c r="J394" t="n">
+        <v>0.0193</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -9388,6 +10525,9 @@
       <c r="I395" t="n">
         <v>0.1001</v>
       </c>
+      <c r="J395" t="n">
+        <v>0.0251</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -9411,6 +10551,9 @@
       <c r="I396" t="n">
         <v>0.109</v>
       </c>
+      <c r="J396" t="n">
+        <v>0.027</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -9434,6 +10577,9 @@
       <c r="I397" t="n">
         <v>0.1085</v>
       </c>
+      <c r="J397" t="n">
+        <v>0.024</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -9457,6 +10603,9 @@
       <c r="I398" t="n">
         <v>0.1079</v>
       </c>
+      <c r="J398" t="n">
+        <v>0.0319</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -9480,6 +10629,9 @@
       <c r="I399" t="n">
         <v>0.1023</v>
       </c>
+      <c r="J399" t="n">
+        <v>0.0279</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -9503,6 +10655,9 @@
       <c r="I400" t="n">
         <v>0.1054</v>
       </c>
+      <c r="J400" t="n">
+        <v>0.0276</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -9526,6 +10681,9 @@
       <c r="I401" t="n">
         <v>0.1044</v>
       </c>
+      <c r="J401" t="n">
+        <v>0.0218</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -9549,6 +10707,9 @@
       <c r="I402" t="n">
         <v>0.1009</v>
       </c>
+      <c r="J402" t="n">
+        <v>0.0215</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -9572,6 +10733,9 @@
       <c r="I403" t="n">
         <v>0.109</v>
       </c>
+      <c r="J403" t="n">
+        <v>0.019</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -9595,6 +10759,9 @@
       <c r="I404" t="n">
         <v>0.1049</v>
       </c>
+      <c r="J404" t="n">
+        <v>0.0241</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -9618,6 +10785,9 @@
       <c r="I405" t="n">
         <v>0.1052</v>
       </c>
+      <c r="J405" t="n">
+        <v>0.0263</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -9641,6 +10811,9 @@
       <c r="I406" t="n">
         <v>0.1057</v>
       </c>
+      <c r="J406" t="n">
+        <v>0.0262</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -9664,6 +10837,9 @@
       <c r="I407" t="n">
         <v>0.1032</v>
       </c>
+      <c r="J407" t="n">
+        <v>0.0338</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -9687,6 +10863,9 @@
       <c r="I408" t="n">
         <v>0.1052</v>
       </c>
+      <c r="J408" t="n">
+        <v>0.0286</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -9710,6 +10889,9 @@
       <c r="I409" t="n">
         <v>0.1071</v>
       </c>
+      <c r="J409" t="n">
+        <v>0.0255</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -9733,6 +10915,9 @@
       <c r="I410" t="n">
         <v>0.1138</v>
       </c>
+      <c r="J410" t="n">
+        <v>0.0225</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -9756,6 +10941,9 @@
       <c r="I411" t="n">
         <v>0.1059</v>
       </c>
+      <c r="J411" t="n">
+        <v>0.0247</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -9779,6 +10967,9 @@
       <c r="I412" t="n">
         <v>0.1004</v>
       </c>
+      <c r="J412" t="n">
+        <v>0.0217</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -9802,6 +10993,9 @@
       <c r="I413" t="n">
         <v>0.1041</v>
       </c>
+      <c r="J413" t="n">
+        <v>0.028</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -9825,6 +11019,9 @@
       <c r="I414" t="n">
         <v>0.1</v>
       </c>
+      <c r="J414" t="n">
+        <v>0.0238</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -9847,6 +11044,9 @@
       </c>
       <c r="I415" t="n">
         <v>0.102</v>
+      </c>
+      <c r="J415" t="n">
+        <v>0.0239</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J415"/>
+  <dimension ref="A1:K415"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="14.33203125" customWidth="1" style="7" min="1" max="1"/>
@@ -602,6 +602,9 @@
       <c r="J5" t="n">
         <v>0.084325</v>
       </c>
+      <c r="K5" t="n">
+        <v>0.1951533333333333</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -628,6 +631,9 @@
       <c r="J6" t="n">
         <v>0.2527071428571429</v>
       </c>
+      <c r="K6" t="n">
+        <v>0.21471</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -654,6 +660,9 @@
       <c r="J7" t="n">
         <v>0.2572611111111111</v>
       </c>
+      <c r="K7" t="n">
+        <v>0.2510296296296297</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -680,6 +689,9 @@
       <c r="J8" t="n">
         <v>0.3903916666666667</v>
       </c>
+      <c r="K8" t="n">
+        <v>0.3639933333333333</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -706,6 +718,9 @@
       <c r="J9" t="n">
         <v>0.4041571428571428</v>
       </c>
+      <c r="K9" t="n">
+        <v>0.427447619047619</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -732,6 +747,9 @@
       <c r="J10" t="n">
         <v>0.509775</v>
       </c>
+      <c r="K10" t="n">
+        <v>0.5213411764705882</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -758,6 +776,9 @@
       <c r="J11" t="n">
         <v>0.5659884615384616</v>
       </c>
+      <c r="K11" t="n">
+        <v>0.6026611111111111</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -784,6 +805,9 @@
       <c r="J12" t="n">
         <v>0.6995205882352941</v>
       </c>
+      <c r="K12" t="n">
+        <v>0.6553483870967741</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -810,6 +834,9 @@
       <c r="J13" t="n">
         <v>0.646334375</v>
       </c>
+      <c r="K13" t="n">
+        <v>0.7062999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -836,6 +863,9 @@
       <c r="J14" t="n">
         <v>0.7051977272727273</v>
       </c>
+      <c r="K14" t="n">
+        <v>0.7733886363636363</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -862,6 +892,9 @@
       <c r="J15" t="n">
         <v>0.7101333333333334</v>
       </c>
+      <c r="K15" t="n">
+        <v>0.8058658536585366</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -888,6 +921,9 @@
       <c r="J16" t="n">
         <v>0.7276179487179487</v>
       </c>
+      <c r="K16" t="n">
+        <v>0.774</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -914,6 +950,9 @@
       <c r="J17" t="n">
         <v>0.7821196078431373</v>
       </c>
+      <c r="K17" t="n">
+        <v>0.7800034482758622</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -940,6 +979,9 @@
       <c r="J18" t="n">
         <v>0.8010444444444444</v>
       </c>
+      <c r="K18" t="n">
+        <v>0.8323</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -966,6 +1008,9 @@
       <c r="J19" t="n">
         <v>0.777974358974359</v>
       </c>
+      <c r="K19" t="n">
+        <v>0.7548035714285714</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -992,6 +1037,9 @@
       <c r="J20" t="n">
         <v>0.674482</v>
       </c>
+      <c r="K20" t="n">
+        <v>0.8140499999999999</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1018,6 +1066,9 @@
       <c r="J21" t="n">
         <v>0.6924926829268293</v>
       </c>
+      <c r="K21" t="n">
+        <v>0.8498490909090908</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1044,6 +1095,9 @@
       <c r="J22" t="n">
         <v>0.786239393939394</v>
       </c>
+      <c r="K22" t="n">
+        <v>0.8427045454545453</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1070,6 +1124,9 @@
       <c r="J23" t="n">
         <v>0.8290617647058824</v>
       </c>
+      <c r="K23" t="n">
+        <v>0.8532945945945946</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1096,6 +1153,9 @@
       <c r="J24" t="n">
         <v>0.7833928571428571</v>
       </c>
+      <c r="K24" t="n">
+        <v>0.8620846153846153</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1122,6 +1182,9 @@
       <c r="J25" t="n">
         <v>0.7791833333333333</v>
       </c>
+      <c r="K25" t="n">
+        <v>0.8343942307692308</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1148,6 +1211,9 @@
       <c r="J26" t="n">
         <v>0.8023947368421053</v>
       </c>
+      <c r="K26" t="n">
+        <v>0.85884</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1174,6 +1240,9 @@
       <c r="J27" t="n">
         <v>0.794712</v>
       </c>
+      <c r="K27" t="n">
+        <v>0.8782936170212765</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1200,6 +1269,9 @@
       <c r="J28" t="n">
         <v>0.8642666666666668</v>
       </c>
+      <c r="K28" t="n">
+        <v>0.855548076923077</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1226,6 +1298,9 @@
       <c r="J29" t="n">
         <v>0.8025583333333333</v>
       </c>
+      <c r="K29" t="n">
+        <v>0.8577343750000002</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1252,6 +1327,9 @@
       <c r="J30" t="n">
         <v>0.841264864864865</v>
       </c>
+      <c r="K30" t="n">
+        <v>0.8817441860465116</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1278,6 +1356,9 @@
       <c r="J31" t="n">
         <v>0.8277212121212121</v>
       </c>
+      <c r="K31" t="n">
+        <v>0.8863066666666666</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1304,6 +1385,9 @@
       <c r="J32" t="n">
         <v>0.8714515151515152</v>
       </c>
+      <c r="K32" t="n">
+        <v>0.8715184210526316</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1330,6 +1414,9 @@
       <c r="J33" t="n">
         <v>0.8257514285714286</v>
       </c>
+      <c r="K33" t="n">
+        <v>0.8748904761904763</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1356,6 +1443,9 @@
       <c r="J34" t="n">
         <v>0.713465</v>
       </c>
+      <c r="K34" t="n">
+        <v>0.8967526315789476</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1382,6 +1472,9 @@
       <c r="J35" t="n">
         <v>0.8098421052631579</v>
       </c>
+      <c r="K35" t="n">
+        <v>0.8482499999999999</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1408,6 +1501,9 @@
       <c r="J36" t="n">
         <v>0.8045666666666667</v>
       </c>
+      <c r="K36" t="n">
+        <v>0.8702771428571429</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1434,6 +1530,9 @@
       <c r="J37" t="n">
         <v>0.7566081081081082</v>
       </c>
+      <c r="K37" t="n">
+        <v>0.8849851851851852</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1460,6 +1559,9 @@
       <c r="J38" t="n">
         <v>0.8094117647058825</v>
       </c>
+      <c r="K38" t="n">
+        <v>0.873328125</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1486,6 +1588,9 @@
       <c r="J39" t="n">
         <v>0.857563043478261</v>
       </c>
+      <c r="K39" t="n">
+        <v>0.864854716981132</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1512,6 +1617,9 @@
       <c r="J40" t="n">
         <v>0.8153321428571428</v>
       </c>
+      <c r="K40" t="n">
+        <v>0.8815781249999999</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1538,6 +1646,9 @@
       <c r="J41" t="n">
         <v>0.83691875</v>
       </c>
+      <c r="K41" t="n">
+        <v>0.8889037735849057</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1564,6 +1675,9 @@
       <c r="J42" t="n">
         <v>0.8283978260869567</v>
       </c>
+      <c r="K42" t="n">
+        <v>0.8704055555555557</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1590,6 +1704,9 @@
       <c r="J43" t="n">
         <v>0.8282827586206897</v>
       </c>
+      <c r="K43" t="n">
+        <v>0.9067980769230769</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1616,6 +1733,9 @@
       <c r="J44" t="n">
         <v>0.8807318181818182</v>
       </c>
+      <c r="K44" t="n">
+        <v>0.8863294117647059</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1642,6 +1762,9 @@
       <c r="J45" t="n">
         <v>0.8044952380952382</v>
       </c>
+      <c r="K45" t="n">
+        <v>0.9259891891891893</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1668,6 +1791,9 @@
       <c r="J46" t="n">
         <v>0.8225977777777778</v>
       </c>
+      <c r="K46" t="n">
+        <v>0.8958088235294117</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1694,6 +1820,9 @@
       <c r="J47" t="n">
         <v>0.8230216216216216</v>
       </c>
+      <c r="K47" t="n">
+        <v>0.8954203703703704</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1720,6 +1849,9 @@
       <c r="J48" t="n">
         <v>0.8747666666666668</v>
       </c>
+      <c r="K48" t="n">
+        <v>0.9098777777777778</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -1746,6 +1878,9 @@
       <c r="J49" t="n">
         <v>0.8695774193548389</v>
       </c>
+      <c r="K49" t="n">
+        <v>0.8730687500000002</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1772,6 +1907,9 @@
       <c r="J50" t="n">
         <v>0.8196439024390245</v>
       </c>
+      <c r="K50" t="n">
+        <v>0.8753659574468085</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -1798,6 +1936,9 @@
       <c r="J51" t="n">
         <v>0.8887681818181818</v>
       </c>
+      <c r="K51" t="n">
+        <v>0.8415500000000001</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1824,6 +1965,9 @@
       <c r="J52" t="n">
         <v>0.8855155555555555</v>
       </c>
+      <c r="K52" t="n">
+        <v>0.914186111111111</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1850,6 +1994,9 @@
       <c r="J53" t="n">
         <v>0.76078</v>
       </c>
+      <c r="K53" t="n">
+        <v>0.8870527777777778</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -1876,6 +2023,9 @@
       <c r="J54" t="n">
         <v>0.8361736842105261</v>
       </c>
+      <c r="K54" t="n">
+        <v>0.8897145833333333</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -1902,6 +2052,9 @@
       <c r="J55" t="n">
         <v>0.8737023809523811</v>
       </c>
+      <c r="K55" t="n">
+        <v>0.8873117647058822</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -1928,6 +2081,9 @@
       <c r="J56" t="n">
         <v>0.9107047619047619</v>
       </c>
+      <c r="K56" t="n">
+        <v>0.8893343750000001</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -1954,6 +2110,9 @@
       <c r="J57" t="n">
         <v>0.8687533333333335</v>
       </c>
+      <c r="K57" t="n">
+        <v>0.8669575757575759</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -1980,6 +2139,9 @@
       <c r="J58" t="n">
         <v>0.842967857142857</v>
       </c>
+      <c r="K58" t="n">
+        <v>0.881057894736842</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -2006,6 +2168,9 @@
       <c r="J59" t="n">
         <v>0.8244981132075472</v>
       </c>
+      <c r="K59" t="n">
+        <v>0.9435074074074075</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -2032,6 +2197,9 @@
       <c r="J60" t="n">
         <v>0.8236529411764707</v>
       </c>
+      <c r="K60" t="n">
+        <v>0.9162809523809524</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -2058,6 +2226,9 @@
       <c r="J61" t="n">
         <v>0.8588763157894738</v>
       </c>
+      <c r="K61" t="n">
+        <v>0.9152452380952381</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -2084,6 +2255,9 @@
       <c r="J62" t="n">
         <v>0.8965612903225807</v>
       </c>
+      <c r="K62" t="n">
+        <v>0.8960166666666667</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -2110,6 +2284,9 @@
       <c r="J63" t="n">
         <v>0.8717281250000001</v>
       </c>
+      <c r="K63" t="n">
+        <v>0.8804823529411765</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -2136,6 +2313,9 @@
       <c r="J64" t="n">
         <v>0.8515315789473685</v>
       </c>
+      <c r="K64" t="n">
+        <v>0.8925510204081633</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -2162,6 +2342,9 @@
       <c r="J65" t="n">
         <v>0.8058722222222223</v>
       </c>
+      <c r="K65" t="n">
+        <v>0.905932258064516</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -2188,6 +2371,9 @@
       <c r="J66" t="n">
         <v>0.8136958333333334</v>
       </c>
+      <c r="K66" t="n">
+        <v>0.8808489795918367</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -2214,6 +2400,9 @@
       <c r="J67" t="n">
         <v>0.8007903225806452</v>
       </c>
+      <c r="K67" t="n">
+        <v>0.8596228571428572</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -2240,6 +2429,9 @@
       <c r="J68" t="n">
         <v>0.8431424999999999</v>
       </c>
+      <c r="K68" t="n">
+        <v>0.8948968749999999</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -2266,6 +2458,9 @@
       <c r="J69" t="n">
         <v>0.8015155172413793</v>
       </c>
+      <c r="K69" t="n">
+        <v>0.8754760869565218</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -2292,6 +2487,9 @@
       <c r="J70" t="n">
         <v>0.8374625</v>
       </c>
+      <c r="K70" t="n">
+        <v>0.8865</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -2318,6 +2516,9 @@
       <c r="J71" t="n">
         <v>0.812629268292683</v>
       </c>
+      <c r="K71" t="n">
+        <v>0.9064321428571428</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -2344,6 +2545,9 @@
       <c r="J72" t="n">
         <v>0.8550695652173913</v>
       </c>
+      <c r="K72" t="n">
+        <v>0.9231083333333334</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -2370,6 +2574,9 @@
       <c r="J73" t="n">
         <v>0.7988055555555555</v>
       </c>
+      <c r="K73" t="n">
+        <v>0.8927354838709677</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -2396,6 +2603,9 @@
       <c r="J74" t="n">
         <v>0.8802259259259259</v>
       </c>
+      <c r="K74" t="n">
+        <v>0.9336589743589744</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -2422,6 +2632,9 @@
       <c r="J75" t="n">
         <v>0.8824487804878048</v>
       </c>
+      <c r="K75" t="n">
+        <v>0.9086173913043478</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -2448,6 +2661,9 @@
       <c r="J76" t="n">
         <v>0.8494771428571427</v>
       </c>
+      <c r="K76" t="n">
+        <v>0.9154605263157896</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -2474,6 +2690,9 @@
       <c r="J77" t="n">
         <v>0.8099722222222222</v>
       </c>
+      <c r="K77" t="n">
+        <v>0.8871681818181817</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -2500,6 +2719,9 @@
       <c r="J78" t="n">
         <v>0.8352948717948717</v>
       </c>
+      <c r="K78" t="n">
+        <v>0.8978333333333333</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -2526,6 +2748,9 @@
       <c r="J79" t="n">
         <v>0.7850076923076924</v>
       </c>
+      <c r="K79" t="n">
+        <v>0.8927047619047618</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -2552,6 +2777,9 @@
       <c r="J80" t="n">
         <v>0.8836761904761905</v>
       </c>
+      <c r="K80" t="n">
+        <v>0.8844783783783785</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -2578,6 +2806,9 @@
       <c r="J81" t="n">
         <v>0.7918697674418603</v>
       </c>
+      <c r="K81" t="n">
+        <v>0.9270149999999999</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -2604,6 +2835,9 @@
       <c r="J82" t="n">
         <v>0.8031800000000001</v>
       </c>
+      <c r="K82" t="n">
+        <v>0.86255</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -2630,6 +2864,9 @@
       <c r="J83" t="n">
         <v>0.8663222222222221</v>
       </c>
+      <c r="K83" t="n">
+        <v>0.898957575757576</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -2656,6 +2893,9 @@
       <c r="J84" t="n">
         <v>0.8505545454545456</v>
       </c>
+      <c r="K84" t="n">
+        <v>0.9068680851063829</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -2682,6 +2922,9 @@
       <c r="J85" t="n">
         <v>0.8456575757575757</v>
       </c>
+      <c r="K85" t="n">
+        <v>0.8962117647058824</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -2708,6 +2951,9 @@
       <c r="J86" t="n">
         <v>0.8337040816326531</v>
       </c>
+      <c r="K86" t="n">
+        <v>0.8998302325581395</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -2734,6 +2980,9 @@
       <c r="J87" t="n">
         <v>0.8017185185185185</v>
       </c>
+      <c r="K87" t="n">
+        <v>0.894243103448276</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -2760,6 +3009,9 @@
       <c r="J88" t="n">
         <v>0.8196030303030303</v>
       </c>
+      <c r="K88" t="n">
+        <v>0.9006134615384617</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -2786,6 +3038,9 @@
       <c r="J89" t="n">
         <v>0.8074947368421052</v>
       </c>
+      <c r="K89" t="n">
+        <v>0.8897395348837212</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -2812,6 +3067,9 @@
       <c r="J90" t="n">
         <v>0.781253125</v>
       </c>
+      <c r="K90" t="n">
+        <v>0.9146222222222222</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -2838,6 +3096,9 @@
       <c r="J91" t="n">
         <v>0.8277413793103449</v>
       </c>
+      <c r="K91" t="n">
+        <v>0.8980471698113207</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -2864,6 +3125,9 @@
       <c r="J92" t="n">
         <v>0.8489088888888888</v>
       </c>
+      <c r="K92" t="n">
+        <v>0.8979479166666667</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -2890,6 +3154,9 @@
       <c r="J93" t="n">
         <v>0.8572111111111111</v>
       </c>
+      <c r="K93" t="n">
+        <v>0.8965212765957447</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -2916,6 +3183,9 @@
       <c r="J94" t="n">
         <v>0.7635352941176471</v>
       </c>
+      <c r="K94" t="n">
+        <v>0.897338888888889</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -2942,6 +3212,9 @@
       <c r="J95" t="n">
         <v>0.8265319999999999</v>
       </c>
+      <c r="K95" t="n">
+        <v>0.8996</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -2968,6 +3241,9 @@
       <c r="J96" t="n">
         <v>0.8006685714285714</v>
       </c>
+      <c r="K96" t="n">
+        <v>0.8894853658536587</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -2994,6 +3270,9 @@
       <c r="J97" t="n">
         <v>0.7916</v>
       </c>
+      <c r="K97" t="n">
+        <v>0.8845500000000001</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -3020,6 +3299,9 @@
       <c r="J98" t="n">
         <v>0.8065529411764706</v>
       </c>
+      <c r="K98" t="n">
+        <v>0.8764833333333334</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -3046,6 +3328,9 @@
       <c r="J99" t="n">
         <v>0.8485624999999999</v>
       </c>
+      <c r="K99" t="n">
+        <v>0.8986862068965518</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -3072,6 +3357,9 @@
       <c r="J100" t="n">
         <v>0.8383518518518519</v>
       </c>
+      <c r="K100" t="n">
+        <v>0.9244617021276595</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -3098,6 +3386,9 @@
       <c r="J101" t="n">
         <v>0.8121136363636364</v>
       </c>
+      <c r="K101" t="n">
+        <v>0.9070520833333334</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -3124,6 +3415,9 @@
       <c r="J102" t="n">
         <v>0.8871957446808511</v>
       </c>
+      <c r="K102" t="n">
+        <v>0.9168692307692308</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -3150,6 +3444,9 @@
       <c r="J103" t="n">
         <v>0.8266685714285714</v>
       </c>
+      <c r="K103" t="n">
+        <v>0.9233956521739131</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -3175,6 +3472,9 @@
       </c>
       <c r="J104" t="n">
         <v>0.8704032258064517</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.8970476190476191</v>
       </c>
     </row>
     <row r="106">
@@ -3226,6 +3526,9 @@
       <c r="J108" t="n">
         <v>0.8</v>
       </c>
+      <c r="K108" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -3252,6 +3555,9 @@
       <c r="J109" t="n">
         <v>0.7692307692307693</v>
       </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -3278,6 +3584,9 @@
       <c r="J110" t="n">
         <v>1</v>
       </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -3304,6 +3613,9 @@
       <c r="J111" t="n">
         <v>0.75</v>
       </c>
+      <c r="K111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -3330,6 +3642,9 @@
       <c r="J112" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="K112" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -3356,6 +3671,9 @@
       <c r="J113" t="n">
         <v>0.5</v>
       </c>
+      <c r="K113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -3382,6 +3700,9 @@
       <c r="J114" t="n">
         <v>1</v>
       </c>
+      <c r="K114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -3408,6 +3729,9 @@
       <c r="J115" t="n">
         <v>1</v>
       </c>
+      <c r="K115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -3434,6 +3758,9 @@
       <c r="J116" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -3460,6 +3787,9 @@
       <c r="J117" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="K117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -3486,6 +3816,9 @@
       <c r="J118" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="K118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -3512,6 +3845,9 @@
       <c r="J119" t="n">
         <v>1</v>
       </c>
+      <c r="K119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -3538,6 +3874,9 @@
       <c r="J120" t="n">
         <v>1</v>
       </c>
+      <c r="K120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -3564,6 +3903,9 @@
       <c r="J121" t="n">
         <v>1</v>
       </c>
+      <c r="K121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -3590,6 +3932,9 @@
       <c r="J122" t="n">
         <v>1</v>
       </c>
+      <c r="K122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -3616,6 +3961,9 @@
       <c r="J123" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="K123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -3642,6 +3990,9 @@
       <c r="J124" t="n">
         <v>1</v>
       </c>
+      <c r="K124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -3668,6 +4019,9 @@
       <c r="J125" t="n">
         <v>1</v>
       </c>
+      <c r="K125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -3694,6 +4048,9 @@
       <c r="J126" t="n">
         <v>1</v>
       </c>
+      <c r="K126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -3720,6 +4077,9 @@
       <c r="J127" t="n">
         <v>1</v>
       </c>
+      <c r="K127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -3746,6 +4106,9 @@
       <c r="J128" t="n">
         <v>1</v>
       </c>
+      <c r="K128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -3772,6 +4135,9 @@
       <c r="J129" t="n">
         <v>1</v>
       </c>
+      <c r="K129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -3798,6 +4164,9 @@
       <c r="J130" t="n">
         <v>1</v>
       </c>
+      <c r="K130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -3824,6 +4193,9 @@
       <c r="J131" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="K131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -3850,6 +4222,9 @@
       <c r="J132" t="n">
         <v>1</v>
       </c>
+      <c r="K132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -3876,6 +4251,9 @@
       <c r="J133" t="n">
         <v>1</v>
       </c>
+      <c r="K133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -3902,6 +4280,9 @@
       <c r="J134" t="n">
         <v>1</v>
       </c>
+      <c r="K134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -3928,6 +4309,9 @@
       <c r="J135" t="n">
         <v>1</v>
       </c>
+      <c r="K135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -3954,6 +4338,9 @@
       <c r="J136" t="n">
         <v>1</v>
       </c>
+      <c r="K136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -3980,6 +4367,9 @@
       <c r="J137" t="n">
         <v>1</v>
       </c>
+      <c r="K137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -4006,6 +4396,9 @@
       <c r="J138" t="n">
         <v>1</v>
       </c>
+      <c r="K138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -4032,6 +4425,9 @@
       <c r="J139" t="n">
         <v>1</v>
       </c>
+      <c r="K139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -4058,6 +4454,9 @@
       <c r="J140" t="n">
         <v>1</v>
       </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -4084,6 +4483,9 @@
       <c r="J141" t="n">
         <v>1</v>
       </c>
+      <c r="K141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -4110,6 +4512,9 @@
       <c r="J142" t="n">
         <v>1</v>
       </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -4136,6 +4541,9 @@
       <c r="J143" t="n">
         <v>1</v>
       </c>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -4162,6 +4570,9 @@
       <c r="J144" t="n">
         <v>1</v>
       </c>
+      <c r="K144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -4188,6 +4599,9 @@
       <c r="J145" t="n">
         <v>1</v>
       </c>
+      <c r="K145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -4214,6 +4628,9 @@
       <c r="J146" t="n">
         <v>1</v>
       </c>
+      <c r="K146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -4240,6 +4657,9 @@
       <c r="J147" t="n">
         <v>1</v>
       </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -4266,6 +4686,9 @@
       <c r="J148" t="n">
         <v>1</v>
       </c>
+      <c r="K148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -4292,6 +4715,9 @@
       <c r="J149" t="n">
         <v>1</v>
       </c>
+      <c r="K149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -4318,6 +4744,9 @@
       <c r="J150" t="n">
         <v>1</v>
       </c>
+      <c r="K150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -4344,6 +4773,9 @@
       <c r="J151" t="n">
         <v>1</v>
       </c>
+      <c r="K151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -4370,6 +4802,9 @@
       <c r="J152" t="n">
         <v>1</v>
       </c>
+      <c r="K152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -4396,6 +4831,9 @@
       <c r="J153" t="n">
         <v>1</v>
       </c>
+      <c r="K153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -4422,6 +4860,9 @@
       <c r="J154" t="n">
         <v>1</v>
       </c>
+      <c r="K154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -4448,6 +4889,9 @@
       <c r="J155" t="n">
         <v>1</v>
       </c>
+      <c r="K155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -4474,6 +4918,9 @@
       <c r="J156" t="n">
         <v>1</v>
       </c>
+      <c r="K156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -4500,6 +4947,9 @@
       <c r="J157" t="n">
         <v>1</v>
       </c>
+      <c r="K157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -4526,6 +4976,9 @@
       <c r="J158" t="n">
         <v>1</v>
       </c>
+      <c r="K158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -4552,6 +5005,9 @@
       <c r="J159" t="n">
         <v>1</v>
       </c>
+      <c r="K159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -4578,6 +5034,9 @@
       <c r="J160" t="n">
         <v>1</v>
       </c>
+      <c r="K160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -4604,6 +5063,9 @@
       <c r="J161" t="n">
         <v>1</v>
       </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -4630,6 +5092,9 @@
       <c r="J162" t="n">
         <v>1</v>
       </c>
+      <c r="K162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -4656,6 +5121,9 @@
       <c r="J163" t="n">
         <v>1</v>
       </c>
+      <c r="K163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -4682,6 +5150,9 @@
       <c r="J164" t="n">
         <v>1</v>
       </c>
+      <c r="K164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -4708,6 +5179,9 @@
       <c r="J165" t="n">
         <v>1</v>
       </c>
+      <c r="K165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -4734,6 +5208,9 @@
       <c r="J166" t="n">
         <v>1</v>
       </c>
+      <c r="K166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -4760,6 +5237,9 @@
       <c r="J167" t="n">
         <v>1</v>
       </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -4786,6 +5266,9 @@
       <c r="J168" t="n">
         <v>1</v>
       </c>
+      <c r="K168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -4812,6 +5295,9 @@
       <c r="J169" t="n">
         <v>1</v>
       </c>
+      <c r="K169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -4838,6 +5324,9 @@
       <c r="J170" t="n">
         <v>1</v>
       </c>
+      <c r="K170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -4864,6 +5353,9 @@
       <c r="J171" t="n">
         <v>1</v>
       </c>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -4890,6 +5382,9 @@
       <c r="J172" t="n">
         <v>1</v>
       </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -4916,6 +5411,9 @@
       <c r="J173" t="n">
         <v>1</v>
       </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -4942,6 +5440,9 @@
       <c r="J174" t="n">
         <v>1</v>
       </c>
+      <c r="K174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -4968,6 +5469,9 @@
       <c r="J175" t="n">
         <v>1</v>
       </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -4994,6 +5498,9 @@
       <c r="J176" t="n">
         <v>1</v>
       </c>
+      <c r="K176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -5020,6 +5527,9 @@
       <c r="J177" t="n">
         <v>1</v>
       </c>
+      <c r="K177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -5046,6 +5556,9 @@
       <c r="J178" t="n">
         <v>1</v>
       </c>
+      <c r="K178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -5072,6 +5585,9 @@
       <c r="J179" t="n">
         <v>1</v>
       </c>
+      <c r="K179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -5098,6 +5614,9 @@
       <c r="J180" t="n">
         <v>1</v>
       </c>
+      <c r="K180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -5124,6 +5643,9 @@
       <c r="J181" t="n">
         <v>1</v>
       </c>
+      <c r="K181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -5150,6 +5672,9 @@
       <c r="J182" t="n">
         <v>1</v>
       </c>
+      <c r="K182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -5176,6 +5701,9 @@
       <c r="J183" t="n">
         <v>1</v>
       </c>
+      <c r="K183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -5202,6 +5730,9 @@
       <c r="J184" t="n">
         <v>1</v>
       </c>
+      <c r="K184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -5228,6 +5759,9 @@
       <c r="J185" t="n">
         <v>1</v>
       </c>
+      <c r="K185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -5254,6 +5788,9 @@
       <c r="J186" t="n">
         <v>1</v>
       </c>
+      <c r="K186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -5280,6 +5817,9 @@
       <c r="J187" t="n">
         <v>1</v>
       </c>
+      <c r="K187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -5306,6 +5846,9 @@
       <c r="J188" t="n">
         <v>1</v>
       </c>
+      <c r="K188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -5332,6 +5875,9 @@
       <c r="J189" t="n">
         <v>1</v>
       </c>
+      <c r="K189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -5358,6 +5904,9 @@
       <c r="J190" t="n">
         <v>1</v>
       </c>
+      <c r="K190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -5384,6 +5933,9 @@
       <c r="J191" t="n">
         <v>1</v>
       </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -5410,6 +5962,9 @@
       <c r="J192" t="n">
         <v>1</v>
       </c>
+      <c r="K192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -5436,6 +5991,9 @@
       <c r="J193" t="n">
         <v>1</v>
       </c>
+      <c r="K193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -5462,6 +6020,9 @@
       <c r="J194" t="n">
         <v>1</v>
       </c>
+      <c r="K194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -5488,6 +6049,9 @@
       <c r="J195" t="n">
         <v>1</v>
       </c>
+      <c r="K195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -5514,6 +6078,9 @@
       <c r="J196" t="n">
         <v>1</v>
       </c>
+      <c r="K196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -5540,6 +6107,9 @@
       <c r="J197" t="n">
         <v>1</v>
       </c>
+      <c r="K197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -5566,6 +6136,9 @@
       <c r="J198" t="n">
         <v>1</v>
       </c>
+      <c r="K198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -5592,6 +6165,9 @@
       <c r="J199" t="n">
         <v>1</v>
       </c>
+      <c r="K199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -5618,6 +6194,9 @@
       <c r="J200" t="n">
         <v>1</v>
       </c>
+      <c r="K200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -5644,6 +6223,9 @@
       <c r="J201" t="n">
         <v>1</v>
       </c>
+      <c r="K201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -5670,6 +6252,9 @@
       <c r="J202" t="n">
         <v>1</v>
       </c>
+      <c r="K202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -5696,6 +6281,9 @@
       <c r="J203" t="n">
         <v>1</v>
       </c>
+      <c r="K203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -5722,6 +6310,9 @@
       <c r="J204" t="n">
         <v>1</v>
       </c>
+      <c r="K204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -5748,6 +6339,9 @@
       <c r="J205" t="n">
         <v>1</v>
       </c>
+      <c r="K205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -5774,6 +6368,9 @@
       <c r="J206" t="n">
         <v>1</v>
       </c>
+      <c r="K206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -5798,6 +6395,9 @@
         <v>1</v>
       </c>
       <c r="J207" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5850,6 +6450,9 @@
       <c r="J212" t="n">
         <v>0.8452</v>
       </c>
+      <c r="K212" t="n">
+        <v>0.8877125</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -5876,6 +6479,9 @@
       <c r="J213" t="n">
         <v>0.6774625000000001</v>
       </c>
+      <c r="K213" t="n">
+        <v>0.8949142857142858</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -5902,6 +6508,9 @@
       <c r="J214" t="n">
         <v>0.7674111111111112</v>
       </c>
+      <c r="K214" t="n">
+        <v>0.8497166666666667</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -5928,6 +6537,9 @@
       <c r="J215" t="n">
         <v>0.7663500000000001</v>
       </c>
+      <c r="K215" t="n">
+        <v>0.7973166666666666</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -5954,6 +6566,9 @@
       <c r="J216" t="n">
         <v>0.6505777777777778</v>
       </c>
+      <c r="K216" t="n">
+        <v>0.837075</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -5980,6 +6595,9 @@
       <c r="J217" t="n">
         <v>0.6559818181818181</v>
       </c>
+      <c r="K217" t="n">
+        <v>0.8573999999999999</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -6006,6 +6624,9 @@
       <c r="J218" t="n">
         <v>0.4963333333333333</v>
       </c>
+      <c r="K218" t="n">
+        <v>0.8161124999999999</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -6032,6 +6653,9 @@
       <c r="J219" t="n">
         <v>0.5920555555555556</v>
       </c>
+      <c r="K219" t="n">
+        <v>0.8026142857142856</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -6058,6 +6682,9 @@
       <c r="J220" t="n">
         <v>0.5877</v>
       </c>
+      <c r="K220" t="n">
+        <v>0.8240142857142858</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -6084,6 +6711,9 @@
       <c r="J221" t="n">
         <v>0.7752444444444444</v>
       </c>
+      <c r="K221" t="n">
+        <v>0.75115</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -6110,6 +6740,9 @@
       <c r="J222" t="n">
         <v>0.64361</v>
       </c>
+      <c r="K222" t="n">
+        <v>0.7710999999999999</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -6136,6 +6769,9 @@
       <c r="J223" t="n">
         <v>0.4885714285714285</v>
       </c>
+      <c r="K223" t="n">
+        <v>0.7929999999999999</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -6162,6 +6798,9 @@
       <c r="J224" t="n">
         <v>0.6527000000000001</v>
       </c>
+      <c r="K224" t="n">
+        <v>0.7176750000000001</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -6188,6 +6827,9 @@
       <c r="J225" t="n">
         <v>0.5255399999999999</v>
       </c>
+      <c r="K225" t="n">
+        <v>0.6937666666666665</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -6214,6 +6856,9 @@
       <c r="J226" t="n">
         <v>0.5496444444444444</v>
       </c>
+      <c r="K226" t="n">
+        <v>0.7655625</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -6240,6 +6885,9 @@
       <c r="J227" t="n">
         <v>0.5828166666666666</v>
       </c>
+      <c r="K227" t="n">
+        <v>0.749057142857143</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -6266,6 +6914,9 @@
       <c r="J228" t="n">
         <v>0.5203636363636363</v>
       </c>
+      <c r="K228" t="n">
+        <v>0.7416999999999999</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -6292,6 +6943,9 @@
       <c r="J229" t="n">
         <v>0.564888888888889</v>
       </c>
+      <c r="K229" t="n">
+        <v>0.7341333333333333</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -6318,6 +6972,9 @@
       <c r="J230" t="n">
         <v>0.5632777777777778</v>
       </c>
+      <c r="K230" t="n">
+        <v>0.7264499999999999</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -6344,6 +7001,9 @@
       <c r="J231" t="n">
         <v>0.5177875000000001</v>
       </c>
+      <c r="K231" t="n">
+        <v>0.74265</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -6370,6 +7030,9 @@
       <c r="J232" t="n">
         <v>0.5377307692307692</v>
       </c>
+      <c r="K232" t="n">
+        <v>0.7272333333333334</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -6396,6 +7059,9 @@
       <c r="J233" t="n">
         <v>0.5020625000000001</v>
       </c>
+      <c r="K233" t="n">
+        <v>0.7821166666666667</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -6422,6 +7088,9 @@
       <c r="J234" t="n">
         <v>0.6765333333333333</v>
       </c>
+      <c r="K234" t="n">
+        <v>0.74068</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -6448,6 +7117,9 @@
       <c r="J235" t="n">
         <v>0.5295375</v>
       </c>
+      <c r="K235" t="n">
+        <v>0.6967999999999999</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -6474,6 +7146,9 @@
       <c r="J236" t="n">
         <v>0.4566909090909091</v>
       </c>
+      <c r="K236" t="n">
+        <v>0.7294833333333334</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -6500,6 +7175,9 @@
       <c r="J237" t="n">
         <v>0.3461</v>
       </c>
+      <c r="K237" t="n">
+        <v>0.7562</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -6526,6 +7204,9 @@
       <c r="J238" t="n">
         <v>0.6089545454545454</v>
       </c>
+      <c r="K238" t="n">
+        <v>0.69194</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -6552,6 +7233,9 @@
       <c r="J239" t="n">
         <v>0.5529818181818181</v>
       </c>
+      <c r="K239" t="n">
+        <v>0.7410333333333333</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -6578,6 +7262,9 @@
       <c r="J240" t="n">
         <v>0.5207799999999999</v>
       </c>
+      <c r="K240" t="n">
+        <v>0.7626250000000001</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -6604,6 +7291,9 @@
       <c r="J241" t="n">
         <v>0.5360666666666666</v>
       </c>
+      <c r="K241" t="n">
+        <v>0.64125</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -6630,6 +7320,9 @@
       <c r="J242" t="n">
         <v>0.50887</v>
       </c>
+      <c r="K242" t="n">
+        <v>0.6709333333333335</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -6656,6 +7349,9 @@
       <c r="J243" t="n">
         <v>0.4766727272727273</v>
       </c>
+      <c r="K243" t="n">
+        <v>0.7323714285714287</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -6682,6 +7378,9 @@
       <c r="J244" t="n">
         <v>0.6740777777777778</v>
       </c>
+      <c r="K244" t="n">
+        <v>0.7318000000000001</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -6708,6 +7407,9 @@
       <c r="J245" t="n">
         <v>0.5428363636363636</v>
       </c>
+      <c r="K245" t="n">
+        <v>0.5970500000000001</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -6734,6 +7436,9 @@
       <c r="J246" t="n">
         <v>0.4670285714285715</v>
       </c>
+      <c r="K246" t="n">
+        <v>0.7243666666666666</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -6760,6 +7465,9 @@
       <c r="J247" t="n">
         <v>0.4177</v>
       </c>
+      <c r="K247" t="n">
+        <v>0.7333200000000001</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -6786,6 +7494,9 @@
       <c r="J248" t="n">
         <v>0.4193727272727273</v>
       </c>
+      <c r="K248" t="n">
+        <v>0.7058199999999999</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -6812,6 +7523,9 @@
       <c r="J249" t="n">
         <v>0.3126111111111111</v>
       </c>
+      <c r="K249" t="n">
+        <v>0.7429285714285714</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -6838,6 +7552,9 @@
       <c r="J250" t="n">
         <v>0.52541</v>
       </c>
+      <c r="K250" t="n">
+        <v>0.7788999999999999</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -6864,6 +7581,9 @@
       <c r="J251" t="n">
         <v>0.62101</v>
       </c>
+      <c r="K251" t="n">
+        <v>0.7731</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -6890,6 +7610,9 @@
       <c r="J252" t="n">
         <v>0.47405</v>
       </c>
+      <c r="K252" t="n">
+        <v>0.6255249999999999</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -6916,6 +7639,9 @@
       <c r="J253" t="n">
         <v>0.2976124999999999</v>
       </c>
+      <c r="K253" t="n">
+        <v>0.6585000000000001</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -6942,6 +7668,9 @@
       <c r="J254" t="n">
         <v>0.5305636363636363</v>
       </c>
+      <c r="K254" t="n">
+        <v>0.7111500000000001</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -6968,6 +7697,9 @@
       <c r="J255" t="n">
         <v>0.453675</v>
       </c>
+      <c r="K255" t="n">
+        <v>0.6625333333333333</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -6994,6 +7726,9 @@
       <c r="J256" t="n">
         <v>0.5264</v>
       </c>
+      <c r="K256" t="n">
+        <v>0.6811166666666667</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -7020,6 +7755,9 @@
       <c r="J257" t="n">
         <v>0.5061099999999999</v>
       </c>
+      <c r="K257" t="n">
+        <v>0.6466428571428572</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -7046,6 +7784,9 @@
       <c r="J258" t="n">
         <v>0.5704727272727272</v>
       </c>
+      <c r="K258" t="n">
+        <v>0.77522</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -7072,6 +7813,9 @@
       <c r="J259" t="n">
         <v>0.4940125</v>
       </c>
+      <c r="K259" t="n">
+        <v>0.7147250000000001</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -7098,6 +7842,9 @@
       <c r="J260" t="n">
         <v>0.49337</v>
       </c>
+      <c r="K260" t="n">
+        <v>0.725325</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -7124,6 +7871,9 @@
       <c r="J261" t="n">
         <v>0.4787125</v>
       </c>
+      <c r="K261" t="n">
+        <v>0.7619666666666666</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -7150,6 +7900,9 @@
       <c r="J262" t="n">
         <v>0.5332166666666667</v>
       </c>
+      <c r="K262" t="n">
+        <v>0.6705399999999999</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -7176,6 +7929,9 @@
       <c r="J263" t="n">
         <v>0.4821777777777778</v>
       </c>
+      <c r="K263" t="n">
+        <v>0.7006888888888889</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -7202,6 +7958,9 @@
       <c r="J264" t="n">
         <v>0.2785666666666666</v>
       </c>
+      <c r="K264" t="n">
+        <v>0.7812999999999999</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -7228,6 +7987,9 @@
       <c r="J265" t="n">
         <v>0.37362</v>
       </c>
+      <c r="K265" t="n">
+        <v>0.73072</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -7254,6 +8016,9 @@
       <c r="J266" t="n">
         <v>0.5777333333333333</v>
       </c>
+      <c r="K266" t="n">
+        <v>0.69538</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -7280,6 +8045,9 @@
       <c r="J267" t="n">
         <v>0.4187555555555555</v>
       </c>
+      <c r="K267" t="n">
+        <v>0.6702857142857143</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -7306,6 +8074,9 @@
       <c r="J268" t="n">
         <v>0.4432923076923077</v>
       </c>
+      <c r="K268" t="n">
+        <v>0.6602333333333333</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -7332,6 +8103,9 @@
       <c r="J269" t="n">
         <v>0.3992545454545455</v>
       </c>
+      <c r="K269" t="n">
+        <v>0.7246874999999999</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -7358,6 +8132,9 @@
       <c r="J270" t="n">
         <v>0.53024</v>
       </c>
+      <c r="K270" t="n">
+        <v>0.7534666666666667</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -7384,6 +8161,9 @@
       <c r="J271" t="n">
         <v>0.35245</v>
       </c>
+      <c r="K271" t="n">
+        <v>0.7375666666666666</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -7410,6 +8190,9 @@
       <c r="J272" t="n">
         <v>0.5364099999999999</v>
       </c>
+      <c r="K272" t="n">
+        <v>0.7409142857142857</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -7436,6 +8219,9 @@
       <c r="J273" t="n">
         <v>0.49046</v>
       </c>
+      <c r="K273" t="n">
+        <v>0.6977375</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -7462,6 +8248,9 @@
       <c r="J274" t="n">
         <v>0.5271454545454546</v>
       </c>
+      <c r="K274" t="n">
+        <v>0.7393833333333332</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -7488,6 +8277,9 @@
       <c r="J275" t="n">
         <v>0.6258583333333333</v>
       </c>
+      <c r="K275" t="n">
+        <v>0.6601714285714285</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -7514,6 +8306,9 @@
       <c r="J276" t="n">
         <v>0.5662900000000001</v>
       </c>
+      <c r="K276" t="n">
+        <v>0.708375</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -7540,6 +8335,9 @@
       <c r="J277" t="n">
         <v>0.5481333333333334</v>
       </c>
+      <c r="K277" t="n">
+        <v>0.77276</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -7566,6 +8364,9 @@
       <c r="J278" t="n">
         <v>0.6872499999999999</v>
       </c>
+      <c r="K278" t="n">
+        <v>0.71804</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -7592,6 +8393,9 @@
       <c r="J279" t="n">
         <v>0.38228</v>
       </c>
+      <c r="K279" t="n">
+        <v>0.7485166666666667</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -7618,6 +8422,9 @@
       <c r="J280" t="n">
         <v>0.5379111111111111</v>
       </c>
+      <c r="K280" t="n">
+        <v>0.7121222222222222</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -7644,6 +8451,9 @@
       <c r="J281" t="n">
         <v>0.3585</v>
       </c>
+      <c r="K281" t="n">
+        <v>0.8013833333333333</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -7670,6 +8480,9 @@
       <c r="J282" t="n">
         <v>0.46475</v>
       </c>
+      <c r="K282" t="n">
+        <v>0.7207750000000001</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -7696,6 +8509,9 @@
       <c r="J283" t="n">
         <v>0.5285444444444445</v>
       </c>
+      <c r="K283" t="n">
+        <v>0.741</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -7722,6 +8538,9 @@
       <c r="J284" t="n">
         <v>0.6937299999999998</v>
       </c>
+      <c r="K284" t="n">
+        <v>0.7226333333333333</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -7748,6 +8567,9 @@
       <c r="J285" t="n">
         <v>0.619257142857143</v>
       </c>
+      <c r="K285" t="n">
+        <v>0.7185285714285715</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -7774,6 +8596,9 @@
       <c r="J286" t="n">
         <v>0.4541099999999999</v>
       </c>
+      <c r="K286" t="n">
+        <v>0.7076399999999999</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -7800,6 +8625,9 @@
       <c r="J287" t="n">
         <v>0.36542</v>
       </c>
+      <c r="K287" t="n">
+        <v>0.7272</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -7826,6 +8654,9 @@
       <c r="J288" t="n">
         <v>0.4118777777777777</v>
       </c>
+      <c r="K288" t="n">
+        <v>0.72135</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -7852,6 +8683,9 @@
       <c r="J289" t="n">
         <v>0.4954363636363638</v>
       </c>
+      <c r="K289" t="n">
+        <v>0.8254</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -7878,6 +8712,9 @@
       <c r="J290" t="n">
         <v>0.5547111111111112</v>
       </c>
+      <c r="K290" t="n">
+        <v>0.7574799999999999</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -7904,6 +8741,9 @@
       <c r="J291" t="n">
         <v>0.4500666666666667</v>
       </c>
+      <c r="K291" t="n">
+        <v>0.7030142857142857</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -7930,6 +8770,9 @@
       <c r="J292" t="n">
         <v>0.4856444444444444</v>
       </c>
+      <c r="K292" t="n">
+        <v>0.6989166666666667</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -7956,6 +8799,9 @@
       <c r="J293" t="n">
         <v>0.5432083333333333</v>
       </c>
+      <c r="K293" t="n">
+        <v>0.7136499999999999</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -7982,6 +8828,9 @@
       <c r="J294" t="n">
         <v>0.4857363636363636</v>
       </c>
+      <c r="K294" t="n">
+        <v>0.71695</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -8008,6 +8857,9 @@
       <c r="J295" t="n">
         <v>0.43847</v>
       </c>
+      <c r="K295" t="n">
+        <v>0.6839333333333334</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -8034,6 +8886,9 @@
       <c r="J296" t="n">
         <v>0.5291</v>
       </c>
+      <c r="K296" t="n">
+        <v>0.7252999999999999</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -8060,6 +8915,9 @@
       <c r="J297" t="n">
         <v>0.5162</v>
       </c>
+      <c r="K297" t="n">
+        <v>0.7389714285714284</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -8086,6 +8944,9 @@
       <c r="J298" t="n">
         <v>0.5041545454545454</v>
       </c>
+      <c r="K298" t="n">
+        <v>0.6939000000000001</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -8112,6 +8973,9 @@
       <c r="J299" t="n">
         <v>0.401623076923077</v>
       </c>
+      <c r="K299" t="n">
+        <v>0.6912555555555555</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -8138,6 +9002,9 @@
       <c r="J300" t="n">
         <v>0.45561</v>
       </c>
+      <c r="K300" t="n">
+        <v>0.7672</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -8164,6 +9031,9 @@
       <c r="J301" t="n">
         <v>0.3771777777777778</v>
       </c>
+      <c r="K301" t="n">
+        <v>0.6999222222222223</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -8190,6 +9060,9 @@
       <c r="J302" t="n">
         <v>0.6104636363636364</v>
       </c>
+      <c r="K302" t="n">
+        <v>0.68635</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -8216,6 +9089,9 @@
       <c r="J303" t="n">
         <v>0.4274909090909091</v>
       </c>
+      <c r="K303" t="n">
+        <v>0.74976</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -8242,6 +9118,9 @@
       <c r="J304" t="n">
         <v>0.4839090909090908</v>
       </c>
+      <c r="K304" t="n">
+        <v>0.6350250000000001</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -8268,6 +9147,9 @@
       <c r="J305" t="n">
         <v>0.6493749999999999</v>
       </c>
+      <c r="K305" t="n">
+        <v>0.6577333333333333</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -8294,6 +9176,9 @@
       <c r="J306" t="n">
         <v>0.5018142857142857</v>
       </c>
+      <c r="K306" t="n">
+        <v>0.7294875000000001</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -8320,6 +9205,9 @@
       <c r="J307" t="n">
         <v>0.4604571428571429</v>
       </c>
+      <c r="K307" t="n">
+        <v>0.8187142857142857</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -8346,6 +9234,9 @@
       <c r="J308" t="n">
         <v>0.4075545454545454</v>
       </c>
+      <c r="K308" t="n">
+        <v>0.7634428571428572</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -8372,6 +9263,9 @@
       <c r="J309" t="n">
         <v>0.6233666666666667</v>
       </c>
+      <c r="K309" t="n">
+        <v>0.7476666666666666</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -8398,6 +9292,9 @@
       <c r="J310" t="n">
         <v>0.5002555555555555</v>
       </c>
+      <c r="K310" t="n">
+        <v>0.7706428571428571</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -8423,6 +9320,9 @@
       </c>
       <c r="J311" t="n">
         <v>0.4580555555555555</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0.7271</v>
       </c>
     </row>
     <row r="314">
@@ -8474,6 +9374,9 @@
       <c r="J316" t="n">
         <v>0.0002</v>
       </c>
+      <c r="K316" t="n">
+        <v>0.0135</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -8500,6 +9403,9 @@
       <c r="J317" t="n">
         <v>0.0526</v>
       </c>
+      <c r="K317" t="n">
+        <v>0.0005</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -8526,6 +9432,9 @@
       <c r="J318" t="n">
         <v>0.016</v>
       </c>
+      <c r="K318" t="n">
+        <v>0.0129</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -8552,6 +9461,9 @@
       <c r="J319" t="n">
         <v>0.015</v>
       </c>
+      <c r="K319" t="n">
+        <v>0.0505</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -8578,6 +9490,9 @@
       <c r="J320" t="n">
         <v>0.0237</v>
       </c>
+      <c r="K320" t="n">
+        <v>0.0307</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -8604,6 +9519,9 @@
       <c r="J321" t="n">
         <v>0.0725</v>
       </c>
+      <c r="K321" t="n">
+        <v>0.0529</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -8630,6 +9548,9 @@
       <c r="J322" t="n">
         <v>0.09470000000000001</v>
       </c>
+      <c r="K322" t="n">
+        <v>0.09039999999999999</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -8656,6 +9577,9 @@
       <c r="J323" t="n">
         <v>0.0693</v>
       </c>
+      <c r="K323" t="n">
+        <v>0.113</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -8682,6 +9606,9 @@
       <c r="J324" t="n">
         <v>0.0493</v>
       </c>
+      <c r="K324" t="n">
+        <v>0.0721</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -8708,6 +9635,9 @@
       <c r="J325" t="n">
         <v>0.0482</v>
       </c>
+      <c r="K325" t="n">
+        <v>0.0697</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -8734,6 +9664,9 @@
       <c r="J326" t="n">
         <v>0.0401</v>
       </c>
+      <c r="K326" t="n">
+        <v>0.08500000000000001</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -8760,6 +9693,9 @@
       <c r="J327" t="n">
         <v>0.0561</v>
       </c>
+      <c r="K327" t="n">
+        <v>0.0898</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -8786,6 +9722,9 @@
       <c r="J328" t="n">
         <v>0.0392</v>
       </c>
+      <c r="K328" t="n">
+        <v>0.0833</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -8812,6 +9751,9 @@
       <c r="J329" t="n">
         <v>0.0558</v>
       </c>
+      <c r="K329" t="n">
+        <v>0.1286</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -8838,6 +9780,9 @@
       <c r="J330" t="n">
         <v>0.0553</v>
       </c>
+      <c r="K330" t="n">
+        <v>0.06809999999999999</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -8864,6 +9809,9 @@
       <c r="J331" t="n">
         <v>0.0285</v>
       </c>
+      <c r="K331" t="n">
+        <v>0.1164</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -8890,6 +9838,9 @@
       <c r="J332" t="n">
         <v>0.0508</v>
       </c>
+      <c r="K332" t="n">
+        <v>0.0871</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -8916,6 +9867,9 @@
       <c r="J333" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="K333" t="n">
+        <v>0.0853</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -8942,6 +9896,9 @@
       <c r="J334" t="n">
         <v>0.0398</v>
       </c>
+      <c r="K334" t="n">
+        <v>0.0789</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -8968,6 +9925,9 @@
       <c r="J335" t="n">
         <v>0.0322</v>
       </c>
+      <c r="K335" t="n">
+        <v>0.1048</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -8994,6 +9954,9 @@
       <c r="J336" t="n">
         <v>0.0294</v>
       </c>
+      <c r="K336" t="n">
+        <v>0.0992</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -9020,6 +9983,9 @@
       <c r="J337" t="n">
         <v>0.0354</v>
       </c>
+      <c r="K337" t="n">
+        <v>0.1163</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -9046,6 +10012,9 @@
       <c r="J338" t="n">
         <v>0.0385</v>
       </c>
+      <c r="K338" t="n">
+        <v>0.1165</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -9072,6 +10041,9 @@
       <c r="J339" t="n">
         <v>0.0335</v>
       </c>
+      <c r="K339" t="n">
+        <v>0.1166</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -9098,6 +10070,9 @@
       <c r="J340" t="n">
         <v>0.0356</v>
       </c>
+      <c r="K340" t="n">
+        <v>0.0761</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -9124,6 +10099,9 @@
       <c r="J341" t="n">
         <v>0.0394</v>
       </c>
+      <c r="K341" t="n">
+        <v>0.09089999999999999</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -9150,6 +10128,9 @@
       <c r="J342" t="n">
         <v>0.042</v>
       </c>
+      <c r="K342" t="n">
+        <v>0.08450000000000001</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -9176,6 +10157,9 @@
       <c r="J343" t="n">
         <v>0.0272</v>
       </c>
+      <c r="K343" t="n">
+        <v>0.07290000000000001</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -9202,6 +10186,9 @@
       <c r="J344" t="n">
         <v>0.0345</v>
       </c>
+      <c r="K344" t="n">
+        <v>0.1029</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -9228,6 +10215,9 @@
       <c r="J345" t="n">
         <v>0.0417</v>
       </c>
+      <c r="K345" t="n">
+        <v>0.1049</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -9254,6 +10244,9 @@
       <c r="J346" t="n">
         <v>0.0375</v>
       </c>
+      <c r="K346" t="n">
+        <v>0.1154</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -9280,6 +10273,9 @@
       <c r="J347" t="n">
         <v>0.0414</v>
       </c>
+      <c r="K347" t="n">
+        <v>0.1009</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -9306,6 +10302,9 @@
       <c r="J348" t="n">
         <v>0.0342</v>
       </c>
+      <c r="K348" t="n">
+        <v>0.1112</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -9332,6 +10331,9 @@
       <c r="J349" t="n">
         <v>0.0432</v>
       </c>
+      <c r="K349" t="n">
+        <v>0.1227</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -9358,6 +10360,9 @@
       <c r="J350" t="n">
         <v>0.043</v>
       </c>
+      <c r="K350" t="n">
+        <v>0.09660000000000001</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -9384,6 +10389,9 @@
       <c r="J351" t="n">
         <v>0.0282</v>
       </c>
+      <c r="K351" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -9410,6 +10418,9 @@
       <c r="J352" t="n">
         <v>0.0362</v>
       </c>
+      <c r="K352" t="n">
+        <v>0.1172</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -9436,6 +10447,9 @@
       <c r="J353" t="n">
         <v>0.0443</v>
       </c>
+      <c r="K353" t="n">
+        <v>0.1155</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -9462,6 +10476,9 @@
       <c r="J354" t="n">
         <v>0.0515</v>
       </c>
+      <c r="K354" t="n">
+        <v>0.111</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -9488,6 +10505,9 @@
       <c r="J355" t="n">
         <v>0.0294</v>
       </c>
+      <c r="K355" t="n">
+        <v>0.126</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -9514,6 +10534,9 @@
       <c r="J356" t="n">
         <v>0.0305</v>
       </c>
+      <c r="K356" t="n">
+        <v>0.1135</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -9540,6 +10563,9 @@
       <c r="J357" t="n">
         <v>0.0321</v>
       </c>
+      <c r="K357" t="n">
+        <v>0.0883</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -9566,6 +10592,9 @@
       <c r="J358" t="n">
         <v>0.039</v>
       </c>
+      <c r="K358" t="n">
+        <v>0.1119</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -9592,6 +10621,9 @@
       <c r="J359" t="n">
         <v>0.0455</v>
       </c>
+      <c r="K359" t="n">
+        <v>0.1121</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -9618,6 +10650,9 @@
       <c r="J360" t="n">
         <v>0.032</v>
       </c>
+      <c r="K360" t="n">
+        <v>0.1014</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -9644,6 +10679,9 @@
       <c r="J361" t="n">
         <v>0.0382</v>
       </c>
+      <c r="K361" t="n">
+        <v>0.0793</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -9670,6 +10708,9 @@
       <c r="J362" t="n">
         <v>0.0446</v>
       </c>
+      <c r="K362" t="n">
+        <v>0.0936</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -9696,6 +10737,9 @@
       <c r="J363" t="n">
         <v>0.0287</v>
       </c>
+      <c r="K363" t="n">
+        <v>0.0987</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -9722,6 +10766,9 @@
       <c r="J364" t="n">
         <v>0.0258</v>
       </c>
+      <c r="K364" t="n">
+        <v>0.0896</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -9748,6 +10795,9 @@
       <c r="J365" t="n">
         <v>0.0368</v>
       </c>
+      <c r="K365" t="n">
+        <v>0.1063</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -9774,6 +10824,9 @@
       <c r="J366" t="n">
         <v>0.0369</v>
       </c>
+      <c r="K366" t="n">
+        <v>0.0963</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -9800,6 +10853,9 @@
       <c r="J367" t="n">
         <v>0.0319</v>
       </c>
+      <c r="K367" t="n">
+        <v>0.0833</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -9826,6 +10882,9 @@
       <c r="J368" t="n">
         <v>0.0326</v>
       </c>
+      <c r="K368" t="n">
+        <v>0.1001</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -9852,6 +10911,9 @@
       <c r="J369" t="n">
         <v>0.0381</v>
       </c>
+      <c r="K369" t="n">
+        <v>0.0953</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -9878,6 +10940,9 @@
       <c r="J370" t="n">
         <v>0.0297</v>
       </c>
+      <c r="K370" t="n">
+        <v>0.1176</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -9904,6 +10969,9 @@
       <c r="J371" t="n">
         <v>0.027</v>
       </c>
+      <c r="K371" t="n">
+        <v>0.1246</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -9930,6 +10998,9 @@
       <c r="J372" t="n">
         <v>0.0266</v>
       </c>
+      <c r="K372" t="n">
+        <v>0.1054</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -9956,6 +11027,9 @@
       <c r="J373" t="n">
         <v>0.0433</v>
       </c>
+      <c r="K373" t="n">
+        <v>0.1146</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -9982,6 +11056,9 @@
       <c r="J374" t="n">
         <v>0.0389</v>
       </c>
+      <c r="K374" t="n">
+        <v>0.0936</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -10008,6 +11085,9 @@
       <c r="J375" t="n">
         <v>0.0271</v>
       </c>
+      <c r="K375" t="n">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -10034,6 +11114,9 @@
       <c r="J376" t="n">
         <v>0.0274</v>
       </c>
+      <c r="K376" t="n">
+        <v>0.1115</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -10060,6 +11143,9 @@
       <c r="J377" t="n">
         <v>0.032</v>
       </c>
+      <c r="K377" t="n">
+        <v>0.0911</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -10086,6 +11172,9 @@
       <c r="J378" t="n">
         <v>0.0393</v>
       </c>
+      <c r="K378" t="n">
+        <v>0.1059</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -10112,6 +11201,9 @@
       <c r="J379" t="n">
         <v>0.0429</v>
       </c>
+      <c r="K379" t="n">
+        <v>0.1235</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -10138,6 +11230,9 @@
       <c r="J380" t="n">
         <v>0.0336</v>
       </c>
+      <c r="K380" t="n">
+        <v>0.1246</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -10164,6 +11259,9 @@
       <c r="J381" t="n">
         <v>0.0257</v>
       </c>
+      <c r="K381" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -10190,6 +11288,9 @@
       <c r="J382" t="n">
         <v>0.0257</v>
       </c>
+      <c r="K382" t="n">
+        <v>0.095</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -10216,6 +11317,9 @@
       <c r="J383" t="n">
         <v>0.0262</v>
       </c>
+      <c r="K383" t="n">
+        <v>0.1006</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -10242,6 +11346,9 @@
       <c r="J384" t="n">
         <v>0.0275</v>
       </c>
+      <c r="K384" t="n">
+        <v>0.0978</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -10268,6 +11375,9 @@
       <c r="J385" t="n">
         <v>0.0242</v>
       </c>
+      <c r="K385" t="n">
+        <v>0.1106</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -10294,6 +11404,9 @@
       <c r="J386" t="n">
         <v>0.028</v>
       </c>
+      <c r="K386" t="n">
+        <v>0.1026</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -10320,6 +11433,9 @@
       <c r="J387" t="n">
         <v>0.0338</v>
       </c>
+      <c r="K387" t="n">
+        <v>0.1325</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -10346,6 +11462,9 @@
       <c r="J388" t="n">
         <v>0.0229</v>
       </c>
+      <c r="K388" t="n">
+        <v>0.1328</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -10372,6 +11491,9 @@
       <c r="J389" t="n">
         <v>0.0264</v>
       </c>
+      <c r="K389" t="n">
+        <v>0.1114</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -10398,6 +11520,9 @@
       <c r="J390" t="n">
         <v>0.027</v>
       </c>
+      <c r="K390" t="n">
+        <v>0.1056</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -10424,6 +11549,9 @@
       <c r="J391" t="n">
         <v>0.0313</v>
       </c>
+      <c r="K391" t="n">
+        <v>0.1173</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -10450,6 +11578,9 @@
       <c r="J392" t="n">
         <v>0.0238</v>
       </c>
+      <c r="K392" t="n">
+        <v>0.1018</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -10476,6 +11607,9 @@
       <c r="J393" t="n">
         <v>0.0217</v>
       </c>
+      <c r="K393" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -10502,6 +11636,9 @@
       <c r="J394" t="n">
         <v>0.0193</v>
       </c>
+      <c r="K394" t="n">
+        <v>0.1057</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -10528,6 +11665,9 @@
       <c r="J395" t="n">
         <v>0.0251</v>
       </c>
+      <c r="K395" t="n">
+        <v>0.09039999999999999</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -10554,6 +11694,9 @@
       <c r="J396" t="n">
         <v>0.027</v>
       </c>
+      <c r="K396" t="n">
+        <v>0.0867</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -10580,6 +11723,9 @@
       <c r="J397" t="n">
         <v>0.024</v>
       </c>
+      <c r="K397" t="n">
+        <v>0.1273</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -10606,6 +11752,9 @@
       <c r="J398" t="n">
         <v>0.0319</v>
       </c>
+      <c r="K398" t="n">
+        <v>0.1111</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -10632,6 +11781,9 @@
       <c r="J399" t="n">
         <v>0.0279</v>
       </c>
+      <c r="K399" t="n">
+        <v>0.1077</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -10658,6 +11810,9 @@
       <c r="J400" t="n">
         <v>0.0276</v>
       </c>
+      <c r="K400" t="n">
+        <v>0.1166</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -10684,6 +11839,9 @@
       <c r="J401" t="n">
         <v>0.0218</v>
       </c>
+      <c r="K401" t="n">
+        <v>0.1368</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -10710,6 +11868,9 @@
       <c r="J402" t="n">
         <v>0.0215</v>
       </c>
+      <c r="K402" t="n">
+        <v>0.1244</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -10736,6 +11897,9 @@
       <c r="J403" t="n">
         <v>0.019</v>
       </c>
+      <c r="K403" t="n">
+        <v>0.128</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -10762,6 +11926,9 @@
       <c r="J404" t="n">
         <v>0.0241</v>
       </c>
+      <c r="K404" t="n">
+        <v>0.1187</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -10788,6 +11955,9 @@
       <c r="J405" t="n">
         <v>0.0263</v>
       </c>
+      <c r="K405" t="n">
+        <v>0.1215</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -10814,6 +11984,9 @@
       <c r="J406" t="n">
         <v>0.0262</v>
       </c>
+      <c r="K406" t="n">
+        <v>0.143</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -10840,6 +12013,9 @@
       <c r="J407" t="n">
         <v>0.0338</v>
       </c>
+      <c r="K407" t="n">
+        <v>0.1254</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -10866,6 +12042,9 @@
       <c r="J408" t="n">
         <v>0.0286</v>
       </c>
+      <c r="K408" t="n">
+        <v>0.1181</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -10892,6 +12071,9 @@
       <c r="J409" t="n">
         <v>0.0255</v>
       </c>
+      <c r="K409" t="n">
+        <v>0.1317</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -10918,6 +12100,9 @@
       <c r="J410" t="n">
         <v>0.0225</v>
       </c>
+      <c r="K410" t="n">
+        <v>0.1233</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -10944,6 +12129,9 @@
       <c r="J411" t="n">
         <v>0.0247</v>
       </c>
+      <c r="K411" t="n">
+        <v>0.1155</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -10970,6 +12158,9 @@
       <c r="J412" t="n">
         <v>0.0217</v>
       </c>
+      <c r="K412" t="n">
+        <v>0.112</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -10996,6 +12187,9 @@
       <c r="J413" t="n">
         <v>0.028</v>
       </c>
+      <c r="K413" t="n">
+        <v>0.1395</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -11022,6 +12216,9 @@
       <c r="J414" t="n">
         <v>0.0238</v>
       </c>
+      <c r="K414" t="n">
+        <v>0.1271</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -11047,6 +12244,9 @@
       </c>
       <c r="J415" t="n">
         <v>0.0239</v>
+      </c>
+      <c r="K415" t="n">
+        <v>0.1222</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -669,6 +669,9 @@
       <c r="M5" s="10" t="n">
         <v>0.1869090909090909</v>
       </c>
+      <c r="N5" t="n">
+        <v>0.09279999999999999</v>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1" s="11">
       <c r="A6" s="18" t="n">
@@ -701,6 +704,9 @@
       <c r="M6" s="10" t="n">
         <v>0.138824</v>
       </c>
+      <c r="N6" t="n">
+        <v>0.2353263157894737</v>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1" s="11">
       <c r="A7" s="18" t="n">
@@ -733,6 +739,9 @@
       <c r="M7" s="10" t="n">
         <v>0.2518083333333334</v>
       </c>
+      <c r="N7" t="n">
+        <v>0.274504347826087</v>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1" s="11">
       <c r="A8" s="18" t="n">
@@ -765,6 +774,9 @@
       <c r="M8" s="10" t="n">
         <v>0.3698666666666667</v>
       </c>
+      <c r="N8" t="n">
+        <v>0.3215147058823529</v>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1" s="11">
       <c r="A9" s="18" t="n">
@@ -797,6 +809,9 @@
       <c r="M9" s="10" t="n">
         <v>0.3514</v>
       </c>
+      <c r="N9" t="n">
+        <v>0.3930472222222222</v>
+      </c>
     </row>
     <row r="10" ht="16" customHeight="1" s="11">
       <c r="A10" s="18" t="n">
@@ -829,6 +844,9 @@
       <c r="M10" s="10" t="n">
         <v>0.4646285714285714</v>
       </c>
+      <c r="N10" t="n">
+        <v>0.4396758620689655</v>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1" s="11">
       <c r="A11" s="18" t="n">
@@ -858,8 +876,11 @@
       <c r="K11" s="10" t="n">
         <v>0.5397373913043479</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="10" t="n">
         <v>0.5696769230769231</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4832086956521739</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="11">
@@ -890,8 +911,11 @@
       <c r="K12" s="10" t="n">
         <v>0.594390434782609</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="10" t="n">
         <v>0.3973416666666667</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5772291666666667</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1" s="11">
@@ -922,8 +946,11 @@
       <c r="K13" s="10" t="n">
         <v>0.663806923076923</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="10" t="n">
         <v>0.567176</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4163192307692307</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="11">
@@ -954,8 +981,11 @@
       <c r="K14" s="10" t="n">
         <v>0.699257692307692</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="10" t="n">
         <v>0.6389068965517241</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5317766666666667</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="11">
@@ -986,8 +1016,11 @@
       <c r="K15" s="10" t="n">
         <v>0.722392307692308</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="10" t="n">
         <v>0.6665208333333333</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.583564705882353</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="11">
@@ -1018,8 +1051,11 @@
       <c r="K16" s="10" t="n">
         <v>0.745989230769231</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="10" t="n">
         <v>0.6746</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.7064615384615386</v>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="11">
@@ -1050,8 +1086,11 @@
       <c r="K17" s="10" t="n">
         <v>0.763288461538462</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="10" t="n">
         <v>0.8905</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.5909714285714286</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="11">
@@ -1082,8 +1121,11 @@
       <c r="K18" s="10" t="n">
         <v>0.774463846153846</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="10" t="n">
         <v>0.8375846153846154</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.6155055555555555</v>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="11">
@@ -1114,8 +1156,11 @@
       <c r="K19" s="10" t="n">
         <v>0.781146923076923</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="10" t="n">
         <v>0.7931928571428569</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.6931615384615385</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="11">
@@ -1146,8 +1191,11 @@
       <c r="K20" s="10" t="n">
         <v>0.7911784615384611</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="10" t="n">
         <v>0.7452285714285715</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.6954259259259259</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="11">
@@ -1178,8 +1226,11 @@
       <c r="K21" s="10" t="n">
         <v>0.796523846153846</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="10" t="n">
         <v>0.7665750000000001</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.7208681818181818</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="11">
@@ -1210,8 +1261,11 @@
       <c r="K22" s="10" t="n">
         <v>0.806830769230769</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="10" t="n">
         <v>0.81155</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.6757333333333334</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1" s="11">
@@ -1242,8 +1296,11 @@
       <c r="K23" s="10" t="n">
         <v>0.814345384615385</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="10" t="n">
         <v>0.8190473684210527</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.7586851851851852</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1" s="11">
@@ -1274,8 +1331,11 @@
       <c r="K24" s="10" t="n">
         <v>0.811363076923077</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="10" t="n">
         <v>0.8160083333333333</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.6258</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1" s="11">
@@ -1306,8 +1366,11 @@
       <c r="K25" s="10" t="n">
         <v>0.826729230769231</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="10" t="n">
         <v>0.819016129032258</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.6926928571428572</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1" s="11">
@@ -1338,8 +1401,11 @@
       <c r="K26" s="10" t="n">
         <v>0.822984615384615</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="10" t="n">
         <v>0.800376</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.7689243902439025</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1" s="11">
@@ -1370,8 +1436,11 @@
       <c r="K27" s="10" t="n">
         <v>0.825206153846154</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="10" t="n">
         <v>0.8317777777777777</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.8026111111111112</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1" s="11">
@@ -1402,8 +1471,11 @@
       <c r="K28" s="10" t="n">
         <v>0.826743846153846</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="10" t="n">
         <v>0.8663357142857143</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.8487620689655171</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1" s="11">
@@ -1434,8 +1506,11 @@
       <c r="K29" s="10" t="n">
         <v>0.830370769230769</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="10" t="n">
         <v>0.8481645161290323</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.7313730769230771</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1" s="11">
@@ -1466,8 +1541,11 @@
       <c r="K30" s="10" t="n">
         <v>0.8273200000000001</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="10" t="n">
         <v>0.8360954545454544</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.8426740740740741</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1" s="11">
@@ -1498,8 +1576,11 @@
       <c r="K31" s="10" t="n">
         <v>0.832953846153846</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="10" t="n">
         <v>0.8196447368421053</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.7710591836734693</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1" s="11">
@@ -1530,8 +1611,11 @@
       <c r="K32" s="10" t="n">
         <v>0.836345384615384</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="10" t="n">
         <v>0.91625</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.7232619047619048</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1" s="11">
@@ -1562,8 +1646,11 @@
       <c r="K33" s="10" t="n">
         <v>0.839691538461538</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="10" t="n">
         <v>0.8377368421052631</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.7280200000000001</v>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1" s="11">
@@ -1594,8 +1681,11 @@
       <c r="K34" s="10" t="n">
         <v>0.841285384615384</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="10" t="n">
         <v>0.8785285714285714</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.8458410256410256</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1" s="11">
@@ -1626,8 +1716,11 @@
       <c r="K35" s="10" t="n">
         <v>0.842516153846154</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="10" t="n">
         <v>0.8667842105263157</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.8215210526315789</v>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1" s="11">
@@ -1658,8 +1751,11 @@
       <c r="K36" s="10" t="n">
         <v>0.84278</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" s="10" t="n">
         <v>0.8169363636363637</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.8271181818181819</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1" s="11">
@@ -1690,8 +1786,11 @@
       <c r="K37" s="10" t="n">
         <v>0.8428130769230771</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="10" t="n">
         <v>0.8512157894736841</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.759484</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1" s="11">
@@ -1722,8 +1821,11 @@
       <c r="K38" s="10" t="n">
         <v>0.846044615384615</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="10" t="n">
         <v>0.8428</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.7245290322580645</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1" s="11">
@@ -1754,8 +1856,11 @@
       <c r="K39" s="10" t="n">
         <v>0.847500769230769</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="10" t="n">
         <v>0.8182478260869566</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.7952843749999999</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1" s="11">
@@ -1786,8 +1891,11 @@
       <c r="K40" s="10" t="n">
         <v>0.847058461538461</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="10" t="n">
         <v>0.8591923076923078</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.8183166666666666</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="11">
@@ -1818,8 +1926,11 @@
       <c r="K41" s="10" t="n">
         <v>0.849780769230769</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M41" s="10" t="n">
         <v>0.9093941176470588</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.7012096774193549</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="11">
@@ -1850,8 +1961,11 @@
       <c r="K42" s="10" t="n">
         <v>0.853227692307692</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42" s="10" t="n">
         <v>0.8544142857142857</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.8291181818181819</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="11">
@@ -1882,8 +1996,11 @@
       <c r="K43" s="10" t="n">
         <v>0.849375384615384</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43" s="10" t="n">
         <v>0.8557325581395347</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.8715249999999999</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="11">
@@ -1914,8 +2031,11 @@
       <c r="K44" s="10" t="n">
         <v>0.85051923076923</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44" s="10" t="n">
         <v>0.8781812500000001</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.8116214285714286</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1" s="11">
@@ -1946,8 +2066,11 @@
       <c r="K45" s="10" t="n">
         <v>0.848966153846154</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M45" s="10" t="n">
         <v>0.8173041666666666</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.7751409090909092</v>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1" s="11">
@@ -1978,8 +2101,11 @@
       <c r="K46" s="10" t="n">
         <v>0.854006153846154</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M46" s="10" t="n">
         <v>0.8770809523809524</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.7962413793103449</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1" s="11">
@@ -2010,8 +2136,11 @@
       <c r="K47" s="10" t="n">
         <v>0.85319</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47" s="10" t="n">
         <v>0.7956400000000001</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.7753555555555557</v>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1" s="11">
@@ -2042,8 +2171,11 @@
       <c r="K48" s="10" t="n">
         <v>0.852940769230769</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M48" s="10" t="n">
         <v>0.871456</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.8330464285714285</v>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1" s="11">
@@ -2074,8 +2206,11 @@
       <c r="K49" s="10" t="n">
         <v>0.851881538461538</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M49" s="10" t="n">
         <v>0.8120384615384615</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.634508</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" s="11">
@@ -2106,8 +2241,11 @@
       <c r="K50" s="10" t="n">
         <v>0.852568461538461</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M50" s="10" t="n">
         <v>0.8598541666666666</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.840105</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="11">
@@ -2138,8 +2276,11 @@
       <c r="K51" s="10" t="n">
         <v>0.852883076923077</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M51" s="10" t="n">
         <v>0.8482484848484848</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.7060705882352941</v>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1" s="11">
@@ -2170,8 +2311,11 @@
       <c r="K52" s="10" t="n">
         <v>0.855603076923077</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M52" s="10" t="n">
         <v>0.8915194444444443</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.7423461538461539</v>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1" s="11">
@@ -2202,8 +2346,11 @@
       <c r="K53" s="10" t="n">
         <v>0.857236153846154</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M53" s="10" t="n">
         <v>0.9129176470588236</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.8302133333333334</v>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="11">
@@ -2234,8 +2381,11 @@
       <c r="K54" s="10" t="n">
         <v>0.859004615384615</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M54" s="10" t="n">
         <v>0.8237</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.7507957446808512</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1" s="11">
@@ -2266,8 +2416,11 @@
       <c r="K55" s="10" t="n">
         <v>0.858283076923077</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M55" s="10" t="n">
         <v>0.8023666666666667</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.8164939393939393</v>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1" s="11">
@@ -2298,8 +2451,11 @@
       <c r="K56" s="10" t="n">
         <v>0.857934615384615</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M56" s="10" t="n">
         <v>0.9308533333333334</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.8507481481481481</v>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1" s="11">
@@ -2330,8 +2486,11 @@
       <c r="K57" s="10" t="n">
         <v>0.859003846153846</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M57" s="10" t="n">
         <v>0.8568866666666667</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.8110064516129033</v>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1" s="11">
@@ -2362,8 +2521,11 @@
       <c r="K58" s="10" t="n">
         <v>0.858422307692308</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M58" s="10" t="n">
         <v>0.8825473684210526</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.7516735294117647</v>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1" s="11">
@@ -2394,8 +2556,11 @@
       <c r="K59" s="10" t="n">
         <v>0.85805</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M59" s="10" t="n">
         <v>0.8528863636363636</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.7675923076923077</v>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1" s="11">
@@ -2426,8 +2591,11 @@
       <c r="K60" s="10" t="n">
         <v>0.858092307692308</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M60" s="10" t="n">
         <v>0.8295878787878788</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.7682129032258065</v>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1" s="11">
@@ -2458,8 +2626,11 @@
       <c r="K61" s="10" t="n">
         <v>0.859066923076923</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M61" s="10" t="n">
         <v>0.8941941176470588</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.6901315789473684</v>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1" s="11">
@@ -2490,8 +2661,11 @@
       <c r="K62" s="10" t="n">
         <v>0.858716923076923</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M62" s="10" t="n">
         <v>0.8776878787878788</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.7398857142857143</v>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1" s="11">
@@ -2522,8 +2696,11 @@
       <c r="K63" s="10" t="n">
         <v>0.859483076923077</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M63" s="10" t="n">
         <v>0.8672030303030303</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.6727555555555556</v>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1" s="11">
@@ -2554,8 +2731,11 @@
       <c r="K64" s="10" t="n">
         <v>0.856952307692307</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M64" s="10" t="n">
         <v>0.9006526315789474</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.83423125</v>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1" s="11">
@@ -2586,8 +2766,11 @@
       <c r="K65" s="10" t="n">
         <v>0.858702307692308</v>
       </c>
-      <c r="M65" t="n">
+      <c r="M65" s="10" t="n">
         <v>0.8324178571428572</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.7577433333333334</v>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1" s="11">
@@ -2618,8 +2801,11 @@
       <c r="K66" s="10" t="n">
         <v>0.857615384615385</v>
       </c>
-      <c r="M66" t="n">
+      <c r="M66" s="10" t="n">
         <v>0.8579961538461537</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.7123186046511628</v>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1" s="11">
@@ -2650,8 +2836,11 @@
       <c r="K67" s="10" t="n">
         <v>0.85873</v>
       </c>
-      <c r="M67" t="n">
+      <c r="M67" s="10" t="n">
         <v>0.8567708333333334</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.681888888888889</v>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1" s="11">
@@ -2682,8 +2871,11 @@
       <c r="K68" s="10" t="n">
         <v>0.857892307692307</v>
       </c>
-      <c r="M68" t="n">
+      <c r="M68" s="10" t="n">
         <v>0.8655875000000002</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.8249142857142857</v>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1" s="11">
@@ -2714,8 +2906,11 @@
       <c r="K69" s="10" t="n">
         <v>0.859708461538461</v>
       </c>
-      <c r="M69" t="n">
+      <c r="M69" s="10" t="n">
         <v>0.8712071428571428</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.7955882352941178</v>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1" s="11">
@@ -2746,8 +2941,11 @@
       <c r="K70" s="10" t="n">
         <v>0.85967</v>
       </c>
-      <c r="M70" t="n">
+      <c r="M70" s="10" t="n">
         <v>0.864895</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.788678</v>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1" s="11">
@@ -2778,8 +2976,11 @@
       <c r="K71" s="10" t="n">
         <v>0.859407692307692</v>
       </c>
-      <c r="M71" t="n">
+      <c r="M71" s="10" t="n">
         <v>0.8924238095238097</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.7767631578947369</v>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1" s="11">
@@ -2810,8 +3011,11 @@
       <c r="K72" s="10" t="n">
         <v>0.860503846153846</v>
       </c>
-      <c r="M72" t="n">
+      <c r="M72" s="10" t="n">
         <v>0.9009695652173915</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.7267807692307693</v>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1" s="11">
@@ -2842,8 +3046,11 @@
       <c r="K73" s="10" t="n">
         <v>0.859063076923077</v>
       </c>
-      <c r="M73" t="n">
+      <c r="M73" s="10" t="n">
         <v>0.9029473684210527</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.8130521739130434</v>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1" s="11">
@@ -2874,8 +3081,11 @@
       <c r="K74" s="10" t="n">
         <v>0.859748461538461</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M74" s="10" t="n">
         <v>0.8609264705882353</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.8167785714285715</v>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1" s="11">
@@ -2906,8 +3116,11 @@
       <c r="K75" s="10" t="n">
         <v>0.857257692307692</v>
       </c>
-      <c r="M75" t="n">
+      <c r="M75" s="10" t="n">
         <v>0.8881739130434783</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.80575</v>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1" s="11">
@@ -2938,8 +3151,11 @@
       <c r="K76" s="10" t="n">
         <v>0.860387692307692</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M76" s="10" t="n">
         <v>0.8360800000000002</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.8016190476190476</v>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1" s="11">
@@ -2970,8 +3186,11 @@
       <c r="K77" s="10" t="n">
         <v>0.859401538461538</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M77" s="10" t="n">
         <v>0.8866658536585366</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.779913043478261</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1" s="11">
@@ -3002,8 +3221,11 @@
       <c r="K78" s="10" t="n">
         <v>0.859062307692308</v>
       </c>
-      <c r="M78" t="n">
+      <c r="M78" s="10" t="n">
         <v>0.9142322580645161</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.8567357142857145</v>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1" s="11">
@@ -3034,8 +3256,11 @@
       <c r="K79" s="10" t="n">
         <v>0.858740769230769</v>
       </c>
-      <c r="M79" t="n">
+      <c r="M79" s="10" t="n">
         <v>0.9071875000000001</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.7588764705882354</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1" s="11">
@@ -3066,8 +3291,11 @@
       <c r="K80" s="10" t="n">
         <v>0.860453076923077</v>
       </c>
-      <c r="M80" t="n">
+      <c r="M80" s="10" t="n">
         <v>0.8460631578947367</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.7777281250000001</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1" s="11">
@@ -3098,8 +3326,11 @@
       <c r="K81" s="10" t="n">
         <v>0.860108461538461</v>
       </c>
-      <c r="M81" t="n">
+      <c r="M81" s="10" t="n">
         <v>0.8665</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.7613750000000001</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1" s="11">
@@ -3130,8 +3361,11 @@
       <c r="K82" s="10" t="n">
         <v>0.85903</v>
       </c>
-      <c r="M82" t="n">
+      <c r="M82" s="10" t="n">
         <v>0.7966333333333333</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.838671875</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1" s="11">
@@ -3162,8 +3396,11 @@
       <c r="K83" s="10" t="n">
         <v>0.858614615384615</v>
       </c>
-      <c r="M83" t="n">
+      <c r="M83" s="10" t="n">
         <v>0.8748655172413794</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.792909375</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1" s="11">
@@ -3194,8 +3431,11 @@
       <c r="K84" s="10" t="n">
         <v>0.859703076923077</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M84" s="10" t="n">
         <v>0.8646142857142858</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.7617243243243242</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1" s="11">
@@ -3226,8 +3466,11 @@
       <c r="K85" s="10" t="n">
         <v>0.860047692307692</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M85" s="10" t="n">
         <v>0.8899000000000001</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.7913162162162163</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1" s="11">
@@ -3258,8 +3501,11 @@
       <c r="K86" s="10" t="n">
         <v>0.85932</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M86" s="10" t="n">
         <v>0.8825500000000001</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.8398325581395351</v>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1" s="11">
@@ -3290,8 +3536,11 @@
       <c r="K87" s="10" t="n">
         <v>0.859293076923077</v>
       </c>
-      <c r="M87" t="n">
+      <c r="M87" s="10" t="n">
         <v>0.890473076923077</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.774444</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1" s="11">
@@ -3322,8 +3571,11 @@
       <c r="K88" s="10" t="n">
         <v>0.858625384615384</v>
       </c>
-      <c r="M88" t="n">
+      <c r="M88" s="10" t="n">
         <v>0.77555</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.7538024390243903</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1" s="11">
@@ -3354,8 +3606,11 @@
       <c r="K89" s="10" t="n">
         <v>0.85903</v>
       </c>
-      <c r="M89" t="n">
+      <c r="M89" s="10" t="n">
         <v>0.8602703703703704</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.7902307692307692</v>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1" s="11">
@@ -3386,8 +3641,11 @@
       <c r="K90" s="10" t="n">
         <v>0.8600423076923081</v>
       </c>
-      <c r="M90" t="n">
+      <c r="M90" s="10" t="n">
         <v>0.8716130434782609</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.7373966666666667</v>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1" s="11">
@@ -3418,8 +3676,11 @@
       <c r="K91" s="10" t="n">
         <v>0.859703076923077</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M91" s="10" t="n">
         <v>0.7576000000000001</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.7704999999999999</v>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1" s="11">
@@ -3450,8 +3711,11 @@
       <c r="K92" s="10" t="n">
         <v>0.859085384615385</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M92" s="10" t="n">
         <v>0.8530315789473684</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.8550957446808509</v>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1" s="11">
@@ -3482,8 +3746,11 @@
       <c r="K93" s="10" t="n">
         <v>0.859731538461538</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M93" s="10" t="n">
         <v>0.8781960000000001</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.8248238095238095</v>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1" s="11">
@@ -3514,8 +3781,11 @@
       <c r="K94" s="10" t="n">
         <v>0.860103076923077</v>
       </c>
-      <c r="M94" t="n">
+      <c r="M94" s="10" t="n">
         <v>0.8743272727272727</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.8461375</v>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1" s="11">
@@ -3546,8 +3816,11 @@
       <c r="K95" s="10" t="n">
         <v>0.860824615384615</v>
       </c>
-      <c r="M95" t="n">
+      <c r="M95" s="10" t="n">
         <v>0.8619818181818182</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.7295190476190476</v>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1" s="11">
@@ -3578,8 +3851,11 @@
       <c r="K96" s="10" t="n">
         <v>0.860777692307692</v>
       </c>
-      <c r="M96" t="n">
+      <c r="M96" s="10" t="n">
         <v>0.8519916666666667</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.8256032258064515</v>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1" s="11">
@@ -3610,8 +3886,11 @@
       <c r="K97" s="10" t="n">
         <v>0.860447692307692</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M97" s="10" t="n">
         <v>0.8274</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.7570315789473684</v>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1" s="11">
@@ -3642,8 +3921,11 @@
       <c r="K98" s="10" t="n">
         <v>0.859374615384615</v>
       </c>
-      <c r="M98" t="n">
+      <c r="M98" s="10" t="n">
         <v>0.8591160000000001</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.7786372093023257</v>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1" s="11">
@@ -3674,8 +3956,11 @@
       <c r="K99" s="10" t="n">
         <v>0.860426153846154</v>
       </c>
-      <c r="M99" t="n">
+      <c r="M99" s="10" t="n">
         <v>0.8396424242424243</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.8155652173913043</v>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1" s="11">
@@ -3706,8 +3991,11 @@
       <c r="K100" s="10" t="n">
         <v>0.8593530769230771</v>
       </c>
-      <c r="M100" t="n">
+      <c r="M100" s="10" t="n">
         <v>0.8525555555555555</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.7994022222222222</v>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1" s="11">
@@ -3738,8 +4026,11 @@
       <c r="K101" s="10" t="n">
         <v>0.860047692307692</v>
       </c>
-      <c r="M101" t="n">
+      <c r="M101" s="10" t="n">
         <v>0.8753692307692309</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.7036</v>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1" s="11">
@@ -3770,8 +4061,11 @@
       <c r="K102" s="10" t="n">
         <v>0.859758461538461</v>
       </c>
-      <c r="M102" t="n">
+      <c r="M102" s="10" t="n">
         <v>0.85886</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.7512750000000001</v>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1" s="11">
@@ -3802,8 +4096,11 @@
       <c r="K103" s="10" t="n">
         <v>0.860124615384615</v>
       </c>
-      <c r="M103" t="n">
+      <c r="M103" s="10" t="n">
         <v>0.8541730769230769</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.8170277777777778</v>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1" s="11">
@@ -3834,8 +4131,11 @@
       <c r="K104" s="10" t="n">
         <v>0.860124615384615</v>
       </c>
-      <c r="M104" t="n">
+      <c r="M104" s="10" t="n">
         <v>0.9033464285714284</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.8098358974358975</v>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1" s="11">
@@ -3893,6 +4193,9 @@
       <c r="M108" s="10" t="n">
         <v>0.9333333333333333</v>
       </c>
+      <c r="N108" t="n">
+        <v>0.9333333333333333</v>
+      </c>
     </row>
     <row r="109" ht="16" customHeight="1" s="11">
       <c r="A109" s="18" t="n">
@@ -3925,6 +4228,9 @@
       <c r="M109" s="10" t="n">
         <v>0.9230769230769231</v>
       </c>
+      <c r="N109" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="110" ht="16" customHeight="1" s="11">
       <c r="A110" s="18" t="n">
@@ -3957,6 +4263,9 @@
       <c r="M110" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N110" t="n">
+        <v>0.9166666666666666</v>
+      </c>
     </row>
     <row r="111" ht="16" customHeight="1" s="11">
       <c r="A111" s="18" t="n">
@@ -3989,6 +4298,9 @@
       <c r="M111" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N111" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="112" ht="16" customHeight="1" s="11">
       <c r="A112" s="18" t="n">
@@ -4021,6 +4333,9 @@
       <c r="M112" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N112" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="113" ht="16" customHeight="1" s="11">
       <c r="A113" s="18" t="n">
@@ -4053,6 +4368,9 @@
       <c r="M113" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114" ht="16" customHeight="1" s="11">
       <c r="A114" s="18" t="n">
@@ -4082,8 +4400,11 @@
       <c r="K114" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M114" t="n">
-        <v>1</v>
+      <c r="M114" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1" s="11">
@@ -4114,8 +4435,11 @@
       <c r="K115" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M115" t="n">
+      <c r="M115" s="10" t="n">
         <v>0.2857142857142857</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1" s="11">
@@ -4146,8 +4470,11 @@
       <c r="K116" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M116" t="n">
-        <v>1</v>
+      <c r="M116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1" s="11">
@@ -4178,7 +4505,10 @@
       <c r="K117" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M117" t="n">
+      <c r="M117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N117" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4210,7 +4540,10 @@
       <c r="K118" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M118" t="n">
+      <c r="M118" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N118" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4242,7 +4575,10 @@
       <c r="K119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M119" t="n">
+      <c r="M119" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N119" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4274,7 +4610,10 @@
       <c r="K120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M120" t="n">
+      <c r="M120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N120" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4306,7 +4645,10 @@
       <c r="K121" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M121" t="n">
+      <c r="M121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N121" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4338,7 +4680,10 @@
       <c r="K122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M122" t="n">
+      <c r="M122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4370,7 +4715,10 @@
       <c r="K123" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M123" t="n">
+      <c r="M123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N123" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4402,7 +4750,10 @@
       <c r="K124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M124" t="n">
+      <c r="M124" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N124" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4434,7 +4785,10 @@
       <c r="K125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M125" t="n">
+      <c r="M125" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N125" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4466,7 +4820,10 @@
       <c r="K126" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M126" t="n">
+      <c r="M126" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4498,7 +4855,10 @@
       <c r="K127" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M127" t="n">
+      <c r="M127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4530,7 +4890,10 @@
       <c r="K128" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M128" t="n">
+      <c r="M128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4562,7 +4925,10 @@
       <c r="K129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M129" t="n">
+      <c r="M129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4594,7 +4960,10 @@
       <c r="K130" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M130" t="n">
+      <c r="M130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N130" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4626,8 +4995,11 @@
       <c r="K131" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M131" t="n">
+      <c r="M131" s="10" t="n">
         <v>0.75</v>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="132" ht="16" customHeight="1" s="11">
@@ -4658,8 +5030,11 @@
       <c r="K132" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M132" t="n">
-        <v>1</v>
+      <c r="M132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="133" ht="16" customHeight="1" s="11">
@@ -4690,7 +5065,10 @@
       <c r="K133" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M133" t="n">
+      <c r="M133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4722,7 +5100,10 @@
       <c r="K134" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M134" t="n">
+      <c r="M134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4754,7 +5135,10 @@
       <c r="K135" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M135" t="n">
+      <c r="M135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4786,7 +5170,10 @@
       <c r="K136" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M136" t="n">
+      <c r="M136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N136" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4818,7 +5205,10 @@
       <c r="K137" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M137" t="n">
+      <c r="M137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4850,7 +5240,10 @@
       <c r="K138" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M138" t="n">
+      <c r="M138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4882,7 +5275,10 @@
       <c r="K139" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M139" t="n">
+      <c r="M139" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4914,7 +5310,10 @@
       <c r="K140" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M140" t="n">
+      <c r="M140" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4946,7 +5345,10 @@
       <c r="K141" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M141" t="n">
+      <c r="M141" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4978,7 +5380,10 @@
       <c r="K142" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M142" t="n">
+      <c r="M142" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5010,7 +5415,10 @@
       <c r="K143" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M143" t="n">
+      <c r="M143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5042,7 +5450,10 @@
       <c r="K144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M144" t="n">
+      <c r="M144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5074,7 +5485,10 @@
       <c r="K145" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M145" t="n">
+      <c r="M145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5106,7 +5520,10 @@
       <c r="K146" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M146" t="n">
+      <c r="M146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5138,7 +5555,10 @@
       <c r="K147" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M147" t="n">
+      <c r="M147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5170,7 +5590,10 @@
       <c r="K148" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M148" t="n">
+      <c r="M148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5202,7 +5625,10 @@
       <c r="K149" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M149" t="n">
+      <c r="M149" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5234,7 +5660,10 @@
       <c r="K150" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M150" t="n">
+      <c r="M150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N150" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5266,7 +5695,10 @@
       <c r="K151" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M151" t="n">
+      <c r="M151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5298,7 +5730,10 @@
       <c r="K152" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M152" t="n">
+      <c r="M152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N152" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5330,7 +5765,10 @@
       <c r="K153" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M153" t="n">
+      <c r="M153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5362,7 +5800,10 @@
       <c r="K154" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M154" t="n">
+      <c r="M154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5394,7 +5835,10 @@
       <c r="K155" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M155" t="n">
+      <c r="M155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5426,7 +5870,10 @@
       <c r="K156" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M156" t="n">
+      <c r="M156" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N156" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5458,7 +5905,10 @@
       <c r="K157" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M157" t="n">
+      <c r="M157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5490,7 +5940,10 @@
       <c r="K158" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M158" t="n">
+      <c r="M158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5522,7 +5975,10 @@
       <c r="K159" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M159" t="n">
+      <c r="M159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5554,7 +6010,10 @@
       <c r="K160" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M160" t="n">
+      <c r="M160" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5586,7 +6045,10 @@
       <c r="K161" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M161" t="n">
+      <c r="M161" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N161" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5618,7 +6080,10 @@
       <c r="K162" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M162" t="n">
+      <c r="M162" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N162" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5650,7 +6115,10 @@
       <c r="K163" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M163" t="n">
+      <c r="M163" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N163" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5682,7 +6150,10 @@
       <c r="K164" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M164" t="n">
+      <c r="M164" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5714,7 +6185,10 @@
       <c r="K165" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M165" t="n">
+      <c r="M165" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5746,7 +6220,10 @@
       <c r="K166" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M166" t="n">
+      <c r="M166" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5778,7 +6255,10 @@
       <c r="K167" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M167" t="n">
+      <c r="M167" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5810,7 +6290,10 @@
       <c r="K168" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M168" t="n">
+      <c r="M168" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5842,7 +6325,10 @@
       <c r="K169" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M169" t="n">
+      <c r="M169" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5874,7 +6360,10 @@
       <c r="K170" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M170" t="n">
+      <c r="M170" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5906,7 +6395,10 @@
       <c r="K171" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M171" t="n">
+      <c r="M171" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5938,7 +6430,10 @@
       <c r="K172" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M172" t="n">
+      <c r="M172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N172" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5970,7 +6465,10 @@
       <c r="K173" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M173" t="n">
+      <c r="M173" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N173" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6002,7 +6500,10 @@
       <c r="K174" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M174" t="n">
+      <c r="M174" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N174" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6034,7 +6535,10 @@
       <c r="K175" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M175" t="n">
+      <c r="M175" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6066,7 +6570,10 @@
       <c r="K176" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M176" t="n">
+      <c r="M176" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N176" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6098,7 +6605,10 @@
       <c r="K177" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M177" t="n">
+      <c r="M177" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N177" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6130,7 +6640,10 @@
       <c r="K178" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M178" t="n">
+      <c r="M178" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6162,7 +6675,10 @@
       <c r="K179" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M179" t="n">
+      <c r="M179" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N179" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6194,7 +6710,10 @@
       <c r="K180" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M180" t="n">
+      <c r="M180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N180" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6226,7 +6745,10 @@
       <c r="K181" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M181" t="n">
+      <c r="M181" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N181" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6258,7 +6780,10 @@
       <c r="K182" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M182" t="n">
+      <c r="M182" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6290,7 +6815,10 @@
       <c r="K183" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M183" t="n">
+      <c r="M183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N183" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6322,7 +6850,10 @@
       <c r="K184" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M184" t="n">
+      <c r="M184" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6354,7 +6885,10 @@
       <c r="K185" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M185" t="n">
+      <c r="M185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N185" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6386,7 +6920,10 @@
       <c r="K186" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M186" t="n">
+      <c r="M186" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N186" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6418,7 +6955,10 @@
       <c r="K187" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M187" t="n">
+      <c r="M187" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N187" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6450,7 +6990,10 @@
       <c r="K188" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M188" t="n">
+      <c r="M188" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N188" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6482,7 +7025,10 @@
       <c r="K189" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M189" t="n">
+      <c r="M189" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N189" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6514,7 +7060,10 @@
       <c r="K190" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M190" t="n">
+      <c r="M190" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N190" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6546,7 +7095,10 @@
       <c r="K191" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M191" t="n">
+      <c r="M191" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N191" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6578,7 +7130,10 @@
       <c r="K192" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M192" t="n">
+      <c r="M192" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N192" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6610,7 +7165,10 @@
       <c r="K193" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M193" t="n">
+      <c r="M193" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N193" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6642,7 +7200,10 @@
       <c r="K194" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M194" t="n">
+      <c r="M194" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N194" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6674,7 +7235,10 @@
       <c r="K195" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M195" t="n">
+      <c r="M195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N195" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6706,7 +7270,10 @@
       <c r="K196" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M196" t="n">
+      <c r="M196" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N196" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6738,7 +7305,10 @@
       <c r="K197" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M197" t="n">
+      <c r="M197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6770,7 +7340,10 @@
       <c r="K198" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M198" t="n">
+      <c r="M198" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N198" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6802,7 +7375,10 @@
       <c r="K199" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M199" t="n">
+      <c r="M199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6834,7 +7410,10 @@
       <c r="K200" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M200" t="n">
+      <c r="M200" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N200" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6866,7 +7445,10 @@
       <c r="K201" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M201" t="n">
+      <c r="M201" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N201" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6898,7 +7480,10 @@
       <c r="K202" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M202" t="n">
+      <c r="M202" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N202" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6930,7 +7515,10 @@
       <c r="K203" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M203" t="n">
+      <c r="M203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N203" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6962,7 +7550,10 @@
       <c r="K204" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M204" t="n">
+      <c r="M204" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N204" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6994,7 +7585,10 @@
       <c r="K205" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M205" t="n">
+      <c r="M205" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N205" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7026,7 +7620,10 @@
       <c r="K206" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M206" t="n">
+      <c r="M206" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N206" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7058,7 +7655,10 @@
       <c r="K207" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M207" t="n">
+      <c r="M207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7117,6 +7717,9 @@
       <c r="M212" s="10" t="n">
         <v>0.95448</v>
       </c>
+      <c r="N212" t="n">
+        <v>0.9517333333333333</v>
+      </c>
     </row>
     <row r="213" ht="16" customHeight="1" s="11">
       <c r="A213" s="18" t="n">
@@ -7149,6 +7752,9 @@
       <c r="M213" s="10" t="n">
         <v>0.9643888888888887</v>
       </c>
+      <c r="N213" t="n">
+        <v>0.8558428571428571</v>
+      </c>
     </row>
     <row r="214" ht="16" customHeight="1" s="11">
       <c r="A214" s="18" t="n">
@@ -7181,6 +7787,9 @@
       <c r="M214" s="10" t="n">
         <v>0.9180333333333333</v>
       </c>
+      <c r="N214" t="n">
+        <v>0.8695875000000001</v>
+      </c>
     </row>
     <row r="215" ht="16" customHeight="1" s="11">
       <c r="A215" s="18" t="n">
@@ -7213,6 +7822,9 @@
       <c r="M215" s="10" t="n">
         <v>0.8192499999999999</v>
       </c>
+      <c r="N215" t="n">
+        <v>0.7975333333333333</v>
+      </c>
     </row>
     <row r="216" ht="16" customHeight="1" s="11">
       <c r="A216" s="18" t="n">
@@ -7245,6 +7857,9 @@
       <c r="M216" s="10" t="n">
         <v>0.9631874999999999</v>
       </c>
+      <c r="N216" t="n">
+        <v>0.9340714285714286</v>
+      </c>
     </row>
     <row r="217" ht="16" customHeight="1" s="11">
       <c r="A217" s="18" t="n">
@@ -7277,6 +7892,9 @@
       <c r="M217" s="10" t="n">
         <v>0.8031499999999999</v>
       </c>
+      <c r="N217" t="n">
+        <v>0.89367</v>
+      </c>
     </row>
     <row r="218" ht="16" customHeight="1" s="11">
       <c r="A218" s="18" t="n">
@@ -7306,8 +7924,11 @@
       <c r="K218" s="10" t="n">
         <v>0.76554</v>
       </c>
-      <c r="M218" t="n">
+      <c r="M218" s="10" t="n">
         <v>0.851175</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0.9314875</v>
       </c>
     </row>
     <row r="219" ht="16" customHeight="1" s="11">
@@ -7338,8 +7959,11 @@
       <c r="K219" s="10" t="n">
         <v>0.7835375</v>
       </c>
-      <c r="M219" t="n">
+      <c r="M219" s="10" t="n">
         <v>0.9032555555555556</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0.8687400000000001</v>
       </c>
     </row>
     <row r="220" ht="16" customHeight="1" s="11">
@@ -7370,8 +7994,11 @@
       <c r="K220" s="10" t="n">
         <v>0.701</v>
       </c>
-      <c r="M220" t="n">
+      <c r="M220" s="10" t="n">
         <v>0.8391299999999999</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0.8081230769230771</v>
       </c>
     </row>
     <row r="221" ht="16" customHeight="1" s="11">
@@ -7402,8 +8029,11 @@
       <c r="K221" s="10" t="n">
         <v>0.71178</v>
       </c>
-      <c r="M221" t="n">
+      <c r="M221" s="10" t="n">
         <v>0.7792000000000001</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0.8773583333333334</v>
       </c>
     </row>
     <row r="222" ht="16" customHeight="1" s="11">
@@ -7434,8 +8064,11 @@
       <c r="K222" s="10" t="n">
         <v>0.7729200000000001</v>
       </c>
-      <c r="M222" t="n">
+      <c r="M222" s="10" t="n">
         <v>0.8301999999999999</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0.8576916666666667</v>
       </c>
     </row>
     <row r="223" ht="16" customHeight="1" s="11">
@@ -7466,8 +8099,11 @@
       <c r="K223" s="10" t="n">
         <v>0.741075</v>
       </c>
-      <c r="M223" t="n">
+      <c r="M223" s="10" t="n">
         <v>0.7985916666666667</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0.75815</v>
       </c>
     </row>
     <row r="224" ht="16" customHeight="1" s="11">
@@ -7498,8 +8134,11 @@
       <c r="K224" s="10" t="n">
         <v>0.73814</v>
       </c>
-      <c r="M224" t="n">
+      <c r="M224" s="10" t="n">
         <v>0.7278666666666668</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0.8044777777777778</v>
       </c>
     </row>
     <row r="225" ht="16" customHeight="1" s="11">
@@ -7530,8 +8169,11 @@
       <c r="K225" s="10" t="n">
         <v>0.7081166666666669</v>
       </c>
-      <c r="M225" t="n">
+      <c r="M225" s="10" t="n">
         <v>0.6041769230769231</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0.8150111111111111</v>
       </c>
     </row>
     <row r="226" ht="16" customHeight="1" s="11">
@@ -7562,8 +8204,11 @@
       <c r="K226" s="10" t="n">
         <v>0.748016666666667</v>
       </c>
-      <c r="M226" t="n">
+      <c r="M226" s="10" t="n">
         <v>0.62185</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0.5669454545454545</v>
       </c>
     </row>
     <row r="227" ht="16" customHeight="1" s="11">
@@ -7594,8 +8239,11 @@
       <c r="K227" s="10" t="n">
         <v>0.65868</v>
       </c>
-      <c r="M227" t="n">
+      <c r="M227" s="10" t="n">
         <v>0.8665538461538461</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0.66072</v>
       </c>
     </row>
     <row r="228" ht="16" customHeight="1" s="11">
@@ -7626,8 +8274,11 @@
       <c r="K228" s="10" t="n">
         <v>0.671</v>
       </c>
-      <c r="M228" t="n">
+      <c r="M228" s="10" t="n">
         <v>0.6977999999999999</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0.6590916666666666</v>
       </c>
     </row>
     <row r="229" ht="16" customHeight="1" s="11">
@@ -7658,8 +8309,11 @@
       <c r="K229" s="10" t="n">
         <v>0.6813</v>
       </c>
-      <c r="M229" t="n">
+      <c r="M229" s="10" t="n">
         <v>0.7325818181818182</v>
+      </c>
+      <c r="N229" t="n">
+        <v>0.7596999999999999</v>
       </c>
     </row>
     <row r="230" ht="16" customHeight="1" s="11">
@@ -7690,8 +8344,11 @@
       <c r="K230" s="10" t="n">
         <v>0.73034</v>
       </c>
-      <c r="M230" t="n">
+      <c r="M230" s="10" t="n">
         <v>0.8012909090909091</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0.6077499999999999</v>
       </c>
     </row>
     <row r="231" ht="16" customHeight="1" s="11">
@@ -7722,8 +8379,11 @@
       <c r="K231" s="10" t="n">
         <v>0.711971428571429</v>
       </c>
-      <c r="M231" t="n">
+      <c r="M231" s="10" t="n">
         <v>0.6818076923076923</v>
+      </c>
+      <c r="N231" t="n">
+        <v>0.7041000000000001</v>
       </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="11">
@@ -7754,8 +8414,11 @@
       <c r="K232" s="10" t="n">
         <v>0.695742857142857</v>
       </c>
-      <c r="M232" t="n">
+      <c r="M232" s="10" t="n">
         <v>0.7709357142857144</v>
+      </c>
+      <c r="N232" t="n">
+        <v>0.7224444444444443</v>
       </c>
     </row>
     <row r="233" ht="16" customHeight="1" s="11">
@@ -7786,8 +8449,11 @@
       <c r="K233" s="10" t="n">
         <v>0.74025</v>
       </c>
-      <c r="M233" t="n">
+      <c r="M233" s="10" t="n">
         <v>0.79527</v>
+      </c>
+      <c r="N233" t="n">
+        <v>0.77475</v>
       </c>
     </row>
     <row r="234" ht="16" customHeight="1" s="11">
@@ -7818,8 +8484,11 @@
       <c r="K234" s="10" t="n">
         <v>0.66184</v>
       </c>
-      <c r="M234" t="n">
+      <c r="M234" s="10" t="n">
         <v>0.6966333333333333</v>
+      </c>
+      <c r="N234" t="n">
+        <v>0.7979375</v>
       </c>
     </row>
     <row r="235" ht="16" customHeight="1" s="11">
@@ -7850,8 +8519,11 @@
       <c r="K235" s="10" t="n">
         <v>0.656666666666667</v>
       </c>
-      <c r="M235" t="n">
+      <c r="M235" s="10" t="n">
         <v>0.7867416666666666</v>
+      </c>
+      <c r="N235" t="n">
+        <v>0.7042444444444445</v>
       </c>
     </row>
     <row r="236" ht="16" customHeight="1" s="11">
@@ -7882,8 +8554,11 @@
       <c r="K236" s="10" t="n">
         <v>0.676842857142857</v>
       </c>
-      <c r="M236" t="n">
+      <c r="M236" s="10" t="n">
         <v>0.70808</v>
+      </c>
+      <c r="N236" t="n">
+        <v>0.6681818181818181</v>
       </c>
     </row>
     <row r="237" ht="16" customHeight="1" s="11">
@@ -7914,8 +8589,11 @@
       <c r="K237" s="10" t="n">
         <v>0.755783333333334</v>
       </c>
-      <c r="M237" t="n">
+      <c r="M237" s="10" t="n">
         <v>0.7024285714285715</v>
+      </c>
+      <c r="N237" t="n">
+        <v>0.74951</v>
       </c>
     </row>
     <row r="238" ht="16" customHeight="1" s="11">
@@ -7946,8 +8624,11 @@
       <c r="K238" s="10" t="n">
         <v>0.7425428571428569</v>
       </c>
-      <c r="M238" t="n">
+      <c r="M238" s="10" t="n">
         <v>0.7859166666666667</v>
+      </c>
+      <c r="N238" t="n">
+        <v>0.7732</v>
       </c>
     </row>
     <row r="239" ht="16" customHeight="1" s="11">
@@ -7978,8 +8659,11 @@
       <c r="K239" s="10" t="n">
         <v>0.752571428571429</v>
       </c>
-      <c r="M239" t="n">
+      <c r="M239" s="10" t="n">
         <v>0.8797727272727273</v>
+      </c>
+      <c r="N239" t="n">
+        <v>0.66165</v>
       </c>
     </row>
     <row r="240" ht="16" customHeight="1" s="11">
@@ -8010,8 +8694,11 @@
       <c r="K240" s="10" t="n">
         <v>0.756825</v>
       </c>
-      <c r="M240" t="n">
+      <c r="M240" s="10" t="n">
         <v>0.5745181818181819</v>
+      </c>
+      <c r="N240" t="n">
+        <v>0.6185555555555556</v>
       </c>
     </row>
     <row r="241" ht="16" customHeight="1" s="11">
@@ -8042,8 +8729,11 @@
       <c r="K241" s="10" t="n">
         <v>0.711822222222222</v>
       </c>
-      <c r="M241" t="n">
+      <c r="M241" s="10" t="n">
         <v>0.7170666666666667</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0.9008199999999998</v>
       </c>
     </row>
     <row r="242" ht="16" customHeight="1" s="11">
@@ -8074,8 +8764,11 @@
       <c r="K242" s="10" t="n">
         <v>0.622116666666667</v>
       </c>
-      <c r="M242" t="n">
+      <c r="M242" s="10" t="n">
         <v>0.6881749999999999</v>
+      </c>
+      <c r="N242" t="n">
+        <v>0.549875</v>
       </c>
     </row>
     <row r="243" ht="16" customHeight="1" s="11">
@@ -8106,8 +8799,11 @@
       <c r="K243" s="10" t="n">
         <v>0.722125</v>
       </c>
-      <c r="M243" t="n">
+      <c r="M243" s="10" t="n">
         <v>0.6048416666666667</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0.7113833333333331</v>
       </c>
     </row>
     <row r="244" ht="16" customHeight="1" s="11">
@@ -8138,8 +8834,11 @@
       <c r="K244" s="10" t="n">
         <v>0.6569</v>
       </c>
-      <c r="M244" t="n">
+      <c r="M244" s="10" t="n">
         <v>0.5412363636363636</v>
+      </c>
+      <c r="N244" t="n">
+        <v>0.6219333333333333</v>
       </c>
     </row>
     <row r="245" ht="16" customHeight="1" s="11">
@@ -8170,8 +8869,11 @@
       <c r="K245" s="10" t="n">
         <v>0.65505</v>
       </c>
-      <c r="M245" t="n">
+      <c r="M245" s="10" t="n">
         <v>0.7234444444444443</v>
+      </c>
+      <c r="N245" t="n">
+        <v>0.63115</v>
       </c>
     </row>
     <row r="246" ht="16" customHeight="1" s="11">
@@ -8202,8 +8904,11 @@
       <c r="K246" s="10" t="n">
         <v>0.72412</v>
       </c>
-      <c r="M246" t="n">
+      <c r="M246" s="10" t="n">
         <v>0.8002272727272728</v>
+      </c>
+      <c r="N246" t="n">
+        <v>0.50536</v>
       </c>
     </row>
     <row r="247" ht="16" customHeight="1" s="11">
@@ -8234,8 +8939,11 @@
       <c r="K247" s="10" t="n">
         <v>0.684357142857143</v>
       </c>
-      <c r="M247" t="n">
+      <c r="M247" s="10" t="n">
         <v>0.6703363636363636</v>
+      </c>
+      <c r="N247" t="n">
+        <v>0.5980692307692308</v>
       </c>
     </row>
     <row r="248" ht="16" customHeight="1" s="11">
@@ -8266,8 +8974,11 @@
       <c r="K248" s="10" t="n">
         <v>0.729033333333333</v>
       </c>
-      <c r="M248" t="n">
+      <c r="M248" s="10" t="n">
         <v>0.6680307692307692</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0.6073428571428572</v>
       </c>
     </row>
     <row r="249" ht="16" customHeight="1" s="11">
@@ -8298,8 +9009,11 @@
       <c r="K249" s="10" t="n">
         <v>0.6624</v>
       </c>
-      <c r="M249" t="n">
+      <c r="M249" s="10" t="n">
         <v>0.6627599999999999</v>
+      </c>
+      <c r="N249" t="n">
+        <v>0.7083636363636364</v>
       </c>
     </row>
     <row r="250" ht="16" customHeight="1" s="11">
@@ -8330,8 +9044,11 @@
       <c r="K250" s="10" t="n">
         <v>0.75966</v>
       </c>
-      <c r="M250" t="n">
+      <c r="M250" s="10" t="n">
         <v>0.8192000000000002</v>
+      </c>
+      <c r="N250" t="n">
+        <v>0.725925</v>
       </c>
     </row>
     <row r="251" ht="16" customHeight="1" s="11">
@@ -8362,8 +9079,11 @@
       <c r="K251" s="10" t="n">
         <v>0.691833333333333</v>
       </c>
-      <c r="M251" t="n">
+      <c r="M251" s="10" t="n">
         <v>0.6285545454545455</v>
+      </c>
+      <c r="N251" t="n">
+        <v>0.6767545454545454</v>
       </c>
     </row>
     <row r="252" ht="16" customHeight="1" s="11">
@@ -8394,8 +9114,11 @@
       <c r="K252" s="10" t="n">
         <v>0.739833333333333</v>
       </c>
-      <c r="M252" t="n">
+      <c r="M252" s="10" t="n">
         <v>0.7125642857142858</v>
+      </c>
+      <c r="N252" t="n">
+        <v>0.7953600000000001</v>
       </c>
     </row>
     <row r="253" ht="16" customHeight="1" s="11">
@@ -8426,8 +9149,11 @@
       <c r="K253" s="10" t="n">
         <v>0.685366666666667</v>
       </c>
-      <c r="M253" t="n">
+      <c r="M253" s="10" t="n">
         <v>0.795490909090909</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0.7009833333333333</v>
       </c>
     </row>
     <row r="254" ht="16" customHeight="1" s="11">
@@ -8458,8 +9184,11 @@
       <c r="K254" s="10" t="n">
         <v>0.7075222222222221</v>
       </c>
-      <c r="M254" t="n">
+      <c r="M254" s="10" t="n">
         <v>0.7667599999999999</v>
+      </c>
+      <c r="N254" t="n">
+        <v>0.745990909090909</v>
       </c>
     </row>
     <row r="255" ht="16" customHeight="1" s="11">
@@ -8490,8 +9219,11 @@
       <c r="K255" s="10" t="n">
         <v>0.744633333333333</v>
       </c>
-      <c r="M255" t="n">
+      <c r="M255" s="10" t="n">
         <v>0.6928166666666667</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0.7475909090909091</v>
       </c>
     </row>
     <row r="256" ht="16" customHeight="1" s="11">
@@ -8522,8 +9254,11 @@
       <c r="K256" s="10" t="n">
         <v>0.7101666666666669</v>
       </c>
-      <c r="M256" t="n">
+      <c r="M256" s="10" t="n">
         <v>0.6839642857142856</v>
+      </c>
+      <c r="N256" t="n">
+        <v>0.672342857142857</v>
       </c>
     </row>
     <row r="257" ht="16" customHeight="1" s="11">
@@ -8554,8 +9289,11 @@
       <c r="K257" s="10" t="n">
         <v>0.695911111111111</v>
       </c>
-      <c r="M257" t="n">
+      <c r="M257" s="10" t="n">
         <v>0.622</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0.6914090909090909</v>
       </c>
     </row>
     <row r="258" ht="16" customHeight="1" s="11">
@@ -8586,8 +9324,11 @@
       <c r="K258" s="10" t="n">
         <v>0.672633333333333</v>
       </c>
-      <c r="M258" t="n">
+      <c r="M258" s="10" t="n">
         <v>0.6281307692307692</v>
+      </c>
+      <c r="N258" t="n">
+        <v>0.7792333333333333</v>
       </c>
     </row>
     <row r="259" ht="16" customHeight="1" s="11">
@@ -8618,8 +9359,11 @@
       <c r="K259" s="10" t="n">
         <v>0.73278</v>
       </c>
-      <c r="M259" t="n">
+      <c r="M259" s="10" t="n">
         <v>0.7049785714285715</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0.5992200000000001</v>
       </c>
     </row>
     <row r="260" ht="16" customHeight="1" s="11">
@@ -8650,8 +9394,11 @@
       <c r="K260" s="10" t="n">
         <v>0.735514285714286</v>
       </c>
-      <c r="M260" t="n">
+      <c r="M260" s="10" t="n">
         <v>0.7828333333333335</v>
+      </c>
+      <c r="N260" t="n">
+        <v>0.6557181818181819</v>
       </c>
     </row>
     <row r="261" ht="16" customHeight="1" s="11">
@@ -8682,8 +9429,11 @@
       <c r="K261" s="10" t="n">
         <v>0.717983333333333</v>
       </c>
-      <c r="M261" t="n">
+      <c r="M261" s="10" t="n">
         <v>0.5884153846153846</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0.7368400000000002</v>
       </c>
     </row>
     <row r="262" ht="16" customHeight="1" s="11">
@@ -8714,8 +9464,11 @@
       <c r="K262" s="10" t="n">
         <v>0.77455</v>
       </c>
-      <c r="M262" t="n">
+      <c r="M262" s="10" t="n">
         <v>0.7360545454545453</v>
+      </c>
+      <c r="N262" t="n">
+        <v>0.57424</v>
       </c>
     </row>
     <row r="263" ht="16" customHeight="1" s="11">
@@ -8746,8 +9499,11 @@
       <c r="K263" s="10" t="n">
         <v>0.698</v>
       </c>
-      <c r="M263" t="n">
+      <c r="M263" s="10" t="n">
         <v>0.46515</v>
+      </c>
+      <c r="N263" t="n">
+        <v>0.7599400000000001</v>
       </c>
     </row>
     <row r="264" ht="16" customHeight="1" s="11">
@@ -8778,8 +9534,11 @@
       <c r="K264" s="10" t="n">
         <v>0.75418</v>
       </c>
-      <c r="M264" t="n">
+      <c r="M264" s="10" t="n">
         <v>0.7920272727272727</v>
+      </c>
+      <c r="N264" t="n">
+        <v>0.6841</v>
       </c>
     </row>
     <row r="265" ht="16" customHeight="1" s="11">
@@ -8810,8 +9569,11 @@
       <c r="K265" s="10" t="n">
         <v>0.741444444444444</v>
       </c>
-      <c r="M265" t="n">
+      <c r="M265" s="10" t="n">
         <v>0.6039692307692308</v>
+      </c>
+      <c r="N265" t="n">
+        <v>0.6193363636363637</v>
       </c>
     </row>
     <row r="266" ht="16" customHeight="1" s="11">
@@ -8842,8 +9604,11 @@
       <c r="K266" s="10" t="n">
         <v>0.65856</v>
       </c>
-      <c r="M266" t="n">
+      <c r="M266" s="10" t="n">
         <v>0.7218666666666667</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0.7343499999999999</v>
       </c>
     </row>
     <row r="267" ht="16" customHeight="1" s="11">
@@ -8874,8 +9639,11 @@
       <c r="K267" s="10" t="n">
         <v>0.7156875</v>
       </c>
-      <c r="M267" t="n">
+      <c r="M267" s="10" t="n">
         <v>0.7068363636363637</v>
+      </c>
+      <c r="N267" t="n">
+        <v>0.7803125</v>
       </c>
     </row>
     <row r="268" ht="16" customHeight="1" s="11">
@@ -8906,8 +9674,11 @@
       <c r="K268" s="10" t="n">
         <v>0.6874125</v>
       </c>
-      <c r="M268" t="n">
+      <c r="M268" s="10" t="n">
         <v>0.8097200000000001</v>
+      </c>
+      <c r="N268" t="n">
+        <v>0.6929444444444444</v>
       </c>
     </row>
     <row r="269" ht="16" customHeight="1" s="11">
@@ -8938,8 +9709,11 @@
       <c r="K269" s="10" t="n">
         <v>0.76126</v>
       </c>
-      <c r="M269" t="n">
+      <c r="M269" s="10" t="n">
         <v>0.6770230769230768</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0.73512</v>
       </c>
     </row>
     <row r="270" ht="16" customHeight="1" s="11">
@@ -8970,8 +9744,11 @@
       <c r="K270" s="10" t="n">
         <v>0.7598857142857141</v>
       </c>
-      <c r="M270" t="n">
+      <c r="M270" s="10" t="n">
         <v>0.662811111111111</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0.7524</v>
       </c>
     </row>
     <row r="271" ht="16" customHeight="1" s="11">
@@ -9002,8 +9779,11 @@
       <c r="K271" s="10" t="n">
         <v>0.682716666666667</v>
       </c>
-      <c r="M271" t="n">
+      <c r="M271" s="10" t="n">
         <v>0.7926916666666665</v>
+      </c>
+      <c r="N271" t="n">
+        <v>0.6547999999999999</v>
       </c>
     </row>
     <row r="272" ht="16" customHeight="1" s="11">
@@ -9034,8 +9814,11 @@
       <c r="K272" s="10" t="n">
         <v>0.68924</v>
       </c>
-      <c r="M272" t="n">
+      <c r="M272" s="10" t="n">
         <v>0.5866500000000001</v>
+      </c>
+      <c r="N272" t="n">
+        <v>0.6574249999999999</v>
       </c>
     </row>
     <row r="273" ht="16" customHeight="1" s="11">
@@ -9066,8 +9849,11 @@
       <c r="K273" s="10" t="n">
         <v>0.681357142857143</v>
       </c>
-      <c r="M273" t="n">
+      <c r="M273" s="10" t="n">
         <v>0.6981999999999999</v>
+      </c>
+      <c r="N273" t="n">
+        <v>0.7640777777777779</v>
       </c>
     </row>
     <row r="274" ht="16" customHeight="1" s="11">
@@ -9098,8 +9884,11 @@
       <c r="K274" s="10" t="n">
         <v>0.65382</v>
       </c>
-      <c r="M274" t="n">
+      <c r="M274" s="10" t="n">
         <v>0.7342</v>
+      </c>
+      <c r="N274" t="n">
+        <v>0.7905099999999999</v>
       </c>
     </row>
     <row r="275" ht="16" customHeight="1" s="11">
@@ -9130,8 +9919,11 @@
       <c r="K275" s="10" t="n">
         <v>0.7396875000000001</v>
       </c>
-      <c r="M275" t="n">
+      <c r="M275" s="10" t="n">
         <v>0.804990909090909</v>
+      </c>
+      <c r="N275" t="n">
+        <v>0.6994666666666666</v>
       </c>
     </row>
     <row r="276" ht="16" customHeight="1" s="11">
@@ -9162,8 +9954,11 @@
       <c r="K276" s="10" t="n">
         <v>0.7282999999999999</v>
       </c>
-      <c r="M276" t="n">
+      <c r="M276" s="10" t="n">
         <v>0.790575</v>
+      </c>
+      <c r="N276" t="n">
+        <v>0.5936166666666667</v>
       </c>
     </row>
     <row r="277" ht="16" customHeight="1" s="11">
@@ -9194,8 +9989,11 @@
       <c r="K277" s="10" t="n">
         <v>0.66762</v>
       </c>
-      <c r="M277" t="n">
+      <c r="M277" s="10" t="n">
         <v>0.6164583333333334</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0.7161333333333333</v>
       </c>
     </row>
     <row r="278" ht="16" customHeight="1" s="11">
@@ -9226,8 +10024,11 @@
       <c r="K278" s="10" t="n">
         <v>0.738225</v>
       </c>
-      <c r="M278" t="n">
+      <c r="M278" s="10" t="n">
         <v>0.7985500000000001</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0.7859636363636363</v>
       </c>
     </row>
     <row r="279" ht="16" customHeight="1" s="11">
@@ -9258,8 +10059,11 @@
       <c r="K279" s="10" t="n">
         <v>0.734275</v>
       </c>
-      <c r="M279" t="n">
+      <c r="M279" s="10" t="n">
         <v>0.79965</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0.6587833333333333</v>
       </c>
     </row>
     <row r="280" ht="16" customHeight="1" s="11">
@@ -9290,8 +10094,11 @@
       <c r="K280" s="10" t="n">
         <v>0.738728571428571</v>
       </c>
-      <c r="M280" t="n">
+      <c r="M280" s="10" t="n">
         <v>0.67042</v>
+      </c>
+      <c r="N280" t="n">
+        <v>0.6964666666666667</v>
       </c>
     </row>
     <row r="281" ht="16" customHeight="1" s="11">
@@ -9322,8 +10129,11 @@
       <c r="K281" s="10" t="n">
         <v>0.73498</v>
       </c>
-      <c r="M281" t="n">
+      <c r="M281" s="10" t="n">
         <v>0.6719083333333332</v>
+      </c>
+      <c r="N281" t="n">
+        <v>0.6656000000000001</v>
       </c>
     </row>
     <row r="282" ht="16" customHeight="1" s="11">
@@ -9354,8 +10164,11 @@
       <c r="K282" s="10" t="n">
         <v>0.758842857142857</v>
       </c>
-      <c r="M282" t="n">
+      <c r="M282" s="10" t="n">
         <v>0.7953583333333333</v>
+      </c>
+      <c r="N282" t="n">
+        <v>0.7348636363636364</v>
       </c>
     </row>
     <row r="283" ht="16" customHeight="1" s="11">
@@ -9386,8 +10199,11 @@
       <c r="K283" s="10" t="n">
         <v>0.681328571428571</v>
       </c>
-      <c r="M283" t="n">
+      <c r="M283" s="10" t="n">
         <v>0.7745599999999999</v>
+      </c>
+      <c r="N283" t="n">
+        <v>0.8373299999999999</v>
       </c>
     </row>
     <row r="284" ht="16" customHeight="1" s="11">
@@ -9418,8 +10234,11 @@
       <c r="K284" s="10" t="n">
         <v>0.71275</v>
       </c>
-      <c r="M284" t="n">
+      <c r="M284" s="10" t="n">
         <v>0.6955</v>
+      </c>
+      <c r="N284" t="n">
+        <v>0.6446444444444445</v>
       </c>
     </row>
     <row r="285" ht="16" customHeight="1" s="11">
@@ -9450,8 +10269,11 @@
       <c r="K285" s="10" t="n">
         <v>0.77206</v>
       </c>
-      <c r="M285" t="n">
+      <c r="M285" s="10" t="n">
         <v>0.8084416666666668</v>
+      </c>
+      <c r="N285" t="n">
+        <v>0.6422899999999999</v>
       </c>
     </row>
     <row r="286" ht="16" customHeight="1" s="11">
@@ -9482,8 +10304,11 @@
       <c r="K286" s="10" t="n">
         <v>0.690075</v>
       </c>
-      <c r="M286" t="n">
+      <c r="M286" s="10" t="n">
         <v>0.6684363636363636</v>
+      </c>
+      <c r="N286" t="n">
+        <v>0.52607</v>
       </c>
     </row>
     <row r="287" ht="16" customHeight="1" s="11">
@@ -9514,8 +10339,11 @@
       <c r="K287" s="10" t="n">
         <v>0.672714285714286</v>
       </c>
-      <c r="M287" t="n">
+      <c r="M287" s="10" t="n">
         <v>0.6285461538461538</v>
+      </c>
+      <c r="N287" t="n">
+        <v>0.6165222222222222</v>
       </c>
     </row>
     <row r="288" ht="16" customHeight="1" s="11">
@@ -9546,8 +10374,11 @@
       <c r="K288" s="10" t="n">
         <v>0.750666666666667</v>
       </c>
-      <c r="M288" t="n">
+      <c r="M288" s="10" t="n">
         <v>0.6467636363636364</v>
+      </c>
+      <c r="N288" t="n">
+        <v>0.6945714285714286</v>
       </c>
     </row>
     <row r="289" ht="16" customHeight="1" s="11">
@@ -9578,8 +10409,11 @@
       <c r="K289" s="10" t="n">
         <v>0.74598</v>
       </c>
-      <c r="M289" t="n">
+      <c r="M289" s="10" t="n">
         <v>0.5219999999999999</v>
+      </c>
+      <c r="N289" t="n">
+        <v>0.6649181818181817</v>
       </c>
     </row>
     <row r="290" ht="16" customHeight="1" s="11">
@@ -9610,8 +10444,11 @@
       <c r="K290" s="10" t="n">
         <v>0.70002</v>
       </c>
-      <c r="M290" t="n">
+      <c r="M290" s="10" t="n">
         <v>0.695576923076923</v>
+      </c>
+      <c r="N290" t="n">
+        <v>0.70416</v>
       </c>
     </row>
     <row r="291" ht="16" customHeight="1" s="11">
@@ -9642,8 +10479,11 @@
       <c r="K291" s="10" t="n">
         <v>0.706614285714286</v>
       </c>
-      <c r="M291" t="n">
+      <c r="M291" s="10" t="n">
         <v>0.5340888888888888</v>
+      </c>
+      <c r="N291" t="n">
+        <v>0.6937599999999999</v>
       </c>
     </row>
     <row r="292" ht="16" customHeight="1" s="11">
@@ -9674,8 +10514,11 @@
       <c r="K292" s="10" t="n">
         <v>0.623233333333333</v>
       </c>
-      <c r="M292" t="n">
+      <c r="M292" s="10" t="n">
         <v>0.6761</v>
+      </c>
+      <c r="N292" t="n">
+        <v>0.80542</v>
       </c>
     </row>
     <row r="293" ht="16" customHeight="1" s="11">
@@ -9706,8 +10549,11 @@
       <c r="K293" s="10" t="n">
         <v>0.7419</v>
       </c>
-      <c r="M293" t="n">
+      <c r="M293" s="10" t="n">
         <v>0.7425916666666668</v>
+      </c>
+      <c r="N293" t="n">
+        <v>0.5407875</v>
       </c>
     </row>
     <row r="294" ht="16" customHeight="1" s="11">
@@ -9738,8 +10584,11 @@
       <c r="K294" s="10" t="n">
         <v>0.700716666666667</v>
       </c>
-      <c r="M294" t="n">
+      <c r="M294" s="10" t="n">
         <v>0.7010454545454546</v>
+      </c>
+      <c r="N294" t="n">
+        <v>0.85695</v>
       </c>
     </row>
     <row r="295" ht="16" customHeight="1" s="11">
@@ -9770,8 +10619,11 @@
       <c r="K295" s="10" t="n">
         <v>0.71846</v>
       </c>
-      <c r="M295" t="n">
+      <c r="M295" s="10" t="n">
         <v>0.6985111111111111</v>
+      </c>
+      <c r="N295" t="n">
+        <v>0.6269899999999999</v>
       </c>
     </row>
     <row r="296" ht="16" customHeight="1" s="11">
@@ -9802,8 +10654,11 @@
       <c r="K296" s="10" t="n">
         <v>0.776533333333333</v>
       </c>
-      <c r="M296" t="n">
+      <c r="M296" s="10" t="n">
         <v>0.5680538461538462</v>
+      </c>
+      <c r="N296" t="n">
+        <v>0.7906875</v>
       </c>
     </row>
     <row r="297" ht="16" customHeight="1" s="11">
@@ -9834,8 +10689,11 @@
       <c r="K297" s="10" t="n">
         <v>0.7534999999999999</v>
       </c>
-      <c r="M297" t="n">
+      <c r="M297" s="10" t="n">
         <v>0.55708</v>
+      </c>
+      <c r="N297" t="n">
+        <v>0.72844</v>
       </c>
     </row>
     <row r="298" ht="16" customHeight="1" s="11">
@@ -9866,8 +10724,11 @@
       <c r="K298" s="10" t="n">
         <v>0.7107</v>
       </c>
-      <c r="M298" t="n">
+      <c r="M298" s="10" t="n">
         <v>0.6442272727272728</v>
+      </c>
+      <c r="N298" t="n">
+        <v>0.7217</v>
       </c>
     </row>
     <row r="299" ht="16" customHeight="1" s="11">
@@ -9898,8 +10759,11 @@
       <c r="K299" s="10" t="n">
         <v>0.708555555555556</v>
       </c>
-      <c r="M299" t="n">
+      <c r="M299" s="10" t="n">
         <v>0.7373249999999999</v>
+      </c>
+      <c r="N299" t="n">
+        <v>0.5995818181818181</v>
       </c>
     </row>
     <row r="300" ht="16" customHeight="1" s="11">
@@ -9930,8 +10794,11 @@
       <c r="K300" s="10" t="n">
         <v>0.70448</v>
       </c>
-      <c r="M300" t="n">
+      <c r="M300" s="10" t="n">
         <v>0.5086545454545456</v>
+      </c>
+      <c r="N300" t="n">
+        <v>0.7830777777777778</v>
       </c>
     </row>
     <row r="301" ht="16" customHeight="1" s="11">
@@ -9962,8 +10829,11 @@
       <c r="K301" s="10" t="n">
         <v>0.721657142857143</v>
       </c>
-      <c r="M301" t="n">
+      <c r="M301" s="10" t="n">
         <v>0.7366076923076922</v>
+      </c>
+      <c r="N301" t="n">
+        <v>0.6350461538461538</v>
       </c>
     </row>
     <row r="302" ht="16" customHeight="1" s="11">
@@ -9994,8 +10864,11 @@
       <c r="K302" s="10" t="n">
         <v>0.678383333333333</v>
       </c>
-      <c r="M302" t="n">
+      <c r="M302" s="10" t="n">
         <v>0.6941363636363637</v>
+      </c>
+      <c r="N302" t="n">
+        <v>0.6479199999999999</v>
       </c>
     </row>
     <row r="303" ht="16" customHeight="1" s="11">
@@ -10026,8 +10899,11 @@
       <c r="K303" s="10" t="n">
         <v>0.736371428571429</v>
       </c>
-      <c r="M303" t="n">
+      <c r="M303" s="10" t="n">
         <v>0.76358</v>
+      </c>
+      <c r="N303" t="n">
+        <v>0.5394666666666668</v>
       </c>
     </row>
     <row r="304" ht="16" customHeight="1" s="11">
@@ -10058,8 +10934,11 @@
       <c r="K304" s="10" t="n">
         <v>0.74105</v>
       </c>
-      <c r="M304" t="n">
+      <c r="M304" s="10" t="n">
         <v>0.6135900000000001</v>
+      </c>
+      <c r="N304" t="n">
+        <v>0.5691166666666666</v>
       </c>
     </row>
     <row r="305" ht="16" customHeight="1" s="11">
@@ -10090,8 +10969,11 @@
       <c r="K305" s="10" t="n">
         <v>0.7956</v>
       </c>
-      <c r="M305" t="n">
+      <c r="M305" s="10" t="n">
         <v>0.7072000000000001</v>
+      </c>
+      <c r="N305" t="n">
+        <v>0.7358272727272728</v>
       </c>
     </row>
     <row r="306" ht="16" customHeight="1" s="11">
@@ -10122,8 +11004,11 @@
       <c r="K306" s="10" t="n">
         <v>0.675655555555556</v>
       </c>
-      <c r="M306" t="n">
+      <c r="M306" s="10" t="n">
         <v>0.7458</v>
+      </c>
+      <c r="N306" t="n">
+        <v>0.81753</v>
       </c>
     </row>
     <row r="307" ht="16" customHeight="1" s="11">
@@ -10154,8 +11039,11 @@
       <c r="K307" s="10" t="n">
         <v>0.6877</v>
       </c>
-      <c r="M307" t="n">
+      <c r="M307" s="10" t="n">
         <v>0.7621555555555556</v>
+      </c>
+      <c r="N307" t="n">
+        <v>0.62556</v>
       </c>
     </row>
     <row r="308" ht="16" customHeight="1" s="11">
@@ -10186,8 +11074,11 @@
       <c r="K308" s="10" t="n">
         <v>0.741533333333333</v>
       </c>
-      <c r="M308" t="n">
+      <c r="M308" s="10" t="n">
         <v>0.7753181818181819</v>
+      </c>
+      <c r="N308" t="n">
+        <v>0.8653999999999999</v>
       </c>
     </row>
     <row r="309" ht="16" customHeight="1" s="11">
@@ -10218,8 +11109,11 @@
       <c r="K309" s="10" t="n">
         <v>0.630775</v>
       </c>
-      <c r="M309" t="n">
+      <c r="M309" s="10" t="n">
         <v>0.7042700000000001</v>
+      </c>
+      <c r="N309" t="n">
+        <v>0.7075222222222224</v>
       </c>
     </row>
     <row r="310" ht="16" customHeight="1" s="11">
@@ -10250,8 +11144,11 @@
       <c r="K310" s="10" t="n">
         <v>0.617</v>
       </c>
-      <c r="M310" t="n">
+      <c r="M310" s="10" t="n">
         <v>0.6168461538461538</v>
+      </c>
+      <c r="N310" t="n">
+        <v>0.6212636363636364</v>
       </c>
     </row>
     <row r="311" ht="16" customHeight="1" s="11">
@@ -10282,8 +11179,11 @@
       <c r="K311" s="10" t="n">
         <v>0.748666666666667</v>
       </c>
-      <c r="M311" t="n">
+      <c r="M311" s="10" t="n">
         <v>0.6274769230769232</v>
+      </c>
+      <c r="N311" t="n">
+        <v>0.6803666666666666</v>
       </c>
     </row>
     <row r="314" ht="16" customHeight="1" s="11">
@@ -10341,6 +11241,9 @@
       <c r="M316" s="10" t="n">
         <v>0.0081</v>
       </c>
+      <c r="N316" t="n">
+        <v>0.0007</v>
+      </c>
     </row>
     <row r="317" ht="16" customHeight="1" s="11">
       <c r="A317" s="18" t="n">
@@ -10373,6 +11276,9 @@
       <c r="M317" s="10" t="n">
         <v>0.0029</v>
       </c>
+      <c r="N317" t="n">
+        <v>0.0519</v>
+      </c>
     </row>
     <row r="318" ht="16" customHeight="1" s="11">
       <c r="A318" s="18" t="n">
@@ -10405,6 +11311,9 @@
       <c r="M318" s="10" t="n">
         <v>0.0002</v>
       </c>
+      <c r="N318" t="n">
+        <v>0.0149</v>
+      </c>
     </row>
     <row r="319" ht="16" customHeight="1" s="11">
       <c r="A319" s="18" t="n">
@@ -10437,6 +11346,9 @@
       <c r="M319" s="10" t="n">
         <v>0.0074</v>
       </c>
+      <c r="N319" t="n">
+        <v>0.0482</v>
+      </c>
     </row>
     <row r="320" ht="16" customHeight="1" s="11">
       <c r="A320" s="18" t="n">
@@ -10469,6 +11381,9 @@
       <c r="M320" s="10" t="n">
         <v>0.0464</v>
       </c>
+      <c r="N320" t="n">
+        <v>0.07920000000000001</v>
+      </c>
     </row>
     <row r="321" ht="16" customHeight="1" s="11">
       <c r="A321" s="18" t="n">
@@ -10501,6 +11416,9 @@
       <c r="M321" s="10" t="n">
         <v>0.0404</v>
       </c>
+      <c r="N321" t="n">
+        <v>0.0482</v>
+      </c>
     </row>
     <row r="322" ht="16" customHeight="1" s="11">
       <c r="A322" s="18" t="n">
@@ -10530,8 +11448,11 @@
       <c r="K322" s="10" t="n">
         <v>0.1081</v>
       </c>
-      <c r="M322" t="n">
+      <c r="M322" s="10" t="n">
         <v>0.0926</v>
+      </c>
+      <c r="N322" t="n">
+        <v>0.0801</v>
       </c>
     </row>
     <row r="323" ht="16" customHeight="1" s="11">
@@ -10562,8 +11483,11 @@
       <c r="K323" s="10" t="n">
         <v>0.1753</v>
       </c>
-      <c r="M323" t="n">
+      <c r="M323" s="10" t="n">
         <v>0.0309</v>
+      </c>
+      <c r="N323" t="n">
+        <v>0.0856</v>
       </c>
     </row>
     <row r="324" ht="16" customHeight="1" s="11">
@@ -10594,8 +11518,11 @@
       <c r="K324" s="10" t="n">
         <v>0.0728</v>
       </c>
-      <c r="M324" t="n">
+      <c r="M324" s="10" t="n">
         <v>0.0667</v>
+      </c>
+      <c r="N324" t="n">
+        <v>0.0076</v>
       </c>
     </row>
     <row r="325" ht="16" customHeight="1" s="11">
@@ -10626,8 +11553,11 @@
       <c r="K325" s="10" t="n">
         <v>0.0906</v>
       </c>
-      <c r="M325" t="n">
+      <c r="M325" s="10" t="n">
         <v>0.0481</v>
+      </c>
+      <c r="N325" t="n">
+        <v>0.0243</v>
       </c>
     </row>
     <row r="326" ht="16" customHeight="1" s="11">
@@ -10658,8 +11588,11 @@
       <c r="K326" s="10" t="n">
         <v>0.0732</v>
       </c>
-      <c r="M326" t="n">
+      <c r="M326" s="10" t="n">
         <v>0.0888</v>
+      </c>
+      <c r="N326" t="n">
+        <v>0.0687</v>
       </c>
     </row>
     <row r="327" ht="16" customHeight="1" s="11">
@@ -10690,8 +11623,11 @@
       <c r="K327" s="10" t="n">
         <v>0.0704</v>
       </c>
-      <c r="M327" t="n">
+      <c r="M327" s="10" t="n">
         <v>0.0248</v>
+      </c>
+      <c r="N327" t="n">
+        <v>0.048</v>
       </c>
     </row>
     <row r="328" ht="16" customHeight="1" s="11">
@@ -10722,8 +11658,11 @@
       <c r="K328" s="10" t="n">
         <v>0.06710000000000001</v>
       </c>
-      <c r="M328" t="n">
+      <c r="M328" s="10" t="n">
         <v>0.07199999999999999</v>
+      </c>
+      <c r="N328" t="n">
+        <v>0.0723</v>
       </c>
     </row>
     <row r="329" ht="16" customHeight="1" s="11">
@@ -10754,8 +11693,11 @@
       <c r="K329" s="10" t="n">
         <v>0.07630000000000001</v>
       </c>
-      <c r="M329" t="n">
+      <c r="M329" s="10" t="n">
         <v>0.1264</v>
+      </c>
+      <c r="N329" t="n">
+        <v>0.062</v>
       </c>
     </row>
     <row r="330" ht="16" customHeight="1" s="11">
@@ -10786,8 +11728,11 @@
       <c r="K330" s="10" t="n">
         <v>0.135</v>
       </c>
-      <c r="M330" t="n">
+      <c r="M330" s="10" t="n">
         <v>0.0825</v>
+      </c>
+      <c r="N330" t="n">
+        <v>0.0895</v>
       </c>
     </row>
     <row r="331" ht="16" customHeight="1" s="11">
@@ -10818,8 +11763,11 @@
       <c r="K331" s="10" t="n">
         <v>0.1158</v>
       </c>
-      <c r="M331" t="n">
+      <c r="M331" s="10" t="n">
         <v>0.0354</v>
+      </c>
+      <c r="N331" t="n">
+        <v>0.1107</v>
       </c>
     </row>
     <row r="332" ht="16" customHeight="1" s="11">
@@ -10850,8 +11798,11 @@
       <c r="K332" s="10" t="n">
         <v>0.107</v>
       </c>
-      <c r="M332" t="n">
+      <c r="M332" s="10" t="n">
         <v>0.0233</v>
+      </c>
+      <c r="N332" t="n">
+        <v>0.0795</v>
       </c>
     </row>
     <row r="333" ht="16" customHeight="1" s="11">
@@ -10882,8 +11833,11 @@
       <c r="K333" s="10" t="n">
         <v>0.1069</v>
       </c>
-      <c r="M333" t="n">
+      <c r="M333" s="10" t="n">
         <v>0.09470000000000001</v>
+      </c>
+      <c r="N333" t="n">
+        <v>0.1086</v>
       </c>
     </row>
     <row r="334" ht="16" customHeight="1" s="11">
@@ -10914,8 +11868,11 @@
       <c r="K334" s="10" t="n">
         <v>0.1013</v>
       </c>
-      <c r="M334" t="n">
+      <c r="M334" s="10" t="n">
         <v>0.08939999999999999</v>
+      </c>
+      <c r="N334" t="n">
+        <v>0.108</v>
       </c>
     </row>
     <row r="335" ht="16" customHeight="1" s="11">
@@ -10946,8 +11903,11 @@
       <c r="K335" s="10" t="n">
         <v>0.0859</v>
       </c>
-      <c r="M335" t="n">
+      <c r="M335" s="10" t="n">
         <v>0.1058</v>
+      </c>
+      <c r="N335" t="n">
+        <v>0.0961</v>
       </c>
     </row>
     <row r="336" ht="16" customHeight="1" s="11">
@@ -10978,8 +11938,11 @@
       <c r="K336" s="10" t="n">
         <v>0.07580000000000001</v>
       </c>
-      <c r="M336" t="n">
+      <c r="M336" s="10" t="n">
         <v>0.0608</v>
+      </c>
+      <c r="N336" t="n">
+        <v>0.1168</v>
       </c>
     </row>
     <row r="337" ht="16" customHeight="1" s="11">
@@ -11010,8 +11973,11 @@
       <c r="K337" s="10" t="n">
         <v>0.0892</v>
       </c>
-      <c r="M337" t="n">
+      <c r="M337" s="10" t="n">
         <v>0.1024</v>
+      </c>
+      <c r="N337" t="n">
+        <v>0.0888</v>
       </c>
     </row>
     <row r="338" ht="16" customHeight="1" s="11">
@@ -11042,8 +12008,11 @@
       <c r="K338" s="10" t="n">
         <v>0.09619999999999999</v>
       </c>
-      <c r="M338" t="n">
+      <c r="M338" s="10" t="n">
         <v>0.0264</v>
+      </c>
+      <c r="N338" t="n">
+        <v>0.1068</v>
       </c>
     </row>
     <row r="339" ht="16" customHeight="1" s="11">
@@ -11074,8 +12043,11 @@
       <c r="K339" s="10" t="n">
         <v>0.0818</v>
       </c>
-      <c r="M339" t="n">
+      <c r="M339" s="10" t="n">
         <v>0.0331</v>
+      </c>
+      <c r="N339" t="n">
+        <v>0.1391</v>
       </c>
     </row>
     <row r="340" ht="16" customHeight="1" s="11">
@@ -11106,8 +12078,11 @@
       <c r="K340" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M340" t="n">
+      <c r="M340" s="10" t="n">
         <v>0.0495</v>
+      </c>
+      <c r="N340" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="341" ht="16" customHeight="1" s="11">
@@ -11138,8 +12113,11 @@
       <c r="K341" s="10" t="n">
         <v>0.115</v>
       </c>
-      <c r="M341" t="n">
+      <c r="M341" s="10" t="n">
         <v>0.0473</v>
+      </c>
+      <c r="N341" t="n">
+        <v>0.1081</v>
       </c>
     </row>
     <row r="342" ht="16" customHeight="1" s="11">
@@ -11170,8 +12148,11 @@
       <c r="K342" s="10" t="n">
         <v>0.1295</v>
       </c>
-      <c r="M342" t="n">
+      <c r="M342" s="10" t="n">
         <v>0.0505</v>
+      </c>
+      <c r="N342" t="n">
+        <v>0.0795</v>
       </c>
     </row>
     <row r="343" ht="16" customHeight="1" s="11">
@@ -11202,8 +12183,11 @@
       <c r="K343" s="10" t="n">
         <v>0.0982</v>
       </c>
-      <c r="M343" t="n">
+      <c r="M343" s="10" t="n">
         <v>0.0395</v>
+      </c>
+      <c r="N343" t="n">
+        <v>0.0965</v>
       </c>
     </row>
     <row r="344" ht="16" customHeight="1" s="11">
@@ -11234,8 +12218,11 @@
       <c r="K344" s="10" t="n">
         <v>0.0921</v>
       </c>
-      <c r="M344" t="n">
+      <c r="M344" s="10" t="n">
         <v>0.0259</v>
+      </c>
+      <c r="N344" t="n">
+        <v>0.09470000000000001</v>
       </c>
     </row>
     <row r="345" ht="16" customHeight="1" s="11">
@@ -11266,8 +12253,11 @@
       <c r="K345" s="10" t="n">
         <v>0.0825</v>
       </c>
-      <c r="M345" t="n">
+      <c r="M345" s="10" t="n">
         <v>0.0395</v>
+      </c>
+      <c r="N345" t="n">
+        <v>0.108</v>
       </c>
     </row>
     <row r="346" ht="16" customHeight="1" s="11">
@@ -11298,8 +12288,11 @@
       <c r="K346" s="10" t="n">
         <v>0.0809</v>
       </c>
-      <c r="M346" t="n">
+      <c r="M346" s="10" t="n">
         <v>0.03</v>
+      </c>
+      <c r="N346" t="n">
+        <v>0.1004</v>
       </c>
     </row>
     <row r="347" ht="16" customHeight="1" s="11">
@@ -11330,8 +12323,11 @@
       <c r="K347" s="10" t="n">
         <v>0.0873</v>
       </c>
-      <c r="M347" t="n">
+      <c r="M347" s="10" t="n">
         <v>0.0271</v>
+      </c>
+      <c r="N347" t="n">
+        <v>0.1094</v>
       </c>
     </row>
     <row r="348" ht="16" customHeight="1" s="11">
@@ -11362,8 +12358,11 @@
       <c r="K348" s="10" t="n">
         <v>0.0688</v>
       </c>
-      <c r="M348" t="n">
+      <c r="M348" s="10" t="n">
         <v>0.0497</v>
+      </c>
+      <c r="N348" t="n">
+        <v>0.1047</v>
       </c>
     </row>
     <row r="349" ht="16" customHeight="1" s="11">
@@ -11394,8 +12393,11 @@
       <c r="K349" s="10" t="n">
         <v>0.0665</v>
       </c>
-      <c r="M349" t="n">
+      <c r="M349" s="10" t="n">
         <v>0.0447</v>
+      </c>
+      <c r="N349" t="n">
+        <v>0.09279999999999999</v>
       </c>
     </row>
     <row r="350" ht="16" customHeight="1" s="11">
@@ -11426,8 +12428,11 @@
       <c r="K350" s="10" t="n">
         <v>0.0731</v>
       </c>
-      <c r="M350" t="n">
+      <c r="M350" s="10" t="n">
         <v>0.0341</v>
+      </c>
+      <c r="N350" t="n">
+        <v>0.1028</v>
       </c>
     </row>
     <row r="351" ht="16" customHeight="1" s="11">
@@ -11458,8 +12463,11 @@
       <c r="K351" s="10" t="n">
         <v>0.1057</v>
       </c>
-      <c r="M351" t="n">
+      <c r="M351" s="10" t="n">
         <v>0.0332</v>
+      </c>
+      <c r="N351" t="n">
+        <v>0.08359999999999999</v>
       </c>
     </row>
     <row r="352" ht="16" customHeight="1" s="11">
@@ -11490,8 +12498,11 @@
       <c r="K352" s="10" t="n">
         <v>0.0988</v>
       </c>
-      <c r="M352" t="n">
+      <c r="M352" s="10" t="n">
         <v>0.0424</v>
+      </c>
+      <c r="N352" t="n">
+        <v>0.1027</v>
       </c>
     </row>
     <row r="353" ht="16" customHeight="1" s="11">
@@ -11522,8 +12533,11 @@
       <c r="K353" s="10" t="n">
         <v>0.0796</v>
       </c>
-      <c r="M353" t="n">
+      <c r="M353" s="10" t="n">
         <v>0.0365</v>
+      </c>
+      <c r="N353" t="n">
+        <v>0.1052</v>
       </c>
     </row>
     <row r="354" ht="16" customHeight="1" s="11">
@@ -11554,8 +12568,11 @@
       <c r="K354" s="10" t="n">
         <v>0.0689</v>
       </c>
-      <c r="M354" t="n">
+      <c r="M354" s="10" t="n">
         <v>0.0342</v>
+      </c>
+      <c r="N354" t="n">
+        <v>0.0919</v>
       </c>
     </row>
     <row r="355" ht="16" customHeight="1" s="11">
@@ -11586,8 +12603,11 @@
       <c r="K355" s="10" t="n">
         <v>0.0832</v>
       </c>
-      <c r="M355" t="n">
+      <c r="M355" s="10" t="n">
         <v>0.0555</v>
+      </c>
+      <c r="N355" t="n">
+        <v>0.1087</v>
       </c>
     </row>
     <row r="356" ht="16" customHeight="1" s="11">
@@ -11618,8 +12638,11 @@
       <c r="K356" s="10" t="n">
         <v>0.0766</v>
       </c>
-      <c r="M356" t="n">
+      <c r="M356" s="10" t="n">
         <v>0.0511</v>
+      </c>
+      <c r="N356" t="n">
+        <v>0.0963</v>
       </c>
     </row>
     <row r="357" ht="16" customHeight="1" s="11">
@@ -11650,8 +12673,11 @@
       <c r="K357" s="10" t="n">
         <v>0.0788</v>
       </c>
-      <c r="M357" t="n">
+      <c r="M357" s="10" t="n">
         <v>0.048</v>
+      </c>
+      <c r="N357" t="n">
+        <v>0.1015</v>
       </c>
     </row>
     <row r="358" ht="16" customHeight="1" s="11">
@@ -11682,8 +12708,11 @@
       <c r="K358" s="10" t="n">
         <v>0.0954</v>
       </c>
-      <c r="M358" t="n">
+      <c r="M358" s="10" t="n">
         <v>0.0601</v>
+      </c>
+      <c r="N358" t="n">
+        <v>0.0965</v>
       </c>
     </row>
     <row r="359" ht="16" customHeight="1" s="11">
@@ -11714,8 +12743,11 @@
       <c r="K359" s="10" t="n">
         <v>0.0998</v>
       </c>
-      <c r="M359" t="n">
+      <c r="M359" s="10" t="n">
         <v>0.0573</v>
+      </c>
+      <c r="N359" t="n">
+        <v>0.092</v>
       </c>
     </row>
     <row r="360" ht="16" customHeight="1" s="11">
@@ -11746,8 +12778,11 @@
       <c r="K360" s="10" t="n">
         <v>0.0945</v>
       </c>
-      <c r="M360" t="n">
+      <c r="M360" s="10" t="n">
         <v>0.0451</v>
+      </c>
+      <c r="N360" t="n">
+        <v>0.0856</v>
       </c>
     </row>
     <row r="361" ht="16" customHeight="1" s="11">
@@ -11778,8 +12813,11 @@
       <c r="K361" s="10" t="n">
         <v>0.1014</v>
       </c>
-      <c r="M361" t="n">
+      <c r="M361" s="10" t="n">
         <v>0.0423</v>
+      </c>
+      <c r="N361" t="n">
+        <v>0.0886</v>
       </c>
     </row>
     <row r="362" ht="16" customHeight="1" s="11">
@@ -11810,8 +12848,11 @@
       <c r="K362" s="10" t="n">
         <v>0.0983</v>
       </c>
-      <c r="M362" t="n">
+      <c r="M362" s="10" t="n">
         <v>0.0508</v>
+      </c>
+      <c r="N362" t="n">
+        <v>0.09959999999999999</v>
       </c>
     </row>
     <row r="363" ht="16" customHeight="1" s="11">
@@ -11842,8 +12883,11 @@
       <c r="K363" s="10" t="n">
         <v>0.0983</v>
       </c>
-      <c r="M363" t="n">
+      <c r="M363" s="10" t="n">
         <v>0.045</v>
+      </c>
+      <c r="N363" t="n">
+        <v>0.0988</v>
       </c>
     </row>
     <row r="364" ht="16" customHeight="1" s="11">
@@ -11874,8 +12918,11 @@
       <c r="K364" s="10" t="n">
         <v>0.09379999999999999</v>
       </c>
-      <c r="M364" t="n">
+      <c r="M364" s="10" t="n">
         <v>0.0415</v>
+      </c>
+      <c r="N364" t="n">
+        <v>0.0955</v>
       </c>
     </row>
     <row r="365" ht="16" customHeight="1" s="11">
@@ -11906,8 +12953,11 @@
       <c r="K365" s="10" t="n">
         <v>0.1037</v>
       </c>
-      <c r="M365" t="n">
+      <c r="M365" s="10" t="n">
         <v>0.0373</v>
+      </c>
+      <c r="N365" t="n">
+        <v>0.09180000000000001</v>
       </c>
     </row>
     <row r="366" ht="16" customHeight="1" s="11">
@@ -11938,8 +12988,11 @@
       <c r="K366" s="10" t="n">
         <v>0.1042</v>
       </c>
-      <c r="M366" t="n">
+      <c r="M366" s="10" t="n">
         <v>0.0449</v>
+      </c>
+      <c r="N366" t="n">
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="367" ht="16" customHeight="1" s="11">
@@ -11970,8 +13023,11 @@
       <c r="K367" s="10" t="n">
         <v>0.1136</v>
       </c>
-      <c r="M367" t="n">
+      <c r="M367" s="10" t="n">
         <v>0.0477</v>
+      </c>
+      <c r="N367" t="n">
+        <v>0.0919</v>
       </c>
     </row>
     <row r="368" ht="16" customHeight="1" s="11">
@@ -12002,8 +13058,11 @@
       <c r="K368" s="10" t="n">
         <v>0.0799</v>
       </c>
-      <c r="M368" t="n">
+      <c r="M368" s="10" t="n">
         <v>0.0446</v>
+      </c>
+      <c r="N368" t="n">
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="369" ht="16" customHeight="1" s="11">
@@ -12034,8 +13093,11 @@
       <c r="K369" s="10" t="n">
         <v>0.0779</v>
       </c>
-      <c r="M369" t="n">
+      <c r="M369" s="10" t="n">
         <v>0.0521</v>
+      </c>
+      <c r="N369" t="n">
+        <v>0.07489999999999999</v>
       </c>
     </row>
     <row r="370" ht="16" customHeight="1" s="11">
@@ -12066,8 +13128,11 @@
       <c r="K370" s="10" t="n">
         <v>0.0891</v>
       </c>
-      <c r="M370" t="n">
+      <c r="M370" s="10" t="n">
         <v>0.055</v>
+      </c>
+      <c r="N370" t="n">
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="371" ht="16" customHeight="1" s="11">
@@ -12098,8 +13163,11 @@
       <c r="K371" s="10" t="n">
         <v>0.09030000000000001</v>
       </c>
-      <c r="M371" t="n">
+      <c r="M371" s="10" t="n">
         <v>0.0385</v>
+      </c>
+      <c r="N371" t="n">
+        <v>0.0678</v>
       </c>
     </row>
     <row r="372" ht="16" customHeight="1" s="11">
@@ -12130,8 +13198,11 @@
       <c r="K372" s="10" t="n">
         <v>0.1057</v>
       </c>
-      <c r="M372" t="n">
+      <c r="M372" s="10" t="n">
         <v>0.0539</v>
+      </c>
+      <c r="N372" t="n">
+        <v>0.0743</v>
       </c>
     </row>
     <row r="373" ht="16" customHeight="1" s="11">
@@ -12162,8 +13233,11 @@
       <c r="K373" s="10" t="n">
         <v>0.0921</v>
       </c>
-      <c r="M373" t="n">
+      <c r="M373" s="10" t="n">
         <v>0.0394</v>
+      </c>
+      <c r="N373" t="n">
+        <v>0.06320000000000001</v>
       </c>
     </row>
     <row r="374" ht="16" customHeight="1" s="11">
@@ -12194,8 +13268,11 @@
       <c r="K374" s="10" t="n">
         <v>0.09859999999999999</v>
       </c>
-      <c r="M374" t="n">
+      <c r="M374" s="10" t="n">
         <v>0.0439</v>
+      </c>
+      <c r="N374" t="n">
+        <v>0.0858</v>
       </c>
     </row>
     <row r="375" ht="16" customHeight="1" s="11">
@@ -12226,8 +13303,11 @@
       <c r="K375" s="10" t="n">
         <v>0.08740000000000001</v>
       </c>
-      <c r="M375" t="n">
+      <c r="M375" s="10" t="n">
         <v>0.0436</v>
+      </c>
+      <c r="N375" t="n">
+        <v>0.0794</v>
       </c>
     </row>
     <row r="376" ht="16" customHeight="1" s="11">
@@ -12258,8 +13338,11 @@
       <c r="K376" s="10" t="n">
         <v>0.1101</v>
       </c>
-      <c r="M376" t="n">
+      <c r="M376" s="10" t="n">
         <v>0.03</v>
+      </c>
+      <c r="N376" t="n">
+        <v>0.07820000000000001</v>
       </c>
     </row>
     <row r="377" ht="16" customHeight="1" s="11">
@@ -12290,8 +13373,11 @@
       <c r="K377" s="10" t="n">
         <v>0.1097</v>
       </c>
-      <c r="M377" t="n">
+      <c r="M377" s="10" t="n">
         <v>0.0433</v>
+      </c>
+      <c r="N377" t="n">
+        <v>0.0723</v>
       </c>
     </row>
     <row r="378" ht="16" customHeight="1" s="11">
@@ -12322,8 +13408,11 @@
       <c r="K378" s="10" t="n">
         <v>0.1006</v>
       </c>
-      <c r="M378" t="n">
+      <c r="M378" s="10" t="n">
         <v>0.0365</v>
+      </c>
+      <c r="N378" t="n">
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="379" ht="16" customHeight="1" s="11">
@@ -12354,8 +13443,11 @@
       <c r="K379" s="10" t="n">
         <v>0.09669999999999999</v>
       </c>
-      <c r="M379" t="n">
+      <c r="M379" s="10" t="n">
         <v>0.0556</v>
+      </c>
+      <c r="N379" t="n">
+        <v>0.0829</v>
       </c>
     </row>
     <row r="380" ht="16" customHeight="1" s="11">
@@ -12386,8 +13478,11 @@
       <c r="K380" s="10" t="n">
         <v>0.1026</v>
       </c>
-      <c r="M380" t="n">
+      <c r="M380" s="10" t="n">
         <v>0.0551</v>
+      </c>
+      <c r="N380" t="n">
+        <v>0.07820000000000001</v>
       </c>
     </row>
     <row r="381" ht="16" customHeight="1" s="11">
@@ -12418,8 +13513,11 @@
       <c r="K381" s="10" t="n">
         <v>0.09279999999999999</v>
       </c>
-      <c r="M381" t="n">
+      <c r="M381" s="10" t="n">
         <v>0.0482</v>
+      </c>
+      <c r="N381" t="n">
+        <v>0.0711</v>
       </c>
     </row>
     <row r="382" ht="16" customHeight="1" s="11">
@@ -12450,8 +13548,11 @@
       <c r="K382" s="10" t="n">
         <v>0.0946</v>
       </c>
-      <c r="M382" t="n">
+      <c r="M382" s="10" t="n">
         <v>0.0426</v>
+      </c>
+      <c r="N382" t="n">
+        <v>0.0849</v>
       </c>
     </row>
     <row r="383" ht="16" customHeight="1" s="11">
@@ -12482,8 +13583,11 @@
       <c r="K383" s="10" t="n">
         <v>0.0876</v>
       </c>
-      <c r="M383" t="n">
+      <c r="M383" s="10" t="n">
         <v>0.0477</v>
+      </c>
+      <c r="N383" t="n">
+        <v>0.0827</v>
       </c>
     </row>
     <row r="384" ht="16" customHeight="1" s="11">
@@ -12514,8 +13618,11 @@
       <c r="K384" s="10" t="n">
         <v>0.0911</v>
       </c>
-      <c r="M384" t="n">
+      <c r="M384" s="10" t="n">
         <v>0.0508</v>
+      </c>
+      <c r="N384" t="n">
+        <v>0.0844</v>
       </c>
     </row>
     <row r="385" ht="16" customHeight="1" s="11">
@@ -12546,8 +13653,11 @@
       <c r="K385" s="10" t="n">
         <v>0.09180000000000001</v>
       </c>
-      <c r="M385" t="n">
+      <c r="M385" s="10" t="n">
         <v>0.0433</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0.0868</v>
       </c>
     </row>
     <row r="386" ht="16" customHeight="1" s="11">
@@ -12578,8 +13688,11 @@
       <c r="K386" s="10" t="n">
         <v>0.0934</v>
       </c>
-      <c r="M386" t="n">
+      <c r="M386" s="10" t="n">
         <v>0.04</v>
+      </c>
+      <c r="N386" t="n">
+        <v>0.0717</v>
       </c>
     </row>
     <row r="387" ht="16" customHeight="1" s="11">
@@ -12610,8 +13723,11 @@
       <c r="K387" s="10" t="n">
         <v>0.0798</v>
       </c>
-      <c r="M387" t="n">
+      <c r="M387" s="10" t="n">
         <v>0.0475</v>
+      </c>
+      <c r="N387" t="n">
+        <v>0.0795</v>
       </c>
     </row>
     <row r="388" ht="16" customHeight="1" s="11">
@@ -12642,8 +13758,11 @@
       <c r="K388" s="10" t="n">
         <v>0.0867</v>
       </c>
-      <c r="M388" t="n">
+      <c r="M388" s="10" t="n">
         <v>0.0477</v>
+      </c>
+      <c r="N388" t="n">
+        <v>0.0725</v>
       </c>
     </row>
     <row r="389" ht="16" customHeight="1" s="11">
@@ -12674,8 +13793,11 @@
       <c r="K389" s="10" t="n">
         <v>0.0931</v>
       </c>
-      <c r="M389" t="n">
+      <c r="M389" s="10" t="n">
         <v>0.0362</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0.0799</v>
       </c>
     </row>
     <row r="390" ht="16" customHeight="1" s="11">
@@ -12706,8 +13828,11 @@
       <c r="K390" s="10" t="n">
         <v>0.1007</v>
       </c>
-      <c r="M390" t="n">
+      <c r="M390" s="10" t="n">
         <v>0.0379</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0.06859999999999999</v>
       </c>
     </row>
     <row r="391" ht="16" customHeight="1" s="11">
@@ -12738,8 +13863,11 @@
       <c r="K391" s="10" t="n">
         <v>0.07439999999999999</v>
       </c>
-      <c r="M391" t="n">
+      <c r="M391" s="10" t="n">
         <v>0.0362</v>
+      </c>
+      <c r="N391" t="n">
+        <v>0.07630000000000001</v>
       </c>
     </row>
     <row r="392" ht="16" customHeight="1" s="11">
@@ -12770,8 +13898,11 @@
       <c r="K392" s="10" t="n">
         <v>0.0852</v>
       </c>
-      <c r="M392" t="n">
+      <c r="M392" s="10" t="n">
         <v>0.0303</v>
+      </c>
+      <c r="N392" t="n">
+        <v>0.0723</v>
       </c>
     </row>
     <row r="393" ht="16" customHeight="1" s="11">
@@ -12802,8 +13933,11 @@
       <c r="K393" s="10" t="n">
         <v>0.09320000000000001</v>
       </c>
-      <c r="M393" t="n">
+      <c r="M393" s="10" t="n">
         <v>0.0352</v>
+      </c>
+      <c r="N393" t="n">
+        <v>0.0762</v>
       </c>
     </row>
     <row r="394" ht="16" customHeight="1" s="11">
@@ -12834,8 +13968,11 @@
       <c r="K394" s="10" t="n">
         <v>0.0854</v>
       </c>
-      <c r="M394" t="n">
+      <c r="M394" s="10" t="n">
         <v>0.0365</v>
+      </c>
+      <c r="N394" t="n">
+        <v>0.0993</v>
       </c>
     </row>
     <row r="395" ht="16" customHeight="1" s="11">
@@ -12866,8 +14003,11 @@
       <c r="K395" s="10" t="n">
         <v>0.0954</v>
       </c>
-      <c r="M395" t="n">
+      <c r="M395" s="10" t="n">
         <v>0.0395</v>
+      </c>
+      <c r="N395" t="n">
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="396" ht="16" customHeight="1" s="11">
@@ -12898,8 +14038,11 @@
       <c r="K396" s="10" t="n">
         <v>0.09229999999999999</v>
       </c>
-      <c r="M396" t="n">
+      <c r="M396" s="10" t="n">
         <v>0.0444</v>
+      </c>
+      <c r="N396" t="n">
+        <v>0.0737</v>
       </c>
     </row>
     <row r="397" ht="16" customHeight="1" s="11">
@@ -12930,8 +14073,11 @@
       <c r="K397" s="10" t="n">
         <v>0.0895</v>
       </c>
-      <c r="M397" t="n">
+      <c r="M397" s="10" t="n">
         <v>0.039</v>
+      </c>
+      <c r="N397" t="n">
+        <v>0.081</v>
       </c>
     </row>
     <row r="398" ht="16" customHeight="1" s="11">
@@ -12962,8 +14108,11 @@
       <c r="K398" s="10" t="n">
         <v>0.0969</v>
       </c>
-      <c r="M398" t="n">
+      <c r="M398" s="10" t="n">
         <v>0.0546</v>
+      </c>
+      <c r="N398" t="n">
+        <v>0.0771</v>
       </c>
     </row>
     <row r="399" ht="16" customHeight="1" s="11">
@@ -12994,8 +14143,11 @@
       <c r="K399" s="10" t="n">
         <v>0.0994</v>
       </c>
-      <c r="M399" t="n">
+      <c r="M399" s="10" t="n">
         <v>0.0508</v>
+      </c>
+      <c r="N399" t="n">
+        <v>0.0602</v>
       </c>
     </row>
     <row r="400" ht="16" customHeight="1" s="11">
@@ -13026,8 +14178,11 @@
       <c r="K400" s="10" t="n">
         <v>0.095</v>
       </c>
-      <c r="M400" t="n">
+      <c r="M400" s="10" t="n">
         <v>0.0576</v>
+      </c>
+      <c r="N400" t="n">
+        <v>0.0795</v>
       </c>
     </row>
     <row r="401" ht="16" customHeight="1" s="11">
@@ -13058,8 +14213,11 @@
       <c r="K401" s="10" t="n">
         <v>0.0847</v>
       </c>
-      <c r="M401" t="n">
+      <c r="M401" s="10" t="n">
         <v>0.0543</v>
+      </c>
+      <c r="N401" t="n">
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="402" ht="16" customHeight="1" s="11">
@@ -13090,8 +14248,11 @@
       <c r="K402" s="10" t="n">
         <v>0.0989</v>
       </c>
-      <c r="M402" t="n">
+      <c r="M402" s="10" t="n">
         <v>0.0645</v>
+      </c>
+      <c r="N402" t="n">
+        <v>0.0762</v>
       </c>
     </row>
     <row r="403" ht="16" customHeight="1" s="11">
@@ -13122,8 +14283,11 @@
       <c r="K403" s="10" t="n">
         <v>0.1037</v>
       </c>
-      <c r="M403" t="n">
+      <c r="M403" s="10" t="n">
         <v>0.0478</v>
+      </c>
+      <c r="N403" t="n">
+        <v>0.0752</v>
       </c>
     </row>
     <row r="404" ht="16" customHeight="1" s="11">
@@ -13154,8 +14318,11 @@
       <c r="K404" s="10" t="n">
         <v>0.1087</v>
       </c>
-      <c r="M404" t="n">
+      <c r="M404" s="10" t="n">
         <v>0.0481</v>
+      </c>
+      <c r="N404" t="n">
+        <v>0.078</v>
       </c>
     </row>
     <row r="405" ht="16" customHeight="1" s="11">
@@ -13186,8 +14353,11 @@
       <c r="K405" s="10" t="n">
         <v>0.09569999999999999</v>
       </c>
-      <c r="M405" t="n">
+      <c r="M405" s="10" t="n">
         <v>0.0378</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0.0684</v>
       </c>
     </row>
     <row r="406" ht="16" customHeight="1" s="11">
@@ -13218,8 +14388,11 @@
       <c r="K406" s="10" t="n">
         <v>0.0848</v>
       </c>
-      <c r="M406" t="n">
+      <c r="M406" s="10" t="n">
         <v>0.036</v>
+      </c>
+      <c r="N406" t="n">
+        <v>0.07820000000000001</v>
       </c>
     </row>
     <row r="407" ht="16" customHeight="1" s="11">
@@ -13250,8 +14423,11 @@
       <c r="K407" s="10" t="n">
         <v>0.1022</v>
       </c>
-      <c r="M407" t="n">
+      <c r="M407" s="10" t="n">
         <v>0.0363</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0.0725</v>
       </c>
     </row>
     <row r="408" ht="16" customHeight="1" s="11">
@@ -13282,8 +14458,11 @@
       <c r="K408" s="10" t="n">
         <v>0.1098</v>
       </c>
-      <c r="M408" t="n">
+      <c r="M408" s="10" t="n">
         <v>0.04</v>
+      </c>
+      <c r="N408" t="n">
+        <v>0.0679</v>
       </c>
     </row>
     <row r="409" ht="16" customHeight="1" s="11">
@@ -13314,8 +14493,11 @@
       <c r="K409" s="10" t="n">
         <v>0.0886</v>
       </c>
-      <c r="M409" t="n">
+      <c r="M409" s="10" t="n">
         <v>0.0578</v>
+      </c>
+      <c r="N409" t="n">
+        <v>0.0774</v>
       </c>
     </row>
     <row r="410" ht="16" customHeight="1" s="11">
@@ -13346,8 +14528,11 @@
       <c r="K410" s="10" t="n">
         <v>0.08210000000000001</v>
       </c>
-      <c r="M410" t="n">
+      <c r="M410" s="10" t="n">
         <v>0.0483</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0.0891</v>
       </c>
     </row>
     <row r="411" ht="16" customHeight="1" s="11">
@@ -13378,8 +14563,11 @@
       <c r="K411" s="10" t="n">
         <v>0.0925</v>
       </c>
-      <c r="M411" t="n">
+      <c r="M411" s="10" t="n">
         <v>0.0487</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0.08110000000000001</v>
       </c>
     </row>
     <row r="412" ht="16" customHeight="1" s="11">
@@ -13410,8 +14598,11 @@
       <c r="K412" s="10" t="n">
         <v>0.1123</v>
       </c>
-      <c r="M412" t="n">
+      <c r="M412" s="10" t="n">
         <v>0.0493</v>
+      </c>
+      <c r="N412" t="n">
+        <v>0.07770000000000001</v>
       </c>
     </row>
     <row r="413" ht="16" customHeight="1" s="11">
@@ -13442,8 +14633,11 @@
       <c r="K413" s="10" t="n">
         <v>0.1133</v>
       </c>
-      <c r="M413" t="n">
+      <c r="M413" s="10" t="n">
         <v>0.045</v>
+      </c>
+      <c r="N413" t="n">
+        <v>0.0721</v>
       </c>
     </row>
     <row r="414" ht="16" customHeight="1" s="11">
@@ -13474,8 +14668,11 @@
       <c r="K414" s="10" t="n">
         <v>0.103</v>
       </c>
-      <c r="M414" t="n">
+      <c r="M414" s="10" t="n">
         <v>0.031</v>
+      </c>
+      <c r="N414" t="n">
+        <v>0.1053</v>
       </c>
     </row>
     <row r="415" ht="16" customHeight="1" s="11">
@@ -13506,8 +14703,11 @@
       <c r="K415" s="10" t="n">
         <v>0.09370000000000001</v>
       </c>
-      <c r="M415" t="n">
+      <c r="M415" s="10" t="n">
         <v>0.0252</v>
+      </c>
+      <c r="N415" t="n">
+        <v>0.0853</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N415"/>
+  <dimension ref="A1:O517"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.5" defaultRowHeight="16" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="14.33" customWidth="1" style="10" min="1" max="1"/>
@@ -669,8 +669,11 @@
       <c r="M5" s="10" t="n">
         <v>0.1869090909090909</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="10" t="n">
         <v>0.09279999999999999</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>0.15085</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1" s="11">
@@ -704,8 +707,11 @@
       <c r="M6" s="10" t="n">
         <v>0.138824</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="10" t="n">
         <v>0.2353263157894737</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>0.3156952380952381</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1" s="11">
@@ -739,8 +745,11 @@
       <c r="M7" s="10" t="n">
         <v>0.2518083333333334</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="10" t="n">
         <v>0.274504347826087</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>0.2623789473684211</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1" s="11">
@@ -774,8 +783,11 @@
       <c r="M8" s="10" t="n">
         <v>0.3698666666666667</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="10" t="n">
         <v>0.3215147058823529</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>0.336076</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" s="11">
@@ -809,8 +821,11 @@
       <c r="M9" s="10" t="n">
         <v>0.3514</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="10" t="n">
         <v>0.3930472222222222</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>0.4068193548387097</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1" s="11">
@@ -844,8 +859,11 @@
       <c r="M10" s="10" t="n">
         <v>0.4646285714285714</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="10" t="n">
         <v>0.4396758620689655</v>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>0.4127666666666667</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1" s="11">
@@ -879,8 +897,11 @@
       <c r="M11" s="10" t="n">
         <v>0.5696769230769231</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="10" t="n">
         <v>0.4832086956521739</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>0.4828740740740741</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="11">
@@ -914,8 +935,11 @@
       <c r="M12" s="10" t="n">
         <v>0.3973416666666667</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="10" t="n">
         <v>0.5772291666666667</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>0.4825780487804878</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1" s="11">
@@ -949,8 +973,11 @@
       <c r="M13" s="10" t="n">
         <v>0.567176</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="10" t="n">
         <v>0.4163192307692307</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>0.6143458333333334</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="11">
@@ -984,8 +1011,11 @@
       <c r="M14" s="10" t="n">
         <v>0.6389068965517241</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="10" t="n">
         <v>0.5317766666666667</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <v>0.6242810810810812</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="11">
@@ -1019,8 +1049,11 @@
       <c r="M15" s="10" t="n">
         <v>0.6665208333333333</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="10" t="n">
         <v>0.583564705882353</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>0.6279682926829269</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="11">
@@ -1054,8 +1087,11 @@
       <c r="M16" s="10" t="n">
         <v>0.6746</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="10" t="n">
         <v>0.7064615384615386</v>
+      </c>
+      <c r="O16" s="10" t="n">
+        <v>0.62561</v>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="11">
@@ -1089,8 +1125,11 @@
       <c r="M17" s="10" t="n">
         <v>0.8905</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="10" t="n">
         <v>0.5909714285714286</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.7070395833333333</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="11">
@@ -1124,8 +1163,11 @@
       <c r="M18" s="10" t="n">
         <v>0.8375846153846154</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="10" t="n">
         <v>0.6155055555555555</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.7015650000000001</v>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="11">
@@ -1159,8 +1201,11 @@
       <c r="M19" s="10" t="n">
         <v>0.7931928571428569</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="10" t="n">
         <v>0.6931615384615385</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.7706250000000001</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="11">
@@ -1194,8 +1239,11 @@
       <c r="M20" s="10" t="n">
         <v>0.7452285714285715</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="10" t="n">
         <v>0.6954259259259259</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.7268062499999999</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="11">
@@ -1229,8 +1277,11 @@
       <c r="M21" s="10" t="n">
         <v>0.7665750000000001</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="10" t="n">
         <v>0.7208681818181818</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.7121030303030302</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="11">
@@ -1264,8 +1315,11 @@
       <c r="M22" s="10" t="n">
         <v>0.81155</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="10" t="n">
         <v>0.6757333333333334</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.7713296296296297</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1" s="11">
@@ -1299,8 +1353,11 @@
       <c r="M23" s="10" t="n">
         <v>0.8190473684210527</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="10" t="n">
         <v>0.7586851851851852</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.7712057142857143</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1" s="11">
@@ -1334,8 +1391,11 @@
       <c r="M24" s="10" t="n">
         <v>0.8160083333333333</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="10" t="n">
         <v>0.6258</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.7573777777777778</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1" s="11">
@@ -1369,8 +1429,11 @@
       <c r="M25" s="10" t="n">
         <v>0.819016129032258</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="10" t="n">
         <v>0.6926928571428572</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.8077400000000001</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1" s="11">
@@ -1404,8 +1467,11 @@
       <c r="M26" s="10" t="n">
         <v>0.800376</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="10" t="n">
         <v>0.7689243902439025</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.808397435897436</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1" s="11">
@@ -1439,8 +1505,11 @@
       <c r="M27" s="10" t="n">
         <v>0.8317777777777777</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="10" t="n">
         <v>0.8026111111111112</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.7290928571428571</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1" s="11">
@@ -1474,8 +1543,11 @@
       <c r="M28" s="10" t="n">
         <v>0.8663357142857143</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="10" t="n">
         <v>0.8487620689655171</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.8504</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1" s="11">
@@ -1509,8 +1581,11 @@
       <c r="M29" s="10" t="n">
         <v>0.8481645161290323</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="10" t="n">
         <v>0.7313730769230771</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.704325</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1" s="11">
@@ -1544,8 +1619,11 @@
       <c r="M30" s="10" t="n">
         <v>0.8360954545454544</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="10" t="n">
         <v>0.8426740740740741</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.7864136363636365</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1" s="11">
@@ -1579,8 +1657,11 @@
       <c r="M31" s="10" t="n">
         <v>0.8196447368421053</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" s="10" t="n">
         <v>0.7710591836734693</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.747890243902439</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1" s="11">
@@ -1614,8 +1695,11 @@
       <c r="M32" s="10" t="n">
         <v>0.91625</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" s="10" t="n">
         <v>0.7232619047619048</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.831660465116279</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1" s="11">
@@ -1649,8 +1733,11 @@
       <c r="M33" s="10" t="n">
         <v>0.8377368421052631</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="10" t="n">
         <v>0.7280200000000001</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.832017857142857</v>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1" s="11">
@@ -1684,8 +1771,11 @@
       <c r="M34" s="10" t="n">
         <v>0.8785285714285714</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" s="10" t="n">
         <v>0.8458410256410256</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.7479230769230769</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1" s="11">
@@ -1719,8 +1809,11 @@
       <c r="M35" s="10" t="n">
         <v>0.8667842105263157</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" s="10" t="n">
         <v>0.8215210526315789</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.7984472727272728</v>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1" s="11">
@@ -1754,8 +1847,11 @@
       <c r="M36" s="10" t="n">
         <v>0.8169363636363637</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" s="10" t="n">
         <v>0.8271181818181819</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.7752833333333333</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1" s="11">
@@ -1789,8 +1885,11 @@
       <c r="M37" s="10" t="n">
         <v>0.8512157894736841</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" s="10" t="n">
         <v>0.759484</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.8712935483870967</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1" s="11">
@@ -1824,8 +1923,11 @@
       <c r="M38" s="10" t="n">
         <v>0.8428</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" s="10" t="n">
         <v>0.7245290322580645</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.8072918367346938</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1" s="11">
@@ -1859,8 +1961,11 @@
       <c r="M39" s="10" t="n">
         <v>0.8182478260869566</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" s="10" t="n">
         <v>0.7952843749999999</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.8565735294117647</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1" s="11">
@@ -1894,8 +1999,11 @@
       <c r="M40" s="10" t="n">
         <v>0.8591923076923078</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" s="10" t="n">
         <v>0.8183166666666666</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.8196600000000001</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="11">
@@ -1929,8 +2037,11 @@
       <c r="M41" s="10" t="n">
         <v>0.9093941176470588</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41" s="10" t="n">
         <v>0.7012096774193549</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.8514558823529413</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="11">
@@ -1964,8 +2075,11 @@
       <c r="M42" s="10" t="n">
         <v>0.8544142857142857</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N42" s="10" t="n">
         <v>0.8291181818181819</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.7641133333333333</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="11">
@@ -1999,8 +2113,11 @@
       <c r="M43" s="10" t="n">
         <v>0.8557325581395347</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N43" s="10" t="n">
         <v>0.8715249999999999</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.8065107142857143</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="11">
@@ -2034,8 +2151,11 @@
       <c r="M44" s="10" t="n">
         <v>0.8781812500000001</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N44" s="10" t="n">
         <v>0.8116214285714286</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.7783157894736842</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1" s="11">
@@ -2069,8 +2189,11 @@
       <c r="M45" s="10" t="n">
         <v>0.8173041666666666</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N45" s="10" t="n">
         <v>0.7751409090909092</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.8453258064516129</v>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1" s="11">
@@ -2104,8 +2227,11 @@
       <c r="M46" s="10" t="n">
         <v>0.8770809523809524</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N46" s="10" t="n">
         <v>0.7962413793103449</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.83335</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1" s="11">
@@ -2139,8 +2265,11 @@
       <c r="M47" s="10" t="n">
         <v>0.7956400000000001</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N47" s="10" t="n">
         <v>0.7753555555555557</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.8887628571428572</v>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1" s="11">
@@ -2174,8 +2303,11 @@
       <c r="M48" s="10" t="n">
         <v>0.871456</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N48" s="10" t="n">
         <v>0.8330464285714285</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.7538766666666668</v>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1" s="11">
@@ -2209,8 +2341,11 @@
       <c r="M49" s="10" t="n">
         <v>0.8120384615384615</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N49" s="10" t="n">
         <v>0.634508</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.8872657894736842</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" s="11">
@@ -2244,8 +2379,11 @@
       <c r="M50" s="10" t="n">
         <v>0.8598541666666666</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N50" s="10" t="n">
         <v>0.840105</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.8248838709677419</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="11">
@@ -2279,8 +2417,11 @@
       <c r="M51" s="10" t="n">
         <v>0.8482484848484848</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N51" s="10" t="n">
         <v>0.7060705882352941</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.7423947368421053</v>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1" s="11">
@@ -2314,8 +2455,11 @@
       <c r="M52" s="10" t="n">
         <v>0.8915194444444443</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N52" s="10" t="n">
         <v>0.7423461538461539</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.7411925</v>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1" s="11">
@@ -2349,8 +2493,11 @@
       <c r="M53" s="10" t="n">
         <v>0.9129176470588236</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N53" s="10" t="n">
         <v>0.8302133333333334</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.76683</v>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="11">
@@ -2384,8 +2531,11 @@
       <c r="M54" s="10" t="n">
         <v>0.8237</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N54" s="10" t="n">
         <v>0.7507957446808512</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.8015062500000001</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1" s="11">
@@ -2419,8 +2569,11 @@
       <c r="M55" s="10" t="n">
         <v>0.8023666666666667</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N55" s="10" t="n">
         <v>0.8164939393939393</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.8676695652173912</v>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1" s="11">
@@ -2454,8 +2607,11 @@
       <c r="M56" s="10" t="n">
         <v>0.9308533333333334</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N56" s="10" t="n">
         <v>0.8507481481481481</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8515625</v>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1" s="11">
@@ -2489,8 +2645,11 @@
       <c r="M57" s="10" t="n">
         <v>0.8568866666666667</v>
       </c>
-      <c r="N57" t="n">
+      <c r="N57" s="10" t="n">
         <v>0.8110064516129033</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.8353740740740742</v>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1" s="11">
@@ -2524,8 +2683,11 @@
       <c r="M58" s="10" t="n">
         <v>0.8825473684210526</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N58" s="10" t="n">
         <v>0.7516735294117647</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.8190999999999999</v>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1" s="11">
@@ -2559,8 +2721,11 @@
       <c r="M59" s="10" t="n">
         <v>0.8528863636363636</v>
       </c>
-      <c r="N59" t="n">
+      <c r="N59" s="10" t="n">
         <v>0.7675923076923077</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.8521428571428572</v>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1" s="11">
@@ -2594,8 +2759,11 @@
       <c r="M60" s="10" t="n">
         <v>0.8295878787878788</v>
       </c>
-      <c r="N60" t="n">
+      <c r="N60" s="10" t="n">
         <v>0.7682129032258065</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.8195052631578947</v>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1" s="11">
@@ -2629,8 +2797,11 @@
       <c r="M61" s="10" t="n">
         <v>0.8941941176470588</v>
       </c>
-      <c r="N61" t="n">
+      <c r="N61" s="10" t="n">
         <v>0.6901315789473684</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.8021882352941176</v>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1" s="11">
@@ -2664,8 +2835,11 @@
       <c r="M62" s="10" t="n">
         <v>0.8776878787878788</v>
       </c>
-      <c r="N62" t="n">
+      <c r="N62" s="10" t="n">
         <v>0.7398857142857143</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.8121833333333333</v>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1" s="11">
@@ -2699,8 +2873,11 @@
       <c r="M63" s="10" t="n">
         <v>0.8672030303030303</v>
       </c>
-      <c r="N63" t="n">
+      <c r="N63" s="10" t="n">
         <v>0.6727555555555556</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.8327522727272728</v>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1" s="11">
@@ -2734,8 +2911,11 @@
       <c r="M64" s="10" t="n">
         <v>0.9006526315789474</v>
       </c>
-      <c r="N64" t="n">
+      <c r="N64" s="10" t="n">
         <v>0.83423125</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.8472206896551724</v>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1" s="11">
@@ -2769,8 +2949,11 @@
       <c r="M65" s="10" t="n">
         <v>0.8324178571428572</v>
       </c>
-      <c r="N65" t="n">
+      <c r="N65" s="10" t="n">
         <v>0.7577433333333334</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.877721212121212</v>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1" s="11">
@@ -2804,8 +2987,11 @@
       <c r="M66" s="10" t="n">
         <v>0.8579961538461537</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N66" s="10" t="n">
         <v>0.7123186046511628</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.8271577777777778</v>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1" s="11">
@@ -2839,8 +3025,11 @@
       <c r="M67" s="10" t="n">
         <v>0.8567708333333334</v>
       </c>
-      <c r="N67" t="n">
+      <c r="N67" s="10" t="n">
         <v>0.681888888888889</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.8950612903225805</v>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1" s="11">
@@ -2874,8 +3063,11 @@
       <c r="M68" s="10" t="n">
         <v>0.8655875000000002</v>
       </c>
-      <c r="N68" t="n">
+      <c r="N68" s="10" t="n">
         <v>0.8249142857142857</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.8208851851851853</v>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1" s="11">
@@ -2909,8 +3101,11 @@
       <c r="M69" s="10" t="n">
         <v>0.8712071428571428</v>
       </c>
-      <c r="N69" t="n">
+      <c r="N69" s="10" t="n">
         <v>0.7955882352941178</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.8241200000000001</v>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1" s="11">
@@ -2944,8 +3139,11 @@
       <c r="M70" s="10" t="n">
         <v>0.864895</v>
       </c>
-      <c r="N70" t="n">
+      <c r="N70" s="10" t="n">
         <v>0.788678</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.7361799999999999</v>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1" s="11">
@@ -2979,8 +3177,11 @@
       <c r="M71" s="10" t="n">
         <v>0.8924238095238097</v>
       </c>
-      <c r="N71" t="n">
+      <c r="N71" s="10" t="n">
         <v>0.7767631578947369</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.7952465116279069</v>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1" s="11">
@@ -3014,8 +3215,11 @@
       <c r="M72" s="10" t="n">
         <v>0.9009695652173915</v>
       </c>
-      <c r="N72" t="n">
+      <c r="N72" s="10" t="n">
         <v>0.7267807692307693</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.8150404761904761</v>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1" s="11">
@@ -3049,8 +3253,11 @@
       <c r="M73" s="10" t="n">
         <v>0.9029473684210527</v>
       </c>
-      <c r="N73" t="n">
+      <c r="N73" s="10" t="n">
         <v>0.8130521739130434</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.8184999999999999</v>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1" s="11">
@@ -3084,8 +3291,11 @@
       <c r="M74" s="10" t="n">
         <v>0.8609264705882353</v>
       </c>
-      <c r="N74" t="n">
+      <c r="N74" s="10" t="n">
         <v>0.8167785714285715</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.7927041666666668</v>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1" s="11">
@@ -3119,8 +3329,11 @@
       <c r="M75" s="10" t="n">
         <v>0.8881739130434783</v>
       </c>
-      <c r="N75" t="n">
+      <c r="N75" s="10" t="n">
         <v>0.80575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.8676108108108107</v>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1" s="11">
@@ -3154,8 +3367,11 @@
       <c r="M76" s="10" t="n">
         <v>0.8360800000000002</v>
       </c>
-      <c r="N76" t="n">
+      <c r="N76" s="10" t="n">
         <v>0.8016190476190476</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.8355978260869565</v>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1" s="11">
@@ -3189,8 +3405,11 @@
       <c r="M77" s="10" t="n">
         <v>0.8866658536585366</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N77" s="10" t="n">
         <v>0.779913043478261</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.8077564102564103</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1" s="11">
@@ -3224,8 +3443,11 @@
       <c r="M78" s="10" t="n">
         <v>0.9142322580645161</v>
       </c>
-      <c r="N78" t="n">
+      <c r="N78" s="10" t="n">
         <v>0.8567357142857145</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.7781379310344827</v>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1" s="11">
@@ -3259,8 +3481,11 @@
       <c r="M79" s="10" t="n">
         <v>0.9071875000000001</v>
       </c>
-      <c r="N79" t="n">
+      <c r="N79" s="10" t="n">
         <v>0.7588764705882354</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.7934813953488372</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1" s="11">
@@ -3294,8 +3519,11 @@
       <c r="M80" s="10" t="n">
         <v>0.8460631578947367</v>
       </c>
-      <c r="N80" t="n">
+      <c r="N80" s="10" t="n">
         <v>0.7777281250000001</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.7933666666666666</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1" s="11">
@@ -3329,8 +3557,11 @@
       <c r="M81" s="10" t="n">
         <v>0.8665</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N81" s="10" t="n">
         <v>0.7613750000000001</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.8372115384615385</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1" s="11">
@@ -3364,8 +3595,11 @@
       <c r="M82" s="10" t="n">
         <v>0.7966333333333333</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N82" s="10" t="n">
         <v>0.838671875</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.7177749999999999</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1" s="11">
@@ -3399,8 +3633,11 @@
       <c r="M83" s="10" t="n">
         <v>0.8748655172413794</v>
       </c>
-      <c r="N83" t="n">
+      <c r="N83" s="10" t="n">
         <v>0.792909375</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.8539733333333331</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1" s="11">
@@ -3434,8 +3671,11 @@
       <c r="M84" s="10" t="n">
         <v>0.8646142857142858</v>
       </c>
-      <c r="N84" t="n">
+      <c r="N84" s="10" t="n">
         <v>0.7617243243243242</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.7717875</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1" s="11">
@@ -3469,8 +3709,11 @@
       <c r="M85" s="10" t="n">
         <v>0.8899000000000001</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N85" s="10" t="n">
         <v>0.7913162162162163</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.7740973684210527</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1" s="11">
@@ -3504,8 +3747,11 @@
       <c r="M86" s="10" t="n">
         <v>0.8825500000000001</v>
       </c>
-      <c r="N86" t="n">
+      <c r="N86" s="10" t="n">
         <v>0.8398325581395351</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.7998414634146341</v>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1" s="11">
@@ -3539,8 +3785,11 @@
       <c r="M87" s="10" t="n">
         <v>0.890473076923077</v>
       </c>
-      <c r="N87" t="n">
+      <c r="N87" s="10" t="n">
         <v>0.774444</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.8547483870967741</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1" s="11">
@@ -3574,8 +3823,11 @@
       <c r="M88" s="10" t="n">
         <v>0.77555</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N88" s="10" t="n">
         <v>0.7538024390243903</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.8368510638297872</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1" s="11">
@@ -3609,8 +3861,11 @@
       <c r="M89" s="10" t="n">
         <v>0.8602703703703704</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N89" s="10" t="n">
         <v>0.7902307692307692</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.8002222222222222</v>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1" s="11">
@@ -3644,8 +3899,11 @@
       <c r="M90" s="10" t="n">
         <v>0.8716130434782609</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N90" s="10" t="n">
         <v>0.7373966666666667</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.9067611111111111</v>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1" s="11">
@@ -3679,8 +3937,11 @@
       <c r="M91" s="10" t="n">
         <v>0.7576000000000001</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N91" s="10" t="n">
         <v>0.7704999999999999</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.801996153846154</v>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1" s="11">
@@ -3714,8 +3975,11 @@
       <c r="M92" s="10" t="n">
         <v>0.8530315789473684</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N92" s="10" t="n">
         <v>0.8550957446808509</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.8734612903225807</v>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1" s="11">
@@ -3749,8 +4013,11 @@
       <c r="M93" s="10" t="n">
         <v>0.8781960000000001</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N93" s="10" t="n">
         <v>0.8248238095238095</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.8890142857142856</v>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1" s="11">
@@ -3784,8 +4051,11 @@
       <c r="M94" s="10" t="n">
         <v>0.8743272727272727</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N94" s="10" t="n">
         <v>0.8461375</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.8057421052631579</v>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1" s="11">
@@ -3819,8 +4089,11 @@
       <c r="M95" s="10" t="n">
         <v>0.8619818181818182</v>
       </c>
-      <c r="N95" t="n">
+      <c r="N95" s="10" t="n">
         <v>0.7295190476190476</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.7664151515151515</v>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1" s="11">
@@ -3854,8 +4127,11 @@
       <c r="M96" s="10" t="n">
         <v>0.8519916666666667</v>
       </c>
-      <c r="N96" t="n">
+      <c r="N96" s="10" t="n">
         <v>0.8256032258064515</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.8572195121951219</v>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1" s="11">
@@ -3889,8 +4165,11 @@
       <c r="M97" s="10" t="n">
         <v>0.8274</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N97" s="10" t="n">
         <v>0.7570315789473684</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.8078027777777778</v>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1" s="11">
@@ -3924,8 +4203,11 @@
       <c r="M98" s="10" t="n">
         <v>0.8591160000000001</v>
       </c>
-      <c r="N98" t="n">
+      <c r="N98" s="10" t="n">
         <v>0.7786372093023257</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.8278793103448276</v>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1" s="11">
@@ -3959,8 +4241,11 @@
       <c r="M99" s="10" t="n">
         <v>0.8396424242424243</v>
       </c>
-      <c r="N99" t="n">
+      <c r="N99" s="10" t="n">
         <v>0.8155652173913043</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.8558685714285714</v>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1" s="11">
@@ -3994,8 +4279,11 @@
       <c r="M100" s="10" t="n">
         <v>0.8525555555555555</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N100" s="10" t="n">
         <v>0.7994022222222222</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.7458166666666666</v>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1" s="11">
@@ -4029,8 +4317,11 @@
       <c r="M101" s="10" t="n">
         <v>0.8753692307692309</v>
       </c>
-      <c r="N101" t="n">
+      <c r="N101" s="10" t="n">
         <v>0.7036</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.7962804347826087</v>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1" s="11">
@@ -4064,8 +4355,11 @@
       <c r="M102" s="10" t="n">
         <v>0.85886</v>
       </c>
-      <c r="N102" t="n">
+      <c r="N102" s="10" t="n">
         <v>0.7512750000000001</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.8597463414634144</v>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1" s="11">
@@ -4099,8 +4393,11 @@
       <c r="M103" s="10" t="n">
         <v>0.8541730769230769</v>
       </c>
-      <c r="N103" t="n">
+      <c r="N103" s="10" t="n">
         <v>0.8170277777777778</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.8049322580645162</v>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1" s="11">
@@ -4134,8 +4431,11 @@
       <c r="M104" s="10" t="n">
         <v>0.9033464285714284</v>
       </c>
-      <c r="N104" t="n">
+      <c r="N104" s="10" t="n">
         <v>0.8098358974358975</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.8411076923076923</v>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1" s="11">
@@ -4193,8 +4493,11 @@
       <c r="M108" s="10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="N108" t="n">
+      <c r="N108" s="10" t="n">
         <v>0.9333333333333333</v>
+      </c>
+      <c r="O108" s="10" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="109" ht="16" customHeight="1" s="11">
@@ -4228,8 +4531,11 @@
       <c r="M109" s="10" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="N109" t="n">
+      <c r="N109" s="10" t="n">
         <v>0.8</v>
+      </c>
+      <c r="O109" s="10" t="n">
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1" s="11">
@@ -4263,8 +4569,11 @@
       <c r="M110" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N110" t="n">
+      <c r="N110" s="10" t="n">
         <v>0.9166666666666666</v>
+      </c>
+      <c r="O110" s="10" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1" s="11">
@@ -4298,8 +4607,11 @@
       <c r="M111" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N111" t="n">
+      <c r="N111" s="10" t="n">
         <v>0.8</v>
+      </c>
+      <c r="O111" s="10" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1" s="11">
@@ -4333,8 +4645,11 @@
       <c r="M112" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N112" t="n">
+      <c r="N112" s="10" t="n">
         <v>0.8</v>
+      </c>
+      <c r="O112" s="10" t="n">
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="113" ht="16" customHeight="1" s="11">
@@ -4368,8 +4683,11 @@
       <c r="M113" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N113" t="n">
-        <v>1</v>
+      <c r="N113" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" s="10" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="114" ht="16" customHeight="1" s="11">
@@ -4403,8 +4721,11 @@
       <c r="M114" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N114" t="n">
+      <c r="N114" s="10" t="n">
         <v>0.8</v>
+      </c>
+      <c r="O114" s="10" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1" s="11">
@@ -4438,8 +4759,11 @@
       <c r="M115" s="10" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N115" t="n">
-        <v>1</v>
+      <c r="N115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" s="10" t="n">
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1" s="11">
@@ -4473,8 +4797,11 @@
       <c r="M116" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N116" t="n">
+      <c r="N116" s="10" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="O116" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1" s="11">
@@ -4508,7 +4835,10 @@
       <c r="M117" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N117" t="n">
+      <c r="N117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O117" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4543,7 +4873,10 @@
       <c r="M118" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N118" t="n">
+      <c r="N118" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4578,7 +4911,10 @@
       <c r="M119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N119" t="n">
+      <c r="N119" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4613,7 +4949,10 @@
       <c r="M120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N120" t="n">
+      <c r="N120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O120" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4648,7 +4987,10 @@
       <c r="M121" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N121" t="n">
+      <c r="N121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4683,7 +5025,10 @@
       <c r="M122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N122" t="n">
+      <c r="N122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4718,7 +5063,10 @@
       <c r="M123" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N123" t="n">
+      <c r="N123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4753,7 +5101,10 @@
       <c r="M124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N124" t="n">
+      <c r="N124" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4788,7 +5139,10 @@
       <c r="M125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N125" t="n">
+      <c r="N125" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4823,7 +5177,10 @@
       <c r="M126" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N126" t="n">
+      <c r="N126" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4858,7 +5215,10 @@
       <c r="M127" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N127" t="n">
+      <c r="N127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4893,7 +5253,10 @@
       <c r="M128" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N128" t="n">
+      <c r="N128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4928,7 +5291,10 @@
       <c r="M129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N129" t="n">
+      <c r="N129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4963,7 +5329,10 @@
       <c r="M130" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N130" t="n">
+      <c r="N130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4998,7 +5367,10 @@
       <c r="M131" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="N131" t="n">
+      <c r="N131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5033,8 +5405,11 @@
       <c r="M132" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N132" s="10" t="n">
         <v>0.75</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="133" ht="16" customHeight="1" s="11">
@@ -5068,7 +5443,10 @@
       <c r="M133" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N133" t="n">
+      <c r="N133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5103,7 +5481,10 @@
       <c r="M134" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N134" t="n">
+      <c r="N134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5138,7 +5519,10 @@
       <c r="M135" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N135" t="n">
+      <c r="N135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5173,7 +5557,10 @@
       <c r="M136" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N136" t="n">
+      <c r="N136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5208,7 +5595,10 @@
       <c r="M137" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N137" t="n">
+      <c r="N137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5243,7 +5633,10 @@
       <c r="M138" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N138" t="n">
+      <c r="N138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5278,7 +5671,10 @@
       <c r="M139" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N139" t="n">
+      <c r="N139" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O139" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5313,7 +5709,10 @@
       <c r="M140" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N140" t="n">
+      <c r="N140" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5348,7 +5747,10 @@
       <c r="M141" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N141" t="n">
+      <c r="N141" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5383,7 +5785,10 @@
       <c r="M142" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N142" t="n">
+      <c r="N142" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5418,7 +5823,10 @@
       <c r="M143" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N143" t="n">
+      <c r="N143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5453,7 +5861,10 @@
       <c r="M144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N144" t="n">
+      <c r="N144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5488,7 +5899,10 @@
       <c r="M145" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N145" t="n">
+      <c r="N145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5523,7 +5937,10 @@
       <c r="M146" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N146" t="n">
+      <c r="N146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5558,7 +5975,10 @@
       <c r="M147" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N147" t="n">
+      <c r="N147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5593,7 +6013,10 @@
       <c r="M148" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N148" t="n">
+      <c r="N148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5628,7 +6051,10 @@
       <c r="M149" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N149" t="n">
+      <c r="N149" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5663,7 +6089,10 @@
       <c r="M150" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N150" t="n">
+      <c r="N150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5698,7 +6127,10 @@
       <c r="M151" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N151" t="n">
+      <c r="N151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5733,7 +6165,10 @@
       <c r="M152" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N152" t="n">
+      <c r="N152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O152" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5768,7 +6203,10 @@
       <c r="M153" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N153" t="n">
+      <c r="N153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5803,7 +6241,10 @@
       <c r="M154" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N154" t="n">
+      <c r="N154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5838,7 +6279,10 @@
       <c r="M155" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N155" t="n">
+      <c r="N155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5873,7 +6317,10 @@
       <c r="M156" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N156" t="n">
+      <c r="N156" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O156" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5908,7 +6355,10 @@
       <c r="M157" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N157" t="n">
+      <c r="N157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5943,7 +6393,10 @@
       <c r="M158" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N158" t="n">
+      <c r="N158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5978,7 +6431,10 @@
       <c r="M159" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N159" t="n">
+      <c r="N159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6013,7 +6469,10 @@
       <c r="M160" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N160" t="n">
+      <c r="N160" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6048,7 +6507,10 @@
       <c r="M161" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N161" t="n">
+      <c r="N161" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6083,7 +6545,10 @@
       <c r="M162" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N162" t="n">
+      <c r="N162" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6118,7 +6583,10 @@
       <c r="M163" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N163" t="n">
+      <c r="N163" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6153,7 +6621,10 @@
       <c r="M164" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N164" t="n">
+      <c r="N164" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6188,7 +6659,10 @@
       <c r="M165" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N165" t="n">
+      <c r="N165" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6223,7 +6697,10 @@
       <c r="M166" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N166" t="n">
+      <c r="N166" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6258,7 +6735,10 @@
       <c r="M167" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N167" t="n">
+      <c r="N167" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6293,7 +6773,10 @@
       <c r="M168" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N168" t="n">
+      <c r="N168" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6328,7 +6811,10 @@
       <c r="M169" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N169" t="n">
+      <c r="N169" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6363,7 +6849,10 @@
       <c r="M170" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N170" t="n">
+      <c r="N170" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O170" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6398,7 +6887,10 @@
       <c r="M171" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N171" t="n">
+      <c r="N171" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O171" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6433,7 +6925,10 @@
       <c r="M172" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N172" t="n">
+      <c r="N172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6468,7 +6963,10 @@
       <c r="M173" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N173" t="n">
+      <c r="N173" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O173" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6503,7 +7001,10 @@
       <c r="M174" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N174" t="n">
+      <c r="N174" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6538,7 +7039,10 @@
       <c r="M175" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N175" t="n">
+      <c r="N175" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O175" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6573,7 +7077,10 @@
       <c r="M176" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N176" t="n">
+      <c r="N176" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O176" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6608,7 +7115,10 @@
       <c r="M177" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N177" t="n">
+      <c r="N177" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O177" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6643,7 +7153,10 @@
       <c r="M178" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N178" t="n">
+      <c r="N178" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O178" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6678,7 +7191,10 @@
       <c r="M179" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N179" t="n">
+      <c r="N179" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6713,7 +7229,10 @@
       <c r="M180" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N180" t="n">
+      <c r="N180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O180" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6748,7 +7267,10 @@
       <c r="M181" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N181" t="n">
+      <c r="N181" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6783,7 +7305,10 @@
       <c r="M182" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N182" t="n">
+      <c r="N182" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6818,7 +7343,10 @@
       <c r="M183" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N183" t="n">
+      <c r="N183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O183" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6853,7 +7381,10 @@
       <c r="M184" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N184" t="n">
+      <c r="N184" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O184" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6888,7 +7419,10 @@
       <c r="M185" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N185" t="n">
+      <c r="N185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O185" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6923,7 +7457,10 @@
       <c r="M186" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N186" t="n">
+      <c r="N186" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O186" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6958,7 +7495,10 @@
       <c r="M187" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N187" t="n">
+      <c r="N187" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O187" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6993,7 +7533,10 @@
       <c r="M188" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N188" t="n">
+      <c r="N188" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O188" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7028,7 +7571,10 @@
       <c r="M189" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N189" t="n">
+      <c r="N189" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O189" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7063,7 +7609,10 @@
       <c r="M190" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N190" t="n">
+      <c r="N190" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O190" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7098,7 +7647,10 @@
       <c r="M191" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N191" t="n">
+      <c r="N191" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7133,7 +7685,10 @@
       <c r="M192" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N192" t="n">
+      <c r="N192" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O192" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7168,7 +7723,10 @@
       <c r="M193" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N193" t="n">
+      <c r="N193" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7203,7 +7761,10 @@
       <c r="M194" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N194" t="n">
+      <c r="N194" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O194" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7238,7 +7799,10 @@
       <c r="M195" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N195" t="n">
+      <c r="N195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O195" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7273,7 +7837,10 @@
       <c r="M196" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N196" t="n">
+      <c r="N196" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7308,7 +7875,10 @@
       <c r="M197" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N197" t="n">
+      <c r="N197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O197" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7343,7 +7913,10 @@
       <c r="M198" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N198" t="n">
+      <c r="N198" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O198" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7378,7 +7951,10 @@
       <c r="M199" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N199" t="n">
+      <c r="N199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O199" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7413,7 +7989,10 @@
       <c r="M200" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N200" t="n">
+      <c r="N200" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O200" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7448,7 +8027,10 @@
       <c r="M201" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N201" t="n">
+      <c r="N201" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O201" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7483,7 +8065,10 @@
       <c r="M202" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N202" t="n">
+      <c r="N202" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O202" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7518,7 +8103,10 @@
       <c r="M203" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N203" t="n">
+      <c r="N203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7553,7 +8141,10 @@
       <c r="M204" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N204" t="n">
+      <c r="N204" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O204" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7588,7 +8179,10 @@
       <c r="M205" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N205" t="n">
+      <c r="N205" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O205" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7623,7 +8217,10 @@
       <c r="M206" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N206" t="n">
+      <c r="N206" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O206" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7658,7 +8255,10 @@
       <c r="M207" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N207" t="n">
+      <c r="N207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7717,8 +8317,11 @@
       <c r="M212" s="10" t="n">
         <v>0.95448</v>
       </c>
-      <c r="N212" t="n">
+      <c r="N212" s="10" t="n">
         <v>0.9517333333333333</v>
+      </c>
+      <c r="O212" s="10" t="n">
+        <v>0.9887</v>
       </c>
     </row>
     <row r="213" ht="16" customHeight="1" s="11">
@@ -7752,8 +8355,11 @@
       <c r="M213" s="10" t="n">
         <v>0.9643888888888887</v>
       </c>
-      <c r="N213" t="n">
+      <c r="N213" s="10" t="n">
         <v>0.8558428571428571</v>
+      </c>
+      <c r="O213" s="10" t="n">
+        <v>0.8561399999999999</v>
       </c>
     </row>
     <row r="214" ht="16" customHeight="1" s="11">
@@ -7787,8 +8393,11 @@
       <c r="M214" s="10" t="n">
         <v>0.9180333333333333</v>
       </c>
-      <c r="N214" t="n">
+      <c r="N214" s="10" t="n">
         <v>0.8695875000000001</v>
+      </c>
+      <c r="O214" s="10" t="n">
+        <v>0.572775</v>
       </c>
     </row>
     <row r="215" ht="16" customHeight="1" s="11">
@@ -7822,8 +8431,11 @@
       <c r="M215" s="10" t="n">
         <v>0.8192499999999999</v>
       </c>
-      <c r="N215" t="n">
+      <c r="N215" s="10" t="n">
         <v>0.7975333333333333</v>
+      </c>
+      <c r="O215" s="10" t="n">
+        <v>0.7227857142857143</v>
       </c>
     </row>
     <row r="216" ht="16" customHeight="1" s="11">
@@ -7857,8 +8469,11 @@
       <c r="M216" s="10" t="n">
         <v>0.9631874999999999</v>
       </c>
-      <c r="N216" t="n">
+      <c r="N216" s="10" t="n">
         <v>0.9340714285714286</v>
+      </c>
+      <c r="O216" s="10" t="n">
+        <v>0.714475</v>
       </c>
     </row>
     <row r="217" ht="16" customHeight="1" s="11">
@@ -7892,8 +8507,11 @@
       <c r="M217" s="10" t="n">
         <v>0.8031499999999999</v>
       </c>
-      <c r="N217" t="n">
+      <c r="N217" s="10" t="n">
         <v>0.89367</v>
+      </c>
+      <c r="O217" s="10" t="n">
+        <v>0.6282</v>
       </c>
     </row>
     <row r="218" ht="16" customHeight="1" s="11">
@@ -7927,8 +8545,11 @@
       <c r="M218" s="10" t="n">
         <v>0.851175</v>
       </c>
-      <c r="N218" t="n">
+      <c r="N218" s="10" t="n">
         <v>0.9314875</v>
+      </c>
+      <c r="O218" s="10" t="n">
+        <v>0.5764777777777778</v>
       </c>
     </row>
     <row r="219" ht="16" customHeight="1" s="11">
@@ -7962,8 +8583,11 @@
       <c r="M219" s="10" t="n">
         <v>0.9032555555555556</v>
       </c>
-      <c r="N219" t="n">
+      <c r="N219" s="10" t="n">
         <v>0.8687400000000001</v>
+      </c>
+      <c r="O219" s="10" t="n">
+        <v>0.6116999999999999</v>
       </c>
     </row>
     <row r="220" ht="16" customHeight="1" s="11">
@@ -7997,8 +8621,11 @@
       <c r="M220" s="10" t="n">
         <v>0.8391299999999999</v>
       </c>
-      <c r="N220" t="n">
+      <c r="N220" s="10" t="n">
         <v>0.8081230769230771</v>
+      </c>
+      <c r="O220" s="10" t="n">
+        <v>0.522790909090909</v>
       </c>
     </row>
     <row r="221" ht="16" customHeight="1" s="11">
@@ -8032,8 +8659,11 @@
       <c r="M221" s="10" t="n">
         <v>0.7792000000000001</v>
       </c>
-      <c r="N221" t="n">
+      <c r="N221" s="10" t="n">
         <v>0.8773583333333334</v>
+      </c>
+      <c r="O221" s="10" t="n">
+        <v>0.5536300000000001</v>
       </c>
     </row>
     <row r="222" ht="16" customHeight="1" s="11">
@@ -8067,8 +8697,11 @@
       <c r="M222" s="10" t="n">
         <v>0.8301999999999999</v>
       </c>
-      <c r="N222" t="n">
+      <c r="N222" s="10" t="n">
         <v>0.8576916666666667</v>
+      </c>
+      <c r="O222" s="10" t="n">
+        <v>0.5041888888888888</v>
       </c>
     </row>
     <row r="223" ht="16" customHeight="1" s="11">
@@ -8102,8 +8735,11 @@
       <c r="M223" s="10" t="n">
         <v>0.7985916666666667</v>
       </c>
-      <c r="N223" t="n">
+      <c r="N223" s="10" t="n">
         <v>0.75815</v>
+      </c>
+      <c r="O223" s="10" t="n">
+        <v>0.66301</v>
       </c>
     </row>
     <row r="224" ht="16" customHeight="1" s="11">
@@ -8137,8 +8773,11 @@
       <c r="M224" s="10" t="n">
         <v>0.7278666666666668</v>
       </c>
-      <c r="N224" t="n">
+      <c r="N224" s="10" t="n">
         <v>0.8044777777777778</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0.50227</v>
       </c>
     </row>
     <row r="225" ht="16" customHeight="1" s="11">
@@ -8172,8 +8811,11 @@
       <c r="M225" s="10" t="n">
         <v>0.6041769230769231</v>
       </c>
-      <c r="N225" t="n">
+      <c r="N225" s="10" t="n">
         <v>0.8150111111111111</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0.7592125000000001</v>
       </c>
     </row>
     <row r="226" ht="16" customHeight="1" s="11">
@@ -8207,8 +8849,11 @@
       <c r="M226" s="10" t="n">
         <v>0.62185</v>
       </c>
-      <c r="N226" t="n">
+      <c r="N226" s="10" t="n">
         <v>0.5669454545454545</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0.3407999999999999</v>
       </c>
     </row>
     <row r="227" ht="16" customHeight="1" s="11">
@@ -8242,8 +8887,11 @@
       <c r="M227" s="10" t="n">
         <v>0.8665538461538461</v>
       </c>
-      <c r="N227" t="n">
+      <c r="N227" s="10" t="n">
         <v>0.66072</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0.390625</v>
       </c>
     </row>
     <row r="228" ht="16" customHeight="1" s="11">
@@ -8277,8 +8925,11 @@
       <c r="M228" s="10" t="n">
         <v>0.6977999999999999</v>
       </c>
-      <c r="N228" t="n">
+      <c r="N228" s="10" t="n">
         <v>0.6590916666666666</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0.5567857142857143</v>
       </c>
     </row>
     <row r="229" ht="16" customHeight="1" s="11">
@@ -8312,8 +8963,11 @@
       <c r="M229" s="10" t="n">
         <v>0.7325818181818182</v>
       </c>
-      <c r="N229" t="n">
+      <c r="N229" s="10" t="n">
         <v>0.7596999999999999</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0.7359250000000001</v>
       </c>
     </row>
     <row r="230" ht="16" customHeight="1" s="11">
@@ -8347,8 +9001,11 @@
       <c r="M230" s="10" t="n">
         <v>0.8012909090909091</v>
       </c>
-      <c r="N230" t="n">
+      <c r="N230" s="10" t="n">
         <v>0.6077499999999999</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0.6124624999999999</v>
       </c>
     </row>
     <row r="231" ht="16" customHeight="1" s="11">
@@ -8382,8 +9039,11 @@
       <c r="M231" s="10" t="n">
         <v>0.6818076923076923</v>
       </c>
-      <c r="N231" t="n">
+      <c r="N231" s="10" t="n">
         <v>0.7041000000000001</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0.4303</v>
       </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="11">
@@ -8417,8 +9077,11 @@
       <c r="M232" s="10" t="n">
         <v>0.7709357142857144</v>
       </c>
-      <c r="N232" t="n">
+      <c r="N232" s="10" t="n">
         <v>0.7224444444444443</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0.4421727272727273</v>
       </c>
     </row>
     <row r="233" ht="16" customHeight="1" s="11">
@@ -8452,8 +9115,11 @@
       <c r="M233" s="10" t="n">
         <v>0.79527</v>
       </c>
-      <c r="N233" t="n">
+      <c r="N233" s="10" t="n">
         <v>0.77475</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0.70084</v>
       </c>
     </row>
     <row r="234" ht="16" customHeight="1" s="11">
@@ -8487,8 +9153,11 @@
       <c r="M234" s="10" t="n">
         <v>0.6966333333333333</v>
       </c>
-      <c r="N234" t="n">
+      <c r="N234" s="10" t="n">
         <v>0.7979375</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0.6185444444444443</v>
       </c>
     </row>
     <row r="235" ht="16" customHeight="1" s="11">
@@ -8522,8 +9191,11 @@
       <c r="M235" s="10" t="n">
         <v>0.7867416666666666</v>
       </c>
-      <c r="N235" t="n">
+      <c r="N235" s="10" t="n">
         <v>0.7042444444444445</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0.4373428571428571</v>
       </c>
     </row>
     <row r="236" ht="16" customHeight="1" s="11">
@@ -8557,8 +9229,11 @@
       <c r="M236" s="10" t="n">
         <v>0.70808</v>
       </c>
-      <c r="N236" t="n">
+      <c r="N236" s="10" t="n">
         <v>0.6681818181818181</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0.5215000000000001</v>
       </c>
     </row>
     <row r="237" ht="16" customHeight="1" s="11">
@@ -8592,8 +9267,11 @@
       <c r="M237" s="10" t="n">
         <v>0.7024285714285715</v>
       </c>
-      <c r="N237" t="n">
+      <c r="N237" s="10" t="n">
         <v>0.74951</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0.5088374999999999</v>
       </c>
     </row>
     <row r="238" ht="16" customHeight="1" s="11">
@@ -8627,8 +9305,11 @@
       <c r="M238" s="10" t="n">
         <v>0.7859166666666667</v>
       </c>
-      <c r="N238" t="n">
+      <c r="N238" s="10" t="n">
         <v>0.7732</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0.4101555555555556</v>
       </c>
     </row>
     <row r="239" ht="16" customHeight="1" s="11">
@@ -8662,8 +9343,11 @@
       <c r="M239" s="10" t="n">
         <v>0.8797727272727273</v>
       </c>
-      <c r="N239" t="n">
+      <c r="N239" s="10" t="n">
         <v>0.66165</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0.5927100000000001</v>
       </c>
     </row>
     <row r="240" ht="16" customHeight="1" s="11">
@@ -8697,8 +9381,11 @@
       <c r="M240" s="10" t="n">
         <v>0.5745181818181819</v>
       </c>
-      <c r="N240" t="n">
+      <c r="N240" s="10" t="n">
         <v>0.6185555555555556</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0.5346249999999999</v>
       </c>
     </row>
     <row r="241" ht="16" customHeight="1" s="11">
@@ -8732,8 +9419,11 @@
       <c r="M241" s="10" t="n">
         <v>0.7170666666666667</v>
       </c>
-      <c r="N241" t="n">
+      <c r="N241" s="10" t="n">
         <v>0.9008199999999998</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0.5625777777777778</v>
       </c>
     </row>
     <row r="242" ht="16" customHeight="1" s="11">
@@ -8767,8 +9457,11 @@
       <c r="M242" s="10" t="n">
         <v>0.6881749999999999</v>
       </c>
-      <c r="N242" t="n">
+      <c r="N242" s="10" t="n">
         <v>0.549875</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0.7341499999999999</v>
       </c>
     </row>
     <row r="243" ht="16" customHeight="1" s="11">
@@ -8802,8 +9495,11 @@
       <c r="M243" s="10" t="n">
         <v>0.6048416666666667</v>
       </c>
-      <c r="N243" t="n">
+      <c r="N243" s="10" t="n">
         <v>0.7113833333333331</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0.4191444444444444</v>
       </c>
     </row>
     <row r="244" ht="16" customHeight="1" s="11">
@@ -8837,8 +9533,11 @@
       <c r="M244" s="10" t="n">
         <v>0.5412363636363636</v>
       </c>
-      <c r="N244" t="n">
+      <c r="N244" s="10" t="n">
         <v>0.6219333333333333</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0.5688500000000001</v>
       </c>
     </row>
     <row r="245" ht="16" customHeight="1" s="11">
@@ -8872,8 +9571,11 @@
       <c r="M245" s="10" t="n">
         <v>0.7234444444444443</v>
       </c>
-      <c r="N245" t="n">
+      <c r="N245" s="10" t="n">
         <v>0.63115</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0.5880875</v>
       </c>
     </row>
     <row r="246" ht="16" customHeight="1" s="11">
@@ -8907,8 +9609,11 @@
       <c r="M246" s="10" t="n">
         <v>0.8002272727272728</v>
       </c>
-      <c r="N246" t="n">
+      <c r="N246" s="10" t="n">
         <v>0.50536</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0.3421272727272728</v>
       </c>
     </row>
     <row r="247" ht="16" customHeight="1" s="11">
@@ -8942,8 +9647,11 @@
       <c r="M247" s="10" t="n">
         <v>0.6703363636363636</v>
       </c>
-      <c r="N247" t="n">
+      <c r="N247" s="10" t="n">
         <v>0.5980692307692308</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0.598675</v>
       </c>
     </row>
     <row r="248" ht="16" customHeight="1" s="11">
@@ -8977,8 +9685,11 @@
       <c r="M248" s="10" t="n">
         <v>0.6680307692307692</v>
       </c>
-      <c r="N248" t="n">
+      <c r="N248" s="10" t="n">
         <v>0.6073428571428572</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0.5289777777777778</v>
       </c>
     </row>
     <row r="249" ht="16" customHeight="1" s="11">
@@ -9012,8 +9723,11 @@
       <c r="M249" s="10" t="n">
         <v>0.6627599999999999</v>
       </c>
-      <c r="N249" t="n">
+      <c r="N249" s="10" t="n">
         <v>0.7083636363636364</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0.506275</v>
       </c>
     </row>
     <row r="250" ht="16" customHeight="1" s="11">
@@ -9047,8 +9761,11 @@
       <c r="M250" s="10" t="n">
         <v>0.8192000000000002</v>
       </c>
-      <c r="N250" t="n">
+      <c r="N250" s="10" t="n">
         <v>0.725925</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0.3439800000000001</v>
       </c>
     </row>
     <row r="251" ht="16" customHeight="1" s="11">
@@ -9082,8 +9799,11 @@
       <c r="M251" s="10" t="n">
         <v>0.6285545454545455</v>
       </c>
-      <c r="N251" t="n">
+      <c r="N251" s="10" t="n">
         <v>0.6767545454545454</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0.3728181818181818</v>
       </c>
     </row>
     <row r="252" ht="16" customHeight="1" s="11">
@@ -9117,8 +9837,11 @@
       <c r="M252" s="10" t="n">
         <v>0.7125642857142858</v>
       </c>
-      <c r="N252" t="n">
+      <c r="N252" s="10" t="n">
         <v>0.7953600000000001</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0.4370444444444444</v>
       </c>
     </row>
     <row r="253" ht="16" customHeight="1" s="11">
@@ -9152,8 +9875,11 @@
       <c r="M253" s="10" t="n">
         <v>0.795490909090909</v>
       </c>
-      <c r="N253" t="n">
+      <c r="N253" s="10" t="n">
         <v>0.7009833333333333</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0.2969333333333333</v>
       </c>
     </row>
     <row r="254" ht="16" customHeight="1" s="11">
@@ -9187,8 +9913,11 @@
       <c r="M254" s="10" t="n">
         <v>0.7667599999999999</v>
       </c>
-      <c r="N254" t="n">
+      <c r="N254" s="10" t="n">
         <v>0.745990909090909</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0.53584</v>
       </c>
     </row>
     <row r="255" ht="16" customHeight="1" s="11">
@@ -9222,8 +9951,11 @@
       <c r="M255" s="10" t="n">
         <v>0.6928166666666667</v>
       </c>
-      <c r="N255" t="n">
+      <c r="N255" s="10" t="n">
         <v>0.7475909090909091</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0.4010444444444444</v>
       </c>
     </row>
     <row r="256" ht="16" customHeight="1" s="11">
@@ -9257,8 +9989,11 @@
       <c r="M256" s="10" t="n">
         <v>0.6839642857142856</v>
       </c>
-      <c r="N256" t="n">
+      <c r="N256" s="10" t="n">
         <v>0.672342857142857</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0.3849181818181819</v>
       </c>
     </row>
     <row r="257" ht="16" customHeight="1" s="11">
@@ -9292,8 +10027,11 @@
       <c r="M257" s="10" t="n">
         <v>0.622</v>
       </c>
-      <c r="N257" t="n">
+      <c r="N257" s="10" t="n">
         <v>0.6914090909090909</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0.6454666666666666</v>
       </c>
     </row>
     <row r="258" ht="16" customHeight="1" s="11">
@@ -9327,8 +10065,11 @@
       <c r="M258" s="10" t="n">
         <v>0.6281307692307692</v>
       </c>
-      <c r="N258" t="n">
+      <c r="N258" s="10" t="n">
         <v>0.7792333333333333</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0.5446875</v>
       </c>
     </row>
     <row r="259" ht="16" customHeight="1" s="11">
@@ -9362,8 +10103,11 @@
       <c r="M259" s="10" t="n">
         <v>0.7049785714285715</v>
       </c>
-      <c r="N259" t="n">
+      <c r="N259" s="10" t="n">
         <v>0.5992200000000001</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0.6154545454545454</v>
       </c>
     </row>
     <row r="260" ht="16" customHeight="1" s="11">
@@ -9397,8 +10141,11 @@
       <c r="M260" s="10" t="n">
         <v>0.7828333333333335</v>
       </c>
-      <c r="N260" t="n">
+      <c r="N260" s="10" t="n">
         <v>0.6557181818181819</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0.4440090909090909</v>
       </c>
     </row>
     <row r="261" ht="16" customHeight="1" s="11">
@@ -9432,8 +10179,11 @@
       <c r="M261" s="10" t="n">
         <v>0.5884153846153846</v>
       </c>
-      <c r="N261" t="n">
+      <c r="N261" s="10" t="n">
         <v>0.7368400000000002</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0.4924899999999999</v>
       </c>
     </row>
     <row r="262" ht="16" customHeight="1" s="11">
@@ -9467,8 +10217,11 @@
       <c r="M262" s="10" t="n">
         <v>0.7360545454545453</v>
       </c>
-      <c r="N262" t="n">
+      <c r="N262" s="10" t="n">
         <v>0.57424</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0.5437125</v>
       </c>
     </row>
     <row r="263" ht="16" customHeight="1" s="11">
@@ -9502,8 +10255,11 @@
       <c r="M263" s="10" t="n">
         <v>0.46515</v>
       </c>
-      <c r="N263" t="n">
+      <c r="N263" s="10" t="n">
         <v>0.7599400000000001</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0.55088</v>
       </c>
     </row>
     <row r="264" ht="16" customHeight="1" s="11">
@@ -9537,8 +10293,11 @@
       <c r="M264" s="10" t="n">
         <v>0.7920272727272727</v>
       </c>
-      <c r="N264" t="n">
+      <c r="N264" s="10" t="n">
         <v>0.6841</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0.4628444444444444</v>
       </c>
     </row>
     <row r="265" ht="16" customHeight="1" s="11">
@@ -9572,8 +10331,11 @@
       <c r="M265" s="10" t="n">
         <v>0.6039692307692308</v>
       </c>
-      <c r="N265" t="n">
+      <c r="N265" s="10" t="n">
         <v>0.6193363636363637</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0.6087</v>
       </c>
     </row>
     <row r="266" ht="16" customHeight="1" s="11">
@@ -9607,8 +10369,11 @@
       <c r="M266" s="10" t="n">
         <v>0.7218666666666667</v>
       </c>
-      <c r="N266" t="n">
+      <c r="N266" s="10" t="n">
         <v>0.7343499999999999</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0.5354428571428571</v>
       </c>
     </row>
     <row r="267" ht="16" customHeight="1" s="11">
@@ -9642,8 +10407,11 @@
       <c r="M267" s="10" t="n">
         <v>0.7068363636363637</v>
       </c>
-      <c r="N267" t="n">
+      <c r="N267" s="10" t="n">
         <v>0.7803125</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0.4913444444444444</v>
       </c>
     </row>
     <row r="268" ht="16" customHeight="1" s="11">
@@ -9677,8 +10445,11 @@
       <c r="M268" s="10" t="n">
         <v>0.8097200000000001</v>
       </c>
-      <c r="N268" t="n">
+      <c r="N268" s="10" t="n">
         <v>0.6929444444444444</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0.4629666666666667</v>
       </c>
     </row>
     <row r="269" ht="16" customHeight="1" s="11">
@@ -9712,8 +10483,11 @@
       <c r="M269" s="10" t="n">
         <v>0.6770230769230768</v>
       </c>
-      <c r="N269" t="n">
+      <c r="N269" s="10" t="n">
         <v>0.73512</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0.5498181818181819</v>
       </c>
     </row>
     <row r="270" ht="16" customHeight="1" s="11">
@@ -9747,8 +10521,11 @@
       <c r="M270" s="10" t="n">
         <v>0.662811111111111</v>
       </c>
-      <c r="N270" t="n">
+      <c r="N270" s="10" t="n">
         <v>0.7524</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0.3328923076923077</v>
       </c>
     </row>
     <row r="271" ht="16" customHeight="1" s="11">
@@ -9782,8 +10559,11 @@
       <c r="M271" s="10" t="n">
         <v>0.7926916666666665</v>
       </c>
-      <c r="N271" t="n">
+      <c r="N271" s="10" t="n">
         <v>0.6547999999999999</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0.3874285714285715</v>
       </c>
     </row>
     <row r="272" ht="16" customHeight="1" s="11">
@@ -9817,8 +10597,11 @@
       <c r="M272" s="10" t="n">
         <v>0.5866500000000001</v>
       </c>
-      <c r="N272" t="n">
+      <c r="N272" s="10" t="n">
         <v>0.6574249999999999</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0.58423</v>
       </c>
     </row>
     <row r="273" ht="16" customHeight="1" s="11">
@@ -9852,8 +10635,11 @@
       <c r="M273" s="10" t="n">
         <v>0.6981999999999999</v>
       </c>
-      <c r="N273" t="n">
+      <c r="N273" s="10" t="n">
         <v>0.7640777777777779</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0.44114</v>
       </c>
     </row>
     <row r="274" ht="16" customHeight="1" s="11">
@@ -9887,8 +10673,11 @@
       <c r="M274" s="10" t="n">
         <v>0.7342</v>
       </c>
-      <c r="N274" t="n">
+      <c r="N274" s="10" t="n">
         <v>0.7905099999999999</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0.5112166666666667</v>
       </c>
     </row>
     <row r="275" ht="16" customHeight="1" s="11">
@@ -9922,8 +10711,11 @@
       <c r="M275" s="10" t="n">
         <v>0.804990909090909</v>
       </c>
-      <c r="N275" t="n">
+      <c r="N275" s="10" t="n">
         <v>0.6994666666666666</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0.4745444444444444</v>
       </c>
     </row>
     <row r="276" ht="16" customHeight="1" s="11">
@@ -9957,8 +10749,11 @@
       <c r="M276" s="10" t="n">
         <v>0.790575</v>
       </c>
-      <c r="N276" t="n">
+      <c r="N276" s="10" t="n">
         <v>0.5936166666666667</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0.5658625</v>
       </c>
     </row>
     <row r="277" ht="16" customHeight="1" s="11">
@@ -9992,8 +10787,11 @@
       <c r="M277" s="10" t="n">
         <v>0.6164583333333334</v>
       </c>
-      <c r="N277" t="n">
+      <c r="N277" s="10" t="n">
         <v>0.7161333333333333</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0.39552</v>
       </c>
     </row>
     <row r="278" ht="16" customHeight="1" s="11">
@@ -10027,8 +10825,11 @@
       <c r="M278" s="10" t="n">
         <v>0.7985500000000001</v>
       </c>
-      <c r="N278" t="n">
+      <c r="N278" s="10" t="n">
         <v>0.7859636363636363</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0.526275</v>
       </c>
     </row>
     <row r="279" ht="16" customHeight="1" s="11">
@@ -10062,8 +10863,11 @@
       <c r="M279" s="10" t="n">
         <v>0.79965</v>
       </c>
-      <c r="N279" t="n">
+      <c r="N279" s="10" t="n">
         <v>0.6587833333333333</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0.4762428571428572</v>
       </c>
     </row>
     <row r="280" ht="16" customHeight="1" s="11">
@@ -10097,8 +10901,11 @@
       <c r="M280" s="10" t="n">
         <v>0.67042</v>
       </c>
-      <c r="N280" t="n">
+      <c r="N280" s="10" t="n">
         <v>0.6964666666666667</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0.6118444444444443</v>
       </c>
     </row>
     <row r="281" ht="16" customHeight="1" s="11">
@@ -10132,8 +10939,11 @@
       <c r="M281" s="10" t="n">
         <v>0.6719083333333332</v>
       </c>
-      <c r="N281" t="n">
+      <c r="N281" s="10" t="n">
         <v>0.6656000000000001</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0.506225</v>
       </c>
     </row>
     <row r="282" ht="16" customHeight="1" s="11">
@@ -10167,8 +10977,11 @@
       <c r="M282" s="10" t="n">
         <v>0.7953583333333333</v>
       </c>
-      <c r="N282" t="n">
+      <c r="N282" s="10" t="n">
         <v>0.7348636363636364</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0.52346</v>
       </c>
     </row>
     <row r="283" ht="16" customHeight="1" s="11">
@@ -10202,8 +11015,11 @@
       <c r="M283" s="10" t="n">
         <v>0.7745599999999999</v>
       </c>
-      <c r="N283" t="n">
+      <c r="N283" s="10" t="n">
         <v>0.8373299999999999</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0.4927444444444445</v>
       </c>
     </row>
     <row r="284" ht="16" customHeight="1" s="11">
@@ -10237,8 +11053,11 @@
       <c r="M284" s="10" t="n">
         <v>0.6955</v>
       </c>
-      <c r="N284" t="n">
+      <c r="N284" s="10" t="n">
         <v>0.6446444444444445</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0.5898</v>
       </c>
     </row>
     <row r="285" ht="16" customHeight="1" s="11">
@@ -10272,8 +11091,11 @@
       <c r="M285" s="10" t="n">
         <v>0.8084416666666668</v>
       </c>
-      <c r="N285" t="n">
+      <c r="N285" s="10" t="n">
         <v>0.6422899999999999</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0.58948</v>
       </c>
     </row>
     <row r="286" ht="16" customHeight="1" s="11">
@@ -10307,8 +11129,11 @@
       <c r="M286" s="10" t="n">
         <v>0.6684363636363636</v>
       </c>
-      <c r="N286" t="n">
+      <c r="N286" s="10" t="n">
         <v>0.52607</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0.34166</v>
       </c>
     </row>
     <row r="287" ht="16" customHeight="1" s="11">
@@ -10342,8 +11167,11 @@
       <c r="M287" s="10" t="n">
         <v>0.6285461538461538</v>
       </c>
-      <c r="N287" t="n">
+      <c r="N287" s="10" t="n">
         <v>0.6165222222222222</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0.3526666666666666</v>
       </c>
     </row>
     <row r="288" ht="16" customHeight="1" s="11">
@@ -10377,8 +11205,11 @@
       <c r="M288" s="10" t="n">
         <v>0.6467636363636364</v>
       </c>
-      <c r="N288" t="n">
+      <c r="N288" s="10" t="n">
         <v>0.6945714285714286</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0.44889</v>
       </c>
     </row>
     <row r="289" ht="16" customHeight="1" s="11">
@@ -10412,8 +11243,11 @@
       <c r="M289" s="10" t="n">
         <v>0.5219999999999999</v>
       </c>
-      <c r="N289" t="n">
+      <c r="N289" s="10" t="n">
         <v>0.6649181818181817</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0.5686272727272728</v>
       </c>
     </row>
     <row r="290" ht="16" customHeight="1" s="11">
@@ -10447,8 +11281,11 @@
       <c r="M290" s="10" t="n">
         <v>0.695576923076923</v>
       </c>
-      <c r="N290" t="n">
+      <c r="N290" s="10" t="n">
         <v>0.70416</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0.3283777777777778</v>
       </c>
     </row>
     <row r="291" ht="16" customHeight="1" s="11">
@@ -10482,8 +11319,11 @@
       <c r="M291" s="10" t="n">
         <v>0.5340888888888888</v>
       </c>
-      <c r="N291" t="n">
+      <c r="N291" s="10" t="n">
         <v>0.6937599999999999</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0.7632090909090908</v>
       </c>
     </row>
     <row r="292" ht="16" customHeight="1" s="11">
@@ -10517,8 +11357,11 @@
       <c r="M292" s="10" t="n">
         <v>0.6761</v>
       </c>
-      <c r="N292" t="n">
+      <c r="N292" s="10" t="n">
         <v>0.80542</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0.4981666666666667</v>
       </c>
     </row>
     <row r="293" ht="16" customHeight="1" s="11">
@@ -10552,8 +11395,11 @@
       <c r="M293" s="10" t="n">
         <v>0.7425916666666668</v>
       </c>
-      <c r="N293" t="n">
+      <c r="N293" s="10" t="n">
         <v>0.5407875</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0.463388888888889</v>
       </c>
     </row>
     <row r="294" ht="16" customHeight="1" s="11">
@@ -10587,8 +11433,11 @@
       <c r="M294" s="10" t="n">
         <v>0.7010454545454546</v>
       </c>
-      <c r="N294" t="n">
+      <c r="N294" s="10" t="n">
         <v>0.85695</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0.54137</v>
       </c>
     </row>
     <row r="295" ht="16" customHeight="1" s="11">
@@ -10622,8 +11471,11 @@
       <c r="M295" s="10" t="n">
         <v>0.6985111111111111</v>
       </c>
-      <c r="N295" t="n">
+      <c r="N295" s="10" t="n">
         <v>0.6269899999999999</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0.4514444444444445</v>
       </c>
     </row>
     <row r="296" ht="16" customHeight="1" s="11">
@@ -10657,8 +11509,11 @@
       <c r="M296" s="10" t="n">
         <v>0.5680538461538462</v>
       </c>
-      <c r="N296" t="n">
+      <c r="N296" s="10" t="n">
         <v>0.7906875</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0.3154888888888889</v>
       </c>
     </row>
     <row r="297" ht="16" customHeight="1" s="11">
@@ -10692,8 +11547,11 @@
       <c r="M297" s="10" t="n">
         <v>0.55708</v>
       </c>
-      <c r="N297" t="n">
+      <c r="N297" s="10" t="n">
         <v>0.72844</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0.3064125</v>
       </c>
     </row>
     <row r="298" ht="16" customHeight="1" s="11">
@@ -10727,8 +11585,11 @@
       <c r="M298" s="10" t="n">
         <v>0.6442272727272728</v>
       </c>
-      <c r="N298" t="n">
+      <c r="N298" s="10" t="n">
         <v>0.7217</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0.4458625</v>
       </c>
     </row>
     <row r="299" ht="16" customHeight="1" s="11">
@@ -10762,8 +11623,11 @@
       <c r="M299" s="10" t="n">
         <v>0.7373249999999999</v>
       </c>
-      <c r="N299" t="n">
+      <c r="N299" s="10" t="n">
         <v>0.5995818181818181</v>
+      </c>
+      <c r="O299" t="n">
+        <v>0.2909666666666667</v>
       </c>
     </row>
     <row r="300" ht="16" customHeight="1" s="11">
@@ -10797,8 +11661,11 @@
       <c r="M300" s="10" t="n">
         <v>0.5086545454545456</v>
       </c>
-      <c r="N300" t="n">
+      <c r="N300" s="10" t="n">
         <v>0.7830777777777778</v>
+      </c>
+      <c r="O300" t="n">
+        <v>0.5773375000000001</v>
       </c>
     </row>
     <row r="301" ht="16" customHeight="1" s="11">
@@ -10832,8 +11699,11 @@
       <c r="M301" s="10" t="n">
         <v>0.7366076923076922</v>
       </c>
-      <c r="N301" t="n">
+      <c r="N301" s="10" t="n">
         <v>0.6350461538461538</v>
+      </c>
+      <c r="O301" t="n">
+        <v>0.52158</v>
       </c>
     </row>
     <row r="302" ht="16" customHeight="1" s="11">
@@ -10867,8 +11737,11 @@
       <c r="M302" s="10" t="n">
         <v>0.6941363636363637</v>
       </c>
-      <c r="N302" t="n">
+      <c r="N302" s="10" t="n">
         <v>0.6479199999999999</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0.7072375000000001</v>
       </c>
     </row>
     <row r="303" ht="16" customHeight="1" s="11">
@@ -10902,8 +11775,11 @@
       <c r="M303" s="10" t="n">
         <v>0.76358</v>
       </c>
-      <c r="N303" t="n">
+      <c r="N303" s="10" t="n">
         <v>0.5394666666666668</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0.4819555555555556</v>
       </c>
     </row>
     <row r="304" ht="16" customHeight="1" s="11">
@@ -10937,8 +11813,11 @@
       <c r="M304" s="10" t="n">
         <v>0.6135900000000001</v>
       </c>
-      <c r="N304" t="n">
+      <c r="N304" s="10" t="n">
         <v>0.5691166666666666</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0.53499</v>
       </c>
     </row>
     <row r="305" ht="16" customHeight="1" s="11">
@@ -10972,8 +11851,11 @@
       <c r="M305" s="10" t="n">
         <v>0.7072000000000001</v>
       </c>
-      <c r="N305" t="n">
+      <c r="N305" s="10" t="n">
         <v>0.7358272727272728</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0.5887363636363637</v>
       </c>
     </row>
     <row r="306" ht="16" customHeight="1" s="11">
@@ -11007,8 +11889,11 @@
       <c r="M306" s="10" t="n">
         <v>0.7458</v>
       </c>
-      <c r="N306" t="n">
+      <c r="N306" s="10" t="n">
         <v>0.81753</v>
+      </c>
+      <c r="O306" t="n">
+        <v>0.5072333333333332</v>
       </c>
     </row>
     <row r="307" ht="16" customHeight="1" s="11">
@@ -11042,8 +11927,11 @@
       <c r="M307" s="10" t="n">
         <v>0.7621555555555556</v>
       </c>
-      <c r="N307" t="n">
+      <c r="N307" s="10" t="n">
         <v>0.62556</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0.296075</v>
       </c>
     </row>
     <row r="308" ht="16" customHeight="1" s="11">
@@ -11077,8 +11965,11 @@
       <c r="M308" s="10" t="n">
         <v>0.7753181818181819</v>
       </c>
-      <c r="N308" t="n">
+      <c r="N308" s="10" t="n">
         <v>0.8653999999999999</v>
+      </c>
+      <c r="O308" t="n">
+        <v>0.5168400000000001</v>
       </c>
     </row>
     <row r="309" ht="16" customHeight="1" s="11">
@@ -11112,8 +12003,11 @@
       <c r="M309" s="10" t="n">
         <v>0.7042700000000001</v>
       </c>
-      <c r="N309" t="n">
+      <c r="N309" s="10" t="n">
         <v>0.7075222222222224</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0.7185333333333335</v>
       </c>
     </row>
     <row r="310" ht="16" customHeight="1" s="11">
@@ -11147,8 +12041,11 @@
       <c r="M310" s="10" t="n">
         <v>0.6168461538461538</v>
       </c>
-      <c r="N310" t="n">
+      <c r="N310" s="10" t="n">
         <v>0.6212636363636364</v>
+      </c>
+      <c r="O310" t="n">
+        <v>0.5232333333333332</v>
       </c>
     </row>
     <row r="311" ht="16" customHeight="1" s="11">
@@ -11182,8 +12079,11 @@
       <c r="M311" s="10" t="n">
         <v>0.6274769230769232</v>
       </c>
-      <c r="N311" t="n">
+      <c r="N311" s="10" t="n">
         <v>0.6803666666666666</v>
+      </c>
+      <c r="O311" t="n">
+        <v>0.5273625</v>
       </c>
     </row>
     <row r="314" ht="16" customHeight="1" s="11">
@@ -11241,8 +12141,11 @@
       <c r="M316" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="N316" t="n">
+      <c r="N316" s="10" t="n">
         <v>0.0007</v>
+      </c>
+      <c r="O316" s="10" t="n">
+        <v>0.0009</v>
       </c>
     </row>
     <row r="317" ht="16" customHeight="1" s="11">
@@ -11276,8 +12179,11 @@
       <c r="M317" s="10" t="n">
         <v>0.0029</v>
       </c>
-      <c r="N317" t="n">
+      <c r="N317" s="10" t="n">
         <v>0.0519</v>
+      </c>
+      <c r="O317" s="10" t="n">
+        <v>0.0141</v>
       </c>
     </row>
     <row r="318" ht="16" customHeight="1" s="11">
@@ -11311,8 +12217,11 @@
       <c r="M318" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="N318" t="n">
+      <c r="N318" s="10" t="n">
         <v>0.0149</v>
+      </c>
+      <c r="O318" s="10" t="n">
+        <v>0.0133</v>
       </c>
     </row>
     <row r="319" ht="16" customHeight="1" s="11">
@@ -11346,8 +12255,11 @@
       <c r="M319" s="10" t="n">
         <v>0.0074</v>
       </c>
-      <c r="N319" t="n">
+      <c r="N319" s="10" t="n">
         <v>0.0482</v>
+      </c>
+      <c r="O319" s="10" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="320" ht="16" customHeight="1" s="11">
@@ -11381,8 +12293,11 @@
       <c r="M320" s="10" t="n">
         <v>0.0464</v>
       </c>
-      <c r="N320" t="n">
+      <c r="N320" s="10" t="n">
         <v>0.07920000000000001</v>
+      </c>
+      <c r="O320" s="10" t="n">
+        <v>0.0209</v>
       </c>
     </row>
     <row r="321" ht="16" customHeight="1" s="11">
@@ -11416,8 +12331,11 @@
       <c r="M321" s="10" t="n">
         <v>0.0404</v>
       </c>
-      <c r="N321" t="n">
+      <c r="N321" s="10" t="n">
         <v>0.0482</v>
+      </c>
+      <c r="O321" s="10" t="n">
+        <v>0.0609</v>
       </c>
     </row>
     <row r="322" ht="16" customHeight="1" s="11">
@@ -11451,8 +12369,11 @@
       <c r="M322" s="10" t="n">
         <v>0.0926</v>
       </c>
-      <c r="N322" t="n">
+      <c r="N322" s="10" t="n">
         <v>0.0801</v>
+      </c>
+      <c r="O322" s="10" t="n">
+        <v>0.0544</v>
       </c>
     </row>
     <row r="323" ht="16" customHeight="1" s="11">
@@ -11486,8 +12407,11 @@
       <c r="M323" s="10" t="n">
         <v>0.0309</v>
       </c>
-      <c r="N323" t="n">
+      <c r="N323" s="10" t="n">
         <v>0.0856</v>
+      </c>
+      <c r="O323" s="10" t="n">
+        <v>0.0217</v>
       </c>
     </row>
     <row r="324" ht="16" customHeight="1" s="11">
@@ -11521,8 +12445,11 @@
       <c r="M324" s="10" t="n">
         <v>0.0667</v>
       </c>
-      <c r="N324" t="n">
+      <c r="N324" s="10" t="n">
         <v>0.0076</v>
+      </c>
+      <c r="O324" s="10" t="n">
+        <v>0.1229</v>
       </c>
     </row>
     <row r="325" ht="16" customHeight="1" s="11">
@@ -11556,8 +12483,11 @@
       <c r="M325" s="10" t="n">
         <v>0.0481</v>
       </c>
-      <c r="N325" t="n">
+      <c r="N325" s="10" t="n">
         <v>0.0243</v>
+      </c>
+      <c r="O325" s="10" t="n">
+        <v>0.0633</v>
       </c>
     </row>
     <row r="326" ht="16" customHeight="1" s="11">
@@ -11591,8 +12521,11 @@
       <c r="M326" s="10" t="n">
         <v>0.0888</v>
       </c>
-      <c r="N326" t="n">
+      <c r="N326" s="10" t="n">
         <v>0.0687</v>
+      </c>
+      <c r="O326" s="10" t="n">
+        <v>0.0849</v>
       </c>
     </row>
     <row r="327" ht="16" customHeight="1" s="11">
@@ -11626,8 +12559,11 @@
       <c r="M327" s="10" t="n">
         <v>0.0248</v>
       </c>
-      <c r="N327" t="n">
+      <c r="N327" s="10" t="n">
         <v>0.048</v>
+      </c>
+      <c r="O327" s="10" t="n">
+        <v>0.0576</v>
       </c>
     </row>
     <row r="328" ht="16" customHeight="1" s="11">
@@ -11661,8 +12597,11 @@
       <c r="M328" s="10" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="N328" t="n">
+      <c r="N328" s="10" t="n">
         <v>0.0723</v>
+      </c>
+      <c r="O328" t="n">
+        <v>0.0722</v>
       </c>
     </row>
     <row r="329" ht="16" customHeight="1" s="11">
@@ -11696,8 +12635,11 @@
       <c r="M329" s="10" t="n">
         <v>0.1264</v>
       </c>
-      <c r="N329" t="n">
+      <c r="N329" s="10" t="n">
         <v>0.062</v>
+      </c>
+      <c r="O329" t="n">
+        <v>0.1002</v>
       </c>
     </row>
     <row r="330" ht="16" customHeight="1" s="11">
@@ -11731,8 +12673,11 @@
       <c r="M330" s="10" t="n">
         <v>0.0825</v>
       </c>
-      <c r="N330" t="n">
+      <c r="N330" s="10" t="n">
         <v>0.0895</v>
+      </c>
+      <c r="O330" t="n">
+        <v>0.076</v>
       </c>
     </row>
     <row r="331" ht="16" customHeight="1" s="11">
@@ -11766,8 +12711,11 @@
       <c r="M331" s="10" t="n">
         <v>0.0354</v>
       </c>
-      <c r="N331" t="n">
+      <c r="N331" s="10" t="n">
         <v>0.1107</v>
+      </c>
+      <c r="O331" t="n">
+        <v>0.07149999999999999</v>
       </c>
     </row>
     <row r="332" ht="16" customHeight="1" s="11">
@@ -11801,8 +12749,11 @@
       <c r="M332" s="10" t="n">
         <v>0.0233</v>
       </c>
-      <c r="N332" t="n">
+      <c r="N332" s="10" t="n">
         <v>0.0795</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0.0636</v>
       </c>
     </row>
     <row r="333" ht="16" customHeight="1" s="11">
@@ -11836,8 +12787,11 @@
       <c r="M333" s="10" t="n">
         <v>0.09470000000000001</v>
       </c>
-      <c r="N333" t="n">
+      <c r="N333" s="10" t="n">
         <v>0.1086</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0.0544</v>
       </c>
     </row>
     <row r="334" ht="16" customHeight="1" s="11">
@@ -11871,8 +12825,11 @@
       <c r="M334" s="10" t="n">
         <v>0.08939999999999999</v>
       </c>
-      <c r="N334" t="n">
+      <c r="N334" s="10" t="n">
         <v>0.108</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="335" ht="16" customHeight="1" s="11">
@@ -11906,8 +12863,11 @@
       <c r="M335" s="10" t="n">
         <v>0.1058</v>
       </c>
-      <c r="N335" t="n">
+      <c r="N335" s="10" t="n">
         <v>0.0961</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0.0766</v>
       </c>
     </row>
     <row r="336" ht="16" customHeight="1" s="11">
@@ -11941,8 +12901,11 @@
       <c r="M336" s="10" t="n">
         <v>0.0608</v>
       </c>
-      <c r="N336" t="n">
+      <c r="N336" s="10" t="n">
         <v>0.1168</v>
+      </c>
+      <c r="O336" t="n">
+        <v>0.0603</v>
       </c>
     </row>
     <row r="337" ht="16" customHeight="1" s="11">
@@ -11976,8 +12939,11 @@
       <c r="M337" s="10" t="n">
         <v>0.1024</v>
       </c>
-      <c r="N337" t="n">
+      <c r="N337" s="10" t="n">
         <v>0.0888</v>
+      </c>
+      <c r="O337" t="n">
+        <v>0.0558</v>
       </c>
     </row>
     <row r="338" ht="16" customHeight="1" s="11">
@@ -12011,8 +12977,11 @@
       <c r="M338" s="10" t="n">
         <v>0.0264</v>
       </c>
-      <c r="N338" t="n">
+      <c r="N338" s="10" t="n">
         <v>0.1068</v>
+      </c>
+      <c r="O338" t="n">
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="339" ht="16" customHeight="1" s="11">
@@ -12046,8 +13015,11 @@
       <c r="M339" s="10" t="n">
         <v>0.0331</v>
       </c>
-      <c r="N339" t="n">
+      <c r="N339" s="10" t="n">
         <v>0.1391</v>
+      </c>
+      <c r="O339" t="n">
+        <v>0.0616</v>
       </c>
     </row>
     <row r="340" ht="16" customHeight="1" s="11">
@@ -12081,8 +13053,11 @@
       <c r="M340" s="10" t="n">
         <v>0.0495</v>
       </c>
-      <c r="N340" t="n">
+      <c r="N340" s="10" t="n">
         <v>0.11</v>
+      </c>
+      <c r="O340" t="n">
+        <v>0.0557</v>
       </c>
     </row>
     <row r="341" ht="16" customHeight="1" s="11">
@@ -12116,8 +13091,11 @@
       <c r="M341" s="10" t="n">
         <v>0.0473</v>
       </c>
-      <c r="N341" t="n">
+      <c r="N341" s="10" t="n">
         <v>0.1081</v>
+      </c>
+      <c r="O341" t="n">
+        <v>0.0501</v>
       </c>
     </row>
     <row r="342" ht="16" customHeight="1" s="11">
@@ -12151,8 +13129,11 @@
       <c r="M342" s="10" t="n">
         <v>0.0505</v>
       </c>
-      <c r="N342" t="n">
+      <c r="N342" s="10" t="n">
         <v>0.0795</v>
+      </c>
+      <c r="O342" t="n">
+        <v>0.054</v>
       </c>
     </row>
     <row r="343" ht="16" customHeight="1" s="11">
@@ -12186,8 +13167,11 @@
       <c r="M343" s="10" t="n">
         <v>0.0395</v>
       </c>
-      <c r="N343" t="n">
+      <c r="N343" s="10" t="n">
         <v>0.0965</v>
+      </c>
+      <c r="O343" t="n">
+        <v>0.097</v>
       </c>
     </row>
     <row r="344" ht="16" customHeight="1" s="11">
@@ -12221,8 +13205,11 @@
       <c r="M344" s="10" t="n">
         <v>0.0259</v>
       </c>
-      <c r="N344" t="n">
+      <c r="N344" s="10" t="n">
         <v>0.09470000000000001</v>
+      </c>
+      <c r="O344" t="n">
+        <v>0.1138</v>
       </c>
     </row>
     <row r="345" ht="16" customHeight="1" s="11">
@@ -12256,8 +13243,11 @@
       <c r="M345" s="10" t="n">
         <v>0.0395</v>
       </c>
-      <c r="N345" t="n">
+      <c r="N345" s="10" t="n">
         <v>0.108</v>
+      </c>
+      <c r="O345" t="n">
+        <v>0.1074</v>
       </c>
     </row>
     <row r="346" ht="16" customHeight="1" s="11">
@@ -12291,8 +13281,11 @@
       <c r="M346" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="N346" t="n">
+      <c r="N346" s="10" t="n">
         <v>0.1004</v>
+      </c>
+      <c r="O346" t="n">
+        <v>0.1196</v>
       </c>
     </row>
     <row r="347" ht="16" customHeight="1" s="11">
@@ -12326,8 +13319,11 @@
       <c r="M347" s="10" t="n">
         <v>0.0271</v>
       </c>
-      <c r="N347" t="n">
+      <c r="N347" s="10" t="n">
         <v>0.1094</v>
+      </c>
+      <c r="O347" t="n">
+        <v>0.1105</v>
       </c>
     </row>
     <row r="348" ht="16" customHeight="1" s="11">
@@ -12361,8 +13357,11 @@
       <c r="M348" s="10" t="n">
         <v>0.0497</v>
       </c>
-      <c r="N348" t="n">
+      <c r="N348" s="10" t="n">
         <v>0.1047</v>
+      </c>
+      <c r="O348" t="n">
+        <v>0.0781</v>
       </c>
     </row>
     <row r="349" ht="16" customHeight="1" s="11">
@@ -12396,8 +13395,11 @@
       <c r="M349" s="10" t="n">
         <v>0.0447</v>
       </c>
-      <c r="N349" t="n">
+      <c r="N349" s="10" t="n">
         <v>0.09279999999999999</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0.0867</v>
       </c>
     </row>
     <row r="350" ht="16" customHeight="1" s="11">
@@ -12431,8 +13433,11 @@
       <c r="M350" s="10" t="n">
         <v>0.0341</v>
       </c>
-      <c r="N350" t="n">
+      <c r="N350" s="10" t="n">
         <v>0.1028</v>
+      </c>
+      <c r="O350" t="n">
+        <v>0.07829999999999999</v>
       </c>
     </row>
     <row r="351" ht="16" customHeight="1" s="11">
@@ -12466,8 +13471,11 @@
       <c r="M351" s="10" t="n">
         <v>0.0332</v>
       </c>
-      <c r="N351" t="n">
+      <c r="N351" s="10" t="n">
         <v>0.08359999999999999</v>
+      </c>
+      <c r="O351" t="n">
+        <v>0.057</v>
       </c>
     </row>
     <row r="352" ht="16" customHeight="1" s="11">
@@ -12501,8 +13509,11 @@
       <c r="M352" s="10" t="n">
         <v>0.0424</v>
       </c>
-      <c r="N352" t="n">
+      <c r="N352" s="10" t="n">
         <v>0.1027</v>
+      </c>
+      <c r="O352" t="n">
+        <v>0.0598</v>
       </c>
     </row>
     <row r="353" ht="16" customHeight="1" s="11">
@@ -12536,8 +13547,11 @@
       <c r="M353" s="10" t="n">
         <v>0.0365</v>
       </c>
-      <c r="N353" t="n">
+      <c r="N353" s="10" t="n">
         <v>0.1052</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="354" ht="16" customHeight="1" s="11">
@@ -12571,8 +13585,11 @@
       <c r="M354" s="10" t="n">
         <v>0.0342</v>
       </c>
-      <c r="N354" t="n">
+      <c r="N354" s="10" t="n">
         <v>0.0919</v>
+      </c>
+      <c r="O354" t="n">
+        <v>0.0599</v>
       </c>
     </row>
     <row r="355" ht="16" customHeight="1" s="11">
@@ -12606,8 +13623,11 @@
       <c r="M355" s="10" t="n">
         <v>0.0555</v>
       </c>
-      <c r="N355" t="n">
+      <c r="N355" s="10" t="n">
         <v>0.1087</v>
+      </c>
+      <c r="O355" t="n">
+        <v>0.0674</v>
       </c>
     </row>
     <row r="356" ht="16" customHeight="1" s="11">
@@ -12641,8 +13661,11 @@
       <c r="M356" s="10" t="n">
         <v>0.0511</v>
       </c>
-      <c r="N356" t="n">
+      <c r="N356" s="10" t="n">
         <v>0.0963</v>
+      </c>
+      <c r="O356" t="n">
+        <v>0.0584</v>
       </c>
     </row>
     <row r="357" ht="16" customHeight="1" s="11">
@@ -12676,8 +13699,11 @@
       <c r="M357" s="10" t="n">
         <v>0.048</v>
       </c>
-      <c r="N357" t="n">
+      <c r="N357" s="10" t="n">
         <v>0.1015</v>
+      </c>
+      <c r="O357" t="n">
+        <v>0.0598</v>
       </c>
     </row>
     <row r="358" ht="16" customHeight="1" s="11">
@@ -12711,8 +13737,11 @@
       <c r="M358" s="10" t="n">
         <v>0.0601</v>
       </c>
-      <c r="N358" t="n">
+      <c r="N358" s="10" t="n">
         <v>0.0965</v>
+      </c>
+      <c r="O358" t="n">
+        <v>0.09569999999999999</v>
       </c>
     </row>
     <row r="359" ht="16" customHeight="1" s="11">
@@ -12746,8 +13775,11 @@
       <c r="M359" s="10" t="n">
         <v>0.0573</v>
       </c>
-      <c r="N359" t="n">
+      <c r="N359" s="10" t="n">
         <v>0.092</v>
+      </c>
+      <c r="O359" t="n">
+        <v>0.0793</v>
       </c>
     </row>
     <row r="360" ht="16" customHeight="1" s="11">
@@ -12781,8 +13813,11 @@
       <c r="M360" s="10" t="n">
         <v>0.0451</v>
       </c>
-      <c r="N360" t="n">
+      <c r="N360" s="10" t="n">
         <v>0.0856</v>
+      </c>
+      <c r="O360" t="n">
+        <v>0.1088</v>
       </c>
     </row>
     <row r="361" ht="16" customHeight="1" s="11">
@@ -12816,8 +13851,11 @@
       <c r="M361" s="10" t="n">
         <v>0.0423</v>
       </c>
-      <c r="N361" t="n">
+      <c r="N361" s="10" t="n">
         <v>0.0886</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0.0804</v>
       </c>
     </row>
     <row r="362" ht="16" customHeight="1" s="11">
@@ -12851,8 +13889,11 @@
       <c r="M362" s="10" t="n">
         <v>0.0508</v>
       </c>
-      <c r="N362" t="n">
+      <c r="N362" s="10" t="n">
         <v>0.09959999999999999</v>
+      </c>
+      <c r="O362" t="n">
+        <v>0.0868</v>
       </c>
     </row>
     <row r="363" ht="16" customHeight="1" s="11">
@@ -12886,8 +13927,11 @@
       <c r="M363" s="10" t="n">
         <v>0.045</v>
       </c>
-      <c r="N363" t="n">
+      <c r="N363" s="10" t="n">
         <v>0.0988</v>
+      </c>
+      <c r="O363" t="n">
+        <v>0.0752</v>
       </c>
     </row>
     <row r="364" ht="16" customHeight="1" s="11">
@@ -12921,8 +13965,11 @@
       <c r="M364" s="10" t="n">
         <v>0.0415</v>
       </c>
-      <c r="N364" t="n">
+      <c r="N364" s="10" t="n">
         <v>0.0955</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0.0727</v>
       </c>
     </row>
     <row r="365" ht="16" customHeight="1" s="11">
@@ -12956,8 +14003,11 @@
       <c r="M365" s="10" t="n">
         <v>0.0373</v>
       </c>
-      <c r="N365" t="n">
+      <c r="N365" s="10" t="n">
         <v>0.09180000000000001</v>
+      </c>
+      <c r="O365" t="n">
+        <v>0.1038</v>
       </c>
     </row>
     <row r="366" ht="16" customHeight="1" s="11">
@@ -12991,8 +14041,11 @@
       <c r="M366" s="10" t="n">
         <v>0.0449</v>
       </c>
-      <c r="N366" t="n">
+      <c r="N366" s="10" t="n">
         <v>0.07870000000000001</v>
+      </c>
+      <c r="O366" t="n">
+        <v>0.0969</v>
       </c>
     </row>
     <row r="367" ht="16" customHeight="1" s="11">
@@ -13026,8 +14079,11 @@
       <c r="M367" s="10" t="n">
         <v>0.0477</v>
       </c>
-      <c r="N367" t="n">
+      <c r="N367" s="10" t="n">
         <v>0.0919</v>
+      </c>
+      <c r="O367" t="n">
+        <v>0.09959999999999999</v>
       </c>
     </row>
     <row r="368" ht="16" customHeight="1" s="11">
@@ -13061,8 +14117,11 @@
       <c r="M368" s="10" t="n">
         <v>0.0446</v>
       </c>
-      <c r="N368" t="n">
+      <c r="N368" s="10" t="n">
         <v>0.07099999999999999</v>
+      </c>
+      <c r="O368" t="n">
+        <v>0.06370000000000001</v>
       </c>
     </row>
     <row r="369" ht="16" customHeight="1" s="11">
@@ -13096,8 +14155,11 @@
       <c r="M369" s="10" t="n">
         <v>0.0521</v>
       </c>
-      <c r="N369" t="n">
+      <c r="N369" s="10" t="n">
         <v>0.07489999999999999</v>
+      </c>
+      <c r="O369" t="n">
+        <v>0.0659</v>
       </c>
     </row>
     <row r="370" ht="16" customHeight="1" s="11">
@@ -13131,8 +14193,11 @@
       <c r="M370" s="10" t="n">
         <v>0.055</v>
       </c>
-      <c r="N370" t="n">
+      <c r="N370" s="10" t="n">
         <v>0.07140000000000001</v>
+      </c>
+      <c r="O370" t="n">
+        <v>0.0725</v>
       </c>
     </row>
     <row r="371" ht="16" customHeight="1" s="11">
@@ -13166,8 +14231,11 @@
       <c r="M371" s="10" t="n">
         <v>0.0385</v>
       </c>
-      <c r="N371" t="n">
+      <c r="N371" s="10" t="n">
         <v>0.0678</v>
+      </c>
+      <c r="O371" t="n">
+        <v>0.0886</v>
       </c>
     </row>
     <row r="372" ht="16" customHeight="1" s="11">
@@ -13201,8 +14269,11 @@
       <c r="M372" s="10" t="n">
         <v>0.0539</v>
       </c>
-      <c r="N372" t="n">
+      <c r="N372" s="10" t="n">
         <v>0.0743</v>
+      </c>
+      <c r="O372" t="n">
+        <v>0.07829999999999999</v>
       </c>
     </row>
     <row r="373" ht="16" customHeight="1" s="11">
@@ -13236,8 +14307,11 @@
       <c r="M373" s="10" t="n">
         <v>0.0394</v>
       </c>
-      <c r="N373" t="n">
+      <c r="N373" s="10" t="n">
         <v>0.06320000000000001</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0.0752</v>
       </c>
     </row>
     <row r="374" ht="16" customHeight="1" s="11">
@@ -13271,8 +14345,11 @@
       <c r="M374" s="10" t="n">
         <v>0.0439</v>
       </c>
-      <c r="N374" t="n">
+      <c r="N374" s="10" t="n">
         <v>0.0858</v>
+      </c>
+      <c r="O374" t="n">
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="375" ht="16" customHeight="1" s="11">
@@ -13306,8 +14383,11 @@
       <c r="M375" s="10" t="n">
         <v>0.0436</v>
       </c>
-      <c r="N375" t="n">
+      <c r="N375" s="10" t="n">
         <v>0.0794</v>
+      </c>
+      <c r="O375" t="n">
+        <v>0.0639</v>
       </c>
     </row>
     <row r="376" ht="16" customHeight="1" s="11">
@@ -13341,8 +14421,11 @@
       <c r="M376" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="N376" t="n">
+      <c r="N376" s="10" t="n">
         <v>0.07820000000000001</v>
+      </c>
+      <c r="O376" t="n">
+        <v>0.07679999999999999</v>
       </c>
     </row>
     <row r="377" ht="16" customHeight="1" s="11">
@@ -13376,8 +14459,11 @@
       <c r="M377" s="10" t="n">
         <v>0.0433</v>
       </c>
-      <c r="N377" t="n">
+      <c r="N377" s="10" t="n">
         <v>0.0723</v>
+      </c>
+      <c r="O377" t="n">
+        <v>0.0886</v>
       </c>
     </row>
     <row r="378" ht="16" customHeight="1" s="11">
@@ -13411,8 +14497,11 @@
       <c r="M378" s="10" t="n">
         <v>0.0365</v>
       </c>
-      <c r="N378" t="n">
+      <c r="N378" s="10" t="n">
         <v>0.06419999999999999</v>
+      </c>
+      <c r="O378" t="n">
+        <v>0.0882</v>
       </c>
     </row>
     <row r="379" ht="16" customHeight="1" s="11">
@@ -13446,8 +14535,11 @@
       <c r="M379" s="10" t="n">
         <v>0.0556</v>
       </c>
-      <c r="N379" t="n">
+      <c r="N379" s="10" t="n">
         <v>0.0829</v>
+      </c>
+      <c r="O379" t="n">
+        <v>0.0793</v>
       </c>
     </row>
     <row r="380" ht="16" customHeight="1" s="11">
@@ -13481,8 +14573,11 @@
       <c r="M380" s="10" t="n">
         <v>0.0551</v>
       </c>
-      <c r="N380" t="n">
+      <c r="N380" s="10" t="n">
         <v>0.07820000000000001</v>
+      </c>
+      <c r="O380" t="n">
+        <v>0.09080000000000001</v>
       </c>
     </row>
     <row r="381" ht="16" customHeight="1" s="11">
@@ -13516,8 +14611,11 @@
       <c r="M381" s="10" t="n">
         <v>0.0482</v>
       </c>
-      <c r="N381" t="n">
+      <c r="N381" s="10" t="n">
         <v>0.0711</v>
+      </c>
+      <c r="O381" t="n">
+        <v>0.0688</v>
       </c>
     </row>
     <row r="382" ht="16" customHeight="1" s="11">
@@ -13551,8 +14649,11 @@
       <c r="M382" s="10" t="n">
         <v>0.0426</v>
       </c>
-      <c r="N382" t="n">
+      <c r="N382" s="10" t="n">
         <v>0.0849</v>
+      </c>
+      <c r="O382" t="n">
+        <v>0.076</v>
       </c>
     </row>
     <row r="383" ht="16" customHeight="1" s="11">
@@ -13586,8 +14687,11 @@
       <c r="M383" s="10" t="n">
         <v>0.0477</v>
       </c>
-      <c r="N383" t="n">
+      <c r="N383" s="10" t="n">
         <v>0.0827</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0.0893</v>
       </c>
     </row>
     <row r="384" ht="16" customHeight="1" s="11">
@@ -13621,8 +14725,11 @@
       <c r="M384" s="10" t="n">
         <v>0.0508</v>
       </c>
-      <c r="N384" t="n">
+      <c r="N384" s="10" t="n">
         <v>0.0844</v>
+      </c>
+      <c r="O384" t="n">
+        <v>0.08989999999999999</v>
       </c>
     </row>
     <row r="385" ht="16" customHeight="1" s="11">
@@ -13656,8 +14763,11 @@
       <c r="M385" s="10" t="n">
         <v>0.0433</v>
       </c>
-      <c r="N385" t="n">
+      <c r="N385" s="10" t="n">
         <v>0.0868</v>
+      </c>
+      <c r="O385" t="n">
+        <v>0.0823</v>
       </c>
     </row>
     <row r="386" ht="16" customHeight="1" s="11">
@@ -13691,8 +14801,11 @@
       <c r="M386" s="10" t="n">
         <v>0.04</v>
       </c>
-      <c r="N386" t="n">
+      <c r="N386" s="10" t="n">
         <v>0.0717</v>
+      </c>
+      <c r="O386" t="n">
+        <v>0.0852</v>
       </c>
     </row>
     <row r="387" ht="16" customHeight="1" s="11">
@@ -13726,8 +14839,11 @@
       <c r="M387" s="10" t="n">
         <v>0.0475</v>
       </c>
-      <c r="N387" t="n">
+      <c r="N387" s="10" t="n">
         <v>0.0795</v>
+      </c>
+      <c r="O387" t="n">
+        <v>0.0843</v>
       </c>
     </row>
     <row r="388" ht="16" customHeight="1" s="11">
@@ -13761,8 +14877,11 @@
       <c r="M388" s="10" t="n">
         <v>0.0477</v>
       </c>
-      <c r="N388" t="n">
+      <c r="N388" s="10" t="n">
         <v>0.0725</v>
+      </c>
+      <c r="O388" t="n">
+        <v>0.07480000000000001</v>
       </c>
     </row>
     <row r="389" ht="16" customHeight="1" s="11">
@@ -13796,8 +14915,11 @@
       <c r="M389" s="10" t="n">
         <v>0.0362</v>
       </c>
-      <c r="N389" t="n">
+      <c r="N389" s="10" t="n">
         <v>0.0799</v>
+      </c>
+      <c r="O389" t="n">
+        <v>0.0859</v>
       </c>
     </row>
     <row r="390" ht="16" customHeight="1" s="11">
@@ -13831,8 +14953,11 @@
       <c r="M390" s="10" t="n">
         <v>0.0379</v>
       </c>
-      <c r="N390" t="n">
+      <c r="N390" s="10" t="n">
         <v>0.06859999999999999</v>
+      </c>
+      <c r="O390" t="n">
+        <v>0.0898</v>
       </c>
     </row>
     <row r="391" ht="16" customHeight="1" s="11">
@@ -13866,8 +14991,11 @@
       <c r="M391" s="10" t="n">
         <v>0.0362</v>
       </c>
-      <c r="N391" t="n">
+      <c r="N391" s="10" t="n">
         <v>0.07630000000000001</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0.0914</v>
       </c>
     </row>
     <row r="392" ht="16" customHeight="1" s="11">
@@ -13901,8 +15029,11 @@
       <c r="M392" s="10" t="n">
         <v>0.0303</v>
       </c>
-      <c r="N392" t="n">
+      <c r="N392" s="10" t="n">
         <v>0.0723</v>
+      </c>
+      <c r="O392" t="n">
+        <v>0.078</v>
       </c>
     </row>
     <row r="393" ht="16" customHeight="1" s="11">
@@ -13936,8 +15067,11 @@
       <c r="M393" s="10" t="n">
         <v>0.0352</v>
       </c>
-      <c r="N393" t="n">
+      <c r="N393" s="10" t="n">
         <v>0.0762</v>
+      </c>
+      <c r="O393" t="n">
+        <v>0.0814</v>
       </c>
     </row>
     <row r="394" ht="16" customHeight="1" s="11">
@@ -13971,8 +15105,11 @@
       <c r="M394" s="10" t="n">
         <v>0.0365</v>
       </c>
-      <c r="N394" t="n">
+      <c r="N394" s="10" t="n">
         <v>0.0993</v>
+      </c>
+      <c r="O394" t="n">
+        <v>0.056</v>
       </c>
     </row>
     <row r="395" ht="16" customHeight="1" s="11">
@@ -14006,8 +15143,11 @@
       <c r="M395" s="10" t="n">
         <v>0.0395</v>
       </c>
-      <c r="N395" t="n">
+      <c r="N395" s="10" t="n">
         <v>0.08450000000000001</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0.0591</v>
       </c>
     </row>
     <row r="396" ht="16" customHeight="1" s="11">
@@ -14041,8 +15181,11 @@
       <c r="M396" s="10" t="n">
         <v>0.0444</v>
       </c>
-      <c r="N396" t="n">
+      <c r="N396" s="10" t="n">
         <v>0.0737</v>
+      </c>
+      <c r="O396" t="n">
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="397" ht="16" customHeight="1" s="11">
@@ -14076,8 +15219,11 @@
       <c r="M397" s="10" t="n">
         <v>0.039</v>
       </c>
-      <c r="N397" t="n">
+      <c r="N397" s="10" t="n">
         <v>0.081</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0.0794</v>
       </c>
     </row>
     <row r="398" ht="16" customHeight="1" s="11">
@@ -14111,8 +15257,11 @@
       <c r="M398" s="10" t="n">
         <v>0.0546</v>
       </c>
-      <c r="N398" t="n">
+      <c r="N398" s="10" t="n">
         <v>0.0771</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="399" ht="16" customHeight="1" s="11">
@@ -14146,8 +15295,11 @@
       <c r="M399" s="10" t="n">
         <v>0.0508</v>
       </c>
-      <c r="N399" t="n">
+      <c r="N399" s="10" t="n">
         <v>0.0602</v>
+      </c>
+      <c r="O399" t="n">
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="400" ht="16" customHeight="1" s="11">
@@ -14181,8 +15333,11 @@
       <c r="M400" s="10" t="n">
         <v>0.0576</v>
       </c>
-      <c r="N400" t="n">
+      <c r="N400" s="10" t="n">
         <v>0.0795</v>
+      </c>
+      <c r="O400" t="n">
+        <v>0.0736</v>
       </c>
     </row>
     <row r="401" ht="16" customHeight="1" s="11">
@@ -14216,8 +15371,11 @@
       <c r="M401" s="10" t="n">
         <v>0.0543</v>
       </c>
-      <c r="N401" t="n">
+      <c r="N401" s="10" t="n">
         <v>0.07539999999999999</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0.0745</v>
       </c>
     </row>
     <row r="402" ht="16" customHeight="1" s="11">
@@ -14251,8 +15409,11 @@
       <c r="M402" s="10" t="n">
         <v>0.0645</v>
       </c>
-      <c r="N402" t="n">
+      <c r="N402" s="10" t="n">
         <v>0.0762</v>
+      </c>
+      <c r="O402" t="n">
+        <v>0.07489999999999999</v>
       </c>
     </row>
     <row r="403" ht="16" customHeight="1" s="11">
@@ -14286,8 +15447,11 @@
       <c r="M403" s="10" t="n">
         <v>0.0478</v>
       </c>
-      <c r="N403" t="n">
+      <c r="N403" s="10" t="n">
         <v>0.0752</v>
+      </c>
+      <c r="O403" t="n">
+        <v>0.0635</v>
       </c>
     </row>
     <row r="404" ht="16" customHeight="1" s="11">
@@ -14321,8 +15485,11 @@
       <c r="M404" s="10" t="n">
         <v>0.0481</v>
       </c>
-      <c r="N404" t="n">
+      <c r="N404" s="10" t="n">
         <v>0.078</v>
+      </c>
+      <c r="O404" t="n">
+        <v>0.06320000000000001</v>
       </c>
     </row>
     <row r="405" ht="16" customHeight="1" s="11">
@@ -14356,8 +15523,11 @@
       <c r="M405" s="10" t="n">
         <v>0.0378</v>
       </c>
-      <c r="N405" t="n">
+      <c r="N405" s="10" t="n">
         <v>0.0684</v>
+      </c>
+      <c r="O405" t="n">
+        <v>0.0696</v>
       </c>
     </row>
     <row r="406" ht="16" customHeight="1" s="11">
@@ -14391,8 +15561,11 @@
       <c r="M406" s="10" t="n">
         <v>0.036</v>
       </c>
-      <c r="N406" t="n">
+      <c r="N406" s="10" t="n">
         <v>0.07820000000000001</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="407" ht="16" customHeight="1" s="11">
@@ -14426,8 +15599,11 @@
       <c r="M407" s="10" t="n">
         <v>0.0363</v>
       </c>
-      <c r="N407" t="n">
+      <c r="N407" s="10" t="n">
         <v>0.0725</v>
+      </c>
+      <c r="O407" t="n">
+        <v>0.0619</v>
       </c>
     </row>
     <row r="408" ht="16" customHeight="1" s="11">
@@ -14461,8 +15637,11 @@
       <c r="M408" s="10" t="n">
         <v>0.04</v>
       </c>
-      <c r="N408" t="n">
+      <c r="N408" s="10" t="n">
         <v>0.0679</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0.0767</v>
       </c>
     </row>
     <row r="409" ht="16" customHeight="1" s="11">
@@ -14496,8 +15675,11 @@
       <c r="M409" s="10" t="n">
         <v>0.0578</v>
       </c>
-      <c r="N409" t="n">
+      <c r="N409" s="10" t="n">
         <v>0.0774</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0.0668</v>
       </c>
     </row>
     <row r="410" ht="16" customHeight="1" s="11">
@@ -14531,8 +15713,11 @@
       <c r="M410" s="10" t="n">
         <v>0.0483</v>
       </c>
-      <c r="N410" t="n">
+      <c r="N410" s="10" t="n">
         <v>0.0891</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0.06510000000000001</v>
       </c>
     </row>
     <row r="411" ht="16" customHeight="1" s="11">
@@ -14566,8 +15751,11 @@
       <c r="M411" s="10" t="n">
         <v>0.0487</v>
       </c>
-      <c r="N411" t="n">
+      <c r="N411" s="10" t="n">
         <v>0.08110000000000001</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0.0871</v>
       </c>
     </row>
     <row r="412" ht="16" customHeight="1" s="11">
@@ -14601,8 +15789,11 @@
       <c r="M412" s="10" t="n">
         <v>0.0493</v>
       </c>
-      <c r="N412" t="n">
+      <c r="N412" s="10" t="n">
         <v>0.07770000000000001</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0.07290000000000001</v>
       </c>
     </row>
     <row r="413" ht="16" customHeight="1" s="11">
@@ -14636,8 +15827,11 @@
       <c r="M413" s="10" t="n">
         <v>0.045</v>
       </c>
-      <c r="N413" t="n">
+      <c r="N413" s="10" t="n">
         <v>0.0721</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0.0871</v>
       </c>
     </row>
     <row r="414" ht="16" customHeight="1" s="11">
@@ -14671,8 +15865,11 @@
       <c r="M414" s="10" t="n">
         <v>0.031</v>
       </c>
-      <c r="N414" t="n">
+      <c r="N414" s="10" t="n">
         <v>0.1053</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0.0815</v>
       </c>
     </row>
     <row r="415" ht="16" customHeight="1" s="11">
@@ -14706,8 +15903,511 @@
       <c r="M415" s="10" t="n">
         <v>0.0252</v>
       </c>
-      <c r="N415" t="n">
+      <c r="N415" s="10" t="n">
         <v>0.0853</v>
+      </c>
+      <c r="O415" t="n">
+        <v>0.1001</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="O418" s="10" t="n">
+        <v>0.1534</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="O419" s="10" t="n">
+        <v>0.20408</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="O420" s="10" t="n">
+        <v>0.229425</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="O421" s="10" t="n">
+        <v>0.2533142857142857</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="O422" s="10" t="n">
+        <v>0.2734</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="O423" s="10" t="n">
+        <v>0.2902999999999999</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="O424" s="10" t="n">
+        <v>0.3184888888888889</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="O425" s="10" t="n">
+        <v>0.3095666666666667</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="O426" s="10" t="n">
+        <v>0.3281</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="O427" s="10" t="n">
+        <v>0.33331</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="O428" s="10" t="n">
+        <v>0.3427444444444445</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="O429" s="10" t="n">
+        <v>0.3327000000000001</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="O430" t="n">
+        <v>0.36263</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="O431" t="n">
+        <v>0.344175</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="O432" t="n">
+        <v>0.3694857142857143</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="O433" t="n">
+        <v>0.36075</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="O434" t="n">
+        <v>0.348</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="O435" t="n">
+        <v>0.362825</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="O436" t="n">
+        <v>0.3579375</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="O437" t="n">
+        <v>0.3628</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="O438" t="n">
+        <v>0.3623545454545454</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="O439" t="n">
+        <v>0.35342</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="O440" t="n">
+        <v>0.3619555555555556</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="O441" t="n">
+        <v>0.3715857142857143</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="O442" t="n">
+        <v>0.3630888888888888</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="O443" t="n">
+        <v>0.3579625</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="O444" t="n">
+        <v>0.3726</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="O445" t="n">
+        <v>0.36285</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="O446" t="n">
+        <v>0.3536</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="O447" t="n">
+        <v>0.3689</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="O448" t="n">
+        <v>0.34824</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="O449" t="n">
+        <v>0.3604111111111111</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="O450" t="n">
+        <v>0.3569625</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="O451" t="n">
+        <v>0.3557375</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="O452" t="n">
+        <v>0.3752454545454545</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="O453" t="n">
+        <v>0.34765</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="O454" t="n">
+        <v>0.3615111111111111</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="O455" t="n">
+        <v>0.3572875</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="O456" t="n">
+        <v>0.37473</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="O457" t="n">
+        <v>0.3702818181818182</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="O458" t="n">
+        <v>0.367211111111111</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="O459" t="n">
+        <v>0.393911111111111</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="O460" t="n">
+        <v>0.3624</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="O461" t="n">
+        <v>0.3799555555555555</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="O462" t="n">
+        <v>0.3800545454545455</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="O463" t="n">
+        <v>0.3402555555555555</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="O464" t="n">
+        <v>0.3587500000000001</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="O465" t="n">
+        <v>0.3646</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="O466" t="n">
+        <v>0.3682</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="O467" t="n">
+        <v>0.3640899999999999</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="O468" t="n">
+        <v>0.3629125000000001</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="O469" t="n">
+        <v>0.36263</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="O470" t="n">
+        <v>0.3670666666666667</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="O471" t="n">
+        <v>0.3645375</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="O472" t="n">
+        <v>0.3589142857142857</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="O473" t="n">
+        <v>0.3726444444444444</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="O474" t="n">
+        <v>0.3582666666666666</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="O475" t="n">
+        <v>0.3651727272727273</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="O476" t="n">
+        <v>0.3778384615384616</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="O477" t="n">
+        <v>0.3673571428571428</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="O478" t="n">
+        <v>0.35773</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="O479" t="n">
+        <v>0.35933</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="O480" t="n">
+        <v>0.36935</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="O481" t="n">
+        <v>0.3630444444444445</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="O482" t="n">
+        <v>0.3577</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="O483" t="n">
+        <v>0.37977</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="O484" t="n">
+        <v>0.362075</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="O485" t="n">
+        <v>0.3699</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="O486" t="n">
+        <v>0.3423888888888889</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="O487" t="n">
+        <v>0.3526624999999999</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="O488" t="n">
+        <v>0.35937</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="O489" t="n">
+        <v>0.3591</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="O490" t="n">
+        <v>0.3528125</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="O491" t="n">
+        <v>0.36053</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="O492" t="n">
+        <v>0.37565</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="O493" t="n">
+        <v>0.3728777777777778</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="O494" t="n">
+        <v>0.3743300000000001</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="O495" t="n">
+        <v>0.3485</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="O496" t="n">
+        <v>0.3827333333333334</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="O497" t="n">
+        <v>0.3498000000000001</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="O498" t="n">
+        <v>0.3585666666666667</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="O499" t="n">
+        <v>0.3741888888888889</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="O500" t="n">
+        <v>0.3636399999999999</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="O501" t="n">
+        <v>0.3595666666666667</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="O502" t="n">
+        <v>0.3753666666666666</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="O503" t="n">
+        <v>0.3815000000000001</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="O504" t="n">
+        <v>0.3529875</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="O505" t="n">
+        <v>0.3759</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="O506" t="n">
+        <v>0.3607625</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="O507" t="n">
+        <v>0.35976</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="O508" t="n">
+        <v>0.3505</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="O509" t="n">
+        <v>0.3702555555555556</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="O510" t="n">
+        <v>0.3602900000000001</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="O511" t="n">
+        <v>0.3578181818181818</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="O512" t="n">
+        <v>0.3590888888888888</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="O513" t="n">
+        <v>0.379875</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="O514" t="n">
+        <v>0.34928</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="O515" t="n">
+        <v>0.3451222222222222</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="O516" t="n">
+        <v>0.3571555555555555</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="O517" t="n">
+        <v>0.3550249999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O517"/>
+  <dimension ref="A1:P517"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.5" defaultRowHeight="16" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="14.33" customWidth="1" style="10" min="1" max="1"/>
@@ -675,6 +675,9 @@
       <c r="O5" s="10" t="n">
         <v>0.15085</v>
       </c>
+      <c r="P5" s="10" t="n">
+        <v>0.15261</v>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1" s="11">
       <c r="A6" s="18" t="n">
@@ -713,6 +716,9 @@
       <c r="O6" s="10" t="n">
         <v>0.3156952380952381</v>
       </c>
+      <c r="P6" s="10" t="n">
+        <v>0.1984950819672131</v>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1" s="11">
       <c r="A7" s="18" t="n">
@@ -751,6 +757,9 @@
       <c r="O7" s="10" t="n">
         <v>0.2623789473684211</v>
       </c>
+      <c r="P7" s="10" t="n">
+        <v>0.2687428571428572</v>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1" s="11">
       <c r="A8" s="18" t="n">
@@ -789,6 +798,9 @@
       <c r="O8" s="10" t="n">
         <v>0.336076</v>
       </c>
+      <c r="P8" s="10" t="n">
+        <v>0.3430462686567164</v>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1" s="11">
       <c r="A9" s="18" t="n">
@@ -827,6 +839,9 @@
       <c r="O9" s="10" t="n">
         <v>0.4068193548387097</v>
       </c>
+      <c r="P9" s="10" t="n">
+        <v>0.3991941176470589</v>
+      </c>
     </row>
     <row r="10" ht="16" customHeight="1" s="11">
       <c r="A10" s="18" t="n">
@@ -865,6 +880,9 @@
       <c r="O10" s="10" t="n">
         <v>0.4127666666666667</v>
       </c>
+      <c r="P10" s="10" t="n">
+        <v>0.47485</v>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1" s="11">
       <c r="A11" s="18" t="n">
@@ -903,6 +921,9 @@
       <c r="O11" s="10" t="n">
         <v>0.4828740740740741</v>
       </c>
+      <c r="P11" s="10" t="n">
+        <v>0.4964083333333333</v>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="11">
       <c r="A12" s="18" t="n">
@@ -941,6 +962,9 @@
       <c r="O12" s="10" t="n">
         <v>0.4825780487804878</v>
       </c>
+      <c r="P12" s="10" t="n">
+        <v>0.5717142857142857</v>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1" s="11">
       <c r="A13" s="18" t="n">
@@ -979,6 +1003,9 @@
       <c r="O13" s="10" t="n">
         <v>0.6143458333333334</v>
       </c>
+      <c r="P13" s="10" t="n">
+        <v>0.5899432432432433</v>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="11">
       <c r="A14" s="18" t="n">
@@ -1017,6 +1044,9 @@
       <c r="O14" s="10" t="n">
         <v>0.6242810810810812</v>
       </c>
+      <c r="P14" t="n">
+        <v>0.6585410256410257</v>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="11">
       <c r="A15" s="18" t="n">
@@ -1055,6 +1085,9 @@
       <c r="O15" s="10" t="n">
         <v>0.6279682926829269</v>
       </c>
+      <c r="P15" t="n">
+        <v>0.7212030303030305</v>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="11">
       <c r="A16" s="18" t="n">
@@ -1093,6 +1126,9 @@
       <c r="O16" s="10" t="n">
         <v>0.62561</v>
       </c>
+      <c r="P16" t="n">
+        <v>0.7548338983050846</v>
+      </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="11">
       <c r="A17" s="18" t="n">
@@ -1128,8 +1164,11 @@
       <c r="N17" s="10" t="n">
         <v>0.5909714285714286</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="10" t="n">
         <v>0.7070395833333333</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.7289</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="11">
@@ -1166,8 +1205,11 @@
       <c r="N18" s="10" t="n">
         <v>0.6155055555555555</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="10" t="n">
         <v>0.7015650000000001</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.7507836363636363</v>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="11">
@@ -1204,8 +1246,11 @@
       <c r="N19" s="10" t="n">
         <v>0.6931615384615385</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="10" t="n">
         <v>0.7706250000000001</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.7958651162790698</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="11">
@@ -1242,8 +1287,11 @@
       <c r="N20" s="10" t="n">
         <v>0.6954259259259259</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="10" t="n">
         <v>0.7268062499999999</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.801769387755102</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="11">
@@ -1280,8 +1328,11 @@
       <c r="N21" s="10" t="n">
         <v>0.7208681818181818</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="10" t="n">
         <v>0.7121030303030302</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.7515661290322581</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="11">
@@ -1318,8 +1369,11 @@
       <c r="N22" s="10" t="n">
         <v>0.6757333333333334</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="10" t="n">
         <v>0.7713296296296297</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.7918062499999998</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1" s="11">
@@ -1356,8 +1410,11 @@
       <c r="N23" s="10" t="n">
         <v>0.7586851851851852</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="10" t="n">
         <v>0.7712057142857143</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.7817818181818181</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1" s="11">
@@ -1394,8 +1451,11 @@
       <c r="N24" s="10" t="n">
         <v>0.6258</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="10" t="n">
         <v>0.7573777777777778</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.7532897959183673</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1" s="11">
@@ -1432,8 +1492,11 @@
       <c r="N25" s="10" t="n">
         <v>0.6926928571428572</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" s="10" t="n">
         <v>0.8077400000000001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.7825396551724138</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1" s="11">
@@ -1470,8 +1533,11 @@
       <c r="N26" s="10" t="n">
         <v>0.7689243902439025</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" s="10" t="n">
         <v>0.808397435897436</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.8032945454545454</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1" s="11">
@@ -1508,8 +1574,11 @@
       <c r="N27" s="10" t="n">
         <v>0.8026111111111112</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" s="10" t="n">
         <v>0.7290928571428571</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.7685346153846153</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1" s="11">
@@ -1546,8 +1615,11 @@
       <c r="N28" s="10" t="n">
         <v>0.8487620689655171</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" s="10" t="n">
         <v>0.8504</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.852496551724138</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1" s="11">
@@ -1584,8 +1656,11 @@
       <c r="N29" s="10" t="n">
         <v>0.7313730769230771</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="10" t="n">
         <v>0.704325</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.7836754098360658</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1" s="11">
@@ -1622,8 +1697,11 @@
       <c r="N30" s="10" t="n">
         <v>0.8426740740740741</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" s="10" t="n">
         <v>0.7864136363636365</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.8629081632653063</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1" s="11">
@@ -1660,8 +1738,11 @@
       <c r="N31" s="10" t="n">
         <v>0.7710591836734693</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31" s="10" t="n">
         <v>0.747890243902439</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.7957510204081633</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1" s="11">
@@ -1698,8 +1779,11 @@
       <c r="N32" s="10" t="n">
         <v>0.7232619047619048</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" s="10" t="n">
         <v>0.831660465116279</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.7849555555555555</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1" s="11">
@@ -1736,8 +1820,11 @@
       <c r="N33" s="10" t="n">
         <v>0.7280200000000001</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" s="10" t="n">
         <v>0.832017857142857</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.8214271428571426</v>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1" s="11">
@@ -1774,8 +1861,11 @@
       <c r="N34" s="10" t="n">
         <v>0.8458410256410256</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34" s="10" t="n">
         <v>0.7479230769230769</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.8047169491525423</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1" s="11">
@@ -1812,8 +1902,11 @@
       <c r="N35" s="10" t="n">
         <v>0.8215210526315789</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" s="10" t="n">
         <v>0.7984472727272728</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.81201320754717</v>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1" s="11">
@@ -1850,8 +1943,11 @@
       <c r="N36" s="10" t="n">
         <v>0.8271181818181819</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36" s="10" t="n">
         <v>0.7752833333333333</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.8797207547169811</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1" s="11">
@@ -1888,8 +1984,11 @@
       <c r="N37" s="10" t="n">
         <v>0.759484</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" s="10" t="n">
         <v>0.8712935483870967</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.7600387755102039</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1" s="11">
@@ -1926,8 +2025,11 @@
       <c r="N38" s="10" t="n">
         <v>0.7245290322580645</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38" s="10" t="n">
         <v>0.8072918367346938</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.7619892857142858</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1" s="11">
@@ -1964,8 +2066,11 @@
       <c r="N39" s="10" t="n">
         <v>0.7952843749999999</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39" s="10" t="n">
         <v>0.8565735294117647</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.7554685185185186</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1" s="11">
@@ -2002,8 +2107,11 @@
       <c r="N40" s="10" t="n">
         <v>0.8183166666666666</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40" s="10" t="n">
         <v>0.8196600000000001</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.8158888888888888</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="11">
@@ -2040,8 +2148,11 @@
       <c r="N41" s="10" t="n">
         <v>0.7012096774193549</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41" s="10" t="n">
         <v>0.8514558823529413</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.7949865384615387</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="11">
@@ -2078,8 +2189,11 @@
       <c r="N42" s="10" t="n">
         <v>0.8291181818181819</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O42" s="10" t="n">
         <v>0.7641133333333333</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.848689552238806</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="11">
@@ -2116,8 +2230,11 @@
       <c r="N43" s="10" t="n">
         <v>0.8715249999999999</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O43" s="10" t="n">
         <v>0.8065107142857143</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.805640350877193</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="11">
@@ -2154,8 +2271,11 @@
       <c r="N44" s="10" t="n">
         <v>0.8116214285714286</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O44" s="10" t="n">
         <v>0.7783157894736842</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.7804866666666668</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1" s="11">
@@ -2192,8 +2312,11 @@
       <c r="N45" s="10" t="n">
         <v>0.7751409090909092</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O45" s="10" t="n">
         <v>0.8453258064516129</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.7714301886792454</v>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1" s="11">
@@ -2230,8 +2353,11 @@
       <c r="N46" s="10" t="n">
         <v>0.7962413793103449</v>
       </c>
-      <c r="O46" t="n">
+      <c r="O46" s="10" t="n">
         <v>0.83335</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.7908469387755104</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1" s="11">
@@ -2268,8 +2394,11 @@
       <c r="N47" s="10" t="n">
         <v>0.7753555555555557</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O47" s="10" t="n">
         <v>0.8887628571428572</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.8060130434782609</v>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1" s="11">
@@ -2306,8 +2435,11 @@
       <c r="N48" s="10" t="n">
         <v>0.8330464285714285</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O48" s="10" t="n">
         <v>0.7538766666666668</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.7968766666666668</v>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1" s="11">
@@ -2344,8 +2476,11 @@
       <c r="N49" s="10" t="n">
         <v>0.634508</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O49" s="10" t="n">
         <v>0.8872657894736842</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.847302</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" s="11">
@@ -2382,8 +2517,11 @@
       <c r="N50" s="10" t="n">
         <v>0.840105</v>
       </c>
-      <c r="O50" t="n">
+      <c r="O50" s="10" t="n">
         <v>0.8248838709677419</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.8235936170212766</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="11">
@@ -2420,8 +2558,11 @@
       <c r="N51" s="10" t="n">
         <v>0.7060705882352941</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O51" s="10" t="n">
         <v>0.7423947368421053</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.8411274193548387</v>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1" s="11">
@@ -2458,8 +2599,11 @@
       <c r="N52" s="10" t="n">
         <v>0.7423461538461539</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O52" s="10" t="n">
         <v>0.7411925</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.829236231884058</v>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1" s="11">
@@ -2496,8 +2640,11 @@
       <c r="N53" s="10" t="n">
         <v>0.8302133333333334</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O53" s="10" t="n">
         <v>0.76683</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.828318181818182</v>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="11">
@@ -2534,8 +2681,11 @@
       <c r="N54" s="10" t="n">
         <v>0.7507957446808512</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O54" s="10" t="n">
         <v>0.8015062500000001</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.7923960784313725</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1" s="11">
@@ -2572,8 +2722,11 @@
       <c r="N55" s="10" t="n">
         <v>0.8164939393939393</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O55" s="10" t="n">
         <v>0.8676695652173912</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.7454235294117648</v>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1" s="11">
@@ -2610,8 +2763,11 @@
       <c r="N56" s="10" t="n">
         <v>0.8507481481481481</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O56" s="10" t="n">
         <v>0.8515625</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.7452173076923077</v>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1" s="11">
@@ -2648,8 +2804,11 @@
       <c r="N57" s="10" t="n">
         <v>0.8110064516129033</v>
       </c>
-      <c r="O57" t="n">
+      <c r="O57" s="10" t="n">
         <v>0.8353740740740742</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.8157472222222224</v>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1" s="11">
@@ -2686,8 +2845,11 @@
       <c r="N58" s="10" t="n">
         <v>0.7516735294117647</v>
       </c>
-      <c r="O58" t="n">
+      <c r="O58" s="10" t="n">
         <v>0.8190999999999999</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.8774123076923076</v>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1" s="11">
@@ -2724,8 +2886,11 @@
       <c r="N59" s="10" t="n">
         <v>0.7675923076923077</v>
       </c>
-      <c r="O59" t="n">
+      <c r="O59" s="10" t="n">
         <v>0.8521428571428572</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.7787633333333335</v>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1" s="11">
@@ -2762,8 +2927,11 @@
       <c r="N60" s="10" t="n">
         <v>0.7682129032258065</v>
       </c>
-      <c r="O60" t="n">
+      <c r="O60" s="10" t="n">
         <v>0.8195052631578947</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.8054249999999999</v>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1" s="11">
@@ -2800,8 +2968,11 @@
       <c r="N61" s="10" t="n">
         <v>0.6901315789473684</v>
       </c>
-      <c r="O61" t="n">
+      <c r="O61" s="10" t="n">
         <v>0.8021882352941176</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.7335270833333333</v>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1" s="11">
@@ -2838,8 +3009,11 @@
       <c r="N62" s="10" t="n">
         <v>0.7398857142857143</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O62" s="10" t="n">
         <v>0.8121833333333333</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.8155257142857144</v>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1" s="11">
@@ -2876,8 +3050,11 @@
       <c r="N63" s="10" t="n">
         <v>0.6727555555555556</v>
       </c>
-      <c r="O63" t="n">
+      <c r="O63" s="10" t="n">
         <v>0.8327522727272728</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.8670568627450981</v>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1" s="11">
@@ -2914,8 +3091,11 @@
       <c r="N64" s="10" t="n">
         <v>0.83423125</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O64" s="10" t="n">
         <v>0.8472206896551724</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.825203125</v>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1" s="11">
@@ -2952,8 +3132,11 @@
       <c r="N65" s="10" t="n">
         <v>0.7577433333333334</v>
       </c>
-      <c r="O65" t="n">
+      <c r="O65" s="10" t="n">
         <v>0.877721212121212</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.871386956521739</v>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1" s="11">
@@ -2990,8 +3173,11 @@
       <c r="N66" s="10" t="n">
         <v>0.7123186046511628</v>
       </c>
-      <c r="O66" t="n">
+      <c r="O66" s="10" t="n">
         <v>0.8271577777777778</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.802637037037037</v>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1" s="11">
@@ -3028,8 +3214,11 @@
       <c r="N67" s="10" t="n">
         <v>0.681888888888889</v>
       </c>
-      <c r="O67" t="n">
+      <c r="O67" s="10" t="n">
         <v>0.8950612903225805</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.8435847826086957</v>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1" s="11">
@@ -3066,8 +3255,11 @@
       <c r="N68" s="10" t="n">
         <v>0.8249142857142857</v>
       </c>
-      <c r="O68" t="n">
+      <c r="O68" s="10" t="n">
         <v>0.8208851851851853</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.8590350000000001</v>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1" s="11">
@@ -3104,8 +3296,11 @@
       <c r="N69" s="10" t="n">
         <v>0.7955882352941178</v>
       </c>
-      <c r="O69" t="n">
+      <c r="O69" s="10" t="n">
         <v>0.8241200000000001</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.8759350877192984</v>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1" s="11">
@@ -3142,8 +3337,11 @@
       <c r="N70" s="10" t="n">
         <v>0.788678</v>
       </c>
-      <c r="O70" t="n">
+      <c r="O70" s="10" t="n">
         <v>0.7361799999999999</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.8231616666666668</v>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1" s="11">
@@ -3180,8 +3378,11 @@
       <c r="N71" s="10" t="n">
         <v>0.7767631578947369</v>
       </c>
-      <c r="O71" t="n">
+      <c r="O71" s="10" t="n">
         <v>0.7952465116279069</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.7884809523809524</v>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1" s="11">
@@ -3218,8 +3419,11 @@
       <c r="N72" s="10" t="n">
         <v>0.7267807692307693</v>
       </c>
-      <c r="O72" t="n">
+      <c r="O72" s="10" t="n">
         <v>0.8150404761904761</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.8661859999999999</v>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1" s="11">
@@ -3256,8 +3460,11 @@
       <c r="N73" s="10" t="n">
         <v>0.8130521739130434</v>
       </c>
-      <c r="O73" t="n">
+      <c r="O73" s="10" t="n">
         <v>0.8184999999999999</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.823008620689655</v>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1" s="11">
@@ -3294,8 +3501,11 @@
       <c r="N74" s="10" t="n">
         <v>0.8167785714285715</v>
       </c>
-      <c r="O74" t="n">
+      <c r="O74" s="10" t="n">
         <v>0.7927041666666668</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.8082636363636365</v>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1" s="11">
@@ -3332,8 +3542,11 @@
       <c r="N75" s="10" t="n">
         <v>0.80575</v>
       </c>
-      <c r="O75" t="n">
+      <c r="O75" s="10" t="n">
         <v>0.8676108108108107</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.7854543859649122</v>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1" s="11">
@@ -3370,8 +3583,11 @@
       <c r="N76" s="10" t="n">
         <v>0.8016190476190476</v>
       </c>
-      <c r="O76" t="n">
+      <c r="O76" s="10" t="n">
         <v>0.8355978260869565</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.8904769230769232</v>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1" s="11">
@@ -3408,8 +3624,11 @@
       <c r="N77" s="10" t="n">
         <v>0.779913043478261</v>
       </c>
-      <c r="O77" t="n">
+      <c r="O77" s="10" t="n">
         <v>0.8077564102564103</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.8339460000000001</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1" s="11">
@@ -3446,8 +3665,11 @@
       <c r="N78" s="10" t="n">
         <v>0.8567357142857145</v>
       </c>
-      <c r="O78" t="n">
+      <c r="O78" s="10" t="n">
         <v>0.7781379310344827</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.8598074074074076</v>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1" s="11">
@@ -3484,8 +3706,11 @@
       <c r="N79" s="10" t="n">
         <v>0.7588764705882354</v>
       </c>
-      <c r="O79" t="n">
+      <c r="O79" s="10" t="n">
         <v>0.7934813953488372</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.8219124999999999</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1" s="11">
@@ -3522,8 +3747,11 @@
       <c r="N80" s="10" t="n">
         <v>0.7777281250000001</v>
       </c>
-      <c r="O80" t="n">
+      <c r="O80" s="10" t="n">
         <v>0.7933666666666666</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.7906830508474575</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1" s="11">
@@ -3560,8 +3788,11 @@
       <c r="N81" s="10" t="n">
         <v>0.7613750000000001</v>
       </c>
-      <c r="O81" t="n">
+      <c r="O81" s="10" t="n">
         <v>0.8372115384615385</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.8215666666666667</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1" s="11">
@@ -3598,8 +3829,11 @@
       <c r="N82" s="10" t="n">
         <v>0.838671875</v>
       </c>
-      <c r="O82" t="n">
+      <c r="O82" s="10" t="n">
         <v>0.7177749999999999</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.8959931818181819</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1" s="11">
@@ -3636,8 +3870,11 @@
       <c r="N83" s="10" t="n">
         <v>0.792909375</v>
       </c>
-      <c r="O83" t="n">
+      <c r="O83" s="10" t="n">
         <v>0.8539733333333331</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.8801450000000001</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1" s="11">
@@ -3674,8 +3911,11 @@
       <c r="N84" s="10" t="n">
         <v>0.7617243243243242</v>
       </c>
-      <c r="O84" t="n">
+      <c r="O84" s="10" t="n">
         <v>0.7717875</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.8693808510638298</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1" s="11">
@@ -3712,8 +3952,11 @@
       <c r="N85" s="10" t="n">
         <v>0.7913162162162163</v>
       </c>
-      <c r="O85" t="n">
+      <c r="O85" s="10" t="n">
         <v>0.7740973684210527</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.7518274509803922</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1" s="11">
@@ -3750,8 +3993,11 @@
       <c r="N86" s="10" t="n">
         <v>0.8398325581395351</v>
       </c>
-      <c r="O86" t="n">
+      <c r="O86" s="10" t="n">
         <v>0.7998414634146341</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.8782517241379312</v>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1" s="11">
@@ -3788,8 +4034,11 @@
       <c r="N87" s="10" t="n">
         <v>0.774444</v>
       </c>
-      <c r="O87" t="n">
+      <c r="O87" s="10" t="n">
         <v>0.8547483870967741</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.8327225806451614</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1" s="11">
@@ -3826,8 +4075,11 @@
       <c r="N88" s="10" t="n">
         <v>0.7538024390243903</v>
       </c>
-      <c r="O88" t="n">
+      <c r="O88" s="10" t="n">
         <v>0.8368510638297872</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.822353125</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1" s="11">
@@ -3864,8 +4116,11 @@
       <c r="N89" s="10" t="n">
         <v>0.7902307692307692</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O89" s="10" t="n">
         <v>0.8002222222222222</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.7828509433962265</v>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1" s="11">
@@ -3902,8 +4157,11 @@
       <c r="N90" s="10" t="n">
         <v>0.7373966666666667</v>
       </c>
-      <c r="O90" t="n">
+      <c r="O90" s="10" t="n">
         <v>0.9067611111111111</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.8139633333333334</v>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1" s="11">
@@ -3940,8 +4198,11 @@
       <c r="N91" s="10" t="n">
         <v>0.7704999999999999</v>
       </c>
-      <c r="O91" t="n">
+      <c r="O91" s="10" t="n">
         <v>0.801996153846154</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.7494227272727273</v>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1" s="11">
@@ -3978,8 +4239,11 @@
       <c r="N92" s="10" t="n">
         <v>0.8550957446808509</v>
       </c>
-      <c r="O92" t="n">
+      <c r="O92" s="10" t="n">
         <v>0.8734612903225807</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.7614102564102564</v>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1" s="11">
@@ -4016,8 +4280,11 @@
       <c r="N93" s="10" t="n">
         <v>0.8248238095238095</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O93" s="10" t="n">
         <v>0.8890142857142856</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.8496822580645162</v>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1" s="11">
@@ -4054,8 +4321,11 @@
       <c r="N94" s="10" t="n">
         <v>0.8461375</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O94" s="10" t="n">
         <v>0.8057421052631579</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.8329784615384616</v>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1" s="11">
@@ -4092,8 +4362,11 @@
       <c r="N95" s="10" t="n">
         <v>0.7295190476190476</v>
       </c>
-      <c r="O95" t="n">
+      <c r="O95" s="10" t="n">
         <v>0.7664151515151515</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.7783044444444444</v>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1" s="11">
@@ -4130,8 +4403,11 @@
       <c r="N96" s="10" t="n">
         <v>0.8256032258064515</v>
       </c>
-      <c r="O96" t="n">
+      <c r="O96" s="10" t="n">
         <v>0.8572195121951219</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.8662607142857145</v>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1" s="11">
@@ -4168,8 +4444,11 @@
       <c r="N97" s="10" t="n">
         <v>0.7570315789473684</v>
       </c>
-      <c r="O97" t="n">
+      <c r="O97" s="10" t="n">
         <v>0.8078027777777778</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.8142370967741935</v>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1" s="11">
@@ -4206,8 +4485,11 @@
       <c r="N98" s="10" t="n">
         <v>0.7786372093023257</v>
       </c>
-      <c r="O98" t="n">
+      <c r="O98" s="10" t="n">
         <v>0.8278793103448276</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.8131533333333334</v>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1" s="11">
@@ -4244,8 +4526,11 @@
       <c r="N99" s="10" t="n">
         <v>0.8155652173913043</v>
       </c>
-      <c r="O99" t="n">
+      <c r="O99" s="10" t="n">
         <v>0.8558685714285714</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.8077301587301585</v>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1" s="11">
@@ -4282,8 +4567,11 @@
       <c r="N100" s="10" t="n">
         <v>0.7994022222222222</v>
       </c>
-      <c r="O100" t="n">
+      <c r="O100" s="10" t="n">
         <v>0.7458166666666666</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.8587238095238096</v>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1" s="11">
@@ -4320,8 +4608,11 @@
       <c r="N101" s="10" t="n">
         <v>0.7036</v>
       </c>
-      <c r="O101" t="n">
+      <c r="O101" s="10" t="n">
         <v>0.7962804347826087</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.7944982456140351</v>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1" s="11">
@@ -4358,8 +4649,11 @@
       <c r="N102" s="10" t="n">
         <v>0.7512750000000001</v>
       </c>
-      <c r="O102" t="n">
+      <c r="O102" s="10" t="n">
         <v>0.8597463414634144</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.856493023255814</v>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1" s="11">
@@ -4396,8 +4690,11 @@
       <c r="N103" s="10" t="n">
         <v>0.8170277777777778</v>
       </c>
-      <c r="O103" t="n">
+      <c r="O103" s="10" t="n">
         <v>0.8049322580645162</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.8993225806451614</v>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1" s="11">
@@ -4434,8 +4731,11 @@
       <c r="N104" s="10" t="n">
         <v>0.8098358974358975</v>
       </c>
-      <c r="O104" t="n">
+      <c r="O104" s="10" t="n">
         <v>0.8411076923076923</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.8014220588235292</v>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1" s="11">
@@ -4499,6 +4799,9 @@
       <c r="O108" s="10" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="P108" s="10" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="109" ht="16" customHeight="1" s="11">
       <c r="A109" s="18" t="n">
@@ -4537,6 +4840,9 @@
       <c r="O109" s="10" t="n">
         <v>0.6923076923076923</v>
       </c>
+      <c r="P109" s="10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="110" ht="16" customHeight="1" s="11">
       <c r="A110" s="18" t="n">
@@ -4575,6 +4881,9 @@
       <c r="O110" s="10" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="P110" s="10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="111" ht="16" customHeight="1" s="11">
       <c r="A111" s="18" t="n">
@@ -4613,6 +4922,9 @@
       <c r="O111" s="10" t="n">
         <v>0.9</v>
       </c>
+      <c r="P111" s="10" t="n">
+        <v>0.5333333333333333</v>
+      </c>
     </row>
     <row r="112" ht="16" customHeight="1" s="11">
       <c r="A112" s="18" t="n">
@@ -4651,6 +4963,9 @@
       <c r="O112" s="10" t="n">
         <v>0.8461538461538461</v>
       </c>
+      <c r="P112" s="10" t="n">
+        <v>0.9333333333333333</v>
+      </c>
     </row>
     <row r="113" ht="16" customHeight="1" s="11">
       <c r="A113" s="18" t="n">
@@ -4689,6 +5004,9 @@
       <c r="O113" s="10" t="n">
         <v>0.9</v>
       </c>
+      <c r="P113" s="10" t="n">
+        <v>0.7333333333333333</v>
+      </c>
     </row>
     <row r="114" ht="16" customHeight="1" s="11">
       <c r="A114" s="18" t="n">
@@ -4727,6 +5045,9 @@
       <c r="O114" s="10" t="n">
         <v>0.75</v>
       </c>
+      <c r="P114" s="10" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="115" ht="16" customHeight="1" s="11">
       <c r="A115" s="18" t="n">
@@ -4765,6 +5086,9 @@
       <c r="O115" s="10" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="P115" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116" ht="16" customHeight="1" s="11">
       <c r="A116" s="18" t="n">
@@ -4803,6 +5127,9 @@
       <c r="O116" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="P116" s="10" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="117" ht="16" customHeight="1" s="11">
       <c r="A117" s="18" t="n">
@@ -4841,6 +5168,9 @@
       <c r="O117" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="P117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118" ht="16" customHeight="1" s="11">
       <c r="A118" s="18" t="n">
@@ -4879,6 +5209,9 @@
       <c r="O118" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119" ht="16" customHeight="1" s="11">
       <c r="A119" s="18" t="n">
@@ -4917,6 +5250,9 @@
       <c r="O119" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="P119" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="120" ht="16" customHeight="1" s="11">
       <c r="A120" s="18" t="n">
@@ -4952,8 +5288,11 @@
       <c r="N120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O120" t="n">
-        <v>1</v>
+      <c r="O120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1" s="11">
@@ -4990,8 +5329,11 @@
       <c r="N121" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O121" t="n">
-        <v>1</v>
+      <c r="O121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1" s="11">
@@ -5028,8 +5370,11 @@
       <c r="N122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O122" t="n">
-        <v>1</v>
+      <c r="O122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="123" ht="16" customHeight="1" s="11">
@@ -5066,8 +5411,11 @@
       <c r="N123" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O123" t="n">
-        <v>1</v>
+      <c r="O123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="124" ht="16" customHeight="1" s="11">
@@ -5104,8 +5452,11 @@
       <c r="N124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O124" t="n">
-        <v>1</v>
+      <c r="O124" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="125" ht="16" customHeight="1" s="11">
@@ -5142,7 +5493,10 @@
       <c r="N125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O125" t="n">
+      <c r="O125" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5180,7 +5534,10 @@
       <c r="N126" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O126" t="n">
+      <c r="O126" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5218,7 +5575,10 @@
       <c r="N127" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O127" t="n">
+      <c r="O127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5256,8 +5616,11 @@
       <c r="N128" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O128" t="n">
-        <v>1</v>
+      <c r="O128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="129" ht="16" customHeight="1" s="11">
@@ -5294,7 +5657,10 @@
       <c r="N129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O129" t="n">
+      <c r="O129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5332,7 +5698,10 @@
       <c r="N130" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O130" t="n">
+      <c r="O130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5370,7 +5739,10 @@
       <c r="N131" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O131" t="n">
+      <c r="O131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5408,7 +5780,10 @@
       <c r="N132" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="O132" t="n">
+      <c r="O132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5446,7 +5821,10 @@
       <c r="N133" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O133" t="n">
+      <c r="O133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5484,7 +5862,10 @@
       <c r="N134" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O134" t="n">
+      <c r="O134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5522,7 +5903,10 @@
       <c r="N135" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O135" t="n">
+      <c r="O135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5560,7 +5944,10 @@
       <c r="N136" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O136" t="n">
+      <c r="O136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P136" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5598,7 +5985,10 @@
       <c r="N137" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O137" t="n">
+      <c r="O137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P137" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5636,7 +6026,10 @@
       <c r="N138" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O138" t="n">
+      <c r="O138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5674,7 +6067,10 @@
       <c r="N139" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O139" t="n">
+      <c r="O139" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5712,7 +6108,10 @@
       <c r="N140" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O140" t="n">
+      <c r="O140" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5750,7 +6149,10 @@
       <c r="N141" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O141" t="n">
+      <c r="O141" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5788,7 +6190,10 @@
       <c r="N142" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O142" t="n">
+      <c r="O142" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5826,7 +6231,10 @@
       <c r="N143" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O143" t="n">
+      <c r="O143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P143" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5864,7 +6272,10 @@
       <c r="N144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O144" t="n">
+      <c r="O144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P144" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5902,7 +6313,10 @@
       <c r="N145" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O145" t="n">
+      <c r="O145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P145" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5940,7 +6354,10 @@
       <c r="N146" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O146" t="n">
+      <c r="O146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5978,7 +6395,10 @@
       <c r="N147" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O147" t="n">
+      <c r="O147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6016,7 +6436,10 @@
       <c r="N148" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O148" t="n">
+      <c r="O148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P148" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6054,7 +6477,10 @@
       <c r="N149" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O149" t="n">
+      <c r="O149" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P149" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6092,7 +6518,10 @@
       <c r="N150" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O150" t="n">
+      <c r="O150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P150" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6130,7 +6559,10 @@
       <c r="N151" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O151" t="n">
+      <c r="O151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P151" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6168,7 +6600,10 @@
       <c r="N152" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O152" t="n">
+      <c r="O152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P152" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6206,7 +6641,10 @@
       <c r="N153" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O153" t="n">
+      <c r="O153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P153" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6244,7 +6682,10 @@
       <c r="N154" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O154" t="n">
+      <c r="O154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P154" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6282,7 +6723,10 @@
       <c r="N155" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O155" t="n">
+      <c r="O155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P155" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6320,7 +6764,10 @@
       <c r="N156" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O156" t="n">
+      <c r="O156" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P156" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6358,7 +6805,10 @@
       <c r="N157" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O157" t="n">
+      <c r="O157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P157" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6396,7 +6846,10 @@
       <c r="N158" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O158" t="n">
+      <c r="O158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P158" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6434,7 +6887,10 @@
       <c r="N159" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O159" t="n">
+      <c r="O159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P159" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6472,7 +6928,10 @@
       <c r="N160" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O160" t="n">
+      <c r="O160" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P160" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6510,7 +6969,10 @@
       <c r="N161" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O161" t="n">
+      <c r="O161" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P161" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6548,7 +7010,10 @@
       <c r="N162" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O162" t="n">
+      <c r="O162" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P162" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6586,7 +7051,10 @@
       <c r="N163" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O163" t="n">
+      <c r="O163" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P163" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6624,7 +7092,10 @@
       <c r="N164" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O164" t="n">
+      <c r="O164" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P164" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6662,7 +7133,10 @@
       <c r="N165" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O165" t="n">
+      <c r="O165" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P165" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6700,7 +7174,10 @@
       <c r="N166" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O166" t="n">
+      <c r="O166" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P166" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6738,7 +7215,10 @@
       <c r="N167" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O167" t="n">
+      <c r="O167" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P167" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6776,7 +7256,10 @@
       <c r="N168" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O168" t="n">
+      <c r="O168" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P168" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6814,7 +7297,10 @@
       <c r="N169" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O169" t="n">
+      <c r="O169" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P169" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6852,7 +7338,10 @@
       <c r="N170" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O170" t="n">
+      <c r="O170" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P170" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6890,7 +7379,10 @@
       <c r="N171" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O171" t="n">
+      <c r="O171" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P171" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6928,7 +7420,10 @@
       <c r="N172" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O172" t="n">
+      <c r="O172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P172" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6966,7 +7461,10 @@
       <c r="N173" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O173" t="n">
+      <c r="O173" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P173" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7004,7 +7502,10 @@
       <c r="N174" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O174" t="n">
+      <c r="O174" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P174" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7042,7 +7543,10 @@
       <c r="N175" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O175" t="n">
+      <c r="O175" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P175" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7080,7 +7584,10 @@
       <c r="N176" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O176" t="n">
+      <c r="O176" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P176" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7118,7 +7625,10 @@
       <c r="N177" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O177" t="n">
+      <c r="O177" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P177" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7156,7 +7666,10 @@
       <c r="N178" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O178" t="n">
+      <c r="O178" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P178" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7194,7 +7707,10 @@
       <c r="N179" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O179" t="n">
+      <c r="O179" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P179" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7232,7 +7748,10 @@
       <c r="N180" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O180" t="n">
+      <c r="O180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P180" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7270,7 +7789,10 @@
       <c r="N181" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O181" t="n">
+      <c r="O181" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P181" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7308,7 +7830,10 @@
       <c r="N182" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O182" t="n">
+      <c r="O182" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P182" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7346,7 +7871,10 @@
       <c r="N183" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O183" t="n">
+      <c r="O183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P183" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7384,7 +7912,10 @@
       <c r="N184" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O184" t="n">
+      <c r="O184" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P184" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7422,7 +7953,10 @@
       <c r="N185" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O185" t="n">
+      <c r="O185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P185" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7460,7 +7994,10 @@
       <c r="N186" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O186" t="n">
+      <c r="O186" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P186" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7498,7 +8035,10 @@
       <c r="N187" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O187" t="n">
+      <c r="O187" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P187" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7536,7 +8076,10 @@
       <c r="N188" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O188" t="n">
+      <c r="O188" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P188" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7574,7 +8117,10 @@
       <c r="N189" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O189" t="n">
+      <c r="O189" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P189" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7612,7 +8158,10 @@
       <c r="N190" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O190" t="n">
+      <c r="O190" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P190" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7650,7 +8199,10 @@
       <c r="N191" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O191" t="n">
+      <c r="O191" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P191" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7688,7 +8240,10 @@
       <c r="N192" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O192" t="n">
+      <c r="O192" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P192" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7726,7 +8281,10 @@
       <c r="N193" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O193" t="n">
+      <c r="O193" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P193" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7764,7 +8322,10 @@
       <c r="N194" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O194" t="n">
+      <c r="O194" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P194" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7802,7 +8363,10 @@
       <c r="N195" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O195" t="n">
+      <c r="O195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P195" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7840,7 +8404,10 @@
       <c r="N196" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O196" t="n">
+      <c r="O196" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P196" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7878,7 +8445,10 @@
       <c r="N197" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O197" t="n">
+      <c r="O197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P197" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7916,7 +8486,10 @@
       <c r="N198" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O198" t="n">
+      <c r="O198" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P198" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7954,7 +8527,10 @@
       <c r="N199" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O199" t="n">
+      <c r="O199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P199" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7992,7 +8568,10 @@
       <c r="N200" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O200" t="n">
+      <c r="O200" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P200" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8030,7 +8609,10 @@
       <c r="N201" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O201" t="n">
+      <c r="O201" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P201" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8068,7 +8650,10 @@
       <c r="N202" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O202" t="n">
+      <c r="O202" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P202" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8106,7 +8691,10 @@
       <c r="N203" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O203" t="n">
+      <c r="O203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P203" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8144,7 +8732,10 @@
       <c r="N204" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O204" t="n">
+      <c r="O204" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P204" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8182,7 +8773,10 @@
       <c r="N205" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O205" t="n">
+      <c r="O205" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P205" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8220,7 +8814,10 @@
       <c r="N206" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O206" t="n">
+      <c r="O206" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P206" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8258,7 +8855,10 @@
       <c r="N207" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O207" t="n">
+      <c r="O207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8323,6 +8923,9 @@
       <c r="O212" s="10" t="n">
         <v>0.9887</v>
       </c>
+      <c r="P212" s="10" t="n">
+        <v>0.9616666666666668</v>
+      </c>
     </row>
     <row r="213" ht="16" customHeight="1" s="11">
       <c r="A213" s="18" t="n">
@@ -8361,6 +8964,9 @@
       <c r="O213" s="10" t="n">
         <v>0.8561399999999999</v>
       </c>
+      <c r="P213" s="10" t="n">
+        <v>0.9585999999999999</v>
+      </c>
     </row>
     <row r="214" ht="16" customHeight="1" s="11">
       <c r="A214" s="18" t="n">
@@ -8399,6 +9005,9 @@
       <c r="O214" s="10" t="n">
         <v>0.572775</v>
       </c>
+      <c r="P214" s="10" t="n">
+        <v>0.9546</v>
+      </c>
     </row>
     <row r="215" ht="16" customHeight="1" s="11">
       <c r="A215" s="18" t="n">
@@ -8437,6 +9046,9 @@
       <c r="O215" s="10" t="n">
         <v>0.7227857142857143</v>
       </c>
+      <c r="P215" s="10" t="n">
+        <v>0.9296</v>
+      </c>
     </row>
     <row r="216" ht="16" customHeight="1" s="11">
       <c r="A216" s="18" t="n">
@@ -8475,6 +9087,9 @@
       <c r="O216" s="10" t="n">
         <v>0.714475</v>
       </c>
+      <c r="P216" s="10" t="n">
+        <v>0.93</v>
+      </c>
     </row>
     <row r="217" ht="16" customHeight="1" s="11">
       <c r="A217" s="18" t="n">
@@ -8513,6 +9128,9 @@
       <c r="O217" s="10" t="n">
         <v>0.6282</v>
       </c>
+      <c r="P217" s="10" t="n">
+        <v>0.9439333333333333</v>
+      </c>
     </row>
     <row r="218" ht="16" customHeight="1" s="11">
       <c r="A218" s="18" t="n">
@@ -8551,6 +9169,9 @@
       <c r="O218" s="10" t="n">
         <v>0.5764777777777778</v>
       </c>
+      <c r="P218" s="10" t="n">
+        <v>0.9519</v>
+      </c>
     </row>
     <row r="219" ht="16" customHeight="1" s="11">
       <c r="A219" s="18" t="n">
@@ -8589,6 +9210,9 @@
       <c r="O219" s="10" t="n">
         <v>0.6116999999999999</v>
       </c>
+      <c r="P219" s="10" t="n">
+        <v>0.4595666666666667</v>
+      </c>
     </row>
     <row r="220" ht="16" customHeight="1" s="11">
       <c r="A220" s="18" t="n">
@@ -8627,6 +9251,9 @@
       <c r="O220" s="10" t="n">
         <v>0.522790909090909</v>
       </c>
+      <c r="P220" s="10" t="n">
+        <v>0.588</v>
+      </c>
     </row>
     <row r="221" ht="16" customHeight="1" s="11">
       <c r="A221" s="18" t="n">
@@ -8665,6 +9292,9 @@
       <c r="O221" s="10" t="n">
         <v>0.5536300000000001</v>
       </c>
+      <c r="P221" t="n">
+        <v>0.6745428571428571</v>
+      </c>
     </row>
     <row r="222" ht="16" customHeight="1" s="11">
       <c r="A222" s="18" t="n">
@@ -8703,6 +9333,9 @@
       <c r="O222" s="10" t="n">
         <v>0.5041888888888888</v>
       </c>
+      <c r="P222" t="n">
+        <v>0.347725</v>
+      </c>
     </row>
     <row r="223" ht="16" customHeight="1" s="11">
       <c r="A223" s="18" t="n">
@@ -8741,6 +9374,9 @@
       <c r="O223" s="10" t="n">
         <v>0.66301</v>
       </c>
+      <c r="P223" t="n">
+        <v>0.6248199999999999</v>
+      </c>
     </row>
     <row r="224" ht="16" customHeight="1" s="11">
       <c r="A224" s="18" t="n">
@@ -8776,8 +9412,11 @@
       <c r="N224" s="10" t="n">
         <v>0.8044777777777778</v>
       </c>
-      <c r="O224" t="n">
+      <c r="O224" s="10" t="n">
         <v>0.50227</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0.6308875</v>
       </c>
     </row>
     <row r="225" ht="16" customHeight="1" s="11">
@@ -8814,8 +9453,11 @@
       <c r="N225" s="10" t="n">
         <v>0.8150111111111111</v>
       </c>
-      <c r="O225" t="n">
+      <c r="O225" s="10" t="n">
         <v>0.7592125000000001</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0.6324</v>
       </c>
     </row>
     <row r="226" ht="16" customHeight="1" s="11">
@@ -8852,8 +9494,11 @@
       <c r="N226" s="10" t="n">
         <v>0.5669454545454545</v>
       </c>
-      <c r="O226" t="n">
+      <c r="O226" s="10" t="n">
         <v>0.3407999999999999</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0.6020666666666666</v>
       </c>
     </row>
     <row r="227" ht="16" customHeight="1" s="11">
@@ -8890,8 +9535,11 @@
       <c r="N227" s="10" t="n">
         <v>0.66072</v>
       </c>
-      <c r="O227" t="n">
+      <c r="O227" s="10" t="n">
         <v>0.390625</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0.7043200000000001</v>
       </c>
     </row>
     <row r="228" ht="16" customHeight="1" s="11">
@@ -8928,8 +9576,11 @@
       <c r="N228" s="10" t="n">
         <v>0.6590916666666666</v>
       </c>
-      <c r="O228" t="n">
+      <c r="O228" s="10" t="n">
         <v>0.5567857142857143</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0.5544</v>
       </c>
     </row>
     <row r="229" ht="16" customHeight="1" s="11">
@@ -8966,8 +9617,11 @@
       <c r="N229" s="10" t="n">
         <v>0.7596999999999999</v>
       </c>
-      <c r="O229" t="n">
+      <c r="O229" s="10" t="n">
         <v>0.7359250000000001</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0.6156666666666666</v>
       </c>
     </row>
     <row r="230" ht="16" customHeight="1" s="11">
@@ -9004,8 +9658,11 @@
       <c r="N230" s="10" t="n">
         <v>0.6077499999999999</v>
       </c>
-      <c r="O230" t="n">
+      <c r="O230" s="10" t="n">
         <v>0.6124624999999999</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0.4762142857142857</v>
       </c>
     </row>
     <row r="231" ht="16" customHeight="1" s="11">
@@ -9042,8 +9699,11 @@
       <c r="N231" s="10" t="n">
         <v>0.7041000000000001</v>
       </c>
-      <c r="O231" t="n">
+      <c r="O231" s="10" t="n">
         <v>0.4303</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0.5985833333333334</v>
       </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="11">
@@ -9080,8 +9740,11 @@
       <c r="N232" s="10" t="n">
         <v>0.7224444444444443</v>
       </c>
-      <c r="O232" t="n">
+      <c r="O232" s="10" t="n">
         <v>0.4421727272727273</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0.4775833333333333</v>
       </c>
     </row>
     <row r="233" ht="16" customHeight="1" s="11">
@@ -9118,8 +9781,11 @@
       <c r="N233" s="10" t="n">
         <v>0.77475</v>
       </c>
-      <c r="O233" t="n">
+      <c r="O233" s="10" t="n">
         <v>0.70084</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0.41359</v>
       </c>
     </row>
     <row r="234" ht="16" customHeight="1" s="11">
@@ -9156,8 +9822,11 @@
       <c r="N234" s="10" t="n">
         <v>0.7979375</v>
       </c>
-      <c r="O234" t="n">
+      <c r="O234" s="10" t="n">
         <v>0.6185444444444443</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0.5590888888888889</v>
       </c>
     </row>
     <row r="235" ht="16" customHeight="1" s="11">
@@ -9194,8 +9863,11 @@
       <c r="N235" s="10" t="n">
         <v>0.7042444444444445</v>
       </c>
-      <c r="O235" t="n">
+      <c r="O235" s="10" t="n">
         <v>0.4373428571428571</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0.41585</v>
       </c>
     </row>
     <row r="236" ht="16" customHeight="1" s="11">
@@ -9232,8 +9904,11 @@
       <c r="N236" s="10" t="n">
         <v>0.6681818181818181</v>
       </c>
-      <c r="O236" t="n">
+      <c r="O236" s="10" t="n">
         <v>0.5215000000000001</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0.391375</v>
       </c>
     </row>
     <row r="237" ht="16" customHeight="1" s="11">
@@ -9270,8 +9945,11 @@
       <c r="N237" s="10" t="n">
         <v>0.74951</v>
       </c>
-      <c r="O237" t="n">
+      <c r="O237" s="10" t="n">
         <v>0.5088374999999999</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0.4048333333333333</v>
       </c>
     </row>
     <row r="238" ht="16" customHeight="1" s="11">
@@ -9308,8 +9986,11 @@
       <c r="N238" s="10" t="n">
         <v>0.7732</v>
       </c>
-      <c r="O238" t="n">
+      <c r="O238" s="10" t="n">
         <v>0.4101555555555556</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0.4722818181818182</v>
       </c>
     </row>
     <row r="239" ht="16" customHeight="1" s="11">
@@ -9346,8 +10027,11 @@
       <c r="N239" s="10" t="n">
         <v>0.66165</v>
       </c>
-      <c r="O239" t="n">
+      <c r="O239" s="10" t="n">
         <v>0.5927100000000001</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0.4226090909090909</v>
       </c>
     </row>
     <row r="240" ht="16" customHeight="1" s="11">
@@ -9384,8 +10068,11 @@
       <c r="N240" s="10" t="n">
         <v>0.6185555555555556</v>
       </c>
-      <c r="O240" t="n">
+      <c r="O240" s="10" t="n">
         <v>0.5346249999999999</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0.3178</v>
       </c>
     </row>
     <row r="241" ht="16" customHeight="1" s="11">
@@ -9422,8 +10109,11 @@
       <c r="N241" s="10" t="n">
         <v>0.9008199999999998</v>
       </c>
-      <c r="O241" t="n">
+      <c r="O241" s="10" t="n">
         <v>0.5625777777777778</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0.6666000000000001</v>
       </c>
     </row>
     <row r="242" ht="16" customHeight="1" s="11">
@@ -9460,8 +10150,11 @@
       <c r="N242" s="10" t="n">
         <v>0.549875</v>
       </c>
-      <c r="O242" t="n">
+      <c r="O242" s="10" t="n">
         <v>0.7341499999999999</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0.5260714285714286</v>
       </c>
     </row>
     <row r="243" ht="16" customHeight="1" s="11">
@@ -9498,8 +10191,11 @@
       <c r="N243" s="10" t="n">
         <v>0.7113833333333331</v>
       </c>
-      <c r="O243" t="n">
+      <c r="O243" s="10" t="n">
         <v>0.4191444444444444</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0.7247571428571428</v>
       </c>
     </row>
     <row r="244" ht="16" customHeight="1" s="11">
@@ -9536,8 +10232,11 @@
       <c r="N244" s="10" t="n">
         <v>0.6219333333333333</v>
       </c>
-      <c r="O244" t="n">
+      <c r="O244" s="10" t="n">
         <v>0.5688500000000001</v>
+      </c>
+      <c r="P244" t="n">
+        <v>0.5217714285714286</v>
       </c>
     </row>
     <row r="245" ht="16" customHeight="1" s="11">
@@ -9574,8 +10273,11 @@
       <c r="N245" s="10" t="n">
         <v>0.63115</v>
       </c>
-      <c r="O245" t="n">
+      <c r="O245" s="10" t="n">
         <v>0.5880875</v>
+      </c>
+      <c r="P245" t="n">
+        <v>0.704157142857143</v>
       </c>
     </row>
     <row r="246" ht="16" customHeight="1" s="11">
@@ -9612,8 +10314,11 @@
       <c r="N246" s="10" t="n">
         <v>0.50536</v>
       </c>
-      <c r="O246" t="n">
+      <c r="O246" s="10" t="n">
         <v>0.3421272727272728</v>
+      </c>
+      <c r="P246" t="n">
+        <v>0.350975</v>
       </c>
     </row>
     <row r="247" ht="16" customHeight="1" s="11">
@@ -9650,8 +10355,11 @@
       <c r="N247" s="10" t="n">
         <v>0.5980692307692308</v>
       </c>
-      <c r="O247" t="n">
+      <c r="O247" s="10" t="n">
         <v>0.598675</v>
+      </c>
+      <c r="P247" t="n">
+        <v>0.5421333333333334</v>
       </c>
     </row>
     <row r="248" ht="16" customHeight="1" s="11">
@@ -9688,8 +10396,11 @@
       <c r="N248" s="10" t="n">
         <v>0.6073428571428572</v>
       </c>
-      <c r="O248" t="n">
+      <c r="O248" s="10" t="n">
         <v>0.5289777777777778</v>
+      </c>
+      <c r="P248" t="n">
+        <v>0.3823285714285714</v>
       </c>
     </row>
     <row r="249" ht="16" customHeight="1" s="11">
@@ -9726,8 +10437,11 @@
       <c r="N249" s="10" t="n">
         <v>0.7083636363636364</v>
       </c>
-      <c r="O249" t="n">
+      <c r="O249" s="10" t="n">
         <v>0.506275</v>
+      </c>
+      <c r="P249" t="n">
+        <v>0.3710875</v>
       </c>
     </row>
     <row r="250" ht="16" customHeight="1" s="11">
@@ -9764,8 +10478,11 @@
       <c r="N250" s="10" t="n">
         <v>0.725925</v>
       </c>
-      <c r="O250" t="n">
+      <c r="O250" s="10" t="n">
         <v>0.3439800000000001</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0.6193000000000001</v>
       </c>
     </row>
     <row r="251" ht="16" customHeight="1" s="11">
@@ -9802,8 +10519,11 @@
       <c r="N251" s="10" t="n">
         <v>0.6767545454545454</v>
       </c>
-      <c r="O251" t="n">
+      <c r="O251" s="10" t="n">
         <v>0.3728181818181818</v>
+      </c>
+      <c r="P251" t="n">
+        <v>0.4987142857142857</v>
       </c>
     </row>
     <row r="252" ht="16" customHeight="1" s="11">
@@ -9840,8 +10560,11 @@
       <c r="N252" s="10" t="n">
         <v>0.7953600000000001</v>
       </c>
-      <c r="O252" t="n">
+      <c r="O252" s="10" t="n">
         <v>0.4370444444444444</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0.6304875</v>
       </c>
     </row>
     <row r="253" ht="16" customHeight="1" s="11">
@@ -9878,8 +10601,11 @@
       <c r="N253" s="10" t="n">
         <v>0.7009833333333333</v>
       </c>
-      <c r="O253" t="n">
+      <c r="O253" s="10" t="n">
         <v>0.2969333333333333</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0.44525</v>
       </c>
     </row>
     <row r="254" ht="16" customHeight="1" s="11">
@@ -9916,8 +10642,11 @@
       <c r="N254" s="10" t="n">
         <v>0.745990909090909</v>
       </c>
-      <c r="O254" t="n">
+      <c r="O254" s="10" t="n">
         <v>0.53584</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0.47864</v>
       </c>
     </row>
     <row r="255" ht="16" customHeight="1" s="11">
@@ -9954,8 +10683,11 @@
       <c r="N255" s="10" t="n">
         <v>0.7475909090909091</v>
       </c>
-      <c r="O255" t="n">
+      <c r="O255" s="10" t="n">
         <v>0.4010444444444444</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0.5522833333333333</v>
       </c>
     </row>
     <row r="256" ht="16" customHeight="1" s="11">
@@ -9992,8 +10724,11 @@
       <c r="N256" s="10" t="n">
         <v>0.672342857142857</v>
       </c>
-      <c r="O256" t="n">
+      <c r="O256" s="10" t="n">
         <v>0.3849181818181819</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0.466</v>
       </c>
     </row>
     <row r="257" ht="16" customHeight="1" s="11">
@@ -10030,8 +10765,11 @@
       <c r="N257" s="10" t="n">
         <v>0.6914090909090909</v>
       </c>
-      <c r="O257" t="n">
+      <c r="O257" s="10" t="n">
         <v>0.6454666666666666</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0.44885</v>
       </c>
     </row>
     <row r="258" ht="16" customHeight="1" s="11">
@@ -10068,8 +10806,11 @@
       <c r="N258" s="10" t="n">
         <v>0.7792333333333333</v>
       </c>
-      <c r="O258" t="n">
+      <c r="O258" s="10" t="n">
         <v>0.5446875</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0.3034888888888889</v>
       </c>
     </row>
     <row r="259" ht="16" customHeight="1" s="11">
@@ -10106,8 +10847,11 @@
       <c r="N259" s="10" t="n">
         <v>0.5992200000000001</v>
       </c>
-      <c r="O259" t="n">
+      <c r="O259" s="10" t="n">
         <v>0.6154545454545454</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0.32685</v>
       </c>
     </row>
     <row r="260" ht="16" customHeight="1" s="11">
@@ -10144,8 +10888,11 @@
       <c r="N260" s="10" t="n">
         <v>0.6557181818181819</v>
       </c>
-      <c r="O260" t="n">
+      <c r="O260" s="10" t="n">
         <v>0.4440090909090909</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0.384</v>
       </c>
     </row>
     <row r="261" ht="16" customHeight="1" s="11">
@@ -10182,8 +10929,11 @@
       <c r="N261" s="10" t="n">
         <v>0.7368400000000002</v>
       </c>
-      <c r="O261" t="n">
+      <c r="O261" s="10" t="n">
         <v>0.4924899999999999</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0.5474</v>
       </c>
     </row>
     <row r="262" ht="16" customHeight="1" s="11">
@@ -10220,8 +10970,11 @@
       <c r="N262" s="10" t="n">
         <v>0.57424</v>
       </c>
-      <c r="O262" t="n">
+      <c r="O262" s="10" t="n">
         <v>0.5437125</v>
+      </c>
+      <c r="P262" t="n">
+        <v>0.3782888888888889</v>
       </c>
     </row>
     <row r="263" ht="16" customHeight="1" s="11">
@@ -10258,8 +11011,11 @@
       <c r="N263" s="10" t="n">
         <v>0.7599400000000001</v>
       </c>
-      <c r="O263" t="n">
+      <c r="O263" s="10" t="n">
         <v>0.55088</v>
+      </c>
+      <c r="P263" t="n">
+        <v>0.4435333333333333</v>
       </c>
     </row>
     <row r="264" ht="16" customHeight="1" s="11">
@@ -10296,8 +11052,11 @@
       <c r="N264" s="10" t="n">
         <v>0.6841</v>
       </c>
-      <c r="O264" t="n">
+      <c r="O264" s="10" t="n">
         <v>0.4628444444444444</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0.4705142857142857</v>
       </c>
     </row>
     <row r="265" ht="16" customHeight="1" s="11">
@@ -10334,8 +11093,11 @@
       <c r="N265" s="10" t="n">
         <v>0.6193363636363637</v>
       </c>
-      <c r="O265" t="n">
+      <c r="O265" s="10" t="n">
         <v>0.6087</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0.667925</v>
       </c>
     </row>
     <row r="266" ht="16" customHeight="1" s="11">
@@ -10372,8 +11134,11 @@
       <c r="N266" s="10" t="n">
         <v>0.7343499999999999</v>
       </c>
-      <c r="O266" t="n">
+      <c r="O266" s="10" t="n">
         <v>0.5354428571428571</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0.4527249999999999</v>
       </c>
     </row>
     <row r="267" ht="16" customHeight="1" s="11">
@@ -10410,8 +11175,11 @@
       <c r="N267" s="10" t="n">
         <v>0.7803125</v>
       </c>
-      <c r="O267" t="n">
+      <c r="O267" s="10" t="n">
         <v>0.4913444444444444</v>
+      </c>
+      <c r="P267" t="n">
+        <v>0.6414624999999999</v>
       </c>
     </row>
     <row r="268" ht="16" customHeight="1" s="11">
@@ -10448,8 +11216,11 @@
       <c r="N268" s="10" t="n">
         <v>0.6929444444444444</v>
       </c>
-      <c r="O268" t="n">
+      <c r="O268" s="10" t="n">
         <v>0.4629666666666667</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0.4687571428571428</v>
       </c>
     </row>
     <row r="269" ht="16" customHeight="1" s="11">
@@ -10486,8 +11257,11 @@
       <c r="N269" s="10" t="n">
         <v>0.73512</v>
       </c>
-      <c r="O269" t="n">
+      <c r="O269" s="10" t="n">
         <v>0.5498181818181819</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0.53915</v>
       </c>
     </row>
     <row r="270" ht="16" customHeight="1" s="11">
@@ -10524,8 +11298,11 @@
       <c r="N270" s="10" t="n">
         <v>0.7524</v>
       </c>
-      <c r="O270" t="n">
+      <c r="O270" s="10" t="n">
         <v>0.3328923076923077</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0.429675</v>
       </c>
     </row>
     <row r="271" ht="16" customHeight="1" s="11">
@@ -10562,8 +11339,11 @@
       <c r="N271" s="10" t="n">
         <v>0.6547999999999999</v>
       </c>
-      <c r="O271" t="n">
+      <c r="O271" s="10" t="n">
         <v>0.3874285714285715</v>
+      </c>
+      <c r="P271" t="n">
+        <v>0.32685</v>
       </c>
     </row>
     <row r="272" ht="16" customHeight="1" s="11">
@@ -10600,8 +11380,11 @@
       <c r="N272" s="10" t="n">
         <v>0.6574249999999999</v>
       </c>
-      <c r="O272" t="n">
+      <c r="O272" s="10" t="n">
         <v>0.58423</v>
+      </c>
+      <c r="P272" t="n">
+        <v>0.519525</v>
       </c>
     </row>
     <row r="273" ht="16" customHeight="1" s="11">
@@ -10638,8 +11421,11 @@
       <c r="N273" s="10" t="n">
         <v>0.7640777777777779</v>
       </c>
-      <c r="O273" t="n">
+      <c r="O273" s="10" t="n">
         <v>0.44114</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0.6115571428571428</v>
       </c>
     </row>
     <row r="274" ht="16" customHeight="1" s="11">
@@ -10676,8 +11462,11 @@
       <c r="N274" s="10" t="n">
         <v>0.7905099999999999</v>
       </c>
-      <c r="O274" t="n">
+      <c r="O274" s="10" t="n">
         <v>0.5112166666666667</v>
+      </c>
+      <c r="P274" t="n">
+        <v>0.6342428571428572</v>
       </c>
     </row>
     <row r="275" ht="16" customHeight="1" s="11">
@@ -10714,8 +11503,11 @@
       <c r="N275" s="10" t="n">
         <v>0.6994666666666666</v>
       </c>
-      <c r="O275" t="n">
+      <c r="O275" s="10" t="n">
         <v>0.4745444444444444</v>
+      </c>
+      <c r="P275" t="n">
+        <v>0.4938</v>
       </c>
     </row>
     <row r="276" ht="16" customHeight="1" s="11">
@@ -10752,8 +11544,11 @@
       <c r="N276" s="10" t="n">
         <v>0.5936166666666667</v>
       </c>
-      <c r="O276" t="n">
+      <c r="O276" s="10" t="n">
         <v>0.5658625</v>
+      </c>
+      <c r="P276" t="n">
+        <v>0.4204454545454546</v>
       </c>
     </row>
     <row r="277" ht="16" customHeight="1" s="11">
@@ -10790,8 +11585,11 @@
       <c r="N277" s="10" t="n">
         <v>0.7161333333333333</v>
       </c>
-      <c r="O277" t="n">
+      <c r="O277" s="10" t="n">
         <v>0.39552</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0.570188888888889</v>
       </c>
     </row>
     <row r="278" ht="16" customHeight="1" s="11">
@@ -10828,8 +11626,11 @@
       <c r="N278" s="10" t="n">
         <v>0.7859636363636363</v>
       </c>
-      <c r="O278" t="n">
+      <c r="O278" s="10" t="n">
         <v>0.526275</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0.4854166666666666</v>
       </c>
     </row>
     <row r="279" ht="16" customHeight="1" s="11">
@@ -10866,8 +11667,11 @@
       <c r="N279" s="10" t="n">
         <v>0.6587833333333333</v>
       </c>
-      <c r="O279" t="n">
+      <c r="O279" s="10" t="n">
         <v>0.4762428571428572</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0.3961</v>
       </c>
     </row>
     <row r="280" ht="16" customHeight="1" s="11">
@@ -10904,8 +11708,11 @@
       <c r="N280" s="10" t="n">
         <v>0.6964666666666667</v>
       </c>
-      <c r="O280" t="n">
+      <c r="O280" s="10" t="n">
         <v>0.6118444444444443</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0.324775</v>
       </c>
     </row>
     <row r="281" ht="16" customHeight="1" s="11">
@@ -10942,8 +11749,11 @@
       <c r="N281" s="10" t="n">
         <v>0.6656000000000001</v>
       </c>
-      <c r="O281" t="n">
+      <c r="O281" s="10" t="n">
         <v>0.506225</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0.5243375</v>
       </c>
     </row>
     <row r="282" ht="16" customHeight="1" s="11">
@@ -10980,8 +11790,11 @@
       <c r="N282" s="10" t="n">
         <v>0.7348636363636364</v>
       </c>
-      <c r="O282" t="n">
+      <c r="O282" s="10" t="n">
         <v>0.52346</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0.5305333333333334</v>
       </c>
     </row>
     <row r="283" ht="16" customHeight="1" s="11">
@@ -11018,8 +11831,11 @@
       <c r="N283" s="10" t="n">
         <v>0.8373299999999999</v>
       </c>
-      <c r="O283" t="n">
+      <c r="O283" s="10" t="n">
         <v>0.4927444444444445</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0.4491875</v>
       </c>
     </row>
     <row r="284" ht="16" customHeight="1" s="11">
@@ -11056,8 +11872,11 @@
       <c r="N284" s="10" t="n">
         <v>0.6446444444444445</v>
       </c>
-      <c r="O284" t="n">
+      <c r="O284" s="10" t="n">
         <v>0.5898</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0.3994222222222222</v>
       </c>
     </row>
     <row r="285" ht="16" customHeight="1" s="11">
@@ -11094,8 +11913,11 @@
       <c r="N285" s="10" t="n">
         <v>0.6422899999999999</v>
       </c>
-      <c r="O285" t="n">
+      <c r="O285" s="10" t="n">
         <v>0.58948</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0.3662875</v>
       </c>
     </row>
     <row r="286" ht="16" customHeight="1" s="11">
@@ -11132,8 +11954,11 @@
       <c r="N286" s="10" t="n">
         <v>0.52607</v>
       </c>
-      <c r="O286" t="n">
+      <c r="O286" s="10" t="n">
         <v>0.34166</v>
+      </c>
+      <c r="P286" t="n">
+        <v>0.4001</v>
       </c>
     </row>
     <row r="287" ht="16" customHeight="1" s="11">
@@ -11170,8 +11995,11 @@
       <c r="N287" s="10" t="n">
         <v>0.6165222222222222</v>
       </c>
-      <c r="O287" t="n">
+      <c r="O287" s="10" t="n">
         <v>0.3526666666666666</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0.4036</v>
       </c>
     </row>
     <row r="288" ht="16" customHeight="1" s="11">
@@ -11208,8 +12036,11 @@
       <c r="N288" s="10" t="n">
         <v>0.6945714285714286</v>
       </c>
-      <c r="O288" t="n">
+      <c r="O288" s="10" t="n">
         <v>0.44889</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0.5738857142857144</v>
       </c>
     </row>
     <row r="289" ht="16" customHeight="1" s="11">
@@ -11246,8 +12077,11 @@
       <c r="N289" s="10" t="n">
         <v>0.6649181818181817</v>
       </c>
-      <c r="O289" t="n">
+      <c r="O289" s="10" t="n">
         <v>0.5686272727272728</v>
+      </c>
+      <c r="P289" t="n">
+        <v>0.4988142857142858</v>
       </c>
     </row>
     <row r="290" ht="16" customHeight="1" s="11">
@@ -11284,8 +12118,11 @@
       <c r="N290" s="10" t="n">
         <v>0.70416</v>
       </c>
-      <c r="O290" t="n">
+      <c r="O290" s="10" t="n">
         <v>0.3283777777777778</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0.5148454545454545</v>
       </c>
     </row>
     <row r="291" ht="16" customHeight="1" s="11">
@@ -11322,8 +12159,11 @@
       <c r="N291" s="10" t="n">
         <v>0.6937599999999999</v>
       </c>
-      <c r="O291" t="n">
+      <c r="O291" s="10" t="n">
         <v>0.7632090909090908</v>
+      </c>
+      <c r="P291" t="n">
+        <v>0.5336</v>
       </c>
     </row>
     <row r="292" ht="16" customHeight="1" s="11">
@@ -11360,8 +12200,11 @@
       <c r="N292" s="10" t="n">
         <v>0.80542</v>
       </c>
-      <c r="O292" t="n">
+      <c r="O292" s="10" t="n">
         <v>0.4981666666666667</v>
+      </c>
+      <c r="P292" t="n">
+        <v>0.5538111111111111</v>
       </c>
     </row>
     <row r="293" ht="16" customHeight="1" s="11">
@@ -11398,8 +12241,11 @@
       <c r="N293" s="10" t="n">
         <v>0.5407875</v>
       </c>
-      <c r="O293" t="n">
+      <c r="O293" s="10" t="n">
         <v>0.463388888888889</v>
+      </c>
+      <c r="P293" t="n">
+        <v>0.3777166666666667</v>
       </c>
     </row>
     <row r="294" ht="16" customHeight="1" s="11">
@@ -11436,8 +12282,11 @@
       <c r="N294" s="10" t="n">
         <v>0.85695</v>
       </c>
-      <c r="O294" t="n">
+      <c r="O294" s="10" t="n">
         <v>0.54137</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0.7475333333333333</v>
       </c>
     </row>
     <row r="295" ht="16" customHeight="1" s="11">
@@ -11474,8 +12323,11 @@
       <c r="N295" s="10" t="n">
         <v>0.6269899999999999</v>
       </c>
-      <c r="O295" t="n">
+      <c r="O295" s="10" t="n">
         <v>0.4514444444444445</v>
+      </c>
+      <c r="P295" t="n">
+        <v>0.72482</v>
       </c>
     </row>
     <row r="296" ht="16" customHeight="1" s="11">
@@ -11512,8 +12364,11 @@
       <c r="N296" s="10" t="n">
         <v>0.7906875</v>
       </c>
-      <c r="O296" t="n">
+      <c r="O296" s="10" t="n">
         <v>0.3154888888888889</v>
+      </c>
+      <c r="P296" t="n">
+        <v>0.3156818181818181</v>
       </c>
     </row>
     <row r="297" ht="16" customHeight="1" s="11">
@@ -11550,8 +12405,11 @@
       <c r="N297" s="10" t="n">
         <v>0.72844</v>
       </c>
-      <c r="O297" t="n">
+      <c r="O297" s="10" t="n">
         <v>0.3064125</v>
+      </c>
+      <c r="P297" t="n">
+        <v>0.3331875</v>
       </c>
     </row>
     <row r="298" ht="16" customHeight="1" s="11">
@@ -11588,8 +12446,11 @@
       <c r="N298" s="10" t="n">
         <v>0.7217</v>
       </c>
-      <c r="O298" t="n">
+      <c r="O298" s="10" t="n">
         <v>0.4458625</v>
+      </c>
+      <c r="P298" t="n">
+        <v>0.4858714285714286</v>
       </c>
     </row>
     <row r="299" ht="16" customHeight="1" s="11">
@@ -11626,8 +12487,11 @@
       <c r="N299" s="10" t="n">
         <v>0.5995818181818181</v>
       </c>
-      <c r="O299" t="n">
+      <c r="O299" s="10" t="n">
         <v>0.2909666666666667</v>
+      </c>
+      <c r="P299" t="n">
+        <v>0.2434500000000001</v>
       </c>
     </row>
     <row r="300" ht="16" customHeight="1" s="11">
@@ -11664,8 +12528,11 @@
       <c r="N300" s="10" t="n">
         <v>0.7830777777777778</v>
       </c>
-      <c r="O300" t="n">
+      <c r="O300" s="10" t="n">
         <v>0.5773375000000001</v>
+      </c>
+      <c r="P300" t="n">
+        <v>0.39305</v>
       </c>
     </row>
     <row r="301" ht="16" customHeight="1" s="11">
@@ -11702,8 +12569,11 @@
       <c r="N301" s="10" t="n">
         <v>0.6350461538461538</v>
       </c>
-      <c r="O301" t="n">
+      <c r="O301" s="10" t="n">
         <v>0.52158</v>
+      </c>
+      <c r="P301" t="n">
+        <v>0.5786714285714286</v>
       </c>
     </row>
     <row r="302" ht="16" customHeight="1" s="11">
@@ -11740,8 +12610,11 @@
       <c r="N302" s="10" t="n">
         <v>0.6479199999999999</v>
       </c>
-      <c r="O302" t="n">
+      <c r="O302" s="10" t="n">
         <v>0.7072375000000001</v>
+      </c>
+      <c r="P302" t="n">
+        <v>0.29976</v>
       </c>
     </row>
     <row r="303" ht="16" customHeight="1" s="11">
@@ -11778,8 +12651,11 @@
       <c r="N303" s="10" t="n">
         <v>0.5394666666666668</v>
       </c>
-      <c r="O303" t="n">
+      <c r="O303" s="10" t="n">
         <v>0.4819555555555556</v>
+      </c>
+      <c r="P303" t="n">
+        <v>0.3846888888888889</v>
       </c>
     </row>
     <row r="304" ht="16" customHeight="1" s="11">
@@ -11816,8 +12692,11 @@
       <c r="N304" s="10" t="n">
         <v>0.5691166666666666</v>
       </c>
-      <c r="O304" t="n">
+      <c r="O304" s="10" t="n">
         <v>0.53499</v>
+      </c>
+      <c r="P304" t="n">
+        <v>0.4402333333333333</v>
       </c>
     </row>
     <row r="305" ht="16" customHeight="1" s="11">
@@ -11854,8 +12733,11 @@
       <c r="N305" s="10" t="n">
         <v>0.7358272727272728</v>
       </c>
-      <c r="O305" t="n">
+      <c r="O305" s="10" t="n">
         <v>0.5887363636363637</v>
+      </c>
+      <c r="P305" t="n">
+        <v>0.3688666666666667</v>
       </c>
     </row>
     <row r="306" ht="16" customHeight="1" s="11">
@@ -11892,8 +12774,11 @@
       <c r="N306" s="10" t="n">
         <v>0.81753</v>
       </c>
-      <c r="O306" t="n">
+      <c r="O306" s="10" t="n">
         <v>0.5072333333333332</v>
+      </c>
+      <c r="P306" t="n">
+        <v>0.5933999999999999</v>
       </c>
     </row>
     <row r="307" ht="16" customHeight="1" s="11">
@@ -11930,8 +12815,11 @@
       <c r="N307" s="10" t="n">
         <v>0.62556</v>
       </c>
-      <c r="O307" t="n">
+      <c r="O307" s="10" t="n">
         <v>0.296075</v>
+      </c>
+      <c r="P307" t="n">
+        <v>0.3485625</v>
       </c>
     </row>
     <row r="308" ht="16" customHeight="1" s="11">
@@ -11968,8 +12856,11 @@
       <c r="N308" s="10" t="n">
         <v>0.8653999999999999</v>
       </c>
-      <c r="O308" t="n">
+      <c r="O308" s="10" t="n">
         <v>0.5168400000000001</v>
+      </c>
+      <c r="P308" t="n">
+        <v>0.7590249999999999</v>
       </c>
     </row>
     <row r="309" ht="16" customHeight="1" s="11">
@@ -12006,8 +12897,11 @@
       <c r="N309" s="10" t="n">
         <v>0.7075222222222224</v>
       </c>
-      <c r="O309" t="n">
+      <c r="O309" s="10" t="n">
         <v>0.7185333333333335</v>
+      </c>
+      <c r="P309" t="n">
+        <v>0.6256428571428572</v>
       </c>
     </row>
     <row r="310" ht="16" customHeight="1" s="11">
@@ -12044,8 +12938,11 @@
       <c r="N310" s="10" t="n">
         <v>0.6212636363636364</v>
       </c>
-      <c r="O310" t="n">
+      <c r="O310" s="10" t="n">
         <v>0.5232333333333332</v>
+      </c>
+      <c r="P310" t="n">
+        <v>0.4016</v>
       </c>
     </row>
     <row r="311" ht="16" customHeight="1" s="11">
@@ -12082,8 +12979,11 @@
       <c r="N311" s="10" t="n">
         <v>0.6803666666666666</v>
       </c>
-      <c r="O311" t="n">
+      <c r="O311" s="10" t="n">
         <v>0.5273625</v>
+      </c>
+      <c r="P311" t="n">
+        <v>0.43205</v>
       </c>
     </row>
     <row r="314" ht="16" customHeight="1" s="11">
@@ -12147,6 +13047,9 @@
       <c r="O316" s="10" t="n">
         <v>0.0009</v>
       </c>
+      <c r="P316" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317" ht="16" customHeight="1" s="11">
       <c r="A317" s="18" t="n">
@@ -12185,6 +13088,9 @@
       <c r="O317" s="10" t="n">
         <v>0.0141</v>
       </c>
+      <c r="P317" s="10" t="n">
+        <v>0.0009</v>
+      </c>
     </row>
     <row r="318" ht="16" customHeight="1" s="11">
       <c r="A318" s="18" t="n">
@@ -12223,6 +13129,9 @@
       <c r="O318" s="10" t="n">
         <v>0.0133</v>
       </c>
+      <c r="P318" s="10" t="n">
+        <v>0.1628</v>
+      </c>
     </row>
     <row r="319" ht="16" customHeight="1" s="11">
       <c r="A319" s="18" t="n">
@@ -12261,6 +13170,9 @@
       <c r="O319" s="10" t="n">
         <v>0.0176</v>
       </c>
+      <c r="P319" s="10" t="n">
+        <v>0.1792</v>
+      </c>
     </row>
     <row r="320" ht="16" customHeight="1" s="11">
       <c r="A320" s="18" t="n">
@@ -12299,6 +13211,9 @@
       <c r="O320" s="10" t="n">
         <v>0.0209</v>
       </c>
+      <c r="P320" s="10" t="n">
+        <v>0.1065</v>
+      </c>
     </row>
     <row r="321" ht="16" customHeight="1" s="11">
       <c r="A321" s="18" t="n">
@@ -12337,6 +13252,9 @@
       <c r="O321" s="10" t="n">
         <v>0.0609</v>
       </c>
+      <c r="P321" s="10" t="n">
+        <v>0.1528</v>
+      </c>
     </row>
     <row r="322" ht="16" customHeight="1" s="11">
       <c r="A322" s="18" t="n">
@@ -12375,6 +13293,9 @@
       <c r="O322" s="10" t="n">
         <v>0.0544</v>
       </c>
+      <c r="P322" s="10" t="n">
+        <v>0.1262</v>
+      </c>
     </row>
     <row r="323" ht="16" customHeight="1" s="11">
       <c r="A323" s="18" t="n">
@@ -12413,6 +13334,9 @@
       <c r="O323" s="10" t="n">
         <v>0.0217</v>
       </c>
+      <c r="P323" s="10" t="n">
+        <v>0.1044</v>
+      </c>
     </row>
     <row r="324" ht="16" customHeight="1" s="11">
       <c r="A324" s="18" t="n">
@@ -12451,6 +13375,9 @@
       <c r="O324" s="10" t="n">
         <v>0.1229</v>
       </c>
+      <c r="P324" s="10" t="n">
+        <v>0.2162</v>
+      </c>
     </row>
     <row r="325" ht="16" customHeight="1" s="11">
       <c r="A325" s="18" t="n">
@@ -12489,6 +13416,9 @@
       <c r="O325" s="10" t="n">
         <v>0.0633</v>
       </c>
+      <c r="P325" t="n">
+        <v>0.1586</v>
+      </c>
     </row>
     <row r="326" ht="16" customHeight="1" s="11">
       <c r="A326" s="18" t="n">
@@ -12527,6 +13457,9 @@
       <c r="O326" s="10" t="n">
         <v>0.0849</v>
       </c>
+      <c r="P326" t="n">
+        <v>0.2228</v>
+      </c>
     </row>
     <row r="327" ht="16" customHeight="1" s="11">
       <c r="A327" s="18" t="n">
@@ -12565,6 +13498,9 @@
       <c r="O327" s="10" t="n">
         <v>0.0576</v>
       </c>
+      <c r="P327" t="n">
+        <v>0.2382</v>
+      </c>
     </row>
     <row r="328" ht="16" customHeight="1" s="11">
       <c r="A328" s="18" t="n">
@@ -12600,8 +13536,11 @@
       <c r="N328" s="10" t="n">
         <v>0.0723</v>
       </c>
-      <c r="O328" t="n">
+      <c r="O328" s="10" t="n">
         <v>0.0722</v>
+      </c>
+      <c r="P328" t="n">
+        <v>0.3328</v>
       </c>
     </row>
     <row r="329" ht="16" customHeight="1" s="11">
@@ -12638,8 +13577,11 @@
       <c r="N329" s="10" t="n">
         <v>0.062</v>
       </c>
-      <c r="O329" t="n">
+      <c r="O329" s="10" t="n">
         <v>0.1002</v>
+      </c>
+      <c r="P329" t="n">
+        <v>0.286</v>
       </c>
     </row>
     <row r="330" ht="16" customHeight="1" s="11">
@@ -12676,8 +13618,11 @@
       <c r="N330" s="10" t="n">
         <v>0.0895</v>
       </c>
-      <c r="O330" t="n">
+      <c r="O330" s="10" t="n">
         <v>0.076</v>
+      </c>
+      <c r="P330" t="n">
+        <v>0.4127</v>
       </c>
     </row>
     <row r="331" ht="16" customHeight="1" s="11">
@@ -12714,8 +13659,11 @@
       <c r="N331" s="10" t="n">
         <v>0.1107</v>
       </c>
-      <c r="O331" t="n">
+      <c r="O331" s="10" t="n">
         <v>0.07149999999999999</v>
+      </c>
+      <c r="P331" t="n">
+        <v>0.3831</v>
       </c>
     </row>
     <row r="332" ht="16" customHeight="1" s="11">
@@ -12752,8 +13700,11 @@
       <c r="N332" s="10" t="n">
         <v>0.0795</v>
       </c>
-      <c r="O332" t="n">
+      <c r="O332" s="10" t="n">
         <v>0.0636</v>
+      </c>
+      <c r="P332" t="n">
+        <v>0.4004</v>
       </c>
     </row>
     <row r="333" ht="16" customHeight="1" s="11">
@@ -12790,8 +13741,11 @@
       <c r="N333" s="10" t="n">
         <v>0.1086</v>
       </c>
-      <c r="O333" t="n">
+      <c r="O333" s="10" t="n">
         <v>0.0544</v>
+      </c>
+      <c r="P333" t="n">
+        <v>0.3795</v>
       </c>
     </row>
     <row r="334" ht="16" customHeight="1" s="11">
@@ -12828,8 +13782,11 @@
       <c r="N334" s="10" t="n">
         <v>0.108</v>
       </c>
-      <c r="O334" t="n">
+      <c r="O334" s="10" t="n">
         <v>0.06619999999999999</v>
+      </c>
+      <c r="P334" t="n">
+        <v>0.3051</v>
       </c>
     </row>
     <row r="335" ht="16" customHeight="1" s="11">
@@ -12866,8 +13823,11 @@
       <c r="N335" s="10" t="n">
         <v>0.0961</v>
       </c>
-      <c r="O335" t="n">
+      <c r="O335" s="10" t="n">
         <v>0.0766</v>
+      </c>
+      <c r="P335" t="n">
+        <v>0.2582</v>
       </c>
     </row>
     <row r="336" ht="16" customHeight="1" s="11">
@@ -12904,8 +13864,11 @@
       <c r="N336" s="10" t="n">
         <v>0.1168</v>
       </c>
-      <c r="O336" t="n">
+      <c r="O336" s="10" t="n">
         <v>0.0603</v>
+      </c>
+      <c r="P336" t="n">
+        <v>0.2389</v>
       </c>
     </row>
     <row r="337" ht="16" customHeight="1" s="11">
@@ -12942,8 +13905,11 @@
       <c r="N337" s="10" t="n">
         <v>0.0888</v>
       </c>
-      <c r="O337" t="n">
+      <c r="O337" s="10" t="n">
         <v>0.0558</v>
+      </c>
+      <c r="P337" t="n">
+        <v>0.1894</v>
       </c>
     </row>
     <row r="338" ht="16" customHeight="1" s="11">
@@ -12980,8 +13946,11 @@
       <c r="N338" s="10" t="n">
         <v>0.1068</v>
       </c>
-      <c r="O338" t="n">
+      <c r="O338" s="10" t="n">
         <v>0.06560000000000001</v>
+      </c>
+      <c r="P338" t="n">
+        <v>0.2329</v>
       </c>
     </row>
     <row r="339" ht="16" customHeight="1" s="11">
@@ -13018,8 +13987,11 @@
       <c r="N339" s="10" t="n">
         <v>0.1391</v>
       </c>
-      <c r="O339" t="n">
+      <c r="O339" s="10" t="n">
         <v>0.0616</v>
+      </c>
+      <c r="P339" t="n">
+        <v>0.1987</v>
       </c>
     </row>
     <row r="340" ht="16" customHeight="1" s="11">
@@ -13056,8 +14028,11 @@
       <c r="N340" s="10" t="n">
         <v>0.11</v>
       </c>
-      <c r="O340" t="n">
+      <c r="O340" s="10" t="n">
         <v>0.0557</v>
+      </c>
+      <c r="P340" t="n">
+        <v>0.207</v>
       </c>
     </row>
     <row r="341" ht="16" customHeight="1" s="11">
@@ -13094,8 +14069,11 @@
       <c r="N341" s="10" t="n">
         <v>0.1081</v>
       </c>
-      <c r="O341" t="n">
+      <c r="O341" s="10" t="n">
         <v>0.0501</v>
+      </c>
+      <c r="P341" t="n">
+        <v>0.2539</v>
       </c>
     </row>
     <row r="342" ht="16" customHeight="1" s="11">
@@ -13132,8 +14110,11 @@
       <c r="N342" s="10" t="n">
         <v>0.0795</v>
       </c>
-      <c r="O342" t="n">
+      <c r="O342" s="10" t="n">
         <v>0.054</v>
+      </c>
+      <c r="P342" t="n">
+        <v>0.2325</v>
       </c>
     </row>
     <row r="343" ht="16" customHeight="1" s="11">
@@ -13170,8 +14151,11 @@
       <c r="N343" s="10" t="n">
         <v>0.0965</v>
       </c>
-      <c r="O343" t="n">
+      <c r="O343" s="10" t="n">
         <v>0.097</v>
+      </c>
+      <c r="P343" t="n">
+        <v>0.2404</v>
       </c>
     </row>
     <row r="344" ht="16" customHeight="1" s="11">
@@ -13208,8 +14192,11 @@
       <c r="N344" s="10" t="n">
         <v>0.09470000000000001</v>
       </c>
-      <c r="O344" t="n">
+      <c r="O344" s="10" t="n">
         <v>0.1138</v>
+      </c>
+      <c r="P344" t="n">
+        <v>0.2223</v>
       </c>
     </row>
     <row r="345" ht="16" customHeight="1" s="11">
@@ -13246,8 +14233,11 @@
       <c r="N345" s="10" t="n">
         <v>0.108</v>
       </c>
-      <c r="O345" t="n">
+      <c r="O345" s="10" t="n">
         <v>0.1074</v>
+      </c>
+      <c r="P345" t="n">
+        <v>0.3002</v>
       </c>
     </row>
     <row r="346" ht="16" customHeight="1" s="11">
@@ -13284,8 +14274,11 @@
       <c r="N346" s="10" t="n">
         <v>0.1004</v>
       </c>
-      <c r="O346" t="n">
+      <c r="O346" s="10" t="n">
         <v>0.1196</v>
+      </c>
+      <c r="P346" t="n">
+        <v>0.2839</v>
       </c>
     </row>
     <row r="347" ht="16" customHeight="1" s="11">
@@ -13322,8 +14315,11 @@
       <c r="N347" s="10" t="n">
         <v>0.1094</v>
       </c>
-      <c r="O347" t="n">
+      <c r="O347" s="10" t="n">
         <v>0.1105</v>
+      </c>
+      <c r="P347" t="n">
+        <v>0.2278</v>
       </c>
     </row>
     <row r="348" ht="16" customHeight="1" s="11">
@@ -13360,8 +14356,11 @@
       <c r="N348" s="10" t="n">
         <v>0.1047</v>
       </c>
-      <c r="O348" t="n">
+      <c r="O348" s="10" t="n">
         <v>0.0781</v>
+      </c>
+      <c r="P348" t="n">
+        <v>0.2267</v>
       </c>
     </row>
     <row r="349" ht="16" customHeight="1" s="11">
@@ -13398,8 +14397,11 @@
       <c r="N349" s="10" t="n">
         <v>0.09279999999999999</v>
       </c>
-      <c r="O349" t="n">
+      <c r="O349" s="10" t="n">
         <v>0.0867</v>
+      </c>
+      <c r="P349" t="n">
+        <v>0.158</v>
       </c>
     </row>
     <row r="350" ht="16" customHeight="1" s="11">
@@ -13436,8 +14438,11 @@
       <c r="N350" s="10" t="n">
         <v>0.1028</v>
       </c>
-      <c r="O350" t="n">
+      <c r="O350" s="10" t="n">
         <v>0.07829999999999999</v>
+      </c>
+      <c r="P350" t="n">
+        <v>0.1745</v>
       </c>
     </row>
     <row r="351" ht="16" customHeight="1" s="11">
@@ -13474,8 +14479,11 @@
       <c r="N351" s="10" t="n">
         <v>0.08359999999999999</v>
       </c>
-      <c r="O351" t="n">
+      <c r="O351" s="10" t="n">
         <v>0.057</v>
+      </c>
+      <c r="P351" t="n">
+        <v>0.1614</v>
       </c>
     </row>
     <row r="352" ht="16" customHeight="1" s="11">
@@ -13512,8 +14520,11 @@
       <c r="N352" s="10" t="n">
         <v>0.1027</v>
       </c>
-      <c r="O352" t="n">
+      <c r="O352" s="10" t="n">
         <v>0.0598</v>
+      </c>
+      <c r="P352" t="n">
+        <v>0.1987</v>
       </c>
     </row>
     <row r="353" ht="16" customHeight="1" s="11">
@@ -13550,8 +14561,11 @@
       <c r="N353" s="10" t="n">
         <v>0.1052</v>
       </c>
-      <c r="O353" t="n">
+      <c r="O353" s="10" t="n">
         <v>0.061</v>
+      </c>
+      <c r="P353" t="n">
+        <v>0.244</v>
       </c>
     </row>
     <row r="354" ht="16" customHeight="1" s="11">
@@ -13588,8 +14602,11 @@
       <c r="N354" s="10" t="n">
         <v>0.0919</v>
       </c>
-      <c r="O354" t="n">
+      <c r="O354" s="10" t="n">
         <v>0.0599</v>
+      </c>
+      <c r="P354" t="n">
+        <v>0.1951</v>
       </c>
     </row>
     <row r="355" ht="16" customHeight="1" s="11">
@@ -13626,8 +14643,11 @@
       <c r="N355" s="10" t="n">
         <v>0.1087</v>
       </c>
-      <c r="O355" t="n">
+      <c r="O355" s="10" t="n">
         <v>0.0674</v>
+      </c>
+      <c r="P355" t="n">
+        <v>0.2161</v>
       </c>
     </row>
     <row r="356" ht="16" customHeight="1" s="11">
@@ -13664,8 +14684,11 @@
       <c r="N356" s="10" t="n">
         <v>0.0963</v>
       </c>
-      <c r="O356" t="n">
+      <c r="O356" s="10" t="n">
         <v>0.0584</v>
+      </c>
+      <c r="P356" t="n">
+        <v>0.2062</v>
       </c>
     </row>
     <row r="357" ht="16" customHeight="1" s="11">
@@ -13702,8 +14725,11 @@
       <c r="N357" s="10" t="n">
         <v>0.1015</v>
       </c>
-      <c r="O357" t="n">
+      <c r="O357" s="10" t="n">
         <v>0.0598</v>
+      </c>
+      <c r="P357" t="n">
+        <v>0.1925</v>
       </c>
     </row>
     <row r="358" ht="16" customHeight="1" s="11">
@@ -13740,8 +14766,11 @@
       <c r="N358" s="10" t="n">
         <v>0.0965</v>
       </c>
-      <c r="O358" t="n">
+      <c r="O358" s="10" t="n">
         <v>0.09569999999999999</v>
+      </c>
+      <c r="P358" t="n">
+        <v>0.1924</v>
       </c>
     </row>
     <row r="359" ht="16" customHeight="1" s="11">
@@ -13778,8 +14807,11 @@
       <c r="N359" s="10" t="n">
         <v>0.092</v>
       </c>
-      <c r="O359" t="n">
+      <c r="O359" s="10" t="n">
         <v>0.0793</v>
+      </c>
+      <c r="P359" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="360" ht="16" customHeight="1" s="11">
@@ -13816,8 +14848,11 @@
       <c r="N360" s="10" t="n">
         <v>0.0856</v>
       </c>
-      <c r="O360" t="n">
+      <c r="O360" s="10" t="n">
         <v>0.1088</v>
+      </c>
+      <c r="P360" t="n">
+        <v>0.2077</v>
       </c>
     </row>
     <row r="361" ht="16" customHeight="1" s="11">
@@ -13854,8 +14889,11 @@
       <c r="N361" s="10" t="n">
         <v>0.0886</v>
       </c>
-      <c r="O361" t="n">
+      <c r="O361" s="10" t="n">
         <v>0.0804</v>
+      </c>
+      <c r="P361" t="n">
+        <v>0.1808</v>
       </c>
     </row>
     <row r="362" ht="16" customHeight="1" s="11">
@@ -13892,8 +14930,11 @@
       <c r="N362" s="10" t="n">
         <v>0.09959999999999999</v>
       </c>
-      <c r="O362" t="n">
+      <c r="O362" s="10" t="n">
         <v>0.0868</v>
+      </c>
+      <c r="P362" t="n">
+        <v>0.1964</v>
       </c>
     </row>
     <row r="363" ht="16" customHeight="1" s="11">
@@ -13930,8 +14971,11 @@
       <c r="N363" s="10" t="n">
         <v>0.0988</v>
       </c>
-      <c r="O363" t="n">
+      <c r="O363" s="10" t="n">
         <v>0.0752</v>
+      </c>
+      <c r="P363" t="n">
+        <v>0.2082</v>
       </c>
     </row>
     <row r="364" ht="16" customHeight="1" s="11">
@@ -13968,8 +15012,11 @@
       <c r="N364" s="10" t="n">
         <v>0.0955</v>
       </c>
-      <c r="O364" t="n">
+      <c r="O364" s="10" t="n">
         <v>0.0727</v>
+      </c>
+      <c r="P364" t="n">
+        <v>0.2209</v>
       </c>
     </row>
     <row r="365" ht="16" customHeight="1" s="11">
@@ -14006,8 +15053,11 @@
       <c r="N365" s="10" t="n">
         <v>0.09180000000000001</v>
       </c>
-      <c r="O365" t="n">
+      <c r="O365" s="10" t="n">
         <v>0.1038</v>
+      </c>
+      <c r="P365" t="n">
+        <v>0.2205</v>
       </c>
     </row>
     <row r="366" ht="16" customHeight="1" s="11">
@@ -14044,8 +15094,11 @@
       <c r="N366" s="10" t="n">
         <v>0.07870000000000001</v>
       </c>
-      <c r="O366" t="n">
+      <c r="O366" s="10" t="n">
         <v>0.0969</v>
+      </c>
+      <c r="P366" t="n">
+        <v>0.2428</v>
       </c>
     </row>
     <row r="367" ht="16" customHeight="1" s="11">
@@ -14082,8 +15135,11 @@
       <c r="N367" s="10" t="n">
         <v>0.0919</v>
       </c>
-      <c r="O367" t="n">
+      <c r="O367" s="10" t="n">
         <v>0.09959999999999999</v>
+      </c>
+      <c r="P367" t="n">
+        <v>0.2135</v>
       </c>
     </row>
     <row r="368" ht="16" customHeight="1" s="11">
@@ -14120,8 +15176,11 @@
       <c r="N368" s="10" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="O368" t="n">
+      <c r="O368" s="10" t="n">
         <v>0.06370000000000001</v>
+      </c>
+      <c r="P368" t="n">
+        <v>0.1919</v>
       </c>
     </row>
     <row r="369" ht="16" customHeight="1" s="11">
@@ -14158,8 +15217,11 @@
       <c r="N369" s="10" t="n">
         <v>0.07489999999999999</v>
       </c>
-      <c r="O369" t="n">
+      <c r="O369" s="10" t="n">
         <v>0.0659</v>
+      </c>
+      <c r="P369" t="n">
+        <v>0.1507</v>
       </c>
     </row>
     <row r="370" ht="16" customHeight="1" s="11">
@@ -14196,8 +15258,11 @@
       <c r="N370" s="10" t="n">
         <v>0.07140000000000001</v>
       </c>
-      <c r="O370" t="n">
+      <c r="O370" s="10" t="n">
         <v>0.0725</v>
+      </c>
+      <c r="P370" t="n">
+        <v>0.1504</v>
       </c>
     </row>
     <row r="371" ht="16" customHeight="1" s="11">
@@ -14234,8 +15299,11 @@
       <c r="N371" s="10" t="n">
         <v>0.0678</v>
       </c>
-      <c r="O371" t="n">
+      <c r="O371" s="10" t="n">
         <v>0.0886</v>
+      </c>
+      <c r="P371" t="n">
+        <v>0.1567</v>
       </c>
     </row>
     <row r="372" ht="16" customHeight="1" s="11">
@@ -14272,8 +15340,11 @@
       <c r="N372" s="10" t="n">
         <v>0.0743</v>
       </c>
-      <c r="O372" t="n">
+      <c r="O372" s="10" t="n">
         <v>0.07829999999999999</v>
+      </c>
+      <c r="P372" t="n">
+        <v>0.1852</v>
       </c>
     </row>
     <row r="373" ht="16" customHeight="1" s="11">
@@ -14310,8 +15381,11 @@
       <c r="N373" s="10" t="n">
         <v>0.06320000000000001</v>
       </c>
-      <c r="O373" t="n">
+      <c r="O373" s="10" t="n">
         <v>0.0752</v>
+      </c>
+      <c r="P373" t="n">
+        <v>0.1937</v>
       </c>
     </row>
     <row r="374" ht="16" customHeight="1" s="11">
@@ -14348,8 +15422,11 @@
       <c r="N374" s="10" t="n">
         <v>0.0858</v>
       </c>
-      <c r="O374" t="n">
+      <c r="O374" s="10" t="n">
         <v>0.06660000000000001</v>
+      </c>
+      <c r="P374" t="n">
+        <v>0.1485</v>
       </c>
     </row>
     <row r="375" ht="16" customHeight="1" s="11">
@@ -14386,8 +15463,11 @@
       <c r="N375" s="10" t="n">
         <v>0.0794</v>
       </c>
-      <c r="O375" t="n">
+      <c r="O375" s="10" t="n">
         <v>0.0639</v>
+      </c>
+      <c r="P375" t="n">
+        <v>0.1461</v>
       </c>
     </row>
     <row r="376" ht="16" customHeight="1" s="11">
@@ -14424,8 +15504,11 @@
       <c r="N376" s="10" t="n">
         <v>0.07820000000000001</v>
       </c>
-      <c r="O376" t="n">
+      <c r="O376" s="10" t="n">
         <v>0.07679999999999999</v>
+      </c>
+      <c r="P376" t="n">
+        <v>0.1607</v>
       </c>
     </row>
     <row r="377" ht="16" customHeight="1" s="11">
@@ -14462,8 +15545,11 @@
       <c r="N377" s="10" t="n">
         <v>0.0723</v>
       </c>
-      <c r="O377" t="n">
+      <c r="O377" s="10" t="n">
         <v>0.0886</v>
+      </c>
+      <c r="P377" t="n">
+        <v>0.1686</v>
       </c>
     </row>
     <row r="378" ht="16" customHeight="1" s="11">
@@ -14500,8 +15586,11 @@
       <c r="N378" s="10" t="n">
         <v>0.06419999999999999</v>
       </c>
-      <c r="O378" t="n">
+      <c r="O378" s="10" t="n">
         <v>0.0882</v>
+      </c>
+      <c r="P378" t="n">
+        <v>0.1679</v>
       </c>
     </row>
     <row r="379" ht="16" customHeight="1" s="11">
@@ -14538,8 +15627,11 @@
       <c r="N379" s="10" t="n">
         <v>0.0829</v>
       </c>
-      <c r="O379" t="n">
+      <c r="O379" s="10" t="n">
         <v>0.0793</v>
+      </c>
+      <c r="P379" t="n">
+        <v>0.1706</v>
       </c>
     </row>
     <row r="380" ht="16" customHeight="1" s="11">
@@ -14576,8 +15668,11 @@
       <c r="N380" s="10" t="n">
         <v>0.07820000000000001</v>
       </c>
-      <c r="O380" t="n">
+      <c r="O380" s="10" t="n">
         <v>0.09080000000000001</v>
+      </c>
+      <c r="P380" t="n">
+        <v>0.2021</v>
       </c>
     </row>
     <row r="381" ht="16" customHeight="1" s="11">
@@ -14614,8 +15709,11 @@
       <c r="N381" s="10" t="n">
         <v>0.0711</v>
       </c>
-      <c r="O381" t="n">
+      <c r="O381" s="10" t="n">
         <v>0.0688</v>
+      </c>
+      <c r="P381" t="n">
+        <v>0.1755</v>
       </c>
     </row>
     <row r="382" ht="16" customHeight="1" s="11">
@@ -14652,8 +15750,11 @@
       <c r="N382" s="10" t="n">
         <v>0.0849</v>
       </c>
-      <c r="O382" t="n">
+      <c r="O382" s="10" t="n">
         <v>0.076</v>
+      </c>
+      <c r="P382" t="n">
+        <v>0.1376</v>
       </c>
     </row>
     <row r="383" ht="16" customHeight="1" s="11">
@@ -14690,8 +15791,11 @@
       <c r="N383" s="10" t="n">
         <v>0.0827</v>
       </c>
-      <c r="O383" t="n">
+      <c r="O383" s="10" t="n">
         <v>0.0893</v>
+      </c>
+      <c r="P383" t="n">
+        <v>0.1631</v>
       </c>
     </row>
     <row r="384" ht="16" customHeight="1" s="11">
@@ -14728,8 +15832,11 @@
       <c r="N384" s="10" t="n">
         <v>0.0844</v>
       </c>
-      <c r="O384" t="n">
+      <c r="O384" s="10" t="n">
         <v>0.08989999999999999</v>
+      </c>
+      <c r="P384" t="n">
+        <v>0.1349</v>
       </c>
     </row>
     <row r="385" ht="16" customHeight="1" s="11">
@@ -14766,8 +15873,11 @@
       <c r="N385" s="10" t="n">
         <v>0.0868</v>
       </c>
-      <c r="O385" t="n">
+      <c r="O385" s="10" t="n">
         <v>0.0823</v>
+      </c>
+      <c r="P385" t="n">
+        <v>0.1934</v>
       </c>
     </row>
     <row r="386" ht="16" customHeight="1" s="11">
@@ -14804,8 +15914,11 @@
       <c r="N386" s="10" t="n">
         <v>0.0717</v>
       </c>
-      <c r="O386" t="n">
+      <c r="O386" s="10" t="n">
         <v>0.0852</v>
+      </c>
+      <c r="P386" t="n">
+        <v>0.1759</v>
       </c>
     </row>
     <row r="387" ht="16" customHeight="1" s="11">
@@ -14842,8 +15955,11 @@
       <c r="N387" s="10" t="n">
         <v>0.0795</v>
       </c>
-      <c r="O387" t="n">
+      <c r="O387" s="10" t="n">
         <v>0.0843</v>
+      </c>
+      <c r="P387" t="n">
+        <v>0.1837</v>
       </c>
     </row>
     <row r="388" ht="16" customHeight="1" s="11">
@@ -14880,8 +15996,11 @@
       <c r="N388" s="10" t="n">
         <v>0.0725</v>
       </c>
-      <c r="O388" t="n">
+      <c r="O388" s="10" t="n">
         <v>0.07480000000000001</v>
+      </c>
+      <c r="P388" t="n">
+        <v>0.1739</v>
       </c>
     </row>
     <row r="389" ht="16" customHeight="1" s="11">
@@ -14918,8 +16037,11 @@
       <c r="N389" s="10" t="n">
         <v>0.0799</v>
       </c>
-      <c r="O389" t="n">
+      <c r="O389" s="10" t="n">
         <v>0.0859</v>
+      </c>
+      <c r="P389" t="n">
+        <v>0.2179</v>
       </c>
     </row>
     <row r="390" ht="16" customHeight="1" s="11">
@@ -14956,8 +16078,11 @@
       <c r="N390" s="10" t="n">
         <v>0.06859999999999999</v>
       </c>
-      <c r="O390" t="n">
+      <c r="O390" s="10" t="n">
         <v>0.0898</v>
+      </c>
+      <c r="P390" t="n">
+        <v>0.1873</v>
       </c>
     </row>
     <row r="391" ht="16" customHeight="1" s="11">
@@ -14994,8 +16119,11 @@
       <c r="N391" s="10" t="n">
         <v>0.07630000000000001</v>
       </c>
-      <c r="O391" t="n">
+      <c r="O391" s="10" t="n">
         <v>0.0914</v>
+      </c>
+      <c r="P391" t="n">
+        <v>0.1959</v>
       </c>
     </row>
     <row r="392" ht="16" customHeight="1" s="11">
@@ -15032,8 +16160,11 @@
       <c r="N392" s="10" t="n">
         <v>0.0723</v>
       </c>
-      <c r="O392" t="n">
+      <c r="O392" s="10" t="n">
         <v>0.078</v>
+      </c>
+      <c r="P392" t="n">
+        <v>0.1573</v>
       </c>
     </row>
     <row r="393" ht="16" customHeight="1" s="11">
@@ -15070,8 +16201,11 @@
       <c r="N393" s="10" t="n">
         <v>0.0762</v>
       </c>
-      <c r="O393" t="n">
+      <c r="O393" s="10" t="n">
         <v>0.0814</v>
+      </c>
+      <c r="P393" t="n">
+        <v>0.1809</v>
       </c>
     </row>
     <row r="394" ht="16" customHeight="1" s="11">
@@ -15108,8 +16242,11 @@
       <c r="N394" s="10" t="n">
         <v>0.0993</v>
       </c>
-      <c r="O394" t="n">
+      <c r="O394" s="10" t="n">
         <v>0.056</v>
+      </c>
+      <c r="P394" t="n">
+        <v>0.1785</v>
       </c>
     </row>
     <row r="395" ht="16" customHeight="1" s="11">
@@ -15146,8 +16283,11 @@
       <c r="N395" s="10" t="n">
         <v>0.08450000000000001</v>
       </c>
-      <c r="O395" t="n">
+      <c r="O395" s="10" t="n">
         <v>0.0591</v>
+      </c>
+      <c r="P395" t="n">
+        <v>0.1973</v>
       </c>
     </row>
     <row r="396" ht="16" customHeight="1" s="11">
@@ -15184,8 +16324,11 @@
       <c r="N396" s="10" t="n">
         <v>0.0737</v>
       </c>
-      <c r="O396" t="n">
+      <c r="O396" s="10" t="n">
         <v>0.08450000000000001</v>
+      </c>
+      <c r="P396" t="n">
+        <v>0.1811</v>
       </c>
     </row>
     <row r="397" ht="16" customHeight="1" s="11">
@@ -15222,8 +16365,11 @@
       <c r="N397" s="10" t="n">
         <v>0.081</v>
       </c>
-      <c r="O397" t="n">
+      <c r="O397" s="10" t="n">
         <v>0.0794</v>
+      </c>
+      <c r="P397" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="398" ht="16" customHeight="1" s="11">
@@ -15260,8 +16406,11 @@
       <c r="N398" s="10" t="n">
         <v>0.0771</v>
       </c>
-      <c r="O398" t="n">
+      <c r="O398" s="10" t="n">
         <v>0.075</v>
+      </c>
+      <c r="P398" t="n">
+        <v>0.1749</v>
       </c>
     </row>
     <row r="399" ht="16" customHeight="1" s="11">
@@ -15298,8 +16447,11 @@
       <c r="N399" s="10" t="n">
         <v>0.0602</v>
       </c>
-      <c r="O399" t="n">
+      <c r="O399" s="10" t="n">
         <v>0.06759999999999999</v>
+      </c>
+      <c r="P399" t="n">
+        <v>0.1611</v>
       </c>
     </row>
     <row r="400" ht="16" customHeight="1" s="11">
@@ -15336,8 +16488,11 @@
       <c r="N400" s="10" t="n">
         <v>0.0795</v>
       </c>
-      <c r="O400" t="n">
+      <c r="O400" s="10" t="n">
         <v>0.0736</v>
+      </c>
+      <c r="P400" t="n">
+        <v>0.1674</v>
       </c>
     </row>
     <row r="401" ht="16" customHeight="1" s="11">
@@ -15374,8 +16529,11 @@
       <c r="N401" s="10" t="n">
         <v>0.07539999999999999</v>
       </c>
-      <c r="O401" t="n">
+      <c r="O401" s="10" t="n">
         <v>0.0745</v>
+      </c>
+      <c r="P401" t="n">
+        <v>0.152</v>
       </c>
     </row>
     <row r="402" ht="16" customHeight="1" s="11">
@@ -15412,8 +16570,11 @@
       <c r="N402" s="10" t="n">
         <v>0.0762</v>
       </c>
-      <c r="O402" t="n">
+      <c r="O402" s="10" t="n">
         <v>0.07489999999999999</v>
+      </c>
+      <c r="P402" t="n">
+        <v>0.1631</v>
       </c>
     </row>
     <row r="403" ht="16" customHeight="1" s="11">
@@ -15450,8 +16611,11 @@
       <c r="N403" s="10" t="n">
         <v>0.0752</v>
       </c>
-      <c r="O403" t="n">
+      <c r="O403" s="10" t="n">
         <v>0.0635</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0.1536</v>
       </c>
     </row>
     <row r="404" ht="16" customHeight="1" s="11">
@@ -15488,8 +16652,11 @@
       <c r="N404" s="10" t="n">
         <v>0.078</v>
       </c>
-      <c r="O404" t="n">
+      <c r="O404" s="10" t="n">
         <v>0.06320000000000001</v>
+      </c>
+      <c r="P404" t="n">
+        <v>0.161</v>
       </c>
     </row>
     <row r="405" ht="16" customHeight="1" s="11">
@@ -15526,8 +16693,11 @@
       <c r="N405" s="10" t="n">
         <v>0.0684</v>
       </c>
-      <c r="O405" t="n">
+      <c r="O405" s="10" t="n">
         <v>0.0696</v>
+      </c>
+      <c r="P405" t="n">
+        <v>0.1654</v>
       </c>
     </row>
     <row r="406" ht="16" customHeight="1" s="11">
@@ -15564,8 +16734,11 @@
       <c r="N406" s="10" t="n">
         <v>0.07820000000000001</v>
       </c>
-      <c r="O406" t="n">
+      <c r="O406" s="10" t="n">
         <v>0.07140000000000001</v>
+      </c>
+      <c r="P406" t="n">
+        <v>0.1482</v>
       </c>
     </row>
     <row r="407" ht="16" customHeight="1" s="11">
@@ -15602,8 +16775,11 @@
       <c r="N407" s="10" t="n">
         <v>0.0725</v>
       </c>
-      <c r="O407" t="n">
+      <c r="O407" s="10" t="n">
         <v>0.0619</v>
+      </c>
+      <c r="P407" t="n">
+        <v>0.1513</v>
       </c>
     </row>
     <row r="408" ht="16" customHeight="1" s="11">
@@ -15640,8 +16816,11 @@
       <c r="N408" s="10" t="n">
         <v>0.0679</v>
       </c>
-      <c r="O408" t="n">
+      <c r="O408" s="10" t="n">
         <v>0.0767</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0.1827</v>
       </c>
     </row>
     <row r="409" ht="16" customHeight="1" s="11">
@@ -15678,8 +16857,11 @@
       <c r="N409" s="10" t="n">
         <v>0.0774</v>
       </c>
-      <c r="O409" t="n">
+      <c r="O409" s="10" t="n">
         <v>0.0668</v>
+      </c>
+      <c r="P409" t="n">
+        <v>0.1504</v>
       </c>
     </row>
     <row r="410" ht="16" customHeight="1" s="11">
@@ -15716,8 +16898,11 @@
       <c r="N410" s="10" t="n">
         <v>0.0891</v>
       </c>
-      <c r="O410" t="n">
+      <c r="O410" s="10" t="n">
         <v>0.06510000000000001</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0.1796</v>
       </c>
     </row>
     <row r="411" ht="16" customHeight="1" s="11">
@@ -15754,8 +16939,11 @@
       <c r="N411" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
-      <c r="O411" t="n">
+      <c r="O411" s="10" t="n">
         <v>0.0871</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0.1628</v>
       </c>
     </row>
     <row r="412" ht="16" customHeight="1" s="11">
@@ -15792,8 +16980,11 @@
       <c r="N412" s="10" t="n">
         <v>0.07770000000000001</v>
       </c>
-      <c r="O412" t="n">
+      <c r="O412" s="10" t="n">
         <v>0.07290000000000001</v>
+      </c>
+      <c r="P412" t="n">
+        <v>0.1953</v>
       </c>
     </row>
     <row r="413" ht="16" customHeight="1" s="11">
@@ -15830,8 +17021,11 @@
       <c r="N413" s="10" t="n">
         <v>0.0721</v>
       </c>
-      <c r="O413" t="n">
+      <c r="O413" s="10" t="n">
         <v>0.0871</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0.1384</v>
       </c>
     </row>
     <row r="414" ht="16" customHeight="1" s="11">
@@ -15868,8 +17062,11 @@
       <c r="N414" s="10" t="n">
         <v>0.1053</v>
       </c>
-      <c r="O414" t="n">
+      <c r="O414" s="10" t="n">
         <v>0.0815</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0.1427</v>
       </c>
     </row>
     <row r="415" ht="16" customHeight="1" s="11">
@@ -15906,508 +17103,811 @@
       <c r="N415" s="10" t="n">
         <v>0.0853</v>
       </c>
-      <c r="O415" t="n">
+      <c r="O415" s="10" t="n">
         <v>0.1001</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0.1574</v>
       </c>
     </row>
     <row r="418">
       <c r="O418" s="10" t="n">
         <v>0.1534</v>
       </c>
+      <c r="P418" s="10" t="n">
+        <v>0.1796</v>
+      </c>
     </row>
     <row r="419">
       <c r="O419" s="10" t="n">
         <v>0.20408</v>
       </c>
+      <c r="P419" s="10" t="n">
+        <v>0.1966</v>
+      </c>
     </row>
     <row r="420">
       <c r="O420" s="10" t="n">
         <v>0.229425</v>
       </c>
+      <c r="P420" s="10" t="n">
+        <v>0.2219</v>
+      </c>
     </row>
     <row r="421">
       <c r="O421" s="10" t="n">
         <v>0.2533142857142857</v>
       </c>
+      <c r="P421" s="10" t="n">
+        <v>0.2627</v>
+      </c>
     </row>
     <row r="422">
       <c r="O422" s="10" t="n">
         <v>0.2734</v>
       </c>
+      <c r="P422" s="10" t="n">
+        <v>0.2856</v>
+      </c>
     </row>
     <row r="423">
       <c r="O423" s="10" t="n">
         <v>0.2902999999999999</v>
       </c>
+      <c r="P423" s="10" t="n">
+        <v>0.3033333333333333</v>
+      </c>
     </row>
     <row r="424">
       <c r="O424" s="10" t="n">
         <v>0.3184888888888889</v>
       </c>
+      <c r="P424" s="10" t="n">
+        <v>0.3084</v>
+      </c>
     </row>
     <row r="425">
       <c r="O425" s="10" t="n">
         <v>0.3095666666666667</v>
       </c>
+      <c r="P425" s="10" t="n">
+        <v>0.3276</v>
+      </c>
     </row>
     <row r="426">
       <c r="O426" s="10" t="n">
         <v>0.3281</v>
       </c>
+      <c r="P426" s="10" t="n">
+        <v>0.3310333333333333</v>
+      </c>
     </row>
     <row r="427">
       <c r="O427" s="10" t="n">
         <v>0.33331</v>
       </c>
+      <c r="P427" t="n">
+        <v>0.3424571428571428</v>
+      </c>
     </row>
     <row r="428">
       <c r="O428" s="10" t="n">
         <v>0.3427444444444445</v>
       </c>
+      <c r="P428" t="n">
+        <v>0.3593875</v>
+      </c>
     </row>
     <row r="429">
       <c r="O429" s="10" t="n">
         <v>0.3327000000000001</v>
       </c>
+      <c r="P429" t="n">
+        <v>0.35318</v>
+      </c>
     </row>
     <row r="430">
-      <c r="O430" t="n">
+      <c r="O430" s="10" t="n">
         <v>0.36263</v>
       </c>
+      <c r="P430" t="n">
+        <v>0.3455625000000001</v>
+      </c>
     </row>
     <row r="431">
-      <c r="O431" t="n">
+      <c r="O431" s="10" t="n">
         <v>0.344175</v>
       </c>
+      <c r="P431" t="n">
+        <v>0.3509571428571428</v>
+      </c>
     </row>
     <row r="432">
-      <c r="O432" t="n">
+      <c r="O432" s="10" t="n">
         <v>0.3694857142857143</v>
       </c>
+      <c r="P432" t="n">
+        <v>0.3697666666666666</v>
+      </c>
     </row>
     <row r="433">
-      <c r="O433" t="n">
+      <c r="O433" s="10" t="n">
         <v>0.36075</v>
       </c>
+      <c r="P433" t="n">
+        <v>0.37632</v>
+      </c>
     </row>
     <row r="434">
-      <c r="O434" t="n">
+      <c r="O434" s="10" t="n">
         <v>0.348</v>
       </c>
+      <c r="P434" t="n">
+        <v>0.3664857142857142</v>
+      </c>
     </row>
     <row r="435">
-      <c r="O435" t="n">
+      <c r="O435" s="10" t="n">
         <v>0.362825</v>
       </c>
+      <c r="P435" t="n">
+        <v>0.3626222222222222</v>
+      </c>
     </row>
     <row r="436">
-      <c r="O436" t="n">
+      <c r="O436" s="10" t="n">
         <v>0.3579375</v>
       </c>
+      <c r="P436" t="n">
+        <v>0.3788857142857143</v>
+      </c>
     </row>
     <row r="437">
-      <c r="O437" t="n">
+      <c r="O437" s="10" t="n">
         <v>0.3628</v>
       </c>
+      <c r="P437" t="n">
+        <v>0.37955</v>
+      </c>
     </row>
     <row r="438">
-      <c r="O438" t="n">
+      <c r="O438" s="10" t="n">
         <v>0.3623545454545454</v>
       </c>
+      <c r="P438" t="n">
+        <v>0.39585</v>
+      </c>
     </row>
     <row r="439">
-      <c r="O439" t="n">
+      <c r="O439" s="10" t="n">
         <v>0.35342</v>
       </c>
+      <c r="P439" t="n">
+        <v>0.38019</v>
+      </c>
     </row>
     <row r="440">
-      <c r="O440" t="n">
+      <c r="O440" s="10" t="n">
         <v>0.3619555555555556</v>
       </c>
+      <c r="P440" t="n">
+        <v>0.3779777777777777</v>
+      </c>
     </row>
     <row r="441">
-      <c r="O441" t="n">
+      <c r="O441" s="10" t="n">
         <v>0.3715857142857143</v>
       </c>
+      <c r="P441" t="n">
+        <v>0.3747375</v>
+      </c>
     </row>
     <row r="442">
-      <c r="O442" t="n">
+      <c r="O442" s="10" t="n">
         <v>0.3630888888888888</v>
       </c>
+      <c r="P442" t="n">
+        <v>0.384825</v>
+      </c>
     </row>
     <row r="443">
-      <c r="O443" t="n">
+      <c r="O443" s="10" t="n">
         <v>0.3579625</v>
       </c>
+      <c r="P443" t="n">
+        <v>0.3827</v>
+      </c>
     </row>
     <row r="444">
-      <c r="O444" t="n">
+      <c r="O444" s="10" t="n">
         <v>0.3726</v>
       </c>
+      <c r="P444" t="n">
+        <v>0.3838545454545454</v>
+      </c>
     </row>
     <row r="445">
-      <c r="O445" t="n">
+      <c r="O445" s="10" t="n">
         <v>0.36285</v>
       </c>
+      <c r="P445" t="n">
+        <v>0.3914636363636363</v>
+      </c>
     </row>
     <row r="446">
-      <c r="O446" t="n">
+      <c r="O446" s="10" t="n">
         <v>0.3536</v>
       </c>
+      <c r="P446" t="n">
+        <v>0.4006571428571428</v>
+      </c>
     </row>
     <row r="447">
-      <c r="O447" t="n">
+      <c r="O447" s="10" t="n">
         <v>0.3689</v>
       </c>
+      <c r="P447" t="n">
+        <v>0.3713777777777778</v>
+      </c>
     </row>
     <row r="448">
-      <c r="O448" t="n">
+      <c r="O448" s="10" t="n">
         <v>0.34824</v>
       </c>
+      <c r="P448" t="n">
+        <v>0.3767857142857143</v>
+      </c>
     </row>
     <row r="449">
-      <c r="O449" t="n">
+      <c r="O449" s="10" t="n">
         <v>0.3604111111111111</v>
       </c>
+      <c r="P449" t="n">
+        <v>0.3697142857142857</v>
+      </c>
     </row>
     <row r="450">
-      <c r="O450" t="n">
+      <c r="O450" s="10" t="n">
         <v>0.3569625</v>
       </c>
+      <c r="P450" t="n">
+        <v>0.3760428571428571</v>
+      </c>
     </row>
     <row r="451">
-      <c r="O451" t="n">
+      <c r="O451" s="10" t="n">
         <v>0.3557375</v>
       </c>
+      <c r="P451" t="n">
+        <v>0.3682714285714286</v>
+      </c>
     </row>
     <row r="452">
-      <c r="O452" t="n">
+      <c r="O452" s="10" t="n">
         <v>0.3752454545454545</v>
       </c>
+      <c r="P452" t="n">
+        <v>0.3964624999999999</v>
+      </c>
     </row>
     <row r="453">
-      <c r="O453" t="n">
+      <c r="O453" s="10" t="n">
         <v>0.34765</v>
       </c>
+      <c r="P453" t="n">
+        <v>0.3771333333333333</v>
+      </c>
     </row>
     <row r="454">
-      <c r="O454" t="n">
+      <c r="O454" s="10" t="n">
         <v>0.3615111111111111</v>
       </c>
+      <c r="P454" t="n">
+        <v>0.3884</v>
+      </c>
     </row>
     <row r="455">
-      <c r="O455" t="n">
+      <c r="O455" s="10" t="n">
         <v>0.3572875</v>
       </c>
+      <c r="P455" t="n">
+        <v>0.4002500000000001</v>
+      </c>
     </row>
     <row r="456">
-      <c r="O456" t="n">
+      <c r="O456" s="10" t="n">
         <v>0.37473</v>
       </c>
+      <c r="P456" t="n">
+        <v>0.37242</v>
+      </c>
     </row>
     <row r="457">
-      <c r="O457" t="n">
+      <c r="O457" s="10" t="n">
         <v>0.3702818181818182</v>
       </c>
+      <c r="P457" t="n">
+        <v>0.3771428571428572</v>
+      </c>
     </row>
     <row r="458">
-      <c r="O458" t="n">
+      <c r="O458" s="10" t="n">
         <v>0.367211111111111</v>
       </c>
+      <c r="P458" t="n">
+        <v>0.37285</v>
+      </c>
     </row>
     <row r="459">
-      <c r="O459" t="n">
+      <c r="O459" s="10" t="n">
         <v>0.393911111111111</v>
       </c>
+      <c r="P459" t="n">
+        <v>0.3871125</v>
+      </c>
     </row>
     <row r="460">
-      <c r="O460" t="n">
+      <c r="O460" s="10" t="n">
         <v>0.3624</v>
       </c>
+      <c r="P460" t="n">
+        <v>0.3772</v>
+      </c>
     </row>
     <row r="461">
-      <c r="O461" t="n">
+      <c r="O461" s="10" t="n">
         <v>0.3799555555555555</v>
       </c>
+      <c r="P461" t="n">
+        <v>0.3809333333333333</v>
+      </c>
     </row>
     <row r="462">
-      <c r="O462" t="n">
+      <c r="O462" s="10" t="n">
         <v>0.3800545454545455</v>
       </c>
+      <c r="P462" t="n">
+        <v>0.3833</v>
+      </c>
     </row>
     <row r="463">
-      <c r="O463" t="n">
+      <c r="O463" s="10" t="n">
         <v>0.3402555555555555</v>
       </c>
+      <c r="P463" t="n">
+        <v>0.3886</v>
+      </c>
     </row>
     <row r="464">
-      <c r="O464" t="n">
+      <c r="O464" s="10" t="n">
         <v>0.3587500000000001</v>
       </c>
+      <c r="P464" t="n">
+        <v>0.3896333333333333</v>
+      </c>
     </row>
     <row r="465">
-      <c r="O465" t="n">
+      <c r="O465" s="10" t="n">
         <v>0.3646</v>
       </c>
+      <c r="P465" t="n">
+        <v>0.39907</v>
+      </c>
     </row>
     <row r="466">
-      <c r="O466" t="n">
+      <c r="O466" s="10" t="n">
         <v>0.3682</v>
       </c>
+      <c r="P466" t="n">
+        <v>0.3786857142857143</v>
+      </c>
     </row>
     <row r="467">
-      <c r="O467" t="n">
+      <c r="O467" s="10" t="n">
         <v>0.3640899999999999</v>
       </c>
+      <c r="P467" t="n">
+        <v>0.3669222222222222</v>
+      </c>
     </row>
     <row r="468">
-      <c r="O468" t="n">
+      <c r="O468" s="10" t="n">
         <v>0.3629125000000001</v>
       </c>
+      <c r="P468" t="n">
+        <v>0.3920444444444445</v>
+      </c>
     </row>
     <row r="469">
-      <c r="O469" t="n">
+      <c r="O469" s="10" t="n">
         <v>0.36263</v>
       </c>
+      <c r="P469" t="n">
+        <v>0.3870333333333333</v>
+      </c>
     </row>
     <row r="470">
-      <c r="O470" t="n">
+      <c r="O470" s="10" t="n">
         <v>0.3670666666666667</v>
       </c>
+      <c r="P470" t="n">
+        <v>0.3842571428571429</v>
+      </c>
     </row>
     <row r="471">
-      <c r="O471" t="n">
+      <c r="O471" s="10" t="n">
         <v>0.3645375</v>
       </c>
+      <c r="P471" t="n">
+        <v>0.3712125</v>
+      </c>
     </row>
     <row r="472">
-      <c r="O472" t="n">
+      <c r="O472" s="10" t="n">
         <v>0.3589142857142857</v>
       </c>
+      <c r="P472" t="n">
+        <v>0.3911874999999999</v>
+      </c>
     </row>
     <row r="473">
-      <c r="O473" t="n">
+      <c r="O473" s="10" t="n">
         <v>0.3726444444444444</v>
       </c>
+      <c r="P473" t="n">
+        <v>0.365725</v>
+      </c>
     </row>
     <row r="474">
-      <c r="O474" t="n">
+      <c r="O474" s="10" t="n">
         <v>0.3582666666666666</v>
       </c>
+      <c r="P474" t="n">
+        <v>0.3872714285714286</v>
+      </c>
     </row>
     <row r="475">
-      <c r="O475" t="n">
+      <c r="O475" s="10" t="n">
         <v>0.3651727272727273</v>
       </c>
+      <c r="P475" t="n">
+        <v>0.3735625</v>
+      </c>
     </row>
     <row r="476">
-      <c r="O476" t="n">
+      <c r="O476" s="10" t="n">
         <v>0.3778384615384616</v>
       </c>
+      <c r="P476" t="n">
+        <v>0.3921250000000001</v>
+      </c>
     </row>
     <row r="477">
-      <c r="O477" t="n">
+      <c r="O477" s="10" t="n">
         <v>0.3673571428571428</v>
       </c>
+      <c r="P477" t="n">
+        <v>0.3953125</v>
+      </c>
     </row>
     <row r="478">
-      <c r="O478" t="n">
+      <c r="O478" s="10" t="n">
         <v>0.35773</v>
       </c>
+      <c r="P478" t="n">
+        <v>0.3746875</v>
+      </c>
     </row>
     <row r="479">
-      <c r="O479" t="n">
+      <c r="O479" s="10" t="n">
         <v>0.35933</v>
       </c>
+      <c r="P479" t="n">
+        <v>0.3690285714285714</v>
+      </c>
     </row>
     <row r="480">
-      <c r="O480" t="n">
+      <c r="O480" s="10" t="n">
         <v>0.36935</v>
       </c>
+      <c r="P480" t="n">
+        <v>0.3655285714285714</v>
+      </c>
     </row>
     <row r="481">
-      <c r="O481" t="n">
+      <c r="O481" s="10" t="n">
         <v>0.3630444444444445</v>
       </c>
+      <c r="P481" t="n">
+        <v>0.3946571428571429</v>
+      </c>
     </row>
     <row r="482">
-      <c r="O482" t="n">
+      <c r="O482" s="10" t="n">
         <v>0.3577</v>
       </c>
+      <c r="P482" t="n">
+        <v>0.3904727272727272</v>
+      </c>
     </row>
     <row r="483">
-      <c r="O483" t="n">
+      <c r="O483" s="10" t="n">
         <v>0.37977</v>
       </c>
+      <c r="P483" t="n">
+        <v>0.3767</v>
+      </c>
     </row>
     <row r="484">
-      <c r="O484" t="n">
+      <c r="O484" s="10" t="n">
         <v>0.362075</v>
       </c>
+      <c r="P484" t="n">
+        <v>0.3709</v>
+      </c>
     </row>
     <row r="485">
-      <c r="O485" t="n">
+      <c r="O485" s="10" t="n">
         <v>0.3699</v>
       </c>
+      <c r="P485" t="n">
+        <v>0.3895666666666667</v>
+      </c>
     </row>
     <row r="486">
-      <c r="O486" t="n">
+      <c r="O486" s="10" t="n">
         <v>0.3423888888888889</v>
       </c>
+      <c r="P486" t="n">
+        <v>0.402075</v>
+      </c>
     </row>
     <row r="487">
-      <c r="O487" t="n">
+      <c r="O487" s="10" t="n">
         <v>0.3526624999999999</v>
       </c>
+      <c r="P487" t="n">
+        <v>0.3783874999999999</v>
+      </c>
     </row>
     <row r="488">
-      <c r="O488" t="n">
+      <c r="O488" s="10" t="n">
         <v>0.35937</v>
       </c>
+      <c r="P488" t="n">
+        <v>0.3784444444444444</v>
+      </c>
     </row>
     <row r="489">
-      <c r="O489" t="n">
+      <c r="O489" s="10" t="n">
         <v>0.3591</v>
       </c>
+      <c r="P489" t="n">
+        <v>0.3935625</v>
+      </c>
     </row>
     <row r="490">
-      <c r="O490" t="n">
+      <c r="O490" s="10" t="n">
         <v>0.3528125</v>
       </c>
+      <c r="P490" t="n">
+        <v>0.3924222222222223</v>
+      </c>
     </row>
     <row r="491">
-      <c r="O491" t="n">
+      <c r="O491" s="10" t="n">
         <v>0.36053</v>
       </c>
+      <c r="P491" t="n">
+        <v>0.39195</v>
+      </c>
     </row>
     <row r="492">
-      <c r="O492" t="n">
+      <c r="O492" s="10" t="n">
         <v>0.37565</v>
       </c>
+      <c r="P492" t="n">
+        <v>0.3808</v>
+      </c>
     </row>
     <row r="493">
-      <c r="O493" t="n">
+      <c r="O493" s="10" t="n">
         <v>0.3728777777777778</v>
       </c>
+      <c r="P493" t="n">
+        <v>0.389425</v>
+      </c>
     </row>
     <row r="494">
-      <c r="O494" t="n">
+      <c r="O494" s="10" t="n">
         <v>0.3743300000000001</v>
       </c>
+      <c r="P494" t="n">
+        <v>0.3714857142857143</v>
+      </c>
     </row>
     <row r="495">
-      <c r="O495" t="n">
+      <c r="O495" s="10" t="n">
         <v>0.3485</v>
       </c>
+      <c r="P495" t="n">
+        <v>0.3810142857142857</v>
+      </c>
     </row>
     <row r="496">
-      <c r="O496" t="n">
+      <c r="O496" s="10" t="n">
         <v>0.3827333333333334</v>
       </c>
+      <c r="P496" t="n">
+        <v>0.3808909090909091</v>
+      </c>
     </row>
     <row r="497">
-      <c r="O497" t="n">
+      <c r="O497" s="10" t="n">
         <v>0.3498000000000001</v>
       </c>
+      <c r="P497" t="n">
+        <v>0.3751333333333333</v>
+      </c>
     </row>
     <row r="498">
-      <c r="O498" t="n">
+      <c r="O498" s="10" t="n">
         <v>0.3585666666666667</v>
       </c>
+      <c r="P498" t="n">
+        <v>0.3777111111111111</v>
+      </c>
     </row>
     <row r="499">
-      <c r="O499" t="n">
+      <c r="O499" s="10" t="n">
         <v>0.3741888888888889</v>
       </c>
+      <c r="P499" t="n">
+        <v>0.3931166666666666</v>
+      </c>
     </row>
     <row r="500">
-      <c r="O500" t="n">
+      <c r="O500" s="10" t="n">
         <v>0.3636399999999999</v>
       </c>
+      <c r="P500" t="n">
+        <v>0.3601666666666667</v>
+      </c>
     </row>
     <row r="501">
-      <c r="O501" t="n">
+      <c r="O501" s="10" t="n">
         <v>0.3595666666666667</v>
       </c>
+      <c r="P501" t="n">
+        <v>0.36358</v>
+      </c>
     </row>
     <row r="502">
-      <c r="O502" t="n">
+      <c r="O502" s="10" t="n">
         <v>0.3753666666666666</v>
       </c>
+      <c r="P502" t="n">
+        <v>0.3882</v>
+      </c>
     </row>
     <row r="503">
-      <c r="O503" t="n">
+      <c r="O503" s="10" t="n">
         <v>0.3815000000000001</v>
       </c>
+      <c r="P503" t="n">
+        <v>0.3856125</v>
+      </c>
     </row>
     <row r="504">
-      <c r="O504" t="n">
+      <c r="O504" s="10" t="n">
         <v>0.3529875</v>
       </c>
+      <c r="P504" t="n">
+        <v>0.3849428571428571</v>
+      </c>
     </row>
     <row r="505">
-      <c r="O505" t="n">
+      <c r="O505" s="10" t="n">
         <v>0.3759</v>
       </c>
+      <c r="P505" t="n">
+        <v>0.4070666666666667</v>
+      </c>
     </row>
     <row r="506">
-      <c r="O506" t="n">
+      <c r="O506" s="10" t="n">
         <v>0.3607625</v>
       </c>
+      <c r="P506" t="n">
+        <v>0.380925</v>
+      </c>
     </row>
     <row r="507">
-      <c r="O507" t="n">
+      <c r="O507" s="10" t="n">
         <v>0.35976</v>
       </c>
+      <c r="P507" t="n">
+        <v>0.3798857142857143</v>
+      </c>
     </row>
     <row r="508">
-      <c r="O508" t="n">
+      <c r="O508" s="10" t="n">
         <v>0.3505</v>
       </c>
+      <c r="P508" t="n">
+        <v>0.4000199999999999</v>
+      </c>
     </row>
     <row r="509">
-      <c r="O509" t="n">
+      <c r="O509" s="10" t="n">
         <v>0.3702555555555556</v>
       </c>
+      <c r="P509" t="n">
+        <v>0.3834555555555557</v>
+      </c>
     </row>
     <row r="510">
-      <c r="O510" t="n">
+      <c r="O510" s="10" t="n">
         <v>0.3602900000000001</v>
       </c>
+      <c r="P510" t="n">
+        <v>0.3879111111111111</v>
+      </c>
     </row>
     <row r="511">
-      <c r="O511" t="n">
+      <c r="O511" s="10" t="n">
         <v>0.3578181818181818</v>
       </c>
+      <c r="P511" t="n">
+        <v>0.3958166666666667</v>
+      </c>
     </row>
     <row r="512">
-      <c r="O512" t="n">
+      <c r="O512" s="10" t="n">
         <v>0.3590888888888888</v>
       </c>
+      <c r="P512" t="n">
+        <v>0.3758</v>
+      </c>
     </row>
     <row r="513">
-      <c r="O513" t="n">
+      <c r="O513" s="10" t="n">
         <v>0.379875</v>
       </c>
+      <c r="P513" t="n">
+        <v>0.3948125</v>
+      </c>
     </row>
     <row r="514">
-      <c r="O514" t="n">
+      <c r="O514" s="10" t="n">
         <v>0.34928</v>
       </c>
+      <c r="P514" t="n">
+        <v>0.351375</v>
+      </c>
     </row>
     <row r="515">
-      <c r="O515" t="n">
+      <c r="O515" s="10" t="n">
         <v>0.3451222222222222</v>
       </c>
+      <c r="P515" t="n">
+        <v>0.3665142857142857</v>
+      </c>
     </row>
     <row r="516">
-      <c r="O516" t="n">
+      <c r="O516" s="10" t="n">
         <v>0.3571555555555555</v>
       </c>
+      <c r="P516" t="n">
+        <v>0.3787428571428572</v>
+      </c>
     </row>
     <row r="517">
-      <c r="O517" t="n">
+      <c r="O517" s="10" t="n">
         <v>0.3550249999999999</v>
+      </c>
+      <c r="P517" t="n">
+        <v>0.37862</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -711,7 +711,7 @@
         <v>0.103556338028169</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.159803125</v>
+        <v>0.1503263157894737</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1" s="8">
@@ -779,7 +779,7 @@
         <v>0.2109014285714285</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2039896551724138</v>
+        <v>0.1370313432835821</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1" s="8">
@@ -847,7 +847,7 @@
         <v>0.2334857142857143</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2350042857142857</v>
+        <v>0.2822538461538462</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1" s="8">
@@ -915,7 +915,7 @@
         <v>0.3046275362318841</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2935114754098361</v>
+        <v>0.3265232558139535</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" s="8">
@@ -983,7 +983,7 @@
         <v>0.3064169230769231</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4313333333333333</v>
+        <v>0.3048380952380952</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1" s="8">
@@ -1051,7 +1051,7 @@
         <v>0.4758535714285715</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.4659799999999999</v>
+        <v>0.4200117647058824</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1" s="8">
@@ -1119,7 +1119,7 @@
         <v>0.4890434782608696</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.5163555555555557</v>
+        <v>0.3645641025641025</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="8">
@@ -1187,7 +1187,7 @@
         <v>0.5618625</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.602135</v>
+        <v>0.4690476190476191</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1" s="8">
@@ -1255,7 +1255,7 @@
         <v>0.596935294117647</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.5899965517241379</v>
+        <v>0.5697461538461538</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="8">
@@ -1323,7 +1323,7 @@
         <v>0.6677971428571428</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.6510384615384616</v>
+        <v>0.6524676470588234</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="8">
@@ -1382,7 +1382,7 @@
         <v>0.6684878048780487</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.7198342857142856</v>
+        <v>0.6183310344827586</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="8">
@@ -1441,7 +1441,7 @@
         <v>0.6819565217391304</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.734604347826087</v>
+        <v>0.6850227272727273</v>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="8">
@@ -1500,7 +1500,7 @@
         <v>0.7487381818181817</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.684239393939394</v>
+        <v>0.6262787878787878</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="8">
@@ -1559,7 +1559,7 @@
         <v>0.8014029411764706</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.6608567567567567</v>
+        <v>0.7097275862068966</v>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="8">
@@ -1618,7 +1618,7 @@
         <v>0.820660465116279</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.6564714285714286</v>
+        <v>0.6938717948717948</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="8">
@@ -1677,7 +1677,7 @@
         <v>0.8246818181818182</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.7613931034482759</v>
+        <v>0.731275</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="8">
@@ -1736,7 +1736,7 @@
         <v>0.7513022727272728</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.8021241379310345</v>
+        <v>0.8297653846153847</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="8">
@@ -1795,7 +1795,7 @@
         <v>0.8123183673469389</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.7069862068965517</v>
+        <v>0.7652514285714286</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1" s="8">
@@ -1854,7 +1854,7 @@
         <v>0.7562448275862069</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.7125785714285714</v>
+        <v>0.7396179487179487</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1" s="8">
@@ -1913,7 +1913,7 @@
         <v>0.8563333333333334</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.7943826086956522</v>
+        <v>0.7673863636363637</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1" s="8">
@@ -1972,7 +1972,7 @@
         <v>0.778740625</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.8263838709677419</v>
+        <v>0.7187775000000001</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1" s="8">
@@ -2031,7 +2031,7 @@
         <v>0.8566777777777779</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.7938074074074074</v>
+        <v>0.7476266666666668</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1" s="8">
@@ -2090,7 +2090,7 @@
         <v>0.8937090909090911</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.7473170731707317</v>
+        <v>0.8238355555555554</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1" s="8">
@@ -2149,7 +2149,7 @@
         <v>0.8481799999999999</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.8510818181818183</v>
+        <v>0.833539534883721</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1" s="8">
@@ -2208,7 +2208,7 @@
         <v>0.8565853658536586</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.8030193548387097</v>
+        <v>0.809702564102564</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1" s="8">
@@ -2267,7 +2267,7 @@
         <v>0.8162160000000001</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.7269428571428571</v>
+        <v>0.76524375</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1" s="8">
@@ -2326,7 +2326,7 @@
         <v>0.8287</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.8143699999999999</v>
+        <v>0.8324634146341465</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1" s="8">
@@ -2385,7 +2385,7 @@
         <v>0.8696729166666667</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.725685294117647</v>
+        <v>0.7792032258064516</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1" s="8">
@@ -2444,7 +2444,7 @@
         <v>0.87915625</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.7663236842105263</v>
+        <v>0.8311673469387755</v>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1" s="8">
@@ -2503,7 +2503,7 @@
         <v>0.7557628571428571</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.8385117647058822</v>
+        <v>0.7618885714285716</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1" s="8">
@@ -2562,7 +2562,7 @@
         <v>0.7996833333333333</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.7050025641025641</v>
+        <v>0.8191325</v>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1" s="8">
@@ -2621,7 +2621,7 @@
         <v>0.8671486486486488</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.7323096774193548</v>
+        <v>0.8419833333333333</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1" s="8">
@@ -2680,7 +2680,7 @@
         <v>0.8657755555555555</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.6998486486486487</v>
+        <v>0.850497142857143</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1" s="8">
@@ -2739,7 +2739,7 @@
         <v>0.869174358974359</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.8530639999999999</v>
+        <v>0.7746090909090908</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1" s="8">
@@ -2798,7 +2798,7 @@
         <v>0.781051282051282</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.7993499999999999</v>
+        <v>0.7947928571428571</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1" s="8">
@@ -2857,7 +2857,7 @@
         <v>0.8639615384615384</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.82945</v>
+        <v>0.819278947368421</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="8">
@@ -2916,7 +2916,7 @@
         <v>0.8219853658536586</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.8611127659574468</v>
+        <v>0.8360870967741936</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="8">
@@ -2975,7 +2975,7 @@
         <v>0.9354263157894737</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.8543891891891893</v>
+        <v>0.8378558823529412</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="8">
@@ -3034,7 +3034,7 @@
         <v>0.9015404761904762</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.7284827586206896</v>
+        <v>0.817224</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="8">
@@ -3093,7 +3093,7 @@
         <v>0.8391812500000001</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.8153285714285714</v>
+        <v>0.7912714285714287</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1" s="8">
@@ -3152,7 +3152,7 @@
         <v>0.8947833333333334</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.7938924999999999</v>
+        <v>0.8187472222222224</v>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1" s="8">
@@ -3211,7 +3211,7 @@
         <v>0.79016</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.7618512195121953</v>
+        <v>0.7164423076923078</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1" s="8">
@@ -3270,7 +3270,7 @@
         <v>0.7948435897435899</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.8598750000000001</v>
+        <v>0.7947</v>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1" s="8">
@@ -3329,7 +3329,7 @@
         <v>0.8265454545454546</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.8435170731707318</v>
+        <v>0.8059649999999999</v>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1" s="8">
@@ -3388,7 +3388,7 @@
         <v>0.9146176470588235</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.8164730769230769</v>
+        <v>0.8694388888888888</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" s="8">
@@ -3447,7 +3447,7 @@
         <v>0.8873043478260868</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.8586612903225807</v>
+        <v>0.7681151515151515</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="8">
@@ -3506,7 +3506,7 @@
         <v>0.8472333333333334</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.7274410256410256</v>
+        <v>0.7985548387096775</v>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1" s="8">
@@ -3565,7 +3565,7 @@
         <v>0.8932710526315789</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.7854695652173914</v>
+        <v>0.7410625000000001</v>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1" s="8">
@@ -3624,7 +3624,7 @@
         <v>0.853651219512195</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.765586274509804</v>
+        <v>0.8776172413793104</v>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="8">
@@ -3683,7 +3683,7 @@
         <v>0.9081081081081082</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.7133718750000001</v>
+        <v>0.7919543478260869</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1" s="8">
@@ -3742,7 +3742,7 @@
         <v>0.9006880000000002</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.8380260869565216</v>
+        <v>0.8011666666666667</v>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1" s="8">
@@ -3801,7 +3801,7 @@
         <v>0.7787725</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.7259722222222221</v>
+        <v>0.8763342105263158</v>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1" s="8">
@@ -3860,7 +3860,7 @@
         <v>0.8484509433962264</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.7593652173913045</v>
+        <v>0.71888125</v>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1" s="8">
@@ -3919,7 +3919,7 @@
         <v>0.7833510638297871</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.8519055555555555</v>
+        <v>0.7224274999999998</v>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1" s="8">
@@ -3978,7 +3978,7 @@
         <v>0.7745192307692309</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.8299066666666667</v>
+        <v>0.8722051282051283</v>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1" s="8">
@@ -4037,7 +4037,7 @@
         <v>0.8875121951219513</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.830509090909091</v>
+        <v>0.8074731707317072</v>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1" s="8">
@@ -4096,7 +4096,7 @@
         <v>0.8809921052631579</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.7933694444444445</v>
+        <v>0.7406347826086958</v>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1" s="8">
@@ -4155,7 +4155,7 @@
         <v>0.8298769230769231</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.8132888888888888</v>
+        <v>0.8017111111111112</v>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1" s="8">
@@ -4214,7 +4214,7 @@
         <v>0.8344282608695651</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.8071575</v>
+        <v>0.8512631578947368</v>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1" s="8">
@@ -4273,7 +4273,7 @@
         <v>0.843491304347826</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.8122473684210526</v>
+        <v>0.7684000000000001</v>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1" s="8">
@@ -4332,7 +4332,7 @@
         <v>0.7752325</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.8093854166666667</v>
+        <v>0.7363871794871795</v>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1" s="8">
@@ -4391,7 +4391,7 @@
         <v>0.9436777777777778</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.7376400000000001</v>
+        <v>0.804758</v>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1" s="8">
@@ -4450,7 +4450,7 @@
         <v>0.8873340425531916</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.8077414634146343</v>
+        <v>0.823209375</v>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1" s="8">
@@ -4509,7 +4509,7 @@
         <v>0.9132740740740741</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.8568666666666667</v>
+        <v>0.8456238095238094</v>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1" s="8">
@@ -4568,7 +4568,7 @@
         <v>0.7655272727272727</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.7480545454545454</v>
+        <v>0.8573868421052629</v>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1" s="8">
@@ -4627,7 +4627,7 @@
         <v>0.8720675675675674</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.823546875</v>
+        <v>0.8333857142857143</v>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1" s="8">
@@ -4686,7 +4686,7 @@
         <v>0.8107264705882352</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.7913300000000001</v>
+        <v>0.8163066666666666</v>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1" s="8">
@@ -4745,7 +4745,7 @@
         <v>0.8971153846153845</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.8463605263157895</v>
+        <v>0.8520303030303029</v>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1" s="8">
@@ -4804,7 +4804,7 @@
         <v>0.8625869565217392</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.8910027027027028</v>
+        <v>0.6898043478260869</v>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1" s="8">
@@ -4863,7 +4863,7 @@
         <v>0.8338537037037037</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.8553147058823529</v>
+        <v>0.6442952380952381</v>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1" s="8">
@@ -4922,7 +4922,7 @@
         <v>0.9103166666666667</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.7979866666666666</v>
+        <v>0.8359</v>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1" s="8">
@@ -4981,7 +4981,7 @@
         <v>0.8054410256410256</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.8430837837837838</v>
+        <v>0.7940199999999998</v>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1" s="8">
@@ -5040,7 +5040,7 @@
         <v>0.8790905660377357</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.7673428571428572</v>
+        <v>0.829121212121212</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1" s="8">
@@ -5099,7 +5099,7 @@
         <v>0.8092034482758621</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.7807780487804877</v>
+        <v>0.8609709677419355</v>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1" s="8">
@@ -5158,7 +5158,7 @@
         <v>0.9282400000000001</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.808092105263158</v>
+        <v>0.8138607142857143</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1" s="8">
@@ -5217,7 +5217,7 @@
         <v>0.8228673913043478</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.8468450000000001</v>
+        <v>0.796008</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1" s="8">
@@ -5276,7 +5276,7 @@
         <v>0.7999391304347825</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.8278777777777779</v>
+        <v>0.7934555555555556</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1" s="8">
@@ -5335,7 +5335,7 @@
         <v>0.879858064516129</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.8348051282051281</v>
+        <v>0.7808673913043478</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1" s="8">
@@ -5394,7 +5394,7 @@
         <v>0.936175</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.7512119047619049</v>
+        <v>0.7231868421052632</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1" s="8">
@@ -5453,7 +5453,7 @@
         <v>0.7749199999999999</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.7963552631578947</v>
+        <v>0.8570974999999998</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1" s="8">
@@ -5512,7 +5512,7 @@
         <v>0.8494488888888889</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.7476277777777778</v>
+        <v>0.7442029411764706</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1" s="8">
@@ -5571,7 +5571,7 @@
         <v>0.9170520833333334</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.82945</v>
+        <v>0.7758206896551724</v>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1" s="8">
@@ -5630,7 +5630,7 @@
         <v>0.8021333333333334</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.8618076923076924</v>
+        <v>0.80975</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1" s="8">
@@ -5689,7 +5689,7 @@
         <v>0.8394657142857144</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.8034052631578947</v>
+        <v>0.8153874999999999</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1" s="8">
@@ -5748,7 +5748,7 @@
         <v>0.858904347826087</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.8503233333333333</v>
+        <v>0.7818152173913044</v>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1" s="8">
@@ -5807,7 +5807,7 @@
         <v>0.7943088235294118</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.8276446808510639</v>
+        <v>0.7884325581395348</v>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1" s="8">
@@ -5866,7 +5866,7 @@
         <v>0.8757400000000001</v>
       </c>
       <c r="AA91" t="n">
-        <v>0.7633962962962964</v>
+        <v>0.8589088888888889</v>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1" s="8">
@@ -5925,7 +5925,7 @@
         <v>0.9223026315789475</v>
       </c>
       <c r="AA92" t="n">
-        <v>0.7699500000000001</v>
+        <v>0.7775310344827585</v>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1" s="8">
@@ -5984,7 +5984,7 @@
         <v>0.8183372093023256</v>
       </c>
       <c r="AA93" t="n">
-        <v>0.8317055555555555</v>
+        <v>0.8064666666666667</v>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1" s="8">
@@ -6043,7 +6043,7 @@
         <v>0.8008088888888888</v>
       </c>
       <c r="AA94" t="n">
-        <v>0.83855</v>
+        <v>0.75695</v>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1" s="8">
@@ -6102,7 +6102,7 @@
         <v>0.8087625000000001</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.71859375</v>
+        <v>0.7976933333333334</v>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1" s="8">
@@ -6161,7 +6161,7 @@
         <v>0.917834375</v>
       </c>
       <c r="AA96" t="n">
-        <v>0.8319384615384615</v>
+        <v>0.863455882352941</v>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1" s="8">
@@ -6220,7 +6220,7 @@
         <v>0.823058</v>
       </c>
       <c r="AA97" t="n">
-        <v>0.8275488888888889</v>
+        <v>0.8395789473684211</v>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1" s="8">
@@ -6279,7 +6279,7 @@
         <v>0.865326923076923</v>
       </c>
       <c r="AA98" t="n">
-        <v>0.812552380952381</v>
+        <v>0.685928947368421</v>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1" s="8">
@@ -6338,7 +6338,7 @@
         <v>0.8112428571428573</v>
       </c>
       <c r="AA99" t="n">
-        <v>0.7946142857142857</v>
+        <v>0.8575571428571427</v>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1" s="8">
@@ -6397,7 +6397,7 @@
         <v>0.8017000000000001</v>
       </c>
       <c r="AA100" t="n">
-        <v>0.8114375</v>
+        <v>0.8421500000000001</v>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1" s="8">
@@ -6456,7 +6456,7 @@
         <v>0.8494071428571427</v>
       </c>
       <c r="AA101" t="n">
-        <v>0.8525692307692309</v>
+        <v>0.8254195121951219</v>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1" s="8">
@@ -6515,7 +6515,7 @@
         <v>0.8558675675675677</v>
       </c>
       <c r="AA102" t="n">
-        <v>0.8629249999999999</v>
+        <v>0.82172</v>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1" s="8">
@@ -6574,7 +6574,7 @@
         <v>0.807334</v>
       </c>
       <c r="AA103" t="n">
-        <v>0.8592333333333334</v>
+        <v>0.8741260869565216</v>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1" s="8">
@@ -6633,7 +6633,7 @@
         <v>0.8502645833333332</v>
       </c>
       <c r="AA104" t="n">
-        <v>0.8402444444444442</v>
+        <v>0.7542333333333333</v>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1" s="8">
@@ -6793,7 +6793,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="AA109" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1" s="8">
@@ -6861,7 +6861,7 @@
         <v>0.6</v>
       </c>
       <c r="AA110" t="n">
-        <v>0.8</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1" s="8">
@@ -6929,7 +6929,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AA111" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1" s="8">
@@ -6997,7 +6997,7 @@
         <v>0.6</v>
       </c>
       <c r="AA112" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="113" ht="16" customHeight="1" s="8">
@@ -7133,7 +7133,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AA114" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1" s="8">
@@ -7201,7 +7201,7 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="AA115" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1" s="8">
@@ -7269,7 +7269,7 @@
         <v>0.7</v>
       </c>
       <c r="AA116" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1" s="8">
@@ -7337,7 +7337,7 @@
         <v>0.9230769230769231</v>
       </c>
       <c r="AA117" t="n">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1" s="8">
@@ -7393,7 +7393,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AA118" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1" s="8">
@@ -7452,7 +7452,7 @@
         <v>1</v>
       </c>
       <c r="AA119" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1" s="8">
@@ -7511,7 +7511,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AA120" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1" s="8">
@@ -7570,7 +7570,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AA121" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1" s="8">
@@ -7629,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="AA122" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" ht="16" customHeight="1" s="8">
@@ -7688,7 +7688,7 @@
         <v>1</v>
       </c>
       <c r="AA123" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" ht="16" customHeight="1" s="8">
@@ -7747,7 +7747,7 @@
         <v>1</v>
       </c>
       <c r="AA124" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" ht="16" customHeight="1" s="8">
@@ -7806,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="AA125" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" ht="16" customHeight="1" s="8">
@@ -8042,7 +8042,7 @@
         <v>1</v>
       </c>
       <c r="AA129" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" ht="16" customHeight="1" s="8">
@@ -8101,7 +8101,7 @@
         <v>1</v>
       </c>
       <c r="AA130" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" ht="16" customHeight="1" s="8">
@@ -8160,7 +8160,7 @@
         <v>1</v>
       </c>
       <c r="AA131" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" ht="16" customHeight="1" s="8">
@@ -8219,7 +8219,7 @@
         <v>1</v>
       </c>
       <c r="AA132" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" ht="16" customHeight="1" s="8">
@@ -8337,7 +8337,7 @@
         <v>1</v>
       </c>
       <c r="AA134" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" ht="16" customHeight="1" s="8">
@@ -8514,7 +8514,7 @@
         <v>1</v>
       </c>
       <c r="AA137" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" ht="16" customHeight="1" s="8">
@@ -8632,7 +8632,7 @@
         <v>1</v>
       </c>
       <c r="AA139" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1" s="8">
@@ -8688,7 +8688,7 @@
         <v>1</v>
       </c>
       <c r="AA140" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" ht="16" customHeight="1" s="8">
@@ -8747,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="AA141" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" ht="16" customHeight="1" s="8">
@@ -8806,7 +8806,7 @@
         <v>1</v>
       </c>
       <c r="AA142" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" ht="16" customHeight="1" s="8">
@@ -8921,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="AA144" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" ht="16" customHeight="1" s="8">
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="AA145" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" ht="16" customHeight="1" s="8">
@@ -9039,7 +9039,7 @@
         <v>1</v>
       </c>
       <c r="AA146" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" ht="16" customHeight="1" s="8">
@@ -9098,7 +9098,7 @@
         <v>1</v>
       </c>
       <c r="AA147" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" ht="16" customHeight="1" s="8">
@@ -9157,7 +9157,7 @@
         <v>1</v>
       </c>
       <c r="AA148" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" ht="16" customHeight="1" s="8">
@@ -9216,7 +9216,7 @@
         <v>1</v>
       </c>
       <c r="AA149" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" ht="16" customHeight="1" s="8">
@@ -9275,7 +9275,7 @@
         <v>1</v>
       </c>
       <c r="AA150" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" ht="16" customHeight="1" s="8">
@@ -9334,7 +9334,7 @@
         <v>1</v>
       </c>
       <c r="AA151" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" ht="16" customHeight="1" s="8">
@@ -9393,7 +9393,7 @@
         <v>1</v>
       </c>
       <c r="AA152" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" ht="16" customHeight="1" s="8">
@@ -9511,7 +9511,7 @@
         <v>1</v>
       </c>
       <c r="AA154" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" ht="16" customHeight="1" s="8">
@@ -9629,7 +9629,7 @@
         <v>1</v>
       </c>
       <c r="AA156" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" ht="16" customHeight="1" s="8">
@@ -9688,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="AA157" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" ht="16" customHeight="1" s="8">
@@ -9747,7 +9747,7 @@
         <v>1</v>
       </c>
       <c r="AA158" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" ht="16" customHeight="1" s="8">
@@ -9806,7 +9806,7 @@
         <v>1</v>
       </c>
       <c r="AA159" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" ht="16" customHeight="1" s="8">
@@ -9865,7 +9865,7 @@
         <v>1</v>
       </c>
       <c r="AA160" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" ht="16" customHeight="1" s="8">
@@ -9924,7 +9924,7 @@
         <v>1</v>
       </c>
       <c r="AA161" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" ht="16" customHeight="1" s="8">
@@ -9983,7 +9983,7 @@
         <v>1</v>
       </c>
       <c r="AA162" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" ht="16" customHeight="1" s="8">
@@ -10042,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="AA163" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" ht="16" customHeight="1" s="8">
@@ -10101,7 +10101,7 @@
         <v>1</v>
       </c>
       <c r="AA164" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" ht="16" customHeight="1" s="8">
@@ -10160,7 +10160,7 @@
         <v>1</v>
       </c>
       <c r="AA165" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" ht="16" customHeight="1" s="8">
@@ -10219,7 +10219,7 @@
         <v>1</v>
       </c>
       <c r="AA166" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" ht="16" customHeight="1" s="8">
@@ -10278,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="AA167" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" ht="16" customHeight="1" s="8">
@@ -10396,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="AA169" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" ht="16" customHeight="1" s="8">
@@ -10455,7 +10455,7 @@
         <v>1</v>
       </c>
       <c r="AA170" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" ht="16" customHeight="1" s="8">
@@ -10632,7 +10632,7 @@
         <v>1</v>
       </c>
       <c r="AA173" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" ht="16" customHeight="1" s="8">
@@ -10986,7 +10986,7 @@
         <v>1</v>
       </c>
       <c r="AA179" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" ht="16" customHeight="1" s="8">
@@ -11101,7 +11101,7 @@
         <v>1</v>
       </c>
       <c r="AA181" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" ht="16" customHeight="1" s="8">
@@ -11160,7 +11160,7 @@
         <v>1</v>
       </c>
       <c r="AA182" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" ht="16" customHeight="1" s="8">
@@ -11573,7 +11573,7 @@
         <v>1</v>
       </c>
       <c r="AA189" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" ht="16" customHeight="1" s="8">
@@ -11632,7 +11632,7 @@
         <v>1</v>
       </c>
       <c r="AA190" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" ht="16" customHeight="1" s="8">
@@ -11809,7 +11809,7 @@
         <v>1</v>
       </c>
       <c r="AA193" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" ht="16" customHeight="1" s="8">
@@ -11986,7 +11986,7 @@
         <v>1</v>
       </c>
       <c r="AA196" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" ht="16" customHeight="1" s="8">
@@ -12045,7 +12045,7 @@
         <v>1</v>
       </c>
       <c r="AA197" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" ht="16" customHeight="1" s="8">
@@ -12104,7 +12104,7 @@
         <v>1</v>
       </c>
       <c r="AA198" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" ht="16" customHeight="1" s="8">
@@ -12163,7 +12163,7 @@
         <v>1</v>
       </c>
       <c r="AA199" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" ht="16" customHeight="1" s="8">
@@ -12222,7 +12222,7 @@
         <v>1</v>
       </c>
       <c r="AA200" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" ht="16" customHeight="1" s="8">
@@ -12281,7 +12281,7 @@
         <v>1</v>
       </c>
       <c r="AA201" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" ht="16" customHeight="1" s="8">
@@ -12340,7 +12340,7 @@
         <v>1</v>
       </c>
       <c r="AA202" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" ht="16" customHeight="1" s="8">
@@ -12458,7 +12458,7 @@
         <v>1</v>
       </c>
       <c r="AA204" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" ht="16" customHeight="1" s="8">
@@ -12517,7 +12517,7 @@
         <v>1</v>
       </c>
       <c r="AA205" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" ht="16" customHeight="1" s="8">
@@ -12576,7 +12576,7 @@
         <v>1</v>
       </c>
       <c r="AA206" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" ht="16" customHeight="1" s="8">
@@ -12727,7 +12727,7 @@
         <v>0.9604499999999999</v>
       </c>
       <c r="AA212" t="n">
-        <v>0.9446714285714286</v>
+        <v>0.9589999999999999</v>
       </c>
     </row>
     <row r="213" ht="16" customHeight="1" s="8">
@@ -12795,7 +12795,7 @@
         <v>0.921225</v>
       </c>
       <c r="AA213" t="n">
-        <v>0.9247571428571428</v>
+        <v>0.9613400000000001</v>
       </c>
     </row>
     <row r="214" ht="16" customHeight="1" s="8">
@@ -12863,7 +12863,7 @@
         <v>0.9586400000000002</v>
       </c>
       <c r="AA214" t="n">
-        <v>0.9516499999999999</v>
+        <v>0.7975166666666667</v>
       </c>
     </row>
     <row r="215" ht="16" customHeight="1" s="8">
@@ -12931,7 +12931,7 @@
         <v>0.9305</v>
       </c>
       <c r="AA215" t="n">
-        <v>0.9102</v>
+        <v>0.8271750000000001</v>
       </c>
     </row>
     <row r="216" ht="16" customHeight="1" s="8">
@@ -12999,7 +12999,7 @@
         <v>0.9410166666666666</v>
       </c>
       <c r="AA216" t="n">
-        <v>0.9383833333333333</v>
+        <v>0.8929888888888888</v>
       </c>
     </row>
     <row r="217" ht="16" customHeight="1" s="8">
@@ -13067,7 +13067,7 @@
         <v>0.77655</v>
       </c>
       <c r="AA217" t="n">
-        <v>0.8288125</v>
+        <v>0.6562166666666668</v>
       </c>
     </row>
     <row r="218" ht="16" customHeight="1" s="8">
@@ -13135,7 +13135,7 @@
         <v>0.5885142857142858</v>
       </c>
       <c r="AA218" t="n">
-        <v>0.5633285714285715</v>
+        <v>0.7219272727272729</v>
       </c>
     </row>
     <row r="219" ht="16" customHeight="1" s="8">
@@ -13203,7 +13203,7 @@
         <v>0.8728142857142858</v>
       </c>
       <c r="AA219" t="n">
-        <v>0.6662666666666667</v>
+        <v>0.6075</v>
       </c>
     </row>
     <row r="220" ht="16" customHeight="1" s="8">
@@ -13271,7 +13271,7 @@
         <v>0.8415166666666666</v>
       </c>
       <c r="AA220" t="n">
-        <v>0.6883222222222223</v>
+        <v>0.5728727272727273</v>
       </c>
     </row>
     <row r="221" ht="16" customHeight="1" s="8">
@@ -13339,7 +13339,7 @@
         <v>0.6889666666666666</v>
       </c>
       <c r="AA221" t="n">
-        <v>0.7597555555555555</v>
+        <v>0.4577222222222223</v>
       </c>
     </row>
     <row r="222" ht="16" customHeight="1" s="8">
@@ -13395,7 +13395,7 @@
         <v>0.7400285714285714</v>
       </c>
       <c r="AA222" t="n">
-        <v>0.8287374999999999</v>
+        <v>0.8120375000000001</v>
       </c>
     </row>
     <row r="223" ht="16" customHeight="1" s="8">
@@ -13454,7 +13454,7 @@
         <v>0.5814</v>
       </c>
       <c r="AA223" t="n">
-        <v>0.8856454545454546</v>
+        <v>0.6921999999999999</v>
       </c>
     </row>
     <row r="224" ht="16" customHeight="1" s="8">
@@ -13513,7 +13513,7 @@
         <v>0.6781700000000001</v>
       </c>
       <c r="AA224" t="n">
-        <v>0.62133</v>
+        <v>0.5952142857142857</v>
       </c>
     </row>
     <row r="225" ht="16" customHeight="1" s="8">
@@ -13572,7 +13572,7 @@
         <v>0.6407571428571428</v>
       </c>
       <c r="AA225" t="n">
-        <v>0.6850916666666667</v>
+        <v>0.7197545454545454</v>
       </c>
     </row>
     <row r="226" ht="16" customHeight="1" s="8">
@@ -13631,7 +13631,7 @@
         <v>0.4694333333333333</v>
       </c>
       <c r="AA226" t="n">
-        <v>0.76187</v>
+        <v>0.6146499999999999</v>
       </c>
     </row>
     <row r="227" ht="16" customHeight="1" s="8">
@@ -13690,7 +13690,7 @@
         <v>0.7830666666666666</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.7148600000000001</v>
+        <v>0.7538181818181816</v>
       </c>
     </row>
     <row r="228" ht="16" customHeight="1" s="8">
@@ -13749,7 +13749,7 @@
         <v>0.7216333333333332</v>
       </c>
       <c r="AA228" t="n">
-        <v>0.8703749999999998</v>
+        <v>0.6402777777777778</v>
       </c>
     </row>
     <row r="229" ht="16" customHeight="1" s="8">
@@ -13808,7 +13808,7 @@
         <v>0.6610833333333332</v>
       </c>
       <c r="AA229" t="n">
-        <v>0.7953300000000001</v>
+        <v>0.65245</v>
       </c>
     </row>
     <row r="230" ht="16" customHeight="1" s="8">
@@ -13867,7 +13867,7 @@
         <v>0.7928909090909091</v>
       </c>
       <c r="AA230" t="n">
-        <v>0.6503</v>
+        <v>0.499675</v>
       </c>
     </row>
     <row r="231" ht="16" customHeight="1" s="8">
@@ -13926,7 +13926,7 @@
         <v>0.6842</v>
       </c>
       <c r="AA231" t="n">
-        <v>0.674025</v>
+        <v>0.6245857142857142</v>
       </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="8">
@@ -13985,7 +13985,7 @@
         <v>0.7787000000000001</v>
       </c>
       <c r="AA232" t="n">
-        <v>0.7153636363636363</v>
+        <v>0.5972222222222222</v>
       </c>
     </row>
     <row r="233" ht="16" customHeight="1" s="8">
@@ -14044,7 +14044,7 @@
         <v>0.5124833333333333</v>
       </c>
       <c r="AA233" t="n">
-        <v>0.7777250000000001</v>
+        <v>0.563790909090909</v>
       </c>
     </row>
     <row r="234" ht="16" customHeight="1" s="8">
@@ -14103,7 +14103,7 @@
         <v>0.72365</v>
       </c>
       <c r="AA234" t="n">
-        <v>0.7695636363636363</v>
+        <v>0.7048222222222221</v>
       </c>
     </row>
     <row r="235" ht="16" customHeight="1" s="8">
@@ -14162,7 +14162,7 @@
         <v>0.6020142857142857</v>
       </c>
       <c r="AA235" t="n">
-        <v>0.7653416666666666</v>
+        <v>0.6388125</v>
       </c>
     </row>
     <row r="236" ht="16" customHeight="1" s="8">
@@ -14221,7 +14221,7 @@
         <v>0.7853222222222223</v>
       </c>
       <c r="AA236" t="n">
-        <v>0.7935800000000001</v>
+        <v>0.8177875</v>
       </c>
     </row>
     <row r="237" ht="16" customHeight="1" s="8">
@@ -14280,7 +14280,7 @@
         <v>0.4809285714285715</v>
       </c>
       <c r="AA237" t="n">
-        <v>0.6731199999999999</v>
+        <v>0.7290777777777779</v>
       </c>
     </row>
     <row r="238" ht="16" customHeight="1" s="8">
@@ -14339,7 +14339,7 @@
         <v>0.8669000000000001</v>
       </c>
       <c r="AA238" t="n">
-        <v>0.70657</v>
+        <v>0.6530444444444445</v>
       </c>
     </row>
     <row r="239" ht="16" customHeight="1" s="8">
@@ -14398,7 +14398,7 @@
         <v>0.6245333333333334</v>
       </c>
       <c r="AA239" t="n">
-        <v>0.7953181818181818</v>
+        <v>0.5757272727272728</v>
       </c>
     </row>
     <row r="240" ht="16" customHeight="1" s="8">
@@ -14457,7 +14457,7 @@
         <v>0.66613</v>
       </c>
       <c r="AA240" t="n">
-        <v>0.6883250000000002</v>
+        <v>0.4133</v>
       </c>
     </row>
     <row r="241" ht="16" customHeight="1" s="8">
@@ -14516,7 +14516,7 @@
         <v>0.7665333333333334</v>
       </c>
       <c r="AA241" t="n">
-        <v>0.7533769230769229</v>
+        <v>0.4657333333333333</v>
       </c>
     </row>
     <row r="242" ht="16" customHeight="1" s="8">
@@ -14575,7 +14575,7 @@
         <v>0.7538285714285714</v>
       </c>
       <c r="AA242" t="n">
-        <v>0.83</v>
+        <v>0.3931444444444445</v>
       </c>
     </row>
     <row r="243" ht="16" customHeight="1" s="8">
@@ -14634,7 +14634,7 @@
         <v>0.6245142857142858</v>
       </c>
       <c r="AA243" t="n">
-        <v>0.845009090909091</v>
+        <v>0.7176999999999999</v>
       </c>
     </row>
     <row r="244" ht="16" customHeight="1" s="8">
@@ -14690,7 +14690,7 @@
         <v>0.7220142857142857</v>
       </c>
       <c r="AA244" t="n">
-        <v>0.8481166666666665</v>
+        <v>0.65104</v>
       </c>
     </row>
     <row r="245" ht="16" customHeight="1" s="8">
@@ -14749,7 +14749,7 @@
         <v>0.6247916666666666</v>
       </c>
       <c r="AA245" t="n">
-        <v>0.8013384615384616</v>
+        <v>0.4791142857142857</v>
       </c>
     </row>
     <row r="246" ht="16" customHeight="1" s="8">
@@ -14808,7 +14808,7 @@
         <v>0.7158181818181819</v>
       </c>
       <c r="AA246" t="n">
-        <v>0.8886444444444445</v>
+        <v>0.5206222222222222</v>
       </c>
     </row>
     <row r="247" ht="16" customHeight="1" s="8">
@@ -14864,7 +14864,7 @@
         <v>0.6883111111111111</v>
       </c>
       <c r="AA247" t="n">
-        <v>0.82006</v>
+        <v>0.67815</v>
       </c>
     </row>
     <row r="248" ht="16" customHeight="1" s="8">
@@ -14923,7 +14923,7 @@
         <v>0.5952555555555555</v>
       </c>
       <c r="AA248" t="n">
-        <v>0.8447000000000001</v>
+        <v>0.770009090909091</v>
       </c>
     </row>
     <row r="249" ht="16" customHeight="1" s="8">
@@ -14982,7 +14982,7 @@
         <v>0.69333</v>
       </c>
       <c r="AA249" t="n">
-        <v>0.8671818181818182</v>
+        <v>0.4843818181818182</v>
       </c>
     </row>
     <row r="250" ht="16" customHeight="1" s="8">
@@ -15041,7 +15041,7 @@
         <v>0.57575</v>
       </c>
       <c r="AA250" t="n">
-        <v>0.9107083333333333</v>
+        <v>0.5959700000000001</v>
       </c>
     </row>
     <row r="251" ht="16" customHeight="1" s="8">
@@ -15100,7 +15100,7 @@
         <v>0.6855</v>
       </c>
       <c r="AA251" t="n">
-        <v>0.8540199999999999</v>
+        <v>0.74593</v>
       </c>
     </row>
     <row r="252" ht="16" customHeight="1" s="8">
@@ -15159,7 +15159,7 @@
         <v>0.5016875000000001</v>
       </c>
       <c r="AA252" t="n">
-        <v>0.9269545454545455</v>
+        <v>0.5476222222222222</v>
       </c>
     </row>
     <row r="253" ht="16" customHeight="1" s="8">
@@ -15218,7 +15218,7 @@
         <v>0.5528857142857143</v>
       </c>
       <c r="AA253" t="n">
-        <v>0.8973363636363636</v>
+        <v>0.6644222222222222</v>
       </c>
     </row>
     <row r="254" ht="16" customHeight="1" s="8">
@@ -15277,7 +15277,7 @@
         <v>0.4901714285714286</v>
       </c>
       <c r="AA254" t="n">
-        <v>0.8987499999999999</v>
+        <v>0.7835333333333333</v>
       </c>
     </row>
     <row r="255" ht="16" customHeight="1" s="8">
@@ -15336,7 +15336,7 @@
         <v>0.633975</v>
       </c>
       <c r="AA255" t="n">
-        <v>0.90962</v>
+        <v>0.5727375</v>
       </c>
     </row>
     <row r="256" ht="16" customHeight="1" s="8">
@@ -15395,7 +15395,7 @@
         <v>0.4669666666666667</v>
       </c>
       <c r="AA256" t="n">
-        <v>0.9201999999999999</v>
+        <v>0.56565</v>
       </c>
     </row>
     <row r="257" ht="16" customHeight="1" s="8">
@@ -15454,7 +15454,7 @@
         <v>0.5381166666666667</v>
       </c>
       <c r="AA257" t="n">
-        <v>0.9230818181818183</v>
+        <v>0.6419999999999999</v>
       </c>
     </row>
     <row r="258" ht="16" customHeight="1" s="8">
@@ -15513,7 +15513,7 @@
         <v>0.51522</v>
       </c>
       <c r="AA258" t="n">
-        <v>0.8860272727272726</v>
+        <v>0.4525625</v>
       </c>
     </row>
     <row r="259" ht="16" customHeight="1" s="8">
@@ -15572,7 +15572,7 @@
         <v>0.6206666666666667</v>
       </c>
       <c r="AA259" t="n">
-        <v>0.8806</v>
+        <v>0.55225</v>
       </c>
     </row>
     <row r="260" ht="16" customHeight="1" s="8">
@@ -15631,7 +15631,7 @@
         <v>0.5560444444444445</v>
       </c>
       <c r="AA260" t="n">
-        <v>0.8958615384615385</v>
+        <v>0.6992636363636365</v>
       </c>
     </row>
     <row r="261" ht="16" customHeight="1" s="8">
@@ -15690,7 +15690,7 @@
         <v>0.6426545454545454</v>
       </c>
       <c r="AA261" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.5652099999999999</v>
       </c>
     </row>
     <row r="262" ht="16" customHeight="1" s="8">
@@ -15749,7 +15749,7 @@
         <v>0.6213333333333334</v>
       </c>
       <c r="AA262" t="n">
-        <v>0.87224</v>
+        <v>0.7332599999999999</v>
       </c>
     </row>
     <row r="263" ht="16" customHeight="1" s="8">
@@ -15808,7 +15808,7 @@
         <v>0.5230499999999999</v>
       </c>
       <c r="AA263" t="n">
-        <v>0.8851</v>
+        <v>0.6323923076923077</v>
       </c>
     </row>
     <row r="264" ht="16" customHeight="1" s="8">
@@ -15867,7 +15867,7 @@
         <v>0.7114200000000001</v>
       </c>
       <c r="AA264" t="n">
-        <v>0.9206083333333335</v>
+        <v>0.5804555555555555</v>
       </c>
     </row>
     <row r="265" ht="16" customHeight="1" s="8">
@@ -15926,7 +15926,7 @@
         <v>0.5777</v>
       </c>
       <c r="AA265" t="n">
-        <v>0.8815181818181818</v>
+        <v>0.5861799999999999</v>
       </c>
     </row>
     <row r="266" ht="16" customHeight="1" s="8">
@@ -15985,7 +15985,7 @@
         <v>0.6360625</v>
       </c>
       <c r="AA266" t="n">
-        <v>0.8662416666666667</v>
+        <v>0.6159333333333333</v>
       </c>
     </row>
     <row r="267" ht="16" customHeight="1" s="8">
@@ -16044,7 +16044,7 @@
         <v>0.5738375</v>
       </c>
       <c r="AA267" t="n">
-        <v>0.9477833333333333</v>
+        <v>0.601075</v>
       </c>
     </row>
     <row r="268" ht="16" customHeight="1" s="8">
@@ -16103,7 +16103,7 @@
         <v>0.6311125000000001</v>
       </c>
       <c r="AA268" t="n">
-        <v>0.9048769230769231</v>
+        <v>0.6919636363636363</v>
       </c>
     </row>
     <row r="269" ht="16" customHeight="1" s="8">
@@ -16162,7 +16162,7 @@
         <v>0.6063222222222222</v>
       </c>
       <c r="AA269" t="n">
-        <v>0.9123249999999999</v>
+        <v>0.7020999999999999</v>
       </c>
     </row>
     <row r="270" ht="16" customHeight="1" s="8">
@@ -16221,7 +16221,7 @@
         <v>0.499325</v>
       </c>
       <c r="AA270" t="n">
-        <v>0.89276</v>
+        <v>0.6463857142857143</v>
       </c>
     </row>
     <row r="271" ht="16" customHeight="1" s="8">
@@ -16280,7 +16280,7 @@
         <v>0.7702000000000001</v>
       </c>
       <c r="AA271" t="n">
-        <v>0.9616545454545453</v>
+        <v>0.6303</v>
       </c>
     </row>
     <row r="272" ht="16" customHeight="1" s="8">
@@ -16339,7 +16339,7 @@
         <v>0.4498555555555556</v>
       </c>
       <c r="AA272" t="n">
-        <v>0.9318000000000001</v>
+        <v>0.509725</v>
       </c>
     </row>
     <row r="273" ht="16" customHeight="1" s="8">
@@ -16398,7 +16398,7 @@
         <v>0.57734</v>
       </c>
       <c r="AA273" t="n">
-        <v>0.9306272727272726</v>
+        <v>0.7052142857142858</v>
       </c>
     </row>
     <row r="274" ht="16" customHeight="1" s="8">
@@ -16457,7 +16457,7 @@
         <v>0.6010000000000001</v>
       </c>
       <c r="AA274" t="n">
-        <v>0.9144615384615384</v>
+        <v>0.6361699999999999</v>
       </c>
     </row>
     <row r="275" ht="16" customHeight="1" s="8">
@@ -16516,7 +16516,7 @@
         <v>0.4734222222222222</v>
       </c>
       <c r="AA275" t="n">
-        <v>0.8955636363636366</v>
+        <v>0.7335111111111111</v>
       </c>
     </row>
     <row r="276" ht="16" customHeight="1" s="8">
@@ -16575,7 +16575,7 @@
         <v>0.6892142857142858</v>
       </c>
       <c r="AA276" t="n">
-        <v>0.7797571428571428</v>
+        <v>0.7299099999999999</v>
       </c>
     </row>
     <row r="277" ht="16" customHeight="1" s="8">
@@ -16634,7 +16634,7 @@
         <v>0.5299166666666667</v>
       </c>
       <c r="AA277" t="n">
-        <v>0.9003181818181818</v>
+        <v>0.7526999999999999</v>
       </c>
     </row>
     <row r="278" ht="16" customHeight="1" s="8">
@@ -16693,7 +16693,7 @@
         <v>0.6238571428571429</v>
       </c>
       <c r="AA278" t="n">
-        <v>0.8971615384615385</v>
+        <v>0.5824800000000001</v>
       </c>
     </row>
     <row r="279" ht="16" customHeight="1" s="8">
@@ -16752,7 +16752,7 @@
         <v>0.6045285714285714</v>
       </c>
       <c r="AA279" t="n">
-        <v>0.84863</v>
+        <v>0.6862818181818182</v>
       </c>
     </row>
     <row r="280" ht="16" customHeight="1" s="8">
@@ -16811,7 +16811,7 @@
         <v>0.6177285714285715</v>
       </c>
       <c r="AA280" t="n">
-        <v>0.934209090909091</v>
+        <v>0.6921</v>
       </c>
     </row>
     <row r="281" ht="16" customHeight="1" s="8">
@@ -16870,7 +16870,7 @@
         <v>0.6491333333333335</v>
       </c>
       <c r="AA281" t="n">
-        <v>0.8649363636363637</v>
+        <v>0.5591083333333333</v>
       </c>
     </row>
     <row r="282" ht="16" customHeight="1" s="8">
@@ -16929,7 +16929,7 @@
         <v>0.6691555555555556</v>
       </c>
       <c r="AA282" t="n">
-        <v>0.855</v>
+        <v>0.587125</v>
       </c>
     </row>
     <row r="283" ht="16" customHeight="1" s="8">
@@ -16988,7 +16988,7 @@
         <v>0.6769800000000001</v>
       </c>
       <c r="AA283" t="n">
-        <v>0.8012</v>
+        <v>0.6295555555555555</v>
       </c>
     </row>
     <row r="284" ht="16" customHeight="1" s="8">
@@ -17047,7 +17047,7 @@
         <v>0.4736111111111111</v>
       </c>
       <c r="AA284" t="n">
-        <v>0.8389625000000001</v>
+        <v>0.7339875</v>
       </c>
     </row>
     <row r="285" ht="16" customHeight="1" s="8">
@@ -17103,7 +17103,7 @@
         <v>0.5888714285714285</v>
       </c>
       <c r="AA285" t="n">
-        <v>0.8311000000000001</v>
+        <v>0.7849090909090909</v>
       </c>
     </row>
     <row r="286" ht="16" customHeight="1" s="8">
@@ -17162,7 +17162,7 @@
         <v>0.5822833333333333</v>
       </c>
       <c r="AA286" t="n">
-        <v>0.8759857142857143</v>
+        <v>0.5895875</v>
       </c>
     </row>
     <row r="287" ht="16" customHeight="1" s="8">
@@ -17221,7 +17221,7 @@
         <v>0.4322125</v>
       </c>
       <c r="AA287" t="n">
-        <v>0.9411615384615385</v>
+        <v>0.7396333333333334</v>
       </c>
     </row>
     <row r="288" ht="16" customHeight="1" s="8">
@@ -17280,7 +17280,7 @@
         <v>0.437</v>
       </c>
       <c r="AA288" t="n">
-        <v>0.86059</v>
+        <v>0.7434222222222222</v>
       </c>
     </row>
     <row r="289" ht="16" customHeight="1" s="8">
@@ -17339,7 +17339,7 @@
         <v>0.557875</v>
       </c>
       <c r="AA289" t="n">
-        <v>0.848776923076923</v>
+        <v>0.7987</v>
       </c>
     </row>
     <row r="290" ht="16" customHeight="1" s="8">
@@ -17398,7 +17398,7 @@
         <v>0.8310500000000001</v>
       </c>
       <c r="AA290" t="n">
-        <v>0.9180636363636364</v>
+        <v>0.4774625</v>
       </c>
     </row>
     <row r="291" ht="16" customHeight="1" s="8">
@@ -17457,7 +17457,7 @@
         <v>0.6517875</v>
       </c>
       <c r="AA291" t="n">
-        <v>0.8920166666666667</v>
+        <v>0.5572500000000001</v>
       </c>
     </row>
     <row r="292" ht="16" customHeight="1" s="8">
@@ -17516,7 +17516,7 @@
         <v>0.4768875</v>
       </c>
       <c r="AA292" t="n">
-        <v>0.8446000000000001</v>
+        <v>0.490725</v>
       </c>
     </row>
     <row r="293" ht="16" customHeight="1" s="8">
@@ -17575,7 +17575,7 @@
         <v>0.6599666666666667</v>
       </c>
       <c r="AA293" t="n">
-        <v>0.91235</v>
+        <v>0.5648636363636362</v>
       </c>
     </row>
     <row r="294" ht="16" customHeight="1" s="8">
@@ -17634,7 +17634,7 @@
         <v>0.6001555555555556</v>
       </c>
       <c r="AA294" t="n">
-        <v>0.8923666666666668</v>
+        <v>0.423075</v>
       </c>
     </row>
     <row r="295" ht="16" customHeight="1" s="8">
@@ -17693,7 +17693,7 @@
         <v>0.6065571428571428</v>
       </c>
       <c r="AA295" t="n">
-        <v>0.8967666666666667</v>
+        <v>0.4989727272727272</v>
       </c>
     </row>
     <row r="296" ht="16" customHeight="1" s="8">
@@ -17752,7 +17752,7 @@
         <v>0.4883142857142858</v>
       </c>
       <c r="AA296" t="n">
-        <v>0.8484700000000001</v>
+        <v>0.7508499999999999</v>
       </c>
     </row>
     <row r="297" ht="16" customHeight="1" s="8">
@@ -17811,7 +17811,7 @@
         <v>0.5488</v>
       </c>
       <c r="AA297" t="n">
-        <v>0.92295</v>
+        <v>0.5100777777777777</v>
       </c>
     </row>
     <row r="298" ht="16" customHeight="1" s="8">
@@ -17870,7 +17870,7 @@
         <v>0.56172</v>
       </c>
       <c r="AA298" t="n">
-        <v>0.8443636363636362</v>
+        <v>0.6275999999999999</v>
       </c>
     </row>
     <row r="299" ht="16" customHeight="1" s="8">
@@ -17929,7 +17929,7 @@
         <v>0.501875</v>
       </c>
       <c r="AA299" t="n">
-        <v>0.9059000000000001</v>
+        <v>0.4120666666666666</v>
       </c>
     </row>
     <row r="300" ht="16" customHeight="1" s="8">
@@ -17988,7 +17988,7 @@
         <v>0.6917181818181818</v>
       </c>
       <c r="AA300" t="n">
-        <v>0.8680923076923077</v>
+        <v>0.79434</v>
       </c>
     </row>
     <row r="301" ht="16" customHeight="1" s="8">
@@ -18047,7 +18047,7 @@
         <v>0.6568125</v>
       </c>
       <c r="AA301" t="n">
-        <v>0.92541</v>
+        <v>0.5645333333333333</v>
       </c>
     </row>
     <row r="302" ht="16" customHeight="1" s="8">
@@ -18106,7 +18106,7 @@
         <v>0.6630272727272728</v>
       </c>
       <c r="AA302" t="n">
-        <v>0.9224833333333334</v>
+        <v>0.6232</v>
       </c>
     </row>
     <row r="303" ht="16" customHeight="1" s="8">
@@ -18165,7 +18165,7 @@
         <v>0.4856</v>
       </c>
       <c r="AA303" t="n">
-        <v>0.941375</v>
+        <v>0.5212727272727273</v>
       </c>
     </row>
     <row r="304" ht="16" customHeight="1" s="8">
@@ -18224,7 +18224,7 @@
         <v>0.5725</v>
       </c>
       <c r="AA304" t="n">
-        <v>0.9108636363636363</v>
+        <v>0.4818125</v>
       </c>
     </row>
     <row r="305" ht="16" customHeight="1" s="8">
@@ -18283,7 +18283,7 @@
         <v>0.6419499999999999</v>
       </c>
       <c r="AA305" t="n">
-        <v>0.9411624999999999</v>
+        <v>0.6407999999999999</v>
       </c>
     </row>
     <row r="306" ht="16" customHeight="1" s="8">
@@ -18342,7 +18342,7 @@
         <v>0.6812874999999999</v>
       </c>
       <c r="AA306" t="n">
-        <v>0.9328</v>
+        <v>0.8015600000000001</v>
       </c>
     </row>
     <row r="307" ht="16" customHeight="1" s="8">
@@ -18401,7 +18401,7 @@
         <v>0.7117444444444446</v>
       </c>
       <c r="AA307" t="n">
-        <v>0.9402111111111111</v>
+        <v>0.5751333333333333</v>
       </c>
     </row>
     <row r="308" ht="16" customHeight="1" s="8">
@@ -18460,7 +18460,7 @@
         <v>0.6568714285714287</v>
       </c>
       <c r="AA308" t="n">
-        <v>0.932888888888889</v>
+        <v>0.4388625</v>
       </c>
     </row>
     <row r="309" ht="16" customHeight="1" s="8">
@@ -18519,7 +18519,7 @@
         <v>0.5346500000000001</v>
       </c>
       <c r="AA309" t="n">
-        <v>0.9087000000000001</v>
+        <v>0.604475</v>
       </c>
     </row>
     <row r="310" ht="16" customHeight="1" s="8">
@@ -18578,7 +18578,7 @@
         <v>0.672</v>
       </c>
       <c r="AA310" t="n">
-        <v>0.9292333333333334</v>
+        <v>0.69906</v>
       </c>
     </row>
     <row r="311" ht="16" customHeight="1" s="8">
@@ -18637,7 +18637,7 @@
         <v>0.3054444444444444</v>
       </c>
       <c r="AA311" t="n">
-        <v>0.8749454545454545</v>
+        <v>0.5989555555555555</v>
       </c>
     </row>
     <row r="314" ht="16" customHeight="1" s="8">
@@ -18729,7 +18729,7 @@
         <v>0.0089</v>
       </c>
       <c r="AA316" t="n">
-        <v>0.0107</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="317" ht="16" customHeight="1" s="8">
@@ -18797,7 +18797,7 @@
         <v>0.026</v>
       </c>
       <c r="AA317" t="n">
-        <v>0.0078</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="318" ht="16" customHeight="1" s="8">
@@ -18865,7 +18865,7 @@
         <v>0.0008</v>
       </c>
       <c r="AA318" t="n">
-        <v>0.0112</v>
+        <v>0.0593</v>
       </c>
     </row>
     <row r="319" ht="16" customHeight="1" s="8">
@@ -18933,7 +18933,7 @@
         <v>0.1005</v>
       </c>
       <c r="AA319" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1163</v>
       </c>
     </row>
     <row r="320" ht="16" customHeight="1" s="8">
@@ -19001,7 +19001,7 @@
         <v>0.008399999999999999</v>
       </c>
       <c r="AA320" t="n">
-        <v>0.0592</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="321" ht="16" customHeight="1" s="8">
@@ -19069,7 +19069,7 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="AA321" t="n">
-        <v>0.0498</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="322" ht="16" customHeight="1" s="8">
@@ -19137,7 +19137,7 @@
         <v>0.1637</v>
       </c>
       <c r="AA322" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0319</v>
       </c>
     </row>
     <row r="323" ht="16" customHeight="1" s="8">
@@ -19205,7 +19205,7 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="AA323" t="n">
-        <v>0.1557</v>
+        <v>0.0553</v>
       </c>
     </row>
     <row r="324" ht="16" customHeight="1" s="8">
@@ -19273,7 +19273,7 @@
         <v>0.0557</v>
       </c>
       <c r="AA324" t="n">
-        <v>0.2438</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="325" ht="16" customHeight="1" s="8">
@@ -19341,7 +19341,7 @@
         <v>0.1191</v>
       </c>
       <c r="AA325" t="n">
-        <v>0.1173</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="326" ht="16" customHeight="1" s="8">
@@ -19400,7 +19400,7 @@
         <v>0.1619</v>
       </c>
       <c r="AA326" t="n">
-        <v>0.5966</v>
+        <v>0.0609</v>
       </c>
     </row>
     <row r="327" ht="16" customHeight="1" s="8">
@@ -19459,7 +19459,7 @@
         <v>0.0978</v>
       </c>
       <c r="AA327" t="n">
-        <v>0.5583</v>
+        <v>0.0771</v>
       </c>
     </row>
     <row r="328" ht="16" customHeight="1" s="8">
@@ -19518,7 +19518,7 @@
         <v>0.2095</v>
       </c>
       <c r="AA328" t="n">
-        <v>0.5546</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="329" ht="16" customHeight="1" s="8">
@@ -19577,7 +19577,7 @@
         <v>0.2394</v>
       </c>
       <c r="AA329" t="n">
-        <v>0.7607</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="330" ht="16" customHeight="1" s="8">
@@ -19636,7 +19636,7 @@
         <v>0.2403</v>
       </c>
       <c r="AA330" t="n">
-        <v>0.6617</v>
+        <v>0.0593</v>
       </c>
     </row>
     <row r="331" ht="16" customHeight="1" s="8">
@@ -19695,7 +19695,7 @@
         <v>0.1884</v>
       </c>
       <c r="AA331" t="n">
-        <v>0.7612</v>
+        <v>0.0622</v>
       </c>
     </row>
     <row r="332" ht="16" customHeight="1" s="8">
@@ -19754,7 +19754,7 @@
         <v>0.1883</v>
       </c>
       <c r="AA332" t="n">
-        <v>0.7678</v>
+        <v>0.0738</v>
       </c>
     </row>
     <row r="333" ht="16" customHeight="1" s="8">
@@ -19813,7 +19813,7 @@
         <v>0.1782</v>
       </c>
       <c r="AA333" t="n">
-        <v>0.6442</v>
+        <v>0.0607</v>
       </c>
     </row>
     <row r="334" ht="16" customHeight="1" s="8">
@@ -19872,7 +19872,7 @@
         <v>0.1595</v>
       </c>
       <c r="AA334" t="n">
-        <v>0.6317</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="335" ht="16" customHeight="1" s="8">
@@ -19931,7 +19931,7 @@
         <v>0.1449</v>
       </c>
       <c r="AA335" t="n">
-        <v>0.5668</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="336" ht="16" customHeight="1" s="8">
@@ -19990,7 +19990,7 @@
         <v>0.1789</v>
       </c>
       <c r="AA336" t="n">
-        <v>0.4931</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="337" ht="16" customHeight="1" s="8">
@@ -20049,7 +20049,7 @@
         <v>0.183</v>
       </c>
       <c r="AA337" t="n">
-        <v>0.6071</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="338" ht="16" customHeight="1" s="8">
@@ -20108,7 +20108,7 @@
         <v>0.1676</v>
       </c>
       <c r="AA338" t="n">
-        <v>0.6833</v>
+        <v>0.0509</v>
       </c>
     </row>
     <row r="339" ht="16" customHeight="1" s="8">
@@ -20167,7 +20167,7 @@
         <v>0.1621</v>
       </c>
       <c r="AA339" t="n">
-        <v>0.7416</v>
+        <v>0.0515</v>
       </c>
     </row>
     <row r="340" ht="16" customHeight="1" s="8">
@@ -20226,7 +20226,7 @@
         <v>0.169</v>
       </c>
       <c r="AA340" t="n">
-        <v>0.7682</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="341" ht="16" customHeight="1" s="8">
@@ -20285,7 +20285,7 @@
         <v>0.1498</v>
       </c>
       <c r="AA341" t="n">
-        <v>0.7391</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="342" ht="16" customHeight="1" s="8">
@@ -20344,7 +20344,7 @@
         <v>0.1504</v>
       </c>
       <c r="AA342" t="n">
-        <v>0.7378</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="343" ht="16" customHeight="1" s="8">
@@ -20403,7 +20403,7 @@
         <v>0.1749</v>
       </c>
       <c r="AA343" t="n">
-        <v>0.6985</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="344" ht="16" customHeight="1" s="8">
@@ -20462,7 +20462,7 @@
         <v>0.1207</v>
       </c>
       <c r="AA344" t="n">
-        <v>0.659</v>
+        <v>0.0472</v>
       </c>
     </row>
     <row r="345" ht="16" customHeight="1" s="8">
@@ -20521,7 +20521,7 @@
         <v>0.1407</v>
       </c>
       <c r="AA345" t="n">
-        <v>0.8135</v>
+        <v>0.0433</v>
       </c>
     </row>
     <row r="346" ht="16" customHeight="1" s="8">
@@ -20580,7 +20580,7 @@
         <v>0.1545</v>
       </c>
       <c r="AA346" t="n">
-        <v>0.8534</v>
+        <v>0.0397</v>
       </c>
     </row>
     <row r="347" ht="16" customHeight="1" s="8">
@@ -20639,7 +20639,7 @@
         <v>0.1722</v>
       </c>
       <c r="AA347" t="n">
-        <v>0.8435</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="348" ht="16" customHeight="1" s="8">
@@ -20698,7 +20698,7 @@
         <v>0.1668</v>
       </c>
       <c r="AA348" t="n">
-        <v>0.878</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="349" ht="16" customHeight="1" s="8">
@@ -20757,7 +20757,7 @@
         <v>0.1393</v>
       </c>
       <c r="AA349" t="n">
-        <v>0.8903</v>
+        <v>0.0442</v>
       </c>
     </row>
     <row r="350" ht="16" customHeight="1" s="8">
@@ -20816,7 +20816,7 @@
         <v>0.1023</v>
       </c>
       <c r="AA350" t="n">
-        <v>0.8782</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="351" ht="16" customHeight="1" s="8">
@@ -20875,7 +20875,7 @@
         <v>0.1097</v>
       </c>
       <c r="AA351" t="n">
-        <v>0.8776</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="352" ht="16" customHeight="1" s="8">
@@ -20934,7 +20934,7 @@
         <v>0.1181</v>
       </c>
       <c r="AA352" t="n">
-        <v>0.8618</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="353" ht="16" customHeight="1" s="8">
@@ -20993,7 +20993,7 @@
         <v>0.1379</v>
       </c>
       <c r="AA353" t="n">
-        <v>0.8377</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="354" ht="16" customHeight="1" s="8">
@@ -21052,7 +21052,7 @@
         <v>0.1187</v>
       </c>
       <c r="AA354" t="n">
-        <v>0.8794</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="355" ht="16" customHeight="1" s="8">
@@ -21111,7 +21111,7 @@
         <v>0.1356</v>
       </c>
       <c r="AA355" t="n">
-        <v>0.9102</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="356" ht="16" customHeight="1" s="8">
@@ -21170,7 +21170,7 @@
         <v>0.1572</v>
       </c>
       <c r="AA356" t="n">
-        <v>0.9202</v>
+        <v>0.0487</v>
       </c>
     </row>
     <row r="357" ht="16" customHeight="1" s="8">
@@ -21229,7 +21229,7 @@
         <v>0.1535</v>
       </c>
       <c r="AA357" t="n">
-        <v>0.9066</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="358" ht="16" customHeight="1" s="8">
@@ -21288,7 +21288,7 @@
         <v>0.1471</v>
       </c>
       <c r="AA358" t="n">
-        <v>0.9252</v>
+        <v>0.0412</v>
       </c>
     </row>
     <row r="359" ht="16" customHeight="1" s="8">
@@ -21347,7 +21347,7 @@
         <v>0.1486</v>
       </c>
       <c r="AA359" t="n">
-        <v>0.927</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="360" ht="16" customHeight="1" s="8">
@@ -21406,7 +21406,7 @@
         <v>0.134</v>
       </c>
       <c r="AA360" t="n">
-        <v>0.9153</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="361" ht="16" customHeight="1" s="8">
@@ -21465,7 +21465,7 @@
         <v>0.1355</v>
       </c>
       <c r="AA361" t="n">
-        <v>0.9126</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="362" ht="16" customHeight="1" s="8">
@@ -21524,7 +21524,7 @@
         <v>0.1498</v>
       </c>
       <c r="AA362" t="n">
-        <v>0.9053</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="363" ht="16" customHeight="1" s="8">
@@ -21583,7 +21583,7 @@
         <v>0.1591</v>
       </c>
       <c r="AA363" t="n">
-        <v>0.9136</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="364" ht="16" customHeight="1" s="8">
@@ -21642,7 +21642,7 @@
         <v>0.1486</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.9422</v>
+        <v>0.0327</v>
       </c>
     </row>
     <row r="365" ht="16" customHeight="1" s="8">
@@ -21701,7 +21701,7 @@
         <v>0.1462</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.9197</v>
+        <v>0.0329</v>
       </c>
     </row>
     <row r="366" ht="16" customHeight="1" s="8">
@@ -21760,7 +21760,7 @@
         <v>0.1398</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.9248</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="367" ht="16" customHeight="1" s="8">
@@ -21819,7 +21819,7 @@
         <v>0.1414</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.9231</v>
+        <v>0.0532</v>
       </c>
     </row>
     <row r="368" ht="16" customHeight="1" s="8">
@@ -21878,7 +21878,7 @@
         <v>0.1343</v>
       </c>
       <c r="AA368" t="n">
-        <v>0.924</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="369" ht="16" customHeight="1" s="8">
@@ -21937,7 +21937,7 @@
         <v>0.1527</v>
       </c>
       <c r="AA369" t="n">
-        <v>0.9315</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="370" ht="16" customHeight="1" s="8">
@@ -21996,7 +21996,7 @@
         <v>0.1313</v>
       </c>
       <c r="AA370" t="n">
-        <v>0.9438</v>
+        <v>0.0341</v>
       </c>
     </row>
     <row r="371" ht="16" customHeight="1" s="8">
@@ -22055,7 +22055,7 @@
         <v>0.1261</v>
       </c>
       <c r="AA371" t="n">
-        <v>0.9457</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="372" ht="16" customHeight="1" s="8">
@@ -22114,7 +22114,7 @@
         <v>0.1239</v>
       </c>
       <c r="AA372" t="n">
-        <v>0.9598</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="373" ht="16" customHeight="1" s="8">
@@ -22173,7 +22173,7 @@
         <v>0.1189</v>
       </c>
       <c r="AA373" t="n">
-        <v>0.9549</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="374" ht="16" customHeight="1" s="8">
@@ -22232,7 +22232,7 @@
         <v>0.1323</v>
       </c>
       <c r="AA374" t="n">
-        <v>0.9475</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="375" ht="16" customHeight="1" s="8">
@@ -22291,7 +22291,7 @@
         <v>0.1281</v>
       </c>
       <c r="AA375" t="n">
-        <v>0.9412</v>
+        <v>0.0408</v>
       </c>
     </row>
     <row r="376" ht="16" customHeight="1" s="8">
@@ -22350,7 +22350,7 @@
         <v>0.1227</v>
       </c>
       <c r="AA376" t="n">
-        <v>0.9358</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="377" ht="16" customHeight="1" s="8">
@@ -22409,7 +22409,7 @@
         <v>0.1231</v>
       </c>
       <c r="AA377" t="n">
-        <v>0.9343</v>
+        <v>0.0384</v>
       </c>
     </row>
     <row r="378" ht="16" customHeight="1" s="8">
@@ -22468,7 +22468,7 @@
         <v>0.1364</v>
       </c>
       <c r="AA378" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.0468</v>
       </c>
     </row>
     <row r="379" ht="16" customHeight="1" s="8">
@@ -22527,7 +22527,7 @@
         <v>0.121</v>
       </c>
       <c r="AA379" t="n">
-        <v>0.91</v>
+        <v>0.0434</v>
       </c>
     </row>
     <row r="380" ht="16" customHeight="1" s="8">
@@ -22586,7 +22586,7 @@
         <v>0.1253</v>
       </c>
       <c r="AA380" t="n">
-        <v>0.8912</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="381" ht="16" customHeight="1" s="8">
@@ -22645,7 +22645,7 @@
         <v>0.1136</v>
       </c>
       <c r="AA381" t="n">
-        <v>0.9185</v>
+        <v>0.0469</v>
       </c>
     </row>
     <row r="382" ht="16" customHeight="1" s="8">
@@ -22704,7 +22704,7 @@
         <v>0.1316</v>
       </c>
       <c r="AA382" t="n">
-        <v>0.9023</v>
+        <v>0.0442</v>
       </c>
     </row>
     <row r="383" ht="16" customHeight="1" s="8">
@@ -22763,7 +22763,7 @@
         <v>0.1311</v>
       </c>
       <c r="AA383" t="n">
-        <v>0.8934</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="384" ht="16" customHeight="1" s="8">
@@ -22822,7 +22822,7 @@
         <v>0.1175</v>
       </c>
       <c r="AA384" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="385" ht="16" customHeight="1" s="8">
@@ -22881,7 +22881,7 @@
         <v>0.1426</v>
       </c>
       <c r="AA385" t="n">
-        <v>0.8742</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="386" ht="16" customHeight="1" s="8">
@@ -22940,7 +22940,7 @@
         <v>0.1171</v>
       </c>
       <c r="AA386" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.0305</v>
       </c>
     </row>
     <row r="387" ht="16" customHeight="1" s="8">
@@ -22999,7 +22999,7 @@
         <v>0.1537</v>
       </c>
       <c r="AA387" t="n">
-        <v>0.8534</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="388" ht="16" customHeight="1" s="8">
@@ -23058,7 +23058,7 @@
         <v>0.1002</v>
       </c>
       <c r="AA388" t="n">
-        <v>0.8585</v>
+        <v>0.0371</v>
       </c>
     </row>
     <row r="389" ht="16" customHeight="1" s="8">
@@ -23117,7 +23117,7 @@
         <v>0.132</v>
       </c>
       <c r="AA389" t="n">
-        <v>0.8993</v>
+        <v>0.0432</v>
       </c>
     </row>
     <row r="390" ht="16" customHeight="1" s="8">
@@ -23176,7 +23176,7 @@
         <v>0.1254</v>
       </c>
       <c r="AA390" t="n">
-        <v>0.9425</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="391" ht="16" customHeight="1" s="8">
@@ -23235,7 +23235,7 @@
         <v>0.1255</v>
       </c>
       <c r="AA391" t="n">
-        <v>0.9258</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="392" ht="16" customHeight="1" s="8">
@@ -23294,7 +23294,7 @@
         <v>0.1253</v>
       </c>
       <c r="AA392" t="n">
-        <v>0.9069</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="393" ht="16" customHeight="1" s="8">
@@ -23353,7 +23353,7 @@
         <v>0.0994</v>
       </c>
       <c r="AA393" t="n">
-        <v>0.8677</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="394" ht="16" customHeight="1" s="8">
@@ -23412,7 +23412,7 @@
         <v>0.1282</v>
       </c>
       <c r="AA394" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.0428</v>
       </c>
     </row>
     <row r="395" ht="16" customHeight="1" s="8">
@@ -23471,7 +23471,7 @@
         <v>0.1256</v>
       </c>
       <c r="AA395" t="n">
-        <v>0.8895</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="396" ht="16" customHeight="1" s="8">
@@ -23530,7 +23530,7 @@
         <v>0.1142</v>
       </c>
       <c r="AA396" t="n">
-        <v>0.8841</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="397" ht="16" customHeight="1" s="8">
@@ -23589,7 +23589,7 @@
         <v>0.1151</v>
       </c>
       <c r="AA397" t="n">
-        <v>0.9006</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="398" ht="16" customHeight="1" s="8">
@@ -23648,7 +23648,7 @@
         <v>0.1354</v>
       </c>
       <c r="AA398" t="n">
-        <v>0.9376</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="399" ht="16" customHeight="1" s="8">
@@ -23707,7 +23707,7 @@
         <v>0.1161</v>
       </c>
       <c r="AA399" t="n">
-        <v>0.9126</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="400" ht="16" customHeight="1" s="8">
@@ -23766,7 +23766,7 @@
         <v>0.1086</v>
       </c>
       <c r="AA400" t="n">
-        <v>0.9266</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="401" ht="16" customHeight="1" s="8">
@@ -23825,7 +23825,7 @@
         <v>0.1299</v>
       </c>
       <c r="AA401" t="n">
-        <v>0.9315</v>
+        <v>0.0331</v>
       </c>
     </row>
     <row r="402" ht="16" customHeight="1" s="8">
@@ -23884,7 +23884,7 @@
         <v>0.1333</v>
       </c>
       <c r="AA402" t="n">
-        <v>0.923</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="403" ht="16" customHeight="1" s="8">
@@ -23943,7 +23943,7 @@
         <v>0.128</v>
       </c>
       <c r="AA403" t="n">
-        <v>0.9135</v>
+        <v>0.0317</v>
       </c>
     </row>
     <row r="404" ht="16" customHeight="1" s="8">
@@ -24002,7 +24002,7 @@
         <v>0.116</v>
       </c>
       <c r="AA404" t="n">
-        <v>0.9355</v>
+        <v>0.0318</v>
       </c>
     </row>
     <row r="405" ht="16" customHeight="1" s="8">
@@ -24061,7 +24061,7 @@
         <v>0.1313</v>
       </c>
       <c r="AA405" t="n">
-        <v>0.9425</v>
+        <v>0.0538</v>
       </c>
     </row>
     <row r="406" ht="16" customHeight="1" s="8">
@@ -24120,7 +24120,7 @@
         <v>0.1121</v>
       </c>
       <c r="AA406" t="n">
-        <v>0.9502</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="407" ht="16" customHeight="1" s="8">
@@ -24179,7 +24179,7 @@
         <v>0.1031</v>
       </c>
       <c r="AA407" t="n">
-        <v>0.9613</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="408" ht="16" customHeight="1" s="8">
@@ -24238,7 +24238,7 @@
         <v>0.1207</v>
       </c>
       <c r="AA408" t="n">
-        <v>0.9584</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="409" ht="16" customHeight="1" s="8">
@@ -24297,7 +24297,7 @@
         <v>0.1026</v>
       </c>
       <c r="AA409" t="n">
-        <v>0.9558</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="410" ht="16" customHeight="1" s="8">
@@ -24356,7 +24356,7 @@
         <v>0.1049</v>
       </c>
       <c r="AA410" t="n">
-        <v>0.9546</v>
+        <v>0.0411</v>
       </c>
     </row>
     <row r="411" ht="16" customHeight="1" s="8">
@@ -24415,7 +24415,7 @@
         <v>0.132</v>
       </c>
       <c r="AA411" t="n">
-        <v>0.9423</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="412" ht="16" customHeight="1" s="8">
@@ -24474,7 +24474,7 @@
         <v>0.11</v>
       </c>
       <c r="AA412" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="413" ht="16" customHeight="1" s="8">
@@ -24533,7 +24533,7 @@
         <v>0.1236</v>
       </c>
       <c r="AA413" t="n">
-        <v>0.9416</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="414" ht="16" customHeight="1" s="8">
@@ -24592,7 +24592,7 @@
         <v>0.1299</v>
       </c>
       <c r="AA414" t="n">
-        <v>0.9613</v>
+        <v>0.0319</v>
       </c>
     </row>
     <row r="415" ht="16" customHeight="1" s="8">
@@ -24651,7 +24651,7 @@
         <v>0.1187</v>
       </c>
       <c r="AA415" t="n">
-        <v>0.9573</v>
+        <v>0.0432</v>
       </c>
     </row>
     <row r="416">
@@ -24703,7 +24703,7 @@
         <v>0.13635</v>
       </c>
       <c r="AA418" t="n">
-        <v>0.2383142857142857</v>
+        <v>0.1385</v>
       </c>
     </row>
     <row r="419">
@@ -24741,7 +24741,7 @@
         <v>0.153325</v>
       </c>
       <c r="AA419" t="n">
-        <v>0.2001</v>
+        <v>0.11364</v>
       </c>
     </row>
     <row r="420">
@@ -24779,7 +24779,7 @@
         <v>0.19912</v>
       </c>
       <c r="AA420" t="n">
-        <v>0.1565833333333333</v>
+        <v>0.1579333333333333</v>
       </c>
     </row>
     <row r="421">
@@ -24817,7 +24817,7 @@
         <v>0.2224285714285714</v>
       </c>
       <c r="AA421" t="n">
-        <v>0.25774</v>
+        <v>0.2806875</v>
       </c>
     </row>
     <row r="422">
@@ -24855,7 +24855,7 @@
         <v>0.2053</v>
       </c>
       <c r="AA422" t="n">
-        <v>0.2678833333333333</v>
+        <v>0.2632444444444444</v>
       </c>
     </row>
     <row r="423">
@@ -24893,7 +24893,7 @@
         <v>0.3503</v>
       </c>
       <c r="AA423" t="n">
-        <v>0.336025</v>
+        <v>0.3480333333333334</v>
       </c>
     </row>
     <row r="424">
@@ -24931,7 +24931,7 @@
         <v>0.3723285714285715</v>
       </c>
       <c r="AA424" t="n">
-        <v>0.3323428571428572</v>
+        <v>0.3068363636363636</v>
       </c>
     </row>
     <row r="425">
@@ -24969,7 +24969,7 @@
         <v>0.3189714285714286</v>
       </c>
       <c r="AA425" t="n">
-        <v>0.3585555555555556</v>
+        <v>0.42354</v>
       </c>
     </row>
     <row r="426">
@@ -25007,7 +25007,7 @@
         <v>0.4746166666666667</v>
       </c>
       <c r="AA426" t="n">
-        <v>0.3757333333333334</v>
+        <v>0.4242181818181818</v>
       </c>
     </row>
     <row r="427">
@@ -25045,7 +25045,7 @@
         <v>0.5252333333333333</v>
       </c>
       <c r="AA427" t="n">
-        <v>0.5565777777777777</v>
+        <v>0.4758444444444445</v>
       </c>
     </row>
     <row r="428">
@@ -25071,7 +25071,7 @@
         <v>0.5607857142857142</v>
       </c>
       <c r="AA428" t="n">
-        <v>0.452425</v>
+        <v>0.4650500000000001</v>
       </c>
     </row>
     <row r="429">
@@ -25100,7 +25100,7 @@
         <v>0.5459000000000001</v>
       </c>
       <c r="AA429" t="n">
-        <v>0.5060454545454545</v>
+        <v>0.4757666666666667</v>
       </c>
     </row>
     <row r="430">
@@ -25129,7 +25129,7 @@
         <v>0.6047800000000001</v>
       </c>
       <c r="AA430" t="n">
-        <v>0.5587199999999999</v>
+        <v>0.5172714285714286</v>
       </c>
     </row>
     <row r="431">
@@ -25158,7 +25158,7 @@
         <v>0.5497857142857143</v>
       </c>
       <c r="AA431" t="n">
-        <v>0.6409250000000001</v>
+        <v>0.5813090909090909</v>
       </c>
     </row>
     <row r="432">
@@ -25187,7 +25187,7 @@
         <v>0.6221000000000001</v>
       </c>
       <c r="AA432" t="n">
-        <v>0.65021</v>
+        <v>0.5715100000000001</v>
       </c>
     </row>
     <row r="433">
@@ -25216,7 +25216,7 @@
         <v>0.7314166666666666</v>
       </c>
       <c r="AA433" t="n">
-        <v>0.68621</v>
+        <v>0.5614</v>
       </c>
     </row>
     <row r="434">
@@ -25245,7 +25245,7 @@
         <v>0.6358166666666666</v>
       </c>
       <c r="AA434" t="n">
-        <v>0.6781416666666668</v>
+        <v>0.5625666666666667</v>
       </c>
     </row>
     <row r="435">
@@ -25274,7 +25274,7 @@
         <v>0.7117</v>
       </c>
       <c r="AA435" t="n">
-        <v>0.59658</v>
+        <v>0.5525600000000001</v>
       </c>
     </row>
     <row r="436">
@@ -25303,7 +25303,7 @@
         <v>0.6544272727272727</v>
       </c>
       <c r="AA436" t="n">
-        <v>0.6793699999999999</v>
+        <v>0.5790375000000001</v>
       </c>
     </row>
     <row r="437">
@@ -25332,7 +25332,7 @@
         <v>0.73231</v>
       </c>
       <c r="AA437" t="n">
-        <v>0.7057249999999999</v>
+        <v>0.6462714285714285</v>
       </c>
     </row>
     <row r="438">
@@ -25361,7 +25361,7 @@
         <v>0.7155374999999999</v>
       </c>
       <c r="AA438" t="n">
-        <v>0.7513272727272727</v>
+        <v>0.6219333333333333</v>
       </c>
     </row>
     <row r="439">
@@ -25390,7 +25390,7 @@
         <v>0.8525666666666667</v>
       </c>
       <c r="AA439" t="n">
-        <v>0.6941333333333333</v>
+        <v>0.6233181818181819</v>
       </c>
     </row>
     <row r="440">
@@ -25419,7 +25419,7 @@
         <v>0.7095375</v>
       </c>
       <c r="AA440" t="n">
-        <v>0.7221090909090908</v>
+        <v>0.6385111111111113</v>
       </c>
     </row>
     <row r="441">
@@ -25448,7 +25448,7 @@
         <v>0.7535999999999998</v>
       </c>
       <c r="AA441" t="n">
-        <v>0.7629333333333332</v>
+        <v>0.6656875</v>
       </c>
     </row>
     <row r="442">
@@ -25477,7 +25477,7 @@
         <v>0.6710888888888888</v>
       </c>
       <c r="AA442" t="n">
-        <v>0.7676300000000001</v>
+        <v>0.6785</v>
       </c>
     </row>
     <row r="443">
@@ -25506,7 +25506,7 @@
         <v>0.7878857142857143</v>
       </c>
       <c r="AA443" t="n">
-        <v>0.7958999999999999</v>
+        <v>0.5369777777777779</v>
       </c>
     </row>
     <row r="444">
@@ -25535,7 +25535,7 @@
         <v>0.7796714285714286</v>
       </c>
       <c r="AA444" t="n">
-        <v>0.833</v>
+        <v>0.6877222222222222</v>
       </c>
     </row>
     <row r="445">
@@ -25564,7 +25564,7 @@
         <v>0.6811222222222223</v>
       </c>
       <c r="AA445" t="n">
-        <v>0.7427818181818182</v>
+        <v>0.6557272727272726</v>
       </c>
     </row>
     <row r="446">
@@ -25593,7 +25593,7 @@
         <v>0.7314000000000001</v>
       </c>
       <c r="AA446" t="n">
-        <v>0.7793916666666667</v>
+        <v>0.7241</v>
       </c>
     </row>
     <row r="447">
@@ -25622,7 +25622,7 @@
         <v>0.7011222222222222</v>
       </c>
       <c r="AA447" t="n">
-        <v>0.7009000000000001</v>
+        <v>0.7413444444444444</v>
       </c>
     </row>
     <row r="448">
@@ -25651,7 +25651,7 @@
         <v>0.6636428571428572</v>
       </c>
       <c r="AA448" t="n">
-        <v>0.7077636363636365</v>
+        <v>0.7255777777777778</v>
       </c>
     </row>
     <row r="449">
@@ -25680,7 +25680,7 @@
         <v>0.7542285714285715</v>
       </c>
       <c r="AA449" t="n">
-        <v>0.6953454545454545</v>
+        <v>0.6183363636363637</v>
       </c>
     </row>
     <row r="450">
@@ -25706,7 +25706,7 @@
         <v>0.6986428571428572</v>
       </c>
       <c r="AA450" t="n">
-        <v>0.7183833333333333</v>
+        <v>0.6870900000000002</v>
       </c>
     </row>
     <row r="451">
@@ -25735,7 +25735,7 @@
         <v>0.7181833333333333</v>
       </c>
       <c r="AA451" t="n">
-        <v>0.7562923076923078</v>
+        <v>0.6491571428571429</v>
       </c>
     </row>
     <row r="452">
@@ -25764,7 +25764,7 @@
         <v>0.6237363636363636</v>
       </c>
       <c r="AA452" t="n">
-        <v>0.7994555555555557</v>
+        <v>0.7239666666666666</v>
       </c>
     </row>
     <row r="453">
@@ -25790,7 +25790,7 @@
         <v>0.712288888888889</v>
       </c>
       <c r="AA453" t="n">
-        <v>0.8340500000000001</v>
+        <v>0.6639199999999998</v>
       </c>
     </row>
     <row r="454">
@@ -25819,7 +25819,7 @@
         <v>0.7845888888888888</v>
       </c>
       <c r="AA454" t="n">
-        <v>0.7117499999999999</v>
+        <v>0.6278818181818182</v>
       </c>
     </row>
     <row r="455">
@@ -25848,7 +25848,7 @@
         <v>0.76297</v>
       </c>
       <c r="AA455" t="n">
-        <v>0.8112363636363636</v>
+        <v>0.660709090909091</v>
       </c>
     </row>
     <row r="456">
@@ -25877,7 +25877,7 @@
         <v>0.7825124999999999</v>
       </c>
       <c r="AA456" t="n">
-        <v>0.6969583333333333</v>
+        <v>0.64244</v>
       </c>
     </row>
     <row r="457">
@@ -25906,7 +25906,7 @@
         <v>0.6687399999999999</v>
       </c>
       <c r="AA457" t="n">
-        <v>0.75656</v>
+        <v>0.6693999999999999</v>
       </c>
     </row>
     <row r="458">
@@ -25935,7 +25935,7 @@
         <v>0.7573375000000001</v>
       </c>
       <c r="AA458" t="n">
-        <v>0.8090545454545454</v>
+        <v>0.6659888888888889</v>
       </c>
     </row>
     <row r="459">
@@ -25964,7 +25964,7 @@
         <v>0.8084285714285714</v>
       </c>
       <c r="AA459" t="n">
-        <v>0.7951636363636364</v>
+        <v>0.6313111111111112</v>
       </c>
     </row>
     <row r="460">
@@ -25993,7 +25993,7 @@
         <v>0.7853428571428571</v>
       </c>
       <c r="AA460" t="n">
-        <v>0.785</v>
+        <v>0.6701555555555555</v>
       </c>
     </row>
     <row r="461">
@@ -26022,7 +26022,7 @@
         <v>0.6994374999999999</v>
       </c>
       <c r="AA461" t="n">
-        <v>0.7561500000000001</v>
+        <v>0.7104875</v>
       </c>
     </row>
     <row r="462">
@@ -26051,7 +26051,7 @@
         <v>0.8050999999999999</v>
       </c>
       <c r="AA462" t="n">
-        <v>0.8655222222222222</v>
+        <v>0.6573</v>
       </c>
     </row>
     <row r="463">
@@ -26080,7 +26080,7 @@
         <v>0.7909666666666668</v>
       </c>
       <c r="AA463" t="n">
-        <v>0.802909090909091</v>
+        <v>0.6970555555555555</v>
       </c>
     </row>
     <row r="464">
@@ -26109,7 +26109,7 @@
         <v>0.7268800000000001</v>
       </c>
       <c r="AA464" t="n">
-        <v>0.7966454545454545</v>
+        <v>0.7023125</v>
       </c>
     </row>
     <row r="465">
@@ -26138,7 +26138,7 @@
         <v>0.7758333333333333</v>
       </c>
       <c r="AA465" t="n">
-        <v>0.8082545454545454</v>
+        <v>0.75595</v>
       </c>
     </row>
     <row r="466">
@@ -26167,7 +26167,7 @@
         <v>0.7756555555555554</v>
       </c>
       <c r="AA466" t="n">
-        <v>0.8190307692307692</v>
+        <v>0.7135909090909091</v>
       </c>
     </row>
     <row r="467">
@@ -26196,7 +26196,7 @@
         <v>0.8026363636363637</v>
       </c>
       <c r="AA467" t="n">
-        <v>0.7904099999999999</v>
+        <v>0.58553</v>
       </c>
     </row>
     <row r="468">
@@ -26225,7 +26225,7 @@
         <v>0.6862666666666667</v>
       </c>
       <c r="AA468" t="n">
-        <v>0.8568700000000001</v>
+        <v>0.6592100000000001</v>
       </c>
     </row>
     <row r="469">
@@ -26254,7 +26254,7 @@
         <v>0.7603333333333334</v>
       </c>
       <c r="AA469" t="n">
-        <v>0.7698083333333333</v>
+        <v>0.698476923076923</v>
       </c>
     </row>
     <row r="470">
@@ -26283,7 +26283,7 @@
         <v>0.77699</v>
       </c>
       <c r="AA470" t="n">
-        <v>0.7809083333333334</v>
+        <v>0.6918555555555554</v>
       </c>
     </row>
     <row r="471">
@@ -26312,7 +26312,7 @@
         <v>0.7846000000000001</v>
       </c>
       <c r="AA471" t="n">
-        <v>0.7118272727272728</v>
+        <v>0.69656</v>
       </c>
     </row>
     <row r="472">
@@ -26341,7 +26341,7 @@
         <v>0.762625</v>
       </c>
       <c r="AA472" t="n">
-        <v>0.7352333333333334</v>
+        <v>0.6682166666666666</v>
       </c>
     </row>
     <row r="473">
@@ -26370,7 +26370,7 @@
         <v>0.6857</v>
       </c>
       <c r="AA473" t="n">
-        <v>0.726975</v>
+        <v>0.6366875</v>
       </c>
     </row>
     <row r="474">
@@ -26399,7 +26399,7 @@
         <v>0.8213375000000001</v>
       </c>
       <c r="AA474" t="n">
-        <v>0.8056846153846153</v>
+        <v>0.5790909090909091</v>
       </c>
     </row>
     <row r="475">
@@ -26428,7 +26428,7 @@
         <v>0.7006666666666665</v>
       </c>
       <c r="AA475" t="n">
-        <v>0.8007416666666667</v>
+        <v>0.6073500000000001</v>
       </c>
     </row>
     <row r="476">
@@ -26457,7 +26457,7 @@
         <v>0.7847500000000001</v>
       </c>
       <c r="AA476" t="n">
-        <v>0.76074</v>
+        <v>0.6441571428571429</v>
       </c>
     </row>
     <row r="477">
@@ -26486,7 +26486,7 @@
         <v>0.70289</v>
       </c>
       <c r="AA477" t="n">
-        <v>0.8442818181818182</v>
+        <v>0.6373333333333334</v>
       </c>
     </row>
     <row r="478">
@@ -26515,7 +26515,7 @@
         <v>0.8324555555555555</v>
       </c>
       <c r="AA478" t="n">
-        <v>0.7921909090909091</v>
+        <v>0.6788875</v>
       </c>
     </row>
     <row r="479">
@@ -26544,7 +26544,7 @@
         <v>0.8105200000000001</v>
       </c>
       <c r="AA479" t="n">
-        <v>0.7624818181818184</v>
+        <v>0.6533142857142857</v>
       </c>
     </row>
     <row r="480">
@@ -26573,7 +26573,7 @@
         <v>0.7547285714285714</v>
       </c>
       <c r="AA480" t="n">
-        <v>0.7362615384615385</v>
+        <v>0.6851800000000001</v>
       </c>
     </row>
     <row r="481">
@@ -26602,7 +26602,7 @@
         <v>0.7634888888888889</v>
       </c>
       <c r="AA481" t="n">
-        <v>0.7492272727272727</v>
+        <v>0.6532777777777778</v>
       </c>
     </row>
     <row r="482">
@@ -26631,7 +26631,7 @@
         <v>0.7140285714285716</v>
       </c>
       <c r="AA482" t="n">
-        <v>0.7383285714285713</v>
+        <v>0.6102500000000001</v>
       </c>
     </row>
     <row r="483">
@@ -26660,7 +26660,7 @@
         <v>0.6510166666666667</v>
       </c>
       <c r="AA483" t="n">
-        <v>0.802390909090909</v>
+        <v>0.569225</v>
       </c>
     </row>
     <row r="484">
@@ -26689,7 +26689,7 @@
         <v>0.7686142857142857</v>
       </c>
       <c r="AA484" t="n">
-        <v>0.7501846153846153</v>
+        <v>0.6590400000000001</v>
       </c>
     </row>
     <row r="485">
@@ -26718,7 +26718,7 @@
         <v>0.7226000000000001</v>
       </c>
       <c r="AA485" t="n">
-        <v>0.7008799999999999</v>
+        <v>0.6167545454545453</v>
       </c>
     </row>
     <row r="486">
@@ -26747,7 +26747,7 @@
         <v>0.8128285714285715</v>
       </c>
       <c r="AA486" t="n">
-        <v>0.824590909090909</v>
+        <v>0.6664714285714286</v>
       </c>
     </row>
     <row r="487">
@@ -26776,7 +26776,7 @@
         <v>0.6820888888888889</v>
       </c>
       <c r="AA487" t="n">
-        <v>0.8314363636363638</v>
+        <v>0.679675</v>
       </c>
     </row>
     <row r="488">
@@ -26805,7 +26805,7 @@
         <v>0.7239444444444445</v>
       </c>
       <c r="AA488" t="n">
-        <v>0.8320727272727275</v>
+        <v>0.6391083333333334</v>
       </c>
     </row>
     <row r="489">
@@ -26834,7 +26834,7 @@
         <v>0.67659</v>
       </c>
       <c r="AA489" t="n">
-        <v>0.7052272727272727</v>
+        <v>0.7452888888888888</v>
       </c>
     </row>
     <row r="490">
@@ -26863,7 +26863,7 @@
         <v>0.7241222222222221</v>
       </c>
       <c r="AA490" t="n">
-        <v>0.7577999999999999</v>
+        <v>0.5895625000000001</v>
       </c>
     </row>
     <row r="491">
@@ -26889,7 +26889,7 @@
         <v>0.7269571428571429</v>
       </c>
       <c r="AA491" t="n">
-        <v>0.7205083333333332</v>
+        <v>0.6596090909090909</v>
       </c>
     </row>
     <row r="492">
@@ -26918,7 +26918,7 @@
         <v>0.72215</v>
       </c>
       <c r="AA492" t="n">
-        <v>0.8176071428571429</v>
+        <v>0.6394749999999999</v>
       </c>
     </row>
     <row r="493">
@@ -26947,7 +26947,7 @@
         <v>0.7744375</v>
       </c>
       <c r="AA493" t="n">
-        <v>0.8184692307692306</v>
+        <v>0.6769166666666667</v>
       </c>
     </row>
     <row r="494">
@@ -26976,7 +26976,7 @@
         <v>0.7859571428571429</v>
       </c>
       <c r="AA494" t="n">
-        <v>0.7696</v>
+        <v>0.6338444444444445</v>
       </c>
     </row>
     <row r="495">
@@ -27005,7 +27005,7 @@
         <v>0.7507250000000001</v>
       </c>
       <c r="AA495" t="n">
-        <v>0.800323076923077</v>
+        <v>0.6018</v>
       </c>
     </row>
     <row r="496">
@@ -27034,7 +27034,7 @@
         <v>0.7325</v>
       </c>
       <c r="AA496" t="n">
-        <v>0.7580727272727272</v>
+        <v>0.676325</v>
       </c>
     </row>
     <row r="497">
@@ -27063,7 +27063,7 @@
         <v>0.784325</v>
       </c>
       <c r="AA497" t="n">
-        <v>0.811225</v>
+        <v>0.6805499999999999</v>
       </c>
     </row>
     <row r="498">
@@ -27092,7 +27092,7 @@
         <v>0.8074750000000001</v>
       </c>
       <c r="AA498" t="n">
-        <v>0.8155333333333333</v>
+        <v>0.7142625</v>
       </c>
     </row>
     <row r="499">
@@ -27121,7 +27121,7 @@
         <v>0.7681</v>
       </c>
       <c r="AA499" t="n">
-        <v>0.7878375000000001</v>
+        <v>0.6307363636363637</v>
       </c>
     </row>
     <row r="500">
@@ -27150,7 +27150,7 @@
         <v>0.6880222222222223</v>
       </c>
       <c r="AA500" t="n">
-        <v>0.7902416666666666</v>
+        <v>0.70325</v>
       </c>
     </row>
     <row r="501">
@@ -27179,7 +27179,7 @@
         <v>0.7469714285714285</v>
       </c>
       <c r="AA501" t="n">
-        <v>0.7641249999999999</v>
+        <v>0.6362545454545454</v>
       </c>
     </row>
     <row r="502">
@@ -27208,7 +27208,7 @@
         <v>0.8234714285714286</v>
       </c>
       <c r="AA502" t="n">
-        <v>0.8403499999999999</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="503">
@@ -27237,7 +27237,7 @@
         <v>0.7871666666666667</v>
       </c>
       <c r="AA503" t="n">
-        <v>0.797025</v>
+        <v>0.6817111111111112</v>
       </c>
     </row>
     <row r="504">
@@ -27266,7 +27266,7 @@
         <v>0.77788</v>
       </c>
       <c r="AA504" t="n">
-        <v>0.7466272727272727</v>
+        <v>0.70706</v>
       </c>
     </row>
     <row r="505">
@@ -27295,7 +27295,7 @@
         <v>0.7355750000000001</v>
       </c>
       <c r="AA505" t="n">
-        <v>0.8142400000000002</v>
+        <v>0.6916777777777777</v>
       </c>
     </row>
     <row r="506">
@@ -27324,7 +27324,7 @@
         <v>0.7288363636363637</v>
       </c>
       <c r="AA506" t="n">
-        <v>0.7745307692307691</v>
+        <v>0.52351</v>
       </c>
     </row>
     <row r="507">
@@ -27353,7 +27353,7 @@
         <v>0.7825625</v>
       </c>
       <c r="AA507" t="n">
-        <v>0.8110200000000001</v>
+        <v>0.6459083333333333</v>
       </c>
     </row>
     <row r="508">
@@ -27382,7 +27382,7 @@
         <v>0.7443000000000001</v>
       </c>
       <c r="AA508" t="n">
-        <v>0.8440416666666666</v>
+        <v>0.61317</v>
       </c>
     </row>
     <row r="509">
@@ -27411,7 +27411,7 @@
         <v>0.72465</v>
       </c>
       <c r="AA509" t="n">
-        <v>0.7975083333333332</v>
+        <v>0.6411272727272728</v>
       </c>
     </row>
     <row r="510">
@@ -27440,7 +27440,7 @@
         <v>0.8114374999999999</v>
       </c>
       <c r="AA510" t="n">
-        <v>0.7963181818181819</v>
+        <v>0.69145</v>
       </c>
     </row>
     <row r="511">
@@ -27469,7 +27469,7 @@
         <v>0.74186</v>
       </c>
       <c r="AA511" t="n">
-        <v>0.82575</v>
+        <v>0.6253900000000001</v>
       </c>
     </row>
     <row r="512">
@@ -27498,7 +27498,7 @@
         <v>0.7042875</v>
       </c>
       <c r="AA512" t="n">
-        <v>0.84256</v>
+        <v>0.5757899999999999</v>
       </c>
     </row>
     <row r="513">
@@ -27527,7 +27527,7 @@
         <v>0.7661555555555556</v>
       </c>
       <c r="AA513" t="n">
-        <v>0.7998333333333333</v>
+        <v>0.6960999999999999</v>
       </c>
     </row>
     <row r="514">
@@ -27556,7 +27556,7 @@
         <v>0.7123428571428571</v>
       </c>
       <c r="AA514" t="n">
-        <v>0.8805555555555555</v>
+        <v>0.6923125</v>
       </c>
     </row>
     <row r="515">
@@ -27585,7 +27585,7 @@
         <v>0.7414000000000001</v>
       </c>
       <c r="AA515" t="n">
-        <v>0.817590909090909</v>
+        <v>0.6928916666666667</v>
       </c>
     </row>
     <row r="516">
@@ -27614,7 +27614,7 @@
         <v>0.6870888888888889</v>
       </c>
       <c r="AA516" t="n">
-        <v>0.8302083333333333</v>
+        <v>0.62975</v>
       </c>
     </row>
     <row r="517">
@@ -27643,7 +27643,7 @@
         <v>0.8057111111111112</v>
       </c>
       <c r="AA517" t="n">
-        <v>0.8079727272727272</v>
+        <v>0.6751888888888888</v>
       </c>
     </row>
     <row r="518">
@@ -27680,7 +27680,7 @@
         <v>0.103556338028169</v>
       </c>
       <c r="AA520" t="n">
-        <v>0.159803125</v>
+        <v>0.1503263157894737</v>
       </c>
     </row>
     <row r="521">
@@ -27703,7 +27703,7 @@
         <v>0.2109014285714285</v>
       </c>
       <c r="AA521" t="n">
-        <v>0.2039896551724138</v>
+        <v>0.1285157894736842</v>
       </c>
     </row>
     <row r="522">
@@ -27726,7 +27726,7 @@
         <v>0.2334857142857143</v>
       </c>
       <c r="AA522" t="n">
-        <v>0.2350042857142857</v>
+        <v>0.25116</v>
       </c>
     </row>
     <row r="523">
@@ -27749,7 +27749,7 @@
         <v>0.3046275362318841</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.2935114754098361</v>
+        <v>0.2358083333333333</v>
       </c>
     </row>
     <row r="524">
@@ -27772,7 +27772,7 @@
         <v>0.310447619047619</v>
       </c>
       <c r="AA524" t="n">
-        <v>0.4095238095238095</v>
+        <v>0.3285516129032258</v>
       </c>
     </row>
     <row r="525">
@@ -27795,7 +27795,7 @@
         <v>0.3079133333333334</v>
       </c>
       <c r="AA525" t="n">
-        <v>0.3886434782608696</v>
+        <v>0.3412743589743589</v>
       </c>
     </row>
     <row r="526">
@@ -27818,7 +27818,7 @@
         <v>0.4530117647058823</v>
       </c>
       <c r="AA526" t="n">
-        <v>0.3700875000000001</v>
+        <v>0.3485416666666666</v>
       </c>
     </row>
     <row r="527">
@@ -27841,7 +27841,7 @@
         <v>0.4978473684210527</v>
       </c>
       <c r="AA527" t="n">
-        <v>0.4903526315789473</v>
+        <v>0.41335</v>
       </c>
     </row>
     <row r="528">
@@ -27864,7 +27864,7 @@
         <v>0.4378411764705883</v>
       </c>
       <c r="AA528" t="n">
-        <v>0.4874161290322581</v>
+        <v>0.43766</v>
       </c>
     </row>
     <row r="529">
@@ -27887,7 +27887,7 @@
         <v>0.511625</v>
       </c>
       <c r="AA529" t="n">
-        <v>0.4264875</v>
+        <v>0.4951630434782608</v>
       </c>
     </row>
     <row r="530">
@@ -27901,7 +27901,7 @@
         <v>0.5153000000000001</v>
       </c>
       <c r="AA530" t="n">
-        <v>0.6499343750000001</v>
+        <v>0.4348</v>
       </c>
     </row>
     <row r="531">
@@ -27915,7 +27915,7 @@
         <v>0.6090731707317073</v>
       </c>
       <c r="AA531" t="n">
-        <v>0.54401</v>
+        <v>0.470075</v>
       </c>
     </row>
     <row r="532">
@@ -27929,7 +27929,7 @@
         <v>0.6020342857142857</v>
       </c>
       <c r="AA532" t="n">
-        <v>0.5242787878787879</v>
+        <v>0.4910022727272728</v>
       </c>
     </row>
     <row r="533">
@@ -27943,7 +27943,7 @@
         <v>0.5946</v>
       </c>
       <c r="AA533" t="n">
-        <v>0.6848279069767441</v>
+        <v>0.521045</v>
       </c>
     </row>
     <row r="534">
@@ -27957,7 +27957,7 @@
         <v>0.66096</v>
       </c>
       <c r="AA534" t="n">
-        <v>0.5456272727272726</v>
+        <v>0.4969525</v>
       </c>
     </row>
     <row r="535">
@@ -27971,7 +27971,7 @@
         <v>0.6568466666666666</v>
       </c>
       <c r="AA535" t="n">
-        <v>0.6258264705882354</v>
+        <v>0.596545238095238</v>
       </c>
     </row>
     <row r="536">
@@ -27985,7 +27985,7 @@
         <v>0.4319142857142858</v>
       </c>
       <c r="AA536" t="n">
-        <v>0.6185942857142857</v>
+        <v>0.5141229166666667</v>
       </c>
     </row>
     <row r="537">
@@ -27999,7 +27999,7 @@
         <v>0.4905466666666667</v>
       </c>
       <c r="AA537" t="n">
-        <v>0.6100846153846153</v>
+        <v>0.5377682926829268</v>
       </c>
     </row>
     <row r="538">
@@ -28013,7 +28013,7 @@
         <v>0.5662631578947369</v>
       </c>
       <c r="AA538" t="n">
-        <v>0.5728333333333334</v>
+        <v>0.5237775</v>
       </c>
     </row>
     <row r="539">
@@ -28027,7 +28027,7 @@
         <v>0.6549142857142857</v>
       </c>
       <c r="AA539" t="n">
-        <v>0.6313678571428571</v>
+        <v>0.5336933333333334</v>
       </c>
     </row>
     <row r="540">
@@ -28041,7 +28041,7 @@
         <v>0.6198611111111111</v>
       </c>
       <c r="AA540" t="n">
-        <v>0.6163673076923076</v>
+        <v>0.4066681818181818</v>
       </c>
     </row>
     <row r="541">
@@ -28055,7 +28055,7 @@
         <v>0.5274348837209303</v>
       </c>
       <c r="AA541" t="n">
-        <v>0.4877974358974358</v>
+        <v>0.5121327868852459</v>
       </c>
     </row>
     <row r="542">
@@ -28069,7 +28069,7 @@
         <v>0.6896666666666665</v>
       </c>
       <c r="AA542" t="n">
-        <v>0.665665</v>
+        <v>0.6524575757575758</v>
       </c>
     </row>
     <row r="543">
@@ -28083,7 +28083,7 @@
         <v>0.5695717948717949</v>
       </c>
       <c r="AA543" t="n">
-        <v>0.6173057692307693</v>
+        <v>0.5775309523809523</v>
       </c>
     </row>
     <row r="544">
@@ -28097,7 +28097,7 @@
         <v>0.6639787878787879</v>
       </c>
       <c r="AA544" t="n">
-        <v>0.5988727272727273</v>
+        <v>0.5077702127659574</v>
       </c>
     </row>
     <row r="545">
@@ -28111,7 +28111,7 @@
         <v>0.5534250000000001</v>
       </c>
       <c r="AA545" t="n">
-        <v>0.5021037037037037</v>
+        <v>0.5702750000000001</v>
       </c>
     </row>
     <row r="546">
@@ -28125,7 +28125,7 @@
         <v>0.6399192307692307</v>
       </c>
       <c r="AA546" t="n">
-        <v>0.6558608695652174</v>
+        <v>0.51461</v>
       </c>
     </row>
     <row r="547">
@@ -28139,7 +28139,7 @@
         <v>0.5865676470588235</v>
       </c>
       <c r="AA547" t="n">
-        <v>0.5952891891891892</v>
+        <v>0.4843984126984127</v>
       </c>
     </row>
     <row r="548">
@@ -28153,7 +28153,7 @@
         <v>0.7291124999999999</v>
       </c>
       <c r="AA548" t="n">
-        <v>0.57834375</v>
+        <v>0.6421205128205129</v>
       </c>
     </row>
     <row r="549">
@@ -28167,7 +28167,7 @@
         <v>0.51255</v>
       </c>
       <c r="AA549" t="n">
-        <v>0.6257139534883721</v>
+        <v>0.6260354166666667</v>
       </c>
     </row>
     <row r="550">
@@ -28181,7 +28181,7 @@
         <v>0.403544</v>
       </c>
       <c r="AA550" t="n">
-        <v>0.5888906976744187</v>
+        <v>0.48785625</v>
       </c>
     </row>
     <row r="551">
@@ -28195,7 +28195,7 @@
         <v>0.6891782608695652</v>
       </c>
       <c r="AA551" t="n">
-        <v>0.5116847826086958</v>
+        <v>0.5245673076923077</v>
       </c>
     </row>
     <row r="552">
@@ -28209,7 +28209,7 @@
         <v>0.665109090909091</v>
       </c>
       <c r="AA552" t="n">
-        <v>0.6573733333333335</v>
+        <v>0.6220530612244899</v>
       </c>
     </row>
     <row r="553">
@@ -28223,7 +28223,7 @@
         <v>0.7633285714285715</v>
       </c>
       <c r="AA553" t="n">
-        <v>0.7558745098039216</v>
+        <v>0.4655435897435897</v>
       </c>
     </row>
     <row r="554">
@@ -28237,7 +28237,7 @@
         <v>0.5718235294117647</v>
       </c>
       <c r="AA554" t="n">
-        <v>0.6680148936170212</v>
+        <v>0.4998842105263158</v>
       </c>
     </row>
     <row r="555">
@@ -28251,7 +28251,7 @@
         <v>0.4944333333333334</v>
       </c>
       <c r="AA555" t="n">
-        <v>0.5950466666666666</v>
+        <v>0.4882384615384615</v>
       </c>
     </row>
     <row r="556">
@@ -28265,7 +28265,7 @@
         <v>0.5334192307692307</v>
       </c>
       <c r="AA556" t="n">
-        <v>0.6421466666666666</v>
+        <v>0.6413152173913044</v>
       </c>
     </row>
     <row r="557">
@@ -28279,7 +28279,7 @@
         <v>0.6652948717948717</v>
       </c>
       <c r="AA557" t="n">
-        <v>0.7343022222222223</v>
+        <v>0.5343605263157895</v>
       </c>
     </row>
     <row r="558">
@@ -28293,7 +28293,7 @@
         <v>0.6767871794871795</v>
       </c>
       <c r="AA558" t="n">
-        <v>0.6711365384615385</v>
+        <v>0.5329367346938776</v>
       </c>
     </row>
     <row r="559">
@@ -28307,7 +28307,7 @@
         <v>0.6643642857142857</v>
       </c>
       <c r="AA559" t="n">
-        <v>0.6895866666666667</v>
+        <v>0.6104410256410256</v>
       </c>
     </row>
     <row r="560">
@@ -28321,7 +28321,7 @@
         <v>0.5512888888888889</v>
       </c>
       <c r="AA560" t="n">
-        <v>0.6887972972972972</v>
+        <v>0.5950268292682928</v>
       </c>
     </row>
     <row r="561">
@@ -28335,7 +28335,7 @@
         <v>0.5340041666666667</v>
       </c>
       <c r="AA561" t="n">
-        <v>0.5922727272727273</v>
+        <v>0.441603125</v>
       </c>
     </row>
     <row r="562">
@@ -28349,7 +28349,7 @@
         <v>0.5774548387096774</v>
       </c>
       <c r="AA562" t="n">
-        <v>0.6309488888888889</v>
+        <v>0.6010678571428573</v>
       </c>
     </row>
     <row r="563">
@@ -28363,7 +28363,7 @@
         <v>0.5707469387755102</v>
       </c>
       <c r="AA563" t="n">
-        <v>0.6445028571428572</v>
+        <v>0.6127653846153845</v>
       </c>
     </row>
     <row r="564">
@@ -28377,7 +28377,7 @@
         <v>0.6892228571428571</v>
       </c>
       <c r="AA564" t="n">
-        <v>0.6663933333333334</v>
+        <v>0.6603836734693878</v>
       </c>
     </row>
     <row r="565">
@@ -28391,7 +28391,7 @@
         <v>0.7552735294117646</v>
       </c>
       <c r="AA565" t="n">
-        <v>0.6736270833333333</v>
+        <v>0.5141492307692308</v>
       </c>
     </row>
     <row r="566">
@@ -28405,7 +28405,7 @@
         <v>0.6122038461538462</v>
       </c>
       <c r="AA566" t="n">
-        <v>0.6882424242424243</v>
+        <v>0.4987422222222223</v>
       </c>
     </row>
     <row r="567">
@@ -28419,7 +28419,7 @@
         <v>0.6051033333333333</v>
       </c>
       <c r="AA567" t="n">
-        <v>0.6665745098039215</v>
+        <v>0.5939326086956522</v>
       </c>
     </row>
     <row r="568">
@@ -28433,7 +28433,7 @@
         <v>0.5728085714285714</v>
       </c>
       <c r="AA568" t="n">
-        <v>0.7017230769230769</v>
+        <v>0.5251333333333333</v>
       </c>
     </row>
     <row r="569">
@@ -28447,7 +28447,7 @@
         <v>0.6224448275862069</v>
       </c>
       <c r="AA569" t="n">
-        <v>0.659205</v>
+        <v>0.5992499999999999</v>
       </c>
     </row>
     <row r="570">
@@ -28461,7 +28461,7 @@
         <v>0.5463219512195122</v>
       </c>
       <c r="AA570" t="n">
-        <v>0.651242372881356</v>
+        <v>0.6631638297872341</v>
       </c>
     </row>
     <row r="571">
@@ -28475,7 +28475,7 @@
         <v>0.6152882352941177</v>
       </c>
       <c r="AA571" t="n">
-        <v>0.7250404761904763</v>
+        <v>0.5964181818181817</v>
       </c>
     </row>
     <row r="572">
@@ -28489,7 +28489,7 @@
         <v>0.7281888888888889</v>
       </c>
       <c r="AA572" t="n">
-        <v>0.6657388888888889</v>
+        <v>0.5253585365853659</v>
       </c>
     </row>
     <row r="573">
@@ -28503,7 +28503,7 @@
         <v>0.6208342857142858</v>
       </c>
       <c r="AA573" t="n">
-        <v>0.7583479166666666</v>
+        <v>0.5742934782608696</v>
       </c>
     </row>
     <row r="574">
@@ -28517,7 +28517,7 @@
         <v>0.5563942857142858</v>
       </c>
       <c r="AA574" t="n">
-        <v>0.6681622222222223</v>
+        <v>0.5569725</v>
       </c>
     </row>
     <row r="575">
@@ -28531,7 +28531,7 @@
         <v>0.6112519999999999</v>
       </c>
       <c r="AA575" t="n">
-        <v>0.6068476190476191</v>
+        <v>0.6183319999999999</v>
       </c>
     </row>
     <row r="576">
@@ -28545,7 +28545,7 @@
         <v>0.6955290322580645</v>
       </c>
       <c r="AA576" t="n">
-        <v>0.6538309523809525</v>
+        <v>0.5858706896551724</v>
       </c>
     </row>
     <row r="577">
@@ -28559,7 +28559,7 @@
         <v>0.4959947368421053</v>
       </c>
       <c r="AA577" t="n">
-        <v>0.6121457142857143</v>
+        <v>0.5512756756756757</v>
       </c>
     </row>
     <row r="578">
@@ -28573,7 +28573,7 @@
         <v>0.6100741935483872</v>
       </c>
       <c r="AA578" t="n">
-        <v>0.7064173913043478</v>
+        <v>0.5080931034482759</v>
       </c>
     </row>
     <row r="579">
@@ -28587,7 +28587,7 @@
         <v>0.5967152173913043</v>
       </c>
       <c r="AA579" t="n">
-        <v>0.6773547619047618</v>
+        <v>0.5646800000000001</v>
       </c>
     </row>
     <row r="580">
@@ -28601,7 +28601,7 @@
         <v>0.6547142857142856</v>
       </c>
       <c r="AA580" t="n">
-        <v>0.7281342857142855</v>
+        <v>0.5087804347826087</v>
       </c>
     </row>
     <row r="581">
@@ -28615,7 +28615,7 @@
         <v>0.5921229166666667</v>
       </c>
       <c r="AA581" t="n">
-        <v>0.6583474576271187</v>
+        <v>0.6648603773584905</v>
       </c>
     </row>
     <row r="582">
@@ -28629,7 +28629,7 @@
         <v>0.4805809523809524</v>
       </c>
       <c r="AA582" t="n">
-        <v>0.7289357142857142</v>
+        <v>0.4996593749999999</v>
       </c>
     </row>
     <row r="583">
@@ -28643,7 +28643,7 @@
         <v>0.6079785714285715</v>
       </c>
       <c r="AA583" t="n">
-        <v>0.6687142857142858</v>
+        <v>0.5465696428571428</v>
       </c>
     </row>
     <row r="584">
@@ -28657,7 +28657,7 @@
         <v>0.598955172413793</v>
       </c>
       <c r="AA584" t="n">
-        <v>0.6521333333333333</v>
+        <v>0.6259864864864864</v>
       </c>
     </row>
     <row r="585">
@@ -28671,7 +28671,7 @@
         <v>0.6390794117647057</v>
       </c>
       <c r="AA585" t="n">
-        <v>0.6670575</v>
+        <v>0.5657333333333333</v>
       </c>
     </row>
     <row r="586">
@@ -28685,7 +28685,7 @@
         <v>0.5833744680851064</v>
       </c>
       <c r="AA586" t="n">
-        <v>0.8039488372093023</v>
+        <v>0.5171553191489361</v>
       </c>
     </row>
     <row r="587">
@@ -28699,7 +28699,7 @@
         <v>0.5716243243243243</v>
       </c>
       <c r="AA587" t="n">
-        <v>0.6614073170731707</v>
+        <v>0.5934499999999999</v>
       </c>
     </row>
     <row r="588">
@@ -28713,7 +28713,7 @@
         <v>0.7240564102564102</v>
       </c>
       <c r="AA588" t="n">
-        <v>0.6679297872340426</v>
+        <v>0.5607759259259258</v>
       </c>
     </row>
     <row r="589">
@@ -28727,7 +28727,7 @@
         <v>0.52284</v>
       </c>
       <c r="AA589" t="n">
-        <v>0.7550333333333333</v>
+        <v>0.49087</v>
       </c>
     </row>
     <row r="590">
@@ -28741,7 +28741,7 @@
         <v>0.4799804878048781</v>
       </c>
       <c r="AA590" t="n">
-        <v>0.7116791666666668</v>
+        <v>0.5817833333333334</v>
       </c>
     </row>
     <row r="591">
@@ -28755,7 +28755,7 @@
         <v>0.4990285714285714</v>
       </c>
       <c r="AA591" t="n">
-        <v>0.6067279069767442</v>
+        <v>0.5406019607843137</v>
       </c>
     </row>
     <row r="592">
@@ -28769,7 +28769,7 @@
         <v>0.694125</v>
       </c>
       <c r="AA592" t="n">
-        <v>0.6801018518518518</v>
+        <v>0.5149092592592592</v>
       </c>
     </row>
     <row r="593">
@@ -28783,7 +28783,7 @@
         <v>0.6150069767441861</v>
       </c>
       <c r="AA593" t="n">
-        <v>0.6837478260869565</v>
+        <v>0.7144238095238096</v>
       </c>
     </row>
     <row r="594">
@@ -28797,7 +28797,7 @@
         <v>0.5700219512195123</v>
       </c>
       <c r="AA594" t="n">
-        <v>0.6470499999999999</v>
+        <v>0.5592714285714285</v>
       </c>
     </row>
     <row r="595">
@@ -28811,7 +28811,7 @@
         <v>0.5627275862068966</v>
       </c>
       <c r="AA595" t="n">
-        <v>0.6458870967741935</v>
+        <v>0.479385</v>
       </c>
     </row>
     <row r="596">
@@ -28825,7 +28825,7 @@
         <v>0.6455302325581395</v>
       </c>
       <c r="AA596" t="n">
-        <v>0.786396551724138</v>
+        <v>0.6223137254901961</v>
       </c>
     </row>
     <row r="597">
@@ -28839,7 +28839,7 @@
         <v>0.7108176470588237</v>
       </c>
       <c r="AA597" t="n">
-        <v>0.667086842105263</v>
+        <v>0.5880897959183672</v>
       </c>
     </row>
     <row r="598">
@@ -28853,7 +28853,7 @@
         <v>0.6385071428571428</v>
       </c>
       <c r="AA598" t="n">
-        <v>0.6423523809523809</v>
+        <v>0.5511517857142857</v>
       </c>
     </row>
     <row r="599">
@@ -28867,7 +28867,7 @@
         <v>0.5458820512820513</v>
       </c>
       <c r="AA599" t="n">
-        <v>0.6490739999999999</v>
+        <v>0.5589740740740742</v>
       </c>
     </row>
     <row r="600">
@@ -28881,7 +28881,7 @@
         <v>0.532246875</v>
       </c>
       <c r="AA600" t="n">
-        <v>0.6220224137931034</v>
+        <v>0.5019096153846154</v>
       </c>
     </row>
     <row r="601">
@@ -28895,7 +28895,7 @@
         <v>0.5549357142857142</v>
       </c>
       <c r="AA601" t="n">
-        <v>0.7154021739130434</v>
+        <v>0.5391431818181819</v>
       </c>
     </row>
     <row r="602">
@@ -28909,7 +28909,7 @@
         <v>0.7065083333333333</v>
       </c>
       <c r="AA602" t="n">
-        <v>0.7579340909090907</v>
+        <v>0.5390069767441861</v>
       </c>
     </row>
     <row r="603">
@@ -28923,7 +28923,7 @@
         <v>0.6395676470588235</v>
       </c>
       <c r="AA603" t="n">
-        <v>0.638104081632653</v>
+        <v>0.5873901639344262</v>
       </c>
     </row>
     <row r="604">
@@ -28937,7 +28937,7 @@
         <v>0.6396636363636362</v>
       </c>
       <c r="AA604" t="n">
-        <v>0.6717448979591836</v>
+        <v>0.5095324999999999</v>
       </c>
     </row>
     <row r="605">
@@ -28951,7 +28951,7 @@
         <v>0.5641179487179487</v>
       </c>
       <c r="AA605" t="n">
-        <v>0.771755882352941</v>
+        <v>0.6173886363636364</v>
       </c>
     </row>
     <row r="606">
@@ -28965,7 +28965,7 @@
         <v>0.621946875</v>
       </c>
       <c r="AA606" t="n">
-        <v>0.7031678571428573</v>
+        <v>0.5851760869565218</v>
       </c>
     </row>
     <row r="607">
@@ -28979,7 +28979,7 @@
         <v>0.6232799999999999</v>
       </c>
       <c r="AA607" t="n">
-        <v>0.6817839999999999</v>
+        <v>0.4493627450980393</v>
       </c>
     </row>
     <row r="608">
@@ -28993,7 +28993,7 @@
         <v>0.6362740000000001</v>
       </c>
       <c r="AA608" t="n">
-        <v>0.7092674999999999</v>
+        <v>0.5960224489795919</v>
       </c>
     </row>
     <row r="609">
@@ -29007,7 +29007,7 @@
         <v>0.55772</v>
       </c>
       <c r="AA609" t="n">
-        <v>0.5889354838709678</v>
+        <v>0.547230303030303</v>
       </c>
     </row>
     <row r="610">
@@ -29021,7 +29021,7 @@
         <v>0.4664517241379311</v>
       </c>
       <c r="AA610" t="n">
-        <v>0.5540348837209302</v>
+        <v>0.6911536585365854</v>
       </c>
     </row>
     <row r="611">
@@ -29035,7 +29035,7 @@
         <v>0.6732795454545454</v>
       </c>
       <c r="AA611" t="n">
-        <v>0.7603851063829786</v>
+        <v>0.6239090909090909</v>
       </c>
     </row>
     <row r="612">
@@ -29049,7 +29049,7 @@
         <v>0.6169535714285715</v>
       </c>
       <c r="AA612" t="n">
-        <v>0.7477951219512194</v>
+        <v>0.7069095238095239</v>
       </c>
     </row>
     <row r="613">
@@ -29063,7 +29063,7 @@
         <v>0.4789849999999999</v>
       </c>
       <c r="AA613" t="n">
-        <v>0.7485960784313724</v>
+        <v>0.4788657894736842</v>
       </c>
     </row>
     <row r="614">
@@ -29077,7 +29077,7 @@
         <v>0.5759888888888889</v>
       </c>
       <c r="AA614" t="n">
-        <v>0.7261137254901961</v>
+        <v>0.5634488888888888</v>
       </c>
     </row>
     <row r="615">
@@ -29091,7 +29091,7 @@
         <v>0.668975</v>
       </c>
       <c r="AA615" t="n">
-        <v>0.6867090909090909</v>
+        <v>0.440453488372093</v>
       </c>
     </row>
     <row r="616">
@@ -29105,7 +29105,7 @@
         <v>0.6202913043478261</v>
       </c>
       <c r="AA616" t="n">
-        <v>0.60194</v>
+        <v>0.5414022727272728</v>
       </c>
     </row>
     <row r="617">
@@ -29119,7 +29119,7 @@
         <v>0.62405625</v>
       </c>
       <c r="AA617" t="n">
-        <v>0.7461047619047618</v>
+        <v>0.5687756097560975</v>
       </c>
     </row>
     <row r="618">
@@ -29133,7 +29133,7 @@
         <v>0.5123303030303029</v>
       </c>
       <c r="AA618" t="n">
-        <v>0.5818157894736843</v>
+        <v>0.7262470588235295</v>
       </c>
     </row>
     <row r="619">
@@ -29147,7 +29147,7 @@
         <v>0.7207055555555555</v>
       </c>
       <c r="AA619" t="n">
-        <v>0.6838878048780488</v>
+        <v>0.556756</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -713,6 +713,12 @@
       <c r="AA5" t="n">
         <v>0.1503263157894737</v>
       </c>
+      <c r="AB5" t="n">
+        <v>0.1565506493506493</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1717970149253731</v>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1" s="8">
       <c r="A6" s="5" t="n">
@@ -781,6 +787,12 @@
       <c r="AA6" t="n">
         <v>0.1370313432835821</v>
       </c>
+      <c r="AB6" t="n">
+        <v>0.2966888888888889</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1786</v>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1" s="8">
       <c r="A7" s="5" t="n">
@@ -849,6 +861,12 @@
       <c r="AA7" t="n">
         <v>0.2822538461538462</v>
       </c>
+      <c r="AB7" t="n">
+        <v>0.2955571428571429</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.2222</v>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1" s="8">
       <c r="A8" s="5" t="n">
@@ -917,6 +935,12 @@
       <c r="AA8" t="n">
         <v>0.3265232558139535</v>
       </c>
+      <c r="AB8" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.3138875</v>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1" s="8">
       <c r="A9" s="5" t="n">
@@ -985,6 +1009,9 @@
       <c r="AA9" t="n">
         <v>0.3048380952380952</v>
       </c>
+      <c r="AB9" t="n">
+        <v>0.4813499999999999</v>
+      </c>
     </row>
     <row r="10" ht="16" customHeight="1" s="8">
       <c r="A10" s="5" t="n">
@@ -1053,6 +1080,9 @@
       <c r="AA10" t="n">
         <v>0.4200117647058824</v>
       </c>
+      <c r="AB10" t="n">
+        <v>0.6071333333333333</v>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1" s="8">
       <c r="A11" s="5" t="n">
@@ -1121,6 +1151,9 @@
       <c r="AA11" t="n">
         <v>0.3645641025641025</v>
       </c>
+      <c r="AB11" t="n">
+        <v>0.5877588235294118</v>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="8">
       <c r="A12" s="5" t="n">
@@ -1189,6 +1222,9 @@
       <c r="AA12" t="n">
         <v>0.4690476190476191</v>
       </c>
+      <c r="AB12" t="n">
+        <v>0.543996</v>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1" s="8">
       <c r="A13" s="5" t="n">
@@ -1257,6 +1293,9 @@
       <c r="AA13" t="n">
         <v>0.5697461538461538</v>
       </c>
+      <c r="AB13" t="n">
+        <v>0.63365</v>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="8">
       <c r="A14" s="5" t="n">
@@ -1325,6 +1364,9 @@
       <c r="AA14" t="n">
         <v>0.6524676470588234</v>
       </c>
+      <c r="AB14" t="n">
+        <v>0.7116666666666667</v>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="8">
       <c r="A15" s="5" t="n">
@@ -1384,6 +1426,9 @@
       <c r="AA15" t="n">
         <v>0.6183310344827586</v>
       </c>
+      <c r="AB15" t="n">
+        <v>0.7897307692307692</v>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="8">
       <c r="A16" s="5" t="n">
@@ -1443,6 +1488,9 @@
       <c r="AA16" t="n">
         <v>0.6850227272727273</v>
       </c>
+      <c r="AB16" t="n">
+        <v>0.6891272727272729</v>
+      </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="8">
       <c r="A17" s="5" t="n">
@@ -1502,6 +1550,9 @@
       <c r="AA17" t="n">
         <v>0.6262787878787878</v>
       </c>
+      <c r="AB17" t="n">
+        <v>0.711895652173913</v>
+      </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="8">
       <c r="A18" s="5" t="n">
@@ -1561,6 +1612,9 @@
       <c r="AA18" t="n">
         <v>0.7097275862068966</v>
       </c>
+      <c r="AB18" t="n">
+        <v>0.7979647058823529</v>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="8">
       <c r="A19" s="5" t="n">
@@ -1620,6 +1674,9 @@
       <c r="AA19" t="n">
         <v>0.6938717948717948</v>
       </c>
+      <c r="AB19" t="n">
+        <v>0.7774757575757576</v>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="8">
       <c r="A20" s="5" t="n">
@@ -1679,6 +1736,9 @@
       <c r="AA20" t="n">
         <v>0.731275</v>
       </c>
+      <c r="AB20" t="n">
+        <v>0.7733652173913044</v>
+      </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="8">
       <c r="A21" s="5" t="n">
@@ -1738,6 +1798,9 @@
       <c r="AA21" t="n">
         <v>0.8297653846153847</v>
       </c>
+      <c r="AB21" t="n">
+        <v>0.8179666666666667</v>
+      </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="8">
       <c r="A22" s="5" t="n">
@@ -1797,6 +1860,9 @@
       <c r="AA22" t="n">
         <v>0.7652514285714286</v>
       </c>
+      <c r="AB22" t="n">
+        <v>0.8153793103448276</v>
+      </c>
     </row>
     <row r="23" ht="16" customHeight="1" s="8">
       <c r="A23" s="5" t="n">
@@ -1856,6 +1922,9 @@
       <c r="AA23" t="n">
         <v>0.7396179487179487</v>
       </c>
+      <c r="AB23" t="n">
+        <v>0.8028736842105263</v>
+      </c>
     </row>
     <row r="24" ht="16" customHeight="1" s="8">
       <c r="A24" s="5" t="n">
@@ -1915,6 +1984,9 @@
       <c r="AA24" t="n">
         <v>0.7673863636363637</v>
       </c>
+      <c r="AB24" t="n">
+        <v>0.7993926829268293</v>
+      </c>
     </row>
     <row r="25" ht="16" customHeight="1" s="8">
       <c r="A25" s="5" t="n">
@@ -1974,6 +2046,9 @@
       <c r="AA25" t="n">
         <v>0.7187775000000001</v>
       </c>
+      <c r="AB25" t="n">
+        <v>0.8418794117647059</v>
+      </c>
     </row>
     <row r="26" ht="16" customHeight="1" s="8">
       <c r="A26" s="5" t="n">
@@ -2033,6 +2108,9 @@
       <c r="AA26" t="n">
         <v>0.7476266666666668</v>
       </c>
+      <c r="AB26" t="n">
+        <v>0.8243666666666667</v>
+      </c>
     </row>
     <row r="27" ht="16" customHeight="1" s="8">
       <c r="A27" s="5" t="n">
@@ -2092,6 +2170,9 @@
       <c r="AA27" t="n">
         <v>0.8238355555555554</v>
       </c>
+      <c r="AB27" t="n">
+        <v>0.8491581395348838</v>
+      </c>
     </row>
     <row r="28" ht="16" customHeight="1" s="8">
       <c r="A28" s="5" t="n">
@@ -2151,6 +2232,9 @@
       <c r="AA28" t="n">
         <v>0.833539534883721</v>
       </c>
+      <c r="AB28" t="n">
+        <v>0.8293333333333334</v>
+      </c>
     </row>
     <row r="29" ht="16" customHeight="1" s="8">
       <c r="A29" s="5" t="n">
@@ -2210,6 +2294,9 @@
       <c r="AA29" t="n">
         <v>0.809702564102564</v>
       </c>
+      <c r="AB29" t="n">
+        <v>0.8446454545454546</v>
+      </c>
     </row>
     <row r="30" ht="16" customHeight="1" s="8">
       <c r="A30" s="5" t="n">
@@ -2269,6 +2356,9 @@
       <c r="AA30" t="n">
         <v>0.76524375</v>
       </c>
+      <c r="AB30" t="n">
+        <v>0.8001500000000001</v>
+      </c>
     </row>
     <row r="31" ht="16" customHeight="1" s="8">
       <c r="A31" s="5" t="n">
@@ -2328,6 +2418,9 @@
       <c r="AA31" t="n">
         <v>0.8324634146341465</v>
       </c>
+      <c r="AB31" t="n">
+        <v>0.851904</v>
+      </c>
     </row>
     <row r="32" ht="16" customHeight="1" s="8">
       <c r="A32" s="5" t="n">
@@ -2387,6 +2480,9 @@
       <c r="AA32" t="n">
         <v>0.7792032258064516</v>
       </c>
+      <c r="AB32" t="n">
+        <v>0.8850120000000001</v>
+      </c>
     </row>
     <row r="33" ht="16" customHeight="1" s="8">
       <c r="A33" s="5" t="n">
@@ -2446,6 +2542,9 @@
       <c r="AA33" t="n">
         <v>0.8311673469387755</v>
       </c>
+      <c r="AB33" t="n">
+        <v>0.8240428571428572</v>
+      </c>
     </row>
     <row r="34" ht="16" customHeight="1" s="8">
       <c r="A34" s="5" t="n">
@@ -2505,6 +2604,9 @@
       <c r="AA34" t="n">
         <v>0.7618885714285716</v>
       </c>
+      <c r="AB34" t="n">
+        <v>0.8328300000000001</v>
+      </c>
     </row>
     <row r="35" ht="16" customHeight="1" s="8">
       <c r="A35" s="5" t="n">
@@ -2564,6 +2666,9 @@
       <c r="AA35" t="n">
         <v>0.8191325</v>
       </c>
+      <c r="AB35" t="n">
+        <v>0.7856739130434782</v>
+      </c>
     </row>
     <row r="36" ht="16" customHeight="1" s="8">
       <c r="A36" s="5" t="n">
@@ -2623,6 +2728,9 @@
       <c r="AA36" t="n">
         <v>0.8419833333333333</v>
       </c>
+      <c r="AB36" t="n">
+        <v>0.8822038461538462</v>
+      </c>
     </row>
     <row r="37" ht="16" customHeight="1" s="8">
       <c r="A37" s="5" t="n">
@@ -2682,6 +2790,9 @@
       <c r="AA37" t="n">
         <v>0.850497142857143</v>
       </c>
+      <c r="AB37" t="n">
+        <v>0.879169696969697</v>
+      </c>
     </row>
     <row r="38" ht="16" customHeight="1" s="8">
       <c r="A38" s="5" t="n">
@@ -2741,6 +2852,9 @@
       <c r="AA38" t="n">
         <v>0.7746090909090908</v>
       </c>
+      <c r="AB38" t="n">
+        <v>0.868892857142857</v>
+      </c>
     </row>
     <row r="39" ht="16" customHeight="1" s="8">
       <c r="A39" s="5" t="n">
@@ -2800,6 +2914,9 @@
       <c r="AA39" t="n">
         <v>0.7947928571428571</v>
       </c>
+      <c r="AB39" t="n">
+        <v>0.8924771428571429</v>
+      </c>
     </row>
     <row r="40" ht="16" customHeight="1" s="8">
       <c r="A40" s="5" t="n">
@@ -2859,6 +2976,9 @@
       <c r="AA40" t="n">
         <v>0.819278947368421</v>
       </c>
+      <c r="AB40" t="n">
+        <v>0.7941434782608695</v>
+      </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="8">
       <c r="A41" s="5" t="n">
@@ -2918,6 +3038,9 @@
       <c r="AA41" t="n">
         <v>0.8360870967741936</v>
       </c>
+      <c r="AB41" t="n">
+        <v>0.8387541666666668</v>
+      </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="8">
       <c r="A42" s="5" t="n">
@@ -2977,6 +3100,9 @@
       <c r="AA42" t="n">
         <v>0.8378558823529412</v>
       </c>
+      <c r="AB42" t="n">
+        <v>0.8306114285714286</v>
+      </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="8">
       <c r="A43" s="5" t="n">
@@ -3036,6 +3162,9 @@
       <c r="AA43" t="n">
         <v>0.817224</v>
       </c>
+      <c r="AB43" t="n">
+        <v>0.9300814814814815</v>
+      </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="8">
       <c r="A44" s="5" t="n">
@@ -3095,6 +3224,9 @@
       <c r="AA44" t="n">
         <v>0.7912714285714287</v>
       </c>
+      <c r="AB44" t="n">
+        <v>0.8689578947368422</v>
+      </c>
     </row>
     <row r="45" ht="16" customHeight="1" s="8">
       <c r="A45" s="5" t="n">
@@ -3154,6 +3286,9 @@
       <c r="AA45" t="n">
         <v>0.8187472222222224</v>
       </c>
+      <c r="AB45" t="n">
+        <v>0.9127233333333333</v>
+      </c>
     </row>
     <row r="46" ht="16" customHeight="1" s="8">
       <c r="A46" s="5" t="n">
@@ -3213,6 +3348,9 @@
       <c r="AA46" t="n">
         <v>0.7164423076923078</v>
       </c>
+      <c r="AB46" t="n">
+        <v>0.7973818181818182</v>
+      </c>
     </row>
     <row r="47" ht="16" customHeight="1" s="8">
       <c r="A47" s="5" t="n">
@@ -3272,6 +3410,9 @@
       <c r="AA47" t="n">
         <v>0.7947</v>
       </c>
+      <c r="AB47" t="n">
+        <v>0.9488800000000002</v>
+      </c>
     </row>
     <row r="48" ht="16" customHeight="1" s="8">
       <c r="A48" s="5" t="n">
@@ -3331,6 +3472,9 @@
       <c r="AA48" t="n">
         <v>0.8059649999999999</v>
       </c>
+      <c r="AB48" t="n">
+        <v>0.7659250000000001</v>
+      </c>
     </row>
     <row r="49" ht="16" customHeight="1" s="8">
       <c r="A49" s="5" t="n">
@@ -3390,6 +3534,9 @@
       <c r="AA49" t="n">
         <v>0.8694388888888888</v>
       </c>
+      <c r="AB49" t="n">
+        <v>0.8882869565217391</v>
+      </c>
     </row>
     <row r="50" ht="16" customHeight="1" s="8">
       <c r="A50" s="5" t="n">
@@ -3449,6 +3596,9 @@
       <c r="AA50" t="n">
         <v>0.7681151515151515</v>
       </c>
+      <c r="AB50" t="n">
+        <v>0.8594724137931035</v>
+      </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="8">
       <c r="A51" s="5" t="n">
@@ -3508,6 +3658,9 @@
       <c r="AA51" t="n">
         <v>0.7985548387096775</v>
       </c>
+      <c r="AB51" t="n">
+        <v>0.7463260869565218</v>
+      </c>
     </row>
     <row r="52" ht="16" customHeight="1" s="8">
       <c r="A52" s="5" t="n">
@@ -3567,6 +3720,9 @@
       <c r="AA52" t="n">
         <v>0.7410625000000001</v>
       </c>
+      <c r="AB52" t="n">
+        <v>0.8244222222222223</v>
+      </c>
     </row>
     <row r="53" ht="16" customHeight="1" s="8">
       <c r="A53" s="5" t="n">
@@ -3626,6 +3782,9 @@
       <c r="AA53" t="n">
         <v>0.8776172413793104</v>
       </c>
+      <c r="AB53" t="n">
+        <v>0.8351823529411765</v>
+      </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="8">
       <c r="A54" s="5" t="n">
@@ -3685,6 +3844,9 @@
       <c r="AA54" t="n">
         <v>0.7919543478260869</v>
       </c>
+      <c r="AB54" t="n">
+        <v>0.8721192307692309</v>
+      </c>
     </row>
     <row r="55" ht="16" customHeight="1" s="8">
       <c r="A55" s="5" t="n">
@@ -3744,6 +3906,9 @@
       <c r="AA55" t="n">
         <v>0.8011666666666667</v>
       </c>
+      <c r="AB55" t="n">
+        <v>0.8632266666666667</v>
+      </c>
     </row>
     <row r="56" ht="16" customHeight="1" s="8">
       <c r="A56" s="5" t="n">
@@ -3803,6 +3968,9 @@
       <c r="AA56" t="n">
         <v>0.8763342105263158</v>
       </c>
+      <c r="AB56" t="n">
+        <v>0.8737571428571429</v>
+      </c>
     </row>
     <row r="57" ht="16" customHeight="1" s="8">
       <c r="A57" s="5" t="n">
@@ -3862,6 +4030,9 @@
       <c r="AA57" t="n">
         <v>0.71888125</v>
       </c>
+      <c r="AB57" t="n">
+        <v>0.8767655172413792</v>
+      </c>
     </row>
     <row r="58" ht="16" customHeight="1" s="8">
       <c r="A58" s="5" t="n">
@@ -3921,6 +4092,9 @@
       <c r="AA58" t="n">
         <v>0.7224274999999998</v>
       </c>
+      <c r="AB58" t="n">
+        <v>0.8986703703703705</v>
+      </c>
     </row>
     <row r="59" ht="16" customHeight="1" s="8">
       <c r="A59" s="5" t="n">
@@ -3980,6 +4154,9 @@
       <c r="AA59" t="n">
         <v>0.8722051282051283</v>
       </c>
+      <c r="AB59" t="n">
+        <v>0.8903555555555555</v>
+      </c>
     </row>
     <row r="60" ht="16" customHeight="1" s="8">
       <c r="A60" s="5" t="n">
@@ -4039,6 +4216,9 @@
       <c r="AA60" t="n">
         <v>0.8074731707317072</v>
       </c>
+      <c r="AB60" t="n">
+        <v>0.8382350000000001</v>
+      </c>
     </row>
     <row r="61" ht="16" customHeight="1" s="8">
       <c r="A61" s="5" t="n">
@@ -4098,6 +4278,9 @@
       <c r="AA61" t="n">
         <v>0.7406347826086958</v>
       </c>
+      <c r="AB61" t="n">
+        <v>0.8725458333333335</v>
+      </c>
     </row>
     <row r="62" ht="16" customHeight="1" s="8">
       <c r="A62" s="5" t="n">
@@ -4157,6 +4340,9 @@
       <c r="AA62" t="n">
         <v>0.8017111111111112</v>
       </c>
+      <c r="AB62" t="n">
+        <v>0.8268099999999999</v>
+      </c>
     </row>
     <row r="63" ht="16" customHeight="1" s="8">
       <c r="A63" s="5" t="n">
@@ -4216,6 +4402,9 @@
       <c r="AA63" t="n">
         <v>0.8512631578947368</v>
       </c>
+      <c r="AB63" t="n">
+        <v>0.8560375</v>
+      </c>
     </row>
     <row r="64" ht="16" customHeight="1" s="8">
       <c r="A64" s="5" t="n">
@@ -4275,6 +4464,9 @@
       <c r="AA64" t="n">
         <v>0.7684000000000001</v>
       </c>
+      <c r="AB64" t="n">
+        <v>0.8609512195121951</v>
+      </c>
     </row>
     <row r="65" ht="16" customHeight="1" s="8">
       <c r="A65" s="5" t="n">
@@ -4334,6 +4526,9 @@
       <c r="AA65" t="n">
         <v>0.7363871794871795</v>
       </c>
+      <c r="AB65" t="n">
+        <v>0.9158225806451613</v>
+      </c>
     </row>
     <row r="66" ht="16" customHeight="1" s="8">
       <c r="A66" s="5" t="n">
@@ -4393,6 +4588,9 @@
       <c r="AA66" t="n">
         <v>0.804758</v>
       </c>
+      <c r="AB66" t="n">
+        <v>0.7863666666666667</v>
+      </c>
     </row>
     <row r="67" ht="16" customHeight="1" s="8">
       <c r="A67" s="5" t="n">
@@ -4452,6 +4650,9 @@
       <c r="AA67" t="n">
         <v>0.823209375</v>
       </c>
+      <c r="AB67" t="n">
+        <v>0.8075142857142857</v>
+      </c>
     </row>
     <row r="68" ht="16" customHeight="1" s="8">
       <c r="A68" s="5" t="n">
@@ -4511,6 +4712,9 @@
       <c r="AA68" t="n">
         <v>0.8456238095238094</v>
       </c>
+      <c r="AB68" t="n">
+        <v>0.8336285714285714</v>
+      </c>
     </row>
     <row r="69" ht="16" customHeight="1" s="8">
       <c r="A69" s="5" t="n">
@@ -4570,6 +4774,9 @@
       <c r="AA69" t="n">
         <v>0.8573868421052629</v>
       </c>
+      <c r="AB69" t="n">
+        <v>0.892</v>
+      </c>
     </row>
     <row r="70" ht="16" customHeight="1" s="8">
       <c r="A70" s="5" t="n">
@@ -4629,6 +4836,9 @@
       <c r="AA70" t="n">
         <v>0.8333857142857143</v>
       </c>
+      <c r="AB70" t="n">
+        <v>0.8063292682926829</v>
+      </c>
     </row>
     <row r="71" ht="16" customHeight="1" s="8">
       <c r="A71" s="5" t="n">
@@ -4688,6 +4898,9 @@
       <c r="AA71" t="n">
         <v>0.8163066666666666</v>
       </c>
+      <c r="AB71" t="n">
+        <v>0.9095689655172415</v>
+      </c>
     </row>
     <row r="72" ht="16" customHeight="1" s="8">
       <c r="A72" s="5" t="n">
@@ -4747,6 +4960,9 @@
       <c r="AA72" t="n">
         <v>0.8520303030303029</v>
       </c>
+      <c r="AB72" t="n">
+        <v>0.8695194444444444</v>
+      </c>
     </row>
     <row r="73" ht="16" customHeight="1" s="8">
       <c r="A73" s="5" t="n">
@@ -4806,6 +5022,9 @@
       <c r="AA73" t="n">
         <v>0.6898043478260869</v>
       </c>
+      <c r="AB73" t="n">
+        <v>0.8746653846153845</v>
+      </c>
     </row>
     <row r="74" ht="16" customHeight="1" s="8">
       <c r="A74" s="5" t="n">
@@ -4865,6 +5084,9 @@
       <c r="AA74" t="n">
         <v>0.6442952380952381</v>
       </c>
+      <c r="AB74" t="n">
+        <v>0.8889000000000001</v>
+      </c>
     </row>
     <row r="75" ht="16" customHeight="1" s="8">
       <c r="A75" s="5" t="n">
@@ -4924,6 +5146,9 @@
       <c r="AA75" t="n">
         <v>0.8359</v>
       </c>
+      <c r="AB75" t="n">
+        <v>0.6309923076923076</v>
+      </c>
     </row>
     <row r="76" ht="16" customHeight="1" s="8">
       <c r="A76" s="5" t="n">
@@ -4983,6 +5208,9 @@
       <c r="AA76" t="n">
         <v>0.7940199999999998</v>
       </c>
+      <c r="AB76" t="n">
+        <v>0.8597695652173912</v>
+      </c>
     </row>
     <row r="77" ht="16" customHeight="1" s="8">
       <c r="A77" s="5" t="n">
@@ -5042,6 +5270,9 @@
       <c r="AA77" t="n">
         <v>0.829121212121212</v>
       </c>
+      <c r="AB77" t="n">
+        <v>0.8647280000000001</v>
+      </c>
     </row>
     <row r="78" ht="16" customHeight="1" s="8">
       <c r="A78" s="5" t="n">
@@ -5101,6 +5332,9 @@
       <c r="AA78" t="n">
         <v>0.8609709677419355</v>
       </c>
+      <c r="AB78" t="n">
+        <v>0.8679470588235293</v>
+      </c>
     </row>
     <row r="79" ht="16" customHeight="1" s="8">
       <c r="A79" s="5" t="n">
@@ -5160,6 +5394,9 @@
       <c r="AA79" t="n">
         <v>0.8138607142857143</v>
       </c>
+      <c r="AB79" t="n">
+        <v>0.8089615384615385</v>
+      </c>
     </row>
     <row r="80" ht="16" customHeight="1" s="8">
       <c r="A80" s="5" t="n">
@@ -5219,6 +5456,9 @@
       <c r="AA80" t="n">
         <v>0.796008</v>
       </c>
+      <c r="AB80" t="n">
+        <v>0.7944740740740741</v>
+      </c>
     </row>
     <row r="81" ht="16" customHeight="1" s="8">
       <c r="A81" s="5" t="n">
@@ -5278,6 +5518,9 @@
       <c r="AA81" t="n">
         <v>0.7934555555555556</v>
       </c>
+      <c r="AB81" t="n">
+        <v>0.8063806451612904</v>
+      </c>
     </row>
     <row r="82" ht="16" customHeight="1" s="8">
       <c r="A82" s="5" t="n">
@@ -5337,6 +5580,9 @@
       <c r="AA82" t="n">
         <v>0.7808673913043478</v>
       </c>
+      <c r="AB82" t="n">
+        <v>0.8380391304347827</v>
+      </c>
     </row>
     <row r="83" ht="16" customHeight="1" s="8">
       <c r="A83" s="5" t="n">
@@ -5396,6 +5642,9 @@
       <c r="AA83" t="n">
         <v>0.7231868421052632</v>
       </c>
+      <c r="AB83" t="n">
+        <v>0.754224</v>
+      </c>
     </row>
     <row r="84" ht="16" customHeight="1" s="8">
       <c r="A84" s="5" t="n">
@@ -5455,6 +5704,9 @@
       <c r="AA84" t="n">
         <v>0.8570974999999998</v>
       </c>
+      <c r="AB84" t="n">
+        <v>0.7973821428571428</v>
+      </c>
     </row>
     <row r="85" ht="16" customHeight="1" s="8">
       <c r="A85" s="5" t="n">
@@ -5514,6 +5766,9 @@
       <c r="AA85" t="n">
         <v>0.7442029411764706</v>
       </c>
+      <c r="AB85" t="n">
+        <v>0.8075692307692308</v>
+      </c>
     </row>
     <row r="86" ht="16" customHeight="1" s="8">
       <c r="A86" s="5" t="n">
@@ -5573,6 +5828,9 @@
       <c r="AA86" t="n">
         <v>0.7758206896551724</v>
       </c>
+      <c r="AB86" t="n">
+        <v>0.9157846153846154</v>
+      </c>
     </row>
     <row r="87" ht="16" customHeight="1" s="8">
       <c r="A87" s="5" t="n">
@@ -5632,6 +5890,9 @@
       <c r="AA87" t="n">
         <v>0.80975</v>
       </c>
+      <c r="AB87" t="n">
+        <v>0.8368129032258064</v>
+      </c>
     </row>
     <row r="88" ht="16" customHeight="1" s="8">
       <c r="A88" s="5" t="n">
@@ -5691,6 +5952,9 @@
       <c r="AA88" t="n">
         <v>0.8153874999999999</v>
       </c>
+      <c r="AB88" t="n">
+        <v>0.8699851851851853</v>
+      </c>
     </row>
     <row r="89" ht="16" customHeight="1" s="8">
       <c r="A89" s="5" t="n">
@@ -5750,6 +6014,9 @@
       <c r="AA89" t="n">
         <v>0.7818152173913044</v>
       </c>
+      <c r="AB89" t="n">
+        <v>0.9266358974358975</v>
+      </c>
     </row>
     <row r="90" ht="16" customHeight="1" s="8">
       <c r="A90" s="5" t="n">
@@ -5809,6 +6076,9 @@
       <c r="AA90" t="n">
         <v>0.7884325581395348</v>
       </c>
+      <c r="AB90" t="n">
+        <v>0.8890166666666667</v>
+      </c>
     </row>
     <row r="91" ht="16" customHeight="1" s="8">
       <c r="A91" s="5" t="n">
@@ -5868,6 +6138,9 @@
       <c r="AA91" t="n">
         <v>0.8589088888888889</v>
       </c>
+      <c r="AB91" t="n">
+        <v>0.8737764705882354</v>
+      </c>
     </row>
     <row r="92" ht="16" customHeight="1" s="8">
       <c r="A92" s="5" t="n">
@@ -5927,6 +6200,9 @@
       <c r="AA92" t="n">
         <v>0.7775310344827585</v>
       </c>
+      <c r="AB92" t="n">
+        <v>0.7849954545454545</v>
+      </c>
     </row>
     <row r="93" ht="16" customHeight="1" s="8">
       <c r="A93" s="5" t="n">
@@ -5986,6 +6262,9 @@
       <c r="AA93" t="n">
         <v>0.8064666666666667</v>
       </c>
+      <c r="AB93" t="n">
+        <v>0.8794647058823529</v>
+      </c>
     </row>
     <row r="94" ht="16" customHeight="1" s="8">
       <c r="A94" s="5" t="n">
@@ -6045,6 +6324,9 @@
       <c r="AA94" t="n">
         <v>0.75695</v>
       </c>
+      <c r="AB94" t="n">
+        <v>0.8630000000000001</v>
+      </c>
     </row>
     <row r="95" ht="16" customHeight="1" s="8">
       <c r="A95" s="5" t="n">
@@ -6104,6 +6386,9 @@
       <c r="AA95" t="n">
         <v>0.7976933333333334</v>
       </c>
+      <c r="AB95" t="n">
+        <v>0.8597</v>
+      </c>
     </row>
     <row r="96" ht="16" customHeight="1" s="8">
       <c r="A96" s="5" t="n">
@@ -6163,6 +6448,9 @@
       <c r="AA96" t="n">
         <v>0.863455882352941</v>
       </c>
+      <c r="AB96" t="n">
+        <v>0.9143307692307693</v>
+      </c>
     </row>
     <row r="97" ht="16" customHeight="1" s="8">
       <c r="A97" s="5" t="n">
@@ -6222,6 +6510,9 @@
       <c r="AA97" t="n">
         <v>0.8395789473684211</v>
       </c>
+      <c r="AB97" t="n">
+        <v>0.78554</v>
+      </c>
     </row>
     <row r="98" ht="16" customHeight="1" s="8">
       <c r="A98" s="5" t="n">
@@ -6281,6 +6572,9 @@
       <c r="AA98" t="n">
         <v>0.685928947368421</v>
       </c>
+      <c r="AB98" t="n">
+        <v>0.8819684210526316</v>
+      </c>
     </row>
     <row r="99" ht="16" customHeight="1" s="8">
       <c r="A99" s="5" t="n">
@@ -6340,6 +6634,9 @@
       <c r="AA99" t="n">
         <v>0.8575571428571427</v>
       </c>
+      <c r="AB99" t="n">
+        <v>0.8868533333333334</v>
+      </c>
     </row>
     <row r="100" ht="16" customHeight="1" s="8">
       <c r="A100" s="5" t="n">
@@ -6399,6 +6696,9 @@
       <c r="AA100" t="n">
         <v>0.8421500000000001</v>
       </c>
+      <c r="AB100" t="n">
+        <v>0.8900187500000001</v>
+      </c>
     </row>
     <row r="101" ht="16" customHeight="1" s="8">
       <c r="A101" s="5" t="n">
@@ -6458,6 +6758,9 @@
       <c r="AA101" t="n">
         <v>0.8254195121951219</v>
       </c>
+      <c r="AB101" t="n">
+        <v>0.8328264705882353</v>
+      </c>
     </row>
     <row r="102" ht="16" customHeight="1" s="8">
       <c r="A102" s="5" t="n">
@@ -6517,6 +6820,9 @@
       <c r="AA102" t="n">
         <v>0.82172</v>
       </c>
+      <c r="AB102" t="n">
+        <v>0.7871741935483871</v>
+      </c>
     </row>
     <row r="103" ht="16" customHeight="1" s="8">
       <c r="A103" s="5" t="n">
@@ -6576,6 +6882,9 @@
       <c r="AA103" t="n">
         <v>0.8741260869565216</v>
       </c>
+      <c r="AB103" t="n">
+        <v>0.874335</v>
+      </c>
     </row>
     <row r="104" ht="16" customHeight="1" s="8">
       <c r="A104" s="5" t="n">
@@ -6634,6 +6943,9 @@
       </c>
       <c r="AA104" t="n">
         <v>0.7542333333333333</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0.7958472222222224</v>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1" s="8">
@@ -6727,6 +7039,12 @@
       <c r="AA108" t="n">
         <v>0.9333333333333333</v>
       </c>
+      <c r="AB108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0.5333333333333333</v>
+      </c>
     </row>
     <row r="109" ht="16" customHeight="1" s="8">
       <c r="A109" s="5" t="n">
@@ -6795,6 +7113,12 @@
       <c r="AA109" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AB109" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="110" ht="16" customHeight="1" s="8">
       <c r="A110" s="5" t="n">
@@ -6863,6 +7187,12 @@
       <c r="AA110" t="n">
         <v>0.8181818181818182</v>
       </c>
+      <c r="AB110" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0.5555555555555556</v>
+      </c>
     </row>
     <row r="111" ht="16" customHeight="1" s="8">
       <c r="A111" s="5" t="n">
@@ -6931,6 +7261,12 @@
       <c r="AA111" t="n">
         <v>0.7272727272727273</v>
       </c>
+      <c r="AB111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112" ht="16" customHeight="1" s="8">
       <c r="A112" s="5" t="n">
@@ -6999,6 +7335,9 @@
       <c r="AA112" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="AB112" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="113" ht="16" customHeight="1" s="8">
       <c r="A113" s="5" t="n">
@@ -7067,6 +7406,9 @@
       <c r="AA113" t="n">
         <v>1</v>
       </c>
+      <c r="AB113" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="114" ht="16" customHeight="1" s="8">
       <c r="A114" s="5" t="n">
@@ -7135,6 +7477,9 @@
       <c r="AA114" t="n">
         <v>0.8</v>
       </c>
+      <c r="AB114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115" ht="16" customHeight="1" s="8">
       <c r="A115" s="5" t="n">
@@ -7203,6 +7548,9 @@
       <c r="AA115" t="n">
         <v>1</v>
       </c>
+      <c r="AB115" t="n">
+        <v>0.7142857142857143</v>
+      </c>
     </row>
     <row r="116" ht="16" customHeight="1" s="8">
       <c r="A116" s="5" t="n">
@@ -7271,6 +7619,9 @@
       <c r="AA116" t="n">
         <v>1</v>
       </c>
+      <c r="AB116" t="n">
+        <v>0.8571428571428571</v>
+      </c>
     </row>
     <row r="117" ht="16" customHeight="1" s="8">
       <c r="A117" s="5" t="n">
@@ -7339,6 +7690,9 @@
       <c r="AA117" t="n">
         <v>1</v>
       </c>
+      <c r="AB117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118" ht="16" customHeight="1" s="8">
       <c r="A118" s="5" t="n">
@@ -7395,6 +7749,9 @@
       <c r="AA118" t="n">
         <v>0.875</v>
       </c>
+      <c r="AB118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119" ht="16" customHeight="1" s="8">
       <c r="A119" s="5" t="n">
@@ -7454,6 +7811,9 @@
       <c r="AA119" t="n">
         <v>1</v>
       </c>
+      <c r="AB119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120" ht="16" customHeight="1" s="8">
       <c r="A120" s="5" t="n">
@@ -7513,6 +7873,9 @@
       <c r="AA120" t="n">
         <v>1</v>
       </c>
+      <c r="AB120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121" ht="16" customHeight="1" s="8">
       <c r="A121" s="5" t="n">
@@ -7572,6 +7935,9 @@
       <c r="AA121" t="n">
         <v>1</v>
       </c>
+      <c r="AB121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122" ht="16" customHeight="1" s="8">
       <c r="A122" s="5" t="n">
@@ -7631,6 +7997,9 @@
       <c r="AA122" t="n">
         <v>1</v>
       </c>
+      <c r="AB122" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="123" ht="16" customHeight="1" s="8">
       <c r="A123" s="5" t="n">
@@ -7690,6 +8059,9 @@
       <c r="AA123" t="n">
         <v>1</v>
       </c>
+      <c r="AB123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124" ht="16" customHeight="1" s="8">
       <c r="A124" s="5" t="n">
@@ -7749,6 +8121,9 @@
       <c r="AA124" t="n">
         <v>1</v>
       </c>
+      <c r="AB124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125" ht="16" customHeight="1" s="8">
       <c r="A125" s="5" t="n">
@@ -7808,6 +8183,9 @@
       <c r="AA125" t="n">
         <v>1</v>
       </c>
+      <c r="AB125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126" ht="16" customHeight="1" s="8">
       <c r="A126" s="5" t="n">
@@ -7867,6 +8245,9 @@
       <c r="AA126" t="n">
         <v>1</v>
       </c>
+      <c r="AB126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127" ht="16" customHeight="1" s="8">
       <c r="A127" s="5" t="n">
@@ -7926,6 +8307,9 @@
       <c r="AA127" t="n">
         <v>1</v>
       </c>
+      <c r="AB127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128" ht="16" customHeight="1" s="8">
       <c r="A128" s="5" t="n">
@@ -7985,6 +8369,9 @@
       <c r="AA128" t="n">
         <v>1</v>
       </c>
+      <c r="AB128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129" ht="16" customHeight="1" s="8">
       <c r="A129" s="5" t="n">
@@ -8044,6 +8431,9 @@
       <c r="AA129" t="n">
         <v>1</v>
       </c>
+      <c r="AB129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130" ht="16" customHeight="1" s="8">
       <c r="A130" s="5" t="n">
@@ -8103,6 +8493,9 @@
       <c r="AA130" t="n">
         <v>1</v>
       </c>
+      <c r="AB130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131" ht="16" customHeight="1" s="8">
       <c r="A131" s="5" t="n">
@@ -8162,6 +8555,9 @@
       <c r="AA131" t="n">
         <v>1</v>
       </c>
+      <c r="AB131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132" ht="16" customHeight="1" s="8">
       <c r="A132" s="5" t="n">
@@ -8221,6 +8617,9 @@
       <c r="AA132" t="n">
         <v>1</v>
       </c>
+      <c r="AB132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133" ht="16" customHeight="1" s="8">
       <c r="A133" s="5" t="n">
@@ -8280,6 +8679,9 @@
       <c r="AA133" t="n">
         <v>1</v>
       </c>
+      <c r="AB133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134" ht="16" customHeight="1" s="8">
       <c r="A134" s="5" t="n">
@@ -8339,6 +8741,9 @@
       <c r="AA134" t="n">
         <v>1</v>
       </c>
+      <c r="AB134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135" ht="16" customHeight="1" s="8">
       <c r="A135" s="5" t="n">
@@ -8398,6 +8803,9 @@
       <c r="AA135" t="n">
         <v>1</v>
       </c>
+      <c r="AB135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136" ht="16" customHeight="1" s="8">
       <c r="A136" s="5" t="n">
@@ -8457,6 +8865,9 @@
       <c r="AA136" t="n">
         <v>1</v>
       </c>
+      <c r="AB136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137" ht="16" customHeight="1" s="8">
       <c r="A137" s="5" t="n">
@@ -8516,6 +8927,9 @@
       <c r="AA137" t="n">
         <v>1</v>
       </c>
+      <c r="AB137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138" ht="16" customHeight="1" s="8">
       <c r="A138" s="5" t="n">
@@ -8575,6 +8989,9 @@
       <c r="AA138" t="n">
         <v>1</v>
       </c>
+      <c r="AB138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139" ht="16" customHeight="1" s="8">
       <c r="A139" s="5" t="n">
@@ -8634,6 +9051,9 @@
       <c r="AA139" t="n">
         <v>1</v>
       </c>
+      <c r="AB139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140" ht="16" customHeight="1" s="8">
       <c r="A140" s="5" t="n">
@@ -8690,6 +9110,9 @@
       <c r="AA140" t="n">
         <v>1</v>
       </c>
+      <c r="AB140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141" ht="16" customHeight="1" s="8">
       <c r="A141" s="5" t="n">
@@ -8749,6 +9172,9 @@
       <c r="AA141" t="n">
         <v>1</v>
       </c>
+      <c r="AB141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" ht="16" customHeight="1" s="8">
       <c r="A142" s="5" t="n">
@@ -8808,6 +9234,9 @@
       <c r="AA142" t="n">
         <v>1</v>
       </c>
+      <c r="AB142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143" ht="16" customHeight="1" s="8">
       <c r="A143" s="5" t="n">
@@ -8864,6 +9293,9 @@
       <c r="AA143" t="n">
         <v>1</v>
       </c>
+      <c r="AB143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144" ht="16" customHeight="1" s="8">
       <c r="A144" s="5" t="n">
@@ -8923,6 +9355,9 @@
       <c r="AA144" t="n">
         <v>1</v>
       </c>
+      <c r="AB144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145" ht="16" customHeight="1" s="8">
       <c r="A145" s="5" t="n">
@@ -8982,6 +9417,9 @@
       <c r="AA145" t="n">
         <v>1</v>
       </c>
+      <c r="AB145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146" ht="16" customHeight="1" s="8">
       <c r="A146" s="5" t="n">
@@ -9041,6 +9479,9 @@
       <c r="AA146" t="n">
         <v>1</v>
       </c>
+      <c r="AB146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147" ht="16" customHeight="1" s="8">
       <c r="A147" s="5" t="n">
@@ -9100,6 +9541,9 @@
       <c r="AA147" t="n">
         <v>1</v>
       </c>
+      <c r="AB147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148" ht="16" customHeight="1" s="8">
       <c r="A148" s="5" t="n">
@@ -9159,6 +9603,9 @@
       <c r="AA148" t="n">
         <v>1</v>
       </c>
+      <c r="AB148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149" ht="16" customHeight="1" s="8">
       <c r="A149" s="5" t="n">
@@ -9218,6 +9665,9 @@
       <c r="AA149" t="n">
         <v>1</v>
       </c>
+      <c r="AB149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150" ht="16" customHeight="1" s="8">
       <c r="A150" s="5" t="n">
@@ -9277,6 +9727,9 @@
       <c r="AA150" t="n">
         <v>1</v>
       </c>
+      <c r="AB150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151" ht="16" customHeight="1" s="8">
       <c r="A151" s="5" t="n">
@@ -9336,6 +9789,9 @@
       <c r="AA151" t="n">
         <v>1</v>
       </c>
+      <c r="AB151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152" ht="16" customHeight="1" s="8">
       <c r="A152" s="5" t="n">
@@ -9395,6 +9851,9 @@
       <c r="AA152" t="n">
         <v>1</v>
       </c>
+      <c r="AB152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153" ht="16" customHeight="1" s="8">
       <c r="A153" s="5" t="n">
@@ -9454,6 +9913,9 @@
       <c r="AA153" t="n">
         <v>1</v>
       </c>
+      <c r="AB153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" ht="16" customHeight="1" s="8">
       <c r="A154" s="5" t="n">
@@ -9513,6 +9975,9 @@
       <c r="AA154" t="n">
         <v>1</v>
       </c>
+      <c r="AB154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" ht="16" customHeight="1" s="8">
       <c r="A155" s="5" t="n">
@@ -9572,6 +10037,9 @@
       <c r="AA155" t="n">
         <v>1</v>
       </c>
+      <c r="AB155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156" ht="16" customHeight="1" s="8">
       <c r="A156" s="5" t="n">
@@ -9631,6 +10099,9 @@
       <c r="AA156" t="n">
         <v>1</v>
       </c>
+      <c r="AB156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157" ht="16" customHeight="1" s="8">
       <c r="A157" s="5" t="n">
@@ -9690,6 +10161,9 @@
       <c r="AA157" t="n">
         <v>1</v>
       </c>
+      <c r="AB157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158" ht="16" customHeight="1" s="8">
       <c r="A158" s="5" t="n">
@@ -9749,6 +10223,9 @@
       <c r="AA158" t="n">
         <v>1</v>
       </c>
+      <c r="AB158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159" ht="16" customHeight="1" s="8">
       <c r="A159" s="5" t="n">
@@ -9808,6 +10285,9 @@
       <c r="AA159" t="n">
         <v>1</v>
       </c>
+      <c r="AB159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160" ht="16" customHeight="1" s="8">
       <c r="A160" s="5" t="n">
@@ -9867,6 +10347,9 @@
       <c r="AA160" t="n">
         <v>1</v>
       </c>
+      <c r="AB160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161" ht="16" customHeight="1" s="8">
       <c r="A161" s="5" t="n">
@@ -9926,6 +10409,9 @@
       <c r="AA161" t="n">
         <v>1</v>
       </c>
+      <c r="AB161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162" ht="16" customHeight="1" s="8">
       <c r="A162" s="5" t="n">
@@ -9985,6 +10471,9 @@
       <c r="AA162" t="n">
         <v>1</v>
       </c>
+      <c r="AB162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163" ht="16" customHeight="1" s="8">
       <c r="A163" s="5" t="n">
@@ -10044,6 +10533,9 @@
       <c r="AA163" t="n">
         <v>1</v>
       </c>
+      <c r="AB163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164" ht="16" customHeight="1" s="8">
       <c r="A164" s="5" t="n">
@@ -10103,6 +10595,9 @@
       <c r="AA164" t="n">
         <v>1</v>
       </c>
+      <c r="AB164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165" ht="16" customHeight="1" s="8">
       <c r="A165" s="5" t="n">
@@ -10162,6 +10657,9 @@
       <c r="AA165" t="n">
         <v>1</v>
       </c>
+      <c r="AB165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166" ht="16" customHeight="1" s="8">
       <c r="A166" s="5" t="n">
@@ -10221,6 +10719,9 @@
       <c r="AA166" t="n">
         <v>1</v>
       </c>
+      <c r="AB166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167" ht="16" customHeight="1" s="8">
       <c r="A167" s="5" t="n">
@@ -10280,6 +10781,9 @@
       <c r="AA167" t="n">
         <v>1</v>
       </c>
+      <c r="AB167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168" ht="16" customHeight="1" s="8">
       <c r="A168" s="5" t="n">
@@ -10339,6 +10843,9 @@
       <c r="AA168" t="n">
         <v>1</v>
       </c>
+      <c r="AB168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169" ht="16" customHeight="1" s="8">
       <c r="A169" s="5" t="n">
@@ -10398,6 +10905,9 @@
       <c r="AA169" t="n">
         <v>1</v>
       </c>
+      <c r="AB169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170" ht="16" customHeight="1" s="8">
       <c r="A170" s="5" t="n">
@@ -10457,6 +10967,9 @@
       <c r="AA170" t="n">
         <v>1</v>
       </c>
+      <c r="AB170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171" ht="16" customHeight="1" s="8">
       <c r="A171" s="5" t="n">
@@ -10516,6 +11029,9 @@
       <c r="AA171" t="n">
         <v>1</v>
       </c>
+      <c r="AB171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172" ht="16" customHeight="1" s="8">
       <c r="A172" s="5" t="n">
@@ -10575,6 +11091,9 @@
       <c r="AA172" t="n">
         <v>1</v>
       </c>
+      <c r="AB172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173" ht="16" customHeight="1" s="8">
       <c r="A173" s="5" t="n">
@@ -10634,6 +11153,9 @@
       <c r="AA173" t="n">
         <v>1</v>
       </c>
+      <c r="AB173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174" ht="16" customHeight="1" s="8">
       <c r="A174" s="5" t="n">
@@ -10693,6 +11215,9 @@
       <c r="AA174" t="n">
         <v>1</v>
       </c>
+      <c r="AB174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175" ht="16" customHeight="1" s="8">
       <c r="A175" s="5" t="n">
@@ -10752,6 +11277,9 @@
       <c r="AA175" t="n">
         <v>1</v>
       </c>
+      <c r="AB175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176" ht="16" customHeight="1" s="8">
       <c r="A176" s="5" t="n">
@@ -10811,6 +11339,9 @@
       <c r="AA176" t="n">
         <v>1</v>
       </c>
+      <c r="AB176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177" ht="16" customHeight="1" s="8">
       <c r="A177" s="5" t="n">
@@ -10870,6 +11401,9 @@
       <c r="AA177" t="n">
         <v>1</v>
       </c>
+      <c r="AB177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178" ht="16" customHeight="1" s="8">
       <c r="A178" s="5" t="n">
@@ -10929,6 +11463,9 @@
       <c r="AA178" t="n">
         <v>1</v>
       </c>
+      <c r="AB178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179" ht="16" customHeight="1" s="8">
       <c r="A179" s="5" t="n">
@@ -10988,6 +11525,9 @@
       <c r="AA179" t="n">
         <v>1</v>
       </c>
+      <c r="AB179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180" ht="16" customHeight="1" s="8">
       <c r="A180" s="5" t="n">
@@ -11047,6 +11587,9 @@
       <c r="AA180" t="n">
         <v>1</v>
       </c>
+      <c r="AB180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181" ht="16" customHeight="1" s="8">
       <c r="A181" s="5" t="n">
@@ -11103,6 +11646,9 @@
       <c r="AA181" t="n">
         <v>1</v>
       </c>
+      <c r="AB181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182" ht="16" customHeight="1" s="8">
       <c r="A182" s="5" t="n">
@@ -11162,6 +11708,9 @@
       <c r="AA182" t="n">
         <v>1</v>
       </c>
+      <c r="AB182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183" ht="16" customHeight="1" s="8">
       <c r="A183" s="5" t="n">
@@ -11221,6 +11770,9 @@
       <c r="AA183" t="n">
         <v>1</v>
       </c>
+      <c r="AB183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184" ht="16" customHeight="1" s="8">
       <c r="A184" s="5" t="n">
@@ -11280,6 +11832,9 @@
       <c r="AA184" t="n">
         <v>1</v>
       </c>
+      <c r="AB184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185" ht="16" customHeight="1" s="8">
       <c r="A185" s="5" t="n">
@@ -11339,6 +11894,9 @@
       <c r="AA185" t="n">
         <v>1</v>
       </c>
+      <c r="AB185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186" ht="16" customHeight="1" s="8">
       <c r="A186" s="5" t="n">
@@ -11398,6 +11956,9 @@
       <c r="AA186" t="n">
         <v>1</v>
       </c>
+      <c r="AB186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187" ht="16" customHeight="1" s="8">
       <c r="A187" s="5" t="n">
@@ -11457,6 +12018,9 @@
       <c r="AA187" t="n">
         <v>1</v>
       </c>
+      <c r="AB187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188" ht="16" customHeight="1" s="8">
       <c r="A188" s="5" t="n">
@@ -11516,6 +12080,9 @@
       <c r="AA188" t="n">
         <v>1</v>
       </c>
+      <c r="AB188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189" ht="16" customHeight="1" s="8">
       <c r="A189" s="5" t="n">
@@ -11575,6 +12142,9 @@
       <c r="AA189" t="n">
         <v>1</v>
       </c>
+      <c r="AB189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190" ht="16" customHeight="1" s="8">
       <c r="A190" s="5" t="n">
@@ -11634,6 +12204,9 @@
       <c r="AA190" t="n">
         <v>1</v>
       </c>
+      <c r="AB190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191" ht="16" customHeight="1" s="8">
       <c r="A191" s="5" t="n">
@@ -11693,6 +12266,9 @@
       <c r="AA191" t="n">
         <v>1</v>
       </c>
+      <c r="AB191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192" ht="16" customHeight="1" s="8">
       <c r="A192" s="5" t="n">
@@ -11752,6 +12328,9 @@
       <c r="AA192" t="n">
         <v>1</v>
       </c>
+      <c r="AB192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193" ht="16" customHeight="1" s="8">
       <c r="A193" s="5" t="n">
@@ -11811,6 +12390,9 @@
       <c r="AA193" t="n">
         <v>1</v>
       </c>
+      <c r="AB193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194" ht="16" customHeight="1" s="8">
       <c r="A194" s="5" t="n">
@@ -11870,6 +12452,9 @@
       <c r="AA194" t="n">
         <v>1</v>
       </c>
+      <c r="AB194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195" ht="16" customHeight="1" s="8">
       <c r="A195" s="5" t="n">
@@ -11929,6 +12514,9 @@
       <c r="AA195" t="n">
         <v>1</v>
       </c>
+      <c r="AB195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196" ht="16" customHeight="1" s="8">
       <c r="A196" s="5" t="n">
@@ -11988,6 +12576,9 @@
       <c r="AA196" t="n">
         <v>1</v>
       </c>
+      <c r="AB196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197" ht="16" customHeight="1" s="8">
       <c r="A197" s="5" t="n">
@@ -12047,6 +12638,9 @@
       <c r="AA197" t="n">
         <v>1</v>
       </c>
+      <c r="AB197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198" ht="16" customHeight="1" s="8">
       <c r="A198" s="5" t="n">
@@ -12106,6 +12700,9 @@
       <c r="AA198" t="n">
         <v>1</v>
       </c>
+      <c r="AB198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199" ht="16" customHeight="1" s="8">
       <c r="A199" s="5" t="n">
@@ -12165,6 +12762,9 @@
       <c r="AA199" t="n">
         <v>1</v>
       </c>
+      <c r="AB199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200" ht="16" customHeight="1" s="8">
       <c r="A200" s="5" t="n">
@@ -12224,6 +12824,9 @@
       <c r="AA200" t="n">
         <v>1</v>
       </c>
+      <c r="AB200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201" ht="16" customHeight="1" s="8">
       <c r="A201" s="5" t="n">
@@ -12283,6 +12886,9 @@
       <c r="AA201" t="n">
         <v>1</v>
       </c>
+      <c r="AB201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202" ht="16" customHeight="1" s="8">
       <c r="A202" s="5" t="n">
@@ -12342,6 +12948,9 @@
       <c r="AA202" t="n">
         <v>1</v>
       </c>
+      <c r="AB202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203" ht="16" customHeight="1" s="8">
       <c r="A203" s="5" t="n">
@@ -12401,6 +13010,9 @@
       <c r="AA203" t="n">
         <v>1</v>
       </c>
+      <c r="AB203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204" ht="16" customHeight="1" s="8">
       <c r="A204" s="5" t="n">
@@ -12460,6 +13072,9 @@
       <c r="AA204" t="n">
         <v>1</v>
       </c>
+      <c r="AB204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205" ht="16" customHeight="1" s="8">
       <c r="A205" s="5" t="n">
@@ -12519,6 +13134,9 @@
       <c r="AA205" t="n">
         <v>1</v>
       </c>
+      <c r="AB205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206" ht="16" customHeight="1" s="8">
       <c r="A206" s="5" t="n">
@@ -12578,6 +13196,9 @@
       <c r="AA206" t="n">
         <v>1</v>
       </c>
+      <c r="AB206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207" ht="16" customHeight="1" s="8">
       <c r="A207" s="5" t="n">
@@ -12635,6 +13256,9 @@
         <v>1</v>
       </c>
       <c r="AA207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12729,6 +13353,12 @@
       <c r="AA212" t="n">
         <v>0.9589999999999999</v>
       </c>
+      <c r="AB212" t="n">
+        <v>0.945975</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>0.9564374999999999</v>
+      </c>
     </row>
     <row r="213" ht="16" customHeight="1" s="8">
       <c r="A213" s="5" t="n">
@@ -12797,6 +13427,12 @@
       <c r="AA213" t="n">
         <v>0.9613400000000001</v>
       </c>
+      <c r="AB213" t="n">
+        <v>0.9561833333333333</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>0.9480727272727273</v>
+      </c>
     </row>
     <row r="214" ht="16" customHeight="1" s="8">
       <c r="A214" s="5" t="n">
@@ -12865,6 +13501,12 @@
       <c r="AA214" t="n">
         <v>0.7975166666666667</v>
       </c>
+      <c r="AB214" t="n">
+        <v>0.9385800000000002</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>0.8638181818181817</v>
+      </c>
     </row>
     <row r="215" ht="16" customHeight="1" s="8">
       <c r="A215" s="5" t="n">
@@ -12933,6 +13575,12 @@
       <c r="AA215" t="n">
         <v>0.8271750000000001</v>
       </c>
+      <c r="AB215" t="n">
+        <v>0.8617111111111111</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>0.9053000000000001</v>
+      </c>
     </row>
     <row r="216" ht="16" customHeight="1" s="8">
       <c r="A216" s="5" t="n">
@@ -13001,6 +13649,9 @@
       <c r="AA216" t="n">
         <v>0.8929888888888888</v>
       </c>
+      <c r="AB216" t="n">
+        <v>0.7094999999999999</v>
+      </c>
     </row>
     <row r="217" ht="16" customHeight="1" s="8">
       <c r="A217" s="5" t="n">
@@ -13069,6 +13720,9 @@
       <c r="AA217" t="n">
         <v>0.6562166666666668</v>
       </c>
+      <c r="AB217" t="n">
+        <v>0.9389222222222222</v>
+      </c>
     </row>
     <row r="218" ht="16" customHeight="1" s="8">
       <c r="A218" s="5" t="n">
@@ -13137,6 +13791,9 @@
       <c r="AA218" t="n">
         <v>0.7219272727272729</v>
       </c>
+      <c r="AB218" t="n">
+        <v>0.8261555555555556</v>
+      </c>
     </row>
     <row r="219" ht="16" customHeight="1" s="8">
       <c r="A219" s="5" t="n">
@@ -13205,6 +13862,9 @@
       <c r="AA219" t="n">
         <v>0.6075</v>
       </c>
+      <c r="AB219" t="n">
+        <v>0.74186</v>
+      </c>
     </row>
     <row r="220" ht="16" customHeight="1" s="8">
       <c r="A220" s="5" t="n">
@@ -13273,6 +13933,9 @@
       <c r="AA220" t="n">
         <v>0.5728727272727273</v>
       </c>
+      <c r="AB220" t="n">
+        <v>0.75689</v>
+      </c>
     </row>
     <row r="221" ht="16" customHeight="1" s="8">
       <c r="A221" s="5" t="n">
@@ -13341,6 +14004,9 @@
       <c r="AA221" t="n">
         <v>0.4577222222222223</v>
       </c>
+      <c r="AB221" t="n">
+        <v>0.8344750000000001</v>
+      </c>
     </row>
     <row r="222" ht="16" customHeight="1" s="8">
       <c r="A222" s="5" t="n">
@@ -13397,6 +14063,9 @@
       <c r="AA222" t="n">
         <v>0.8120375000000001</v>
       </c>
+      <c r="AB222" t="n">
+        <v>0.8927999999999999</v>
+      </c>
     </row>
     <row r="223" ht="16" customHeight="1" s="8">
       <c r="A223" s="5" t="n">
@@ -13456,6 +14125,9 @@
       <c r="AA223" t="n">
         <v>0.6921999999999999</v>
       </c>
+      <c r="AB223" t="n">
+        <v>0.6485181818181819</v>
+      </c>
     </row>
     <row r="224" ht="16" customHeight="1" s="8">
       <c r="A224" s="5" t="n">
@@ -13515,6 +14187,9 @@
       <c r="AA224" t="n">
         <v>0.5952142857142857</v>
       </c>
+      <c r="AB224" t="n">
+        <v>0.7489222222222222</v>
+      </c>
     </row>
     <row r="225" ht="16" customHeight="1" s="8">
       <c r="A225" s="5" t="n">
@@ -13574,6 +14249,9 @@
       <c r="AA225" t="n">
         <v>0.7197545454545454</v>
       </c>
+      <c r="AB225" t="n">
+        <v>0.7000666666666666</v>
+      </c>
     </row>
     <row r="226" ht="16" customHeight="1" s="8">
       <c r="A226" s="5" t="n">
@@ -13633,6 +14311,9 @@
       <c r="AA226" t="n">
         <v>0.6146499999999999</v>
       </c>
+      <c r="AB226" t="n">
+        <v>0.73653</v>
+      </c>
     </row>
     <row r="227" ht="16" customHeight="1" s="8">
       <c r="A227" s="5" t="n">
@@ -13692,6 +14373,9 @@
       <c r="AA227" t="n">
         <v>0.7538181818181816</v>
       </c>
+      <c r="AB227" t="n">
+        <v>0.7327666666666667</v>
+      </c>
     </row>
     <row r="228" ht="16" customHeight="1" s="8">
       <c r="A228" s="5" t="n">
@@ -13751,6 +14435,9 @@
       <c r="AA228" t="n">
         <v>0.6402777777777778</v>
       </c>
+      <c r="AB228" t="n">
+        <v>0.5726666666666667</v>
+      </c>
     </row>
     <row r="229" ht="16" customHeight="1" s="8">
       <c r="A229" s="5" t="n">
@@ -13810,6 +14497,9 @@
       <c r="AA229" t="n">
         <v>0.65245</v>
       </c>
+      <c r="AB229" t="n">
+        <v>0.8396166666666666</v>
+      </c>
     </row>
     <row r="230" ht="16" customHeight="1" s="8">
       <c r="A230" s="5" t="n">
@@ -13869,6 +14559,9 @@
       <c r="AA230" t="n">
         <v>0.499675</v>
       </c>
+      <c r="AB230" t="n">
+        <v>0.6778444444444445</v>
+      </c>
     </row>
     <row r="231" ht="16" customHeight="1" s="8">
       <c r="A231" s="5" t="n">
@@ -13928,6 +14621,9 @@
       <c r="AA231" t="n">
         <v>0.6245857142857142</v>
       </c>
+      <c r="AB231" t="n">
+        <v>0.5468416666666667</v>
+      </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="8">
       <c r="A232" s="5" t="n">
@@ -13987,6 +14683,9 @@
       <c r="AA232" t="n">
         <v>0.5972222222222222</v>
       </c>
+      <c r="AB232" t="n">
+        <v>0.6597000000000001</v>
+      </c>
     </row>
     <row r="233" ht="16" customHeight="1" s="8">
       <c r="A233" s="5" t="n">
@@ -14046,6 +14745,9 @@
       <c r="AA233" t="n">
         <v>0.563790909090909</v>
       </c>
+      <c r="AB233" t="n">
+        <v>0.7221399999999999</v>
+      </c>
     </row>
     <row r="234" ht="16" customHeight="1" s="8">
       <c r="A234" s="5" t="n">
@@ -14105,6 +14807,9 @@
       <c r="AA234" t="n">
         <v>0.7048222222222221</v>
       </c>
+      <c r="AB234" t="n">
+        <v>0.7933874999999999</v>
+      </c>
     </row>
     <row r="235" ht="16" customHeight="1" s="8">
       <c r="A235" s="5" t="n">
@@ -14164,6 +14869,9 @@
       <c r="AA235" t="n">
         <v>0.6388125</v>
       </c>
+      <c r="AB235" t="n">
+        <v>0.70082</v>
+      </c>
     </row>
     <row r="236" ht="16" customHeight="1" s="8">
       <c r="A236" s="5" t="n">
@@ -14223,6 +14931,9 @@
       <c r="AA236" t="n">
         <v>0.8177875</v>
       </c>
+      <c r="AB236" t="n">
+        <v>0.7525545454545455</v>
+      </c>
     </row>
     <row r="237" ht="16" customHeight="1" s="8">
       <c r="A237" s="5" t="n">
@@ -14282,6 +14993,9 @@
       <c r="AA237" t="n">
         <v>0.7290777777777779</v>
       </c>
+      <c r="AB237" t="n">
+        <v>0.6757199999999999</v>
+      </c>
     </row>
     <row r="238" ht="16" customHeight="1" s="8">
       <c r="A238" s="5" t="n">
@@ -14341,6 +15055,9 @@
       <c r="AA238" t="n">
         <v>0.6530444444444445</v>
       </c>
+      <c r="AB238" t="n">
+        <v>0.64214</v>
+      </c>
     </row>
     <row r="239" ht="16" customHeight="1" s="8">
       <c r="A239" s="5" t="n">
@@ -14400,6 +15117,9 @@
       <c r="AA239" t="n">
         <v>0.5757272727272728</v>
       </c>
+      <c r="AB239" t="n">
+        <v>0.7617363636363635</v>
+      </c>
     </row>
     <row r="240" ht="16" customHeight="1" s="8">
       <c r="A240" s="5" t="n">
@@ -14459,6 +15179,9 @@
       <c r="AA240" t="n">
         <v>0.4133</v>
       </c>
+      <c r="AB240" t="n">
+        <v>0.6537666666666666</v>
+      </c>
     </row>
     <row r="241" ht="16" customHeight="1" s="8">
       <c r="A241" s="5" t="n">
@@ -14518,6 +15241,9 @@
       <c r="AA241" t="n">
         <v>0.4657333333333333</v>
       </c>
+      <c r="AB241" t="n">
+        <v>0.7624899999999999</v>
+      </c>
     </row>
     <row r="242" ht="16" customHeight="1" s="8">
       <c r="A242" s="5" t="n">
@@ -14577,6 +15303,9 @@
       <c r="AA242" t="n">
         <v>0.3931444444444445</v>
       </c>
+      <c r="AB242" t="n">
+        <v>0.6906500000000001</v>
+      </c>
     </row>
     <row r="243" ht="16" customHeight="1" s="8">
       <c r="A243" s="5" t="n">
@@ -14636,6 +15365,9 @@
       <c r="AA243" t="n">
         <v>0.7176999999999999</v>
       </c>
+      <c r="AB243" t="n">
+        <v>0.6684111111111112</v>
+      </c>
     </row>
     <row r="244" ht="16" customHeight="1" s="8">
       <c r="A244" s="5" t="n">
@@ -14692,6 +15424,9 @@
       <c r="AA244" t="n">
         <v>0.65104</v>
       </c>
+      <c r="AB244" t="n">
+        <v>0.6328375000000001</v>
+      </c>
     </row>
     <row r="245" ht="16" customHeight="1" s="8">
       <c r="A245" s="5" t="n">
@@ -14751,6 +15486,9 @@
       <c r="AA245" t="n">
         <v>0.4791142857142857</v>
       </c>
+      <c r="AB245" t="n">
+        <v>0.7722</v>
+      </c>
     </row>
     <row r="246" ht="16" customHeight="1" s="8">
       <c r="A246" s="5" t="n">
@@ -14810,6 +15548,9 @@
       <c r="AA246" t="n">
         <v>0.5206222222222222</v>
       </c>
+      <c r="AB246" t="n">
+        <v>0.731218181818182</v>
+      </c>
     </row>
     <row r="247" ht="16" customHeight="1" s="8">
       <c r="A247" s="5" t="n">
@@ -14866,6 +15607,9 @@
       <c r="AA247" t="n">
         <v>0.67815</v>
       </c>
+      <c r="AB247" t="n">
+        <v>0.8242833333333333</v>
+      </c>
     </row>
     <row r="248" ht="16" customHeight="1" s="8">
       <c r="A248" s="5" t="n">
@@ -14925,6 +15669,9 @@
       <c r="AA248" t="n">
         <v>0.770009090909091</v>
       </c>
+      <c r="AB248" t="n">
+        <v>0.6457285714285714</v>
+      </c>
     </row>
     <row r="249" ht="16" customHeight="1" s="8">
       <c r="A249" s="5" t="n">
@@ -14984,6 +15731,9 @@
       <c r="AA249" t="n">
         <v>0.4843818181818182</v>
       </c>
+      <c r="AB249" t="n">
+        <v>0.7223111111111111</v>
+      </c>
     </row>
     <row r="250" ht="16" customHeight="1" s="8">
       <c r="A250" s="5" t="n">
@@ -15043,6 +15793,9 @@
       <c r="AA250" t="n">
         <v>0.5959700000000001</v>
       </c>
+      <c r="AB250" t="n">
+        <v>0.7336454545454546</v>
+      </c>
     </row>
     <row r="251" ht="16" customHeight="1" s="8">
       <c r="A251" s="5" t="n">
@@ -15102,6 +15855,9 @@
       <c r="AA251" t="n">
         <v>0.74593</v>
       </c>
+      <c r="AB251" t="n">
+        <v>0.4760375</v>
+      </c>
     </row>
     <row r="252" ht="16" customHeight="1" s="8">
       <c r="A252" s="5" t="n">
@@ -15161,6 +15917,9 @@
       <c r="AA252" t="n">
         <v>0.5476222222222222</v>
       </c>
+      <c r="AB252" t="n">
+        <v>0.7316166666666667</v>
+      </c>
     </row>
     <row r="253" ht="16" customHeight="1" s="8">
       <c r="A253" s="5" t="n">
@@ -15220,6 +15979,9 @@
       <c r="AA253" t="n">
         <v>0.6644222222222222</v>
       </c>
+      <c r="AB253" t="n">
+        <v>0.63619</v>
+      </c>
     </row>
     <row r="254" ht="16" customHeight="1" s="8">
       <c r="A254" s="5" t="n">
@@ -15279,6 +16041,9 @@
       <c r="AA254" t="n">
         <v>0.7835333333333333</v>
       </c>
+      <c r="AB254" t="n">
+        <v>0.7097454545454546</v>
+      </c>
     </row>
     <row r="255" ht="16" customHeight="1" s="8">
       <c r="A255" s="5" t="n">
@@ -15338,6 +16103,9 @@
       <c r="AA255" t="n">
         <v>0.5727375</v>
       </c>
+      <c r="AB255" t="n">
+        <v>0.7767307692307692</v>
+      </c>
     </row>
     <row r="256" ht="16" customHeight="1" s="8">
       <c r="A256" s="5" t="n">
@@ -15397,6 +16165,9 @@
       <c r="AA256" t="n">
         <v>0.56565</v>
       </c>
+      <c r="AB256" t="n">
+        <v>0.63409</v>
+      </c>
     </row>
     <row r="257" ht="16" customHeight="1" s="8">
       <c r="A257" s="5" t="n">
@@ -15456,6 +16227,9 @@
       <c r="AA257" t="n">
         <v>0.6419999999999999</v>
       </c>
+      <c r="AB257" t="n">
+        <v>0.7080272727272727</v>
+      </c>
     </row>
     <row r="258" ht="16" customHeight="1" s="8">
       <c r="A258" s="5" t="n">
@@ -15515,6 +16289,9 @@
       <c r="AA258" t="n">
         <v>0.4525625</v>
       </c>
+      <c r="AB258" t="n">
+        <v>0.63758</v>
+      </c>
     </row>
     <row r="259" ht="16" customHeight="1" s="8">
       <c r="A259" s="5" t="n">
@@ -15574,6 +16351,9 @@
       <c r="AA259" t="n">
         <v>0.55225</v>
       </c>
+      <c r="AB259" t="n">
+        <v>0.7251727272727272</v>
+      </c>
     </row>
     <row r="260" ht="16" customHeight="1" s="8">
       <c r="A260" s="5" t="n">
@@ -15633,6 +16413,9 @@
       <c r="AA260" t="n">
         <v>0.6992636363636365</v>
       </c>
+      <c r="AB260" t="n">
+        <v>0.6167777777777779</v>
+      </c>
     </row>
     <row r="261" ht="16" customHeight="1" s="8">
       <c r="A261" s="5" t="n">
@@ -15692,6 +16475,9 @@
       <c r="AA261" t="n">
         <v>0.5652099999999999</v>
       </c>
+      <c r="AB261" t="n">
+        <v>0.6271899999999999</v>
+      </c>
     </row>
     <row r="262" ht="16" customHeight="1" s="8">
       <c r="A262" s="5" t="n">
@@ -15751,6 +16537,9 @@
       <c r="AA262" t="n">
         <v>0.7332599999999999</v>
       </c>
+      <c r="AB262" t="n">
+        <v>0.571775</v>
+      </c>
     </row>
     <row r="263" ht="16" customHeight="1" s="8">
       <c r="A263" s="5" t="n">
@@ -15810,6 +16599,9 @@
       <c r="AA263" t="n">
         <v>0.6323923076923077</v>
       </c>
+      <c r="AB263" t="n">
+        <v>0.6547307692307693</v>
+      </c>
     </row>
     <row r="264" ht="16" customHeight="1" s="8">
       <c r="A264" s="5" t="n">
@@ -15869,6 +16661,9 @@
       <c r="AA264" t="n">
         <v>0.5804555555555555</v>
       </c>
+      <c r="AB264" t="n">
+        <v>0.8918874999999999</v>
+      </c>
     </row>
     <row r="265" ht="16" customHeight="1" s="8">
       <c r="A265" s="5" t="n">
@@ -15928,6 +16723,9 @@
       <c r="AA265" t="n">
         <v>0.5861799999999999</v>
       </c>
+      <c r="AB265" t="n">
+        <v>0.83503</v>
+      </c>
     </row>
     <row r="266" ht="16" customHeight="1" s="8">
       <c r="A266" s="5" t="n">
@@ -15987,6 +16785,9 @@
       <c r="AA266" t="n">
         <v>0.6159333333333333</v>
       </c>
+      <c r="AB266" t="n">
+        <v>0.7237888888888889</v>
+      </c>
     </row>
     <row r="267" ht="16" customHeight="1" s="8">
       <c r="A267" s="5" t="n">
@@ -16046,6 +16847,9 @@
       <c r="AA267" t="n">
         <v>0.601075</v>
       </c>
+      <c r="AB267" t="n">
+        <v>0.4552444444444445</v>
+      </c>
     </row>
     <row r="268" ht="16" customHeight="1" s="8">
       <c r="A268" s="5" t="n">
@@ -16105,6 +16909,9 @@
       <c r="AA268" t="n">
         <v>0.6919636363636363</v>
       </c>
+      <c r="AB268" t="n">
+        <v>0.7277333333333335</v>
+      </c>
     </row>
     <row r="269" ht="16" customHeight="1" s="8">
       <c r="A269" s="5" t="n">
@@ -16164,6 +16971,9 @@
       <c r="AA269" t="n">
         <v>0.7020999999999999</v>
       </c>
+      <c r="AB269" t="n">
+        <v>0.5953363636363637</v>
+      </c>
     </row>
     <row r="270" ht="16" customHeight="1" s="8">
       <c r="A270" s="5" t="n">
@@ -16223,6 +17033,9 @@
       <c r="AA270" t="n">
         <v>0.6463857142857143</v>
       </c>
+      <c r="AB270" t="n">
+        <v>0.7486</v>
+      </c>
     </row>
     <row r="271" ht="16" customHeight="1" s="8">
       <c r="A271" s="5" t="n">
@@ -16282,6 +17095,9 @@
       <c r="AA271" t="n">
         <v>0.6303</v>
       </c>
+      <c r="AB271" t="n">
+        <v>0.64428</v>
+      </c>
     </row>
     <row r="272" ht="16" customHeight="1" s="8">
       <c r="A272" s="5" t="n">
@@ -16341,6 +17157,9 @@
       <c r="AA272" t="n">
         <v>0.509725</v>
       </c>
+      <c r="AB272" t="n">
+        <v>0.6922333333333333</v>
+      </c>
     </row>
     <row r="273" ht="16" customHeight="1" s="8">
       <c r="A273" s="5" t="n">
@@ -16400,6 +17219,9 @@
       <c r="AA273" t="n">
         <v>0.7052142857142858</v>
       </c>
+      <c r="AB273" t="n">
+        <v>0.6371999999999999</v>
+      </c>
     </row>
     <row r="274" ht="16" customHeight="1" s="8">
       <c r="A274" s="5" t="n">
@@ -16459,6 +17281,9 @@
       <c r="AA274" t="n">
         <v>0.6361699999999999</v>
       </c>
+      <c r="AB274" t="n">
+        <v>0.7016999999999999</v>
+      </c>
     </row>
     <row r="275" ht="16" customHeight="1" s="8">
       <c r="A275" s="5" t="n">
@@ -16518,6 +17343,9 @@
       <c r="AA275" t="n">
         <v>0.7335111111111111</v>
       </c>
+      <c r="AB275" t="n">
+        <v>0.6962111111111111</v>
+      </c>
     </row>
     <row r="276" ht="16" customHeight="1" s="8">
       <c r="A276" s="5" t="n">
@@ -16577,6 +17405,9 @@
       <c r="AA276" t="n">
         <v>0.7299099999999999</v>
       </c>
+      <c r="AB276" t="n">
+        <v>0.5692</v>
+      </c>
     </row>
     <row r="277" ht="16" customHeight="1" s="8">
       <c r="A277" s="5" t="n">
@@ -16636,6 +17467,9 @@
       <c r="AA277" t="n">
         <v>0.7526999999999999</v>
       </c>
+      <c r="AB277" t="n">
+        <v>0.6575181818181818</v>
+      </c>
     </row>
     <row r="278" ht="16" customHeight="1" s="8">
       <c r="A278" s="5" t="n">
@@ -16695,6 +17529,9 @@
       <c r="AA278" t="n">
         <v>0.5824800000000001</v>
       </c>
+      <c r="AB278" t="n">
+        <v>0.6304499999999998</v>
+      </c>
     </row>
     <row r="279" ht="16" customHeight="1" s="8">
       <c r="A279" s="5" t="n">
@@ -16754,6 +17591,9 @@
       <c r="AA279" t="n">
         <v>0.6862818181818182</v>
       </c>
+      <c r="AB279" t="n">
+        <v>0.6911444444444445</v>
+      </c>
     </row>
     <row r="280" ht="16" customHeight="1" s="8">
       <c r="A280" s="5" t="n">
@@ -16813,6 +17653,9 @@
       <c r="AA280" t="n">
         <v>0.6921</v>
       </c>
+      <c r="AB280" t="n">
+        <v>0.6052</v>
+      </c>
     </row>
     <row r="281" ht="16" customHeight="1" s="8">
       <c r="A281" s="5" t="n">
@@ -16872,6 +17715,9 @@
       <c r="AA281" t="n">
         <v>0.5591083333333333</v>
       </c>
+      <c r="AB281" t="n">
+        <v>0.5792888888888889</v>
+      </c>
     </row>
     <row r="282" ht="16" customHeight="1" s="8">
       <c r="A282" s="5" t="n">
@@ -16931,6 +17777,9 @@
       <c r="AA282" t="n">
         <v>0.587125</v>
       </c>
+      <c r="AB282" t="n">
+        <v>0.7244916666666666</v>
+      </c>
     </row>
     <row r="283" ht="16" customHeight="1" s="8">
       <c r="A283" s="5" t="n">
@@ -16990,6 +17839,9 @@
       <c r="AA283" t="n">
         <v>0.6295555555555555</v>
       </c>
+      <c r="AB283" t="n">
+        <v>0.6353090909090908</v>
+      </c>
     </row>
     <row r="284" ht="16" customHeight="1" s="8">
       <c r="A284" s="5" t="n">
@@ -17049,6 +17901,9 @@
       <c r="AA284" t="n">
         <v>0.7339875</v>
       </c>
+      <c r="AB284" t="n">
+        <v>0.6921625</v>
+      </c>
     </row>
     <row r="285" ht="16" customHeight="1" s="8">
       <c r="A285" s="5" t="n">
@@ -17105,6 +17960,9 @@
       <c r="AA285" t="n">
         <v>0.7849090909090909</v>
       </c>
+      <c r="AB285" t="n">
+        <v>0.7570818181818182</v>
+      </c>
     </row>
     <row r="286" ht="16" customHeight="1" s="8">
       <c r="A286" s="5" t="n">
@@ -17164,6 +18022,9 @@
       <c r="AA286" t="n">
         <v>0.5895875</v>
       </c>
+      <c r="AB286" t="n">
+        <v>0.7657833333333331</v>
+      </c>
     </row>
     <row r="287" ht="16" customHeight="1" s="8">
       <c r="A287" s="5" t="n">
@@ -17223,6 +18084,9 @@
       <c r="AA287" t="n">
         <v>0.7396333333333334</v>
       </c>
+      <c r="AB287" t="n">
+        <v>0.6864666666666667</v>
+      </c>
     </row>
     <row r="288" ht="16" customHeight="1" s="8">
       <c r="A288" s="5" t="n">
@@ -17282,6 +18146,9 @@
       <c r="AA288" t="n">
         <v>0.7434222222222222</v>
       </c>
+      <c r="AB288" t="n">
+        <v>0.7069666666666667</v>
+      </c>
     </row>
     <row r="289" ht="16" customHeight="1" s="8">
       <c r="A289" s="5" t="n">
@@ -17341,6 +18208,9 @@
       <c r="AA289" t="n">
         <v>0.7987</v>
       </c>
+      <c r="AB289" t="n">
+        <v>0.6086</v>
+      </c>
     </row>
     <row r="290" ht="16" customHeight="1" s="8">
       <c r="A290" s="5" t="n">
@@ -17400,6 +18270,9 @@
       <c r="AA290" t="n">
         <v>0.4774625</v>
       </c>
+      <c r="AB290" t="n">
+        <v>0.7044100000000001</v>
+      </c>
     </row>
     <row r="291" ht="16" customHeight="1" s="8">
       <c r="A291" s="5" t="n">
@@ -17459,6 +18332,9 @@
       <c r="AA291" t="n">
         <v>0.5572500000000001</v>
       </c>
+      <c r="AB291" t="n">
+        <v>0.6983100000000001</v>
+      </c>
     </row>
     <row r="292" ht="16" customHeight="1" s="8">
       <c r="A292" s="5" t="n">
@@ -17518,6 +18394,9 @@
       <c r="AA292" t="n">
         <v>0.490725</v>
       </c>
+      <c r="AB292" t="n">
+        <v>0.48245</v>
+      </c>
     </row>
     <row r="293" ht="16" customHeight="1" s="8">
       <c r="A293" s="5" t="n">
@@ -17577,6 +18456,9 @@
       <c r="AA293" t="n">
         <v>0.5648636363636362</v>
       </c>
+      <c r="AB293" t="n">
+        <v>0.5845416666666667</v>
+      </c>
     </row>
     <row r="294" ht="16" customHeight="1" s="8">
       <c r="A294" s="5" t="n">
@@ -17636,6 +18518,9 @@
       <c r="AA294" t="n">
         <v>0.423075</v>
       </c>
+      <c r="AB294" t="n">
+        <v>0.7699666666666666</v>
+      </c>
     </row>
     <row r="295" ht="16" customHeight="1" s="8">
       <c r="A295" s="5" t="n">
@@ -17695,6 +18580,9 @@
       <c r="AA295" t="n">
         <v>0.4989727272727272</v>
       </c>
+      <c r="AB295" t="n">
+        <v>0.7778799999999999</v>
+      </c>
     </row>
     <row r="296" ht="16" customHeight="1" s="8">
       <c r="A296" s="5" t="n">
@@ -17754,6 +18642,9 @@
       <c r="AA296" t="n">
         <v>0.7508499999999999</v>
       </c>
+      <c r="AB296" t="n">
+        <v>0.6850307692307692</v>
+      </c>
     </row>
     <row r="297" ht="16" customHeight="1" s="8">
       <c r="A297" s="5" t="n">
@@ -17813,6 +18704,9 @@
       <c r="AA297" t="n">
         <v>0.5100777777777777</v>
       </c>
+      <c r="AB297" t="n">
+        <v>0.5437333333333333</v>
+      </c>
     </row>
     <row r="298" ht="16" customHeight="1" s="8">
       <c r="A298" s="5" t="n">
@@ -17872,6 +18766,9 @@
       <c r="AA298" t="n">
         <v>0.6275999999999999</v>
       </c>
+      <c r="AB298" t="n">
+        <v>0.6059272727272728</v>
+      </c>
     </row>
     <row r="299" ht="16" customHeight="1" s="8">
       <c r="A299" s="5" t="n">
@@ -17931,6 +18828,9 @@
       <c r="AA299" t="n">
         <v>0.4120666666666666</v>
       </c>
+      <c r="AB299" t="n">
+        <v>0.5445583333333334</v>
+      </c>
     </row>
     <row r="300" ht="16" customHeight="1" s="8">
       <c r="A300" s="5" t="n">
@@ -17990,6 +18890,9 @@
       <c r="AA300" t="n">
         <v>0.79434</v>
       </c>
+      <c r="AB300" t="n">
+        <v>0.7297333333333333</v>
+      </c>
     </row>
     <row r="301" ht="16" customHeight="1" s="8">
       <c r="A301" s="5" t="n">
@@ -18049,6 +18952,9 @@
       <c r="AA301" t="n">
         <v>0.5645333333333333</v>
       </c>
+      <c r="AB301" t="n">
+        <v>0.7012454545454544</v>
+      </c>
     </row>
     <row r="302" ht="16" customHeight="1" s="8">
       <c r="A302" s="5" t="n">
@@ -18108,6 +19014,9 @@
       <c r="AA302" t="n">
         <v>0.6232</v>
       </c>
+      <c r="AB302" t="n">
+        <v>0.5287333333333334</v>
+      </c>
     </row>
     <row r="303" ht="16" customHeight="1" s="8">
       <c r="A303" s="5" t="n">
@@ -18167,6 +19076,9 @@
       <c r="AA303" t="n">
         <v>0.5212727272727273</v>
       </c>
+      <c r="AB303" t="n">
+        <v>0.7496222222222222</v>
+      </c>
     </row>
     <row r="304" ht="16" customHeight="1" s="8">
       <c r="A304" s="5" t="n">
@@ -18226,6 +19138,9 @@
       <c r="AA304" t="n">
         <v>0.4818125</v>
       </c>
+      <c r="AB304" t="n">
+        <v>0.6539374999999999</v>
+      </c>
     </row>
     <row r="305" ht="16" customHeight="1" s="8">
       <c r="A305" s="5" t="n">
@@ -18285,6 +19200,9 @@
       <c r="AA305" t="n">
         <v>0.6407999999999999</v>
       </c>
+      <c r="AB305" t="n">
+        <v>0.7149666666666668</v>
+      </c>
     </row>
     <row r="306" ht="16" customHeight="1" s="8">
       <c r="A306" s="5" t="n">
@@ -18344,6 +19262,9 @@
       <c r="AA306" t="n">
         <v>0.8015600000000001</v>
       </c>
+      <c r="AB306" t="n">
+        <v>0.62009</v>
+      </c>
     </row>
     <row r="307" ht="16" customHeight="1" s="8">
       <c r="A307" s="5" t="n">
@@ -18403,6 +19324,9 @@
       <c r="AA307" t="n">
         <v>0.5751333333333333</v>
       </c>
+      <c r="AB307" t="n">
+        <v>0.8117500000000002</v>
+      </c>
     </row>
     <row r="308" ht="16" customHeight="1" s="8">
       <c r="A308" s="5" t="n">
@@ -18462,6 +19386,9 @@
       <c r="AA308" t="n">
         <v>0.4388625</v>
       </c>
+      <c r="AB308" t="n">
+        <v>0.73348</v>
+      </c>
     </row>
     <row r="309" ht="16" customHeight="1" s="8">
       <c r="A309" s="5" t="n">
@@ -18521,6 +19448,9 @@
       <c r="AA309" t="n">
         <v>0.604475</v>
       </c>
+      <c r="AB309" t="n">
+        <v>0.6241428571428572</v>
+      </c>
     </row>
     <row r="310" ht="16" customHeight="1" s="8">
       <c r="A310" s="5" t="n">
@@ -18580,6 +19510,9 @@
       <c r="AA310" t="n">
         <v>0.69906</v>
       </c>
+      <c r="AB310" t="n">
+        <v>0.6362999999999999</v>
+      </c>
     </row>
     <row r="311" ht="16" customHeight="1" s="8">
       <c r="A311" s="5" t="n">
@@ -18638,6 +19571,9 @@
       </c>
       <c r="AA311" t="n">
         <v>0.5989555555555555</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>0.6525909090909091</v>
       </c>
     </row>
     <row r="314" ht="16" customHeight="1" s="8">
@@ -18731,6 +19667,12 @@
       <c r="AA316" t="n">
         <v>0.0009</v>
       </c>
+      <c r="AB316" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>0.293</v>
+      </c>
     </row>
     <row r="317" ht="16" customHeight="1" s="8">
       <c r="A317" s="5" t="n">
@@ -18799,6 +19741,12 @@
       <c r="AA317" t="n">
         <v>0.0022</v>
       </c>
+      <c r="AB317" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>0.2067</v>
+      </c>
     </row>
     <row r="318" ht="16" customHeight="1" s="8">
       <c r="A318" s="5" t="n">
@@ -18867,6 +19815,12 @@
       <c r="AA318" t="n">
         <v>0.0593</v>
       </c>
+      <c r="AB318" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>0.4589</v>
+      </c>
     </row>
     <row r="319" ht="16" customHeight="1" s="8">
       <c r="A319" s="5" t="n">
@@ -18935,6 +19889,12 @@
       <c r="AA319" t="n">
         <v>0.1163</v>
       </c>
+      <c r="AB319" t="n">
+        <v>0.09229999999999999</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>0.2224</v>
+      </c>
     </row>
     <row r="320" ht="16" customHeight="1" s="8">
       <c r="A320" s="5" t="n">
@@ -19003,6 +19963,9 @@
       <c r="AA320" t="n">
         <v>0.0108</v>
       </c>
+      <c r="AB320" t="n">
+        <v>0.1119</v>
+      </c>
     </row>
     <row r="321" ht="16" customHeight="1" s="8">
       <c r="A321" s="5" t="n">
@@ -19071,6 +20034,9 @@
       <c r="AA321" t="n">
         <v>0.058</v>
       </c>
+      <c r="AB321" t="n">
+        <v>0.0568</v>
+      </c>
     </row>
     <row r="322" ht="16" customHeight="1" s="8">
       <c r="A322" s="5" t="n">
@@ -19139,6 +20105,9 @@
       <c r="AA322" t="n">
         <v>0.0319</v>
       </c>
+      <c r="AB322" t="n">
+        <v>0.09080000000000001</v>
+      </c>
     </row>
     <row r="323" ht="16" customHeight="1" s="8">
       <c r="A323" s="5" t="n">
@@ -19207,6 +20176,9 @@
       <c r="AA323" t="n">
         <v>0.0553</v>
       </c>
+      <c r="AB323" t="n">
+        <v>0.0606</v>
+      </c>
     </row>
     <row r="324" ht="16" customHeight="1" s="8">
       <c r="A324" s="5" t="n">
@@ -19275,6 +20247,9 @@
       <c r="AA324" t="n">
         <v>0.062</v>
       </c>
+      <c r="AB324" t="n">
+        <v>0.0897</v>
+      </c>
     </row>
     <row r="325" ht="16" customHeight="1" s="8">
       <c r="A325" s="5" t="n">
@@ -19343,6 +20318,9 @@
       <c r="AA325" t="n">
         <v>0.0505</v>
       </c>
+      <c r="AB325" t="n">
+        <v>0.0934</v>
+      </c>
     </row>
     <row r="326" ht="16" customHeight="1" s="8">
       <c r="A326" s="5" t="n">
@@ -19402,6 +20380,9 @@
       <c r="AA326" t="n">
         <v>0.0609</v>
       </c>
+      <c r="AB326" t="n">
+        <v>0.098</v>
+      </c>
     </row>
     <row r="327" ht="16" customHeight="1" s="8">
       <c r="A327" s="5" t="n">
@@ -19461,6 +20442,9 @@
       <c r="AA327" t="n">
         <v>0.0771</v>
       </c>
+      <c r="AB327" t="n">
+        <v>0.07489999999999999</v>
+      </c>
     </row>
     <row r="328" ht="16" customHeight="1" s="8">
       <c r="A328" s="5" t="n">
@@ -19520,6 +20504,9 @@
       <c r="AA328" t="n">
         <v>0.0505</v>
       </c>
+      <c r="AB328" t="n">
+        <v>0.1351</v>
+      </c>
     </row>
     <row r="329" ht="16" customHeight="1" s="8">
       <c r="A329" s="5" t="n">
@@ -19579,6 +20566,9 @@
       <c r="AA329" t="n">
         <v>0.0718</v>
       </c>
+      <c r="AB329" t="n">
+        <v>0.0786</v>
+      </c>
     </row>
     <row r="330" ht="16" customHeight="1" s="8">
       <c r="A330" s="5" t="n">
@@ -19638,6 +20628,9 @@
       <c r="AA330" t="n">
         <v>0.0593</v>
       </c>
+      <c r="AB330" t="n">
+        <v>0.06759999999999999</v>
+      </c>
     </row>
     <row r="331" ht="16" customHeight="1" s="8">
       <c r="A331" s="5" t="n">
@@ -19697,6 +20690,9 @@
       <c r="AA331" t="n">
         <v>0.0622</v>
       </c>
+      <c r="AB331" t="n">
+        <v>0.0833</v>
+      </c>
     </row>
     <row r="332" ht="16" customHeight="1" s="8">
       <c r="A332" s="5" t="n">
@@ -19756,6 +20752,9 @@
       <c r="AA332" t="n">
         <v>0.0738</v>
       </c>
+      <c r="AB332" t="n">
+        <v>0.07439999999999999</v>
+      </c>
     </row>
     <row r="333" ht="16" customHeight="1" s="8">
       <c r="A333" s="5" t="n">
@@ -19815,6 +20814,9 @@
       <c r="AA333" t="n">
         <v>0.0607</v>
       </c>
+      <c r="AB333" t="n">
+        <v>0.0751</v>
+      </c>
     </row>
     <row r="334" ht="16" customHeight="1" s="8">
       <c r="A334" s="5" t="n">
@@ -19874,6 +20876,9 @@
       <c r="AA334" t="n">
         <v>0.0484</v>
       </c>
+      <c r="AB334" t="n">
+        <v>0.0668</v>
+      </c>
     </row>
     <row r="335" ht="16" customHeight="1" s="8">
       <c r="A335" s="5" t="n">
@@ -19933,6 +20938,9 @@
       <c r="AA335" t="n">
         <v>0.053</v>
       </c>
+      <c r="AB335" t="n">
+        <v>0.1011</v>
+      </c>
     </row>
     <row r="336" ht="16" customHeight="1" s="8">
       <c r="A336" s="5" t="n">
@@ -19992,6 +21000,9 @@
       <c r="AA336" t="n">
         <v>0.0606</v>
       </c>
+      <c r="AB336" t="n">
+        <v>0.06569999999999999</v>
+      </c>
     </row>
     <row r="337" ht="16" customHeight="1" s="8">
       <c r="A337" s="5" t="n">
@@ -20051,6 +21062,9 @@
       <c r="AA337" t="n">
         <v>0.0376</v>
       </c>
+      <c r="AB337" t="n">
+        <v>0.0477</v>
+      </c>
     </row>
     <row r="338" ht="16" customHeight="1" s="8">
       <c r="A338" s="5" t="n">
@@ -20110,6 +21124,9 @@
       <c r="AA338" t="n">
         <v>0.0509</v>
       </c>
+      <c r="AB338" t="n">
+        <v>0.07340000000000001</v>
+      </c>
     </row>
     <row r="339" ht="16" customHeight="1" s="8">
       <c r="A339" s="5" t="n">
@@ -20169,6 +21186,9 @@
       <c r="AA339" t="n">
         <v>0.0515</v>
       </c>
+      <c r="AB339" t="n">
+        <v>0.08019999999999999</v>
+      </c>
     </row>
     <row r="340" ht="16" customHeight="1" s="8">
       <c r="A340" s="5" t="n">
@@ -20228,6 +21248,9 @@
       <c r="AA340" t="n">
         <v>0.0597</v>
       </c>
+      <c r="AB340" t="n">
+        <v>0.1139</v>
+      </c>
     </row>
     <row r="341" ht="16" customHeight="1" s="8">
       <c r="A341" s="5" t="n">
@@ -20287,6 +21310,9 @@
       <c r="AA341" t="n">
         <v>0.0534</v>
       </c>
+      <c r="AB341" t="n">
+        <v>0.08019999999999999</v>
+      </c>
     </row>
     <row r="342" ht="16" customHeight="1" s="8">
       <c r="A342" s="5" t="n">
@@ -20346,6 +21372,9 @@
       <c r="AA342" t="n">
         <v>0.066</v>
       </c>
+      <c r="AB342" t="n">
+        <v>0.0784</v>
+      </c>
     </row>
     <row r="343" ht="16" customHeight="1" s="8">
       <c r="A343" s="5" t="n">
@@ -20405,6 +21434,9 @@
       <c r="AA343" t="n">
         <v>0.0497</v>
       </c>
+      <c r="AB343" t="n">
+        <v>0.063</v>
+      </c>
     </row>
     <row r="344" ht="16" customHeight="1" s="8">
       <c r="A344" s="5" t="n">
@@ -20464,6 +21496,9 @@
       <c r="AA344" t="n">
         <v>0.0472</v>
       </c>
+      <c r="AB344" t="n">
+        <v>0.07439999999999999</v>
+      </c>
     </row>
     <row r="345" ht="16" customHeight="1" s="8">
       <c r="A345" s="5" t="n">
@@ -20523,6 +21558,9 @@
       <c r="AA345" t="n">
         <v>0.0433</v>
       </c>
+      <c r="AB345" t="n">
+        <v>0.06859999999999999</v>
+      </c>
     </row>
     <row r="346" ht="16" customHeight="1" s="8">
       <c r="A346" s="5" t="n">
@@ -20582,6 +21620,9 @@
       <c r="AA346" t="n">
         <v>0.0397</v>
       </c>
+      <c r="AB346" t="n">
+        <v>0.0736</v>
+      </c>
     </row>
     <row r="347" ht="16" customHeight="1" s="8">
       <c r="A347" s="5" t="n">
@@ -20641,6 +21682,9 @@
       <c r="AA347" t="n">
         <v>0.0353</v>
       </c>
+      <c r="AB347" t="n">
+        <v>0.06320000000000001</v>
+      </c>
     </row>
     <row r="348" ht="16" customHeight="1" s="8">
       <c r="A348" s="5" t="n">
@@ -20700,6 +21744,9 @@
       <c r="AA348" t="n">
         <v>0.0494</v>
       </c>
+      <c r="AB348" t="n">
+        <v>0.0765</v>
+      </c>
     </row>
     <row r="349" ht="16" customHeight="1" s="8">
       <c r="A349" s="5" t="n">
@@ -20759,6 +21806,9 @@
       <c r="AA349" t="n">
         <v>0.0442</v>
       </c>
+      <c r="AB349" t="n">
+        <v>0.0468</v>
+      </c>
     </row>
     <row r="350" ht="16" customHeight="1" s="8">
       <c r="A350" s="5" t="n">
@@ -20818,6 +21868,9 @@
       <c r="AA350" t="n">
         <v>0.0376</v>
       </c>
+      <c r="AB350" t="n">
+        <v>0.0634</v>
+      </c>
     </row>
     <row r="351" ht="16" customHeight="1" s="8">
       <c r="A351" s="5" t="n">
@@ -20877,6 +21930,9 @@
       <c r="AA351" t="n">
         <v>0.0458</v>
       </c>
+      <c r="AB351" t="n">
+        <v>0.0611</v>
+      </c>
     </row>
     <row r="352" ht="16" customHeight="1" s="8">
       <c r="A352" s="5" t="n">
@@ -20936,6 +21992,9 @@
       <c r="AA352" t="n">
         <v>0.0426</v>
       </c>
+      <c r="AB352" t="n">
+        <v>0.0599</v>
+      </c>
     </row>
     <row r="353" ht="16" customHeight="1" s="8">
       <c r="A353" s="5" t="n">
@@ -20995,6 +22054,9 @@
       <c r="AA353" t="n">
         <v>0.0358</v>
       </c>
+      <c r="AB353" t="n">
+        <v>0.06660000000000001</v>
+      </c>
     </row>
     <row r="354" ht="16" customHeight="1" s="8">
       <c r="A354" s="5" t="n">
@@ -21054,6 +22116,9 @@
       <c r="AA354" t="n">
         <v>0.0426</v>
       </c>
+      <c r="AB354" t="n">
+        <v>0.08119999999999999</v>
+      </c>
     </row>
     <row r="355" ht="16" customHeight="1" s="8">
       <c r="A355" s="5" t="n">
@@ -21113,6 +22178,9 @@
       <c r="AA355" t="n">
         <v>0.0444</v>
       </c>
+      <c r="AB355" t="n">
+        <v>0.0732</v>
+      </c>
     </row>
     <row r="356" ht="16" customHeight="1" s="8">
       <c r="A356" s="5" t="n">
@@ -21172,6 +22240,9 @@
       <c r="AA356" t="n">
         <v>0.0487</v>
       </c>
+      <c r="AB356" t="n">
+        <v>0.0586</v>
+      </c>
     </row>
     <row r="357" ht="16" customHeight="1" s="8">
       <c r="A357" s="5" t="n">
@@ -21231,6 +22302,9 @@
       <c r="AA357" t="n">
         <v>0.0459</v>
       </c>
+      <c r="AB357" t="n">
+        <v>0.057</v>
+      </c>
     </row>
     <row r="358" ht="16" customHeight="1" s="8">
       <c r="A358" s="5" t="n">
@@ -21290,6 +22364,9 @@
       <c r="AA358" t="n">
         <v>0.0412</v>
       </c>
+      <c r="AB358" t="n">
+        <v>0.0576</v>
+      </c>
     </row>
     <row r="359" ht="16" customHeight="1" s="8">
       <c r="A359" s="5" t="n">
@@ -21349,6 +22426,9 @@
       <c r="AA359" t="n">
         <v>0.0413</v>
       </c>
+      <c r="AB359" t="n">
+        <v>0.0526</v>
+      </c>
     </row>
     <row r="360" ht="16" customHeight="1" s="8">
       <c r="A360" s="5" t="n">
@@ -21408,6 +22488,9 @@
       <c r="AA360" t="n">
         <v>0.039</v>
       </c>
+      <c r="AB360" t="n">
+        <v>0.06279999999999999</v>
+      </c>
     </row>
     <row r="361" ht="16" customHeight="1" s="8">
       <c r="A361" s="5" t="n">
@@ -21467,6 +22550,9 @@
       <c r="AA361" t="n">
         <v>0.045</v>
       </c>
+      <c r="AB361" t="n">
+        <v>0.07779999999999999</v>
+      </c>
     </row>
     <row r="362" ht="16" customHeight="1" s="8">
       <c r="A362" s="5" t="n">
@@ -21526,6 +22612,9 @@
       <c r="AA362" t="n">
         <v>0.0353</v>
       </c>
+      <c r="AB362" t="n">
+        <v>0.0623</v>
+      </c>
     </row>
     <row r="363" ht="16" customHeight="1" s="8">
       <c r="A363" s="5" t="n">
@@ -21585,6 +22674,9 @@
       <c r="AA363" t="n">
         <v>0.0435</v>
       </c>
+      <c r="AB363" t="n">
+        <v>0.0546</v>
+      </c>
     </row>
     <row r="364" ht="16" customHeight="1" s="8">
       <c r="A364" s="5" t="n">
@@ -21644,6 +22736,9 @@
       <c r="AA364" t="n">
         <v>0.0327</v>
       </c>
+      <c r="AB364" t="n">
+        <v>0.0536</v>
+      </c>
     </row>
     <row r="365" ht="16" customHeight="1" s="8">
       <c r="A365" s="5" t="n">
@@ -21703,6 +22798,9 @@
       <c r="AA365" t="n">
         <v>0.0329</v>
       </c>
+      <c r="AB365" t="n">
+        <v>0.0525</v>
+      </c>
     </row>
     <row r="366" ht="16" customHeight="1" s="8">
       <c r="A366" s="5" t="n">
@@ -21762,6 +22860,9 @@
       <c r="AA366" t="n">
         <v>0.0385</v>
       </c>
+      <c r="AB366" t="n">
+        <v>0.0545</v>
+      </c>
     </row>
     <row r="367" ht="16" customHeight="1" s="8">
       <c r="A367" s="5" t="n">
@@ -21821,6 +22922,9 @@
       <c r="AA367" t="n">
         <v>0.0532</v>
       </c>
+      <c r="AB367" t="n">
+        <v>0.0708</v>
+      </c>
     </row>
     <row r="368" ht="16" customHeight="1" s="8">
       <c r="A368" s="5" t="n">
@@ -21880,6 +22984,9 @@
       <c r="AA368" t="n">
         <v>0.0369</v>
       </c>
+      <c r="AB368" t="n">
+        <v>0.06610000000000001</v>
+      </c>
     </row>
     <row r="369" ht="16" customHeight="1" s="8">
       <c r="A369" s="5" t="n">
@@ -21939,6 +23046,9 @@
       <c r="AA369" t="n">
         <v>0.0365</v>
       </c>
+      <c r="AB369" t="n">
+        <v>0.0786</v>
+      </c>
     </row>
     <row r="370" ht="16" customHeight="1" s="8">
       <c r="A370" s="5" t="n">
@@ -21998,6 +23108,9 @@
       <c r="AA370" t="n">
         <v>0.0341</v>
       </c>
+      <c r="AB370" t="n">
+        <v>0.066</v>
+      </c>
     </row>
     <row r="371" ht="16" customHeight="1" s="8">
       <c r="A371" s="5" t="n">
@@ -22057,6 +23170,9 @@
       <c r="AA371" t="n">
         <v>0.0403</v>
       </c>
+      <c r="AB371" t="n">
+        <v>0.0634</v>
+      </c>
     </row>
     <row r="372" ht="16" customHeight="1" s="8">
       <c r="A372" s="5" t="n">
@@ -22116,6 +23232,9 @@
       <c r="AA372" t="n">
         <v>0.0314</v>
       </c>
+      <c r="AB372" t="n">
+        <v>0.0561</v>
+      </c>
     </row>
     <row r="373" ht="16" customHeight="1" s="8">
       <c r="A373" s="5" t="n">
@@ -22175,6 +23294,9 @@
       <c r="AA373" t="n">
         <v>0.0482</v>
       </c>
+      <c r="AB373" t="n">
+        <v>0.07770000000000001</v>
+      </c>
     </row>
     <row r="374" ht="16" customHeight="1" s="8">
       <c r="A374" s="5" t="n">
@@ -22234,6 +23356,9 @@
       <c r="AA374" t="n">
         <v>0.0419</v>
       </c>
+      <c r="AB374" t="n">
+        <v>0.0892</v>
+      </c>
     </row>
     <row r="375" ht="16" customHeight="1" s="8">
       <c r="A375" s="5" t="n">
@@ -22293,6 +23418,9 @@
       <c r="AA375" t="n">
         <v>0.0408</v>
       </c>
+      <c r="AB375" t="n">
+        <v>0.0791</v>
+      </c>
     </row>
     <row r="376" ht="16" customHeight="1" s="8">
       <c r="A376" s="5" t="n">
@@ -22352,6 +23480,9 @@
       <c r="AA376" t="n">
         <v>0.0435</v>
       </c>
+      <c r="AB376" t="n">
+        <v>0.0693</v>
+      </c>
     </row>
     <row r="377" ht="16" customHeight="1" s="8">
       <c r="A377" s="5" t="n">
@@ -22411,6 +23542,9 @@
       <c r="AA377" t="n">
         <v>0.0384</v>
       </c>
+      <c r="AB377" t="n">
+        <v>0.0598</v>
+      </c>
     </row>
     <row r="378" ht="16" customHeight="1" s="8">
       <c r="A378" s="5" t="n">
@@ -22470,6 +23604,9 @@
       <c r="AA378" t="n">
         <v>0.0468</v>
       </c>
+      <c r="AB378" t="n">
+        <v>0.0602</v>
+      </c>
     </row>
     <row r="379" ht="16" customHeight="1" s="8">
       <c r="A379" s="5" t="n">
@@ -22529,6 +23666,9 @@
       <c r="AA379" t="n">
         <v>0.0434</v>
       </c>
+      <c r="AB379" t="n">
+        <v>0.0603</v>
+      </c>
     </row>
     <row r="380" ht="16" customHeight="1" s="8">
       <c r="A380" s="5" t="n">
@@ -22588,6 +23728,9 @@
       <c r="AA380" t="n">
         <v>0.044</v>
       </c>
+      <c r="AB380" t="n">
+        <v>0.07969999999999999</v>
+      </c>
     </row>
     <row r="381" ht="16" customHeight="1" s="8">
       <c r="A381" s="5" t="n">
@@ -22647,6 +23790,9 @@
       <c r="AA381" t="n">
         <v>0.0469</v>
       </c>
+      <c r="AB381" t="n">
+        <v>0.07530000000000001</v>
+      </c>
     </row>
     <row r="382" ht="16" customHeight="1" s="8">
       <c r="A382" s="5" t="n">
@@ -22706,6 +23852,9 @@
       <c r="AA382" t="n">
         <v>0.0442</v>
       </c>
+      <c r="AB382" t="n">
+        <v>0.0849</v>
+      </c>
     </row>
     <row r="383" ht="16" customHeight="1" s="8">
       <c r="A383" s="5" t="n">
@@ -22765,6 +23914,9 @@
       <c r="AA383" t="n">
         <v>0.045</v>
       </c>
+      <c r="AB383" t="n">
+        <v>0.0698</v>
+      </c>
     </row>
     <row r="384" ht="16" customHeight="1" s="8">
       <c r="A384" s="5" t="n">
@@ -22824,6 +23976,9 @@
       <c r="AA384" t="n">
         <v>0.0366</v>
       </c>
+      <c r="AB384" t="n">
+        <v>0.06950000000000001</v>
+      </c>
     </row>
     <row r="385" ht="16" customHeight="1" s="8">
       <c r="A385" s="5" t="n">
@@ -22883,6 +24038,9 @@
       <c r="AA385" t="n">
         <v>0.0366</v>
       </c>
+      <c r="AB385" t="n">
+        <v>0.07779999999999999</v>
+      </c>
     </row>
     <row r="386" ht="16" customHeight="1" s="8">
       <c r="A386" s="5" t="n">
@@ -22942,6 +24100,9 @@
       <c r="AA386" t="n">
         <v>0.0305</v>
       </c>
+      <c r="AB386" t="n">
+        <v>0.0497</v>
+      </c>
     </row>
     <row r="387" ht="16" customHeight="1" s="8">
       <c r="A387" s="5" t="n">
@@ -23001,6 +24162,9 @@
       <c r="AA387" t="n">
         <v>0.0339</v>
       </c>
+      <c r="AB387" t="n">
+        <v>0.0494</v>
+      </c>
     </row>
     <row r="388" ht="16" customHeight="1" s="8">
       <c r="A388" s="5" t="n">
@@ -23060,6 +24224,9 @@
       <c r="AA388" t="n">
         <v>0.0371</v>
       </c>
+      <c r="AB388" t="n">
+        <v>0.0606</v>
+      </c>
     </row>
     <row r="389" ht="16" customHeight="1" s="8">
       <c r="A389" s="5" t="n">
@@ -23119,6 +24286,9 @@
       <c r="AA389" t="n">
         <v>0.0432</v>
       </c>
+      <c r="AB389" t="n">
+        <v>0.0716</v>
+      </c>
     </row>
     <row r="390" ht="16" customHeight="1" s="8">
       <c r="A390" s="5" t="n">
@@ -23178,6 +24348,9 @@
       <c r="AA390" t="n">
         <v>0.0389</v>
       </c>
+      <c r="AB390" t="n">
+        <v>0.0549</v>
+      </c>
     </row>
     <row r="391" ht="16" customHeight="1" s="8">
       <c r="A391" s="5" t="n">
@@ -23237,6 +24410,9 @@
       <c r="AA391" t="n">
         <v>0.0292</v>
       </c>
+      <c r="AB391" t="n">
+        <v>0.0622</v>
+      </c>
     </row>
     <row r="392" ht="16" customHeight="1" s="8">
       <c r="A392" s="5" t="n">
@@ -23296,6 +24472,9 @@
       <c r="AA392" t="n">
         <v>0.0392</v>
       </c>
+      <c r="AB392" t="n">
+        <v>0.0587</v>
+      </c>
     </row>
     <row r="393" ht="16" customHeight="1" s="8">
       <c r="A393" s="5" t="n">
@@ -23355,6 +24534,9 @@
       <c r="AA393" t="n">
         <v>0.039</v>
       </c>
+      <c r="AB393" t="n">
+        <v>0.0709</v>
+      </c>
     </row>
     <row r="394" ht="16" customHeight="1" s="8">
       <c r="A394" s="5" t="n">
@@ -23414,6 +24596,9 @@
       <c r="AA394" t="n">
         <v>0.0428</v>
       </c>
+      <c r="AB394" t="n">
+        <v>0.06909999999999999</v>
+      </c>
     </row>
     <row r="395" ht="16" customHeight="1" s="8">
       <c r="A395" s="5" t="n">
@@ -23473,6 +24658,9 @@
       <c r="AA395" t="n">
         <v>0.0403</v>
       </c>
+      <c r="AB395" t="n">
+        <v>0.0677</v>
+      </c>
     </row>
     <row r="396" ht="16" customHeight="1" s="8">
       <c r="A396" s="5" t="n">
@@ -23532,6 +24720,9 @@
       <c r="AA396" t="n">
         <v>0.041</v>
       </c>
+      <c r="AB396" t="n">
+        <v>0.0601</v>
+      </c>
     </row>
     <row r="397" ht="16" customHeight="1" s="8">
       <c r="A397" s="5" t="n">
@@ -23591,6 +24782,9 @@
       <c r="AA397" t="n">
         <v>0.0353</v>
       </c>
+      <c r="AB397" t="n">
+        <v>0.0712</v>
+      </c>
     </row>
     <row r="398" ht="16" customHeight="1" s="8">
       <c r="A398" s="5" t="n">
@@ -23650,6 +24844,9 @@
       <c r="AA398" t="n">
         <v>0.0367</v>
       </c>
+      <c r="AB398" t="n">
+        <v>0.0737</v>
+      </c>
     </row>
     <row r="399" ht="16" customHeight="1" s="8">
       <c r="A399" s="5" t="n">
@@ -23709,6 +24906,9 @@
       <c r="AA399" t="n">
         <v>0.0303</v>
       </c>
+      <c r="AB399" t="n">
+        <v>0.0648</v>
+      </c>
     </row>
     <row r="400" ht="16" customHeight="1" s="8">
       <c r="A400" s="5" t="n">
@@ -23768,6 +24968,9 @@
       <c r="AA400" t="n">
         <v>0.0321</v>
       </c>
+      <c r="AB400" t="n">
+        <v>0.0677</v>
+      </c>
     </row>
     <row r="401" ht="16" customHeight="1" s="8">
       <c r="A401" s="5" t="n">
@@ -23827,6 +25030,9 @@
       <c r="AA401" t="n">
         <v>0.0331</v>
       </c>
+      <c r="AB401" t="n">
+        <v>0.07149999999999999</v>
+      </c>
     </row>
     <row r="402" ht="16" customHeight="1" s="8">
       <c r="A402" s="5" t="n">
@@ -23886,6 +25092,9 @@
       <c r="AA402" t="n">
         <v>0.0368</v>
       </c>
+      <c r="AB402" t="n">
+        <v>0.0882</v>
+      </c>
     </row>
     <row r="403" ht="16" customHeight="1" s="8">
       <c r="A403" s="5" t="n">
@@ -23945,6 +25154,9 @@
       <c r="AA403" t="n">
         <v>0.0317</v>
       </c>
+      <c r="AB403" t="n">
+        <v>0.0851</v>
+      </c>
     </row>
     <row r="404" ht="16" customHeight="1" s="8">
       <c r="A404" s="5" t="n">
@@ -24004,6 +25216,9 @@
       <c r="AA404" t="n">
         <v>0.0318</v>
       </c>
+      <c r="AB404" t="n">
+        <v>0.06569999999999999</v>
+      </c>
     </row>
     <row r="405" ht="16" customHeight="1" s="8">
       <c r="A405" s="5" t="n">
@@ -24063,6 +25278,9 @@
       <c r="AA405" t="n">
         <v>0.0538</v>
       </c>
+      <c r="AB405" t="n">
+        <v>0.0815</v>
+      </c>
     </row>
     <row r="406" ht="16" customHeight="1" s="8">
       <c r="A406" s="5" t="n">
@@ -24122,6 +25340,9 @@
       <c r="AA406" t="n">
         <v>0.0476</v>
       </c>
+      <c r="AB406" t="n">
+        <v>0.0623</v>
+      </c>
     </row>
     <row r="407" ht="16" customHeight="1" s="8">
       <c r="A407" s="5" t="n">
@@ -24181,6 +25402,9 @@
       <c r="AA407" t="n">
         <v>0.037</v>
       </c>
+      <c r="AB407" t="n">
+        <v>0.0759</v>
+      </c>
     </row>
     <row r="408" ht="16" customHeight="1" s="8">
       <c r="A408" s="5" t="n">
@@ -24240,6 +25464,9 @@
       <c r="AA408" t="n">
         <v>0.041</v>
       </c>
+      <c r="AB408" t="n">
+        <v>0.07870000000000001</v>
+      </c>
     </row>
     <row r="409" ht="16" customHeight="1" s="8">
       <c r="A409" s="5" t="n">
@@ -24299,6 +25526,9 @@
       <c r="AA409" t="n">
         <v>0.0312</v>
       </c>
+      <c r="AB409" t="n">
+        <v>0.0732</v>
+      </c>
     </row>
     <row r="410" ht="16" customHeight="1" s="8">
       <c r="A410" s="5" t="n">
@@ -24358,6 +25588,9 @@
       <c r="AA410" t="n">
         <v>0.0411</v>
       </c>
+      <c r="AB410" t="n">
+        <v>0.07240000000000001</v>
+      </c>
     </row>
     <row r="411" ht="16" customHeight="1" s="8">
       <c r="A411" s="5" t="n">
@@ -24417,6 +25650,9 @@
       <c r="AA411" t="n">
         <v>0.0335</v>
       </c>
+      <c r="AB411" t="n">
+        <v>0.08799999999999999</v>
+      </c>
     </row>
     <row r="412" ht="16" customHeight="1" s="8">
       <c r="A412" s="5" t="n">
@@ -24476,6 +25712,9 @@
       <c r="AA412" t="n">
         <v>0.0391</v>
       </c>
+      <c r="AB412" t="n">
+        <v>0.0593</v>
+      </c>
     </row>
     <row r="413" ht="16" customHeight="1" s="8">
       <c r="A413" s="5" t="n">
@@ -24535,6 +25774,9 @@
       <c r="AA413" t="n">
         <v>0.0376</v>
       </c>
+      <c r="AB413" t="n">
+        <v>0.0718</v>
+      </c>
     </row>
     <row r="414" ht="16" customHeight="1" s="8">
       <c r="A414" s="5" t="n">
@@ -24594,6 +25836,9 @@
       <c r="AA414" t="n">
         <v>0.0319</v>
       </c>
+      <c r="AB414" t="n">
+        <v>0.0757</v>
+      </c>
     </row>
     <row r="415" ht="16" customHeight="1" s="8">
       <c r="A415" s="5" t="n">
@@ -24652,6 +25897,9 @@
       </c>
       <c r="AA415" t="n">
         <v>0.0432</v>
+      </c>
+      <c r="AB415" t="n">
+        <v>0.06320000000000001</v>
       </c>
     </row>
     <row r="416">
@@ -24705,6 +25953,12 @@
       <c r="AA418" t="n">
         <v>0.1385</v>
       </c>
+      <c r="AB418" t="n">
+        <v>0.16215</v>
+      </c>
+      <c r="AC418" t="n">
+        <v>0.203975</v>
+      </c>
     </row>
     <row r="419">
       <c r="H419" s="5" t="n">
@@ -24743,6 +25997,12 @@
       <c r="AA419" t="n">
         <v>0.11364</v>
       </c>
+      <c r="AB419" t="n">
+        <v>0.1993166666666667</v>
+      </c>
+      <c r="AC419" t="n">
+        <v>0.1578</v>
+      </c>
     </row>
     <row r="420">
       <c r="H420" s="5" t="n">
@@ -24781,6 +26041,12 @@
       <c r="AA420" t="n">
         <v>0.1579333333333333</v>
       </c>
+      <c r="AB420" t="n">
+        <v>0.21489</v>
+      </c>
+      <c r="AC420" t="n">
+        <v>0.2339181818181818</v>
+      </c>
     </row>
     <row r="421">
       <c r="H421" s="5" t="n">
@@ -24819,6 +26085,12 @@
       <c r="AA421" t="n">
         <v>0.2806875</v>
       </c>
+      <c r="AB421" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="AC421" t="n">
+        <v>0.21715</v>
+      </c>
     </row>
     <row r="422">
       <c r="H422" s="5" t="n">
@@ -24857,6 +26129,9 @@
       <c r="AA422" t="n">
         <v>0.2632444444444444</v>
       </c>
+      <c r="AB422" t="n">
+        <v>0.2463125</v>
+      </c>
     </row>
     <row r="423">
       <c r="H423" s="5" t="n">
@@ -24895,6 +26170,9 @@
       <c r="AA423" t="n">
         <v>0.3480333333333334</v>
       </c>
+      <c r="AB423" t="n">
+        <v>0.3504888888888888</v>
+      </c>
     </row>
     <row r="424">
       <c r="H424" s="5" t="n">
@@ -24933,6 +26211,9 @@
       <c r="AA424" t="n">
         <v>0.3068363636363636</v>
       </c>
+      <c r="AB424" t="n">
+        <v>0.3586111111111111</v>
+      </c>
     </row>
     <row r="425">
       <c r="H425" s="5" t="n">
@@ -24971,6 +26252,9 @@
       <c r="AA425" t="n">
         <v>0.42354</v>
       </c>
+      <c r="AB425" t="n">
+        <v>0.38989</v>
+      </c>
     </row>
     <row r="426">
       <c r="H426" s="5" t="n">
@@ -25009,6 +26293,9 @@
       <c r="AA426" t="n">
         <v>0.4242181818181818</v>
       </c>
+      <c r="AB426" t="n">
+        <v>0.45862</v>
+      </c>
     </row>
     <row r="427">
       <c r="H427" s="5" t="n">
@@ -25047,6 +26334,9 @@
       <c r="AA427" t="n">
         <v>0.4758444444444445</v>
       </c>
+      <c r="AB427" t="n">
+        <v>0.4329625</v>
+      </c>
     </row>
     <row r="428">
       <c r="H428" s="5" t="n">
@@ -25073,6 +26363,9 @@
       <c r="AA428" t="n">
         <v>0.4650500000000001</v>
       </c>
+      <c r="AB428" t="n">
+        <v>0.4788777777777777</v>
+      </c>
     </row>
     <row r="429">
       <c r="H429" s="5" t="n">
@@ -25102,6 +26395,9 @@
       <c r="AA429" t="n">
         <v>0.4757666666666667</v>
       </c>
+      <c r="AB429" t="n">
+        <v>0.5476818181818182</v>
+      </c>
     </row>
     <row r="430">
       <c r="H430" s="5" t="n">
@@ -25131,6 +26427,9 @@
       <c r="AA430" t="n">
         <v>0.5172714285714286</v>
       </c>
+      <c r="AB430" t="n">
+        <v>0.5440222222222223</v>
+      </c>
     </row>
     <row r="431">
       <c r="H431" s="5" t="n">
@@ -25160,6 +26459,9 @@
       <c r="AA431" t="n">
         <v>0.5813090909090909</v>
       </c>
+      <c r="AB431" t="n">
+        <v>0.5485111111111112</v>
+      </c>
     </row>
     <row r="432">
       <c r="H432" s="5" t="n">
@@ -25189,6 +26491,9 @@
       <c r="AA432" t="n">
         <v>0.5715100000000001</v>
       </c>
+      <c r="AB432" t="n">
+        <v>0.6080699999999999</v>
+      </c>
     </row>
     <row r="433">
       <c r="H433" s="5" t="n">
@@ -25218,6 +26523,9 @@
       <c r="AA433" t="n">
         <v>0.5614</v>
       </c>
+      <c r="AB433" t="n">
+        <v>0.58855</v>
+      </c>
     </row>
     <row r="434">
       <c r="H434" s="5" t="n">
@@ -25247,6 +26555,9 @@
       <c r="AA434" t="n">
         <v>0.5625666666666667</v>
       </c>
+      <c r="AB434" t="n">
+        <v>0.6215444444444445</v>
+      </c>
     </row>
     <row r="435">
       <c r="H435" s="5" t="n">
@@ -25276,6 +26587,9 @@
       <c r="AA435" t="n">
         <v>0.5525600000000001</v>
       </c>
+      <c r="AB435" t="n">
+        <v>0.5857833333333333</v>
+      </c>
     </row>
     <row r="436">
       <c r="H436" s="5" t="n">
@@ -25305,6 +26619,9 @@
       <c r="AA436" t="n">
         <v>0.5790375000000001</v>
       </c>
+      <c r="AB436" t="n">
+        <v>0.6111333333333334</v>
+      </c>
     </row>
     <row r="437">
       <c r="H437" s="5" t="n">
@@ -25334,6 +26651,9 @@
       <c r="AA437" t="n">
         <v>0.6462714285714285</v>
       </c>
+      <c r="AB437" t="n">
+        <v>0.6626833333333334</v>
+      </c>
     </row>
     <row r="438">
       <c r="H438" s="5" t="n">
@@ -25363,6 +26683,9 @@
       <c r="AA438" t="n">
         <v>0.6219333333333333</v>
       </c>
+      <c r="AB438" t="n">
+        <v>0.7265181818181818</v>
+      </c>
     </row>
     <row r="439">
       <c r="H439" s="5" t="n">
@@ -25392,6 +26715,9 @@
       <c r="AA439" t="n">
         <v>0.6233181818181819</v>
       </c>
+      <c r="AB439" t="n">
+        <v>0.57873</v>
+      </c>
     </row>
     <row r="440">
       <c r="H440" s="5" t="n">
@@ -25421,6 +26747,9 @@
       <c r="AA440" t="n">
         <v>0.6385111111111113</v>
       </c>
+      <c r="AB440" t="n">
+        <v>0.5887875</v>
+      </c>
     </row>
     <row r="441">
       <c r="H441" s="5" t="n">
@@ -25450,6 +26779,9 @@
       <c r="AA441" t="n">
         <v>0.6656875</v>
       </c>
+      <c r="AB441" t="n">
+        <v>0.5946400000000001</v>
+      </c>
     </row>
     <row r="442">
       <c r="H442" s="5" t="n">
@@ -25479,6 +26811,9 @@
       <c r="AA442" t="n">
         <v>0.6785</v>
       </c>
+      <c r="AB442" t="n">
+        <v>0.6194999999999999</v>
+      </c>
     </row>
     <row r="443">
       <c r="H443" s="5" t="n">
@@ -25508,6 +26843,9 @@
       <c r="AA443" t="n">
         <v>0.5369777777777779</v>
       </c>
+      <c r="AB443" t="n">
+        <v>0.66425</v>
+      </c>
     </row>
     <row r="444">
       <c r="H444" s="5" t="n">
@@ -25537,6 +26875,9 @@
       <c r="AA444" t="n">
         <v>0.6877222222222222</v>
       </c>
+      <c r="AB444" t="n">
+        <v>0.67204</v>
+      </c>
     </row>
     <row r="445">
       <c r="H445" s="5" t="n">
@@ -25566,6 +26907,9 @@
       <c r="AA445" t="n">
         <v>0.6557272727272726</v>
       </c>
+      <c r="AB445" t="n">
+        <v>0.6517272727272728</v>
+      </c>
     </row>
     <row r="446">
       <c r="H446" s="5" t="n">
@@ -25595,6 +26939,9 @@
       <c r="AA446" t="n">
         <v>0.7241</v>
       </c>
+      <c r="AB446" t="n">
+        <v>0.6582444444444444</v>
+      </c>
     </row>
     <row r="447">
       <c r="H447" s="5" t="n">
@@ -25624,6 +26971,9 @@
       <c r="AA447" t="n">
         <v>0.7413444444444444</v>
       </c>
+      <c r="AB447" t="n">
+        <v>0.6647999999999999</v>
+      </c>
     </row>
     <row r="448">
       <c r="H448" s="5" t="n">
@@ -25653,6 +27003,9 @@
       <c r="AA448" t="n">
         <v>0.7255777777777778</v>
       </c>
+      <c r="AB448" t="n">
+        <v>0.7194750000000001</v>
+      </c>
     </row>
     <row r="449">
       <c r="H449" s="5" t="n">
@@ -25682,6 +27035,9 @@
       <c r="AA449" t="n">
         <v>0.6183363636363637</v>
       </c>
+      <c r="AB449" t="n">
+        <v>0.7014777777777778</v>
+      </c>
     </row>
     <row r="450">
       <c r="H450" s="5" t="n">
@@ -25708,6 +27064,9 @@
       <c r="AA450" t="n">
         <v>0.6870900000000002</v>
       </c>
+      <c r="AB450" t="n">
+        <v>0.6422</v>
+      </c>
     </row>
     <row r="451">
       <c r="H451" s="5" t="n">
@@ -25737,6 +27096,9 @@
       <c r="AA451" t="n">
         <v>0.6491571428571429</v>
       </c>
+      <c r="AB451" t="n">
+        <v>0.63023</v>
+      </c>
     </row>
     <row r="452">
       <c r="H452" s="5" t="n">
@@ -25766,6 +27128,9 @@
       <c r="AA452" t="n">
         <v>0.7239666666666666</v>
       </c>
+      <c r="AB452" t="n">
+        <v>0.6449181818181817</v>
+      </c>
     </row>
     <row r="453">
       <c r="H453" s="5" t="n">
@@ -25792,6 +27157,9 @@
       <c r="AA453" t="n">
         <v>0.6639199999999998</v>
       </c>
+      <c r="AB453" t="n">
+        <v>0.6359833333333332</v>
+      </c>
     </row>
     <row r="454">
       <c r="H454" s="5" t="n">
@@ -25821,6 +27189,9 @@
       <c r="AA454" t="n">
         <v>0.6278818181818182</v>
       </c>
+      <c r="AB454" t="n">
+        <v>0.6783857142857144</v>
+      </c>
     </row>
     <row r="455">
       <c r="H455" s="5" t="n">
@@ -25850,6 +27221,9 @@
       <c r="AA455" t="n">
         <v>0.660709090909091</v>
       </c>
+      <c r="AB455" t="n">
+        <v>0.6874999999999999</v>
+      </c>
     </row>
     <row r="456">
       <c r="H456" s="5" t="n">
@@ -25879,6 +27253,9 @@
       <c r="AA456" t="n">
         <v>0.64244</v>
       </c>
+      <c r="AB456" t="n">
+        <v>0.7225454545454546</v>
+      </c>
     </row>
     <row r="457">
       <c r="H457" s="5" t="n">
@@ -25908,6 +27285,9 @@
       <c r="AA457" t="n">
         <v>0.6693999999999999</v>
       </c>
+      <c r="AB457" t="n">
+        <v>0.7101875</v>
+      </c>
     </row>
     <row r="458">
       <c r="H458" s="5" t="n">
@@ -25937,6 +27317,9 @@
       <c r="AA458" t="n">
         <v>0.6659888888888889</v>
       </c>
+      <c r="AB458" t="n">
+        <v>0.5951666666666666</v>
+      </c>
     </row>
     <row r="459">
       <c r="H459" s="5" t="n">
@@ -25966,6 +27349,9 @@
       <c r="AA459" t="n">
         <v>0.6313111111111112</v>
       </c>
+      <c r="AB459" t="n">
+        <v>0.59263</v>
+      </c>
     </row>
     <row r="460">
       <c r="H460" s="5" t="n">
@@ -25995,6 +27381,9 @@
       <c r="AA460" t="n">
         <v>0.6701555555555555</v>
       </c>
+      <c r="AB460" t="n">
+        <v>0.6884999999999999</v>
+      </c>
     </row>
     <row r="461">
       <c r="H461" s="5" t="n">
@@ -26024,6 +27413,9 @@
       <c r="AA461" t="n">
         <v>0.7104875</v>
       </c>
+      <c r="AB461" t="n">
+        <v>0.5920153846153846</v>
+      </c>
     </row>
     <row r="462">
       <c r="H462" s="5" t="n">
@@ -26053,6 +27445,9 @@
       <c r="AA462" t="n">
         <v>0.6573</v>
       </c>
+      <c r="AB462" t="n">
+        <v>0.67069</v>
+      </c>
     </row>
     <row r="463">
       <c r="H463" s="5" t="n">
@@ -26082,6 +27477,9 @@
       <c r="AA463" t="n">
         <v>0.6970555555555555</v>
       </c>
+      <c r="AB463" t="n">
+        <v>0.6010545454545454</v>
+      </c>
     </row>
     <row r="464">
       <c r="H464" s="5" t="n">
@@ -26111,6 +27509,9 @@
       <c r="AA464" t="n">
         <v>0.7023125</v>
       </c>
+      <c r="AB464" t="n">
+        <v>0.65249</v>
+      </c>
     </row>
     <row r="465">
       <c r="H465" s="5" t="n">
@@ -26140,6 +27541,9 @@
       <c r="AA465" t="n">
         <v>0.75595</v>
       </c>
+      <c r="AB465" t="n">
+        <v>0.6362181818181818</v>
+      </c>
     </row>
     <row r="466">
       <c r="H466" s="5" t="n">
@@ -26169,6 +27573,9 @@
       <c r="AA466" t="n">
         <v>0.7135909090909091</v>
       </c>
+      <c r="AB466" t="n">
+        <v>0.7072222222222223</v>
+      </c>
     </row>
     <row r="467">
       <c r="H467" s="5" t="n">
@@ -26198,6 +27605,9 @@
       <c r="AA467" t="n">
         <v>0.58553</v>
       </c>
+      <c r="AB467" t="n">
+        <v>0.60287</v>
+      </c>
     </row>
     <row r="468">
       <c r="H468" s="5" t="n">
@@ -26227,6 +27637,9 @@
       <c r="AA468" t="n">
         <v>0.6592100000000001</v>
       </c>
+      <c r="AB468" t="n">
+        <v>0.6426666666666666</v>
+      </c>
     </row>
     <row r="469">
       <c r="H469" s="5" t="n">
@@ -26256,6 +27669,9 @@
       <c r="AA469" t="n">
         <v>0.698476923076923</v>
       </c>
+      <c r="AB469" t="n">
+        <v>0.5769769230769231</v>
+      </c>
     </row>
     <row r="470">
       <c r="H470" s="5" t="n">
@@ -26285,6 +27701,9 @@
       <c r="AA470" t="n">
         <v>0.6918555555555554</v>
       </c>
+      <c r="AB470" t="n">
+        <v>0.572125</v>
+      </c>
     </row>
     <row r="471">
       <c r="H471" s="5" t="n">
@@ -26314,6 +27733,9 @@
       <c r="AA471" t="n">
         <v>0.69656</v>
       </c>
+      <c r="AB471" t="n">
+        <v>0.58383</v>
+      </c>
     </row>
     <row r="472">
       <c r="H472" s="5" t="n">
@@ -26343,6 +27765,9 @@
       <c r="AA472" t="n">
         <v>0.6682166666666666</v>
       </c>
+      <c r="AB472" t="n">
+        <v>0.6255555555555556</v>
+      </c>
     </row>
     <row r="473">
       <c r="H473" s="5" t="n">
@@ -26372,6 +27797,9 @@
       <c r="AA473" t="n">
         <v>0.6366875</v>
       </c>
+      <c r="AB473" t="n">
+        <v>0.7355777777777779</v>
+      </c>
     </row>
     <row r="474">
       <c r="H474" s="5" t="n">
@@ -26401,6 +27829,9 @@
       <c r="AA474" t="n">
         <v>0.5790909090909091</v>
       </c>
+      <c r="AB474" t="n">
+        <v>0.596988888888889</v>
+      </c>
     </row>
     <row r="475">
       <c r="H475" s="5" t="n">
@@ -26430,6 +27861,9 @@
       <c r="AA475" t="n">
         <v>0.6073500000000001</v>
       </c>
+      <c r="AB475" t="n">
+        <v>0.6927545454545455</v>
+      </c>
     </row>
     <row r="476">
       <c r="H476" s="5" t="n">
@@ -26459,6 +27893,9 @@
       <c r="AA476" t="n">
         <v>0.6441571428571429</v>
       </c>
+      <c r="AB476" t="n">
+        <v>0.5732200000000001</v>
+      </c>
     </row>
     <row r="477">
       <c r="H477" s="5" t="n">
@@ -26488,6 +27925,9 @@
       <c r="AA477" t="n">
         <v>0.6373333333333334</v>
       </c>
+      <c r="AB477" t="n">
+        <v>0.67231</v>
+      </c>
     </row>
     <row r="478">
       <c r="H478" s="5" t="n">
@@ -26517,6 +27957,9 @@
       <c r="AA478" t="n">
         <v>0.6788875</v>
       </c>
+      <c r="AB478" t="n">
+        <v>0.6679749999999999</v>
+      </c>
     </row>
     <row r="479">
       <c r="H479" s="5" t="n">
@@ -26546,6 +27989,9 @@
       <c r="AA479" t="n">
         <v>0.6533142857142857</v>
       </c>
+      <c r="AB479" t="n">
+        <v>0.6657000000000001</v>
+      </c>
     </row>
     <row r="480">
       <c r="H480" s="5" t="n">
@@ -26575,6 +28021,9 @@
       <c r="AA480" t="n">
         <v>0.6851800000000001</v>
       </c>
+      <c r="AB480" t="n">
+        <v>0.6530555555555556</v>
+      </c>
     </row>
     <row r="481">
       <c r="H481" s="5" t="n">
@@ -26604,6 +28053,9 @@
       <c r="AA481" t="n">
         <v>0.6532777777777778</v>
       </c>
+      <c r="AB481" t="n">
+        <v>0.6001222222222222</v>
+      </c>
     </row>
     <row r="482">
       <c r="H482" s="5" t="n">
@@ -26633,6 +28085,9 @@
       <c r="AA482" t="n">
         <v>0.6102500000000001</v>
       </c>
+      <c r="AB482" t="n">
+        <v>0.657490909090909</v>
+      </c>
     </row>
     <row r="483">
       <c r="H483" s="5" t="n">
@@ -26662,6 +28117,9 @@
       <c r="AA483" t="n">
         <v>0.569225</v>
       </c>
+      <c r="AB483" t="n">
+        <v>0.6869818181818181</v>
+      </c>
     </row>
     <row r="484">
       <c r="H484" s="5" t="n">
@@ -26691,6 +28149,9 @@
       <c r="AA484" t="n">
         <v>0.6590400000000001</v>
       </c>
+      <c r="AB484" t="n">
+        <v>0.69135</v>
+      </c>
     </row>
     <row r="485">
       <c r="H485" s="5" t="n">
@@ -26720,6 +28181,9 @@
       <c r="AA485" t="n">
         <v>0.6167545454545453</v>
       </c>
+      <c r="AB485" t="n">
+        <v>0.6421444444444444</v>
+      </c>
     </row>
     <row r="486">
       <c r="H486" s="5" t="n">
@@ -26749,6 +28213,9 @@
       <c r="AA486" t="n">
         <v>0.6664714285714286</v>
       </c>
+      <c r="AB486" t="n">
+        <v>0.6169875</v>
+      </c>
     </row>
     <row r="487">
       <c r="H487" s="5" t="n">
@@ -26778,6 +28245,9 @@
       <c r="AA487" t="n">
         <v>0.679675</v>
       </c>
+      <c r="AB487" t="n">
+        <v>0.6336000000000001</v>
+      </c>
     </row>
     <row r="488">
       <c r="H488" s="5" t="n">
@@ -26807,6 +28277,9 @@
       <c r="AA488" t="n">
         <v>0.6391083333333334</v>
       </c>
+      <c r="AB488" t="n">
+        <v>0.6075333333333334</v>
+      </c>
     </row>
     <row r="489">
       <c r="H489" s="5" t="n">
@@ -26836,6 +28309,9 @@
       <c r="AA489" t="n">
         <v>0.7452888888888888</v>
       </c>
+      <c r="AB489" t="n">
+        <v>0.5981727272727272</v>
+      </c>
     </row>
     <row r="490">
       <c r="H490" s="5" t="n">
@@ -26865,6 +28341,9 @@
       <c r="AA490" t="n">
         <v>0.5895625000000001</v>
       </c>
+      <c r="AB490" t="n">
+        <v>0.6459999999999999</v>
+      </c>
     </row>
     <row r="491">
       <c r="H491" s="5" t="n">
@@ -26891,6 +28370,9 @@
       <c r="AA491" t="n">
         <v>0.6596090909090909</v>
       </c>
+      <c r="AB491" t="n">
+        <v>0.6707090909090909</v>
+      </c>
     </row>
     <row r="492">
       <c r="H492" s="5" t="n">
@@ -26920,6 +28402,9 @@
       <c r="AA492" t="n">
         <v>0.6394749999999999</v>
       </c>
+      <c r="AB492" t="n">
+        <v>0.5537166666666666</v>
+      </c>
     </row>
     <row r="493">
       <c r="H493" s="5" t="n">
@@ -26949,6 +28434,9 @@
       <c r="AA493" t="n">
         <v>0.6769166666666667</v>
       </c>
+      <c r="AB493" t="n">
+        <v>0.6687</v>
+      </c>
     </row>
     <row r="494">
       <c r="H494" s="5" t="n">
@@ -26978,6 +28466,9 @@
       <c r="AA494" t="n">
         <v>0.6338444444444445</v>
       </c>
+      <c r="AB494" t="n">
+        <v>0.5714666666666666</v>
+      </c>
     </row>
     <row r="495">
       <c r="H495" s="5" t="n">
@@ -27007,6 +28498,9 @@
       <c r="AA495" t="n">
         <v>0.6018</v>
       </c>
+      <c r="AB495" t="n">
+        <v>0.71056</v>
+      </c>
     </row>
     <row r="496">
       <c r="H496" s="5" t="n">
@@ -27036,6 +28530,9 @@
       <c r="AA496" t="n">
         <v>0.676325</v>
       </c>
+      <c r="AB496" t="n">
+        <v>0.65617</v>
+      </c>
     </row>
     <row r="497">
       <c r="H497" s="5" t="n">
@@ -27065,6 +28562,9 @@
       <c r="AA497" t="n">
         <v>0.6805499999999999</v>
       </c>
+      <c r="AB497" t="n">
+        <v>0.65998</v>
+      </c>
     </row>
     <row r="498">
       <c r="H498" s="5" t="n">
@@ -27094,6 +28594,9 @@
       <c r="AA498" t="n">
         <v>0.7142625</v>
       </c>
+      <c r="AB498" t="n">
+        <v>0.7633749999999999</v>
+      </c>
     </row>
     <row r="499">
       <c r="H499" s="5" t="n">
@@ -27123,6 +28626,9 @@
       <c r="AA499" t="n">
         <v>0.6307363636363637</v>
       </c>
+      <c r="AB499" t="n">
+        <v>0.6127333333333334</v>
+      </c>
     </row>
     <row r="500">
       <c r="H500" s="5" t="n">
@@ -27152,6 +28658,9 @@
       <c r="AA500" t="n">
         <v>0.70325</v>
       </c>
+      <c r="AB500" t="n">
+        <v>0.6565083333333334</v>
+      </c>
     </row>
     <row r="501">
       <c r="H501" s="5" t="n">
@@ -27181,6 +28690,9 @@
       <c r="AA501" t="n">
         <v>0.6362545454545454</v>
       </c>
+      <c r="AB501" t="n">
+        <v>0.58627</v>
+      </c>
     </row>
     <row r="502">
       <c r="H502" s="5" t="n">
@@ -27210,6 +28722,9 @@
       <c r="AA502" t="n">
         <v>0.605</v>
       </c>
+      <c r="AB502" t="n">
+        <v>0.6197846153846154</v>
+      </c>
     </row>
     <row r="503">
       <c r="H503" s="5" t="n">
@@ -27239,6 +28754,9 @@
       <c r="AA503" t="n">
         <v>0.6817111111111112</v>
       </c>
+      <c r="AB503" t="n">
+        <v>0.6321583333333333</v>
+      </c>
     </row>
     <row r="504">
       <c r="H504" s="5" t="n">
@@ -27268,6 +28786,9 @@
       <c r="AA504" t="n">
         <v>0.70706</v>
       </c>
+      <c r="AB504" t="n">
+        <v>0.6656363636363637</v>
+      </c>
     </row>
     <row r="505">
       <c r="H505" s="5" t="n">
@@ -27297,6 +28818,9 @@
       <c r="AA505" t="n">
         <v>0.6916777777777777</v>
       </c>
+      <c r="AB505" t="n">
+        <v>0.6895666666666668</v>
+      </c>
     </row>
     <row r="506">
       <c r="H506" s="5" t="n">
@@ -27326,6 +28850,9 @@
       <c r="AA506" t="n">
         <v>0.52351</v>
       </c>
+      <c r="AB506" t="n">
+        <v>0.6207</v>
+      </c>
     </row>
     <row r="507">
       <c r="H507" s="5" t="n">
@@ -27355,6 +28882,9 @@
       <c r="AA507" t="n">
         <v>0.6459083333333333</v>
       </c>
+      <c r="AB507" t="n">
+        <v>0.6804909090909091</v>
+      </c>
     </row>
     <row r="508">
       <c r="H508" s="5" t="n">
@@ -27384,6 +28914,9 @@
       <c r="AA508" t="n">
         <v>0.61317</v>
       </c>
+      <c r="AB508" t="n">
+        <v>0.6789333333333334</v>
+      </c>
     </row>
     <row r="509">
       <c r="H509" s="5" t="n">
@@ -27413,6 +28946,9 @@
       <c r="AA509" t="n">
         <v>0.6411272727272728</v>
       </c>
+      <c r="AB509" t="n">
+        <v>0.6211222222222221</v>
+      </c>
     </row>
     <row r="510">
       <c r="H510" s="5" t="n">
@@ -27442,6 +28978,9 @@
       <c r="AA510" t="n">
         <v>0.69145</v>
       </c>
+      <c r="AB510" t="n">
+        <v>0.5927500000000001</v>
+      </c>
     </row>
     <row r="511">
       <c r="H511" s="5" t="n">
@@ -27471,6 +29010,9 @@
       <c r="AA511" t="n">
         <v>0.6253900000000001</v>
       </c>
+      <c r="AB511" t="n">
+        <v>0.5595666666666665</v>
+      </c>
     </row>
     <row r="512">
       <c r="H512" s="5" t="n">
@@ -27500,6 +29042,9 @@
       <c r="AA512" t="n">
         <v>0.5757899999999999</v>
       </c>
+      <c r="AB512" t="n">
+        <v>0.6197199999999999</v>
+      </c>
     </row>
     <row r="513">
       <c r="H513" s="5" t="n">
@@ -27529,6 +29074,9 @@
       <c r="AA513" t="n">
         <v>0.6960999999999999</v>
       </c>
+      <c r="AB513" t="n">
+        <v>0.57916</v>
+      </c>
     </row>
     <row r="514">
       <c r="H514" s="5" t="n">
@@ -27558,6 +29106,9 @@
       <c r="AA514" t="n">
         <v>0.6923125</v>
       </c>
+      <c r="AB514" t="n">
+        <v>0.62291</v>
+      </c>
     </row>
     <row r="515">
       <c r="H515" s="5" t="n">
@@ -27587,6 +29138,9 @@
       <c r="AA515" t="n">
         <v>0.6928916666666667</v>
       </c>
+      <c r="AB515" t="n">
+        <v>0.6862285714285715</v>
+      </c>
     </row>
     <row r="516">
       <c r="H516" s="5" t="n">
@@ -27616,6 +29170,9 @@
       <c r="AA516" t="n">
         <v>0.62975</v>
       </c>
+      <c r="AB516" t="n">
+        <v>0.7121818181818182</v>
+      </c>
     </row>
     <row r="517">
       <c r="H517" s="5" t="n">
@@ -27644,6 +29201,9 @@
       </c>
       <c r="AA517" t="n">
         <v>0.6751888888888888</v>
+      </c>
+      <c r="AB517" t="n">
+        <v>0.7012636363636364</v>
       </c>
     </row>
     <row r="518">
@@ -27682,6 +29242,12 @@
       <c r="AA520" t="n">
         <v>0.1503263157894737</v>
       </c>
+      <c r="AB520" t="n">
+        <v>0.1565506493506493</v>
+      </c>
+      <c r="AC520" t="n">
+        <v>0.1717970149253731</v>
+      </c>
     </row>
     <row r="521">
       <c r="H521" s="5" t="n">
@@ -27705,6 +29271,12 @@
       <c r="AA521" t="n">
         <v>0.1285157894736842</v>
       </c>
+      <c r="AB521" t="n">
+        <v>0.1644642857142857</v>
+      </c>
+      <c r="AC521" t="n">
+        <v>0.1411533333333334</v>
+      </c>
     </row>
     <row r="522">
       <c r="H522" s="5" t="n">
@@ -27728,6 +29300,12 @@
       <c r="AA522" t="n">
         <v>0.25116</v>
       </c>
+      <c r="AB522" t="n">
+        <v>0.3002653846153846</v>
+      </c>
+      <c r="AC522" t="n">
+        <v>0.1067428571428571</v>
+      </c>
     </row>
     <row r="523">
       <c r="H523" s="5" t="n">
@@ -27751,6 +29329,12 @@
       <c r="AA523" t="n">
         <v>0.2358083333333333</v>
       </c>
+      <c r="AB523" t="n">
+        <v>0.352927027027027</v>
+      </c>
+      <c r="AC523" t="n">
+        <v>0.2687945945945946</v>
+      </c>
     </row>
     <row r="524">
       <c r="H524" s="5" t="n">
@@ -27774,6 +29358,9 @@
       <c r="AA524" t="n">
         <v>0.3285516129032258</v>
       </c>
+      <c r="AB524" t="n">
+        <v>0.3152666666666668</v>
+      </c>
     </row>
     <row r="525">
       <c r="H525" s="5" t="n">
@@ -27797,6 +29384,9 @@
       <c r="AA525" t="n">
         <v>0.3412743589743589</v>
       </c>
+      <c r="AB525" t="n">
+        <v>0.3486536585365854</v>
+      </c>
     </row>
     <row r="526">
       <c r="H526" s="5" t="n">
@@ -27820,6 +29410,9 @@
       <c r="AA526" t="n">
         <v>0.3485416666666666</v>
       </c>
+      <c r="AB526" t="n">
+        <v>0.3898524999999999</v>
+      </c>
     </row>
     <row r="527">
       <c r="H527" s="5" t="n">
@@ -27843,6 +29436,9 @@
       <c r="AA527" t="n">
         <v>0.41335</v>
       </c>
+      <c r="AB527" t="n">
+        <v>0.4166302325581395</v>
+      </c>
     </row>
     <row r="528">
       <c r="H528" s="5" t="n">
@@ -27866,6 +29462,9 @@
       <c r="AA528" t="n">
         <v>0.43766</v>
       </c>
+      <c r="AB528" t="n">
+        <v>0.43698</v>
+      </c>
     </row>
     <row r="529">
       <c r="H529" s="5" t="n">
@@ -27889,6 +29488,9 @@
       <c r="AA529" t="n">
         <v>0.4951630434782608</v>
       </c>
+      <c r="AB529" t="n">
+        <v>0.4151787234042553</v>
+      </c>
     </row>
     <row r="530">
       <c r="H530" s="5" t="n">
@@ -27903,6 +29505,9 @@
       <c r="AA530" t="n">
         <v>0.4348</v>
       </c>
+      <c r="AB530" t="n">
+        <v>0.4994232142857143</v>
+      </c>
     </row>
     <row r="531">
       <c r="H531" s="5" t="n">
@@ -27917,6 +29522,9 @@
       <c r="AA531" t="n">
         <v>0.470075</v>
       </c>
+      <c r="AB531" t="n">
+        <v>0.5372720930232557</v>
+      </c>
     </row>
     <row r="532">
       <c r="H532" s="5" t="n">
@@ -27931,6 +29539,9 @@
       <c r="AA532" t="n">
         <v>0.4910022727272728</v>
       </c>
+      <c r="AB532" t="n">
+        <v>0.3997775510204082</v>
+      </c>
     </row>
     <row r="533">
       <c r="H533" s="5" t="n">
@@ -27945,6 +29556,9 @@
       <c r="AA533" t="n">
         <v>0.521045</v>
       </c>
+      <c r="AB533" t="n">
+        <v>0.511645652173913</v>
+      </c>
     </row>
     <row r="534">
       <c r="H534" s="5" t="n">
@@ -27959,6 +29573,9 @@
       <c r="AA534" t="n">
         <v>0.4969525</v>
       </c>
+      <c r="AB534" t="n">
+        <v>0.490327027027027</v>
+      </c>
     </row>
     <row r="535">
       <c r="H535" s="5" t="n">
@@ -27973,6 +29590,9 @@
       <c r="AA535" t="n">
         <v>0.596545238095238</v>
       </c>
+      <c r="AB535" t="n">
+        <v>0.4960639344262295</v>
+      </c>
     </row>
     <row r="536">
       <c r="H536" s="5" t="n">
@@ -27987,6 +29607,9 @@
       <c r="AA536" t="n">
         <v>0.5141229166666667</v>
       </c>
+      <c r="AB536" t="n">
+        <v>0.5078483333333333</v>
+      </c>
     </row>
     <row r="537">
       <c r="H537" s="5" t="n">
@@ -28001,6 +29624,9 @@
       <c r="AA537" t="n">
         <v>0.5377682926829268</v>
       </c>
+      <c r="AB537" t="n">
+        <v>0.4695533333333333</v>
+      </c>
     </row>
     <row r="538">
       <c r="H538" s="5" t="n">
@@ -28015,6 +29641,9 @@
       <c r="AA538" t="n">
         <v>0.5237775</v>
       </c>
+      <c r="AB538" t="n">
+        <v>0.4764275862068967</v>
+      </c>
     </row>
     <row r="539">
       <c r="H539" s="5" t="n">
@@ -28029,6 +29658,9 @@
       <c r="AA539" t="n">
         <v>0.5336933333333334</v>
       </c>
+      <c r="AB539" t="n">
+        <v>0.4946375</v>
+      </c>
     </row>
     <row r="540">
       <c r="H540" s="5" t="n">
@@ -28043,6 +29675,9 @@
       <c r="AA540" t="n">
         <v>0.4066681818181818</v>
       </c>
+      <c r="AB540" t="n">
+        <v>0.561448076923077</v>
+      </c>
     </row>
     <row r="541">
       <c r="H541" s="5" t="n">
@@ -28057,6 +29692,9 @@
       <c r="AA541" t="n">
         <v>0.5121327868852459</v>
       </c>
+      <c r="AB541" t="n">
+        <v>0.4783385964912281</v>
+      </c>
     </row>
     <row r="542">
       <c r="H542" s="5" t="n">
@@ -28071,6 +29709,9 @@
       <c r="AA542" t="n">
         <v>0.6524575757575758</v>
       </c>
+      <c r="AB542" t="n">
+        <v>0.5868846153846154</v>
+      </c>
     </row>
     <row r="543">
       <c r="H543" s="5" t="n">
@@ -28085,6 +29726,9 @@
       <c r="AA543" t="n">
         <v>0.5775309523809523</v>
       </c>
+      <c r="AB543" t="n">
+        <v>0.4964914893617021</v>
+      </c>
     </row>
     <row r="544">
       <c r="H544" s="5" t="n">
@@ -28099,6 +29743,9 @@
       <c r="AA544" t="n">
         <v>0.5077702127659574</v>
       </c>
+      <c r="AB544" t="n">
+        <v>0.5538814814814815</v>
+      </c>
     </row>
     <row r="545">
       <c r="H545" s="5" t="n">
@@ -28113,6 +29760,9 @@
       <c r="AA545" t="n">
         <v>0.5702750000000001</v>
       </c>
+      <c r="AB545" t="n">
+        <v>0.6367836734693878</v>
+      </c>
     </row>
     <row r="546">
       <c r="H546" s="5" t="n">
@@ -28127,6 +29777,9 @@
       <c r="AA546" t="n">
         <v>0.51461</v>
       </c>
+      <c r="AB546" t="n">
+        <v>0.5919727272727273</v>
+      </c>
     </row>
     <row r="547">
       <c r="H547" s="5" t="n">
@@ -28141,6 +29794,9 @@
       <c r="AA547" t="n">
         <v>0.4843984126984127</v>
       </c>
+      <c r="AB547" t="n">
+        <v>0.469259649122807</v>
+      </c>
     </row>
     <row r="548">
       <c r="H548" s="5" t="n">
@@ -28155,6 +29811,9 @@
       <c r="AA548" t="n">
         <v>0.6421205128205129</v>
       </c>
+      <c r="AB548" t="n">
+        <v>0.5620295081967213</v>
+      </c>
     </row>
     <row r="549">
       <c r="H549" s="5" t="n">
@@ -28169,6 +29828,9 @@
       <c r="AA549" t="n">
         <v>0.6260354166666667</v>
       </c>
+      <c r="AB549" t="n">
+        <v>0.5043190476190476</v>
+      </c>
     </row>
     <row r="550">
       <c r="H550" s="5" t="n">
@@ -28183,6 +29845,9 @@
       <c r="AA550" t="n">
         <v>0.48785625</v>
       </c>
+      <c r="AB550" t="n">
+        <v>0.4628245614035087</v>
+      </c>
     </row>
     <row r="551">
       <c r="H551" s="5" t="n">
@@ -28197,6 +29862,9 @@
       <c r="AA551" t="n">
         <v>0.5245673076923077</v>
       </c>
+      <c r="AB551" t="n">
+        <v>0.5576653846153847</v>
+      </c>
     </row>
     <row r="552">
       <c r="H552" s="5" t="n">
@@ -28211,6 +29879,9 @@
       <c r="AA552" t="n">
         <v>0.6220530612244899</v>
       </c>
+      <c r="AB552" t="n">
+        <v>0.6387489795918367</v>
+      </c>
     </row>
     <row r="553">
       <c r="H553" s="5" t="n">
@@ -28225,6 +29896,9 @@
       <c r="AA553" t="n">
         <v>0.4655435897435897</v>
       </c>
+      <c r="AB553" t="n">
+        <v>0.6070470588235295</v>
+      </c>
     </row>
     <row r="554">
       <c r="H554" s="5" t="n">
@@ -28239,6 +29913,9 @@
       <c r="AA554" t="n">
         <v>0.4998842105263158</v>
       </c>
+      <c r="AB554" t="n">
+        <v>0.5745648648648649</v>
+      </c>
     </row>
     <row r="555">
       <c r="H555" s="5" t="n">
@@ -28253,6 +29930,9 @@
       <c r="AA555" t="n">
         <v>0.4882384615384615</v>
       </c>
+      <c r="AB555" t="n">
+        <v>0.5844453125</v>
+      </c>
     </row>
     <row r="556">
       <c r="H556" s="5" t="n">
@@ -28267,6 +29947,9 @@
       <c r="AA556" t="n">
         <v>0.6413152173913044</v>
       </c>
+      <c r="AB556" t="n">
+        <v>0.5178318181818183</v>
+      </c>
     </row>
     <row r="557">
       <c r="H557" s="5" t="n">
@@ -28281,6 +29964,9 @@
       <c r="AA557" t="n">
         <v>0.5343605263157895</v>
       </c>
+      <c r="AB557" t="n">
+        <v>0.4459767441860465</v>
+      </c>
     </row>
     <row r="558">
       <c r="H558" s="5" t="n">
@@ -28295,6 +29981,9 @@
       <c r="AA558" t="n">
         <v>0.5329367346938776</v>
       </c>
+      <c r="AB558" t="n">
+        <v>0.5964063829787234</v>
+      </c>
     </row>
     <row r="559">
       <c r="H559" s="5" t="n">
@@ -28309,6 +29998,9 @@
       <c r="AA559" t="n">
         <v>0.6104410256410256</v>
       </c>
+      <c r="AB559" t="n">
+        <v>0.5159064516129033</v>
+      </c>
     </row>
     <row r="560">
       <c r="H560" s="5" t="n">
@@ -28323,6 +30015,9 @@
       <c r="AA560" t="n">
         <v>0.5950268292682928</v>
       </c>
+      <c r="AB560" t="n">
+        <v>0.5529733333333333</v>
+      </c>
     </row>
     <row r="561">
       <c r="H561" s="5" t="n">
@@ -28337,6 +30032,9 @@
       <c r="AA561" t="n">
         <v>0.441603125</v>
       </c>
+      <c r="AB561" t="n">
+        <v>0.5286526315789474</v>
+      </c>
     </row>
     <row r="562">
       <c r="H562" s="5" t="n">
@@ -28351,6 +30049,9 @@
       <c r="AA562" t="n">
         <v>0.6010678571428573</v>
       </c>
+      <c r="AB562" t="n">
+        <v>0.572906</v>
+      </c>
     </row>
     <row r="563">
       <c r="H563" s="5" t="n">
@@ -28365,6 +30066,9 @@
       <c r="AA563" t="n">
         <v>0.6127653846153845</v>
       </c>
+      <c r="AB563" t="n">
+        <v>0.5864673913043479</v>
+      </c>
     </row>
     <row r="564">
       <c r="H564" s="5" t="n">
@@ -28379,6 +30083,9 @@
       <c r="AA564" t="n">
         <v>0.6603836734693878</v>
       </c>
+      <c r="AB564" t="n">
+        <v>0.4584102564102564</v>
+      </c>
     </row>
     <row r="565">
       <c r="H565" s="5" t="n">
@@ -28393,6 +30100,9 @@
       <c r="AA565" t="n">
         <v>0.5141492307692308</v>
       </c>
+      <c r="AB565" t="n">
+        <v>0.5261982456140351</v>
+      </c>
     </row>
     <row r="566">
       <c r="H566" s="5" t="n">
@@ -28407,6 +30117,9 @@
       <c r="AA566" t="n">
         <v>0.4987422222222223</v>
       </c>
+      <c r="AB566" t="n">
+        <v>0.4382428571428572</v>
+      </c>
     </row>
     <row r="567">
       <c r="H567" s="5" t="n">
@@ -28421,6 +30134,9 @@
       <c r="AA567" t="n">
         <v>0.5939326086956522</v>
       </c>
+      <c r="AB567" t="n">
+        <v>0.5711068965517241</v>
+      </c>
     </row>
     <row r="568">
       <c r="H568" s="5" t="n">
@@ -28435,6 +30151,9 @@
       <c r="AA568" t="n">
         <v>0.5251333333333333</v>
       </c>
+      <c r="AB568" t="n">
+        <v>0.6823121951219512</v>
+      </c>
     </row>
     <row r="569">
       <c r="H569" s="5" t="n">
@@ -28449,6 +30168,9 @@
       <c r="AA569" t="n">
         <v>0.5992499999999999</v>
       </c>
+      <c r="AB569" t="n">
+        <v>0.5570901960784314</v>
+      </c>
     </row>
     <row r="570">
       <c r="H570" s="5" t="n">
@@ -28463,6 +30185,9 @@
       <c r="AA570" t="n">
         <v>0.6631638297872341</v>
       </c>
+      <c r="AB570" t="n">
+        <v>0.5068537037037039</v>
+      </c>
     </row>
     <row r="571">
       <c r="H571" s="5" t="n">
@@ -28477,6 +30202,9 @@
       <c r="AA571" t="n">
         <v>0.5964181818181817</v>
       </c>
+      <c r="AB571" t="n">
+        <v>0.4709666666666666</v>
+      </c>
     </row>
     <row r="572">
       <c r="H572" s="5" t="n">
@@ -28491,6 +30219,9 @@
       <c r="AA572" t="n">
         <v>0.5253585365853659</v>
       </c>
+      <c r="AB572" t="n">
+        <v>0.4669441860465117</v>
+      </c>
     </row>
     <row r="573">
       <c r="H573" s="5" t="n">
@@ -28505,6 +30236,9 @@
       <c r="AA573" t="n">
         <v>0.5742934782608696</v>
       </c>
+      <c r="AB573" t="n">
+        <v>0.5654952380952381</v>
+      </c>
     </row>
     <row r="574">
       <c r="H574" s="5" t="n">
@@ -28519,6 +30253,9 @@
       <c r="AA574" t="n">
         <v>0.5569725</v>
       </c>
+      <c r="AB574" t="n">
+        <v>0.5409475409836066</v>
+      </c>
     </row>
     <row r="575">
       <c r="H575" s="5" t="n">
@@ -28533,6 +30270,9 @@
       <c r="AA575" t="n">
         <v>0.6183319999999999</v>
       </c>
+      <c r="AB575" t="n">
+        <v>0.5690542372881355</v>
+      </c>
     </row>
     <row r="576">
       <c r="H576" s="5" t="n">
@@ -28547,6 +30287,9 @@
       <c r="AA576" t="n">
         <v>0.5858706896551724</v>
       </c>
+      <c r="AB576" t="n">
+        <v>0.5787227272727272</v>
+      </c>
     </row>
     <row r="577">
       <c r="H577" s="5" t="n">
@@ -28561,6 +30304,9 @@
       <c r="AA577" t="n">
         <v>0.5512756756756757</v>
       </c>
+      <c r="AB577" t="n">
+        <v>0.5246318181818181</v>
+      </c>
     </row>
     <row r="578">
       <c r="H578" s="5" t="n">
@@ -28575,6 +30321,9 @@
       <c r="AA578" t="n">
         <v>0.5080931034482759</v>
       </c>
+      <c r="AB578" t="n">
+        <v>0.5935340425531915</v>
+      </c>
     </row>
     <row r="579">
       <c r="H579" s="5" t="n">
@@ -28589,6 +30338,9 @@
       <c r="AA579" t="n">
         <v>0.5646800000000001</v>
       </c>
+      <c r="AB579" t="n">
+        <v>0.4899475</v>
+      </c>
     </row>
     <row r="580">
       <c r="H580" s="5" t="n">
@@ -28603,6 +30355,9 @@
       <c r="AA580" t="n">
         <v>0.5087804347826087</v>
       </c>
+      <c r="AB580" t="n">
+        <v>0.5196113636363636</v>
+      </c>
     </row>
     <row r="581">
       <c r="H581" s="5" t="n">
@@ -28617,6 +30372,9 @@
       <c r="AA581" t="n">
         <v>0.6648603773584905</v>
       </c>
+      <c r="AB581" t="n">
+        <v>0.5488625000000001</v>
+      </c>
     </row>
     <row r="582">
       <c r="H582" s="5" t="n">
@@ -28631,6 +30389,9 @@
       <c r="AA582" t="n">
         <v>0.4996593749999999</v>
       </c>
+      <c r="AB582" t="n">
+        <v>0.5066957446808511</v>
+      </c>
     </row>
     <row r="583">
       <c r="H583" s="5" t="n">
@@ -28645,6 +30406,9 @@
       <c r="AA583" t="n">
         <v>0.5465696428571428</v>
       </c>
+      <c r="AB583" t="n">
+        <v>0.5499617021276596</v>
+      </c>
     </row>
     <row r="584">
       <c r="H584" s="5" t="n">
@@ -28659,6 +30423,9 @@
       <c r="AA584" t="n">
         <v>0.6259864864864864</v>
       </c>
+      <c r="AB584" t="n">
+        <v>0.5476288135593221</v>
+      </c>
     </row>
     <row r="585">
       <c r="H585" s="5" t="n">
@@ -28673,6 +30440,9 @@
       <c r="AA585" t="n">
         <v>0.5657333333333333</v>
       </c>
+      <c r="AB585" t="n">
+        <v>0.5353051282051283</v>
+      </c>
     </row>
     <row r="586">
       <c r="H586" s="5" t="n">
@@ -28687,6 +30457,9 @@
       <c r="AA586" t="n">
         <v>0.5171553191489361</v>
       </c>
+      <c r="AB586" t="n">
+        <v>0.4998645833333333</v>
+      </c>
     </row>
     <row r="587">
       <c r="H587" s="5" t="n">
@@ -28701,6 +30474,9 @@
       <c r="AA587" t="n">
         <v>0.5934499999999999</v>
       </c>
+      <c r="AB587" t="n">
+        <v>0.5625863636363636</v>
+      </c>
     </row>
     <row r="588">
       <c r="H588" s="5" t="n">
@@ -28715,6 +30491,9 @@
       <c r="AA588" t="n">
         <v>0.5607759259259258</v>
       </c>
+      <c r="AB588" t="n">
+        <v>0.4317767441860466</v>
+      </c>
     </row>
     <row r="589">
       <c r="H589" s="5" t="n">
@@ -28729,6 +30508,9 @@
       <c r="AA589" t="n">
         <v>0.49087</v>
       </c>
+      <c r="AB589" t="n">
+        <v>0.52338</v>
+      </c>
     </row>
     <row r="590">
       <c r="H590" s="5" t="n">
@@ -28743,6 +30525,9 @@
       <c r="AA590" t="n">
         <v>0.5817833333333334</v>
       </c>
+      <c r="AB590" t="n">
+        <v>0.4071904761904762</v>
+      </c>
     </row>
     <row r="591">
       <c r="H591" s="5" t="n">
@@ -28757,6 +30542,9 @@
       <c r="AA591" t="n">
         <v>0.5406019607843137</v>
       </c>
+      <c r="AB591" t="n">
+        <v>0.5598306122448979</v>
+      </c>
     </row>
     <row r="592">
       <c r="H592" s="5" t="n">
@@ -28771,6 +30559,9 @@
       <c r="AA592" t="n">
         <v>0.5149092592592592</v>
       </c>
+      <c r="AB592" t="n">
+        <v>0.490809756097561</v>
+      </c>
     </row>
     <row r="593">
       <c r="H593" s="5" t="n">
@@ -28785,6 +30576,9 @@
       <c r="AA593" t="n">
         <v>0.7144238095238096</v>
       </c>
+      <c r="AB593" t="n">
+        <v>0.4760387755102042</v>
+      </c>
     </row>
     <row r="594">
       <c r="H594" s="5" t="n">
@@ -28799,6 +30593,9 @@
       <c r="AA594" t="n">
         <v>0.5592714285714285</v>
       </c>
+      <c r="AB594" t="n">
+        <v>0.4513539999999999</v>
+      </c>
     </row>
     <row r="595">
       <c r="H595" s="5" t="n">
@@ -28813,6 +30610,9 @@
       <c r="AA595" t="n">
         <v>0.479385</v>
       </c>
+      <c r="AB595" t="n">
+        <v>0.5368244444444444</v>
+      </c>
     </row>
     <row r="596">
       <c r="H596" s="5" t="n">
@@ -28827,6 +30627,9 @@
       <c r="AA596" t="n">
         <v>0.6223137254901961</v>
       </c>
+      <c r="AB596" t="n">
+        <v>0.4654106382978724</v>
+      </c>
     </row>
     <row r="597">
       <c r="H597" s="5" t="n">
@@ -28841,6 +30644,9 @@
       <c r="AA597" t="n">
         <v>0.5880897959183672</v>
       </c>
+      <c r="AB597" t="n">
+        <v>0.4997245283018869</v>
+      </c>
     </row>
     <row r="598">
       <c r="H598" s="5" t="n">
@@ -28855,6 +30661,9 @@
       <c r="AA598" t="n">
         <v>0.5511517857142857</v>
       </c>
+      <c r="AB598" t="n">
+        <v>0.4607326923076923</v>
+      </c>
     </row>
     <row r="599">
       <c r="H599" s="5" t="n">
@@ -28869,6 +30678,9 @@
       <c r="AA599" t="n">
         <v>0.5589740740740742</v>
       </c>
+      <c r="AB599" t="n">
+        <v>0.4825872340425533</v>
+      </c>
     </row>
     <row r="600">
       <c r="H600" s="5" t="n">
@@ -28883,6 +30695,9 @@
       <c r="AA600" t="n">
         <v>0.5019096153846154</v>
       </c>
+      <c r="AB600" t="n">
+        <v>0.4339749999999999</v>
+      </c>
     </row>
     <row r="601">
       <c r="H601" s="5" t="n">
@@ -28897,6 +30712,9 @@
       <c r="AA601" t="n">
         <v>0.5391431818181819</v>
       </c>
+      <c r="AB601" t="n">
+        <v>0.5613379310344828</v>
+      </c>
     </row>
     <row r="602">
       <c r="H602" s="5" t="n">
@@ -28911,6 +30729,9 @@
       <c r="AA602" t="n">
         <v>0.5390069767441861</v>
       </c>
+      <c r="AB602" t="n">
+        <v>0.4496911111111111</v>
+      </c>
     </row>
     <row r="603">
       <c r="H603" s="5" t="n">
@@ -28925,6 +30746,9 @@
       <c r="AA603" t="n">
         <v>0.5873901639344262</v>
       </c>
+      <c r="AB603" t="n">
+        <v>0.5440725490196079</v>
+      </c>
     </row>
     <row r="604">
       <c r="H604" s="5" t="n">
@@ -28939,6 +30763,9 @@
       <c r="AA604" t="n">
         <v>0.5095324999999999</v>
       </c>
+      <c r="AB604" t="n">
+        <v>0.6281655172413793</v>
+      </c>
     </row>
     <row r="605">
       <c r="H605" s="5" t="n">
@@ -28953,6 +30780,9 @@
       <c r="AA605" t="n">
         <v>0.6173886363636364</v>
       </c>
+      <c r="AB605" t="n">
+        <v>0.4950145833333333</v>
+      </c>
     </row>
     <row r="606">
       <c r="H606" s="5" t="n">
@@ -28967,6 +30797,9 @@
       <c r="AA606" t="n">
         <v>0.5851760869565218</v>
       </c>
+      <c r="AB606" t="n">
+        <v>0.4525132075471699</v>
+      </c>
     </row>
     <row r="607">
       <c r="H607" s="5" t="n">
@@ -28981,6 +30814,9 @@
       <c r="AA607" t="n">
         <v>0.4493627450980393</v>
       </c>
+      <c r="AB607" t="n">
+        <v>0.5117094339622641</v>
+      </c>
     </row>
     <row r="608">
       <c r="H608" s="5" t="n">
@@ -28995,6 +30831,9 @@
       <c r="AA608" t="n">
         <v>0.5960224489795919</v>
       </c>
+      <c r="AB608" t="n">
+        <v>0.6114983050847457</v>
+      </c>
     </row>
     <row r="609">
       <c r="H609" s="5" t="n">
@@ -29009,6 +30848,9 @@
       <c r="AA609" t="n">
         <v>0.547230303030303</v>
       </c>
+      <c r="AB609" t="n">
+        <v>0.4429476190476191</v>
+      </c>
     </row>
     <row r="610">
       <c r="H610" s="5" t="n">
@@ -29023,6 +30865,9 @@
       <c r="AA610" t="n">
         <v>0.6911536585365854</v>
       </c>
+      <c r="AB610" t="n">
+        <v>0.5720607843137255</v>
+      </c>
     </row>
     <row r="611">
       <c r="H611" s="5" t="n">
@@ -29037,6 +30882,9 @@
       <c r="AA611" t="n">
         <v>0.6239090909090909</v>
       </c>
+      <c r="AB611" t="n">
+        <v>0.5301365079365079</v>
+      </c>
     </row>
     <row r="612">
       <c r="H612" s="5" t="n">
@@ -29051,6 +30899,9 @@
       <c r="AA612" t="n">
         <v>0.7069095238095239</v>
       </c>
+      <c r="AB612" t="n">
+        <v>0.6320750000000001</v>
+      </c>
     </row>
     <row r="613">
       <c r="H613" s="5" t="n">
@@ -29065,6 +30916,9 @@
       <c r="AA613" t="n">
         <v>0.4788657894736842</v>
       </c>
+      <c r="AB613" t="n">
+        <v>0.5200589285714287</v>
+      </c>
     </row>
     <row r="614">
       <c r="H614" s="5" t="n">
@@ -29079,6 +30933,9 @@
       <c r="AA614" t="n">
         <v>0.5634488888888888</v>
       </c>
+      <c r="AB614" t="n">
+        <v>0.5528916666666667</v>
+      </c>
     </row>
     <row r="615">
       <c r="H615" s="5" t="n">
@@ -29093,6 +30950,9 @@
       <c r="AA615" t="n">
         <v>0.440453488372093</v>
       </c>
+      <c r="AB615" t="n">
+        <v>0.447402</v>
+      </c>
     </row>
     <row r="616">
       <c r="H616" s="5" t="n">
@@ -29107,6 +30967,9 @@
       <c r="AA616" t="n">
         <v>0.5414022727272728</v>
       </c>
+      <c r="AB616" t="n">
+        <v>0.5260574468085106</v>
+      </c>
     </row>
     <row r="617">
       <c r="H617" s="5" t="n">
@@ -29121,6 +30984,9 @@
       <c r="AA617" t="n">
         <v>0.5687756097560975</v>
       </c>
+      <c r="AB617" t="n">
+        <v>0.446788</v>
+      </c>
     </row>
     <row r="618">
       <c r="H618" s="5" t="n">
@@ -29135,6 +31001,9 @@
       <c r="AA618" t="n">
         <v>0.7262470588235295</v>
       </c>
+      <c r="AB618" t="n">
+        <v>0.4792728813559322</v>
+      </c>
     </row>
     <row r="619">
       <c r="H619" s="5" t="n">
@@ -29148,6 +31017,9 @@
       </c>
       <c r="AA619" t="n">
         <v>0.556756</v>
+      </c>
+      <c r="AB619" t="n">
+        <v>0.6505066666666668</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1012,6 +1012,9 @@
       <c r="AB9" t="n">
         <v>0.4813499999999999</v>
       </c>
+      <c r="AC9" t="n">
+        <v>0.4027142857142857</v>
+      </c>
     </row>
     <row r="10" ht="16" customHeight="1" s="8">
       <c r="A10" s="5" t="n">
@@ -1083,6 +1086,9 @@
       <c r="AB10" t="n">
         <v>0.6071333333333333</v>
       </c>
+      <c r="AC10" t="n">
+        <v>0.5231399999999999</v>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1" s="8">
       <c r="A11" s="5" t="n">
@@ -1154,6 +1160,9 @@
       <c r="AB11" t="n">
         <v>0.5877588235294118</v>
       </c>
+      <c r="AC11" t="n">
+        <v>0.3894666666666666</v>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="8">
       <c r="A12" s="5" t="n">
@@ -1225,6 +1234,9 @@
       <c r="AB12" t="n">
         <v>0.543996</v>
       </c>
+      <c r="AC12" t="n">
+        <v>0.5102</v>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1" s="8">
       <c r="A13" s="5" t="n">
@@ -1296,6 +1308,9 @@
       <c r="AB13" t="n">
         <v>0.63365</v>
       </c>
+      <c r="AC13" t="n">
+        <v>0.6617766666666667</v>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="8">
       <c r="A14" s="5" t="n">
@@ -1367,6 +1382,9 @@
       <c r="AB14" t="n">
         <v>0.7116666666666667</v>
       </c>
+      <c r="AC14" t="n">
+        <v>0.5611692307692308</v>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="8">
       <c r="A15" s="5" t="n">
@@ -1429,6 +1447,9 @@
       <c r="AB15" t="n">
         <v>0.7897307692307692</v>
       </c>
+      <c r="AC15" t="n">
+        <v>0.6324736842105263</v>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="8">
       <c r="A16" s="5" t="n">
@@ -1491,6 +1512,9 @@
       <c r="AB16" t="n">
         <v>0.6891272727272729</v>
       </c>
+      <c r="AC16" t="n">
+        <v>0.5537875</v>
+      </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="8">
       <c r="A17" s="5" t="n">
@@ -1553,6 +1577,9 @@
       <c r="AB17" t="n">
         <v>0.711895652173913</v>
       </c>
+      <c r="AC17" t="n">
+        <v>0.7739652173913044</v>
+      </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="8">
       <c r="A18" s="5" t="n">
@@ -1615,6 +1642,9 @@
       <c r="AB18" t="n">
         <v>0.7979647058823529</v>
       </c>
+      <c r="AC18" t="n">
+        <v>0.6632000000000001</v>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="8">
       <c r="A19" s="5" t="n">
@@ -1677,6 +1707,9 @@
       <c r="AB19" t="n">
         <v>0.7774757575757576</v>
       </c>
+      <c r="AC19" t="n">
+        <v>0.4780041666666667</v>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="8">
       <c r="A20" s="5" t="n">
@@ -1739,6 +1772,9 @@
       <c r="AB20" t="n">
         <v>0.7733652173913044</v>
       </c>
+      <c r="AC20" t="n">
+        <v>0.7402326530612244</v>
+      </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="8">
       <c r="A21" s="5" t="n">
@@ -1801,6 +1837,9 @@
       <c r="AB21" t="n">
         <v>0.8179666666666667</v>
       </c>
+      <c r="AC21" t="n">
+        <v>0.7265599999999999</v>
+      </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="8">
       <c r="A22" s="5" t="n">
@@ -1863,6 +1902,9 @@
       <c r="AB22" t="n">
         <v>0.8153793103448276</v>
       </c>
+      <c r="AC22" t="n">
+        <v>0.6480771428571429</v>
+      </c>
     </row>
     <row r="23" ht="16" customHeight="1" s="8">
       <c r="A23" s="5" t="n">
@@ -1925,6 +1967,9 @@
       <c r="AB23" t="n">
         <v>0.8028736842105263</v>
       </c>
+      <c r="AC23" t="n">
+        <v>0.6816655172413794</v>
+      </c>
     </row>
     <row r="24" ht="16" customHeight="1" s="8">
       <c r="A24" s="5" t="n">
@@ -1987,6 +2032,9 @@
       <c r="AB24" t="n">
         <v>0.7993926829268293</v>
       </c>
+      <c r="AC24" t="n">
+        <v>0.7320621621621622</v>
+      </c>
     </row>
     <row r="25" ht="16" customHeight="1" s="8">
       <c r="A25" s="5" t="n">
@@ -2049,6 +2097,9 @@
       <c r="AB25" t="n">
         <v>0.8418794117647059</v>
       </c>
+      <c r="AC25" t="n">
+        <v>0.6499238095238096</v>
+      </c>
     </row>
     <row r="26" ht="16" customHeight="1" s="8">
       <c r="A26" s="5" t="n">
@@ -2111,6 +2162,9 @@
       <c r="AB26" t="n">
         <v>0.8243666666666667</v>
       </c>
+      <c r="AC26" t="n">
+        <v>0.7309219512195121</v>
+      </c>
     </row>
     <row r="27" ht="16" customHeight="1" s="8">
       <c r="A27" s="5" t="n">
@@ -2173,6 +2227,9 @@
       <c r="AB27" t="n">
         <v>0.8491581395348838</v>
       </c>
+      <c r="AC27" t="n">
+        <v>0.6617269230769232</v>
+      </c>
     </row>
     <row r="28" ht="16" customHeight="1" s="8">
       <c r="A28" s="5" t="n">
@@ -2235,6 +2292,9 @@
       <c r="AB28" t="n">
         <v>0.8293333333333334</v>
       </c>
+      <c r="AC28" t="n">
+        <v>0.7658580645161291</v>
+      </c>
     </row>
     <row r="29" ht="16" customHeight="1" s="8">
       <c r="A29" s="5" t="n">
@@ -2297,6 +2357,9 @@
       <c r="AB29" t="n">
         <v>0.8446454545454546</v>
       </c>
+      <c r="AC29" t="n">
+        <v>0.7673709677419355</v>
+      </c>
     </row>
     <row r="30" ht="16" customHeight="1" s="8">
       <c r="A30" s="5" t="n">
@@ -2359,6 +2422,9 @@
       <c r="AB30" t="n">
         <v>0.8001500000000001</v>
       </c>
+      <c r="AC30" t="n">
+        <v>0.7293500000000001</v>
+      </c>
     </row>
     <row r="31" ht="16" customHeight="1" s="8">
       <c r="A31" s="5" t="n">
@@ -2421,6 +2487,9 @@
       <c r="AB31" t="n">
         <v>0.851904</v>
       </c>
+      <c r="AC31" t="n">
+        <v>0.8548625</v>
+      </c>
     </row>
     <row r="32" ht="16" customHeight="1" s="8">
       <c r="A32" s="5" t="n">
@@ -2483,6 +2552,9 @@
       <c r="AB32" t="n">
         <v>0.8850120000000001</v>
       </c>
+      <c r="AC32" t="n">
+        <v>0.7101125</v>
+      </c>
     </row>
     <row r="33" ht="16" customHeight="1" s="8">
       <c r="A33" s="5" t="n">
@@ -2545,6 +2617,9 @@
       <c r="AB33" t="n">
         <v>0.8240428571428572</v>
       </c>
+      <c r="AC33" t="n">
+        <v>0.8366148148148149</v>
+      </c>
     </row>
     <row r="34" ht="16" customHeight="1" s="8">
       <c r="A34" s="5" t="n">
@@ -2607,6 +2682,9 @@
       <c r="AB34" t="n">
         <v>0.8328300000000001</v>
       </c>
+      <c r="AC34" t="n">
+        <v>0.8187000000000001</v>
+      </c>
     </row>
     <row r="35" ht="16" customHeight="1" s="8">
       <c r="A35" s="5" t="n">
@@ -2669,6 +2747,9 @@
       <c r="AB35" t="n">
         <v>0.7856739130434782</v>
       </c>
+      <c r="AC35" t="n">
+        <v>0.76802</v>
+      </c>
     </row>
     <row r="36" ht="16" customHeight="1" s="8">
       <c r="A36" s="5" t="n">
@@ -2731,6 +2812,9 @@
       <c r="AB36" t="n">
         <v>0.8822038461538462</v>
       </c>
+      <c r="AC36" t="n">
+        <v>0.7461032258064515</v>
+      </c>
     </row>
     <row r="37" ht="16" customHeight="1" s="8">
       <c r="A37" s="5" t="n">
@@ -2793,6 +2877,9 @@
       <c r="AB37" t="n">
         <v>0.879169696969697</v>
       </c>
+      <c r="AC37" t="n">
+        <v>0.6209794117647058</v>
+      </c>
     </row>
     <row r="38" ht="16" customHeight="1" s="8">
       <c r="A38" s="5" t="n">
@@ -2855,6 +2942,9 @@
       <c r="AB38" t="n">
         <v>0.868892857142857</v>
       </c>
+      <c r="AC38" t="n">
+        <v>0.6220857142857142</v>
+      </c>
     </row>
     <row r="39" ht="16" customHeight="1" s="8">
       <c r="A39" s="5" t="n">
@@ -2917,6 +3007,9 @@
       <c r="AB39" t="n">
         <v>0.8924771428571429</v>
       </c>
+      <c r="AC39" t="n">
+        <v>0.658895</v>
+      </c>
     </row>
     <row r="40" ht="16" customHeight="1" s="8">
       <c r="A40" s="5" t="n">
@@ -2979,6 +3072,9 @@
       <c r="AB40" t="n">
         <v>0.7941434782608695</v>
       </c>
+      <c r="AC40" t="n">
+        <v>0.6221153846153846</v>
+      </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="8">
       <c r="A41" s="5" t="n">
@@ -3041,6 +3137,9 @@
       <c r="AB41" t="n">
         <v>0.8387541666666668</v>
       </c>
+      <c r="AC41" t="n">
+        <v>0.5730499999999999</v>
+      </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="8">
       <c r="A42" s="5" t="n">
@@ -3103,6 +3202,9 @@
       <c r="AB42" t="n">
         <v>0.8306114285714286</v>
       </c>
+      <c r="AC42" t="n">
+        <v>0.7893312499999999</v>
+      </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="8">
       <c r="A43" s="5" t="n">
@@ -3165,6 +3267,9 @@
       <c r="AB43" t="n">
         <v>0.9300814814814815</v>
       </c>
+      <c r="AC43" t="n">
+        <v>0.6833541666666667</v>
+      </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="8">
       <c r="A44" s="5" t="n">
@@ -3227,6 +3332,9 @@
       <c r="AB44" t="n">
         <v>0.8689578947368422</v>
       </c>
+      <c r="AC44" t="n">
+        <v>0.89333125</v>
+      </c>
     </row>
     <row r="45" ht="16" customHeight="1" s="8">
       <c r="A45" s="5" t="n">
@@ -3289,6 +3397,9 @@
       <c r="AB45" t="n">
         <v>0.9127233333333333</v>
       </c>
+      <c r="AC45" t="n">
+        <v>0.6783629629629631</v>
+      </c>
     </row>
     <row r="46" ht="16" customHeight="1" s="8">
       <c r="A46" s="5" t="n">
@@ -3351,6 +3462,9 @@
       <c r="AB46" t="n">
         <v>0.7973818181818182</v>
       </c>
+      <c r="AC46" t="n">
+        <v>0.7039423076923078</v>
+      </c>
     </row>
     <row r="47" ht="16" customHeight="1" s="8">
       <c r="A47" s="5" t="n">
@@ -3413,6 +3527,9 @@
       <c r="AB47" t="n">
         <v>0.9488800000000002</v>
       </c>
+      <c r="AC47" t="n">
+        <v>0.7107214285714285</v>
+      </c>
     </row>
     <row r="48" ht="16" customHeight="1" s="8">
       <c r="A48" s="5" t="n">
@@ -3475,6 +3592,9 @@
       <c r="AB48" t="n">
         <v>0.7659250000000001</v>
       </c>
+      <c r="AC48" t="n">
+        <v>0.6087068965517241</v>
+      </c>
     </row>
     <row r="49" ht="16" customHeight="1" s="8">
       <c r="A49" s="5" t="n">
@@ -3537,6 +3657,9 @@
       <c r="AB49" t="n">
         <v>0.8882869565217391</v>
       </c>
+      <c r="AC49" t="n">
+        <v>0.9002777777777778</v>
+      </c>
     </row>
     <row r="50" ht="16" customHeight="1" s="8">
       <c r="A50" s="5" t="n">
@@ -3599,6 +3722,9 @@
       <c r="AB50" t="n">
         <v>0.8594724137931035</v>
       </c>
+      <c r="AC50" t="n">
+        <v>0.7506964285714286</v>
+      </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="8">
       <c r="A51" s="5" t="n">
@@ -3661,6 +3787,9 @@
       <c r="AB51" t="n">
         <v>0.7463260869565218</v>
       </c>
+      <c r="AC51" t="n">
+        <v>0.6922176470588234</v>
+      </c>
     </row>
     <row r="52" ht="16" customHeight="1" s="8">
       <c r="A52" s="5" t="n">
@@ -3723,6 +3852,9 @@
       <c r="AB52" t="n">
         <v>0.8244222222222223</v>
       </c>
+      <c r="AC52" t="n">
+        <v>0.8365461538461538</v>
+      </c>
     </row>
     <row r="53" ht="16" customHeight="1" s="8">
       <c r="A53" s="5" t="n">
@@ -3785,6 +3917,9 @@
       <c r="AB53" t="n">
         <v>0.8351823529411765</v>
       </c>
+      <c r="AC53" t="n">
+        <v>0.7209521739130433</v>
+      </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="8">
       <c r="A54" s="5" t="n">
@@ -3847,6 +3982,9 @@
       <c r="AB54" t="n">
         <v>0.8721192307692309</v>
       </c>
+      <c r="AC54" t="n">
+        <v>0.7889882352941177</v>
+      </c>
     </row>
     <row r="55" ht="16" customHeight="1" s="8">
       <c r="A55" s="5" t="n">
@@ -3909,6 +4047,9 @@
       <c r="AB55" t="n">
         <v>0.8632266666666667</v>
       </c>
+      <c r="AC55" t="n">
+        <v>0.74809</v>
+      </c>
     </row>
     <row r="56" ht="16" customHeight="1" s="8">
       <c r="A56" s="5" t="n">
@@ -3971,6 +4112,9 @@
       <c r="AB56" t="n">
         <v>0.8737571428571429</v>
       </c>
+      <c r="AC56" t="n">
+        <v>0.63329375</v>
+      </c>
     </row>
     <row r="57" ht="16" customHeight="1" s="8">
       <c r="A57" s="5" t="n">
@@ -4033,6 +4177,9 @@
       <c r="AB57" t="n">
         <v>0.8767655172413792</v>
       </c>
+      <c r="AC57" t="n">
+        <v>0.7612760000000001</v>
+      </c>
     </row>
     <row r="58" ht="16" customHeight="1" s="8">
       <c r="A58" s="5" t="n">
@@ -4095,6 +4242,9 @@
       <c r="AB58" t="n">
         <v>0.8986703703703705</v>
       </c>
+      <c r="AC58" t="n">
+        <v>0.786742105263158</v>
+      </c>
     </row>
     <row r="59" ht="16" customHeight="1" s="8">
       <c r="A59" s="5" t="n">
@@ -4157,6 +4307,9 @@
       <c r="AB59" t="n">
         <v>0.8903555555555555</v>
       </c>
+      <c r="AC59" t="n">
+        <v>0.7845176470588235</v>
+      </c>
     </row>
     <row r="60" ht="16" customHeight="1" s="8">
       <c r="A60" s="5" t="n">
@@ -4219,6 +4372,9 @@
       <c r="AB60" t="n">
         <v>0.8382350000000001</v>
       </c>
+      <c r="AC60" t="n">
+        <v>0.6564833333333334</v>
+      </c>
     </row>
     <row r="61" ht="16" customHeight="1" s="8">
       <c r="A61" s="5" t="n">
@@ -4281,6 +4437,9 @@
       <c r="AB61" t="n">
         <v>0.8725458333333335</v>
       </c>
+      <c r="AC61" t="n">
+        <v>0.9235400000000001</v>
+      </c>
     </row>
     <row r="62" ht="16" customHeight="1" s="8">
       <c r="A62" s="5" t="n">
@@ -4343,6 +4502,9 @@
       <c r="AB62" t="n">
         <v>0.8268099999999999</v>
       </c>
+      <c r="AC62" t="n">
+        <v>0.8786249999999999</v>
+      </c>
     </row>
     <row r="63" ht="16" customHeight="1" s="8">
       <c r="A63" s="5" t="n">
@@ -4405,6 +4567,9 @@
       <c r="AB63" t="n">
         <v>0.8560375</v>
       </c>
+      <c r="AC63" t="n">
+        <v>0.7945714285714286</v>
+      </c>
     </row>
     <row r="64" ht="16" customHeight="1" s="8">
       <c r="A64" s="5" t="n">
@@ -4467,6 +4632,9 @@
       <c r="AB64" t="n">
         <v>0.8609512195121951</v>
       </c>
+      <c r="AC64" t="n">
+        <v>0.87956</v>
+      </c>
     </row>
     <row r="65" ht="16" customHeight="1" s="8">
       <c r="A65" s="5" t="n">
@@ -4529,6 +4697,9 @@
       <c r="AB65" t="n">
         <v>0.9158225806451613</v>
       </c>
+      <c r="AC65" t="n">
+        <v>0.6629500000000002</v>
+      </c>
     </row>
     <row r="66" ht="16" customHeight="1" s="8">
       <c r="A66" s="5" t="n">
@@ -4591,6 +4762,9 @@
       <c r="AB66" t="n">
         <v>0.7863666666666667</v>
       </c>
+      <c r="AC66" t="n">
+        <v>0.6877736842105263</v>
+      </c>
     </row>
     <row r="67" ht="16" customHeight="1" s="8">
       <c r="A67" s="5" t="n">
@@ -4653,6 +4827,9 @@
       <c r="AB67" t="n">
         <v>0.8075142857142857</v>
       </c>
+      <c r="AC67" t="n">
+        <v>0.8301263157894736</v>
+      </c>
     </row>
     <row r="68" ht="16" customHeight="1" s="8">
       <c r="A68" s="5" t="n">
@@ -4715,6 +4892,9 @@
       <c r="AB68" t="n">
         <v>0.8336285714285714</v>
       </c>
+      <c r="AC68" t="n">
+        <v>0.7745333333333333</v>
+      </c>
     </row>
     <row r="69" ht="16" customHeight="1" s="8">
       <c r="A69" s="5" t="n">
@@ -4777,6 +4957,9 @@
       <c r="AB69" t="n">
         <v>0.892</v>
       </c>
+      <c r="AC69" t="n">
+        <v>0.6865861111111111</v>
+      </c>
     </row>
     <row r="70" ht="16" customHeight="1" s="8">
       <c r="A70" s="5" t="n">
@@ -4839,6 +5022,9 @@
       <c r="AB70" t="n">
         <v>0.8063292682926829</v>
       </c>
+      <c r="AC70" t="n">
+        <v>0.7472285714285712</v>
+      </c>
     </row>
     <row r="71" ht="16" customHeight="1" s="8">
       <c r="A71" s="5" t="n">
@@ -4901,6 +5087,9 @@
       <c r="AB71" t="n">
         <v>0.9095689655172415</v>
       </c>
+      <c r="AC71" t="n">
+        <v>0.7146173913043478</v>
+      </c>
     </row>
     <row r="72" ht="16" customHeight="1" s="8">
       <c r="A72" s="5" t="n">
@@ -4963,6 +5152,9 @@
       <c r="AB72" t="n">
         <v>0.8695194444444444</v>
       </c>
+      <c r="AC72" t="n">
+        <v>0.6594312499999999</v>
+      </c>
     </row>
     <row r="73" ht="16" customHeight="1" s="8">
       <c r="A73" s="5" t="n">
@@ -5025,6 +5217,9 @@
       <c r="AB73" t="n">
         <v>0.8746653846153845</v>
       </c>
+      <c r="AC73" t="n">
+        <v>0.8336705882352941</v>
+      </c>
     </row>
     <row r="74" ht="16" customHeight="1" s="8">
       <c r="A74" s="5" t="n">
@@ -5087,6 +5282,9 @@
       <c r="AB74" t="n">
         <v>0.8889000000000001</v>
       </c>
+      <c r="AC74" t="n">
+        <v>0.909825</v>
+      </c>
     </row>
     <row r="75" ht="16" customHeight="1" s="8">
       <c r="A75" s="5" t="n">
@@ -5149,6 +5347,9 @@
       <c r="AB75" t="n">
         <v>0.6309923076923076</v>
       </c>
+      <c r="AC75" t="n">
+        <v>0.7867666666666667</v>
+      </c>
     </row>
     <row r="76" ht="16" customHeight="1" s="8">
       <c r="A76" s="5" t="n">
@@ -5211,6 +5412,9 @@
       <c r="AB76" t="n">
         <v>0.8597695652173912</v>
       </c>
+      <c r="AC76" t="n">
+        <v>0.79</v>
+      </c>
     </row>
     <row r="77" ht="16" customHeight="1" s="8">
       <c r="A77" s="5" t="n">
@@ -5273,6 +5477,9 @@
       <c r="AB77" t="n">
         <v>0.8647280000000001</v>
       </c>
+      <c r="AC77" t="n">
+        <v>0.7235066666666667</v>
+      </c>
     </row>
     <row r="78" ht="16" customHeight="1" s="8">
       <c r="A78" s="5" t="n">
@@ -5335,6 +5542,9 @@
       <c r="AB78" t="n">
         <v>0.8679470588235293</v>
       </c>
+      <c r="AC78" t="n">
+        <v>0.71315</v>
+      </c>
     </row>
     <row r="79" ht="16" customHeight="1" s="8">
       <c r="A79" s="5" t="n">
@@ -5397,6 +5607,9 @@
       <c r="AB79" t="n">
         <v>0.8089615384615385</v>
       </c>
+      <c r="AC79" t="n">
+        <v>0.7141636363636364</v>
+      </c>
     </row>
     <row r="80" ht="16" customHeight="1" s="8">
       <c r="A80" s="5" t="n">
@@ -5459,6 +5672,9 @@
       <c r="AB80" t="n">
         <v>0.7944740740740741</v>
       </c>
+      <c r="AC80" t="n">
+        <v>0.8130999999999998</v>
+      </c>
     </row>
     <row r="81" ht="16" customHeight="1" s="8">
       <c r="A81" s="5" t="n">
@@ -5521,6 +5737,9 @@
       <c r="AB81" t="n">
         <v>0.8063806451612904</v>
       </c>
+      <c r="AC81" t="n">
+        <v>0.8183360000000001</v>
+      </c>
     </row>
     <row r="82" ht="16" customHeight="1" s="8">
       <c r="A82" s="5" t="n">
@@ -5583,6 +5802,9 @@
       <c r="AB82" t="n">
         <v>0.8380391304347827</v>
       </c>
+      <c r="AC82" t="n">
+        <v>0.7288558823529412</v>
+      </c>
     </row>
     <row r="83" ht="16" customHeight="1" s="8">
       <c r="A83" s="5" t="n">
@@ -5645,6 +5867,9 @@
       <c r="AB83" t="n">
         <v>0.754224</v>
       </c>
+      <c r="AC83" t="n">
+        <v>0.7396916666666667</v>
+      </c>
     </row>
     <row r="84" ht="16" customHeight="1" s="8">
       <c r="A84" s="5" t="n">
@@ -5707,6 +5932,9 @@
       <c r="AB84" t="n">
         <v>0.7973821428571428</v>
       </c>
+      <c r="AC84" t="n">
+        <v>0.7142178571428571</v>
+      </c>
     </row>
     <row r="85" ht="16" customHeight="1" s="8">
       <c r="A85" s="5" t="n">
@@ -5769,6 +5997,9 @@
       <c r="AB85" t="n">
         <v>0.8075692307692308</v>
       </c>
+      <c r="AC85" t="n">
+        <v>0.7182904761904763</v>
+      </c>
     </row>
     <row r="86" ht="16" customHeight="1" s="8">
       <c r="A86" s="5" t="n">
@@ -5831,6 +6062,9 @@
       <c r="AB86" t="n">
         <v>0.9157846153846154</v>
       </c>
+      <c r="AC86" t="n">
+        <v>0.650344</v>
+      </c>
     </row>
     <row r="87" ht="16" customHeight="1" s="8">
       <c r="A87" s="5" t="n">
@@ -5893,6 +6127,9 @@
       <c r="AB87" t="n">
         <v>0.8368129032258064</v>
       </c>
+      <c r="AC87" t="n">
+        <v>0.7161999999999999</v>
+      </c>
     </row>
     <row r="88" ht="16" customHeight="1" s="8">
       <c r="A88" s="5" t="n">
@@ -5955,6 +6192,9 @@
       <c r="AB88" t="n">
         <v>0.8699851851851853</v>
       </c>
+      <c r="AC88" t="n">
+        <v>0.8810846153846155</v>
+      </c>
     </row>
     <row r="89" ht="16" customHeight="1" s="8">
       <c r="A89" s="5" t="n">
@@ -6017,6 +6257,9 @@
       <c r="AB89" t="n">
         <v>0.9266358974358975</v>
       </c>
+      <c r="AC89" t="n">
+        <v>0.8272608695652174</v>
+      </c>
     </row>
     <row r="90" ht="16" customHeight="1" s="8">
       <c r="A90" s="5" t="n">
@@ -6079,6 +6322,9 @@
       <c r="AB90" t="n">
         <v>0.8890166666666667</v>
       </c>
+      <c r="AC90" t="n">
+        <v>0.7487535714285712</v>
+      </c>
     </row>
     <row r="91" ht="16" customHeight="1" s="8">
       <c r="A91" s="5" t="n">
@@ -6141,6 +6387,9 @@
       <c r="AB91" t="n">
         <v>0.8737764705882354</v>
       </c>
+      <c r="AC91" t="n">
+        <v>0.728514705882353</v>
+      </c>
     </row>
     <row r="92" ht="16" customHeight="1" s="8">
       <c r="A92" s="5" t="n">
@@ -6203,6 +6452,9 @@
       <c r="AB92" t="n">
         <v>0.7849954545454545</v>
       </c>
+      <c r="AC92" t="n">
+        <v>0.7942466666666667</v>
+      </c>
     </row>
     <row r="93" ht="16" customHeight="1" s="8">
       <c r="A93" s="5" t="n">
@@ -6265,6 +6517,9 @@
       <c r="AB93" t="n">
         <v>0.8794647058823529</v>
       </c>
+      <c r="AC93" t="n">
+        <v>0.8554476190476189</v>
+      </c>
     </row>
     <row r="94" ht="16" customHeight="1" s="8">
       <c r="A94" s="5" t="n">
@@ -6327,6 +6582,9 @@
       <c r="AB94" t="n">
         <v>0.8630000000000001</v>
       </c>
+      <c r="AC94" t="n">
+        <v>0.8359722222222222</v>
+      </c>
     </row>
     <row r="95" ht="16" customHeight="1" s="8">
       <c r="A95" s="5" t="n">
@@ -6389,6 +6647,9 @@
       <c r="AB95" t="n">
         <v>0.8597</v>
       </c>
+      <c r="AC95" t="n">
+        <v>0.6074724137931033</v>
+      </c>
     </row>
     <row r="96" ht="16" customHeight="1" s="8">
       <c r="A96" s="5" t="n">
@@ -6451,6 +6712,9 @@
       <c r="AB96" t="n">
         <v>0.9143307692307693</v>
       </c>
+      <c r="AC96" t="n">
+        <v>0.6664967741935484</v>
+      </c>
     </row>
     <row r="97" ht="16" customHeight="1" s="8">
       <c r="A97" s="5" t="n">
@@ -6513,6 +6777,9 @@
       <c r="AB97" t="n">
         <v>0.78554</v>
       </c>
+      <c r="AC97" t="n">
+        <v>0.7465333333333333</v>
+      </c>
     </row>
     <row r="98" ht="16" customHeight="1" s="8">
       <c r="A98" s="5" t="n">
@@ -6575,6 +6842,9 @@
       <c r="AB98" t="n">
         <v>0.8819684210526316</v>
       </c>
+      <c r="AC98" t="n">
+        <v>0.7643193548387096</v>
+      </c>
     </row>
     <row r="99" ht="16" customHeight="1" s="8">
       <c r="A99" s="5" t="n">
@@ -6637,6 +6907,9 @@
       <c r="AB99" t="n">
         <v>0.8868533333333334</v>
       </c>
+      <c r="AC99" t="n">
+        <v>0.7302419354838708</v>
+      </c>
     </row>
     <row r="100" ht="16" customHeight="1" s="8">
       <c r="A100" s="5" t="n">
@@ -6699,6 +6972,9 @@
       <c r="AB100" t="n">
         <v>0.8900187500000001</v>
       </c>
+      <c r="AC100" t="n">
+        <v>0.785048275862069</v>
+      </c>
     </row>
     <row r="101" ht="16" customHeight="1" s="8">
       <c r="A101" s="5" t="n">
@@ -6761,6 +7037,9 @@
       <c r="AB101" t="n">
         <v>0.8328264705882353</v>
       </c>
+      <c r="AC101" t="n">
+        <v>0.8470952380952381</v>
+      </c>
     </row>
     <row r="102" ht="16" customHeight="1" s="8">
       <c r="A102" s="5" t="n">
@@ -6823,6 +7102,9 @@
       <c r="AB102" t="n">
         <v>0.7871741935483871</v>
       </c>
+      <c r="AC102" t="n">
+        <v>0.8757260869565218</v>
+      </c>
     </row>
     <row r="103" ht="16" customHeight="1" s="8">
       <c r="A103" s="5" t="n">
@@ -6885,6 +7167,9 @@
       <c r="AB103" t="n">
         <v>0.874335</v>
       </c>
+      <c r="AC103" t="n">
+        <v>0.8741666666666668</v>
+      </c>
     </row>
     <row r="104" ht="16" customHeight="1" s="8">
       <c r="A104" s="5" t="n">
@@ -6946,6 +7231,9 @@
       </c>
       <c r="AB104" t="n">
         <v>0.7958472222222224</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0.6315714285714286</v>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1" s="8">
@@ -7338,6 +7626,9 @@
       <c r="AB112" t="n">
         <v>0.875</v>
       </c>
+      <c r="AC112" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="113" ht="16" customHeight="1" s="8">
       <c r="A113" s="5" t="n">
@@ -7409,6 +7700,9 @@
       <c r="AB113" t="n">
         <v>0.875</v>
       </c>
+      <c r="AC113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114" ht="16" customHeight="1" s="8">
       <c r="A114" s="5" t="n">
@@ -7480,6 +7774,9 @@
       <c r="AB114" t="n">
         <v>1</v>
       </c>
+      <c r="AC114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115" ht="16" customHeight="1" s="8">
       <c r="A115" s="5" t="n">
@@ -7551,6 +7848,9 @@
       <c r="AB115" t="n">
         <v>0.7142857142857143</v>
       </c>
+      <c r="AC115" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="116" ht="16" customHeight="1" s="8">
       <c r="A116" s="5" t="n">
@@ -7622,6 +7922,9 @@
       <c r="AB116" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="AC116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117" ht="16" customHeight="1" s="8">
       <c r="A117" s="5" t="n">
@@ -7693,6 +7996,9 @@
       <c r="AB117" t="n">
         <v>1</v>
       </c>
+      <c r="AC117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118" ht="16" customHeight="1" s="8">
       <c r="A118" s="5" t="n">
@@ -7752,6 +8058,9 @@
       <c r="AB118" t="n">
         <v>1</v>
       </c>
+      <c r="AC118" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="119" ht="16" customHeight="1" s="8">
       <c r="A119" s="5" t="n">
@@ -7814,6 +8123,9 @@
       <c r="AB119" t="n">
         <v>1</v>
       </c>
+      <c r="AC119" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="120" ht="16" customHeight="1" s="8">
       <c r="A120" s="5" t="n">
@@ -7876,6 +8188,9 @@
       <c r="AB120" t="n">
         <v>1</v>
       </c>
+      <c r="AC120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121" ht="16" customHeight="1" s="8">
       <c r="A121" s="5" t="n">
@@ -7938,6 +8253,9 @@
       <c r="AB121" t="n">
         <v>1</v>
       </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122" ht="16" customHeight="1" s="8">
       <c r="A122" s="5" t="n">
@@ -8000,6 +8318,9 @@
       <c r="AB122" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123" ht="16" customHeight="1" s="8">
       <c r="A123" s="5" t="n">
@@ -8062,6 +8383,9 @@
       <c r="AB123" t="n">
         <v>1</v>
       </c>
+      <c r="AC123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124" ht="16" customHeight="1" s="8">
       <c r="A124" s="5" t="n">
@@ -8124,6 +8448,9 @@
       <c r="AB124" t="n">
         <v>1</v>
       </c>
+      <c r="AC124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125" ht="16" customHeight="1" s="8">
       <c r="A125" s="5" t="n">
@@ -8186,6 +8513,9 @@
       <c r="AB125" t="n">
         <v>1</v>
       </c>
+      <c r="AC125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126" ht="16" customHeight="1" s="8">
       <c r="A126" s="5" t="n">
@@ -8248,6 +8578,9 @@
       <c r="AB126" t="n">
         <v>1</v>
       </c>
+      <c r="AC126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127" ht="16" customHeight="1" s="8">
       <c r="A127" s="5" t="n">
@@ -8310,6 +8643,9 @@
       <c r="AB127" t="n">
         <v>1</v>
       </c>
+      <c r="AC127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128" ht="16" customHeight="1" s="8">
       <c r="A128" s="5" t="n">
@@ -8372,6 +8708,9 @@
       <c r="AB128" t="n">
         <v>1</v>
       </c>
+      <c r="AC128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129" ht="16" customHeight="1" s="8">
       <c r="A129" s="5" t="n">
@@ -8434,6 +8773,9 @@
       <c r="AB129" t="n">
         <v>1</v>
       </c>
+      <c r="AC129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130" ht="16" customHeight="1" s="8">
       <c r="A130" s="5" t="n">
@@ -8496,6 +8838,9 @@
       <c r="AB130" t="n">
         <v>1</v>
       </c>
+      <c r="AC130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131" ht="16" customHeight="1" s="8">
       <c r="A131" s="5" t="n">
@@ -8558,6 +8903,9 @@
       <c r="AB131" t="n">
         <v>1</v>
       </c>
+      <c r="AC131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132" ht="16" customHeight="1" s="8">
       <c r="A132" s="5" t="n">
@@ -8620,6 +8968,9 @@
       <c r="AB132" t="n">
         <v>1</v>
       </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133" ht="16" customHeight="1" s="8">
       <c r="A133" s="5" t="n">
@@ -8682,6 +9033,9 @@
       <c r="AB133" t="n">
         <v>1</v>
       </c>
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134" ht="16" customHeight="1" s="8">
       <c r="A134" s="5" t="n">
@@ -8744,6 +9098,9 @@
       <c r="AB134" t="n">
         <v>1</v>
       </c>
+      <c r="AC134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135" ht="16" customHeight="1" s="8">
       <c r="A135" s="5" t="n">
@@ -8806,6 +9163,9 @@
       <c r="AB135" t="n">
         <v>1</v>
       </c>
+      <c r="AC135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136" ht="16" customHeight="1" s="8">
       <c r="A136" s="5" t="n">
@@ -8868,6 +9228,9 @@
       <c r="AB136" t="n">
         <v>1</v>
       </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137" ht="16" customHeight="1" s="8">
       <c r="A137" s="5" t="n">
@@ -8930,6 +9293,9 @@
       <c r="AB137" t="n">
         <v>1</v>
       </c>
+      <c r="AC137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138" ht="16" customHeight="1" s="8">
       <c r="A138" s="5" t="n">
@@ -8992,6 +9358,9 @@
       <c r="AB138" t="n">
         <v>1</v>
       </c>
+      <c r="AC138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139" ht="16" customHeight="1" s="8">
       <c r="A139" s="5" t="n">
@@ -9054,6 +9423,9 @@
       <c r="AB139" t="n">
         <v>1</v>
       </c>
+      <c r="AC139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140" ht="16" customHeight="1" s="8">
       <c r="A140" s="5" t="n">
@@ -9113,6 +9485,9 @@
       <c r="AB140" t="n">
         <v>1</v>
       </c>
+      <c r="AC140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141" ht="16" customHeight="1" s="8">
       <c r="A141" s="5" t="n">
@@ -9175,6 +9550,9 @@
       <c r="AB141" t="n">
         <v>1</v>
       </c>
+      <c r="AC141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" ht="16" customHeight="1" s="8">
       <c r="A142" s="5" t="n">
@@ -9237,6 +9615,9 @@
       <c r="AB142" t="n">
         <v>1</v>
       </c>
+      <c r="AC142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143" ht="16" customHeight="1" s="8">
       <c r="A143" s="5" t="n">
@@ -9296,6 +9677,9 @@
       <c r="AB143" t="n">
         <v>1</v>
       </c>
+      <c r="AC143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144" ht="16" customHeight="1" s="8">
       <c r="A144" s="5" t="n">
@@ -9358,6 +9742,9 @@
       <c r="AB144" t="n">
         <v>1</v>
       </c>
+      <c r="AC144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145" ht="16" customHeight="1" s="8">
       <c r="A145" s="5" t="n">
@@ -9420,6 +9807,9 @@
       <c r="AB145" t="n">
         <v>1</v>
       </c>
+      <c r="AC145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146" ht="16" customHeight="1" s="8">
       <c r="A146" s="5" t="n">
@@ -9482,6 +9872,9 @@
       <c r="AB146" t="n">
         <v>1</v>
       </c>
+      <c r="AC146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147" ht="16" customHeight="1" s="8">
       <c r="A147" s="5" t="n">
@@ -9544,6 +9937,9 @@
       <c r="AB147" t="n">
         <v>1</v>
       </c>
+      <c r="AC147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148" ht="16" customHeight="1" s="8">
       <c r="A148" s="5" t="n">
@@ -9606,6 +10002,9 @@
       <c r="AB148" t="n">
         <v>1</v>
       </c>
+      <c r="AC148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149" ht="16" customHeight="1" s="8">
       <c r="A149" s="5" t="n">
@@ -9668,6 +10067,9 @@
       <c r="AB149" t="n">
         <v>1</v>
       </c>
+      <c r="AC149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150" ht="16" customHeight="1" s="8">
       <c r="A150" s="5" t="n">
@@ -9730,6 +10132,9 @@
       <c r="AB150" t="n">
         <v>1</v>
       </c>
+      <c r="AC150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151" ht="16" customHeight="1" s="8">
       <c r="A151" s="5" t="n">
@@ -9792,6 +10197,9 @@
       <c r="AB151" t="n">
         <v>1</v>
       </c>
+      <c r="AC151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152" ht="16" customHeight="1" s="8">
       <c r="A152" s="5" t="n">
@@ -9854,6 +10262,9 @@
       <c r="AB152" t="n">
         <v>1</v>
       </c>
+      <c r="AC152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153" ht="16" customHeight="1" s="8">
       <c r="A153" s="5" t="n">
@@ -9916,6 +10327,9 @@
       <c r="AB153" t="n">
         <v>1</v>
       </c>
+      <c r="AC153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" ht="16" customHeight="1" s="8">
       <c r="A154" s="5" t="n">
@@ -9978,6 +10392,9 @@
       <c r="AB154" t="n">
         <v>1</v>
       </c>
+      <c r="AC154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" ht="16" customHeight="1" s="8">
       <c r="A155" s="5" t="n">
@@ -10040,6 +10457,9 @@
       <c r="AB155" t="n">
         <v>1</v>
       </c>
+      <c r="AC155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156" ht="16" customHeight="1" s="8">
       <c r="A156" s="5" t="n">
@@ -10102,6 +10522,9 @@
       <c r="AB156" t="n">
         <v>1</v>
       </c>
+      <c r="AC156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157" ht="16" customHeight="1" s="8">
       <c r="A157" s="5" t="n">
@@ -10164,6 +10587,9 @@
       <c r="AB157" t="n">
         <v>1</v>
       </c>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158" ht="16" customHeight="1" s="8">
       <c r="A158" s="5" t="n">
@@ -10226,6 +10652,9 @@
       <c r="AB158" t="n">
         <v>1</v>
       </c>
+      <c r="AC158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159" ht="16" customHeight="1" s="8">
       <c r="A159" s="5" t="n">
@@ -10288,6 +10717,9 @@
       <c r="AB159" t="n">
         <v>1</v>
       </c>
+      <c r="AC159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160" ht="16" customHeight="1" s="8">
       <c r="A160" s="5" t="n">
@@ -10350,6 +10782,9 @@
       <c r="AB160" t="n">
         <v>1</v>
       </c>
+      <c r="AC160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161" ht="16" customHeight="1" s="8">
       <c r="A161" s="5" t="n">
@@ -10412,6 +10847,9 @@
       <c r="AB161" t="n">
         <v>1</v>
       </c>
+      <c r="AC161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162" ht="16" customHeight="1" s="8">
       <c r="A162" s="5" t="n">
@@ -10474,6 +10912,9 @@
       <c r="AB162" t="n">
         <v>1</v>
       </c>
+      <c r="AC162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163" ht="16" customHeight="1" s="8">
       <c r="A163" s="5" t="n">
@@ -10536,6 +10977,9 @@
       <c r="AB163" t="n">
         <v>1</v>
       </c>
+      <c r="AC163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164" ht="16" customHeight="1" s="8">
       <c r="A164" s="5" t="n">
@@ -10598,6 +11042,9 @@
       <c r="AB164" t="n">
         <v>1</v>
       </c>
+      <c r="AC164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165" ht="16" customHeight="1" s="8">
       <c r="A165" s="5" t="n">
@@ -10660,6 +11107,9 @@
       <c r="AB165" t="n">
         <v>1</v>
       </c>
+      <c r="AC165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166" ht="16" customHeight="1" s="8">
       <c r="A166" s="5" t="n">
@@ -10722,6 +11172,9 @@
       <c r="AB166" t="n">
         <v>1</v>
       </c>
+      <c r="AC166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167" ht="16" customHeight="1" s="8">
       <c r="A167" s="5" t="n">
@@ -10784,6 +11237,9 @@
       <c r="AB167" t="n">
         <v>1</v>
       </c>
+      <c r="AC167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168" ht="16" customHeight="1" s="8">
       <c r="A168" s="5" t="n">
@@ -10846,6 +11302,9 @@
       <c r="AB168" t="n">
         <v>1</v>
       </c>
+      <c r="AC168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169" ht="16" customHeight="1" s="8">
       <c r="A169" s="5" t="n">
@@ -10908,6 +11367,9 @@
       <c r="AB169" t="n">
         <v>1</v>
       </c>
+      <c r="AC169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170" ht="16" customHeight="1" s="8">
       <c r="A170" s="5" t="n">
@@ -10970,6 +11432,9 @@
       <c r="AB170" t="n">
         <v>1</v>
       </c>
+      <c r="AC170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171" ht="16" customHeight="1" s="8">
       <c r="A171" s="5" t="n">
@@ -11032,6 +11497,9 @@
       <c r="AB171" t="n">
         <v>1</v>
       </c>
+      <c r="AC171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172" ht="16" customHeight="1" s="8">
       <c r="A172" s="5" t="n">
@@ -11094,6 +11562,9 @@
       <c r="AB172" t="n">
         <v>1</v>
       </c>
+      <c r="AC172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173" ht="16" customHeight="1" s="8">
       <c r="A173" s="5" t="n">
@@ -11156,6 +11627,9 @@
       <c r="AB173" t="n">
         <v>1</v>
       </c>
+      <c r="AC173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174" ht="16" customHeight="1" s="8">
       <c r="A174" s="5" t="n">
@@ -11218,6 +11692,9 @@
       <c r="AB174" t="n">
         <v>1</v>
       </c>
+      <c r="AC174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175" ht="16" customHeight="1" s="8">
       <c r="A175" s="5" t="n">
@@ -11280,6 +11757,9 @@
       <c r="AB175" t="n">
         <v>1</v>
       </c>
+      <c r="AC175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176" ht="16" customHeight="1" s="8">
       <c r="A176" s="5" t="n">
@@ -11342,6 +11822,9 @@
       <c r="AB176" t="n">
         <v>1</v>
       </c>
+      <c r="AC176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177" ht="16" customHeight="1" s="8">
       <c r="A177" s="5" t="n">
@@ -11404,6 +11887,9 @@
       <c r="AB177" t="n">
         <v>1</v>
       </c>
+      <c r="AC177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178" ht="16" customHeight="1" s="8">
       <c r="A178" s="5" t="n">
@@ -11466,6 +11952,9 @@
       <c r="AB178" t="n">
         <v>1</v>
       </c>
+      <c r="AC178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179" ht="16" customHeight="1" s="8">
       <c r="A179" s="5" t="n">
@@ -11528,6 +12017,9 @@
       <c r="AB179" t="n">
         <v>1</v>
       </c>
+      <c r="AC179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180" ht="16" customHeight="1" s="8">
       <c r="A180" s="5" t="n">
@@ -11590,6 +12082,9 @@
       <c r="AB180" t="n">
         <v>1</v>
       </c>
+      <c r="AC180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181" ht="16" customHeight="1" s="8">
       <c r="A181" s="5" t="n">
@@ -11649,6 +12144,9 @@
       <c r="AB181" t="n">
         <v>1</v>
       </c>
+      <c r="AC181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182" ht="16" customHeight="1" s="8">
       <c r="A182" s="5" t="n">
@@ -11711,6 +12209,9 @@
       <c r="AB182" t="n">
         <v>1</v>
       </c>
+      <c r="AC182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183" ht="16" customHeight="1" s="8">
       <c r="A183" s="5" t="n">
@@ -11773,6 +12274,9 @@
       <c r="AB183" t="n">
         <v>1</v>
       </c>
+      <c r="AC183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184" ht="16" customHeight="1" s="8">
       <c r="A184" s="5" t="n">
@@ -11835,6 +12339,9 @@
       <c r="AB184" t="n">
         <v>1</v>
       </c>
+      <c r="AC184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185" ht="16" customHeight="1" s="8">
       <c r="A185" s="5" t="n">
@@ -11897,6 +12404,9 @@
       <c r="AB185" t="n">
         <v>1</v>
       </c>
+      <c r="AC185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186" ht="16" customHeight="1" s="8">
       <c r="A186" s="5" t="n">
@@ -11959,6 +12469,9 @@
       <c r="AB186" t="n">
         <v>1</v>
       </c>
+      <c r="AC186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187" ht="16" customHeight="1" s="8">
       <c r="A187" s="5" t="n">
@@ -12021,6 +12534,9 @@
       <c r="AB187" t="n">
         <v>1</v>
       </c>
+      <c r="AC187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188" ht="16" customHeight="1" s="8">
       <c r="A188" s="5" t="n">
@@ -12083,6 +12599,9 @@
       <c r="AB188" t="n">
         <v>1</v>
       </c>
+      <c r="AC188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189" ht="16" customHeight="1" s="8">
       <c r="A189" s="5" t="n">
@@ -12145,6 +12664,9 @@
       <c r="AB189" t="n">
         <v>1</v>
       </c>
+      <c r="AC189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190" ht="16" customHeight="1" s="8">
       <c r="A190" s="5" t="n">
@@ -12207,6 +12729,9 @@
       <c r="AB190" t="n">
         <v>1</v>
       </c>
+      <c r="AC190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191" ht="16" customHeight="1" s="8">
       <c r="A191" s="5" t="n">
@@ -12269,6 +12794,9 @@
       <c r="AB191" t="n">
         <v>1</v>
       </c>
+      <c r="AC191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192" ht="16" customHeight="1" s="8">
       <c r="A192" s="5" t="n">
@@ -12331,6 +12859,9 @@
       <c r="AB192" t="n">
         <v>1</v>
       </c>
+      <c r="AC192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193" ht="16" customHeight="1" s="8">
       <c r="A193" s="5" t="n">
@@ -12393,6 +12924,9 @@
       <c r="AB193" t="n">
         <v>1</v>
       </c>
+      <c r="AC193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194" ht="16" customHeight="1" s="8">
       <c r="A194" s="5" t="n">
@@ -12455,6 +12989,9 @@
       <c r="AB194" t="n">
         <v>1</v>
       </c>
+      <c r="AC194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195" ht="16" customHeight="1" s="8">
       <c r="A195" s="5" t="n">
@@ -12517,6 +13054,9 @@
       <c r="AB195" t="n">
         <v>1</v>
       </c>
+      <c r="AC195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196" ht="16" customHeight="1" s="8">
       <c r="A196" s="5" t="n">
@@ -12579,6 +13119,9 @@
       <c r="AB196" t="n">
         <v>1</v>
       </c>
+      <c r="AC196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197" ht="16" customHeight="1" s="8">
       <c r="A197" s="5" t="n">
@@ -12641,6 +13184,9 @@
       <c r="AB197" t="n">
         <v>1</v>
       </c>
+      <c r="AC197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198" ht="16" customHeight="1" s="8">
       <c r="A198" s="5" t="n">
@@ -12703,6 +13249,9 @@
       <c r="AB198" t="n">
         <v>1</v>
       </c>
+      <c r="AC198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199" ht="16" customHeight="1" s="8">
       <c r="A199" s="5" t="n">
@@ -12765,6 +13314,9 @@
       <c r="AB199" t="n">
         <v>1</v>
       </c>
+      <c r="AC199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200" ht="16" customHeight="1" s="8">
       <c r="A200" s="5" t="n">
@@ -12827,6 +13379,9 @@
       <c r="AB200" t="n">
         <v>1</v>
       </c>
+      <c r="AC200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201" ht="16" customHeight="1" s="8">
       <c r="A201" s="5" t="n">
@@ -12889,6 +13444,9 @@
       <c r="AB201" t="n">
         <v>1</v>
       </c>
+      <c r="AC201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202" ht="16" customHeight="1" s="8">
       <c r="A202" s="5" t="n">
@@ -12951,6 +13509,9 @@
       <c r="AB202" t="n">
         <v>1</v>
       </c>
+      <c r="AC202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203" ht="16" customHeight="1" s="8">
       <c r="A203" s="5" t="n">
@@ -13013,6 +13574,9 @@
       <c r="AB203" t="n">
         <v>1</v>
       </c>
+      <c r="AC203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204" ht="16" customHeight="1" s="8">
       <c r="A204" s="5" t="n">
@@ -13075,6 +13639,9 @@
       <c r="AB204" t="n">
         <v>1</v>
       </c>
+      <c r="AC204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205" ht="16" customHeight="1" s="8">
       <c r="A205" s="5" t="n">
@@ -13137,6 +13704,9 @@
       <c r="AB205" t="n">
         <v>1</v>
       </c>
+      <c r="AC205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206" ht="16" customHeight="1" s="8">
       <c r="A206" s="5" t="n">
@@ -13199,6 +13769,9 @@
       <c r="AB206" t="n">
         <v>1</v>
       </c>
+      <c r="AC206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207" ht="16" customHeight="1" s="8">
       <c r="A207" s="5" t="n">
@@ -13259,6 +13832,9 @@
         <v>1</v>
       </c>
       <c r="AB207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13652,6 +14228,9 @@
       <c r="AB216" t="n">
         <v>0.7094999999999999</v>
       </c>
+      <c r="AC216" t="n">
+        <v>0.9598818181818181</v>
+      </c>
     </row>
     <row r="217" ht="16" customHeight="1" s="8">
       <c r="A217" s="5" t="n">
@@ -13723,6 +14302,9 @@
       <c r="AB217" t="n">
         <v>0.9389222222222222</v>
       </c>
+      <c r="AC217" t="n">
+        <v>0.7393444444444444</v>
+      </c>
     </row>
     <row r="218" ht="16" customHeight="1" s="8">
       <c r="A218" s="5" t="n">
@@ -13794,6 +14376,9 @@
       <c r="AB218" t="n">
         <v>0.8261555555555556</v>
       </c>
+      <c r="AC218" t="n">
+        <v>0.7590785714285715</v>
+      </c>
     </row>
     <row r="219" ht="16" customHeight="1" s="8">
       <c r="A219" s="5" t="n">
@@ -13865,6 +14450,9 @@
       <c r="AB219" t="n">
         <v>0.74186</v>
       </c>
+      <c r="AC219" t="n">
+        <v>0.89869</v>
+      </c>
     </row>
     <row r="220" ht="16" customHeight="1" s="8">
       <c r="A220" s="5" t="n">
@@ -13936,6 +14524,9 @@
       <c r="AB220" t="n">
         <v>0.75689</v>
       </c>
+      <c r="AC220" t="n">
+        <v>0.9096500000000003</v>
+      </c>
     </row>
     <row r="221" ht="16" customHeight="1" s="8">
       <c r="A221" s="5" t="n">
@@ -14007,6 +14598,9 @@
       <c r="AB221" t="n">
         <v>0.8344750000000001</v>
       </c>
+      <c r="AC221" t="n">
+        <v>0.8752285714285716</v>
+      </c>
     </row>
     <row r="222" ht="16" customHeight="1" s="8">
       <c r="A222" s="5" t="n">
@@ -14066,6 +14660,9 @@
       <c r="AB222" t="n">
         <v>0.8927999999999999</v>
       </c>
+      <c r="AC222" t="n">
+        <v>0.8626090909090909</v>
+      </c>
     </row>
     <row r="223" ht="16" customHeight="1" s="8">
       <c r="A223" s="5" t="n">
@@ -14128,6 +14725,9 @@
       <c r="AB223" t="n">
         <v>0.6485181818181819</v>
       </c>
+      <c r="AC223" t="n">
+        <v>0.9153399999999999</v>
+      </c>
     </row>
     <row r="224" ht="16" customHeight="1" s="8">
       <c r="A224" s="5" t="n">
@@ -14190,6 +14790,9 @@
       <c r="AB224" t="n">
         <v>0.7489222222222222</v>
       </c>
+      <c r="AC224" t="n">
+        <v>0.7734000000000001</v>
+      </c>
     </row>
     <row r="225" ht="16" customHeight="1" s="8">
       <c r="A225" s="5" t="n">
@@ -14252,6 +14855,9 @@
       <c r="AB225" t="n">
         <v>0.7000666666666666</v>
       </c>
+      <c r="AC225" t="n">
+        <v>0.7958692307692309</v>
+      </c>
     </row>
     <row r="226" ht="16" customHeight="1" s="8">
       <c r="A226" s="5" t="n">
@@ -14314,6 +14920,9 @@
       <c r="AB226" t="n">
         <v>0.73653</v>
       </c>
+      <c r="AC226" t="n">
+        <v>0.8287727272727273</v>
+      </c>
     </row>
     <row r="227" ht="16" customHeight="1" s="8">
       <c r="A227" s="5" t="n">
@@ -14376,6 +14985,9 @@
       <c r="AB227" t="n">
         <v>0.7327666666666667</v>
       </c>
+      <c r="AC227" t="n">
+        <v>0.7518666666666668</v>
+      </c>
     </row>
     <row r="228" ht="16" customHeight="1" s="8">
       <c r="A228" s="5" t="n">
@@ -14438,6 +15050,9 @@
       <c r="AB228" t="n">
         <v>0.5726666666666667</v>
       </c>
+      <c r="AC228" t="n">
+        <v>0.8241333333333334</v>
+      </c>
     </row>
     <row r="229" ht="16" customHeight="1" s="8">
       <c r="A229" s="5" t="n">
@@ -14500,6 +15115,9 @@
       <c r="AB229" t="n">
         <v>0.8396166666666666</v>
       </c>
+      <c r="AC229" t="n">
+        <v>0.846425</v>
+      </c>
     </row>
     <row r="230" ht="16" customHeight="1" s="8">
       <c r="A230" s="5" t="n">
@@ -14562,6 +15180,9 @@
       <c r="AB230" t="n">
         <v>0.6778444444444445</v>
       </c>
+      <c r="AC230" t="n">
+        <v>0.8584636363636363</v>
+      </c>
     </row>
     <row r="231" ht="16" customHeight="1" s="8">
       <c r="A231" s="5" t="n">
@@ -14624,6 +15245,9 @@
       <c r="AB231" t="n">
         <v>0.5468416666666667</v>
       </c>
+      <c r="AC231" t="n">
+        <v>0.8455416666666667</v>
+      </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="8">
       <c r="A232" s="5" t="n">
@@ -14686,6 +15310,9 @@
       <c r="AB232" t="n">
         <v>0.6597000000000001</v>
       </c>
+      <c r="AC232" t="n">
+        <v>0.8252166666666669</v>
+      </c>
     </row>
     <row r="233" ht="16" customHeight="1" s="8">
       <c r="A233" s="5" t="n">
@@ -14748,6 +15375,9 @@
       <c r="AB233" t="n">
         <v>0.7221399999999999</v>
       </c>
+      <c r="AC233" t="n">
+        <v>0.7852076923076923</v>
+      </c>
     </row>
     <row r="234" ht="16" customHeight="1" s="8">
       <c r="A234" s="5" t="n">
@@ -14810,6 +15440,9 @@
       <c r="AB234" t="n">
         <v>0.7933874999999999</v>
       </c>
+      <c r="AC234" t="n">
+        <v>0.8138363636363638</v>
+      </c>
     </row>
     <row r="235" ht="16" customHeight="1" s="8">
       <c r="A235" s="5" t="n">
@@ -14872,6 +15505,9 @@
       <c r="AB235" t="n">
         <v>0.70082</v>
       </c>
+      <c r="AC235" t="n">
+        <v>0.8375888888888889</v>
+      </c>
     </row>
     <row r="236" ht="16" customHeight="1" s="8">
       <c r="A236" s="5" t="n">
@@ -14934,6 +15570,9 @@
       <c r="AB236" t="n">
         <v>0.7525545454545455</v>
       </c>
+      <c r="AC236" t="n">
+        <v>0.7896454545454545</v>
+      </c>
     </row>
     <row r="237" ht="16" customHeight="1" s="8">
       <c r="A237" s="5" t="n">
@@ -14996,6 +15635,9 @@
       <c r="AB237" t="n">
         <v>0.6757199999999999</v>
       </c>
+      <c r="AC237" t="n">
+        <v>0.77021</v>
+      </c>
     </row>
     <row r="238" ht="16" customHeight="1" s="8">
       <c r="A238" s="5" t="n">
@@ -15058,6 +15700,9 @@
       <c r="AB238" t="n">
         <v>0.64214</v>
       </c>
+      <c r="AC238" t="n">
+        <v>0.7551769230769232</v>
+      </c>
     </row>
     <row r="239" ht="16" customHeight="1" s="8">
       <c r="A239" s="5" t="n">
@@ -15120,6 +15765,9 @@
       <c r="AB239" t="n">
         <v>0.7617363636363635</v>
       </c>
+      <c r="AC239" t="n">
+        <v>0.873546153846154</v>
+      </c>
     </row>
     <row r="240" ht="16" customHeight="1" s="8">
       <c r="A240" s="5" t="n">
@@ -15182,6 +15830,9 @@
       <c r="AB240" t="n">
         <v>0.6537666666666666</v>
       </c>
+      <c r="AC240" t="n">
+        <v>0.77228</v>
+      </c>
     </row>
     <row r="241" ht="16" customHeight="1" s="8">
       <c r="A241" s="5" t="n">
@@ -15244,6 +15895,9 @@
       <c r="AB241" t="n">
         <v>0.7624899999999999</v>
       </c>
+      <c r="AC241" t="n">
+        <v>0.8042400000000001</v>
+      </c>
     </row>
     <row r="242" ht="16" customHeight="1" s="8">
       <c r="A242" s="5" t="n">
@@ -15306,6 +15960,9 @@
       <c r="AB242" t="n">
         <v>0.6906500000000001</v>
       </c>
+      <c r="AC242" t="n">
+        <v>0.7886749999999999</v>
+      </c>
     </row>
     <row r="243" ht="16" customHeight="1" s="8">
       <c r="A243" s="5" t="n">
@@ -15368,6 +16025,9 @@
       <c r="AB243" t="n">
         <v>0.6684111111111112</v>
       </c>
+      <c r="AC243" t="n">
+        <v>0.750225</v>
+      </c>
     </row>
     <row r="244" ht="16" customHeight="1" s="8">
       <c r="A244" s="5" t="n">
@@ -15427,6 +16087,9 @@
       <c r="AB244" t="n">
         <v>0.6328375000000001</v>
       </c>
+      <c r="AC244" t="n">
+        <v>0.8188000000000002</v>
+      </c>
     </row>
     <row r="245" ht="16" customHeight="1" s="8">
       <c r="A245" s="5" t="n">
@@ -15489,6 +16152,9 @@
       <c r="AB245" t="n">
         <v>0.7722</v>
       </c>
+      <c r="AC245" t="n">
+        <v>0.7155166666666667</v>
+      </c>
     </row>
     <row r="246" ht="16" customHeight="1" s="8">
       <c r="A246" s="5" t="n">
@@ -15551,6 +16217,9 @@
       <c r="AB246" t="n">
         <v>0.731218181818182</v>
       </c>
+      <c r="AC246" t="n">
+        <v>0.7414700000000001</v>
+      </c>
     </row>
     <row r="247" ht="16" customHeight="1" s="8">
       <c r="A247" s="5" t="n">
@@ -15610,6 +16279,9 @@
       <c r="AB247" t="n">
         <v>0.8242833333333333</v>
       </c>
+      <c r="AC247" t="n">
+        <v>0.7581333333333333</v>
+      </c>
     </row>
     <row r="248" ht="16" customHeight="1" s="8">
       <c r="A248" s="5" t="n">
@@ -15672,6 +16344,9 @@
       <c r="AB248" t="n">
         <v>0.6457285714285714</v>
       </c>
+      <c r="AC248" t="n">
+        <v>0.71614</v>
+      </c>
     </row>
     <row r="249" ht="16" customHeight="1" s="8">
       <c r="A249" s="5" t="n">
@@ -15734,6 +16409,9 @@
       <c r="AB249" t="n">
         <v>0.7223111111111111</v>
       </c>
+      <c r="AC249" t="n">
+        <v>0.9034666666666668</v>
+      </c>
     </row>
     <row r="250" ht="16" customHeight="1" s="8">
       <c r="A250" s="5" t="n">
@@ -15796,6 +16474,9 @@
       <c r="AB250" t="n">
         <v>0.7336454545454546</v>
       </c>
+      <c r="AC250" t="n">
+        <v>0.8942272727272728</v>
+      </c>
     </row>
     <row r="251" ht="16" customHeight="1" s="8">
       <c r="A251" s="5" t="n">
@@ -15858,6 +16539,9 @@
       <c r="AB251" t="n">
         <v>0.4760375</v>
       </c>
+      <c r="AC251" t="n">
+        <v>0.8156454545454545</v>
+      </c>
     </row>
     <row r="252" ht="16" customHeight="1" s="8">
       <c r="A252" s="5" t="n">
@@ -15920,6 +16604,9 @@
       <c r="AB252" t="n">
         <v>0.7316166666666667</v>
       </c>
+      <c r="AC252" t="n">
+        <v>0.7024399999999998</v>
+      </c>
     </row>
     <row r="253" ht="16" customHeight="1" s="8">
       <c r="A253" s="5" t="n">
@@ -15982,6 +16669,9 @@
       <c r="AB253" t="n">
         <v>0.63619</v>
       </c>
+      <c r="AC253" t="n">
+        <v>0.8233250000000001</v>
+      </c>
     </row>
     <row r="254" ht="16" customHeight="1" s="8">
       <c r="A254" s="5" t="n">
@@ -16044,6 +16734,9 @@
       <c r="AB254" t="n">
         <v>0.7097454545454546</v>
       </c>
+      <c r="AC254" t="n">
+        <v>0.9006888888888889</v>
+      </c>
     </row>
     <row r="255" ht="16" customHeight="1" s="8">
       <c r="A255" s="5" t="n">
@@ -16106,6 +16799,9 @@
       <c r="AB255" t="n">
         <v>0.7767307692307692</v>
       </c>
+      <c r="AC255" t="n">
+        <v>0.7589444444444444</v>
+      </c>
     </row>
     <row r="256" ht="16" customHeight="1" s="8">
       <c r="A256" s="5" t="n">
@@ -16168,6 +16864,9 @@
       <c r="AB256" t="n">
         <v>0.63409</v>
       </c>
+      <c r="AC256" t="n">
+        <v>0.8178</v>
+      </c>
     </row>
     <row r="257" ht="16" customHeight="1" s="8">
       <c r="A257" s="5" t="n">
@@ -16230,6 +16929,9 @@
       <c r="AB257" t="n">
         <v>0.7080272727272727</v>
       </c>
+      <c r="AC257" t="n">
+        <v>0.8153250000000001</v>
+      </c>
     </row>
     <row r="258" ht="16" customHeight="1" s="8">
       <c r="A258" s="5" t="n">
@@ -16292,6 +16994,9 @@
       <c r="AB258" t="n">
         <v>0.63758</v>
       </c>
+      <c r="AC258" t="n">
+        <v>0.69499</v>
+      </c>
     </row>
     <row r="259" ht="16" customHeight="1" s="8">
       <c r="A259" s="5" t="n">
@@ -16354,6 +17059,9 @@
       <c r="AB259" t="n">
         <v>0.7251727272727272</v>
       </c>
+      <c r="AC259" t="n">
+        <v>0.7542428571428571</v>
+      </c>
     </row>
     <row r="260" ht="16" customHeight="1" s="8">
       <c r="A260" s="5" t="n">
@@ -16416,6 +17124,9 @@
       <c r="AB260" t="n">
         <v>0.6167777777777779</v>
       </c>
+      <c r="AC260" t="n">
+        <v>0.7819800000000001</v>
+      </c>
     </row>
     <row r="261" ht="16" customHeight="1" s="8">
       <c r="A261" s="5" t="n">
@@ -16478,6 +17189,9 @@
       <c r="AB261" t="n">
         <v>0.6271899999999999</v>
       </c>
+      <c r="AC261" t="n">
+        <v>0.7959833333333334</v>
+      </c>
     </row>
     <row r="262" ht="16" customHeight="1" s="8">
       <c r="A262" s="5" t="n">
@@ -16540,6 +17254,9 @@
       <c r="AB262" t="n">
         <v>0.571775</v>
       </c>
+      <c r="AC262" t="n">
+        <v>0.881646153846154</v>
+      </c>
     </row>
     <row r="263" ht="16" customHeight="1" s="8">
       <c r="A263" s="5" t="n">
@@ -16602,6 +17319,9 @@
       <c r="AB263" t="n">
         <v>0.6547307692307693</v>
       </c>
+      <c r="AC263" t="n">
+        <v>0.8004769230769231</v>
+      </c>
     </row>
     <row r="264" ht="16" customHeight="1" s="8">
       <c r="A264" s="5" t="n">
@@ -16664,6 +17384,9 @@
       <c r="AB264" t="n">
         <v>0.8918874999999999</v>
       </c>
+      <c r="AC264" t="n">
+        <v>0.8668153846153844</v>
+      </c>
     </row>
     <row r="265" ht="16" customHeight="1" s="8">
       <c r="A265" s="5" t="n">
@@ -16726,6 +17449,9 @@
       <c r="AB265" t="n">
         <v>0.83503</v>
       </c>
+      <c r="AC265" t="n">
+        <v>0.7843899999999999</v>
+      </c>
     </row>
     <row r="266" ht="16" customHeight="1" s="8">
       <c r="A266" s="5" t="n">
@@ -16788,6 +17514,9 @@
       <c r="AB266" t="n">
         <v>0.7237888888888889</v>
       </c>
+      <c r="AC266" t="n">
+        <v>0.7934272727272728</v>
+      </c>
     </row>
     <row r="267" ht="16" customHeight="1" s="8">
       <c r="A267" s="5" t="n">
@@ -16850,6 +17579,9 @@
       <c r="AB267" t="n">
         <v>0.4552444444444445</v>
       </c>
+      <c r="AC267" t="n">
+        <v>0.6917916666666666</v>
+      </c>
     </row>
     <row r="268" ht="16" customHeight="1" s="8">
       <c r="A268" s="5" t="n">
@@ -16912,6 +17644,9 @@
       <c r="AB268" t="n">
         <v>0.7277333333333335</v>
       </c>
+      <c r="AC268" t="n">
+        <v>0.7535333333333334</v>
+      </c>
     </row>
     <row r="269" ht="16" customHeight="1" s="8">
       <c r="A269" s="5" t="n">
@@ -16974,6 +17709,9 @@
       <c r="AB269" t="n">
         <v>0.5953363636363637</v>
       </c>
+      <c r="AC269" t="n">
+        <v>0.7960900000000002</v>
+      </c>
     </row>
     <row r="270" ht="16" customHeight="1" s="8">
       <c r="A270" s="5" t="n">
@@ -17036,6 +17774,9 @@
       <c r="AB270" t="n">
         <v>0.7486</v>
       </c>
+      <c r="AC270" t="n">
+        <v>0.7796000000000001</v>
+      </c>
     </row>
     <row r="271" ht="16" customHeight="1" s="8">
       <c r="A271" s="5" t="n">
@@ -17098,6 +17839,9 @@
       <c r="AB271" t="n">
         <v>0.64428</v>
       </c>
+      <c r="AC271" t="n">
+        <v>0.8516846153846152</v>
+      </c>
     </row>
     <row r="272" ht="16" customHeight="1" s="8">
       <c r="A272" s="5" t="n">
@@ -17160,6 +17904,9 @@
       <c r="AB272" t="n">
         <v>0.6922333333333333</v>
       </c>
+      <c r="AC272" t="n">
+        <v>0.7948777777777778</v>
+      </c>
     </row>
     <row r="273" ht="16" customHeight="1" s="8">
       <c r="A273" s="5" t="n">
@@ -17222,6 +17969,9 @@
       <c r="AB273" t="n">
         <v>0.6371999999999999</v>
       </c>
+      <c r="AC273" t="n">
+        <v>0.7156363636363636</v>
+      </c>
     </row>
     <row r="274" ht="16" customHeight="1" s="8">
       <c r="A274" s="5" t="n">
@@ -17284,6 +18034,9 @@
       <c r="AB274" t="n">
         <v>0.7016999999999999</v>
       </c>
+      <c r="AC274" t="n">
+        <v>0.7746333333333332</v>
+      </c>
     </row>
     <row r="275" ht="16" customHeight="1" s="8">
       <c r="A275" s="5" t="n">
@@ -17346,6 +18099,9 @@
       <c r="AB275" t="n">
         <v>0.6962111111111111</v>
       </c>
+      <c r="AC275" t="n">
+        <v>0.8391444444444445</v>
+      </c>
     </row>
     <row r="276" ht="16" customHeight="1" s="8">
       <c r="A276" s="5" t="n">
@@ -17408,6 +18164,9 @@
       <c r="AB276" t="n">
         <v>0.5692</v>
       </c>
+      <c r="AC276" t="n">
+        <v>0.7659600000000001</v>
+      </c>
     </row>
     <row r="277" ht="16" customHeight="1" s="8">
       <c r="A277" s="5" t="n">
@@ -17470,6 +18229,9 @@
       <c r="AB277" t="n">
         <v>0.6575181818181818</v>
       </c>
+      <c r="AC277" t="n">
+        <v>0.8135111111111111</v>
+      </c>
     </row>
     <row r="278" ht="16" customHeight="1" s="8">
       <c r="A278" s="5" t="n">
@@ -17532,6 +18294,9 @@
       <c r="AB278" t="n">
         <v>0.6304499999999998</v>
       </c>
+      <c r="AC278" t="n">
+        <v>0.7887700000000001</v>
+      </c>
     </row>
     <row r="279" ht="16" customHeight="1" s="8">
       <c r="A279" s="5" t="n">
@@ -17594,6 +18359,9 @@
       <c r="AB279" t="n">
         <v>0.6911444444444445</v>
       </c>
+      <c r="AC279" t="n">
+        <v>0.8302363636363637</v>
+      </c>
     </row>
     <row r="280" ht="16" customHeight="1" s="8">
       <c r="A280" s="5" t="n">
@@ -17656,6 +18424,9 @@
       <c r="AB280" t="n">
         <v>0.6052</v>
       </c>
+      <c r="AC280" t="n">
+        <v>0.7131636363636363</v>
+      </c>
     </row>
     <row r="281" ht="16" customHeight="1" s="8">
       <c r="A281" s="5" t="n">
@@ -17718,6 +18489,9 @@
       <c r="AB281" t="n">
         <v>0.5792888888888889</v>
       </c>
+      <c r="AC281" t="n">
+        <v>0.810023076923077</v>
+      </c>
     </row>
     <row r="282" ht="16" customHeight="1" s="8">
       <c r="A282" s="5" t="n">
@@ -17780,6 +18554,9 @@
       <c r="AB282" t="n">
         <v>0.7244916666666666</v>
       </c>
+      <c r="AC282" t="n">
+        <v>0.7601545454545455</v>
+      </c>
     </row>
     <row r="283" ht="16" customHeight="1" s="8">
       <c r="A283" s="5" t="n">
@@ -17842,6 +18619,9 @@
       <c r="AB283" t="n">
         <v>0.6353090909090908</v>
       </c>
+      <c r="AC283" t="n">
+        <v>0.8158499999999999</v>
+      </c>
     </row>
     <row r="284" ht="16" customHeight="1" s="8">
       <c r="A284" s="5" t="n">
@@ -17904,6 +18684,9 @@
       <c r="AB284" t="n">
         <v>0.6921625</v>
       </c>
+      <c r="AC284" t="n">
+        <v>0.7985</v>
+      </c>
     </row>
     <row r="285" ht="16" customHeight="1" s="8">
       <c r="A285" s="5" t="n">
@@ -17963,6 +18746,9 @@
       <c r="AB285" t="n">
         <v>0.7570818181818182</v>
       </c>
+      <c r="AC285" t="n">
+        <v>0.679</v>
+      </c>
     </row>
     <row r="286" ht="16" customHeight="1" s="8">
       <c r="A286" s="5" t="n">
@@ -18025,6 +18811,9 @@
       <c r="AB286" t="n">
         <v>0.7657833333333331</v>
       </c>
+      <c r="AC286" t="n">
+        <v>0.76997</v>
+      </c>
     </row>
     <row r="287" ht="16" customHeight="1" s="8">
       <c r="A287" s="5" t="n">
@@ -18087,6 +18876,9 @@
       <c r="AB287" t="n">
         <v>0.6864666666666667</v>
       </c>
+      <c r="AC287" t="n">
+        <v>0.8828818181818182</v>
+      </c>
     </row>
     <row r="288" ht="16" customHeight="1" s="8">
       <c r="A288" s="5" t="n">
@@ -18149,6 +18941,9 @@
       <c r="AB288" t="n">
         <v>0.7069666666666667</v>
       </c>
+      <c r="AC288" t="n">
+        <v>0.7916583333333334</v>
+      </c>
     </row>
     <row r="289" ht="16" customHeight="1" s="8">
       <c r="A289" s="5" t="n">
@@ -18211,6 +19006,9 @@
       <c r="AB289" t="n">
         <v>0.6086</v>
       </c>
+      <c r="AC289" t="n">
+        <v>0.7966416666666668</v>
+      </c>
     </row>
     <row r="290" ht="16" customHeight="1" s="8">
       <c r="A290" s="5" t="n">
@@ -18273,6 +19071,9 @@
       <c r="AB290" t="n">
         <v>0.7044100000000001</v>
       </c>
+      <c r="AC290" t="n">
+        <v>0.76896</v>
+      </c>
     </row>
     <row r="291" ht="16" customHeight="1" s="8">
       <c r="A291" s="5" t="n">
@@ -18335,6 +19136,9 @@
       <c r="AB291" t="n">
         <v>0.6983100000000001</v>
       </c>
+      <c r="AC291" t="n">
+        <v>0.7798545454545455</v>
+      </c>
     </row>
     <row r="292" ht="16" customHeight="1" s="8">
       <c r="A292" s="5" t="n">
@@ -18397,6 +19201,9 @@
       <c r="AB292" t="n">
         <v>0.48245</v>
       </c>
+      <c r="AC292" t="n">
+        <v>0.8703181818181818</v>
+      </c>
     </row>
     <row r="293" ht="16" customHeight="1" s="8">
       <c r="A293" s="5" t="n">
@@ -18459,6 +19266,9 @@
       <c r="AB293" t="n">
         <v>0.5845416666666667</v>
       </c>
+      <c r="AC293" t="n">
+        <v>0.7761636363636364</v>
+      </c>
     </row>
     <row r="294" ht="16" customHeight="1" s="8">
       <c r="A294" s="5" t="n">
@@ -18521,6 +19331,9 @@
       <c r="AB294" t="n">
         <v>0.7699666666666666</v>
       </c>
+      <c r="AC294" t="n">
+        <v>0.8166916666666667</v>
+      </c>
     </row>
     <row r="295" ht="16" customHeight="1" s="8">
       <c r="A295" s="5" t="n">
@@ -18583,6 +19396,9 @@
       <c r="AB295" t="n">
         <v>0.7778799999999999</v>
       </c>
+      <c r="AC295" t="n">
+        <v>0.7560083333333334</v>
+      </c>
     </row>
     <row r="296" ht="16" customHeight="1" s="8">
       <c r="A296" s="5" t="n">
@@ -18645,6 +19461,9 @@
       <c r="AB296" t="n">
         <v>0.6850307692307692</v>
       </c>
+      <c r="AC296" t="n">
+        <v>0.8292571428571428</v>
+      </c>
     </row>
     <row r="297" ht="16" customHeight="1" s="8">
       <c r="A297" s="5" t="n">
@@ -18707,6 +19526,9 @@
       <c r="AB297" t="n">
         <v>0.5437333333333333</v>
       </c>
+      <c r="AC297" t="n">
+        <v>0.7179</v>
+      </c>
     </row>
     <row r="298" ht="16" customHeight="1" s="8">
       <c r="A298" s="5" t="n">
@@ -18769,6 +19591,9 @@
       <c r="AB298" t="n">
         <v>0.6059272727272728</v>
       </c>
+      <c r="AC298" t="n">
+        <v>0.8125083333333335</v>
+      </c>
     </row>
     <row r="299" ht="16" customHeight="1" s="8">
       <c r="A299" s="5" t="n">
@@ -18831,6 +19656,9 @@
       <c r="AB299" t="n">
         <v>0.5445583333333334</v>
       </c>
+      <c r="AC299" t="n">
+        <v>0.7862100000000001</v>
+      </c>
     </row>
     <row r="300" ht="16" customHeight="1" s="8">
       <c r="A300" s="5" t="n">
@@ -18893,6 +19721,9 @@
       <c r="AB300" t="n">
         <v>0.7297333333333333</v>
       </c>
+      <c r="AC300" t="n">
+        <v>0.8091750000000001</v>
+      </c>
     </row>
     <row r="301" ht="16" customHeight="1" s="8">
       <c r="A301" s="5" t="n">
@@ -18955,6 +19786,9 @@
       <c r="AB301" t="n">
         <v>0.7012454545454544</v>
       </c>
+      <c r="AC301" t="n">
+        <v>0.7670769230769232</v>
+      </c>
     </row>
     <row r="302" ht="16" customHeight="1" s="8">
       <c r="A302" s="5" t="n">
@@ -19017,6 +19851,9 @@
       <c r="AB302" t="n">
         <v>0.5287333333333334</v>
       </c>
+      <c r="AC302" t="n">
+        <v>0.8822599999999999</v>
+      </c>
     </row>
     <row r="303" ht="16" customHeight="1" s="8">
       <c r="A303" s="5" t="n">
@@ -19079,6 +19916,9 @@
       <c r="AB303" t="n">
         <v>0.7496222222222222</v>
       </c>
+      <c r="AC303" t="n">
+        <v>0.7861</v>
+      </c>
     </row>
     <row r="304" ht="16" customHeight="1" s="8">
       <c r="A304" s="5" t="n">
@@ -19141,6 +19981,9 @@
       <c r="AB304" t="n">
         <v>0.6539374999999999</v>
       </c>
+      <c r="AC304" t="n">
+        <v>0.8343666666666666</v>
+      </c>
     </row>
     <row r="305" ht="16" customHeight="1" s="8">
       <c r="A305" s="5" t="n">
@@ -19203,6 +20046,9 @@
       <c r="AB305" t="n">
         <v>0.7149666666666668</v>
       </c>
+      <c r="AC305" t="n">
+        <v>0.6367</v>
+      </c>
     </row>
     <row r="306" ht="16" customHeight="1" s="8">
       <c r="A306" s="5" t="n">
@@ -19265,6 +20111,9 @@
       <c r="AB306" t="n">
         <v>0.62009</v>
       </c>
+      <c r="AC306" t="n">
+        <v>0.7104199999999999</v>
+      </c>
     </row>
     <row r="307" ht="16" customHeight="1" s="8">
       <c r="A307" s="5" t="n">
@@ -19327,6 +20176,9 @@
       <c r="AB307" t="n">
         <v>0.8117500000000002</v>
       </c>
+      <c r="AC307" t="n">
+        <v>0.826325</v>
+      </c>
     </row>
     <row r="308" ht="16" customHeight="1" s="8">
       <c r="A308" s="5" t="n">
@@ -19389,6 +20241,9 @@
       <c r="AB308" t="n">
         <v>0.73348</v>
       </c>
+      <c r="AC308" t="n">
+        <v>0.71153</v>
+      </c>
     </row>
     <row r="309" ht="16" customHeight="1" s="8">
       <c r="A309" s="5" t="n">
@@ -19451,6 +20306,9 @@
       <c r="AB309" t="n">
         <v>0.6241428571428572</v>
       </c>
+      <c r="AC309" t="n">
+        <v>0.9014416666666666</v>
+      </c>
     </row>
     <row r="310" ht="16" customHeight="1" s="8">
       <c r="A310" s="5" t="n">
@@ -19513,6 +20371,9 @@
       <c r="AB310" t="n">
         <v>0.6362999999999999</v>
       </c>
+      <c r="AC310" t="n">
+        <v>0.7578900000000001</v>
+      </c>
     </row>
     <row r="311" ht="16" customHeight="1" s="8">
       <c r="A311" s="5" t="n">
@@ -19574,6 +20435,9 @@
       </c>
       <c r="AB311" t="n">
         <v>0.6525909090909091</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>0.8588909090909091</v>
       </c>
     </row>
     <row r="314" ht="16" customHeight="1" s="8">
@@ -19966,6 +20830,9 @@
       <c r="AB320" t="n">
         <v>0.1119</v>
       </c>
+      <c r="AC320" t="n">
+        <v>0.2555</v>
+      </c>
     </row>
     <row r="321" ht="16" customHeight="1" s="8">
       <c r="A321" s="5" t="n">
@@ -20037,6 +20904,9 @@
       <c r="AB321" t="n">
         <v>0.0568</v>
       </c>
+      <c r="AC321" t="n">
+        <v>0.1289</v>
+      </c>
     </row>
     <row r="322" ht="16" customHeight="1" s="8">
       <c r="A322" s="5" t="n">
@@ -20108,6 +20978,9 @@
       <c r="AB322" t="n">
         <v>0.09080000000000001</v>
       </c>
+      <c r="AC322" t="n">
+        <v>0.5621</v>
+      </c>
     </row>
     <row r="323" ht="16" customHeight="1" s="8">
       <c r="A323" s="5" t="n">
@@ -20179,6 +21052,9 @@
       <c r="AB323" t="n">
         <v>0.0606</v>
       </c>
+      <c r="AC323" t="n">
+        <v>0.377</v>
+      </c>
     </row>
     <row r="324" ht="16" customHeight="1" s="8">
       <c r="A324" s="5" t="n">
@@ -20250,6 +21126,9 @@
       <c r="AB324" t="n">
         <v>0.0897</v>
       </c>
+      <c r="AC324" t="n">
+        <v>0.2501</v>
+      </c>
     </row>
     <row r="325" ht="16" customHeight="1" s="8">
       <c r="A325" s="5" t="n">
@@ -20321,6 +21200,9 @@
       <c r="AB325" t="n">
         <v>0.0934</v>
       </c>
+      <c r="AC325" t="n">
+        <v>0.2059</v>
+      </c>
     </row>
     <row r="326" ht="16" customHeight="1" s="8">
       <c r="A326" s="5" t="n">
@@ -20383,6 +21265,9 @@
       <c r="AB326" t="n">
         <v>0.098</v>
       </c>
+      <c r="AC326" t="n">
+        <v>0.1342</v>
+      </c>
     </row>
     <row r="327" ht="16" customHeight="1" s="8">
       <c r="A327" s="5" t="n">
@@ -20445,6 +21330,9 @@
       <c r="AB327" t="n">
         <v>0.07489999999999999</v>
       </c>
+      <c r="AC327" t="n">
+        <v>0.3377</v>
+      </c>
     </row>
     <row r="328" ht="16" customHeight="1" s="8">
       <c r="A328" s="5" t="n">
@@ -20507,6 +21395,9 @@
       <c r="AB328" t="n">
         <v>0.1351</v>
       </c>
+      <c r="AC328" t="n">
+        <v>0.3543</v>
+      </c>
     </row>
     <row r="329" ht="16" customHeight="1" s="8">
       <c r="A329" s="5" t="n">
@@ -20569,6 +21460,9 @@
       <c r="AB329" t="n">
         <v>0.0786</v>
       </c>
+      <c r="AC329" t="n">
+        <v>0.302</v>
+      </c>
     </row>
     <row r="330" ht="16" customHeight="1" s="8">
       <c r="A330" s="5" t="n">
@@ -20631,6 +21525,9 @@
       <c r="AB330" t="n">
         <v>0.06759999999999999</v>
       </c>
+      <c r="AC330" t="n">
+        <v>0.3552</v>
+      </c>
     </row>
     <row r="331" ht="16" customHeight="1" s="8">
       <c r="A331" s="5" t="n">
@@ -20693,6 +21590,9 @@
       <c r="AB331" t="n">
         <v>0.0833</v>
       </c>
+      <c r="AC331" t="n">
+        <v>0.3816</v>
+      </c>
     </row>
     <row r="332" ht="16" customHeight="1" s="8">
       <c r="A332" s="5" t="n">
@@ -20755,6 +21655,9 @@
       <c r="AB332" t="n">
         <v>0.07439999999999999</v>
       </c>
+      <c r="AC332" t="n">
+        <v>0.3935</v>
+      </c>
     </row>
     <row r="333" ht="16" customHeight="1" s="8">
       <c r="A333" s="5" t="n">
@@ -20817,6 +21720,9 @@
       <c r="AB333" t="n">
         <v>0.0751</v>
       </c>
+      <c r="AC333" t="n">
+        <v>0.3258</v>
+      </c>
     </row>
     <row r="334" ht="16" customHeight="1" s="8">
       <c r="A334" s="5" t="n">
@@ -20879,6 +21785,9 @@
       <c r="AB334" t="n">
         <v>0.0668</v>
       </c>
+      <c r="AC334" t="n">
+        <v>0.2384</v>
+      </c>
     </row>
     <row r="335" ht="16" customHeight="1" s="8">
       <c r="A335" s="5" t="n">
@@ -20941,6 +21850,9 @@
       <c r="AB335" t="n">
         <v>0.1011</v>
       </c>
+      <c r="AC335" t="n">
+        <v>0.2158</v>
+      </c>
     </row>
     <row r="336" ht="16" customHeight="1" s="8">
       <c r="A336" s="5" t="n">
@@ -21003,6 +21915,9 @@
       <c r="AB336" t="n">
         <v>0.06569999999999999</v>
       </c>
+      <c r="AC336" t="n">
+        <v>0.2395</v>
+      </c>
     </row>
     <row r="337" ht="16" customHeight="1" s="8">
       <c r="A337" s="5" t="n">
@@ -21065,6 +21980,9 @@
       <c r="AB337" t="n">
         <v>0.0477</v>
       </c>
+      <c r="AC337" t="n">
+        <v>0.2683</v>
+      </c>
     </row>
     <row r="338" ht="16" customHeight="1" s="8">
       <c r="A338" s="5" t="n">
@@ -21127,6 +22045,9 @@
       <c r="AB338" t="n">
         <v>0.07340000000000001</v>
       </c>
+      <c r="AC338" t="n">
+        <v>0.221</v>
+      </c>
     </row>
     <row r="339" ht="16" customHeight="1" s="8">
       <c r="A339" s="5" t="n">
@@ -21189,6 +22110,9 @@
       <c r="AB339" t="n">
         <v>0.08019999999999999</v>
       </c>
+      <c r="AC339" t="n">
+        <v>0.2652</v>
+      </c>
     </row>
     <row r="340" ht="16" customHeight="1" s="8">
       <c r="A340" s="5" t="n">
@@ -21251,6 +22175,9 @@
       <c r="AB340" t="n">
         <v>0.1139</v>
       </c>
+      <c r="AC340" t="n">
+        <v>0.2437</v>
+      </c>
     </row>
     <row r="341" ht="16" customHeight="1" s="8">
       <c r="A341" s="5" t="n">
@@ -21313,6 +22240,9 @@
       <c r="AB341" t="n">
         <v>0.08019999999999999</v>
       </c>
+      <c r="AC341" t="n">
+        <v>0.2178</v>
+      </c>
     </row>
     <row r="342" ht="16" customHeight="1" s="8">
       <c r="A342" s="5" t="n">
@@ -21375,6 +22305,9 @@
       <c r="AB342" t="n">
         <v>0.0784</v>
       </c>
+      <c r="AC342" t="n">
+        <v>0.2679</v>
+      </c>
     </row>
     <row r="343" ht="16" customHeight="1" s="8">
       <c r="A343" s="5" t="n">
@@ -21437,6 +22370,9 @@
       <c r="AB343" t="n">
         <v>0.063</v>
       </c>
+      <c r="AC343" t="n">
+        <v>0.2669</v>
+      </c>
     </row>
     <row r="344" ht="16" customHeight="1" s="8">
       <c r="A344" s="5" t="n">
@@ -21499,6 +22435,9 @@
       <c r="AB344" t="n">
         <v>0.07439999999999999</v>
       </c>
+      <c r="AC344" t="n">
+        <v>0.1945</v>
+      </c>
     </row>
     <row r="345" ht="16" customHeight="1" s="8">
       <c r="A345" s="5" t="n">
@@ -21561,6 +22500,9 @@
       <c r="AB345" t="n">
         <v>0.06859999999999999</v>
       </c>
+      <c r="AC345" t="n">
+        <v>0.2959</v>
+      </c>
     </row>
     <row r="346" ht="16" customHeight="1" s="8">
       <c r="A346" s="5" t="n">
@@ -21623,6 +22565,9 @@
       <c r="AB346" t="n">
         <v>0.0736</v>
       </c>
+      <c r="AC346" t="n">
+        <v>0.2954</v>
+      </c>
     </row>
     <row r="347" ht="16" customHeight="1" s="8">
       <c r="A347" s="5" t="n">
@@ -21685,6 +22630,9 @@
       <c r="AB347" t="n">
         <v>0.06320000000000001</v>
       </c>
+      <c r="AC347" t="n">
+        <v>0.2613</v>
+      </c>
     </row>
     <row r="348" ht="16" customHeight="1" s="8">
       <c r="A348" s="5" t="n">
@@ -21747,6 +22695,9 @@
       <c r="AB348" t="n">
         <v>0.0765</v>
       </c>
+      <c r="AC348" t="n">
+        <v>0.2979</v>
+      </c>
     </row>
     <row r="349" ht="16" customHeight="1" s="8">
       <c r="A349" s="5" t="n">
@@ -21809,6 +22760,9 @@
       <c r="AB349" t="n">
         <v>0.0468</v>
       </c>
+      <c r="AC349" t="n">
+        <v>0.3478</v>
+      </c>
     </row>
     <row r="350" ht="16" customHeight="1" s="8">
       <c r="A350" s="5" t="n">
@@ -21871,6 +22825,9 @@
       <c r="AB350" t="n">
         <v>0.0634</v>
       </c>
+      <c r="AC350" t="n">
+        <v>0.3019</v>
+      </c>
     </row>
     <row r="351" ht="16" customHeight="1" s="8">
       <c r="A351" s="5" t="n">
@@ -21933,6 +22890,9 @@
       <c r="AB351" t="n">
         <v>0.0611</v>
       </c>
+      <c r="AC351" t="n">
+        <v>0.2835</v>
+      </c>
     </row>
     <row r="352" ht="16" customHeight="1" s="8">
       <c r="A352" s="5" t="n">
@@ -21995,6 +22955,9 @@
       <c r="AB352" t="n">
         <v>0.0599</v>
       </c>
+      <c r="AC352" t="n">
+        <v>0.303</v>
+      </c>
     </row>
     <row r="353" ht="16" customHeight="1" s="8">
       <c r="A353" s="5" t="n">
@@ -22057,6 +23020,9 @@
       <c r="AB353" t="n">
         <v>0.06660000000000001</v>
       </c>
+      <c r="AC353" t="n">
+        <v>0.309</v>
+      </c>
     </row>
     <row r="354" ht="16" customHeight="1" s="8">
       <c r="A354" s="5" t="n">
@@ -22119,6 +23085,9 @@
       <c r="AB354" t="n">
         <v>0.08119999999999999</v>
       </c>
+      <c r="AC354" t="n">
+        <v>0.3185</v>
+      </c>
     </row>
     <row r="355" ht="16" customHeight="1" s="8">
       <c r="A355" s="5" t="n">
@@ -22181,6 +23150,9 @@
       <c r="AB355" t="n">
         <v>0.0732</v>
       </c>
+      <c r="AC355" t="n">
+        <v>0.2363</v>
+      </c>
     </row>
     <row r="356" ht="16" customHeight="1" s="8">
       <c r="A356" s="5" t="n">
@@ -22243,6 +23215,9 @@
       <c r="AB356" t="n">
         <v>0.0586</v>
       </c>
+      <c r="AC356" t="n">
+        <v>0.2625</v>
+      </c>
     </row>
     <row r="357" ht="16" customHeight="1" s="8">
       <c r="A357" s="5" t="n">
@@ -22305,6 +23280,9 @@
       <c r="AB357" t="n">
         <v>0.057</v>
       </c>
+      <c r="AC357" t="n">
+        <v>0.3122</v>
+      </c>
     </row>
     <row r="358" ht="16" customHeight="1" s="8">
       <c r="A358" s="5" t="n">
@@ -22367,6 +23345,9 @@
       <c r="AB358" t="n">
         <v>0.0576</v>
       </c>
+      <c r="AC358" t="n">
+        <v>0.2671</v>
+      </c>
     </row>
     <row r="359" ht="16" customHeight="1" s="8">
       <c r="A359" s="5" t="n">
@@ -22429,6 +23410,9 @@
       <c r="AB359" t="n">
         <v>0.0526</v>
       </c>
+      <c r="AC359" t="n">
+        <v>0.2504</v>
+      </c>
     </row>
     <row r="360" ht="16" customHeight="1" s="8">
       <c r="A360" s="5" t="n">
@@ -22491,6 +23475,9 @@
       <c r="AB360" t="n">
         <v>0.06279999999999999</v>
       </c>
+      <c r="AC360" t="n">
+        <v>0.2273</v>
+      </c>
     </row>
     <row r="361" ht="16" customHeight="1" s="8">
       <c r="A361" s="5" t="n">
@@ -22553,6 +23540,9 @@
       <c r="AB361" t="n">
         <v>0.07779999999999999</v>
       </c>
+      <c r="AC361" t="n">
+        <v>0.2306</v>
+      </c>
     </row>
     <row r="362" ht="16" customHeight="1" s="8">
       <c r="A362" s="5" t="n">
@@ -22615,6 +23605,9 @@
       <c r="AB362" t="n">
         <v>0.0623</v>
       </c>
+      <c r="AC362" t="n">
+        <v>0.2772</v>
+      </c>
     </row>
     <row r="363" ht="16" customHeight="1" s="8">
       <c r="A363" s="5" t="n">
@@ -22677,6 +23670,9 @@
       <c r="AB363" t="n">
         <v>0.0546</v>
       </c>
+      <c r="AC363" t="n">
+        <v>0.2291</v>
+      </c>
     </row>
     <row r="364" ht="16" customHeight="1" s="8">
       <c r="A364" s="5" t="n">
@@ -22739,6 +23735,9 @@
       <c r="AB364" t="n">
         <v>0.0536</v>
       </c>
+      <c r="AC364" t="n">
+        <v>0.2518</v>
+      </c>
     </row>
     <row r="365" ht="16" customHeight="1" s="8">
       <c r="A365" s="5" t="n">
@@ -22801,6 +23800,9 @@
       <c r="AB365" t="n">
         <v>0.0525</v>
       </c>
+      <c r="AC365" t="n">
+        <v>0.3212</v>
+      </c>
     </row>
     <row r="366" ht="16" customHeight="1" s="8">
       <c r="A366" s="5" t="n">
@@ -22863,6 +23865,9 @@
       <c r="AB366" t="n">
         <v>0.0545</v>
       </c>
+      <c r="AC366" t="n">
+        <v>0.2958</v>
+      </c>
     </row>
     <row r="367" ht="16" customHeight="1" s="8">
       <c r="A367" s="5" t="n">
@@ -22925,6 +23930,9 @@
       <c r="AB367" t="n">
         <v>0.0708</v>
       </c>
+      <c r="AC367" t="n">
+        <v>0.2597</v>
+      </c>
     </row>
     <row r="368" ht="16" customHeight="1" s="8">
       <c r="A368" s="5" t="n">
@@ -22987,6 +23995,9 @@
       <c r="AB368" t="n">
         <v>0.06610000000000001</v>
       </c>
+      <c r="AC368" t="n">
+        <v>0.2718</v>
+      </c>
     </row>
     <row r="369" ht="16" customHeight="1" s="8">
       <c r="A369" s="5" t="n">
@@ -23049,6 +24060,9 @@
       <c r="AB369" t="n">
         <v>0.0786</v>
       </c>
+      <c r="AC369" t="n">
+        <v>0.2503</v>
+      </c>
     </row>
     <row r="370" ht="16" customHeight="1" s="8">
       <c r="A370" s="5" t="n">
@@ -23111,6 +24125,9 @@
       <c r="AB370" t="n">
         <v>0.066</v>
       </c>
+      <c r="AC370" t="n">
+        <v>0.2768</v>
+      </c>
     </row>
     <row r="371" ht="16" customHeight="1" s="8">
       <c r="A371" s="5" t="n">
@@ -23173,6 +24190,9 @@
       <c r="AB371" t="n">
         <v>0.0634</v>
       </c>
+      <c r="AC371" t="n">
+        <v>0.2604</v>
+      </c>
     </row>
     <row r="372" ht="16" customHeight="1" s="8">
       <c r="A372" s="5" t="n">
@@ -23235,6 +24255,9 @@
       <c r="AB372" t="n">
         <v>0.0561</v>
       </c>
+      <c r="AC372" t="n">
+        <v>0.2355</v>
+      </c>
     </row>
     <row r="373" ht="16" customHeight="1" s="8">
       <c r="A373" s="5" t="n">
@@ -23297,6 +24320,9 @@
       <c r="AB373" t="n">
         <v>0.07770000000000001</v>
       </c>
+      <c r="AC373" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="374" ht="16" customHeight="1" s="8">
       <c r="A374" s="5" t="n">
@@ -23359,6 +24385,9 @@
       <c r="AB374" t="n">
         <v>0.0892</v>
       </c>
+      <c r="AC374" t="n">
+        <v>0.268</v>
+      </c>
     </row>
     <row r="375" ht="16" customHeight="1" s="8">
       <c r="A375" s="5" t="n">
@@ -23421,6 +24450,9 @@
       <c r="AB375" t="n">
         <v>0.0791</v>
       </c>
+      <c r="AC375" t="n">
+        <v>0.2589</v>
+      </c>
     </row>
     <row r="376" ht="16" customHeight="1" s="8">
       <c r="A376" s="5" t="n">
@@ -23483,6 +24515,9 @@
       <c r="AB376" t="n">
         <v>0.0693</v>
       </c>
+      <c r="AC376" t="n">
+        <v>0.2692</v>
+      </c>
     </row>
     <row r="377" ht="16" customHeight="1" s="8">
       <c r="A377" s="5" t="n">
@@ -23545,6 +24580,9 @@
       <c r="AB377" t="n">
         <v>0.0598</v>
       </c>
+      <c r="AC377" t="n">
+        <v>0.2553</v>
+      </c>
     </row>
     <row r="378" ht="16" customHeight="1" s="8">
       <c r="A378" s="5" t="n">
@@ -23607,6 +24645,9 @@
       <c r="AB378" t="n">
         <v>0.0602</v>
       </c>
+      <c r="AC378" t="n">
+        <v>0.2738</v>
+      </c>
     </row>
     <row r="379" ht="16" customHeight="1" s="8">
       <c r="A379" s="5" t="n">
@@ -23669,6 +24710,9 @@
       <c r="AB379" t="n">
         <v>0.0603</v>
       </c>
+      <c r="AC379" t="n">
+        <v>0.2734</v>
+      </c>
     </row>
     <row r="380" ht="16" customHeight="1" s="8">
       <c r="A380" s="5" t="n">
@@ -23731,6 +24775,9 @@
       <c r="AB380" t="n">
         <v>0.07969999999999999</v>
       </c>
+      <c r="AC380" t="n">
+        <v>0.2439</v>
+      </c>
     </row>
     <row r="381" ht="16" customHeight="1" s="8">
       <c r="A381" s="5" t="n">
@@ -23793,6 +24840,9 @@
       <c r="AB381" t="n">
         <v>0.07530000000000001</v>
       </c>
+      <c r="AC381" t="n">
+        <v>0.2187</v>
+      </c>
     </row>
     <row r="382" ht="16" customHeight="1" s="8">
       <c r="A382" s="5" t="n">
@@ -23855,6 +24905,9 @@
       <c r="AB382" t="n">
         <v>0.0849</v>
       </c>
+      <c r="AC382" t="n">
+        <v>0.2221</v>
+      </c>
     </row>
     <row r="383" ht="16" customHeight="1" s="8">
       <c r="A383" s="5" t="n">
@@ -23917,6 +24970,9 @@
       <c r="AB383" t="n">
         <v>0.0698</v>
       </c>
+      <c r="AC383" t="n">
+        <v>0.2112</v>
+      </c>
     </row>
     <row r="384" ht="16" customHeight="1" s="8">
       <c r="A384" s="5" t="n">
@@ -23979,6 +25035,9 @@
       <c r="AB384" t="n">
         <v>0.06950000000000001</v>
       </c>
+      <c r="AC384" t="n">
+        <v>0.2726</v>
+      </c>
     </row>
     <row r="385" ht="16" customHeight="1" s="8">
       <c r="A385" s="5" t="n">
@@ -24041,6 +25100,9 @@
       <c r="AB385" t="n">
         <v>0.07779999999999999</v>
       </c>
+      <c r="AC385" t="n">
+        <v>0.2032</v>
+      </c>
     </row>
     <row r="386" ht="16" customHeight="1" s="8">
       <c r="A386" s="5" t="n">
@@ -24103,6 +25165,9 @@
       <c r="AB386" t="n">
         <v>0.0497</v>
       </c>
+      <c r="AC386" t="n">
+        <v>0.2444</v>
+      </c>
     </row>
     <row r="387" ht="16" customHeight="1" s="8">
       <c r="A387" s="5" t="n">
@@ -24165,6 +25230,9 @@
       <c r="AB387" t="n">
         <v>0.0494</v>
       </c>
+      <c r="AC387" t="n">
+        <v>0.2356</v>
+      </c>
     </row>
     <row r="388" ht="16" customHeight="1" s="8">
       <c r="A388" s="5" t="n">
@@ -24227,6 +25295,9 @@
       <c r="AB388" t="n">
         <v>0.0606</v>
       </c>
+      <c r="AC388" t="n">
+        <v>0.2194</v>
+      </c>
     </row>
     <row r="389" ht="16" customHeight="1" s="8">
       <c r="A389" s="5" t="n">
@@ -24289,6 +25360,9 @@
       <c r="AB389" t="n">
         <v>0.0716</v>
       </c>
+      <c r="AC389" t="n">
+        <v>0.2235</v>
+      </c>
     </row>
     <row r="390" ht="16" customHeight="1" s="8">
       <c r="A390" s="5" t="n">
@@ -24351,6 +25425,9 @@
       <c r="AB390" t="n">
         <v>0.0549</v>
       </c>
+      <c r="AC390" t="n">
+        <v>0.226</v>
+      </c>
     </row>
     <row r="391" ht="16" customHeight="1" s="8">
       <c r="A391" s="5" t="n">
@@ -24413,6 +25490,9 @@
       <c r="AB391" t="n">
         <v>0.0622</v>
       </c>
+      <c r="AC391" t="n">
+        <v>0.2157</v>
+      </c>
     </row>
     <row r="392" ht="16" customHeight="1" s="8">
       <c r="A392" s="5" t="n">
@@ -24475,6 +25555,9 @@
       <c r="AB392" t="n">
         <v>0.0587</v>
       </c>
+      <c r="AC392" t="n">
+        <v>0.2336</v>
+      </c>
     </row>
     <row r="393" ht="16" customHeight="1" s="8">
       <c r="A393" s="5" t="n">
@@ -24537,6 +25620,9 @@
       <c r="AB393" t="n">
         <v>0.0709</v>
       </c>
+      <c r="AC393" t="n">
+        <v>0.232</v>
+      </c>
     </row>
     <row r="394" ht="16" customHeight="1" s="8">
       <c r="A394" s="5" t="n">
@@ -24599,6 +25685,9 @@
       <c r="AB394" t="n">
         <v>0.06909999999999999</v>
       </c>
+      <c r="AC394" t="n">
+        <v>0.2388</v>
+      </c>
     </row>
     <row r="395" ht="16" customHeight="1" s="8">
       <c r="A395" s="5" t="n">
@@ -24661,6 +25750,9 @@
       <c r="AB395" t="n">
         <v>0.0677</v>
       </c>
+      <c r="AC395" t="n">
+        <v>0.2506</v>
+      </c>
     </row>
     <row r="396" ht="16" customHeight="1" s="8">
       <c r="A396" s="5" t="n">
@@ -24723,6 +25815,9 @@
       <c r="AB396" t="n">
         <v>0.0601</v>
       </c>
+      <c r="AC396" t="n">
+        <v>0.2643</v>
+      </c>
     </row>
     <row r="397" ht="16" customHeight="1" s="8">
       <c r="A397" s="5" t="n">
@@ -24785,6 +25880,9 @@
       <c r="AB397" t="n">
         <v>0.0712</v>
       </c>
+      <c r="AC397" t="n">
+        <v>0.2382</v>
+      </c>
     </row>
     <row r="398" ht="16" customHeight="1" s="8">
       <c r="A398" s="5" t="n">
@@ -24847,6 +25945,9 @@
       <c r="AB398" t="n">
         <v>0.0737</v>
       </c>
+      <c r="AC398" t="n">
+        <v>0.2418</v>
+      </c>
     </row>
     <row r="399" ht="16" customHeight="1" s="8">
       <c r="A399" s="5" t="n">
@@ -24909,6 +26010,9 @@
       <c r="AB399" t="n">
         <v>0.0648</v>
       </c>
+      <c r="AC399" t="n">
+        <v>0.2329</v>
+      </c>
     </row>
     <row r="400" ht="16" customHeight="1" s="8">
       <c r="A400" s="5" t="n">
@@ -24971,6 +26075,9 @@
       <c r="AB400" t="n">
         <v>0.0677</v>
       </c>
+      <c r="AC400" t="n">
+        <v>0.2705</v>
+      </c>
     </row>
     <row r="401" ht="16" customHeight="1" s="8">
       <c r="A401" s="5" t="n">
@@ -25033,6 +26140,9 @@
       <c r="AB401" t="n">
         <v>0.07149999999999999</v>
       </c>
+      <c r="AC401" t="n">
+        <v>0.3021</v>
+      </c>
     </row>
     <row r="402" ht="16" customHeight="1" s="8">
       <c r="A402" s="5" t="n">
@@ -25095,6 +26205,9 @@
       <c r="AB402" t="n">
         <v>0.0882</v>
       </c>
+      <c r="AC402" t="n">
+        <v>0.2261</v>
+      </c>
     </row>
     <row r="403" ht="16" customHeight="1" s="8">
       <c r="A403" s="5" t="n">
@@ -25157,6 +26270,9 @@
       <c r="AB403" t="n">
         <v>0.0851</v>
       </c>
+      <c r="AC403" t="n">
+        <v>0.1723</v>
+      </c>
     </row>
     <row r="404" ht="16" customHeight="1" s="8">
       <c r="A404" s="5" t="n">
@@ -25219,6 +26335,9 @@
       <c r="AB404" t="n">
         <v>0.06569999999999999</v>
       </c>
+      <c r="AC404" t="n">
+        <v>0.2499</v>
+      </c>
     </row>
     <row r="405" ht="16" customHeight="1" s="8">
       <c r="A405" s="5" t="n">
@@ -25281,6 +26400,9 @@
       <c r="AB405" t="n">
         <v>0.0815</v>
       </c>
+      <c r="AC405" t="n">
+        <v>0.2403</v>
+      </c>
     </row>
     <row r="406" ht="16" customHeight="1" s="8">
       <c r="A406" s="5" t="n">
@@ -25343,6 +26465,9 @@
       <c r="AB406" t="n">
         <v>0.0623</v>
       </c>
+      <c r="AC406" t="n">
+        <v>0.2287</v>
+      </c>
     </row>
     <row r="407" ht="16" customHeight="1" s="8">
       <c r="A407" s="5" t="n">
@@ -25405,6 +26530,9 @@
       <c r="AB407" t="n">
         <v>0.0759</v>
       </c>
+      <c r="AC407" t="n">
+        <v>0.184</v>
+      </c>
     </row>
     <row r="408" ht="16" customHeight="1" s="8">
       <c r="A408" s="5" t="n">
@@ -25467,6 +26595,9 @@
       <c r="AB408" t="n">
         <v>0.07870000000000001</v>
       </c>
+      <c r="AC408" t="n">
+        <v>0.1672</v>
+      </c>
     </row>
     <row r="409" ht="16" customHeight="1" s="8">
       <c r="A409" s="5" t="n">
@@ -25529,6 +26660,9 @@
       <c r="AB409" t="n">
         <v>0.0732</v>
       </c>
+      <c r="AC409" t="n">
+        <v>0.216</v>
+      </c>
     </row>
     <row r="410" ht="16" customHeight="1" s="8">
       <c r="A410" s="5" t="n">
@@ -25591,6 +26725,9 @@
       <c r="AB410" t="n">
         <v>0.07240000000000001</v>
       </c>
+      <c r="AC410" t="n">
+        <v>0.2245</v>
+      </c>
     </row>
     <row r="411" ht="16" customHeight="1" s="8">
       <c r="A411" s="5" t="n">
@@ -25653,6 +26790,9 @@
       <c r="AB411" t="n">
         <v>0.08799999999999999</v>
       </c>
+      <c r="AC411" t="n">
+        <v>0.2363</v>
+      </c>
     </row>
     <row r="412" ht="16" customHeight="1" s="8">
       <c r="A412" s="5" t="n">
@@ -25715,6 +26855,9 @@
       <c r="AB412" t="n">
         <v>0.0593</v>
       </c>
+      <c r="AC412" t="n">
+        <v>0.1994</v>
+      </c>
     </row>
     <row r="413" ht="16" customHeight="1" s="8">
       <c r="A413" s="5" t="n">
@@ -25777,6 +26920,9 @@
       <c r="AB413" t="n">
         <v>0.0718</v>
       </c>
+      <c r="AC413" t="n">
+        <v>0.2372</v>
+      </c>
     </row>
     <row r="414" ht="16" customHeight="1" s="8">
       <c r="A414" s="5" t="n">
@@ -25839,6 +26985,9 @@
       <c r="AB414" t="n">
         <v>0.0757</v>
       </c>
+      <c r="AC414" t="n">
+        <v>0.2534</v>
+      </c>
     </row>
     <row r="415" ht="16" customHeight="1" s="8">
       <c r="A415" s="5" t="n">
@@ -25900,6 +27049,9 @@
       </c>
       <c r="AB415" t="n">
         <v>0.06320000000000001</v>
+      </c>
+      <c r="AC415" t="n">
+        <v>0.2301</v>
       </c>
     </row>
     <row r="416">
@@ -26132,6 +27284,9 @@
       <c r="AB422" t="n">
         <v>0.2463125</v>
       </c>
+      <c r="AC422" t="n">
+        <v>0.2825545454545454</v>
+      </c>
     </row>
     <row r="423">
       <c r="H423" s="5" t="n">
@@ -26173,6 +27328,9 @@
       <c r="AB423" t="n">
         <v>0.3504888888888888</v>
       </c>
+      <c r="AC423" t="n">
+        <v>0.2945888888888889</v>
+      </c>
     </row>
     <row r="424">
       <c r="H424" s="5" t="n">
@@ -26214,6 +27372,9 @@
       <c r="AB424" t="n">
         <v>0.3586111111111111</v>
       </c>
+      <c r="AC424" t="n">
+        <v>0.3743428571428571</v>
+      </c>
     </row>
     <row r="425">
       <c r="H425" s="5" t="n">
@@ -26255,6 +27416,9 @@
       <c r="AB425" t="n">
         <v>0.38989</v>
       </c>
+      <c r="AC425" t="n">
+        <v>0.39163</v>
+      </c>
     </row>
     <row r="426">
       <c r="H426" s="5" t="n">
@@ -26296,6 +27460,9 @@
       <c r="AB426" t="n">
         <v>0.45862</v>
       </c>
+      <c r="AC426" t="n">
+        <v>0.41951</v>
+      </c>
     </row>
     <row r="427">
       <c r="H427" s="5" t="n">
@@ -26337,6 +27504,9 @@
       <c r="AB427" t="n">
         <v>0.4329625</v>
       </c>
+      <c r="AC427" t="n">
+        <v>0.5502999999999999</v>
+      </c>
     </row>
     <row r="428">
       <c r="H428" s="5" t="n">
@@ -26366,6 +27536,9 @@
       <c r="AB428" t="n">
         <v>0.4788777777777777</v>
       </c>
+      <c r="AC428" t="n">
+        <v>0.4633545454545455</v>
+      </c>
     </row>
     <row r="429">
       <c r="H429" s="5" t="n">
@@ -26398,6 +27571,9 @@
       <c r="AB429" t="n">
         <v>0.5476818181818182</v>
       </c>
+      <c r="AC429" t="n">
+        <v>0.5069100000000001</v>
+      </c>
     </row>
     <row r="430">
       <c r="H430" s="5" t="n">
@@ -26430,6 +27606,9 @@
       <c r="AB430" t="n">
         <v>0.5440222222222223</v>
       </c>
+      <c r="AC430" t="n">
+        <v>0.6112818181818181</v>
+      </c>
     </row>
     <row r="431">
       <c r="H431" s="5" t="n">
@@ -26462,6 +27641,9 @@
       <c r="AB431" t="n">
         <v>0.5485111111111112</v>
       </c>
+      <c r="AC431" t="n">
+        <v>0.6110384615384615</v>
+      </c>
     </row>
     <row r="432">
       <c r="H432" s="5" t="n">
@@ -26494,6 +27676,9 @@
       <c r="AB432" t="n">
         <v>0.6080699999999999</v>
       </c>
+      <c r="AC432" t="n">
+        <v>0.6088636363636364</v>
+      </c>
     </row>
     <row r="433">
       <c r="H433" s="5" t="n">
@@ -26526,6 +27711,9 @@
       <c r="AB433" t="n">
         <v>0.58855</v>
       </c>
+      <c r="AC433" t="n">
+        <v>0.6194916666666667</v>
+      </c>
     </row>
     <row r="434">
       <c r="H434" s="5" t="n">
@@ -26558,6 +27746,9 @@
       <c r="AB434" t="n">
         <v>0.6215444444444445</v>
       </c>
+      <c r="AC434" t="n">
+        <v>0.6226111111111111</v>
+      </c>
     </row>
     <row r="435">
       <c r="H435" s="5" t="n">
@@ -26590,6 +27781,9 @@
       <c r="AB435" t="n">
         <v>0.5857833333333333</v>
       </c>
+      <c r="AC435" t="n">
+        <v>0.6300833333333332</v>
+      </c>
     </row>
     <row r="436">
       <c r="H436" s="5" t="n">
@@ -26622,6 +27816,9 @@
       <c r="AB436" t="n">
         <v>0.6111333333333334</v>
       </c>
+      <c r="AC436" t="n">
+        <v>0.6258909090909091</v>
+      </c>
     </row>
     <row r="437">
       <c r="H437" s="5" t="n">
@@ -26654,6 +27851,9 @@
       <c r="AB437" t="n">
         <v>0.6626833333333334</v>
       </c>
+      <c r="AC437" t="n">
+        <v>0.591025</v>
+      </c>
     </row>
     <row r="438">
       <c r="H438" s="5" t="n">
@@ -26686,6 +27886,9 @@
       <c r="AB438" t="n">
         <v>0.7265181818181818</v>
       </c>
+      <c r="AC438" t="n">
+        <v>0.6619666666666667</v>
+      </c>
     </row>
     <row r="439">
       <c r="H439" s="5" t="n">
@@ -26718,6 +27921,9 @@
       <c r="AB439" t="n">
         <v>0.57873</v>
       </c>
+      <c r="AC439" t="n">
+        <v>0.6757230769230771</v>
+      </c>
     </row>
     <row r="440">
       <c r="H440" s="5" t="n">
@@ -26750,6 +27956,9 @@
       <c r="AB440" t="n">
         <v>0.5887875</v>
       </c>
+      <c r="AC440" t="n">
+        <v>0.6185090909090909</v>
+      </c>
     </row>
     <row r="441">
       <c r="H441" s="5" t="n">
@@ -26782,6 +27991,9 @@
       <c r="AB441" t="n">
         <v>0.5946400000000001</v>
       </c>
+      <c r="AC441" t="n">
+        <v>0.6336777777777778</v>
+      </c>
     </row>
     <row r="442">
       <c r="H442" s="5" t="n">
@@ -26814,6 +28026,9 @@
       <c r="AB442" t="n">
         <v>0.6194999999999999</v>
       </c>
+      <c r="AC442" t="n">
+        <v>0.6481636363636364</v>
+      </c>
     </row>
     <row r="443">
       <c r="H443" s="5" t="n">
@@ -26846,6 +28061,9 @@
       <c r="AB443" t="n">
         <v>0.66425</v>
       </c>
+      <c r="AC443" t="n">
+        <v>0.68449</v>
+      </c>
     </row>
     <row r="444">
       <c r="H444" s="5" t="n">
@@ -26878,6 +28096,9 @@
       <c r="AB444" t="n">
         <v>0.67204</v>
       </c>
+      <c r="AC444" t="n">
+        <v>0.6728307692307692</v>
+      </c>
     </row>
     <row r="445">
       <c r="H445" s="5" t="n">
@@ -26910,6 +28131,9 @@
       <c r="AB445" t="n">
         <v>0.6517272727272728</v>
       </c>
+      <c r="AC445" t="n">
+        <v>0.6218615384615386</v>
+      </c>
     </row>
     <row r="446">
       <c r="H446" s="5" t="n">
@@ -26942,6 +28166,9 @@
       <c r="AB446" t="n">
         <v>0.6582444444444444</v>
       </c>
+      <c r="AC446" t="n">
+        <v>0.6355299999999999</v>
+      </c>
     </row>
     <row r="447">
       <c r="H447" s="5" t="n">
@@ -26974,6 +28201,9 @@
       <c r="AB447" t="n">
         <v>0.6647999999999999</v>
       </c>
+      <c r="AC447" t="n">
+        <v>0.62498</v>
+      </c>
     </row>
     <row r="448">
       <c r="H448" s="5" t="n">
@@ -27006,6 +28236,9 @@
       <c r="AB448" t="n">
         <v>0.7194750000000001</v>
       </c>
+      <c r="AC448" t="n">
+        <v>0.7292625</v>
+      </c>
     </row>
     <row r="449">
       <c r="H449" s="5" t="n">
@@ -27038,6 +28271,9 @@
       <c r="AB449" t="n">
         <v>0.7014777777777778</v>
       </c>
+      <c r="AC449" t="n">
+        <v>0.6859625</v>
+      </c>
     </row>
     <row r="450">
       <c r="H450" s="5" t="n">
@@ -27067,6 +28303,9 @@
       <c r="AB450" t="n">
         <v>0.6422</v>
       </c>
+      <c r="AC450" t="n">
+        <v>0.6300909090909091</v>
+      </c>
     </row>
     <row r="451">
       <c r="H451" s="5" t="n">
@@ -27099,6 +28338,9 @@
       <c r="AB451" t="n">
         <v>0.63023</v>
       </c>
+      <c r="AC451" t="n">
+        <v>0.7466666666666667</v>
+      </c>
     </row>
     <row r="452">
       <c r="H452" s="5" t="n">
@@ -27131,6 +28373,9 @@
       <c r="AB452" t="n">
         <v>0.6449181818181817</v>
       </c>
+      <c r="AC452" t="n">
+        <v>0.66817</v>
+      </c>
     </row>
     <row r="453">
       <c r="H453" s="5" t="n">
@@ -27160,6 +28405,9 @@
       <c r="AB453" t="n">
         <v>0.6359833333333332</v>
       </c>
+      <c r="AC453" t="n">
+        <v>0.6806999999999999</v>
+      </c>
     </row>
     <row r="454">
       <c r="H454" s="5" t="n">
@@ -27192,6 +28440,9 @@
       <c r="AB454" t="n">
         <v>0.6783857142857144</v>
       </c>
+      <c r="AC454" t="n">
+        <v>0.6747299999999999</v>
+      </c>
     </row>
     <row r="455">
       <c r="H455" s="5" t="n">
@@ -27224,6 +28475,9 @@
       <c r="AB455" t="n">
         <v>0.6874999999999999</v>
       </c>
+      <c r="AC455" t="n">
+        <v>0.6295083333333332</v>
+      </c>
     </row>
     <row r="456">
       <c r="H456" s="5" t="n">
@@ -27256,6 +28510,9 @@
       <c r="AB456" t="n">
         <v>0.7225454545454546</v>
       </c>
+      <c r="AC456" t="n">
+        <v>0.6647909090909091</v>
+      </c>
     </row>
     <row r="457">
       <c r="H457" s="5" t="n">
@@ -27288,6 +28545,9 @@
       <c r="AB457" t="n">
         <v>0.7101875</v>
       </c>
+      <c r="AC457" t="n">
+        <v>0.7308090909090909</v>
+      </c>
     </row>
     <row r="458">
       <c r="H458" s="5" t="n">
@@ -27320,6 +28580,9 @@
       <c r="AB458" t="n">
         <v>0.5951666666666666</v>
       </c>
+      <c r="AC458" t="n">
+        <v>0.7065900000000001</v>
+      </c>
     </row>
     <row r="459">
       <c r="H459" s="5" t="n">
@@ -27352,6 +28615,9 @@
       <c r="AB459" t="n">
         <v>0.59263</v>
       </c>
+      <c r="AC459" t="n">
+        <v>0.6377166666666666</v>
+      </c>
     </row>
     <row r="460">
       <c r="H460" s="5" t="n">
@@ -27384,6 +28650,9 @@
       <c r="AB460" t="n">
         <v>0.6884999999999999</v>
       </c>
+      <c r="AC460" t="n">
+        <v>0.6746444444444445</v>
+      </c>
     </row>
     <row r="461">
       <c r="H461" s="5" t="n">
@@ -27416,6 +28685,9 @@
       <c r="AB461" t="n">
         <v>0.5920153846153846</v>
       </c>
+      <c r="AC461" t="n">
+        <v>0.6575222222222221</v>
+      </c>
     </row>
     <row r="462">
       <c r="H462" s="5" t="n">
@@ -27448,6 +28720,9 @@
       <c r="AB462" t="n">
         <v>0.67069</v>
       </c>
+      <c r="AC462" t="n">
+        <v>0.631225</v>
+      </c>
     </row>
     <row r="463">
       <c r="H463" s="5" t="n">
@@ -27480,6 +28755,9 @@
       <c r="AB463" t="n">
         <v>0.6010545454545454</v>
       </c>
+      <c r="AC463" t="n">
+        <v>0.6227999999999999</v>
+      </c>
     </row>
     <row r="464">
       <c r="H464" s="5" t="n">
@@ -27512,6 +28790,9 @@
       <c r="AB464" t="n">
         <v>0.65249</v>
       </c>
+      <c r="AC464" t="n">
+        <v>0.70076</v>
+      </c>
     </row>
     <row r="465">
       <c r="H465" s="5" t="n">
@@ -27544,6 +28825,9 @@
       <c r="AB465" t="n">
         <v>0.6362181818181818</v>
       </c>
+      <c r="AC465" t="n">
+        <v>0.7426571428571428</v>
+      </c>
     </row>
     <row r="466">
       <c r="H466" s="5" t="n">
@@ -27576,6 +28860,9 @@
       <c r="AB466" t="n">
         <v>0.7072222222222223</v>
       </c>
+      <c r="AC466" t="n">
+        <v>0.62868</v>
+      </c>
     </row>
     <row r="467">
       <c r="H467" s="5" t="n">
@@ -27608,6 +28895,9 @@
       <c r="AB467" t="n">
         <v>0.60287</v>
       </c>
+      <c r="AC467" t="n">
+        <v>0.6145999999999999</v>
+      </c>
     </row>
     <row r="468">
       <c r="H468" s="5" t="n">
@@ -27640,6 +28930,9 @@
       <c r="AB468" t="n">
         <v>0.6426666666666666</v>
       </c>
+      <c r="AC468" t="n">
+        <v>0.670046153846154</v>
+      </c>
     </row>
     <row r="469">
       <c r="H469" s="5" t="n">
@@ -27672,6 +28965,9 @@
       <c r="AB469" t="n">
         <v>0.5769769230769231</v>
       </c>
+      <c r="AC469" t="n">
+        <v>0.6443692307692308</v>
+      </c>
     </row>
     <row r="470">
       <c r="H470" s="5" t="n">
@@ -27704,6 +29000,9 @@
       <c r="AB470" t="n">
         <v>0.572125</v>
       </c>
+      <c r="AC470" t="n">
+        <v>0.6477615384615386</v>
+      </c>
     </row>
     <row r="471">
       <c r="H471" s="5" t="n">
@@ -27736,6 +29035,9 @@
       <c r="AB471" t="n">
         <v>0.58383</v>
       </c>
+      <c r="AC471" t="n">
+        <v>0.71028</v>
+      </c>
     </row>
     <row r="472">
       <c r="H472" s="5" t="n">
@@ -27768,6 +29070,9 @@
       <c r="AB472" t="n">
         <v>0.6255555555555556</v>
       </c>
+      <c r="AC472" t="n">
+        <v>0.7052909090909091</v>
+      </c>
     </row>
     <row r="473">
       <c r="H473" s="5" t="n">
@@ -27800,6 +29105,9 @@
       <c r="AB473" t="n">
         <v>0.7355777777777779</v>
       </c>
+      <c r="AC473" t="n">
+        <v>0.6906499999999999</v>
+      </c>
     </row>
     <row r="474">
       <c r="H474" s="5" t="n">
@@ -27832,6 +29140,9 @@
       <c r="AB474" t="n">
         <v>0.596988888888889</v>
       </c>
+      <c r="AC474" t="n">
+        <v>0.7107250000000001</v>
+      </c>
     </row>
     <row r="475">
       <c r="H475" s="5" t="n">
@@ -27864,6 +29175,9 @@
       <c r="AB475" t="n">
         <v>0.6927545454545455</v>
       </c>
+      <c r="AC475" t="n">
+        <v>0.5992599999999999</v>
+      </c>
     </row>
     <row r="476">
       <c r="H476" s="5" t="n">
@@ -27896,6 +29210,9 @@
       <c r="AB476" t="n">
         <v>0.5732200000000001</v>
       </c>
+      <c r="AC476" t="n">
+        <v>0.6731857142857144</v>
+      </c>
     </row>
     <row r="477">
       <c r="H477" s="5" t="n">
@@ -27928,6 +29245,9 @@
       <c r="AB477" t="n">
         <v>0.67231</v>
       </c>
+      <c r="AC477" t="n">
+        <v>0.6505153846153846</v>
+      </c>
     </row>
     <row r="478">
       <c r="H478" s="5" t="n">
@@ -27960,6 +29280,9 @@
       <c r="AB478" t="n">
         <v>0.6679749999999999</v>
       </c>
+      <c r="AC478" t="n">
+        <v>0.6317999999999999</v>
+      </c>
     </row>
     <row r="479">
       <c r="H479" s="5" t="n">
@@ -27992,6 +29315,9 @@
       <c r="AB479" t="n">
         <v>0.6657000000000001</v>
       </c>
+      <c r="AC479" t="n">
+        <v>0.6861090909090909</v>
+      </c>
     </row>
     <row r="480">
       <c r="H480" s="5" t="n">
@@ -28024,6 +29350,9 @@
       <c r="AB480" t="n">
         <v>0.6530555555555556</v>
       </c>
+      <c r="AC480" t="n">
+        <v>0.6335</v>
+      </c>
     </row>
     <row r="481">
       <c r="H481" s="5" t="n">
@@ -28056,6 +29385,9 @@
       <c r="AB481" t="n">
         <v>0.6001222222222222</v>
       </c>
+      <c r="AC481" t="n">
+        <v>0.6945777777777778</v>
+      </c>
     </row>
     <row r="482">
       <c r="H482" s="5" t="n">
@@ -28088,6 +29420,9 @@
       <c r="AB482" t="n">
         <v>0.657490909090909</v>
       </c>
+      <c r="AC482" t="n">
+        <v>0.67079</v>
+      </c>
     </row>
     <row r="483">
       <c r="H483" s="5" t="n">
@@ -28120,6 +29455,9 @@
       <c r="AB483" t="n">
         <v>0.6869818181818181</v>
       </c>
+      <c r="AC483" t="n">
+        <v>0.7135444444444444</v>
+      </c>
     </row>
     <row r="484">
       <c r="H484" s="5" t="n">
@@ -28152,6 +29490,9 @@
       <c r="AB484" t="n">
         <v>0.69135</v>
       </c>
+      <c r="AC484" t="n">
+        <v>0.6470899999999999</v>
+      </c>
     </row>
     <row r="485">
       <c r="H485" s="5" t="n">
@@ -28184,6 +29525,9 @@
       <c r="AB485" t="n">
         <v>0.6421444444444444</v>
       </c>
+      <c r="AC485" t="n">
+        <v>0.6208090909090909</v>
+      </c>
     </row>
     <row r="486">
       <c r="H486" s="5" t="n">
@@ -28216,6 +29560,9 @@
       <c r="AB486" t="n">
         <v>0.6169875</v>
       </c>
+      <c r="AC486" t="n">
+        <v>0.6831545454545455</v>
+      </c>
     </row>
     <row r="487">
       <c r="H487" s="5" t="n">
@@ -28248,6 +29595,9 @@
       <c r="AB487" t="n">
         <v>0.6336000000000001</v>
       </c>
+      <c r="AC487" t="n">
+        <v>0.7086230769230769</v>
+      </c>
     </row>
     <row r="488">
       <c r="H488" s="5" t="n">
@@ -28280,6 +29630,9 @@
       <c r="AB488" t="n">
         <v>0.6075333333333334</v>
       </c>
+      <c r="AC488" t="n">
+        <v>0.6122727272727273</v>
+      </c>
     </row>
     <row r="489">
       <c r="H489" s="5" t="n">
@@ -28312,6 +29665,9 @@
       <c r="AB489" t="n">
         <v>0.5981727272727272</v>
       </c>
+      <c r="AC489" t="n">
+        <v>0.6919099999999999</v>
+      </c>
     </row>
     <row r="490">
       <c r="H490" s="5" t="n">
@@ -28344,6 +29700,9 @@
       <c r="AB490" t="n">
         <v>0.6459999999999999</v>
       </c>
+      <c r="AC490" t="n">
+        <v>0.6508125</v>
+      </c>
     </row>
     <row r="491">
       <c r="H491" s="5" t="n">
@@ -28373,6 +29732,9 @@
       <c r="AB491" t="n">
         <v>0.6707090909090909</v>
       </c>
+      <c r="AC491" t="n">
+        <v>0.6692555555555555</v>
+      </c>
     </row>
     <row r="492">
       <c r="H492" s="5" t="n">
@@ -28405,6 +29767,9 @@
       <c r="AB492" t="n">
         <v>0.5537166666666666</v>
       </c>
+      <c r="AC492" t="n">
+        <v>0.6859599999999999</v>
+      </c>
     </row>
     <row r="493">
       <c r="H493" s="5" t="n">
@@ -28437,6 +29802,9 @@
       <c r="AB493" t="n">
         <v>0.6687</v>
       </c>
+      <c r="AC493" t="n">
+        <v>0.6544727272727272</v>
+      </c>
     </row>
     <row r="494">
       <c r="H494" s="5" t="n">
@@ -28469,6 +29837,9 @@
       <c r="AB494" t="n">
         <v>0.5714666666666666</v>
       </c>
+      <c r="AC494" t="n">
+        <v>0.7038749999999999</v>
+      </c>
     </row>
     <row r="495">
       <c r="H495" s="5" t="n">
@@ -28501,6 +29872,9 @@
       <c r="AB495" t="n">
         <v>0.71056</v>
       </c>
+      <c r="AC495" t="n">
+        <v>0.6908499999999999</v>
+      </c>
     </row>
     <row r="496">
       <c r="H496" s="5" t="n">
@@ -28533,6 +29907,9 @@
       <c r="AB496" t="n">
         <v>0.65617</v>
       </c>
+      <c r="AC496" t="n">
+        <v>0.6450100000000001</v>
+      </c>
     </row>
     <row r="497">
       <c r="H497" s="5" t="n">
@@ -28565,6 +29942,9 @@
       <c r="AB497" t="n">
         <v>0.65998</v>
       </c>
+      <c r="AC497" t="n">
+        <v>0.7003000000000001</v>
+      </c>
     </row>
     <row r="498">
       <c r="H498" s="5" t="n">
@@ -28597,6 +29977,9 @@
       <c r="AB498" t="n">
         <v>0.7633749999999999</v>
       </c>
+      <c r="AC498" t="n">
+        <v>0.6149727272727272</v>
+      </c>
     </row>
     <row r="499">
       <c r="H499" s="5" t="n">
@@ -28629,6 +30012,9 @@
       <c r="AB499" t="n">
         <v>0.6127333333333334</v>
       </c>
+      <c r="AC499" t="n">
+        <v>0.592290909090909</v>
+      </c>
     </row>
     <row r="500">
       <c r="H500" s="5" t="n">
@@ -28661,6 +30047,9 @@
       <c r="AB500" t="n">
         <v>0.6565083333333334</v>
       </c>
+      <c r="AC500" t="n">
+        <v>0.5992166666666666</v>
+      </c>
     </row>
     <row r="501">
       <c r="H501" s="5" t="n">
@@ -28693,6 +30082,9 @@
       <c r="AB501" t="n">
         <v>0.58627</v>
       </c>
+      <c r="AC501" t="n">
+        <v>0.6273416666666666</v>
+      </c>
     </row>
     <row r="502">
       <c r="H502" s="5" t="n">
@@ -28725,6 +30117,9 @@
       <c r="AB502" t="n">
         <v>0.6197846153846154</v>
       </c>
+      <c r="AC502" t="n">
+        <v>0.6762214285714284</v>
+      </c>
     </row>
     <row r="503">
       <c r="H503" s="5" t="n">
@@ -28757,6 +30152,9 @@
       <c r="AB503" t="n">
         <v>0.6321583333333333</v>
       </c>
+      <c r="AC503" t="n">
+        <v>0.6226333333333334</v>
+      </c>
     </row>
     <row r="504">
       <c r="H504" s="5" t="n">
@@ -28789,6 +30187,9 @@
       <c r="AB504" t="n">
         <v>0.6656363636363637</v>
       </c>
+      <c r="AC504" t="n">
+        <v>0.6638000000000001</v>
+      </c>
     </row>
     <row r="505">
       <c r="H505" s="5" t="n">
@@ -28821,6 +30222,9 @@
       <c r="AB505" t="n">
         <v>0.6895666666666668</v>
       </c>
+      <c r="AC505" t="n">
+        <v>0.6990099999999999</v>
+      </c>
     </row>
     <row r="506">
       <c r="H506" s="5" t="n">
@@ -28853,6 +30257,9 @@
       <c r="AB506" t="n">
         <v>0.6207</v>
       </c>
+      <c r="AC506" t="n">
+        <v>0.6102916666666667</v>
+      </c>
     </row>
     <row r="507">
       <c r="H507" s="5" t="n">
@@ -28885,6 +30292,9 @@
       <c r="AB507" t="n">
         <v>0.6804909090909091</v>
       </c>
+      <c r="AC507" t="n">
+        <v>0.6316769230769231</v>
+      </c>
     </row>
     <row r="508">
       <c r="H508" s="5" t="n">
@@ -28917,6 +30327,9 @@
       <c r="AB508" t="n">
         <v>0.6789333333333334</v>
       </c>
+      <c r="AC508" t="n">
+        <v>0.6014700000000001</v>
+      </c>
     </row>
     <row r="509">
       <c r="H509" s="5" t="n">
@@ -28949,6 +30362,9 @@
       <c r="AB509" t="n">
         <v>0.6211222222222221</v>
       </c>
+      <c r="AC509" t="n">
+        <v>0.6811545454545453</v>
+      </c>
     </row>
     <row r="510">
       <c r="H510" s="5" t="n">
@@ -28981,6 +30397,9 @@
       <c r="AB510" t="n">
         <v>0.5927500000000001</v>
       </c>
+      <c r="AC510" t="n">
+        <v>0.6541555555555555</v>
+      </c>
     </row>
     <row r="511">
       <c r="H511" s="5" t="n">
@@ -29013,6 +30432,9 @@
       <c r="AB511" t="n">
         <v>0.5595666666666665</v>
       </c>
+      <c r="AC511" t="n">
+        <v>0.71183</v>
+      </c>
     </row>
     <row r="512">
       <c r="H512" s="5" t="n">
@@ -29045,6 +30467,9 @@
       <c r="AB512" t="n">
         <v>0.6197199999999999</v>
       </c>
+      <c r="AC512" t="n">
+        <v>0.6182300000000001</v>
+      </c>
     </row>
     <row r="513">
       <c r="H513" s="5" t="n">
@@ -29077,6 +30502,9 @@
       <c r="AB513" t="n">
         <v>0.57916</v>
       </c>
+      <c r="AC513" t="n">
+        <v>0.6813375</v>
+      </c>
     </row>
     <row r="514">
       <c r="H514" s="5" t="n">
@@ -29109,6 +30537,9 @@
       <c r="AB514" t="n">
         <v>0.62291</v>
       </c>
+      <c r="AC514" t="n">
+        <v>0.6289100000000001</v>
+      </c>
     </row>
     <row r="515">
       <c r="H515" s="5" t="n">
@@ -29141,6 +30572,9 @@
       <c r="AB515" t="n">
         <v>0.6862285714285715</v>
       </c>
+      <c r="AC515" t="n">
+        <v>0.6308166666666667</v>
+      </c>
     </row>
     <row r="516">
       <c r="H516" s="5" t="n">
@@ -29173,6 +30607,9 @@
       <c r="AB516" t="n">
         <v>0.7121818181818182</v>
       </c>
+      <c r="AC516" t="n">
+        <v>0.66883</v>
+      </c>
     </row>
     <row r="517">
       <c r="H517" s="5" t="n">
@@ -29204,6 +30641,9 @@
       </c>
       <c r="AB517" t="n">
         <v>0.7012636363636364</v>
+      </c>
+      <c r="AC517" t="n">
+        <v>0.6282272727272727</v>
       </c>
     </row>
     <row r="518">
@@ -29361,6 +30801,9 @@
       <c r="AB524" t="n">
         <v>0.3152666666666668</v>
       </c>
+      <c r="AC524" t="n">
+        <v>0.3114653846153846</v>
+      </c>
     </row>
     <row r="525">
       <c r="H525" s="5" t="n">
@@ -29387,6 +30830,9 @@
       <c r="AB525" t="n">
         <v>0.3486536585365854</v>
       </c>
+      <c r="AC525" t="n">
+        <v>0.320658064516129</v>
+      </c>
     </row>
     <row r="526">
       <c r="H526" s="5" t="n">
@@ -29413,6 +30859,9 @@
       <c r="AB526" t="n">
         <v>0.3898524999999999</v>
       </c>
+      <c r="AC526" t="n">
+        <v>0.3008333333333333</v>
+      </c>
     </row>
     <row r="527">
       <c r="H527" s="5" t="n">
@@ -29439,6 +30888,9 @@
       <c r="AB527" t="n">
         <v>0.4166302325581395</v>
       </c>
+      <c r="AC527" t="n">
+        <v>0.4534700000000001</v>
+      </c>
     </row>
     <row r="528">
       <c r="H528" s="5" t="n">
@@ -29465,6 +30917,9 @@
       <c r="AB528" t="n">
         <v>0.43698</v>
       </c>
+      <c r="AC528" t="n">
+        <v>0.473651282051282</v>
+      </c>
     </row>
     <row r="529">
       <c r="H529" s="5" t="n">
@@ -29491,6 +30946,9 @@
       <c r="AB529" t="n">
         <v>0.4151787234042553</v>
       </c>
+      <c r="AC529" t="n">
+        <v>0.385475</v>
+      </c>
     </row>
     <row r="530">
       <c r="H530" s="5" t="n">
@@ -29508,6 +30966,9 @@
       <c r="AB530" t="n">
         <v>0.4994232142857143</v>
       </c>
+      <c r="AC530" t="n">
+        <v>0.4202036363636363</v>
+      </c>
     </row>
     <row r="531">
       <c r="H531" s="5" t="n">
@@ -29525,6 +30986,9 @@
       <c r="AB531" t="n">
         <v>0.5372720930232557</v>
       </c>
+      <c r="AC531" t="n">
+        <v>0.4706806451612903</v>
+      </c>
     </row>
     <row r="532">
       <c r="H532" s="5" t="n">
@@ -29542,6 +31006,9 @@
       <c r="AB532" t="n">
         <v>0.3997775510204082</v>
       </c>
+      <c r="AC532" t="n">
+        <v>0.423764</v>
+      </c>
     </row>
     <row r="533">
       <c r="H533" s="5" t="n">
@@ -29559,6 +31026,9 @@
       <c r="AB533" t="n">
         <v>0.511645652173913</v>
       </c>
+      <c r="AC533" t="n">
+        <v>0.4927620689655172</v>
+      </c>
     </row>
     <row r="534">
       <c r="H534" s="5" t="n">
@@ -29576,6 +31046,9 @@
       <c r="AB534" t="n">
         <v>0.490327027027027</v>
       </c>
+      <c r="AC534" t="n">
+        <v>0.4340441176470589</v>
+      </c>
     </row>
     <row r="535">
       <c r="H535" s="5" t="n">
@@ -29593,6 +31066,9 @@
       <c r="AB535" t="n">
         <v>0.4960639344262295</v>
       </c>
+      <c r="AC535" t="n">
+        <v>0.4540571428571428</v>
+      </c>
     </row>
     <row r="536">
       <c r="H536" s="5" t="n">
@@ -29610,6 +31086,9 @@
       <c r="AB536" t="n">
         <v>0.5078483333333333</v>
       </c>
+      <c r="AC536" t="n">
+        <v>0.3857666666666667</v>
+      </c>
     </row>
     <row r="537">
       <c r="H537" s="5" t="n">
@@ -29627,6 +31106,9 @@
       <c r="AB537" t="n">
         <v>0.4695533333333333</v>
       </c>
+      <c r="AC537" t="n">
+        <v>0.4606111111111112</v>
+      </c>
     </row>
     <row r="538">
       <c r="H538" s="5" t="n">
@@ -29644,6 +31126,9 @@
       <c r="AB538" t="n">
         <v>0.4764275862068967</v>
       </c>
+      <c r="AC538" t="n">
+        <v>0.3950470588235294</v>
+      </c>
     </row>
     <row r="539">
       <c r="H539" s="5" t="n">
@@ -29661,6 +31146,9 @@
       <c r="AB539" t="n">
         <v>0.4946375</v>
       </c>
+      <c r="AC539" t="n">
+        <v>0.4576727272727272</v>
+      </c>
     </row>
     <row r="540">
       <c r="H540" s="5" t="n">
@@ -29678,6 +31166,9 @@
       <c r="AB540" t="n">
         <v>0.561448076923077</v>
       </c>
+      <c r="AC540" t="n">
+        <v>0.4830616666666667</v>
+      </c>
     </row>
     <row r="541">
       <c r="H541" s="5" t="n">
@@ -29695,6 +31186,9 @@
       <c r="AB541" t="n">
         <v>0.4783385964912281</v>
       </c>
+      <c r="AC541" t="n">
+        <v>0.4468162162162161</v>
+      </c>
     </row>
     <row r="542">
       <c r="H542" s="5" t="n">
@@ -29712,6 +31206,9 @@
       <c r="AB542" t="n">
         <v>0.5868846153846154</v>
       </c>
+      <c r="AC542" t="n">
+        <v>0.4251416666666667</v>
+      </c>
     </row>
     <row r="543">
       <c r="H543" s="5" t="n">
@@ -29729,6 +31226,9 @@
       <c r="AB543" t="n">
         <v>0.4964914893617021</v>
       </c>
+      <c r="AC543" t="n">
+        <v>0.4719418181818183</v>
+      </c>
     </row>
     <row r="544">
       <c r="H544" s="5" t="n">
@@ -29746,6 +31246,9 @@
       <c r="AB544" t="n">
         <v>0.5538814814814815</v>
       </c>
+      <c r="AC544" t="n">
+        <v>0.4258657894736842</v>
+      </c>
     </row>
     <row r="545">
       <c r="H545" s="5" t="n">
@@ -29763,6 +31266,9 @@
       <c r="AB545" t="n">
         <v>0.6367836734693878</v>
       </c>
+      <c r="AC545" t="n">
+        <v>0.5719</v>
+      </c>
     </row>
     <row r="546">
       <c r="H546" s="5" t="n">
@@ -29780,6 +31286,9 @@
       <c r="AB546" t="n">
         <v>0.5919727272727273</v>
       </c>
+      <c r="AC546" t="n">
+        <v>0.4884340425531914</v>
+      </c>
     </row>
     <row r="547">
       <c r="H547" s="5" t="n">
@@ -29797,6 +31306,9 @@
       <c r="AB547" t="n">
         <v>0.469259649122807</v>
       </c>
+      <c r="AC547" t="n">
+        <v>0.440151724137931</v>
+      </c>
     </row>
     <row r="548">
       <c r="H548" s="5" t="n">
@@ -29814,6 +31326,9 @@
       <c r="AB548" t="n">
         <v>0.5620295081967213</v>
       </c>
+      <c r="AC548" t="n">
+        <v>0.5954666666666666</v>
+      </c>
     </row>
     <row r="549">
       <c r="H549" s="5" t="n">
@@ -29831,6 +31346,9 @@
       <c r="AB549" t="n">
         <v>0.5043190476190476</v>
       </c>
+      <c r="AC549" t="n">
+        <v>0.5291627906976745</v>
+      </c>
     </row>
     <row r="550">
       <c r="H550" s="5" t="n">
@@ -29848,6 +31366,9 @@
       <c r="AB550" t="n">
         <v>0.4628245614035087</v>
       </c>
+      <c r="AC550" t="n">
+        <v>0.553379069767442</v>
+      </c>
     </row>
     <row r="551">
       <c r="H551" s="5" t="n">
@@ -29865,6 +31386,9 @@
       <c r="AB551" t="n">
         <v>0.5576653846153847</v>
       </c>
+      <c r="AC551" t="n">
+        <v>0.5229659574468085</v>
+      </c>
     </row>
     <row r="552">
       <c r="H552" s="5" t="n">
@@ -29882,6 +31406,9 @@
       <c r="AB552" t="n">
         <v>0.6387489795918367</v>
       </c>
+      <c r="AC552" t="n">
+        <v>0.4228833333333334</v>
+      </c>
     </row>
     <row r="553">
       <c r="H553" s="5" t="n">
@@ -29899,6 +31426,9 @@
       <c r="AB553" t="n">
         <v>0.6070470588235295</v>
       </c>
+      <c r="AC553" t="n">
+        <v>0.4439272727272728</v>
+      </c>
     </row>
     <row r="554">
       <c r="H554" s="5" t="n">
@@ -29916,6 +31446,9 @@
       <c r="AB554" t="n">
         <v>0.5745648648648649</v>
       </c>
+      <c r="AC554" t="n">
+        <v>0.4442618181818181</v>
+      </c>
     </row>
     <row r="555">
       <c r="H555" s="5" t="n">
@@ -29933,6 +31466,9 @@
       <c r="AB555" t="n">
         <v>0.5844453125</v>
       </c>
+      <c r="AC555" t="n">
+        <v>0.4640044776119404</v>
+      </c>
     </row>
     <row r="556">
       <c r="H556" s="5" t="n">
@@ -29950,6 +31486,9 @@
       <c r="AB556" t="n">
         <v>0.5178318181818183</v>
       </c>
+      <c r="AC556" t="n">
+        <v>0.4917359375</v>
+      </c>
     </row>
     <row r="557">
       <c r="H557" s="5" t="n">
@@ -29967,6 +31506,9 @@
       <c r="AB557" t="n">
         <v>0.4459767441860465</v>
       </c>
+      <c r="AC557" t="n">
+        <v>0.473854347826087</v>
+      </c>
     </row>
     <row r="558">
       <c r="H558" s="5" t="n">
@@ -29984,6 +31526,9 @@
       <c r="AB558" t="n">
         <v>0.5964063829787234</v>
       </c>
+      <c r="AC558" t="n">
+        <v>0.4933491525423728</v>
+      </c>
     </row>
     <row r="559">
       <c r="H559" s="5" t="n">
@@ -30001,6 +31546,9 @@
       <c r="AB559" t="n">
         <v>0.5159064516129033</v>
       </c>
+      <c r="AC559" t="n">
+        <v>0.4775265306122449</v>
+      </c>
     </row>
     <row r="560">
       <c r="H560" s="5" t="n">
@@ -30018,6 +31566,9 @@
       <c r="AB560" t="n">
         <v>0.5529733333333333</v>
       </c>
+      <c r="AC560" t="n">
+        <v>0.4505978260869566</v>
+      </c>
     </row>
     <row r="561">
       <c r="H561" s="5" t="n">
@@ -30035,6 +31586,9 @@
       <c r="AB561" t="n">
         <v>0.5286526315789474</v>
       </c>
+      <c r="AC561" t="n">
+        <v>0.5058844827586207</v>
+      </c>
     </row>
     <row r="562">
       <c r="H562" s="5" t="n">
@@ -30052,6 +31606,9 @@
       <c r="AB562" t="n">
         <v>0.572906</v>
       </c>
+      <c r="AC562" t="n">
+        <v>0.4639964912280703</v>
+      </c>
     </row>
     <row r="563">
       <c r="H563" s="5" t="n">
@@ -30069,6 +31626,9 @@
       <c r="AB563" t="n">
         <v>0.5864673913043479</v>
       </c>
+      <c r="AC563" t="n">
+        <v>0.5215610169491526</v>
+      </c>
     </row>
     <row r="564">
       <c r="H564" s="5" t="n">
@@ -30086,6 +31646,9 @@
       <c r="AB564" t="n">
         <v>0.4584102564102564</v>
       </c>
+      <c r="AC564" t="n">
+        <v>0.5012666666666667</v>
+      </c>
     </row>
     <row r="565">
       <c r="H565" s="5" t="n">
@@ -30103,6 +31666,9 @@
       <c r="AB565" t="n">
         <v>0.5261982456140351</v>
       </c>
+      <c r="AC565" t="n">
+        <v>0.5636481481481481</v>
+      </c>
     </row>
     <row r="566">
       <c r="H566" s="5" t="n">
@@ -30120,6 +31686,9 @@
       <c r="AB566" t="n">
         <v>0.4382428571428572</v>
       </c>
+      <c r="AC566" t="n">
+        <v>0.4845943396226415</v>
+      </c>
     </row>
     <row r="567">
       <c r="H567" s="5" t="n">
@@ -30137,6 +31706,9 @@
       <c r="AB567" t="n">
         <v>0.5711068965517241</v>
       </c>
+      <c r="AC567" t="n">
+        <v>0.5870885245901639</v>
+      </c>
     </row>
     <row r="568">
       <c r="H568" s="5" t="n">
@@ -30154,6 +31726,9 @@
       <c r="AB568" t="n">
         <v>0.6823121951219512</v>
       </c>
+      <c r="AC568" t="n">
+        <v>0.4556418181818181</v>
+      </c>
     </row>
     <row r="569">
       <c r="H569" s="5" t="n">
@@ -30171,6 +31746,9 @@
       <c r="AB569" t="n">
         <v>0.5570901960784314</v>
       </c>
+      <c r="AC569" t="n">
+        <v>0.4760230769230769</v>
+      </c>
     </row>
     <row r="570">
       <c r="H570" s="5" t="n">
@@ -30188,6 +31766,9 @@
       <c r="AB570" t="n">
         <v>0.5068537037037039</v>
       </c>
+      <c r="AC570" t="n">
+        <v>0.4464396551724138</v>
+      </c>
     </row>
     <row r="571">
       <c r="H571" s="5" t="n">
@@ -30205,6 +31786,9 @@
       <c r="AB571" t="n">
         <v>0.4709666666666666</v>
       </c>
+      <c r="AC571" t="n">
+        <v>0.5016596491228071</v>
+      </c>
     </row>
     <row r="572">
       <c r="H572" s="5" t="n">
@@ -30222,6 +31806,9 @@
       <c r="AB572" t="n">
         <v>0.4669441860465117</v>
       </c>
+      <c r="AC572" t="n">
+        <v>0.5284846153846154</v>
+      </c>
     </row>
     <row r="573">
       <c r="H573" s="5" t="n">
@@ -30239,6 +31826,9 @@
       <c r="AB573" t="n">
         <v>0.5654952380952381</v>
       </c>
+      <c r="AC573" t="n">
+        <v>0.5577039215686276</v>
+      </c>
     </row>
     <row r="574">
       <c r="H574" s="5" t="n">
@@ -30256,6 +31846,9 @@
       <c r="AB574" t="n">
         <v>0.5409475409836066</v>
       </c>
+      <c r="AC574" t="n">
+        <v>0.4178051724137931</v>
+      </c>
     </row>
     <row r="575">
       <c r="H575" s="5" t="n">
@@ -30273,6 +31866,9 @@
       <c r="AB575" t="n">
         <v>0.5690542372881355</v>
       </c>
+      <c r="AC575" t="n">
+        <v>0.4079163265306122</v>
+      </c>
     </row>
     <row r="576">
       <c r="H576" s="5" t="n">
@@ -30290,6 +31886,9 @@
       <c r="AB576" t="n">
         <v>0.5787227272727272</v>
       </c>
+      <c r="AC576" t="n">
+        <v>0.4376264150943396</v>
+      </c>
     </row>
     <row r="577">
       <c r="H577" s="5" t="n">
@@ -30307,6 +31906,9 @@
       <c r="AB577" t="n">
         <v>0.5246318181818181</v>
       </c>
+      <c r="AC577" t="n">
+        <v>0.5301208333333333</v>
+      </c>
     </row>
     <row r="578">
       <c r="H578" s="5" t="n">
@@ -30324,6 +31926,9 @@
       <c r="AB578" t="n">
         <v>0.5935340425531915</v>
       </c>
+      <c r="AC578" t="n">
+        <v>0.4531745762711865</v>
+      </c>
     </row>
     <row r="579">
       <c r="H579" s="5" t="n">
@@ -30341,6 +31946,9 @@
       <c r="AB579" t="n">
         <v>0.4899475</v>
       </c>
+      <c r="AC579" t="n">
+        <v>0.441308510638298</v>
+      </c>
     </row>
     <row r="580">
       <c r="H580" s="5" t="n">
@@ -30358,6 +31966,9 @@
       <c r="AB580" t="n">
         <v>0.5196113636363636</v>
       </c>
+      <c r="AC580" t="n">
+        <v>0.4620152173913045</v>
+      </c>
     </row>
     <row r="581">
       <c r="H581" s="5" t="n">
@@ -30375,6 +31986,9 @@
       <c r="AB581" t="n">
         <v>0.5488625000000001</v>
       </c>
+      <c r="AC581" t="n">
+        <v>0.4210833333333333</v>
+      </c>
     </row>
     <row r="582">
       <c r="H582" s="5" t="n">
@@ -30392,6 +32006,9 @@
       <c r="AB582" t="n">
         <v>0.5066957446808511</v>
       </c>
+      <c r="AC582" t="n">
+        <v>0.4505561403508773</v>
+      </c>
     </row>
     <row r="583">
       <c r="H583" s="5" t="n">
@@ -30409,6 +32026,9 @@
       <c r="AB583" t="n">
         <v>0.5499617021276596</v>
       </c>
+      <c r="AC583" t="n">
+        <v>0.4776411764705882</v>
+      </c>
     </row>
     <row r="584">
       <c r="H584" s="5" t="n">
@@ -30426,6 +32046,9 @@
       <c r="AB584" t="n">
         <v>0.5476288135593221</v>
       </c>
+      <c r="AC584" t="n">
+        <v>0.4109849056603774</v>
+      </c>
     </row>
     <row r="585">
       <c r="H585" s="5" t="n">
@@ -30443,6 +32066,9 @@
       <c r="AB585" t="n">
         <v>0.5353051282051283</v>
       </c>
+      <c r="AC585" t="n">
+        <v>0.5089309523809524</v>
+      </c>
     </row>
     <row r="586">
       <c r="H586" s="5" t="n">
@@ -30460,6 +32086,9 @@
       <c r="AB586" t="n">
         <v>0.4998645833333333</v>
       </c>
+      <c r="AC586" t="n">
+        <v>0.4393166666666666</v>
+      </c>
     </row>
     <row r="587">
       <c r="H587" s="5" t="n">
@@ -30477,6 +32106,9 @@
       <c r="AB587" t="n">
         <v>0.5625863636363636</v>
       </c>
+      <c r="AC587" t="n">
+        <v>0.4491819672131148</v>
+      </c>
     </row>
     <row r="588">
       <c r="H588" s="5" t="n">
@@ -30494,6 +32126,9 @@
       <c r="AB588" t="n">
         <v>0.4317767441860466</v>
       </c>
+      <c r="AC588" t="n">
+        <v>0.5330923076923076</v>
+      </c>
     </row>
     <row r="589">
       <c r="H589" s="5" t="n">
@@ -30511,6 +32146,9 @@
       <c r="AB589" t="n">
         <v>0.52338</v>
       </c>
+      <c r="AC589" t="n">
+        <v>0.4170953125</v>
+      </c>
     </row>
     <row r="590">
       <c r="H590" s="5" t="n">
@@ -30528,6 +32166,9 @@
       <c r="AB590" t="n">
         <v>0.4071904761904762</v>
       </c>
+      <c r="AC590" t="n">
+        <v>0.4568477272727273</v>
+      </c>
     </row>
     <row r="591">
       <c r="H591" s="5" t="n">
@@ -30545,6 +32186,9 @@
       <c r="AB591" t="n">
         <v>0.5598306122448979</v>
       </c>
+      <c r="AC591" t="n">
+        <v>0.4356693877551022</v>
+      </c>
     </row>
     <row r="592">
       <c r="H592" s="5" t="n">
@@ -30562,6 +32206,9 @@
       <c r="AB592" t="n">
         <v>0.490809756097561</v>
       </c>
+      <c r="AC592" t="n">
+        <v>0.5417568181818182</v>
+      </c>
     </row>
     <row r="593">
       <c r="H593" s="5" t="n">
@@ -30579,6 +32226,9 @@
       <c r="AB593" t="n">
         <v>0.4760387755102042</v>
       </c>
+      <c r="AC593" t="n">
+        <v>0.5064277777777778</v>
+      </c>
     </row>
     <row r="594">
       <c r="H594" s="5" t="n">
@@ -30596,6 +32246,9 @@
       <c r="AB594" t="n">
         <v>0.4513539999999999</v>
       </c>
+      <c r="AC594" t="n">
+        <v>0.4637018867924528</v>
+      </c>
     </row>
     <row r="595">
       <c r="H595" s="5" t="n">
@@ -30613,6 +32266,9 @@
       <c r="AB595" t="n">
         <v>0.5368244444444444</v>
       </c>
+      <c r="AC595" t="n">
+        <v>0.4351666666666666</v>
+      </c>
     </row>
     <row r="596">
       <c r="H596" s="5" t="n">
@@ -30630,6 +32286,9 @@
       <c r="AB596" t="n">
         <v>0.4654106382978724</v>
       </c>
+      <c r="AC596" t="n">
+        <v>0.4903068181818183</v>
+      </c>
     </row>
     <row r="597">
       <c r="H597" s="5" t="n">
@@ -30647,6 +32306,9 @@
       <c r="AB597" t="n">
         <v>0.4997245283018869</v>
       </c>
+      <c r="AC597" t="n">
+        <v>0.4596080000000001</v>
+      </c>
     </row>
     <row r="598">
       <c r="H598" s="5" t="n">
@@ -30664,6 +32326,9 @@
       <c r="AB598" t="n">
         <v>0.4607326923076923</v>
       </c>
+      <c r="AC598" t="n">
+        <v>0.5123920000000001</v>
+      </c>
     </row>
     <row r="599">
       <c r="H599" s="5" t="n">
@@ -30681,6 +32346,9 @@
       <c r="AB599" t="n">
         <v>0.4825872340425533</v>
       </c>
+      <c r="AC599" t="n">
+        <v>0.5604883720930233</v>
+      </c>
     </row>
     <row r="600">
       <c r="H600" s="5" t="n">
@@ -30698,6 +32366,9 @@
       <c r="AB600" t="n">
         <v>0.4339749999999999</v>
       </c>
+      <c r="AC600" t="n">
+        <v>0.5573912280701754</v>
+      </c>
     </row>
     <row r="601">
       <c r="H601" s="5" t="n">
@@ -30715,6 +32386,9 @@
       <c r="AB601" t="n">
         <v>0.5613379310344828</v>
       </c>
+      <c r="AC601" t="n">
+        <v>0.4888222222222223</v>
+      </c>
     </row>
     <row r="602">
       <c r="H602" s="5" t="n">
@@ -30732,6 +32406,9 @@
       <c r="AB602" t="n">
         <v>0.4496911111111111</v>
       </c>
+      <c r="AC602" t="n">
+        <v>0.5167</v>
+      </c>
     </row>
     <row r="603">
       <c r="H603" s="5" t="n">
@@ -30749,6 +32426,9 @@
       <c r="AB603" t="n">
         <v>0.5440725490196079</v>
       </c>
+      <c r="AC603" t="n">
+        <v>0.4778945945945947</v>
+      </c>
     </row>
     <row r="604">
       <c r="H604" s="5" t="n">
@@ -30766,6 +32446,9 @@
       <c r="AB604" t="n">
         <v>0.6281655172413793</v>
       </c>
+      <c r="AC604" t="n">
+        <v>0.43458</v>
+      </c>
     </row>
     <row r="605">
       <c r="H605" s="5" t="n">
@@ -30783,6 +32466,9 @@
       <c r="AB605" t="n">
         <v>0.4950145833333333</v>
       </c>
+      <c r="AC605" t="n">
+        <v>0.394240425531915</v>
+      </c>
     </row>
     <row r="606">
       <c r="H606" s="5" t="n">
@@ -30800,6 +32486,9 @@
       <c r="AB606" t="n">
         <v>0.4525132075471699</v>
       </c>
+      <c r="AC606" t="n">
+        <v>0.4701790697674418</v>
+      </c>
     </row>
     <row r="607">
       <c r="H607" s="5" t="n">
@@ -30817,6 +32506,9 @@
       <c r="AB607" t="n">
         <v>0.5117094339622641</v>
       </c>
+      <c r="AC607" t="n">
+        <v>0.4663360000000001</v>
+      </c>
     </row>
     <row r="608">
       <c r="H608" s="5" t="n">
@@ -30834,6 +32526,9 @@
       <c r="AB608" t="n">
         <v>0.6114983050847457</v>
       </c>
+      <c r="AC608" t="n">
+        <v>0.41053125</v>
+      </c>
     </row>
     <row r="609">
       <c r="H609" s="5" t="n">
@@ -30851,6 +32546,9 @@
       <c r="AB609" t="n">
         <v>0.4429476190476191</v>
       </c>
+      <c r="AC609" t="n">
+        <v>0.431428</v>
+      </c>
     </row>
     <row r="610">
       <c r="H610" s="5" t="n">
@@ -30868,6 +32566,9 @@
       <c r="AB610" t="n">
         <v>0.5720607843137255</v>
       </c>
+      <c r="AC610" t="n">
+        <v>0.5161903846153847</v>
+      </c>
     </row>
     <row r="611">
       <c r="H611" s="5" t="n">
@@ -30885,6 +32586,9 @@
       <c r="AB611" t="n">
         <v>0.5301365079365079</v>
       </c>
+      <c r="AC611" t="n">
+        <v>0.482958</v>
+      </c>
     </row>
     <row r="612">
       <c r="H612" s="5" t="n">
@@ -30902,6 +32606,9 @@
       <c r="AB612" t="n">
         <v>0.6320750000000001</v>
       </c>
+      <c r="AC612" t="n">
+        <v>0.45343125</v>
+      </c>
     </row>
     <row r="613">
       <c r="H613" s="5" t="n">
@@ -30919,6 +32626,9 @@
       <c r="AB613" t="n">
         <v>0.5200589285714287</v>
       </c>
+      <c r="AC613" t="n">
+        <v>0.5457659090909092</v>
+      </c>
     </row>
     <row r="614">
       <c r="H614" s="5" t="n">
@@ -30936,6 +32646,9 @@
       <c r="AB614" t="n">
         <v>0.5528916666666667</v>
       </c>
+      <c r="AC614" t="n">
+        <v>0.4784367346938775</v>
+      </c>
     </row>
     <row r="615">
       <c r="H615" s="5" t="n">
@@ -30953,6 +32666,9 @@
       <c r="AB615" t="n">
         <v>0.447402</v>
       </c>
+      <c r="AC615" t="n">
+        <v>0.5347275</v>
+      </c>
     </row>
     <row r="616">
       <c r="H616" s="5" t="n">
@@ -30970,6 +32686,9 @@
       <c r="AB616" t="n">
         <v>0.5260574468085106</v>
       </c>
+      <c r="AC616" t="n">
+        <v>0.4511044444444444</v>
+      </c>
     </row>
     <row r="617">
       <c r="H617" s="5" t="n">
@@ -30987,6 +32706,9 @@
       <c r="AB617" t="n">
         <v>0.446788</v>
       </c>
+      <c r="AC617" t="n">
+        <v>0.4783062499999999</v>
+      </c>
     </row>
     <row r="618">
       <c r="H618" s="5" t="n">
@@ -31004,6 +32726,9 @@
       <c r="AB618" t="n">
         <v>0.4792728813559322</v>
       </c>
+      <c r="AC618" t="n">
+        <v>0.4767510204081633</v>
+      </c>
     </row>
     <row r="619">
       <c r="H619" s="5" t="n">
@@ -31020,6 +32745,9 @@
       </c>
       <c r="AB619" t="n">
         <v>0.6505066666666668</v>
+      </c>
+      <c r="AC619" t="n">
+        <v>0.4264708333333334</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3AE813-71FF-9C42-BE40-B37EF16A69E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1C07D5-FBB6-EA4B-AEC4-51C55799EB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-39520" yWindow="-2440" windowWidth="34560" windowHeight="20180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
   <si>
     <t>My Algorithm</t>
   </si>
@@ -103,7 +103,10 @@
     <t>Global Dirty Accuracy</t>
   </si>
   <si>
-    <t>Finalised</t>
+    <t>Finalised (My Algorithm)</t>
+  </si>
+  <si>
+    <t>Finalised (All Benign)</t>
   </si>
 </sst>
 </file>
@@ -498,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC619"/>
+  <dimension ref="A1:AI619"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -508,7 +511,7 @@
     <col min="13" max="13" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,8 +542,15 @@
       <c r="AA1" s="11"/>
       <c r="AB1" s="11"/>
       <c r="AC1" s="11"/>
-    </row>
-    <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+      <c r="AH1" s="11"/>
+      <c r="AI1" s="11"/>
+    </row>
+    <row r="2" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -613,8 +623,23 @@
       <c r="AC2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
@@ -622,7 +647,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
@@ -630,7 +655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -704,7 +729,7 @@
         <v>0.17179701492537311</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -778,7 +803,7 @@
         <v>0.17860000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -852,7 +877,7 @@
         <v>0.22220000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>4</v>
       </c>
@@ -926,7 +951,7 @@
         <v>0.31388749999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -1000,7 +1025,7 @@
         <v>0.40271428571428569</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>6</v>
       </c>
@@ -1074,7 +1099,7 @@
         <v>0.52313999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -1148,7 +1173,7 @@
         <v>0.38946666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -1222,7 +1247,7 @@
         <v>0.51019999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -1296,7 +1321,7 @@
         <v>0.66177666666666668</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>10</v>
       </c>
@@ -1370,7 +1395,7 @@
         <v>0.56116923076923075</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>11</v>
       </c>
@@ -1435,7 +1460,7 @@
         <v>0.6324736842105263</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>12</v>
       </c>
@@ -32703,7 +32728,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:F1"/>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -761,7 +761,10 @@
         <v>0.1565506493506493</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1717970149253731</v>
+        <v>0.1778257575757576</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.1444220588235294</v>
       </c>
       <c r="AI5" t="n">
         <v>0.1300313432835821</v>
@@ -838,7 +841,10 @@
         <v>0.2966888888888889</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1786</v>
+        <v>0.1841777777777778</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.2546185185185185</v>
       </c>
       <c r="AI6" t="n">
         <v>0.1945</v>
@@ -915,7 +921,10 @@
         <v>0.2955571428571429</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2222</v>
+        <v>0.2581</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.29529375</v>
       </c>
       <c r="AI7" t="n">
         <v>0.2252636363636364</v>
@@ -992,7 +1001,10 @@
         <v>0.3333</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3138875</v>
+        <v>0.3944363636363636</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.3587086956521739</v>
       </c>
       <c r="AI8" t="n">
         <v>0.3551473684210526</v>
@@ -1069,7 +1081,10 @@
         <v>0.4813499999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.4027142857142857</v>
+        <v>0.4470642857142857</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.4033733333333333</v>
       </c>
       <c r="AI9" t="n">
         <v>0.4464521739130435</v>
@@ -1146,7 +1161,10 @@
         <v>0.6071333333333333</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.5231399999999999</v>
+        <v>0.46318</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.5431333333333334</v>
       </c>
       <c r="AI10" t="n">
         <v>0.4737409090909091</v>
@@ -1223,7 +1241,10 @@
         <v>0.5877588235294118</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.3894666666666666</v>
+        <v>0.574416129032258</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.6328703703703703</v>
       </c>
       <c r="AI11" t="n">
         <v>0.5550304347826086</v>
@@ -1300,7 +1321,10 @@
         <v>0.543996</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.5102</v>
+        <v>0.51483</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.6659105263157894</v>
       </c>
       <c r="AI12" t="n">
         <v>0.5381</v>
@@ -1377,7 +1401,10 @@
         <v>0.63365</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.6617766666666667</v>
+        <v>0.6904677419354839</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.7138029411764706</v>
       </c>
       <c r="AI13" t="n">
         <v>0.6533703703703705</v>
@@ -1454,7 +1481,10 @@
         <v>0.7116666666666667</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.5611692307692308</v>
+        <v>0.55475</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.7791452380952381</v>
       </c>
       <c r="AI14" t="n">
         <v>0.64605</v>
@@ -1522,7 +1552,10 @@
         <v>0.7897307692307692</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.6324736842105263</v>
+        <v>0.6941181818181819</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.6907088235294117</v>
       </c>
       <c r="AI15" t="n">
         <v>0.6991238095238095</v>
@@ -1590,7 +1623,10 @@
         <v>0.6891272727272729</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.5537875</v>
+        <v>0.7501740740740742</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.8044242424242424</v>
       </c>
       <c r="AI16" t="n">
         <v>0.7390000000000001</v>
@@ -1658,7 +1694,10 @@
         <v>0.711895652173913</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.7739652173913044</v>
+        <v>0.767936</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.8216470588235293</v>
       </c>
       <c r="AI17" t="n">
         <v>0.7603636363636365</v>
@@ -1726,7 +1765,10 @@
         <v>0.7979647058823529</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.6632000000000001</v>
+        <v>0.8150133333333334</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.8476916666666665</v>
       </c>
       <c r="AI18" t="n">
         <v>0.81838</v>
@@ -1794,7 +1836,10 @@
         <v>0.7774757575757576</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.4780041666666667</v>
+        <v>0.4809538461538461</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.8462595238095239</v>
       </c>
       <c r="AI19" t="n">
         <v>0.8034599999999998</v>
@@ -1862,7 +1907,10 @@
         <v>0.7733652173913044</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.7402326530612244</v>
+        <v>0.7703739130434782</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.8139575757575758</v>
       </c>
       <c r="AI20" t="n">
         <v>0.6894499999999999</v>
@@ -1930,7 +1978,10 @@
         <v>0.8179666666666667</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.7265599999999999</v>
+        <v>0.8132562500000001</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.8129480000000001</v>
       </c>
       <c r="AI21" t="n">
         <v>0.7377157894736841</v>
@@ -1998,7 +2049,10 @@
         <v>0.8153793103448276</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.6480771428571429</v>
+        <v>0.714878125</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.8506088235294118</v>
       </c>
       <c r="AI22" t="n">
         <v>0.3317</v>
@@ -2066,7 +2120,10 @@
         <v>0.8028736842105263</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.6816655172413794</v>
+        <v>0.8276619047619048</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.7732114285714287</v>
       </c>
       <c r="AI23" t="n">
         <v>0.7929571428571428</v>
@@ -2134,7 +2191,10 @@
         <v>0.7993926829268293</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.7320621621621622</v>
+        <v>0.6806578947368421</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.8626111111111112</v>
       </c>
       <c r="AI24" t="n">
         <v>0.7378400000000001</v>
@@ -2202,7 +2262,10 @@
         <v>0.8418794117647059</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.6499238095238096</v>
+        <v>0.8548842105263157</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.8401619047619048</v>
       </c>
       <c r="AI25" t="n">
         <v>0.74299</v>
@@ -2270,7 +2333,10 @@
         <v>0.8243666666666667</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.7309219512195121</v>
+        <v>0.7023619047619047</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.8851699999999999</v>
       </c>
       <c r="AI26" t="n">
         <v>0.8164666666666666</v>
@@ -2338,7 +2404,10 @@
         <v>0.8491581395348838</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.6617269230769232</v>
+        <v>0.8953454545454546</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.8068071428571428</v>
       </c>
       <c r="AI27" t="n">
         <v>0.69924</v>
@@ -2406,7 +2475,10 @@
         <v>0.8293333333333334</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.7658580645161291</v>
+        <v>0.8215583333333333</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.8382950000000001</v>
       </c>
       <c r="AI28" t="n">
         <v>0.7915764705882352</v>
@@ -2474,7 +2546,10 @@
         <v>0.8446454545454546</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.7673709677419355</v>
+        <v>0.8405549999999999</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.8456666666666667</v>
       </c>
       <c r="AI29" t="n">
         <v>0.7888333333333333</v>
@@ -2542,7 +2617,10 @@
         <v>0.8001500000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.7293500000000001</v>
+        <v>0.7895799999999999</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.8683558139534883</v>
       </c>
       <c r="AI30" t="n">
         <v>0.7172551724137931</v>
@@ -2610,7 +2688,10 @@
         <v>0.851904</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.8548625</v>
+        <v>0.8073346153846153</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.9041483870967743</v>
       </c>
       <c r="AI31" t="n">
         <v>0.80762</v>
@@ -2678,7 +2759,10 @@
         <v>0.8850120000000001</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.7101125</v>
+        <v>0.7860285714285714</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.8286275</v>
       </c>
       <c r="AI32" t="n">
         <v>0.7754629629629629</v>
@@ -2746,7 +2830,10 @@
         <v>0.8240428571428572</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.8366148148148149</v>
+        <v>0.89875</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.8586911111111112</v>
       </c>
       <c r="AI33" t="n">
         <v>0.861742105263158</v>
@@ -2814,7 +2901,10 @@
         <v>0.8328300000000001</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.8187000000000001</v>
+        <v>0.8057473684210527</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.8450769230769232</v>
       </c>
       <c r="AI34" t="n">
         <v>0.8034428571428572</v>
@@ -2882,7 +2972,10 @@
         <v>0.7856739130434782</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.76802</v>
+        <v>0.8584181818181819</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.7788975609756098</v>
       </c>
       <c r="AI35" t="n">
         <v>0.7826291666666667</v>
@@ -2950,7 +3043,10 @@
         <v>0.8822038461538462</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.7461032258064515</v>
+        <v>0.8302687500000001</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.8721238095238096</v>
       </c>
       <c r="AI36" t="n">
         <v>0.8525666666666667</v>
@@ -3018,7 +3114,10 @@
         <v>0.879169696969697</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.6209794117647058</v>
+        <v>0.8016722222222222</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.7873033333333334</v>
       </c>
       <c r="AI37" t="n">
         <v>0.7153318181818181</v>
@@ -3086,7 +3185,10 @@
         <v>0.868892857142857</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.6220857142857142</v>
+        <v>0.8125315789473685</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.8196461538461539</v>
       </c>
       <c r="AI38" t="n">
         <v>0.648242857142857</v>
@@ -3154,7 +3256,10 @@
         <v>0.8924771428571429</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.658895</v>
+        <v>0.813073076923077</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.9542833333333335</v>
       </c>
       <c r="AI39" t="n">
         <v>0.7635384615384615</v>
@@ -3222,7 +3327,10 @@
         <v>0.7941434782608695</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.6221153846153846</v>
+        <v>0.8184586206896552</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.8326086956521739</v>
       </c>
       <c r="AI40" t="n">
         <v>0.8502416666666667</v>
@@ -3290,7 +3398,10 @@
         <v>0.8387541666666668</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.5730499999999999</v>
+        <v>0.8377333333333333</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.766475</v>
       </c>
       <c r="AI41" t="n">
         <v>0.7248052631578947</v>
@@ -3358,7 +3469,10 @@
         <v>0.8306114285714286</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.7893312499999999</v>
+        <v>0.771</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.8674059999999999</v>
       </c>
       <c r="AI42" t="n">
         <v>0.8111619047619049</v>
@@ -3426,7 +3540,10 @@
         <v>0.9300814814814815</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.6833541666666667</v>
+        <v>0.8446210526315788</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.8555219512195121</v>
       </c>
       <c r="AI43" t="n">
         <v>0.9117714285714287</v>
@@ -3494,7 +3611,10 @@
         <v>0.8689578947368422</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.89333125</v>
+        <v>0.8415050000000001</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.8947911764705883</v>
       </c>
       <c r="AI44" t="n">
         <v>0.8577357142857143</v>
@@ -3562,7 +3682,10 @@
         <v>0.9127233333333333</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.6783629629629631</v>
+        <v>0.8024636363636364</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0.8364026315789473</v>
       </c>
       <c r="AI45" t="n">
         <v>0.7950076923076922</v>
@@ -3630,7 +3753,10 @@
         <v>0.7973818181818182</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.7039423076923078</v>
+        <v>0.8450529411764706</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0.7907058823529411</v>
       </c>
       <c r="AI46" t="n">
         <v>0.8558136363636364</v>
@@ -3698,7 +3824,10 @@
         <v>0.9488800000000002</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.7107214285714285</v>
+        <v>0.8374142857142858</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0.8581365853658536</v>
       </c>
       <c r="AI47" t="n">
         <v>0.7612833333333332</v>
@@ -3766,7 +3895,10 @@
         <v>0.7659250000000001</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.6087068965517241</v>
+        <v>0.7865749999999999</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0.9355870967741936</v>
       </c>
       <c r="AI48" t="n">
         <v>0.7560608695652175</v>
@@ -3834,7 +3966,10 @@
         <v>0.8882869565217391</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.9002777777777778</v>
+        <v>0.7560166666666667</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0.8349897435897435</v>
       </c>
       <c r="AI49" t="n">
         <v>0.7343642857142857</v>
@@ -3902,7 +4037,10 @@
         <v>0.8594724137931035</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.7506964285714286</v>
+        <v>0.8125933333333333</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0.8626372093023255</v>
       </c>
       <c r="AI50" t="n">
         <v>0.8132285714285714</v>
@@ -3970,7 +4108,10 @@
         <v>0.7463260869565218</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.6922176470588234</v>
+        <v>0.7979192307692308</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.8403444444444443</v>
       </c>
       <c r="AI51" t="n">
         <v>0.8495578947368422</v>
@@ -4038,7 +4179,10 @@
         <v>0.8244222222222223</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.8365461538461538</v>
+        <v>0.8103206896551725</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0.87743</v>
       </c>
       <c r="AI52" t="n">
         <v>0.8635695652173914</v>
@@ -4106,7 +4250,10 @@
         <v>0.8351823529411765</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.7209521739130433</v>
+        <v>0.8048999999999999</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0.8419816326530611</v>
       </c>
       <c r="AI53" t="n">
         <v>0.8532714285714286</v>
@@ -4174,7 +4321,10 @@
         <v>0.8721192307692309</v>
       </c>
       <c r="AC54" t="n">
-        <v>0.7889882352941177</v>
+        <v>0.805169696969697</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0.8447468085106383</v>
       </c>
       <c r="AI54" t="n">
         <v>0.7911</v>
@@ -4242,7 +4392,10 @@
         <v>0.8632266666666667</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.74809</v>
+        <v>0.8160833333333333</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0.7363166666666667</v>
       </c>
       <c r="AI55" t="n">
         <v>0.82185</v>
@@ -4310,7 +4463,10 @@
         <v>0.8737571428571429</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.63329375</v>
+        <v>0.8642833333333334</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0.8710487179487182</v>
       </c>
       <c r="AI56" t="n">
         <v>0.7447764705882354</v>
@@ -4378,7 +4534,10 @@
         <v>0.8767655172413792</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.7612760000000001</v>
+        <v>0.8099125</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0.91634</v>
       </c>
       <c r="AI57" t="n">
         <v>0.7757166666666667</v>
@@ -4446,7 +4605,10 @@
         <v>0.8986703703703705</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.786742105263158</v>
+        <v>0.8868058823529412</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0.9305969696969696</v>
       </c>
       <c r="AI58" t="n">
         <v>0.8056529411764707</v>
@@ -4514,7 +4676,10 @@
         <v>0.8903555555555555</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.7845176470588235</v>
+        <v>0.8621346153846154</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0.8735666666666667</v>
       </c>
       <c r="AI59" t="n">
         <v>0.8226588235294118</v>
@@ -4582,7 +4747,10 @@
         <v>0.8382350000000001</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.6564833333333334</v>
+        <v>0.8122380952380953</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0.8537196078431372</v>
       </c>
       <c r="AI60" t="n">
         <v>0.74572</v>
@@ -4650,7 +4818,10 @@
         <v>0.8725458333333335</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.9235400000000001</v>
+        <v>0.8192285714285715</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0.92111875</v>
       </c>
       <c r="AI61" t="n">
         <v>0.7422347826086957</v>
@@ -4718,7 +4889,10 @@
         <v>0.8268099999999999</v>
       </c>
       <c r="AC62" t="n">
-        <v>0.8786249999999999</v>
+        <v>0.8367733333333334</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0.9207299999999999</v>
       </c>
       <c r="AI62" t="n">
         <v>0.9042545454545454</v>
@@ -4786,7 +4960,10 @@
         <v>0.8560375</v>
       </c>
       <c r="AC63" t="n">
-        <v>0.7945714285714286</v>
+        <v>0.79815</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0.9001749999999999</v>
       </c>
       <c r="AI63" t="n">
         <v>0.8332333333333333</v>
@@ -4854,7 +5031,10 @@
         <v>0.8609512195121951</v>
       </c>
       <c r="AC64" t="n">
-        <v>0.87956</v>
+        <v>0.7964366666666667</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0.865484</v>
       </c>
       <c r="AI64" t="n">
         <v>0.89825</v>
@@ -4922,7 +5102,10 @@
         <v>0.9158225806451613</v>
       </c>
       <c r="AC65" t="n">
-        <v>0.6629500000000002</v>
+        <v>0.7861571428571429</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0.942934210526316</v>
       </c>
       <c r="AI65" t="n">
         <v>0.8747909090909091</v>
@@ -4990,7 +5173,10 @@
         <v>0.7863666666666667</v>
       </c>
       <c r="AC66" t="n">
-        <v>0.6877736842105263</v>
+        <v>0.7881066666666666</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0.8442041666666666</v>
       </c>
       <c r="AI66" t="n">
         <v>0.8047294117647058</v>
@@ -5058,7 +5244,10 @@
         <v>0.8075142857142857</v>
       </c>
       <c r="AC67" t="n">
-        <v>0.8301263157894736</v>
+        <v>0.8141</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0.845618918918919</v>
       </c>
       <c r="AI67" t="n">
         <v>0.8612222222222222</v>
@@ -5126,7 +5315,10 @@
         <v>0.8336285714285714</v>
       </c>
       <c r="AC68" t="n">
-        <v>0.7745333333333333</v>
+        <v>0.7976428571428571</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0.871286046511628</v>
       </c>
       <c r="AI68" t="n">
         <v>0.8662904761904762</v>
@@ -5194,7 +5386,10 @@
         <v>0.892</v>
       </c>
       <c r="AC69" t="n">
-        <v>0.6865861111111111</v>
+        <v>0.8991</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0.734975</v>
       </c>
       <c r="AI69" t="n">
         <v>0.830925</v>
@@ -5262,7 +5457,10 @@
         <v>0.8063292682926829</v>
       </c>
       <c r="AC70" t="n">
-        <v>0.7472285714285712</v>
+        <v>0.8285071428571429</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0.9112117647058824</v>
       </c>
       <c r="AI70" t="n">
         <v>0.8072952380952382</v>
@@ -5330,7 +5528,10 @@
         <v>0.9095689655172415</v>
       </c>
       <c r="AC71" t="n">
-        <v>0.7146173913043478</v>
+        <v>0.8124909090909092</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0.8813255813953488</v>
       </c>
       <c r="AI71" t="n">
         <v>0.8981545454545454</v>
@@ -5398,7 +5599,10 @@
         <v>0.8695194444444444</v>
       </c>
       <c r="AC72" t="n">
-        <v>0.6594312499999999</v>
+        <v>0.7806142857142857</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0.8930333333333331</v>
       </c>
       <c r="AI72" t="n">
         <v>0.8337</v>
@@ -5466,7 +5670,10 @@
         <v>0.8746653846153845</v>
       </c>
       <c r="AC73" t="n">
-        <v>0.8336705882352941</v>
+        <v>0.8651384615384614</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0.9014681818181818</v>
       </c>
       <c r="AI73" t="n">
         <v>0.8648571428571429</v>
@@ -5534,7 +5741,10 @@
         <v>0.8889000000000001</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.909825</v>
+        <v>0.7983347826086956</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0.870672</v>
       </c>
       <c r="AI74" t="n">
         <v>0.8498</v>
@@ -5602,7 +5812,10 @@
         <v>0.6309923076923076</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.7867666666666667</v>
+        <v>0.819905</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0.8901314285714287</v>
       </c>
       <c r="AI75" t="n">
         <v>0.8002600000000001</v>
@@ -5670,7 +5883,10 @@
         <v>0.8597695652173912</v>
       </c>
       <c r="AC76" t="n">
-        <v>0.79</v>
+        <v>0.8066333333333333</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>0.9011222222222223</v>
       </c>
       <c r="AI76" t="n">
         <v>0.7300083333333335</v>
@@ -5738,7 +5954,10 @@
         <v>0.8647280000000001</v>
       </c>
       <c r="AC77" t="n">
-        <v>0.7235066666666667</v>
+        <v>0.8635769230769232</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0.8690860465116279</v>
       </c>
       <c r="AI77" t="n">
         <v>0.79581875</v>
@@ -5806,7 +6025,10 @@
         <v>0.8679470588235293</v>
       </c>
       <c r="AC78" t="n">
-        <v>0.71315</v>
+        <v>0.8692789473684212</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0.845924</v>
       </c>
       <c r="AI78" t="n">
         <v>0.8825818181818181</v>
@@ -5874,7 +6096,10 @@
         <v>0.8089615384615385</v>
       </c>
       <c r="AC79" t="n">
-        <v>0.7141636363636364</v>
+        <v>0.8399827586206896</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0.8899279069767442</v>
       </c>
       <c r="AI79" t="n">
         <v>0.7831111111111112</v>
@@ -5942,7 +6167,10 @@
         <v>0.7944740740740741</v>
       </c>
       <c r="AC80" t="n">
-        <v>0.8130999999999998</v>
+        <v>0.7929894736842106</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0.8731923076923078</v>
       </c>
       <c r="AI80" t="n">
         <v>0.7742857142857144</v>
@@ -6010,7 +6238,10 @@
         <v>0.8063806451612904</v>
       </c>
       <c r="AC81" t="n">
-        <v>0.8183360000000001</v>
+        <v>0.8125333333333332</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0.8634222222222222</v>
       </c>
       <c r="AI81" t="n">
         <v>0.7648411764705882</v>
@@ -6078,7 +6309,10 @@
         <v>0.8380391304347827</v>
       </c>
       <c r="AC82" t="n">
-        <v>0.7288558823529412</v>
+        <v>0.8307266666666667</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0.8649288888888889</v>
       </c>
       <c r="AI82" t="n">
         <v>0.82875</v>
@@ -6146,7 +6380,10 @@
         <v>0.754224</v>
       </c>
       <c r="AC83" t="n">
-        <v>0.7396916666666667</v>
+        <v>0.82816</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0.8624686274509804</v>
       </c>
       <c r="AI83" t="n">
         <v>0.7655000000000001</v>
@@ -6214,7 +6451,10 @@
         <v>0.7973821428571428</v>
       </c>
       <c r="AC84" t="n">
-        <v>0.7142178571428571</v>
+        <v>0.8325095238095239</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0.8451090909090908</v>
       </c>
       <c r="AI84" t="n">
         <v>0.8789187500000001</v>
@@ -6282,7 +6522,10 @@
         <v>0.8075692307692308</v>
       </c>
       <c r="AC85" t="n">
-        <v>0.7182904761904763</v>
+        <v>0.85517</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0.8907369565217391</v>
       </c>
       <c r="AI85" t="n">
         <v>0.8657625000000001</v>
@@ -6350,7 +6593,10 @@
         <v>0.9157846153846154</v>
       </c>
       <c r="AC86" t="n">
-        <v>0.650344</v>
+        <v>0.8028875000000001</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0.9096526315789474</v>
       </c>
       <c r="AI86" t="n">
         <v>0.7613666666666666</v>
@@ -6418,7 +6664,10 @@
         <v>0.8368129032258064</v>
       </c>
       <c r="AC87" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.8091333333333334</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0.8535130434782608</v>
       </c>
       <c r="AI87" t="n">
         <v>0.7791842105263158</v>
@@ -6486,7 +6735,10 @@
         <v>0.8699851851851853</v>
       </c>
       <c r="AC88" t="n">
-        <v>0.8810846153846155</v>
+        <v>0.8229588235294119</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0.8412625</v>
       </c>
       <c r="AI88" t="n">
         <v>0.801004761904762</v>
@@ -6554,7 +6806,10 @@
         <v>0.9266358974358975</v>
       </c>
       <c r="AC89" t="n">
-        <v>0.8272608695652174</v>
+        <v>0.8089263157894738</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0.8927854166666668</v>
       </c>
       <c r="AI89" t="n">
         <v>0.8487666666666667</v>
@@ -6622,7 +6877,10 @@
         <v>0.8890166666666667</v>
       </c>
       <c r="AC90" t="n">
-        <v>0.7487535714285712</v>
+        <v>0.8167846153846153</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>0.8915225000000001</v>
       </c>
       <c r="AI90" t="n">
         <v>0.8916153846153846</v>
@@ -6690,7 +6948,10 @@
         <v>0.8737764705882354</v>
       </c>
       <c r="AC91" t="n">
-        <v>0.728514705882353</v>
+        <v>0.8498916666666666</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>0.834263888888889</v>
       </c>
       <c r="AI91" t="n">
         <v>0.7642</v>
@@ -6758,7 +7019,10 @@
         <v>0.7849954545454545</v>
       </c>
       <c r="AC92" t="n">
-        <v>0.7942466666666667</v>
+        <v>0.89875</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>0.9011121951219512</v>
       </c>
       <c r="AI92" t="n">
         <v>0.8095</v>
@@ -6826,7 +7090,10 @@
         <v>0.8794647058823529</v>
       </c>
       <c r="AC93" t="n">
-        <v>0.8554476190476189</v>
+        <v>0.87325625</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>0.8462468750000001</v>
       </c>
       <c r="AI93" t="n">
         <v>0.8826357142857143</v>
@@ -6894,7 +7161,10 @@
         <v>0.8630000000000001</v>
       </c>
       <c r="AC94" t="n">
-        <v>0.8359722222222222</v>
+        <v>0.8562166666666666</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>0.8884404761904763</v>
       </c>
       <c r="AI94" t="n">
         <v>0.838004761904762</v>
@@ -6962,7 +7232,10 @@
         <v>0.8597</v>
       </c>
       <c r="AC95" t="n">
-        <v>0.6074724137931033</v>
+        <v>0.86829375</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>0.8711861111111112</v>
       </c>
       <c r="AI95" t="n">
         <v>0.7770615384615385</v>
@@ -7030,7 +7303,10 @@
         <v>0.9143307692307693</v>
       </c>
       <c r="AC96" t="n">
-        <v>0.6664967741935484</v>
+        <v>0.8327052631578947</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>0.857909375</v>
       </c>
       <c r="AI96" t="n">
         <v>0.8062428571428571</v>
@@ -7098,7 +7374,10 @@
         <v>0.78554</v>
       </c>
       <c r="AC97" t="n">
-        <v>0.7465333333333333</v>
+        <v>0.8147647058823528</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>0.8854935483870968</v>
       </c>
       <c r="AI97" t="n">
         <v>0.8111068965517242</v>
@@ -7166,7 +7445,10 @@
         <v>0.8819684210526316</v>
       </c>
       <c r="AC98" t="n">
-        <v>0.7643193548387096</v>
+        <v>0.8474666666666667</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>0.8519176470588236</v>
       </c>
       <c r="AI98" t="n">
         <v>0.8417523809523809</v>
@@ -7234,7 +7516,10 @@
         <v>0.8868533333333334</v>
       </c>
       <c r="AC99" t="n">
-        <v>0.7302419354838708</v>
+        <v>0.8588611111111111</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>0.8394272727272728</v>
       </c>
       <c r="AI99" t="n">
         <v>0.8653090909090909</v>
@@ -7302,7 +7587,10 @@
         <v>0.8900187500000001</v>
       </c>
       <c r="AC100" t="n">
-        <v>0.785048275862069</v>
+        <v>0.8243916666666666</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>0.8813866666666667</v>
       </c>
       <c r="AI100" t="n">
         <v>0.8858357142857144</v>
@@ -7370,7 +7658,10 @@
         <v>0.8328264705882353</v>
       </c>
       <c r="AC101" t="n">
-        <v>0.8470952380952381</v>
+        <v>0.817807142857143</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0.8519739130434781</v>
       </c>
       <c r="AI101" t="n">
         <v>0.8938117647058824</v>
@@ -7438,7 +7729,10 @@
         <v>0.7871741935483871</v>
       </c>
       <c r="AC102" t="n">
-        <v>0.8757260869565218</v>
+        <v>0.8752421052631579</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>0.8819733333333334</v>
       </c>
       <c r="AI102" t="n">
         <v>0.8413999999999999</v>
@@ -7506,7 +7800,10 @@
         <v>0.874335</v>
       </c>
       <c r="AC103" t="n">
-        <v>0.8741666666666668</v>
+        <v>0.8328842105263159</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>0.8554162790697677</v>
       </c>
       <c r="AI103" t="n">
         <v>0.8463416666666667</v>
@@ -7574,7 +7871,10 @@
         <v>0.7958472222222224</v>
       </c>
       <c r="AC104" t="n">
-        <v>0.6315714285714286</v>
+        <v>0.8440260869565218</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0.8421581395348837</v>
       </c>
       <c r="AI104" t="n">
         <v>0.851348</v>
@@ -7675,7 +7975,10 @@
         <v>1</v>
       </c>
       <c r="AC108" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0.9333333333333333</v>
       </c>
       <c r="AI108" t="n">
         <v>1</v>
@@ -7752,6 +8055,9 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="AC109" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AG109" t="n">
         <v>0.8666666666666667</v>
       </c>
       <c r="AI109" t="n">
@@ -7829,7 +8135,10 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="AC110" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>0.9230769230769231</v>
       </c>
       <c r="AI110" t="n">
         <v>0.8461538461538461</v>
@@ -7906,7 +8215,10 @@
         <v>1</v>
       </c>
       <c r="AC111" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0.7777777777777778</v>
       </c>
       <c r="AI111" t="n">
         <v>1</v>
@@ -7983,7 +8295,10 @@
         <v>0.875</v>
       </c>
       <c r="AC112" t="n">
-        <v>0.7</v>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>1</v>
       </c>
       <c r="AI112" t="n">
         <v>0.75</v>
@@ -8062,6 +8377,9 @@
       <c r="AC113" t="n">
         <v>1</v>
       </c>
+      <c r="AG113" t="n">
+        <v>1</v>
+      </c>
       <c r="AI113" t="n">
         <v>1</v>
       </c>
@@ -8139,6 +8457,9 @@
       <c r="AC114" t="n">
         <v>1</v>
       </c>
+      <c r="AG114" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI114" t="n">
         <v>1</v>
       </c>
@@ -8214,7 +8535,10 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="AC115" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>1</v>
       </c>
       <c r="AI115" t="n">
         <v>0.6666666666666666</v>
@@ -8293,6 +8617,9 @@
       <c r="AC116" t="n">
         <v>1</v>
       </c>
+      <c r="AG116" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AI116" t="n">
         <v>1</v>
       </c>
@@ -8370,6 +8697,9 @@
       <c r="AC117" t="n">
         <v>1</v>
       </c>
+      <c r="AG117" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AI117" t="n">
         <v>1</v>
       </c>
@@ -8433,7 +8763,10 @@
         <v>1</v>
       </c>
       <c r="AC118" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>1</v>
       </c>
       <c r="AI118" t="n">
         <v>1</v>
@@ -8501,7 +8834,10 @@
         <v>1</v>
       </c>
       <c r="AC119" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1</v>
       </c>
       <c r="AI119" t="n">
         <v>1</v>
@@ -8571,6 +8907,9 @@
       <c r="AC120" t="n">
         <v>1</v>
       </c>
+      <c r="AG120" t="n">
+        <v>1</v>
+      </c>
       <c r="AI120" t="n">
         <v>1</v>
       </c>
@@ -8637,6 +8976,9 @@
         <v>1</v>
       </c>
       <c r="AC121" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG121" t="n">
         <v>1</v>
       </c>
       <c r="AI121" t="n">
@@ -8707,6 +9049,9 @@
       <c r="AC122" t="n">
         <v>1</v>
       </c>
+      <c r="AG122" t="n">
+        <v>1</v>
+      </c>
       <c r="AI122" t="n">
         <v>1</v>
       </c>
@@ -8775,6 +9120,9 @@
       <c r="AC123" t="n">
         <v>1</v>
       </c>
+      <c r="AG123" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AI123" t="n">
         <v>1</v>
       </c>
@@ -8843,6 +9191,9 @@
       <c r="AC124" t="n">
         <v>1</v>
       </c>
+      <c r="AG124" t="n">
+        <v>1</v>
+      </c>
       <c r="AI124" t="n">
         <v>1</v>
       </c>
@@ -8911,6 +9262,9 @@
       <c r="AC125" t="n">
         <v>1</v>
       </c>
+      <c r="AG125" t="n">
+        <v>1</v>
+      </c>
       <c r="AI125" t="n">
         <v>1</v>
       </c>
@@ -8979,6 +9333,9 @@
       <c r="AC126" t="n">
         <v>1</v>
       </c>
+      <c r="AG126" t="n">
+        <v>1</v>
+      </c>
       <c r="AI126" t="n">
         <v>1</v>
       </c>
@@ -9045,6 +9402,9 @@
         <v>1</v>
       </c>
       <c r="AC127" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG127" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9112,6 +9472,9 @@
       <c r="AC128" t="n">
         <v>1</v>
       </c>
+      <c r="AG128" t="n">
+        <v>1</v>
+      </c>
       <c r="AI128" t="n">
         <v>1</v>
       </c>
@@ -9180,6 +9543,9 @@
       <c r="AC129" t="n">
         <v>1</v>
       </c>
+      <c r="AG129" t="n">
+        <v>1</v>
+      </c>
       <c r="AI129" t="n">
         <v>1</v>
       </c>
@@ -9248,6 +9614,9 @@
       <c r="AC130" t="n">
         <v>1</v>
       </c>
+      <c r="AG130" t="n">
+        <v>1</v>
+      </c>
       <c r="AI130" t="n">
         <v>1</v>
       </c>
@@ -9316,6 +9685,9 @@
       <c r="AC131" t="n">
         <v>1</v>
       </c>
+      <c r="AG131" t="n">
+        <v>1</v>
+      </c>
       <c r="AI131" t="n">
         <v>1</v>
       </c>
@@ -9384,6 +9756,9 @@
       <c r="AC132" t="n">
         <v>1</v>
       </c>
+      <c r="AG132" t="n">
+        <v>1</v>
+      </c>
       <c r="AI132" t="n">
         <v>1</v>
       </c>
@@ -9452,6 +9827,9 @@
       <c r="AC133" t="n">
         <v>1</v>
       </c>
+      <c r="AG133" t="n">
+        <v>1</v>
+      </c>
       <c r="AI133" t="n">
         <v>1</v>
       </c>
@@ -9520,6 +9898,9 @@
       <c r="AC134" t="n">
         <v>1</v>
       </c>
+      <c r="AG134" t="n">
+        <v>1</v>
+      </c>
       <c r="AI134" t="n">
         <v>1</v>
       </c>
@@ -9588,6 +9969,9 @@
       <c r="AC135" t="n">
         <v>1</v>
       </c>
+      <c r="AG135" t="n">
+        <v>1</v>
+      </c>
       <c r="AI135" t="n">
         <v>1</v>
       </c>
@@ -9656,6 +10040,9 @@
       <c r="AC136" t="n">
         <v>1</v>
       </c>
+      <c r="AG136" t="n">
+        <v>1</v>
+      </c>
       <c r="AI136" t="n">
         <v>1</v>
       </c>
@@ -9724,6 +10111,9 @@
       <c r="AC137" t="n">
         <v>1</v>
       </c>
+      <c r="AG137" t="n">
+        <v>1</v>
+      </c>
       <c r="AI137" t="n">
         <v>1</v>
       </c>
@@ -9792,6 +10182,9 @@
       <c r="AC138" t="n">
         <v>1</v>
       </c>
+      <c r="AG138" t="n">
+        <v>1</v>
+      </c>
       <c r="AI138" t="n">
         <v>1</v>
       </c>
@@ -9860,6 +10253,9 @@
       <c r="AC139" t="n">
         <v>1</v>
       </c>
+      <c r="AG139" t="n">
+        <v>1</v>
+      </c>
       <c r="AI139" t="n">
         <v>1</v>
       </c>
@@ -9925,6 +10321,9 @@
       <c r="AC140" t="n">
         <v>1</v>
       </c>
+      <c r="AG140" t="n">
+        <v>1</v>
+      </c>
       <c r="AI140" t="n">
         <v>1</v>
       </c>
@@ -9993,6 +10392,9 @@
       <c r="AC141" t="n">
         <v>1</v>
       </c>
+      <c r="AG141" t="n">
+        <v>1</v>
+      </c>
       <c r="AI141" t="n">
         <v>1</v>
       </c>
@@ -10061,6 +10463,9 @@
       <c r="AC142" t="n">
         <v>1</v>
       </c>
+      <c r="AG142" t="n">
+        <v>1</v>
+      </c>
       <c r="AI142" t="n">
         <v>1</v>
       </c>
@@ -10126,6 +10531,9 @@
       <c r="AC143" t="n">
         <v>1</v>
       </c>
+      <c r="AG143" t="n">
+        <v>1</v>
+      </c>
       <c r="AI143" t="n">
         <v>1</v>
       </c>
@@ -10194,6 +10602,9 @@
       <c r="AC144" t="n">
         <v>1</v>
       </c>
+      <c r="AG144" t="n">
+        <v>1</v>
+      </c>
       <c r="AI144" t="n">
         <v>1</v>
       </c>
@@ -10262,6 +10673,9 @@
       <c r="AC145" t="n">
         <v>1</v>
       </c>
+      <c r="AG145" t="n">
+        <v>1</v>
+      </c>
       <c r="AI145" t="n">
         <v>1</v>
       </c>
@@ -10330,6 +10744,9 @@
       <c r="AC146" t="n">
         <v>1</v>
       </c>
+      <c r="AG146" t="n">
+        <v>1</v>
+      </c>
       <c r="AI146" t="n">
         <v>1</v>
       </c>
@@ -10398,6 +10815,9 @@
       <c r="AC147" t="n">
         <v>1</v>
       </c>
+      <c r="AG147" t="n">
+        <v>1</v>
+      </c>
       <c r="AI147" t="n">
         <v>1</v>
       </c>
@@ -10466,6 +10886,9 @@
       <c r="AC148" t="n">
         <v>1</v>
       </c>
+      <c r="AG148" t="n">
+        <v>1</v>
+      </c>
       <c r="AI148" t="n">
         <v>1</v>
       </c>
@@ -10534,6 +10957,9 @@
       <c r="AC149" t="n">
         <v>1</v>
       </c>
+      <c r="AG149" t="n">
+        <v>1</v>
+      </c>
       <c r="AI149" t="n">
         <v>1</v>
       </c>
@@ -10602,6 +11028,9 @@
       <c r="AC150" t="n">
         <v>1</v>
       </c>
+      <c r="AG150" t="n">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AI150" t="n">
         <v>1</v>
       </c>
@@ -10670,6 +11099,9 @@
       <c r="AC151" t="n">
         <v>1</v>
       </c>
+      <c r="AG151" t="n">
+        <v>1</v>
+      </c>
       <c r="AI151" t="n">
         <v>1</v>
       </c>
@@ -10738,6 +11170,9 @@
       <c r="AC152" t="n">
         <v>1</v>
       </c>
+      <c r="AG152" t="n">
+        <v>1</v>
+      </c>
       <c r="AI152" t="n">
         <v>1</v>
       </c>
@@ -10806,6 +11241,9 @@
       <c r="AC153" t="n">
         <v>1</v>
       </c>
+      <c r="AG153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" ht="16" customHeight="1" s="8">
       <c r="A154" s="5" t="n">
@@ -10871,6 +11309,9 @@
       <c r="AC154" t="n">
         <v>1</v>
       </c>
+      <c r="AG154" t="n">
+        <v>1</v>
+      </c>
       <c r="AI154" t="n">
         <v>1</v>
       </c>
@@ -10939,6 +11380,9 @@
       <c r="AC155" t="n">
         <v>1</v>
       </c>
+      <c r="AG155" t="n">
+        <v>1</v>
+      </c>
       <c r="AI155" t="n">
         <v>1</v>
       </c>
@@ -11007,6 +11451,9 @@
       <c r="AC156" t="n">
         <v>1</v>
       </c>
+      <c r="AG156" t="n">
+        <v>1</v>
+      </c>
       <c r="AI156" t="n">
         <v>1</v>
       </c>
@@ -11075,6 +11522,9 @@
       <c r="AC157" t="n">
         <v>1</v>
       </c>
+      <c r="AG157" t="n">
+        <v>1</v>
+      </c>
       <c r="AI157" t="n">
         <v>1</v>
       </c>
@@ -11143,6 +11593,9 @@
       <c r="AC158" t="n">
         <v>1</v>
       </c>
+      <c r="AG158" t="n">
+        <v>1</v>
+      </c>
       <c r="AI158" t="n">
         <v>1</v>
       </c>
@@ -11211,6 +11664,9 @@
       <c r="AC159" t="n">
         <v>1</v>
       </c>
+      <c r="AG159" t="n">
+        <v>1</v>
+      </c>
       <c r="AI159" t="n">
         <v>1</v>
       </c>
@@ -11279,6 +11735,9 @@
       <c r="AC160" t="n">
         <v>1</v>
       </c>
+      <c r="AG160" t="n">
+        <v>1</v>
+      </c>
       <c r="AI160" t="n">
         <v>1</v>
       </c>
@@ -11347,6 +11806,9 @@
       <c r="AC161" t="n">
         <v>1</v>
       </c>
+      <c r="AG161" t="n">
+        <v>1</v>
+      </c>
       <c r="AI161" t="n">
         <v>1</v>
       </c>
@@ -11415,6 +11877,9 @@
       <c r="AC162" t="n">
         <v>1</v>
       </c>
+      <c r="AG162" t="n">
+        <v>1</v>
+      </c>
       <c r="AI162" t="n">
         <v>1</v>
       </c>
@@ -11483,6 +11948,9 @@
       <c r="AC163" t="n">
         <v>1</v>
       </c>
+      <c r="AG163" t="n">
+        <v>1</v>
+      </c>
       <c r="AI163" t="n">
         <v>1</v>
       </c>
@@ -11551,6 +12019,9 @@
       <c r="AC164" t="n">
         <v>1</v>
       </c>
+      <c r="AG164" t="n">
+        <v>1</v>
+      </c>
       <c r="AI164" t="n">
         <v>1</v>
       </c>
@@ -11619,6 +12090,9 @@
       <c r="AC165" t="n">
         <v>1</v>
       </c>
+      <c r="AG165" t="n">
+        <v>1</v>
+      </c>
       <c r="AI165" t="n">
         <v>1</v>
       </c>
@@ -11687,6 +12161,9 @@
       <c r="AC166" t="n">
         <v>1</v>
       </c>
+      <c r="AG166" t="n">
+        <v>1</v>
+      </c>
       <c r="AI166" t="n">
         <v>1</v>
       </c>
@@ -11755,6 +12232,9 @@
       <c r="AC167" t="n">
         <v>1</v>
       </c>
+      <c r="AG167" t="n">
+        <v>1</v>
+      </c>
       <c r="AI167" t="n">
         <v>1</v>
       </c>
@@ -11823,6 +12303,9 @@
       <c r="AC168" t="n">
         <v>1</v>
       </c>
+      <c r="AG168" t="n">
+        <v>1</v>
+      </c>
       <c r="AI168" t="n">
         <v>1</v>
       </c>
@@ -11891,6 +12374,9 @@
       <c r="AC169" t="n">
         <v>1</v>
       </c>
+      <c r="AG169" t="n">
+        <v>1</v>
+      </c>
       <c r="AI169" t="n">
         <v>1</v>
       </c>
@@ -11959,6 +12445,9 @@
       <c r="AC170" t="n">
         <v>1</v>
       </c>
+      <c r="AG170" t="n">
+        <v>1</v>
+      </c>
       <c r="AI170" t="n">
         <v>1</v>
       </c>
@@ -12027,6 +12516,9 @@
       <c r="AC171" t="n">
         <v>1</v>
       </c>
+      <c r="AG171" t="n">
+        <v>1</v>
+      </c>
       <c r="AI171" t="n">
         <v>1</v>
       </c>
@@ -12095,6 +12587,9 @@
       <c r="AC172" t="n">
         <v>1</v>
       </c>
+      <c r="AG172" t="n">
+        <v>1</v>
+      </c>
       <c r="AI172" t="n">
         <v>1</v>
       </c>
@@ -12163,6 +12658,9 @@
       <c r="AC173" t="n">
         <v>1</v>
       </c>
+      <c r="AG173" t="n">
+        <v>1</v>
+      </c>
       <c r="AI173" t="n">
         <v>1</v>
       </c>
@@ -12231,6 +12729,9 @@
       <c r="AC174" t="n">
         <v>1</v>
       </c>
+      <c r="AG174" t="n">
+        <v>1</v>
+      </c>
       <c r="AI174" t="n">
         <v>1</v>
       </c>
@@ -12299,6 +12800,9 @@
       <c r="AC175" t="n">
         <v>1</v>
       </c>
+      <c r="AG175" t="n">
+        <v>1</v>
+      </c>
       <c r="AI175" t="n">
         <v>1</v>
       </c>
@@ -12367,6 +12871,9 @@
       <c r="AC176" t="n">
         <v>1</v>
       </c>
+      <c r="AG176" t="n">
+        <v>1</v>
+      </c>
       <c r="AI176" t="n">
         <v>1</v>
       </c>
@@ -12435,6 +12942,9 @@
       <c r="AC177" t="n">
         <v>1</v>
       </c>
+      <c r="AG177" t="n">
+        <v>1</v>
+      </c>
       <c r="AI177" t="n">
         <v>1</v>
       </c>
@@ -12503,6 +13013,9 @@
       <c r="AC178" t="n">
         <v>1</v>
       </c>
+      <c r="AG178" t="n">
+        <v>1</v>
+      </c>
       <c r="AI178" t="n">
         <v>1</v>
       </c>
@@ -12571,6 +13084,9 @@
       <c r="AC179" t="n">
         <v>1</v>
       </c>
+      <c r="AG179" t="n">
+        <v>1</v>
+      </c>
       <c r="AI179" t="n">
         <v>1</v>
       </c>
@@ -12639,6 +13155,9 @@
       <c r="AC180" t="n">
         <v>1</v>
       </c>
+      <c r="AG180" t="n">
+        <v>1</v>
+      </c>
       <c r="AI180" t="n">
         <v>1</v>
       </c>
@@ -12704,6 +13223,9 @@
       <c r="AC181" t="n">
         <v>1</v>
       </c>
+      <c r="AG181" t="n">
+        <v>1</v>
+      </c>
       <c r="AI181" t="n">
         <v>1</v>
       </c>
@@ -12772,6 +13294,9 @@
       <c r="AC182" t="n">
         <v>1</v>
       </c>
+      <c r="AG182" t="n">
+        <v>1</v>
+      </c>
       <c r="AI182" t="n">
         <v>1</v>
       </c>
@@ -12840,6 +13365,9 @@
       <c r="AC183" t="n">
         <v>1</v>
       </c>
+      <c r="AG183" t="n">
+        <v>1</v>
+      </c>
       <c r="AI183" t="n">
         <v>1</v>
       </c>
@@ -12908,6 +13436,9 @@
       <c r="AC184" t="n">
         <v>1</v>
       </c>
+      <c r="AG184" t="n">
+        <v>1</v>
+      </c>
       <c r="AI184" t="n">
         <v>1</v>
       </c>
@@ -12976,6 +13507,9 @@
       <c r="AC185" t="n">
         <v>1</v>
       </c>
+      <c r="AG185" t="n">
+        <v>1</v>
+      </c>
       <c r="AI185" t="n">
         <v>1</v>
       </c>
@@ -13044,6 +13578,9 @@
       <c r="AC186" t="n">
         <v>1</v>
       </c>
+      <c r="AG186" t="n">
+        <v>1</v>
+      </c>
       <c r="AI186" t="n">
         <v>1</v>
       </c>
@@ -13112,6 +13649,9 @@
       <c r="AC187" t="n">
         <v>1</v>
       </c>
+      <c r="AG187" t="n">
+        <v>1</v>
+      </c>
       <c r="AI187" t="n">
         <v>1</v>
       </c>
@@ -13180,6 +13720,9 @@
       <c r="AC188" t="n">
         <v>1</v>
       </c>
+      <c r="AG188" t="n">
+        <v>1</v>
+      </c>
       <c r="AI188" t="n">
         <v>1</v>
       </c>
@@ -13248,6 +13791,9 @@
       <c r="AC189" t="n">
         <v>1</v>
       </c>
+      <c r="AG189" t="n">
+        <v>1</v>
+      </c>
       <c r="AI189" t="n">
         <v>1</v>
       </c>
@@ -13316,6 +13862,9 @@
       <c r="AC190" t="n">
         <v>1</v>
       </c>
+      <c r="AG190" t="n">
+        <v>1</v>
+      </c>
       <c r="AI190" t="n">
         <v>1</v>
       </c>
@@ -13384,6 +13933,9 @@
       <c r="AC191" t="n">
         <v>1</v>
       </c>
+      <c r="AG191" t="n">
+        <v>1</v>
+      </c>
       <c r="AI191" t="n">
         <v>1</v>
       </c>
@@ -13452,6 +14004,9 @@
       <c r="AC192" t="n">
         <v>1</v>
       </c>
+      <c r="AG192" t="n">
+        <v>1</v>
+      </c>
       <c r="AI192" t="n">
         <v>1</v>
       </c>
@@ -13520,6 +14075,9 @@
       <c r="AC193" t="n">
         <v>1</v>
       </c>
+      <c r="AG193" t="n">
+        <v>1</v>
+      </c>
       <c r="AI193" t="n">
         <v>1</v>
       </c>
@@ -13588,6 +14146,9 @@
       <c r="AC194" t="n">
         <v>1</v>
       </c>
+      <c r="AG194" t="n">
+        <v>1</v>
+      </c>
       <c r="AI194" t="n">
         <v>1</v>
       </c>
@@ -13656,6 +14217,9 @@
       <c r="AC195" t="n">
         <v>1</v>
       </c>
+      <c r="AG195" t="n">
+        <v>1</v>
+      </c>
       <c r="AI195" t="n">
         <v>1</v>
       </c>
@@ -13724,6 +14288,9 @@
       <c r="AC196" t="n">
         <v>1</v>
       </c>
+      <c r="AG196" t="n">
+        <v>1</v>
+      </c>
       <c r="AI196" t="n">
         <v>1</v>
       </c>
@@ -13792,6 +14359,9 @@
       <c r="AC197" t="n">
         <v>1</v>
       </c>
+      <c r="AG197" t="n">
+        <v>1</v>
+      </c>
       <c r="AI197" t="n">
         <v>1</v>
       </c>
@@ -13860,6 +14430,9 @@
       <c r="AC198" t="n">
         <v>1</v>
       </c>
+      <c r="AG198" t="n">
+        <v>1</v>
+      </c>
       <c r="AI198" t="n">
         <v>1</v>
       </c>
@@ -13928,6 +14501,9 @@
       <c r="AC199" t="n">
         <v>1</v>
       </c>
+      <c r="AG199" t="n">
+        <v>1</v>
+      </c>
       <c r="AI199" t="n">
         <v>1</v>
       </c>
@@ -13996,6 +14572,9 @@
       <c r="AC200" t="n">
         <v>1</v>
       </c>
+      <c r="AG200" t="n">
+        <v>1</v>
+      </c>
       <c r="AI200" t="n">
         <v>1</v>
       </c>
@@ -14064,6 +14643,9 @@
       <c r="AC201" t="n">
         <v>1</v>
       </c>
+      <c r="AG201" t="n">
+        <v>1</v>
+      </c>
       <c r="AI201" t="n">
         <v>1</v>
       </c>
@@ -14132,6 +14714,9 @@
       <c r="AC202" t="n">
         <v>1</v>
       </c>
+      <c r="AG202" t="n">
+        <v>1</v>
+      </c>
       <c r="AI202" t="n">
         <v>1</v>
       </c>
@@ -14200,6 +14785,9 @@
       <c r="AC203" t="n">
         <v>1</v>
       </c>
+      <c r="AG203" t="n">
+        <v>1</v>
+      </c>
       <c r="AI203" t="n">
         <v>1</v>
       </c>
@@ -14268,6 +14856,9 @@
       <c r="AC204" t="n">
         <v>1</v>
       </c>
+      <c r="AG204" t="n">
+        <v>1</v>
+      </c>
       <c r="AI204" t="n">
         <v>1</v>
       </c>
@@ -14336,6 +14927,9 @@
       <c r="AC205" t="n">
         <v>1</v>
       </c>
+      <c r="AG205" t="n">
+        <v>1</v>
+      </c>
       <c r="AI205" t="n">
         <v>1</v>
       </c>
@@ -14404,6 +14998,9 @@
       <c r="AC206" t="n">
         <v>1</v>
       </c>
+      <c r="AG206" t="n">
+        <v>1</v>
+      </c>
       <c r="AI206" t="n">
         <v>1</v>
       </c>
@@ -14470,6 +15067,9 @@
         <v>1</v>
       </c>
       <c r="AC207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG207" t="n">
         <v>1</v>
       </c>
       <c r="AI207" t="n">
@@ -14571,7 +15171,10 @@
         <v>0.945975</v>
       </c>
       <c r="AC212" t="n">
-        <v>0.9564374999999999</v>
+        <v>0.9430666666666667</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>0.955125</v>
       </c>
       <c r="AI212" t="n">
         <v>0.9532299999999999</v>
@@ -14648,7 +15251,10 @@
         <v>0.9561833333333333</v>
       </c>
       <c r="AC213" t="n">
-        <v>0.9480727272727273</v>
+        <v>0.9698250000000002</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>0.9441285714285714</v>
       </c>
       <c r="AI213" t="n">
         <v>0.9537142857142858</v>
@@ -14725,7 +15331,10 @@
         <v>0.9385800000000002</v>
       </c>
       <c r="AC214" t="n">
-        <v>0.8638181818181817</v>
+        <v>0.94275</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>0.9409599999999999</v>
       </c>
       <c r="AI214" t="n">
         <v>0.9496249999999999</v>
@@ -14802,7 +15411,10 @@
         <v>0.8617111111111111</v>
       </c>
       <c r="AC215" t="n">
-        <v>0.9053000000000001</v>
+        <v>0.9284222222222223</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>0.8693</v>
       </c>
       <c r="AI215" t="n">
         <v>0.71899</v>
@@ -14879,7 +15491,10 @@
         <v>0.7094999999999999</v>
       </c>
       <c r="AC216" t="n">
-        <v>0.9598818181818181</v>
+        <v>0.9310363636363637</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>0.7681833333333334</v>
       </c>
       <c r="AI216" t="n">
         <v>0.7120200000000001</v>
@@ -14956,7 +15571,10 @@
         <v>0.9389222222222222</v>
       </c>
       <c r="AC217" t="n">
-        <v>0.7393444444444444</v>
+        <v>0.8764615384615385</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>0.8476100000000001</v>
       </c>
       <c r="AI217" t="n">
         <v>0.76971</v>
@@ -15033,7 +15651,10 @@
         <v>0.8261555555555556</v>
       </c>
       <c r="AC218" t="n">
-        <v>0.7590785714285715</v>
+        <v>0.9289875</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>0.8501666666666666</v>
       </c>
       <c r="AI218" t="n">
         <v>0.7489899999999999</v>
@@ -15110,7 +15731,10 @@
         <v>0.74186</v>
       </c>
       <c r="AC219" t="n">
-        <v>0.89869</v>
+        <v>0.6568833333333333</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>0.7333875000000001</v>
       </c>
       <c r="AI219" t="n">
         <v>0.6724923076923077</v>
@@ -15187,7 +15811,10 @@
         <v>0.75689</v>
       </c>
       <c r="AC220" t="n">
-        <v>0.9096500000000003</v>
+        <v>0.5305545454545454</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>0.7582</v>
       </c>
       <c r="AI220" t="n">
         <v>0.7551099999999999</v>
@@ -15264,7 +15891,10 @@
         <v>0.8344750000000001</v>
       </c>
       <c r="AC221" t="n">
-        <v>0.8752285714285716</v>
+        <v>0.9188076923076924</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>0.8130875</v>
       </c>
       <c r="AI221" t="n">
         <v>0.7041166666666666</v>
@@ -15329,7 +15959,10 @@
         <v>0.8927999999999999</v>
       </c>
       <c r="AC222" t="n">
-        <v>0.8626090909090909</v>
+        <v>0.8268818181818181</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>0.7564111111111111</v>
       </c>
       <c r="AI222" t="n">
         <v>0.7263400000000001</v>
@@ -15397,7 +16030,10 @@
         <v>0.6485181818181819</v>
       </c>
       <c r="AC223" t="n">
-        <v>0.9153399999999999</v>
+        <v>0.75125</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>0.8121625</v>
       </c>
       <c r="AI223" t="n">
         <v>0.6934083333333335</v>
@@ -15465,7 +16101,10 @@
         <v>0.7489222222222222</v>
       </c>
       <c r="AC224" t="n">
-        <v>0.7734000000000001</v>
+        <v>0.6753083333333335</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>0.6998090909090908</v>
       </c>
       <c r="AI224" t="n">
         <v>0.7491555555555556</v>
@@ -15533,7 +16172,10 @@
         <v>0.7000666666666666</v>
       </c>
       <c r="AC225" t="n">
-        <v>0.7958692307692309</v>
+        <v>0.746990909090909</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>0.6655888888888889</v>
       </c>
       <c r="AI225" t="n">
         <v>0.6531454545454546</v>
@@ -15601,7 +16243,10 @@
         <v>0.73653</v>
       </c>
       <c r="AC226" t="n">
-        <v>0.8287727272727273</v>
+        <v>0.6548928571428572</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>0.8338666666666668</v>
       </c>
       <c r="AI226" t="n">
         <v>0.7161000000000001</v>
@@ -15669,7 +16314,10 @@
         <v>0.7327666666666667</v>
       </c>
       <c r="AC227" t="n">
-        <v>0.7518666666666668</v>
+        <v>0.68125</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>0.5132874999999999</v>
       </c>
       <c r="AI227" t="n">
         <v>0.7423083333333333</v>
@@ -15737,7 +16385,10 @@
         <v>0.5726666666666667</v>
       </c>
       <c r="AC228" t="n">
-        <v>0.8241333333333334</v>
+        <v>0.7630923076923077</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>0.5997</v>
       </c>
       <c r="AI228" t="n">
         <v>0.6454500000000001</v>
@@ -15805,7 +16456,10 @@
         <v>0.8396166666666666</v>
       </c>
       <c r="AC229" t="n">
-        <v>0.846425</v>
+        <v>0.6697571428571427</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>0.7098166666666668</v>
       </c>
       <c r="AI229" t="n">
         <v>0.7297714285714287</v>
@@ -15873,7 +16527,10 @@
         <v>0.6778444444444445</v>
       </c>
       <c r="AC230" t="n">
-        <v>0.8584636363636363</v>
+        <v>0.7526923076923079</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>0.5988222222222221</v>
       </c>
       <c r="AI230" t="n">
         <v>0.8171799999999999</v>
@@ -15941,7 +16598,10 @@
         <v>0.5468416666666667</v>
       </c>
       <c r="AC231" t="n">
-        <v>0.8455416666666667</v>
+        <v>0.7578307692307692</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>0.5894111111111111</v>
       </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="8">
@@ -16006,7 +16666,10 @@
         <v>0.6597000000000001</v>
       </c>
       <c r="AC232" t="n">
-        <v>0.8252166666666669</v>
+        <v>0.6034545454545456</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>0.5751625</v>
       </c>
       <c r="AI232" t="n">
         <v>0.7732916666666667</v>
@@ -16074,7 +16737,10 @@
         <v>0.7221399999999999</v>
       </c>
       <c r="AC233" t="n">
-        <v>0.7852076923076923</v>
+        <v>0.7568461538461537</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>0.7272222222222222</v>
       </c>
       <c r="AI233" t="n">
         <v>0.7760583333333333</v>
@@ -16142,7 +16808,10 @@
         <v>0.7933874999999999</v>
       </c>
       <c r="AC234" t="n">
-        <v>0.8138363636363638</v>
+        <v>0.6984749999999998</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>0.4850909090909091</v>
       </c>
       <c r="AI234" t="n">
         <v>0.7528833333333335</v>
@@ -16210,7 +16879,10 @@
         <v>0.70082</v>
       </c>
       <c r="AC235" t="n">
-        <v>0.8375888888888889</v>
+        <v>0.6754166666666667</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>0.4899125</v>
       </c>
       <c r="AI235" t="n">
         <v>0.6315538461538461</v>
@@ -16278,7 +16950,10 @@
         <v>0.7525545454545455</v>
       </c>
       <c r="AC236" t="n">
-        <v>0.7896454545454545</v>
+        <v>0.6302083333333333</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>0.4749666666666666</v>
       </c>
       <c r="AI236" t="n">
         <v>0.6624500000000001</v>
@@ -16346,7 +17021,10 @@
         <v>0.6757199999999999</v>
       </c>
       <c r="AC237" t="n">
-        <v>0.77021</v>
+        <v>0.6648181818181818</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>0.58648</v>
       </c>
       <c r="AI237" t="n">
         <v>0.751525</v>
@@ -16414,7 +17092,10 @@
         <v>0.64214</v>
       </c>
       <c r="AC238" t="n">
-        <v>0.7551769230769232</v>
+        <v>0.4744249999999999</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>0.5892000000000001</v>
       </c>
       <c r="AI238" t="n">
         <v>0.652825</v>
@@ -16482,7 +17163,10 @@
         <v>0.7617363636363635</v>
       </c>
       <c r="AC239" t="n">
-        <v>0.873546153846154</v>
+        <v>0.6172</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>0.7491499999999999</v>
       </c>
       <c r="AI239" t="n">
         <v>0.8661999999999999</v>
@@ -16550,7 +17234,10 @@
         <v>0.6537666666666666</v>
       </c>
       <c r="AC240" t="n">
-        <v>0.77228</v>
+        <v>0.5145076923076923</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>0.5813714285714287</v>
       </c>
       <c r="AI240" t="n">
         <v>0.7905111111111112</v>
@@ -16618,7 +17305,10 @@
         <v>0.7624899999999999</v>
       </c>
       <c r="AC241" t="n">
-        <v>0.8042400000000001</v>
+        <v>0.5498833333333334</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>0.7499399999999999</v>
       </c>
       <c r="AI241" t="n">
         <v>0.7470818181818182</v>
@@ -16686,7 +17376,10 @@
         <v>0.6906500000000001</v>
       </c>
       <c r="AC242" t="n">
-        <v>0.7886749999999999</v>
+        <v>0.5574333333333333</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>0.6617250000000001</v>
       </c>
       <c r="AI242" t="n">
         <v>0.5965727272727274</v>
@@ -16754,7 +17447,10 @@
         <v>0.6684111111111112</v>
       </c>
       <c r="AC243" t="n">
-        <v>0.750225</v>
+        <v>0.6808384615384615</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>0.7671</v>
       </c>
       <c r="AI243" t="n">
         <v>0.7137785714285714</v>
@@ -16819,7 +17515,10 @@
         <v>0.6328375000000001</v>
       </c>
       <c r="AC244" t="n">
-        <v>0.8188000000000002</v>
+        <v>0.6706454545454545</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>0.6970500000000001</v>
       </c>
       <c r="AI244" t="n">
         <v>0.7739833333333334</v>
@@ -16889,6 +17588,9 @@
       <c r="AC245" t="n">
         <v>0.7155166666666667</v>
       </c>
+      <c r="AG245" t="n">
+        <v>0.5966222222222223</v>
+      </c>
       <c r="AI245" t="n">
         <v>0.654</v>
       </c>
@@ -16957,6 +17659,9 @@
       <c r="AC246" t="n">
         <v>0.7414700000000001</v>
       </c>
+      <c r="AG246" t="n">
+        <v>0.6594750000000001</v>
+      </c>
       <c r="AI246" t="n">
         <v>0.551011111111111</v>
       </c>
@@ -17020,7 +17725,10 @@
         <v>0.8242833333333333</v>
       </c>
       <c r="AC247" t="n">
-        <v>0.7581333333333333</v>
+        <v>0.5861727272727273</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>0.5673</v>
       </c>
       <c r="AI247" t="n">
         <v>0.5978249999999999</v>
@@ -17088,7 +17796,10 @@
         <v>0.6457285714285714</v>
       </c>
       <c r="AC248" t="n">
-        <v>0.71614</v>
+        <v>0.5184846153846154</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>0.8148</v>
       </c>
       <c r="AI248" t="n">
         <v>0.7105615384615382</v>
@@ -17156,7 +17867,10 @@
         <v>0.7223111111111111</v>
       </c>
       <c r="AC249" t="n">
-        <v>0.9034666666666668</v>
+        <v>0.7905099999999999</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>0.7287000000000001</v>
       </c>
       <c r="AI249" t="n">
         <v>0.6842090909090909</v>
@@ -17226,6 +17940,9 @@
       <c r="AC250" t="n">
         <v>0.8942272727272728</v>
       </c>
+      <c r="AG250" t="n">
+        <v>0.5727571428571429</v>
+      </c>
       <c r="AI250" t="n">
         <v>0.6877636363636364</v>
       </c>
@@ -17292,7 +18009,10 @@
         <v>0.4760375</v>
       </c>
       <c r="AC251" t="n">
-        <v>0.8156454545454545</v>
+        <v>0.6176571428571427</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>0.6977142857142857</v>
       </c>
       <c r="AI251" t="n">
         <v>0.7553833333333334</v>
@@ -17360,7 +18080,10 @@
         <v>0.7316166666666667</v>
       </c>
       <c r="AC252" t="n">
-        <v>0.7024399999999998</v>
+        <v>0.6792333333333334</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>0.6966875</v>
       </c>
       <c r="AI252" t="n">
         <v>0.7040461538461538</v>
@@ -17428,7 +18151,10 @@
         <v>0.63619</v>
       </c>
       <c r="AC253" t="n">
-        <v>0.8233250000000001</v>
+        <v>0.7642916666666667</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>0.5240571428571429</v>
       </c>
       <c r="AI253" t="n">
         <v>0.5232083333333333</v>
@@ -17496,7 +18222,10 @@
         <v>0.7097454545454546</v>
       </c>
       <c r="AC254" t="n">
-        <v>0.9006888888888889</v>
+        <v>0.5722999999999999</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>0.6985874999999999</v>
       </c>
       <c r="AI254" t="n">
         <v>0.7925636363636365</v>
@@ -17564,7 +18293,10 @@
         <v>0.7767307692307692</v>
       </c>
       <c r="AC255" t="n">
-        <v>0.7589444444444444</v>
+        <v>0.7110769230769231</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>0.6282</v>
       </c>
       <c r="AI255" t="n">
         <v>0.6208083333333333</v>
@@ -17632,7 +18364,10 @@
         <v>0.63409</v>
       </c>
       <c r="AC256" t="n">
-        <v>0.8178</v>
+        <v>0.658525</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>0.6270749999999999</v>
       </c>
       <c r="AI256" t="n">
         <v>0.7818818181818181</v>
@@ -17700,7 +18435,10 @@
         <v>0.7080272727272727</v>
       </c>
       <c r="AC257" t="n">
-        <v>0.8153250000000001</v>
+        <v>0.6434928571428572</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>0.5711000000000001</v>
       </c>
     </row>
     <row r="258" ht="16" customHeight="1" s="8">
@@ -17765,7 +18503,10 @@
         <v>0.63758</v>
       </c>
       <c r="AC258" t="n">
-        <v>0.69499</v>
+        <v>0.6624100000000002</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>0.70428</v>
       </c>
       <c r="AI258" t="n">
         <v>0.8083272727272728</v>
@@ -17833,7 +18574,10 @@
         <v>0.7251727272727272</v>
       </c>
       <c r="AC259" t="n">
-        <v>0.7542428571428571</v>
+        <v>0.6921538461538461</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>0.58897</v>
       </c>
       <c r="AI259" t="n">
         <v>0.7523076923076922</v>
@@ -17901,7 +18645,10 @@
         <v>0.6167777777777779</v>
       </c>
       <c r="AC260" t="n">
-        <v>0.7819800000000001</v>
+        <v>0.6954454545454546</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>0.6454</v>
       </c>
       <c r="AI260" t="n">
         <v>0.866390909090909</v>
@@ -17969,7 +18716,10 @@
         <v>0.6271899999999999</v>
       </c>
       <c r="AC261" t="n">
-        <v>0.7959833333333334</v>
+        <v>0.6671083333333333</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>0.6931181818181816</v>
       </c>
       <c r="AI261" t="n">
         <v>0.732525</v>
@@ -18037,7 +18787,10 @@
         <v>0.571775</v>
       </c>
       <c r="AC262" t="n">
-        <v>0.881646153846154</v>
+        <v>0.7742166666666668</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>0.6600200000000001</v>
       </c>
       <c r="AI262" t="n">
         <v>0.8668090909090908</v>
@@ -18105,7 +18858,10 @@
         <v>0.6547307692307693</v>
       </c>
       <c r="AC263" t="n">
-        <v>0.8004769230769231</v>
+        <v>0.6933928571428573</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>0.4840125</v>
       </c>
       <c r="AI263" t="n">
         <v>0.6957999999999999</v>
@@ -18173,7 +18929,10 @@
         <v>0.8918874999999999</v>
       </c>
       <c r="AC264" t="n">
-        <v>0.8668153846153844</v>
+        <v>0.6937615384615383</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>0.6907166666666668</v>
       </c>
       <c r="AI264" t="n">
         <v>0.7173818181818181</v>
@@ -18241,7 +19000,10 @@
         <v>0.83503</v>
       </c>
       <c r="AC265" t="n">
-        <v>0.7843899999999999</v>
+        <v>0.6265599999999999</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>0.5547285714285713</v>
       </c>
       <c r="AI265" t="n">
         <v>0.6610461538461537</v>
@@ -18309,7 +19071,10 @@
         <v>0.7237888888888889</v>
       </c>
       <c r="AC266" t="n">
-        <v>0.7934272727272728</v>
+        <v>0.7003333333333334</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>0.56168</v>
       </c>
       <c r="AI266" t="n">
         <v>0.6746272727272727</v>
@@ -18377,7 +19142,10 @@
         <v>0.4552444444444445</v>
       </c>
       <c r="AC267" t="n">
-        <v>0.6917916666666666</v>
+        <v>0.6253416666666666</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>0.502</v>
       </c>
       <c r="AI267" t="n">
         <v>0.9139363636363637</v>
@@ -18445,7 +19213,10 @@
         <v>0.7277333333333335</v>
       </c>
       <c r="AC268" t="n">
-        <v>0.7535333333333334</v>
+        <v>0.7623416666666668</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>0.58985</v>
       </c>
       <c r="AI268" t="n">
         <v>0.67318</v>
@@ -18513,7 +19284,10 @@
         <v>0.5953363636363637</v>
       </c>
       <c r="AC269" t="n">
-        <v>0.7960900000000002</v>
+        <v>0.7108181818181818</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>0.5053444444444444</v>
       </c>
       <c r="AI269" t="n">
         <v>0.7978499999999999</v>
@@ -18581,7 +19355,10 @@
         <v>0.7486</v>
       </c>
       <c r="AC270" t="n">
-        <v>0.7796000000000001</v>
+        <v>0.58785</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>0.5276777777777778</v>
       </c>
       <c r="AI270" t="n">
         <v>0.6577642857142856</v>
@@ -18649,7 +19426,10 @@
         <v>0.64428</v>
       </c>
       <c r="AC271" t="n">
-        <v>0.8516846153846152</v>
+        <v>0.5422833333333333</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>0.6467222222222222</v>
       </c>
       <c r="AI271" t="n">
         <v>0.7966727272727273</v>
@@ -18717,7 +19497,10 @@
         <v>0.6922333333333333</v>
       </c>
       <c r="AC272" t="n">
-        <v>0.7948777777777778</v>
+        <v>0.690523076923077</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>0.5596666666666668</v>
       </c>
       <c r="AI272" t="n">
         <v>0.7604692307692307</v>
@@ -18785,7 +19568,10 @@
         <v>0.6371999999999999</v>
       </c>
       <c r="AC273" t="n">
-        <v>0.7156363636363636</v>
+        <v>0.7784307692307691</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>0.4824888888888889</v>
       </c>
       <c r="AI273" t="n">
         <v>0.6132111111111112</v>
@@ -18853,7 +19639,10 @@
         <v>0.7016999999999999</v>
       </c>
       <c r="AC274" t="n">
-        <v>0.7746333333333332</v>
+        <v>0.6181</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>0.6259555555555556</v>
       </c>
       <c r="AI274" t="n">
         <v>0.7624749999999999</v>
@@ -18921,7 +19710,10 @@
         <v>0.6962111111111111</v>
       </c>
       <c r="AC275" t="n">
-        <v>0.8391444444444445</v>
+        <v>0.6315727272727272</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>0.6092875</v>
       </c>
       <c r="AI275" t="n">
         <v>0.7679000000000001</v>
@@ -18989,7 +19781,10 @@
         <v>0.5692</v>
       </c>
       <c r="AC276" t="n">
-        <v>0.7659600000000001</v>
+        <v>0.8835272727272727</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>0.6101555555555556</v>
       </c>
       <c r="AI276" t="n">
         <v>0.6080375000000001</v>
@@ -19057,7 +19852,10 @@
         <v>0.6575181818181818</v>
       </c>
       <c r="AC277" t="n">
-        <v>0.8135111111111111</v>
+        <v>0.6828615384615385</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>0.6498857142857143</v>
       </c>
       <c r="AI277" t="n">
         <v>0.6941900000000001</v>
@@ -19125,7 +19923,10 @@
         <v>0.6304499999999998</v>
       </c>
       <c r="AC278" t="n">
-        <v>0.7887700000000001</v>
+        <v>0.6131500000000001</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>0.6383181818181819</v>
       </c>
       <c r="AI278" t="n">
         <v>0.5813875000000001</v>
@@ -19193,7 +19994,10 @@
         <v>0.6911444444444445</v>
       </c>
       <c r="AC279" t="n">
-        <v>0.8302363636363637</v>
+        <v>0.784</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>0.479425</v>
       </c>
       <c r="AI279" t="n">
         <v>0.701675</v>
@@ -19261,7 +20065,10 @@
         <v>0.6052</v>
       </c>
       <c r="AC280" t="n">
-        <v>0.7131636363636363</v>
+        <v>0.5932727272727273</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>0.7653125000000001</v>
       </c>
       <c r="AI280" t="n">
         <v>0.7212833333333334</v>
@@ -19329,7 +20136,10 @@
         <v>0.5792888888888889</v>
       </c>
       <c r="AC281" t="n">
-        <v>0.810023076923077</v>
+        <v>0.510776923076923</v>
+      </c>
+      <c r="AG281" t="n">
+        <v>0.6362000000000001</v>
       </c>
       <c r="AI281" t="n">
         <v>0.6912166666666667</v>
@@ -19397,7 +20207,10 @@
         <v>0.7244916666666666</v>
       </c>
       <c r="AC282" t="n">
-        <v>0.7601545454545455</v>
+        <v>0.6183916666666667</v>
+      </c>
+      <c r="AG282" t="n">
+        <v>0.6117833333333333</v>
       </c>
       <c r="AI282" t="n">
         <v>0.7964818181818182</v>
@@ -19465,7 +20278,10 @@
         <v>0.6353090909090908</v>
       </c>
       <c r="AC283" t="n">
-        <v>0.8158499999999999</v>
+        <v>0.5914</v>
+      </c>
+      <c r="AG283" t="n">
+        <v>0.6411428571428572</v>
       </c>
       <c r="AI283" t="n">
         <v>0.6120642857142856</v>
@@ -19533,7 +20349,10 @@
         <v>0.6921625</v>
       </c>
       <c r="AC284" t="n">
-        <v>0.7985</v>
+        <v>0.4789100000000001</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>0.6673428571428571</v>
       </c>
       <c r="AI284" t="n">
         <v>0.7942444444444444</v>
@@ -19598,7 +20417,10 @@
         <v>0.7570818181818182</v>
       </c>
       <c r="AC285" t="n">
-        <v>0.679</v>
+        <v>0.789875</v>
+      </c>
+      <c r="AG285" t="n">
+        <v>0.7033700000000001</v>
       </c>
       <c r="AI285" t="n">
         <v>0.6682333333333333</v>
@@ -19666,7 +20488,10 @@
         <v>0.7657833333333331</v>
       </c>
       <c r="AC286" t="n">
-        <v>0.76997</v>
+        <v>0.61785</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>0.5954777777777778</v>
       </c>
       <c r="AI286" t="n">
         <v>0.557975</v>
@@ -19734,7 +20559,10 @@
         <v>0.6864666666666667</v>
       </c>
       <c r="AC287" t="n">
-        <v>0.8828818181818182</v>
+        <v>0.6519833333333335</v>
+      </c>
+      <c r="AG287" t="n">
+        <v>0.8079499999999999</v>
       </c>
       <c r="AI287" t="n">
         <v>0.6525166666666666</v>
@@ -19802,7 +20630,10 @@
         <v>0.7069666666666667</v>
       </c>
       <c r="AC288" t="n">
-        <v>0.7916583333333334</v>
+        <v>0.5246099999999999</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>0.6327363636363635</v>
       </c>
       <c r="AI288" t="n">
         <v>0.7697272727272728</v>
@@ -19870,7 +20701,10 @@
         <v>0.6086</v>
       </c>
       <c r="AC289" t="n">
-        <v>0.7966416666666668</v>
+        <v>0.7857416666666667</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>0.7100363636363637</v>
       </c>
       <c r="AI289" t="n">
         <v>0.7886666666666667</v>
@@ -19938,7 +20772,10 @@
         <v>0.7044100000000001</v>
       </c>
       <c r="AC290" t="n">
-        <v>0.76896</v>
+        <v>0.6232642857142858</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>0.6602500000000001</v>
       </c>
       <c r="AI290" t="n">
         <v>0.6970333333333334</v>
@@ -20006,7 +20843,10 @@
         <v>0.6983100000000001</v>
       </c>
       <c r="AC291" t="n">
-        <v>0.7798545454545455</v>
+        <v>0.7201307692307691</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>0.7329777777777778</v>
       </c>
       <c r="AI291" t="n">
         <v>0.74704</v>
@@ -20074,7 +20914,10 @@
         <v>0.48245</v>
       </c>
       <c r="AC292" t="n">
-        <v>0.8703181818181818</v>
+        <v>0.7859545454545455</v>
+      </c>
+      <c r="AG292" t="n">
+        <v>0.5553375</v>
       </c>
       <c r="AI292" t="n">
         <v>0.6335333333333334</v>
@@ -20142,7 +20985,10 @@
         <v>0.5845416666666667</v>
       </c>
       <c r="AC293" t="n">
-        <v>0.7761636363636364</v>
+        <v>0.7449</v>
+      </c>
+      <c r="AG293" t="n">
+        <v>0.4731625</v>
       </c>
       <c r="AI293" t="n">
         <v>0.717190909090909</v>
@@ -20210,7 +21056,10 @@
         <v>0.7699666666666666</v>
       </c>
       <c r="AC294" t="n">
-        <v>0.8166916666666667</v>
+        <v>0.51884</v>
+      </c>
+      <c r="AG294" t="n">
+        <v>0.5788099999999999</v>
       </c>
       <c r="AI294" t="n">
         <v>0.6918</v>
@@ -20278,7 +21127,10 @@
         <v>0.7778799999999999</v>
       </c>
       <c r="AC295" t="n">
-        <v>0.7560083333333334</v>
+        <v>0.7127916666666666</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>0.6827545454545454</v>
       </c>
       <c r="AI295" t="n">
         <v>0.6006166666666667</v>
@@ -20346,7 +21198,10 @@
         <v>0.6850307692307692</v>
       </c>
       <c r="AC296" t="n">
-        <v>0.8292571428571428</v>
+        <v>0.7771363636363637</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>0.5544400000000002</v>
       </c>
       <c r="AI296" t="n">
         <v>0.6607090909090909</v>
@@ -20414,7 +21269,10 @@
         <v>0.5437333333333333</v>
       </c>
       <c r="AC297" t="n">
-        <v>0.7179</v>
+        <v>0.7240090909090908</v>
+      </c>
+      <c r="AG297" t="n">
+        <v>0.5004222222222222</v>
       </c>
       <c r="AI297" t="n">
         <v>0.6926916666666666</v>
@@ -20482,7 +21340,10 @@
         <v>0.6059272727272728</v>
       </c>
       <c r="AC298" t="n">
-        <v>0.8125083333333335</v>
+        <v>0.6199416666666667</v>
+      </c>
+      <c r="AG298" t="n">
+        <v>0.6577888888888889</v>
       </c>
       <c r="AI298" t="n">
         <v>0.7512545454545454</v>
@@ -20550,7 +21411,10 @@
         <v>0.5445583333333334</v>
       </c>
       <c r="AC299" t="n">
-        <v>0.7862100000000001</v>
+        <v>0.5825699999999999</v>
+      </c>
+      <c r="AG299" t="n">
+        <v>0.5005727272727273</v>
       </c>
       <c r="AI299" t="n">
         <v>0.79486</v>
@@ -20618,7 +21482,10 @@
         <v>0.7297333333333333</v>
       </c>
       <c r="AC300" t="n">
-        <v>0.8091750000000001</v>
+        <v>0.5921666666666667</v>
+      </c>
+      <c r="AG300" t="n">
+        <v>0.4616125</v>
       </c>
       <c r="AI300" t="n">
         <v>0.6619250000000001</v>
@@ -20686,7 +21553,10 @@
         <v>0.7012454545454544</v>
       </c>
       <c r="AC301" t="n">
-        <v>0.7670769230769232</v>
+        <v>0.6927</v>
+      </c>
+      <c r="AG301" t="n">
+        <v>0.548025</v>
       </c>
       <c r="AI301" t="n">
         <v>0.6759833333333333</v>
@@ -20754,7 +21624,10 @@
         <v>0.5287333333333334</v>
       </c>
       <c r="AC302" t="n">
-        <v>0.8822599999999999</v>
+        <v>0.7154833333333332</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>0.7055666666666668</v>
       </c>
       <c r="AI302" t="n">
         <v>0.8137363636363637</v>
@@ -20822,7 +21695,10 @@
         <v>0.7496222222222222</v>
       </c>
       <c r="AC303" t="n">
-        <v>0.7861</v>
+        <v>0.6155846153846155</v>
+      </c>
+      <c r="AG303" t="n">
+        <v>0.7041666666666667</v>
       </c>
       <c r="AI303" t="n">
         <v>0.6278818181818181</v>
@@ -20890,7 +21766,10 @@
         <v>0.6539374999999999</v>
       </c>
       <c r="AC304" t="n">
-        <v>0.8343666666666666</v>
+        <v>0.6663666666666668</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>0.6187666666666667</v>
       </c>
       <c r="AI304" t="n">
         <v>0.6649999999999999</v>
@@ -20958,7 +21837,10 @@
         <v>0.7149666666666668</v>
       </c>
       <c r="AC305" t="n">
-        <v>0.6367</v>
+        <v>0.5321666666666667</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>0.5088625</v>
       </c>
       <c r="AI305" t="n">
         <v>0.7369615384615383</v>
@@ -21026,7 +21908,10 @@
         <v>0.62009</v>
       </c>
       <c r="AC306" t="n">
-        <v>0.7104199999999999</v>
+        <v>0.67135</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>0.6848909090909091</v>
       </c>
       <c r="AI306" t="n">
         <v>0.5822999999999999</v>
@@ -21094,7 +21979,10 @@
         <v>0.8117500000000002</v>
       </c>
       <c r="AC307" t="n">
-        <v>0.826325</v>
+        <v>0.6589090909090909</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>0.6076777777777778</v>
       </c>
       <c r="AI307" t="n">
         <v>0.6626199999999999</v>
@@ -21162,7 +22050,10 @@
         <v>0.73348</v>
       </c>
       <c r="AC308" t="n">
-        <v>0.71153</v>
+        <v>0.591325</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>0.6058285714285715</v>
       </c>
       <c r="AI308" t="n">
         <v>0.6873090909090909</v>
@@ -21230,7 +22121,10 @@
         <v>0.6241428571428572</v>
       </c>
       <c r="AC309" t="n">
-        <v>0.9014416666666666</v>
+        <v>0.7921454545454545</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>0.6448333333333333</v>
       </c>
       <c r="AI309" t="n">
         <v>0.7913444444444444</v>
@@ -21298,7 +22192,10 @@
         <v>0.6362999999999999</v>
       </c>
       <c r="AC310" t="n">
-        <v>0.7578900000000001</v>
+        <v>0.7512714285714285</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>0.67424</v>
       </c>
       <c r="AI310" t="n">
         <v>0.8221999999999999</v>
@@ -21366,7 +22263,10 @@
         <v>0.6525909090909091</v>
       </c>
       <c r="AC311" t="n">
-        <v>0.8588909090909091</v>
+        <v>0.6005499999999999</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>0.5765636363636364</v>
       </c>
       <c r="AI311" t="n">
         <v>0.7314700000000001</v>
@@ -21467,7 +22367,10 @@
         <v>0.0047</v>
       </c>
       <c r="AC316" t="n">
-        <v>0.293</v>
+        <v>0</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>0.0001</v>
       </c>
       <c r="AI316" t="n">
         <v>0.0003</v>
@@ -21544,7 +22447,10 @@
         <v>0.005</v>
       </c>
       <c r="AC317" t="n">
-        <v>0.2067</v>
+        <v>0.0005</v>
+      </c>
+      <c r="AG317" t="n">
+        <v>0.0011</v>
       </c>
       <c r="AI317" t="n">
         <v>0.0003</v>
@@ -21621,7 +22527,10 @@
         <v>0.0199</v>
       </c>
       <c r="AC318" t="n">
-        <v>0.4589</v>
+        <v>0.0185</v>
+      </c>
+      <c r="AG318" t="n">
+        <v>0.008999999999999999</v>
       </c>
       <c r="AI318" t="n">
         <v>0.0005</v>
@@ -21698,7 +22607,10 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="AC319" t="n">
-        <v>0.2224</v>
+        <v>0.0504</v>
+      </c>
+      <c r="AG319" t="n">
+        <v>0.0327</v>
       </c>
       <c r="AI319" t="n">
         <v>0.0034</v>
@@ -21775,7 +22687,10 @@
         <v>0.1119</v>
       </c>
       <c r="AC320" t="n">
-        <v>0.2555</v>
+        <v>0.0428</v>
+      </c>
+      <c r="AG320" t="n">
+        <v>0.0883</v>
       </c>
       <c r="AI320" t="n">
         <v>0.0159</v>
@@ -21852,7 +22767,10 @@
         <v>0.0568</v>
       </c>
       <c r="AC321" t="n">
-        <v>0.1289</v>
+        <v>0.0482</v>
+      </c>
+      <c r="AG321" t="n">
+        <v>0.029</v>
       </c>
       <c r="AI321" t="n">
         <v>0.0357</v>
@@ -21929,7 +22847,10 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="AC322" t="n">
-        <v>0.5621</v>
+        <v>0.0514</v>
+      </c>
+      <c r="AG322" t="n">
+        <v>0.0738</v>
       </c>
       <c r="AI322" t="n">
         <v>0.0247</v>
@@ -22006,7 +22927,10 @@
         <v>0.0606</v>
       </c>
       <c r="AC323" t="n">
-        <v>0.377</v>
+        <v>0.0683</v>
+      </c>
+      <c r="AG323" t="n">
+        <v>0.0521</v>
       </c>
       <c r="AI323" t="n">
         <v>0</v>
@@ -22083,7 +23007,10 @@
         <v>0.0897</v>
       </c>
       <c r="AC324" t="n">
-        <v>0.2501</v>
+        <v>0.0605</v>
+      </c>
+      <c r="AG324" t="n">
+        <v>0.0775</v>
       </c>
       <c r="AI324" t="n">
         <v>0.0677</v>
@@ -22160,7 +23087,10 @@
         <v>0.0934</v>
       </c>
       <c r="AC325" t="n">
-        <v>0.2059</v>
+        <v>0.0073</v>
+      </c>
+      <c r="AG325" t="n">
+        <v>0.07779999999999999</v>
       </c>
       <c r="AI325" t="n">
         <v>0.0137</v>
@@ -22228,7 +23158,10 @@
         <v>0.098</v>
       </c>
       <c r="AC326" t="n">
-        <v>0.1342</v>
+        <v>0.0274</v>
+      </c>
+      <c r="AG326" t="n">
+        <v>0.1193</v>
       </c>
       <c r="AI326" t="n">
         <v>0.0101</v>
@@ -22296,7 +23229,10 @@
         <v>0.07489999999999999</v>
       </c>
       <c r="AC327" t="n">
-        <v>0.3377</v>
+        <v>0.0547</v>
+      </c>
+      <c r="AG327" t="n">
+        <v>0.0999</v>
       </c>
       <c r="AI327" t="n">
         <v>0.0092</v>
@@ -22364,7 +23300,10 @@
         <v>0.1351</v>
       </c>
       <c r="AC328" t="n">
-        <v>0.3543</v>
+        <v>0.083</v>
+      </c>
+      <c r="AG328" t="n">
+        <v>0.1124</v>
       </c>
       <c r="AI328" t="n">
         <v>0.0363</v>
@@ -22432,7 +23371,10 @@
         <v>0.0786</v>
       </c>
       <c r="AC329" t="n">
-        <v>0.302</v>
+        <v>0.0585</v>
+      </c>
+      <c r="AG329" t="n">
+        <v>0.1336</v>
       </c>
       <c r="AI329" t="n">
         <v>0.0482</v>
@@ -22500,7 +23442,10 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="AC330" t="n">
-        <v>0.3552</v>
+        <v>0.1335</v>
+      </c>
+      <c r="AG330" t="n">
+        <v>0.1333</v>
       </c>
       <c r="AI330" t="n">
         <v>0.0463</v>
@@ -22568,7 +23513,10 @@
         <v>0.0833</v>
       </c>
       <c r="AC331" t="n">
-        <v>0.3816</v>
+        <v>0.0939</v>
+      </c>
+      <c r="AG331" t="n">
+        <v>0.123</v>
       </c>
       <c r="AI331" t="n">
         <v>0.0259</v>
@@ -22636,7 +23584,10 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="AC332" t="n">
-        <v>0.3935</v>
+        <v>0.0735</v>
+      </c>
+      <c r="AG332" t="n">
+        <v>0.1625</v>
       </c>
       <c r="AI332" t="n">
         <v>0.0474</v>
@@ -22704,7 +23655,10 @@
         <v>0.0751</v>
       </c>
       <c r="AC333" t="n">
-        <v>0.3258</v>
+        <v>0.0921</v>
+      </c>
+      <c r="AG333" t="n">
+        <v>0.0973</v>
       </c>
       <c r="AI333" t="n">
         <v>0.0008</v>
@@ -22772,7 +23726,10 @@
         <v>0.0668</v>
       </c>
       <c r="AC334" t="n">
-        <v>0.2384</v>
+        <v>0.07770000000000001</v>
+      </c>
+      <c r="AG334" t="n">
+        <v>0.098</v>
       </c>
       <c r="AI334" t="n">
         <v>0.0188</v>
@@ -22840,7 +23797,10 @@
         <v>0.1011</v>
       </c>
       <c r="AC335" t="n">
-        <v>0.2158</v>
+        <v>0.1596</v>
+      </c>
+      <c r="AG335" t="n">
+        <v>0.098</v>
       </c>
       <c r="AI335" t="n">
         <v>0.0188</v>
@@ -22908,7 +23868,10 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="AC336" t="n">
-        <v>0.2395</v>
+        <v>0.1138</v>
+      </c>
+      <c r="AG336" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="AI336" t="n">
         <v>0.0442</v>
@@ -22976,7 +23939,10 @@
         <v>0.0477</v>
       </c>
       <c r="AC337" t="n">
-        <v>0.2683</v>
+        <v>0.1322</v>
+      </c>
+      <c r="AG337" t="n">
+        <v>0.1092</v>
       </c>
       <c r="AI337" t="n">
         <v>0.0232</v>
@@ -23044,7 +24010,10 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="AC338" t="n">
-        <v>0.221</v>
+        <v>0.132</v>
+      </c>
+      <c r="AG338" t="n">
+        <v>0.174</v>
       </c>
       <c r="AI338" t="n">
         <v>0.0334</v>
@@ -23112,7 +24081,10 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="AC339" t="n">
-        <v>0.2652</v>
+        <v>0.0704</v>
+      </c>
+      <c r="AG339" t="n">
+        <v>0.1212</v>
       </c>
       <c r="AI339" t="n">
         <v>0.0115</v>
@@ -23180,7 +24152,10 @@
         <v>0.1139</v>
       </c>
       <c r="AC340" t="n">
-        <v>0.2437</v>
+        <v>0.0622</v>
+      </c>
+      <c r="AG340" t="n">
+        <v>0.1672</v>
       </c>
       <c r="AI340" t="n">
         <v>0.0327</v>
@@ -23248,7 +24223,10 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="AC341" t="n">
-        <v>0.2178</v>
+        <v>0.0709</v>
+      </c>
+      <c r="AG341" t="n">
+        <v>0.1078</v>
       </c>
       <c r="AI341" t="n">
         <v>0.0213</v>
@@ -23316,7 +24294,10 @@
         <v>0.0784</v>
       </c>
       <c r="AC342" t="n">
-        <v>0.2679</v>
+        <v>0.0992</v>
+      </c>
+      <c r="AG342" t="n">
+        <v>0.0973</v>
       </c>
       <c r="AI342" t="n">
         <v>0.0279</v>
@@ -23384,7 +24365,10 @@
         <v>0.063</v>
       </c>
       <c r="AC343" t="n">
-        <v>0.2669</v>
+        <v>0.0813</v>
+      </c>
+      <c r="AG343" t="n">
+        <v>0.1529</v>
       </c>
       <c r="AI343" t="n">
         <v>0.0208</v>
@@ -23452,7 +24436,10 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="AC344" t="n">
-        <v>0.1945</v>
+        <v>0.1049</v>
+      </c>
+      <c r="AG344" t="n">
+        <v>0.1</v>
       </c>
       <c r="AI344" t="n">
         <v>0.0244</v>
@@ -23520,7 +24507,10 @@
         <v>0.06859999999999999</v>
       </c>
       <c r="AC345" t="n">
-        <v>0.2959</v>
+        <v>0.1039</v>
+      </c>
+      <c r="AG345" t="n">
+        <v>0.1345</v>
       </c>
       <c r="AI345" t="n">
         <v>0.0138</v>
@@ -23588,7 +24578,10 @@
         <v>0.0736</v>
       </c>
       <c r="AC346" t="n">
-        <v>0.2954</v>
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="AG346" t="n">
+        <v>0.1275</v>
       </c>
       <c r="AI346" t="n">
         <v>0.0371</v>
@@ -23656,7 +24649,10 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="AC347" t="n">
-        <v>0.2613</v>
+        <v>0.0741</v>
+      </c>
+      <c r="AG347" t="n">
+        <v>0.101</v>
       </c>
       <c r="AI347" t="n">
         <v>0.0214</v>
@@ -23724,7 +24720,10 @@
         <v>0.0765</v>
       </c>
       <c r="AC348" t="n">
-        <v>0.2979</v>
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="AG348" t="n">
+        <v>0.1233</v>
       </c>
       <c r="AI348" t="n">
         <v>0.025</v>
@@ -23792,7 +24791,10 @@
         <v>0.0468</v>
       </c>
       <c r="AC349" t="n">
-        <v>0.3478</v>
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="AG349" t="n">
+        <v>0.1487</v>
       </c>
       <c r="AI349" t="n">
         <v>0.03</v>
@@ -23860,7 +24862,10 @@
         <v>0.0634</v>
       </c>
       <c r="AC350" t="n">
-        <v>0.3019</v>
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="AG350" t="n">
+        <v>0.1065</v>
       </c>
       <c r="AI350" t="n">
         <v>0.0275</v>
@@ -23928,7 +24933,10 @@
         <v>0.0611</v>
       </c>
       <c r="AC351" t="n">
-        <v>0.2835</v>
+        <v>0.0712</v>
+      </c>
+      <c r="AG351" t="n">
+        <v>0.1043</v>
       </c>
       <c r="AI351" t="n">
         <v>0.0177</v>
@@ -23996,7 +25004,10 @@
         <v>0.0599</v>
       </c>
       <c r="AC352" t="n">
-        <v>0.303</v>
+        <v>0.055</v>
+      </c>
+      <c r="AG352" t="n">
+        <v>0.113</v>
       </c>
       <c r="AI352" t="n">
         <v>0.0144</v>
@@ -24064,7 +25075,10 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="AC353" t="n">
-        <v>0.309</v>
+        <v>0.06</v>
+      </c>
+      <c r="AG353" t="n">
+        <v>0.1133</v>
       </c>
       <c r="AI353" t="n">
         <v>0.0124</v>
@@ -24132,7 +25146,10 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="AC354" t="n">
-        <v>0.3185</v>
+        <v>0.06</v>
+      </c>
+      <c r="AG354" t="n">
+        <v>0.1105</v>
       </c>
       <c r="AI354" t="n">
         <v>0.008500000000000001</v>
@@ -24200,7 +25217,10 @@
         <v>0.0732</v>
       </c>
       <c r="AC355" t="n">
-        <v>0.2363</v>
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="AG355" t="n">
+        <v>0.1289</v>
       </c>
       <c r="AI355" t="n">
         <v>0.0208</v>
@@ -24268,7 +25288,10 @@
         <v>0.0586</v>
       </c>
       <c r="AC356" t="n">
-        <v>0.2625</v>
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="AG356" t="n">
+        <v>0.0897</v>
       </c>
       <c r="AI356" t="n">
         <v>0.0249</v>
@@ -24336,7 +25359,10 @@
         <v>0.057</v>
       </c>
       <c r="AC357" t="n">
-        <v>0.3122</v>
+        <v>0.1074</v>
+      </c>
+      <c r="AG357" t="n">
+        <v>0.1079</v>
       </c>
       <c r="AI357" t="n">
         <v>0.0091</v>
@@ -24404,7 +25430,10 @@
         <v>0.0576</v>
       </c>
       <c r="AC358" t="n">
-        <v>0.2671</v>
+        <v>0.1081</v>
+      </c>
+      <c r="AG358" t="n">
+        <v>0.1009</v>
       </c>
       <c r="AI358" t="n">
         <v>0.0264</v>
@@ -24472,7 +25501,10 @@
         <v>0.0526</v>
       </c>
       <c r="AC359" t="n">
-        <v>0.2504</v>
+        <v>0.0649</v>
+      </c>
+      <c r="AG359" t="n">
+        <v>0.1047</v>
       </c>
       <c r="AI359" t="n">
         <v>0.0197</v>
@@ -24540,7 +25572,10 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="AC360" t="n">
-        <v>0.2273</v>
+        <v>0.0818</v>
+      </c>
+      <c r="AG360" t="n">
+        <v>0.1035</v>
       </c>
       <c r="AI360" t="n">
         <v>0.0134</v>
@@ -24608,7 +25643,10 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="AC361" t="n">
-        <v>0.2306</v>
+        <v>0.118</v>
+      </c>
+      <c r="AG361" t="n">
+        <v>0.115</v>
       </c>
       <c r="AI361" t="n">
         <v>0.0134</v>
@@ -24676,7 +25714,10 @@
         <v>0.0623</v>
       </c>
       <c r="AC362" t="n">
-        <v>0.2772</v>
+        <v>0.0769</v>
+      </c>
+      <c r="AG362" t="n">
+        <v>0.1009</v>
       </c>
       <c r="AI362" t="n">
         <v>0.0223</v>
@@ -24744,7 +25785,10 @@
         <v>0.0546</v>
       </c>
       <c r="AC363" t="n">
-        <v>0.2291</v>
+        <v>0.1271</v>
+      </c>
+      <c r="AG363" t="n">
+        <v>0.1013</v>
       </c>
       <c r="AI363" t="n">
         <v>0.027</v>
@@ -24812,7 +25856,10 @@
         <v>0.0536</v>
       </c>
       <c r="AC364" t="n">
-        <v>0.2518</v>
+        <v>0.0953</v>
+      </c>
+      <c r="AG364" t="n">
+        <v>0.0902</v>
       </c>
       <c r="AI364" t="n">
         <v>0.0282</v>
@@ -24880,7 +25927,10 @@
         <v>0.0525</v>
       </c>
       <c r="AC365" t="n">
-        <v>0.3212</v>
+        <v>0.1078</v>
+      </c>
+      <c r="AG365" t="n">
+        <v>0.1037</v>
       </c>
       <c r="AI365" t="n">
         <v>0.0246</v>
@@ -24948,7 +25998,10 @@
         <v>0.0545</v>
       </c>
       <c r="AC366" t="n">
-        <v>0.2958</v>
+        <v>0.0736</v>
+      </c>
+      <c r="AG366" t="n">
+        <v>0.1019</v>
       </c>
       <c r="AI366" t="n">
         <v>0.0209</v>
@@ -25016,7 +26069,10 @@
         <v>0.0708</v>
       </c>
       <c r="AC367" t="n">
-        <v>0.2597</v>
+        <v>0.07539999999999999</v>
+      </c>
+      <c r="AG367" t="n">
+        <v>0.1003</v>
       </c>
       <c r="AI367" t="n">
         <v>0.0181</v>
@@ -25084,7 +26140,10 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="AC368" t="n">
-        <v>0.2718</v>
+        <v>0.0397</v>
+      </c>
+      <c r="AG368" t="n">
+        <v>0.0859</v>
       </c>
       <c r="AI368" t="n">
         <v>0.0218</v>
@@ -25152,7 +26211,10 @@
         <v>0.0786</v>
       </c>
       <c r="AC369" t="n">
-        <v>0.2503</v>
+        <v>0.0575</v>
+      </c>
+      <c r="AG369" t="n">
+        <v>0.0867</v>
       </c>
       <c r="AI369" t="n">
         <v>0.0209</v>
@@ -25220,7 +26282,10 @@
         <v>0.066</v>
       </c>
       <c r="AC370" t="n">
-        <v>0.2768</v>
+        <v>0.0593</v>
+      </c>
+      <c r="AG370" t="n">
+        <v>0.0828</v>
       </c>
       <c r="AI370" t="n">
         <v>0.017</v>
@@ -25288,7 +26353,10 @@
         <v>0.0634</v>
       </c>
       <c r="AC371" t="n">
-        <v>0.2604</v>
+        <v>0.0621</v>
+      </c>
+      <c r="AG371" t="n">
+        <v>0.0898</v>
       </c>
       <c r="AI371" t="n">
         <v>0.0209</v>
@@ -25356,7 +26424,10 @@
         <v>0.0561</v>
       </c>
       <c r="AC372" t="n">
-        <v>0.2355</v>
+        <v>0.048</v>
+      </c>
+      <c r="AG372" t="n">
+        <v>0.0813</v>
       </c>
       <c r="AI372" t="n">
         <v>0.0204</v>
@@ -25424,7 +26495,10 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="AC373" t="n">
-        <v>0.24</v>
+        <v>0.059</v>
+      </c>
+      <c r="AG373" t="n">
+        <v>0.0708</v>
       </c>
       <c r="AI373" t="n">
         <v>0.0247</v>
@@ -25492,7 +26566,10 @@
         <v>0.0892</v>
       </c>
       <c r="AC374" t="n">
-        <v>0.268</v>
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="AG374" t="n">
+        <v>0.0838</v>
       </c>
       <c r="AI374" t="n">
         <v>0.0589</v>
@@ -25560,7 +26637,10 @@
         <v>0.0791</v>
       </c>
       <c r="AC375" t="n">
-        <v>0.2589</v>
+        <v>0.0667</v>
+      </c>
+      <c r="AG375" t="n">
+        <v>0.0761</v>
       </c>
       <c r="AI375" t="n">
         <v>0.0366</v>
@@ -25628,7 +26708,10 @@
         <v>0.0693</v>
       </c>
       <c r="AC376" t="n">
-        <v>0.2692</v>
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AG376" t="n">
+        <v>0.0946</v>
       </c>
       <c r="AI376" t="n">
         <v>0.0282</v>
@@ -25696,7 +26779,10 @@
         <v>0.0598</v>
       </c>
       <c r="AC377" t="n">
-        <v>0.2553</v>
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="AG377" t="n">
+        <v>0.1018</v>
       </c>
       <c r="AI377" t="n">
         <v>0.0202</v>
@@ -25764,7 +26850,10 @@
         <v>0.0602</v>
       </c>
       <c r="AC378" t="n">
-        <v>0.2738</v>
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="AG378" t="n">
+        <v>0.094</v>
       </c>
       <c r="AI378" t="n">
         <v>0.0222</v>
@@ -25832,7 +26921,10 @@
         <v>0.0603</v>
       </c>
       <c r="AC379" t="n">
-        <v>0.2734</v>
+        <v>0.0767</v>
+      </c>
+      <c r="AG379" t="n">
+        <v>0.0994</v>
       </c>
       <c r="AI379" t="n">
         <v>0.0199</v>
@@ -25900,7 +26992,10 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="AC380" t="n">
-        <v>0.2439</v>
+        <v>0.078</v>
+      </c>
+      <c r="AG380" t="n">
+        <v>0.1002</v>
       </c>
       <c r="AI380" t="n">
         <v>0.0172</v>
@@ -25968,7 +27063,10 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="AC381" t="n">
-        <v>0.2187</v>
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="AG381" t="n">
+        <v>0.0973</v>
       </c>
       <c r="AI381" t="n">
         <v>0.0203</v>
@@ -26036,7 +27134,10 @@
         <v>0.0849</v>
       </c>
       <c r="AC382" t="n">
-        <v>0.2221</v>
+        <v>0.0492</v>
+      </c>
+      <c r="AG382" t="n">
+        <v>0.0391</v>
       </c>
       <c r="AI382" t="n">
         <v>0.0169</v>
@@ -26104,7 +27205,10 @@
         <v>0.0698</v>
       </c>
       <c r="AC383" t="n">
-        <v>0.2112</v>
+        <v>0.0593</v>
+      </c>
+      <c r="AG383" t="n">
+        <v>0.0447</v>
       </c>
       <c r="AI383" t="n">
         <v>0.018</v>
@@ -26172,7 +27276,10 @@
         <v>0.06950000000000001</v>
       </c>
       <c r="AC384" t="n">
-        <v>0.2726</v>
+        <v>0.0741</v>
+      </c>
+      <c r="AG384" t="n">
+        <v>0.0494</v>
       </c>
       <c r="AI384" t="n">
         <v>0.0227</v>
@@ -26240,7 +27347,10 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="AC385" t="n">
-        <v>0.2032</v>
+        <v>0.081</v>
+      </c>
+      <c r="AG385" t="n">
+        <v>0.0575</v>
       </c>
       <c r="AI385" t="n">
         <v>0.0274</v>
@@ -26308,7 +27418,10 @@
         <v>0.0497</v>
       </c>
       <c r="AC386" t="n">
-        <v>0.2444</v>
+        <v>0.0687</v>
+      </c>
+      <c r="AG386" t="n">
+        <v>0.052</v>
       </c>
       <c r="AI386" t="n">
         <v>0.0239</v>
@@ -26376,7 +27489,10 @@
         <v>0.0494</v>
       </c>
       <c r="AC387" t="n">
-        <v>0.2356</v>
+        <v>0.0994</v>
+      </c>
+      <c r="AG387" t="n">
+        <v>0.0364</v>
       </c>
       <c r="AI387" t="n">
         <v>0.02</v>
@@ -26444,7 +27560,10 @@
         <v>0.0606</v>
       </c>
       <c r="AC388" t="n">
-        <v>0.2194</v>
+        <v>0.0761</v>
+      </c>
+      <c r="AG388" t="n">
+        <v>0.0379</v>
       </c>
       <c r="AI388" t="n">
         <v>0.0249</v>
@@ -26512,7 +27631,10 @@
         <v>0.0716</v>
       </c>
       <c r="AC389" t="n">
-        <v>0.2235</v>
+        <v>0.0623</v>
+      </c>
+      <c r="AG389" t="n">
+        <v>0.0208</v>
       </c>
       <c r="AI389" t="n">
         <v>0.0281</v>
@@ -26580,7 +27702,10 @@
         <v>0.0549</v>
       </c>
       <c r="AC390" t="n">
-        <v>0.226</v>
+        <v>0.0614</v>
+      </c>
+      <c r="AG390" t="n">
+        <v>0.028</v>
       </c>
       <c r="AI390" t="n">
         <v>0.0277</v>
@@ -26648,7 +27773,10 @@
         <v>0.0622</v>
       </c>
       <c r="AC391" t="n">
-        <v>0.2157</v>
+        <v>0.0747</v>
+      </c>
+      <c r="AG391" t="n">
+        <v>0.0335</v>
       </c>
       <c r="AI391" t="n">
         <v>0.0166</v>
@@ -26716,7 +27844,10 @@
         <v>0.0587</v>
       </c>
       <c r="AC392" t="n">
-        <v>0.2336</v>
+        <v>0.07580000000000001</v>
+      </c>
+      <c r="AG392" t="n">
+        <v>0.0199</v>
       </c>
       <c r="AI392" t="n">
         <v>0.0215</v>
@@ -26784,7 +27915,10 @@
         <v>0.0709</v>
       </c>
       <c r="AC393" t="n">
-        <v>0.232</v>
+        <v>0.0608</v>
+      </c>
+      <c r="AG393" t="n">
+        <v>0.036</v>
       </c>
       <c r="AI393" t="n">
         <v>0.0229</v>
@@ -26852,7 +27986,10 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="AC394" t="n">
-        <v>0.2388</v>
+        <v>0.0965</v>
+      </c>
+      <c r="AG394" t="n">
+        <v>0.0159</v>
       </c>
       <c r="AI394" t="n">
         <v>0.0217</v>
@@ -26920,7 +28057,10 @@
         <v>0.0677</v>
       </c>
       <c r="AC395" t="n">
-        <v>0.2506</v>
+        <v>0.0747</v>
+      </c>
+      <c r="AG395" t="n">
+        <v>0.0389</v>
       </c>
       <c r="AI395" t="n">
         <v>0.0209</v>
@@ -26988,7 +28128,10 @@
         <v>0.0601</v>
       </c>
       <c r="AC396" t="n">
-        <v>0.2643</v>
+        <v>0.0687</v>
+      </c>
+      <c r="AG396" t="n">
+        <v>0.029</v>
       </c>
       <c r="AI396" t="n">
         <v>0.0208</v>
@@ -27056,7 +28199,10 @@
         <v>0.0712</v>
       </c>
       <c r="AC397" t="n">
-        <v>0.2382</v>
+        <v>0.0696</v>
+      </c>
+      <c r="AG397" t="n">
+        <v>0.0346</v>
       </c>
       <c r="AI397" t="n">
         <v>0.0186</v>
@@ -27124,7 +28270,10 @@
         <v>0.0737</v>
       </c>
       <c r="AC398" t="n">
-        <v>0.2418</v>
+        <v>0.0712</v>
+      </c>
+      <c r="AG398" t="n">
+        <v>0.0388</v>
       </c>
       <c r="AI398" t="n">
         <v>0.0193</v>
@@ -27192,7 +28341,10 @@
         <v>0.0648</v>
       </c>
       <c r="AC399" t="n">
-        <v>0.2329</v>
+        <v>0.081</v>
+      </c>
+      <c r="AG399" t="n">
+        <v>0.0197</v>
       </c>
       <c r="AI399" t="n">
         <v>0.0227</v>
@@ -27260,7 +28412,10 @@
         <v>0.0677</v>
       </c>
       <c r="AC400" t="n">
-        <v>0.2705</v>
+        <v>0.0644</v>
+      </c>
+      <c r="AG400" t="n">
+        <v>0.0232</v>
       </c>
       <c r="AI400" t="n">
         <v>0.0304</v>
@@ -27328,7 +28483,10 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="AC401" t="n">
-        <v>0.3021</v>
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="AG401" t="n">
+        <v>0.0375</v>
       </c>
       <c r="AI401" t="n">
         <v>0.0201</v>
@@ -27396,7 +28554,10 @@
         <v>0.0882</v>
       </c>
       <c r="AC402" t="n">
-        <v>0.2261</v>
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="AG402" t="n">
+        <v>0.0298</v>
       </c>
       <c r="AI402" t="n">
         <v>0.0244</v>
@@ -27464,7 +28625,10 @@
         <v>0.0851</v>
       </c>
       <c r="AC403" t="n">
-        <v>0.1723</v>
+        <v>0.0612</v>
+      </c>
+      <c r="AG403" t="n">
+        <v>0.0273</v>
       </c>
       <c r="AI403" t="n">
         <v>0.0215</v>
@@ -27532,7 +28696,10 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="AC404" t="n">
-        <v>0.2499</v>
+        <v>0.0731</v>
+      </c>
+      <c r="AG404" t="n">
+        <v>0.0291</v>
       </c>
       <c r="AI404" t="n">
         <v>0.0283</v>
@@ -27600,7 +28767,10 @@
         <v>0.0815</v>
       </c>
       <c r="AC405" t="n">
-        <v>0.2403</v>
+        <v>0.0645</v>
+      </c>
+      <c r="AG405" t="n">
+        <v>0.0438</v>
       </c>
       <c r="AI405" t="n">
         <v>0.0148</v>
@@ -27668,7 +28838,10 @@
         <v>0.0623</v>
       </c>
       <c r="AC406" t="n">
-        <v>0.2287</v>
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="AG406" t="n">
+        <v>0.0474</v>
       </c>
       <c r="AI406" t="n">
         <v>0.0246</v>
@@ -27736,7 +28909,10 @@
         <v>0.0759</v>
       </c>
       <c r="AC407" t="n">
-        <v>0.184</v>
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="AG407" t="n">
+        <v>0.0294</v>
       </c>
       <c r="AI407" t="n">
         <v>0.0187</v>
@@ -27804,7 +28980,10 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="AC408" t="n">
-        <v>0.1672</v>
+        <v>0.0809</v>
+      </c>
+      <c r="AG408" t="n">
+        <v>0.0321</v>
       </c>
       <c r="AI408" t="n">
         <v>0.0214</v>
@@ -27872,7 +29051,10 @@
         <v>0.0732</v>
       </c>
       <c r="AC409" t="n">
-        <v>0.216</v>
+        <v>0.0639</v>
+      </c>
+      <c r="AG409" t="n">
+        <v>0.0293</v>
       </c>
       <c r="AI409" t="n">
         <v>0.0263</v>
@@ -27940,7 +29122,10 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="AC410" t="n">
-        <v>0.2245</v>
+        <v>0.0573</v>
+      </c>
+      <c r="AG410" t="n">
+        <v>0.0449</v>
       </c>
       <c r="AI410" t="n">
         <v>0.0159</v>
@@ -28008,7 +29193,10 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="AC411" t="n">
-        <v>0.2363</v>
+        <v>0.0815</v>
+      </c>
+      <c r="AG411" t="n">
+        <v>0.0331</v>
       </c>
       <c r="AI411" t="n">
         <v>0.018</v>
@@ -28076,7 +29264,10 @@
         <v>0.0593</v>
       </c>
       <c r="AC412" t="n">
-        <v>0.1994</v>
+        <v>0.0692</v>
+      </c>
+      <c r="AG412" t="n">
+        <v>0.0348</v>
       </c>
       <c r="AI412" t="n">
         <v>0.0234</v>
@@ -28144,7 +29335,10 @@
         <v>0.0718</v>
       </c>
       <c r="AC413" t="n">
-        <v>0.2372</v>
+        <v>0.0514</v>
+      </c>
+      <c r="AG413" t="n">
+        <v>0.0454</v>
       </c>
       <c r="AI413" t="n">
         <v>0.0247</v>
@@ -28212,7 +29406,10 @@
         <v>0.0757</v>
       </c>
       <c r="AC414" t="n">
-        <v>0.2534</v>
+        <v>0.0537</v>
+      </c>
+      <c r="AG414" t="n">
+        <v>0.0332</v>
       </c>
       <c r="AI414" t="n">
         <v>0.0213</v>
@@ -28280,7 +29477,10 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="AC415" t="n">
-        <v>0.2301</v>
+        <v>0.0513</v>
+      </c>
+      <c r="AG415" t="n">
+        <v>0.0246</v>
       </c>
       <c r="AI415" t="n">
         <v>0.0193</v>
@@ -28341,7 +29541,10 @@
         <v>0.16215</v>
       </c>
       <c r="AC418" t="n">
-        <v>0.203975</v>
+        <v>0.1534222222222222</v>
+      </c>
+      <c r="AG418" t="n">
+        <v>0.150375</v>
       </c>
       <c r="AI418" t="n">
         <v>0.11844</v>
@@ -28388,7 +29591,10 @@
         <v>0.1993166666666667</v>
       </c>
       <c r="AC419" t="n">
-        <v>0.1578</v>
+        <v>0.1649125</v>
+      </c>
+      <c r="AG419" t="n">
+        <v>0.1805142857142857</v>
       </c>
       <c r="AI419" t="n">
         <v>0.1168142857142857</v>
@@ -28435,7 +29641,10 @@
         <v>0.21489</v>
       </c>
       <c r="AC420" t="n">
-        <v>0.2339181818181818</v>
+        <v>0.22192</v>
+      </c>
+      <c r="AG420" t="n">
+        <v>0.21036</v>
       </c>
       <c r="AI420" t="n">
         <v>0.2085875</v>
@@ -28482,7 +29691,10 @@
         <v>0.1975</v>
       </c>
       <c r="AC421" t="n">
-        <v>0.21715</v>
+        <v>0.2449</v>
+      </c>
+      <c r="AG421" t="n">
+        <v>0.252225</v>
       </c>
       <c r="AI421" t="n">
         <v>0.28051</v>
@@ -28529,7 +29741,10 @@
         <v>0.2463125</v>
       </c>
       <c r="AC422" t="n">
-        <v>0.2825545454545454</v>
+        <v>0.2429181818181818</v>
+      </c>
+      <c r="AG422" t="n">
+        <v>0.2460166666666667</v>
       </c>
       <c r="AI422" t="n">
         <v>0.29418</v>
@@ -28576,7 +29791,10 @@
         <v>0.3504888888888888</v>
       </c>
       <c r="AC423" t="n">
-        <v>0.2945888888888889</v>
+        <v>0.2873692307692307</v>
+      </c>
+      <c r="AG423" t="n">
+        <v>0.30364</v>
       </c>
       <c r="AI423" t="n">
         <v>0.30703</v>
@@ -28623,7 +29841,10 @@
         <v>0.3586111111111111</v>
       </c>
       <c r="AC424" t="n">
-        <v>0.3743428571428571</v>
+        <v>0.3680125</v>
+      </c>
+      <c r="AG424" t="n">
+        <v>0.35805</v>
       </c>
       <c r="AI424" t="n">
         <v>0.32345</v>
@@ -28670,7 +29891,10 @@
         <v>0.38989</v>
       </c>
       <c r="AC425" t="n">
-        <v>0.39163</v>
+        <v>0.4224416666666668</v>
+      </c>
+      <c r="AG425" t="n">
+        <v>0.3969</v>
       </c>
       <c r="AI425" t="n">
         <v>0.4134384615384615</v>
@@ -28717,7 +29941,10 @@
         <v>0.45862</v>
       </c>
       <c r="AC426" t="n">
-        <v>0.41951</v>
+        <v>0.4952454545454547</v>
+      </c>
+      <c r="AG426" t="n">
+        <v>0.4283750000000001</v>
       </c>
       <c r="AI426" t="n">
         <v>0.41214</v>
@@ -28764,7 +29991,10 @@
         <v>0.4329625</v>
       </c>
       <c r="AC427" t="n">
-        <v>0.5502999999999999</v>
+        <v>0.3912846153846154</v>
+      </c>
+      <c r="AG427" t="n">
+        <v>0.4914125</v>
       </c>
       <c r="AI427" t="n">
         <v>0.45495</v>
@@ -28799,7 +30029,10 @@
         <v>0.4788777777777777</v>
       </c>
       <c r="AC428" t="n">
-        <v>0.4633545454545455</v>
+        <v>0.4736</v>
+      </c>
+      <c r="AG428" t="n">
+        <v>0.5786777777777778</v>
       </c>
       <c r="AI428" t="n">
         <v>0.47021</v>
@@ -28837,7 +30070,10 @@
         <v>0.5476818181818182</v>
       </c>
       <c r="AC429" t="n">
-        <v>0.5069100000000001</v>
+        <v>0.57748</v>
+      </c>
+      <c r="AG429" t="n">
+        <v>0.5446749999999999</v>
       </c>
       <c r="AI429" t="n">
         <v>0.5647</v>
@@ -28875,7 +30111,10 @@
         <v>0.5440222222222223</v>
       </c>
       <c r="AC430" t="n">
-        <v>0.6112818181818181</v>
+        <v>0.5227833333333333</v>
+      </c>
+      <c r="AG430" t="n">
+        <v>0.6261636363636364</v>
       </c>
       <c r="AI430" t="n">
         <v>0.4968555555555556</v>
@@ -28913,7 +30152,10 @@
         <v>0.5485111111111112</v>
       </c>
       <c r="AC431" t="n">
-        <v>0.6110384615384615</v>
+        <v>0.4797818181818183</v>
+      </c>
+      <c r="AG431" t="n">
+        <v>0.6130666666666666</v>
       </c>
       <c r="AI431" t="n">
         <v>0.5662363636363636</v>
@@ -28951,7 +30193,10 @@
         <v>0.6080699999999999</v>
       </c>
       <c r="AC432" t="n">
-        <v>0.6088636363636364</v>
+        <v>0.5757357142857142</v>
+      </c>
+      <c r="AG432" t="n">
+        <v>0.539988888888889</v>
       </c>
       <c r="AI432" t="n">
         <v>0.6087</v>
@@ -28989,7 +30234,10 @@
         <v>0.58855</v>
       </c>
       <c r="AC433" t="n">
-        <v>0.6194916666666667</v>
+        <v>0.6213583333333332</v>
+      </c>
+      <c r="AG433" t="n">
+        <v>0.6403624999999999</v>
       </c>
       <c r="AI433" t="n">
         <v>0.5527083333333334</v>
@@ -29027,7 +30275,10 @@
         <v>0.6215444444444445</v>
       </c>
       <c r="AC434" t="n">
-        <v>0.6226111111111111</v>
+        <v>0.6040615384615384</v>
+      </c>
+      <c r="AG434" t="n">
+        <v>0.6644099999999999</v>
       </c>
       <c r="AI434" t="n">
         <v>0.5567333333333333</v>
@@ -29065,7 +30316,10 @@
         <v>0.5857833333333333</v>
       </c>
       <c r="AC435" t="n">
-        <v>0.6300833333333332</v>
+        <v>0.5855714285714286</v>
+      </c>
+      <c r="AG435" t="n">
+        <v>0.6553249999999999</v>
       </c>
       <c r="AI435" t="n">
         <v>0.4903428571428572</v>
@@ -29103,7 +30357,10 @@
         <v>0.6111333333333334</v>
       </c>
       <c r="AC436" t="n">
-        <v>0.6258909090909091</v>
+        <v>0.5823153846153846</v>
+      </c>
+      <c r="AG436" t="n">
+        <v>0.6570666666666667</v>
       </c>
       <c r="AI436" t="n">
         <v>0.4620100000000001</v>
@@ -29141,7 +30398,10 @@
         <v>0.6626833333333334</v>
       </c>
       <c r="AC437" t="n">
-        <v>0.591025</v>
+        <v>0.6298692307692307</v>
+      </c>
+      <c r="AG437" t="n">
+        <v>0.6755555555555556</v>
       </c>
     </row>
     <row r="438">
@@ -29176,7 +30436,10 @@
         <v>0.7265181818181818</v>
       </c>
       <c r="AC438" t="n">
-        <v>0.6619666666666667</v>
+        <v>0.6617545454545455</v>
+      </c>
+      <c r="AG438" t="n">
+        <v>0.7323125</v>
       </c>
       <c r="AI438" t="n">
         <v>0.5260916666666667</v>
@@ -29214,7 +30477,10 @@
         <v>0.57873</v>
       </c>
       <c r="AC439" t="n">
-        <v>0.6757230769230771</v>
+        <v>0.5704692307692307</v>
+      </c>
+      <c r="AG439" t="n">
+        <v>0.6723000000000001</v>
       </c>
       <c r="AI439" t="n">
         <v>0.5456</v>
@@ -29252,7 +30518,10 @@
         <v>0.5887875</v>
       </c>
       <c r="AC440" t="n">
-        <v>0.6185090909090909</v>
+        <v>0.5971083333333332</v>
+      </c>
+      <c r="AG440" t="n">
+        <v>0.8287636363636363</v>
       </c>
       <c r="AI440" t="n">
         <v>0.5898333333333333</v>
@@ -29290,7 +30559,10 @@
         <v>0.5946400000000001</v>
       </c>
       <c r="AC441" t="n">
-        <v>0.6336777777777778</v>
+        <v>0.6017916666666667</v>
+      </c>
+      <c r="AG441" t="n">
+        <v>0.6786749999999999</v>
       </c>
       <c r="AI441" t="n">
         <v>0.5843999999999998</v>
@@ -29328,7 +30600,10 @@
         <v>0.6194999999999999</v>
       </c>
       <c r="AC442" t="n">
-        <v>0.6481636363636364</v>
+        <v>0.6147750000000001</v>
+      </c>
+      <c r="AG442" t="n">
+        <v>0.7175777777777778</v>
       </c>
       <c r="AI442" t="n">
         <v>0.5954928571428572</v>
@@ -29366,7 +30641,10 @@
         <v>0.66425</v>
       </c>
       <c r="AC443" t="n">
-        <v>0.68449</v>
+        <v>0.6563272727272726</v>
+      </c>
+      <c r="AG443" t="n">
+        <v>0.7514000000000001</v>
       </c>
       <c r="AI443" t="n">
         <v>0.5881416666666667</v>
@@ -29404,7 +30682,10 @@
         <v>0.67204</v>
       </c>
       <c r="AC444" t="n">
-        <v>0.6728307692307692</v>
+        <v>0.6547500000000001</v>
+      </c>
+      <c r="AG444" t="n">
+        <v>0.6881</v>
       </c>
       <c r="AI444" t="n">
         <v>0.6613625000000001</v>
@@ -29442,7 +30723,10 @@
         <v>0.6517272727272728</v>
       </c>
       <c r="AC445" t="n">
-        <v>0.6218615384615386</v>
+        <v>0.6375999999999998</v>
+      </c>
+      <c r="AG445" t="n">
+        <v>0.6619375</v>
       </c>
       <c r="AI445" t="n">
         <v>0.57875</v>
@@ -29480,7 +30764,10 @@
         <v>0.6582444444444444</v>
       </c>
       <c r="AC446" t="n">
-        <v>0.6355299999999999</v>
+        <v>0.7462461538461537</v>
+      </c>
+      <c r="AG446" t="n">
+        <v>0.7056571428571428</v>
       </c>
       <c r="AI446" t="n">
         <v>0.6669777777777778</v>
@@ -29518,7 +30805,10 @@
         <v>0.6647999999999999</v>
       </c>
       <c r="AC447" t="n">
-        <v>0.62498</v>
+        <v>0.6812083333333335</v>
+      </c>
+      <c r="AG447" t="n">
+        <v>0.70548</v>
       </c>
       <c r="AI447" t="n">
         <v>0.5179363636363636</v>
@@ -29556,7 +30846,10 @@
         <v>0.7194750000000001</v>
       </c>
       <c r="AC448" t="n">
-        <v>0.7292625</v>
+        <v>0.6009833333333334</v>
+      </c>
+      <c r="AG448" t="n">
+        <v>0.6137875</v>
       </c>
       <c r="AI448" t="n">
         <v>0.6869727272727273</v>
@@ -29594,7 +30887,10 @@
         <v>0.7014777777777778</v>
       </c>
       <c r="AC449" t="n">
-        <v>0.6859625</v>
+        <v>0.6493846153846154</v>
+      </c>
+      <c r="AG449" t="n">
+        <v>0.6373571428571428</v>
       </c>
       <c r="AI449" t="n">
         <v>0.5404214285714286</v>
@@ -29629,7 +30925,10 @@
         <v>0.6422</v>
       </c>
       <c r="AC450" t="n">
-        <v>0.6300909090909091</v>
+        <v>0.6377272727272726</v>
+      </c>
+      <c r="AG450" t="n">
+        <v>0.7039375000000001</v>
       </c>
       <c r="AI450" t="n">
         <v>0.6353583333333334</v>
@@ -29669,6 +30968,9 @@
       <c r="AC451" t="n">
         <v>0.7466666666666667</v>
       </c>
+      <c r="AG451" t="n">
+        <v>0.6523</v>
+      </c>
       <c r="AI451" t="n">
         <v>0.6264909090909091</v>
       </c>
@@ -29707,6 +31009,9 @@
       <c r="AC452" t="n">
         <v>0.66817</v>
       </c>
+      <c r="AG452" t="n">
+        <v>0.7395875</v>
+      </c>
       <c r="AI452" t="n">
         <v>0.6068666666666667</v>
       </c>
@@ -29740,7 +31045,10 @@
         <v>0.6359833333333332</v>
       </c>
       <c r="AC453" t="n">
-        <v>0.6806999999999999</v>
+        <v>0.6596909090909091</v>
+      </c>
+      <c r="AG453" t="n">
+        <v>0.7404299999999999</v>
       </c>
       <c r="AI453" t="n">
         <v>0.5649916666666667</v>
@@ -29778,7 +31086,10 @@
         <v>0.6783857142857144</v>
       </c>
       <c r="AC454" t="n">
-        <v>0.6747299999999999</v>
+        <v>0.6688923076923078</v>
+      </c>
+      <c r="AG454" t="n">
+        <v>0.6936199999999999</v>
       </c>
       <c r="AI454" t="n">
         <v>0.5550153846153846</v>
@@ -29816,7 +31127,10 @@
         <v>0.6874999999999999</v>
       </c>
       <c r="AC455" t="n">
-        <v>0.6295083333333332</v>
+        <v>0.5749</v>
+      </c>
+      <c r="AG455" t="n">
+        <v>0.66187</v>
       </c>
       <c r="AI455" t="n">
         <v>0.6625272727272727</v>
@@ -29856,6 +31170,9 @@
       <c r="AC456" t="n">
         <v>0.6647909090909091</v>
       </c>
+      <c r="AG456" t="n">
+        <v>0.7350857142857142</v>
+      </c>
       <c r="AI456" t="n">
         <v>0.5782636363636363</v>
       </c>
@@ -29892,7 +31209,10 @@
         <v>0.7101875</v>
       </c>
       <c r="AC457" t="n">
-        <v>0.7308090909090909</v>
+        <v>0.6804928571428571</v>
+      </c>
+      <c r="AG457" t="n">
+        <v>0.7047857142857143</v>
       </c>
       <c r="AI457" t="n">
         <v>0.5540833333333334</v>
@@ -29930,7 +31250,10 @@
         <v>0.5951666666666666</v>
       </c>
       <c r="AC458" t="n">
-        <v>0.7065900000000001</v>
+        <v>0.6463</v>
+      </c>
+      <c r="AG458" t="n">
+        <v>0.6754875</v>
       </c>
       <c r="AI458" t="n">
         <v>0.6508307692307691</v>
@@ -29968,7 +31291,10 @@
         <v>0.59263</v>
       </c>
       <c r="AC459" t="n">
-        <v>0.6377166666666666</v>
+        <v>0.632775</v>
+      </c>
+      <c r="AG459" t="n">
+        <v>0.7225428571428572</v>
       </c>
       <c r="AI459" t="n">
         <v>0.6123333333333334</v>
@@ -30006,7 +31332,10 @@
         <v>0.6884999999999999</v>
       </c>
       <c r="AC460" t="n">
-        <v>0.6746444444444445</v>
+        <v>0.6456636363636363</v>
+      </c>
+      <c r="AG460" t="n">
+        <v>0.71025</v>
       </c>
       <c r="AI460" t="n">
         <v>0.6267272727272727</v>
@@ -30044,7 +31373,10 @@
         <v>0.5920153846153846</v>
       </c>
       <c r="AC461" t="n">
-        <v>0.6575222222222221</v>
+        <v>0.6230384615384614</v>
+      </c>
+      <c r="AG461" t="n">
+        <v>0.7363333333333333</v>
       </c>
       <c r="AI461" t="n">
         <v>0.5632166666666667</v>
@@ -30082,7 +31414,10 @@
         <v>0.67069</v>
       </c>
       <c r="AC462" t="n">
-        <v>0.631225</v>
+        <v>0.6374583333333333</v>
+      </c>
+      <c r="AG462" t="n">
+        <v>0.7300749999999999</v>
       </c>
       <c r="AI462" t="n">
         <v>0.588290909090909</v>
@@ -30120,7 +31455,10 @@
         <v>0.6010545454545454</v>
       </c>
       <c r="AC463" t="n">
-        <v>0.6227999999999999</v>
+        <v>0.59465</v>
+      </c>
+      <c r="AG463" t="n">
+        <v>0.7068000000000001</v>
       </c>
     </row>
     <row r="464">
@@ -30155,7 +31493,10 @@
         <v>0.65249</v>
       </c>
       <c r="AC464" t="n">
-        <v>0.70076</v>
+        <v>0.66703</v>
+      </c>
+      <c r="AG464" t="n">
+        <v>0.65405</v>
       </c>
       <c r="AI464" t="n">
         <v>0.5247090909090909</v>
@@ -30193,7 +31534,10 @@
         <v>0.6362181818181818</v>
       </c>
       <c r="AC465" t="n">
-        <v>0.7426571428571428</v>
+        <v>0.6334999999999998</v>
+      </c>
+      <c r="AG465" t="n">
+        <v>0.7337300000000001</v>
       </c>
       <c r="AI465" t="n">
         <v>0.5759461538461538</v>
@@ -30231,7 +31575,10 @@
         <v>0.7072222222222223</v>
       </c>
       <c r="AC466" t="n">
-        <v>0.62868</v>
+        <v>0.6330727272727272</v>
+      </c>
+      <c r="AG466" t="n">
+        <v>0.6647545454545455</v>
       </c>
       <c r="AI466" t="n">
         <v>0.6231818181818182</v>
@@ -30269,7 +31616,10 @@
         <v>0.60287</v>
       </c>
       <c r="AC467" t="n">
-        <v>0.6145999999999999</v>
+        <v>0.5960500000000001</v>
+      </c>
+      <c r="AG467" t="n">
+        <v>0.6775</v>
       </c>
       <c r="AI467" t="n">
         <v>0.566625</v>
@@ -30307,7 +31657,10 @@
         <v>0.6426666666666666</v>
       </c>
       <c r="AC468" t="n">
-        <v>0.670046153846154</v>
+        <v>0.6233416666666666</v>
+      </c>
+      <c r="AG468" t="n">
+        <v>0.6735899999999999</v>
       </c>
       <c r="AI468" t="n">
         <v>0.5158727272727273</v>
@@ -30345,7 +31698,10 @@
         <v>0.5769769230769231</v>
       </c>
       <c r="AC469" t="n">
-        <v>0.6443692307692308</v>
+        <v>0.6418142857142858</v>
+      </c>
+      <c r="AG469" t="n">
+        <v>0.7087625</v>
       </c>
       <c r="AI469" t="n">
         <v>0.5371222222222223</v>
@@ -30383,7 +31739,10 @@
         <v>0.572125</v>
       </c>
       <c r="AC470" t="n">
-        <v>0.6477615384615386</v>
+        <v>0.5600846153846153</v>
+      </c>
+      <c r="AG470" t="n">
+        <v>0.6691666666666666</v>
       </c>
       <c r="AI470" t="n">
         <v>0.6442727272727272</v>
@@ -30421,7 +31780,10 @@
         <v>0.58383</v>
       </c>
       <c r="AC471" t="n">
-        <v>0.71028</v>
+        <v>0.6603999999999999</v>
+      </c>
+      <c r="AG471" t="n">
+        <v>0.7505285714285713</v>
       </c>
       <c r="AI471" t="n">
         <v>0.5924461538461538</v>
@@ -30459,7 +31821,10 @@
         <v>0.6255555555555556</v>
       </c>
       <c r="AC472" t="n">
-        <v>0.7052909090909091</v>
+        <v>0.6093916666666667</v>
+      </c>
+      <c r="AG472" t="n">
+        <v>0.76529</v>
       </c>
       <c r="AI472" t="n">
         <v>0.5593545454545454</v>
@@ -30497,7 +31862,10 @@
         <v>0.7355777777777779</v>
       </c>
       <c r="AC473" t="n">
-        <v>0.6906499999999999</v>
+        <v>0.5775499999999999</v>
+      </c>
+      <c r="AG473" t="n">
+        <v>0.7139499999999999</v>
       </c>
       <c r="AI473" t="n">
         <v>0.5250272727272728</v>
@@ -30535,7 +31903,10 @@
         <v>0.596988888888889</v>
       </c>
       <c r="AC474" t="n">
-        <v>0.7107250000000001</v>
+        <v>0.5617666666666666</v>
+      </c>
+      <c r="AG474" t="n">
+        <v>0.6641666666666667</v>
       </c>
       <c r="AI474" t="n">
         <v>0.6432600000000001</v>
@@ -30573,7 +31944,10 @@
         <v>0.6927545454545455</v>
       </c>
       <c r="AC475" t="n">
-        <v>0.5992599999999999</v>
+        <v>0.6169272727272728</v>
+      </c>
+      <c r="AG475" t="n">
+        <v>0.7051555555555555</v>
       </c>
       <c r="AI475" t="n">
         <v>0.54559</v>
@@ -30611,7 +31985,10 @@
         <v>0.5732200000000001</v>
       </c>
       <c r="AC476" t="n">
-        <v>0.6731857142857144</v>
+        <v>0.6776</v>
+      </c>
+      <c r="AG476" t="n">
+        <v>0.7401555555555556</v>
       </c>
       <c r="AI476" t="n">
         <v>0.6434</v>
@@ -30649,7 +32026,10 @@
         <v>0.67231</v>
       </c>
       <c r="AC477" t="n">
-        <v>0.6505153846153846</v>
+        <v>0.6557916666666667</v>
+      </c>
+      <c r="AG477" t="n">
+        <v>0.6803</v>
       </c>
       <c r="AI477" t="n">
         <v>0.6002181818181819</v>
@@ -30687,7 +32067,10 @@
         <v>0.6679749999999999</v>
       </c>
       <c r="AC478" t="n">
-        <v>0.6317999999999999</v>
+        <v>0.5943307692307692</v>
+      </c>
+      <c r="AG478" t="n">
+        <v>0.7415666666666668</v>
       </c>
       <c r="AI478" t="n">
         <v>0.5306615384615383</v>
@@ -30725,7 +32108,10 @@
         <v>0.6657000000000001</v>
       </c>
       <c r="AC479" t="n">
-        <v>0.6861090909090909</v>
+        <v>0.5615307692307693</v>
+      </c>
+      <c r="AG479" t="n">
+        <v>0.7402444444444444</v>
       </c>
       <c r="AI479" t="n">
         <v>0.5950222222222222</v>
@@ -30763,7 +32149,10 @@
         <v>0.6530555555555556</v>
       </c>
       <c r="AC480" t="n">
-        <v>0.6335</v>
+        <v>0.6657083333333333</v>
+      </c>
+      <c r="AG480" t="n">
+        <v>0.6899555555555554</v>
       </c>
       <c r="AI480" t="n">
         <v>0.473225</v>
@@ -30801,7 +32190,10 @@
         <v>0.6001222222222222</v>
       </c>
       <c r="AC481" t="n">
-        <v>0.6945777777777778</v>
+        <v>0.6474818181818182</v>
+      </c>
+      <c r="AG481" t="n">
+        <v>0.7259625</v>
       </c>
       <c r="AI481" t="n">
         <v>0.58578</v>
@@ -30839,7 +32231,10 @@
         <v>0.657490909090909</v>
       </c>
       <c r="AC482" t="n">
-        <v>0.67079</v>
+        <v>0.5884272727272726</v>
+      </c>
+      <c r="AG482" t="n">
+        <v>0.6759777777777779</v>
       </c>
       <c r="AI482" t="n">
         <v>0.5609749999999999</v>
@@ -30877,7 +32272,10 @@
         <v>0.6869818181818181</v>
       </c>
       <c r="AC483" t="n">
-        <v>0.7135444444444444</v>
+        <v>0.6607461538461538</v>
+      </c>
+      <c r="AG483" t="n">
+        <v>0.6821142857142857</v>
       </c>
       <c r="AI483" t="n">
         <v>0.5564600000000001</v>
@@ -30915,7 +32313,10 @@
         <v>0.69135</v>
       </c>
       <c r="AC484" t="n">
-        <v>0.6470899999999999</v>
+        <v>0.6403333333333333</v>
+      </c>
+      <c r="AG484" t="n">
+        <v>0.6997181818181818</v>
       </c>
       <c r="AI484" t="n">
         <v>0.6442125000000001</v>
@@ -30953,7 +32354,10 @@
         <v>0.6421444444444444</v>
       </c>
       <c r="AC485" t="n">
-        <v>0.6208090909090909</v>
+        <v>0.5938999999999999</v>
+      </c>
+      <c r="AG485" t="n">
+        <v>0.7626375</v>
       </c>
       <c r="AI485" t="n">
         <v>0.562275</v>
@@ -30991,7 +32395,10 @@
         <v>0.6169875</v>
       </c>
       <c r="AC486" t="n">
-        <v>0.6831545454545455</v>
+        <v>0.6617818181818181</v>
+      </c>
+      <c r="AG486" t="n">
+        <v>0.5654125</v>
       </c>
       <c r="AI486" t="n">
         <v>0.5865250000000001</v>
@@ -31029,7 +32436,10 @@
         <v>0.6336000000000001</v>
       </c>
       <c r="AC487" t="n">
-        <v>0.7086230769230769</v>
+        <v>0.7187000000000001</v>
+      </c>
+      <c r="AG487" t="n">
+        <v>0.6277888888888888</v>
       </c>
       <c r="AI487" t="n">
         <v>0.6254666666666667</v>
@@ -31067,7 +32477,10 @@
         <v>0.6075333333333334</v>
       </c>
       <c r="AC488" t="n">
-        <v>0.6122727272727273</v>
+        <v>0.6532749999999999</v>
+      </c>
+      <c r="AG488" t="n">
+        <v>0.7060166666666667</v>
       </c>
       <c r="AI488" t="n">
         <v>0.5931272727272727</v>
@@ -31105,7 +32518,10 @@
         <v>0.5981727272727272</v>
       </c>
       <c r="AC489" t="n">
-        <v>0.6919099999999999</v>
+        <v>0.6956785714285714</v>
+      </c>
+      <c r="AG489" t="n">
+        <v>0.6575571428571428</v>
       </c>
       <c r="AI489" t="n">
         <v>0.7043928571428573</v>
@@ -31143,7 +32559,10 @@
         <v>0.6459999999999999</v>
       </c>
       <c r="AC490" t="n">
-        <v>0.6508125</v>
+        <v>0.70672</v>
+      </c>
+      <c r="AG490" t="n">
+        <v>0.6117</v>
       </c>
       <c r="AI490" t="n">
         <v>0.6163777777777777</v>
@@ -31178,7 +32597,10 @@
         <v>0.6707090909090909</v>
       </c>
       <c r="AC491" t="n">
-        <v>0.6692555555555555</v>
+        <v>0.5745083333333333</v>
+      </c>
+      <c r="AG491" t="n">
+        <v>0.60181</v>
       </c>
       <c r="AI491" t="n">
         <v>0.5878583333333333</v>
@@ -31216,7 +32638,10 @@
         <v>0.5537166666666666</v>
       </c>
       <c r="AC492" t="n">
-        <v>0.6859599999999999</v>
+        <v>0.6133583333333333</v>
+      </c>
+      <c r="AG492" t="n">
+        <v>0.6725333333333333</v>
       </c>
       <c r="AI492" t="n">
         <v>0.5871583333333334</v>
@@ -31254,7 +32679,10 @@
         <v>0.6687</v>
       </c>
       <c r="AC493" t="n">
-        <v>0.6544727272727272</v>
+        <v>0.65625</v>
+      </c>
+      <c r="AG493" t="n">
+        <v>0.569925</v>
       </c>
       <c r="AI493" t="n">
         <v>0.5515666666666666</v>
@@ -31292,7 +32720,10 @@
         <v>0.5714666666666666</v>
       </c>
       <c r="AC494" t="n">
-        <v>0.7038749999999999</v>
+        <v>0.6596900000000001</v>
+      </c>
+      <c r="AG494" t="n">
+        <v>0.6724636363636363</v>
       </c>
       <c r="AI494" t="n">
         <v>0.583290909090909</v>
@@ -31330,7 +32761,10 @@
         <v>0.71056</v>
       </c>
       <c r="AC495" t="n">
-        <v>0.6908499999999999</v>
+        <v>0.6137333333333334</v>
+      </c>
+      <c r="AG495" t="n">
+        <v>0.6555363636363636</v>
       </c>
       <c r="AI495" t="n">
         <v>0.5609166666666667</v>
@@ -31368,7 +32802,10 @@
         <v>0.65617</v>
       </c>
       <c r="AC496" t="n">
-        <v>0.6450100000000001</v>
+        <v>0.6244071428571428</v>
+      </c>
+      <c r="AG496" t="n">
+        <v>0.6922799999999999</v>
       </c>
       <c r="AI496" t="n">
         <v>0.6091666666666665</v>
@@ -31406,7 +32843,10 @@
         <v>0.65998</v>
       </c>
       <c r="AC497" t="n">
-        <v>0.7003000000000001</v>
+        <v>0.5975307692307692</v>
+      </c>
+      <c r="AG497" t="n">
+        <v>0.6037777777777777</v>
       </c>
       <c r="AI497" t="n">
         <v>0.5709799999999999</v>
@@ -31444,7 +32884,10 @@
         <v>0.7633749999999999</v>
       </c>
       <c r="AC498" t="n">
-        <v>0.6149727272727272</v>
+        <v>0.6383727272727273</v>
+      </c>
+      <c r="AG498" t="n">
+        <v>0.6193875000000001</v>
       </c>
       <c r="AI498" t="n">
         <v>0.5998222222222221</v>
@@ -31482,7 +32925,10 @@
         <v>0.6127333333333334</v>
       </c>
       <c r="AC499" t="n">
-        <v>0.592290909090909</v>
+        <v>0.6384083333333334</v>
+      </c>
+      <c r="AG499" t="n">
+        <v>0.6744375</v>
       </c>
       <c r="AI499" t="n">
         <v>0.5218636363636363</v>
@@ -31520,7 +32966,10 @@
         <v>0.6565083333333334</v>
       </c>
       <c r="AC500" t="n">
-        <v>0.5992166666666666</v>
+        <v>0.6275999999999999</v>
+      </c>
+      <c r="AG500" t="n">
+        <v>0.70008</v>
       </c>
       <c r="AI500" t="n">
         <v>0.6140090909090909</v>
@@ -31558,7 +33007,10 @@
         <v>0.58627</v>
       </c>
       <c r="AC501" t="n">
-        <v>0.6273416666666666</v>
+        <v>0.6562333333333333</v>
+      </c>
+      <c r="AG501" t="n">
+        <v>0.6196545454545456</v>
       </c>
       <c r="AI501" t="n">
         <v>0.6233333333333334</v>
@@ -31596,7 +33048,10 @@
         <v>0.6197846153846154</v>
       </c>
       <c r="AC502" t="n">
-        <v>0.6762214285714284</v>
+        <v>0.6236636363636363</v>
+      </c>
+      <c r="AG502" t="n">
+        <v>0.7309099999999999</v>
       </c>
       <c r="AI502" t="n">
         <v>0.6382636363636365</v>
@@ -31634,7 +33089,10 @@
         <v>0.6321583333333333</v>
       </c>
       <c r="AC503" t="n">
-        <v>0.6226333333333334</v>
+        <v>0.5678</v>
+      </c>
+      <c r="AG503" t="n">
+        <v>0.6705666666666666</v>
       </c>
       <c r="AI503" t="n">
         <v>0.5552083333333334</v>
@@ -31672,7 +33130,10 @@
         <v>0.6656363636363637</v>
       </c>
       <c r="AC504" t="n">
-        <v>0.6638000000000001</v>
+        <v>0.7335583333333334</v>
+      </c>
+      <c r="AG504" t="n">
+        <v>0.6718666666666667</v>
       </c>
       <c r="AI504" t="n">
         <v>0.5549090909090908</v>
@@ -31710,7 +33171,10 @@
         <v>0.6895666666666668</v>
       </c>
       <c r="AC505" t="n">
-        <v>0.6990099999999999</v>
+        <v>0.6456</v>
+      </c>
+      <c r="AG505" t="n">
+        <v>0.7518636363636362</v>
       </c>
       <c r="AI505" t="n">
         <v>0.61391</v>
@@ -31748,7 +33212,10 @@
         <v>0.6207</v>
       </c>
       <c r="AC506" t="n">
-        <v>0.6102916666666667</v>
+        <v>0.6514</v>
+      </c>
+      <c r="AG506" t="n">
+        <v>0.7943874999999999</v>
       </c>
       <c r="AI506" t="n">
         <v>0.5387916666666667</v>
@@ -31786,7 +33253,10 @@
         <v>0.6804909090909091</v>
       </c>
       <c r="AC507" t="n">
-        <v>0.6316769230769231</v>
+        <v>0.6392454545454546</v>
+      </c>
+      <c r="AG507" t="n">
+        <v>0.69035</v>
       </c>
       <c r="AI507" t="n">
         <v>0.5796749999999999</v>
@@ -31824,7 +33294,10 @@
         <v>0.6789333333333334</v>
       </c>
       <c r="AC508" t="n">
-        <v>0.6014700000000001</v>
+        <v>0.6178833333333333</v>
+      </c>
+      <c r="AG508" t="n">
+        <v>0.6579166666666666</v>
       </c>
       <c r="AI508" t="n">
         <v>0.5518545454545455</v>
@@ -31862,7 +33335,10 @@
         <v>0.6211222222222221</v>
       </c>
       <c r="AC509" t="n">
-        <v>0.6811545454545453</v>
+        <v>0.6232076923076921</v>
+      </c>
+      <c r="AG509" t="n">
+        <v>0.5816000000000001</v>
       </c>
       <c r="AI509" t="n">
         <v>0.5947818181818182</v>
@@ -31900,7 +33376,10 @@
         <v>0.5927500000000001</v>
       </c>
       <c r="AC510" t="n">
-        <v>0.6541555555555555</v>
+        <v>0.6369083333333333</v>
+      </c>
+      <c r="AG510" t="n">
+        <v>0.7370444444444444</v>
       </c>
       <c r="AI510" t="n">
         <v>0.59485</v>
@@ -31938,7 +33417,10 @@
         <v>0.5595666666666665</v>
       </c>
       <c r="AC511" t="n">
-        <v>0.71183</v>
+        <v>0.6822777777777778</v>
+      </c>
+      <c r="AG511" t="n">
+        <v>0.6631375</v>
       </c>
       <c r="AI511" t="n">
         <v>0.5214846153846153</v>
@@ -31976,7 +33458,10 @@
         <v>0.6197199999999999</v>
       </c>
       <c r="AC512" t="n">
-        <v>0.6182300000000001</v>
+        <v>0.5748</v>
+      </c>
+      <c r="AG512" t="n">
+        <v>0.6413454545454546</v>
       </c>
       <c r="AI512" t="n">
         <v>0.6764363636363636</v>
@@ -32014,7 +33499,10 @@
         <v>0.57916</v>
       </c>
       <c r="AC513" t="n">
-        <v>0.6813375</v>
+        <v>0.6514545454545455</v>
+      </c>
+      <c r="AG513" t="n">
+        <v>0.6904888888888889</v>
       </c>
       <c r="AI513" t="n">
         <v>0.5963499999999999</v>
@@ -32052,7 +33540,10 @@
         <v>0.62291</v>
       </c>
       <c r="AC514" t="n">
-        <v>0.6289100000000001</v>
+        <v>0.6691583333333333</v>
+      </c>
+      <c r="AG514" t="n">
+        <v>0.6874714285714286</v>
       </c>
       <c r="AI514" t="n">
         <v>0.5021545454545454</v>
@@ -32090,7 +33581,10 @@
         <v>0.6862285714285715</v>
       </c>
       <c r="AC515" t="n">
-        <v>0.6308166666666667</v>
+        <v>0.5082</v>
+      </c>
+      <c r="AG515" t="n">
+        <v>0.6931666666666666</v>
       </c>
       <c r="AI515" t="n">
         <v>0.5428000000000001</v>
@@ -32128,7 +33622,10 @@
         <v>0.7121818181818182</v>
       </c>
       <c r="AC516" t="n">
-        <v>0.66883</v>
+        <v>0.6212714285714285</v>
+      </c>
+      <c r="AG516" t="n">
+        <v>0.6112299999999999</v>
       </c>
       <c r="AI516" t="n">
         <v>0.49555</v>
@@ -32166,7 +33663,10 @@
         <v>0.7012636363636364</v>
       </c>
       <c r="AC517" t="n">
-        <v>0.6282272727272727</v>
+        <v>0.6714166666666667</v>
+      </c>
+      <c r="AG517" t="n">
+        <v>0.6666818181818182</v>
       </c>
       <c r="AI517" t="n">
         <v>0.52064</v>
@@ -32212,7 +33712,10 @@
         <v>0.1565506493506493</v>
       </c>
       <c r="AC520" t="n">
-        <v>0.1717970149253731</v>
+        <v>0.1778257575757576</v>
+      </c>
+      <c r="AG520" t="n">
+        <v>0.1444220588235294</v>
       </c>
       <c r="AI520" t="n">
         <v>0.1300313432835821</v>
@@ -32244,7 +33747,10 @@
         <v>0.1644642857142857</v>
       </c>
       <c r="AC521" t="n">
-        <v>0.1411533333333334</v>
+        <v>0.1586368421052632</v>
+      </c>
+      <c r="AG521" t="n">
+        <v>0.1429</v>
       </c>
       <c r="AI521" t="n">
         <v>0.16574375</v>
@@ -32276,7 +33782,10 @@
         <v>0.3002653846153846</v>
       </c>
       <c r="AC522" t="n">
-        <v>0.1067428571428571</v>
+        <v>0.2495617647058823</v>
+      </c>
+      <c r="AG522" t="n">
+        <v>0.2835</v>
       </c>
       <c r="AI522" t="n">
         <v>0.3067285714285714</v>
@@ -32308,7 +33817,10 @@
         <v>0.352927027027027</v>
       </c>
       <c r="AC523" t="n">
-        <v>0.2687945945945946</v>
+        <v>0.2561083333333333</v>
+      </c>
+      <c r="AG523" t="n">
+        <v>0.3022452380952381</v>
       </c>
       <c r="AI523" t="n">
         <v>0.31178</v>
@@ -32340,7 +33852,10 @@
         <v>0.3152666666666668</v>
       </c>
       <c r="AC524" t="n">
-        <v>0.3114653846153846</v>
+        <v>0.3331469387755102</v>
+      </c>
+      <c r="AG524" t="n">
+        <v>0.3887216216216217</v>
       </c>
       <c r="AI524" t="n">
         <v>0.3213083333333334</v>
@@ -32372,7 +33887,10 @@
         <v>0.3486536585365854</v>
       </c>
       <c r="AC525" t="n">
-        <v>0.320658064516129</v>
+        <v>0.3252390243902439</v>
+      </c>
+      <c r="AG525" t="n">
+        <v>0.4646130434782609</v>
       </c>
       <c r="AI525" t="n">
         <v>0.3844896551724138</v>
@@ -32404,7 +33922,10 @@
         <v>0.3898524999999999</v>
       </c>
       <c r="AC526" t="n">
-        <v>0.3008333333333333</v>
+        <v>0.3929862068965517</v>
+      </c>
+      <c r="AG526" t="n">
+        <v>0.41598</v>
       </c>
       <c r="AI526" t="n">
         <v>0.31800625</v>
@@ -32436,7 +33957,10 @@
         <v>0.4166302325581395</v>
       </c>
       <c r="AC527" t="n">
-        <v>0.4534700000000001</v>
+        <v>0.3442854166666667</v>
+      </c>
+      <c r="AG527" t="n">
+        <v>0.5046870967741935</v>
       </c>
       <c r="AI527" t="n">
         <v>0.2846541666666667</v>
@@ -32468,7 +33992,10 @@
         <v>0.43698</v>
       </c>
       <c r="AC528" t="n">
-        <v>0.473651282051282</v>
+        <v>0.4050230769230769</v>
+      </c>
+      <c r="AG528" t="n">
+        <v>0.579425</v>
       </c>
       <c r="AI528" t="n">
         <v>0.5116583333333334</v>
@@ -32500,7 +34027,10 @@
         <v>0.4151787234042553</v>
       </c>
       <c r="AC529" t="n">
-        <v>0.385475</v>
+        <v>0.3247592592592592</v>
+      </c>
+      <c r="AG529" t="n">
+        <v>0.5007578947368421</v>
       </c>
       <c r="AI529" t="n">
         <v>0.4508945454545455</v>
@@ -32523,7 +34053,10 @@
         <v>0.4994232142857143</v>
       </c>
       <c r="AC530" t="n">
-        <v>0.4202036363636363</v>
+        <v>0.3995566037735849</v>
+      </c>
+      <c r="AG530" t="n">
+        <v>0.5682999999999999</v>
       </c>
       <c r="AI530" t="n">
         <v>0.4951224137931035</v>
@@ -32546,7 +34079,10 @@
         <v>0.5372720930232557</v>
       </c>
       <c r="AC531" t="n">
-        <v>0.4706806451612903</v>
+        <v>0.4958045454545454</v>
+      </c>
+      <c r="AG531" t="n">
+        <v>0.4866378378378379</v>
       </c>
       <c r="AI531" t="n">
         <v>0.3783961538461539</v>
@@ -32569,7 +34105,10 @@
         <v>0.3997775510204082</v>
       </c>
       <c r="AC532" t="n">
-        <v>0.423764</v>
+        <v>0.4621510638297872</v>
+      </c>
+      <c r="AG532" t="n">
+        <v>0.3932771428571429</v>
       </c>
       <c r="AI532" t="n">
         <v>0.5010883333333334</v>
@@ -32592,7 +34131,10 @@
         <v>0.511645652173913</v>
       </c>
       <c r="AC533" t="n">
-        <v>0.4927620689655172</v>
+        <v>0.4349719999999999</v>
+      </c>
+      <c r="AG533" t="n">
+        <v>0.5558023809523809</v>
       </c>
       <c r="AI533" t="n">
         <v>0.4608</v>
@@ -32615,7 +34157,10 @@
         <v>0.490327027027027</v>
       </c>
       <c r="AC534" t="n">
-        <v>0.4340441176470589</v>
+        <v>0.3115254545454545</v>
+      </c>
+      <c r="AG534" t="n">
+        <v>0.6494636363636364</v>
       </c>
       <c r="AI534" t="n">
         <v>0.4022145833333333</v>
@@ -32638,7 +34183,10 @@
         <v>0.4960639344262295</v>
       </c>
       <c r="AC535" t="n">
-        <v>0.4540571428571428</v>
+        <v>0.5511894736842106</v>
+      </c>
+      <c r="AG535" t="n">
+        <v>0.4816966666666668</v>
       </c>
       <c r="AI535" t="n">
         <v>0.465167213114754</v>
@@ -32661,7 +34209,10 @@
         <v>0.5078483333333333</v>
       </c>
       <c r="AC536" t="n">
-        <v>0.3857666666666667</v>
+        <v>0.4592083333333334</v>
+      </c>
+      <c r="AG536" t="n">
+        <v>0.4411063829787234</v>
       </c>
       <c r="AI536" t="n">
         <v>0.3577081081081081</v>
@@ -32684,7 +34235,10 @@
         <v>0.4695533333333333</v>
       </c>
       <c r="AC537" t="n">
-        <v>0.4606111111111112</v>
+        <v>0.5164607843137256</v>
+      </c>
+      <c r="AG537" t="n">
+        <v>0.54195</v>
       </c>
       <c r="AI537" t="n">
         <v>0.297085</v>
@@ -32707,7 +34261,10 @@
         <v>0.4764275862068967</v>
       </c>
       <c r="AC538" t="n">
-        <v>0.3950470588235294</v>
+        <v>0.5510245283018868</v>
+      </c>
+      <c r="AG538" t="n">
+        <v>0.6228867647058824</v>
       </c>
       <c r="AI538" t="n">
         <v>0.4526016666666667</v>
@@ -32730,7 +34287,10 @@
         <v>0.4946375</v>
       </c>
       <c r="AC539" t="n">
-        <v>0.4576727272727272</v>
+        <v>0.3734129032258064</v>
+      </c>
+      <c r="AG539" t="n">
+        <v>0.5045277777777778</v>
       </c>
       <c r="AI539" t="n">
         <v>0.3811</v>
@@ -32753,7 +34313,10 @@
         <v>0.561448076923077</v>
       </c>
       <c r="AC540" t="n">
-        <v>0.4830616666666667</v>
+        <v>0.4671789473684211</v>
+      </c>
+      <c r="AG540" t="n">
+        <v>0.6734275000000001</v>
       </c>
       <c r="AI540" t="n">
         <v>0.4125803571428571</v>
@@ -32776,7 +34339,10 @@
         <v>0.4783385964912281</v>
       </c>
       <c r="AC541" t="n">
-        <v>0.4468162162162161</v>
+        <v>0.4401520000000001</v>
+      </c>
+      <c r="AG541" t="n">
+        <v>0.4816444444444445</v>
       </c>
       <c r="AI541" t="n">
         <v>0.5831545454545455</v>
@@ -32799,7 +34365,10 @@
         <v>0.5868846153846154</v>
       </c>
       <c r="AC542" t="n">
-        <v>0.4251416666666667</v>
+        <v>0.482588524590164</v>
+      </c>
+      <c r="AG542" t="n">
+        <v>0.5161395348837209</v>
       </c>
       <c r="AI542" t="n">
         <v>0.4331245901639345</v>
@@ -32822,7 +34391,10 @@
         <v>0.4964914893617021</v>
       </c>
       <c r="AC543" t="n">
-        <v>0.4719418181818183</v>
+        <v>0.5452616666666666</v>
+      </c>
+      <c r="AG543" t="n">
+        <v>0.4877159090909091</v>
       </c>
       <c r="AI543" t="n">
         <v>0.4620406779661017</v>
@@ -32845,7 +34417,10 @@
         <v>0.5538814814814815</v>
       </c>
       <c r="AC544" t="n">
-        <v>0.4258657894736842</v>
+        <v>0.4851044444444444</v>
+      </c>
+      <c r="AG544" t="n">
+        <v>0.6173763157894737</v>
       </c>
       <c r="AI544" t="n">
         <v>0.4957734374999999</v>
@@ -32868,7 +34443,10 @@
         <v>0.6367836734693878</v>
       </c>
       <c r="AC545" t="n">
-        <v>0.5719</v>
+        <v>0.5073206896551724</v>
+      </c>
+      <c r="AG545" t="n">
+        <v>0.4667423076923077</v>
       </c>
       <c r="AI545" t="n">
         <v>0.575545945945946</v>
@@ -32891,7 +34469,10 @@
         <v>0.5919727272727273</v>
       </c>
       <c r="AC546" t="n">
-        <v>0.4884340425531914</v>
+        <v>0.5798599999999999</v>
+      </c>
+      <c r="AG546" t="n">
+        <v>0.5142375</v>
       </c>
       <c r="AI546" t="n">
         <v>0.482527868852459</v>
@@ -32914,7 +34495,10 @@
         <v>0.469259649122807</v>
       </c>
       <c r="AC547" t="n">
-        <v>0.440151724137931</v>
+        <v>0.4528525423728814</v>
+      </c>
+      <c r="AG547" t="n">
+        <v>0.4867585365853659</v>
       </c>
       <c r="AI547" t="n">
         <v>0.4267274509803923</v>
@@ -32937,7 +34521,10 @@
         <v>0.5620295081967213</v>
       </c>
       <c r="AC548" t="n">
-        <v>0.5954666666666666</v>
+        <v>0.4840848484848485</v>
+      </c>
+      <c r="AG548" t="n">
+        <v>0.5193512195121951</v>
       </c>
       <c r="AI548" t="n">
         <v>0.5417542372881355</v>
@@ -32960,7 +34547,10 @@
         <v>0.5043190476190476</v>
       </c>
       <c r="AC549" t="n">
-        <v>0.5291627906976745</v>
+        <v>0.602350909090909</v>
+      </c>
+      <c r="AG549" t="n">
+        <v>0.5403441860465117</v>
       </c>
       <c r="AI549" t="n">
         <v>0.4767525423728814</v>
@@ -32983,7 +34573,10 @@
         <v>0.4628245614035087</v>
       </c>
       <c r="AC550" t="n">
-        <v>0.553379069767442</v>
+        <v>0.46843125</v>
+      </c>
+      <c r="AG550" t="n">
+        <v>0.442425</v>
       </c>
       <c r="AI550" t="n">
         <v>0.4262102564102564</v>
@@ -33006,7 +34599,10 @@
         <v>0.5576653846153847</v>
       </c>
       <c r="AC551" t="n">
-        <v>0.5229659574468085</v>
+        <v>0.4655830188679245</v>
+      </c>
+      <c r="AG551" t="n">
+        <v>0.499976923076923</v>
       </c>
       <c r="AI551" t="n">
         <v>0.4427032786885246</v>
@@ -33029,7 +34625,10 @@
         <v>0.6387489795918367</v>
       </c>
       <c r="AC552" t="n">
-        <v>0.4228833333333334</v>
+        <v>0.3781510204081632</v>
+      </c>
+      <c r="AG552" t="n">
+        <v>0.5988116666666666</v>
       </c>
       <c r="AI552" t="n">
         <v>0.3574173913043478</v>
@@ -33052,7 +34651,10 @@
         <v>0.6070470588235295</v>
       </c>
       <c r="AC553" t="n">
-        <v>0.4439272727272728</v>
+        <v>0.4317800000000001</v>
+      </c>
+      <c r="AG553" t="n">
+        <v>0.5693342857142857</v>
       </c>
       <c r="AI553" t="n">
         <v>0.4145642857142858</v>
@@ -33075,7 +34677,10 @@
         <v>0.5745648648648649</v>
       </c>
       <c r="AC554" t="n">
-        <v>0.4442618181818181</v>
+        <v>0.5104254545454546</v>
+      </c>
+      <c r="AG554" t="n">
+        <v>0.4613942307692307</v>
       </c>
       <c r="AI554" t="n">
         <v>0.4851067796610169</v>
@@ -33098,7 +34703,10 @@
         <v>0.5844453125</v>
       </c>
       <c r="AC555" t="n">
-        <v>0.4640044776119404</v>
+        <v>0.5542551020408163</v>
+      </c>
+      <c r="AG555" t="n">
+        <v>0.5178790697674418</v>
       </c>
       <c r="AI555" t="n">
         <v>0.4232666666666667</v>
@@ -33121,7 +34729,10 @@
         <v>0.5178318181818183</v>
       </c>
       <c r="AC556" t="n">
-        <v>0.4917359375</v>
+        <v>0.5214836065573771</v>
+      </c>
+      <c r="AG556" t="n">
+        <v>0.5133842105263158</v>
       </c>
       <c r="AI556" t="n">
         <v>0.444435</v>
@@ -33144,7 +34755,10 @@
         <v>0.4459767441860465</v>
       </c>
       <c r="AC557" t="n">
-        <v>0.473854347826087</v>
+        <v>0.386245283018868</v>
+      </c>
+      <c r="AG557" t="n">
+        <v>0.6144459459459459</v>
       </c>
       <c r="AI557" t="n">
         <v>0.41788</v>
@@ -33167,7 +34781,10 @@
         <v>0.5964063829787234</v>
       </c>
       <c r="AC558" t="n">
-        <v>0.4933491525423728</v>
+        <v>0.4671999999999999</v>
+      </c>
+      <c r="AG558" t="n">
+        <v>0.6063604651162789</v>
       </c>
       <c r="AI558" t="n">
         <v>0.4011245901639344</v>
@@ -33190,7 +34807,10 @@
         <v>0.5159064516129033</v>
       </c>
       <c r="AC559" t="n">
-        <v>0.4775265306122449</v>
+        <v>0.5137327586206897</v>
+      </c>
+      <c r="AG559" t="n">
+        <v>0.5964913043478262</v>
       </c>
       <c r="AI559" t="n">
         <v>0.4532693548387098</v>
@@ -33213,7 +34833,10 @@
         <v>0.5529733333333333</v>
       </c>
       <c r="AC560" t="n">
-        <v>0.4505978260869566</v>
+        <v>0.5099728813559321</v>
+      </c>
+      <c r="AG560" t="n">
+        <v>0.4655409090909091</v>
       </c>
       <c r="AI560" t="n">
         <v>0.4451980392156863</v>
@@ -33236,7 +34859,10 @@
         <v>0.5286526315789474</v>
       </c>
       <c r="AC561" t="n">
-        <v>0.5058844827586207</v>
+        <v>0.4863826923076923</v>
+      </c>
+      <c r="AG561" t="n">
+        <v>0.5085512195121952</v>
       </c>
       <c r="AI561" t="n">
         <v>0.5603049999999999</v>
@@ -33259,7 +34885,10 @@
         <v>0.572906</v>
       </c>
       <c r="AC562" t="n">
-        <v>0.4639964912280703</v>
+        <v>0.453912962962963</v>
+      </c>
+      <c r="AG562" t="n">
+        <v>0.5657425531914894</v>
       </c>
       <c r="AI562" t="n">
         <v>0.5377527272727273</v>
@@ -33282,7 +34911,10 @@
         <v>0.5864673913043479</v>
       </c>
       <c r="AC563" t="n">
-        <v>0.5215610169491526</v>
+        <v>0.4765818181818182</v>
+      </c>
+      <c r="AG563" t="n">
+        <v>0.5546979591836736</v>
       </c>
       <c r="AI563" t="n">
         <v>0.4258238095238095</v>
@@ -33305,7 +34937,10 @@
         <v>0.4584102564102564</v>
       </c>
       <c r="AC564" t="n">
-        <v>0.5012666666666667</v>
+        <v>0.4980166666666667</v>
+      </c>
+      <c r="AG564" t="n">
+        <v>0.5413347826086957</v>
       </c>
       <c r="AI564" t="n">
         <v>0.3946571428571428</v>
@@ -33328,7 +34963,10 @@
         <v>0.5261982456140351</v>
       </c>
       <c r="AC565" t="n">
-        <v>0.5636481481481481</v>
+        <v>0.5015952380952382</v>
+      </c>
+      <c r="AG565" t="n">
+        <v>0.6386893617021278</v>
       </c>
       <c r="AI565" t="n">
         <v>0.397948076923077</v>
@@ -33351,7 +34989,10 @@
         <v>0.4382428571428572</v>
       </c>
       <c r="AC566" t="n">
-        <v>0.4845943396226415</v>
+        <v>0.473925</v>
+      </c>
+      <c r="AG566" t="n">
+        <v>0.5430470588235295</v>
       </c>
       <c r="AI566" t="n">
         <v>0.4954880952380952</v>
@@ -33374,7 +35015,10 @@
         <v>0.5711068965517241</v>
       </c>
       <c r="AC567" t="n">
-        <v>0.5870885245901639</v>
+        <v>0.5536673076923078</v>
+      </c>
+      <c r="AG567" t="n">
+        <v>0.6642942307692307</v>
       </c>
       <c r="AI567" t="n">
         <v>0.3712135135135136</v>
@@ -33397,7 +35041,10 @@
         <v>0.6823121951219512</v>
       </c>
       <c r="AC568" t="n">
-        <v>0.4556418181818181</v>
+        <v>0.56925</v>
+      </c>
+      <c r="AG568" t="n">
+        <v>0.5320285714285714</v>
       </c>
       <c r="AI568" t="n">
         <v>0.5167102040816326</v>
@@ -33420,7 +35067,10 @@
         <v>0.5570901960784314</v>
       </c>
       <c r="AC569" t="n">
-        <v>0.4760230769230769</v>
+        <v>0.4714163265306122</v>
+      </c>
+      <c r="AG569" t="n">
+        <v>0.6177075000000001</v>
       </c>
       <c r="AI569" t="n">
         <v>0.4900320754716981</v>
@@ -33443,7 +35093,10 @@
         <v>0.5068537037037039</v>
       </c>
       <c r="AC570" t="n">
-        <v>0.4464396551724138</v>
+        <v>0.3889018518518519</v>
+      </c>
+      <c r="AG570" t="n">
+        <v>0.5955615384615386</v>
       </c>
       <c r="AI570" t="n">
         <v>0.5515588235294117</v>
@@ -33466,7 +35119,10 @@
         <v>0.4709666666666666</v>
       </c>
       <c r="AC571" t="n">
-        <v>0.5016596491228071</v>
+        <v>0.5314942028985506</v>
+      </c>
+      <c r="AG571" t="n">
+        <v>0.5553441860465116</v>
       </c>
       <c r="AI571" t="n">
         <v>0.4389015873015872</v>
@@ -33489,7 +35145,10 @@
         <v>0.4669441860465117</v>
       </c>
       <c r="AC572" t="n">
-        <v>0.5284846153846154</v>
+        <v>0.4576981818181818</v>
+      </c>
+      <c r="AG572" t="n">
+        <v>0.4775645833333333</v>
       </c>
       <c r="AI572" t="n">
         <v>0.5389327868852459</v>
@@ -33512,7 +35171,10 @@
         <v>0.5654952380952381</v>
       </c>
       <c r="AC573" t="n">
-        <v>0.5577039215686276</v>
+        <v>0.4552840000000001</v>
+      </c>
+      <c r="AG573" t="n">
+        <v>0.4887617647058824</v>
       </c>
       <c r="AI573" t="n">
         <v>0.4695723404255319</v>
@@ -33535,7 +35197,10 @@
         <v>0.5409475409836066</v>
       </c>
       <c r="AC574" t="n">
-        <v>0.4178051724137931</v>
+        <v>0.5154547169811321</v>
+      </c>
+      <c r="AG574" t="n">
+        <v>0.5916138888888889</v>
       </c>
       <c r="AI574" t="n">
         <v>0.5264584615384615</v>
@@ -33558,7 +35223,10 @@
         <v>0.5690542372881355</v>
       </c>
       <c r="AC575" t="n">
-        <v>0.4079163265306122</v>
+        <v>0.46138125</v>
+      </c>
+      <c r="AG575" t="n">
+        <v>0.5611488888888888</v>
       </c>
       <c r="AI575" t="n">
         <v>0.4963703703703704</v>
@@ -33581,7 +35249,10 @@
         <v>0.5787227272727272</v>
       </c>
       <c r="AC576" t="n">
-        <v>0.4376264150943396</v>
+        <v>0.5618811320754716</v>
+      </c>
+      <c r="AG576" t="n">
+        <v>0.5429072727272727</v>
       </c>
       <c r="AI576" t="n">
         <v>0.4018028571428571</v>
@@ -33604,7 +35275,10 @@
         <v>0.5246318181818181</v>
       </c>
       <c r="AC577" t="n">
-        <v>0.5301208333333333</v>
+        <v>0.4938596491228071</v>
+      </c>
+      <c r="AG577" t="n">
+        <v>0.6382439024390244</v>
       </c>
       <c r="AI577" t="n">
         <v>0.4824263157894737</v>
@@ -33627,7 +35301,10 @@
         <v>0.5935340425531915</v>
       </c>
       <c r="AC578" t="n">
-        <v>0.4531745762711865</v>
+        <v>0.5270279999999999</v>
+      </c>
+      <c r="AG578" t="n">
+        <v>0.6048185185185184</v>
       </c>
       <c r="AI578" t="n">
         <v>0.4637245901639344</v>
@@ -33650,7 +35327,10 @@
         <v>0.4899475</v>
       </c>
       <c r="AC579" t="n">
-        <v>0.441308510638298</v>
+        <v>0.4145636363636363</v>
+      </c>
+      <c r="AG579" t="n">
+        <v>0.5165086956521739</v>
       </c>
       <c r="AI579" t="n">
         <v>0.4540272727272727</v>
@@ -33673,7 +35353,10 @@
         <v>0.5196113636363636</v>
       </c>
       <c r="AC580" t="n">
-        <v>0.4620152173913045</v>
+        <v>0.4867090909090909</v>
+      </c>
+      <c r="AG580" t="n">
+        <v>0.6554473684210527</v>
       </c>
       <c r="AI580" t="n">
         <v>0.4959056603773584</v>
@@ -33696,7 +35379,10 @@
         <v>0.5488625000000001</v>
       </c>
       <c r="AC581" t="n">
-        <v>0.4210833333333333</v>
+        <v>0.4416783333333333</v>
+      </c>
+      <c r="AG581" t="n">
+        <v>0.61</v>
       </c>
       <c r="AI581" t="n">
         <v>0.4562163636363637</v>
@@ -33719,7 +35405,10 @@
         <v>0.5066957446808511</v>
       </c>
       <c r="AC582" t="n">
-        <v>0.4505561403508773</v>
+        <v>0.4763433333333334</v>
+      </c>
+      <c r="AG582" t="n">
+        <v>0.5082950000000001</v>
       </c>
       <c r="AI582" t="n">
         <v>0.5284689655172413</v>
@@ -33742,7 +35431,10 @@
         <v>0.5499617021276596</v>
       </c>
       <c r="AC583" t="n">
-        <v>0.4776411764705882</v>
+        <v>0.5356261904761905</v>
+      </c>
+      <c r="AG583" t="n">
+        <v>0.5488657142857143</v>
       </c>
       <c r="AI583" t="n">
         <v>0.4816906976744186</v>
@@ -33765,7 +35457,10 @@
         <v>0.5476288135593221</v>
       </c>
       <c r="AC584" t="n">
-        <v>0.4109849056603774</v>
+        <v>0.4988000000000001</v>
+      </c>
+      <c r="AG584" t="n">
+        <v>0.4263096153846154</v>
       </c>
       <c r="AI584" t="n">
         <v>0.5130322580645161</v>
@@ -33788,7 +35483,10 @@
         <v>0.5353051282051283</v>
       </c>
       <c r="AC585" t="n">
-        <v>0.5089309523809524</v>
+        <v>0.4746367647058825</v>
+      </c>
+      <c r="AG585" t="n">
+        <v>0.542578</v>
       </c>
       <c r="AI585" t="n">
         <v>0.4921869565217391</v>
@@ -33811,7 +35509,10 @@
         <v>0.4998645833333333</v>
       </c>
       <c r="AC586" t="n">
-        <v>0.4393166666666666</v>
+        <v>0.5125636363636364</v>
+      </c>
+      <c r="AG586" t="n">
+        <v>0.5622434782608696</v>
       </c>
       <c r="AI586" t="n">
         <v>0.4462366666666667</v>
@@ -33834,7 +35535,10 @@
         <v>0.5625863636363636</v>
       </c>
       <c r="AC587" t="n">
-        <v>0.4491819672131148</v>
+        <v>0.4961435483870968</v>
+      </c>
+      <c r="AG587" t="n">
+        <v>0.629788</v>
       </c>
       <c r="AI587" t="n">
         <v>0.4618345454545454</v>
@@ -33857,7 +35561,10 @@
         <v>0.4317767441860466</v>
       </c>
       <c r="AC588" t="n">
-        <v>0.5330923076923076</v>
+        <v>0.5781661016949152</v>
+      </c>
+      <c r="AG588" t="n">
+        <v>0.5338622641509434</v>
       </c>
       <c r="AI588" t="n">
         <v>0.5012519999999999</v>
@@ -33880,7 +35587,10 @@
         <v>0.52338</v>
       </c>
       <c r="AC589" t="n">
-        <v>0.4170953125</v>
+        <v>0.4489958333333333</v>
+      </c>
+      <c r="AG589" t="n">
+        <v>0.6660233333333333</v>
       </c>
       <c r="AI589" t="n">
         <v>0.5026981132075472</v>
@@ -33903,7 +35613,10 @@
         <v>0.4071904761904762</v>
       </c>
       <c r="AC590" t="n">
-        <v>0.4568477272727273</v>
+        <v>0.484944</v>
+      </c>
+      <c r="AG590" t="n">
+        <v>0.622885</v>
       </c>
       <c r="AI590" t="n">
         <v>0.4446111111111111</v>
@@ -33926,7 +35639,10 @@
         <v>0.5598306122448979</v>
       </c>
       <c r="AC591" t="n">
-        <v>0.4356693877551022</v>
+        <v>0.4910307692307692</v>
+      </c>
+      <c r="AG591" t="n">
+        <v>0.477947619047619</v>
       </c>
       <c r="AI591" t="n">
         <v>0.4232176470588236</v>
@@ -33949,7 +35665,10 @@
         <v>0.490809756097561</v>
       </c>
       <c r="AC592" t="n">
-        <v>0.5417568181818182</v>
+        <v>0.5456555555555556</v>
+      </c>
+      <c r="AG592" t="n">
+        <v>0.4996968750000001</v>
       </c>
       <c r="AI592" t="n">
         <v>0.5659461538461539</v>
@@ -33972,7 +35691,10 @@
         <v>0.4760387755102042</v>
       </c>
       <c r="AC593" t="n">
-        <v>0.5064277777777778</v>
+        <v>0.460562</v>
+      </c>
+      <c r="AG593" t="n">
+        <v>0.5798840000000002</v>
       </c>
       <c r="AI593" t="n">
         <v>0.4670844827586206</v>
@@ -33995,7 +35717,10 @@
         <v>0.4513539999999999</v>
       </c>
       <c r="AC594" t="n">
-        <v>0.4637018867924528</v>
+        <v>0.494990909090909</v>
+      </c>
+      <c r="AG594" t="n">
+        <v>0.446626923076923</v>
       </c>
       <c r="AI594" t="n">
         <v>0.5047617021276595</v>
@@ -34018,7 +35743,10 @@
         <v>0.5368244444444444</v>
       </c>
       <c r="AC595" t="n">
-        <v>0.4351666666666666</v>
+        <v>0.4614648148148149</v>
+      </c>
+      <c r="AG595" t="n">
+        <v>0.5939585365853658</v>
       </c>
       <c r="AI595" t="n">
         <v>0.5065603773584906</v>
@@ -34041,7 +35769,10 @@
         <v>0.4654106382978724</v>
       </c>
       <c r="AC596" t="n">
-        <v>0.4903068181818183</v>
+        <v>0.4555960784313727</v>
+      </c>
+      <c r="AG596" t="n">
+        <v>0.6019325581395348</v>
       </c>
       <c r="AI596" t="n">
         <v>0.4321127659574467</v>
@@ -34064,7 +35795,10 @@
         <v>0.4997245283018869</v>
       </c>
       <c r="AC597" t="n">
-        <v>0.4596080000000001</v>
+        <v>0.499428</v>
+      </c>
+      <c r="AG597" t="n">
+        <v>0.5208736842105263</v>
       </c>
       <c r="AI597" t="n">
         <v>0.4917372549019607</v>
@@ -34087,7 +35821,10 @@
         <v>0.4607326923076923</v>
       </c>
       <c r="AC598" t="n">
-        <v>0.5123920000000001</v>
+        <v>0.5547301587301587</v>
+      </c>
+      <c r="AG598" t="n">
+        <v>0.4400714285714286</v>
       </c>
       <c r="AI598" t="n">
         <v>0.4583737704918033</v>
@@ -34110,7 +35847,10 @@
         <v>0.4825872340425533</v>
       </c>
       <c r="AC599" t="n">
-        <v>0.5604883720930233</v>
+        <v>0.555325</v>
+      </c>
+      <c r="AG599" t="n">
+        <v>0.4712206896551724</v>
       </c>
       <c r="AI599" t="n">
         <v>0.442138775510204</v>
@@ -34133,7 +35873,10 @@
         <v>0.4339749999999999</v>
       </c>
       <c r="AC600" t="n">
-        <v>0.5573912280701754</v>
+        <v>0.5739622950819672</v>
+      </c>
+      <c r="AG600" t="n">
+        <v>0.6081968750000001</v>
       </c>
       <c r="AI600" t="n">
         <v>0.5020217391304347</v>
@@ -34156,7 +35899,10 @@
         <v>0.5613379310344828</v>
       </c>
       <c r="AC601" t="n">
-        <v>0.4888222222222223</v>
+        <v>0.4337241379310345</v>
+      </c>
+      <c r="AG601" t="n">
+        <v>0.4639152173913043</v>
       </c>
       <c r="AI601" t="n">
         <v>0.48162</v>
@@ -34179,7 +35925,10 @@
         <v>0.4496911111111111</v>
       </c>
       <c r="AC602" t="n">
-        <v>0.5167</v>
+        <v>0.4740122807017544</v>
+      </c>
+      <c r="AG602" t="n">
+        <v>0.6336108108108109</v>
       </c>
       <c r="AI602" t="n">
         <v>0.5103782608695653</v>
@@ -34202,7 +35951,10 @@
         <v>0.5440725490196079</v>
       </c>
       <c r="AC603" t="n">
-        <v>0.4778945945945947</v>
+        <v>0.4773112903225806</v>
+      </c>
+      <c r="AG603" t="n">
+        <v>0.46076</v>
       </c>
       <c r="AI603" t="n">
         <v>0.567101923076923</v>
@@ -34225,7 +35977,10 @@
         <v>0.6281655172413793</v>
       </c>
       <c r="AC604" t="n">
-        <v>0.43458</v>
+        <v>0.4504599999999999</v>
+      </c>
+      <c r="AG604" t="n">
+        <v>0.6705846153846153</v>
       </c>
       <c r="AI604" t="n">
         <v>0.4864060606060606</v>
@@ -34248,7 +36003,10 @@
         <v>0.4950145833333333</v>
       </c>
       <c r="AC605" t="n">
-        <v>0.394240425531915</v>
+        <v>0.4857470588235293</v>
+      </c>
+      <c r="AG605" t="n">
+        <v>0.6011774193548388</v>
       </c>
       <c r="AI605" t="n">
         <v>0.4698021739130435</v>
@@ -34271,7 +36029,10 @@
         <v>0.4525132075471699</v>
       </c>
       <c r="AC606" t="n">
-        <v>0.4701790697674418</v>
+        <v>0.5282092592592592</v>
+      </c>
+      <c r="AG606" t="n">
+        <v>0.5838275000000001</v>
       </c>
       <c r="AI606" t="n">
         <v>0.4769766666666667</v>
@@ -34294,7 +36055,10 @@
         <v>0.5117094339622641</v>
       </c>
       <c r="AC607" t="n">
-        <v>0.4663360000000001</v>
+        <v>0.4499311475409836</v>
+      </c>
+      <c r="AG607" t="n">
+        <v>0.5910333333333333</v>
       </c>
       <c r="AI607" t="n">
         <v>0.5219344262295083</v>
@@ -34317,7 +36081,10 @@
         <v>0.6114983050847457</v>
       </c>
       <c r="AC608" t="n">
-        <v>0.41053125</v>
+        <v>0.5719953125</v>
+      </c>
+      <c r="AG608" t="n">
+        <v>0.541629268292683</v>
       </c>
       <c r="AI608" t="n">
         <v>0.467019696969697</v>
@@ -34340,7 +36107,10 @@
         <v>0.4429476190476191</v>
       </c>
       <c r="AC609" t="n">
-        <v>0.431428</v>
+        <v>0.5563676470588235</v>
+      </c>
+      <c r="AG609" t="n">
+        <v>0.6393599999999999</v>
       </c>
       <c r="AI609" t="n">
         <v>0.4993666666666666</v>
@@ -34363,7 +36133,10 @@
         <v>0.5720607843137255</v>
       </c>
       <c r="AC610" t="n">
-        <v>0.5161903846153847</v>
+        <v>0.5162607142857143</v>
+      </c>
+      <c r="AG610" t="n">
+        <v>0.5253106382978723</v>
       </c>
       <c r="AI610" t="n">
         <v>0.4155879999999999</v>
@@ -34386,7 +36159,10 @@
         <v>0.5301365079365079</v>
       </c>
       <c r="AC611" t="n">
-        <v>0.482958</v>
+        <v>0.4721854545454546</v>
+      </c>
+      <c r="AG611" t="n">
+        <v>0.52815</v>
       </c>
       <c r="AI611" t="n">
         <v>0.535139534883721</v>
@@ -34409,7 +36185,10 @@
         <v>0.6320750000000001</v>
       </c>
       <c r="AC612" t="n">
-        <v>0.45343125</v>
+        <v>0.5489823529411766</v>
+      </c>
+      <c r="AG612" t="n">
+        <v>0.5162054054054054</v>
       </c>
       <c r="AI612" t="n">
         <v>0.4739463414634146</v>
@@ -34432,7 +36211,10 @@
         <v>0.5200589285714287</v>
       </c>
       <c r="AC613" t="n">
-        <v>0.5457659090909092</v>
+        <v>0.5557716666666667</v>
+      </c>
+      <c r="AG613" t="n">
+        <v>0.6759567567567568</v>
       </c>
       <c r="AI613" t="n">
         <v>0.5428290909090909</v>
@@ -34455,7 +36237,10 @@
         <v>0.5528916666666667</v>
       </c>
       <c r="AC614" t="n">
-        <v>0.4784367346938775</v>
+        <v>0.5175136363636365</v>
+      </c>
+      <c r="AG614" t="n">
+        <v>0.4732853658536585</v>
       </c>
       <c r="AI614" t="n">
         <v>0.4532660377358492</v>
@@ -34478,7 +36263,10 @@
         <v>0.447402</v>
       </c>
       <c r="AC615" t="n">
-        <v>0.5347275</v>
+        <v>0.5153795918367347</v>
+      </c>
+      <c r="AG615" t="n">
+        <v>0.681017142857143</v>
       </c>
       <c r="AI615" t="n">
         <v>0.4543424242424242</v>
@@ -34501,7 +36289,10 @@
         <v>0.5260574468085106</v>
       </c>
       <c r="AC616" t="n">
-        <v>0.4511044444444444</v>
+        <v>0.5326830769230769</v>
+      </c>
+      <c r="AG616" t="n">
+        <v>0.5610877551020409</v>
       </c>
       <c r="AI616" t="n">
         <v>0.4755127659574467</v>
@@ -34524,7 +36315,10 @@
         <v>0.446788</v>
       </c>
       <c r="AC617" t="n">
-        <v>0.4783062499999999</v>
+        <v>0.5707408163265306</v>
+      </c>
+      <c r="AG617" t="n">
+        <v>0.4817318181818181</v>
       </c>
       <c r="AI617" t="n">
         <v>0.377054</v>
@@ -34547,7 +36341,10 @@
         <v>0.4792728813559322</v>
       </c>
       <c r="AC618" t="n">
-        <v>0.4767510204081633</v>
+        <v>0.456211475409836</v>
+      </c>
+      <c r="AG618" t="n">
+        <v>0.631939393939394</v>
       </c>
       <c r="AI618" t="n">
         <v>0.4300561403508771</v>
@@ -34570,7 +36367,10 @@
         <v>0.6505066666666668</v>
       </c>
       <c r="AC619" t="n">
-        <v>0.4264708333333334</v>
+        <v>0.5503807692307692</v>
+      </c>
+      <c r="AG619" t="n">
+        <v>0.515921212121212</v>
       </c>
       <c r="AI619" t="n">
         <v>0.5009944444444445</v>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -766,6 +766,9 @@
       <c r="AG5" t="n">
         <v>0.1444220588235294</v>
       </c>
+      <c r="AH5" t="n">
+        <v>0.1384455882352941</v>
+      </c>
       <c r="AI5" t="n">
         <v>0.1300313432835821</v>
       </c>
@@ -846,6 +849,9 @@
       <c r="AG6" t="n">
         <v>0.2546185185185185</v>
       </c>
+      <c r="AH6" t="n">
+        <v>0.2015333333333333</v>
+      </c>
       <c r="AI6" t="n">
         <v>0.1945</v>
       </c>
@@ -926,6 +932,9 @@
       <c r="AG7" t="n">
         <v>0.29529375</v>
       </c>
+      <c r="AH7" t="n">
+        <v>0.3248823529411765</v>
+      </c>
       <c r="AI7" t="n">
         <v>0.2252636363636364</v>
       </c>
@@ -1006,6 +1015,9 @@
       <c r="AG8" t="n">
         <v>0.3587086956521739</v>
       </c>
+      <c r="AH8" t="n">
+        <v>0.2428086956521739</v>
+      </c>
       <c r="AI8" t="n">
         <v>0.3551473684210526</v>
       </c>
@@ -1086,6 +1098,9 @@
       <c r="AG9" t="n">
         <v>0.4033733333333333</v>
       </c>
+      <c r="AH9" t="n">
+        <v>0.4491285714285715</v>
+      </c>
       <c r="AI9" t="n">
         <v>0.4464521739130435</v>
       </c>
@@ -1166,6 +1181,9 @@
       <c r="AG10" t="n">
         <v>0.5431333333333334</v>
       </c>
+      <c r="AH10" t="n">
+        <v>0.4541260869565217</v>
+      </c>
       <c r="AI10" t="n">
         <v>0.4737409090909091</v>
       </c>
@@ -1246,6 +1264,9 @@
       <c r="AG11" t="n">
         <v>0.6328703703703703</v>
       </c>
+      <c r="AH11" t="n">
+        <v>0.6454277777777777</v>
+      </c>
       <c r="AI11" t="n">
         <v>0.5550304347826086</v>
       </c>
@@ -1326,6 +1347,9 @@
       <c r="AG12" t="n">
         <v>0.6659105263157894</v>
       </c>
+      <c r="AH12" t="n">
+        <v>0.65925</v>
+      </c>
       <c r="AI12" t="n">
         <v>0.5381</v>
       </c>
@@ -1406,6 +1430,9 @@
       <c r="AG13" t="n">
         <v>0.7138029411764706</v>
       </c>
+      <c r="AH13" t="n">
+        <v>0.6519966666666667</v>
+      </c>
       <c r="AI13" t="n">
         <v>0.6533703703703705</v>
       </c>
@@ -1486,6 +1513,9 @@
       <c r="AG14" t="n">
         <v>0.7791452380952381</v>
       </c>
+      <c r="AH14" t="n">
+        <v>0.7383620689655173</v>
+      </c>
       <c r="AI14" t="n">
         <v>0.64605</v>
       </c>
@@ -1557,6 +1587,9 @@
       <c r="AG15" t="n">
         <v>0.6907088235294117</v>
       </c>
+      <c r="AH15" t="n">
+        <v>0.667452380952381</v>
+      </c>
       <c r="AI15" t="n">
         <v>0.6991238095238095</v>
       </c>
@@ -1628,6 +1661,9 @@
       <c r="AG16" t="n">
         <v>0.8044242424242424</v>
       </c>
+      <c r="AH16" t="n">
+        <v>0.7701888888888889</v>
+      </c>
       <c r="AI16" t="n">
         <v>0.7390000000000001</v>
       </c>
@@ -1699,6 +1735,9 @@
       <c r="AG17" t="n">
         <v>0.8216470588235293</v>
       </c>
+      <c r="AH17" t="n">
+        <v>0.8126625000000001</v>
+      </c>
       <c r="AI17" t="n">
         <v>0.7603636363636365</v>
       </c>
@@ -1770,6 +1809,9 @@
       <c r="AG18" t="n">
         <v>0.8476916666666665</v>
       </c>
+      <c r="AH18" t="n">
+        <v>0.7617736842105264</v>
+      </c>
       <c r="AI18" t="n">
         <v>0.81838</v>
       </c>
@@ -1841,6 +1883,9 @@
       <c r="AG19" t="n">
         <v>0.8462595238095239</v>
       </c>
+      <c r="AH19" t="n">
+        <v>0.7741047619047619</v>
+      </c>
       <c r="AI19" t="n">
         <v>0.8034599999999998</v>
       </c>
@@ -1912,6 +1957,9 @@
       <c r="AG20" t="n">
         <v>0.8139575757575758</v>
       </c>
+      <c r="AH20" t="n">
+        <v>0.6452142857142857</v>
+      </c>
       <c r="AI20" t="n">
         <v>0.6894499999999999</v>
       </c>
@@ -1983,6 +2031,9 @@
       <c r="AG21" t="n">
         <v>0.8129480000000001</v>
       </c>
+      <c r="AH21" t="n">
+        <v>0.8558538461538461</v>
+      </c>
       <c r="AI21" t="n">
         <v>0.7377157894736841</v>
       </c>
@@ -2054,6 +2105,9 @@
       <c r="AG22" t="n">
         <v>0.8506088235294118</v>
       </c>
+      <c r="AH22" t="n">
+        <v>0.7737538461538461</v>
+      </c>
       <c r="AI22" t="n">
         <v>0.3317</v>
       </c>
@@ -2125,6 +2179,9 @@
       <c r="AG23" t="n">
         <v>0.7732114285714287</v>
       </c>
+      <c r="AH23" t="n">
+        <v>0.762882142857143</v>
+      </c>
       <c r="AI23" t="n">
         <v>0.7929571428571428</v>
       </c>
@@ -2196,6 +2253,9 @@
       <c r="AG24" t="n">
         <v>0.8626111111111112</v>
       </c>
+      <c r="AH24" t="n">
+        <v>0.8332371428571429</v>
+      </c>
       <c r="AI24" t="n">
         <v>0.7378400000000001</v>
       </c>
@@ -2267,6 +2327,9 @@
       <c r="AG25" t="n">
         <v>0.8401619047619048</v>
       </c>
+      <c r="AH25" t="n">
+        <v>0.8108487804878048</v>
+      </c>
       <c r="AI25" t="n">
         <v>0.74299</v>
       </c>
@@ -2338,6 +2401,9 @@
       <c r="AG26" t="n">
         <v>0.8851699999999999</v>
       </c>
+      <c r="AH26" t="n">
+        <v>0.8120717948717948</v>
+      </c>
       <c r="AI26" t="n">
         <v>0.8164666666666666</v>
       </c>
@@ -2409,6 +2475,9 @@
       <c r="AG27" t="n">
         <v>0.8068071428571428</v>
       </c>
+      <c r="AH27" t="n">
+        <v>0.8240700000000001</v>
+      </c>
       <c r="AI27" t="n">
         <v>0.69924</v>
       </c>
@@ -2480,6 +2549,9 @@
       <c r="AG28" t="n">
         <v>0.8382950000000001</v>
       </c>
+      <c r="AH28" t="n">
+        <v>0.8738172413793104</v>
+      </c>
       <c r="AI28" t="n">
         <v>0.7915764705882352</v>
       </c>
@@ -2551,6 +2623,9 @@
       <c r="AG29" t="n">
         <v>0.8456666666666667</v>
       </c>
+      <c r="AH29" t="n">
+        <v>0.8848216216216216</v>
+      </c>
       <c r="AI29" t="n">
         <v>0.7888333333333333</v>
       </c>
@@ -2622,6 +2697,9 @@
       <c r="AG30" t="n">
         <v>0.8683558139534883</v>
       </c>
+      <c r="AH30" t="n">
+        <v>0.8312361111111111</v>
+      </c>
       <c r="AI30" t="n">
         <v>0.7172551724137931</v>
       </c>
@@ -2693,6 +2771,9 @@
       <c r="AG31" t="n">
         <v>0.9041483870967743</v>
       </c>
+      <c r="AH31" t="n">
+        <v>0.8071724999999998</v>
+      </c>
       <c r="AI31" t="n">
         <v>0.80762</v>
       </c>
@@ -2764,6 +2845,9 @@
       <c r="AG32" t="n">
         <v>0.8286275</v>
       </c>
+      <c r="AH32" t="n">
+        <v>0.8405073170731705</v>
+      </c>
       <c r="AI32" t="n">
         <v>0.7754629629629629</v>
       </c>
@@ -2835,6 +2919,9 @@
       <c r="AG33" t="n">
         <v>0.8586911111111112</v>
       </c>
+      <c r="AH33" t="n">
+        <v>0.8492906976744187</v>
+      </c>
       <c r="AI33" t="n">
         <v>0.861742105263158</v>
       </c>
@@ -2906,6 +2993,9 @@
       <c r="AG34" t="n">
         <v>0.8450769230769232</v>
       </c>
+      <c r="AH34" t="n">
+        <v>0.841330303030303</v>
+      </c>
       <c r="AI34" t="n">
         <v>0.8034428571428572</v>
       </c>
@@ -2977,6 +3067,9 @@
       <c r="AG35" t="n">
         <v>0.7788975609756098</v>
       </c>
+      <c r="AH35" t="n">
+        <v>0.8616911764705882</v>
+      </c>
       <c r="AI35" t="n">
         <v>0.7826291666666667</v>
       </c>
@@ -3048,6 +3141,9 @@
       <c r="AG36" t="n">
         <v>0.8721238095238096</v>
       </c>
+      <c r="AH36" t="n">
+        <v>0.8974818181818182</v>
+      </c>
       <c r="AI36" t="n">
         <v>0.8525666666666667</v>
       </c>
@@ -3119,6 +3215,9 @@
       <c r="AG37" t="n">
         <v>0.7873033333333334</v>
       </c>
+      <c r="AH37" t="n">
+        <v>0.9127500000000001</v>
+      </c>
       <c r="AI37" t="n">
         <v>0.7153318181818181</v>
       </c>
@@ -3190,6 +3289,9 @@
       <c r="AG38" t="n">
         <v>0.8196461538461539</v>
       </c>
+      <c r="AH38" t="n">
+        <v>0.83965</v>
+      </c>
       <c r="AI38" t="n">
         <v>0.648242857142857</v>
       </c>
@@ -3261,6 +3363,9 @@
       <c r="AG39" t="n">
         <v>0.9542833333333335</v>
       </c>
+      <c r="AH39" t="n">
+        <v>0.8279218750000001</v>
+      </c>
       <c r="AI39" t="n">
         <v>0.7635384615384615</v>
       </c>
@@ -3332,6 +3437,9 @@
       <c r="AG40" t="n">
         <v>0.8326086956521739</v>
       </c>
+      <c r="AH40" t="n">
+        <v>0.8829129032258065</v>
+      </c>
       <c r="AI40" t="n">
         <v>0.8502416666666667</v>
       </c>
@@ -3403,6 +3511,9 @@
       <c r="AG41" t="n">
         <v>0.766475</v>
       </c>
+      <c r="AH41" t="n">
+        <v>0.8694484848484848</v>
+      </c>
       <c r="AI41" t="n">
         <v>0.7248052631578947</v>
       </c>
@@ -3474,6 +3585,9 @@
       <c r="AG42" t="n">
         <v>0.8674059999999999</v>
       </c>
+      <c r="AH42" t="n">
+        <v>0.8453869565217391</v>
+      </c>
       <c r="AI42" t="n">
         <v>0.8111619047619049</v>
       </c>
@@ -3545,6 +3659,9 @@
       <c r="AG43" t="n">
         <v>0.8555219512195121</v>
       </c>
+      <c r="AH43" t="n">
+        <v>0.8048500000000001</v>
+      </c>
       <c r="AI43" t="n">
         <v>0.9117714285714287</v>
       </c>
@@ -3616,6 +3733,9 @@
       <c r="AG44" t="n">
         <v>0.8947911764705883</v>
       </c>
+      <c r="AH44" t="n">
+        <v>0.7916411764705883</v>
+      </c>
       <c r="AI44" t="n">
         <v>0.8577357142857143</v>
       </c>
@@ -3687,6 +3807,9 @@
       <c r="AG45" t="n">
         <v>0.8364026315789473</v>
       </c>
+      <c r="AH45" t="n">
+        <v>0.8564108108108107</v>
+      </c>
       <c r="AI45" t="n">
         <v>0.7950076923076922</v>
       </c>
@@ -3758,6 +3881,9 @@
       <c r="AG46" t="n">
         <v>0.7907058823529411</v>
       </c>
+      <c r="AH46" t="n">
+        <v>0.8720291666666665</v>
+      </c>
       <c r="AI46" t="n">
         <v>0.8558136363636364</v>
       </c>
@@ -3829,6 +3955,9 @@
       <c r="AG47" t="n">
         <v>0.8581365853658536</v>
       </c>
+      <c r="AH47" t="n">
+        <v>0.8694862068965519</v>
+      </c>
       <c r="AI47" t="n">
         <v>0.7612833333333332</v>
       </c>
@@ -3900,6 +4029,9 @@
       <c r="AG48" t="n">
         <v>0.9355870967741936</v>
       </c>
+      <c r="AH48" t="n">
+        <v>0.876985294117647</v>
+      </c>
       <c r="AI48" t="n">
         <v>0.7560608695652175</v>
       </c>
@@ -3971,6 +4103,9 @@
       <c r="AG49" t="n">
         <v>0.8349897435897435</v>
       </c>
+      <c r="AH49" t="n">
+        <v>0.8379866666666665</v>
+      </c>
       <c r="AI49" t="n">
         <v>0.7343642857142857</v>
       </c>
@@ -4042,6 +4177,9 @@
       <c r="AG50" t="n">
         <v>0.8626372093023255</v>
       </c>
+      <c r="AH50" t="n">
+        <v>0.8068741935483872</v>
+      </c>
       <c r="AI50" t="n">
         <v>0.8132285714285714</v>
       </c>
@@ -4113,6 +4251,9 @@
       <c r="AG51" t="n">
         <v>0.8403444444444443</v>
       </c>
+      <c r="AH51" t="n">
+        <v>0.8953423076923077</v>
+      </c>
       <c r="AI51" t="n">
         <v>0.8495578947368422</v>
       </c>
@@ -4184,6 +4325,9 @@
       <c r="AG52" t="n">
         <v>0.87743</v>
       </c>
+      <c r="AH52" t="n">
+        <v>0.9002727272727273</v>
+      </c>
       <c r="AI52" t="n">
         <v>0.8635695652173914</v>
       </c>
@@ -4255,6 +4399,9 @@
       <c r="AG53" t="n">
         <v>0.8419816326530611</v>
       </c>
+      <c r="AH53" t="n">
+        <v>0.833008</v>
+      </c>
       <c r="AI53" t="n">
         <v>0.8532714285714286</v>
       </c>
@@ -4326,6 +4473,9 @@
       <c r="AG54" t="n">
         <v>0.8447468085106383</v>
       </c>
+      <c r="AH54" t="n">
+        <v>0.8419500000000001</v>
+      </c>
       <c r="AI54" t="n">
         <v>0.7911</v>
       </c>
@@ -4397,6 +4547,9 @@
       <c r="AG55" t="n">
         <v>0.7363166666666667</v>
       </c>
+      <c r="AH55" t="n">
+        <v>0.9225238095238095</v>
+      </c>
       <c r="AI55" t="n">
         <v>0.82185</v>
       </c>
@@ -4468,6 +4621,9 @@
       <c r="AG56" t="n">
         <v>0.8710487179487182</v>
       </c>
+      <c r="AH56" t="n">
+        <v>0.8557307692307692</v>
+      </c>
       <c r="AI56" t="n">
         <v>0.7447764705882354</v>
       </c>
@@ -4539,6 +4695,9 @@
       <c r="AG57" t="n">
         <v>0.91634</v>
       </c>
+      <c r="AH57" t="n">
+        <v>0.8817558823529412</v>
+      </c>
       <c r="AI57" t="n">
         <v>0.7757166666666667</v>
       </c>
@@ -4610,6 +4769,9 @@
       <c r="AG58" t="n">
         <v>0.9305969696969696</v>
       </c>
+      <c r="AH58" t="n">
+        <v>0.8710439999999998</v>
+      </c>
       <c r="AI58" t="n">
         <v>0.8056529411764707</v>
       </c>
@@ -4681,6 +4843,9 @@
       <c r="AG59" t="n">
         <v>0.8735666666666667</v>
       </c>
+      <c r="AH59" t="n">
+        <v>0.8885807692307692</v>
+      </c>
       <c r="AI59" t="n">
         <v>0.8226588235294118</v>
       </c>
@@ -4752,6 +4917,9 @@
       <c r="AG60" t="n">
         <v>0.8537196078431372</v>
       </c>
+      <c r="AH60" t="n">
+        <v>0.8895058823529413</v>
+      </c>
       <c r="AI60" t="n">
         <v>0.74572</v>
       </c>
@@ -4823,6 +4991,9 @@
       <c r="AG61" t="n">
         <v>0.92111875</v>
       </c>
+      <c r="AH61" t="n">
+        <v>0.8522344827586207</v>
+      </c>
       <c r="AI61" t="n">
         <v>0.7422347826086957</v>
       </c>
@@ -4894,6 +5065,9 @@
       <c r="AG62" t="n">
         <v>0.9207299999999999</v>
       </c>
+      <c r="AH62" t="n">
+        <v>0.8214625</v>
+      </c>
       <c r="AI62" t="n">
         <v>0.9042545454545454</v>
       </c>
@@ -4965,6 +5139,9 @@
       <c r="AG63" t="n">
         <v>0.9001749999999999</v>
       </c>
+      <c r="AH63" t="n">
+        <v>0.8729137931034484</v>
+      </c>
       <c r="AI63" t="n">
         <v>0.8332333333333333</v>
       </c>
@@ -5036,6 +5213,9 @@
       <c r="AG64" t="n">
         <v>0.865484</v>
       </c>
+      <c r="AH64" t="n">
+        <v>0.8827219512195122</v>
+      </c>
       <c r="AI64" t="n">
         <v>0.89825</v>
       </c>
@@ -5107,6 +5287,9 @@
       <c r="AG65" t="n">
         <v>0.942934210526316</v>
       </c>
+      <c r="AH65" t="n">
+        <v>0.8627684210526316</v>
+      </c>
       <c r="AI65" t="n">
         <v>0.8747909090909091</v>
       </c>
@@ -5178,6 +5361,9 @@
       <c r="AG66" t="n">
         <v>0.8442041666666666</v>
       </c>
+      <c r="AH66" t="n">
+        <v>0.8280023255813954</v>
+      </c>
       <c r="AI66" t="n">
         <v>0.8047294117647058</v>
       </c>
@@ -5249,6 +5435,9 @@
       <c r="AG67" t="n">
         <v>0.845618918918919</v>
       </c>
+      <c r="AH67" t="n">
+        <v>0.8673909090909091</v>
+      </c>
       <c r="AI67" t="n">
         <v>0.8612222222222222</v>
       </c>
@@ -5320,6 +5509,9 @@
       <c r="AG68" t="n">
         <v>0.871286046511628</v>
       </c>
+      <c r="AH68" t="n">
+        <v>0.8567416666666666</v>
+      </c>
       <c r="AI68" t="n">
         <v>0.8662904761904762</v>
       </c>
@@ -5391,6 +5583,9 @@
       <c r="AG69" t="n">
         <v>0.734975</v>
       </c>
+      <c r="AH69" t="n">
+        <v>0.8673739130434781</v>
+      </c>
       <c r="AI69" t="n">
         <v>0.830925</v>
       </c>
@@ -5462,6 +5657,9 @@
       <c r="AG70" t="n">
         <v>0.9112117647058824</v>
       </c>
+      <c r="AH70" t="n">
+        <v>0.8169114285714285</v>
+      </c>
       <c r="AI70" t="n">
         <v>0.8072952380952382</v>
       </c>
@@ -5531,7 +5729,10 @@
         <v>0.8124909090909092</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.8813255813953488</v>
+        <v>0.8561836363636364</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0.8336034482758621</v>
       </c>
       <c r="AI71" t="n">
         <v>0.8981545454545454</v>
@@ -5602,7 +5803,10 @@
         <v>0.7806142857142857</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.8930333333333331</v>
+        <v>0.8720466666666666</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0.8490897435897435</v>
       </c>
       <c r="AI72" t="n">
         <v>0.8337</v>
@@ -5675,6 +5879,9 @@
       <c r="AG73" t="n">
         <v>0.9014681818181818</v>
       </c>
+      <c r="AH73" t="n">
+        <v>0.7436294117647058</v>
+      </c>
       <c r="AI73" t="n">
         <v>0.8648571428571429</v>
       </c>
@@ -5746,6 +5953,9 @@
       <c r="AG74" t="n">
         <v>0.870672</v>
       </c>
+      <c r="AH74" t="n">
+        <v>0.7783615384615385</v>
+      </c>
       <c r="AI74" t="n">
         <v>0.8498</v>
       </c>
@@ -5817,6 +6027,9 @@
       <c r="AG75" t="n">
         <v>0.8901314285714287</v>
       </c>
+      <c r="AH75" t="n">
+        <v>0.8139382352941178</v>
+      </c>
       <c r="AI75" t="n">
         <v>0.8002600000000001</v>
       </c>
@@ -5888,6 +6101,9 @@
       <c r="AG76" t="n">
         <v>0.9011222222222223</v>
       </c>
+      <c r="AH76" t="n">
+        <v>0.8426739130434783</v>
+      </c>
       <c r="AI76" t="n">
         <v>0.7300083333333335</v>
       </c>
@@ -5959,6 +6175,9 @@
       <c r="AG77" t="n">
         <v>0.8690860465116279</v>
       </c>
+      <c r="AH77" t="n">
+        <v>0.8412176470588236</v>
+      </c>
       <c r="AI77" t="n">
         <v>0.79581875</v>
       </c>
@@ -6030,6 +6249,9 @@
       <c r="AG78" t="n">
         <v>0.845924</v>
       </c>
+      <c r="AH78" t="n">
+        <v>0.8194846153846155</v>
+      </c>
       <c r="AI78" t="n">
         <v>0.8825818181818181</v>
       </c>
@@ -6101,6 +6323,9 @@
       <c r="AG79" t="n">
         <v>0.8899279069767442</v>
       </c>
+      <c r="AH79" t="n">
+        <v>0.8936153846153847</v>
+      </c>
       <c r="AI79" t="n">
         <v>0.7831111111111112</v>
       </c>
@@ -6172,6 +6397,9 @@
       <c r="AG80" t="n">
         <v>0.8731923076923078</v>
       </c>
+      <c r="AH80" t="n">
+        <v>0.8983466666666667</v>
+      </c>
       <c r="AI80" t="n">
         <v>0.7742857142857144</v>
       </c>
@@ -6243,6 +6471,9 @@
       <c r="AG81" t="n">
         <v>0.8634222222222222</v>
       </c>
+      <c r="AH81" t="n">
+        <v>0.8359085714285714</v>
+      </c>
       <c r="AI81" t="n">
         <v>0.7648411764705882</v>
       </c>
@@ -6314,6 +6545,9 @@
       <c r="AG82" t="n">
         <v>0.8649288888888889</v>
       </c>
+      <c r="AH82" t="n">
+        <v>0.8762444444444446</v>
+      </c>
       <c r="AI82" t="n">
         <v>0.82875</v>
       </c>
@@ -6385,6 +6619,9 @@
       <c r="AG83" t="n">
         <v>0.8624686274509804</v>
       </c>
+      <c r="AH83" t="n">
+        <v>0.8619348837209301</v>
+      </c>
       <c r="AI83" t="n">
         <v>0.7655000000000001</v>
       </c>
@@ -6456,6 +6693,9 @@
       <c r="AG84" t="n">
         <v>0.8451090909090908</v>
       </c>
+      <c r="AH84" t="n">
+        <v>0.8569099999999999</v>
+      </c>
       <c r="AI84" t="n">
         <v>0.8789187500000001</v>
       </c>
@@ -6527,6 +6767,9 @@
       <c r="AG85" t="n">
         <v>0.8907369565217391</v>
       </c>
+      <c r="AH85" t="n">
+        <v>0.8442777777777778</v>
+      </c>
       <c r="AI85" t="n">
         <v>0.8657625000000001</v>
       </c>
@@ -6598,6 +6841,9 @@
       <c r="AG86" t="n">
         <v>0.9096526315789474</v>
       </c>
+      <c r="AH86" t="n">
+        <v>0.8836121951219512</v>
+      </c>
       <c r="AI86" t="n">
         <v>0.7613666666666666</v>
       </c>
@@ -6669,6 +6915,9 @@
       <c r="AG87" t="n">
         <v>0.8535130434782608</v>
       </c>
+      <c r="AH87" t="n">
+        <v>0.8382804878048781</v>
+      </c>
       <c r="AI87" t="n">
         <v>0.7791842105263158</v>
       </c>
@@ -6740,6 +6989,9 @@
       <c r="AG88" t="n">
         <v>0.8412625</v>
       </c>
+      <c r="AH88" t="n">
+        <v>0.8419387096774192</v>
+      </c>
       <c r="AI88" t="n">
         <v>0.801004761904762</v>
       </c>
@@ -6811,6 +7063,9 @@
       <c r="AG89" t="n">
         <v>0.8927854166666668</v>
       </c>
+      <c r="AH89" t="n">
+        <v>0.8526846153846152</v>
+      </c>
       <c r="AI89" t="n">
         <v>0.8487666666666667</v>
       </c>
@@ -6882,6 +7137,9 @@
       <c r="AG90" t="n">
         <v>0.8915225000000001</v>
       </c>
+      <c r="AH90" t="n">
+        <v>0.9271621621621622</v>
+      </c>
       <c r="AI90" t="n">
         <v>0.8916153846153846</v>
       </c>
@@ -6953,6 +7211,9 @@
       <c r="AG91" t="n">
         <v>0.834263888888889</v>
       </c>
+      <c r="AH91" t="n">
+        <v>0.8098648648648648</v>
+      </c>
       <c r="AI91" t="n">
         <v>0.7642</v>
       </c>
@@ -7024,6 +7285,9 @@
       <c r="AG92" t="n">
         <v>0.9011121951219512</v>
       </c>
+      <c r="AH92" t="n">
+        <v>0.8394939393939393</v>
+      </c>
       <c r="AI92" t="n">
         <v>0.8095</v>
       </c>
@@ -7095,6 +7359,9 @@
       <c r="AG93" t="n">
         <v>0.8462468750000001</v>
       </c>
+      <c r="AH93" t="n">
+        <v>0.8351500000000001</v>
+      </c>
       <c r="AI93" t="n">
         <v>0.8826357142857143</v>
       </c>
@@ -7166,6 +7433,9 @@
       <c r="AG94" t="n">
         <v>0.8884404761904763</v>
       </c>
+      <c r="AH94" t="n">
+        <v>0.9249739130434783</v>
+      </c>
       <c r="AI94" t="n">
         <v>0.838004761904762</v>
       </c>
@@ -7237,6 +7507,9 @@
       <c r="AG95" t="n">
         <v>0.8711861111111112</v>
       </c>
+      <c r="AH95" t="n">
+        <v>0.8619685714285714</v>
+      </c>
       <c r="AI95" t="n">
         <v>0.7770615384615385</v>
       </c>
@@ -7308,6 +7581,9 @@
       <c r="AG96" t="n">
         <v>0.857909375</v>
       </c>
+      <c r="AH96" t="n">
+        <v>0.8194423076923077</v>
+      </c>
       <c r="AI96" t="n">
         <v>0.8062428571428571</v>
       </c>
@@ -7379,6 +7655,9 @@
       <c r="AG97" t="n">
         <v>0.8854935483870968</v>
       </c>
+      <c r="AH97" t="n">
+        <v>0.8053208333333332</v>
+      </c>
       <c r="AI97" t="n">
         <v>0.8111068965517242</v>
       </c>
@@ -7450,6 +7729,9 @@
       <c r="AG98" t="n">
         <v>0.8519176470588236</v>
       </c>
+      <c r="AH98" t="n">
+        <v>0.792378947368421</v>
+      </c>
       <c r="AI98" t="n">
         <v>0.8417523809523809</v>
       </c>
@@ -7521,6 +7803,9 @@
       <c r="AG99" t="n">
         <v>0.8394272727272728</v>
       </c>
+      <c r="AH99" t="n">
+        <v>0.8941628571428571</v>
+      </c>
       <c r="AI99" t="n">
         <v>0.8653090909090909</v>
       </c>
@@ -7592,6 +7877,9 @@
       <c r="AG100" t="n">
         <v>0.8813866666666667</v>
       </c>
+      <c r="AH100" t="n">
+        <v>0.7646714285714283</v>
+      </c>
       <c r="AI100" t="n">
         <v>0.8858357142857144</v>
       </c>
@@ -7663,6 +7951,9 @@
       <c r="AG101" t="n">
         <v>0.8519739130434781</v>
       </c>
+      <c r="AH101" t="n">
+        <v>0.8619964285714284</v>
+      </c>
       <c r="AI101" t="n">
         <v>0.8938117647058824</v>
       </c>
@@ -7734,6 +8025,9 @@
       <c r="AG102" t="n">
         <v>0.8819733333333334</v>
       </c>
+      <c r="AH102" t="n">
+        <v>0.8644555555555556</v>
+      </c>
       <c r="AI102" t="n">
         <v>0.8413999999999999</v>
       </c>
@@ -7805,6 +8099,9 @@
       <c r="AG103" t="n">
         <v>0.8554162790697677</v>
       </c>
+      <c r="AH103" t="n">
+        <v>0.8488749999999999</v>
+      </c>
       <c r="AI103" t="n">
         <v>0.8463416666666667</v>
       </c>
@@ -7875,6 +8172,9 @@
       </c>
       <c r="AG104" t="n">
         <v>0.8421581395348837</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>0.8246193548387097</v>
       </c>
       <c r="AI104" t="n">
         <v>0.851348</v>
@@ -7980,6 +8280,9 @@
       <c r="AG108" t="n">
         <v>0.9333333333333333</v>
       </c>
+      <c r="AH108" t="n">
+        <v>0.8666666666666667</v>
+      </c>
       <c r="AI108" t="n">
         <v>1</v>
       </c>
@@ -8060,6 +8363,9 @@
       <c r="AG109" t="n">
         <v>0.8666666666666667</v>
       </c>
+      <c r="AH109" t="n">
+        <v>0.9333333333333333</v>
+      </c>
       <c r="AI109" t="n">
         <v>0.8</v>
       </c>
@@ -8140,6 +8446,9 @@
       <c r="AG110" t="n">
         <v>0.9230769230769231</v>
       </c>
+      <c r="AH110" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AI110" t="n">
         <v>0.8461538461538461</v>
       </c>
@@ -8220,6 +8529,9 @@
       <c r="AG111" t="n">
         <v>0.7777777777777778</v>
       </c>
+      <c r="AH111" t="n">
+        <v>0.9090909090909091</v>
+      </c>
       <c r="AI111" t="n">
         <v>1</v>
       </c>
@@ -8300,6 +8612,9 @@
       <c r="AG112" t="n">
         <v>1</v>
       </c>
+      <c r="AH112" t="n">
+        <v>1</v>
+      </c>
       <c r="AI112" t="n">
         <v>0.75</v>
       </c>
@@ -8380,6 +8695,9 @@
       <c r="AG113" t="n">
         <v>1</v>
       </c>
+      <c r="AH113" t="n">
+        <v>1</v>
+      </c>
       <c r="AI113" t="n">
         <v>1</v>
       </c>
@@ -8460,6 +8778,9 @@
       <c r="AG114" t="n">
         <v>0.9</v>
       </c>
+      <c r="AH114" t="n">
+        <v>1</v>
+      </c>
       <c r="AI114" t="n">
         <v>1</v>
       </c>
@@ -8540,6 +8861,9 @@
       <c r="AG115" t="n">
         <v>1</v>
       </c>
+      <c r="AH115" t="n">
+        <v>1</v>
+      </c>
       <c r="AI115" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -8620,6 +8944,9 @@
       <c r="AG116" t="n">
         <v>0.75</v>
       </c>
+      <c r="AH116" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AI116" t="n">
         <v>1</v>
       </c>
@@ -8700,6 +9027,9 @@
       <c r="AG117" t="n">
         <v>0.875</v>
       </c>
+      <c r="AH117" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AI117" t="n">
         <v>1</v>
       </c>
@@ -8768,6 +9098,9 @@
       <c r="AG118" t="n">
         <v>1</v>
       </c>
+      <c r="AH118" t="n">
+        <v>1</v>
+      </c>
       <c r="AI118" t="n">
         <v>1</v>
       </c>
@@ -8839,6 +9172,9 @@
       <c r="AG119" t="n">
         <v>1</v>
       </c>
+      <c r="AH119" t="n">
+        <v>1</v>
+      </c>
       <c r="AI119" t="n">
         <v>1</v>
       </c>
@@ -8910,6 +9246,9 @@
       <c r="AG120" t="n">
         <v>1</v>
       </c>
+      <c r="AH120" t="n">
+        <v>1</v>
+      </c>
       <c r="AI120" t="n">
         <v>1</v>
       </c>
@@ -8981,6 +9320,9 @@
       <c r="AG121" t="n">
         <v>1</v>
       </c>
+      <c r="AH121" t="n">
+        <v>1</v>
+      </c>
       <c r="AI121" t="n">
         <v>1</v>
       </c>
@@ -9052,6 +9394,9 @@
       <c r="AG122" t="n">
         <v>1</v>
       </c>
+      <c r="AH122" t="n">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="AI122" t="n">
         <v>1</v>
       </c>
@@ -9123,6 +9468,9 @@
       <c r="AG123" t="n">
         <v>0.875</v>
       </c>
+      <c r="AH123" t="n">
+        <v>1</v>
+      </c>
       <c r="AI123" t="n">
         <v>1</v>
       </c>
@@ -9194,6 +9542,9 @@
       <c r="AG124" t="n">
         <v>1</v>
       </c>
+      <c r="AH124" t="n">
+        <v>1</v>
+      </c>
       <c r="AI124" t="n">
         <v>1</v>
       </c>
@@ -9265,6 +9616,9 @@
       <c r="AG125" t="n">
         <v>1</v>
       </c>
+      <c r="AH125" t="n">
+        <v>1</v>
+      </c>
       <c r="AI125" t="n">
         <v>1</v>
       </c>
@@ -9336,6 +9690,9 @@
       <c r="AG126" t="n">
         <v>1</v>
       </c>
+      <c r="AH126" t="n">
+        <v>1</v>
+      </c>
       <c r="AI126" t="n">
         <v>1</v>
       </c>
@@ -9407,6 +9764,9 @@
       <c r="AG127" t="n">
         <v>1</v>
       </c>
+      <c r="AH127" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="128" ht="16" customHeight="1" s="8">
       <c r="A128" s="5" t="n">
@@ -9475,6 +9835,9 @@
       <c r="AG128" t="n">
         <v>1</v>
       </c>
+      <c r="AH128" t="n">
+        <v>1</v>
+      </c>
       <c r="AI128" t="n">
         <v>1</v>
       </c>
@@ -9546,6 +9909,9 @@
       <c r="AG129" t="n">
         <v>1</v>
       </c>
+      <c r="AH129" t="n">
+        <v>1</v>
+      </c>
       <c r="AI129" t="n">
         <v>1</v>
       </c>
@@ -9617,6 +9983,9 @@
       <c r="AG130" t="n">
         <v>1</v>
       </c>
+      <c r="AH130" t="n">
+        <v>1</v>
+      </c>
       <c r="AI130" t="n">
         <v>1</v>
       </c>
@@ -9688,6 +10057,9 @@
       <c r="AG131" t="n">
         <v>1</v>
       </c>
+      <c r="AH131" t="n">
+        <v>1</v>
+      </c>
       <c r="AI131" t="n">
         <v>1</v>
       </c>
@@ -9759,6 +10131,9 @@
       <c r="AG132" t="n">
         <v>1</v>
       </c>
+      <c r="AH132" t="n">
+        <v>1</v>
+      </c>
       <c r="AI132" t="n">
         <v>1</v>
       </c>
@@ -9830,6 +10205,9 @@
       <c r="AG133" t="n">
         <v>1</v>
       </c>
+      <c r="AH133" t="n">
+        <v>1</v>
+      </c>
       <c r="AI133" t="n">
         <v>1</v>
       </c>
@@ -9901,6 +10279,9 @@
       <c r="AG134" t="n">
         <v>1</v>
       </c>
+      <c r="AH134" t="n">
+        <v>1</v>
+      </c>
       <c r="AI134" t="n">
         <v>1</v>
       </c>
@@ -9972,6 +10353,9 @@
       <c r="AG135" t="n">
         <v>1</v>
       </c>
+      <c r="AH135" t="n">
+        <v>1</v>
+      </c>
       <c r="AI135" t="n">
         <v>1</v>
       </c>
@@ -10043,6 +10427,9 @@
       <c r="AG136" t="n">
         <v>1</v>
       </c>
+      <c r="AH136" t="n">
+        <v>1</v>
+      </c>
       <c r="AI136" t="n">
         <v>1</v>
       </c>
@@ -10114,6 +10501,9 @@
       <c r="AG137" t="n">
         <v>1</v>
       </c>
+      <c r="AH137" t="n">
+        <v>1</v>
+      </c>
       <c r="AI137" t="n">
         <v>1</v>
       </c>
@@ -10185,6 +10575,9 @@
       <c r="AG138" t="n">
         <v>1</v>
       </c>
+      <c r="AH138" t="n">
+        <v>1</v>
+      </c>
       <c r="AI138" t="n">
         <v>1</v>
       </c>
@@ -10256,6 +10649,9 @@
       <c r="AG139" t="n">
         <v>1</v>
       </c>
+      <c r="AH139" t="n">
+        <v>1</v>
+      </c>
       <c r="AI139" t="n">
         <v>1</v>
       </c>
@@ -10324,6 +10720,9 @@
       <c r="AG140" t="n">
         <v>1</v>
       </c>
+      <c r="AH140" t="n">
+        <v>1</v>
+      </c>
       <c r="AI140" t="n">
         <v>1</v>
       </c>
@@ -10395,6 +10794,9 @@
       <c r="AG141" t="n">
         <v>1</v>
       </c>
+      <c r="AH141" t="n">
+        <v>1</v>
+      </c>
       <c r="AI141" t="n">
         <v>1</v>
       </c>
@@ -10466,6 +10868,9 @@
       <c r="AG142" t="n">
         <v>1</v>
       </c>
+      <c r="AH142" t="n">
+        <v>1</v>
+      </c>
       <c r="AI142" t="n">
         <v>1</v>
       </c>
@@ -10534,6 +10939,9 @@
       <c r="AG143" t="n">
         <v>1</v>
       </c>
+      <c r="AH143" t="n">
+        <v>1</v>
+      </c>
       <c r="AI143" t="n">
         <v>1</v>
       </c>
@@ -10605,6 +11013,9 @@
       <c r="AG144" t="n">
         <v>1</v>
       </c>
+      <c r="AH144" t="n">
+        <v>1</v>
+      </c>
       <c r="AI144" t="n">
         <v>1</v>
       </c>
@@ -10676,6 +11087,9 @@
       <c r="AG145" t="n">
         <v>1</v>
       </c>
+      <c r="AH145" t="n">
+        <v>1</v>
+      </c>
       <c r="AI145" t="n">
         <v>1</v>
       </c>
@@ -10747,6 +11161,9 @@
       <c r="AG146" t="n">
         <v>1</v>
       </c>
+      <c r="AH146" t="n">
+        <v>1</v>
+      </c>
       <c r="AI146" t="n">
         <v>1</v>
       </c>
@@ -10818,6 +11235,9 @@
       <c r="AG147" t="n">
         <v>1</v>
       </c>
+      <c r="AH147" t="n">
+        <v>1</v>
+      </c>
       <c r="AI147" t="n">
         <v>1</v>
       </c>
@@ -10889,6 +11309,9 @@
       <c r="AG148" t="n">
         <v>1</v>
       </c>
+      <c r="AH148" t="n">
+        <v>1</v>
+      </c>
       <c r="AI148" t="n">
         <v>1</v>
       </c>
@@ -10960,6 +11383,9 @@
       <c r="AG149" t="n">
         <v>1</v>
       </c>
+      <c r="AH149" t="n">
+        <v>1</v>
+      </c>
       <c r="AI149" t="n">
         <v>1</v>
       </c>
@@ -11031,6 +11457,9 @@
       <c r="AG150" t="n">
         <v>0.7142857142857143</v>
       </c>
+      <c r="AH150" t="n">
+        <v>1</v>
+      </c>
       <c r="AI150" t="n">
         <v>1</v>
       </c>
@@ -11102,6 +11531,9 @@
       <c r="AG151" t="n">
         <v>1</v>
       </c>
+      <c r="AH151" t="n">
+        <v>1</v>
+      </c>
       <c r="AI151" t="n">
         <v>1</v>
       </c>
@@ -11173,6 +11605,9 @@
       <c r="AG152" t="n">
         <v>1</v>
       </c>
+      <c r="AH152" t="n">
+        <v>1</v>
+      </c>
       <c r="AI152" t="n">
         <v>1</v>
       </c>
@@ -11244,6 +11679,9 @@
       <c r="AG153" t="n">
         <v>1</v>
       </c>
+      <c r="AH153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" ht="16" customHeight="1" s="8">
       <c r="A154" s="5" t="n">
@@ -11312,6 +11750,9 @@
       <c r="AG154" t="n">
         <v>1</v>
       </c>
+      <c r="AH154" t="n">
+        <v>1</v>
+      </c>
       <c r="AI154" t="n">
         <v>1</v>
       </c>
@@ -11383,6 +11824,9 @@
       <c r="AG155" t="n">
         <v>1</v>
       </c>
+      <c r="AH155" t="n">
+        <v>1</v>
+      </c>
       <c r="AI155" t="n">
         <v>1</v>
       </c>
@@ -11454,6 +11898,9 @@
       <c r="AG156" t="n">
         <v>1</v>
       </c>
+      <c r="AH156" t="n">
+        <v>1</v>
+      </c>
       <c r="AI156" t="n">
         <v>1</v>
       </c>
@@ -11525,6 +11972,9 @@
       <c r="AG157" t="n">
         <v>1</v>
       </c>
+      <c r="AH157" t="n">
+        <v>1</v>
+      </c>
       <c r="AI157" t="n">
         <v>1</v>
       </c>
@@ -11596,6 +12046,9 @@
       <c r="AG158" t="n">
         <v>1</v>
       </c>
+      <c r="AH158" t="n">
+        <v>1</v>
+      </c>
       <c r="AI158" t="n">
         <v>1</v>
       </c>
@@ -11667,6 +12120,9 @@
       <c r="AG159" t="n">
         <v>1</v>
       </c>
+      <c r="AH159" t="n">
+        <v>1</v>
+      </c>
       <c r="AI159" t="n">
         <v>1</v>
       </c>
@@ -11738,6 +12194,9 @@
       <c r="AG160" t="n">
         <v>1</v>
       </c>
+      <c r="AH160" t="n">
+        <v>1</v>
+      </c>
       <c r="AI160" t="n">
         <v>1</v>
       </c>
@@ -11809,6 +12268,9 @@
       <c r="AG161" t="n">
         <v>1</v>
       </c>
+      <c r="AH161" t="n">
+        <v>1</v>
+      </c>
       <c r="AI161" t="n">
         <v>1</v>
       </c>
@@ -11880,6 +12342,9 @@
       <c r="AG162" t="n">
         <v>1</v>
       </c>
+      <c r="AH162" t="n">
+        <v>1</v>
+      </c>
       <c r="AI162" t="n">
         <v>1</v>
       </c>
@@ -11951,6 +12416,9 @@
       <c r="AG163" t="n">
         <v>1</v>
       </c>
+      <c r="AH163" t="n">
+        <v>1</v>
+      </c>
       <c r="AI163" t="n">
         <v>1</v>
       </c>
@@ -12022,6 +12490,9 @@
       <c r="AG164" t="n">
         <v>1</v>
       </c>
+      <c r="AH164" t="n">
+        <v>1</v>
+      </c>
       <c r="AI164" t="n">
         <v>1</v>
       </c>
@@ -12093,6 +12564,9 @@
       <c r="AG165" t="n">
         <v>1</v>
       </c>
+      <c r="AH165" t="n">
+        <v>1</v>
+      </c>
       <c r="AI165" t="n">
         <v>1</v>
       </c>
@@ -12164,6 +12638,9 @@
       <c r="AG166" t="n">
         <v>1</v>
       </c>
+      <c r="AH166" t="n">
+        <v>1</v>
+      </c>
       <c r="AI166" t="n">
         <v>1</v>
       </c>
@@ -12235,6 +12712,9 @@
       <c r="AG167" t="n">
         <v>1</v>
       </c>
+      <c r="AH167" t="n">
+        <v>1</v>
+      </c>
       <c r="AI167" t="n">
         <v>1</v>
       </c>
@@ -12306,6 +12786,9 @@
       <c r="AG168" t="n">
         <v>1</v>
       </c>
+      <c r="AH168" t="n">
+        <v>1</v>
+      </c>
       <c r="AI168" t="n">
         <v>1</v>
       </c>
@@ -12377,6 +12860,9 @@
       <c r="AG169" t="n">
         <v>1</v>
       </c>
+      <c r="AH169" t="n">
+        <v>1</v>
+      </c>
       <c r="AI169" t="n">
         <v>1</v>
       </c>
@@ -12448,6 +12934,9 @@
       <c r="AG170" t="n">
         <v>1</v>
       </c>
+      <c r="AH170" t="n">
+        <v>1</v>
+      </c>
       <c r="AI170" t="n">
         <v>1</v>
       </c>
@@ -12519,6 +13008,9 @@
       <c r="AG171" t="n">
         <v>1</v>
       </c>
+      <c r="AH171" t="n">
+        <v>1</v>
+      </c>
       <c r="AI171" t="n">
         <v>1</v>
       </c>
@@ -12590,6 +13082,9 @@
       <c r="AG172" t="n">
         <v>1</v>
       </c>
+      <c r="AH172" t="n">
+        <v>1</v>
+      </c>
       <c r="AI172" t="n">
         <v>1</v>
       </c>
@@ -12661,6 +13156,9 @@
       <c r="AG173" t="n">
         <v>1</v>
       </c>
+      <c r="AH173" t="n">
+        <v>1</v>
+      </c>
       <c r="AI173" t="n">
         <v>1</v>
       </c>
@@ -12732,6 +13230,9 @@
       <c r="AG174" t="n">
         <v>1</v>
       </c>
+      <c r="AH174" t="n">
+        <v>1</v>
+      </c>
       <c r="AI174" t="n">
         <v>1</v>
       </c>
@@ -12803,6 +13304,9 @@
       <c r="AG175" t="n">
         <v>1</v>
       </c>
+      <c r="AH175" t="n">
+        <v>1</v>
+      </c>
       <c r="AI175" t="n">
         <v>1</v>
       </c>
@@ -12874,6 +13378,9 @@
       <c r="AG176" t="n">
         <v>1</v>
       </c>
+      <c r="AH176" t="n">
+        <v>1</v>
+      </c>
       <c r="AI176" t="n">
         <v>1</v>
       </c>
@@ -12945,6 +13452,9 @@
       <c r="AG177" t="n">
         <v>1</v>
       </c>
+      <c r="AH177" t="n">
+        <v>1</v>
+      </c>
       <c r="AI177" t="n">
         <v>1</v>
       </c>
@@ -13016,6 +13526,9 @@
       <c r="AG178" t="n">
         <v>1</v>
       </c>
+      <c r="AH178" t="n">
+        <v>1</v>
+      </c>
       <c r="AI178" t="n">
         <v>1</v>
       </c>
@@ -13087,6 +13600,9 @@
       <c r="AG179" t="n">
         <v>1</v>
       </c>
+      <c r="AH179" t="n">
+        <v>1</v>
+      </c>
       <c r="AI179" t="n">
         <v>1</v>
       </c>
@@ -13158,6 +13674,9 @@
       <c r="AG180" t="n">
         <v>1</v>
       </c>
+      <c r="AH180" t="n">
+        <v>1</v>
+      </c>
       <c r="AI180" t="n">
         <v>1</v>
       </c>
@@ -13226,6 +13745,9 @@
       <c r="AG181" t="n">
         <v>1</v>
       </c>
+      <c r="AH181" t="n">
+        <v>1</v>
+      </c>
       <c r="AI181" t="n">
         <v>1</v>
       </c>
@@ -13297,6 +13819,9 @@
       <c r="AG182" t="n">
         <v>1</v>
       </c>
+      <c r="AH182" t="n">
+        <v>1</v>
+      </c>
       <c r="AI182" t="n">
         <v>1</v>
       </c>
@@ -13368,6 +13893,9 @@
       <c r="AG183" t="n">
         <v>1</v>
       </c>
+      <c r="AH183" t="n">
+        <v>1</v>
+      </c>
       <c r="AI183" t="n">
         <v>1</v>
       </c>
@@ -13439,6 +13967,9 @@
       <c r="AG184" t="n">
         <v>1</v>
       </c>
+      <c r="AH184" t="n">
+        <v>1</v>
+      </c>
       <c r="AI184" t="n">
         <v>1</v>
       </c>
@@ -13510,6 +14041,9 @@
       <c r="AG185" t="n">
         <v>1</v>
       </c>
+      <c r="AH185" t="n">
+        <v>1</v>
+      </c>
       <c r="AI185" t="n">
         <v>1</v>
       </c>
@@ -13581,6 +14115,9 @@
       <c r="AG186" t="n">
         <v>1</v>
       </c>
+      <c r="AH186" t="n">
+        <v>1</v>
+      </c>
       <c r="AI186" t="n">
         <v>1</v>
       </c>
@@ -13652,6 +14189,9 @@
       <c r="AG187" t="n">
         <v>1</v>
       </c>
+      <c r="AH187" t="n">
+        <v>1</v>
+      </c>
       <c r="AI187" t="n">
         <v>1</v>
       </c>
@@ -13723,6 +14263,9 @@
       <c r="AG188" t="n">
         <v>1</v>
       </c>
+      <c r="AH188" t="n">
+        <v>1</v>
+      </c>
       <c r="AI188" t="n">
         <v>1</v>
       </c>
@@ -13794,6 +14337,9 @@
       <c r="AG189" t="n">
         <v>1</v>
       </c>
+      <c r="AH189" t="n">
+        <v>1</v>
+      </c>
       <c r="AI189" t="n">
         <v>1</v>
       </c>
@@ -13865,6 +14411,9 @@
       <c r="AG190" t="n">
         <v>1</v>
       </c>
+      <c r="AH190" t="n">
+        <v>1</v>
+      </c>
       <c r="AI190" t="n">
         <v>1</v>
       </c>
@@ -13936,6 +14485,9 @@
       <c r="AG191" t="n">
         <v>1</v>
       </c>
+      <c r="AH191" t="n">
+        <v>1</v>
+      </c>
       <c r="AI191" t="n">
         <v>1</v>
       </c>
@@ -14007,6 +14559,9 @@
       <c r="AG192" t="n">
         <v>1</v>
       </c>
+      <c r="AH192" t="n">
+        <v>1</v>
+      </c>
       <c r="AI192" t="n">
         <v>1</v>
       </c>
@@ -14078,6 +14633,9 @@
       <c r="AG193" t="n">
         <v>1</v>
       </c>
+      <c r="AH193" t="n">
+        <v>1</v>
+      </c>
       <c r="AI193" t="n">
         <v>1</v>
       </c>
@@ -14149,6 +14707,9 @@
       <c r="AG194" t="n">
         <v>1</v>
       </c>
+      <c r="AH194" t="n">
+        <v>1</v>
+      </c>
       <c r="AI194" t="n">
         <v>1</v>
       </c>
@@ -14220,6 +14781,9 @@
       <c r="AG195" t="n">
         <v>1</v>
       </c>
+      <c r="AH195" t="n">
+        <v>1</v>
+      </c>
       <c r="AI195" t="n">
         <v>1</v>
       </c>
@@ -14291,6 +14855,9 @@
       <c r="AG196" t="n">
         <v>1</v>
       </c>
+      <c r="AH196" t="n">
+        <v>1</v>
+      </c>
       <c r="AI196" t="n">
         <v>1</v>
       </c>
@@ -14362,6 +14929,9 @@
       <c r="AG197" t="n">
         <v>1</v>
       </c>
+      <c r="AH197" t="n">
+        <v>1</v>
+      </c>
       <c r="AI197" t="n">
         <v>1</v>
       </c>
@@ -14433,6 +15003,9 @@
       <c r="AG198" t="n">
         <v>1</v>
       </c>
+      <c r="AH198" t="n">
+        <v>1</v>
+      </c>
       <c r="AI198" t="n">
         <v>1</v>
       </c>
@@ -14504,6 +15077,9 @@
       <c r="AG199" t="n">
         <v>1</v>
       </c>
+      <c r="AH199" t="n">
+        <v>1</v>
+      </c>
       <c r="AI199" t="n">
         <v>1</v>
       </c>
@@ -14575,6 +15151,9 @@
       <c r="AG200" t="n">
         <v>1</v>
       </c>
+      <c r="AH200" t="n">
+        <v>1</v>
+      </c>
       <c r="AI200" t="n">
         <v>1</v>
       </c>
@@ -14646,6 +15225,9 @@
       <c r="AG201" t="n">
         <v>1</v>
       </c>
+      <c r="AH201" t="n">
+        <v>1</v>
+      </c>
       <c r="AI201" t="n">
         <v>1</v>
       </c>
@@ -14717,6 +15299,9 @@
       <c r="AG202" t="n">
         <v>1</v>
       </c>
+      <c r="AH202" t="n">
+        <v>1</v>
+      </c>
       <c r="AI202" t="n">
         <v>1</v>
       </c>
@@ -14788,6 +15373,9 @@
       <c r="AG203" t="n">
         <v>1</v>
       </c>
+      <c r="AH203" t="n">
+        <v>1</v>
+      </c>
       <c r="AI203" t="n">
         <v>1</v>
       </c>
@@ -14859,6 +15447,9 @@
       <c r="AG204" t="n">
         <v>1</v>
       </c>
+      <c r="AH204" t="n">
+        <v>1</v>
+      </c>
       <c r="AI204" t="n">
         <v>1</v>
       </c>
@@ -14930,6 +15521,9 @@
       <c r="AG205" t="n">
         <v>1</v>
       </c>
+      <c r="AH205" t="n">
+        <v>1</v>
+      </c>
       <c r="AI205" t="n">
         <v>1</v>
       </c>
@@ -15001,6 +15595,9 @@
       <c r="AG206" t="n">
         <v>1</v>
       </c>
+      <c r="AH206" t="n">
+        <v>1</v>
+      </c>
       <c r="AI206" t="n">
         <v>1</v>
       </c>
@@ -15070,6 +15667,9 @@
         <v>1</v>
       </c>
       <c r="AG207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH207" t="n">
         <v>1</v>
       </c>
       <c r="AI207" t="n">
@@ -15176,6 +15776,9 @@
       <c r="AG212" t="n">
         <v>0.955125</v>
       </c>
+      <c r="AH212" t="n">
+        <v>0.9444555555555557</v>
+      </c>
       <c r="AI212" t="n">
         <v>0.9532299999999999</v>
       </c>
@@ -15256,6 +15859,9 @@
       <c r="AG213" t="n">
         <v>0.9441285714285714</v>
       </c>
+      <c r="AH213" t="n">
+        <v>0.9454500000000001</v>
+      </c>
       <c r="AI213" t="n">
         <v>0.9537142857142858</v>
       </c>
@@ -15336,6 +15942,9 @@
       <c r="AG214" t="n">
         <v>0.9409599999999999</v>
       </c>
+      <c r="AH214" t="n">
+        <v>0.9219555555555554</v>
+      </c>
       <c r="AI214" t="n">
         <v>0.9496249999999999</v>
       </c>
@@ -15416,6 +16025,9 @@
       <c r="AG215" t="n">
         <v>0.8693</v>
       </c>
+      <c r="AH215" t="n">
+        <v>0.825</v>
+      </c>
       <c r="AI215" t="n">
         <v>0.71899</v>
       </c>
@@ -15496,6 +16108,9 @@
       <c r="AG216" t="n">
         <v>0.7681833333333334</v>
       </c>
+      <c r="AH216" t="n">
+        <v>0.8714454545454544</v>
+      </c>
       <c r="AI216" t="n">
         <v>0.7120200000000001</v>
       </c>
@@ -15576,6 +16191,9 @@
       <c r="AG217" t="n">
         <v>0.8476100000000001</v>
       </c>
+      <c r="AH217" t="n">
+        <v>0.76684</v>
+      </c>
       <c r="AI217" t="n">
         <v>0.76971</v>
       </c>
@@ -15656,6 +16274,9 @@
       <c r="AG218" t="n">
         <v>0.8501666666666666</v>
       </c>
+      <c r="AH218" t="n">
+        <v>0.8747374999999999</v>
+      </c>
       <c r="AI218" t="n">
         <v>0.7489899999999999</v>
       </c>
@@ -15736,6 +16357,9 @@
       <c r="AG219" t="n">
         <v>0.7333875000000001</v>
       </c>
+      <c r="AH219" t="n">
+        <v>0.9117454545454545</v>
+      </c>
       <c r="AI219" t="n">
         <v>0.6724923076923077</v>
       </c>
@@ -15816,6 +16440,9 @@
       <c r="AG220" t="n">
         <v>0.7582</v>
       </c>
+      <c r="AH220" t="n">
+        <v>0.9240499999999999</v>
+      </c>
       <c r="AI220" t="n">
         <v>0.7551099999999999</v>
       </c>
@@ -15896,6 +16523,9 @@
       <c r="AG221" t="n">
         <v>0.8130875</v>
       </c>
+      <c r="AH221" t="n">
+        <v>0.8117111111111112</v>
+      </c>
       <c r="AI221" t="n">
         <v>0.7041166666666666</v>
       </c>
@@ -15964,6 +16594,9 @@
       <c r="AG222" t="n">
         <v>0.7564111111111111</v>
       </c>
+      <c r="AH222" t="n">
+        <v>0.8307363636363636</v>
+      </c>
       <c r="AI222" t="n">
         <v>0.7263400000000001</v>
       </c>
@@ -16035,6 +16668,9 @@
       <c r="AG223" t="n">
         <v>0.8121625</v>
       </c>
+      <c r="AH223" t="n">
+        <v>0.8277428571428571</v>
+      </c>
       <c r="AI223" t="n">
         <v>0.6934083333333335</v>
       </c>
@@ -16106,6 +16742,9 @@
       <c r="AG224" t="n">
         <v>0.6998090909090908</v>
       </c>
+      <c r="AH224" t="n">
+        <v>0.90535</v>
+      </c>
       <c r="AI224" t="n">
         <v>0.7491555555555556</v>
       </c>
@@ -16177,6 +16816,9 @@
       <c r="AG225" t="n">
         <v>0.6655888888888889</v>
       </c>
+      <c r="AH225" t="n">
+        <v>0.8235499999999999</v>
+      </c>
       <c r="AI225" t="n">
         <v>0.6531454545454546</v>
       </c>
@@ -16248,6 +16890,9 @@
       <c r="AG226" t="n">
         <v>0.8338666666666668</v>
       </c>
+      <c r="AH226" t="n">
+        <v>0.8165222222222221</v>
+      </c>
       <c r="AI226" t="n">
         <v>0.7161000000000001</v>
       </c>
@@ -16319,6 +16964,9 @@
       <c r="AG227" t="n">
         <v>0.5132874999999999</v>
       </c>
+      <c r="AH227" t="n">
+        <v>0.7955699999999999</v>
+      </c>
       <c r="AI227" t="n">
         <v>0.7423083333333333</v>
       </c>
@@ -16390,6 +17038,9 @@
       <c r="AG228" t="n">
         <v>0.5997</v>
       </c>
+      <c r="AH228" t="n">
+        <v>0.8126909090909091</v>
+      </c>
       <c r="AI228" t="n">
         <v>0.6454500000000001</v>
       </c>
@@ -16461,6 +17112,9 @@
       <c r="AG229" t="n">
         <v>0.7098166666666668</v>
       </c>
+      <c r="AH229" t="n">
+        <v>0.7168888888888889</v>
+      </c>
       <c r="AI229" t="n">
         <v>0.7297714285714287</v>
       </c>
@@ -16532,6 +17186,9 @@
       <c r="AG230" t="n">
         <v>0.5988222222222221</v>
       </c>
+      <c r="AH230" t="n">
+        <v>0.7331444444444445</v>
+      </c>
       <c r="AI230" t="n">
         <v>0.8171799999999999</v>
       </c>
@@ -16603,6 +17260,9 @@
       <c r="AG231" t="n">
         <v>0.5894111111111111</v>
       </c>
+      <c r="AH231" t="n">
+        <v>0.8160699999999999</v>
+      </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="8">
       <c r="A232" s="5" t="n">
@@ -16671,6 +17331,9 @@
       <c r="AG232" t="n">
         <v>0.5751625</v>
       </c>
+      <c r="AH232" t="n">
+        <v>0.8341222222222222</v>
+      </c>
       <c r="AI232" t="n">
         <v>0.7732916666666667</v>
       </c>
@@ -16742,6 +17405,9 @@
       <c r="AG233" t="n">
         <v>0.7272222222222222</v>
       </c>
+      <c r="AH233" t="n">
+        <v>0.6517714285714286</v>
+      </c>
       <c r="AI233" t="n">
         <v>0.7760583333333333</v>
       </c>
@@ -16813,6 +17479,9 @@
       <c r="AG234" t="n">
         <v>0.4850909090909091</v>
       </c>
+      <c r="AH234" t="n">
+        <v>0.6071916666666667</v>
+      </c>
       <c r="AI234" t="n">
         <v>0.7528833333333335</v>
       </c>
@@ -16884,6 +17553,9 @@
       <c r="AG235" t="n">
         <v>0.4899125</v>
       </c>
+      <c r="AH235" t="n">
+        <v>0.7896</v>
+      </c>
       <c r="AI235" t="n">
         <v>0.6315538461538461</v>
       </c>
@@ -16955,6 +17627,9 @@
       <c r="AG236" t="n">
         <v>0.4749666666666666</v>
       </c>
+      <c r="AH236" t="n">
+        <v>0.760325</v>
+      </c>
       <c r="AI236" t="n">
         <v>0.6624500000000001</v>
       </c>
@@ -17026,6 +17701,9 @@
       <c r="AG237" t="n">
         <v>0.58648</v>
       </c>
+      <c r="AH237" t="n">
+        <v>0.6512600000000002</v>
+      </c>
       <c r="AI237" t="n">
         <v>0.751525</v>
       </c>
@@ -17097,6 +17775,9 @@
       <c r="AG238" t="n">
         <v>0.5892000000000001</v>
       </c>
+      <c r="AH238" t="n">
+        <v>0.8279727272727272</v>
+      </c>
       <c r="AI238" t="n">
         <v>0.652825</v>
       </c>
@@ -17168,6 +17849,9 @@
       <c r="AG239" t="n">
         <v>0.7491499999999999</v>
       </c>
+      <c r="AH239" t="n">
+        <v>0.6429555555555556</v>
+      </c>
       <c r="AI239" t="n">
         <v>0.8661999999999999</v>
       </c>
@@ -17239,6 +17923,9 @@
       <c r="AG240" t="n">
         <v>0.5813714285714287</v>
       </c>
+      <c r="AH240" t="n">
+        <v>0.6098916666666667</v>
+      </c>
       <c r="AI240" t="n">
         <v>0.7905111111111112</v>
       </c>
@@ -17310,6 +17997,9 @@
       <c r="AG241" t="n">
         <v>0.7499399999999999</v>
       </c>
+      <c r="AH241" t="n">
+        <v>0.7305727272727274</v>
+      </c>
       <c r="AI241" t="n">
         <v>0.7470818181818182</v>
       </c>
@@ -17381,6 +18071,9 @@
       <c r="AG242" t="n">
         <v>0.6617250000000001</v>
       </c>
+      <c r="AH242" t="n">
+        <v>0.7224999999999999</v>
+      </c>
       <c r="AI242" t="n">
         <v>0.5965727272727274</v>
       </c>
@@ -17452,6 +18145,9 @@
       <c r="AG243" t="n">
         <v>0.7671</v>
       </c>
+      <c r="AH243" t="n">
+        <v>0.6183333333333334</v>
+      </c>
       <c r="AI243" t="n">
         <v>0.7137785714285714</v>
       </c>
@@ -17520,6 +18216,9 @@
       <c r="AG244" t="n">
         <v>0.6970500000000001</v>
       </c>
+      <c r="AH244" t="n">
+        <v>0.7500916666666667</v>
+      </c>
       <c r="AI244" t="n">
         <v>0.7739833333333334</v>
       </c>
@@ -17591,6 +18290,9 @@
       <c r="AG245" t="n">
         <v>0.5966222222222223</v>
       </c>
+      <c r="AH245" t="n">
+        <v>0.7988111111111112</v>
+      </c>
       <c r="AI245" t="n">
         <v>0.654</v>
       </c>
@@ -17662,6 +18364,9 @@
       <c r="AG246" t="n">
         <v>0.6594750000000001</v>
       </c>
+      <c r="AH246" t="n">
+        <v>0.7220333333333333</v>
+      </c>
       <c r="AI246" t="n">
         <v>0.551011111111111</v>
       </c>
@@ -17730,6 +18435,9 @@
       <c r="AG247" t="n">
         <v>0.5673</v>
       </c>
+      <c r="AH247" t="n">
+        <v>0.6818636363636363</v>
+      </c>
       <c r="AI247" t="n">
         <v>0.5978249999999999</v>
       </c>
@@ -17801,6 +18509,9 @@
       <c r="AG248" t="n">
         <v>0.8148</v>
       </c>
+      <c r="AH248" t="n">
+        <v>0.6484800000000001</v>
+      </c>
       <c r="AI248" t="n">
         <v>0.7105615384615382</v>
       </c>
@@ -17872,6 +18583,9 @@
       <c r="AG249" t="n">
         <v>0.7287000000000001</v>
       </c>
+      <c r="AH249" t="n">
+        <v>0.6788500000000001</v>
+      </c>
       <c r="AI249" t="n">
         <v>0.6842090909090909</v>
       </c>
@@ -17943,6 +18657,9 @@
       <c r="AG250" t="n">
         <v>0.5727571428571429</v>
       </c>
+      <c r="AH250" t="n">
+        <v>0.6896833333333333</v>
+      </c>
       <c r="AI250" t="n">
         <v>0.6877636363636364</v>
       </c>
@@ -18014,6 +18731,9 @@
       <c r="AG251" t="n">
         <v>0.6977142857142857</v>
       </c>
+      <c r="AH251" t="n">
+        <v>0.5914272727272727</v>
+      </c>
       <c r="AI251" t="n">
         <v>0.7553833333333334</v>
       </c>
@@ -18085,6 +18805,9 @@
       <c r="AG252" t="n">
         <v>0.6966875</v>
       </c>
+      <c r="AH252" t="n">
+        <v>0.6572249999999999</v>
+      </c>
       <c r="AI252" t="n">
         <v>0.7040461538461538</v>
       </c>
@@ -18156,6 +18879,9 @@
       <c r="AG253" t="n">
         <v>0.5240571428571429</v>
       </c>
+      <c r="AH253" t="n">
+        <v>0.801011111111111</v>
+      </c>
       <c r="AI253" t="n">
         <v>0.5232083333333333</v>
       </c>
@@ -18227,6 +18953,9 @@
       <c r="AG254" t="n">
         <v>0.6985874999999999</v>
       </c>
+      <c r="AH254" t="n">
+        <v>0.6367444444444446</v>
+      </c>
       <c r="AI254" t="n">
         <v>0.7925636363636365</v>
       </c>
@@ -18298,6 +19027,9 @@
       <c r="AG255" t="n">
         <v>0.6282</v>
       </c>
+      <c r="AH255" t="n">
+        <v>0.8117909090909093</v>
+      </c>
       <c r="AI255" t="n">
         <v>0.6208083333333333</v>
       </c>
@@ -18369,6 +19101,9 @@
       <c r="AG256" t="n">
         <v>0.6270749999999999</v>
       </c>
+      <c r="AH256" t="n">
+        <v>0.7343083333333332</v>
+      </c>
       <c r="AI256" t="n">
         <v>0.7818818181818181</v>
       </c>
@@ -18440,6 +19175,9 @@
       <c r="AG257" t="n">
         <v>0.5711000000000001</v>
       </c>
+      <c r="AH257" t="n">
+        <v>0.6896000000000001</v>
+      </c>
     </row>
     <row r="258" ht="16" customHeight="1" s="8">
       <c r="A258" s="5" t="n">
@@ -18508,6 +19246,9 @@
       <c r="AG258" t="n">
         <v>0.70428</v>
       </c>
+      <c r="AH258" t="n">
+        <v>0.7345818181818182</v>
+      </c>
       <c r="AI258" t="n">
         <v>0.8083272727272728</v>
       </c>
@@ -18579,6 +19320,9 @@
       <c r="AG259" t="n">
         <v>0.58897</v>
       </c>
+      <c r="AH259" t="n">
+        <v>0.715809090909091</v>
+      </c>
       <c r="AI259" t="n">
         <v>0.7523076923076922</v>
       </c>
@@ -18650,6 +19394,9 @@
       <c r="AG260" t="n">
         <v>0.6454</v>
       </c>
+      <c r="AH260" t="n">
+        <v>0.7738699999999999</v>
+      </c>
       <c r="AI260" t="n">
         <v>0.866390909090909</v>
       </c>
@@ -18721,6 +19468,9 @@
       <c r="AG261" t="n">
         <v>0.6931181818181816</v>
       </c>
+      <c r="AH261" t="n">
+        <v>0.7773</v>
+      </c>
       <c r="AI261" t="n">
         <v>0.732525</v>
       </c>
@@ -18792,6 +19542,9 @@
       <c r="AG262" t="n">
         <v>0.6600200000000001</v>
       </c>
+      <c r="AH262" t="n">
+        <v>0.592575</v>
+      </c>
       <c r="AI262" t="n">
         <v>0.8668090909090908</v>
       </c>
@@ -18863,6 +19616,9 @@
       <c r="AG263" t="n">
         <v>0.4840125</v>
       </c>
+      <c r="AH263" t="n">
+        <v>0.8530900000000001</v>
+      </c>
       <c r="AI263" t="n">
         <v>0.6957999999999999</v>
       </c>
@@ -18934,6 +19690,9 @@
       <c r="AG264" t="n">
         <v>0.6907166666666668</v>
       </c>
+      <c r="AH264" t="n">
+        <v>0.6594555555555556</v>
+      </c>
       <c r="AI264" t="n">
         <v>0.7173818181818181</v>
       </c>
@@ -19005,6 +19764,9 @@
       <c r="AG265" t="n">
         <v>0.5547285714285713</v>
       </c>
+      <c r="AH265" t="n">
+        <v>0.72148</v>
+      </c>
       <c r="AI265" t="n">
         <v>0.6610461538461537</v>
       </c>
@@ -19076,6 +19838,9 @@
       <c r="AG266" t="n">
         <v>0.56168</v>
       </c>
+      <c r="AH266" t="n">
+        <v>0.6518571428571428</v>
+      </c>
       <c r="AI266" t="n">
         <v>0.6746272727272727</v>
       </c>
@@ -19147,6 +19912,9 @@
       <c r="AG267" t="n">
         <v>0.502</v>
       </c>
+      <c r="AH267" t="n">
+        <v>0.7375999999999999</v>
+      </c>
       <c r="AI267" t="n">
         <v>0.9139363636363637</v>
       </c>
@@ -19218,6 +19986,9 @@
       <c r="AG268" t="n">
         <v>0.58985</v>
       </c>
+      <c r="AH268" t="n">
+        <v>0.6406857142857144</v>
+      </c>
       <c r="AI268" t="n">
         <v>0.67318</v>
       </c>
@@ -19289,6 +20060,9 @@
       <c r="AG269" t="n">
         <v>0.5053444444444444</v>
       </c>
+      <c r="AH269" t="n">
+        <v>0.6367333333333334</v>
+      </c>
       <c r="AI269" t="n">
         <v>0.7978499999999999</v>
       </c>
@@ -19360,6 +20134,9 @@
       <c r="AG270" t="n">
         <v>0.5276777777777778</v>
       </c>
+      <c r="AH270" t="n">
+        <v>0.5206142857142856</v>
+      </c>
       <c r="AI270" t="n">
         <v>0.6577642857142856</v>
       </c>
@@ -19431,6 +20208,9 @@
       <c r="AG271" t="n">
         <v>0.6467222222222222</v>
       </c>
+      <c r="AH271" t="n">
+        <v>0.6225888888888889</v>
+      </c>
       <c r="AI271" t="n">
         <v>0.7966727272727273</v>
       </c>
@@ -19502,6 +20282,9 @@
       <c r="AG272" t="n">
         <v>0.5596666666666668</v>
       </c>
+      <c r="AH272" t="n">
+        <v>0.6169384615384617</v>
+      </c>
       <c r="AI272" t="n">
         <v>0.7604692307692307</v>
       </c>
@@ -19573,6 +20356,9 @@
       <c r="AG273" t="n">
         <v>0.4824888888888889</v>
       </c>
+      <c r="AH273" t="n">
+        <v>0.7008875000000001</v>
+      </c>
       <c r="AI273" t="n">
         <v>0.6132111111111112</v>
       </c>
@@ -19644,6 +20430,9 @@
       <c r="AG274" t="n">
         <v>0.6259555555555556</v>
       </c>
+      <c r="AH274" t="n">
+        <v>0.7708625</v>
+      </c>
       <c r="AI274" t="n">
         <v>0.7624749999999999</v>
       </c>
@@ -19715,6 +20504,9 @@
       <c r="AG275" t="n">
         <v>0.6092875</v>
       </c>
+      <c r="AH275" t="n">
+        <v>0.63719</v>
+      </c>
       <c r="AI275" t="n">
         <v>0.7679000000000001</v>
       </c>
@@ -19786,6 +20578,9 @@
       <c r="AG276" t="n">
         <v>0.6101555555555556</v>
       </c>
+      <c r="AH276" t="n">
+        <v>0.6113625</v>
+      </c>
       <c r="AI276" t="n">
         <v>0.6080375000000001</v>
       </c>
@@ -19857,6 +20652,9 @@
       <c r="AG277" t="n">
         <v>0.6498857142857143</v>
       </c>
+      <c r="AH277" t="n">
+        <v>0.7692444444444444</v>
+      </c>
       <c r="AI277" t="n">
         <v>0.6941900000000001</v>
       </c>
@@ -19926,7 +20724,10 @@
         <v>0.6131500000000001</v>
       </c>
       <c r="AG278" t="n">
-        <v>0.6383181818181819</v>
+        <v>0.509125</v>
+      </c>
+      <c r="AH278" t="n">
+        <v>0.5251777777777779</v>
       </c>
       <c r="AI278" t="n">
         <v>0.5813875000000001</v>
@@ -19997,7 +20798,10 @@
         <v>0.784</v>
       </c>
       <c r="AG279" t="n">
-        <v>0.479425</v>
+        <v>0.7049666666666667</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>0.80449</v>
       </c>
       <c r="AI279" t="n">
         <v>0.701675</v>
@@ -20070,6 +20874,9 @@
       <c r="AG280" t="n">
         <v>0.7653125000000001</v>
       </c>
+      <c r="AH280" t="n">
+        <v>0.6073750000000001</v>
+      </c>
       <c r="AI280" t="n">
         <v>0.7212833333333334</v>
       </c>
@@ -20141,6 +20948,9 @@
       <c r="AG281" t="n">
         <v>0.6362000000000001</v>
       </c>
+      <c r="AH281" t="n">
+        <v>0.666525</v>
+      </c>
       <c r="AI281" t="n">
         <v>0.6912166666666667</v>
       </c>
@@ -20212,6 +21022,9 @@
       <c r="AG282" t="n">
         <v>0.6117833333333333</v>
       </c>
+      <c r="AH282" t="n">
+        <v>0.6465818181818181</v>
+      </c>
       <c r="AI282" t="n">
         <v>0.7964818181818182</v>
       </c>
@@ -20283,6 +21096,9 @@
       <c r="AG283" t="n">
         <v>0.6411428571428572</v>
       </c>
+      <c r="AH283" t="n">
+        <v>0.6680333333333334</v>
+      </c>
       <c r="AI283" t="n">
         <v>0.6120642857142856</v>
       </c>
@@ -20354,6 +21170,9 @@
       <c r="AG284" t="n">
         <v>0.6673428571428571</v>
       </c>
+      <c r="AH284" t="n">
+        <v>0.7922199999999999</v>
+      </c>
       <c r="AI284" t="n">
         <v>0.7942444444444444</v>
       </c>
@@ -20422,6 +21241,9 @@
       <c r="AG285" t="n">
         <v>0.7033700000000001</v>
       </c>
+      <c r="AH285" t="n">
+        <v>0.8504909090909091</v>
+      </c>
       <c r="AI285" t="n">
         <v>0.6682333333333333</v>
       </c>
@@ -20493,6 +21315,9 @@
       <c r="AG286" t="n">
         <v>0.5954777777777778</v>
       </c>
+      <c r="AH286" t="n">
+        <v>0.6757444444444445</v>
+      </c>
       <c r="AI286" t="n">
         <v>0.557975</v>
       </c>
@@ -20564,6 +21389,9 @@
       <c r="AG287" t="n">
         <v>0.8079499999999999</v>
       </c>
+      <c r="AH287" t="n">
+        <v>0.6121555555555556</v>
+      </c>
       <c r="AI287" t="n">
         <v>0.6525166666666666</v>
       </c>
@@ -20635,6 +21463,9 @@
       <c r="AG288" t="n">
         <v>0.6327363636363635</v>
       </c>
+      <c r="AH288" t="n">
+        <v>0.8393875000000001</v>
+      </c>
       <c r="AI288" t="n">
         <v>0.7697272727272728</v>
       </c>
@@ -20706,6 +21537,9 @@
       <c r="AG289" t="n">
         <v>0.7100363636363637</v>
       </c>
+      <c r="AH289" t="n">
+        <v>0.58272</v>
+      </c>
       <c r="AI289" t="n">
         <v>0.7886666666666667</v>
       </c>
@@ -20777,6 +21611,9 @@
       <c r="AG290" t="n">
         <v>0.6602500000000001</v>
       </c>
+      <c r="AH290" t="n">
+        <v>0.7600727272727273</v>
+      </c>
       <c r="AI290" t="n">
         <v>0.6970333333333334</v>
       </c>
@@ -20848,6 +21685,9 @@
       <c r="AG291" t="n">
         <v>0.7329777777777778</v>
       </c>
+      <c r="AH291" t="n">
+        <v>0.69635</v>
+      </c>
       <c r="AI291" t="n">
         <v>0.74704</v>
       </c>
@@ -20919,6 +21759,9 @@
       <c r="AG292" t="n">
         <v>0.5553375</v>
       </c>
+      <c r="AH292" t="n">
+        <v>0.75748</v>
+      </c>
       <c r="AI292" t="n">
         <v>0.6335333333333334</v>
       </c>
@@ -20990,6 +21833,9 @@
       <c r="AG293" t="n">
         <v>0.4731625</v>
       </c>
+      <c r="AH293" t="n">
+        <v>0.5494</v>
+      </c>
       <c r="AI293" t="n">
         <v>0.717190909090909</v>
       </c>
@@ -21061,6 +21907,9 @@
       <c r="AG294" t="n">
         <v>0.5788099999999999</v>
       </c>
+      <c r="AH294" t="n">
+        <v>0.6747875</v>
+      </c>
       <c r="AI294" t="n">
         <v>0.6918</v>
       </c>
@@ -21132,6 +21981,9 @@
       <c r="AG295" t="n">
         <v>0.6827545454545454</v>
       </c>
+      <c r="AH295" t="n">
+        <v>0.7490999999999999</v>
+      </c>
       <c r="AI295" t="n">
         <v>0.6006166666666667</v>
       </c>
@@ -21203,6 +22055,9 @@
       <c r="AG296" t="n">
         <v>0.5544400000000002</v>
       </c>
+      <c r="AH296" t="n">
+        <v>0.7139</v>
+      </c>
       <c r="AI296" t="n">
         <v>0.6607090909090909</v>
       </c>
@@ -21274,6 +22129,9 @@
       <c r="AG297" t="n">
         <v>0.5004222222222222</v>
       </c>
+      <c r="AH297" t="n">
+        <v>0.3509875</v>
+      </c>
       <c r="AI297" t="n">
         <v>0.6926916666666666</v>
       </c>
@@ -21345,6 +22203,9 @@
       <c r="AG298" t="n">
         <v>0.6577888888888889</v>
       </c>
+      <c r="AH298" t="n">
+        <v>0.6662625</v>
+      </c>
       <c r="AI298" t="n">
         <v>0.7512545454545454</v>
       </c>
@@ -21416,6 +22277,9 @@
       <c r="AG299" t="n">
         <v>0.5005727272727273</v>
       </c>
+      <c r="AH299" t="n">
+        <v>0.78474</v>
+      </c>
       <c r="AI299" t="n">
         <v>0.79486</v>
       </c>
@@ -21487,6 +22351,9 @@
       <c r="AG300" t="n">
         <v>0.4616125</v>
       </c>
+      <c r="AH300" t="n">
+        <v>0.4238400000000001</v>
+      </c>
       <c r="AI300" t="n">
         <v>0.6619250000000001</v>
       </c>
@@ -21558,6 +22425,9 @@
       <c r="AG301" t="n">
         <v>0.548025</v>
       </c>
+      <c r="AH301" t="n">
+        <v>0.691975</v>
+      </c>
       <c r="AI301" t="n">
         <v>0.6759833333333333</v>
       </c>
@@ -21629,6 +22499,9 @@
       <c r="AG302" t="n">
         <v>0.7055666666666668</v>
       </c>
+      <c r="AH302" t="n">
+        <v>0.6433785714285715</v>
+      </c>
       <c r="AI302" t="n">
         <v>0.8137363636363637</v>
       </c>
@@ -21700,6 +22573,9 @@
       <c r="AG303" t="n">
         <v>0.7041666666666667</v>
       </c>
+      <c r="AH303" t="n">
+        <v>0.7767666666666666</v>
+      </c>
       <c r="AI303" t="n">
         <v>0.6278818181818181</v>
       </c>
@@ -21771,6 +22647,9 @@
       <c r="AG304" t="n">
         <v>0.6187666666666667</v>
       </c>
+      <c r="AH304" t="n">
+        <v>0.6414272727272727</v>
+      </c>
       <c r="AI304" t="n">
         <v>0.6649999999999999</v>
       </c>
@@ -21842,6 +22721,9 @@
       <c r="AG305" t="n">
         <v>0.5088625</v>
       </c>
+      <c r="AH305" t="n">
+        <v>0.75671</v>
+      </c>
       <c r="AI305" t="n">
         <v>0.7369615384615383</v>
       </c>
@@ -21913,6 +22795,9 @@
       <c r="AG306" t="n">
         <v>0.6848909090909091</v>
       </c>
+      <c r="AH306" t="n">
+        <v>0.7481833333333334</v>
+      </c>
       <c r="AI306" t="n">
         <v>0.5822999999999999</v>
       </c>
@@ -21984,6 +22869,9 @@
       <c r="AG307" t="n">
         <v>0.6076777777777778</v>
       </c>
+      <c r="AH307" t="n">
+        <v>0.586690909090909</v>
+      </c>
       <c r="AI307" t="n">
         <v>0.6626199999999999</v>
       </c>
@@ -22055,6 +22943,9 @@
       <c r="AG308" t="n">
         <v>0.6058285714285715</v>
       </c>
+      <c r="AH308" t="n">
+        <v>0.5873666666666667</v>
+      </c>
       <c r="AI308" t="n">
         <v>0.6873090909090909</v>
       </c>
@@ -22126,6 +23017,9 @@
       <c r="AG309" t="n">
         <v>0.6448333333333333</v>
       </c>
+      <c r="AH309" t="n">
+        <v>0.5850636363636363</v>
+      </c>
       <c r="AI309" t="n">
         <v>0.7913444444444444</v>
       </c>
@@ -22197,6 +23091,9 @@
       <c r="AG310" t="n">
         <v>0.67424</v>
       </c>
+      <c r="AH310" t="n">
+        <v>0.6983416666666667</v>
+      </c>
       <c r="AI310" t="n">
         <v>0.8221999999999999</v>
       </c>
@@ -22267,6 +23164,9 @@
       </c>
       <c r="AG311" t="n">
         <v>0.5765636363636364</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>0.7975909090909091</v>
       </c>
       <c r="AI311" t="n">
         <v>0.7314700000000001</v>
@@ -22372,6 +23272,9 @@
       <c r="AG316" t="n">
         <v>0.0001</v>
       </c>
+      <c r="AH316" t="n">
+        <v>0</v>
+      </c>
       <c r="AI316" t="n">
         <v>0.0003</v>
       </c>
@@ -22452,6 +23355,9 @@
       <c r="AG317" t="n">
         <v>0.0011</v>
       </c>
+      <c r="AH317" t="n">
+        <v>0.0022</v>
+      </c>
       <c r="AI317" t="n">
         <v>0.0003</v>
       </c>
@@ -22532,6 +23438,9 @@
       <c r="AG318" t="n">
         <v>0.008999999999999999</v>
       </c>
+      <c r="AH318" t="n">
+        <v>0.09470000000000001</v>
+      </c>
       <c r="AI318" t="n">
         <v>0.0005</v>
       </c>
@@ -22612,6 +23521,9 @@
       <c r="AG319" t="n">
         <v>0.0327</v>
       </c>
+      <c r="AH319" t="n">
+        <v>0.0472</v>
+      </c>
       <c r="AI319" t="n">
         <v>0.0034</v>
       </c>
@@ -22692,6 +23604,9 @@
       <c r="AG320" t="n">
         <v>0.0883</v>
       </c>
+      <c r="AH320" t="n">
+        <v>0.032</v>
+      </c>
       <c r="AI320" t="n">
         <v>0.0159</v>
       </c>
@@ -22772,6 +23687,9 @@
       <c r="AG321" t="n">
         <v>0.029</v>
       </c>
+      <c r="AH321" t="n">
+        <v>0.0541</v>
+      </c>
       <c r="AI321" t="n">
         <v>0.0357</v>
       </c>
@@ -22852,6 +23770,9 @@
       <c r="AG322" t="n">
         <v>0.0738</v>
       </c>
+      <c r="AH322" t="n">
+        <v>0.0992</v>
+      </c>
       <c r="AI322" t="n">
         <v>0.0247</v>
       </c>
@@ -22932,6 +23853,9 @@
       <c r="AG323" t="n">
         <v>0.0521</v>
       </c>
+      <c r="AH323" t="n">
+        <v>0.1524</v>
+      </c>
       <c r="AI323" t="n">
         <v>0</v>
       </c>
@@ -23012,6 +23936,9 @@
       <c r="AG324" t="n">
         <v>0.0775</v>
       </c>
+      <c r="AH324" t="n">
+        <v>0.0772</v>
+      </c>
       <c r="AI324" t="n">
         <v>0.0677</v>
       </c>
@@ -23092,6 +24019,9 @@
       <c r="AG325" t="n">
         <v>0.07779999999999999</v>
       </c>
+      <c r="AH325" t="n">
+        <v>0.0636</v>
+      </c>
       <c r="AI325" t="n">
         <v>0.0137</v>
       </c>
@@ -23163,6 +24093,9 @@
       <c r="AG326" t="n">
         <v>0.1193</v>
       </c>
+      <c r="AH326" t="n">
+        <v>0.048</v>
+      </c>
       <c r="AI326" t="n">
         <v>0.0101</v>
       </c>
@@ -23234,6 +24167,9 @@
       <c r="AG327" t="n">
         <v>0.0999</v>
       </c>
+      <c r="AH327" t="n">
+        <v>0.0391</v>
+      </c>
       <c r="AI327" t="n">
         <v>0.0092</v>
       </c>
@@ -23305,6 +24241,9 @@
       <c r="AG328" t="n">
         <v>0.1124</v>
       </c>
+      <c r="AH328" t="n">
+        <v>0.0984</v>
+      </c>
       <c r="AI328" t="n">
         <v>0.0363</v>
       </c>
@@ -23376,6 +24315,9 @@
       <c r="AG329" t="n">
         <v>0.1336</v>
       </c>
+      <c r="AH329" t="n">
+        <v>0.0669</v>
+      </c>
       <c r="AI329" t="n">
         <v>0.0482</v>
       </c>
@@ -23447,6 +24389,9 @@
       <c r="AG330" t="n">
         <v>0.1333</v>
       </c>
+      <c r="AH330" t="n">
+        <v>0.0591</v>
+      </c>
       <c r="AI330" t="n">
         <v>0.0463</v>
       </c>
@@ -23518,6 +24463,9 @@
       <c r="AG331" t="n">
         <v>0.123</v>
       </c>
+      <c r="AH331" t="n">
+        <v>0.0693</v>
+      </c>
       <c r="AI331" t="n">
         <v>0.0259</v>
       </c>
@@ -23589,6 +24537,9 @@
       <c r="AG332" t="n">
         <v>0.1625</v>
       </c>
+      <c r="AH332" t="n">
+        <v>0.0467</v>
+      </c>
       <c r="AI332" t="n">
         <v>0.0474</v>
       </c>
@@ -23660,6 +24611,9 @@
       <c r="AG333" t="n">
         <v>0.0973</v>
       </c>
+      <c r="AH333" t="n">
+        <v>0.0684</v>
+      </c>
       <c r="AI333" t="n">
         <v>0.0008</v>
       </c>
@@ -23731,6 +24685,9 @@
       <c r="AG334" t="n">
         <v>0.098</v>
       </c>
+      <c r="AH334" t="n">
+        <v>0.0718</v>
+      </c>
       <c r="AI334" t="n">
         <v>0.0188</v>
       </c>
@@ -23802,6 +24759,9 @@
       <c r="AG335" t="n">
         <v>0.098</v>
       </c>
+      <c r="AH335" t="n">
+        <v>0.0532</v>
+      </c>
       <c r="AI335" t="n">
         <v>0.0188</v>
       </c>
@@ -23873,6 +24833,9 @@
       <c r="AG336" t="n">
         <v>0.08699999999999999</v>
       </c>
+      <c r="AH336" t="n">
+        <v>0.0394</v>
+      </c>
       <c r="AI336" t="n">
         <v>0.0442</v>
       </c>
@@ -23944,6 +24907,9 @@
       <c r="AG337" t="n">
         <v>0.1092</v>
       </c>
+      <c r="AH337" t="n">
+        <v>0.0515</v>
+      </c>
       <c r="AI337" t="n">
         <v>0.0232</v>
       </c>
@@ -24015,6 +24981,9 @@
       <c r="AG338" t="n">
         <v>0.174</v>
       </c>
+      <c r="AH338" t="n">
+        <v>0.0469</v>
+      </c>
       <c r="AI338" t="n">
         <v>0.0334</v>
       </c>
@@ -24086,6 +25055,9 @@
       <c r="AG339" t="n">
         <v>0.1212</v>
       </c>
+      <c r="AH339" t="n">
+        <v>0.0434</v>
+      </c>
       <c r="AI339" t="n">
         <v>0.0115</v>
       </c>
@@ -24157,6 +25129,9 @@
       <c r="AG340" t="n">
         <v>0.1672</v>
       </c>
+      <c r="AH340" t="n">
+        <v>0.031</v>
+      </c>
       <c r="AI340" t="n">
         <v>0.0327</v>
       </c>
@@ -24228,6 +25203,9 @@
       <c r="AG341" t="n">
         <v>0.1078</v>
       </c>
+      <c r="AH341" t="n">
+        <v>0.0621</v>
+      </c>
       <c r="AI341" t="n">
         <v>0.0213</v>
       </c>
@@ -24299,6 +25277,9 @@
       <c r="AG342" t="n">
         <v>0.0973</v>
       </c>
+      <c r="AH342" t="n">
+        <v>0.06469999999999999</v>
+      </c>
       <c r="AI342" t="n">
         <v>0.0279</v>
       </c>
@@ -24370,6 +25351,9 @@
       <c r="AG343" t="n">
         <v>0.1529</v>
       </c>
+      <c r="AH343" t="n">
+        <v>0.0615</v>
+      </c>
       <c r="AI343" t="n">
         <v>0.0208</v>
       </c>
@@ -24441,6 +25425,9 @@
       <c r="AG344" t="n">
         <v>0.1</v>
       </c>
+      <c r="AH344" t="n">
+        <v>0.0654</v>
+      </c>
       <c r="AI344" t="n">
         <v>0.0244</v>
       </c>
@@ -24512,6 +25499,9 @@
       <c r="AG345" t="n">
         <v>0.1345</v>
       </c>
+      <c r="AH345" t="n">
+        <v>0.0574</v>
+      </c>
       <c r="AI345" t="n">
         <v>0.0138</v>
       </c>
@@ -24583,6 +25573,9 @@
       <c r="AG346" t="n">
         <v>0.1275</v>
       </c>
+      <c r="AH346" t="n">
+        <v>0.055</v>
+      </c>
       <c r="AI346" t="n">
         <v>0.0371</v>
       </c>
@@ -24654,6 +25647,9 @@
       <c r="AG347" t="n">
         <v>0.101</v>
       </c>
+      <c r="AH347" t="n">
+        <v>0.0512</v>
+      </c>
       <c r="AI347" t="n">
         <v>0.0214</v>
       </c>
@@ -24725,6 +25721,9 @@
       <c r="AG348" t="n">
         <v>0.1233</v>
       </c>
+      <c r="AH348" t="n">
+        <v>0.0588</v>
+      </c>
       <c r="AI348" t="n">
         <v>0.025</v>
       </c>
@@ -24796,6 +25795,9 @@
       <c r="AG349" t="n">
         <v>0.1487</v>
       </c>
+      <c r="AH349" t="n">
+        <v>0.0649</v>
+      </c>
       <c r="AI349" t="n">
         <v>0.03</v>
       </c>
@@ -24867,6 +25869,9 @@
       <c r="AG350" t="n">
         <v>0.1065</v>
       </c>
+      <c r="AH350" t="n">
+        <v>0.0545</v>
+      </c>
       <c r="AI350" t="n">
         <v>0.0275</v>
       </c>
@@ -24938,6 +25943,9 @@
       <c r="AG351" t="n">
         <v>0.1043</v>
       </c>
+      <c r="AH351" t="n">
+        <v>0.0556</v>
+      </c>
       <c r="AI351" t="n">
         <v>0.0177</v>
       </c>
@@ -25009,6 +26017,9 @@
       <c r="AG352" t="n">
         <v>0.113</v>
       </c>
+      <c r="AH352" t="n">
+        <v>0.0622</v>
+      </c>
       <c r="AI352" t="n">
         <v>0.0144</v>
       </c>
@@ -25080,6 +26091,9 @@
       <c r="AG353" t="n">
         <v>0.1133</v>
       </c>
+      <c r="AH353" t="n">
+        <v>0.043</v>
+      </c>
       <c r="AI353" t="n">
         <v>0.0124</v>
       </c>
@@ -25151,6 +26165,9 @@
       <c r="AG354" t="n">
         <v>0.1105</v>
       </c>
+      <c r="AH354" t="n">
+        <v>0.0466</v>
+      </c>
       <c r="AI354" t="n">
         <v>0.008500000000000001</v>
       </c>
@@ -25222,6 +26239,9 @@
       <c r="AG355" t="n">
         <v>0.1289</v>
       </c>
+      <c r="AH355" t="n">
+        <v>0.0496</v>
+      </c>
       <c r="AI355" t="n">
         <v>0.0208</v>
       </c>
@@ -25293,6 +26313,9 @@
       <c r="AG356" t="n">
         <v>0.0897</v>
       </c>
+      <c r="AH356" t="n">
+        <v>0.0484</v>
+      </c>
       <c r="AI356" t="n">
         <v>0.0249</v>
       </c>
@@ -25364,6 +26387,9 @@
       <c r="AG357" t="n">
         <v>0.1079</v>
       </c>
+      <c r="AH357" t="n">
+        <v>0.0595</v>
+      </c>
       <c r="AI357" t="n">
         <v>0.0091</v>
       </c>
@@ -25435,6 +26461,9 @@
       <c r="AG358" t="n">
         <v>0.1009</v>
       </c>
+      <c r="AH358" t="n">
+        <v>0.0467</v>
+      </c>
       <c r="AI358" t="n">
         <v>0.0264</v>
       </c>
@@ -25506,6 +26535,9 @@
       <c r="AG359" t="n">
         <v>0.1047</v>
       </c>
+      <c r="AH359" t="n">
+        <v>0.0463</v>
+      </c>
       <c r="AI359" t="n">
         <v>0.0197</v>
       </c>
@@ -25577,6 +26609,9 @@
       <c r="AG360" t="n">
         <v>0.1035</v>
       </c>
+      <c r="AH360" t="n">
+        <v>0.0488</v>
+      </c>
       <c r="AI360" t="n">
         <v>0.0134</v>
       </c>
@@ -25648,6 +26683,9 @@
       <c r="AG361" t="n">
         <v>0.115</v>
       </c>
+      <c r="AH361" t="n">
+        <v>0.0425</v>
+      </c>
       <c r="AI361" t="n">
         <v>0.0134</v>
       </c>
@@ -25719,6 +26757,9 @@
       <c r="AG362" t="n">
         <v>0.1009</v>
       </c>
+      <c r="AH362" t="n">
+        <v>0.0457</v>
+      </c>
       <c r="AI362" t="n">
         <v>0.0223</v>
       </c>
@@ -25790,6 +26831,9 @@
       <c r="AG363" t="n">
         <v>0.1013</v>
       </c>
+      <c r="AH363" t="n">
+        <v>0.0442</v>
+      </c>
       <c r="AI363" t="n">
         <v>0.027</v>
       </c>
@@ -25861,6 +26905,9 @@
       <c r="AG364" t="n">
         <v>0.0902</v>
       </c>
+      <c r="AH364" t="n">
+        <v>0.0358</v>
+      </c>
       <c r="AI364" t="n">
         <v>0.0282</v>
       </c>
@@ -25932,6 +26979,9 @@
       <c r="AG365" t="n">
         <v>0.1037</v>
       </c>
+      <c r="AH365" t="n">
+        <v>0.0504</v>
+      </c>
       <c r="AI365" t="n">
         <v>0.0246</v>
       </c>
@@ -26003,6 +27053,9 @@
       <c r="AG366" t="n">
         <v>0.1019</v>
       </c>
+      <c r="AH366" t="n">
+        <v>0.0476</v>
+      </c>
       <c r="AI366" t="n">
         <v>0.0209</v>
       </c>
@@ -26074,6 +27127,9 @@
       <c r="AG367" t="n">
         <v>0.1003</v>
       </c>
+      <c r="AH367" t="n">
+        <v>0.0566</v>
+      </c>
       <c r="AI367" t="n">
         <v>0.0181</v>
       </c>
@@ -26145,6 +27201,9 @@
       <c r="AG368" t="n">
         <v>0.0859</v>
       </c>
+      <c r="AH368" t="n">
+        <v>0.073</v>
+      </c>
       <c r="AI368" t="n">
         <v>0.0218</v>
       </c>
@@ -26216,6 +27275,9 @@
       <c r="AG369" t="n">
         <v>0.0867</v>
       </c>
+      <c r="AH369" t="n">
+        <v>0.0542</v>
+      </c>
       <c r="AI369" t="n">
         <v>0.0209</v>
       </c>
@@ -26287,6 +27349,9 @@
       <c r="AG370" t="n">
         <v>0.0828</v>
       </c>
+      <c r="AH370" t="n">
+        <v>0.0526</v>
+      </c>
       <c r="AI370" t="n">
         <v>0.017</v>
       </c>
@@ -26358,6 +27423,9 @@
       <c r="AG371" t="n">
         <v>0.0898</v>
       </c>
+      <c r="AH371" t="n">
+        <v>0.0613</v>
+      </c>
       <c r="AI371" t="n">
         <v>0.0209</v>
       </c>
@@ -26429,6 +27497,9 @@
       <c r="AG372" t="n">
         <v>0.0813</v>
       </c>
+      <c r="AH372" t="n">
+        <v>0.0594</v>
+      </c>
       <c r="AI372" t="n">
         <v>0.0204</v>
       </c>
@@ -26500,6 +27571,9 @@
       <c r="AG373" t="n">
         <v>0.0708</v>
       </c>
+      <c r="AH373" t="n">
+        <v>0.0575</v>
+      </c>
       <c r="AI373" t="n">
         <v>0.0247</v>
       </c>
@@ -26571,6 +27645,9 @@
       <c r="AG374" t="n">
         <v>0.0838</v>
       </c>
+      <c r="AH374" t="n">
+        <v>0.07770000000000001</v>
+      </c>
       <c r="AI374" t="n">
         <v>0.0589</v>
       </c>
@@ -26642,6 +27719,9 @@
       <c r="AG375" t="n">
         <v>0.0761</v>
       </c>
+      <c r="AH375" t="n">
+        <v>0.07539999999999999</v>
+      </c>
       <c r="AI375" t="n">
         <v>0.0366</v>
       </c>
@@ -26713,6 +27793,9 @@
       <c r="AG376" t="n">
         <v>0.0946</v>
       </c>
+      <c r="AH376" t="n">
+        <v>0.0683</v>
+      </c>
       <c r="AI376" t="n">
         <v>0.0282</v>
       </c>
@@ -26784,6 +27867,9 @@
       <c r="AG377" t="n">
         <v>0.1018</v>
       </c>
+      <c r="AH377" t="n">
+        <v>0.0648</v>
+      </c>
       <c r="AI377" t="n">
         <v>0.0202</v>
       </c>
@@ -26855,6 +27941,9 @@
       <c r="AG378" t="n">
         <v>0.094</v>
       </c>
+      <c r="AH378" t="n">
+        <v>0.0549</v>
+      </c>
       <c r="AI378" t="n">
         <v>0.0222</v>
       </c>
@@ -26926,6 +28015,9 @@
       <c r="AG379" t="n">
         <v>0.0994</v>
       </c>
+      <c r="AH379" t="n">
+        <v>0.0535</v>
+      </c>
       <c r="AI379" t="n">
         <v>0.0199</v>
       </c>
@@ -26997,6 +28089,9 @@
       <c r="AG380" t="n">
         <v>0.1002</v>
       </c>
+      <c r="AH380" t="n">
+        <v>0.06519999999999999</v>
+      </c>
       <c r="AI380" t="n">
         <v>0.0172</v>
       </c>
@@ -27068,6 +28163,9 @@
       <c r="AG381" t="n">
         <v>0.0973</v>
       </c>
+      <c r="AH381" t="n">
+        <v>0.0548</v>
+      </c>
       <c r="AI381" t="n">
         <v>0.0203</v>
       </c>
@@ -27137,7 +28235,10 @@
         <v>0.0492</v>
       </c>
       <c r="AG382" t="n">
-        <v>0.0391</v>
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="AH382" t="n">
+        <v>0.0436</v>
       </c>
       <c r="AI382" t="n">
         <v>0.0169</v>
@@ -27208,7 +28309,10 @@
         <v>0.0593</v>
       </c>
       <c r="AG383" t="n">
-        <v>0.0447</v>
+        <v>0.0944</v>
+      </c>
+      <c r="AH383" t="n">
+        <v>0.0587</v>
       </c>
       <c r="AI383" t="n">
         <v>0.018</v>
@@ -27281,6 +28385,9 @@
       <c r="AG384" t="n">
         <v>0.0494</v>
       </c>
+      <c r="AH384" t="n">
+        <v>0.0551</v>
+      </c>
       <c r="AI384" t="n">
         <v>0.0227</v>
       </c>
@@ -27352,6 +28459,9 @@
       <c r="AG385" t="n">
         <v>0.0575</v>
       </c>
+      <c r="AH385" t="n">
+        <v>0.0589</v>
+      </c>
       <c r="AI385" t="n">
         <v>0.0274</v>
       </c>
@@ -27423,6 +28533,9 @@
       <c r="AG386" t="n">
         <v>0.052</v>
       </c>
+      <c r="AH386" t="n">
+        <v>0.0643</v>
+      </c>
       <c r="AI386" t="n">
         <v>0.0239</v>
       </c>
@@ -27494,6 +28607,9 @@
       <c r="AG387" t="n">
         <v>0.0364</v>
       </c>
+      <c r="AH387" t="n">
+        <v>0.0626</v>
+      </c>
       <c r="AI387" t="n">
         <v>0.02</v>
       </c>
@@ -27565,6 +28681,9 @@
       <c r="AG388" t="n">
         <v>0.0379</v>
       </c>
+      <c r="AH388" t="n">
+        <v>0.0562</v>
+      </c>
       <c r="AI388" t="n">
         <v>0.0249</v>
       </c>
@@ -27636,6 +28755,9 @@
       <c r="AG389" t="n">
         <v>0.0208</v>
       </c>
+      <c r="AH389" t="n">
+        <v>0.0533</v>
+      </c>
       <c r="AI389" t="n">
         <v>0.0281</v>
       </c>
@@ -27707,6 +28829,9 @@
       <c r="AG390" t="n">
         <v>0.028</v>
       </c>
+      <c r="AH390" t="n">
+        <v>0.0602</v>
+      </c>
       <c r="AI390" t="n">
         <v>0.0277</v>
       </c>
@@ -27778,6 +28903,9 @@
       <c r="AG391" t="n">
         <v>0.0335</v>
       </c>
+      <c r="AH391" t="n">
+        <v>0.0582</v>
+      </c>
       <c r="AI391" t="n">
         <v>0.0166</v>
       </c>
@@ -27849,6 +28977,9 @@
       <c r="AG392" t="n">
         <v>0.0199</v>
       </c>
+      <c r="AH392" t="n">
+        <v>0.0561</v>
+      </c>
       <c r="AI392" t="n">
         <v>0.0215</v>
       </c>
@@ -27920,6 +29051,9 @@
       <c r="AG393" t="n">
         <v>0.036</v>
       </c>
+      <c r="AH393" t="n">
+        <v>0.0505</v>
+      </c>
       <c r="AI393" t="n">
         <v>0.0229</v>
       </c>
@@ -27991,6 +29125,9 @@
       <c r="AG394" t="n">
         <v>0.0159</v>
       </c>
+      <c r="AH394" t="n">
+        <v>0.0412</v>
+      </c>
       <c r="AI394" t="n">
         <v>0.0217</v>
       </c>
@@ -28062,6 +29199,9 @@
       <c r="AG395" t="n">
         <v>0.0389</v>
       </c>
+      <c r="AH395" t="n">
+        <v>0.0478</v>
+      </c>
       <c r="AI395" t="n">
         <v>0.0209</v>
       </c>
@@ -28133,6 +29273,9 @@
       <c r="AG396" t="n">
         <v>0.029</v>
       </c>
+      <c r="AH396" t="n">
+        <v>0.0494</v>
+      </c>
       <c r="AI396" t="n">
         <v>0.0208</v>
       </c>
@@ -28204,6 +29347,9 @@
       <c r="AG397" t="n">
         <v>0.0346</v>
       </c>
+      <c r="AH397" t="n">
+        <v>0.053</v>
+      </c>
       <c r="AI397" t="n">
         <v>0.0186</v>
       </c>
@@ -28275,6 +29421,9 @@
       <c r="AG398" t="n">
         <v>0.0388</v>
       </c>
+      <c r="AH398" t="n">
+        <v>0.0558</v>
+      </c>
       <c r="AI398" t="n">
         <v>0.0193</v>
       </c>
@@ -28346,6 +29495,9 @@
       <c r="AG399" t="n">
         <v>0.0197</v>
       </c>
+      <c r="AH399" t="n">
+        <v>0.0477</v>
+      </c>
       <c r="AI399" t="n">
         <v>0.0227</v>
       </c>
@@ -28417,6 +29569,9 @@
       <c r="AG400" t="n">
         <v>0.0232</v>
       </c>
+      <c r="AH400" t="n">
+        <v>0.0522</v>
+      </c>
       <c r="AI400" t="n">
         <v>0.0304</v>
       </c>
@@ -28488,6 +29643,9 @@
       <c r="AG401" t="n">
         <v>0.0375</v>
       </c>
+      <c r="AH401" t="n">
+        <v>0.0564</v>
+      </c>
       <c r="AI401" t="n">
         <v>0.0201</v>
       </c>
@@ -28559,6 +29717,9 @@
       <c r="AG402" t="n">
         <v>0.0298</v>
       </c>
+      <c r="AH402" t="n">
+        <v>0.0498</v>
+      </c>
       <c r="AI402" t="n">
         <v>0.0244</v>
       </c>
@@ -28630,6 +29791,9 @@
       <c r="AG403" t="n">
         <v>0.0273</v>
       </c>
+      <c r="AH403" t="n">
+        <v>0.056</v>
+      </c>
       <c r="AI403" t="n">
         <v>0.0215</v>
       </c>
@@ -28701,6 +29865,9 @@
       <c r="AG404" t="n">
         <v>0.0291</v>
       </c>
+      <c r="AH404" t="n">
+        <v>0.0505</v>
+      </c>
       <c r="AI404" t="n">
         <v>0.0283</v>
       </c>
@@ -28772,6 +29939,9 @@
       <c r="AG405" t="n">
         <v>0.0438</v>
       </c>
+      <c r="AH405" t="n">
+        <v>0.0516</v>
+      </c>
       <c r="AI405" t="n">
         <v>0.0148</v>
       </c>
@@ -28843,6 +30013,9 @@
       <c r="AG406" t="n">
         <v>0.0474</v>
       </c>
+      <c r="AH406" t="n">
+        <v>0.0481</v>
+      </c>
       <c r="AI406" t="n">
         <v>0.0246</v>
       </c>
@@ -28914,6 +30087,9 @@
       <c r="AG407" t="n">
         <v>0.0294</v>
       </c>
+      <c r="AH407" t="n">
+        <v>0.0505</v>
+      </c>
       <c r="AI407" t="n">
         <v>0.0187</v>
       </c>
@@ -28985,6 +30161,9 @@
       <c r="AG408" t="n">
         <v>0.0321</v>
       </c>
+      <c r="AH408" t="n">
+        <v>0.0411</v>
+      </c>
       <c r="AI408" t="n">
         <v>0.0214</v>
       </c>
@@ -29056,6 +30235,9 @@
       <c r="AG409" t="n">
         <v>0.0293</v>
       </c>
+      <c r="AH409" t="n">
+        <v>0.0464</v>
+      </c>
       <c r="AI409" t="n">
         <v>0.0263</v>
       </c>
@@ -29127,6 +30309,9 @@
       <c r="AG410" t="n">
         <v>0.0449</v>
       </c>
+      <c r="AH410" t="n">
+        <v>0.0594</v>
+      </c>
       <c r="AI410" t="n">
         <v>0.0159</v>
       </c>
@@ -29198,6 +30383,9 @@
       <c r="AG411" t="n">
         <v>0.0331</v>
       </c>
+      <c r="AH411" t="n">
+        <v>0.0539</v>
+      </c>
       <c r="AI411" t="n">
         <v>0.018</v>
       </c>
@@ -29269,6 +30457,9 @@
       <c r="AG412" t="n">
         <v>0.0348</v>
       </c>
+      <c r="AH412" t="n">
+        <v>0.0488</v>
+      </c>
       <c r="AI412" t="n">
         <v>0.0234</v>
       </c>
@@ -29340,6 +30531,9 @@
       <c r="AG413" t="n">
         <v>0.0454</v>
       </c>
+      <c r="AH413" t="n">
+        <v>0.0538</v>
+      </c>
       <c r="AI413" t="n">
         <v>0.0247</v>
       </c>
@@ -29411,6 +30605,9 @@
       <c r="AG414" t="n">
         <v>0.0332</v>
       </c>
+      <c r="AH414" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AI414" t="n">
         <v>0.0213</v>
       </c>
@@ -29481,6 +30678,9 @@
       </c>
       <c r="AG415" t="n">
         <v>0.0246</v>
+      </c>
+      <c r="AH415" t="n">
+        <v>0.053</v>
       </c>
       <c r="AI415" t="n">
         <v>0.0193</v>
@@ -29546,6 +30746,9 @@
       <c r="AG418" t="n">
         <v>0.150375</v>
       </c>
+      <c r="AH418" t="n">
+        <v>0.1496333333333333</v>
+      </c>
       <c r="AI418" t="n">
         <v>0.11844</v>
       </c>
@@ -29596,6 +30799,9 @@
       <c r="AG419" t="n">
         <v>0.1805142857142857</v>
       </c>
+      <c r="AH419" t="n">
+        <v>0.1386166666666667</v>
+      </c>
       <c r="AI419" t="n">
         <v>0.1168142857142857</v>
       </c>
@@ -29646,6 +30852,9 @@
       <c r="AG420" t="n">
         <v>0.21036</v>
       </c>
+      <c r="AH420" t="n">
+        <v>0.2046444444444444</v>
+      </c>
       <c r="AI420" t="n">
         <v>0.2085875</v>
       </c>
@@ -29696,6 +30905,9 @@
       <c r="AG421" t="n">
         <v>0.252225</v>
       </c>
+      <c r="AH421" t="n">
+        <v>0.2634125</v>
+      </c>
       <c r="AI421" t="n">
         <v>0.28051</v>
       </c>
@@ -29746,6 +30958,9 @@
       <c r="AG422" t="n">
         <v>0.2460166666666667</v>
       </c>
+      <c r="AH422" t="n">
+        <v>0.2185727272727273</v>
+      </c>
       <c r="AI422" t="n">
         <v>0.29418</v>
       </c>
@@ -29796,6 +31011,9 @@
       <c r="AG423" t="n">
         <v>0.30364</v>
       </c>
+      <c r="AH423" t="n">
+        <v>0.3071</v>
+      </c>
       <c r="AI423" t="n">
         <v>0.30703</v>
       </c>
@@ -29846,6 +31064,9 @@
       <c r="AG424" t="n">
         <v>0.35805</v>
       </c>
+      <c r="AH424" t="n">
+        <v>0.3373125</v>
+      </c>
       <c r="AI424" t="n">
         <v>0.32345</v>
       </c>
@@ -29896,6 +31117,9 @@
       <c r="AG425" t="n">
         <v>0.3969</v>
       </c>
+      <c r="AH425" t="n">
+        <v>0.3982999999999999</v>
+      </c>
       <c r="AI425" t="n">
         <v>0.4134384615384615</v>
       </c>
@@ -29946,6 +31170,9 @@
       <c r="AG426" t="n">
         <v>0.4283750000000001</v>
       </c>
+      <c r="AH426" t="n">
+        <v>0.3959374999999999</v>
+      </c>
       <c r="AI426" t="n">
         <v>0.41214</v>
       </c>
@@ -29996,6 +31223,9 @@
       <c r="AG427" t="n">
         <v>0.4914125</v>
       </c>
+      <c r="AH427" t="n">
+        <v>0.4546444444444445</v>
+      </c>
       <c r="AI427" t="n">
         <v>0.45495</v>
       </c>
@@ -30034,6 +31264,9 @@
       <c r="AG428" t="n">
         <v>0.5786777777777778</v>
       </c>
+      <c r="AH428" t="n">
+        <v>0.5218545454545456</v>
+      </c>
       <c r="AI428" t="n">
         <v>0.47021</v>
       </c>
@@ -30075,6 +31308,9 @@
       <c r="AG429" t="n">
         <v>0.5446749999999999</v>
       </c>
+      <c r="AH429" t="n">
+        <v>0.5055285714285713</v>
+      </c>
       <c r="AI429" t="n">
         <v>0.5647</v>
       </c>
@@ -30116,6 +31352,9 @@
       <c r="AG430" t="n">
         <v>0.6261636363636364</v>
       </c>
+      <c r="AH430" t="n">
+        <v>0.5853625</v>
+      </c>
       <c r="AI430" t="n">
         <v>0.4968555555555556</v>
       </c>
@@ -30157,6 +31396,9 @@
       <c r="AG431" t="n">
         <v>0.6130666666666666</v>
       </c>
+      <c r="AH431" t="n">
+        <v>0.554525</v>
+      </c>
       <c r="AI431" t="n">
         <v>0.5662363636363636</v>
       </c>
@@ -30198,6 +31440,9 @@
       <c r="AG432" t="n">
         <v>0.539988888888889</v>
       </c>
+      <c r="AH432" t="n">
+        <v>0.5792</v>
+      </c>
       <c r="AI432" t="n">
         <v>0.6087</v>
       </c>
@@ -30239,6 +31484,9 @@
       <c r="AG433" t="n">
         <v>0.6403624999999999</v>
       </c>
+      <c r="AH433" t="n">
+        <v>0.5571200000000001</v>
+      </c>
       <c r="AI433" t="n">
         <v>0.5527083333333334</v>
       </c>
@@ -30280,6 +31528,9 @@
       <c r="AG434" t="n">
         <v>0.6644099999999999</v>
       </c>
+      <c r="AH434" t="n">
+        <v>0.5871727272727273</v>
+      </c>
       <c r="AI434" t="n">
         <v>0.5567333333333333</v>
       </c>
@@ -30321,6 +31572,9 @@
       <c r="AG435" t="n">
         <v>0.6553249999999999</v>
       </c>
+      <c r="AH435" t="n">
+        <v>0.6639111111111112</v>
+      </c>
       <c r="AI435" t="n">
         <v>0.4903428571428572</v>
       </c>
@@ -30362,6 +31616,9 @@
       <c r="AG436" t="n">
         <v>0.6570666666666667</v>
       </c>
+      <c r="AH436" t="n">
+        <v>0.6520111111111111</v>
+      </c>
       <c r="AI436" t="n">
         <v>0.4620100000000001</v>
       </c>
@@ -30403,6 +31660,9 @@
       <c r="AG437" t="n">
         <v>0.6755555555555556</v>
       </c>
+      <c r="AH437" t="n">
+        <v>0.64175</v>
+      </c>
     </row>
     <row r="438">
       <c r="H438" s="5" t="n">
@@ -30441,6 +31701,9 @@
       <c r="AG438" t="n">
         <v>0.7323125</v>
       </c>
+      <c r="AH438" t="n">
+        <v>0.5242555555555556</v>
+      </c>
       <c r="AI438" t="n">
         <v>0.5260916666666667</v>
       </c>
@@ -30482,6 +31745,9 @@
       <c r="AG439" t="n">
         <v>0.6723000000000001</v>
       </c>
+      <c r="AH439" t="n">
+        <v>0.5906571428571429</v>
+      </c>
       <c r="AI439" t="n">
         <v>0.5456</v>
       </c>
@@ -30523,6 +31789,9 @@
       <c r="AG440" t="n">
         <v>0.8287636363636363</v>
       </c>
+      <c r="AH440" t="n">
+        <v>0.7551083333333334</v>
+      </c>
       <c r="AI440" t="n">
         <v>0.5898333333333333</v>
       </c>
@@ -30564,6 +31833,9 @@
       <c r="AG441" t="n">
         <v>0.6786749999999999</v>
       </c>
+      <c r="AH441" t="n">
+        <v>0.6199222222222223</v>
+      </c>
       <c r="AI441" t="n">
         <v>0.5843999999999998</v>
       </c>
@@ -30605,6 +31877,9 @@
       <c r="AG442" t="n">
         <v>0.7175777777777778</v>
       </c>
+      <c r="AH442" t="n">
+        <v>0.6417916666666666</v>
+      </c>
       <c r="AI442" t="n">
         <v>0.5954928571428572</v>
       </c>
@@ -30646,6 +31921,9 @@
       <c r="AG443" t="n">
         <v>0.7514000000000001</v>
       </c>
+      <c r="AH443" t="n">
+        <v>0.66647</v>
+      </c>
       <c r="AI443" t="n">
         <v>0.5881416666666667</v>
       </c>
@@ -30687,6 +31965,9 @@
       <c r="AG444" t="n">
         <v>0.6881</v>
       </c>
+      <c r="AH444" t="n">
+        <v>0.6148363636363636</v>
+      </c>
       <c r="AI444" t="n">
         <v>0.6613625000000001</v>
       </c>
@@ -30728,6 +32009,9 @@
       <c r="AG445" t="n">
         <v>0.6619375</v>
       </c>
+      <c r="AH445" t="n">
+        <v>0.6054777777777778</v>
+      </c>
       <c r="AI445" t="n">
         <v>0.57875</v>
       </c>
@@ -30769,6 +32053,9 @@
       <c r="AG446" t="n">
         <v>0.7056571428571428</v>
       </c>
+      <c r="AH446" t="n">
+        <v>0.7241499999999998</v>
+      </c>
       <c r="AI446" t="n">
         <v>0.6669777777777778</v>
       </c>
@@ -30810,6 +32097,9 @@
       <c r="AG447" t="n">
         <v>0.70548</v>
       </c>
+      <c r="AH447" t="n">
+        <v>0.7092181818181817</v>
+      </c>
       <c r="AI447" t="n">
         <v>0.5179363636363636</v>
       </c>
@@ -30851,6 +32141,9 @@
       <c r="AG448" t="n">
         <v>0.6137875</v>
       </c>
+      <c r="AH448" t="n">
+        <v>0.7539100000000001</v>
+      </c>
       <c r="AI448" t="n">
         <v>0.6869727272727273</v>
       </c>
@@ -30892,6 +32185,9 @@
       <c r="AG449" t="n">
         <v>0.6373571428571428</v>
       </c>
+      <c r="AH449" t="n">
+        <v>0.6296111111111111</v>
+      </c>
       <c r="AI449" t="n">
         <v>0.5404214285714286</v>
       </c>
@@ -30930,6 +32226,9 @@
       <c r="AG450" t="n">
         <v>0.7039375000000001</v>
       </c>
+      <c r="AH450" t="n">
+        <v>0.7224750000000001</v>
+      </c>
       <c r="AI450" t="n">
         <v>0.6353583333333334</v>
       </c>
@@ -30971,6 +32270,9 @@
       <c r="AG451" t="n">
         <v>0.6523</v>
       </c>
+      <c r="AH451" t="n">
+        <v>0.6101222222222222</v>
+      </c>
       <c r="AI451" t="n">
         <v>0.6264909090909091</v>
       </c>
@@ -31012,6 +32314,9 @@
       <c r="AG452" t="n">
         <v>0.7395875</v>
       </c>
+      <c r="AH452" t="n">
+        <v>0.6760666666666667</v>
+      </c>
       <c r="AI452" t="n">
         <v>0.6068666666666667</v>
       </c>
@@ -31050,6 +32355,9 @@
       <c r="AG453" t="n">
         <v>0.7404299999999999</v>
       </c>
+      <c r="AH453" t="n">
+        <v>0.6695909090909091</v>
+      </c>
       <c r="AI453" t="n">
         <v>0.5649916666666667</v>
       </c>
@@ -31091,6 +32399,9 @@
       <c r="AG454" t="n">
         <v>0.6936199999999999</v>
       </c>
+      <c r="AH454" t="n">
+        <v>0.7111499999999999</v>
+      </c>
       <c r="AI454" t="n">
         <v>0.5550153846153846</v>
       </c>
@@ -31132,6 +32443,9 @@
       <c r="AG455" t="n">
         <v>0.66187</v>
       </c>
+      <c r="AH455" t="n">
+        <v>0.7222166666666666</v>
+      </c>
       <c r="AI455" t="n">
         <v>0.6625272727272727</v>
       </c>
@@ -31173,6 +32487,9 @@
       <c r="AG456" t="n">
         <v>0.7350857142857142</v>
       </c>
+      <c r="AH456" t="n">
+        <v>0.7070333333333334</v>
+      </c>
       <c r="AI456" t="n">
         <v>0.5782636363636363</v>
       </c>
@@ -31214,6 +32531,9 @@
       <c r="AG457" t="n">
         <v>0.7047857142857143</v>
       </c>
+      <c r="AH457" t="n">
+        <v>0.6972</v>
+      </c>
       <c r="AI457" t="n">
         <v>0.5540833333333334</v>
       </c>
@@ -31255,6 +32575,9 @@
       <c r="AG458" t="n">
         <v>0.6754875</v>
       </c>
+      <c r="AH458" t="n">
+        <v>0.7030125</v>
+      </c>
       <c r="AI458" t="n">
         <v>0.6508307692307691</v>
       </c>
@@ -31296,6 +32619,9 @@
       <c r="AG459" t="n">
         <v>0.7225428571428572</v>
       </c>
+      <c r="AH459" t="n">
+        <v>0.6403444444444444</v>
+      </c>
       <c r="AI459" t="n">
         <v>0.6123333333333334</v>
       </c>
@@ -31337,6 +32663,9 @@
       <c r="AG460" t="n">
         <v>0.71025</v>
       </c>
+      <c r="AH460" t="n">
+        <v>0.6918555555555557</v>
+      </c>
       <c r="AI460" t="n">
         <v>0.6267272727272727</v>
       </c>
@@ -31378,6 +32707,9 @@
       <c r="AG461" t="n">
         <v>0.7363333333333333</v>
       </c>
+      <c r="AH461" t="n">
+        <v>0.6079636363636363</v>
+      </c>
       <c r="AI461" t="n">
         <v>0.5632166666666667</v>
       </c>
@@ -31419,6 +32751,9 @@
       <c r="AG462" t="n">
         <v>0.7300749999999999</v>
       </c>
+      <c r="AH462" t="n">
+        <v>0.7348833333333332</v>
+      </c>
       <c r="AI462" t="n">
         <v>0.588290909090909</v>
       </c>
@@ -31460,6 +32795,9 @@
       <c r="AG463" t="n">
         <v>0.7068000000000001</v>
       </c>
+      <c r="AH463" t="n">
+        <v>0.6648636363636364</v>
+      </c>
     </row>
     <row r="464">
       <c r="H464" s="5" t="n">
@@ -31498,6 +32836,9 @@
       <c r="AG464" t="n">
         <v>0.65405</v>
       </c>
+      <c r="AH464" t="n">
+        <v>0.7024272727272728</v>
+      </c>
       <c r="AI464" t="n">
         <v>0.5247090909090909</v>
       </c>
@@ -31539,6 +32880,9 @@
       <c r="AG465" t="n">
         <v>0.7337300000000001</v>
       </c>
+      <c r="AH465" t="n">
+        <v>0.6746727272727273</v>
+      </c>
       <c r="AI465" t="n">
         <v>0.5759461538461538</v>
       </c>
@@ -31580,6 +32924,9 @@
       <c r="AG466" t="n">
         <v>0.6647545454545455</v>
       </c>
+      <c r="AH466" t="n">
+        <v>0.69796</v>
+      </c>
       <c r="AI466" t="n">
         <v>0.6231818181818182</v>
       </c>
@@ -31621,6 +32968,9 @@
       <c r="AG467" t="n">
         <v>0.6775</v>
       </c>
+      <c r="AH467" t="n">
+        <v>0.6180181818181818</v>
+      </c>
       <c r="AI467" t="n">
         <v>0.566625</v>
       </c>
@@ -31662,6 +33012,9 @@
       <c r="AG468" t="n">
         <v>0.6735899999999999</v>
       </c>
+      <c r="AH468" t="n">
+        <v>0.751825</v>
+      </c>
       <c r="AI468" t="n">
         <v>0.5158727272727273</v>
       </c>
@@ -31703,6 +33056,9 @@
       <c r="AG469" t="n">
         <v>0.7087625</v>
       </c>
+      <c r="AH469" t="n">
+        <v>0.6065199999999999</v>
+      </c>
       <c r="AI469" t="n">
         <v>0.5371222222222223</v>
       </c>
@@ -31744,6 +33100,9 @@
       <c r="AG470" t="n">
         <v>0.6691666666666666</v>
       </c>
+      <c r="AH470" t="n">
+        <v>0.6785222222222222</v>
+      </c>
       <c r="AI470" t="n">
         <v>0.6442727272727272</v>
       </c>
@@ -31785,6 +33144,9 @@
       <c r="AG471" t="n">
         <v>0.7505285714285713</v>
       </c>
+      <c r="AH471" t="n">
+        <v>0.6489</v>
+      </c>
       <c r="AI471" t="n">
         <v>0.5924461538461538</v>
       </c>
@@ -31826,6 +33188,9 @@
       <c r="AG472" t="n">
         <v>0.76529</v>
       </c>
+      <c r="AH472" t="n">
+        <v>0.7252285714285713</v>
+      </c>
       <c r="AI472" t="n">
         <v>0.5593545454545454</v>
       </c>
@@ -31867,6 +33232,9 @@
       <c r="AG473" t="n">
         <v>0.7139499999999999</v>
       </c>
+      <c r="AH473" t="n">
+        <v>0.6969375</v>
+      </c>
       <c r="AI473" t="n">
         <v>0.5250272727272728</v>
       </c>
@@ -31908,6 +33276,9 @@
       <c r="AG474" t="n">
         <v>0.6641666666666667</v>
       </c>
+      <c r="AH474" t="n">
+        <v>0.7255571428571429</v>
+      </c>
       <c r="AI474" t="n">
         <v>0.6432600000000001</v>
       </c>
@@ -31949,6 +33320,9 @@
       <c r="AG475" t="n">
         <v>0.7051555555555555</v>
       </c>
+      <c r="AH475" t="n">
+        <v>0.7406888888888888</v>
+      </c>
       <c r="AI475" t="n">
         <v>0.54559</v>
       </c>
@@ -31990,6 +33364,9 @@
       <c r="AG476" t="n">
         <v>0.7401555555555556</v>
       </c>
+      <c r="AH476" t="n">
+        <v>0.7217000000000001</v>
+      </c>
       <c r="AI476" t="n">
         <v>0.6434</v>
       </c>
@@ -32031,6 +33408,9 @@
       <c r="AG477" t="n">
         <v>0.6803</v>
       </c>
+      <c r="AH477" t="n">
+        <v>0.7513333333333334</v>
+      </c>
       <c r="AI477" t="n">
         <v>0.6002181818181819</v>
       </c>
@@ -32072,6 +33452,9 @@
       <c r="AG478" t="n">
         <v>0.7415666666666668</v>
       </c>
+      <c r="AH478" t="n">
+        <v>0.7607538461538461</v>
+      </c>
       <c r="AI478" t="n">
         <v>0.5306615384615383</v>
       </c>
@@ -32113,6 +33496,9 @@
       <c r="AG479" t="n">
         <v>0.7402444444444444</v>
       </c>
+      <c r="AH479" t="n">
+        <v>0.7331500000000001</v>
+      </c>
       <c r="AI479" t="n">
         <v>0.5950222222222222</v>
       </c>
@@ -32154,6 +33540,9 @@
       <c r="AG480" t="n">
         <v>0.6899555555555554</v>
       </c>
+      <c r="AH480" t="n">
+        <v>0.6978125000000001</v>
+      </c>
       <c r="AI480" t="n">
         <v>0.473225</v>
       </c>
@@ -32195,6 +33584,9 @@
       <c r="AG481" t="n">
         <v>0.7259625</v>
       </c>
+      <c r="AH481" t="n">
+        <v>0.7151700000000001</v>
+      </c>
       <c r="AI481" t="n">
         <v>0.58578</v>
       </c>
@@ -32236,6 +33628,9 @@
       <c r="AG482" t="n">
         <v>0.6759777777777779</v>
       </c>
+      <c r="AH482" t="n">
+        <v>0.7460874999999999</v>
+      </c>
       <c r="AI482" t="n">
         <v>0.5609749999999999</v>
       </c>
@@ -32277,6 +33672,9 @@
       <c r="AG483" t="n">
         <v>0.6821142857142857</v>
       </c>
+      <c r="AH483" t="n">
+        <v>0.6716444444444445</v>
+      </c>
       <c r="AI483" t="n">
         <v>0.5564600000000001</v>
       </c>
@@ -32316,7 +33714,10 @@
         <v>0.6403333333333333</v>
       </c>
       <c r="AG484" t="n">
-        <v>0.6997181818181818</v>
+        <v>0.616275</v>
+      </c>
+      <c r="AH484" t="n">
+        <v>0.8001111111111112</v>
       </c>
       <c r="AI484" t="n">
         <v>0.6442125000000001</v>
@@ -32357,7 +33758,10 @@
         <v>0.5938999999999999</v>
       </c>
       <c r="AG485" t="n">
-        <v>0.7626375</v>
+        <v>0.6479444444444445</v>
+      </c>
+      <c r="AH485" t="n">
+        <v>0.60615</v>
       </c>
       <c r="AI485" t="n">
         <v>0.562275</v>
@@ -32400,6 +33804,9 @@
       <c r="AG486" t="n">
         <v>0.5654125</v>
       </c>
+      <c r="AH486" t="n">
+        <v>0.6726583333333332</v>
+      </c>
       <c r="AI486" t="n">
         <v>0.5865250000000001</v>
       </c>
@@ -32441,6 +33848,9 @@
       <c r="AG487" t="n">
         <v>0.6277888888888888</v>
       </c>
+      <c r="AH487" t="n">
+        <v>0.6137125</v>
+      </c>
       <c r="AI487" t="n">
         <v>0.6254666666666667</v>
       </c>
@@ -32482,6 +33892,9 @@
       <c r="AG488" t="n">
         <v>0.7060166666666667</v>
       </c>
+      <c r="AH488" t="n">
+        <v>0.6932181818181818</v>
+      </c>
       <c r="AI488" t="n">
         <v>0.5931272727272727</v>
       </c>
@@ -32523,6 +33936,9 @@
       <c r="AG489" t="n">
         <v>0.6575571428571428</v>
       </c>
+      <c r="AH489" t="n">
+        <v>0.7275666666666667</v>
+      </c>
       <c r="AI489" t="n">
         <v>0.7043928571428573</v>
       </c>
@@ -32564,6 +33980,9 @@
       <c r="AG490" t="n">
         <v>0.6117</v>
       </c>
+      <c r="AH490" t="n">
+        <v>0.6887899999999999</v>
+      </c>
       <c r="AI490" t="n">
         <v>0.6163777777777777</v>
       </c>
@@ -32602,6 +34021,9 @@
       <c r="AG491" t="n">
         <v>0.60181</v>
       </c>
+      <c r="AH491" t="n">
+        <v>0.6098</v>
+      </c>
       <c r="AI491" t="n">
         <v>0.5878583333333333</v>
       </c>
@@ -32643,6 +34065,9 @@
       <c r="AG492" t="n">
         <v>0.6725333333333333</v>
       </c>
+      <c r="AH492" t="n">
+        <v>0.6169666666666667</v>
+      </c>
       <c r="AI492" t="n">
         <v>0.5871583333333334</v>
       </c>
@@ -32684,6 +34109,9 @@
       <c r="AG493" t="n">
         <v>0.569925</v>
       </c>
+      <c r="AH493" t="n">
+        <v>0.7438666666666667</v>
+      </c>
       <c r="AI493" t="n">
         <v>0.5515666666666666</v>
       </c>
@@ -32725,6 +34153,9 @@
       <c r="AG494" t="n">
         <v>0.6724636363636363</v>
       </c>
+      <c r="AH494" t="n">
+        <v>0.6833874999999999</v>
+      </c>
       <c r="AI494" t="n">
         <v>0.583290909090909</v>
       </c>
@@ -32766,6 +34197,9 @@
       <c r="AG495" t="n">
         <v>0.6555363636363636</v>
       </c>
+      <c r="AH495" t="n">
+        <v>0.63773</v>
+      </c>
       <c r="AI495" t="n">
         <v>0.5609166666666667</v>
       </c>
@@ -32807,6 +34241,9 @@
       <c r="AG496" t="n">
         <v>0.6922799999999999</v>
       </c>
+      <c r="AH496" t="n">
+        <v>0.6243363636363636</v>
+      </c>
       <c r="AI496" t="n">
         <v>0.6091666666666665</v>
       </c>
@@ -32848,6 +34285,9 @@
       <c r="AG497" t="n">
         <v>0.6037777777777777</v>
       </c>
+      <c r="AH497" t="n">
+        <v>0.60795</v>
+      </c>
       <c r="AI497" t="n">
         <v>0.5709799999999999</v>
       </c>
@@ -32889,6 +34329,9 @@
       <c r="AG498" t="n">
         <v>0.6193875000000001</v>
       </c>
+      <c r="AH498" t="n">
+        <v>0.6485100000000001</v>
+      </c>
       <c r="AI498" t="n">
         <v>0.5998222222222221</v>
       </c>
@@ -32930,6 +34373,9 @@
       <c r="AG499" t="n">
         <v>0.6744375</v>
       </c>
+      <c r="AH499" t="n">
+        <v>0.703325</v>
+      </c>
       <c r="AI499" t="n">
         <v>0.5218636363636363</v>
       </c>
@@ -32971,6 +34417,9 @@
       <c r="AG500" t="n">
         <v>0.70008</v>
       </c>
+      <c r="AH500" t="n">
+        <v>0.6943</v>
+      </c>
       <c r="AI500" t="n">
         <v>0.6140090909090909</v>
       </c>
@@ -33012,6 +34461,9 @@
       <c r="AG501" t="n">
         <v>0.6196545454545456</v>
       </c>
+      <c r="AH501" t="n">
+        <v>0.6657727272727272</v>
+      </c>
       <c r="AI501" t="n">
         <v>0.6233333333333334</v>
       </c>
@@ -33053,6 +34505,9 @@
       <c r="AG502" t="n">
         <v>0.7309099999999999</v>
       </c>
+      <c r="AH502" t="n">
+        <v>0.69696</v>
+      </c>
       <c r="AI502" t="n">
         <v>0.6382636363636365</v>
       </c>
@@ -33094,6 +34549,9 @@
       <c r="AG503" t="n">
         <v>0.6705666666666666</v>
       </c>
+      <c r="AH503" t="n">
+        <v>0.7774500000000001</v>
+      </c>
       <c r="AI503" t="n">
         <v>0.5552083333333334</v>
       </c>
@@ -33135,6 +34593,9 @@
       <c r="AG504" t="n">
         <v>0.6718666666666667</v>
       </c>
+      <c r="AH504" t="n">
+        <v>0.70885</v>
+      </c>
       <c r="AI504" t="n">
         <v>0.5549090909090908</v>
       </c>
@@ -33176,6 +34637,9 @@
       <c r="AG505" t="n">
         <v>0.7518636363636362</v>
       </c>
+      <c r="AH505" t="n">
+        <v>0.6255900000000001</v>
+      </c>
       <c r="AI505" t="n">
         <v>0.61391</v>
       </c>
@@ -33217,6 +34681,9 @@
       <c r="AG506" t="n">
         <v>0.7943874999999999</v>
       </c>
+      <c r="AH506" t="n">
+        <v>0.7702699999999999</v>
+      </c>
       <c r="AI506" t="n">
         <v>0.5387916666666667</v>
       </c>
@@ -33258,6 +34725,9 @@
       <c r="AG507" t="n">
         <v>0.69035</v>
       </c>
+      <c r="AH507" t="n">
+        <v>0.7666500000000001</v>
+      </c>
       <c r="AI507" t="n">
         <v>0.5796749999999999</v>
       </c>
@@ -33299,6 +34769,9 @@
       <c r="AG508" t="n">
         <v>0.6579166666666666</v>
       </c>
+      <c r="AH508" t="n">
+        <v>0.7059928571428572</v>
+      </c>
       <c r="AI508" t="n">
         <v>0.5518545454545455</v>
       </c>
@@ -33340,6 +34813,9 @@
       <c r="AG509" t="n">
         <v>0.5816000000000001</v>
       </c>
+      <c r="AH509" t="n">
+        <v>0.6476166666666666</v>
+      </c>
       <c r="AI509" t="n">
         <v>0.5947818181818182</v>
       </c>
@@ -33381,6 +34857,9 @@
       <c r="AG510" t="n">
         <v>0.7370444444444444</v>
       </c>
+      <c r="AH510" t="n">
+        <v>0.6961545454545454</v>
+      </c>
       <c r="AI510" t="n">
         <v>0.59485</v>
       </c>
@@ -33422,6 +34901,9 @@
       <c r="AG511" t="n">
         <v>0.6631375</v>
       </c>
+      <c r="AH511" t="n">
+        <v>0.62356</v>
+      </c>
       <c r="AI511" t="n">
         <v>0.5214846153846153</v>
       </c>
@@ -33463,6 +34945,9 @@
       <c r="AG512" t="n">
         <v>0.6413454545454546</v>
       </c>
+      <c r="AH512" t="n">
+        <v>0.6837999999999999</v>
+      </c>
       <c r="AI512" t="n">
         <v>0.6764363636363636</v>
       </c>
@@ -33504,6 +34989,9 @@
       <c r="AG513" t="n">
         <v>0.6904888888888889</v>
       </c>
+      <c r="AH513" t="n">
+        <v>0.7456727272727274</v>
+      </c>
       <c r="AI513" t="n">
         <v>0.5963499999999999</v>
       </c>
@@ -33545,6 +35033,9 @@
       <c r="AG514" t="n">
         <v>0.6874714285714286</v>
       </c>
+      <c r="AH514" t="n">
+        <v>0.7002999999999999</v>
+      </c>
       <c r="AI514" t="n">
         <v>0.5021545454545454</v>
       </c>
@@ -33586,6 +35077,9 @@
       <c r="AG515" t="n">
         <v>0.6931666666666666</v>
       </c>
+      <c r="AH515" t="n">
+        <v>0.7678272727272727</v>
+      </c>
       <c r="AI515" t="n">
         <v>0.5428000000000001</v>
       </c>
@@ -33627,6 +35121,9 @@
       <c r="AG516" t="n">
         <v>0.6112299999999999</v>
       </c>
+      <c r="AH516" t="n">
+        <v>0.6849666666666666</v>
+      </c>
       <c r="AI516" t="n">
         <v>0.49555</v>
       </c>
@@ -33667,6 +35164,9 @@
       </c>
       <c r="AG517" t="n">
         <v>0.6666818181818182</v>
+      </c>
+      <c r="AH517" t="n">
+        <v>0.6367</v>
       </c>
       <c r="AI517" t="n">
         <v>0.52064</v>
@@ -33717,6 +35217,9 @@
       <c r="AG520" t="n">
         <v>0.1444220588235294</v>
       </c>
+      <c r="AH520" t="n">
+        <v>0.1384455882352941</v>
+      </c>
       <c r="AI520" t="n">
         <v>0.1300313432835821</v>
       </c>
@@ -33752,6 +35255,9 @@
       <c r="AG521" t="n">
         <v>0.1429</v>
       </c>
+      <c r="AH521" t="n">
+        <v>0.1654202898550725</v>
+      </c>
       <c r="AI521" t="n">
         <v>0.16574375</v>
       </c>
@@ -33787,6 +35293,9 @@
       <c r="AG522" t="n">
         <v>0.2835</v>
       </c>
+      <c r="AH522" t="n">
+        <v>0.29118</v>
+      </c>
       <c r="AI522" t="n">
         <v>0.3067285714285714</v>
       </c>
@@ -33822,6 +35331,9 @@
       <c r="AG523" t="n">
         <v>0.3022452380952381</v>
       </c>
+      <c r="AH523" t="n">
+        <v>0.2673111111111111</v>
+      </c>
       <c r="AI523" t="n">
         <v>0.31178</v>
       </c>
@@ -33857,6 +35369,9 @@
       <c r="AG524" t="n">
         <v>0.3887216216216217</v>
       </c>
+      <c r="AH524" t="n">
+        <v>0.31475</v>
+      </c>
       <c r="AI524" t="n">
         <v>0.3213083333333334</v>
       </c>
@@ -33892,6 +35407,9 @@
       <c r="AG525" t="n">
         <v>0.4646130434782609</v>
       </c>
+      <c r="AH525" t="n">
+        <v>0.3252085714285715</v>
+      </c>
       <c r="AI525" t="n">
         <v>0.3844896551724138</v>
       </c>
@@ -33927,6 +35445,9 @@
       <c r="AG526" t="n">
         <v>0.41598</v>
       </c>
+      <c r="AH526" t="n">
+        <v>0.3329666666666667</v>
+      </c>
       <c r="AI526" t="n">
         <v>0.31800625</v>
       </c>
@@ -33962,6 +35483,9 @@
       <c r="AG527" t="n">
         <v>0.5046870967741935</v>
       </c>
+      <c r="AH527" t="n">
+        <v>0.3363875</v>
+      </c>
       <c r="AI527" t="n">
         <v>0.2846541666666667</v>
       </c>
@@ -33997,6 +35521,9 @@
       <c r="AG528" t="n">
         <v>0.579425</v>
       </c>
+      <c r="AH528" t="n">
+        <v>0.4138785714285714</v>
+      </c>
       <c r="AI528" t="n">
         <v>0.5116583333333334</v>
       </c>
@@ -34032,6 +35559,9 @@
       <c r="AG529" t="n">
         <v>0.5007578947368421</v>
       </c>
+      <c r="AH529" t="n">
+        <v>0.4658216216216217</v>
+      </c>
       <c r="AI529" t="n">
         <v>0.4508945454545455</v>
       </c>
@@ -34058,6 +35588,9 @@
       <c r="AG530" t="n">
         <v>0.5682999999999999</v>
       </c>
+      <c r="AH530" t="n">
+        <v>0.4155509803921569</v>
+      </c>
       <c r="AI530" t="n">
         <v>0.4951224137931035</v>
       </c>
@@ -34084,6 +35617,9 @@
       <c r="AG531" t="n">
         <v>0.4866378378378379</v>
       </c>
+      <c r="AH531" t="n">
+        <v>0.4341042553191488</v>
+      </c>
       <c r="AI531" t="n">
         <v>0.3783961538461539</v>
       </c>
@@ -34110,6 +35646,9 @@
       <c r="AG532" t="n">
         <v>0.3932771428571429</v>
       </c>
+      <c r="AH532" t="n">
+        <v>0.4381095238095238</v>
+      </c>
       <c r="AI532" t="n">
         <v>0.5010883333333334</v>
       </c>
@@ -34136,6 +35675,9 @@
       <c r="AG533" t="n">
         <v>0.5558023809523809</v>
       </c>
+      <c r="AH533" t="n">
+        <v>0.4011560975609756</v>
+      </c>
       <c r="AI533" t="n">
         <v>0.4608</v>
       </c>
@@ -34162,6 +35704,9 @@
       <c r="AG534" t="n">
         <v>0.6494636363636364</v>
       </c>
+      <c r="AH534" t="n">
+        <v>0.4839763636363636</v>
+      </c>
       <c r="AI534" t="n">
         <v>0.4022145833333333</v>
       </c>
@@ -34188,6 +35733,9 @@
       <c r="AG535" t="n">
         <v>0.4816966666666668</v>
       </c>
+      <c r="AH535" t="n">
+        <v>0.4271456140350877</v>
+      </c>
       <c r="AI535" t="n">
         <v>0.465167213114754</v>
       </c>
@@ -34214,6 +35762,9 @@
       <c r="AG536" t="n">
         <v>0.4411063829787234</v>
       </c>
+      <c r="AH536" t="n">
+        <v>0.539571794871795</v>
+      </c>
       <c r="AI536" t="n">
         <v>0.3577081081081081</v>
       </c>
@@ -34240,6 +35791,9 @@
       <c r="AG537" t="n">
         <v>0.54195</v>
       </c>
+      <c r="AH537" t="n">
+        <v>0.4696476923076923</v>
+      </c>
       <c r="AI537" t="n">
         <v>0.297085</v>
       </c>
@@ -34266,6 +35820,9 @@
       <c r="AG538" t="n">
         <v>0.6228867647058824</v>
       </c>
+      <c r="AH538" t="n">
+        <v>0.4814236842105262</v>
+      </c>
       <c r="AI538" t="n">
         <v>0.4526016666666667</v>
       </c>
@@ -34292,6 +35849,9 @@
       <c r="AG539" t="n">
         <v>0.5045277777777778</v>
       </c>
+      <c r="AH539" t="n">
+        <v>0.5746521739130435</v>
+      </c>
       <c r="AI539" t="n">
         <v>0.3811</v>
       </c>
@@ -34318,6 +35878,9 @@
       <c r="AG540" t="n">
         <v>0.6734275000000001</v>
       </c>
+      <c r="AH540" t="n">
+        <v>0.5406166666666667</v>
+      </c>
       <c r="AI540" t="n">
         <v>0.4125803571428571</v>
       </c>
@@ -34344,6 +35907,9 @@
       <c r="AG541" t="n">
         <v>0.4816444444444445</v>
       </c>
+      <c r="AH541" t="n">
+        <v>0.4610843749999999</v>
+      </c>
       <c r="AI541" t="n">
         <v>0.5831545454545455</v>
       </c>
@@ -34370,6 +35936,9 @@
       <c r="AG542" t="n">
         <v>0.5161395348837209</v>
       </c>
+      <c r="AH542" t="n">
+        <v>0.41045</v>
+      </c>
       <c r="AI542" t="n">
         <v>0.4331245901639345</v>
       </c>
@@ -34396,6 +35965,9 @@
       <c r="AG543" t="n">
         <v>0.4877159090909091</v>
       </c>
+      <c r="AH543" t="n">
+        <v>0.5829783783783784</v>
+      </c>
       <c r="AI543" t="n">
         <v>0.4620406779661017</v>
       </c>
@@ -34422,6 +35994,9 @@
       <c r="AG544" t="n">
         <v>0.6173763157894737</v>
       </c>
+      <c r="AH544" t="n">
+        <v>0.480835294117647</v>
+      </c>
       <c r="AI544" t="n">
         <v>0.4957734374999999</v>
       </c>
@@ -34448,6 +36023,9 @@
       <c r="AG545" t="n">
         <v>0.4667423076923077</v>
       </c>
+      <c r="AH545" t="n">
+        <v>0.5861459459459459</v>
+      </c>
       <c r="AI545" t="n">
         <v>0.575545945945946</v>
       </c>
@@ -34474,6 +36052,9 @@
       <c r="AG546" t="n">
         <v>0.5142375</v>
       </c>
+      <c r="AH546" t="n">
+        <v>0.4571</v>
+      </c>
       <c r="AI546" t="n">
         <v>0.482527868852459</v>
       </c>
@@ -34500,6 +36081,9 @@
       <c r="AG547" t="n">
         <v>0.4867585365853659</v>
       </c>
+      <c r="AH547" t="n">
+        <v>0.5774666666666667</v>
+      </c>
       <c r="AI547" t="n">
         <v>0.4267274509803923</v>
       </c>
@@ -34526,6 +36110,9 @@
       <c r="AG548" t="n">
         <v>0.5193512195121951</v>
       </c>
+      <c r="AH548" t="n">
+        <v>0.5368424242424242</v>
+      </c>
       <c r="AI548" t="n">
         <v>0.5417542372881355</v>
       </c>
@@ -34552,6 +36139,9 @@
       <c r="AG549" t="n">
         <v>0.5403441860465117</v>
       </c>
+      <c r="AH549" t="n">
+        <v>0.5178847826086955</v>
+      </c>
       <c r="AI549" t="n">
         <v>0.4767525423728814</v>
       </c>
@@ -34578,6 +36168,9 @@
       <c r="AG550" t="n">
         <v>0.442425</v>
       </c>
+      <c r="AH550" t="n">
+        <v>0.4945203703703703</v>
+      </c>
       <c r="AI550" t="n">
         <v>0.4262102564102564</v>
       </c>
@@ -34604,6 +36197,9 @@
       <c r="AG551" t="n">
         <v>0.499976923076923</v>
       </c>
+      <c r="AH551" t="n">
+        <v>0.5444609756097561</v>
+      </c>
       <c r="AI551" t="n">
         <v>0.4427032786885246</v>
       </c>
@@ -34630,6 +36226,9 @@
       <c r="AG552" t="n">
         <v>0.5988116666666666</v>
       </c>
+      <c r="AH552" t="n">
+        <v>0.4972017857142857</v>
+      </c>
       <c r="AI552" t="n">
         <v>0.3574173913043478</v>
       </c>
@@ -34656,6 +36255,9 @@
       <c r="AG553" t="n">
         <v>0.5693342857142857</v>
       </c>
+      <c r="AH553" t="n">
+        <v>0.5013208333333333</v>
+      </c>
       <c r="AI553" t="n">
         <v>0.4145642857142858</v>
       </c>
@@ -34682,6 +36284,9 @@
       <c r="AG554" t="n">
         <v>0.4613942307692307</v>
       </c>
+      <c r="AH554" t="n">
+        <v>0.5984833333333333</v>
+      </c>
       <c r="AI554" t="n">
         <v>0.4851067796610169</v>
       </c>
@@ -34708,6 +36313,9 @@
       <c r="AG555" t="n">
         <v>0.5178790697674418</v>
       </c>
+      <c r="AH555" t="n">
+        <v>0.4133131578947368</v>
+      </c>
       <c r="AI555" t="n">
         <v>0.4232666666666667</v>
       </c>
@@ -34734,6 +36342,9 @@
       <c r="AG556" t="n">
         <v>0.5133842105263158</v>
       </c>
+      <c r="AH556" t="n">
+        <v>0.4701102564102564</v>
+      </c>
       <c r="AI556" t="n">
         <v>0.444435</v>
       </c>
@@ -34760,6 +36371,9 @@
       <c r="AG557" t="n">
         <v>0.6144459459459459</v>
       </c>
+      <c r="AH557" t="n">
+        <v>0.457924</v>
+      </c>
       <c r="AI557" t="n">
         <v>0.41788</v>
       </c>
@@ -34786,6 +36400,9 @@
       <c r="AG558" t="n">
         <v>0.6063604651162789</v>
       </c>
+      <c r="AH558" t="n">
+        <v>0.4429685185185185</v>
+      </c>
       <c r="AI558" t="n">
         <v>0.4011245901639344</v>
       </c>
@@ -34812,6 +36429,9 @@
       <c r="AG559" t="n">
         <v>0.5964913043478262</v>
       </c>
+      <c r="AH559" t="n">
+        <v>0.4947477272727273</v>
+      </c>
       <c r="AI559" t="n">
         <v>0.4532693548387098</v>
       </c>
@@ -34838,6 +36458,9 @@
       <c r="AG560" t="n">
         <v>0.4655409090909091</v>
       </c>
+      <c r="AH560" t="n">
+        <v>0.6247352941176471</v>
+      </c>
       <c r="AI560" t="n">
         <v>0.4451980392156863</v>
       </c>
@@ -34864,6 +36487,9 @@
       <c r="AG561" t="n">
         <v>0.5085512195121952</v>
       </c>
+      <c r="AH561" t="n">
+        <v>0.5042452380952381</v>
+      </c>
       <c r="AI561" t="n">
         <v>0.5603049999999999</v>
       </c>
@@ -34890,6 +36516,9 @@
       <c r="AG562" t="n">
         <v>0.5657425531914894</v>
       </c>
+      <c r="AH562" t="n">
+        <v>0.5153166666666666</v>
+      </c>
       <c r="AI562" t="n">
         <v>0.5377527272727273</v>
       </c>
@@ -34916,6 +36545,9 @@
       <c r="AG563" t="n">
         <v>0.5546979591836736</v>
       </c>
+      <c r="AH563" t="n">
+        <v>0.5991647058823528</v>
+      </c>
       <c r="AI563" t="n">
         <v>0.4258238095238095</v>
       </c>
@@ -34942,6 +36574,9 @@
       <c r="AG564" t="n">
         <v>0.5413347826086957</v>
       </c>
+      <c r="AH564" t="n">
+        <v>0.5046194444444444</v>
+      </c>
       <c r="AI564" t="n">
         <v>0.3946571428571428</v>
       </c>
@@ -34968,6 +36603,9 @@
       <c r="AG565" t="n">
         <v>0.6386893617021278</v>
       </c>
+      <c r="AH565" t="n">
+        <v>0.5434958333333334</v>
+      </c>
       <c r="AI565" t="n">
         <v>0.397948076923077</v>
       </c>
@@ -34994,6 +36632,9 @@
       <c r="AG566" t="n">
         <v>0.5430470588235295</v>
       </c>
+      <c r="AH566" t="n">
+        <v>0.4571097560975609</v>
+      </c>
       <c r="AI566" t="n">
         <v>0.4954880952380952</v>
       </c>
@@ -35020,6 +36661,9 @@
       <c r="AG567" t="n">
         <v>0.6642942307692307</v>
       </c>
+      <c r="AH567" t="n">
+        <v>0.4632666666666667</v>
+      </c>
       <c r="AI567" t="n">
         <v>0.3712135135135136</v>
       </c>
@@ -35046,6 +36690,9 @@
       <c r="AG568" t="n">
         <v>0.5320285714285714</v>
       </c>
+      <c r="AH568" t="n">
+        <v>0.4745111111111111</v>
+      </c>
       <c r="AI568" t="n">
         <v>0.5167102040816326</v>
       </c>
@@ -35072,6 +36719,9 @@
       <c r="AG569" t="n">
         <v>0.6177075000000001</v>
       </c>
+      <c r="AH569" t="n">
+        <v>0.5479684210526315</v>
+      </c>
       <c r="AI569" t="n">
         <v>0.4900320754716981</v>
       </c>
@@ -35098,6 +36748,9 @@
       <c r="AG570" t="n">
         <v>0.5955615384615386</v>
       </c>
+      <c r="AH570" t="n">
+        <v>0.4827871794871794</v>
+      </c>
       <c r="AI570" t="n">
         <v>0.5515588235294117</v>
       </c>
@@ -35124,6 +36777,9 @@
       <c r="AG571" t="n">
         <v>0.5553441860465116</v>
       </c>
+      <c r="AH571" t="n">
+        <v>0.5517641025641026</v>
+      </c>
       <c r="AI571" t="n">
         <v>0.4389015873015872</v>
       </c>
@@ -35150,6 +36806,9 @@
       <c r="AG572" t="n">
         <v>0.4775645833333333</v>
       </c>
+      <c r="AH572" t="n">
+        <v>0.4534483870967742</v>
+      </c>
       <c r="AI572" t="n">
         <v>0.5389327868852459</v>
       </c>
@@ -35176,6 +36835,9 @@
       <c r="AG573" t="n">
         <v>0.4887617647058824</v>
       </c>
+      <c r="AH573" t="n">
+        <v>0.4845145454545455</v>
+      </c>
       <c r="AI573" t="n">
         <v>0.4695723404255319</v>
       </c>
@@ -35202,6 +36864,9 @@
       <c r="AG574" t="n">
         <v>0.5916138888888889</v>
       </c>
+      <c r="AH574" t="n">
+        <v>0.5176224489795919</v>
+      </c>
       <c r="AI574" t="n">
         <v>0.5264584615384615</v>
       </c>
@@ -35228,6 +36893,9 @@
       <c r="AG575" t="n">
         <v>0.5611488888888888</v>
       </c>
+      <c r="AH575" t="n">
+        <v>0.5791434782608695</v>
+      </c>
       <c r="AI575" t="n">
         <v>0.4963703703703704</v>
       </c>
@@ -35254,6 +36922,9 @@
       <c r="AG576" t="n">
         <v>0.5429072727272727</v>
       </c>
+      <c r="AH576" t="n">
+        <v>0.5206872727272727</v>
+      </c>
       <c r="AI576" t="n">
         <v>0.4018028571428571</v>
       </c>
@@ -35280,6 +36951,9 @@
       <c r="AG577" t="n">
         <v>0.6382439024390244</v>
       </c>
+      <c r="AH577" t="n">
+        <v>0.43875625</v>
+      </c>
       <c r="AI577" t="n">
         <v>0.4824263157894737</v>
       </c>
@@ -35306,6 +36980,9 @@
       <c r="AG578" t="n">
         <v>0.6048185185185184</v>
       </c>
+      <c r="AH578" t="n">
+        <v>0.4515955555555555</v>
+      </c>
       <c r="AI578" t="n">
         <v>0.4637245901639344</v>
       </c>
@@ -35332,6 +37009,9 @@
       <c r="AG579" t="n">
         <v>0.5165086956521739</v>
       </c>
+      <c r="AH579" t="n">
+        <v>0.6500454545454546</v>
+      </c>
       <c r="AI579" t="n">
         <v>0.4540272727272727</v>
       </c>
@@ -35358,6 +37038,9 @@
       <c r="AG580" t="n">
         <v>0.6554473684210527</v>
       </c>
+      <c r="AH580" t="n">
+        <v>0.5262333333333333</v>
+      </c>
       <c r="AI580" t="n">
         <v>0.4959056603773584</v>
       </c>
@@ -35384,6 +37067,9 @@
       <c r="AG581" t="n">
         <v>0.61</v>
       </c>
+      <c r="AH581" t="n">
+        <v>0.5362133333333333</v>
+      </c>
       <c r="AI581" t="n">
         <v>0.4562163636363637</v>
       </c>
@@ -35410,6 +37096,9 @@
       <c r="AG582" t="n">
         <v>0.5082950000000001</v>
       </c>
+      <c r="AH582" t="n">
+        <v>0.5075119047619048</v>
+      </c>
       <c r="AI582" t="n">
         <v>0.5284689655172413</v>
       </c>
@@ -35436,6 +37125,9 @@
       <c r="AG583" t="n">
         <v>0.5488657142857143</v>
       </c>
+      <c r="AH583" t="n">
+        <v>0.5325976744186046</v>
+      </c>
       <c r="AI583" t="n">
         <v>0.4816906976744186</v>
       </c>
@@ -35462,6 +37154,9 @@
       <c r="AG584" t="n">
         <v>0.4263096153846154</v>
       </c>
+      <c r="AH584" t="n">
+        <v>0.4194260869565217</v>
+      </c>
       <c r="AI584" t="n">
         <v>0.5130322580645161</v>
       </c>
@@ -35488,6 +37183,9 @@
       <c r="AG585" t="n">
         <v>0.542578</v>
       </c>
+      <c r="AH585" t="n">
+        <v>0.5485529411764707</v>
+      </c>
       <c r="AI585" t="n">
         <v>0.4921869565217391</v>
       </c>
@@ -35512,7 +37210,10 @@
         <v>0.5125636363636364</v>
       </c>
       <c r="AG586" t="n">
-        <v>0.5622434782608696</v>
+        <v>0.6687906250000001</v>
+      </c>
+      <c r="AH586" t="n">
+        <v>0.5197780000000001</v>
       </c>
       <c r="AI586" t="n">
         <v>0.4462366666666667</v>
@@ -35538,7 +37239,10 @@
         <v>0.4961435483870968</v>
       </c>
       <c r="AG587" t="n">
-        <v>0.629788</v>
+        <v>0.5851883333333333</v>
+      </c>
+      <c r="AH587" t="n">
+        <v>0.4922756756756757</v>
       </c>
       <c r="AI587" t="n">
         <v>0.4618345454545454</v>
@@ -35566,6 +37270,9 @@
       <c r="AG588" t="n">
         <v>0.5338622641509434</v>
       </c>
+      <c r="AH588" t="n">
+        <v>0.5408148936170212</v>
+      </c>
       <c r="AI588" t="n">
         <v>0.5012519999999999</v>
       </c>
@@ -35592,6 +37299,9 @@
       <c r="AG589" t="n">
         <v>0.6660233333333333</v>
       </c>
+      <c r="AH589" t="n">
+        <v>0.5243830188679246</v>
+      </c>
       <c r="AI589" t="n">
         <v>0.5026981132075472</v>
       </c>
@@ -35618,6 +37328,9 @@
       <c r="AG590" t="n">
         <v>0.622885</v>
       </c>
+      <c r="AH590" t="n">
+        <v>0.5138934782608696</v>
+      </c>
       <c r="AI590" t="n">
         <v>0.4446111111111111</v>
       </c>
@@ -35644,6 +37357,9 @@
       <c r="AG591" t="n">
         <v>0.477947619047619</v>
       </c>
+      <c r="AH591" t="n">
+        <v>0.447845652173913</v>
+      </c>
       <c r="AI591" t="n">
         <v>0.4232176470588236</v>
       </c>
@@ -35670,6 +37386,9 @@
       <c r="AG592" t="n">
         <v>0.4996968750000001</v>
       </c>
+      <c r="AH592" t="n">
+        <v>0.4880238095238095</v>
+      </c>
       <c r="AI592" t="n">
         <v>0.5659461538461539</v>
       </c>
@@ -35696,6 +37415,9 @@
       <c r="AG593" t="n">
         <v>0.5798840000000002</v>
       </c>
+      <c r="AH593" t="n">
+        <v>0.537166</v>
+      </c>
       <c r="AI593" t="n">
         <v>0.4670844827586206</v>
       </c>
@@ -35722,6 +37444,9 @@
       <c r="AG594" t="n">
         <v>0.446626923076923</v>
       </c>
+      <c r="AH594" t="n">
+        <v>0.5431999999999999</v>
+      </c>
       <c r="AI594" t="n">
         <v>0.5047617021276595</v>
       </c>
@@ -35748,6 +37473,9 @@
       <c r="AG595" t="n">
         <v>0.5939585365853658</v>
       </c>
+      <c r="AH595" t="n">
+        <v>0.5528631578947367</v>
+      </c>
       <c r="AI595" t="n">
         <v>0.5065603773584906</v>
       </c>
@@ -35774,6 +37502,9 @@
       <c r="AG596" t="n">
         <v>0.6019325581395348</v>
       </c>
+      <c r="AH596" t="n">
+        <v>0.5157863636363637</v>
+      </c>
       <c r="AI596" t="n">
         <v>0.4321127659574467</v>
       </c>
@@ -35800,6 +37531,9 @@
       <c r="AG597" t="n">
         <v>0.5208736842105263</v>
       </c>
+      <c r="AH597" t="n">
+        <v>0.5373416666666667</v>
+      </c>
       <c r="AI597" t="n">
         <v>0.4917372549019607</v>
       </c>
@@ -35826,6 +37560,9 @@
       <c r="AG598" t="n">
         <v>0.4400714285714286</v>
       </c>
+      <c r="AH598" t="n">
+        <v>0.4983875</v>
+      </c>
       <c r="AI598" t="n">
         <v>0.4583737704918033</v>
       </c>
@@ -35852,6 +37589,9 @@
       <c r="AG599" t="n">
         <v>0.4712206896551724</v>
       </c>
+      <c r="AH599" t="n">
+        <v>0.4987591836734694</v>
+      </c>
       <c r="AI599" t="n">
         <v>0.442138775510204</v>
       </c>
@@ -35878,6 +37618,9 @@
       <c r="AG600" t="n">
         <v>0.6081968750000001</v>
       </c>
+      <c r="AH600" t="n">
+        <v>0.50485</v>
+      </c>
       <c r="AI600" t="n">
         <v>0.5020217391304347</v>
       </c>
@@ -35904,6 +37647,9 @@
       <c r="AG601" t="n">
         <v>0.4639152173913043</v>
       </c>
+      <c r="AH601" t="n">
+        <v>0.5294414634146343</v>
+      </c>
       <c r="AI601" t="n">
         <v>0.48162</v>
       </c>
@@ -35930,6 +37676,9 @@
       <c r="AG602" t="n">
         <v>0.6336108108108109</v>
       </c>
+      <c r="AH602" t="n">
+        <v>0.5443899999999999</v>
+      </c>
       <c r="AI602" t="n">
         <v>0.5103782608695653</v>
       </c>
@@ -35956,6 +37705,9 @@
       <c r="AG603" t="n">
         <v>0.46076</v>
       </c>
+      <c r="AH603" t="n">
+        <v>0.6180176470588236</v>
+      </c>
       <c r="AI603" t="n">
         <v>0.567101923076923</v>
       </c>
@@ -35982,6 +37734,9 @@
       <c r="AG604" t="n">
         <v>0.6705846153846153</v>
       </c>
+      <c r="AH604" t="n">
+        <v>0.5224961538461538</v>
+      </c>
       <c r="AI604" t="n">
         <v>0.4864060606060606</v>
       </c>
@@ -36008,6 +37763,9 @@
       <c r="AG605" t="n">
         <v>0.6011774193548388</v>
       </c>
+      <c r="AH605" t="n">
+        <v>0.6059823529411765</v>
+      </c>
       <c r="AI605" t="n">
         <v>0.4698021739130435</v>
       </c>
@@ -36034,6 +37792,9 @@
       <c r="AG606" t="n">
         <v>0.5838275000000001</v>
       </c>
+      <c r="AH606" t="n">
+        <v>0.5115878787878788</v>
+      </c>
       <c r="AI606" t="n">
         <v>0.4769766666666667</v>
       </c>
@@ -36060,6 +37821,9 @@
       <c r="AG607" t="n">
         <v>0.5910333333333333</v>
       </c>
+      <c r="AH607" t="n">
+        <v>0.4890975</v>
+      </c>
       <c r="AI607" t="n">
         <v>0.5219344262295083</v>
       </c>
@@ -36086,6 +37850,9 @@
       <c r="AG608" t="n">
         <v>0.541629268292683</v>
       </c>
+      <c r="AH608" t="n">
+        <v>0.5698746031746031</v>
+      </c>
       <c r="AI608" t="n">
         <v>0.467019696969697</v>
       </c>
@@ -36112,6 +37879,9 @@
       <c r="AG609" t="n">
         <v>0.6393599999999999</v>
       </c>
+      <c r="AH609" t="n">
+        <v>0.546662</v>
+      </c>
       <c r="AI609" t="n">
         <v>0.4993666666666666</v>
       </c>
@@ -36138,6 +37908,9 @@
       <c r="AG610" t="n">
         <v>0.5253106382978723</v>
       </c>
+      <c r="AH610" t="n">
+        <v>0.42738125</v>
+      </c>
       <c r="AI610" t="n">
         <v>0.4155879999999999</v>
       </c>
@@ -36164,6 +37937,9 @@
       <c r="AG611" t="n">
         <v>0.52815</v>
       </c>
+      <c r="AH611" t="n">
+        <v>0.536774358974359</v>
+      </c>
       <c r="AI611" t="n">
         <v>0.535139534883721</v>
       </c>
@@ -36190,6 +37966,9 @@
       <c r="AG612" t="n">
         <v>0.5162054054054054</v>
       </c>
+      <c r="AH612" t="n">
+        <v>0.4660133333333333</v>
+      </c>
       <c r="AI612" t="n">
         <v>0.4739463414634146</v>
       </c>
@@ -36216,6 +37995,9 @@
       <c r="AG613" t="n">
         <v>0.6759567567567568</v>
       </c>
+      <c r="AH613" t="n">
+        <v>0.4918965517241379</v>
+      </c>
       <c r="AI613" t="n">
         <v>0.5428290909090909</v>
       </c>
@@ -36242,6 +38024,9 @@
       <c r="AG614" t="n">
         <v>0.4732853658536585</v>
       </c>
+      <c r="AH614" t="n">
+        <v>0.5395061224489796</v>
+      </c>
       <c r="AI614" t="n">
         <v>0.4532660377358492</v>
       </c>
@@ -36268,6 +38053,9 @@
       <c r="AG615" t="n">
         <v>0.681017142857143</v>
       </c>
+      <c r="AH615" t="n">
+        <v>0.4536641509433961</v>
+      </c>
       <c r="AI615" t="n">
         <v>0.4543424242424242</v>
       </c>
@@ -36294,6 +38082,9 @@
       <c r="AG616" t="n">
         <v>0.5610877551020409</v>
       </c>
+      <c r="AH616" t="n">
+        <v>0.4968476190476191</v>
+      </c>
       <c r="AI616" t="n">
         <v>0.4755127659574467</v>
       </c>
@@ -36320,6 +38111,9 @@
       <c r="AG617" t="n">
         <v>0.4817318181818181</v>
       </c>
+      <c r="AH617" t="n">
+        <v>0.5612304347826086</v>
+      </c>
       <c r="AI617" t="n">
         <v>0.377054</v>
       </c>
@@ -36346,6 +38140,9 @@
       <c r="AG618" t="n">
         <v>0.631939393939394</v>
       </c>
+      <c r="AH618" t="n">
+        <v>0.5371017857142858</v>
+      </c>
       <c r="AI618" t="n">
         <v>0.4300561403508771</v>
       </c>
@@ -36371,6 +38168,9 @@
       </c>
       <c r="AG619" t="n">
         <v>0.515921212121212</v>
+      </c>
+      <c r="AH619" t="n">
+        <v>0.5058341463414634</v>
       </c>
       <c r="AI619" t="n">
         <v>0.5009944444444445</v>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -763,11 +763,14 @@
       <c r="AC5" t="n">
         <v>0.1778257575757576</v>
       </c>
+      <c r="AF5" t="n">
+        <v>0.1211935483870968</v>
+      </c>
       <c r="AG5" t="n">
         <v>0.1444220588235294</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.1384455882352941</v>
+        <v>0.1424968253968254</v>
       </c>
       <c r="AI5" t="n">
         <v>0.1300313432835821</v>
@@ -846,11 +849,14 @@
       <c r="AC6" t="n">
         <v>0.1841777777777778</v>
       </c>
+      <c r="AF6" t="n">
+        <v>0.2158</v>
+      </c>
       <c r="AG6" t="n">
         <v>0.2546185185185185</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2015333333333333</v>
+        <v>0.1423461538461538</v>
       </c>
       <c r="AI6" t="n">
         <v>0.1945</v>
@@ -929,11 +935,14 @@
       <c r="AC7" t="n">
         <v>0.2581</v>
       </c>
+      <c r="AF7" t="n">
+        <v>0.3096071428571429</v>
+      </c>
       <c r="AG7" t="n">
         <v>0.29529375</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.3248823529411765</v>
+        <v>0.1828272727272727</v>
       </c>
       <c r="AI7" t="n">
         <v>0.2252636363636364</v>
@@ -1012,11 +1021,14 @@
       <c r="AC8" t="n">
         <v>0.3944363636363636</v>
       </c>
+      <c r="AF8" t="n">
+        <v>0.3051263157894737</v>
+      </c>
       <c r="AG8" t="n">
         <v>0.3587086956521739</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.2428086956521739</v>
+        <v>0.3522999999999999</v>
       </c>
       <c r="AI8" t="n">
         <v>0.3551473684210526</v>
@@ -1095,11 +1107,14 @@
       <c r="AC9" t="n">
         <v>0.4470642857142857</v>
       </c>
+      <c r="AF9" t="n">
+        <v>0.2868</v>
+      </c>
       <c r="AG9" t="n">
         <v>0.4033733333333333</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.4491285714285715</v>
+        <v>0.3851153846153846</v>
       </c>
       <c r="AI9" t="n">
         <v>0.4464521739130435</v>
@@ -1178,11 +1193,14 @@
       <c r="AC10" t="n">
         <v>0.46318</v>
       </c>
+      <c r="AF10" t="n">
+        <v>0.377646</v>
+      </c>
       <c r="AG10" t="n">
         <v>0.5431333333333334</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.4541260869565217</v>
+        <v>0.4923769230769231</v>
       </c>
       <c r="AI10" t="n">
         <v>0.4737409090909091</v>
@@ -1261,11 +1279,14 @@
       <c r="AC11" t="n">
         <v>0.574416129032258</v>
       </c>
+      <c r="AF11" t="n">
+        <v>0.302692</v>
+      </c>
       <c r="AG11" t="n">
         <v>0.6328703703703703</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.6454277777777777</v>
+        <v>0.5345666666666666</v>
       </c>
       <c r="AI11" t="n">
         <v>0.5550304347826086</v>
@@ -1344,11 +1365,14 @@
       <c r="AC12" t="n">
         <v>0.51483</v>
       </c>
+      <c r="AF12" t="n">
+        <v>0.4420933333333333</v>
+      </c>
       <c r="AG12" t="n">
         <v>0.6659105263157894</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.65925</v>
+        <v>0.5387933333333332</v>
       </c>
       <c r="AI12" t="n">
         <v>0.5381</v>
@@ -1427,11 +1451,14 @@
       <c r="AC13" t="n">
         <v>0.6904677419354839</v>
       </c>
+      <c r="AF13" t="n">
+        <v>0.4891961538461538</v>
+      </c>
       <c r="AG13" t="n">
         <v>0.7138029411764706</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.6519966666666667</v>
+        <v>0.51945</v>
       </c>
       <c r="AI13" t="n">
         <v>0.6533703703703705</v>
@@ -1510,11 +1537,14 @@
       <c r="AC14" t="n">
         <v>0.55475</v>
       </c>
+      <c r="AF14" t="n">
+        <v>0.4875537037037037</v>
+      </c>
       <c r="AG14" t="n">
         <v>0.7791452380952381</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.7383620689655173</v>
+        <v>0.6264500000000001</v>
       </c>
       <c r="AI14" t="n">
         <v>0.64605</v>
@@ -1584,11 +1614,14 @@
       <c r="AC15" t="n">
         <v>0.6941181818181819</v>
       </c>
+      <c r="AF15" t="n">
+        <v>0.566505</v>
+      </c>
       <c r="AG15" t="n">
         <v>0.6907088235294117</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.667452380952381</v>
+        <v>0.6431387096774194</v>
       </c>
       <c r="AI15" t="n">
         <v>0.6991238095238095</v>
@@ -1658,11 +1691,14 @@
       <c r="AC16" t="n">
         <v>0.7501740740740742</v>
       </c>
+      <c r="AF16" t="n">
+        <v>0.591214705882353</v>
+      </c>
       <c r="AG16" t="n">
         <v>0.8044242424242424</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.7701888888888889</v>
+        <v>0.7013526315789473</v>
       </c>
       <c r="AI16" t="n">
         <v>0.7390000000000001</v>
@@ -1732,11 +1768,14 @@
       <c r="AC17" t="n">
         <v>0.767936</v>
       </c>
+      <c r="AF17" t="n">
+        <v>0.5701978260869565</v>
+      </c>
       <c r="AG17" t="n">
         <v>0.8216470588235293</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.8126625000000001</v>
+        <v>0.7207969696969698</v>
       </c>
       <c r="AI17" t="n">
         <v>0.7603636363636365</v>
@@ -1806,11 +1845,14 @@
       <c r="AC18" t="n">
         <v>0.8150133333333334</v>
       </c>
+      <c r="AF18" t="n">
+        <v>0.5278999999999999</v>
+      </c>
       <c r="AG18" t="n">
         <v>0.8476916666666665</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.7617736842105264</v>
+        <v>0.6947586206896552</v>
       </c>
       <c r="AI18" t="n">
         <v>0.81838</v>
@@ -1880,11 +1922,14 @@
       <c r="AC19" t="n">
         <v>0.4809538461538461</v>
       </c>
+      <c r="AF19" t="n">
+        <v>0.6256555555555555</v>
+      </c>
       <c r="AG19" t="n">
         <v>0.8462595238095239</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.7741047619047619</v>
+        <v>0.6404666666666667</v>
       </c>
       <c r="AI19" t="n">
         <v>0.8034599999999998</v>
@@ -1954,11 +1999,14 @@
       <c r="AC20" t="n">
         <v>0.7703739130434782</v>
       </c>
+      <c r="AF20" t="n">
+        <v>0.6736951219512195</v>
+      </c>
       <c r="AG20" t="n">
         <v>0.8139575757575758</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.6452142857142857</v>
+        <v>0.750860606060606</v>
       </c>
       <c r="AI20" t="n">
         <v>0.6894499999999999</v>
@@ -2028,11 +2076,14 @@
       <c r="AC21" t="n">
         <v>0.8132562500000001</v>
       </c>
+      <c r="AF21" t="n">
+        <v>0.63368</v>
+      </c>
       <c r="AG21" t="n">
         <v>0.8129480000000001</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.8558538461538461</v>
+        <v>0.7514096774193548</v>
       </c>
       <c r="AI21" t="n">
         <v>0.7377157894736841</v>
@@ -2102,11 +2153,14 @@
       <c r="AC22" t="n">
         <v>0.714878125</v>
       </c>
+      <c r="AF22" t="n">
+        <v>0.6541619047619047</v>
+      </c>
       <c r="AG22" t="n">
         <v>0.8506088235294118</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.7737538461538461</v>
+        <v>0.7932903225806451</v>
       </c>
       <c r="AI22" t="n">
         <v>0.3317</v>
@@ -2176,11 +2230,14 @@
       <c r="AC23" t="n">
         <v>0.8276619047619048</v>
       </c>
+      <c r="AF23" t="n">
+        <v>0.6224535714285715</v>
+      </c>
       <c r="AG23" t="n">
         <v>0.7732114285714287</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.762882142857143</v>
+        <v>0.7427243902439025</v>
       </c>
       <c r="AI23" t="n">
         <v>0.7929571428571428</v>
@@ -2250,11 +2307,14 @@
       <c r="AC24" t="n">
         <v>0.6806578947368421</v>
       </c>
+      <c r="AF24" t="n">
+        <v>0.6992648148148147</v>
+      </c>
       <c r="AG24" t="n">
         <v>0.8626111111111112</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.8332371428571429</v>
+        <v>0.826888</v>
       </c>
       <c r="AI24" t="n">
         <v>0.7378400000000001</v>
@@ -2324,11 +2384,14 @@
       <c r="AC25" t="n">
         <v>0.8548842105263157</v>
       </c>
+      <c r="AF25" t="n">
+        <v>0.7716395833333332</v>
+      </c>
       <c r="AG25" t="n">
         <v>0.8401619047619048</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.8108487804878048</v>
+        <v>0.7898310344827586</v>
       </c>
       <c r="AI25" t="n">
         <v>0.74299</v>
@@ -2398,11 +2461,14 @@
       <c r="AC26" t="n">
         <v>0.7023619047619047</v>
       </c>
+      <c r="AF26" t="n">
+        <v>0.7516045454545455</v>
+      </c>
       <c r="AG26" t="n">
         <v>0.8851699999999999</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.8120717948717948</v>
+        <v>0.8515214285714287</v>
       </c>
       <c r="AI26" t="n">
         <v>0.8164666666666666</v>
@@ -2472,11 +2538,14 @@
       <c r="AC27" t="n">
         <v>0.8953454545454546</v>
       </c>
+      <c r="AF27" t="n">
+        <v>0.683575</v>
+      </c>
       <c r="AG27" t="n">
         <v>0.8068071428571428</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.8240700000000001</v>
+        <v>0.8526173913043478</v>
       </c>
       <c r="AI27" t="n">
         <v>0.69924</v>
@@ -2546,11 +2615,14 @@
       <c r="AC28" t="n">
         <v>0.8215583333333333</v>
       </c>
+      <c r="AF28" t="n">
+        <v>0.718662857142857</v>
+      </c>
       <c r="AG28" t="n">
         <v>0.8382950000000001</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.8738172413793104</v>
+        <v>0.8516962962962962</v>
       </c>
       <c r="AI28" t="n">
         <v>0.7915764705882352</v>
@@ -2620,11 +2692,14 @@
       <c r="AC29" t="n">
         <v>0.8405549999999999</v>
       </c>
+      <c r="AF29" t="n">
+        <v>0.7586853658536586</v>
+      </c>
       <c r="AG29" t="n">
         <v>0.8456666666666667</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.8848216216216216</v>
+        <v>0.8411923076923077</v>
       </c>
       <c r="AI29" t="n">
         <v>0.7888333333333333</v>
@@ -2694,11 +2769,14 @@
       <c r="AC30" t="n">
         <v>0.7895799999999999</v>
       </c>
+      <c r="AF30" t="n">
+        <v>0.6799933333333333</v>
+      </c>
       <c r="AG30" t="n">
         <v>0.8683558139534883</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.8312361111111111</v>
+        <v>0.684423076923077</v>
       </c>
       <c r="AI30" t="n">
         <v>0.7172551724137931</v>
@@ -2768,11 +2846,14 @@
       <c r="AC31" t="n">
         <v>0.8073346153846153</v>
       </c>
+      <c r="AF31" t="n">
+        <v>0.7398852941176471</v>
+      </c>
       <c r="AG31" t="n">
         <v>0.9041483870967743</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.8071724999999998</v>
+        <v>0.7021870967741936</v>
       </c>
       <c r="AI31" t="n">
         <v>0.80762</v>
@@ -2842,11 +2923,14 @@
       <c r="AC32" t="n">
         <v>0.7860285714285714</v>
       </c>
+      <c r="AF32" t="n">
+        <v>0.7788333333333333</v>
+      </c>
       <c r="AG32" t="n">
         <v>0.8286275</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.8405073170731705</v>
+        <v>0.7826521739130435</v>
       </c>
       <c r="AI32" t="n">
         <v>0.7754629629629629</v>
@@ -2916,11 +3000,14 @@
       <c r="AC33" t="n">
         <v>0.89875</v>
       </c>
+      <c r="AF33" t="n">
+        <v>0.7856291666666667</v>
+      </c>
       <c r="AG33" t="n">
         <v>0.8586911111111112</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.8492906976744187</v>
+        <v>0.8233037037037038</v>
       </c>
       <c r="AI33" t="n">
         <v>0.861742105263158</v>
@@ -2990,11 +3077,14 @@
       <c r="AC34" t="n">
         <v>0.8057473684210527</v>
       </c>
+      <c r="AF34" t="n">
+        <v>0.7527744680851063</v>
+      </c>
       <c r="AG34" t="n">
         <v>0.8450769230769232</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.841330303030303</v>
+        <v>0.848917391304348</v>
       </c>
       <c r="AI34" t="n">
         <v>0.8034428571428572</v>
@@ -3064,11 +3154,14 @@
       <c r="AC35" t="n">
         <v>0.8584181818181819</v>
       </c>
+      <c r="AF35" t="n">
+        <v>0.7412694915254238</v>
+      </c>
       <c r="AG35" t="n">
         <v>0.7788975609756098</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.8616911764705882</v>
+        <v>0.6691</v>
       </c>
       <c r="AI35" t="n">
         <v>0.7826291666666667</v>
@@ -3138,11 +3231,14 @@
       <c r="AC36" t="n">
         <v>0.8302687500000001</v>
       </c>
+      <c r="AF36" t="n">
+        <v>0.7180857142857143</v>
+      </c>
       <c r="AG36" t="n">
         <v>0.8721238095238096</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.8974818181818182</v>
+        <v>0.6774</v>
       </c>
       <c r="AI36" t="n">
         <v>0.8525666666666667</v>
@@ -3212,11 +3308,14 @@
       <c r="AC37" t="n">
         <v>0.8016722222222222</v>
       </c>
+      <c r="AF37" t="n">
+        <v>0.8055095238095239</v>
+      </c>
       <c r="AG37" t="n">
         <v>0.7873033333333334</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.9127500000000001</v>
+        <v>0.7932</v>
       </c>
       <c r="AI37" t="n">
         <v>0.7153318181818181</v>
@@ -3286,11 +3385,14 @@
       <c r="AC38" t="n">
         <v>0.8125315789473685</v>
       </c>
+      <c r="AF38" t="n">
+        <v>0.7484777777777778</v>
+      </c>
       <c r="AG38" t="n">
         <v>0.8196461538461539</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.83965</v>
+        <v>0.8423678571428572</v>
       </c>
       <c r="AI38" t="n">
         <v>0.648242857142857</v>
@@ -3360,11 +3462,14 @@
       <c r="AC39" t="n">
         <v>0.813073076923077</v>
       </c>
+      <c r="AF39" t="n">
+        <v>0.6965051282051282</v>
+      </c>
       <c r="AG39" t="n">
         <v>0.9542833333333335</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.8279218750000001</v>
+        <v>0.8939944444444444</v>
       </c>
       <c r="AI39" t="n">
         <v>0.7635384615384615</v>
@@ -3434,11 +3539,14 @@
       <c r="AC40" t="n">
         <v>0.8184586206896552</v>
       </c>
+      <c r="AF40" t="n">
+        <v>0.8004536585365855</v>
+      </c>
       <c r="AG40" t="n">
         <v>0.8326086956521739</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.8829129032258065</v>
+        <v>0.7970458333333333</v>
       </c>
       <c r="AI40" t="n">
         <v>0.8502416666666667</v>
@@ -3508,11 +3616,14 @@
       <c r="AC41" t="n">
         <v>0.8377333333333333</v>
       </c>
+      <c r="AF41" t="n">
+        <v>0.7578836363636364</v>
+      </c>
       <c r="AG41" t="n">
         <v>0.766475</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.8694484848484848</v>
+        <v>0.8548</v>
       </c>
       <c r="AI41" t="n">
         <v>0.7248052631578947</v>
@@ -3582,11 +3693,14 @@
       <c r="AC42" t="n">
         <v>0.771</v>
       </c>
+      <c r="AF42" t="n">
+        <v>0.7189878048780488</v>
+      </c>
       <c r="AG42" t="n">
         <v>0.8674059999999999</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.8453869565217391</v>
+        <v>0.7823806451612902</v>
       </c>
       <c r="AI42" t="n">
         <v>0.8111619047619049</v>
@@ -3656,11 +3770,14 @@
       <c r="AC43" t="n">
         <v>0.8446210526315788</v>
       </c>
+      <c r="AF43" t="n">
+        <v>0.76215</v>
+      </c>
       <c r="AG43" t="n">
         <v>0.8555219512195121</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.8048500000000001</v>
+        <v>0.8664133333333334</v>
       </c>
       <c r="AI43" t="n">
         <v>0.9117714285714287</v>
@@ -3730,11 +3847,14 @@
       <c r="AC44" t="n">
         <v>0.8415050000000001</v>
       </c>
+      <c r="AF44" t="n">
+        <v>0.850783870967742</v>
+      </c>
       <c r="AG44" t="n">
         <v>0.8947911764705883</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.7916411764705883</v>
+        <v>0.7208842105263158</v>
       </c>
       <c r="AI44" t="n">
         <v>0.8577357142857143</v>
@@ -3804,11 +3924,14 @@
       <c r="AC45" t="n">
         <v>0.8024636363636364</v>
       </c>
+      <c r="AF45" t="n">
+        <v>0.8372724999999999</v>
+      </c>
       <c r="AG45" t="n">
         <v>0.8364026315789473</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.8564108108108107</v>
+        <v>0.7902400000000001</v>
       </c>
       <c r="AI45" t="n">
         <v>0.7950076923076922</v>
@@ -3878,11 +4001,14 @@
       <c r="AC46" t="n">
         <v>0.8450529411764706</v>
       </c>
+      <c r="AF46" t="n">
+        <v>0.7954235294117646</v>
+      </c>
       <c r="AG46" t="n">
         <v>0.7907058823529411</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.8720291666666665</v>
+        <v>0.7934114285714285</v>
       </c>
       <c r="AI46" t="n">
         <v>0.8558136363636364</v>
@@ -3952,11 +4078,14 @@
       <c r="AC47" t="n">
         <v>0.8374142857142858</v>
       </c>
+      <c r="AF47" t="n">
+        <v>0.8122710526315789</v>
+      </c>
       <c r="AG47" t="n">
         <v>0.8581365853658536</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.8694862068965519</v>
+        <v>0.8750129032258065</v>
       </c>
       <c r="AI47" t="n">
         <v>0.7612833333333332</v>
@@ -4026,11 +4155,14 @@
       <c r="AC48" t="n">
         <v>0.7865749999999999</v>
       </c>
+      <c r="AF48" t="n">
+        <v>0.7768560975609756</v>
+      </c>
       <c r="AG48" t="n">
         <v>0.9355870967741936</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.876985294117647</v>
+        <v>0.8196351351351352</v>
       </c>
       <c r="AI48" t="n">
         <v>0.7560608695652175</v>
@@ -4100,11 +4232,14 @@
       <c r="AC49" t="n">
         <v>0.7560166666666667</v>
       </c>
+      <c r="AF49" t="n">
+        <v>0.7985172413793102</v>
+      </c>
       <c r="AG49" t="n">
         <v>0.8349897435897435</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.8379866666666665</v>
+        <v>0.7582565217391305</v>
       </c>
       <c r="AI49" t="n">
         <v>0.7343642857142857</v>
@@ -4174,11 +4309,14 @@
       <c r="AC50" t="n">
         <v>0.8125933333333333</v>
       </c>
+      <c r="AF50" t="n">
+        <v>0.8212977777777777</v>
+      </c>
       <c r="AG50" t="n">
         <v>0.8626372093023255</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.8068741935483872</v>
+        <v>0.8263676470588235</v>
       </c>
       <c r="AI50" t="n">
         <v>0.8132285714285714</v>
@@ -4248,11 +4386,14 @@
       <c r="AC51" t="n">
         <v>0.7979192307692308</v>
       </c>
+      <c r="AF51" t="n">
+        <v>0.7167826086956522</v>
+      </c>
       <c r="AG51" t="n">
         <v>0.8403444444444443</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.8953423076923077</v>
+        <v>0.8441299999999998</v>
       </c>
       <c r="AI51" t="n">
         <v>0.8495578947368422</v>
@@ -4322,11 +4463,14 @@
       <c r="AC52" t="n">
         <v>0.8103206896551725</v>
       </c>
+      <c r="AF52" t="n">
+        <v>0.8063586206896551</v>
+      </c>
       <c r="AG52" t="n">
         <v>0.87743</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.9002727272727273</v>
+        <v>0.9025655172413792</v>
       </c>
       <c r="AI52" t="n">
         <v>0.8635695652173914</v>
@@ -4396,11 +4540,14 @@
       <c r="AC53" t="n">
         <v>0.8048999999999999</v>
       </c>
+      <c r="AF53" t="n">
+        <v>0.7686414634146342</v>
+      </c>
       <c r="AG53" t="n">
         <v>0.8419816326530611</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.833008</v>
+        <v>0.859704761904762</v>
       </c>
       <c r="AI53" t="n">
         <v>0.8532714285714286</v>
@@ -4470,11 +4617,14 @@
       <c r="AC54" t="n">
         <v>0.805169696969697</v>
       </c>
+      <c r="AF54" t="n">
+        <v>0.796109375</v>
+      </c>
       <c r="AG54" t="n">
         <v>0.8447468085106383</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.8419500000000001</v>
+        <v>0.8655474999999999</v>
       </c>
       <c r="AI54" t="n">
         <v>0.7911</v>
@@ -4544,11 +4694,14 @@
       <c r="AC55" t="n">
         <v>0.8160833333333333</v>
       </c>
+      <c r="AF55" t="n">
+        <v>0.7950844444444444</v>
+      </c>
       <c r="AG55" t="n">
         <v>0.7363166666666667</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.9225238095238095</v>
+        <v>0.7628869565217392</v>
       </c>
       <c r="AI55" t="n">
         <v>0.82185</v>
@@ -4618,11 +4771,14 @@
       <c r="AC56" t="n">
         <v>0.8642833333333334</v>
       </c>
+      <c r="AF56" t="n">
+        <v>0.6993140000000001</v>
+      </c>
       <c r="AG56" t="n">
         <v>0.8710487179487182</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.8557307692307692</v>
+        <v>0.8694900000000001</v>
       </c>
       <c r="AI56" t="n">
         <v>0.7447764705882354</v>
@@ -4692,11 +4848,14 @@
       <c r="AC57" t="n">
         <v>0.8099125</v>
       </c>
+      <c r="AF57" t="n">
+        <v>0.7823157894736843</v>
+      </c>
       <c r="AG57" t="n">
         <v>0.91634</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.8817558823529412</v>
+        <v>0.8720812499999999</v>
       </c>
       <c r="AI57" t="n">
         <v>0.7757166666666667</v>
@@ -4766,11 +4925,14 @@
       <c r="AC58" t="n">
         <v>0.8868058823529412</v>
       </c>
+      <c r="AF58" t="n">
+        <v>0.7641380952380953</v>
+      </c>
       <c r="AG58" t="n">
         <v>0.9305969696969696</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.8710439999999998</v>
+        <v>0.8046066666666667</v>
       </c>
       <c r="AI58" t="n">
         <v>0.8056529411764707</v>
@@ -4840,11 +5002,14 @@
       <c r="AC59" t="n">
         <v>0.8621346153846154</v>
       </c>
+      <c r="AF59" t="n">
+        <v>0.7457299999999999</v>
+      </c>
       <c r="AG59" t="n">
         <v>0.8735666666666667</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.8885807692307692</v>
+        <v>0.83235</v>
       </c>
       <c r="AI59" t="n">
         <v>0.8226588235294118</v>
@@ -4914,11 +5079,14 @@
       <c r="AC60" t="n">
         <v>0.8122380952380953</v>
       </c>
+      <c r="AF60" t="n">
+        <v>0.8350705882352942</v>
+      </c>
       <c r="AG60" t="n">
         <v>0.8537196078431372</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.8895058823529413</v>
+        <v>0.8313499999999999</v>
       </c>
       <c r="AI60" t="n">
         <v>0.74572</v>
@@ -4988,11 +5156,14 @@
       <c r="AC61" t="n">
         <v>0.8192285714285715</v>
       </c>
+      <c r="AF61" t="n">
+        <v>0.7649038461538461</v>
+      </c>
       <c r="AG61" t="n">
         <v>0.92111875</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.8522344827586207</v>
+        <v>0.8272999999999999</v>
       </c>
       <c r="AI61" t="n">
         <v>0.7422347826086957</v>
@@ -5062,11 +5233,14 @@
       <c r="AC62" t="n">
         <v>0.8367733333333334</v>
       </c>
+      <c r="AF62" t="n">
+        <v>0.7346511111111111</v>
+      </c>
       <c r="AG62" t="n">
         <v>0.9207299999999999</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.8214625</v>
+        <v>0.8872631578947369</v>
       </c>
       <c r="AI62" t="n">
         <v>0.9042545454545454</v>
@@ -5136,11 +5310,14 @@
       <c r="AC63" t="n">
         <v>0.79815</v>
       </c>
+      <c r="AF63" t="n">
+        <v>0.7309825</v>
+      </c>
       <c r="AG63" t="n">
         <v>0.9001749999999999</v>
       </c>
       <c r="AH63" t="n">
-        <v>0.8729137931034484</v>
+        <v>0.7916029411764706</v>
       </c>
       <c r="AI63" t="n">
         <v>0.8332333333333333</v>
@@ -5210,11 +5387,14 @@
       <c r="AC64" t="n">
         <v>0.7964366666666667</v>
       </c>
+      <c r="AF64" t="n">
+        <v>0.737761224489796</v>
+      </c>
       <c r="AG64" t="n">
         <v>0.865484</v>
       </c>
       <c r="AH64" t="n">
-        <v>0.8827219512195122</v>
+        <v>0.7658870967741936</v>
       </c>
       <c r="AI64" t="n">
         <v>0.89825</v>
@@ -5284,11 +5464,14 @@
       <c r="AC65" t="n">
         <v>0.7861571428571429</v>
       </c>
+      <c r="AF65" t="n">
+        <v>0.7681734375</v>
+      </c>
       <c r="AG65" t="n">
         <v>0.942934210526316</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.8627684210526316</v>
+        <v>0.8277296296296295</v>
       </c>
       <c r="AI65" t="n">
         <v>0.8747909090909091</v>
@@ -5358,11 +5541,14 @@
       <c r="AC66" t="n">
         <v>0.7881066666666666</v>
       </c>
+      <c r="AF66" t="n">
+        <v>0.7673023255813953</v>
+      </c>
       <c r="AG66" t="n">
         <v>0.8442041666666666</v>
       </c>
       <c r="AH66" t="n">
-        <v>0.8280023255813954</v>
+        <v>0.8009931034482759</v>
       </c>
       <c r="AI66" t="n">
         <v>0.8047294117647058</v>
@@ -5432,11 +5618,14 @@
       <c r="AC67" t="n">
         <v>0.8141</v>
       </c>
+      <c r="AF67" t="n">
+        <v>0.7821708333333334</v>
+      </c>
       <c r="AG67" t="n">
         <v>0.845618918918919</v>
       </c>
       <c r="AH67" t="n">
-        <v>0.8673909090909091</v>
+        <v>0.7444333333333335</v>
       </c>
       <c r="AI67" t="n">
         <v>0.8612222222222222</v>
@@ -5506,11 +5695,14 @@
       <c r="AC68" t="n">
         <v>0.7976428571428571</v>
       </c>
+      <c r="AF68" t="n">
+        <v>0.7613581818181819</v>
+      </c>
       <c r="AG68" t="n">
         <v>0.871286046511628</v>
       </c>
       <c r="AH68" t="n">
-        <v>0.8567416666666666</v>
+        <v>0.8701375</v>
       </c>
       <c r="AI68" t="n">
         <v>0.8662904761904762</v>
@@ -5580,11 +5772,14 @@
       <c r="AC69" t="n">
         <v>0.8991</v>
       </c>
+      <c r="AF69" t="n">
+        <v>0.8003170212765958</v>
+      </c>
       <c r="AG69" t="n">
         <v>0.734975</v>
       </c>
       <c r="AH69" t="n">
-        <v>0.8673739130434781</v>
+        <v>0.6837666666666666</v>
       </c>
       <c r="AI69" t="n">
         <v>0.830925</v>
@@ -5654,11 +5849,14 @@
       <c r="AC70" t="n">
         <v>0.8285071428571429</v>
       </c>
+      <c r="AF70" t="n">
+        <v>0.8219073170731708</v>
+      </c>
       <c r="AG70" t="n">
         <v>0.9112117647058824</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.8169114285714285</v>
+        <v>0.80914</v>
       </c>
       <c r="AI70" t="n">
         <v>0.8072952380952382</v>
@@ -5728,11 +5926,14 @@
       <c r="AC71" t="n">
         <v>0.8124909090909092</v>
       </c>
+      <c r="AF71" t="n">
+        <v>0.7013918032786886</v>
+      </c>
       <c r="AG71" t="n">
         <v>0.8561836363636364</v>
       </c>
       <c r="AH71" t="n">
-        <v>0.8336034482758621</v>
+        <v>0.8410073170731707</v>
       </c>
       <c r="AI71" t="n">
         <v>0.8981545454545454</v>
@@ -5802,11 +6003,14 @@
       <c r="AC72" t="n">
         <v>0.7806142857142857</v>
       </c>
+      <c r="AF72" t="n">
+        <v>0.8253333333333334</v>
+      </c>
       <c r="AG72" t="n">
         <v>0.8720466666666666</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.8490897435897435</v>
+        <v>0.7789655172413793</v>
       </c>
       <c r="AI72" t="n">
         <v>0.8337</v>
@@ -5876,11 +6080,14 @@
       <c r="AC73" t="n">
         <v>0.8651384615384614</v>
       </c>
+      <c r="AF73" t="n">
+        <v>0.830431914893617</v>
+      </c>
       <c r="AG73" t="n">
         <v>0.9014681818181818</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.7436294117647058</v>
+        <v>0.8785054054054054</v>
       </c>
       <c r="AI73" t="n">
         <v>0.8648571428571429</v>
@@ -5950,11 +6157,14 @@
       <c r="AC74" t="n">
         <v>0.7983347826086956</v>
       </c>
+      <c r="AF74" t="n">
+        <v>0.7466634615384616</v>
+      </c>
       <c r="AG74" t="n">
         <v>0.870672</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.7783615384615385</v>
+        <v>0.8441767441860466</v>
       </c>
       <c r="AI74" t="n">
         <v>0.8498</v>
@@ -6024,11 +6234,14 @@
       <c r="AC75" t="n">
         <v>0.819905</v>
       </c>
+      <c r="AF75" t="n">
+        <v>0.8182203389830509</v>
+      </c>
       <c r="AG75" t="n">
         <v>0.8901314285714287</v>
       </c>
       <c r="AH75" t="n">
-        <v>0.8139382352941178</v>
+        <v>0.7157130434782609</v>
       </c>
       <c r="AI75" t="n">
         <v>0.8002600000000001</v>
@@ -6098,11 +6311,14 @@
       <c r="AC76" t="n">
         <v>0.8066333333333333</v>
       </c>
+      <c r="AF76" t="n">
+        <v>0.7858304347826086</v>
+      </c>
       <c r="AG76" t="n">
         <v>0.9011222222222223</v>
       </c>
       <c r="AH76" t="n">
-        <v>0.8426739130434783</v>
+        <v>0.6965095238095238</v>
       </c>
       <c r="AI76" t="n">
         <v>0.7300083333333335</v>
@@ -6172,11 +6388,14 @@
       <c r="AC77" t="n">
         <v>0.8635769230769232</v>
       </c>
+      <c r="AF77" t="n">
+        <v>0.8292540540540541</v>
+      </c>
       <c r="AG77" t="n">
         <v>0.8690860465116279</v>
       </c>
       <c r="AH77" t="n">
-        <v>0.8412176470588236</v>
+        <v>0.838272972972973</v>
       </c>
       <c r="AI77" t="n">
         <v>0.79581875</v>
@@ -6246,11 +6465,14 @@
       <c r="AC78" t="n">
         <v>0.8692789473684212</v>
       </c>
+      <c r="AF78" t="n">
+        <v>0.7616634615384617</v>
+      </c>
       <c r="AG78" t="n">
         <v>0.845924</v>
       </c>
       <c r="AH78" t="n">
-        <v>0.8194846153846155</v>
+        <v>0.7275999999999999</v>
       </c>
       <c r="AI78" t="n">
         <v>0.8825818181818181</v>
@@ -6320,11 +6542,14 @@
       <c r="AC79" t="n">
         <v>0.8399827586206896</v>
       </c>
+      <c r="AF79" t="n">
+        <v>0.8140846153846154</v>
+      </c>
       <c r="AG79" t="n">
         <v>0.8899279069767442</v>
       </c>
       <c r="AH79" t="n">
-        <v>0.8936153846153847</v>
+        <v>0.7783517241379311</v>
       </c>
       <c r="AI79" t="n">
         <v>0.7831111111111112</v>
@@ -6394,11 +6619,14 @@
       <c r="AC80" t="n">
         <v>0.7929894736842106</v>
       </c>
+      <c r="AF80" t="n">
+        <v>0.7771124999999999</v>
+      </c>
       <c r="AG80" t="n">
         <v>0.8731923076923078</v>
       </c>
       <c r="AH80" t="n">
-        <v>0.8983466666666667</v>
+        <v>0.8916162162162162</v>
       </c>
       <c r="AI80" t="n">
         <v>0.7742857142857144</v>
@@ -6468,11 +6696,14 @@
       <c r="AC81" t="n">
         <v>0.8125333333333332</v>
       </c>
+      <c r="AF81" t="n">
+        <v>0.705746511627907</v>
+      </c>
       <c r="AG81" t="n">
         <v>0.8634222222222222</v>
       </c>
       <c r="AH81" t="n">
-        <v>0.8359085714285714</v>
+        <v>0.7639764705882354</v>
       </c>
       <c r="AI81" t="n">
         <v>0.7648411764705882</v>
@@ -6542,11 +6773,14 @@
       <c r="AC82" t="n">
         <v>0.8307266666666667</v>
       </c>
+      <c r="AF82" t="n">
+        <v>0.8079921052631579</v>
+      </c>
       <c r="AG82" t="n">
         <v>0.8649288888888889</v>
       </c>
       <c r="AH82" t="n">
-        <v>0.8762444444444446</v>
+        <v>0.79995</v>
       </c>
       <c r="AI82" t="n">
         <v>0.82875</v>
@@ -6616,11 +6850,14 @@
       <c r="AC83" t="n">
         <v>0.82816</v>
       </c>
+      <c r="AF83" t="n">
+        <v>0.7309636363636364</v>
+      </c>
       <c r="AG83" t="n">
         <v>0.8624686274509804</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.8619348837209301</v>
+        <v>0.7634827586206897</v>
       </c>
       <c r="AI83" t="n">
         <v>0.7655000000000001</v>
@@ -6690,11 +6927,14 @@
       <c r="AC84" t="n">
         <v>0.8325095238095239</v>
       </c>
+      <c r="AF84" t="n">
+        <v>0.761778947368421</v>
+      </c>
       <c r="AG84" t="n">
         <v>0.8451090909090908</v>
       </c>
       <c r="AH84" t="n">
-        <v>0.8569099999999999</v>
+        <v>0.8402444444444446</v>
       </c>
       <c r="AI84" t="n">
         <v>0.8789187500000001</v>
@@ -6764,11 +7004,14 @@
       <c r="AC85" t="n">
         <v>0.85517</v>
       </c>
+      <c r="AF85" t="n">
+        <v>0.8379250000000001</v>
+      </c>
       <c r="AG85" t="n">
         <v>0.8907369565217391</v>
       </c>
       <c r="AH85" t="n">
-        <v>0.8442777777777778</v>
+        <v>0.8359545454545454</v>
       </c>
       <c r="AI85" t="n">
         <v>0.8657625000000001</v>
@@ -6838,11 +7081,14 @@
       <c r="AC86" t="n">
         <v>0.8028875000000001</v>
       </c>
+      <c r="AF86" t="n">
+        <v>0.8038782608695653</v>
+      </c>
       <c r="AG86" t="n">
         <v>0.9096526315789474</v>
       </c>
       <c r="AH86" t="n">
-        <v>0.8836121951219512</v>
+        <v>0.8242230769230769</v>
       </c>
       <c r="AI86" t="n">
         <v>0.7613666666666666</v>
@@ -6912,11 +7158,14 @@
       <c r="AC87" t="n">
         <v>0.8091333333333334</v>
       </c>
+      <c r="AF87" t="n">
+        <v>0.7474943396226414</v>
+      </c>
       <c r="AG87" t="n">
         <v>0.8535130434782608</v>
       </c>
       <c r="AH87" t="n">
-        <v>0.8382804878048781</v>
+        <v>0.8834285714285715</v>
       </c>
       <c r="AI87" t="n">
         <v>0.7791842105263158</v>
@@ -6986,11 +7235,14 @@
       <c r="AC88" t="n">
         <v>0.8229588235294119</v>
       </c>
+      <c r="AF88" t="n">
+        <v>0.7343703703703703</v>
+      </c>
       <c r="AG88" t="n">
         <v>0.8412625</v>
       </c>
       <c r="AH88" t="n">
-        <v>0.8419387096774192</v>
+        <v>0.8987000000000002</v>
       </c>
       <c r="AI88" t="n">
         <v>0.801004761904762</v>
@@ -7060,11 +7312,14 @@
       <c r="AC89" t="n">
         <v>0.8089263157894738</v>
       </c>
+      <c r="AF89" t="n">
+        <v>0.7854456140350877</v>
+      </c>
       <c r="AG89" t="n">
         <v>0.8927854166666668</v>
       </c>
       <c r="AH89" t="n">
-        <v>0.8526846153846152</v>
+        <v>0.7599541666666667</v>
       </c>
       <c r="AI89" t="n">
         <v>0.8487666666666667</v>
@@ -7134,11 +7389,14 @@
       <c r="AC90" t="n">
         <v>0.8167846153846153</v>
       </c>
+      <c r="AF90" t="n">
+        <v>0.8259139534883719</v>
+      </c>
       <c r="AG90" t="n">
         <v>0.8915225000000001</v>
       </c>
       <c r="AH90" t="n">
-        <v>0.9271621621621622</v>
+        <v>0.7763121951219512</v>
       </c>
       <c r="AI90" t="n">
         <v>0.8916153846153846</v>
@@ -7212,7 +7470,7 @@
         <v>0.834263888888889</v>
       </c>
       <c r="AH91" t="n">
-        <v>0.8098648648648648</v>
+        <v>0.8275351351351351</v>
       </c>
       <c r="AI91" t="n">
         <v>0.7642</v>
@@ -7286,7 +7544,7 @@
         <v>0.9011121951219512</v>
       </c>
       <c r="AH92" t="n">
-        <v>0.8394939393939393</v>
+        <v>0.7645291666666667</v>
       </c>
       <c r="AI92" t="n">
         <v>0.8095</v>
@@ -7360,7 +7618,7 @@
         <v>0.8462468750000001</v>
       </c>
       <c r="AH93" t="n">
-        <v>0.8351500000000001</v>
+        <v>0.7731380952380953</v>
       </c>
       <c r="AI93" t="n">
         <v>0.8826357142857143</v>
@@ -7434,7 +7692,7 @@
         <v>0.8884404761904763</v>
       </c>
       <c r="AH94" t="n">
-        <v>0.9249739130434783</v>
+        <v>0.8357807692307694</v>
       </c>
       <c r="AI94" t="n">
         <v>0.838004761904762</v>
@@ -7508,7 +7766,7 @@
         <v>0.8711861111111112</v>
       </c>
       <c r="AH95" t="n">
-        <v>0.8619685714285714</v>
+        <v>0.8911870967741935</v>
       </c>
       <c r="AI95" t="n">
         <v>0.7770615384615385</v>
@@ -7582,7 +7840,7 @@
         <v>0.857909375</v>
       </c>
       <c r="AH96" t="n">
-        <v>0.8194423076923077</v>
+        <v>0.8718045454545454</v>
       </c>
       <c r="AI96" t="n">
         <v>0.8062428571428571</v>
@@ -7656,7 +7914,7 @@
         <v>0.8854935483870968</v>
       </c>
       <c r="AH97" t="n">
-        <v>0.8053208333333332</v>
+        <v>0.7691814814814815</v>
       </c>
       <c r="AI97" t="n">
         <v>0.8111068965517242</v>
@@ -7730,7 +7988,7 @@
         <v>0.8519176470588236</v>
       </c>
       <c r="AH98" t="n">
-        <v>0.792378947368421</v>
+        <v>0.8479999999999999</v>
       </c>
       <c r="AI98" t="n">
         <v>0.8417523809523809</v>
@@ -7804,7 +8062,7 @@
         <v>0.8394272727272728</v>
       </c>
       <c r="AH99" t="n">
-        <v>0.8941628571428571</v>
+        <v>0.8718111111111111</v>
       </c>
       <c r="AI99" t="n">
         <v>0.8653090909090909</v>
@@ -7878,7 +8136,7 @@
         <v>0.8813866666666667</v>
       </c>
       <c r="AH100" t="n">
-        <v>0.7646714285714283</v>
+        <v>0.8209702702702704</v>
       </c>
       <c r="AI100" t="n">
         <v>0.8858357142857144</v>
@@ -7952,7 +8210,7 @@
         <v>0.8519739130434781</v>
       </c>
       <c r="AH101" t="n">
-        <v>0.8619964285714284</v>
+        <v>0.7918700000000001</v>
       </c>
       <c r="AI101" t="n">
         <v>0.8938117647058824</v>
@@ -8026,7 +8284,7 @@
         <v>0.8819733333333334</v>
       </c>
       <c r="AH102" t="n">
-        <v>0.8644555555555556</v>
+        <v>0.870202564102564</v>
       </c>
       <c r="AI102" t="n">
         <v>0.8413999999999999</v>
@@ -8100,7 +8358,7 @@
         <v>0.8554162790697677</v>
       </c>
       <c r="AH103" t="n">
-        <v>0.8488749999999999</v>
+        <v>0.8475250000000001</v>
       </c>
       <c r="AI103" t="n">
         <v>0.8463416666666667</v>
@@ -8174,7 +8432,7 @@
         <v>0.8421581395348837</v>
       </c>
       <c r="AH104" t="n">
-        <v>0.8246193548387097</v>
+        <v>0.797869696969697</v>
       </c>
       <c r="AI104" t="n">
         <v>0.851348</v>
@@ -8277,11 +8535,14 @@
       <c r="AC108" t="n">
         <v>0.8666666666666667</v>
       </c>
+      <c r="AF108" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="AG108" t="n">
         <v>0.9333333333333333</v>
       </c>
       <c r="AH108" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI108" t="n">
         <v>1</v>
@@ -8360,11 +8621,14 @@
       <c r="AC109" t="n">
         <v>0.9333333333333333</v>
       </c>
+      <c r="AF109" t="n">
+        <v>0.5333333333333333</v>
+      </c>
       <c r="AG109" t="n">
         <v>0.8666666666666667</v>
       </c>
       <c r="AH109" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI109" t="n">
         <v>0.8</v>
@@ -8443,11 +8707,14 @@
       <c r="AC110" t="n">
         <v>0.9166666666666666</v>
       </c>
+      <c r="AF110" t="n">
+        <v>0.2307692307692308</v>
+      </c>
       <c r="AG110" t="n">
         <v>0.9230769230769231</v>
       </c>
       <c r="AH110" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="AI110" t="n">
         <v>0.8461538461538461</v>
@@ -8526,11 +8793,14 @@
       <c r="AC111" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="AF111" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AG111" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="AH111" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AI111" t="n">
         <v>1</v>
@@ -8609,11 +8879,14 @@
       <c r="AC112" t="n">
         <v>0.7142857142857143</v>
       </c>
+      <c r="AF112" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AG112" t="n">
         <v>1</v>
       </c>
       <c r="AH112" t="n">
-        <v>1</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="AI112" t="n">
         <v>0.75</v>
@@ -8692,6 +8965,9 @@
       <c r="AC113" t="n">
         <v>1</v>
       </c>
+      <c r="AF113" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG113" t="n">
         <v>1</v>
       </c>
@@ -8775,11 +9051,14 @@
       <c r="AC114" t="n">
         <v>1</v>
       </c>
+      <c r="AF114" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AG114" t="n">
         <v>0.9</v>
       </c>
       <c r="AH114" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="AI114" t="n">
         <v>1</v>
@@ -8858,11 +9137,14 @@
       <c r="AC115" t="n">
         <v>0.75</v>
       </c>
+      <c r="AF115" t="n">
+        <v>0.6363636363636364</v>
+      </c>
       <c r="AG115" t="n">
         <v>1</v>
       </c>
       <c r="AH115" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AI115" t="n">
         <v>0.6666666666666666</v>
@@ -8941,11 +9223,14 @@
       <c r="AC116" t="n">
         <v>1</v>
       </c>
+      <c r="AF116" t="n">
+        <v>0.4545454545454545</v>
+      </c>
       <c r="AG116" t="n">
         <v>0.75</v>
       </c>
       <c r="AH116" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="AI116" t="n">
         <v>1</v>
@@ -9024,11 +9309,14 @@
       <c r="AC117" t="n">
         <v>1</v>
       </c>
+      <c r="AF117" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG117" t="n">
         <v>0.875</v>
       </c>
       <c r="AH117" t="n">
-        <v>0.875</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AI117" t="n">
         <v>1</v>
@@ -9095,6 +9383,9 @@
       <c r="AC118" t="n">
         <v>1</v>
       </c>
+      <c r="AF118" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG118" t="n">
         <v>1</v>
       </c>
@@ -9169,6 +9460,9 @@
       <c r="AC119" t="n">
         <v>1</v>
       </c>
+      <c r="AF119" t="n">
+        <v>0.6363636363636364</v>
+      </c>
       <c r="AG119" t="n">
         <v>1</v>
       </c>
@@ -9243,6 +9537,9 @@
       <c r="AC120" t="n">
         <v>1</v>
       </c>
+      <c r="AF120" t="n">
+        <v>0.6153846153846154</v>
+      </c>
       <c r="AG120" t="n">
         <v>1</v>
       </c>
@@ -9317,6 +9614,9 @@
       <c r="AC121" t="n">
         <v>0.6</v>
       </c>
+      <c r="AF121" t="n">
+        <v>0.6153846153846154</v>
+      </c>
       <c r="AG121" t="n">
         <v>1</v>
       </c>
@@ -9391,11 +9691,14 @@
       <c r="AC122" t="n">
         <v>1</v>
       </c>
+      <c r="AF122" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG122" t="n">
         <v>1</v>
       </c>
       <c r="AH122" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="AI122" t="n">
         <v>1</v>
@@ -9465,6 +9768,9 @@
       <c r="AC123" t="n">
         <v>1</v>
       </c>
+      <c r="AF123" t="n">
+        <v>0.6153846153846154</v>
+      </c>
       <c r="AG123" t="n">
         <v>0.875</v>
       </c>
@@ -9539,6 +9845,9 @@
       <c r="AC124" t="n">
         <v>1</v>
       </c>
+      <c r="AF124" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG124" t="n">
         <v>1</v>
       </c>
@@ -9613,6 +9922,9 @@
       <c r="AC125" t="n">
         <v>1</v>
       </c>
+      <c r="AF125" t="n">
+        <v>0.4444444444444444</v>
+      </c>
       <c r="AG125" t="n">
         <v>1</v>
       </c>
@@ -9687,6 +9999,9 @@
       <c r="AC126" t="n">
         <v>1</v>
       </c>
+      <c r="AF126" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AG126" t="n">
         <v>1</v>
       </c>
@@ -9761,11 +10076,14 @@
       <c r="AC127" t="n">
         <v>0.5</v>
       </c>
+      <c r="AF127" t="n">
+        <v>0.2222222222222222</v>
+      </c>
       <c r="AG127" t="n">
         <v>1</v>
       </c>
       <c r="AH127" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" ht="16" customHeight="1" s="8">
@@ -9832,6 +10150,9 @@
       <c r="AC128" t="n">
         <v>1</v>
       </c>
+      <c r="AF128" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AG128" t="n">
         <v>1</v>
       </c>
@@ -9906,6 +10227,9 @@
       <c r="AC129" t="n">
         <v>1</v>
       </c>
+      <c r="AF129" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG129" t="n">
         <v>1</v>
       </c>
@@ -9980,6 +10304,9 @@
       <c r="AC130" t="n">
         <v>1</v>
       </c>
+      <c r="AF130" t="n">
+        <v>0.625</v>
+      </c>
       <c r="AG130" t="n">
         <v>1</v>
       </c>
@@ -10054,6 +10381,9 @@
       <c r="AC131" t="n">
         <v>1</v>
       </c>
+      <c r="AF131" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AG131" t="n">
         <v>1</v>
       </c>
@@ -10128,6 +10458,9 @@
       <c r="AC132" t="n">
         <v>1</v>
       </c>
+      <c r="AF132" t="n">
+        <v>0.625</v>
+      </c>
       <c r="AG132" t="n">
         <v>1</v>
       </c>
@@ -10202,6 +10535,9 @@
       <c r="AC133" t="n">
         <v>1</v>
       </c>
+      <c r="AF133" t="n">
+        <v>0.6363636363636364</v>
+      </c>
       <c r="AG133" t="n">
         <v>1</v>
       </c>
@@ -10276,6 +10612,9 @@
       <c r="AC134" t="n">
         <v>1</v>
       </c>
+      <c r="AF134" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG134" t="n">
         <v>1</v>
       </c>
@@ -10350,6 +10689,9 @@
       <c r="AC135" t="n">
         <v>1</v>
       </c>
+      <c r="AF135" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG135" t="n">
         <v>1</v>
       </c>
@@ -10424,6 +10766,9 @@
       <c r="AC136" t="n">
         <v>1</v>
       </c>
+      <c r="AF136" t="n">
+        <v>0.625</v>
+      </c>
       <c r="AG136" t="n">
         <v>1</v>
       </c>
@@ -10498,6 +10843,9 @@
       <c r="AC137" t="n">
         <v>1</v>
       </c>
+      <c r="AF137" t="n">
+        <v>0.5384615384615384</v>
+      </c>
       <c r="AG137" t="n">
         <v>1</v>
       </c>
@@ -10572,6 +10920,9 @@
       <c r="AC138" t="n">
         <v>1</v>
       </c>
+      <c r="AF138" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AG138" t="n">
         <v>1</v>
       </c>
@@ -10646,6 +10997,9 @@
       <c r="AC139" t="n">
         <v>1</v>
       </c>
+      <c r="AF139" t="n">
+        <v>0.4615384615384616</v>
+      </c>
       <c r="AG139" t="n">
         <v>1</v>
       </c>
@@ -10717,6 +11071,9 @@
       <c r="AC140" t="n">
         <v>1</v>
       </c>
+      <c r="AF140" t="n">
+        <v>0.6363636363636364</v>
+      </c>
       <c r="AG140" t="n">
         <v>1</v>
       </c>
@@ -10791,6 +11148,9 @@
       <c r="AC141" t="n">
         <v>1</v>
       </c>
+      <c r="AF141" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AG141" t="n">
         <v>1</v>
       </c>
@@ -10865,6 +11225,9 @@
       <c r="AC142" t="n">
         <v>1</v>
       </c>
+      <c r="AF142" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG142" t="n">
         <v>1</v>
       </c>
@@ -10936,6 +11299,9 @@
       <c r="AC143" t="n">
         <v>1</v>
       </c>
+      <c r="AF143" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AG143" t="n">
         <v>1</v>
       </c>
@@ -11010,6 +11376,9 @@
       <c r="AC144" t="n">
         <v>1</v>
       </c>
+      <c r="AF144" t="n">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="AG144" t="n">
         <v>1</v>
       </c>
@@ -11084,6 +11453,9 @@
       <c r="AC145" t="n">
         <v>1</v>
       </c>
+      <c r="AF145" t="n">
+        <v>0.4444444444444444</v>
+      </c>
       <c r="AG145" t="n">
         <v>1</v>
       </c>
@@ -11158,6 +11530,9 @@
       <c r="AC146" t="n">
         <v>1</v>
       </c>
+      <c r="AF146" t="n">
+        <v>0.5833333333333334</v>
+      </c>
       <c r="AG146" t="n">
         <v>1</v>
       </c>
@@ -11232,6 +11607,9 @@
       <c r="AC147" t="n">
         <v>1</v>
       </c>
+      <c r="AF147" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AG147" t="n">
         <v>1</v>
       </c>
@@ -11306,6 +11684,9 @@
       <c r="AC148" t="n">
         <v>1</v>
       </c>
+      <c r="AF148" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AG148" t="n">
         <v>1</v>
       </c>
@@ -11380,6 +11761,9 @@
       <c r="AC149" t="n">
         <v>1</v>
       </c>
+      <c r="AF149" t="n">
+        <v>0.6363636363636364</v>
+      </c>
       <c r="AG149" t="n">
         <v>1</v>
       </c>
@@ -11454,6 +11838,9 @@
       <c r="AC150" t="n">
         <v>1</v>
       </c>
+      <c r="AF150" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AG150" t="n">
         <v>0.7142857142857143</v>
       </c>
@@ -11528,6 +11915,9 @@
       <c r="AC151" t="n">
         <v>1</v>
       </c>
+      <c r="AF151" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="AG151" t="n">
         <v>1</v>
       </c>
@@ -11602,6 +11992,9 @@
       <c r="AC152" t="n">
         <v>1</v>
       </c>
+      <c r="AF152" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG152" t="n">
         <v>1</v>
       </c>
@@ -11676,6 +12069,9 @@
       <c r="AC153" t="n">
         <v>1</v>
       </c>
+      <c r="AF153" t="n">
+        <v>0.4545454545454545</v>
+      </c>
       <c r="AG153" t="n">
         <v>1</v>
       </c>
@@ -11747,6 +12143,9 @@
       <c r="AC154" t="n">
         <v>1</v>
       </c>
+      <c r="AF154" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG154" t="n">
         <v>1</v>
       </c>
@@ -11821,6 +12220,9 @@
       <c r="AC155" t="n">
         <v>1</v>
       </c>
+      <c r="AF155" t="n">
+        <v>0.625</v>
+      </c>
       <c r="AG155" t="n">
         <v>1</v>
       </c>
@@ -11895,6 +12297,9 @@
       <c r="AC156" t="n">
         <v>1</v>
       </c>
+      <c r="AF156" t="n">
+        <v>0.7272727272727273</v>
+      </c>
       <c r="AG156" t="n">
         <v>1</v>
       </c>
@@ -11969,6 +12374,9 @@
       <c r="AC157" t="n">
         <v>1</v>
       </c>
+      <c r="AF157" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG157" t="n">
         <v>1</v>
       </c>
@@ -12043,6 +12451,9 @@
       <c r="AC158" t="n">
         <v>1</v>
       </c>
+      <c r="AF158" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG158" t="n">
         <v>1</v>
       </c>
@@ -12117,6 +12528,9 @@
       <c r="AC159" t="n">
         <v>1</v>
       </c>
+      <c r="AF159" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AG159" t="n">
         <v>1</v>
       </c>
@@ -12191,6 +12605,9 @@
       <c r="AC160" t="n">
         <v>1</v>
       </c>
+      <c r="AF160" t="n">
+        <v>0.7692307692307693</v>
+      </c>
       <c r="AG160" t="n">
         <v>1</v>
       </c>
@@ -12265,6 +12682,9 @@
       <c r="AC161" t="n">
         <v>1</v>
       </c>
+      <c r="AF161" t="n">
+        <v>0.6923076923076923</v>
+      </c>
       <c r="AG161" t="n">
         <v>1</v>
       </c>
@@ -12339,6 +12759,9 @@
       <c r="AC162" t="n">
         <v>1</v>
       </c>
+      <c r="AF162" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AG162" t="n">
         <v>1</v>
       </c>
@@ -12413,6 +12836,9 @@
       <c r="AC163" t="n">
         <v>1</v>
       </c>
+      <c r="AF163" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG163" t="n">
         <v>1</v>
       </c>
@@ -12487,6 +12913,9 @@
       <c r="AC164" t="n">
         <v>1</v>
       </c>
+      <c r="AF164" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG164" t="n">
         <v>1</v>
       </c>
@@ -12561,6 +12990,9 @@
       <c r="AC165" t="n">
         <v>1</v>
       </c>
+      <c r="AF165" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AG165" t="n">
         <v>1</v>
       </c>
@@ -12635,6 +13067,9 @@
       <c r="AC166" t="n">
         <v>1</v>
       </c>
+      <c r="AF166" t="n">
+        <v>0.3636363636363636</v>
+      </c>
       <c r="AG166" t="n">
         <v>1</v>
       </c>
@@ -12709,6 +13144,9 @@
       <c r="AC167" t="n">
         <v>1</v>
       </c>
+      <c r="AF167" t="n">
+        <v>0.6363636363636364</v>
+      </c>
       <c r="AG167" t="n">
         <v>1</v>
       </c>
@@ -12783,6 +13221,9 @@
       <c r="AC168" t="n">
         <v>1</v>
       </c>
+      <c r="AF168" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG168" t="n">
         <v>1</v>
       </c>
@@ -12857,6 +13298,9 @@
       <c r="AC169" t="n">
         <v>1</v>
       </c>
+      <c r="AF169" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG169" t="n">
         <v>1</v>
       </c>
@@ -12931,6 +13375,9 @@
       <c r="AC170" t="n">
         <v>1</v>
       </c>
+      <c r="AF170" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AG170" t="n">
         <v>1</v>
       </c>
@@ -13005,6 +13452,9 @@
       <c r="AC171" t="n">
         <v>1</v>
       </c>
+      <c r="AF171" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG171" t="n">
         <v>1</v>
       </c>
@@ -13079,6 +13529,9 @@
       <c r="AC172" t="n">
         <v>1</v>
       </c>
+      <c r="AF172" t="n">
+        <v>0.7272727272727273</v>
+      </c>
       <c r="AG172" t="n">
         <v>1</v>
       </c>
@@ -13153,6 +13606,9 @@
       <c r="AC173" t="n">
         <v>1</v>
       </c>
+      <c r="AF173" t="n">
+        <v>0.5454545454545454</v>
+      </c>
       <c r="AG173" t="n">
         <v>1</v>
       </c>
@@ -13227,6 +13683,9 @@
       <c r="AC174" t="n">
         <v>1</v>
       </c>
+      <c r="AF174" t="n">
+        <v>0.625</v>
+      </c>
       <c r="AG174" t="n">
         <v>1</v>
       </c>
@@ -13301,6 +13760,9 @@
       <c r="AC175" t="n">
         <v>1</v>
       </c>
+      <c r="AF175" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AG175" t="n">
         <v>1</v>
       </c>
@@ -13375,6 +13837,9 @@
       <c r="AC176" t="n">
         <v>1</v>
       </c>
+      <c r="AF176" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG176" t="n">
         <v>1</v>
       </c>
@@ -13449,6 +13914,9 @@
       <c r="AC177" t="n">
         <v>1</v>
       </c>
+      <c r="AF177" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG177" t="n">
         <v>1</v>
       </c>
@@ -13523,6 +13991,9 @@
       <c r="AC178" t="n">
         <v>1</v>
       </c>
+      <c r="AF178" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AG178" t="n">
         <v>1</v>
       </c>
@@ -13597,6 +14068,9 @@
       <c r="AC179" t="n">
         <v>1</v>
       </c>
+      <c r="AF179" t="n">
+        <v>0.5833333333333334</v>
+      </c>
       <c r="AG179" t="n">
         <v>1</v>
       </c>
@@ -13671,6 +14145,9 @@
       <c r="AC180" t="n">
         <v>1</v>
       </c>
+      <c r="AF180" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AG180" t="n">
         <v>1</v>
       </c>
@@ -13742,6 +14219,9 @@
       <c r="AC181" t="n">
         <v>1</v>
       </c>
+      <c r="AF181" t="n">
+        <v>0.375</v>
+      </c>
       <c r="AG181" t="n">
         <v>1</v>
       </c>
@@ -13816,6 +14296,9 @@
       <c r="AC182" t="n">
         <v>1</v>
       </c>
+      <c r="AF182" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG182" t="n">
         <v>1</v>
       </c>
@@ -13890,6 +14373,9 @@
       <c r="AC183" t="n">
         <v>1</v>
       </c>
+      <c r="AF183" t="n">
+        <v>0.5454545454545454</v>
+      </c>
       <c r="AG183" t="n">
         <v>1</v>
       </c>
@@ -13964,6 +14450,9 @@
       <c r="AC184" t="n">
         <v>1</v>
       </c>
+      <c r="AF184" t="n">
+        <v>0.5454545454545454</v>
+      </c>
       <c r="AG184" t="n">
         <v>1</v>
       </c>
@@ -14038,6 +14527,9 @@
       <c r="AC185" t="n">
         <v>1</v>
       </c>
+      <c r="AF185" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AG185" t="n">
         <v>1</v>
       </c>
@@ -14112,6 +14604,9 @@
       <c r="AC186" t="n">
         <v>1</v>
       </c>
+      <c r="AF186" t="n">
+        <v>0.8181818181818182</v>
+      </c>
       <c r="AG186" t="n">
         <v>1</v>
       </c>
@@ -14186,6 +14681,9 @@
       <c r="AC187" t="n">
         <v>1</v>
       </c>
+      <c r="AF187" t="n">
+        <v>0.4444444444444444</v>
+      </c>
       <c r="AG187" t="n">
         <v>1</v>
       </c>
@@ -14260,6 +14758,9 @@
       <c r="AC188" t="n">
         <v>1</v>
       </c>
+      <c r="AF188" t="n">
+        <v>0.4</v>
+      </c>
       <c r="AG188" t="n">
         <v>1</v>
       </c>
@@ -14334,6 +14835,9 @@
       <c r="AC189" t="n">
         <v>1</v>
       </c>
+      <c r="AF189" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG189" t="n">
         <v>1</v>
       </c>
@@ -14408,6 +14912,9 @@
       <c r="AC190" t="n">
         <v>1</v>
       </c>
+      <c r="AF190" t="n">
+        <v>0.4</v>
+      </c>
       <c r="AG190" t="n">
         <v>1</v>
       </c>
@@ -14482,6 +14989,9 @@
       <c r="AC191" t="n">
         <v>1</v>
       </c>
+      <c r="AF191" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="AG191" t="n">
         <v>1</v>
       </c>
@@ -14556,6 +15066,9 @@
       <c r="AC192" t="n">
         <v>1</v>
       </c>
+      <c r="AF192" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG192" t="n">
         <v>1</v>
       </c>
@@ -14629,6 +15142,9 @@
       </c>
       <c r="AC193" t="n">
         <v>1</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG193" t="n">
         <v>1</v>
@@ -15773,11 +16289,14 @@
       <c r="AC212" t="n">
         <v>0.9430666666666667</v>
       </c>
+      <c r="AF212" t="n">
+        <v>0.9571400000000001</v>
+      </c>
       <c r="AG212" t="n">
         <v>0.955125</v>
       </c>
       <c r="AH212" t="n">
-        <v>0.9444555555555557</v>
+        <v>0.9364</v>
       </c>
       <c r="AI212" t="n">
         <v>0.9532299999999999</v>
@@ -15856,11 +16375,14 @@
       <c r="AC213" t="n">
         <v>0.9698250000000002</v>
       </c>
+      <c r="AF213" t="n">
+        <v>0.97575</v>
+      </c>
       <c r="AG213" t="n">
         <v>0.9441285714285714</v>
       </c>
       <c r="AH213" t="n">
-        <v>0.9454500000000001</v>
+        <v>0.9519</v>
       </c>
       <c r="AI213" t="n">
         <v>0.9537142857142858</v>
@@ -15939,11 +16461,14 @@
       <c r="AC214" t="n">
         <v>0.94275</v>
       </c>
+      <c r="AF214" t="n">
+        <v>0.8133499999999999</v>
+      </c>
       <c r="AG214" t="n">
         <v>0.9409599999999999</v>
       </c>
       <c r="AH214" t="n">
-        <v>0.9219555555555554</v>
+        <v>0.82565</v>
       </c>
       <c r="AI214" t="n">
         <v>0.9496249999999999</v>
@@ -16022,11 +16547,14 @@
       <c r="AC215" t="n">
         <v>0.9284222222222223</v>
       </c>
+      <c r="AF215" t="n">
+        <v>0.4920888888888889</v>
+      </c>
       <c r="AG215" t="n">
         <v>0.8693</v>
       </c>
       <c r="AH215" t="n">
-        <v>0.825</v>
+        <v>0.8676818181818183</v>
       </c>
       <c r="AI215" t="n">
         <v>0.71899</v>
@@ -16105,11 +16633,14 @@
       <c r="AC216" t="n">
         <v>0.9310363636363637</v>
       </c>
+      <c r="AF216" t="n">
+        <v>0.6964142857142858</v>
+      </c>
       <c r="AG216" t="n">
         <v>0.7681833333333334</v>
       </c>
       <c r="AH216" t="n">
-        <v>0.8714454545454544</v>
+        <v>0.8422999999999999</v>
       </c>
       <c r="AI216" t="n">
         <v>0.7120200000000001</v>
@@ -16188,11 +16719,14 @@
       <c r="AC217" t="n">
         <v>0.8764615384615385</v>
       </c>
+      <c r="AF217" t="n">
+        <v>0.6434636363636363</v>
+      </c>
       <c r="AG217" t="n">
         <v>0.8476100000000001</v>
       </c>
       <c r="AH217" t="n">
-        <v>0.76684</v>
+        <v>0.6752666666666667</v>
       </c>
       <c r="AI217" t="n">
         <v>0.76971</v>
@@ -16271,11 +16805,14 @@
       <c r="AC218" t="n">
         <v>0.9289875</v>
       </c>
+      <c r="AF218" t="n">
+        <v>0.7108222222222222</v>
+      </c>
       <c r="AG218" t="n">
         <v>0.8501666666666666</v>
       </c>
       <c r="AH218" t="n">
-        <v>0.8747374999999999</v>
+        <v>0.5850857142857142</v>
       </c>
       <c r="AI218" t="n">
         <v>0.7489899999999999</v>
@@ -16354,11 +16891,14 @@
       <c r="AC219" t="n">
         <v>0.6568833333333333</v>
       </c>
+      <c r="AF219" t="n">
+        <v>0.84465</v>
+      </c>
       <c r="AG219" t="n">
         <v>0.7333875000000001</v>
       </c>
       <c r="AH219" t="n">
-        <v>0.9117454545454545</v>
+        <v>0.6065199999999999</v>
       </c>
       <c r="AI219" t="n">
         <v>0.6724923076923077</v>
@@ -16437,11 +16977,14 @@
       <c r="AC220" t="n">
         <v>0.5305545454545454</v>
       </c>
+      <c r="AF220" t="n">
+        <v>0.80694</v>
+      </c>
       <c r="AG220" t="n">
         <v>0.7582</v>
       </c>
       <c r="AH220" t="n">
-        <v>0.9240499999999999</v>
+        <v>0.7903384615384615</v>
       </c>
       <c r="AI220" t="n">
         <v>0.7551099999999999</v>
@@ -16520,11 +17063,14 @@
       <c r="AC221" t="n">
         <v>0.9188076923076924</v>
       </c>
+      <c r="AF221" t="n">
+        <v>0.8061400000000001</v>
+      </c>
       <c r="AG221" t="n">
         <v>0.8130875</v>
       </c>
       <c r="AH221" t="n">
-        <v>0.8117111111111112</v>
+        <v>0.7517222222222223</v>
       </c>
       <c r="AI221" t="n">
         <v>0.7041166666666666</v>
@@ -16591,11 +17137,14 @@
       <c r="AC222" t="n">
         <v>0.8268818181818181</v>
       </c>
+      <c r="AF222" t="n">
+        <v>0.8110555555555555</v>
+      </c>
       <c r="AG222" t="n">
         <v>0.7564111111111111</v>
       </c>
       <c r="AH222" t="n">
-        <v>0.8307363636363636</v>
+        <v>0.8266363636363636</v>
       </c>
       <c r="AI222" t="n">
         <v>0.7263400000000001</v>
@@ -16665,11 +17214,14 @@
       <c r="AC223" t="n">
         <v>0.75125</v>
       </c>
+      <c r="AF223" t="n">
+        <v>0.8731625</v>
+      </c>
       <c r="AG223" t="n">
         <v>0.8121625</v>
       </c>
       <c r="AH223" t="n">
-        <v>0.8277428571428571</v>
+        <v>0.7559799999999999</v>
       </c>
       <c r="AI223" t="n">
         <v>0.6934083333333335</v>
@@ -16739,11 +17291,14 @@
       <c r="AC224" t="n">
         <v>0.6753083333333335</v>
       </c>
+      <c r="AF224" t="n">
+        <v>0.9668714285714285</v>
+      </c>
       <c r="AG224" t="n">
         <v>0.6998090909090908</v>
       </c>
       <c r="AH224" t="n">
-        <v>0.90535</v>
+        <v>0.7139</v>
       </c>
       <c r="AI224" t="n">
         <v>0.7491555555555556</v>
@@ -16813,11 +17368,14 @@
       <c r="AC225" t="n">
         <v>0.746990909090909</v>
       </c>
+      <c r="AF225" t="n">
+        <v>0.9683857142857143</v>
+      </c>
       <c r="AG225" t="n">
         <v>0.6655888888888889</v>
       </c>
       <c r="AH225" t="n">
-        <v>0.8235499999999999</v>
+        <v>0.8338499999999999</v>
       </c>
       <c r="AI225" t="n">
         <v>0.6531454545454546</v>
@@ -16887,11 +17445,14 @@
       <c r="AC226" t="n">
         <v>0.6548928571428572</v>
       </c>
+      <c r="AF226" t="n">
+        <v>0.8722444444444445</v>
+      </c>
       <c r="AG226" t="n">
         <v>0.8338666666666668</v>
       </c>
       <c r="AH226" t="n">
-        <v>0.8165222222222221</v>
+        <v>0.7747846153846153</v>
       </c>
       <c r="AI226" t="n">
         <v>0.7161000000000001</v>
@@ -16961,11 +17522,14 @@
       <c r="AC227" t="n">
         <v>0.68125</v>
       </c>
+      <c r="AF227" t="n">
+        <v>0.9111285714285714</v>
+      </c>
       <c r="AG227" t="n">
         <v>0.5132874999999999</v>
       </c>
       <c r="AH227" t="n">
-        <v>0.7955699999999999</v>
+        <v>0.8056833333333332</v>
       </c>
       <c r="AI227" t="n">
         <v>0.7423083333333333</v>
@@ -17035,11 +17599,14 @@
       <c r="AC228" t="n">
         <v>0.7630923076923077</v>
       </c>
+      <c r="AF228" t="n">
+        <v>0.92376</v>
+      </c>
       <c r="AG228" t="n">
         <v>0.5997</v>
       </c>
       <c r="AH228" t="n">
-        <v>0.8126909090909091</v>
+        <v>0.7650571428571429</v>
       </c>
       <c r="AI228" t="n">
         <v>0.6454500000000001</v>
@@ -17109,11 +17676,14 @@
       <c r="AC229" t="n">
         <v>0.6697571428571427</v>
       </c>
+      <c r="AF229" t="n">
+        <v>0.8898454545454545</v>
+      </c>
       <c r="AG229" t="n">
         <v>0.7098166666666668</v>
       </c>
       <c r="AH229" t="n">
-        <v>0.7168888888888889</v>
+        <v>0.6247909090909091</v>
       </c>
       <c r="AI229" t="n">
         <v>0.7297714285714287</v>
@@ -17183,11 +17753,14 @@
       <c r="AC230" t="n">
         <v>0.7526923076923079</v>
       </c>
+      <c r="AF230" t="n">
+        <v>0.8884375</v>
+      </c>
       <c r="AG230" t="n">
         <v>0.5988222222222221</v>
       </c>
       <c r="AH230" t="n">
-        <v>0.7331444444444445</v>
+        <v>0.6883777777777778</v>
       </c>
       <c r="AI230" t="n">
         <v>0.8171799999999999</v>
@@ -17257,11 +17830,14 @@
       <c r="AC231" t="n">
         <v>0.7578307692307692</v>
       </c>
+      <c r="AF231" t="n">
+        <v>0.9359000000000001</v>
+      </c>
       <c r="AG231" t="n">
         <v>0.5894111111111111</v>
       </c>
       <c r="AH231" t="n">
-        <v>0.8160699999999999</v>
+        <v>0.7659333333333334</v>
       </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="8">
@@ -17328,11 +17904,14 @@
       <c r="AC232" t="n">
         <v>0.6034545454545456</v>
       </c>
+      <c r="AF232" t="n">
+        <v>0.9199571428571429</v>
+      </c>
       <c r="AG232" t="n">
         <v>0.5751625</v>
       </c>
       <c r="AH232" t="n">
-        <v>0.8341222222222222</v>
+        <v>0.7731818181818183</v>
       </c>
       <c r="AI232" t="n">
         <v>0.7732916666666667</v>
@@ -17402,11 +17981,14 @@
       <c r="AC233" t="n">
         <v>0.7568461538461537</v>
       </c>
+      <c r="AF233" t="n">
+        <v>0.9106300000000001</v>
+      </c>
       <c r="AG233" t="n">
         <v>0.7272222222222222</v>
       </c>
       <c r="AH233" t="n">
-        <v>0.6517714285714286</v>
+        <v>0.6015818181818182</v>
       </c>
       <c r="AI233" t="n">
         <v>0.7760583333333333</v>
@@ -17476,11 +18058,14 @@
       <c r="AC234" t="n">
         <v>0.6984749999999998</v>
       </c>
+      <c r="AF234" t="n">
+        <v>0.9324199999999999</v>
+      </c>
       <c r="AG234" t="n">
         <v>0.4850909090909091</v>
       </c>
       <c r="AH234" t="n">
-        <v>0.6071916666666667</v>
+        <v>0.7315999999999999</v>
       </c>
       <c r="AI234" t="n">
         <v>0.7528833333333335</v>
@@ -17550,11 +18135,14 @@
       <c r="AC235" t="n">
         <v>0.6754166666666667</v>
       </c>
+      <c r="AF235" t="n">
+        <v>0.9463250000000002</v>
+      </c>
       <c r="AG235" t="n">
         <v>0.4899125</v>
       </c>
       <c r="AH235" t="n">
-        <v>0.7896</v>
+        <v>0.6208666666666667</v>
       </c>
       <c r="AI235" t="n">
         <v>0.6315538461538461</v>
@@ -17624,11 +18212,14 @@
       <c r="AC236" t="n">
         <v>0.6302083333333333</v>
       </c>
+      <c r="AF236" t="n">
+        <v>0.93934</v>
+      </c>
       <c r="AG236" t="n">
         <v>0.4749666666666666</v>
       </c>
       <c r="AH236" t="n">
-        <v>0.760325</v>
+        <v>0.66298</v>
       </c>
       <c r="AI236" t="n">
         <v>0.6624500000000001</v>
@@ -17698,11 +18289,14 @@
       <c r="AC237" t="n">
         <v>0.6648181818181818</v>
       </c>
+      <c r="AF237" t="n">
+        <v>0.9574875</v>
+      </c>
       <c r="AG237" t="n">
         <v>0.58648</v>
       </c>
       <c r="AH237" t="n">
-        <v>0.6512600000000002</v>
+        <v>0.6839500000000001</v>
       </c>
       <c r="AI237" t="n">
         <v>0.751525</v>
@@ -17772,11 +18366,14 @@
       <c r="AC238" t="n">
         <v>0.4744249999999999</v>
       </c>
+      <c r="AF238" t="n">
+        <v>0.9584545454545456</v>
+      </c>
       <c r="AG238" t="n">
         <v>0.5892000000000001</v>
       </c>
       <c r="AH238" t="n">
-        <v>0.8279727272727272</v>
+        <v>0.74095</v>
       </c>
       <c r="AI238" t="n">
         <v>0.652825</v>
@@ -17846,11 +18443,14 @@
       <c r="AC239" t="n">
         <v>0.6172</v>
       </c>
+      <c r="AF239" t="n">
+        <v>0.9596888888888889</v>
+      </c>
       <c r="AG239" t="n">
         <v>0.7491499999999999</v>
       </c>
       <c r="AH239" t="n">
-        <v>0.6429555555555556</v>
+        <v>0.7546230769230768</v>
       </c>
       <c r="AI239" t="n">
         <v>0.8661999999999999</v>
@@ -17920,11 +18520,14 @@
       <c r="AC240" t="n">
         <v>0.5145076923076923</v>
       </c>
+      <c r="AF240" t="n">
+        <v>0.9402100000000001</v>
+      </c>
       <c r="AG240" t="n">
         <v>0.5813714285714287</v>
       </c>
       <c r="AH240" t="n">
-        <v>0.6098916666666667</v>
+        <v>0.6801</v>
       </c>
       <c r="AI240" t="n">
         <v>0.7905111111111112</v>
@@ -17994,11 +18597,14 @@
       <c r="AC241" t="n">
         <v>0.5498833333333334</v>
       </c>
+      <c r="AF241" t="n">
+        <v>0.9728625</v>
+      </c>
       <c r="AG241" t="n">
         <v>0.7499399999999999</v>
       </c>
       <c r="AH241" t="n">
-        <v>0.7305727272727274</v>
+        <v>0.6898375</v>
       </c>
       <c r="AI241" t="n">
         <v>0.7470818181818182</v>
@@ -18068,11 +18674,14 @@
       <c r="AC242" t="n">
         <v>0.5574333333333333</v>
       </c>
+      <c r="AF242" t="n">
+        <v>0.9638083333333335</v>
+      </c>
       <c r="AG242" t="n">
         <v>0.6617250000000001</v>
       </c>
       <c r="AH242" t="n">
-        <v>0.7224999999999999</v>
+        <v>0.6531600000000001</v>
       </c>
       <c r="AI242" t="n">
         <v>0.5965727272727274</v>
@@ -18142,11 +18751,14 @@
       <c r="AC243" t="n">
         <v>0.6808384615384615</v>
       </c>
+      <c r="AF243" t="n">
+        <v>0.9606555555555555</v>
+      </c>
       <c r="AG243" t="n">
         <v>0.7671</v>
       </c>
       <c r="AH243" t="n">
-        <v>0.6183333333333334</v>
+        <v>0.7296888888888887</v>
       </c>
       <c r="AI243" t="n">
         <v>0.7137785714285714</v>
@@ -18213,11 +18825,14 @@
       <c r="AC244" t="n">
         <v>0.6706454545454545</v>
       </c>
+      <c r="AF244" t="n">
+        <v>0.9681375</v>
+      </c>
       <c r="AG244" t="n">
         <v>0.6970500000000001</v>
       </c>
       <c r="AH244" t="n">
-        <v>0.7500916666666667</v>
+        <v>0.65759</v>
       </c>
       <c r="AI244" t="n">
         <v>0.7739833333333334</v>
@@ -18287,11 +18902,14 @@
       <c r="AC245" t="n">
         <v>0.7155166666666667</v>
       </c>
+      <c r="AF245" t="n">
+        <v>0.9090625</v>
+      </c>
       <c r="AG245" t="n">
         <v>0.5966222222222223</v>
       </c>
       <c r="AH245" t="n">
-        <v>0.7988111111111112</v>
+        <v>0.69676</v>
       </c>
       <c r="AI245" t="n">
         <v>0.654</v>
@@ -18361,11 +18979,14 @@
       <c r="AC246" t="n">
         <v>0.7414700000000001</v>
       </c>
+      <c r="AF246" t="n">
+        <v>0.95319</v>
+      </c>
       <c r="AG246" t="n">
         <v>0.6594750000000001</v>
       </c>
       <c r="AH246" t="n">
-        <v>0.7220333333333333</v>
+        <v>0.7759555555555555</v>
       </c>
       <c r="AI246" t="n">
         <v>0.551011111111111</v>
@@ -18432,11 +19053,14 @@
       <c r="AC247" t="n">
         <v>0.5861727272727273</v>
       </c>
+      <c r="AF247" t="n">
+        <v>0.9683428571428571</v>
+      </c>
       <c r="AG247" t="n">
         <v>0.5673</v>
       </c>
       <c r="AH247" t="n">
-        <v>0.6818636363636363</v>
+        <v>0.562875</v>
       </c>
       <c r="AI247" t="n">
         <v>0.5978249999999999</v>
@@ -18506,11 +19130,14 @@
       <c r="AC248" t="n">
         <v>0.5184846153846154</v>
       </c>
+      <c r="AF248" t="n">
+        <v>0.9591666666666666</v>
+      </c>
       <c r="AG248" t="n">
         <v>0.8148</v>
       </c>
       <c r="AH248" t="n">
-        <v>0.6484800000000001</v>
+        <v>0.8208545454545454</v>
       </c>
       <c r="AI248" t="n">
         <v>0.7105615384615382</v>
@@ -18580,11 +19207,14 @@
       <c r="AC249" t="n">
         <v>0.7905099999999999</v>
       </c>
+      <c r="AF249" t="n">
+        <v>0.9689909090909091</v>
+      </c>
       <c r="AG249" t="n">
         <v>0.7287000000000001</v>
       </c>
       <c r="AH249" t="n">
-        <v>0.6788500000000001</v>
+        <v>0.7957916666666668</v>
       </c>
       <c r="AI249" t="n">
         <v>0.6842090909090909</v>
@@ -18654,11 +19284,14 @@
       <c r="AC250" t="n">
         <v>0.8942272727272728</v>
       </c>
+      <c r="AF250" t="n">
+        <v>0.9500999999999999</v>
+      </c>
       <c r="AG250" t="n">
         <v>0.5727571428571429</v>
       </c>
       <c r="AH250" t="n">
-        <v>0.6896833333333333</v>
+        <v>0.6346200000000002</v>
       </c>
       <c r="AI250" t="n">
         <v>0.6877636363636364</v>
@@ -18728,11 +19361,14 @@
       <c r="AC251" t="n">
         <v>0.6176571428571427</v>
       </c>
+      <c r="AF251" t="n">
+        <v>0.9131222222222222</v>
+      </c>
       <c r="AG251" t="n">
         <v>0.6977142857142857</v>
       </c>
       <c r="AH251" t="n">
-        <v>0.5914272727272727</v>
+        <v>0.7200200000000001</v>
       </c>
       <c r="AI251" t="n">
         <v>0.7553833333333334</v>
@@ -18802,11 +19438,14 @@
       <c r="AC252" t="n">
         <v>0.6792333333333334</v>
       </c>
+      <c r="AF252" t="n">
+        <v>0.92581</v>
+      </c>
       <c r="AG252" t="n">
         <v>0.6966875</v>
       </c>
       <c r="AH252" t="n">
-        <v>0.6572249999999999</v>
+        <v>0.6347625</v>
       </c>
       <c r="AI252" t="n">
         <v>0.7040461538461538</v>
@@ -18876,11 +19515,14 @@
       <c r="AC253" t="n">
         <v>0.7642916666666667</v>
       </c>
+      <c r="AF253" t="n">
+        <v>0.92975</v>
+      </c>
       <c r="AG253" t="n">
         <v>0.5240571428571429</v>
       </c>
       <c r="AH253" t="n">
-        <v>0.801011111111111</v>
+        <v>0.6836333333333333</v>
       </c>
       <c r="AI253" t="n">
         <v>0.5232083333333333</v>
@@ -18950,11 +19592,14 @@
       <c r="AC254" t="n">
         <v>0.5722999999999999</v>
       </c>
+      <c r="AF254" t="n">
+        <v>0.9365444444444443</v>
+      </c>
       <c r="AG254" t="n">
         <v>0.6985874999999999</v>
       </c>
       <c r="AH254" t="n">
-        <v>0.6367444444444446</v>
+        <v>0.72095</v>
       </c>
       <c r="AI254" t="n">
         <v>0.7925636363636365</v>
@@ -19024,11 +19669,14 @@
       <c r="AC255" t="n">
         <v>0.7110769230769231</v>
       </c>
+      <c r="AF255" t="n">
+        <v>0.9512083333333333</v>
+      </c>
       <c r="AG255" t="n">
         <v>0.6282</v>
       </c>
       <c r="AH255" t="n">
-        <v>0.8117909090909093</v>
+        <v>0.7337699999999999</v>
       </c>
       <c r="AI255" t="n">
         <v>0.6208083333333333</v>
@@ -19098,11 +19746,14 @@
       <c r="AC256" t="n">
         <v>0.658525</v>
       </c>
+      <c r="AF256" t="n">
+        <v>0.9740777777777778</v>
+      </c>
       <c r="AG256" t="n">
         <v>0.6270749999999999</v>
       </c>
       <c r="AH256" t="n">
-        <v>0.7343083333333332</v>
+        <v>0.6538999999999999</v>
       </c>
       <c r="AI256" t="n">
         <v>0.7818818181818181</v>
@@ -19172,11 +19823,14 @@
       <c r="AC257" t="n">
         <v>0.6434928571428572</v>
       </c>
+      <c r="AF257" t="n">
+        <v>0.9580399999999999</v>
+      </c>
       <c r="AG257" t="n">
         <v>0.5711000000000001</v>
       </c>
       <c r="AH257" t="n">
-        <v>0.6896000000000001</v>
+        <v>0.6768900000000001</v>
       </c>
     </row>
     <row r="258" ht="16" customHeight="1" s="8">
@@ -19243,11 +19897,14 @@
       <c r="AC258" t="n">
         <v>0.6624100000000002</v>
       </c>
+      <c r="AF258" t="n">
+        <v>0.9643666666666666</v>
+      </c>
       <c r="AG258" t="n">
         <v>0.70428</v>
       </c>
       <c r="AH258" t="n">
-        <v>0.7345818181818182</v>
+        <v>0.6139727272727272</v>
       </c>
       <c r="AI258" t="n">
         <v>0.8083272727272728</v>
@@ -19317,11 +19974,14 @@
       <c r="AC259" t="n">
         <v>0.6921538461538461</v>
       </c>
+      <c r="AF259" t="n">
+        <v>0.9442699999999998</v>
+      </c>
       <c r="AG259" t="n">
         <v>0.58897</v>
       </c>
       <c r="AH259" t="n">
-        <v>0.715809090909091</v>
+        <v>0.8404555555555555</v>
       </c>
       <c r="AI259" t="n">
         <v>0.7523076923076922</v>
@@ -19391,11 +20051,14 @@
       <c r="AC260" t="n">
         <v>0.6954454545454546</v>
       </c>
+      <c r="AF260" t="n">
+        <v>0.9583000000000002</v>
+      </c>
       <c r="AG260" t="n">
         <v>0.6454</v>
       </c>
       <c r="AH260" t="n">
-        <v>0.7738699999999999</v>
+        <v>0.7544333333333332</v>
       </c>
       <c r="AI260" t="n">
         <v>0.866390909090909</v>
@@ -19465,11 +20128,14 @@
       <c r="AC261" t="n">
         <v>0.6671083333333333</v>
       </c>
+      <c r="AF261" t="n">
+        <v>0.9735099999999999</v>
+      </c>
       <c r="AG261" t="n">
         <v>0.6931181818181816</v>
       </c>
       <c r="AH261" t="n">
-        <v>0.7773</v>
+        <v>0.8121777777777779</v>
       </c>
       <c r="AI261" t="n">
         <v>0.732525</v>
@@ -19539,11 +20205,14 @@
       <c r="AC262" t="n">
         <v>0.7742166666666668</v>
       </c>
+      <c r="AF262" t="n">
+        <v>0.9576444444444445</v>
+      </c>
       <c r="AG262" t="n">
         <v>0.6600200000000001</v>
       </c>
       <c r="AH262" t="n">
-        <v>0.592575</v>
+        <v>0.7704666666666665</v>
       </c>
       <c r="AI262" t="n">
         <v>0.8668090909090908</v>
@@ -19613,11 +20282,14 @@
       <c r="AC263" t="n">
         <v>0.6933928571428573</v>
       </c>
+      <c r="AF263" t="n">
+        <v>0.952325</v>
+      </c>
       <c r="AG263" t="n">
         <v>0.4840125</v>
       </c>
       <c r="AH263" t="n">
-        <v>0.8530900000000001</v>
+        <v>0.63605</v>
       </c>
       <c r="AI263" t="n">
         <v>0.6957999999999999</v>
@@ -19687,11 +20359,14 @@
       <c r="AC264" t="n">
         <v>0.6937615384615383</v>
       </c>
+      <c r="AF264" t="n">
+        <v>0.93376</v>
+      </c>
       <c r="AG264" t="n">
         <v>0.6907166666666668</v>
       </c>
       <c r="AH264" t="n">
-        <v>0.6594555555555556</v>
+        <v>0.77083</v>
       </c>
       <c r="AI264" t="n">
         <v>0.7173818181818181</v>
@@ -19761,11 +20436,14 @@
       <c r="AC265" t="n">
         <v>0.6265599999999999</v>
       </c>
+      <c r="AF265" t="n">
+        <v>0.9130666666666666</v>
+      </c>
       <c r="AG265" t="n">
         <v>0.5547285714285713</v>
       </c>
       <c r="AH265" t="n">
-        <v>0.72148</v>
+        <v>0.6687777777777779</v>
       </c>
       <c r="AI265" t="n">
         <v>0.6610461538461537</v>
@@ -19835,11 +20513,14 @@
       <c r="AC266" t="n">
         <v>0.7003333333333334</v>
       </c>
+      <c r="AF266" t="n">
+        <v>0.9607222222222221</v>
+      </c>
       <c r="AG266" t="n">
         <v>0.56168</v>
       </c>
       <c r="AH266" t="n">
-        <v>0.6518571428571428</v>
+        <v>0.60616</v>
       </c>
       <c r="AI266" t="n">
         <v>0.6746272727272727</v>
@@ -19909,11 +20590,14 @@
       <c r="AC267" t="n">
         <v>0.6253416666666666</v>
       </c>
+      <c r="AF267" t="n">
+        <v>0.9539555555555554</v>
+      </c>
       <c r="AG267" t="n">
         <v>0.502</v>
       </c>
       <c r="AH267" t="n">
-        <v>0.7375999999999999</v>
+        <v>0.7156250000000001</v>
       </c>
       <c r="AI267" t="n">
         <v>0.9139363636363637</v>
@@ -19983,11 +20667,14 @@
       <c r="AC268" t="n">
         <v>0.7623416666666668</v>
       </c>
+      <c r="AF268" t="n">
+        <v>0.9650400000000001</v>
+      </c>
       <c r="AG268" t="n">
         <v>0.58985</v>
       </c>
       <c r="AH268" t="n">
-        <v>0.6406857142857144</v>
+        <v>0.7052222222222223</v>
       </c>
       <c r="AI268" t="n">
         <v>0.67318</v>
@@ -20057,11 +20744,14 @@
       <c r="AC269" t="n">
         <v>0.7108181818181818</v>
       </c>
+      <c r="AF269" t="n">
+        <v>0.9456999999999999</v>
+      </c>
       <c r="AG269" t="n">
         <v>0.5053444444444444</v>
       </c>
       <c r="AH269" t="n">
-        <v>0.6367333333333334</v>
+        <v>0.73471</v>
       </c>
       <c r="AI269" t="n">
         <v>0.7978499999999999</v>
@@ -20131,11 +20821,14 @@
       <c r="AC270" t="n">
         <v>0.58785</v>
       </c>
+      <c r="AF270" t="n">
+        <v>0.925118181818182</v>
+      </c>
       <c r="AG270" t="n">
         <v>0.5276777777777778</v>
       </c>
       <c r="AH270" t="n">
-        <v>0.5206142857142856</v>
+        <v>0.6290599999999998</v>
       </c>
       <c r="AI270" t="n">
         <v>0.6577642857142856</v>
@@ -20205,11 +20898,14 @@
       <c r="AC271" t="n">
         <v>0.5422833333333333</v>
       </c>
+      <c r="AF271" t="n">
+        <v>0.9696625000000001</v>
+      </c>
       <c r="AG271" t="n">
         <v>0.6467222222222222</v>
       </c>
       <c r="AH271" t="n">
-        <v>0.6225888888888889</v>
+        <v>0.8110444444444443</v>
       </c>
       <c r="AI271" t="n">
         <v>0.7966727272727273</v>
@@ -20279,11 +20975,14 @@
       <c r="AC272" t="n">
         <v>0.690523076923077</v>
       </c>
+      <c r="AF272" t="n">
+        <v>0.9061333333333335</v>
+      </c>
       <c r="AG272" t="n">
         <v>0.5596666666666668</v>
       </c>
       <c r="AH272" t="n">
-        <v>0.6169384615384617</v>
+        <v>0.6917666666666666</v>
       </c>
       <c r="AI272" t="n">
         <v>0.7604692307692307</v>
@@ -20353,11 +21052,14 @@
       <c r="AC273" t="n">
         <v>0.7784307692307691</v>
       </c>
+      <c r="AF273" t="n">
+        <v>0.9095333333333332</v>
+      </c>
       <c r="AG273" t="n">
         <v>0.4824888888888889</v>
       </c>
       <c r="AH273" t="n">
-        <v>0.7008875000000001</v>
+        <v>0.6991769230769231</v>
       </c>
       <c r="AI273" t="n">
         <v>0.6132111111111112</v>
@@ -20427,11 +21129,14 @@
       <c r="AC274" t="n">
         <v>0.6181</v>
       </c>
+      <c r="AF274" t="n">
+        <v>0.9260444444444444</v>
+      </c>
       <c r="AG274" t="n">
         <v>0.6259555555555556</v>
       </c>
       <c r="AH274" t="n">
-        <v>0.7708625</v>
+        <v>0.6227384615384615</v>
       </c>
       <c r="AI274" t="n">
         <v>0.7624749999999999</v>
@@ -20501,11 +21206,14 @@
       <c r="AC275" t="n">
         <v>0.6315727272727272</v>
       </c>
+      <c r="AF275" t="n">
+        <v>0.9708500000000001</v>
+      </c>
       <c r="AG275" t="n">
         <v>0.6092875</v>
       </c>
       <c r="AH275" t="n">
-        <v>0.63719</v>
+        <v>0.7856222222222222</v>
       </c>
       <c r="AI275" t="n">
         <v>0.7679000000000001</v>
@@ -20575,11 +21283,14 @@
       <c r="AC276" t="n">
         <v>0.8835272727272727</v>
       </c>
+      <c r="AF276" t="n">
+        <v>0.9234571428571429</v>
+      </c>
       <c r="AG276" t="n">
         <v>0.6101555555555556</v>
       </c>
       <c r="AH276" t="n">
-        <v>0.6113625</v>
+        <v>0.65947</v>
       </c>
       <c r="AI276" t="n">
         <v>0.6080375000000001</v>
@@ -20649,11 +21360,14 @@
       <c r="AC277" t="n">
         <v>0.6828615384615385</v>
       </c>
+      <c r="AF277" t="n">
+        <v>0.9710333333333333</v>
+      </c>
       <c r="AG277" t="n">
         <v>0.6498857142857143</v>
       </c>
       <c r="AH277" t="n">
-        <v>0.7692444444444444</v>
+        <v>0.6299333333333332</v>
       </c>
       <c r="AI277" t="n">
         <v>0.6941900000000001</v>
@@ -20723,11 +21437,14 @@
       <c r="AC278" t="n">
         <v>0.6131500000000001</v>
       </c>
+      <c r="AF278" t="n">
+        <v>0.9394500000000001</v>
+      </c>
       <c r="AG278" t="n">
         <v>0.509125</v>
       </c>
       <c r="AH278" t="n">
-        <v>0.5251777777777779</v>
+        <v>0.7401999999999999</v>
       </c>
       <c r="AI278" t="n">
         <v>0.5813875000000001</v>
@@ -20797,11 +21514,14 @@
       <c r="AC279" t="n">
         <v>0.784</v>
       </c>
+      <c r="AF279" t="n">
+        <v>0.8977375000000002</v>
+      </c>
       <c r="AG279" t="n">
         <v>0.7049666666666667</v>
       </c>
       <c r="AH279" t="n">
-        <v>0.80449</v>
+        <v>0.78905</v>
       </c>
       <c r="AI279" t="n">
         <v>0.701675</v>
@@ -20871,11 +21591,14 @@
       <c r="AC280" t="n">
         <v>0.5932727272727273</v>
       </c>
+      <c r="AF280" t="n">
+        <v>0.9686499999999999</v>
+      </c>
       <c r="AG280" t="n">
         <v>0.7653125000000001</v>
       </c>
       <c r="AH280" t="n">
-        <v>0.6073750000000001</v>
+        <v>0.7223888888888889</v>
       </c>
       <c r="AI280" t="n">
         <v>0.7212833333333334</v>
@@ -20945,11 +21668,14 @@
       <c r="AC281" t="n">
         <v>0.510776923076923</v>
       </c>
+      <c r="AF281" t="n">
+        <v>0.9368400000000001</v>
+      </c>
       <c r="AG281" t="n">
         <v>0.6362000000000001</v>
       </c>
       <c r="AH281" t="n">
-        <v>0.666525</v>
+        <v>0.7156300000000001</v>
       </c>
       <c r="AI281" t="n">
         <v>0.6912166666666667</v>
@@ -21019,11 +21745,14 @@
       <c r="AC282" t="n">
         <v>0.6183916666666667</v>
       </c>
+      <c r="AF282" t="n">
+        <v>0.9299833333333334</v>
+      </c>
       <c r="AG282" t="n">
         <v>0.6117833333333333</v>
       </c>
       <c r="AH282" t="n">
-        <v>0.6465818181818181</v>
+        <v>0.7188666666666667</v>
       </c>
       <c r="AI282" t="n">
         <v>0.7964818181818182</v>
@@ -21093,11 +21822,14 @@
       <c r="AC283" t="n">
         <v>0.5914</v>
       </c>
+      <c r="AF283" t="n">
+        <v>0.9559000000000001</v>
+      </c>
       <c r="AG283" t="n">
         <v>0.6411428571428572</v>
       </c>
       <c r="AH283" t="n">
-        <v>0.6680333333333334</v>
+        <v>0.6730900000000001</v>
       </c>
       <c r="AI283" t="n">
         <v>0.6120642857142856</v>
@@ -21167,11 +21899,14 @@
       <c r="AC284" t="n">
         <v>0.4789100000000001</v>
       </c>
+      <c r="AF284" t="n">
+        <v>0.9512777777777779</v>
+      </c>
       <c r="AG284" t="n">
         <v>0.6673428571428571</v>
       </c>
       <c r="AH284" t="n">
-        <v>0.7922199999999999</v>
+        <v>0.81541</v>
       </c>
       <c r="AI284" t="n">
         <v>0.7942444444444444</v>
@@ -21238,11 +21973,14 @@
       <c r="AC285" t="n">
         <v>0.789875</v>
       </c>
+      <c r="AF285" t="n">
+        <v>0.9725</v>
+      </c>
       <c r="AG285" t="n">
         <v>0.7033700000000001</v>
       </c>
       <c r="AH285" t="n">
-        <v>0.8504909090909091</v>
+        <v>0.6436545454545455</v>
       </c>
       <c r="AI285" t="n">
         <v>0.6682333333333333</v>
@@ -21312,11 +22050,14 @@
       <c r="AC286" t="n">
         <v>0.61785</v>
       </c>
+      <c r="AF286" t="n">
+        <v>0.9302083333333333</v>
+      </c>
       <c r="AG286" t="n">
         <v>0.5954777777777778</v>
       </c>
       <c r="AH286" t="n">
-        <v>0.6757444444444445</v>
+        <v>0.8249923076923076</v>
       </c>
       <c r="AI286" t="n">
         <v>0.557975</v>
@@ -21386,11 +22127,14 @@
       <c r="AC287" t="n">
         <v>0.6519833333333335</v>
       </c>
+      <c r="AF287" t="n">
+        <v>0.9228000000000001</v>
+      </c>
       <c r="AG287" t="n">
         <v>0.8079499999999999</v>
       </c>
       <c r="AH287" t="n">
-        <v>0.6121555555555556</v>
+        <v>0.6118636363636364</v>
       </c>
       <c r="AI287" t="n">
         <v>0.6525166666666666</v>
@@ -21460,11 +22204,14 @@
       <c r="AC288" t="n">
         <v>0.5246099999999999</v>
       </c>
+      <c r="AF288" t="n">
+        <v>0.966377777777778</v>
+      </c>
       <c r="AG288" t="n">
         <v>0.6327363636363635</v>
       </c>
       <c r="AH288" t="n">
-        <v>0.8393875000000001</v>
+        <v>0.6404500000000001</v>
       </c>
       <c r="AI288" t="n">
         <v>0.7697272727272728</v>
@@ -21534,11 +22281,14 @@
       <c r="AC289" t="n">
         <v>0.7857416666666667</v>
       </c>
+      <c r="AF289" t="n">
+        <v>0.9063555555555557</v>
+      </c>
       <c r="AG289" t="n">
         <v>0.7100363636363637</v>
       </c>
       <c r="AH289" t="n">
-        <v>0.58272</v>
+        <v>0.7069799999999999</v>
       </c>
       <c r="AI289" t="n">
         <v>0.7886666666666667</v>
@@ -21608,11 +22358,14 @@
       <c r="AC290" t="n">
         <v>0.6232642857142858</v>
       </c>
+      <c r="AF290" t="n">
+        <v>0.95885</v>
+      </c>
       <c r="AG290" t="n">
         <v>0.6602500000000001</v>
       </c>
       <c r="AH290" t="n">
-        <v>0.7600727272727273</v>
+        <v>0.787709090909091</v>
       </c>
       <c r="AI290" t="n">
         <v>0.6970333333333334</v>
@@ -21682,11 +22435,14 @@
       <c r="AC291" t="n">
         <v>0.7201307692307691</v>
       </c>
+      <c r="AF291" t="n">
+        <v>0.9317727272727272</v>
+      </c>
       <c r="AG291" t="n">
         <v>0.7329777777777778</v>
       </c>
       <c r="AH291" t="n">
-        <v>0.69635</v>
+        <v>0.7134833333333335</v>
       </c>
       <c r="AI291" t="n">
         <v>0.74704</v>
@@ -21756,11 +22512,14 @@
       <c r="AC292" t="n">
         <v>0.7859545454545455</v>
       </c>
+      <c r="AF292" t="n">
+        <v>0.9765727272727273</v>
+      </c>
       <c r="AG292" t="n">
         <v>0.5553375</v>
       </c>
       <c r="AH292" t="n">
-        <v>0.75748</v>
+        <v>0.77411</v>
       </c>
       <c r="AI292" t="n">
         <v>0.6335333333333334</v>
@@ -21830,11 +22589,14 @@
       <c r="AC293" t="n">
         <v>0.7449</v>
       </c>
+      <c r="AF293" t="n">
+        <v>0.9513888888888888</v>
+      </c>
       <c r="AG293" t="n">
         <v>0.4731625</v>
       </c>
       <c r="AH293" t="n">
-        <v>0.5494</v>
+        <v>0.6763454545454545</v>
       </c>
       <c r="AI293" t="n">
         <v>0.717190909090909</v>
@@ -21904,11 +22666,14 @@
       <c r="AC294" t="n">
         <v>0.51884</v>
       </c>
+      <c r="AF294" t="n">
+        <v>0.9637727272727272</v>
+      </c>
       <c r="AG294" t="n">
         <v>0.5788099999999999</v>
       </c>
       <c r="AH294" t="n">
-        <v>0.6747875</v>
+        <v>0.6251333333333334</v>
       </c>
       <c r="AI294" t="n">
         <v>0.6918</v>
@@ -21978,11 +22743,14 @@
       <c r="AC295" t="n">
         <v>0.7127916666666666</v>
       </c>
+      <c r="AF295" t="n">
+        <v>0.9123249999999999</v>
+      </c>
       <c r="AG295" t="n">
         <v>0.6827545454545454</v>
       </c>
       <c r="AH295" t="n">
-        <v>0.7490999999999999</v>
+        <v>0.7019</v>
       </c>
       <c r="AI295" t="n">
         <v>0.6006166666666667</v>
@@ -22052,11 +22820,14 @@
       <c r="AC296" t="n">
         <v>0.7771363636363637</v>
       </c>
+      <c r="AF296" t="n">
+        <v>0.9691727272727273</v>
+      </c>
       <c r="AG296" t="n">
         <v>0.5544400000000002</v>
       </c>
       <c r="AH296" t="n">
-        <v>0.7139</v>
+        <v>0.9034125</v>
       </c>
       <c r="AI296" t="n">
         <v>0.6607090909090909</v>
@@ -22126,11 +22897,14 @@
       <c r="AC297" t="n">
         <v>0.7240090909090908</v>
       </c>
+      <c r="AF297" t="n">
+        <v>0.9682571428571428</v>
+      </c>
       <c r="AG297" t="n">
         <v>0.5004222222222222</v>
       </c>
       <c r="AH297" t="n">
-        <v>0.3509875</v>
+        <v>0.8128833333333333</v>
       </c>
       <c r="AI297" t="n">
         <v>0.6926916666666666</v>
@@ -22204,7 +22978,7 @@
         <v>0.6577888888888889</v>
       </c>
       <c r="AH298" t="n">
-        <v>0.6662625</v>
+        <v>0.6126142857142857</v>
       </c>
       <c r="AI298" t="n">
         <v>0.7512545454545454</v>
@@ -22278,7 +23052,7 @@
         <v>0.5005727272727273</v>
       </c>
       <c r="AH299" t="n">
-        <v>0.78474</v>
+        <v>0.8563285714285714</v>
       </c>
       <c r="AI299" t="n">
         <v>0.79486</v>
@@ -22352,7 +23126,7 @@
         <v>0.4616125</v>
       </c>
       <c r="AH300" t="n">
-        <v>0.4238400000000001</v>
+        <v>0.73077</v>
       </c>
       <c r="AI300" t="n">
         <v>0.6619250000000001</v>
@@ -22426,7 +23200,7 @@
         <v>0.548025</v>
       </c>
       <c r="AH301" t="n">
-        <v>0.691975</v>
+        <v>0.7375333333333334</v>
       </c>
       <c r="AI301" t="n">
         <v>0.6759833333333333</v>
@@ -22500,7 +23274,7 @@
         <v>0.7055666666666668</v>
       </c>
       <c r="AH302" t="n">
-        <v>0.6433785714285715</v>
+        <v>0.7329363636363637</v>
       </c>
       <c r="AI302" t="n">
         <v>0.8137363636363637</v>
@@ -22574,7 +23348,7 @@
         <v>0.7041666666666667</v>
       </c>
       <c r="AH303" t="n">
-        <v>0.7767666666666666</v>
+        <v>0.6316555555555555</v>
       </c>
       <c r="AI303" t="n">
         <v>0.6278818181818181</v>
@@ -22648,7 +23422,7 @@
         <v>0.6187666666666667</v>
       </c>
       <c r="AH304" t="n">
-        <v>0.6414272727272727</v>
+        <v>0.5893777777777778</v>
       </c>
       <c r="AI304" t="n">
         <v>0.6649999999999999</v>
@@ -22722,7 +23496,7 @@
         <v>0.5088625</v>
       </c>
       <c r="AH305" t="n">
-        <v>0.75671</v>
+        <v>0.7822799999999999</v>
       </c>
       <c r="AI305" t="n">
         <v>0.7369615384615383</v>
@@ -22796,7 +23570,7 @@
         <v>0.6848909090909091</v>
       </c>
       <c r="AH306" t="n">
-        <v>0.7481833333333334</v>
+        <v>0.6386166666666667</v>
       </c>
       <c r="AI306" t="n">
         <v>0.5822999999999999</v>
@@ -22870,7 +23644,7 @@
         <v>0.6076777777777778</v>
       </c>
       <c r="AH307" t="n">
-        <v>0.586690909090909</v>
+        <v>0.7356076923076924</v>
       </c>
       <c r="AI307" t="n">
         <v>0.6626199999999999</v>
@@ -22944,7 +23718,7 @@
         <v>0.6058285714285715</v>
       </c>
       <c r="AH308" t="n">
-        <v>0.5873666666666667</v>
+        <v>0.6588444444444445</v>
       </c>
       <c r="AI308" t="n">
         <v>0.6873090909090909</v>
@@ -23018,7 +23792,7 @@
         <v>0.6448333333333333</v>
       </c>
       <c r="AH309" t="n">
-        <v>0.5850636363636363</v>
+        <v>0.6969777777777778</v>
       </c>
       <c r="AI309" t="n">
         <v>0.7913444444444444</v>
@@ -23092,7 +23866,7 @@
         <v>0.67424</v>
       </c>
       <c r="AH310" t="n">
-        <v>0.6983416666666667</v>
+        <v>0.7597499999999999</v>
       </c>
       <c r="AI310" t="n">
         <v>0.8221999999999999</v>
@@ -23166,7 +23940,7 @@
         <v>0.5765636363636364</v>
       </c>
       <c r="AH311" t="n">
-        <v>0.7975909090909091</v>
+        <v>0.9009714285714285</v>
       </c>
       <c r="AI311" t="n">
         <v>0.7314700000000001</v>
@@ -23269,11 +24043,14 @@
       <c r="AC316" t="n">
         <v>0</v>
       </c>
+      <c r="AF316" t="n">
+        <v>0.2444</v>
+      </c>
       <c r="AG316" t="n">
         <v>0.0001</v>
       </c>
       <c r="AH316" t="n">
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="AI316" t="n">
         <v>0.0003</v>
@@ -23352,11 +24129,14 @@
       <c r="AC317" t="n">
         <v>0.0005</v>
       </c>
+      <c r="AF317" t="n">
+        <v>0.003</v>
+      </c>
       <c r="AG317" t="n">
         <v>0.0011</v>
       </c>
       <c r="AH317" t="n">
-        <v>0.0022</v>
+        <v>0.0077</v>
       </c>
       <c r="AI317" t="n">
         <v>0.0003</v>
@@ -23435,11 +24215,14 @@
       <c r="AC318" t="n">
         <v>0.0185</v>
       </c>
+      <c r="AF318" t="n">
+        <v>0.2789</v>
+      </c>
       <c r="AG318" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="AH318" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0053</v>
       </c>
       <c r="AI318" t="n">
         <v>0.0005</v>
@@ -23518,11 +24301,14 @@
       <c r="AC319" t="n">
         <v>0.0504</v>
       </c>
+      <c r="AF319" t="n">
+        <v>0.292</v>
+      </c>
       <c r="AG319" t="n">
         <v>0.0327</v>
       </c>
       <c r="AH319" t="n">
-        <v>0.0472</v>
+        <v>0.0025</v>
       </c>
       <c r="AI319" t="n">
         <v>0.0034</v>
@@ -23601,11 +24387,14 @@
       <c r="AC320" t="n">
         <v>0.0428</v>
       </c>
+      <c r="AF320" t="n">
+        <v>0.4507</v>
+      </c>
       <c r="AG320" t="n">
         <v>0.0883</v>
       </c>
       <c r="AH320" t="n">
-        <v>0.032</v>
+        <v>0.0124</v>
       </c>
       <c r="AI320" t="n">
         <v>0.0159</v>
@@ -23684,11 +24473,14 @@
       <c r="AC321" t="n">
         <v>0.0482</v>
       </c>
+      <c r="AF321" t="n">
+        <v>0.7766999999999999</v>
+      </c>
       <c r="AG321" t="n">
         <v>0.029</v>
       </c>
       <c r="AH321" t="n">
-        <v>0.0541</v>
+        <v>0.0159</v>
       </c>
       <c r="AI321" t="n">
         <v>0.0357</v>
@@ -23767,11 +24559,14 @@
       <c r="AC322" t="n">
         <v>0.0514</v>
       </c>
+      <c r="AF322" t="n">
+        <v>0.6784</v>
+      </c>
       <c r="AG322" t="n">
         <v>0.0738</v>
       </c>
       <c r="AH322" t="n">
-        <v>0.0992</v>
+        <v>0.0427</v>
       </c>
       <c r="AI322" t="n">
         <v>0.0247</v>
@@ -23850,11 +24645,14 @@
       <c r="AC323" t="n">
         <v>0.0683</v>
       </c>
+      <c r="AF323" t="n">
+        <v>0.7995</v>
+      </c>
       <c r="AG323" t="n">
         <v>0.0521</v>
       </c>
       <c r="AH323" t="n">
-        <v>0.1524</v>
+        <v>0.0968</v>
       </c>
       <c r="AI323" t="n">
         <v>0</v>
@@ -23933,11 +24731,14 @@
       <c r="AC324" t="n">
         <v>0.0605</v>
       </c>
+      <c r="AF324" t="n">
+        <v>0.8919</v>
+      </c>
       <c r="AG324" t="n">
         <v>0.0775</v>
       </c>
       <c r="AH324" t="n">
-        <v>0.0772</v>
+        <v>0.0674</v>
       </c>
       <c r="AI324" t="n">
         <v>0.0677</v>
@@ -24016,11 +24817,14 @@
       <c r="AC325" t="n">
         <v>0.0073</v>
       </c>
+      <c r="AF325" t="n">
+        <v>0.8874</v>
+      </c>
       <c r="AG325" t="n">
         <v>0.07779999999999999</v>
       </c>
       <c r="AH325" t="n">
-        <v>0.0636</v>
+        <v>0.1055</v>
       </c>
       <c r="AI325" t="n">
         <v>0.0137</v>
@@ -24090,11 +24894,14 @@
       <c r="AC326" t="n">
         <v>0.0274</v>
       </c>
+      <c r="AF326" t="n">
+        <v>0.8756</v>
+      </c>
       <c r="AG326" t="n">
         <v>0.1193</v>
       </c>
       <c r="AH326" t="n">
-        <v>0.048</v>
+        <v>0.094</v>
       </c>
       <c r="AI326" t="n">
         <v>0.0101</v>
@@ -24164,11 +24971,14 @@
       <c r="AC327" t="n">
         <v>0.0547</v>
       </c>
+      <c r="AF327" t="n">
+        <v>0.892</v>
+      </c>
       <c r="AG327" t="n">
         <v>0.0999</v>
       </c>
       <c r="AH327" t="n">
-        <v>0.0391</v>
+        <v>0.1043</v>
       </c>
       <c r="AI327" t="n">
         <v>0.0092</v>
@@ -24238,11 +25048,14 @@
       <c r="AC328" t="n">
         <v>0.083</v>
       </c>
+      <c r="AF328" t="n">
+        <v>0.8887</v>
+      </c>
       <c r="AG328" t="n">
         <v>0.1124</v>
       </c>
       <c r="AH328" t="n">
-        <v>0.0984</v>
+        <v>0.0906</v>
       </c>
       <c r="AI328" t="n">
         <v>0.0363</v>
@@ -24312,11 +25125,14 @@
       <c r="AC329" t="n">
         <v>0.0585</v>
       </c>
+      <c r="AF329" t="n">
+        <v>0.901</v>
+      </c>
       <c r="AG329" t="n">
         <v>0.1336</v>
       </c>
       <c r="AH329" t="n">
-        <v>0.0669</v>
+        <v>0.0515</v>
       </c>
       <c r="AI329" t="n">
         <v>0.0482</v>
@@ -24386,11 +25202,14 @@
       <c r="AC330" t="n">
         <v>0.1335</v>
       </c>
+      <c r="AF330" t="n">
+        <v>0.9278</v>
+      </c>
       <c r="AG330" t="n">
         <v>0.1333</v>
       </c>
       <c r="AH330" t="n">
-        <v>0.0591</v>
+        <v>0.1432</v>
       </c>
       <c r="AI330" t="n">
         <v>0.0463</v>
@@ -24460,11 +25279,14 @@
       <c r="AC331" t="n">
         <v>0.0939</v>
       </c>
+      <c r="AF331" t="n">
+        <v>0.9494</v>
+      </c>
       <c r="AG331" t="n">
         <v>0.123</v>
       </c>
       <c r="AH331" t="n">
-        <v>0.0693</v>
+        <v>0.0859</v>
       </c>
       <c r="AI331" t="n">
         <v>0.0259</v>
@@ -24534,11 +25356,14 @@
       <c r="AC332" t="n">
         <v>0.0735</v>
       </c>
+      <c r="AF332" t="n">
+        <v>0.9589</v>
+      </c>
       <c r="AG332" t="n">
         <v>0.1625</v>
       </c>
       <c r="AH332" t="n">
-        <v>0.0467</v>
+        <v>0.0835</v>
       </c>
       <c r="AI332" t="n">
         <v>0.0474</v>
@@ -24608,11 +25433,14 @@
       <c r="AC333" t="n">
         <v>0.0921</v>
       </c>
+      <c r="AF333" t="n">
+        <v>0.9618</v>
+      </c>
       <c r="AG333" t="n">
         <v>0.0973</v>
       </c>
       <c r="AH333" t="n">
-        <v>0.0684</v>
+        <v>0.0785</v>
       </c>
       <c r="AI333" t="n">
         <v>0.0008</v>
@@ -24682,11 +25510,14 @@
       <c r="AC334" t="n">
         <v>0.07770000000000001</v>
       </c>
+      <c r="AF334" t="n">
+        <v>0.9372</v>
+      </c>
       <c r="AG334" t="n">
         <v>0.098</v>
       </c>
       <c r="AH334" t="n">
-        <v>0.0718</v>
+        <v>0.062</v>
       </c>
       <c r="AI334" t="n">
         <v>0.0188</v>
@@ -24756,11 +25587,14 @@
       <c r="AC335" t="n">
         <v>0.1596</v>
       </c>
+      <c r="AF335" t="n">
+        <v>0.9548</v>
+      </c>
       <c r="AG335" t="n">
         <v>0.098</v>
       </c>
       <c r="AH335" t="n">
-        <v>0.0532</v>
+        <v>0.0828</v>
       </c>
       <c r="AI335" t="n">
         <v>0.0188</v>
@@ -24830,11 +25664,14 @@
       <c r="AC336" t="n">
         <v>0.1138</v>
       </c>
+      <c r="AF336" t="n">
+        <v>0.9502</v>
+      </c>
       <c r="AG336" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="AH336" t="n">
-        <v>0.0394</v>
+        <v>0.0706</v>
       </c>
       <c r="AI336" t="n">
         <v>0.0442</v>
@@ -24904,11 +25741,14 @@
       <c r="AC337" t="n">
         <v>0.1322</v>
       </c>
+      <c r="AF337" t="n">
+        <v>0.9597</v>
+      </c>
       <c r="AG337" t="n">
         <v>0.1092</v>
       </c>
       <c r="AH337" t="n">
-        <v>0.0515</v>
+        <v>0.0441</v>
       </c>
       <c r="AI337" t="n">
         <v>0.0232</v>
@@ -24978,11 +25818,14 @@
       <c r="AC338" t="n">
         <v>0.132</v>
       </c>
+      <c r="AF338" t="n">
+        <v>0.9573</v>
+      </c>
       <c r="AG338" t="n">
         <v>0.174</v>
       </c>
       <c r="AH338" t="n">
-        <v>0.0469</v>
+        <v>0.0556</v>
       </c>
       <c r="AI338" t="n">
         <v>0.0334</v>
@@ -25052,11 +25895,14 @@
       <c r="AC339" t="n">
         <v>0.0704</v>
       </c>
+      <c r="AF339" t="n">
+        <v>0.9664</v>
+      </c>
       <c r="AG339" t="n">
         <v>0.1212</v>
       </c>
       <c r="AH339" t="n">
-        <v>0.0434</v>
+        <v>0.0571</v>
       </c>
       <c r="AI339" t="n">
         <v>0.0115</v>
@@ -25126,11 +25972,14 @@
       <c r="AC340" t="n">
         <v>0.0622</v>
       </c>
+      <c r="AF340" t="n">
+        <v>0.9628</v>
+      </c>
       <c r="AG340" t="n">
         <v>0.1672</v>
       </c>
       <c r="AH340" t="n">
-        <v>0.031</v>
+        <v>0.0408</v>
       </c>
       <c r="AI340" t="n">
         <v>0.0327</v>
@@ -25200,11 +26049,14 @@
       <c r="AC341" t="n">
         <v>0.0709</v>
       </c>
+      <c r="AF341" t="n">
+        <v>0.9562</v>
+      </c>
       <c r="AG341" t="n">
         <v>0.1078</v>
       </c>
       <c r="AH341" t="n">
-        <v>0.0621</v>
+        <v>0.0573</v>
       </c>
       <c r="AI341" t="n">
         <v>0.0213</v>
@@ -25274,11 +26126,14 @@
       <c r="AC342" t="n">
         <v>0.0992</v>
       </c>
+      <c r="AF342" t="n">
+        <v>0.9653</v>
+      </c>
       <c r="AG342" t="n">
         <v>0.0973</v>
       </c>
       <c r="AH342" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0582</v>
       </c>
       <c r="AI342" t="n">
         <v>0.0279</v>
@@ -25348,11 +26203,14 @@
       <c r="AC343" t="n">
         <v>0.0813</v>
       </c>
+      <c r="AF343" t="n">
+        <v>0.9663</v>
+      </c>
       <c r="AG343" t="n">
         <v>0.1529</v>
       </c>
       <c r="AH343" t="n">
-        <v>0.0615</v>
+        <v>0.1107</v>
       </c>
       <c r="AI343" t="n">
         <v>0.0208</v>
@@ -25422,11 +26280,14 @@
       <c r="AC344" t="n">
         <v>0.1049</v>
       </c>
+      <c r="AF344" t="n">
+        <v>0.9695</v>
+      </c>
       <c r="AG344" t="n">
         <v>0.1</v>
       </c>
       <c r="AH344" t="n">
-        <v>0.0654</v>
+        <v>0.0822</v>
       </c>
       <c r="AI344" t="n">
         <v>0.0244</v>
@@ -25496,11 +26357,14 @@
       <c r="AC345" t="n">
         <v>0.1039</v>
       </c>
+      <c r="AF345" t="n">
+        <v>0.973</v>
+      </c>
       <c r="AG345" t="n">
         <v>0.1345</v>
       </c>
       <c r="AH345" t="n">
-        <v>0.0574</v>
+        <v>0.0785</v>
       </c>
       <c r="AI345" t="n">
         <v>0.0138</v>
@@ -25570,11 +26434,14 @@
       <c r="AC346" t="n">
         <v>0.06619999999999999</v>
       </c>
+      <c r="AF346" t="n">
+        <v>0.981</v>
+      </c>
       <c r="AG346" t="n">
         <v>0.1275</v>
       </c>
       <c r="AH346" t="n">
-        <v>0.055</v>
+        <v>0.0611</v>
       </c>
       <c r="AI346" t="n">
         <v>0.0371</v>
@@ -25644,11 +26511,14 @@
       <c r="AC347" t="n">
         <v>0.0741</v>
       </c>
+      <c r="AF347" t="n">
+        <v>0.9772999999999999</v>
+      </c>
       <c r="AG347" t="n">
         <v>0.101</v>
       </c>
       <c r="AH347" t="n">
-        <v>0.0512</v>
+        <v>0.0636</v>
       </c>
       <c r="AI347" t="n">
         <v>0.0214</v>
@@ -25718,11 +26588,14 @@
       <c r="AC348" t="n">
         <v>0.07389999999999999</v>
       </c>
+      <c r="AF348" t="n">
+        <v>0.9681999999999999</v>
+      </c>
       <c r="AG348" t="n">
         <v>0.1233</v>
       </c>
       <c r="AH348" t="n">
-        <v>0.0588</v>
+        <v>0.0667</v>
       </c>
       <c r="AI348" t="n">
         <v>0.025</v>
@@ -25792,11 +26665,14 @@
       <c r="AC349" t="n">
         <v>0.07389999999999999</v>
       </c>
+      <c r="AF349" t="n">
+        <v>0.9636</v>
+      </c>
       <c r="AG349" t="n">
         <v>0.1487</v>
       </c>
       <c r="AH349" t="n">
-        <v>0.0649</v>
+        <v>0.0741</v>
       </c>
       <c r="AI349" t="n">
         <v>0.03</v>
@@ -25866,11 +26742,14 @@
       <c r="AC350" t="n">
         <v>0.07389999999999999</v>
       </c>
+      <c r="AF350" t="n">
+        <v>0.9653</v>
+      </c>
       <c r="AG350" t="n">
         <v>0.1065</v>
       </c>
       <c r="AH350" t="n">
-        <v>0.0545</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AI350" t="n">
         <v>0.0275</v>
@@ -25940,11 +26819,14 @@
       <c r="AC351" t="n">
         <v>0.0712</v>
       </c>
+      <c r="AF351" t="n">
+        <v>0.9655</v>
+      </c>
       <c r="AG351" t="n">
         <v>0.1043</v>
       </c>
       <c r="AH351" t="n">
-        <v>0.0556</v>
+        <v>0.0906</v>
       </c>
       <c r="AI351" t="n">
         <v>0.0177</v>
@@ -26014,11 +26896,14 @@
       <c r="AC352" t="n">
         <v>0.055</v>
       </c>
+      <c r="AF352" t="n">
+        <v>0.9714</v>
+      </c>
       <c r="AG352" t="n">
         <v>0.113</v>
       </c>
       <c r="AH352" t="n">
-        <v>0.0622</v>
+        <v>0.0521</v>
       </c>
       <c r="AI352" t="n">
         <v>0.0144</v>
@@ -26088,11 +26973,14 @@
       <c r="AC353" t="n">
         <v>0.06</v>
       </c>
+      <c r="AF353" t="n">
+        <v>0.9758</v>
+      </c>
       <c r="AG353" t="n">
         <v>0.1133</v>
       </c>
       <c r="AH353" t="n">
-        <v>0.043</v>
+        <v>0.0619</v>
       </c>
       <c r="AI353" t="n">
         <v>0.0124</v>
@@ -26162,11 +27050,14 @@
       <c r="AC354" t="n">
         <v>0.06</v>
       </c>
+      <c r="AF354" t="n">
+        <v>0.9769</v>
+      </c>
       <c r="AG354" t="n">
         <v>0.1105</v>
       </c>
       <c r="AH354" t="n">
-        <v>0.0466</v>
+        <v>0.0594</v>
       </c>
       <c r="AI354" t="n">
         <v>0.008500000000000001</v>
@@ -26236,11 +27127,14 @@
       <c r="AC355" t="n">
         <v>0.07049999999999999</v>
       </c>
+      <c r="AF355" t="n">
+        <v>0.9715</v>
+      </c>
       <c r="AG355" t="n">
         <v>0.1289</v>
       </c>
       <c r="AH355" t="n">
-        <v>0.0496</v>
+        <v>0.05</v>
       </c>
       <c r="AI355" t="n">
         <v>0.0208</v>
@@ -26310,11 +27204,14 @@
       <c r="AC356" t="n">
         <v>0.08260000000000001</v>
       </c>
+      <c r="AF356" t="n">
+        <v>0.9637</v>
+      </c>
       <c r="AG356" t="n">
         <v>0.0897</v>
       </c>
       <c r="AH356" t="n">
-        <v>0.0484</v>
+        <v>0.0536</v>
       </c>
       <c r="AI356" t="n">
         <v>0.0249</v>
@@ -26384,11 +27281,14 @@
       <c r="AC357" t="n">
         <v>0.1074</v>
       </c>
+      <c r="AF357" t="n">
+        <v>0.9631</v>
+      </c>
       <c r="AG357" t="n">
         <v>0.1079</v>
       </c>
       <c r="AH357" t="n">
-        <v>0.0595</v>
+        <v>0.0558</v>
       </c>
       <c r="AI357" t="n">
         <v>0.0091</v>
@@ -26458,11 +27358,14 @@
       <c r="AC358" t="n">
         <v>0.1081</v>
       </c>
+      <c r="AF358" t="n">
+        <v>0.9681</v>
+      </c>
       <c r="AG358" t="n">
         <v>0.1009</v>
       </c>
       <c r="AH358" t="n">
-        <v>0.0467</v>
+        <v>0.0534</v>
       </c>
       <c r="AI358" t="n">
         <v>0.0264</v>
@@ -26532,11 +27435,14 @@
       <c r="AC359" t="n">
         <v>0.0649</v>
       </c>
+      <c r="AF359" t="n">
+        <v>0.9815</v>
+      </c>
       <c r="AG359" t="n">
         <v>0.1047</v>
       </c>
       <c r="AH359" t="n">
-        <v>0.0463</v>
+        <v>0.0567</v>
       </c>
       <c r="AI359" t="n">
         <v>0.0197</v>
@@ -26606,11 +27512,14 @@
       <c r="AC360" t="n">
         <v>0.0818</v>
       </c>
+      <c r="AF360" t="n">
+        <v>0.9796</v>
+      </c>
       <c r="AG360" t="n">
         <v>0.1035</v>
       </c>
       <c r="AH360" t="n">
-        <v>0.0488</v>
+        <v>0.0608</v>
       </c>
       <c r="AI360" t="n">
         <v>0.0134</v>
@@ -26680,11 +27589,14 @@
       <c r="AC361" t="n">
         <v>0.118</v>
       </c>
+      <c r="AF361" t="n">
+        <v>0.9757</v>
+      </c>
       <c r="AG361" t="n">
         <v>0.115</v>
       </c>
       <c r="AH361" t="n">
-        <v>0.0425</v>
+        <v>0.0488</v>
       </c>
       <c r="AI361" t="n">
         <v>0.0134</v>
@@ -26754,11 +27666,14 @@
       <c r="AC362" t="n">
         <v>0.0769</v>
       </c>
+      <c r="AF362" t="n">
+        <v>0.9751</v>
+      </c>
       <c r="AG362" t="n">
         <v>0.1009</v>
       </c>
       <c r="AH362" t="n">
-        <v>0.0457</v>
+        <v>0.0428</v>
       </c>
       <c r="AI362" t="n">
         <v>0.0223</v>
@@ -26828,11 +27743,14 @@
       <c r="AC363" t="n">
         <v>0.1271</v>
       </c>
+      <c r="AF363" t="n">
+        <v>0.9736</v>
+      </c>
       <c r="AG363" t="n">
         <v>0.1013</v>
       </c>
       <c r="AH363" t="n">
-        <v>0.0442</v>
+        <v>0.054</v>
       </c>
       <c r="AI363" t="n">
         <v>0.027</v>
@@ -26902,11 +27820,14 @@
       <c r="AC364" t="n">
         <v>0.0953</v>
       </c>
+      <c r="AF364" t="n">
+        <v>0.9724</v>
+      </c>
       <c r="AG364" t="n">
         <v>0.0902</v>
       </c>
       <c r="AH364" t="n">
-        <v>0.0358</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="AI364" t="n">
         <v>0.0282</v>
@@ -26976,11 +27897,14 @@
       <c r="AC365" t="n">
         <v>0.1078</v>
       </c>
+      <c r="AF365" t="n">
+        <v>0.9691</v>
+      </c>
       <c r="AG365" t="n">
         <v>0.1037</v>
       </c>
       <c r="AH365" t="n">
-        <v>0.0504</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="AI365" t="n">
         <v>0.0246</v>
@@ -27050,11 +27974,14 @@
       <c r="AC366" t="n">
         <v>0.0736</v>
       </c>
+      <c r="AF366" t="n">
+        <v>0.9761</v>
+      </c>
       <c r="AG366" t="n">
         <v>0.1019</v>
       </c>
       <c r="AH366" t="n">
-        <v>0.0476</v>
+        <v>0.0381</v>
       </c>
       <c r="AI366" t="n">
         <v>0.0209</v>
@@ -27124,11 +28051,14 @@
       <c r="AC367" t="n">
         <v>0.07539999999999999</v>
       </c>
+      <c r="AF367" t="n">
+        <v>0.9713000000000001</v>
+      </c>
       <c r="AG367" t="n">
         <v>0.1003</v>
       </c>
       <c r="AH367" t="n">
-        <v>0.0566</v>
+        <v>0.0493</v>
       </c>
       <c r="AI367" t="n">
         <v>0.0181</v>
@@ -27198,11 +28128,14 @@
       <c r="AC368" t="n">
         <v>0.0397</v>
       </c>
+      <c r="AF368" t="n">
+        <v>0.9678</v>
+      </c>
       <c r="AG368" t="n">
         <v>0.0859</v>
       </c>
       <c r="AH368" t="n">
-        <v>0.073</v>
+        <v>0.0506</v>
       </c>
       <c r="AI368" t="n">
         <v>0.0218</v>
@@ -27272,11 +28205,14 @@
       <c r="AC369" t="n">
         <v>0.0575</v>
       </c>
+      <c r="AF369" t="n">
+        <v>0.974</v>
+      </c>
       <c r="AG369" t="n">
         <v>0.0867</v>
       </c>
       <c r="AH369" t="n">
-        <v>0.0542</v>
+        <v>0.0506</v>
       </c>
       <c r="AI369" t="n">
         <v>0.0209</v>
@@ -27346,11 +28282,14 @@
       <c r="AC370" t="n">
         <v>0.0593</v>
       </c>
+      <c r="AF370" t="n">
+        <v>0.9698</v>
+      </c>
       <c r="AG370" t="n">
         <v>0.0828</v>
       </c>
       <c r="AH370" t="n">
-        <v>0.0526</v>
+        <v>0.0527</v>
       </c>
       <c r="AI370" t="n">
         <v>0.017</v>
@@ -27420,11 +28359,14 @@
       <c r="AC371" t="n">
         <v>0.0621</v>
       </c>
+      <c r="AF371" t="n">
+        <v>0.9712</v>
+      </c>
       <c r="AG371" t="n">
         <v>0.0898</v>
       </c>
       <c r="AH371" t="n">
-        <v>0.0613</v>
+        <v>0.0418</v>
       </c>
       <c r="AI371" t="n">
         <v>0.0209</v>
@@ -27494,11 +28436,14 @@
       <c r="AC372" t="n">
         <v>0.048</v>
       </c>
+      <c r="AF372" t="n">
+        <v>0.9747</v>
+      </c>
       <c r="AG372" t="n">
         <v>0.0813</v>
       </c>
       <c r="AH372" t="n">
-        <v>0.0594</v>
+        <v>0.049</v>
       </c>
       <c r="AI372" t="n">
         <v>0.0204</v>
@@ -27568,11 +28513,14 @@
       <c r="AC373" t="n">
         <v>0.059</v>
       </c>
+      <c r="AF373" t="n">
+        <v>0.9705</v>
+      </c>
       <c r="AG373" t="n">
         <v>0.0708</v>
       </c>
       <c r="AH373" t="n">
-        <v>0.0575</v>
+        <v>0.0554</v>
       </c>
       <c r="AI373" t="n">
         <v>0.0247</v>
@@ -27642,11 +28590,14 @@
       <c r="AC374" t="n">
         <v>0.07290000000000001</v>
       </c>
+      <c r="AF374" t="n">
+        <v>0.979</v>
+      </c>
       <c r="AG374" t="n">
         <v>0.0838</v>
       </c>
       <c r="AH374" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0566</v>
       </c>
       <c r="AI374" t="n">
         <v>0.0589</v>
@@ -27716,11 +28667,14 @@
       <c r="AC375" t="n">
         <v>0.0667</v>
       </c>
+      <c r="AF375" t="n">
+        <v>0.9831</v>
+      </c>
       <c r="AG375" t="n">
         <v>0.0761</v>
       </c>
       <c r="AH375" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0494</v>
       </c>
       <c r="AI375" t="n">
         <v>0.0366</v>
@@ -27790,11 +28744,14 @@
       <c r="AC376" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="AF376" t="n">
+        <v>0.9802</v>
+      </c>
       <c r="AG376" t="n">
         <v>0.0946</v>
       </c>
       <c r="AH376" t="n">
-        <v>0.0683</v>
+        <v>0.0677</v>
       </c>
       <c r="AI376" t="n">
         <v>0.0282</v>
@@ -27864,11 +28821,14 @@
       <c r="AC377" t="n">
         <v>0.06909999999999999</v>
       </c>
+      <c r="AF377" t="n">
+        <v>0.975</v>
+      </c>
       <c r="AG377" t="n">
         <v>0.1018</v>
       </c>
       <c r="AH377" t="n">
-        <v>0.0648</v>
+        <v>0.0587</v>
       </c>
       <c r="AI377" t="n">
         <v>0.0202</v>
@@ -27938,11 +28898,14 @@
       <c r="AC378" t="n">
         <v>0.06759999999999999</v>
       </c>
+      <c r="AF378" t="n">
+        <v>0.9756</v>
+      </c>
       <c r="AG378" t="n">
         <v>0.094</v>
       </c>
       <c r="AH378" t="n">
-        <v>0.0549</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="AI378" t="n">
         <v>0.0222</v>
@@ -28012,11 +28975,14 @@
       <c r="AC379" t="n">
         <v>0.0767</v>
       </c>
+      <c r="AF379" t="n">
+        <v>0.9774</v>
+      </c>
       <c r="AG379" t="n">
         <v>0.0994</v>
       </c>
       <c r="AH379" t="n">
-        <v>0.0535</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="AI379" t="n">
         <v>0.0199</v>
@@ -28086,11 +29052,14 @@
       <c r="AC380" t="n">
         <v>0.078</v>
       </c>
+      <c r="AF380" t="n">
+        <v>0.983</v>
+      </c>
       <c r="AG380" t="n">
         <v>0.1002</v>
       </c>
       <c r="AH380" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0706</v>
       </c>
       <c r="AI380" t="n">
         <v>0.0172</v>
@@ -28160,11 +29129,14 @@
       <c r="AC381" t="n">
         <v>0.07149999999999999</v>
       </c>
+      <c r="AF381" t="n">
+        <v>0.9802</v>
+      </c>
       <c r="AG381" t="n">
         <v>0.0973</v>
       </c>
       <c r="AH381" t="n">
-        <v>0.0548</v>
+        <v>0.0479</v>
       </c>
       <c r="AI381" t="n">
         <v>0.0203</v>
@@ -28234,11 +29206,14 @@
       <c r="AC382" t="n">
         <v>0.0492</v>
       </c>
+      <c r="AF382" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="AG382" t="n">
         <v>0.08210000000000001</v>
       </c>
       <c r="AH382" t="n">
-        <v>0.0436</v>
+        <v>0.0559</v>
       </c>
       <c r="AI382" t="n">
         <v>0.0169</v>
@@ -28308,11 +29283,14 @@
       <c r="AC383" t="n">
         <v>0.0593</v>
       </c>
+      <c r="AF383" t="n">
+        <v>0.9781</v>
+      </c>
       <c r="AG383" t="n">
         <v>0.0944</v>
       </c>
       <c r="AH383" t="n">
-        <v>0.0587</v>
+        <v>0.056</v>
       </c>
       <c r="AI383" t="n">
         <v>0.018</v>
@@ -28382,11 +29360,14 @@
       <c r="AC384" t="n">
         <v>0.0741</v>
       </c>
+      <c r="AF384" t="n">
+        <v>0.9772</v>
+      </c>
       <c r="AG384" t="n">
         <v>0.0494</v>
       </c>
       <c r="AH384" t="n">
-        <v>0.0551</v>
+        <v>0.0483</v>
       </c>
       <c r="AI384" t="n">
         <v>0.0227</v>
@@ -28456,11 +29437,14 @@
       <c r="AC385" t="n">
         <v>0.081</v>
       </c>
+      <c r="AF385" t="n">
+        <v>0.9856</v>
+      </c>
       <c r="AG385" t="n">
         <v>0.0575</v>
       </c>
       <c r="AH385" t="n">
-        <v>0.0589</v>
+        <v>0.0541</v>
       </c>
       <c r="AI385" t="n">
         <v>0.0274</v>
@@ -28530,11 +29514,14 @@
       <c r="AC386" t="n">
         <v>0.0687</v>
       </c>
+      <c r="AF386" t="n">
+        <v>0.9822</v>
+      </c>
       <c r="AG386" t="n">
         <v>0.052</v>
       </c>
       <c r="AH386" t="n">
-        <v>0.0643</v>
+        <v>0.0587</v>
       </c>
       <c r="AI386" t="n">
         <v>0.0239</v>
@@ -28604,11 +29591,14 @@
       <c r="AC387" t="n">
         <v>0.0994</v>
       </c>
+      <c r="AF387" t="n">
+        <v>0.9846</v>
+      </c>
       <c r="AG387" t="n">
         <v>0.0364</v>
       </c>
       <c r="AH387" t="n">
-        <v>0.0626</v>
+        <v>0.0629</v>
       </c>
       <c r="AI387" t="n">
         <v>0.02</v>
@@ -28678,11 +29668,14 @@
       <c r="AC388" t="n">
         <v>0.0761</v>
       </c>
+      <c r="AF388" t="n">
+        <v>0.9817</v>
+      </c>
       <c r="AG388" t="n">
         <v>0.0379</v>
       </c>
       <c r="AH388" t="n">
-        <v>0.0562</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="AI388" t="n">
         <v>0.0249</v>
@@ -28752,11 +29745,14 @@
       <c r="AC389" t="n">
         <v>0.0623</v>
       </c>
+      <c r="AF389" t="n">
+        <v>0.9802</v>
+      </c>
       <c r="AG389" t="n">
         <v>0.0208</v>
       </c>
       <c r="AH389" t="n">
-        <v>0.0533</v>
+        <v>0.0573</v>
       </c>
       <c r="AI389" t="n">
         <v>0.0281</v>
@@ -28826,11 +29822,14 @@
       <c r="AC390" t="n">
         <v>0.0614</v>
       </c>
+      <c r="AF390" t="n">
+        <v>0.9808</v>
+      </c>
       <c r="AG390" t="n">
         <v>0.028</v>
       </c>
       <c r="AH390" t="n">
-        <v>0.0602</v>
+        <v>0.0487</v>
       </c>
       <c r="AI390" t="n">
         <v>0.0277</v>
@@ -28900,11 +29899,14 @@
       <c r="AC391" t="n">
         <v>0.0747</v>
       </c>
+      <c r="AF391" t="n">
+        <v>0.9775</v>
+      </c>
       <c r="AG391" t="n">
         <v>0.0335</v>
       </c>
       <c r="AH391" t="n">
-        <v>0.0582</v>
+        <v>0.0485</v>
       </c>
       <c r="AI391" t="n">
         <v>0.0166</v>
@@ -28974,11 +29976,14 @@
       <c r="AC392" t="n">
         <v>0.07580000000000001</v>
       </c>
+      <c r="AF392" t="n">
+        <v>0.984</v>
+      </c>
       <c r="AG392" t="n">
         <v>0.0199</v>
       </c>
       <c r="AH392" t="n">
-        <v>0.0561</v>
+        <v>0.0565</v>
       </c>
       <c r="AI392" t="n">
         <v>0.0215</v>
@@ -29048,11 +30053,14 @@
       <c r="AC393" t="n">
         <v>0.0608</v>
       </c>
+      <c r="AF393" t="n">
+        <v>0.982</v>
+      </c>
       <c r="AG393" t="n">
         <v>0.036</v>
       </c>
       <c r="AH393" t="n">
-        <v>0.0505</v>
+        <v>0.0526</v>
       </c>
       <c r="AI393" t="n">
         <v>0.0229</v>
@@ -29122,11 +30130,14 @@
       <c r="AC394" t="n">
         <v>0.0965</v>
       </c>
+      <c r="AF394" t="n">
+        <v>0.981</v>
+      </c>
       <c r="AG394" t="n">
         <v>0.0159</v>
       </c>
       <c r="AH394" t="n">
-        <v>0.0412</v>
+        <v>0.0531</v>
       </c>
       <c r="AI394" t="n">
         <v>0.0217</v>
@@ -29196,11 +30207,14 @@
       <c r="AC395" t="n">
         <v>0.0747</v>
       </c>
+      <c r="AF395" t="n">
+        <v>0.978</v>
+      </c>
       <c r="AG395" t="n">
         <v>0.0389</v>
       </c>
       <c r="AH395" t="n">
-        <v>0.0478</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="AI395" t="n">
         <v>0.0209</v>
@@ -29270,11 +30284,14 @@
       <c r="AC396" t="n">
         <v>0.0687</v>
       </c>
+      <c r="AF396" t="n">
+        <v>0.9828</v>
+      </c>
       <c r="AG396" t="n">
         <v>0.029</v>
       </c>
       <c r="AH396" t="n">
-        <v>0.0494</v>
+        <v>0.0655</v>
       </c>
       <c r="AI396" t="n">
         <v>0.0208</v>
@@ -29344,11 +30361,14 @@
       <c r="AC397" t="n">
         <v>0.0696</v>
       </c>
+      <c r="AF397" t="n">
+        <v>0.982</v>
+      </c>
       <c r="AG397" t="n">
         <v>0.0346</v>
       </c>
       <c r="AH397" t="n">
-        <v>0.053</v>
+        <v>0.081</v>
       </c>
       <c r="AI397" t="n">
         <v>0.0186</v>
@@ -29418,11 +30438,14 @@
       <c r="AC398" t="n">
         <v>0.0712</v>
       </c>
+      <c r="AF398" t="n">
+        <v>0.9833</v>
+      </c>
       <c r="AG398" t="n">
         <v>0.0388</v>
       </c>
       <c r="AH398" t="n">
-        <v>0.0558</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="AI398" t="n">
         <v>0.0193</v>
@@ -29492,11 +30515,14 @@
       <c r="AC399" t="n">
         <v>0.081</v>
       </c>
+      <c r="AF399" t="n">
+        <v>0.9815</v>
+      </c>
       <c r="AG399" t="n">
         <v>0.0197</v>
       </c>
       <c r="AH399" t="n">
-        <v>0.0477</v>
+        <v>0.0615</v>
       </c>
       <c r="AI399" t="n">
         <v>0.0227</v>
@@ -29566,11 +30592,14 @@
       <c r="AC400" t="n">
         <v>0.0644</v>
       </c>
+      <c r="AF400" t="n">
+        <v>0.9791</v>
+      </c>
       <c r="AG400" t="n">
         <v>0.0232</v>
       </c>
       <c r="AH400" t="n">
-        <v>0.0522</v>
+        <v>0.0572</v>
       </c>
       <c r="AI400" t="n">
         <v>0.0304</v>
@@ -29640,11 +30669,14 @@
       <c r="AC401" t="n">
         <v>0.06850000000000001</v>
       </c>
+      <c r="AF401" t="n">
+        <v>0.979</v>
+      </c>
       <c r="AG401" t="n">
         <v>0.0375</v>
       </c>
       <c r="AH401" t="n">
-        <v>0.0564</v>
+        <v>0.0474</v>
       </c>
       <c r="AI401" t="n">
         <v>0.0201</v>
@@ -29718,7 +30750,7 @@
         <v>0.0298</v>
       </c>
       <c r="AH402" t="n">
-        <v>0.0498</v>
+        <v>0.0537</v>
       </c>
       <c r="AI402" t="n">
         <v>0.0244</v>
@@ -29792,7 +30824,7 @@
         <v>0.0273</v>
       </c>
       <c r="AH403" t="n">
-        <v>0.056</v>
+        <v>0.0615</v>
       </c>
       <c r="AI403" t="n">
         <v>0.0215</v>
@@ -29866,7 +30898,7 @@
         <v>0.0291</v>
       </c>
       <c r="AH404" t="n">
-        <v>0.0505</v>
+        <v>0.0663</v>
       </c>
       <c r="AI404" t="n">
         <v>0.0283</v>
@@ -29940,7 +30972,7 @@
         <v>0.0438</v>
       </c>
       <c r="AH405" t="n">
-        <v>0.0516</v>
+        <v>0.0543</v>
       </c>
       <c r="AI405" t="n">
         <v>0.0148</v>
@@ -30014,7 +31046,7 @@
         <v>0.0474</v>
       </c>
       <c r="AH406" t="n">
-        <v>0.0481</v>
+        <v>0.0599</v>
       </c>
       <c r="AI406" t="n">
         <v>0.0246</v>
@@ -30088,7 +31120,7 @@
         <v>0.0294</v>
       </c>
       <c r="AH407" t="n">
-        <v>0.0505</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="AI407" t="n">
         <v>0.0187</v>
@@ -30162,7 +31194,7 @@
         <v>0.0321</v>
       </c>
       <c r="AH408" t="n">
-        <v>0.0411</v>
+        <v>0.0644</v>
       </c>
       <c r="AI408" t="n">
         <v>0.0214</v>
@@ -30236,7 +31268,7 @@
         <v>0.0293</v>
       </c>
       <c r="AH409" t="n">
-        <v>0.0464</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="AI409" t="n">
         <v>0.0263</v>
@@ -30310,7 +31342,7 @@
         <v>0.0449</v>
       </c>
       <c r="AH410" t="n">
-        <v>0.0594</v>
+        <v>0.0742</v>
       </c>
       <c r="AI410" t="n">
         <v>0.0159</v>
@@ -30384,7 +31416,7 @@
         <v>0.0331</v>
       </c>
       <c r="AH411" t="n">
-        <v>0.0539</v>
+        <v>0.0709</v>
       </c>
       <c r="AI411" t="n">
         <v>0.018</v>
@@ -30458,7 +31490,7 @@
         <v>0.0348</v>
       </c>
       <c r="AH412" t="n">
-        <v>0.0488</v>
+        <v>0.0592</v>
       </c>
       <c r="AI412" t="n">
         <v>0.0234</v>
@@ -30532,7 +31564,7 @@
         <v>0.0454</v>
       </c>
       <c r="AH413" t="n">
-        <v>0.0538</v>
+        <v>0.0702</v>
       </c>
       <c r="AI413" t="n">
         <v>0.0247</v>
@@ -30606,7 +31638,7 @@
         <v>0.0332</v>
       </c>
       <c r="AH414" t="n">
-        <v>0.05</v>
+        <v>0.0675</v>
       </c>
       <c r="AI414" t="n">
         <v>0.0213</v>
@@ -30680,7 +31712,7 @@
         <v>0.0246</v>
       </c>
       <c r="AH415" t="n">
-        <v>0.053</v>
+        <v>0.0549</v>
       </c>
       <c r="AI415" t="n">
         <v>0.0193</v>
@@ -30743,11 +31775,14 @@
       <c r="AC418" t="n">
         <v>0.1534222222222222</v>
       </c>
+      <c r="AF418" t="n">
+        <v>0.13216</v>
+      </c>
       <c r="AG418" t="n">
         <v>0.150375</v>
       </c>
       <c r="AH418" t="n">
-        <v>0.1496333333333333</v>
+        <v>0.14585</v>
       </c>
       <c r="AI418" t="n">
         <v>0.11844</v>
@@ -30796,11 +31831,14 @@
       <c r="AC419" t="n">
         <v>0.1649125</v>
       </c>
+      <c r="AF419" t="n">
+        <v>0.11385</v>
+      </c>
       <c r="AG419" t="n">
         <v>0.1805142857142857</v>
       </c>
       <c r="AH419" t="n">
-        <v>0.1386166666666667</v>
+        <v>0.19142</v>
       </c>
       <c r="AI419" t="n">
         <v>0.1168142857142857</v>
@@ -30849,11 +31887,14 @@
       <c r="AC420" t="n">
         <v>0.22192</v>
       </c>
+      <c r="AF420" t="n">
+        <v>0.2421666666666666</v>
+      </c>
       <c r="AG420" t="n">
         <v>0.21036</v>
       </c>
       <c r="AH420" t="n">
-        <v>0.2046444444444444</v>
+        <v>0.192225</v>
       </c>
       <c r="AI420" t="n">
         <v>0.2085875</v>
@@ -30902,11 +31943,14 @@
       <c r="AC421" t="n">
         <v>0.2449</v>
       </c>
+      <c r="AF421" t="n">
+        <v>0.2618</v>
+      </c>
       <c r="AG421" t="n">
         <v>0.252225</v>
       </c>
       <c r="AH421" t="n">
-        <v>0.2634125</v>
+        <v>0.2416272727272727</v>
       </c>
       <c r="AI421" t="n">
         <v>0.28051</v>
@@ -30955,11 +31999,14 @@
       <c r="AC422" t="n">
         <v>0.2429181818181818</v>
       </c>
+      <c r="AF422" t="n">
+        <v>0.2596</v>
+      </c>
       <c r="AG422" t="n">
         <v>0.2460166666666667</v>
       </c>
       <c r="AH422" t="n">
-        <v>0.2185727272727273</v>
+        <v>0.2841</v>
       </c>
       <c r="AI422" t="n">
         <v>0.29418</v>
@@ -31008,11 +32055,14 @@
       <c r="AC423" t="n">
         <v>0.2873692307692307</v>
       </c>
+      <c r="AF423" t="n">
+        <v>0.3299454545454546</v>
+      </c>
       <c r="AG423" t="n">
         <v>0.30364</v>
       </c>
       <c r="AH423" t="n">
-        <v>0.3071</v>
+        <v>0.3128222222222222</v>
       </c>
       <c r="AI423" t="n">
         <v>0.30703</v>
@@ -31061,11 +32111,14 @@
       <c r="AC424" t="n">
         <v>0.3680125</v>
       </c>
+      <c r="AF424" t="n">
+        <v>0.3415666666666666</v>
+      </c>
       <c r="AG424" t="n">
         <v>0.35805</v>
       </c>
       <c r="AH424" t="n">
-        <v>0.3373125</v>
+        <v>0.3545714285714286</v>
       </c>
       <c r="AI424" t="n">
         <v>0.32345</v>
@@ -31114,11 +32167,14 @@
       <c r="AC425" t="n">
         <v>0.4224416666666668</v>
       </c>
+      <c r="AF425" t="n">
+        <v>0.40175</v>
+      </c>
       <c r="AG425" t="n">
         <v>0.3969</v>
       </c>
       <c r="AH425" t="n">
-        <v>0.3982999999999999</v>
+        <v>0.37775</v>
       </c>
       <c r="AI425" t="n">
         <v>0.4134384615384615</v>
@@ -31167,11 +32223,14 @@
       <c r="AC426" t="n">
         <v>0.4952454545454547</v>
       </c>
+      <c r="AF426" t="n">
+        <v>0.3984199999999999</v>
+      </c>
       <c r="AG426" t="n">
         <v>0.4283750000000001</v>
       </c>
       <c r="AH426" t="n">
-        <v>0.3959374999999999</v>
+        <v>0.4151461538461539</v>
       </c>
       <c r="AI426" t="n">
         <v>0.41214</v>
@@ -31220,11 +32279,14 @@
       <c r="AC427" t="n">
         <v>0.3912846153846154</v>
       </c>
+      <c r="AF427" t="n">
+        <v>0.3904</v>
+      </c>
       <c r="AG427" t="n">
         <v>0.4914125</v>
       </c>
       <c r="AH427" t="n">
-        <v>0.4546444444444445</v>
+        <v>0.4358888888888889</v>
       </c>
       <c r="AI427" t="n">
         <v>0.45495</v>
@@ -31261,11 +32323,14 @@
       <c r="AC428" t="n">
         <v>0.4736</v>
       </c>
+      <c r="AF428" t="n">
+        <v>0.4098555555555555</v>
+      </c>
       <c r="AG428" t="n">
         <v>0.5786777777777778</v>
       </c>
       <c r="AH428" t="n">
-        <v>0.5218545454545456</v>
+        <v>0.4628636363636364</v>
       </c>
       <c r="AI428" t="n">
         <v>0.47021</v>
@@ -31305,11 +32370,14 @@
       <c r="AC429" t="n">
         <v>0.57748</v>
       </c>
+      <c r="AF429" t="n">
+        <v>0.4232625</v>
+      </c>
       <c r="AG429" t="n">
         <v>0.5446749999999999</v>
       </c>
       <c r="AH429" t="n">
-        <v>0.5055285714285713</v>
+        <v>0.5359900000000001</v>
       </c>
       <c r="AI429" t="n">
         <v>0.5647</v>
@@ -31349,11 +32417,14 @@
       <c r="AC430" t="n">
         <v>0.5227833333333333</v>
       </c>
+      <c r="AF430" t="n">
+        <v>0.4967714285714285</v>
+      </c>
       <c r="AG430" t="n">
         <v>0.6261636363636364</v>
       </c>
       <c r="AH430" t="n">
-        <v>0.5853625</v>
+        <v>0.5142571428571429</v>
       </c>
       <c r="AI430" t="n">
         <v>0.4968555555555556</v>
@@ -31393,11 +32464,14 @@
       <c r="AC431" t="n">
         <v>0.4797818181818183</v>
       </c>
+      <c r="AF431" t="n">
+        <v>0.4821428571428572</v>
+      </c>
       <c r="AG431" t="n">
         <v>0.6130666666666666</v>
       </c>
       <c r="AH431" t="n">
-        <v>0.554525</v>
+        <v>0.5718333333333333</v>
       </c>
       <c r="AI431" t="n">
         <v>0.5662363636363636</v>
@@ -31437,11 +32511,14 @@
       <c r="AC432" t="n">
         <v>0.5757357142857142</v>
       </c>
+      <c r="AF432" t="n">
+        <v>0.5716555555555556</v>
+      </c>
       <c r="AG432" t="n">
         <v>0.539988888888889</v>
       </c>
       <c r="AH432" t="n">
-        <v>0.5792</v>
+        <v>0.5843076923076922</v>
       </c>
       <c r="AI432" t="n">
         <v>0.6087</v>
@@ -31481,11 +32558,14 @@
       <c r="AC433" t="n">
         <v>0.6213583333333332</v>
       </c>
+      <c r="AF433" t="n">
+        <v>0.5208</v>
+      </c>
       <c r="AG433" t="n">
         <v>0.6403624999999999</v>
       </c>
       <c r="AH433" t="n">
-        <v>0.5571200000000001</v>
+        <v>0.57505</v>
       </c>
       <c r="AI433" t="n">
         <v>0.5527083333333334</v>
@@ -31525,11 +32605,14 @@
       <c r="AC434" t="n">
         <v>0.6040615384615384</v>
       </c>
+      <c r="AF434" t="n">
+        <v>0.61748</v>
+      </c>
       <c r="AG434" t="n">
         <v>0.6644099999999999</v>
       </c>
       <c r="AH434" t="n">
-        <v>0.5871727272727273</v>
+        <v>0.5838571428571429</v>
       </c>
       <c r="AI434" t="n">
         <v>0.5567333333333333</v>
@@ -31569,11 +32652,14 @@
       <c r="AC435" t="n">
         <v>0.5855714285714286</v>
       </c>
+      <c r="AF435" t="n">
+        <v>0.6697636363636364</v>
+      </c>
       <c r="AG435" t="n">
         <v>0.6553249999999999</v>
       </c>
       <c r="AH435" t="n">
-        <v>0.6639111111111112</v>
+        <v>0.6570454545454546</v>
       </c>
       <c r="AI435" t="n">
         <v>0.4903428571428572</v>
@@ -31613,11 +32699,14 @@
       <c r="AC436" t="n">
         <v>0.5823153846153846</v>
       </c>
+      <c r="AF436" t="n">
+        <v>0.6910749999999999</v>
+      </c>
       <c r="AG436" t="n">
         <v>0.6570666666666667</v>
       </c>
       <c r="AH436" t="n">
-        <v>0.6520111111111111</v>
+        <v>0.6746888888888889</v>
       </c>
       <c r="AI436" t="n">
         <v>0.4620100000000001</v>
@@ -31657,11 +32746,14 @@
       <c r="AC437" t="n">
         <v>0.6298692307692307</v>
       </c>
+      <c r="AF437" t="n">
+        <v>0.6272090909090908</v>
+      </c>
       <c r="AG437" t="n">
         <v>0.6755555555555556</v>
       </c>
       <c r="AH437" t="n">
-        <v>0.64175</v>
+        <v>0.5641555555555555</v>
       </c>
     </row>
     <row r="438">
@@ -31698,11 +32790,14 @@
       <c r="AC438" t="n">
         <v>0.6617545454545455</v>
       </c>
+      <c r="AF438" t="n">
+        <v>0.7179285714285714</v>
+      </c>
       <c r="AG438" t="n">
         <v>0.7323125</v>
       </c>
       <c r="AH438" t="n">
-        <v>0.5242555555555556</v>
+        <v>0.5794090909090909</v>
       </c>
       <c r="AI438" t="n">
         <v>0.5260916666666667</v>
@@ -31742,11 +32837,14 @@
       <c r="AC439" t="n">
         <v>0.5704692307692307</v>
       </c>
+      <c r="AF439" t="n">
+        <v>0.7194199999999999</v>
+      </c>
       <c r="AG439" t="n">
         <v>0.6723000000000001</v>
       </c>
       <c r="AH439" t="n">
-        <v>0.5906571428571429</v>
+        <v>0.6429727272727273</v>
       </c>
       <c r="AI439" t="n">
         <v>0.5456</v>
@@ -31786,11 +32884,14 @@
       <c r="AC440" t="n">
         <v>0.5971083333333332</v>
       </c>
+      <c r="AF440" t="n">
+        <v>0.7299</v>
+      </c>
       <c r="AG440" t="n">
         <v>0.8287636363636363</v>
       </c>
       <c r="AH440" t="n">
-        <v>0.7551083333333334</v>
+        <v>0.6490083333333333</v>
       </c>
       <c r="AI440" t="n">
         <v>0.5898333333333333</v>
@@ -31830,11 +32931,14 @@
       <c r="AC441" t="n">
         <v>0.6017916666666667</v>
       </c>
+      <c r="AF441" t="n">
+        <v>0.7723749999999999</v>
+      </c>
       <c r="AG441" t="n">
         <v>0.6786749999999999</v>
       </c>
       <c r="AH441" t="n">
-        <v>0.6199222222222223</v>
+        <v>0.7006333333333334</v>
       </c>
       <c r="AI441" t="n">
         <v>0.5843999999999998</v>
@@ -31874,11 +32978,14 @@
       <c r="AC442" t="n">
         <v>0.6147750000000001</v>
       </c>
+      <c r="AF442" t="n">
+        <v>0.6776599999999999</v>
+      </c>
       <c r="AG442" t="n">
         <v>0.7175777777777778</v>
       </c>
       <c r="AH442" t="n">
-        <v>0.6417916666666666</v>
+        <v>0.62162</v>
       </c>
       <c r="AI442" t="n">
         <v>0.5954928571428572</v>
@@ -31918,11 +33025,14 @@
       <c r="AC443" t="n">
         <v>0.6563272727272726</v>
       </c>
+      <c r="AF443" t="n">
+        <v>0.6970250000000001</v>
+      </c>
       <c r="AG443" t="n">
         <v>0.7514000000000001</v>
       </c>
       <c r="AH443" t="n">
-        <v>0.66647</v>
+        <v>0.6663699999999999</v>
       </c>
       <c r="AI443" t="n">
         <v>0.5881416666666667</v>
@@ -31962,11 +33072,14 @@
       <c r="AC444" t="n">
         <v>0.6547500000000001</v>
       </c>
+      <c r="AF444" t="n">
+        <v>0.7830454545454544</v>
+      </c>
       <c r="AG444" t="n">
         <v>0.6881</v>
       </c>
       <c r="AH444" t="n">
-        <v>0.6148363636363636</v>
+        <v>0.6442</v>
       </c>
       <c r="AI444" t="n">
         <v>0.6613625000000001</v>
@@ -32006,11 +33119,14 @@
       <c r="AC445" t="n">
         <v>0.6375999999999998</v>
       </c>
+      <c r="AF445" t="n">
+        <v>0.8399333333333332</v>
+      </c>
       <c r="AG445" t="n">
         <v>0.6619375</v>
       </c>
       <c r="AH445" t="n">
-        <v>0.6054777777777778</v>
+        <v>0.6435384615384615</v>
       </c>
       <c r="AI445" t="n">
         <v>0.57875</v>
@@ -32050,11 +33166,14 @@
       <c r="AC446" t="n">
         <v>0.7462461538461537</v>
       </c>
+      <c r="AF446" t="n">
+        <v>0.70085</v>
+      </c>
       <c r="AG446" t="n">
         <v>0.7056571428571428</v>
       </c>
       <c r="AH446" t="n">
-        <v>0.7241499999999998</v>
+        <v>0.7002111111111111</v>
       </c>
       <c r="AI446" t="n">
         <v>0.6669777777777778</v>
@@ -32094,11 +33213,14 @@
       <c r="AC447" t="n">
         <v>0.6812083333333335</v>
       </c>
+      <c r="AF447" t="n">
+        <v>0.8234249999999999</v>
+      </c>
       <c r="AG447" t="n">
         <v>0.70548</v>
       </c>
       <c r="AH447" t="n">
-        <v>0.7092181818181817</v>
+        <v>0.590175</v>
       </c>
       <c r="AI447" t="n">
         <v>0.5179363636363636</v>
@@ -32138,11 +33260,14 @@
       <c r="AC448" t="n">
         <v>0.6009833333333334</v>
       </c>
+      <c r="AF448" t="n">
+        <v>0.8590750000000001</v>
+      </c>
       <c r="AG448" t="n">
         <v>0.6137875</v>
       </c>
       <c r="AH448" t="n">
-        <v>0.7539100000000001</v>
+        <v>0.7134099999999999</v>
       </c>
       <c r="AI448" t="n">
         <v>0.6869727272727273</v>
@@ -32182,11 +33307,14 @@
       <c r="AC449" t="n">
         <v>0.6493846153846154</v>
       </c>
+      <c r="AF449" t="n">
+        <v>0.6913888888888888</v>
+      </c>
       <c r="AG449" t="n">
         <v>0.6373571428571428</v>
       </c>
       <c r="AH449" t="n">
-        <v>0.6296111111111111</v>
+        <v>0.5617666666666666</v>
       </c>
       <c r="AI449" t="n">
         <v>0.5404214285714286</v>
@@ -32223,11 +33351,14 @@
       <c r="AC450" t="n">
         <v>0.6377272727272726</v>
       </c>
+      <c r="AF450" t="n">
+        <v>0.8122874999999999</v>
+      </c>
       <c r="AG450" t="n">
         <v>0.7039375000000001</v>
       </c>
       <c r="AH450" t="n">
-        <v>0.7224750000000001</v>
+        <v>0.6574599999999999</v>
       </c>
       <c r="AI450" t="n">
         <v>0.6353583333333334</v>
@@ -32267,11 +33398,14 @@
       <c r="AC451" t="n">
         <v>0.7466666666666667</v>
       </c>
+      <c r="AF451" t="n">
+        <v>0.756</v>
+      </c>
       <c r="AG451" t="n">
         <v>0.6523</v>
       </c>
       <c r="AH451" t="n">
-        <v>0.6101222222222222</v>
+        <v>0.65465</v>
       </c>
       <c r="AI451" t="n">
         <v>0.6264909090909091</v>
@@ -32311,11 +33445,14 @@
       <c r="AC452" t="n">
         <v>0.66817</v>
       </c>
+      <c r="AF452" t="n">
+        <v>0.8365</v>
+      </c>
       <c r="AG452" t="n">
         <v>0.7395875</v>
       </c>
       <c r="AH452" t="n">
-        <v>0.6760666666666667</v>
+        <v>0.6457777777777777</v>
       </c>
       <c r="AI452" t="n">
         <v>0.6068666666666667</v>
@@ -32352,11 +33489,14 @@
       <c r="AC453" t="n">
         <v>0.6596909090909091</v>
       </c>
+      <c r="AF453" t="n">
+        <v>0.8086428571428571</v>
+      </c>
       <c r="AG453" t="n">
         <v>0.7404299999999999</v>
       </c>
       <c r="AH453" t="n">
-        <v>0.6695909090909091</v>
+        <v>0.727125</v>
       </c>
       <c r="AI453" t="n">
         <v>0.5649916666666667</v>
@@ -32396,11 +33536,14 @@
       <c r="AC454" t="n">
         <v>0.6688923076923078</v>
       </c>
+      <c r="AF454" t="n">
+        <v>0.765475</v>
+      </c>
       <c r="AG454" t="n">
         <v>0.6936199999999999</v>
       </c>
       <c r="AH454" t="n">
-        <v>0.7111499999999999</v>
+        <v>0.6069363636363636</v>
       </c>
       <c r="AI454" t="n">
         <v>0.5550153846153846</v>
@@ -32440,11 +33583,14 @@
       <c r="AC455" t="n">
         <v>0.5749</v>
       </c>
+      <c r="AF455" t="n">
+        <v>0.8568363636363638</v>
+      </c>
       <c r="AG455" t="n">
         <v>0.66187</v>
       </c>
       <c r="AH455" t="n">
-        <v>0.7222166666666666</v>
+        <v>0.6490416666666666</v>
       </c>
       <c r="AI455" t="n">
         <v>0.6625272727272727</v>
@@ -32484,11 +33630,14 @@
       <c r="AC456" t="n">
         <v>0.6647909090909091</v>
       </c>
+      <c r="AF456" t="n">
+        <v>0.7533</v>
+      </c>
       <c r="AG456" t="n">
         <v>0.7350857142857142</v>
       </c>
       <c r="AH456" t="n">
-        <v>0.7070333333333334</v>
+        <v>0.6142899999999999</v>
       </c>
       <c r="AI456" t="n">
         <v>0.5782636363636363</v>
@@ -32528,11 +33677,14 @@
       <c r="AC457" t="n">
         <v>0.6804928571428571</v>
       </c>
+      <c r="AF457" t="n">
+        <v>0.7226666666666667</v>
+      </c>
       <c r="AG457" t="n">
         <v>0.7047857142857143</v>
       </c>
       <c r="AH457" t="n">
-        <v>0.6972</v>
+        <v>0.6376200000000001</v>
       </c>
       <c r="AI457" t="n">
         <v>0.5540833333333334</v>
@@ -32572,11 +33724,14 @@
       <c r="AC458" t="n">
         <v>0.6463</v>
       </c>
+      <c r="AF458" t="n">
+        <v>0.73442</v>
+      </c>
       <c r="AG458" t="n">
         <v>0.6754875</v>
       </c>
       <c r="AH458" t="n">
-        <v>0.7030125</v>
+        <v>0.66495</v>
       </c>
       <c r="AI458" t="n">
         <v>0.6508307692307691</v>
@@ -32616,11 +33771,14 @@
       <c r="AC459" t="n">
         <v>0.632775</v>
       </c>
+      <c r="AF459" t="n">
+        <v>0.8531625000000002</v>
+      </c>
       <c r="AG459" t="n">
         <v>0.7225428571428572</v>
       </c>
       <c r="AH459" t="n">
-        <v>0.6403444444444444</v>
+        <v>0.6130888888888889</v>
       </c>
       <c r="AI459" t="n">
         <v>0.6123333333333334</v>
@@ -32660,11 +33818,14 @@
       <c r="AC460" t="n">
         <v>0.6456636363636363</v>
       </c>
+      <c r="AF460" t="n">
+        <v>0.8057333333333333</v>
+      </c>
       <c r="AG460" t="n">
         <v>0.71025</v>
       </c>
       <c r="AH460" t="n">
-        <v>0.6918555555555557</v>
+        <v>0.6965625000000001</v>
       </c>
       <c r="AI460" t="n">
         <v>0.6267272727272727</v>
@@ -32704,11 +33865,14 @@
       <c r="AC461" t="n">
         <v>0.6230384615384614</v>
       </c>
+      <c r="AF461" t="n">
+        <v>0.8199916666666668</v>
+      </c>
       <c r="AG461" t="n">
         <v>0.7363333333333333</v>
       </c>
       <c r="AH461" t="n">
-        <v>0.6079636363636363</v>
+        <v>0.62298</v>
       </c>
       <c r="AI461" t="n">
         <v>0.5632166666666667</v>
@@ -32748,11 +33912,14 @@
       <c r="AC462" t="n">
         <v>0.6374583333333333</v>
       </c>
+      <c r="AF462" t="n">
+        <v>0.862511111111111</v>
+      </c>
       <c r="AG462" t="n">
         <v>0.7300749999999999</v>
       </c>
       <c r="AH462" t="n">
-        <v>0.7348833333333332</v>
+        <v>0.684088888888889</v>
       </c>
       <c r="AI462" t="n">
         <v>0.588290909090909</v>
@@ -32792,11 +33959,14 @@
       <c r="AC463" t="n">
         <v>0.59465</v>
       </c>
+      <c r="AF463" t="n">
+        <v>0.77951</v>
+      </c>
       <c r="AG463" t="n">
         <v>0.7068000000000001</v>
       </c>
       <c r="AH463" t="n">
-        <v>0.6648636363636364</v>
+        <v>0.5842799999999999</v>
       </c>
     </row>
     <row r="464">
@@ -32833,11 +34003,14 @@
       <c r="AC464" t="n">
         <v>0.66703</v>
       </c>
+      <c r="AF464" t="n">
+        <v>0.8257666666666666</v>
+      </c>
       <c r="AG464" t="n">
         <v>0.65405</v>
       </c>
       <c r="AH464" t="n">
-        <v>0.7024272727272728</v>
+        <v>0.6756999999999999</v>
       </c>
       <c r="AI464" t="n">
         <v>0.5247090909090909</v>
@@ -32877,11 +34050,14 @@
       <c r="AC465" t="n">
         <v>0.6334999999999998</v>
       </c>
+      <c r="AF465" t="n">
+        <v>0.8161999999999999</v>
+      </c>
       <c r="AG465" t="n">
         <v>0.7337300000000001</v>
       </c>
       <c r="AH465" t="n">
-        <v>0.6746727272727273</v>
+        <v>0.6254777777777778</v>
       </c>
       <c r="AI465" t="n">
         <v>0.5759461538461538</v>
@@ -32921,11 +34097,14 @@
       <c r="AC466" t="n">
         <v>0.6330727272727272</v>
       </c>
+      <c r="AF466" t="n">
+        <v>0.7726714285714286</v>
+      </c>
       <c r="AG466" t="n">
         <v>0.6647545454545455</v>
       </c>
       <c r="AH466" t="n">
-        <v>0.69796</v>
+        <v>0.6857916666666667</v>
       </c>
       <c r="AI466" t="n">
         <v>0.6231818181818182</v>
@@ -32965,11 +34144,14 @@
       <c r="AC467" t="n">
         <v>0.5960500000000001</v>
       </c>
+      <c r="AF467" t="n">
+        <v>0.9099600000000002</v>
+      </c>
       <c r="AG467" t="n">
         <v>0.6775</v>
       </c>
       <c r="AH467" t="n">
-        <v>0.6180181818181818</v>
+        <v>0.5749333333333334</v>
       </c>
       <c r="AI467" t="n">
         <v>0.566625</v>
@@ -33009,11 +34191,14 @@
       <c r="AC468" t="n">
         <v>0.6233416666666666</v>
       </c>
+      <c r="AF468" t="n">
+        <v>0.7612666666666666</v>
+      </c>
       <c r="AG468" t="n">
         <v>0.6735899999999999</v>
       </c>
       <c r="AH468" t="n">
-        <v>0.751825</v>
+        <v>0.5581222222222222</v>
       </c>
       <c r="AI468" t="n">
         <v>0.5158727272727273</v>
@@ -33053,11 +34238,14 @@
       <c r="AC469" t="n">
         <v>0.6418142857142858</v>
       </c>
+      <c r="AF469" t="n">
+        <v>0.8188249999999999</v>
+      </c>
       <c r="AG469" t="n">
         <v>0.7087625</v>
       </c>
       <c r="AH469" t="n">
-        <v>0.6065199999999999</v>
+        <v>0.654475</v>
       </c>
       <c r="AI469" t="n">
         <v>0.5371222222222223</v>
@@ -33097,11 +34285,14 @@
       <c r="AC470" t="n">
         <v>0.5600846153846153</v>
       </c>
+      <c r="AF470" t="n">
+        <v>0.8237</v>
+      </c>
       <c r="AG470" t="n">
         <v>0.6691666666666666</v>
       </c>
       <c r="AH470" t="n">
-        <v>0.6785222222222222</v>
+        <v>0.5965699999999999</v>
       </c>
       <c r="AI470" t="n">
         <v>0.6442727272727272</v>
@@ -33141,11 +34332,14 @@
       <c r="AC471" t="n">
         <v>0.6603999999999999</v>
       </c>
+      <c r="AF471" t="n">
+        <v>0.8376833333333332</v>
+      </c>
       <c r="AG471" t="n">
         <v>0.7505285714285713</v>
       </c>
       <c r="AH471" t="n">
-        <v>0.6489</v>
+        <v>0.6758111111111111</v>
       </c>
       <c r="AI471" t="n">
         <v>0.5924461538461538</v>
@@ -33185,11 +34379,14 @@
       <c r="AC472" t="n">
         <v>0.6093916666666667</v>
       </c>
+      <c r="AF472" t="n">
+        <v>0.8511555555555554</v>
+      </c>
       <c r="AG472" t="n">
         <v>0.76529</v>
       </c>
       <c r="AH472" t="n">
-        <v>0.7252285714285713</v>
+        <v>0.7150700000000001</v>
       </c>
       <c r="AI472" t="n">
         <v>0.5593545454545454</v>
@@ -33229,11 +34426,14 @@
       <c r="AC473" t="n">
         <v>0.5775499999999999</v>
       </c>
+      <c r="AF473" t="n">
+        <v>0.8157000000000001</v>
+      </c>
       <c r="AG473" t="n">
         <v>0.7139499999999999</v>
       </c>
       <c r="AH473" t="n">
-        <v>0.6969375</v>
+        <v>0.6235416666666667</v>
       </c>
       <c r="AI473" t="n">
         <v>0.5250272727272728</v>
@@ -33273,11 +34473,14 @@
       <c r="AC474" t="n">
         <v>0.5617666666666666</v>
       </c>
+      <c r="AF474" t="n">
+        <v>0.87422</v>
+      </c>
       <c r="AG474" t="n">
         <v>0.6641666666666667</v>
       </c>
       <c r="AH474" t="n">
-        <v>0.7255571428571429</v>
+        <v>0.6763666666666668</v>
       </c>
       <c r="AI474" t="n">
         <v>0.6432600000000001</v>
@@ -33317,11 +34520,14 @@
       <c r="AC475" t="n">
         <v>0.6169272727272728</v>
       </c>
+      <c r="AF475" t="n">
+        <v>0.856275</v>
+      </c>
       <c r="AG475" t="n">
         <v>0.7051555555555555</v>
       </c>
       <c r="AH475" t="n">
-        <v>0.7406888888888888</v>
+        <v>0.6062299999999999</v>
       </c>
       <c r="AI475" t="n">
         <v>0.54559</v>
@@ -33361,11 +34567,14 @@
       <c r="AC476" t="n">
         <v>0.6776</v>
       </c>
+      <c r="AF476" t="n">
+        <v>0.8098727272727273</v>
+      </c>
       <c r="AG476" t="n">
         <v>0.7401555555555556</v>
       </c>
       <c r="AH476" t="n">
-        <v>0.7217000000000001</v>
+        <v>0.63049</v>
       </c>
       <c r="AI476" t="n">
         <v>0.6434</v>
@@ -33405,11 +34614,14 @@
       <c r="AC477" t="n">
         <v>0.6557916666666667</v>
       </c>
+      <c r="AF477" t="n">
+        <v>0.9137624999999999</v>
+      </c>
       <c r="AG477" t="n">
         <v>0.6803</v>
       </c>
       <c r="AH477" t="n">
-        <v>0.7513333333333334</v>
+        <v>0.6231333333333332</v>
       </c>
       <c r="AI477" t="n">
         <v>0.6002181818181819</v>
@@ -33449,11 +34661,14 @@
       <c r="AC478" t="n">
         <v>0.5943307692307692</v>
       </c>
+      <c r="AF478" t="n">
+        <v>0.7263333333333333</v>
+      </c>
       <c r="AG478" t="n">
         <v>0.7415666666666668</v>
       </c>
       <c r="AH478" t="n">
-        <v>0.7607538461538461</v>
+        <v>0.6222555555555556</v>
       </c>
       <c r="AI478" t="n">
         <v>0.5306615384615383</v>
@@ -33493,11 +34708,14 @@
       <c r="AC479" t="n">
         <v>0.5615307692307693</v>
       </c>
+      <c r="AF479" t="n">
+        <v>0.7894111111111112</v>
+      </c>
       <c r="AG479" t="n">
         <v>0.7402444444444444</v>
       </c>
       <c r="AH479" t="n">
-        <v>0.7331500000000001</v>
+        <v>0.6592846153846152</v>
       </c>
       <c r="AI479" t="n">
         <v>0.5950222222222222</v>
@@ -33537,11 +34755,14 @@
       <c r="AC480" t="n">
         <v>0.6657083333333333</v>
       </c>
+      <c r="AF480" t="n">
+        <v>0.8367666666666665</v>
+      </c>
       <c r="AG480" t="n">
         <v>0.6899555555555554</v>
       </c>
       <c r="AH480" t="n">
-        <v>0.6978125000000001</v>
+        <v>0.6669230769230767</v>
       </c>
       <c r="AI480" t="n">
         <v>0.473225</v>
@@ -33581,11 +34802,14 @@
       <c r="AC481" t="n">
         <v>0.6474818181818182</v>
       </c>
+      <c r="AF481" t="n">
+        <v>0.8291600000000001</v>
+      </c>
       <c r="AG481" t="n">
         <v>0.7259625</v>
       </c>
       <c r="AH481" t="n">
-        <v>0.7151700000000001</v>
+        <v>0.5962888888888889</v>
       </c>
       <c r="AI481" t="n">
         <v>0.58578</v>
@@ -33625,11 +34849,14 @@
       <c r="AC482" t="n">
         <v>0.5884272727272726</v>
       </c>
+      <c r="AF482" t="n">
+        <v>0.7949857142857143</v>
+      </c>
       <c r="AG482" t="n">
         <v>0.6759777777777779</v>
       </c>
       <c r="AH482" t="n">
-        <v>0.7460874999999999</v>
+        <v>0.59738</v>
       </c>
       <c r="AI482" t="n">
         <v>0.5609749999999999</v>
@@ -33669,11 +34896,14 @@
       <c r="AC483" t="n">
         <v>0.6607461538461538</v>
       </c>
+      <c r="AF483" t="n">
+        <v>0.8379</v>
+      </c>
       <c r="AG483" t="n">
         <v>0.6821142857142857</v>
       </c>
       <c r="AH483" t="n">
-        <v>0.6716444444444445</v>
+        <v>0.7230111111111112</v>
       </c>
       <c r="AI483" t="n">
         <v>0.5564600000000001</v>
@@ -33713,11 +34943,14 @@
       <c r="AC484" t="n">
         <v>0.6403333333333333</v>
       </c>
+      <c r="AF484" t="n">
+        <v>0.75573</v>
+      </c>
       <c r="AG484" t="n">
         <v>0.616275</v>
       </c>
       <c r="AH484" t="n">
-        <v>0.8001111111111112</v>
+        <v>0.6018333333333333</v>
       </c>
       <c r="AI484" t="n">
         <v>0.6442125000000001</v>
@@ -33757,11 +34990,14 @@
       <c r="AC485" t="n">
         <v>0.5938999999999999</v>
       </c>
+      <c r="AF485" t="n">
+        <v>0.8803000000000001</v>
+      </c>
       <c r="AG485" t="n">
         <v>0.6479444444444445</v>
       </c>
       <c r="AH485" t="n">
-        <v>0.60615</v>
+        <v>0.5719624999999999</v>
       </c>
       <c r="AI485" t="n">
         <v>0.562275</v>
@@ -33801,11 +35037,14 @@
       <c r="AC486" t="n">
         <v>0.6617818181818181</v>
       </c>
+      <c r="AF486" t="n">
+        <v>0.79813</v>
+      </c>
       <c r="AG486" t="n">
         <v>0.5654125</v>
       </c>
       <c r="AH486" t="n">
-        <v>0.6726583333333332</v>
+        <v>0.603388888888889</v>
       </c>
       <c r="AI486" t="n">
         <v>0.5865250000000001</v>
@@ -33845,11 +35084,14 @@
       <c r="AC487" t="n">
         <v>0.7187000000000001</v>
       </c>
+      <c r="AF487" t="n">
+        <v>0.87492</v>
+      </c>
       <c r="AG487" t="n">
         <v>0.6277888888888888</v>
       </c>
       <c r="AH487" t="n">
-        <v>0.6137125</v>
+        <v>0.6064499999999999</v>
       </c>
       <c r="AI487" t="n">
         <v>0.6254666666666667</v>
@@ -33889,11 +35131,14 @@
       <c r="AC488" t="n">
         <v>0.6532749999999999</v>
       </c>
+      <c r="AF488" t="n">
+        <v>0.838225</v>
+      </c>
       <c r="AG488" t="n">
         <v>0.7060166666666667</v>
       </c>
       <c r="AH488" t="n">
-        <v>0.6932181818181818</v>
+        <v>0.6428222222222222</v>
       </c>
       <c r="AI488" t="n">
         <v>0.5931272727272727</v>
@@ -33933,11 +35178,14 @@
       <c r="AC489" t="n">
         <v>0.6956785714285714</v>
       </c>
+      <c r="AF489" t="n">
+        <v>0.8140500000000001</v>
+      </c>
       <c r="AG489" t="n">
         <v>0.6575571428571428</v>
       </c>
       <c r="AH489" t="n">
-        <v>0.7275666666666667</v>
+        <v>0.6355999999999999</v>
       </c>
       <c r="AI489" t="n">
         <v>0.7043928571428573</v>
@@ -33977,11 +35225,14 @@
       <c r="AC490" t="n">
         <v>0.70672</v>
       </c>
+      <c r="AF490" t="n">
+        <v>0.8540111111111112</v>
+      </c>
       <c r="AG490" t="n">
         <v>0.6117</v>
       </c>
       <c r="AH490" t="n">
-        <v>0.6887899999999999</v>
+        <v>0.6076600000000001</v>
       </c>
       <c r="AI490" t="n">
         <v>0.6163777777777777</v>
@@ -34018,11 +35269,14 @@
       <c r="AC491" t="n">
         <v>0.5745083333333333</v>
       </c>
+      <c r="AF491" t="n">
+        <v>0.8558666666666666</v>
+      </c>
       <c r="AG491" t="n">
         <v>0.60181</v>
       </c>
       <c r="AH491" t="n">
-        <v>0.6098</v>
+        <v>0.6063636363636363</v>
       </c>
       <c r="AI491" t="n">
         <v>0.5878583333333333</v>
@@ -34062,11 +35316,14 @@
       <c r="AC492" t="n">
         <v>0.6133583333333333</v>
       </c>
+      <c r="AF492" t="n">
+        <v>0.8560416666666667</v>
+      </c>
       <c r="AG492" t="n">
         <v>0.6725333333333333</v>
       </c>
       <c r="AH492" t="n">
-        <v>0.6169666666666667</v>
+        <v>0.5991153846153847</v>
       </c>
       <c r="AI492" t="n">
         <v>0.5871583333333334</v>
@@ -34106,11 +35363,14 @@
       <c r="AC493" t="n">
         <v>0.65625</v>
       </c>
+      <c r="AF493" t="n">
+        <v>0.861488888888889</v>
+      </c>
       <c r="AG493" t="n">
         <v>0.569925</v>
       </c>
       <c r="AH493" t="n">
-        <v>0.7438666666666667</v>
+        <v>0.6349818181818182</v>
       </c>
       <c r="AI493" t="n">
         <v>0.5515666666666666</v>
@@ -34150,11 +35410,14 @@
       <c r="AC494" t="n">
         <v>0.6596900000000001</v>
       </c>
+      <c r="AF494" t="n">
+        <v>0.8537333333333333</v>
+      </c>
       <c r="AG494" t="n">
         <v>0.6724636363636363</v>
       </c>
       <c r="AH494" t="n">
-        <v>0.6833874999999999</v>
+        <v>0.6494416666666667</v>
       </c>
       <c r="AI494" t="n">
         <v>0.583290909090909</v>
@@ -34194,11 +35457,14 @@
       <c r="AC495" t="n">
         <v>0.6137333333333334</v>
       </c>
+      <c r="AF495" t="n">
+        <v>0.7909555555555555</v>
+      </c>
       <c r="AG495" t="n">
         <v>0.6555363636363636</v>
       </c>
       <c r="AH495" t="n">
-        <v>0.63773</v>
+        <v>0.64103</v>
       </c>
       <c r="AI495" t="n">
         <v>0.5609166666666667</v>
@@ -34238,11 +35504,14 @@
       <c r="AC496" t="n">
         <v>0.6244071428571428</v>
       </c>
+      <c r="AF496" t="n">
+        <v>0.7771333333333333</v>
+      </c>
       <c r="AG496" t="n">
         <v>0.6922799999999999</v>
       </c>
       <c r="AH496" t="n">
-        <v>0.6243363636363636</v>
+        <v>0.6224090909090909</v>
       </c>
       <c r="AI496" t="n">
         <v>0.6091666666666665</v>
@@ -34282,11 +35551,14 @@
       <c r="AC497" t="n">
         <v>0.5975307692307692</v>
       </c>
+      <c r="AF497" t="n">
+        <v>0.7729363636363636</v>
+      </c>
       <c r="AG497" t="n">
         <v>0.6037777777777777</v>
       </c>
       <c r="AH497" t="n">
-        <v>0.60795</v>
+        <v>0.6326583333333332</v>
       </c>
       <c r="AI497" t="n">
         <v>0.5709799999999999</v>
@@ -34326,11 +35598,14 @@
       <c r="AC498" t="n">
         <v>0.6383727272727273</v>
       </c>
+      <c r="AF498" t="n">
+        <v>0.8871909090909091</v>
+      </c>
       <c r="AG498" t="n">
         <v>0.6193875000000001</v>
       </c>
       <c r="AH498" t="n">
-        <v>0.6485100000000001</v>
+        <v>0.5849599999999999</v>
       </c>
       <c r="AI498" t="n">
         <v>0.5998222222222221</v>
@@ -34370,11 +35645,14 @@
       <c r="AC499" t="n">
         <v>0.6384083333333334</v>
       </c>
+      <c r="AF499" t="n">
+        <v>0.7679333333333334</v>
+      </c>
       <c r="AG499" t="n">
         <v>0.6744375</v>
       </c>
       <c r="AH499" t="n">
-        <v>0.703325</v>
+        <v>0.5954545454545453</v>
       </c>
       <c r="AI499" t="n">
         <v>0.5218636363636363</v>
@@ -34414,11 +35692,14 @@
       <c r="AC500" t="n">
         <v>0.6275999999999999</v>
       </c>
+      <c r="AF500" t="n">
+        <v>0.852809090909091</v>
+      </c>
       <c r="AG500" t="n">
         <v>0.70008</v>
       </c>
       <c r="AH500" t="n">
-        <v>0.6943</v>
+        <v>0.5953833333333333</v>
       </c>
       <c r="AI500" t="n">
         <v>0.6140090909090909</v>
@@ -34458,11 +35739,14 @@
       <c r="AC501" t="n">
         <v>0.6562333333333333</v>
       </c>
+      <c r="AF501" t="n">
+        <v>0.853925</v>
+      </c>
       <c r="AG501" t="n">
         <v>0.6196545454545456</v>
       </c>
       <c r="AH501" t="n">
-        <v>0.6657727272727272</v>
+        <v>0.6526099999999999</v>
       </c>
       <c r="AI501" t="n">
         <v>0.6233333333333334</v>
@@ -34502,11 +35786,14 @@
       <c r="AC502" t="n">
         <v>0.6236636363636363</v>
       </c>
+      <c r="AF502" t="n">
+        <v>0.8632727272727273</v>
+      </c>
       <c r="AG502" t="n">
         <v>0.7309099999999999</v>
       </c>
       <c r="AH502" t="n">
-        <v>0.69696</v>
+        <v>0.6100125</v>
       </c>
       <c r="AI502" t="n">
         <v>0.6382636363636365</v>
@@ -34546,11 +35833,14 @@
       <c r="AC503" t="n">
         <v>0.5678</v>
       </c>
+      <c r="AF503" t="n">
+        <v>0.8147714285714286</v>
+      </c>
       <c r="AG503" t="n">
         <v>0.6705666666666666</v>
       </c>
       <c r="AH503" t="n">
-        <v>0.7774500000000001</v>
+        <v>0.6230416666666666</v>
       </c>
       <c r="AI503" t="n">
         <v>0.5552083333333334</v>
@@ -34594,7 +35884,7 @@
         <v>0.6718666666666667</v>
       </c>
       <c r="AH504" t="n">
-        <v>0.70885</v>
+        <v>0.7021857142857143</v>
       </c>
       <c r="AI504" t="n">
         <v>0.5549090909090908</v>
@@ -34638,7 +35928,7 @@
         <v>0.7518636363636362</v>
       </c>
       <c r="AH505" t="n">
-        <v>0.6255900000000001</v>
+        <v>0.6198571428571428</v>
       </c>
       <c r="AI505" t="n">
         <v>0.61391</v>
@@ -34682,7 +35972,7 @@
         <v>0.7943874999999999</v>
       </c>
       <c r="AH506" t="n">
-        <v>0.7702699999999999</v>
+        <v>0.6209100000000001</v>
       </c>
       <c r="AI506" t="n">
         <v>0.5387916666666667</v>
@@ -34726,7 +36016,7 @@
         <v>0.69035</v>
       </c>
       <c r="AH507" t="n">
-        <v>0.7666500000000001</v>
+        <v>0.6587333333333333</v>
       </c>
       <c r="AI507" t="n">
         <v>0.5796749999999999</v>
@@ -34770,7 +36060,7 @@
         <v>0.6579166666666666</v>
       </c>
       <c r="AH508" t="n">
-        <v>0.7059928571428572</v>
+        <v>0.6586636363636363</v>
       </c>
       <c r="AI508" t="n">
         <v>0.5518545454545455</v>
@@ -34814,7 +36104,7 @@
         <v>0.5816000000000001</v>
       </c>
       <c r="AH509" t="n">
-        <v>0.6476166666666666</v>
+        <v>0.6546000000000001</v>
       </c>
       <c r="AI509" t="n">
         <v>0.5947818181818182</v>
@@ -34858,7 +36148,7 @@
         <v>0.7370444444444444</v>
       </c>
       <c r="AH510" t="n">
-        <v>0.6961545454545454</v>
+        <v>0.6388777777777777</v>
       </c>
       <c r="AI510" t="n">
         <v>0.59485</v>
@@ -34902,7 +36192,7 @@
         <v>0.6631375</v>
       </c>
       <c r="AH511" t="n">
-        <v>0.62356</v>
+        <v>0.56611</v>
       </c>
       <c r="AI511" t="n">
         <v>0.5214846153846153</v>
@@ -34946,7 +36236,7 @@
         <v>0.6413454545454546</v>
       </c>
       <c r="AH512" t="n">
-        <v>0.6837999999999999</v>
+        <v>0.6301416666666667</v>
       </c>
       <c r="AI512" t="n">
         <v>0.6764363636363636</v>
@@ -34990,7 +36280,7 @@
         <v>0.6904888888888889</v>
       </c>
       <c r="AH513" t="n">
-        <v>0.7456727272727274</v>
+        <v>0.5802153846153846</v>
       </c>
       <c r="AI513" t="n">
         <v>0.5963499999999999</v>
@@ -35034,7 +36324,7 @@
         <v>0.6874714285714286</v>
       </c>
       <c r="AH514" t="n">
-        <v>0.7002999999999999</v>
+        <v>0.6435333333333334</v>
       </c>
       <c r="AI514" t="n">
         <v>0.5021545454545454</v>
@@ -35078,7 +36368,7 @@
         <v>0.6931666666666666</v>
       </c>
       <c r="AH515" t="n">
-        <v>0.7678272727272727</v>
+        <v>0.6172888888888889</v>
       </c>
       <c r="AI515" t="n">
         <v>0.5428000000000001</v>
@@ -35122,7 +36412,7 @@
         <v>0.6112299999999999</v>
       </c>
       <c r="AH516" t="n">
-        <v>0.6849666666666666</v>
+        <v>0.6019249999999999</v>
       </c>
       <c r="AI516" t="n">
         <v>0.49555</v>
@@ -35166,7 +36456,7 @@
         <v>0.6666818181818182</v>
       </c>
       <c r="AH517" t="n">
-        <v>0.6367</v>
+        <v>0.5482714285714286</v>
       </c>
       <c r="AI517" t="n">
         <v>0.52064</v>
@@ -35214,11 +36504,14 @@
       <c r="AC520" t="n">
         <v>0.1778257575757576</v>
       </c>
+      <c r="AF520" t="n">
+        <v>0.1211935483870968</v>
+      </c>
       <c r="AG520" t="n">
         <v>0.1444220588235294</v>
       </c>
       <c r="AH520" t="n">
-        <v>0.1384455882352941</v>
+        <v>0.1424968253968254</v>
       </c>
       <c r="AI520" t="n">
         <v>0.1300313432835821</v>
@@ -35252,11 +36545,14 @@
       <c r="AC521" t="n">
         <v>0.1586368421052632</v>
       </c>
+      <c r="AF521" t="n">
+        <v>0.02614615384615384</v>
+      </c>
       <c r="AG521" t="n">
         <v>0.1429</v>
       </c>
       <c r="AH521" t="n">
-        <v>0.1654202898550725</v>
+        <v>0.056375</v>
       </c>
       <c r="AI521" t="n">
         <v>0.16574375</v>
@@ -35290,11 +36586,14 @@
       <c r="AC522" t="n">
         <v>0.2495617647058823</v>
       </c>
+      <c r="AF522" t="n">
+        <v>0.1229172413793103</v>
+      </c>
       <c r="AG522" t="n">
         <v>0.2835</v>
       </c>
       <c r="AH522" t="n">
-        <v>0.29118</v>
+        <v>0.1445838709677419</v>
       </c>
       <c r="AI522" t="n">
         <v>0.3067285714285714</v>
@@ -35328,11 +36627,14 @@
       <c r="AC523" t="n">
         <v>0.2561083333333333</v>
       </c>
+      <c r="AF523" t="n">
+        <v>0.165432</v>
+      </c>
       <c r="AG523" t="n">
         <v>0.3022452380952381</v>
       </c>
       <c r="AH523" t="n">
-        <v>0.2673111111111111</v>
+        <v>0.257155</v>
       </c>
       <c r="AI523" t="n">
         <v>0.31178</v>
@@ -35366,11 +36668,14 @@
       <c r="AC524" t="n">
         <v>0.3331469387755102</v>
       </c>
+      <c r="AF524" t="n">
+        <v>0.2831285714285715</v>
+      </c>
       <c r="AG524" t="n">
         <v>0.3887216216216217</v>
       </c>
       <c r="AH524" t="n">
-        <v>0.31475</v>
+        <v>0.34870625</v>
       </c>
       <c r="AI524" t="n">
         <v>0.3213083333333334</v>
@@ -35404,11 +36709,14 @@
       <c r="AC525" t="n">
         <v>0.3252390243902439</v>
       </c>
+      <c r="AF525" t="n">
+        <v>0.2694428571428572</v>
+      </c>
       <c r="AG525" t="n">
         <v>0.4646130434782609</v>
       </c>
       <c r="AH525" t="n">
-        <v>0.3252085714285715</v>
+        <v>0.3548684210526316</v>
       </c>
       <c r="AI525" t="n">
         <v>0.3844896551724138</v>
@@ -35442,11 +36750,14 @@
       <c r="AC526" t="n">
         <v>0.3929862068965517</v>
       </c>
+      <c r="AF526" t="n">
+        <v>0.3458558823529412</v>
+      </c>
       <c r="AG526" t="n">
         <v>0.41598</v>
       </c>
       <c r="AH526" t="n">
-        <v>0.3329666666666667</v>
+        <v>0.4479972972972973</v>
       </c>
       <c r="AI526" t="n">
         <v>0.31800625</v>
@@ -35480,11 +36791,14 @@
       <c r="AC527" t="n">
         <v>0.3442854166666667</v>
       </c>
+      <c r="AF527" t="n">
+        <v>0.5026571428571428</v>
+      </c>
       <c r="AG527" t="n">
         <v>0.5046870967741935</v>
       </c>
       <c r="AH527" t="n">
-        <v>0.3363875</v>
+        <v>0.41466</v>
       </c>
       <c r="AI527" t="n">
         <v>0.2846541666666667</v>
@@ -35518,11 +36832,14 @@
       <c r="AC528" t="n">
         <v>0.4050230769230769</v>
       </c>
+      <c r="AF528" t="n">
+        <v>0.461745</v>
+      </c>
       <c r="AG528" t="n">
         <v>0.579425</v>
       </c>
       <c r="AH528" t="n">
-        <v>0.4138785714285714</v>
+        <v>0.3963542372881356</v>
       </c>
       <c r="AI528" t="n">
         <v>0.5116583333333334</v>
@@ -35556,11 +36873,14 @@
       <c r="AC529" t="n">
         <v>0.3247592592592592</v>
       </c>
+      <c r="AF529" t="n">
+        <v>0.493104347826087</v>
+      </c>
       <c r="AG529" t="n">
         <v>0.5007578947368421</v>
       </c>
       <c r="AH529" t="n">
-        <v>0.4658216216216217</v>
+        <v>0.4145571428571428</v>
       </c>
       <c r="AI529" t="n">
         <v>0.4508945454545455</v>
@@ -35585,11 +36905,14 @@
       <c r="AC530" t="n">
         <v>0.3995566037735849</v>
       </c>
+      <c r="AF530" t="n">
+        <v>0.5617090909090909</v>
+      </c>
       <c r="AG530" t="n">
         <v>0.5682999999999999</v>
       </c>
       <c r="AH530" t="n">
-        <v>0.4155509803921569</v>
+        <v>0.4618348837209303</v>
       </c>
       <c r="AI530" t="n">
         <v>0.4951224137931035</v>
@@ -35614,11 +36937,14 @@
       <c r="AC531" t="n">
         <v>0.4958045454545454</v>
       </c>
+      <c r="AF531" t="n">
+        <v>0.5871416666666667</v>
+      </c>
       <c r="AG531" t="n">
         <v>0.4866378378378379</v>
       </c>
       <c r="AH531" t="n">
-        <v>0.4341042553191488</v>
+        <v>0.5041283018867925</v>
       </c>
       <c r="AI531" t="n">
         <v>0.3783961538461539</v>
@@ -35643,11 +36969,14 @@
       <c r="AC532" t="n">
         <v>0.4621510638297872</v>
       </c>
+      <c r="AF532" t="n">
+        <v>0.7263055555555555</v>
+      </c>
       <c r="AG532" t="n">
         <v>0.3932771428571429</v>
       </c>
       <c r="AH532" t="n">
-        <v>0.4381095238095238</v>
+        <v>0.4644116279069767</v>
       </c>
       <c r="AI532" t="n">
         <v>0.5010883333333334</v>
@@ -35672,11 +37001,14 @@
       <c r="AC533" t="n">
         <v>0.4349719999999999</v>
       </c>
+      <c r="AF533" t="n">
+        <v>0.6344974999999999</v>
+      </c>
       <c r="AG533" t="n">
         <v>0.5558023809523809</v>
       </c>
       <c r="AH533" t="n">
-        <v>0.4011560975609756</v>
+        <v>0.5145844444444445</v>
       </c>
       <c r="AI533" t="n">
         <v>0.4608</v>
@@ -35701,11 +37033,14 @@
       <c r="AC534" t="n">
         <v>0.3115254545454545</v>
       </c>
+      <c r="AF534" t="n">
+        <v>0.7973315789473684</v>
+      </c>
       <c r="AG534" t="n">
         <v>0.6494636363636364</v>
       </c>
       <c r="AH534" t="n">
-        <v>0.4839763636363636</v>
+        <v>0.4305796296296296</v>
       </c>
       <c r="AI534" t="n">
         <v>0.4022145833333333</v>
@@ -35730,11 +37065,14 @@
       <c r="AC535" t="n">
         <v>0.5511894736842106</v>
       </c>
+      <c r="AF535" t="n">
+        <v>0.7573774193548386</v>
+      </c>
       <c r="AG535" t="n">
         <v>0.4816966666666668</v>
       </c>
       <c r="AH535" t="n">
-        <v>0.4271456140350877</v>
+        <v>0.547972</v>
       </c>
       <c r="AI535" t="n">
         <v>0.465167213114754</v>
@@ -35759,11 +37097,14 @@
       <c r="AC536" t="n">
         <v>0.4592083333333334</v>
       </c>
+      <c r="AF536" t="n">
+        <v>0.7032583333333333</v>
+      </c>
       <c r="AG536" t="n">
         <v>0.4411063829787234</v>
       </c>
       <c r="AH536" t="n">
-        <v>0.539571794871795</v>
+        <v>0.5807028571428572</v>
       </c>
       <c r="AI536" t="n">
         <v>0.3577081081081081</v>
@@ -35788,11 +37129,14 @@
       <c r="AC537" t="n">
         <v>0.5164607843137256</v>
       </c>
+      <c r="AF537" t="n">
+        <v>0.69116</v>
+      </c>
       <c r="AG537" t="n">
         <v>0.54195</v>
       </c>
       <c r="AH537" t="n">
-        <v>0.4696476923076923</v>
+        <v>0.5216203703703703</v>
       </c>
       <c r="AI537" t="n">
         <v>0.297085</v>
@@ -35817,11 +37161,14 @@
       <c r="AC538" t="n">
         <v>0.5510245283018868</v>
       </c>
+      <c r="AF538" t="n">
+        <v>0.7289473684210527</v>
+      </c>
       <c r="AG538" t="n">
         <v>0.6228867647058824</v>
       </c>
       <c r="AH538" t="n">
-        <v>0.4814236842105262</v>
+        <v>0.5408146341463413</v>
       </c>
       <c r="AI538" t="n">
         <v>0.4526016666666667</v>
@@ -35846,11 +37193,14 @@
       <c r="AC539" t="n">
         <v>0.3734129032258064</v>
       </c>
+      <c r="AF539" t="n">
+        <v>0.8590499999999999</v>
+      </c>
       <c r="AG539" t="n">
         <v>0.5045277777777778</v>
       </c>
       <c r="AH539" t="n">
-        <v>0.5746521739130435</v>
+        <v>0.588662</v>
       </c>
       <c r="AI539" t="n">
         <v>0.3811</v>
@@ -35875,11 +37225,14 @@
       <c r="AC540" t="n">
         <v>0.4671789473684211</v>
       </c>
+      <c r="AF540" t="n">
+        <v>0.71055</v>
+      </c>
       <c r="AG540" t="n">
         <v>0.6734275000000001</v>
       </c>
       <c r="AH540" t="n">
-        <v>0.5406166666666667</v>
+        <v>0.4647604651162791</v>
       </c>
       <c r="AI540" t="n">
         <v>0.4125803571428571</v>
@@ -35904,11 +37257,14 @@
       <c r="AC541" t="n">
         <v>0.4401520000000001</v>
       </c>
+      <c r="AF541" t="n">
+        <v>0.7131897435897435</v>
+      </c>
       <c r="AG541" t="n">
         <v>0.4816444444444445</v>
       </c>
       <c r="AH541" t="n">
-        <v>0.4610843749999999</v>
+        <v>0.479085</v>
       </c>
       <c r="AI541" t="n">
         <v>0.5831545454545455</v>
@@ -35933,11 +37289,14 @@
       <c r="AC542" t="n">
         <v>0.482588524590164</v>
       </c>
+      <c r="AF542" t="n">
+        <v>0.737990909090909</v>
+      </c>
       <c r="AG542" t="n">
         <v>0.5161395348837209</v>
       </c>
       <c r="AH542" t="n">
-        <v>0.41045</v>
+        <v>0.5543121951219513</v>
       </c>
       <c r="AI542" t="n">
         <v>0.4331245901639345</v>
@@ -35962,11 +37321,14 @@
       <c r="AC543" t="n">
         <v>0.5452616666666666</v>
       </c>
+      <c r="AF543" t="n">
+        <v>0.6332833333333333</v>
+      </c>
       <c r="AG543" t="n">
         <v>0.4877159090909091</v>
       </c>
       <c r="AH543" t="n">
-        <v>0.5829783783783784</v>
+        <v>0.5984227272727272</v>
       </c>
       <c r="AI543" t="n">
         <v>0.4620406779661017</v>
@@ -35991,11 +37353,14 @@
       <c r="AC544" t="n">
         <v>0.4851044444444444</v>
       </c>
+      <c r="AF544" t="n">
+        <v>0.7209125</v>
+      </c>
       <c r="AG544" t="n">
         <v>0.6173763157894737</v>
       </c>
       <c r="AH544" t="n">
-        <v>0.480835294117647</v>
+        <v>0.5302023255813954</v>
       </c>
       <c r="AI544" t="n">
         <v>0.4957734374999999</v>
@@ -36020,11 +37385,14 @@
       <c r="AC545" t="n">
         <v>0.5073206896551724</v>
       </c>
+      <c r="AF545" t="n">
+        <v>0.7447952380952381</v>
+      </c>
       <c r="AG545" t="n">
         <v>0.4667423076923077</v>
       </c>
       <c r="AH545" t="n">
-        <v>0.5861459459459459</v>
+        <v>0.4572047619047618</v>
       </c>
       <c r="AI545" t="n">
         <v>0.575545945945946</v>
@@ -36049,11 +37417,14 @@
       <c r="AC546" t="n">
         <v>0.5798599999999999</v>
       </c>
+      <c r="AF546" t="n">
+        <v>0.6713432432432432</v>
+      </c>
       <c r="AG546" t="n">
         <v>0.5142375</v>
       </c>
       <c r="AH546" t="n">
-        <v>0.4571</v>
+        <v>0.4304073170731707</v>
       </c>
       <c r="AI546" t="n">
         <v>0.482527868852459</v>
@@ -36078,11 +37449,14 @@
       <c r="AC547" t="n">
         <v>0.4528525423728814</v>
       </c>
+      <c r="AF547" t="n">
+        <v>0.61053125</v>
+      </c>
       <c r="AG547" t="n">
         <v>0.4867585365853659</v>
       </c>
       <c r="AH547" t="n">
-        <v>0.5774666666666667</v>
+        <v>0.5890893617021277</v>
       </c>
       <c r="AI547" t="n">
         <v>0.4267274509803923</v>
@@ -36107,11 +37481,14 @@
       <c r="AC548" t="n">
         <v>0.4840848484848485</v>
       </c>
+      <c r="AF548" t="n">
+        <v>0.6718214285714286</v>
+      </c>
       <c r="AG548" t="n">
         <v>0.5193512195121951</v>
       </c>
       <c r="AH548" t="n">
-        <v>0.5368424242424242</v>
+        <v>0.61514375</v>
       </c>
       <c r="AI548" t="n">
         <v>0.5417542372881355</v>
@@ -36136,11 +37513,14 @@
       <c r="AC549" t="n">
         <v>0.602350909090909</v>
       </c>
+      <c r="AF549" t="n">
+        <v>0.814084</v>
+      </c>
       <c r="AG549" t="n">
         <v>0.5403441860465117</v>
       </c>
       <c r="AH549" t="n">
-        <v>0.5178847826086955</v>
+        <v>0.7270243243243243</v>
       </c>
       <c r="AI549" t="n">
         <v>0.4767525423728814</v>
@@ -36165,11 +37545,14 @@
       <c r="AC550" t="n">
         <v>0.46843125</v>
       </c>
+      <c r="AF550" t="n">
+        <v>0.5715625</v>
+      </c>
       <c r="AG550" t="n">
         <v>0.442425</v>
       </c>
       <c r="AH550" t="n">
-        <v>0.4945203703703703</v>
+        <v>0.4462161764705882</v>
       </c>
       <c r="AI550" t="n">
         <v>0.4262102564102564</v>
@@ -36194,11 +37577,14 @@
       <c r="AC551" t="n">
         <v>0.4655830188679245</v>
       </c>
+      <c r="AF551" t="n">
+        <v>0.736153846153846</v>
+      </c>
       <c r="AG551" t="n">
         <v>0.499976923076923</v>
       </c>
       <c r="AH551" t="n">
-        <v>0.5444609756097561</v>
+        <v>0.5090660000000001</v>
       </c>
       <c r="AI551" t="n">
         <v>0.4427032786885246</v>
@@ -36223,11 +37609,14 @@
       <c r="AC552" t="n">
         <v>0.3781510204081632</v>
       </c>
+      <c r="AF552" t="n">
+        <v>0.85438</v>
+      </c>
       <c r="AG552" t="n">
         <v>0.5988116666666666</v>
       </c>
       <c r="AH552" t="n">
-        <v>0.4972017857142857</v>
+        <v>0.5216108695652173</v>
       </c>
       <c r="AI552" t="n">
         <v>0.3574173913043478</v>
@@ -36252,11 +37641,14 @@
       <c r="AC553" t="n">
         <v>0.4317800000000001</v>
       </c>
+      <c r="AF553" t="n">
+        <v>0.6457472222222221</v>
+      </c>
       <c r="AG553" t="n">
         <v>0.5693342857142857</v>
       </c>
       <c r="AH553" t="n">
-        <v>0.5013208333333333</v>
+        <v>0.4451173913043477</v>
       </c>
       <c r="AI553" t="n">
         <v>0.4145642857142858</v>
@@ -36281,11 +37673,14 @@
       <c r="AC554" t="n">
         <v>0.5104254545454546</v>
       </c>
+      <c r="AF554" t="n">
+        <v>0.7196106382978723</v>
+      </c>
       <c r="AG554" t="n">
         <v>0.4613942307692307</v>
       </c>
       <c r="AH554" t="n">
-        <v>0.5984833333333333</v>
+        <v>0.5187563636363636</v>
       </c>
       <c r="AI554" t="n">
         <v>0.4851067796610169</v>
@@ -36310,11 +37705,14 @@
       <c r="AC555" t="n">
         <v>0.5542551020408163</v>
       </c>
+      <c r="AF555" t="n">
+        <v>0.7562777777777777</v>
+      </c>
       <c r="AG555" t="n">
         <v>0.5178790697674418</v>
       </c>
       <c r="AH555" t="n">
-        <v>0.4133131578947368</v>
+        <v>0.5839103448275862</v>
       </c>
       <c r="AI555" t="n">
         <v>0.4232666666666667</v>
@@ -36339,11 +37737,14 @@
       <c r="AC556" t="n">
         <v>0.5214836065573771</v>
       </c>
+      <c r="AF556" t="n">
+        <v>0.7659095238095238</v>
+      </c>
       <c r="AG556" t="n">
         <v>0.5133842105263158</v>
       </c>
       <c r="AH556" t="n">
-        <v>0.4701102564102564</v>
+        <v>0.5669577777777778</v>
       </c>
       <c r="AI556" t="n">
         <v>0.444435</v>
@@ -36368,11 +37769,14 @@
       <c r="AC557" t="n">
         <v>0.386245283018868</v>
       </c>
+      <c r="AF557" t="n">
+        <v>0.844675</v>
+      </c>
       <c r="AG557" t="n">
         <v>0.6144459459459459</v>
       </c>
       <c r="AH557" t="n">
-        <v>0.457924</v>
+        <v>0.5235639999999999</v>
       </c>
       <c r="AI557" t="n">
         <v>0.41788</v>
@@ -36397,11 +37801,14 @@
       <c r="AC558" t="n">
         <v>0.4671999999999999</v>
       </c>
+      <c r="AF558" t="n">
+        <v>0.8064136363636364</v>
+      </c>
       <c r="AG558" t="n">
         <v>0.6063604651162789</v>
       </c>
       <c r="AH558" t="n">
-        <v>0.4429685185185185</v>
+        <v>0.5450291666666666</v>
       </c>
       <c r="AI558" t="n">
         <v>0.4011245901639344</v>
@@ -36426,11 +37833,14 @@
       <c r="AC559" t="n">
         <v>0.5137327586206897</v>
       </c>
+      <c r="AF559" t="n">
+        <v>0.6768302325581396</v>
+      </c>
       <c r="AG559" t="n">
         <v>0.5964913043478262</v>
       </c>
       <c r="AH559" t="n">
-        <v>0.4947477272727273</v>
+        <v>0.4485087719298246</v>
       </c>
       <c r="AI559" t="n">
         <v>0.4532693548387098</v>
@@ -36455,11 +37865,14 @@
       <c r="AC560" t="n">
         <v>0.5099728813559321</v>
       </c>
+      <c r="AF560" t="n">
+        <v>0.6789857142857143</v>
+      </c>
       <c r="AG560" t="n">
         <v>0.4655409090909091</v>
       </c>
       <c r="AH560" t="n">
-        <v>0.6247352941176471</v>
+        <v>0.4459489795918367</v>
       </c>
       <c r="AI560" t="n">
         <v>0.4451980392156863</v>
@@ -36484,11 +37897,14 @@
       <c r="AC561" t="n">
         <v>0.4863826923076923</v>
       </c>
+      <c r="AF561" t="n">
+        <v>0.7579411764705883</v>
+      </c>
       <c r="AG561" t="n">
         <v>0.5085512195121952</v>
       </c>
       <c r="AH561" t="n">
-        <v>0.5042452380952381</v>
+        <v>0.4193428571428572</v>
       </c>
       <c r="AI561" t="n">
         <v>0.5603049999999999</v>
@@ -36513,11 +37929,14 @@
       <c r="AC562" t="n">
         <v>0.453912962962963</v>
       </c>
+      <c r="AF562" t="n">
+        <v>0.7340083333333333</v>
+      </c>
       <c r="AG562" t="n">
         <v>0.5657425531914894</v>
       </c>
       <c r="AH562" t="n">
-        <v>0.5153166666666666</v>
+        <v>0.53844</v>
       </c>
       <c r="AI562" t="n">
         <v>0.5377527272727273</v>
@@ -36542,11 +37961,14 @@
       <c r="AC563" t="n">
         <v>0.4765818181818182</v>
       </c>
+      <c r="AF563" t="n">
+        <v>0.7832630434782609</v>
+      </c>
       <c r="AG563" t="n">
         <v>0.5546979591836736</v>
       </c>
       <c r="AH563" t="n">
-        <v>0.5991647058823528</v>
+        <v>0.5116681818181819</v>
       </c>
       <c r="AI563" t="n">
         <v>0.4258238095238095</v>
@@ -36571,11 +37993,14 @@
       <c r="AC564" t="n">
         <v>0.4980166666666667</v>
       </c>
+      <c r="AF564" t="n">
+        <v>0.6610627450980392</v>
+      </c>
       <c r="AG564" t="n">
         <v>0.5413347826086957</v>
       </c>
       <c r="AH564" t="n">
-        <v>0.5046194444444444</v>
+        <v>0.5013433962264151</v>
       </c>
       <c r="AI564" t="n">
         <v>0.3946571428571428</v>
@@ -36600,11 +38025,14 @@
       <c r="AC565" t="n">
         <v>0.5015952380952382</v>
       </c>
+      <c r="AF565" t="n">
+        <v>0.8073222222222223</v>
+      </c>
       <c r="AG565" t="n">
         <v>0.6386893617021278</v>
       </c>
       <c r="AH565" t="n">
-        <v>0.5434958333333334</v>
+        <v>0.5514325</v>
       </c>
       <c r="AI565" t="n">
         <v>0.397948076923077</v>
@@ -36629,11 +38057,14 @@
       <c r="AC566" t="n">
         <v>0.473925</v>
       </c>
+      <c r="AF566" t="n">
+        <v>0.770428</v>
+      </c>
       <c r="AG566" t="n">
         <v>0.5430470588235295</v>
       </c>
       <c r="AH566" t="n">
-        <v>0.4571097560975609</v>
+        <v>0.3930884615384614</v>
       </c>
       <c r="AI566" t="n">
         <v>0.4954880952380952</v>
@@ -36658,11 +38089,14 @@
       <c r="AC567" t="n">
         <v>0.5536673076923078</v>
       </c>
+      <c r="AF567" t="n">
+        <v>0.8293692307692309</v>
+      </c>
       <c r="AG567" t="n">
         <v>0.6642942307692307</v>
       </c>
       <c r="AH567" t="n">
-        <v>0.4632666666666667</v>
+        <v>0.6051605263157895</v>
       </c>
       <c r="AI567" t="n">
         <v>0.3712135135135136</v>
@@ -36687,11 +38121,14 @@
       <c r="AC568" t="n">
         <v>0.56925</v>
       </c>
+      <c r="AF568" t="n">
+        <v>0.7189634146341464</v>
+      </c>
       <c r="AG568" t="n">
         <v>0.5320285714285714</v>
       </c>
       <c r="AH568" t="n">
-        <v>0.4745111111111111</v>
+        <v>0.5004048780487805</v>
       </c>
       <c r="AI568" t="n">
         <v>0.5167102040816326</v>
@@ -36716,11 +38153,14 @@
       <c r="AC569" t="n">
         <v>0.4714163265306122</v>
       </c>
+      <c r="AF569" t="n">
+        <v>0.8308378378378379</v>
+      </c>
       <c r="AG569" t="n">
         <v>0.6177075000000001</v>
       </c>
       <c r="AH569" t="n">
-        <v>0.5479684210526315</v>
+        <v>0.5446294117647059</v>
       </c>
       <c r="AI569" t="n">
         <v>0.4900320754716981</v>
@@ -36745,11 +38185,14 @@
       <c r="AC570" t="n">
         <v>0.3889018518518519</v>
       </c>
+      <c r="AF570" t="n">
+        <v>0.7310076923076922</v>
+      </c>
       <c r="AG570" t="n">
         <v>0.5955615384615386</v>
       </c>
       <c r="AH570" t="n">
-        <v>0.4827871794871794</v>
+        <v>0.4728735849056604</v>
       </c>
       <c r="AI570" t="n">
         <v>0.5515588235294117</v>
@@ -36774,11 +38217,14 @@
       <c r="AC571" t="n">
         <v>0.5314942028985506</v>
       </c>
+      <c r="AF571" t="n">
+        <v>0.7974440000000002</v>
+      </c>
       <c r="AG571" t="n">
         <v>0.5553441860465116</v>
       </c>
       <c r="AH571" t="n">
-        <v>0.5517641025641026</v>
+        <v>0.5130416666666666</v>
       </c>
       <c r="AI571" t="n">
         <v>0.4389015873015872</v>
@@ -36803,11 +38249,14 @@
       <c r="AC572" t="n">
         <v>0.4576981818181818</v>
       </c>
+      <c r="AF572" t="n">
+        <v>0.8205107142857144</v>
+      </c>
       <c r="AG572" t="n">
         <v>0.4775645833333333</v>
       </c>
       <c r="AH572" t="n">
-        <v>0.4534483870967742</v>
+        <v>0.446286440677966</v>
       </c>
       <c r="AI572" t="n">
         <v>0.5389327868852459</v>
@@ -36832,11 +38281,14 @@
       <c r="AC573" t="n">
         <v>0.4552840000000001</v>
       </c>
+      <c r="AF573" t="n">
+        <v>0.7170222222222222</v>
+      </c>
       <c r="AG573" t="n">
         <v>0.4887617647058824</v>
       </c>
       <c r="AH573" t="n">
-        <v>0.4845145454545455</v>
+        <v>0.3961021276595745</v>
       </c>
       <c r="AI573" t="n">
         <v>0.4695723404255319</v>
@@ -36861,11 +38313,14 @@
       <c r="AC574" t="n">
         <v>0.5154547169811321</v>
       </c>
+      <c r="AF574" t="n">
+        <v>0.7901172413793105</v>
+      </c>
       <c r="AG574" t="n">
         <v>0.5916138888888889</v>
       </c>
       <c r="AH574" t="n">
-        <v>0.5176224489795919</v>
+        <v>0.5626132075471697</v>
       </c>
       <c r="AI574" t="n">
         <v>0.5264584615384615</v>
@@ -36890,11 +38345,14 @@
       <c r="AC575" t="n">
         <v>0.46138125</v>
       </c>
+      <c r="AF575" t="n">
+        <v>0.8535115384615385</v>
+      </c>
       <c r="AG575" t="n">
         <v>0.5611488888888888</v>
       </c>
       <c r="AH575" t="n">
-        <v>0.5791434782608695</v>
+        <v>0.5450594594594594</v>
       </c>
       <c r="AI575" t="n">
         <v>0.4963703703703704</v>
@@ -36919,11 +38377,14 @@
       <c r="AC576" t="n">
         <v>0.5618811320754716</v>
       </c>
+      <c r="AF576" t="n">
+        <v>0.7951052631578946</v>
+      </c>
       <c r="AG576" t="n">
         <v>0.5429072727272727</v>
       </c>
       <c r="AH576" t="n">
-        <v>0.5206872727272727</v>
+        <v>0.620164</v>
       </c>
       <c r="AI576" t="n">
         <v>0.4018028571428571</v>
@@ -36948,11 +38409,14 @@
       <c r="AC577" t="n">
         <v>0.4938596491228071</v>
       </c>
+      <c r="AF577" t="n">
+        <v>0.714855</v>
+      </c>
       <c r="AG577" t="n">
         <v>0.6382439024390244</v>
       </c>
       <c r="AH577" t="n">
-        <v>0.43875625</v>
+        <v>0.5080291666666666</v>
       </c>
       <c r="AI577" t="n">
         <v>0.4824263157894737</v>
@@ -36977,11 +38441,14 @@
       <c r="AC578" t="n">
         <v>0.5270279999999999</v>
       </c>
+      <c r="AF578" t="n">
+        <v>0.8714857142857143</v>
+      </c>
       <c r="AG578" t="n">
         <v>0.6048185185185184</v>
       </c>
       <c r="AH578" t="n">
-        <v>0.4515955555555555</v>
+        <v>0.4752117647058823</v>
       </c>
       <c r="AI578" t="n">
         <v>0.4637245901639344</v>
@@ -37006,11 +38473,14 @@
       <c r="AC579" t="n">
         <v>0.4145636363636363</v>
       </c>
+      <c r="AF579" t="n">
+        <v>0.8457357142857143</v>
+      </c>
       <c r="AG579" t="n">
         <v>0.5165086956521739</v>
       </c>
       <c r="AH579" t="n">
-        <v>0.6500454545454546</v>
+        <v>0.3754323529411765</v>
       </c>
       <c r="AI579" t="n">
         <v>0.4540272727272727</v>
@@ -37035,11 +38505,14 @@
       <c r="AC580" t="n">
         <v>0.4867090909090909</v>
       </c>
+      <c r="AF580" t="n">
+        <v>0.9195</v>
+      </c>
       <c r="AG580" t="n">
         <v>0.6554473684210527</v>
       </c>
       <c r="AH580" t="n">
-        <v>0.5262333333333333</v>
+        <v>0.5023214285714285</v>
       </c>
       <c r="AI580" t="n">
         <v>0.4959056603773584</v>
@@ -37064,11 +38537,14 @@
       <c r="AC581" t="n">
         <v>0.4416783333333333</v>
       </c>
+      <c r="AF581" t="n">
+        <v>0.734874074074074</v>
+      </c>
       <c r="AG581" t="n">
         <v>0.61</v>
       </c>
       <c r="AH581" t="n">
-        <v>0.5362133333333333</v>
+        <v>0.4366617021276596</v>
       </c>
       <c r="AI581" t="n">
         <v>0.4562163636363637</v>
@@ -37093,11 +38569,14 @@
       <c r="AC582" t="n">
         <v>0.4763433333333334</v>
       </c>
+      <c r="AF582" t="n">
+        <v>0.8707457142857143</v>
+      </c>
       <c r="AG582" t="n">
         <v>0.5082950000000001</v>
       </c>
       <c r="AH582" t="n">
-        <v>0.5075119047619048</v>
+        <v>0.5312227272727272</v>
       </c>
       <c r="AI582" t="n">
         <v>0.5284689655172413</v>
@@ -37122,11 +38601,14 @@
       <c r="AC583" t="n">
         <v>0.5356261904761905</v>
       </c>
+      <c r="AF583" t="n">
+        <v>0.7515081081081081</v>
+      </c>
       <c r="AG583" t="n">
         <v>0.5488657142857143</v>
       </c>
       <c r="AH583" t="n">
-        <v>0.5325976744186046</v>
+        <v>0.5294325581395349</v>
       </c>
       <c r="AI583" t="n">
         <v>0.4816906976744186</v>
@@ -37151,11 +38633,14 @@
       <c r="AC584" t="n">
         <v>0.4988000000000001</v>
       </c>
+      <c r="AF584" t="n">
+        <v>0.8834705882352941</v>
+      </c>
       <c r="AG584" t="n">
         <v>0.4263096153846154</v>
       </c>
       <c r="AH584" t="n">
-        <v>0.4194260869565217</v>
+        <v>0.585445283018868</v>
       </c>
       <c r="AI584" t="n">
         <v>0.5130322580645161</v>
@@ -37180,11 +38665,14 @@
       <c r="AC585" t="n">
         <v>0.4746367647058825</v>
       </c>
+      <c r="AF585" t="n">
+        <v>0.8111781250000001</v>
+      </c>
       <c r="AG585" t="n">
         <v>0.542578</v>
       </c>
       <c r="AH585" t="n">
-        <v>0.5485529411764707</v>
+        <v>0.5382116279069767</v>
       </c>
       <c r="AI585" t="n">
         <v>0.4921869565217391</v>
@@ -37209,11 +38697,14 @@
       <c r="AC586" t="n">
         <v>0.5125636363636364</v>
       </c>
+      <c r="AF586" t="n">
+        <v>0.8330000000000001</v>
+      </c>
       <c r="AG586" t="n">
         <v>0.6687906250000001</v>
       </c>
       <c r="AH586" t="n">
-        <v>0.5197780000000001</v>
+        <v>0.6484263157894737</v>
       </c>
       <c r="AI586" t="n">
         <v>0.4462366666666667</v>
@@ -37238,11 +38729,14 @@
       <c r="AC587" t="n">
         <v>0.4961435483870968</v>
       </c>
+      <c r="AF587" t="n">
+        <v>0.6783750000000001</v>
+      </c>
       <c r="AG587" t="n">
         <v>0.5851883333333333</v>
       </c>
       <c r="AH587" t="n">
-        <v>0.4922756756756757</v>
+        <v>0.49578125</v>
       </c>
       <c r="AI587" t="n">
         <v>0.4618345454545454</v>
@@ -37267,11 +38761,14 @@
       <c r="AC588" t="n">
         <v>0.5781661016949152</v>
       </c>
+      <c r="AF588" t="n">
+        <v>0.893804347826087</v>
+      </c>
       <c r="AG588" t="n">
         <v>0.5338622641509434</v>
       </c>
       <c r="AH588" t="n">
-        <v>0.5408148936170212</v>
+        <v>0.6368605263157895</v>
       </c>
       <c r="AI588" t="n">
         <v>0.5012519999999999</v>
@@ -37296,11 +38793,14 @@
       <c r="AC589" t="n">
         <v>0.4489958333333333</v>
       </c>
+      <c r="AF589" t="n">
+        <v>0.968</v>
+      </c>
       <c r="AG589" t="n">
         <v>0.6660233333333333</v>
       </c>
       <c r="AH589" t="n">
-        <v>0.5243830188679246</v>
+        <v>0.6440466666666667</v>
       </c>
       <c r="AI589" t="n">
         <v>0.5026981132075472</v>
@@ -37325,11 +38825,14 @@
       <c r="AC590" t="n">
         <v>0.484944</v>
       </c>
+      <c r="AF590" t="n">
+        <v>0.86465</v>
+      </c>
       <c r="AG590" t="n">
         <v>0.622885</v>
       </c>
       <c r="AH590" t="n">
-        <v>0.5138934782608696</v>
+        <v>0.4693708333333335</v>
       </c>
       <c r="AI590" t="n">
         <v>0.4446111111111111</v>
@@ -37354,11 +38857,14 @@
       <c r="AC591" t="n">
         <v>0.4910307692307692</v>
       </c>
+      <c r="AF591" t="n">
+        <v>0.77676</v>
+      </c>
       <c r="AG591" t="n">
         <v>0.477947619047619</v>
       </c>
       <c r="AH591" t="n">
-        <v>0.447845652173913</v>
+        <v>0.463669090909091</v>
       </c>
       <c r="AI591" t="n">
         <v>0.4232176470588236</v>
@@ -37383,11 +38889,14 @@
       <c r="AC592" t="n">
         <v>0.5456555555555556</v>
       </c>
+      <c r="AF592" t="n">
+        <v>0.7865782608695653</v>
+      </c>
       <c r="AG592" t="n">
         <v>0.4996968750000001</v>
       </c>
       <c r="AH592" t="n">
-        <v>0.4880238095238095</v>
+        <v>0.643213888888889</v>
       </c>
       <c r="AI592" t="n">
         <v>0.5659461538461539</v>
@@ -37412,11 +38921,14 @@
       <c r="AC593" t="n">
         <v>0.460562</v>
       </c>
+      <c r="AF593" t="n">
+        <v>0.7292272727272727</v>
+      </c>
       <c r="AG593" t="n">
         <v>0.5798840000000002</v>
       </c>
       <c r="AH593" t="n">
-        <v>0.537166</v>
+        <v>0.4876681818181819</v>
       </c>
       <c r="AI593" t="n">
         <v>0.4670844827586206</v>
@@ -37441,11 +38953,14 @@
       <c r="AC594" t="n">
         <v>0.494990909090909</v>
       </c>
+      <c r="AF594" t="n">
+        <v>0.7837212121212122</v>
+      </c>
       <c r="AG594" t="n">
         <v>0.446626923076923</v>
       </c>
       <c r="AH594" t="n">
-        <v>0.5431999999999999</v>
+        <v>0.4200947368421052</v>
       </c>
       <c r="AI594" t="n">
         <v>0.5047617021276595</v>
@@ -37470,11 +38985,14 @@
       <c r="AC595" t="n">
         <v>0.4614648148148149</v>
       </c>
+      <c r="AF595" t="n">
+        <v>0.8800653846153847</v>
+      </c>
       <c r="AG595" t="n">
         <v>0.5939585365853658</v>
       </c>
       <c r="AH595" t="n">
-        <v>0.5528631578947367</v>
+        <v>0.5413090909090909</v>
       </c>
       <c r="AI595" t="n">
         <v>0.5065603773584906</v>
@@ -37499,11 +39017,14 @@
       <c r="AC596" t="n">
         <v>0.4555960784313727</v>
       </c>
+      <c r="AF596" t="n">
+        <v>0.7243535714285715</v>
+      </c>
       <c r="AG596" t="n">
         <v>0.6019325581395348</v>
       </c>
       <c r="AH596" t="n">
-        <v>0.5157863636363637</v>
+        <v>0.5092833333333333</v>
       </c>
       <c r="AI596" t="n">
         <v>0.4321127659574467</v>
@@ -37528,11 +39049,14 @@
       <c r="AC597" t="n">
         <v>0.499428</v>
       </c>
+      <c r="AF597" t="n">
+        <v>0.6785035714285714</v>
+      </c>
       <c r="AG597" t="n">
         <v>0.5208736842105263</v>
       </c>
       <c r="AH597" t="n">
-        <v>0.5373416666666667</v>
+        <v>0.4566142857142857</v>
       </c>
       <c r="AI597" t="n">
         <v>0.4917372549019607</v>
@@ -37557,11 +39081,14 @@
       <c r="AC598" t="n">
         <v>0.5547301587301587</v>
       </c>
+      <c r="AF598" t="n">
+        <v>0.9159333333333334</v>
+      </c>
       <c r="AG598" t="n">
         <v>0.4400714285714286</v>
       </c>
       <c r="AH598" t="n">
-        <v>0.4983875</v>
+        <v>0.4780431818181819</v>
       </c>
       <c r="AI598" t="n">
         <v>0.4583737704918033</v>
@@ -37586,11 +39113,14 @@
       <c r="AC599" t="n">
         <v>0.555325</v>
       </c>
+      <c r="AF599" t="n">
+        <v>0.8608500000000001</v>
+      </c>
       <c r="AG599" t="n">
         <v>0.4712206896551724</v>
       </c>
       <c r="AH599" t="n">
-        <v>0.4987591836734694</v>
+        <v>0.3679150943396227</v>
       </c>
       <c r="AI599" t="n">
         <v>0.442138775510204</v>
@@ -37615,11 +39145,14 @@
       <c r="AC600" t="n">
         <v>0.5739622950819672</v>
       </c>
+      <c r="AF600" t="n">
+        <v>0.7267305555555557</v>
+      </c>
       <c r="AG600" t="n">
         <v>0.6081968750000001</v>
       </c>
       <c r="AH600" t="n">
-        <v>0.50485</v>
+        <v>0.5568230769230769</v>
       </c>
       <c r="AI600" t="n">
         <v>0.5020217391304347</v>
@@ -37644,11 +39177,14 @@
       <c r="AC601" t="n">
         <v>0.4337241379310345</v>
       </c>
+      <c r="AF601" t="n">
+        <v>0.9213650000000001</v>
+      </c>
       <c r="AG601" t="n">
         <v>0.4639152173913043</v>
       </c>
       <c r="AH601" t="n">
-        <v>0.5294414634146343</v>
+        <v>0.4079645161290323</v>
       </c>
       <c r="AI601" t="n">
         <v>0.48162</v>
@@ -37673,11 +39209,14 @@
       <c r="AC602" t="n">
         <v>0.4740122807017544</v>
       </c>
+      <c r="AF602" t="n">
+        <v>0.8507416666666666</v>
+      </c>
       <c r="AG602" t="n">
         <v>0.6336108108108109</v>
       </c>
       <c r="AH602" t="n">
-        <v>0.5443899999999999</v>
+        <v>0.53632</v>
       </c>
       <c r="AI602" t="n">
         <v>0.5103782608695653</v>
@@ -37702,11 +39241,14 @@
       <c r="AC603" t="n">
         <v>0.4773112903225806</v>
       </c>
+      <c r="AF603" t="n">
+        <v>0.7035791666666666</v>
+      </c>
       <c r="AG603" t="n">
         <v>0.46076</v>
       </c>
       <c r="AH603" t="n">
-        <v>0.6180176470588236</v>
+        <v>0.5039468085106383</v>
       </c>
       <c r="AI603" t="n">
         <v>0.567101923076923</v>
@@ -37731,11 +39273,14 @@
       <c r="AC604" t="n">
         <v>0.4504599999999999</v>
       </c>
+      <c r="AF604" t="n">
+        <v>0.6684433333333334</v>
+      </c>
       <c r="AG604" t="n">
         <v>0.6705846153846153</v>
       </c>
       <c r="AH604" t="n">
-        <v>0.5224961538461538</v>
+        <v>0.5434708333333333</v>
       </c>
       <c r="AI604" t="n">
         <v>0.4864060606060606</v>
@@ -37760,11 +39305,14 @@
       <c r="AC605" t="n">
         <v>0.4857470588235293</v>
       </c>
+      <c r="AF605" t="n">
+        <v>0.6809564102564102</v>
+      </c>
       <c r="AG605" t="n">
         <v>0.6011774193548388</v>
       </c>
       <c r="AH605" t="n">
-        <v>0.6059823529411765</v>
+        <v>0.3950864864864864</v>
       </c>
       <c r="AI605" t="n">
         <v>0.4698021739130435</v>
@@ -37793,7 +39341,7 @@
         <v>0.5838275000000001</v>
       </c>
       <c r="AH606" t="n">
-        <v>0.5115878787878788</v>
+        <v>0.5844219512195122</v>
       </c>
       <c r="AI606" t="n">
         <v>0.4769766666666667</v>
@@ -37822,7 +39370,7 @@
         <v>0.5910333333333333</v>
       </c>
       <c r="AH607" t="n">
-        <v>0.4890975</v>
+        <v>0.4685553571428571</v>
       </c>
       <c r="AI607" t="n">
         <v>0.5219344262295083</v>
@@ -37851,7 +39399,7 @@
         <v>0.541629268292683</v>
       </c>
       <c r="AH608" t="n">
-        <v>0.5698746031746031</v>
+        <v>0.4587390243902439</v>
       </c>
       <c r="AI608" t="n">
         <v>0.467019696969697</v>
@@ -37880,7 +39428,7 @@
         <v>0.6393599999999999</v>
       </c>
       <c r="AH609" t="n">
-        <v>0.546662</v>
+        <v>0.5492148936170212</v>
       </c>
       <c r="AI609" t="n">
         <v>0.4993666666666666</v>
@@ -37909,7 +39457,7 @@
         <v>0.5253106382978723</v>
       </c>
       <c r="AH610" t="n">
-        <v>0.42738125</v>
+        <v>0.5021342105263158</v>
       </c>
       <c r="AI610" t="n">
         <v>0.4155879999999999</v>
@@ -37938,7 +39486,7 @@
         <v>0.52815</v>
       </c>
       <c r="AH611" t="n">
-        <v>0.536774358974359</v>
+        <v>0.4526240740740742</v>
       </c>
       <c r="AI611" t="n">
         <v>0.535139534883721</v>
@@ -37967,7 +39515,7 @@
         <v>0.5162054054054054</v>
       </c>
       <c r="AH612" t="n">
-        <v>0.4660133333333333</v>
+        <v>0.4582279069767442</v>
       </c>
       <c r="AI612" t="n">
         <v>0.4739463414634146</v>
@@ -37996,7 +39544,7 @@
         <v>0.6759567567567568</v>
       </c>
       <c r="AH613" t="n">
-        <v>0.4918965517241379</v>
+        <v>0.4164564102564103</v>
       </c>
       <c r="AI613" t="n">
         <v>0.5428290909090909</v>
@@ -38025,7 +39573,7 @@
         <v>0.4732853658536585</v>
       </c>
       <c r="AH614" t="n">
-        <v>0.5395061224489796</v>
+        <v>0.5750175</v>
       </c>
       <c r="AI614" t="n">
         <v>0.4532660377358492</v>
@@ -38054,7 +39602,7 @@
         <v>0.681017142857143</v>
       </c>
       <c r="AH615" t="n">
-        <v>0.4536641509433961</v>
+        <v>0.5425775510204082</v>
       </c>
       <c r="AI615" t="n">
         <v>0.4543424242424242</v>
@@ -38083,7 +39631,7 @@
         <v>0.5610877551020409</v>
       </c>
       <c r="AH616" t="n">
-        <v>0.4968476190476191</v>
+        <v>0.5413406779661017</v>
       </c>
       <c r="AI616" t="n">
         <v>0.4755127659574467</v>
@@ -38112,7 +39660,7 @@
         <v>0.4817318181818181</v>
       </c>
       <c r="AH617" t="n">
-        <v>0.5612304347826086</v>
+        <v>0.4880161290322581</v>
       </c>
       <c r="AI617" t="n">
         <v>0.377054</v>
@@ -38141,7 +39689,7 @@
         <v>0.631939393939394</v>
       </c>
       <c r="AH618" t="n">
-        <v>0.5371017857142858</v>
+        <v>0.5454039215686275</v>
       </c>
       <c r="AI618" t="n">
         <v>0.4300561403508771</v>
@@ -38170,7 +39718,7 @@
         <v>0.515921212121212</v>
       </c>
       <c r="AH619" t="n">
-        <v>0.5058341463414634</v>
+        <v>0.5821522727272727</v>
       </c>
       <c r="AI619" t="n">
         <v>0.5009944444444445</v>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -7466,6 +7466,9 @@
       <c r="AC91" t="n">
         <v>0.8498916666666666</v>
       </c>
+      <c r="AF91" t="n">
+        <v>0.7837869565217394</v>
+      </c>
       <c r="AG91" t="n">
         <v>0.834263888888889</v>
       </c>
@@ -7540,6 +7543,9 @@
       <c r="AC92" t="n">
         <v>0.89875</v>
       </c>
+      <c r="AF92" t="n">
+        <v>0.6651650000000001</v>
+      </c>
       <c r="AG92" t="n">
         <v>0.9011121951219512</v>
       </c>
@@ -7614,6 +7620,9 @@
       <c r="AC93" t="n">
         <v>0.87325625</v>
       </c>
+      <c r="AF93" t="n">
+        <v>0.7490516666666666</v>
+      </c>
       <c r="AG93" t="n">
         <v>0.8462468750000001</v>
       </c>
@@ -7688,6 +7697,9 @@
       <c r="AC94" t="n">
         <v>0.8562166666666666</v>
       </c>
+      <c r="AF94" t="n">
+        <v>0.7768717391304348</v>
+      </c>
       <c r="AG94" t="n">
         <v>0.8884404761904763</v>
       </c>
@@ -7762,6 +7774,9 @@
       <c r="AC95" t="n">
         <v>0.86829375</v>
       </c>
+      <c r="AF95" t="n">
+        <v>0.8487095238095238</v>
+      </c>
       <c r="AG95" t="n">
         <v>0.8711861111111112</v>
       </c>
@@ -7836,6 +7851,9 @@
       <c r="AC96" t="n">
         <v>0.8327052631578947</v>
       </c>
+      <c r="AF96" t="n">
+        <v>0.7357827586206895</v>
+      </c>
       <c r="AG96" t="n">
         <v>0.857909375</v>
       </c>
@@ -7910,6 +7928,9 @@
       <c r="AC97" t="n">
         <v>0.8147647058823528</v>
       </c>
+      <c r="AF97" t="n">
+        <v>0.7370184210526316</v>
+      </c>
       <c r="AG97" t="n">
         <v>0.8854935483870968</v>
       </c>
@@ -7984,6 +8005,9 @@
       <c r="AC98" t="n">
         <v>0.8474666666666667</v>
       </c>
+      <c r="AF98" t="n">
+        <v>0.819178</v>
+      </c>
       <c r="AG98" t="n">
         <v>0.8519176470588236</v>
       </c>
@@ -8058,6 +8082,9 @@
       <c r="AC99" t="n">
         <v>0.8588611111111111</v>
       </c>
+      <c r="AF99" t="n">
+        <v>0.7766933333333335</v>
+      </c>
       <c r="AG99" t="n">
         <v>0.8394272727272728</v>
       </c>
@@ -8132,6 +8159,9 @@
       <c r="AC100" t="n">
         <v>0.8243916666666666</v>
       </c>
+      <c r="AF100" t="n">
+        <v>0.8443446808510637</v>
+      </c>
       <c r="AG100" t="n">
         <v>0.8813866666666667</v>
       </c>
@@ -8206,6 +8236,9 @@
       <c r="AC101" t="n">
         <v>0.817807142857143</v>
       </c>
+      <c r="AF101" t="n">
+        <v>0.7568620689655172</v>
+      </c>
       <c r="AG101" t="n">
         <v>0.8519739130434781</v>
       </c>
@@ -8280,6 +8313,9 @@
       <c r="AC102" t="n">
         <v>0.8752421052631579</v>
       </c>
+      <c r="AF102" t="n">
+        <v>0.7723093023255815</v>
+      </c>
       <c r="AG102" t="n">
         <v>0.8819733333333334</v>
       </c>
@@ -8354,6 +8390,9 @@
       <c r="AC103" t="n">
         <v>0.8328842105263159</v>
       </c>
+      <c r="AF103" t="n">
+        <v>0.7391052631578947</v>
+      </c>
       <c r="AG103" t="n">
         <v>0.8554162790697677</v>
       </c>
@@ -8427,6 +8466,9 @@
       </c>
       <c r="AC104" t="n">
         <v>0.8440260869565218</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0.7095041666666667</v>
       </c>
       <c r="AG104" t="n">
         <v>0.8421581395348837</v>
@@ -15220,6 +15262,9 @@
       <c r="AC194" t="n">
         <v>1</v>
       </c>
+      <c r="AF194" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG194" t="n">
         <v>1</v>
       </c>
@@ -15294,6 +15339,9 @@
       <c r="AC195" t="n">
         <v>1</v>
       </c>
+      <c r="AF195" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG195" t="n">
         <v>1</v>
       </c>
@@ -15368,6 +15416,9 @@
       <c r="AC196" t="n">
         <v>1</v>
       </c>
+      <c r="AF196" t="n">
+        <v>0.5454545454545454</v>
+      </c>
       <c r="AG196" t="n">
         <v>1</v>
       </c>
@@ -15442,6 +15493,9 @@
       <c r="AC197" t="n">
         <v>1</v>
       </c>
+      <c r="AF197" t="n">
+        <v>0.375</v>
+      </c>
       <c r="AG197" t="n">
         <v>1</v>
       </c>
@@ -15516,6 +15570,9 @@
       <c r="AC198" t="n">
         <v>1</v>
       </c>
+      <c r="AF198" t="n">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AG198" t="n">
         <v>1</v>
       </c>
@@ -15590,6 +15647,9 @@
       <c r="AC199" t="n">
         <v>1</v>
       </c>
+      <c r="AF199" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="AG199" t="n">
         <v>1</v>
       </c>
@@ -15664,6 +15724,9 @@
       <c r="AC200" t="n">
         <v>1</v>
       </c>
+      <c r="AF200" t="n">
+        <v>0.625</v>
+      </c>
       <c r="AG200" t="n">
         <v>1</v>
       </c>
@@ -15738,6 +15801,9 @@
       <c r="AC201" t="n">
         <v>1</v>
       </c>
+      <c r="AF201" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AG201" t="n">
         <v>1</v>
       </c>
@@ -15812,6 +15878,9 @@
       <c r="AC202" t="n">
         <v>1</v>
       </c>
+      <c r="AF202" t="n">
+        <v>0.4444444444444444</v>
+      </c>
       <c r="AG202" t="n">
         <v>1</v>
       </c>
@@ -15886,6 +15955,9 @@
       <c r="AC203" t="n">
         <v>1</v>
       </c>
+      <c r="AF203" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AG203" t="n">
         <v>1</v>
       </c>
@@ -15960,6 +16032,9 @@
       <c r="AC204" t="n">
         <v>1</v>
       </c>
+      <c r="AF204" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG204" t="n">
         <v>1</v>
       </c>
@@ -16034,6 +16109,9 @@
       <c r="AC205" t="n">
         <v>1</v>
       </c>
+      <c r="AF205" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AG205" t="n">
         <v>1</v>
       </c>
@@ -16108,6 +16186,9 @@
       <c r="AC206" t="n">
         <v>1</v>
       </c>
+      <c r="AF206" t="n">
+        <v>0.6153846153846154</v>
+      </c>
       <c r="AG206" t="n">
         <v>1</v>
       </c>
@@ -16181,6 +16262,9 @@
       </c>
       <c r="AC207" t="n">
         <v>1</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>0.6</v>
       </c>
       <c r="AG207" t="n">
         <v>1</v>
@@ -22974,6 +23058,9 @@
       <c r="AC298" t="n">
         <v>0.6199416666666667</v>
       </c>
+      <c r="AF298" t="n">
+        <v>0.9350399999999999</v>
+      </c>
       <c r="AG298" t="n">
         <v>0.6577888888888889</v>
       </c>
@@ -23048,6 +23135,9 @@
       <c r="AC299" t="n">
         <v>0.5825699999999999</v>
       </c>
+      <c r="AF299" t="n">
+        <v>0.9514799999999999</v>
+      </c>
       <c r="AG299" t="n">
         <v>0.5005727272727273</v>
       </c>
@@ -23122,6 +23212,9 @@
       <c r="AC300" t="n">
         <v>0.5921666666666667</v>
       </c>
+      <c r="AF300" t="n">
+        <v>0.9510222222222223</v>
+      </c>
       <c r="AG300" t="n">
         <v>0.4616125</v>
       </c>
@@ -23196,6 +23289,9 @@
       <c r="AC301" t="n">
         <v>0.6927</v>
       </c>
+      <c r="AF301" t="n">
+        <v>0.9139909090909092</v>
+      </c>
       <c r="AG301" t="n">
         <v>0.548025</v>
       </c>
@@ -23270,6 +23366,9 @@
       <c r="AC302" t="n">
         <v>0.7154833333333332</v>
       </c>
+      <c r="AF302" t="n">
+        <v>0.8933600000000002</v>
+      </c>
       <c r="AG302" t="n">
         <v>0.7055666666666668</v>
       </c>
@@ -23344,6 +23443,9 @@
       <c r="AC303" t="n">
         <v>0.6155846153846155</v>
       </c>
+      <c r="AF303" t="n">
+        <v>0.9230583333333331</v>
+      </c>
       <c r="AG303" t="n">
         <v>0.7041666666666667</v>
       </c>
@@ -23418,6 +23520,9 @@
       <c r="AC304" t="n">
         <v>0.6663666666666668</v>
       </c>
+      <c r="AF304" t="n">
+        <v>0.9414899999999999</v>
+      </c>
       <c r="AG304" t="n">
         <v>0.6187666666666667</v>
       </c>
@@ -23492,6 +23597,9 @@
       <c r="AC305" t="n">
         <v>0.5321666666666667</v>
       </c>
+      <c r="AF305" t="n">
+        <v>0.907825</v>
+      </c>
       <c r="AG305" t="n">
         <v>0.5088625</v>
       </c>
@@ -23566,6 +23674,9 @@
       <c r="AC306" t="n">
         <v>0.67135</v>
       </c>
+      <c r="AF306" t="n">
+        <v>0.9343909090909093</v>
+      </c>
       <c r="AG306" t="n">
         <v>0.6848909090909091</v>
       </c>
@@ -23640,6 +23751,9 @@
       <c r="AC307" t="n">
         <v>0.6589090909090909</v>
       </c>
+      <c r="AF307" t="n">
+        <v>0.9279222222222224</v>
+      </c>
       <c r="AG307" t="n">
         <v>0.6076777777777778</v>
       </c>
@@ -23714,6 +23828,9 @@
       <c r="AC308" t="n">
         <v>0.591325</v>
       </c>
+      <c r="AF308" t="n">
+        <v>0.8938</v>
+      </c>
       <c r="AG308" t="n">
         <v>0.6058285714285715</v>
       </c>
@@ -23788,6 +23905,9 @@
       <c r="AC309" t="n">
         <v>0.7921454545454545</v>
       </c>
+      <c r="AF309" t="n">
+        <v>0.8198888888888889</v>
+      </c>
       <c r="AG309" t="n">
         <v>0.6448333333333333</v>
       </c>
@@ -23862,6 +23982,9 @@
       <c r="AC310" t="n">
         <v>0.7512714285714285</v>
       </c>
+      <c r="AF310" t="n">
+        <v>0.9684571428571429</v>
+      </c>
       <c r="AG310" t="n">
         <v>0.67424</v>
       </c>
@@ -23935,6 +24058,9 @@
       </c>
       <c r="AC311" t="n">
         <v>0.6005499999999999</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>0.8949888888888888</v>
       </c>
       <c r="AG311" t="n">
         <v>0.5765636363636364</v>
@@ -30746,6 +30872,9 @@
       <c r="AC402" t="n">
         <v>0.06950000000000001</v>
       </c>
+      <c r="AF402" t="n">
+        <v>0.9794</v>
+      </c>
       <c r="AG402" t="n">
         <v>0.0298</v>
       </c>
@@ -30820,6 +30949,9 @@
       <c r="AC403" t="n">
         <v>0.0612</v>
       </c>
+      <c r="AF403" t="n">
+        <v>0.9805</v>
+      </c>
       <c r="AG403" t="n">
         <v>0.0273</v>
       </c>
@@ -30894,6 +31026,9 @@
       <c r="AC404" t="n">
         <v>0.0731</v>
       </c>
+      <c r="AF404" t="n">
+        <v>0.9839</v>
+      </c>
       <c r="AG404" t="n">
         <v>0.0291</v>
       </c>
@@ -30968,6 +31103,9 @@
       <c r="AC405" t="n">
         <v>0.0645</v>
       </c>
+      <c r="AF405" t="n">
+        <v>0.9824000000000001</v>
+      </c>
       <c r="AG405" t="n">
         <v>0.0438</v>
       </c>
@@ -31042,6 +31180,9 @@
       <c r="AC406" t="n">
         <v>0.08210000000000001</v>
       </c>
+      <c r="AF406" t="n">
+        <v>0.9846</v>
+      </c>
       <c r="AG406" t="n">
         <v>0.0474</v>
       </c>
@@ -31116,6 +31257,9 @@
       <c r="AC407" t="n">
         <v>0.06900000000000001</v>
       </c>
+      <c r="AF407" t="n">
+        <v>0.983</v>
+      </c>
       <c r="AG407" t="n">
         <v>0.0294</v>
       </c>
@@ -31190,6 +31334,9 @@
       <c r="AC408" t="n">
         <v>0.0809</v>
       </c>
+      <c r="AF408" t="n">
+        <v>0.9838</v>
+      </c>
       <c r="AG408" t="n">
         <v>0.0321</v>
       </c>
@@ -31264,6 +31411,9 @@
       <c r="AC409" t="n">
         <v>0.0639</v>
       </c>
+      <c r="AF409" t="n">
+        <v>0.9812</v>
+      </c>
       <c r="AG409" t="n">
         <v>0.0293</v>
       </c>
@@ -31338,6 +31488,9 @@
       <c r="AC410" t="n">
         <v>0.0573</v>
       </c>
+      <c r="AF410" t="n">
+        <v>0.9857</v>
+      </c>
       <c r="AG410" t="n">
         <v>0.0449</v>
       </c>
@@ -31412,6 +31565,9 @@
       <c r="AC411" t="n">
         <v>0.0815</v>
       </c>
+      <c r="AF411" t="n">
+        <v>0.9799</v>
+      </c>
       <c r="AG411" t="n">
         <v>0.0331</v>
       </c>
@@ -31486,6 +31642,9 @@
       <c r="AC412" t="n">
         <v>0.0692</v>
       </c>
+      <c r="AF412" t="n">
+        <v>0.9818</v>
+      </c>
       <c r="AG412" t="n">
         <v>0.0348</v>
       </c>
@@ -31560,6 +31719,9 @@
       <c r="AC413" t="n">
         <v>0.0514</v>
       </c>
+      <c r="AF413" t="n">
+        <v>0.9817</v>
+      </c>
       <c r="AG413" t="n">
         <v>0.0454</v>
       </c>
@@ -31634,6 +31796,9 @@
       <c r="AC414" t="n">
         <v>0.0537</v>
       </c>
+      <c r="AF414" t="n">
+        <v>0.9818</v>
+      </c>
       <c r="AG414" t="n">
         <v>0.0332</v>
       </c>
@@ -31707,6 +31872,9 @@
       </c>
       <c r="AC415" t="n">
         <v>0.0513</v>
+      </c>
+      <c r="AF415" t="n">
+        <v>0.9815</v>
       </c>
       <c r="AG415" t="n">
         <v>0.0246</v>
@@ -35880,6 +36048,9 @@
       <c r="AC504" t="n">
         <v>0.7335583333333334</v>
       </c>
+      <c r="AF504" t="n">
+        <v>0.8250300000000002</v>
+      </c>
       <c r="AG504" t="n">
         <v>0.6718666666666667</v>
       </c>
@@ -35924,6 +36095,9 @@
       <c r="AC505" t="n">
         <v>0.6456</v>
       </c>
+      <c r="AF505" t="n">
+        <v>0.8677300000000001</v>
+      </c>
       <c r="AG505" t="n">
         <v>0.7518636363636362</v>
       </c>
@@ -35968,6 +36142,9 @@
       <c r="AC506" t="n">
         <v>0.6514</v>
       </c>
+      <c r="AF506" t="n">
+        <v>0.8842111111111112</v>
+      </c>
       <c r="AG506" t="n">
         <v>0.7943874999999999</v>
       </c>
@@ -36012,6 +36189,9 @@
       <c r="AC507" t="n">
         <v>0.6392454545454546</v>
       </c>
+      <c r="AF507" t="n">
+        <v>0.8440090909090909</v>
+      </c>
       <c r="AG507" t="n">
         <v>0.69035</v>
       </c>
@@ -36056,6 +36236,9 @@
       <c r="AC508" t="n">
         <v>0.6178833333333333</v>
       </c>
+      <c r="AF508" t="n">
+        <v>0.7984000000000001</v>
+      </c>
       <c r="AG508" t="n">
         <v>0.6579166666666666</v>
       </c>
@@ -36100,6 +36283,9 @@
       <c r="AC509" t="n">
         <v>0.6232076923076921</v>
       </c>
+      <c r="AF509" t="n">
+        <v>0.8212833333333333</v>
+      </c>
       <c r="AG509" t="n">
         <v>0.5816000000000001</v>
       </c>
@@ -36144,6 +36330,9 @@
       <c r="AC510" t="n">
         <v>0.6369083333333333</v>
       </c>
+      <c r="AF510" t="n">
+        <v>0.82751</v>
+      </c>
       <c r="AG510" t="n">
         <v>0.7370444444444444</v>
       </c>
@@ -36188,6 +36377,9 @@
       <c r="AC511" t="n">
         <v>0.6822777777777778</v>
       </c>
+      <c r="AF511" t="n">
+        <v>0.7893250000000001</v>
+      </c>
       <c r="AG511" t="n">
         <v>0.6631375</v>
       </c>
@@ -36232,6 +36424,9 @@
       <c r="AC512" t="n">
         <v>0.5748</v>
       </c>
+      <c r="AF512" t="n">
+        <v>0.8581727272727271</v>
+      </c>
       <c r="AG512" t="n">
         <v>0.6413454545454546</v>
       </c>
@@ -36276,6 +36471,9 @@
       <c r="AC513" t="n">
         <v>0.6514545454545455</v>
       </c>
+      <c r="AF513" t="n">
+        <v>0.7951555555555555</v>
+      </c>
       <c r="AG513" t="n">
         <v>0.6904888888888889</v>
       </c>
@@ -36320,6 +36518,9 @@
       <c r="AC514" t="n">
         <v>0.6691583333333333</v>
       </c>
+      <c r="AF514" t="n">
+        <v>0.7638400000000001</v>
+      </c>
       <c r="AG514" t="n">
         <v>0.6874714285714286</v>
       </c>
@@ -36364,6 +36565,9 @@
       <c r="AC515" t="n">
         <v>0.5082</v>
       </c>
+      <c r="AF515" t="n">
+        <v>0.8126333333333334</v>
+      </c>
       <c r="AG515" t="n">
         <v>0.6931666666666666</v>
       </c>
@@ -36408,6 +36612,9 @@
       <c r="AC516" t="n">
         <v>0.6212714285714285</v>
       </c>
+      <c r="AF516" t="n">
+        <v>0.8659000000000001</v>
+      </c>
       <c r="AG516" t="n">
         <v>0.6112299999999999</v>
       </c>
@@ -36451,6 +36658,9 @@
       </c>
       <c r="AC517" t="n">
         <v>0.6714166666666667</v>
+      </c>
+      <c r="AF517" t="n">
+        <v>0.783588888888889</v>
       </c>
       <c r="AG517" t="n">
         <v>0.6666818181818182</v>
@@ -39337,6 +39547,9 @@
       <c r="AC606" t="n">
         <v>0.5282092592592592</v>
       </c>
+      <c r="AF606" t="n">
+        <v>0.89698125</v>
+      </c>
       <c r="AG606" t="n">
         <v>0.5838275000000001</v>
       </c>
@@ -39366,6 +39579,9 @@
       <c r="AC607" t="n">
         <v>0.4499311475409836</v>
       </c>
+      <c r="AF607" t="n">
+        <v>0.7692310344827586</v>
+      </c>
       <c r="AG607" t="n">
         <v>0.5910333333333333</v>
       </c>
@@ -39395,6 +39611,9 @@
       <c r="AC608" t="n">
         <v>0.5719953125</v>
       </c>
+      <c r="AF608" t="n">
+        <v>0.826870588235294</v>
+      </c>
       <c r="AG608" t="n">
         <v>0.541629268292683</v>
       </c>
@@ -39424,6 +39643,9 @@
       <c r="AC609" t="n">
         <v>0.5563676470588235</v>
       </c>
+      <c r="AF609" t="n">
+        <v>0.6976925</v>
+      </c>
       <c r="AG609" t="n">
         <v>0.6393599999999999</v>
       </c>
@@ -39453,6 +39675,9 @@
       <c r="AC610" t="n">
         <v>0.5162607142857143</v>
       </c>
+      <c r="AF610" t="n">
+        <v>0.8650954545454546</v>
+      </c>
       <c r="AG610" t="n">
         <v>0.5253106382978723</v>
       </c>
@@ -39482,6 +39707,9 @@
       <c r="AC611" t="n">
         <v>0.4721854545454546</v>
       </c>
+      <c r="AF611" t="n">
+        <v>0.6639594594594594</v>
+      </c>
       <c r="AG611" t="n">
         <v>0.52815</v>
       </c>
@@ -39511,6 +39739,9 @@
       <c r="AC612" t="n">
         <v>0.5489823529411766</v>
       </c>
+      <c r="AF612" t="n">
+        <v>0.8358833333333333</v>
+      </c>
       <c r="AG612" t="n">
         <v>0.5162054054054054</v>
       </c>
@@ -39540,6 +39771,9 @@
       <c r="AC613" t="n">
         <v>0.5557716666666667</v>
       </c>
+      <c r="AF613" t="n">
+        <v>0.7622173913043477</v>
+      </c>
       <c r="AG613" t="n">
         <v>0.6759567567567568</v>
       </c>
@@ -39569,6 +39803,9 @@
       <c r="AC614" t="n">
         <v>0.5175136363636365</v>
       </c>
+      <c r="AF614" t="n">
+        <v>0.8382153846153847</v>
+      </c>
       <c r="AG614" t="n">
         <v>0.4732853658536585</v>
       </c>
@@ -39598,6 +39835,9 @@
       <c r="AC615" t="n">
         <v>0.5153795918367347</v>
       </c>
+      <c r="AF615" t="n">
+        <v>0.8087074074074073</v>
+      </c>
       <c r="AG615" t="n">
         <v>0.681017142857143</v>
       </c>
@@ -39627,6 +39867,9 @@
       <c r="AC616" t="n">
         <v>0.5326830769230769</v>
       </c>
+      <c r="AF616" t="n">
+        <v>0.8023727272727272</v>
+      </c>
       <c r="AG616" t="n">
         <v>0.5610877551020409</v>
       </c>
@@ -39656,6 +39899,9 @@
       <c r="AC617" t="n">
         <v>0.5707408163265306</v>
       </c>
+      <c r="AF617" t="n">
+        <v>0.652753488372093</v>
+      </c>
       <c r="AG617" t="n">
         <v>0.4817318181818181</v>
       </c>
@@ -39685,6 +39931,9 @@
       <c r="AC618" t="n">
         <v>0.456211475409836</v>
       </c>
+      <c r="AF618" t="n">
+        <v>0.7811695652173912</v>
+      </c>
       <c r="AG618" t="n">
         <v>0.631939393939394</v>
       </c>
@@ -39713,6 +39962,9 @@
       </c>
       <c r="AC619" t="n">
         <v>0.5503807692307692</v>
+      </c>
+      <c r="AF619" t="n">
+        <v>0.8658374999999999</v>
       </c>
       <c r="AG619" t="n">
         <v>0.515921212121212</v>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -763,8 +763,11 @@
       <c r="AC5" t="n">
         <v>0.1778257575757576</v>
       </c>
+      <c r="AE5" t="n">
+        <v>0.1409777777777778</v>
+      </c>
       <c r="AF5" t="n">
-        <v>0.1211935483870968</v>
+        <v>0.136831506849315</v>
       </c>
       <c r="AG5" t="n">
         <v>0.1444220588235294</v>
@@ -849,6 +852,9 @@
       <c r="AC6" t="n">
         <v>0.1841777777777778</v>
       </c>
+      <c r="AE6" t="n">
+        <v>0.3522714285714286</v>
+      </c>
       <c r="AF6" t="n">
         <v>0.2158</v>
       </c>
@@ -935,6 +941,9 @@
       <c r="AC7" t="n">
         <v>0.2581</v>
       </c>
+      <c r="AE7" t="n">
+        <v>0.5093</v>
+      </c>
       <c r="AF7" t="n">
         <v>0.3096071428571429</v>
       </c>
@@ -1021,6 +1030,9 @@
       <c r="AC8" t="n">
         <v>0.3944363636363636</v>
       </c>
+      <c r="AE8" t="n">
+        <v>0.3586</v>
+      </c>
       <c r="AF8" t="n">
         <v>0.3051263157894737</v>
       </c>
@@ -1107,6 +1119,9 @@
       <c r="AC9" t="n">
         <v>0.4470642857142857</v>
       </c>
+      <c r="AE9" t="n">
+        <v>0.4496538461538462</v>
+      </c>
       <c r="AF9" t="n">
         <v>0.2868</v>
       </c>
@@ -1193,6 +1208,9 @@
       <c r="AC10" t="n">
         <v>0.46318</v>
       </c>
+      <c r="AE10" t="n">
+        <v>0.5565863636363636</v>
+      </c>
       <c r="AF10" t="n">
         <v>0.377646</v>
       </c>
@@ -1279,6 +1297,9 @@
       <c r="AC11" t="n">
         <v>0.574416129032258</v>
       </c>
+      <c r="AE11" t="n">
+        <v>0.51294</v>
+      </c>
       <c r="AF11" t="n">
         <v>0.302692</v>
       </c>
@@ -1365,6 +1386,9 @@
       <c r="AC12" t="n">
         <v>0.51483</v>
       </c>
+      <c r="AE12" t="n">
+        <v>0.53101875</v>
+      </c>
       <c r="AF12" t="n">
         <v>0.4420933333333333</v>
       </c>
@@ -1451,6 +1475,9 @@
       <c r="AC13" t="n">
         <v>0.6904677419354839</v>
       </c>
+      <c r="AE13" t="n">
+        <v>0.5811628571428571</v>
+      </c>
       <c r="AF13" t="n">
         <v>0.4891961538461538</v>
       </c>
@@ -1537,6 +1564,9 @@
       <c r="AC14" t="n">
         <v>0.55475</v>
       </c>
+      <c r="AE14" t="n">
+        <v>0.5271250000000001</v>
+      </c>
       <c r="AF14" t="n">
         <v>0.4875537037037037</v>
       </c>
@@ -1614,6 +1644,9 @@
       <c r="AC15" t="n">
         <v>0.6941181818181819</v>
       </c>
+      <c r="AE15" t="n">
+        <v>0.6544416666666667</v>
+      </c>
       <c r="AF15" t="n">
         <v>0.566505</v>
       </c>
@@ -1691,6 +1724,9 @@
       <c r="AC16" t="n">
         <v>0.7501740740740742</v>
       </c>
+      <c r="AE16" t="n">
+        <v>0.6866103448275862</v>
+      </c>
       <c r="AF16" t="n">
         <v>0.591214705882353</v>
       </c>
@@ -1768,6 +1804,9 @@
       <c r="AC17" t="n">
         <v>0.767936</v>
       </c>
+      <c r="AE17" t="n">
+        <v>0.6823375</v>
+      </c>
       <c r="AF17" t="n">
         <v>0.5701978260869565</v>
       </c>
@@ -1845,6 +1884,9 @@
       <c r="AC18" t="n">
         <v>0.8150133333333334</v>
       </c>
+      <c r="AE18" t="n">
+        <v>0.7576166666666667</v>
+      </c>
       <c r="AF18" t="n">
         <v>0.5278999999999999</v>
       </c>
@@ -1922,6 +1964,9 @@
       <c r="AC19" t="n">
         <v>0.4809538461538461</v>
       </c>
+      <c r="AE19" t="n">
+        <v>0.8117439024390244</v>
+      </c>
       <c r="AF19" t="n">
         <v>0.6256555555555555</v>
       </c>
@@ -1999,6 +2044,9 @@
       <c r="AC20" t="n">
         <v>0.7703739130434782</v>
       </c>
+      <c r="AE20" t="n">
+        <v>0.81415</v>
+      </c>
       <c r="AF20" t="n">
         <v>0.6736951219512195</v>
       </c>
@@ -2076,6 +2124,9 @@
       <c r="AC21" t="n">
         <v>0.8132562500000001</v>
       </c>
+      <c r="AE21" t="n">
+        <v>0.8060244444444444</v>
+      </c>
       <c r="AF21" t="n">
         <v>0.63368</v>
       </c>
@@ -2153,6 +2204,9 @@
       <c r="AC22" t="n">
         <v>0.714878125</v>
       </c>
+      <c r="AE22" t="n">
+        <v>0.7891365853658536</v>
+      </c>
       <c r="AF22" t="n">
         <v>0.6541619047619047</v>
       </c>
@@ -2230,6 +2284,9 @@
       <c r="AC23" t="n">
         <v>0.8276619047619048</v>
       </c>
+      <c r="AE23" t="n">
+        <v>0.8158588235294119</v>
+      </c>
       <c r="AF23" t="n">
         <v>0.6224535714285715</v>
       </c>
@@ -2307,6 +2364,9 @@
       <c r="AC24" t="n">
         <v>0.6806578947368421</v>
       </c>
+      <c r="AE24" t="n">
+        <v>0.8398</v>
+      </c>
       <c r="AF24" t="n">
         <v>0.6992648148148147</v>
       </c>
@@ -2384,6 +2444,9 @@
       <c r="AC25" t="n">
         <v>0.8548842105263157</v>
       </c>
+      <c r="AE25" t="n">
+        <v>0.753792857142857</v>
+      </c>
       <c r="AF25" t="n">
         <v>0.7716395833333332</v>
       </c>
@@ -2461,6 +2524,9 @@
       <c r="AC26" t="n">
         <v>0.7023619047619047</v>
       </c>
+      <c r="AE26" t="n">
+        <v>0.8495972972972973</v>
+      </c>
       <c r="AF26" t="n">
         <v>0.7516045454545455</v>
       </c>
@@ -2538,6 +2604,9 @@
       <c r="AC27" t="n">
         <v>0.8953454545454546</v>
       </c>
+      <c r="AE27" t="n">
+        <v>0.7380607142857144</v>
+      </c>
       <c r="AF27" t="n">
         <v>0.683575</v>
       </c>
@@ -2615,6 +2684,9 @@
       <c r="AC28" t="n">
         <v>0.8215583333333333</v>
       </c>
+      <c r="AE28" t="n">
+        <v>0.6748875</v>
+      </c>
       <c r="AF28" t="n">
         <v>0.718662857142857</v>
       </c>
@@ -2692,6 +2764,9 @@
       <c r="AC29" t="n">
         <v>0.8405549999999999</v>
       </c>
+      <c r="AE29" t="n">
+        <v>0.8732882352941177</v>
+      </c>
       <c r="AF29" t="n">
         <v>0.7586853658536586</v>
       </c>
@@ -2769,6 +2844,9 @@
       <c r="AC30" t="n">
         <v>0.7895799999999999</v>
       </c>
+      <c r="AE30" t="n">
+        <v>0.8862347826086957</v>
+      </c>
       <c r="AF30" t="n">
         <v>0.6799933333333333</v>
       </c>
@@ -2846,6 +2924,9 @@
       <c r="AC31" t="n">
         <v>0.8073346153846153</v>
       </c>
+      <c r="AE31" t="n">
+        <v>0.8431386363636364</v>
+      </c>
       <c r="AF31" t="n">
         <v>0.7398852941176471</v>
       </c>
@@ -2923,6 +3004,9 @@
       <c r="AC32" t="n">
         <v>0.7860285714285714</v>
       </c>
+      <c r="AE32" t="n">
+        <v>0.794264705882353</v>
+      </c>
       <c r="AF32" t="n">
         <v>0.7788333333333333</v>
       </c>
@@ -3000,6 +3084,9 @@
       <c r="AC33" t="n">
         <v>0.89875</v>
       </c>
+      <c r="AE33" t="n">
+        <v>0.7555484848484848</v>
+      </c>
       <c r="AF33" t="n">
         <v>0.7856291666666667</v>
       </c>
@@ -3077,6 +3164,9 @@
       <c r="AC34" t="n">
         <v>0.8057473684210527</v>
       </c>
+      <c r="AE34" t="n">
+        <v>0.7863555555555556</v>
+      </c>
       <c r="AF34" t="n">
         <v>0.7527744680851063</v>
       </c>
@@ -3154,6 +3244,9 @@
       <c r="AC35" t="n">
         <v>0.8584181818181819</v>
       </c>
+      <c r="AE35" t="n">
+        <v>0.8238179487179488</v>
+      </c>
       <c r="AF35" t="n">
         <v>0.7412694915254238</v>
       </c>
@@ -3231,6 +3324,9 @@
       <c r="AC36" t="n">
         <v>0.8302687500000001</v>
       </c>
+      <c r="AE36" t="n">
+        <v>0.8529190476190477</v>
+      </c>
       <c r="AF36" t="n">
         <v>0.7180857142857143</v>
       </c>
@@ -3308,6 +3404,9 @@
       <c r="AC37" t="n">
         <v>0.8016722222222222</v>
       </c>
+      <c r="AE37" t="n">
+        <v>0.8277053571428572</v>
+      </c>
       <c r="AF37" t="n">
         <v>0.8055095238095239</v>
       </c>
@@ -3385,6 +3484,9 @@
       <c r="AC38" t="n">
         <v>0.8125315789473685</v>
       </c>
+      <c r="AE38" t="n">
+        <v>0.83523125</v>
+      </c>
       <c r="AF38" t="n">
         <v>0.7484777777777778</v>
       </c>
@@ -3462,6 +3564,9 @@
       <c r="AC39" t="n">
         <v>0.813073076923077</v>
       </c>
+      <c r="AE39" t="n">
+        <v>0.825775</v>
+      </c>
       <c r="AF39" t="n">
         <v>0.6965051282051282</v>
       </c>
@@ -3539,6 +3644,9 @@
       <c r="AC40" t="n">
         <v>0.8184586206896552</v>
       </c>
+      <c r="AE40" t="n">
+        <v>0.8958480769230769</v>
+      </c>
       <c r="AF40" t="n">
         <v>0.8004536585365855</v>
       </c>
@@ -3616,6 +3724,9 @@
       <c r="AC41" t="n">
         <v>0.8377333333333333</v>
       </c>
+      <c r="AE41" t="n">
+        <v>0.8732238095238096</v>
+      </c>
       <c r="AF41" t="n">
         <v>0.7578836363636364</v>
       </c>
@@ -3693,6 +3804,9 @@
       <c r="AC42" t="n">
         <v>0.771</v>
       </c>
+      <c r="AE42" t="n">
+        <v>0.8454826086956523</v>
+      </c>
       <c r="AF42" t="n">
         <v>0.7189878048780488</v>
       </c>
@@ -3770,6 +3884,9 @@
       <c r="AC43" t="n">
         <v>0.8446210526315788</v>
       </c>
+      <c r="AE43" t="n">
+        <v>0.8591695652173913</v>
+      </c>
       <c r="AF43" t="n">
         <v>0.76215</v>
       </c>
@@ -3847,6 +3964,9 @@
       <c r="AC44" t="n">
         <v>0.8415050000000001</v>
       </c>
+      <c r="AE44" t="n">
+        <v>0.8114032258064515</v>
+      </c>
       <c r="AF44" t="n">
         <v>0.850783870967742</v>
       </c>
@@ -3924,6 +4044,9 @@
       <c r="AC45" t="n">
         <v>0.8024636363636364</v>
       </c>
+      <c r="AE45" t="n">
+        <v>0.7922142857142855</v>
+      </c>
       <c r="AF45" t="n">
         <v>0.8372724999999999</v>
       </c>
@@ -4001,6 +4124,9 @@
       <c r="AC46" t="n">
         <v>0.8450529411764706</v>
       </c>
+      <c r="AE46" t="n">
+        <v>0.8316641025641025</v>
+      </c>
       <c r="AF46" t="n">
         <v>0.7954235294117646</v>
       </c>
@@ -4078,6 +4204,9 @@
       <c r="AC47" t="n">
         <v>0.8374142857142858</v>
       </c>
+      <c r="AE47" t="n">
+        <v>0.8429891304347825</v>
+      </c>
       <c r="AF47" t="n">
         <v>0.8122710526315789</v>
       </c>
@@ -4155,6 +4284,9 @@
       <c r="AC48" t="n">
         <v>0.7865749999999999</v>
       </c>
+      <c r="AE48" t="n">
+        <v>0.8140172413793105</v>
+      </c>
       <c r="AF48" t="n">
         <v>0.7768560975609756</v>
       </c>
@@ -4232,6 +4364,9 @@
       <c r="AC49" t="n">
         <v>0.7560166666666667</v>
       </c>
+      <c r="AE49" t="n">
+        <v>0.8464034482758621</v>
+      </c>
       <c r="AF49" t="n">
         <v>0.7985172413793102</v>
       </c>
@@ -4309,6 +4444,9 @@
       <c r="AC50" t="n">
         <v>0.8125933333333333</v>
       </c>
+      <c r="AE50" t="n">
+        <v>0.8807258064516128</v>
+      </c>
       <c r="AF50" t="n">
         <v>0.8212977777777777</v>
       </c>
@@ -4386,6 +4524,9 @@
       <c r="AC51" t="n">
         <v>0.7979192307692308</v>
       </c>
+      <c r="AE51" t="n">
+        <v>0.854168888888889</v>
+      </c>
       <c r="AF51" t="n">
         <v>0.7167826086956522</v>
       </c>
@@ -4463,6 +4604,9 @@
       <c r="AC52" t="n">
         <v>0.8103206896551725</v>
       </c>
+      <c r="AE52" t="n">
+        <v>0.8235655172413793</v>
+      </c>
       <c r="AF52" t="n">
         <v>0.8063586206896551</v>
       </c>
@@ -4540,6 +4684,9 @@
       <c r="AC53" t="n">
         <v>0.8048999999999999</v>
       </c>
+      <c r="AE53" t="n">
+        <v>0.7917772727272727</v>
+      </c>
       <c r="AF53" t="n">
         <v>0.7686414634146342</v>
       </c>
@@ -4617,6 +4764,9 @@
       <c r="AC54" t="n">
         <v>0.805169696969697</v>
       </c>
+      <c r="AE54" t="n">
+        <v>0.856812121212121</v>
+      </c>
       <c r="AF54" t="n">
         <v>0.796109375</v>
       </c>
@@ -4694,6 +4844,9 @@
       <c r="AC55" t="n">
         <v>0.8160833333333333</v>
       </c>
+      <c r="AE55" t="n">
+        <v>0.8391934782608695</v>
+      </c>
       <c r="AF55" t="n">
         <v>0.7950844444444444</v>
       </c>
@@ -4771,6 +4924,9 @@
       <c r="AC56" t="n">
         <v>0.8642833333333334</v>
       </c>
+      <c r="AE56" t="n">
+        <v>0.8554736842105262</v>
+      </c>
       <c r="AF56" t="n">
         <v>0.6993140000000001</v>
       </c>
@@ -4848,6 +5004,9 @@
       <c r="AC57" t="n">
         <v>0.8099125</v>
       </c>
+      <c r="AE57" t="n">
+        <v>0.8399542857142855</v>
+      </c>
       <c r="AF57" t="n">
         <v>0.7823157894736843</v>
       </c>
@@ -4925,6 +5084,9 @@
       <c r="AC58" t="n">
         <v>0.8868058823529412</v>
       </c>
+      <c r="AE58" t="n">
+        <v>0.7949428571428573</v>
+      </c>
       <c r="AF58" t="n">
         <v>0.7641380952380953</v>
       </c>
@@ -5002,6 +5164,9 @@
       <c r="AC59" t="n">
         <v>0.8621346153846154</v>
       </c>
+      <c r="AE59" t="n">
+        <v>0.72724</v>
+      </c>
       <c r="AF59" t="n">
         <v>0.7457299999999999</v>
       </c>
@@ -5079,6 +5244,9 @@
       <c r="AC60" t="n">
         <v>0.8122380952380953</v>
       </c>
+      <c r="AE60" t="n">
+        <v>0.779916129032258</v>
+      </c>
       <c r="AF60" t="n">
         <v>0.8350705882352942</v>
       </c>
@@ -5156,6 +5324,9 @@
       <c r="AC61" t="n">
         <v>0.8192285714285715</v>
       </c>
+      <c r="AE61" t="n">
+        <v>0.8505499999999999</v>
+      </c>
       <c r="AF61" t="n">
         <v>0.7649038461538461</v>
       </c>
@@ -5233,6 +5404,9 @@
       <c r="AC62" t="n">
         <v>0.8367733333333334</v>
       </c>
+      <c r="AE62" t="n">
+        <v>0.8555488372093024</v>
+      </c>
       <c r="AF62" t="n">
         <v>0.7346511111111111</v>
       </c>
@@ -5310,6 +5484,9 @@
       <c r="AC63" t="n">
         <v>0.79815</v>
       </c>
+      <c r="AE63" t="n">
+        <v>0.8196916666666666</v>
+      </c>
       <c r="AF63" t="n">
         <v>0.7309825</v>
       </c>
@@ -5387,6 +5564,9 @@
       <c r="AC64" t="n">
         <v>0.7964366666666667</v>
       </c>
+      <c r="AE64" t="n">
+        <v>0.7428659090909092</v>
+      </c>
       <c r="AF64" t="n">
         <v>0.737761224489796</v>
       </c>
@@ -5464,6 +5644,9 @@
       <c r="AC65" t="n">
         <v>0.7861571428571429</v>
       </c>
+      <c r="AE65" t="n">
+        <v>0.8547159090909091</v>
+      </c>
       <c r="AF65" t="n">
         <v>0.7681734375</v>
       </c>
@@ -5541,6 +5724,9 @@
       <c r="AC66" t="n">
         <v>0.7881066666666666</v>
       </c>
+      <c r="AE66" t="n">
+        <v>0.86485</v>
+      </c>
       <c r="AF66" t="n">
         <v>0.7673023255813953</v>
       </c>
@@ -5618,6 +5804,9 @@
       <c r="AC67" t="n">
         <v>0.8141</v>
       </c>
+      <c r="AE67" t="n">
+        <v>0.817658695652174</v>
+      </c>
       <c r="AF67" t="n">
         <v>0.7821708333333334</v>
       </c>
@@ -5695,6 +5884,9 @@
       <c r="AC68" t="n">
         <v>0.7976428571428571</v>
       </c>
+      <c r="AE68" t="n">
+        <v>0.7966615384615385</v>
+      </c>
       <c r="AF68" t="n">
         <v>0.7613581818181819</v>
       </c>
@@ -5772,6 +5964,9 @@
       <c r="AC69" t="n">
         <v>0.8991</v>
       </c>
+      <c r="AE69" t="n">
+        <v>0.8263347826086955</v>
+      </c>
       <c r="AF69" t="n">
         <v>0.8003170212765958</v>
       </c>
@@ -5849,6 +6044,9 @@
       <c r="AC70" t="n">
         <v>0.8285071428571429</v>
       </c>
+      <c r="AE70" t="n">
+        <v>0.68686</v>
+      </c>
       <c r="AF70" t="n">
         <v>0.8219073170731708</v>
       </c>
@@ -5926,6 +6124,9 @@
       <c r="AC71" t="n">
         <v>0.8124909090909092</v>
       </c>
+      <c r="AE71" t="n">
+        <v>0.825217391304348</v>
+      </c>
       <c r="AF71" t="n">
         <v>0.7013918032786886</v>
       </c>
@@ -6003,6 +6204,9 @@
       <c r="AC72" t="n">
         <v>0.7806142857142857</v>
       </c>
+      <c r="AE72" t="n">
+        <v>0.8528735294117646</v>
+      </c>
       <c r="AF72" t="n">
         <v>0.8253333333333334</v>
       </c>
@@ -6080,6 +6284,9 @@
       <c r="AC73" t="n">
         <v>0.8651384615384614</v>
       </c>
+      <c r="AE73" t="n">
+        <v>0.8602120000000001</v>
+      </c>
       <c r="AF73" t="n">
         <v>0.830431914893617</v>
       </c>
@@ -6157,6 +6364,9 @@
       <c r="AC74" t="n">
         <v>0.7983347826086956</v>
       </c>
+      <c r="AE74" t="n">
+        <v>0.7251117647058825</v>
+      </c>
       <c r="AF74" t="n">
         <v>0.7466634615384616</v>
       </c>
@@ -6234,6 +6444,9 @@
       <c r="AC75" t="n">
         <v>0.819905</v>
       </c>
+      <c r="AE75" t="n">
+        <v>0.7983421052631579</v>
+      </c>
       <c r="AF75" t="n">
         <v>0.8182203389830509</v>
       </c>
@@ -6311,6 +6524,9 @@
       <c r="AC76" t="n">
         <v>0.8066333333333333</v>
       </c>
+      <c r="AE76" t="n">
+        <v>0.8929233333333334</v>
+      </c>
       <c r="AF76" t="n">
         <v>0.7858304347826086</v>
       </c>
@@ -6388,6 +6604,9 @@
       <c r="AC77" t="n">
         <v>0.8635769230769232</v>
       </c>
+      <c r="AE77" t="n">
+        <v>0.8933906976744186</v>
+      </c>
       <c r="AF77" t="n">
         <v>0.8292540540540541</v>
       </c>
@@ -6465,6 +6684,9 @@
       <c r="AC78" t="n">
         <v>0.8692789473684212</v>
       </c>
+      <c r="AE78" t="n">
+        <v>0.8172965517241381</v>
+      </c>
       <c r="AF78" t="n">
         <v>0.7616634615384617</v>
       </c>
@@ -6542,6 +6764,9 @@
       <c r="AC79" t="n">
         <v>0.8399827586206896</v>
       </c>
+      <c r="AE79" t="n">
+        <v>0.7938727272727273</v>
+      </c>
       <c r="AF79" t="n">
         <v>0.8140846153846154</v>
       </c>
@@ -6619,6 +6844,9 @@
       <c r="AC80" t="n">
         <v>0.7929894736842106</v>
       </c>
+      <c r="AE80" t="n">
+        <v>0.8341666666666667</v>
+      </c>
       <c r="AF80" t="n">
         <v>0.7771124999999999</v>
       </c>
@@ -6696,6 +6924,9 @@
       <c r="AC81" t="n">
         <v>0.8125333333333332</v>
       </c>
+      <c r="AE81" t="n">
+        <v>0.8427238095238097</v>
+      </c>
       <c r="AF81" t="n">
         <v>0.705746511627907</v>
       </c>
@@ -6773,6 +7004,9 @@
       <c r="AC82" t="n">
         <v>0.8307266666666667</v>
       </c>
+      <c r="AE82" t="n">
+        <v>0.8191081632653062</v>
+      </c>
       <c r="AF82" t="n">
         <v>0.8079921052631579</v>
       </c>
@@ -6850,6 +7084,9 @@
       <c r="AC83" t="n">
         <v>0.82816</v>
       </c>
+      <c r="AE83" t="n">
+        <v>0.8890387096774194</v>
+      </c>
       <c r="AF83" t="n">
         <v>0.7309636363636364</v>
       </c>
@@ -6927,6 +7164,9 @@
       <c r="AC84" t="n">
         <v>0.8325095238095239</v>
       </c>
+      <c r="AE84" t="n">
+        <v>0.9049065217391304</v>
+      </c>
       <c r="AF84" t="n">
         <v>0.761778947368421</v>
       </c>
@@ -7004,6 +7244,9 @@
       <c r="AC85" t="n">
         <v>0.85517</v>
       </c>
+      <c r="AE85" t="n">
+        <v>0.9520903225806452</v>
+      </c>
       <c r="AF85" t="n">
         <v>0.8379250000000001</v>
       </c>
@@ -7081,6 +7324,9 @@
       <c r="AC86" t="n">
         <v>0.8028875000000001</v>
       </c>
+      <c r="AE86" t="n">
+        <v>0.8849652173913043</v>
+      </c>
       <c r="AF86" t="n">
         <v>0.8038782608695653</v>
       </c>
@@ -7158,6 +7404,9 @@
       <c r="AC87" t="n">
         <v>0.8091333333333334</v>
       </c>
+      <c r="AE87" t="n">
+        <v>0.8634027027027027</v>
+      </c>
       <c r="AF87" t="n">
         <v>0.7474943396226414</v>
       </c>
@@ -7235,6 +7484,9 @@
       <c r="AC88" t="n">
         <v>0.8229588235294119</v>
       </c>
+      <c r="AE88" t="n">
+        <v>0.7991558823529411</v>
+      </c>
       <c r="AF88" t="n">
         <v>0.7343703703703703</v>
       </c>
@@ -7312,6 +7564,9 @@
       <c r="AC89" t="n">
         <v>0.8089263157894738</v>
       </c>
+      <c r="AE89" t="n">
+        <v>0.7768318181818181</v>
+      </c>
       <c r="AF89" t="n">
         <v>0.7854456140350877</v>
       </c>
@@ -7389,6 +7644,9 @@
       <c r="AC90" t="n">
         <v>0.8167846153846153</v>
       </c>
+      <c r="AE90" t="n">
+        <v>0.8157133333333334</v>
+      </c>
       <c r="AF90" t="n">
         <v>0.8259139534883719</v>
       </c>
@@ -7466,6 +7724,9 @@
       <c r="AC91" t="n">
         <v>0.8498916666666666</v>
       </c>
+      <c r="AE91" t="n">
+        <v>0.8768411764705882</v>
+      </c>
       <c r="AF91" t="n">
         <v>0.7837869565217394</v>
       </c>
@@ -7543,6 +7804,9 @@
       <c r="AC92" t="n">
         <v>0.89875</v>
       </c>
+      <c r="AE92" t="n">
+        <v>0.8578666666666667</v>
+      </c>
       <c r="AF92" t="n">
         <v>0.6651650000000001</v>
       </c>
@@ -7620,6 +7884,9 @@
       <c r="AC93" t="n">
         <v>0.87325625</v>
       </c>
+      <c r="AE93" t="n">
+        <v>0.7772945945945946</v>
+      </c>
       <c r="AF93" t="n">
         <v>0.7490516666666666</v>
       </c>
@@ -7697,6 +7964,9 @@
       <c r="AC94" t="n">
         <v>0.8562166666666666</v>
       </c>
+      <c r="AE94" t="n">
+        <v>0.794025641025641</v>
+      </c>
       <c r="AF94" t="n">
         <v>0.7768717391304348</v>
       </c>
@@ -7774,6 +8044,9 @@
       <c r="AC95" t="n">
         <v>0.86829375</v>
       </c>
+      <c r="AE95" t="n">
+        <v>0.7852149999999999</v>
+      </c>
       <c r="AF95" t="n">
         <v>0.8487095238095238</v>
       </c>
@@ -7851,6 +8124,9 @@
       <c r="AC96" t="n">
         <v>0.8327052631578947</v>
       </c>
+      <c r="AE96" t="n">
+        <v>0.9281108695652174</v>
+      </c>
       <c r="AF96" t="n">
         <v>0.7357827586206895</v>
       </c>
@@ -7928,6 +8204,9 @@
       <c r="AC97" t="n">
         <v>0.8147647058823528</v>
       </c>
+      <c r="AE97" t="n">
+        <v>0.8262</v>
+      </c>
       <c r="AF97" t="n">
         <v>0.7370184210526316</v>
       </c>
@@ -8005,6 +8284,9 @@
       <c r="AC98" t="n">
         <v>0.8474666666666667</v>
       </c>
+      <c r="AE98" t="n">
+        <v>0.8027107142857143</v>
+      </c>
       <c r="AF98" t="n">
         <v>0.819178</v>
       </c>
@@ -8082,6 +8364,9 @@
       <c r="AC99" t="n">
         <v>0.8588611111111111</v>
       </c>
+      <c r="AE99" t="n">
+        <v>0.8429800000000001</v>
+      </c>
       <c r="AF99" t="n">
         <v>0.7766933333333335</v>
       </c>
@@ -8159,6 +8444,9 @@
       <c r="AC100" t="n">
         <v>0.8243916666666666</v>
       </c>
+      <c r="AE100" t="n">
+        <v>0.8082483870967743</v>
+      </c>
       <c r="AF100" t="n">
         <v>0.8443446808510637</v>
       </c>
@@ -8236,6 +8524,9 @@
       <c r="AC101" t="n">
         <v>0.817807142857143</v>
       </c>
+      <c r="AE101" t="n">
+        <v>0.8170945945945947</v>
+      </c>
       <c r="AF101" t="n">
         <v>0.7568620689655172</v>
       </c>
@@ -8313,6 +8604,9 @@
       <c r="AC102" t="n">
         <v>0.8752421052631579</v>
       </c>
+      <c r="AE102" t="n">
+        <v>0.8249069767441861</v>
+      </c>
       <c r="AF102" t="n">
         <v>0.7723093023255815</v>
       </c>
@@ -8390,6 +8684,9 @@
       <c r="AC103" t="n">
         <v>0.8328842105263159</v>
       </c>
+      <c r="AE103" t="n">
+        <v>0.9088540540540541</v>
+      </c>
       <c r="AF103" t="n">
         <v>0.7391052631578947</v>
       </c>
@@ -8466,6 +8763,9 @@
       </c>
       <c r="AC104" t="n">
         <v>0.8440260869565218</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0.8374355555555556</v>
       </c>
       <c r="AF104" t="n">
         <v>0.7095041666666667</v>
@@ -8577,8 +8877,11 @@
       <c r="AC108" t="n">
         <v>0.8666666666666667</v>
       </c>
+      <c r="AE108" t="n">
+        <v>0.1333333333333333</v>
+      </c>
       <c r="AF108" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="AG108" t="n">
         <v>0.9333333333333333</v>
@@ -8663,6 +8966,9 @@
       <c r="AC109" t="n">
         <v>0.9333333333333333</v>
       </c>
+      <c r="AE109" t="n">
+        <v>0.4666666666666667</v>
+      </c>
       <c r="AF109" t="n">
         <v>0.5333333333333333</v>
       </c>
@@ -8749,6 +9055,9 @@
       <c r="AC110" t="n">
         <v>0.9166666666666666</v>
       </c>
+      <c r="AE110" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AF110" t="n">
         <v>0.2307692307692308</v>
       </c>
@@ -8835,6 +9144,9 @@
       <c r="AC111" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="AE111" t="n">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AF111" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -8921,6 +9233,9 @@
       <c r="AC112" t="n">
         <v>0.7142857142857143</v>
       </c>
+      <c r="AE112" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AF112" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -9007,6 +9322,9 @@
       <c r="AC113" t="n">
         <v>1</v>
       </c>
+      <c r="AE113" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AF113" t="n">
         <v>0.5</v>
       </c>
@@ -9093,6 +9411,9 @@
       <c r="AC114" t="n">
         <v>1</v>
       </c>
+      <c r="AE114" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF114" t="n">
         <v>0.75</v>
       </c>
@@ -9179,6 +9500,9 @@
       <c r="AC115" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE115" t="n">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AF115" t="n">
         <v>0.6363636363636364</v>
       </c>
@@ -9265,6 +9589,9 @@
       <c r="AC116" t="n">
         <v>1</v>
       </c>
+      <c r="AE116" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF116" t="n">
         <v>0.4545454545454545</v>
       </c>
@@ -9351,6 +9678,9 @@
       <c r="AC117" t="n">
         <v>1</v>
       </c>
+      <c r="AE117" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF117" t="n">
         <v>0.5555555555555556</v>
       </c>
@@ -9425,6 +9755,9 @@
       <c r="AC118" t="n">
         <v>1</v>
       </c>
+      <c r="AE118" t="n">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="AF118" t="n">
         <v>0.6</v>
       </c>
@@ -9502,6 +9835,9 @@
       <c r="AC119" t="n">
         <v>1</v>
       </c>
+      <c r="AE119" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF119" t="n">
         <v>0.6363636363636364</v>
       </c>
@@ -9579,6 +9915,9 @@
       <c r="AC120" t="n">
         <v>1</v>
       </c>
+      <c r="AE120" t="n">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="AF120" t="n">
         <v>0.6153846153846154</v>
       </c>
@@ -9656,6 +9995,9 @@
       <c r="AC121" t="n">
         <v>0.6</v>
       </c>
+      <c r="AE121" t="n">
+        <v>0.8888888888888888</v>
+      </c>
       <c r="AF121" t="n">
         <v>0.6153846153846154</v>
       </c>
@@ -9733,6 +10075,9 @@
       <c r="AC122" t="n">
         <v>1</v>
       </c>
+      <c r="AE122" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AF122" t="n">
         <v>0.6</v>
       </c>
@@ -9810,6 +10155,9 @@
       <c r="AC123" t="n">
         <v>1</v>
       </c>
+      <c r="AE123" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF123" t="n">
         <v>0.6153846153846154</v>
       </c>
@@ -9887,6 +10235,9 @@
       <c r="AC124" t="n">
         <v>1</v>
       </c>
+      <c r="AE124" t="n">
+        <v>0.8888888888888888</v>
+      </c>
       <c r="AF124" t="n">
         <v>0.5555555555555556</v>
       </c>
@@ -9964,6 +10315,9 @@
       <c r="AC125" t="n">
         <v>1</v>
       </c>
+      <c r="AE125" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF125" t="n">
         <v>0.4444444444444444</v>
       </c>
@@ -10041,6 +10395,9 @@
       <c r="AC126" t="n">
         <v>1</v>
       </c>
+      <c r="AE126" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF126" t="n">
         <v>0.7</v>
       </c>
@@ -10118,6 +10475,9 @@
       <c r="AC127" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE127" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AF127" t="n">
         <v>0.2222222222222222</v>
       </c>
@@ -10192,6 +10552,9 @@
       <c r="AC128" t="n">
         <v>1</v>
       </c>
+      <c r="AE128" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF128" t="n">
         <v>0.8</v>
       </c>
@@ -10269,6 +10632,9 @@
       <c r="AC129" t="n">
         <v>1</v>
       </c>
+      <c r="AE129" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF129" t="n">
         <v>0.5555555555555556</v>
       </c>
@@ -10346,6 +10712,9 @@
       <c r="AC130" t="n">
         <v>1</v>
       </c>
+      <c r="AE130" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AF130" t="n">
         <v>0.625</v>
       </c>
@@ -10423,6 +10792,9 @@
       <c r="AC131" t="n">
         <v>1</v>
       </c>
+      <c r="AE131" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF131" t="n">
         <v>0.3</v>
       </c>
@@ -10500,6 +10872,9 @@
       <c r="AC132" t="n">
         <v>1</v>
       </c>
+      <c r="AE132" t="n">
+        <v>1</v>
+      </c>
       <c r="AF132" t="n">
         <v>0.625</v>
       </c>
@@ -10577,6 +10952,9 @@
       <c r="AC133" t="n">
         <v>1</v>
       </c>
+      <c r="AE133" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AF133" t="n">
         <v>0.6363636363636364</v>
       </c>
@@ -10654,6 +11032,9 @@
       <c r="AC134" t="n">
         <v>1</v>
       </c>
+      <c r="AE134" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF134" t="n">
         <v>0.5</v>
       </c>
@@ -10731,6 +11112,9 @@
       <c r="AC135" t="n">
         <v>1</v>
       </c>
+      <c r="AE135" t="n">
+        <v>1</v>
+      </c>
       <c r="AF135" t="n">
         <v>0.6</v>
       </c>
@@ -10808,6 +11192,9 @@
       <c r="AC136" t="n">
         <v>1</v>
       </c>
+      <c r="AE136" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF136" t="n">
         <v>0.625</v>
       </c>
@@ -10885,6 +11272,9 @@
       <c r="AC137" t="n">
         <v>1</v>
       </c>
+      <c r="AE137" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF137" t="n">
         <v>0.5384615384615384</v>
       </c>
@@ -10962,6 +11352,9 @@
       <c r="AC138" t="n">
         <v>1</v>
       </c>
+      <c r="AE138" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF138" t="n">
         <v>0.3</v>
       </c>
@@ -11039,6 +11432,9 @@
       <c r="AC139" t="n">
         <v>1</v>
       </c>
+      <c r="AE139" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF139" t="n">
         <v>0.4615384615384616</v>
       </c>
@@ -11113,6 +11509,9 @@
       <c r="AC140" t="n">
         <v>1</v>
       </c>
+      <c r="AE140" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF140" t="n">
         <v>0.6363636363636364</v>
       </c>
@@ -11190,6 +11589,9 @@
       <c r="AC141" t="n">
         <v>1</v>
       </c>
+      <c r="AE141" t="n">
+        <v>1</v>
+      </c>
       <c r="AF141" t="n">
         <v>0.7</v>
       </c>
@@ -11267,6 +11669,9 @@
       <c r="AC142" t="n">
         <v>1</v>
       </c>
+      <c r="AE142" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF142" t="n">
         <v>0.5555555555555556</v>
       </c>
@@ -11341,6 +11746,9 @@
       <c r="AC143" t="n">
         <v>1</v>
       </c>
+      <c r="AE143" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF143" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -11418,6 +11826,9 @@
       <c r="AC144" t="n">
         <v>1</v>
       </c>
+      <c r="AE144" t="n">
+        <v>0.625</v>
+      </c>
       <c r="AF144" t="n">
         <v>0.4285714285714285</v>
       </c>
@@ -11495,6 +11906,9 @@
       <c r="AC145" t="n">
         <v>1</v>
       </c>
+      <c r="AE145" t="n">
+        <v>0.8888888888888888</v>
+      </c>
       <c r="AF145" t="n">
         <v>0.4444444444444444</v>
       </c>
@@ -11572,6 +11986,9 @@
       <c r="AC146" t="n">
         <v>1</v>
       </c>
+      <c r="AE146" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AF146" t="n">
         <v>0.5833333333333334</v>
       </c>
@@ -11649,6 +12066,9 @@
       <c r="AC147" t="n">
         <v>1</v>
       </c>
+      <c r="AE147" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF147" t="n">
         <v>0.75</v>
       </c>
@@ -11726,6 +12146,9 @@
       <c r="AC148" t="n">
         <v>1</v>
       </c>
+      <c r="AE148" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF148" t="n">
         <v>0.8333333333333334</v>
       </c>
@@ -11803,6 +12226,9 @@
       <c r="AC149" t="n">
         <v>1</v>
       </c>
+      <c r="AE149" t="n">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AF149" t="n">
         <v>0.6363636363636364</v>
       </c>
@@ -11880,6 +12306,9 @@
       <c r="AC150" t="n">
         <v>1</v>
       </c>
+      <c r="AE150" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AF150" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -11957,6 +12386,9 @@
       <c r="AC151" t="n">
         <v>1</v>
       </c>
+      <c r="AE151" t="n">
+        <v>1</v>
+      </c>
       <c r="AF151" t="n">
         <v>0.3333333333333333</v>
       </c>
@@ -12034,6 +12466,9 @@
       <c r="AC152" t="n">
         <v>1</v>
       </c>
+      <c r="AE152" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF152" t="n">
         <v>0.5</v>
       </c>
@@ -12111,6 +12546,9 @@
       <c r="AC153" t="n">
         <v>1</v>
       </c>
+      <c r="AE153" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="AF153" t="n">
         <v>0.4545454545454545</v>
       </c>
@@ -12185,6 +12623,9 @@
       <c r="AC154" t="n">
         <v>1</v>
       </c>
+      <c r="AE154" t="n">
+        <v>1</v>
+      </c>
       <c r="AF154" t="n">
         <v>0.6</v>
       </c>
@@ -12262,6 +12703,9 @@
       <c r="AC155" t="n">
         <v>1</v>
       </c>
+      <c r="AE155" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF155" t="n">
         <v>0.625</v>
       </c>
@@ -12339,6 +12783,9 @@
       <c r="AC156" t="n">
         <v>1</v>
       </c>
+      <c r="AE156" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF156" t="n">
         <v>0.7272727272727273</v>
       </c>
@@ -12416,6 +12863,9 @@
       <c r="AC157" t="n">
         <v>1</v>
       </c>
+      <c r="AE157" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF157" t="n">
         <v>0.5</v>
       </c>
@@ -12493,6 +12943,9 @@
       <c r="AC158" t="n">
         <v>1</v>
       </c>
+      <c r="AE158" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="AF158" t="n">
         <v>0.5</v>
       </c>
@@ -12570,6 +13023,9 @@
       <c r="AC159" t="n">
         <v>1</v>
       </c>
+      <c r="AE159" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AF159" t="n">
         <v>0.875</v>
       </c>
@@ -12647,6 +13103,9 @@
       <c r="AC160" t="n">
         <v>1</v>
       </c>
+      <c r="AE160" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF160" t="n">
         <v>0.7692307692307693</v>
       </c>
@@ -12724,6 +13183,9 @@
       <c r="AC161" t="n">
         <v>1</v>
       </c>
+      <c r="AE161" t="n">
+        <v>1</v>
+      </c>
       <c r="AF161" t="n">
         <v>0.6923076923076923</v>
       </c>
@@ -12801,6 +13263,9 @@
       <c r="AC162" t="n">
         <v>1</v>
       </c>
+      <c r="AE162" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF162" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -12878,6 +13343,9 @@
       <c r="AC163" t="n">
         <v>1</v>
       </c>
+      <c r="AE163" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF163" t="n">
         <v>0.6</v>
       </c>
@@ -12955,6 +13423,9 @@
       <c r="AC164" t="n">
         <v>1</v>
       </c>
+      <c r="AE164" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF164" t="n">
         <v>0.5</v>
       </c>
@@ -13032,6 +13503,9 @@
       <c r="AC165" t="n">
         <v>1</v>
       </c>
+      <c r="AE165" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF165" t="n">
         <v>0.875</v>
       </c>
@@ -13109,6 +13583,9 @@
       <c r="AC166" t="n">
         <v>1</v>
       </c>
+      <c r="AE166" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AF166" t="n">
         <v>0.3636363636363636</v>
       </c>
@@ -13186,6 +13663,9 @@
       <c r="AC167" t="n">
         <v>1</v>
       </c>
+      <c r="AE167" t="n">
+        <v>1</v>
+      </c>
       <c r="AF167" t="n">
         <v>0.6363636363636364</v>
       </c>
@@ -13263,6 +13743,9 @@
       <c r="AC168" t="n">
         <v>1</v>
       </c>
+      <c r="AE168" t="n">
+        <v>1</v>
+      </c>
       <c r="AF168" t="n">
         <v>0.6</v>
       </c>
@@ -13340,6 +13823,9 @@
       <c r="AC169" t="n">
         <v>1</v>
       </c>
+      <c r="AE169" t="n">
+        <v>1</v>
+      </c>
       <c r="AF169" t="n">
         <v>0.6</v>
       </c>
@@ -13417,6 +13903,9 @@
       <c r="AC170" t="n">
         <v>1</v>
       </c>
+      <c r="AE170" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF170" t="n">
         <v>0.75</v>
       </c>
@@ -13494,6 +13983,9 @@
       <c r="AC171" t="n">
         <v>1</v>
       </c>
+      <c r="AE171" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF171" t="n">
         <v>0.5</v>
       </c>
@@ -13571,6 +14063,9 @@
       <c r="AC172" t="n">
         <v>1</v>
       </c>
+      <c r="AE172" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AF172" t="n">
         <v>0.7272727272727273</v>
       </c>
@@ -13648,6 +14143,9 @@
       <c r="AC173" t="n">
         <v>1</v>
       </c>
+      <c r="AE173" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF173" t="n">
         <v>0.5454545454545454</v>
       </c>
@@ -13725,6 +14223,9 @@
       <c r="AC174" t="n">
         <v>1</v>
       </c>
+      <c r="AE174" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AF174" t="n">
         <v>0.625</v>
       </c>
@@ -13802,6 +14303,9 @@
       <c r="AC175" t="n">
         <v>1</v>
       </c>
+      <c r="AE175" t="n">
+        <v>1</v>
+      </c>
       <c r="AF175" t="n">
         <v>0.7</v>
       </c>
@@ -13879,6 +14383,9 @@
       <c r="AC176" t="n">
         <v>1</v>
       </c>
+      <c r="AE176" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="AF176" t="n">
         <v>0.5555555555555556</v>
       </c>
@@ -13956,6 +14463,9 @@
       <c r="AC177" t="n">
         <v>1</v>
       </c>
+      <c r="AE177" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF177" t="n">
         <v>0.5555555555555556</v>
       </c>
@@ -14033,6 +14543,9 @@
       <c r="AC178" t="n">
         <v>1</v>
       </c>
+      <c r="AE178" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AF178" t="n">
         <v>0.3</v>
       </c>
@@ -14110,6 +14623,9 @@
       <c r="AC179" t="n">
         <v>1</v>
       </c>
+      <c r="AE179" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF179" t="n">
         <v>0.5833333333333334</v>
       </c>
@@ -14187,6 +14703,9 @@
       <c r="AC180" t="n">
         <v>1</v>
       </c>
+      <c r="AE180" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF180" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -14261,6 +14780,9 @@
       <c r="AC181" t="n">
         <v>1</v>
       </c>
+      <c r="AE181" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF181" t="n">
         <v>0.375</v>
       </c>
@@ -14338,6 +14860,9 @@
       <c r="AC182" t="n">
         <v>1</v>
       </c>
+      <c r="AE182" t="n">
+        <v>0.8888888888888888</v>
+      </c>
       <c r="AF182" t="n">
         <v>0.5</v>
       </c>
@@ -14415,6 +14940,9 @@
       <c r="AC183" t="n">
         <v>1</v>
       </c>
+      <c r="AE183" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AF183" t="n">
         <v>0.5454545454545454</v>
       </c>
@@ -14492,6 +15020,9 @@
       <c r="AC184" t="n">
         <v>1</v>
       </c>
+      <c r="AE184" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AF184" t="n">
         <v>0.5454545454545454</v>
       </c>
@@ -14569,6 +15100,9 @@
       <c r="AC185" t="n">
         <v>1</v>
       </c>
+      <c r="AE185" t="n">
+        <v>0.8888888888888888</v>
+      </c>
       <c r="AF185" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -14646,6 +15180,9 @@
       <c r="AC186" t="n">
         <v>1</v>
       </c>
+      <c r="AE186" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF186" t="n">
         <v>0.8181818181818182</v>
       </c>
@@ -14723,6 +15260,9 @@
       <c r="AC187" t="n">
         <v>1</v>
       </c>
+      <c r="AE187" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AF187" t="n">
         <v>0.4444444444444444</v>
       </c>
@@ -14800,6 +15340,9 @@
       <c r="AC188" t="n">
         <v>1</v>
       </c>
+      <c r="AE188" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF188" t="n">
         <v>0.4</v>
       </c>
@@ -14877,6 +15420,9 @@
       <c r="AC189" t="n">
         <v>1</v>
       </c>
+      <c r="AE189" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF189" t="n">
         <v>0.5</v>
       </c>
@@ -14954,6 +15500,9 @@
       <c r="AC190" t="n">
         <v>1</v>
       </c>
+      <c r="AE190" t="n">
+        <v>1</v>
+      </c>
       <c r="AF190" t="n">
         <v>0.4</v>
       </c>
@@ -15031,6 +15580,9 @@
       <c r="AC191" t="n">
         <v>1</v>
       </c>
+      <c r="AE191" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="AF191" t="n">
         <v>0.7777777777777778</v>
       </c>
@@ -15108,6 +15660,9 @@
       <c r="AC192" t="n">
         <v>1</v>
       </c>
+      <c r="AE192" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="AF192" t="n">
         <v>0.5</v>
       </c>
@@ -15185,6 +15740,9 @@
       <c r="AC193" t="n">
         <v>1</v>
       </c>
+      <c r="AE193" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF193" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -15262,6 +15820,9 @@
       <c r="AC194" t="n">
         <v>1</v>
       </c>
+      <c r="AE194" t="n">
+        <v>1</v>
+      </c>
       <c r="AF194" t="n">
         <v>0.5555555555555556</v>
       </c>
@@ -15339,6 +15900,9 @@
       <c r="AC195" t="n">
         <v>1</v>
       </c>
+      <c r="AE195" t="n">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="AF195" t="n">
         <v>0.5555555555555556</v>
       </c>
@@ -15416,6 +15980,9 @@
       <c r="AC196" t="n">
         <v>1</v>
       </c>
+      <c r="AE196" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF196" t="n">
         <v>0.5454545454545454</v>
       </c>
@@ -15493,6 +16060,9 @@
       <c r="AC197" t="n">
         <v>1</v>
       </c>
+      <c r="AE197" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF197" t="n">
         <v>0.375</v>
       </c>
@@ -15570,6 +16140,9 @@
       <c r="AC198" t="n">
         <v>1</v>
       </c>
+      <c r="AE198" t="n">
+        <v>1</v>
+      </c>
       <c r="AF198" t="n">
         <v>0.7142857142857143</v>
       </c>
@@ -15647,6 +16220,9 @@
       <c r="AC199" t="n">
         <v>1</v>
       </c>
+      <c r="AE199" t="n">
+        <v>1</v>
+      </c>
       <c r="AF199" t="n">
         <v>0.3333333333333333</v>
       </c>
@@ -15724,6 +16300,9 @@
       <c r="AC200" t="n">
         <v>1</v>
       </c>
+      <c r="AE200" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="AF200" t="n">
         <v>0.625</v>
       </c>
@@ -15801,6 +16380,9 @@
       <c r="AC201" t="n">
         <v>1</v>
       </c>
+      <c r="AE201" t="n">
+        <v>0.875</v>
+      </c>
       <c r="AF201" t="n">
         <v>0.7</v>
       </c>
@@ -15878,6 +16460,9 @@
       <c r="AC202" t="n">
         <v>1</v>
       </c>
+      <c r="AE202" t="n">
+        <v>1</v>
+      </c>
       <c r="AF202" t="n">
         <v>0.4444444444444444</v>
       </c>
@@ -15955,6 +16540,9 @@
       <c r="AC203" t="n">
         <v>1</v>
       </c>
+      <c r="AE203" t="n">
+        <v>0.8888888888888888</v>
+      </c>
       <c r="AF203" t="n">
         <v>0.75</v>
       </c>
@@ -16032,6 +16620,9 @@
       <c r="AC204" t="n">
         <v>1</v>
       </c>
+      <c r="AE204" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AF204" t="n">
         <v>0.5555555555555556</v>
       </c>
@@ -16109,6 +16700,9 @@
       <c r="AC205" t="n">
         <v>1</v>
       </c>
+      <c r="AE205" t="n">
+        <v>1</v>
+      </c>
       <c r="AF205" t="n">
         <v>0.75</v>
       </c>
@@ -16186,6 +16780,9 @@
       <c r="AC206" t="n">
         <v>1</v>
       </c>
+      <c r="AE206" t="n">
+        <v>1</v>
+      </c>
       <c r="AF206" t="n">
         <v>0.6153846153846154</v>
       </c>
@@ -16262,6 +16859,9 @@
       </c>
       <c r="AC207" t="n">
         <v>1</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>0.8</v>
       </c>
       <c r="AF207" t="n">
         <v>0.6</v>
@@ -16374,7 +16974,7 @@
         <v>0.9430666666666667</v>
       </c>
       <c r="AF212" t="n">
-        <v>0.9571400000000001</v>
+        <v>0.9323333333333332</v>
       </c>
       <c r="AG212" t="n">
         <v>0.955125</v>
@@ -24170,7 +24770,7 @@
         <v>0</v>
       </c>
       <c r="AF316" t="n">
-        <v>0.2444</v>
+        <v>0</v>
       </c>
       <c r="AG316" t="n">
         <v>0.0001</v>
@@ -31943,8 +32543,11 @@
       <c r="AC418" t="n">
         <v>0.1534222222222222</v>
       </c>
+      <c r="AE418" t="n">
+        <v>0.21082</v>
+      </c>
       <c r="AF418" t="n">
-        <v>0.13216</v>
+        <v>0.2085666666666667</v>
       </c>
       <c r="AG418" t="n">
         <v>0.150375</v>
@@ -31999,6 +32602,9 @@
       <c r="AC419" t="n">
         <v>0.1649125</v>
       </c>
+      <c r="AE419" t="n">
+        <v>0.1962333333333333</v>
+      </c>
       <c r="AF419" t="n">
         <v>0.11385</v>
       </c>
@@ -32055,6 +32661,9 @@
       <c r="AC420" t="n">
         <v>0.22192</v>
       </c>
+      <c r="AE420" t="n">
+        <v>0.2886142857142857</v>
+      </c>
       <c r="AF420" t="n">
         <v>0.2421666666666666</v>
       </c>
@@ -32111,6 +32720,9 @@
       <c r="AC421" t="n">
         <v>0.2449</v>
       </c>
+      <c r="AE421" t="n">
+        <v>0.2237625</v>
+      </c>
       <c r="AF421" t="n">
         <v>0.2618</v>
       </c>
@@ -32167,6 +32779,9 @@
       <c r="AC422" t="n">
         <v>0.2429181818181818</v>
       </c>
+      <c r="AE422" t="n">
+        <v>0.32965</v>
+      </c>
       <c r="AF422" t="n">
         <v>0.2596</v>
       </c>
@@ -32223,6 +32838,9 @@
       <c r="AC423" t="n">
         <v>0.2873692307692307</v>
       </c>
+      <c r="AE423" t="n">
+        <v>0.3196</v>
+      </c>
       <c r="AF423" t="n">
         <v>0.3299454545454546</v>
       </c>
@@ -32279,6 +32897,9 @@
       <c r="AC424" t="n">
         <v>0.3680125</v>
       </c>
+      <c r="AE424" t="n">
+        <v>0.3729444444444444</v>
+      </c>
       <c r="AF424" t="n">
         <v>0.3415666666666666</v>
       </c>
@@ -32335,6 +32956,9 @@
       <c r="AC425" t="n">
         <v>0.4224416666666668</v>
       </c>
+      <c r="AE425" t="n">
+        <v>0.4001899999999999</v>
+      </c>
       <c r="AF425" t="n">
         <v>0.40175</v>
       </c>
@@ -32391,6 +33015,9 @@
       <c r="AC426" t="n">
         <v>0.4952454545454547</v>
       </c>
+      <c r="AE426" t="n">
+        <v>0.4868000000000001</v>
+      </c>
       <c r="AF426" t="n">
         <v>0.3984199999999999</v>
       </c>
@@ -32447,6 +33074,9 @@
       <c r="AC427" t="n">
         <v>0.3912846153846154</v>
       </c>
+      <c r="AE427" t="n">
+        <v>0.4753583333333333</v>
+      </c>
       <c r="AF427" t="n">
         <v>0.3904</v>
       </c>
@@ -32491,6 +33121,9 @@
       <c r="AC428" t="n">
         <v>0.4736</v>
       </c>
+      <c r="AE428" t="n">
+        <v>0.5105272727272728</v>
+      </c>
       <c r="AF428" t="n">
         <v>0.4098555555555555</v>
       </c>
@@ -32538,6 +33171,9 @@
       <c r="AC429" t="n">
         <v>0.57748</v>
       </c>
+      <c r="AE429" t="n">
+        <v>0.6239444444444444</v>
+      </c>
       <c r="AF429" t="n">
         <v>0.4232625</v>
       </c>
@@ -32585,6 +33221,9 @@
       <c r="AC430" t="n">
         <v>0.5227833333333333</v>
       </c>
+      <c r="AE430" t="n">
+        <v>0.6690888888888888</v>
+      </c>
       <c r="AF430" t="n">
         <v>0.4967714285714285</v>
       </c>
@@ -32632,6 +33271,9 @@
       <c r="AC431" t="n">
         <v>0.4797818181818183</v>
       </c>
+      <c r="AE431" t="n">
+        <v>0.5965857142857143</v>
+      </c>
       <c r="AF431" t="n">
         <v>0.4821428571428572</v>
       </c>
@@ -32679,6 +33321,9 @@
       <c r="AC432" t="n">
         <v>0.5757357142857142</v>
       </c>
+      <c r="AE432" t="n">
+        <v>0.6135181818181817</v>
+      </c>
       <c r="AF432" t="n">
         <v>0.5716555555555556</v>
       </c>
@@ -32726,6 +33371,9 @@
       <c r="AC433" t="n">
         <v>0.6213583333333332</v>
       </c>
+      <c r="AE433" t="n">
+        <v>0.6650999999999999</v>
+      </c>
       <c r="AF433" t="n">
         <v>0.5208</v>
       </c>
@@ -32773,6 +33421,9 @@
       <c r="AC434" t="n">
         <v>0.6040615384615384</v>
       </c>
+      <c r="AE434" t="n">
+        <v>0.6131714285714286</v>
+      </c>
       <c r="AF434" t="n">
         <v>0.61748</v>
       </c>
@@ -32820,6 +33471,9 @@
       <c r="AC435" t="n">
         <v>0.5855714285714286</v>
       </c>
+      <c r="AE435" t="n">
+        <v>0.7117333333333333</v>
+      </c>
       <c r="AF435" t="n">
         <v>0.6697636363636364</v>
       </c>
@@ -32867,6 +33521,9 @@
       <c r="AC436" t="n">
         <v>0.5823153846153846</v>
       </c>
+      <c r="AE436" t="n">
+        <v>0.7179666666666668</v>
+      </c>
       <c r="AF436" t="n">
         <v>0.6910749999999999</v>
       </c>
@@ -32914,6 +33571,9 @@
       <c r="AC437" t="n">
         <v>0.6298692307692307</v>
       </c>
+      <c r="AE437" t="n">
+        <v>0.73512</v>
+      </c>
       <c r="AF437" t="n">
         <v>0.6272090909090908</v>
       </c>
@@ -32958,6 +33618,9 @@
       <c r="AC438" t="n">
         <v>0.6617545454545455</v>
       </c>
+      <c r="AE438" t="n">
+        <v>0.7061166666666666</v>
+      </c>
       <c r="AF438" t="n">
         <v>0.7179285714285714</v>
       </c>
@@ -33005,6 +33668,9 @@
       <c r="AC439" t="n">
         <v>0.5704692307692307</v>
       </c>
+      <c r="AE439" t="n">
+        <v>0.7557666666666667</v>
+      </c>
       <c r="AF439" t="n">
         <v>0.7194199999999999</v>
       </c>
@@ -33052,6 +33718,9 @@
       <c r="AC440" t="n">
         <v>0.5971083333333332</v>
       </c>
+      <c r="AE440" t="n">
+        <v>0.7010000000000001</v>
+      </c>
       <c r="AF440" t="n">
         <v>0.7299</v>
       </c>
@@ -33099,6 +33768,9 @@
       <c r="AC441" t="n">
         <v>0.6017916666666667</v>
       </c>
+      <c r="AE441" t="n">
+        <v>0.7742875</v>
+      </c>
       <c r="AF441" t="n">
         <v>0.7723749999999999</v>
       </c>
@@ -33146,6 +33818,9 @@
       <c r="AC442" t="n">
         <v>0.6147750000000001</v>
       </c>
+      <c r="AE442" t="n">
+        <v>0.7402375</v>
+      </c>
       <c r="AF442" t="n">
         <v>0.6776599999999999</v>
       </c>
@@ -33193,6 +33868,9 @@
       <c r="AC443" t="n">
         <v>0.6563272727272726</v>
       </c>
+      <c r="AE443" t="n">
+        <v>0.7714909090909091</v>
+      </c>
       <c r="AF443" t="n">
         <v>0.6970250000000001</v>
       </c>
@@ -33240,6 +33918,9 @@
       <c r="AC444" t="n">
         <v>0.6547500000000001</v>
       </c>
+      <c r="AE444" t="n">
+        <v>0.763975</v>
+      </c>
       <c r="AF444" t="n">
         <v>0.7830454545454544</v>
       </c>
@@ -33287,6 +33968,9 @@
       <c r="AC445" t="n">
         <v>0.6375999999999998</v>
       </c>
+      <c r="AE445" t="n">
+        <v>0.7619333333333334</v>
+      </c>
       <c r="AF445" t="n">
         <v>0.8399333333333332</v>
       </c>
@@ -33334,6 +34018,9 @@
       <c r="AC446" t="n">
         <v>0.7462461538461537</v>
       </c>
+      <c r="AE446" t="n">
+        <v>0.7169375000000001</v>
+      </c>
       <c r="AF446" t="n">
         <v>0.70085</v>
       </c>
@@ -33381,6 +34068,9 @@
       <c r="AC447" t="n">
         <v>0.6812083333333335</v>
       </c>
+      <c r="AE447" t="n">
+        <v>0.8429111111111109</v>
+      </c>
       <c r="AF447" t="n">
         <v>0.8234249999999999</v>
       </c>
@@ -33428,6 +34118,9 @@
       <c r="AC448" t="n">
         <v>0.6009833333333334</v>
       </c>
+      <c r="AE448" t="n">
+        <v>0.7176666666666667</v>
+      </c>
       <c r="AF448" t="n">
         <v>0.8590750000000001</v>
       </c>
@@ -33475,6 +34168,9 @@
       <c r="AC449" t="n">
         <v>0.6493846153846154</v>
       </c>
+      <c r="AE449" t="n">
+        <v>0.7721375</v>
+      </c>
       <c r="AF449" t="n">
         <v>0.6913888888888888</v>
       </c>
@@ -33519,6 +34215,9 @@
       <c r="AC450" t="n">
         <v>0.6377272727272726</v>
       </c>
+      <c r="AE450" t="n">
+        <v>0.7523</v>
+      </c>
       <c r="AF450" t="n">
         <v>0.8122874999999999</v>
       </c>
@@ -33566,6 +34265,9 @@
       <c r="AC451" t="n">
         <v>0.7466666666666667</v>
       </c>
+      <c r="AE451" t="n">
+        <v>0.79535</v>
+      </c>
       <c r="AF451" t="n">
         <v>0.756</v>
       </c>
@@ -33613,6 +34315,9 @@
       <c r="AC452" t="n">
         <v>0.66817</v>
       </c>
+      <c r="AE452" t="n">
+        <v>0.7827375000000001</v>
+      </c>
       <c r="AF452" t="n">
         <v>0.8365</v>
       </c>
@@ -33657,6 +34362,9 @@
       <c r="AC453" t="n">
         <v>0.6596909090909091</v>
       </c>
+      <c r="AE453" t="n">
+        <v>0.8176000000000001</v>
+      </c>
       <c r="AF453" t="n">
         <v>0.8086428571428571</v>
       </c>
@@ -33704,6 +34412,9 @@
       <c r="AC454" t="n">
         <v>0.6688923076923078</v>
       </c>
+      <c r="AE454" t="n">
+        <v>0.7852600000000001</v>
+      </c>
       <c r="AF454" t="n">
         <v>0.765475</v>
       </c>
@@ -33751,6 +34462,9 @@
       <c r="AC455" t="n">
         <v>0.5749</v>
       </c>
+      <c r="AE455" t="n">
+        <v>0.8203571428571428</v>
+      </c>
       <c r="AF455" t="n">
         <v>0.8568363636363638</v>
       </c>
@@ -33798,6 +34512,9 @@
       <c r="AC456" t="n">
         <v>0.6647909090909091</v>
       </c>
+      <c r="AE456" t="n">
+        <v>0.7939833333333333</v>
+      </c>
       <c r="AF456" t="n">
         <v>0.7533</v>
       </c>
@@ -33845,6 +34562,9 @@
       <c r="AC457" t="n">
         <v>0.6804928571428571</v>
       </c>
+      <c r="AE457" t="n">
+        <v>0.7228090909090908</v>
+      </c>
       <c r="AF457" t="n">
         <v>0.7226666666666667</v>
       </c>
@@ -33892,6 +34612,9 @@
       <c r="AC458" t="n">
         <v>0.6463</v>
       </c>
+      <c r="AE458" t="n">
+        <v>0.7877571428571429</v>
+      </c>
       <c r="AF458" t="n">
         <v>0.73442</v>
       </c>
@@ -33939,6 +34662,9 @@
       <c r="AC459" t="n">
         <v>0.632775</v>
       </c>
+      <c r="AE459" t="n">
+        <v>0.7976300000000001</v>
+      </c>
       <c r="AF459" t="n">
         <v>0.8531625000000002</v>
       </c>
@@ -33986,6 +34712,9 @@
       <c r="AC460" t="n">
         <v>0.6456636363636363</v>
       </c>
+      <c r="AE460" t="n">
+        <v>0.7648111111111111</v>
+      </c>
       <c r="AF460" t="n">
         <v>0.8057333333333333</v>
       </c>
@@ -34033,6 +34762,9 @@
       <c r="AC461" t="n">
         <v>0.6230384615384614</v>
       </c>
+      <c r="AE461" t="n">
+        <v>0.7052333333333335</v>
+      </c>
       <c r="AF461" t="n">
         <v>0.8199916666666668</v>
       </c>
@@ -34080,6 +34812,9 @@
       <c r="AC462" t="n">
         <v>0.6374583333333333</v>
       </c>
+      <c r="AE462" t="n">
+        <v>0.8264363636363636</v>
+      </c>
       <c r="AF462" t="n">
         <v>0.862511111111111</v>
       </c>
@@ -34127,6 +34862,9 @@
       <c r="AC463" t="n">
         <v>0.59465</v>
       </c>
+      <c r="AE463" t="n">
+        <v>0.8513875000000001</v>
+      </c>
       <c r="AF463" t="n">
         <v>0.77951</v>
       </c>
@@ -34171,6 +34909,9 @@
       <c r="AC464" t="n">
         <v>0.66703</v>
       </c>
+      <c r="AE464" t="n">
+        <v>0.807988888888889</v>
+      </c>
       <c r="AF464" t="n">
         <v>0.8257666666666666</v>
       </c>
@@ -34218,6 +34959,9 @@
       <c r="AC465" t="n">
         <v>0.6334999999999998</v>
       </c>
+      <c r="AE465" t="n">
+        <v>0.822725</v>
+      </c>
       <c r="AF465" t="n">
         <v>0.8161999999999999</v>
       </c>
@@ -34265,6 +35009,9 @@
       <c r="AC466" t="n">
         <v>0.6330727272727272</v>
       </c>
+      <c r="AE466" t="n">
+        <v>0.8486111111111111</v>
+      </c>
       <c r="AF466" t="n">
         <v>0.7726714285714286</v>
       </c>
@@ -34312,6 +35059,9 @@
       <c r="AC467" t="n">
         <v>0.5960500000000001</v>
       </c>
+      <c r="AE467" t="n">
+        <v>0.7753777777777777</v>
+      </c>
       <c r="AF467" t="n">
         <v>0.9099600000000002</v>
       </c>
@@ -34359,6 +35109,9 @@
       <c r="AC468" t="n">
         <v>0.6233416666666666</v>
       </c>
+      <c r="AE468" t="n">
+        <v>0.800625</v>
+      </c>
       <c r="AF468" t="n">
         <v>0.7612666666666666</v>
       </c>
@@ -34406,6 +35159,9 @@
       <c r="AC469" t="n">
         <v>0.6418142857142858</v>
       </c>
+      <c r="AE469" t="n">
+        <v>0.8267200000000001</v>
+      </c>
       <c r="AF469" t="n">
         <v>0.8188249999999999</v>
       </c>
@@ -34453,6 +35209,9 @@
       <c r="AC470" t="n">
         <v>0.5600846153846153</v>
       </c>
+      <c r="AE470" t="n">
+        <v>0.82225</v>
+      </c>
       <c r="AF470" t="n">
         <v>0.8237</v>
       </c>
@@ -34500,6 +35259,9 @@
       <c r="AC471" t="n">
         <v>0.6603999999999999</v>
       </c>
+      <c r="AE471" t="n">
+        <v>0.8405875</v>
+      </c>
       <c r="AF471" t="n">
         <v>0.8376833333333332</v>
       </c>
@@ -34547,6 +35309,9 @@
       <c r="AC472" t="n">
         <v>0.6093916666666667</v>
       </c>
+      <c r="AE472" t="n">
+        <v>0.7876727272727272</v>
+      </c>
       <c r="AF472" t="n">
         <v>0.8511555555555554</v>
       </c>
@@ -34594,6 +35359,9 @@
       <c r="AC473" t="n">
         <v>0.5775499999999999</v>
       </c>
+      <c r="AE473" t="n">
+        <v>0.7727083333333336</v>
+      </c>
       <c r="AF473" t="n">
         <v>0.8157000000000001</v>
       </c>
@@ -34641,6 +35409,9 @@
       <c r="AC474" t="n">
         <v>0.5617666666666666</v>
       </c>
+      <c r="AE474" t="n">
+        <v>0.7641777777777778</v>
+      </c>
       <c r="AF474" t="n">
         <v>0.87422</v>
       </c>
@@ -34688,6 +35459,9 @@
       <c r="AC475" t="n">
         <v>0.6169272727272728</v>
       </c>
+      <c r="AE475" t="n">
+        <v>0.832225</v>
+      </c>
       <c r="AF475" t="n">
         <v>0.856275</v>
       </c>
@@ -34735,6 +35509,9 @@
       <c r="AC476" t="n">
         <v>0.6776</v>
       </c>
+      <c r="AE476" t="n">
+        <v>0.7699199999999999</v>
+      </c>
       <c r="AF476" t="n">
         <v>0.8098727272727273</v>
       </c>
@@ -34782,6 +35559,9 @@
       <c r="AC477" t="n">
         <v>0.6557916666666667</v>
       </c>
+      <c r="AE477" t="n">
+        <v>0.8388142857142858</v>
+      </c>
       <c r="AF477" t="n">
         <v>0.9137624999999999</v>
       </c>
@@ -34829,6 +35609,9 @@
       <c r="AC478" t="n">
         <v>0.5943307692307692</v>
       </c>
+      <c r="AE478" t="n">
+        <v>0.7797499999999999</v>
+      </c>
       <c r="AF478" t="n">
         <v>0.7263333333333333</v>
       </c>
@@ -34876,6 +35659,9 @@
       <c r="AC479" t="n">
         <v>0.5615307692307693</v>
       </c>
+      <c r="AE479" t="n">
+        <v>0.8019428571428573</v>
+      </c>
       <c r="AF479" t="n">
         <v>0.7894111111111112</v>
       </c>
@@ -34923,6 +35709,9 @@
       <c r="AC480" t="n">
         <v>0.6657083333333333</v>
       </c>
+      <c r="AE480" t="n">
+        <v>0.8722000000000001</v>
+      </c>
       <c r="AF480" t="n">
         <v>0.8367666666666665</v>
       </c>
@@ -34970,6 +35759,9 @@
       <c r="AC481" t="n">
         <v>0.6474818181818182</v>
       </c>
+      <c r="AE481" t="n">
+        <v>0.866125</v>
+      </c>
       <c r="AF481" t="n">
         <v>0.8291600000000001</v>
       </c>
@@ -35017,6 +35809,9 @@
       <c r="AC482" t="n">
         <v>0.5884272727272726</v>
       </c>
+      <c r="AE482" t="n">
+        <v>0.7880230769230768</v>
+      </c>
       <c r="AF482" t="n">
         <v>0.7949857142857143</v>
       </c>
@@ -35064,6 +35859,9 @@
       <c r="AC483" t="n">
         <v>0.6607461538461538</v>
       </c>
+      <c r="AE483" t="n">
+        <v>0.7295666666666666</v>
+      </c>
       <c r="AF483" t="n">
         <v>0.8379</v>
       </c>
@@ -35111,6 +35909,9 @@
       <c r="AC484" t="n">
         <v>0.6403333333333333</v>
       </c>
+      <c r="AE484" t="n">
+        <v>0.8381000000000002</v>
+      </c>
       <c r="AF484" t="n">
         <v>0.75573</v>
       </c>
@@ -35158,6 +35959,9 @@
       <c r="AC485" t="n">
         <v>0.5938999999999999</v>
       </c>
+      <c r="AE485" t="n">
+        <v>0.8558888888888889</v>
+      </c>
       <c r="AF485" t="n">
         <v>0.8803000000000001</v>
       </c>
@@ -35205,6 +36009,9 @@
       <c r="AC486" t="n">
         <v>0.6617818181818181</v>
       </c>
+      <c r="AE486" t="n">
+        <v>0.8108875</v>
+      </c>
       <c r="AF486" t="n">
         <v>0.79813</v>
       </c>
@@ -35252,6 +36059,9 @@
       <c r="AC487" t="n">
         <v>0.7187000000000001</v>
       </c>
+      <c r="AE487" t="n">
+        <v>0.7681888888888889</v>
+      </c>
       <c r="AF487" t="n">
         <v>0.87492</v>
       </c>
@@ -35299,6 +36109,9 @@
       <c r="AC488" t="n">
         <v>0.6532749999999999</v>
       </c>
+      <c r="AE488" t="n">
+        <v>0.7734599999999999</v>
+      </c>
       <c r="AF488" t="n">
         <v>0.838225</v>
       </c>
@@ -35346,6 +36159,9 @@
       <c r="AC489" t="n">
         <v>0.6956785714285714</v>
       </c>
+      <c r="AE489" t="n">
+        <v>0.7183916666666667</v>
+      </c>
       <c r="AF489" t="n">
         <v>0.8140500000000001</v>
       </c>
@@ -35393,6 +36209,9 @@
       <c r="AC490" t="n">
         <v>0.70672</v>
       </c>
+      <c r="AE490" t="n">
+        <v>0.7553222222222223</v>
+      </c>
       <c r="AF490" t="n">
         <v>0.8540111111111112</v>
       </c>
@@ -35437,6 +36256,9 @@
       <c r="AC491" t="n">
         <v>0.5745083333333333</v>
       </c>
+      <c r="AE491" t="n">
+        <v>0.8608222222222222</v>
+      </c>
       <c r="AF491" t="n">
         <v>0.8558666666666666</v>
       </c>
@@ -35484,6 +36306,9 @@
       <c r="AC492" t="n">
         <v>0.6133583333333333</v>
       </c>
+      <c r="AE492" t="n">
+        <v>0.7385571428571429</v>
+      </c>
       <c r="AF492" t="n">
         <v>0.8560416666666667</v>
       </c>
@@ -35531,6 +36356,9 @@
       <c r="AC493" t="n">
         <v>0.65625</v>
       </c>
+      <c r="AE493" t="n">
+        <v>0.7979700000000001</v>
+      </c>
       <c r="AF493" t="n">
         <v>0.861488888888889</v>
       </c>
@@ -35578,6 +36406,9 @@
       <c r="AC494" t="n">
         <v>0.6596900000000001</v>
       </c>
+      <c r="AE494" t="n">
+        <v>0.8495909090909091</v>
+      </c>
       <c r="AF494" t="n">
         <v>0.8537333333333333</v>
       </c>
@@ -35625,6 +36456,9 @@
       <c r="AC495" t="n">
         <v>0.6137333333333334</v>
       </c>
+      <c r="AE495" t="n">
+        <v>0.9012428571428571</v>
+      </c>
       <c r="AF495" t="n">
         <v>0.7909555555555555</v>
       </c>
@@ -35672,6 +36506,9 @@
       <c r="AC496" t="n">
         <v>0.6244071428571428</v>
       </c>
+      <c r="AE496" t="n">
+        <v>0.7677083333333333</v>
+      </c>
       <c r="AF496" t="n">
         <v>0.7771333333333333</v>
       </c>
@@ -35719,6 +36556,9 @@
       <c r="AC497" t="n">
         <v>0.5975307692307692</v>
       </c>
+      <c r="AE497" t="n">
+        <v>0.7753166666666668</v>
+      </c>
       <c r="AF497" t="n">
         <v>0.7729363636363636</v>
       </c>
@@ -35766,6 +36606,9 @@
       <c r="AC498" t="n">
         <v>0.6383727272727273</v>
       </c>
+      <c r="AE498" t="n">
+        <v>0.8414857142857143</v>
+      </c>
       <c r="AF498" t="n">
         <v>0.8871909090909091</v>
       </c>
@@ -35813,6 +36656,9 @@
       <c r="AC499" t="n">
         <v>0.6384083333333334</v>
       </c>
+      <c r="AE499" t="n">
+        <v>0.7575</v>
+      </c>
       <c r="AF499" t="n">
         <v>0.7679333333333334</v>
       </c>
@@ -35860,6 +36706,9 @@
       <c r="AC500" t="n">
         <v>0.6275999999999999</v>
       </c>
+      <c r="AE500" t="n">
+        <v>0.8749272727272728</v>
+      </c>
       <c r="AF500" t="n">
         <v>0.852809090909091</v>
       </c>
@@ -35907,6 +36756,9 @@
       <c r="AC501" t="n">
         <v>0.6562333333333333</v>
       </c>
+      <c r="AE501" t="n">
+        <v>0.8337818181818182</v>
+      </c>
       <c r="AF501" t="n">
         <v>0.853925</v>
       </c>
@@ -35954,6 +36806,9 @@
       <c r="AC502" t="n">
         <v>0.6236636363636363</v>
       </c>
+      <c r="AE502" t="n">
+        <v>0.8487</v>
+      </c>
       <c r="AF502" t="n">
         <v>0.8632727272727273</v>
       </c>
@@ -36001,6 +36856,9 @@
       <c r="AC503" t="n">
         <v>0.5678</v>
       </c>
+      <c r="AE503" t="n">
+        <v>0.7620749999999999</v>
+      </c>
       <c r="AF503" t="n">
         <v>0.8147714285714286</v>
       </c>
@@ -36048,6 +36906,9 @@
       <c r="AC504" t="n">
         <v>0.7335583333333334</v>
       </c>
+      <c r="AE504" t="n">
+        <v>0.8278</v>
+      </c>
       <c r="AF504" t="n">
         <v>0.8250300000000002</v>
       </c>
@@ -36095,6 +36956,9 @@
       <c r="AC505" t="n">
         <v>0.6456</v>
       </c>
+      <c r="AE505" t="n">
+        <v>0.7441</v>
+      </c>
       <c r="AF505" t="n">
         <v>0.8677300000000001</v>
       </c>
@@ -36142,6 +37006,9 @@
       <c r="AC506" t="n">
         <v>0.6514</v>
       </c>
+      <c r="AE506" t="n">
+        <v>0.7855666666666666</v>
+      </c>
       <c r="AF506" t="n">
         <v>0.8842111111111112</v>
       </c>
@@ -36189,6 +37056,9 @@
       <c r="AC507" t="n">
         <v>0.6392454545454546</v>
       </c>
+      <c r="AE507" t="n">
+        <v>0.7847333333333332</v>
+      </c>
       <c r="AF507" t="n">
         <v>0.8440090909090909</v>
       </c>
@@ -36236,6 +37106,9 @@
       <c r="AC508" t="n">
         <v>0.6178833333333333</v>
       </c>
+      <c r="AE508" t="n">
+        <v>0.8195666666666668</v>
+      </c>
       <c r="AF508" t="n">
         <v>0.7984000000000001</v>
       </c>
@@ -36283,6 +37156,9 @@
       <c r="AC509" t="n">
         <v>0.6232076923076921</v>
       </c>
+      <c r="AE509" t="n">
+        <v>0.8851142857142857</v>
+      </c>
       <c r="AF509" t="n">
         <v>0.8212833333333333</v>
       </c>
@@ -36330,6 +37206,9 @@
       <c r="AC510" t="n">
         <v>0.6369083333333333</v>
       </c>
+      <c r="AE510" t="n">
+        <v>0.7951400000000001</v>
+      </c>
       <c r="AF510" t="n">
         <v>0.82751</v>
       </c>
@@ -36377,6 +37256,9 @@
       <c r="AC511" t="n">
         <v>0.6822777777777778</v>
       </c>
+      <c r="AE511" t="n">
+        <v>0.80325</v>
+      </c>
       <c r="AF511" t="n">
         <v>0.7893250000000001</v>
       </c>
@@ -36424,6 +37306,9 @@
       <c r="AC512" t="n">
         <v>0.5748</v>
       </c>
+      <c r="AE512" t="n">
+        <v>0.8198555555555554</v>
+      </c>
       <c r="AF512" t="n">
         <v>0.8581727272727271</v>
       </c>
@@ -36471,6 +37356,9 @@
       <c r="AC513" t="n">
         <v>0.6514545454545455</v>
       </c>
+      <c r="AE513" t="n">
+        <v>0.8551571428571428</v>
+      </c>
       <c r="AF513" t="n">
         <v>0.7951555555555555</v>
       </c>
@@ -36518,6 +37406,9 @@
       <c r="AC514" t="n">
         <v>0.6691583333333333</v>
       </c>
+      <c r="AE514" t="n">
+        <v>0.8432222222222223</v>
+      </c>
       <c r="AF514" t="n">
         <v>0.7638400000000001</v>
       </c>
@@ -36565,6 +37456,9 @@
       <c r="AC515" t="n">
         <v>0.5082</v>
       </c>
+      <c r="AE515" t="n">
+        <v>0.7709111111111111</v>
+      </c>
       <c r="AF515" t="n">
         <v>0.8126333333333334</v>
       </c>
@@ -36612,6 +37506,9 @@
       <c r="AC516" t="n">
         <v>0.6212714285714285</v>
       </c>
+      <c r="AE516" t="n">
+        <v>0.8068363636363636</v>
+      </c>
       <c r="AF516" t="n">
         <v>0.8659000000000001</v>
       </c>
@@ -36658,6 +37555,9 @@
       </c>
       <c r="AC517" t="n">
         <v>0.6714166666666667</v>
+      </c>
+      <c r="AE517" t="n">
+        <v>0.7667818181818181</v>
       </c>
       <c r="AF517" t="n">
         <v>0.783588888888889</v>
@@ -36714,8 +37614,11 @@
       <c r="AC520" t="n">
         <v>0.1778257575757576</v>
       </c>
+      <c r="AE520" t="n">
+        <v>0.1409777777777778</v>
+      </c>
       <c r="AF520" t="n">
-        <v>0.1211935483870968</v>
+        <v>0.136831506849315</v>
       </c>
       <c r="AG520" t="n">
         <v>0.1444220588235294</v>
@@ -36755,6 +37658,9 @@
       <c r="AC521" t="n">
         <v>0.1586368421052632</v>
       </c>
+      <c r="AE521" t="n">
+        <v>0.16495</v>
+      </c>
       <c r="AF521" t="n">
         <v>0.02614615384615384</v>
       </c>
@@ -36796,6 +37702,9 @@
       <c r="AC522" t="n">
         <v>0.2495617647058823</v>
       </c>
+      <c r="AE522" t="n">
+        <v>0.1847148148148148</v>
+      </c>
       <c r="AF522" t="n">
         <v>0.1229172413793103</v>
       </c>
@@ -36837,6 +37746,9 @@
       <c r="AC523" t="n">
         <v>0.2561083333333333</v>
       </c>
+      <c r="AE523" t="n">
+        <v>0.3985833333333333</v>
+      </c>
       <c r="AF523" t="n">
         <v>0.165432</v>
       </c>
@@ -36878,6 +37790,9 @@
       <c r="AC524" t="n">
         <v>0.3331469387755102</v>
       </c>
+      <c r="AE524" t="n">
+        <v>0.3459789473684211</v>
+      </c>
       <c r="AF524" t="n">
         <v>0.2831285714285715</v>
       </c>
@@ -36919,6 +37834,9 @@
       <c r="AC525" t="n">
         <v>0.3252390243902439</v>
       </c>
+      <c r="AE525" t="n">
+        <v>0.3869058823529412</v>
+      </c>
       <c r="AF525" t="n">
         <v>0.2694428571428572</v>
       </c>
@@ -36960,6 +37878,9 @@
       <c r="AC526" t="n">
         <v>0.3929862068965517</v>
       </c>
+      <c r="AE526" t="n">
+        <v>0.5496242424242423</v>
+      </c>
       <c r="AF526" t="n">
         <v>0.3458558823529412</v>
       </c>
@@ -37001,6 +37922,9 @@
       <c r="AC527" t="n">
         <v>0.3442854166666667</v>
       </c>
+      <c r="AE527" t="n">
+        <v>0.504332</v>
+      </c>
       <c r="AF527" t="n">
         <v>0.5026571428571428</v>
       </c>
@@ -37042,6 +37966,9 @@
       <c r="AC528" t="n">
         <v>0.4050230769230769</v>
       </c>
+      <c r="AE528" t="n">
+        <v>0.5666724137931035</v>
+      </c>
       <c r="AF528" t="n">
         <v>0.461745</v>
       </c>
@@ -37083,6 +38010,9 @@
       <c r="AC529" t="n">
         <v>0.3247592592592592</v>
       </c>
+      <c r="AE529" t="n">
+        <v>0.515228947368421</v>
+      </c>
       <c r="AF529" t="n">
         <v>0.493104347826087</v>
       </c>
@@ -37115,6 +38045,9 @@
       <c r="AC530" t="n">
         <v>0.3995566037735849</v>
       </c>
+      <c r="AE530" t="n">
+        <v>0.633141935483871</v>
+      </c>
       <c r="AF530" t="n">
         <v>0.5617090909090909</v>
       </c>
@@ -37147,6 +38080,9 @@
       <c r="AC531" t="n">
         <v>0.4958045454545454</v>
       </c>
+      <c r="AE531" t="n">
+        <v>0.5638625</v>
+      </c>
       <c r="AF531" t="n">
         <v>0.5871416666666667</v>
       </c>
@@ -37179,6 +38115,9 @@
       <c r="AC532" t="n">
         <v>0.4621510638297872</v>
       </c>
+      <c r="AE532" t="n">
+        <v>0.5691249999999999</v>
+      </c>
       <c r="AF532" t="n">
         <v>0.7263055555555555</v>
       </c>
@@ -37211,6 +38150,9 @@
       <c r="AC533" t="n">
         <v>0.4349719999999999</v>
       </c>
+      <c r="AE533" t="n">
+        <v>0.5765804878048779</v>
+      </c>
       <c r="AF533" t="n">
         <v>0.6344974999999999</v>
       </c>
@@ -37243,6 +38185,9 @@
       <c r="AC534" t="n">
         <v>0.3115254545454545</v>
       </c>
+      <c r="AE534" t="n">
+        <v>0.6972346153846154</v>
+      </c>
       <c r="AF534" t="n">
         <v>0.7973315789473684</v>
       </c>
@@ -37275,6 +38220,9 @@
       <c r="AC535" t="n">
         <v>0.5511894736842106</v>
       </c>
+      <c r="AE535" t="n">
+        <v>0.7347864864864865</v>
+      </c>
       <c r="AF535" t="n">
         <v>0.7573774193548386</v>
       </c>
@@ -37307,6 +38255,9 @@
       <c r="AC536" t="n">
         <v>0.4592083333333334</v>
       </c>
+      <c r="AE536" t="n">
+        <v>0.6253411764705883</v>
+      </c>
       <c r="AF536" t="n">
         <v>0.7032583333333333</v>
       </c>
@@ -37339,6 +38290,9 @@
       <c r="AC537" t="n">
         <v>0.5164607843137256</v>
       </c>
+      <c r="AE537" t="n">
+        <v>0.6301266666666667</v>
+      </c>
       <c r="AF537" t="n">
         <v>0.69116</v>
       </c>
@@ -37371,6 +38325,9 @@
       <c r="AC538" t="n">
         <v>0.5510245283018868</v>
       </c>
+      <c r="AE538" t="n">
+        <v>0.7928615384615385</v>
+      </c>
       <c r="AF538" t="n">
         <v>0.7289473684210527</v>
       </c>
@@ -37403,6 +38360,9 @@
       <c r="AC539" t="n">
         <v>0.3734129032258064</v>
       </c>
+      <c r="AE539" t="n">
+        <v>0.7814558139534883</v>
+      </c>
       <c r="AF539" t="n">
         <v>0.8590499999999999</v>
       </c>
@@ -37435,6 +38395,9 @@
       <c r="AC540" t="n">
         <v>0.4671789473684211</v>
       </c>
+      <c r="AE540" t="n">
+        <v>0.6841424999999999</v>
+      </c>
       <c r="AF540" t="n">
         <v>0.71055</v>
       </c>
@@ -37467,6 +38430,9 @@
       <c r="AC541" t="n">
         <v>0.4401520000000001</v>
       </c>
+      <c r="AE541" t="n">
+        <v>0.6000631578947369</v>
+      </c>
       <c r="AF541" t="n">
         <v>0.7131897435897435</v>
       </c>
@@ -37499,6 +38465,9 @@
       <c r="AC542" t="n">
         <v>0.482588524590164</v>
       </c>
+      <c r="AE542" t="n">
+        <v>0.7363255319148937</v>
+      </c>
       <c r="AF542" t="n">
         <v>0.737990909090909</v>
       </c>
@@ -37531,6 +38500,9 @@
       <c r="AC543" t="n">
         <v>0.5452616666666666</v>
       </c>
+      <c r="AE543" t="n">
+        <v>0.7519740740740741</v>
+      </c>
       <c r="AF543" t="n">
         <v>0.6332833333333333</v>
       </c>
@@ -37563,6 +38535,9 @@
       <c r="AC544" t="n">
         <v>0.4851044444444444</v>
       </c>
+      <c r="AE544" t="n">
+        <v>0.68443</v>
+      </c>
       <c r="AF544" t="n">
         <v>0.7209125</v>
       </c>
@@ -37595,6 +38570,9 @@
       <c r="AC545" t="n">
         <v>0.5073206896551724</v>
       </c>
+      <c r="AE545" t="n">
+        <v>0.7553343749999999</v>
+      </c>
       <c r="AF545" t="n">
         <v>0.7447952380952381</v>
       </c>
@@ -37627,6 +38605,9 @@
       <c r="AC546" t="n">
         <v>0.5798599999999999</v>
       </c>
+      <c r="AE546" t="n">
+        <v>0.746855</v>
+      </c>
       <c r="AF546" t="n">
         <v>0.6713432432432432</v>
       </c>
@@ -37659,6 +38640,9 @@
       <c r="AC547" t="n">
         <v>0.4528525423728814</v>
       </c>
+      <c r="AE547" t="n">
+        <v>0.6878399999999999</v>
+      </c>
       <c r="AF547" t="n">
         <v>0.61053125</v>
       </c>
@@ -37691,6 +38675,9 @@
       <c r="AC548" t="n">
         <v>0.4840848484848485</v>
       </c>
+      <c r="AE548" t="n">
+        <v>0.703125</v>
+      </c>
       <c r="AF548" t="n">
         <v>0.6718214285714286</v>
       </c>
@@ -37723,6 +38710,9 @@
       <c r="AC549" t="n">
         <v>0.602350909090909</v>
       </c>
+      <c r="AE549" t="n">
+        <v>0.6480318181818182</v>
+      </c>
       <c r="AF549" t="n">
         <v>0.814084</v>
       </c>
@@ -37755,6 +38745,9 @@
       <c r="AC550" t="n">
         <v>0.46843125</v>
       </c>
+      <c r="AE550" t="n">
+        <v>0.7345029411764705</v>
+      </c>
       <c r="AF550" t="n">
         <v>0.5715625</v>
       </c>
@@ -37787,6 +38780,9 @@
       <c r="AC551" t="n">
         <v>0.4655830188679245</v>
       </c>
+      <c r="AE551" t="n">
+        <v>0.7372044444444444</v>
+      </c>
       <c r="AF551" t="n">
         <v>0.736153846153846</v>
       </c>
@@ -37819,6 +38815,9 @@
       <c r="AC552" t="n">
         <v>0.3781510204081632</v>
       </c>
+      <c r="AE552" t="n">
+        <v>0.8470444444444445</v>
+      </c>
       <c r="AF552" t="n">
         <v>0.85438</v>
       </c>
@@ -37851,6 +38850,9 @@
       <c r="AC553" t="n">
         <v>0.4317800000000001</v>
       </c>
+      <c r="AE553" t="n">
+        <v>0.7875636363636364</v>
+      </c>
       <c r="AF553" t="n">
         <v>0.6457472222222221</v>
       </c>
@@ -37883,6 +38885,9 @@
       <c r="AC554" t="n">
         <v>0.5104254545454546</v>
       </c>
+      <c r="AE554" t="n">
+        <v>0.7744452380952382</v>
+      </c>
       <c r="AF554" t="n">
         <v>0.7196106382978723</v>
       </c>
@@ -37915,6 +38920,9 @@
       <c r="AC555" t="n">
         <v>0.5542551020408163</v>
       </c>
+      <c r="AE555" t="n">
+        <v>0.8044606060606062</v>
+      </c>
       <c r="AF555" t="n">
         <v>0.7562777777777777</v>
       </c>
@@ -37947,6 +38955,9 @@
       <c r="AC556" t="n">
         <v>0.5214836065573771</v>
       </c>
+      <c r="AE556" t="n">
+        <v>0.7770958333333334</v>
+      </c>
       <c r="AF556" t="n">
         <v>0.7659095238095238</v>
       </c>
@@ -37979,6 +38990,9 @@
       <c r="AC557" t="n">
         <v>0.386245283018868</v>
       </c>
+      <c r="AE557" t="n">
+        <v>0.7485594594594595</v>
+      </c>
       <c r="AF557" t="n">
         <v>0.844675</v>
       </c>
@@ -38011,6 +39025,9 @@
       <c r="AC558" t="n">
         <v>0.4671999999999999</v>
       </c>
+      <c r="AE558" t="n">
+        <v>0.6971044444444445</v>
+      </c>
       <c r="AF558" t="n">
         <v>0.8064136363636364</v>
       </c>
@@ -38043,6 +39060,9 @@
       <c r="AC559" t="n">
         <v>0.5137327586206897</v>
       </c>
+      <c r="AE559" t="n">
+        <v>0.684585</v>
+      </c>
       <c r="AF559" t="n">
         <v>0.6768302325581396</v>
       </c>
@@ -38075,6 +39095,9 @@
       <c r="AC560" t="n">
         <v>0.5099728813559321</v>
       </c>
+      <c r="AE560" t="n">
+        <v>0.7710264705882351</v>
+      </c>
       <c r="AF560" t="n">
         <v>0.6789857142857143</v>
       </c>
@@ -38107,6 +39130,9 @@
       <c r="AC561" t="n">
         <v>0.4863826923076923</v>
       </c>
+      <c r="AE561" t="n">
+        <v>0.7394885714285715</v>
+      </c>
       <c r="AF561" t="n">
         <v>0.7579411764705883</v>
       </c>
@@ -38139,6 +39165,9 @@
       <c r="AC562" t="n">
         <v>0.453912962962963</v>
       </c>
+      <c r="AE562" t="n">
+        <v>0.7903105263157894</v>
+      </c>
       <c r="AF562" t="n">
         <v>0.7340083333333333</v>
       </c>
@@ -38171,6 +39200,9 @@
       <c r="AC563" t="n">
         <v>0.4765818181818182</v>
       </c>
+      <c r="AE563" t="n">
+        <v>0.7869628571428571</v>
+      </c>
       <c r="AF563" t="n">
         <v>0.7832630434782609</v>
       </c>
@@ -38203,6 +39235,9 @@
       <c r="AC564" t="n">
         <v>0.4980166666666667</v>
       </c>
+      <c r="AE564" t="n">
+        <v>0.6856972222222222</v>
+      </c>
       <c r="AF564" t="n">
         <v>0.6610627450980392</v>
       </c>
@@ -38235,6 +39270,9 @@
       <c r="AC565" t="n">
         <v>0.5015952380952382</v>
       </c>
+      <c r="AE565" t="n">
+        <v>0.6693722222222223</v>
+      </c>
       <c r="AF565" t="n">
         <v>0.8073222222222223</v>
       </c>
@@ -38267,6 +39305,9 @@
       <c r="AC566" t="n">
         <v>0.473925</v>
       </c>
+      <c r="AE566" t="n">
+        <v>0.7567666666666667</v>
+      </c>
       <c r="AF566" t="n">
         <v>0.770428</v>
       </c>
@@ -38299,6 +39340,9 @@
       <c r="AC567" t="n">
         <v>0.5536673076923078</v>
       </c>
+      <c r="AE567" t="n">
+        <v>0.7825666666666667</v>
+      </c>
       <c r="AF567" t="n">
         <v>0.8293692307692309</v>
       </c>
@@ -38331,6 +39375,9 @@
       <c r="AC568" t="n">
         <v>0.56925</v>
       </c>
+      <c r="AE568" t="n">
+        <v>0.7070041666666667</v>
+      </c>
       <c r="AF568" t="n">
         <v>0.7189634146341464</v>
       </c>
@@ -38363,6 +39410,9 @@
       <c r="AC569" t="n">
         <v>0.4714163265306122</v>
       </c>
+      <c r="AE569" t="n">
+        <v>0.7627861111111111</v>
+      </c>
       <c r="AF569" t="n">
         <v>0.8308378378378379</v>
       </c>
@@ -38395,6 +39445,9 @@
       <c r="AC570" t="n">
         <v>0.3889018518518519</v>
       </c>
+      <c r="AE570" t="n">
+        <v>0.8022387096774193</v>
+      </c>
       <c r="AF570" t="n">
         <v>0.7310076923076922</v>
       </c>
@@ -38427,6 +39480,9 @@
       <c r="AC571" t="n">
         <v>0.5314942028985506</v>
       </c>
+      <c r="AE571" t="n">
+        <v>0.7100853658536584</v>
+      </c>
       <c r="AF571" t="n">
         <v>0.7974440000000002</v>
       </c>
@@ -38459,6 +39515,9 @@
       <c r="AC572" t="n">
         <v>0.4576981818181818</v>
       </c>
+      <c r="AE572" t="n">
+        <v>0.7779638888888889</v>
+      </c>
       <c r="AF572" t="n">
         <v>0.8205107142857144</v>
       </c>
@@ -38491,6 +39550,9 @@
       <c r="AC573" t="n">
         <v>0.4552840000000001</v>
       </c>
+      <c r="AE573" t="n">
+        <v>0.7921697674418604</v>
+      </c>
       <c r="AF573" t="n">
         <v>0.7170222222222222</v>
       </c>
@@ -38523,6 +39585,9 @@
       <c r="AC574" t="n">
         <v>0.5154547169811321</v>
       </c>
+      <c r="AE574" t="n">
+        <v>0.7715212121212123</v>
+      </c>
       <c r="AF574" t="n">
         <v>0.7901172413793105</v>
       </c>
@@ -38555,6 +39620,9 @@
       <c r="AC575" t="n">
         <v>0.46138125</v>
       </c>
+      <c r="AE575" t="n">
+        <v>0.7590916666666666</v>
+      </c>
       <c r="AF575" t="n">
         <v>0.8535115384615385</v>
       </c>
@@ -38587,6 +39655,9 @@
       <c r="AC576" t="n">
         <v>0.5618811320754716</v>
       </c>
+      <c r="AE576" t="n">
+        <v>0.7393531249999999</v>
+      </c>
       <c r="AF576" t="n">
         <v>0.7951052631578946</v>
       </c>
@@ -38619,6 +39690,9 @@
       <c r="AC577" t="n">
         <v>0.4938596491228071</v>
       </c>
+      <c r="AE577" t="n">
+        <v>0.7178054054054054</v>
+      </c>
       <c r="AF577" t="n">
         <v>0.714855</v>
       </c>
@@ -38651,6 +39725,9 @@
       <c r="AC578" t="n">
         <v>0.5270279999999999</v>
       </c>
+      <c r="AE578" t="n">
+        <v>0.7656941176470587</v>
+      </c>
       <c r="AF578" t="n">
         <v>0.8714857142857143</v>
       </c>
@@ -38683,6 +39760,9 @@
       <c r="AC579" t="n">
         <v>0.4145636363636363</v>
       </c>
+      <c r="AE579" t="n">
+        <v>0.7927666666666666</v>
+      </c>
       <c r="AF579" t="n">
         <v>0.8457357142857143</v>
       </c>
@@ -38715,6 +39795,9 @@
       <c r="AC580" t="n">
         <v>0.4867090909090909</v>
       </c>
+      <c r="AE580" t="n">
+        <v>0.647942857142857</v>
+      </c>
       <c r="AF580" t="n">
         <v>0.9195</v>
       </c>
@@ -38747,6 +39830,9 @@
       <c r="AC581" t="n">
         <v>0.4416783333333333</v>
       </c>
+      <c r="AE581" t="n">
+        <v>0.7226864864864865</v>
+      </c>
       <c r="AF581" t="n">
         <v>0.734874074074074</v>
       </c>
@@ -38779,6 +39865,9 @@
       <c r="AC582" t="n">
         <v>0.4763433333333334</v>
       </c>
+      <c r="AE582" t="n">
+        <v>0.6328379310344827</v>
+      </c>
       <c r="AF582" t="n">
         <v>0.8707457142857143</v>
       </c>
@@ -38811,6 +39900,9 @@
       <c r="AC583" t="n">
         <v>0.5356261904761905</v>
       </c>
+      <c r="AE583" t="n">
+        <v>0.8009969696969697</v>
+      </c>
       <c r="AF583" t="n">
         <v>0.7515081081081081</v>
       </c>
@@ -38843,6 +39935,9 @@
       <c r="AC584" t="n">
         <v>0.4988000000000001</v>
       </c>
+      <c r="AE584" t="n">
+        <v>0.845920588235294</v>
+      </c>
       <c r="AF584" t="n">
         <v>0.8834705882352941</v>
       </c>
@@ -38875,6 +39970,9 @@
       <c r="AC585" t="n">
         <v>0.4746367647058825</v>
       </c>
+      <c r="AE585" t="n">
+        <v>0.6767216216216216</v>
+      </c>
       <c r="AF585" t="n">
         <v>0.8111781250000001</v>
       </c>
@@ -38907,6 +40005,9 @@
       <c r="AC586" t="n">
         <v>0.5125636363636364</v>
       </c>
+      <c r="AE586" t="n">
+        <v>0.8328636363636364</v>
+      </c>
       <c r="AF586" t="n">
         <v>0.8330000000000001</v>
       </c>
@@ -38939,6 +40040,9 @@
       <c r="AC587" t="n">
         <v>0.4961435483870968</v>
       </c>
+      <c r="AE587" t="n">
+        <v>0.7467864864864865</v>
+      </c>
       <c r="AF587" t="n">
         <v>0.6783750000000001</v>
       </c>
@@ -38971,6 +40075,9 @@
       <c r="AC588" t="n">
         <v>0.5781661016949152</v>
       </c>
+      <c r="AE588" t="n">
+        <v>0.7588148148148148</v>
+      </c>
       <c r="AF588" t="n">
         <v>0.893804347826087</v>
       </c>
@@ -39003,6 +40110,9 @@
       <c r="AC589" t="n">
         <v>0.4489958333333333</v>
       </c>
+      <c r="AE589" t="n">
+        <v>0.6893111111111112</v>
+      </c>
       <c r="AF589" t="n">
         <v>0.968</v>
       </c>
@@ -39035,6 +40145,9 @@
       <c r="AC590" t="n">
         <v>0.484944</v>
       </c>
+      <c r="AE590" t="n">
+        <v>0.7934965517241379</v>
+      </c>
       <c r="AF590" t="n">
         <v>0.86465</v>
       </c>
@@ -39067,6 +40180,9 @@
       <c r="AC591" t="n">
         <v>0.4910307692307692</v>
       </c>
+      <c r="AE591" t="n">
+        <v>0.6970499999999999</v>
+      </c>
       <c r="AF591" t="n">
         <v>0.77676</v>
       </c>
@@ -39099,6 +40215,9 @@
       <c r="AC592" t="n">
         <v>0.5456555555555556</v>
       </c>
+      <c r="AE592" t="n">
+        <v>0.7083263157894738</v>
+      </c>
       <c r="AF592" t="n">
         <v>0.7865782608695653</v>
       </c>
@@ -39131,6 +40250,9 @@
       <c r="AC593" t="n">
         <v>0.460562</v>
       </c>
+      <c r="AE593" t="n">
+        <v>0.6933194444444444</v>
+      </c>
       <c r="AF593" t="n">
         <v>0.7292272727272727</v>
       </c>
@@ -39163,6 +40285,9 @@
       <c r="AC594" t="n">
         <v>0.494990909090909</v>
       </c>
+      <c r="AE594" t="n">
+        <v>0.64825</v>
+      </c>
       <c r="AF594" t="n">
         <v>0.7837212121212122</v>
       </c>
@@ -39195,6 +40320,9 @@
       <c r="AC595" t="n">
         <v>0.4614648148148149</v>
       </c>
+      <c r="AE595" t="n">
+        <v>0.7274636363636364</v>
+      </c>
       <c r="AF595" t="n">
         <v>0.8800653846153847</v>
       </c>
@@ -39227,6 +40355,9 @@
       <c r="AC596" t="n">
         <v>0.4555960784313727</v>
       </c>
+      <c r="AE596" t="n">
+        <v>0.7105781249999999</v>
+      </c>
       <c r="AF596" t="n">
         <v>0.7243535714285715</v>
       </c>
@@ -39259,6 +40390,9 @@
       <c r="AC597" t="n">
         <v>0.499428</v>
       </c>
+      <c r="AE597" t="n">
+        <v>0.6553857142857142</v>
+      </c>
       <c r="AF597" t="n">
         <v>0.6785035714285714</v>
       </c>
@@ -39291,6 +40425,9 @@
       <c r="AC598" t="n">
         <v>0.5547301587301587</v>
       </c>
+      <c r="AE598" t="n">
+        <v>0.780425</v>
+      </c>
       <c r="AF598" t="n">
         <v>0.9159333333333334</v>
       </c>
@@ -39323,6 +40460,9 @@
       <c r="AC599" t="n">
         <v>0.555325</v>
       </c>
+      <c r="AE599" t="n">
+        <v>0.8202</v>
+      </c>
       <c r="AF599" t="n">
         <v>0.8608500000000001</v>
       </c>
@@ -39355,6 +40495,9 @@
       <c r="AC600" t="n">
         <v>0.5739622950819672</v>
       </c>
+      <c r="AE600" t="n">
+        <v>0.7503111111111109</v>
+      </c>
       <c r="AF600" t="n">
         <v>0.7267305555555557</v>
       </c>
@@ -39387,6 +40530,9 @@
       <c r="AC601" t="n">
         <v>0.4337241379310345</v>
       </c>
+      <c r="AE601" t="n">
+        <v>0.8163709677419355</v>
+      </c>
       <c r="AF601" t="n">
         <v>0.9213650000000001</v>
       </c>
@@ -39419,6 +40565,9 @@
       <c r="AC602" t="n">
         <v>0.4740122807017544</v>
       </c>
+      <c r="AE602" t="n">
+        <v>0.7530135135135136</v>
+      </c>
       <c r="AF602" t="n">
         <v>0.8507416666666666</v>
       </c>
@@ -39451,6 +40600,9 @@
       <c r="AC603" t="n">
         <v>0.4773112903225806</v>
       </c>
+      <c r="AE603" t="n">
+        <v>0.7216</v>
+      </c>
       <c r="AF603" t="n">
         <v>0.7035791666666666</v>
       </c>
@@ -39483,6 +40635,9 @@
       <c r="AC604" t="n">
         <v>0.4504599999999999</v>
       </c>
+      <c r="AE604" t="n">
+        <v>0.6770939393939396</v>
+      </c>
       <c r="AF604" t="n">
         <v>0.6684433333333334</v>
       </c>
@@ -39515,6 +40670,9 @@
       <c r="AC605" t="n">
         <v>0.4857470588235293</v>
       </c>
+      <c r="AE605" t="n">
+        <v>0.7611307692307693</v>
+      </c>
       <c r="AF605" t="n">
         <v>0.6809564102564102</v>
       </c>
@@ -39547,6 +40705,9 @@
       <c r="AC606" t="n">
         <v>0.5282092592592592</v>
       </c>
+      <c r="AE606" t="n">
+        <v>0.7701256410256411</v>
+      </c>
       <c r="AF606" t="n">
         <v>0.89698125</v>
       </c>
@@ -39579,6 +40740,9 @@
       <c r="AC607" t="n">
         <v>0.4499311475409836</v>
       </c>
+      <c r="AE607" t="n">
+        <v>0.6821361111111111</v>
+      </c>
       <c r="AF607" t="n">
         <v>0.7692310344827586</v>
       </c>
@@ -39611,6 +40775,9 @@
       <c r="AC608" t="n">
         <v>0.5719953125</v>
       </c>
+      <c r="AE608" t="n">
+        <v>0.693939024390244</v>
+      </c>
       <c r="AF608" t="n">
         <v>0.826870588235294</v>
       </c>
@@ -39643,6 +40810,9 @@
       <c r="AC609" t="n">
         <v>0.5563676470588235</v>
       </c>
+      <c r="AE609" t="n">
+        <v>0.7293433333333332</v>
+      </c>
       <c r="AF609" t="n">
         <v>0.6976925</v>
       </c>
@@ -39675,6 +40845,9 @@
       <c r="AC610" t="n">
         <v>0.5162607142857143</v>
       </c>
+      <c r="AE610" t="n">
+        <v>0.7142740740740742</v>
+      </c>
       <c r="AF610" t="n">
         <v>0.8650954545454546</v>
       </c>
@@ -39707,6 +40880,9 @@
       <c r="AC611" t="n">
         <v>0.4721854545454546</v>
       </c>
+      <c r="AE611" t="n">
+        <v>0.7648051282051282</v>
+      </c>
       <c r="AF611" t="n">
         <v>0.6639594594594594</v>
       </c>
@@ -39739,6 +40915,9 @@
       <c r="AC612" t="n">
         <v>0.5489823529411766</v>
       </c>
+      <c r="AE612" t="n">
+        <v>0.7327692307692308</v>
+      </c>
       <c r="AF612" t="n">
         <v>0.8358833333333333</v>
       </c>
@@ -39771,6 +40950,9 @@
       <c r="AC613" t="n">
         <v>0.5557716666666667</v>
       </c>
+      <c r="AE613" t="n">
+        <v>0.727274</v>
+      </c>
       <c r="AF613" t="n">
         <v>0.7622173913043477</v>
       </c>
@@ -39803,6 +40985,9 @@
       <c r="AC614" t="n">
         <v>0.5175136363636365</v>
       </c>
+      <c r="AE614" t="n">
+        <v>0.8466314285714285</v>
+      </c>
       <c r="AF614" t="n">
         <v>0.8382153846153847</v>
       </c>
@@ -39835,6 +41020,9 @@
       <c r="AC615" t="n">
         <v>0.5153795918367347</v>
       </c>
+      <c r="AE615" t="n">
+        <v>0.728475</v>
+      </c>
       <c r="AF615" t="n">
         <v>0.8087074074074073</v>
       </c>
@@ -39867,6 +41055,9 @@
       <c r="AC616" t="n">
         <v>0.5326830769230769</v>
       </c>
+      <c r="AE616" t="n">
+        <v>0.7491272727272728</v>
+      </c>
       <c r="AF616" t="n">
         <v>0.8023727272727272</v>
       </c>
@@ -39899,6 +41090,9 @@
       <c r="AC617" t="n">
         <v>0.5707408163265306</v>
       </c>
+      <c r="AE617" t="n">
+        <v>0.7956783783783784</v>
+      </c>
       <c r="AF617" t="n">
         <v>0.652753488372093</v>
       </c>
@@ -39931,6 +41125,9 @@
       <c r="AC618" t="n">
         <v>0.456211475409836</v>
       </c>
+      <c r="AE618" t="n">
+        <v>0.741693023255814</v>
+      </c>
       <c r="AF618" t="n">
         <v>0.7811695652173912</v>
       </c>
@@ -39962,6 +41159,9 @@
       </c>
       <c r="AC619" t="n">
         <v>0.5503807692307692</v>
+      </c>
+      <c r="AE619" t="n">
+        <v>0.756125</v>
       </c>
       <c r="AF619" t="n">
         <v>0.8658374999999999</v>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -767,7 +767,7 @@
         <v>0.1409777777777778</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.136831506849315</v>
+        <v>0.09271029411764704</v>
       </c>
       <c r="AG5" t="n">
         <v>0.1444220588235294</v>
@@ -856,7 +856,7 @@
         <v>0.3522714285714286</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2158</v>
+        <v>0.2696666666666666</v>
       </c>
       <c r="AG6" t="n">
         <v>0.2546185185185185</v>
@@ -945,7 +945,7 @@
         <v>0.5093</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.3096071428571429</v>
+        <v>0.3234045454545454</v>
       </c>
       <c r="AG7" t="n">
         <v>0.29529375</v>
@@ -1034,7 +1034,7 @@
         <v>0.3586</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.3051263157894737</v>
+        <v>0.3275733333333333</v>
       </c>
       <c r="AG8" t="n">
         <v>0.3587086956521739</v>
@@ -1123,7 +1123,7 @@
         <v>0.4496538461538462</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2868</v>
+        <v>0.3607093749999999</v>
       </c>
       <c r="AG9" t="n">
         <v>0.4033733333333333</v>
@@ -1212,7 +1212,7 @@
         <v>0.5565863636363636</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.377646</v>
+        <v>0.4313071428571428</v>
       </c>
       <c r="AG10" t="n">
         <v>0.5431333333333334</v>
@@ -1301,7 +1301,7 @@
         <v>0.51294</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.302692</v>
+        <v>0.487297619047619</v>
       </c>
       <c r="AG11" t="n">
         <v>0.6328703703703703</v>
@@ -1390,7 +1390,7 @@
         <v>0.53101875</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.4420933333333333</v>
+        <v>0.5838794117647059</v>
       </c>
       <c r="AG12" t="n">
         <v>0.6659105263157894</v>
@@ -1479,7 +1479,7 @@
         <v>0.5811628571428571</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.4891961538461538</v>
+        <v>0.6596563636363636</v>
       </c>
       <c r="AG13" t="n">
         <v>0.7138029411764706</v>
@@ -1568,7 +1568,7 @@
         <v>0.5271250000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.4875537037037037</v>
+        <v>0.7104857142857144</v>
       </c>
       <c r="AG14" t="n">
         <v>0.7791452380952381</v>
@@ -1648,7 +1648,7 @@
         <v>0.6544416666666667</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.566505</v>
+        <v>0.7031207547169811</v>
       </c>
       <c r="AG15" t="n">
         <v>0.6907088235294117</v>
@@ -1728,7 +1728,7 @@
         <v>0.6866103448275862</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.591214705882353</v>
+        <v>0.6595676470588235</v>
       </c>
       <c r="AG16" t="n">
         <v>0.8044242424242424</v>
@@ -1808,7 +1808,7 @@
         <v>0.6823375</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.5701978260869565</v>
+        <v>0.6847825</v>
       </c>
       <c r="AG17" t="n">
         <v>0.8216470588235293</v>
@@ -1888,7 +1888,7 @@
         <v>0.7576166666666667</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.5278999999999999</v>
+        <v>0.7248882352941176</v>
       </c>
       <c r="AG18" t="n">
         <v>0.8476916666666665</v>
@@ -1968,7 +1968,7 @@
         <v>0.8117439024390244</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.6256555555555555</v>
+        <v>0.7301058823529413</v>
       </c>
       <c r="AG19" t="n">
         <v>0.8462595238095239</v>
@@ -2048,7 +2048,7 @@
         <v>0.81415</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.6736951219512195</v>
+        <v>0.73783125</v>
       </c>
       <c r="AG20" t="n">
         <v>0.8139575757575758</v>
@@ -2128,7 +2128,7 @@
         <v>0.8060244444444444</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.63368</v>
+        <v>0.7063699999999999</v>
       </c>
       <c r="AG21" t="n">
         <v>0.8129480000000001</v>
@@ -2208,7 +2208,7 @@
         <v>0.7891365853658536</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.6541619047619047</v>
+        <v>0.8212292682926829</v>
       </c>
       <c r="AG22" t="n">
         <v>0.8506088235294118</v>
@@ -2288,7 +2288,7 @@
         <v>0.8158588235294119</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.6224535714285715</v>
+        <v>0.7242377358490566</v>
       </c>
       <c r="AG23" t="n">
         <v>0.7732114285714287</v>
@@ -2368,7 +2368,7 @@
         <v>0.8398</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.6992648148148147</v>
+        <v>0.7113058823529412</v>
       </c>
       <c r="AG24" t="n">
         <v>0.8626111111111112</v>
@@ -2448,7 +2448,7 @@
         <v>0.753792857142857</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.7716395833333332</v>
+        <v>0.8543472727272727</v>
       </c>
       <c r="AG25" t="n">
         <v>0.8401619047619048</v>
@@ -2528,7 +2528,7 @@
         <v>0.8495972972972973</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.7516045454545455</v>
+        <v>0.7485685714285714</v>
       </c>
       <c r="AG26" t="n">
         <v>0.8851699999999999</v>
@@ -2608,7 +2608,7 @@
         <v>0.7380607142857144</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.683575</v>
+        <v>0.804380357142857</v>
       </c>
       <c r="AG27" t="n">
         <v>0.8068071428571428</v>
@@ -2688,7 +2688,7 @@
         <v>0.6748875</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.718662857142857</v>
+        <v>0.7560588235294118</v>
       </c>
       <c r="AG28" t="n">
         <v>0.8382950000000001</v>
@@ -2768,7 +2768,7 @@
         <v>0.8732882352941177</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.7586853658536586</v>
+        <v>0.8004333333333333</v>
       </c>
       <c r="AG29" t="n">
         <v>0.8456666666666667</v>
@@ -2848,7 +2848,7 @@
         <v>0.8862347826086957</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.6799933333333333</v>
+        <v>0.7867521739130434</v>
       </c>
       <c r="AG30" t="n">
         <v>0.8683558139534883</v>
@@ -2928,7 +2928,7 @@
         <v>0.8431386363636364</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.7398852941176471</v>
+        <v>0.8218590909090909</v>
       </c>
       <c r="AG31" t="n">
         <v>0.9041483870967743</v>
@@ -3008,7 +3008,7 @@
         <v>0.794264705882353</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.7788333333333333</v>
+        <v>0.8259243902439025</v>
       </c>
       <c r="AG32" t="n">
         <v>0.8286275</v>
@@ -3088,7 +3088,7 @@
         <v>0.7555484848484848</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.7856291666666667</v>
+        <v>0.8179303571428571</v>
       </c>
       <c r="AG33" t="n">
         <v>0.8586911111111112</v>
@@ -3168,7 +3168,7 @@
         <v>0.7863555555555556</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.7527744680851063</v>
+        <v>0.7847714285714286</v>
       </c>
       <c r="AG34" t="n">
         <v>0.8450769230769232</v>
@@ -3248,7 +3248,7 @@
         <v>0.8238179487179488</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.7412694915254238</v>
+        <v>0.7859263157894737</v>
       </c>
       <c r="AG35" t="n">
         <v>0.7788975609756098</v>
@@ -3328,7 +3328,7 @@
         <v>0.8529190476190477</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.7180857142857143</v>
+        <v>0.8429277777777777</v>
       </c>
       <c r="AG36" t="n">
         <v>0.8721238095238096</v>
@@ -3408,7 +3408,7 @@
         <v>0.8277053571428572</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.8055095238095239</v>
+        <v>0.7741977272727273</v>
       </c>
       <c r="AG37" t="n">
         <v>0.7873033333333334</v>
@@ -3488,7 +3488,7 @@
         <v>0.83523125</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.7484777777777778</v>
+        <v>0.8083276595744681</v>
       </c>
       <c r="AG38" t="n">
         <v>0.8196461538461539</v>
@@ -3568,7 +3568,7 @@
         <v>0.825775</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.6965051282051282</v>
+        <v>0.8482428571428572</v>
       </c>
       <c r="AG39" t="n">
         <v>0.9542833333333335</v>
@@ -3648,7 +3648,7 @@
         <v>0.8958480769230769</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.8004536585365855</v>
+        <v>0.8558754716981132</v>
       </c>
       <c r="AG40" t="n">
         <v>0.8326086956521739</v>
@@ -3728,7 +3728,7 @@
         <v>0.8732238095238096</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.7578836363636364</v>
+        <v>0.7814762711864407</v>
       </c>
       <c r="AG41" t="n">
         <v>0.766475</v>
@@ -3808,7 +3808,7 @@
         <v>0.8454826086956523</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.7189878048780488</v>
+        <v>0.807506779661017</v>
       </c>
       <c r="AG42" t="n">
         <v>0.8674059999999999</v>
@@ -3888,7 +3888,7 @@
         <v>0.8591695652173913</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.76215</v>
+        <v>0.8860260869565216</v>
       </c>
       <c r="AG43" t="n">
         <v>0.8555219512195121</v>
@@ -3968,7 +3968,7 @@
         <v>0.8114032258064515</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.850783870967742</v>
+        <v>0.8648345454545454</v>
       </c>
       <c r="AG44" t="n">
         <v>0.8947911764705883</v>
@@ -4048,7 +4048,7 @@
         <v>0.7922142857142855</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.8372724999999999</v>
+        <v>0.8649384615384617</v>
       </c>
       <c r="AG45" t="n">
         <v>0.8364026315789473</v>
@@ -4128,7 +4128,7 @@
         <v>0.8316641025641025</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.7954235294117646</v>
+        <v>0.8310675</v>
       </c>
       <c r="AG46" t="n">
         <v>0.7907058823529411</v>
@@ -4208,7 +4208,7 @@
         <v>0.8429891304347825</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.8122710526315789</v>
+        <v>0.8390658536585366</v>
       </c>
       <c r="AG47" t="n">
         <v>0.8581365853658536</v>
@@ -4288,7 +4288,7 @@
         <v>0.8140172413793105</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.7768560975609756</v>
+        <v>0.8474888888888888</v>
       </c>
       <c r="AG48" t="n">
         <v>0.9355870967741936</v>
@@ -4368,7 +4368,7 @@
         <v>0.8464034482758621</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.7985172413793102</v>
+        <v>0.8707617021276595</v>
       </c>
       <c r="AG49" t="n">
         <v>0.8349897435897435</v>
@@ -4448,7 +4448,7 @@
         <v>0.8807258064516128</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.8212977777777777</v>
+        <v>0.768836170212766</v>
       </c>
       <c r="AG50" t="n">
         <v>0.8626372093023255</v>
@@ -4528,7 +4528,7 @@
         <v>0.854168888888889</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.7167826086956522</v>
+        <v>0.868490243902439</v>
       </c>
       <c r="AG51" t="n">
         <v>0.8403444444444443</v>
@@ -4608,7 +4608,7 @@
         <v>0.8235655172413793</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.8063586206896551</v>
+        <v>0.8349275862068964</v>
       </c>
       <c r="AG52" t="n">
         <v>0.87743</v>
@@ -4688,7 +4688,7 @@
         <v>0.7917772727272727</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.7686414634146342</v>
+        <v>0.7989062499999999</v>
       </c>
       <c r="AG53" t="n">
         <v>0.8419816326530611</v>
@@ -4768,7 +4768,7 @@
         <v>0.856812121212121</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.796109375</v>
+        <v>0.8769803921568627</v>
       </c>
       <c r="AG54" t="n">
         <v>0.8447468085106383</v>
@@ -4848,7 +4848,7 @@
         <v>0.8391934782608695</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.7950844444444444</v>
+        <v>0.8575259999999999</v>
       </c>
       <c r="AG55" t="n">
         <v>0.7363166666666667</v>
@@ -4928,7 +4928,7 @@
         <v>0.8554736842105262</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.6993140000000001</v>
+        <v>0.9139829268292683</v>
       </c>
       <c r="AG56" t="n">
         <v>0.8710487179487182</v>
@@ -5008,7 +5008,7 @@
         <v>0.8399542857142855</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.7823157894736843</v>
+        <v>0.8319384615384615</v>
       </c>
       <c r="AG57" t="n">
         <v>0.91634</v>
@@ -5088,7 +5088,7 @@
         <v>0.7949428571428573</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.7641380952380953</v>
+        <v>0.8494340909090909</v>
       </c>
       <c r="AG58" t="n">
         <v>0.9305969696969696</v>
@@ -5168,7 +5168,7 @@
         <v>0.72724</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.7457299999999999</v>
+        <v>0.8219897959183674</v>
       </c>
       <c r="AG59" t="n">
         <v>0.8735666666666667</v>
@@ -5248,7 +5248,7 @@
         <v>0.779916129032258</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.8350705882352942</v>
+        <v>0.8800416666666666</v>
       </c>
       <c r="AG60" t="n">
         <v>0.8537196078431372</v>
@@ -5328,7 +5328,7 @@
         <v>0.8505499999999999</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.7649038461538461</v>
+        <v>0.8302984126984125</v>
       </c>
       <c r="AG61" t="n">
         <v>0.92111875</v>
@@ -5408,7 +5408,7 @@
         <v>0.8555488372093024</v>
       </c>
       <c r="AF62" t="n">
-        <v>0.7346511111111111</v>
+        <v>0.8567306122448982</v>
       </c>
       <c r="AG62" t="n">
         <v>0.9207299999999999</v>
@@ -5488,7 +5488,7 @@
         <v>0.8196916666666666</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.7309825</v>
+        <v>0.7998423076923077</v>
       </c>
       <c r="AG63" t="n">
         <v>0.9001749999999999</v>
@@ -5568,7 +5568,7 @@
         <v>0.7428659090909092</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.737761224489796</v>
+        <v>0.8156943396226415</v>
       </c>
       <c r="AG64" t="n">
         <v>0.865484</v>
@@ -5648,7 +5648,7 @@
         <v>0.8547159090909091</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.7681734375</v>
+        <v>0.8355666666666667</v>
       </c>
       <c r="AG65" t="n">
         <v>0.942934210526316</v>
@@ -5728,7 +5728,7 @@
         <v>0.86485</v>
       </c>
       <c r="AF66" t="n">
-        <v>0.7673023255813953</v>
+        <v>0.8460551724137931</v>
       </c>
       <c r="AG66" t="n">
         <v>0.8442041666666666</v>
@@ -5808,7 +5808,7 @@
         <v>0.817658695652174</v>
       </c>
       <c r="AF67" t="n">
-        <v>0.7821708333333334</v>
+        <v>0.8510309090909092</v>
       </c>
       <c r="AG67" t="n">
         <v>0.845618918918919</v>
@@ -5888,7 +5888,7 @@
         <v>0.7966615384615385</v>
       </c>
       <c r="AF68" t="n">
-        <v>0.7613581818181819</v>
+        <v>0.8045399999999999</v>
       </c>
       <c r="AG68" t="n">
         <v>0.871286046511628</v>
@@ -5968,7 +5968,7 @@
         <v>0.8263347826086955</v>
       </c>
       <c r="AF69" t="n">
-        <v>0.8003170212765958</v>
+        <v>0.8885195652173914</v>
       </c>
       <c r="AG69" t="n">
         <v>0.734975</v>
@@ -6048,7 +6048,7 @@
         <v>0.68686</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.8219073170731708</v>
+        <v>0.8527767441860465</v>
       </c>
       <c r="AG70" t="n">
         <v>0.9112117647058824</v>
@@ -6128,7 +6128,7 @@
         <v>0.825217391304348</v>
       </c>
       <c r="AF71" t="n">
-        <v>0.7013918032786886</v>
+        <v>0.8649326530612246</v>
       </c>
       <c r="AG71" t="n">
         <v>0.8561836363636364</v>
@@ -6208,7 +6208,7 @@
         <v>0.8528735294117646</v>
       </c>
       <c r="AF72" t="n">
-        <v>0.8253333333333334</v>
+        <v>0.8976499999999999</v>
       </c>
       <c r="AG72" t="n">
         <v>0.8720466666666666</v>
@@ -6288,7 +6288,7 @@
         <v>0.8602120000000001</v>
       </c>
       <c r="AF73" t="n">
-        <v>0.830431914893617</v>
+        <v>0.836053488372093</v>
       </c>
       <c r="AG73" t="n">
         <v>0.9014681818181818</v>
@@ -6368,7 +6368,7 @@
         <v>0.7251117647058825</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.7466634615384616</v>
+        <v>0.8752292682926829</v>
       </c>
       <c r="AG74" t="n">
         <v>0.870672</v>
@@ -6448,7 +6448,7 @@
         <v>0.7983421052631579</v>
       </c>
       <c r="AF75" t="n">
-        <v>0.8182203389830509</v>
+        <v>0.8320129629629629</v>
       </c>
       <c r="AG75" t="n">
         <v>0.8901314285714287</v>
@@ -6528,7 +6528,7 @@
         <v>0.8929233333333334</v>
       </c>
       <c r="AF76" t="n">
-        <v>0.7858304347826086</v>
+        <v>0.7866306122448978</v>
       </c>
       <c r="AG76" t="n">
         <v>0.9011222222222223</v>
@@ -6608,7 +6608,7 @@
         <v>0.8933906976744186</v>
       </c>
       <c r="AF77" t="n">
-        <v>0.8292540540540541</v>
+        <v>0.8605268292682926</v>
       </c>
       <c r="AG77" t="n">
         <v>0.8690860465116279</v>
@@ -6688,7 +6688,7 @@
         <v>0.8172965517241381</v>
       </c>
       <c r="AF78" t="n">
-        <v>0.7616634615384617</v>
+        <v>0.8291517857142858</v>
       </c>
       <c r="AG78" t="n">
         <v>0.845924</v>
@@ -6768,7 +6768,7 @@
         <v>0.7938727272727273</v>
       </c>
       <c r="AF79" t="n">
-        <v>0.8140846153846154</v>
+        <v>0.8616301886792452</v>
       </c>
       <c r="AG79" t="n">
         <v>0.8899279069767442</v>
@@ -6848,7 +6848,7 @@
         <v>0.8341666666666667</v>
       </c>
       <c r="AF80" t="n">
-        <v>0.7771124999999999</v>
+        <v>0.8150500000000001</v>
       </c>
       <c r="AG80" t="n">
         <v>0.8731923076923078</v>
@@ -6928,7 +6928,7 @@
         <v>0.8427238095238097</v>
       </c>
       <c r="AF81" t="n">
-        <v>0.705746511627907</v>
+        <v>0.8151191489361702</v>
       </c>
       <c r="AG81" t="n">
         <v>0.8634222222222222</v>
@@ -7008,7 +7008,7 @@
         <v>0.8191081632653062</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.8079921052631579</v>
+        <v>0.8504878048780488</v>
       </c>
       <c r="AG82" t="n">
         <v>0.8649288888888889</v>
@@ -7088,7 +7088,7 @@
         <v>0.8890387096774194</v>
       </c>
       <c r="AF83" t="n">
-        <v>0.7309636363636364</v>
+        <v>0.8770098039215686</v>
       </c>
       <c r="AG83" t="n">
         <v>0.8624686274509804</v>
@@ -7168,7 +7168,7 @@
         <v>0.9049065217391304</v>
       </c>
       <c r="AF84" t="n">
-        <v>0.761778947368421</v>
+        <v>0.8778173076923077</v>
       </c>
       <c r="AG84" t="n">
         <v>0.8451090909090908</v>
@@ -7248,7 +7248,7 @@
         <v>0.9520903225806452</v>
       </c>
       <c r="AF85" t="n">
-        <v>0.8379250000000001</v>
+        <v>0.850886046511628</v>
       </c>
       <c r="AG85" t="n">
         <v>0.8907369565217391</v>
@@ -7328,7 +7328,7 @@
         <v>0.8849652173913043</v>
       </c>
       <c r="AF86" t="n">
-        <v>0.8038782608695653</v>
+        <v>0.8825627906976745</v>
       </c>
       <c r="AG86" t="n">
         <v>0.9096526315789474</v>
@@ -7408,7 +7408,7 @@
         <v>0.8634027027027027</v>
       </c>
       <c r="AF87" t="n">
-        <v>0.7474943396226414</v>
+        <v>0.888964705882353</v>
       </c>
       <c r="AG87" t="n">
         <v>0.8535130434782608</v>
@@ -7488,7 +7488,7 @@
         <v>0.7991558823529411</v>
       </c>
       <c r="AF88" t="n">
-        <v>0.7343703703703703</v>
+        <v>0.8718947368421052</v>
       </c>
       <c r="AG88" t="n">
         <v>0.8412625</v>
@@ -7568,7 +7568,7 @@
         <v>0.7768318181818181</v>
       </c>
       <c r="AF89" t="n">
-        <v>0.7854456140350877</v>
+        <v>0.8274745454545455</v>
       </c>
       <c r="AG89" t="n">
         <v>0.8927854166666668</v>
@@ -7648,7 +7648,7 @@
         <v>0.8157133333333334</v>
       </c>
       <c r="AF90" t="n">
-        <v>0.8259139534883719</v>
+        <v>0.8004886363636365</v>
       </c>
       <c r="AG90" t="n">
         <v>0.8915225000000001</v>
@@ -7728,7 +7728,7 @@
         <v>0.8768411764705882</v>
       </c>
       <c r="AF91" t="n">
-        <v>0.7837869565217394</v>
+        <v>0.8294</v>
       </c>
       <c r="AG91" t="n">
         <v>0.834263888888889</v>
@@ -7808,7 +7808,7 @@
         <v>0.8578666666666667</v>
       </c>
       <c r="AF92" t="n">
-        <v>0.6651650000000001</v>
+        <v>0.868578947368421</v>
       </c>
       <c r="AG92" t="n">
         <v>0.9011121951219512</v>
@@ -7888,7 +7888,7 @@
         <v>0.7772945945945946</v>
       </c>
       <c r="AF93" t="n">
-        <v>0.7490516666666666</v>
+        <v>0.8912926829268294</v>
       </c>
       <c r="AG93" t="n">
         <v>0.8462468750000001</v>
@@ -7968,7 +7968,7 @@
         <v>0.794025641025641</v>
       </c>
       <c r="AF94" t="n">
-        <v>0.7768717391304348</v>
+        <v>0.8894866666666668</v>
       </c>
       <c r="AG94" t="n">
         <v>0.8884404761904763</v>
@@ -8048,7 +8048,7 @@
         <v>0.7852149999999999</v>
       </c>
       <c r="AF95" t="n">
-        <v>0.8487095238095238</v>
+        <v>0.9084459459459461</v>
       </c>
       <c r="AG95" t="n">
         <v>0.8711861111111112</v>
@@ -8128,7 +8128,7 @@
         <v>0.9281108695652174</v>
       </c>
       <c r="AF96" t="n">
-        <v>0.7357827586206895</v>
+        <v>0.8451533333333335</v>
       </c>
       <c r="AG96" t="n">
         <v>0.857909375</v>
@@ -8208,7 +8208,7 @@
         <v>0.8262</v>
       </c>
       <c r="AF97" t="n">
-        <v>0.7370184210526316</v>
+        <v>0.860349019607843</v>
       </c>
       <c r="AG97" t="n">
         <v>0.8854935483870968</v>
@@ -8288,7 +8288,7 @@
         <v>0.8027107142857143</v>
       </c>
       <c r="AF98" t="n">
-        <v>0.819178</v>
+        <v>0.881551724137931</v>
       </c>
       <c r="AG98" t="n">
         <v>0.8519176470588236</v>
@@ -8368,7 +8368,7 @@
         <v>0.8429800000000001</v>
       </c>
       <c r="AF99" t="n">
-        <v>0.7766933333333335</v>
+        <v>0.8819274509803923</v>
       </c>
       <c r="AG99" t="n">
         <v>0.8394272727272728</v>
@@ -8448,7 +8448,7 @@
         <v>0.8082483870967743</v>
       </c>
       <c r="AF100" t="n">
-        <v>0.8443446808510637</v>
+        <v>0.8171355555555556</v>
       </c>
       <c r="AG100" t="n">
         <v>0.8813866666666667</v>
@@ -8528,7 +8528,7 @@
         <v>0.8170945945945947</v>
       </c>
       <c r="AF101" t="n">
-        <v>0.7568620689655172</v>
+        <v>0.804910810810811</v>
       </c>
       <c r="AG101" t="n">
         <v>0.8519739130434781</v>
@@ -8608,7 +8608,7 @@
         <v>0.8249069767441861</v>
       </c>
       <c r="AF102" t="n">
-        <v>0.7723093023255815</v>
+        <v>0.8755374999999999</v>
       </c>
       <c r="AG102" t="n">
         <v>0.8819733333333334</v>
@@ -8688,7 +8688,7 @@
         <v>0.9088540540540541</v>
       </c>
       <c r="AF103" t="n">
-        <v>0.7391052631578947</v>
+        <v>0.8392673469387755</v>
       </c>
       <c r="AG103" t="n">
         <v>0.8554162790697677</v>
@@ -8768,7 +8768,7 @@
         <v>0.8374355555555556</v>
       </c>
       <c r="AF104" t="n">
-        <v>0.7095041666666667</v>
+        <v>0.8217150943396226</v>
       </c>
       <c r="AG104" t="n">
         <v>0.8421581395348837</v>
@@ -8970,7 +8970,7 @@
         <v>0.4666666666666667</v>
       </c>
       <c r="AF109" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="AG109" t="n">
         <v>0.8666666666666667</v>
@@ -9059,7 +9059,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="AF110" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AG110" t="n">
         <v>0.9230769230769231</v>
@@ -9148,7 +9148,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="AF111" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="AG111" t="n">
         <v>0.7777777777777778</v>
@@ -9237,7 +9237,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="AF112" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AG112" t="n">
         <v>1</v>
@@ -9326,7 +9326,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AF113" t="n">
-        <v>0.5</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="AG113" t="n">
         <v>1</v>
@@ -9415,7 +9415,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF114" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AG114" t="n">
         <v>0.9</v>
@@ -9504,7 +9504,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="AF115" t="n">
-        <v>0.6363636363636364</v>
+        <v>1</v>
       </c>
       <c r="AG115" t="n">
         <v>1</v>
@@ -9593,7 +9593,7 @@
         <v>0.6</v>
       </c>
       <c r="AF116" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.9</v>
       </c>
       <c r="AG116" t="n">
         <v>0.75</v>
@@ -9682,7 +9682,7 @@
         <v>0.6</v>
       </c>
       <c r="AF117" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AG117" t="n">
         <v>0.875</v>
@@ -9759,7 +9759,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="AF118" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AG118" t="n">
         <v>1</v>
@@ -9839,7 +9839,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF119" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AG119" t="n">
         <v>1</v>
@@ -9919,7 +9919,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="AF120" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.75</v>
       </c>
       <c r="AG120" t="n">
         <v>1</v>
@@ -9999,7 +9999,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AF121" t="n">
-        <v>0.6153846153846154</v>
+        <v>1</v>
       </c>
       <c r="AG121" t="n">
         <v>1</v>
@@ -10079,7 +10079,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AF122" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG122" t="n">
         <v>1</v>
@@ -10159,7 +10159,7 @@
         <v>0.75</v>
       </c>
       <c r="AF123" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.8</v>
       </c>
       <c r="AG123" t="n">
         <v>0.875</v>
@@ -10239,7 +10239,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AF124" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="AG124" t="n">
         <v>1</v>
@@ -10319,7 +10319,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF125" t="n">
-        <v>0.4444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AG125" t="n">
         <v>1</v>
@@ -10399,7 +10399,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF126" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AG126" t="n">
         <v>1</v>
@@ -10479,7 +10479,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AF127" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="AG127" t="n">
         <v>1</v>
@@ -10556,7 +10556,7 @@
         <v>0.6</v>
       </c>
       <c r="AF128" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AG128" t="n">
         <v>1</v>
@@ -10636,7 +10636,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF129" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="AG129" t="n">
         <v>1</v>
@@ -10716,7 +10716,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AF130" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="AG130" t="n">
         <v>1</v>
@@ -10796,7 +10796,7 @@
         <v>0.875</v>
       </c>
       <c r="AF131" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AG131" t="n">
         <v>1</v>
@@ -10876,7 +10876,7 @@
         <v>1</v>
       </c>
       <c r="AF132" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="AG132" t="n">
         <v>1</v>
@@ -10956,7 +10956,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AF133" t="n">
-        <v>0.6363636363636364</v>
+        <v>1</v>
       </c>
       <c r="AG133" t="n">
         <v>1</v>
@@ -11036,7 +11036,7 @@
         <v>0.875</v>
       </c>
       <c r="AF134" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG134" t="n">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>1</v>
       </c>
       <c r="AF135" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AG135" t="n">
         <v>1</v>
@@ -11196,7 +11196,7 @@
         <v>0.875</v>
       </c>
       <c r="AF136" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="AG136" t="n">
         <v>1</v>
@@ -11276,7 +11276,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF137" t="n">
-        <v>0.5384615384615384</v>
+        <v>1</v>
       </c>
       <c r="AG137" t="n">
         <v>1</v>
@@ -11356,7 +11356,7 @@
         <v>0.75</v>
       </c>
       <c r="AF138" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AG138" t="n">
         <v>1</v>
@@ -11436,7 +11436,7 @@
         <v>0.875</v>
       </c>
       <c r="AF139" t="n">
-        <v>0.4615384615384616</v>
+        <v>1</v>
       </c>
       <c r="AG139" t="n">
         <v>1</v>
@@ -11513,7 +11513,7 @@
         <v>0.8</v>
       </c>
       <c r="AF140" t="n">
-        <v>0.6363636363636364</v>
+        <v>1</v>
       </c>
       <c r="AG140" t="n">
         <v>1</v>
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="AF141" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AG141" t="n">
         <v>1</v>
@@ -11673,7 +11673,7 @@
         <v>0.875</v>
       </c>
       <c r="AF142" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="AG142" t="n">
         <v>1</v>
@@ -11750,7 +11750,7 @@
         <v>0.875</v>
       </c>
       <c r="AF143" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AG143" t="n">
         <v>1</v>
@@ -11830,7 +11830,7 @@
         <v>0.625</v>
       </c>
       <c r="AF144" t="n">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="AG144" t="n">
         <v>1</v>
@@ -11910,7 +11910,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AF145" t="n">
-        <v>0.4444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AG145" t="n">
         <v>1</v>
@@ -11990,7 +11990,7 @@
         <v>0.5</v>
       </c>
       <c r="AF146" t="n">
-        <v>0.5833333333333334</v>
+        <v>1</v>
       </c>
       <c r="AG146" t="n">
         <v>1</v>
@@ -12070,7 +12070,7 @@
         <v>0.8</v>
       </c>
       <c r="AF147" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AG147" t="n">
         <v>1</v>
@@ -12150,7 +12150,7 @@
         <v>0.8</v>
       </c>
       <c r="AF148" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AG148" t="n">
         <v>1</v>
@@ -12230,7 +12230,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="AF149" t="n">
-        <v>0.6363636363636364</v>
+        <v>1</v>
       </c>
       <c r="AG149" t="n">
         <v>1</v>
@@ -12310,7 +12310,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AF150" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AG150" t="n">
         <v>0.7142857142857143</v>
@@ -12390,7 +12390,7 @@
         <v>1</v>
       </c>
       <c r="AF151" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AG151" t="n">
         <v>1</v>
@@ -12470,7 +12470,7 @@
         <v>0.8</v>
       </c>
       <c r="AF152" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG152" t="n">
         <v>1</v>
@@ -12550,7 +12550,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="AF153" t="n">
-        <v>0.4545454545454545</v>
+        <v>1</v>
       </c>
       <c r="AG153" t="n">
         <v>1</v>
@@ -12627,7 +12627,7 @@
         <v>1</v>
       </c>
       <c r="AF154" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AG154" t="n">
         <v>1</v>
@@ -12707,7 +12707,7 @@
         <v>0.875</v>
       </c>
       <c r="AF155" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="AG155" t="n">
         <v>1</v>
@@ -12787,7 +12787,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF156" t="n">
-        <v>0.7272727272727273</v>
+        <v>1</v>
       </c>
       <c r="AG156" t="n">
         <v>1</v>
@@ -12867,7 +12867,7 @@
         <v>0.75</v>
       </c>
       <c r="AF157" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG157" t="n">
         <v>1</v>
@@ -12947,7 +12947,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="AF158" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG158" t="n">
         <v>1</v>
@@ -13027,7 +13027,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AF159" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="AG159" t="n">
         <v>1</v>
@@ -13107,7 +13107,7 @@
         <v>0.875</v>
       </c>
       <c r="AF160" t="n">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="AG160" t="n">
         <v>1</v>
@@ -13187,7 +13187,7 @@
         <v>1</v>
       </c>
       <c r="AF161" t="n">
-        <v>0.6923076923076923</v>
+        <v>1</v>
       </c>
       <c r="AG161" t="n">
         <v>1</v>
@@ -13267,7 +13267,7 @@
         <v>0.8</v>
       </c>
       <c r="AF162" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AG162" t="n">
         <v>1</v>
@@ -13347,7 +13347,7 @@
         <v>0.6</v>
       </c>
       <c r="AF163" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AG163" t="n">
         <v>1</v>
@@ -13427,7 +13427,7 @@
         <v>0.75</v>
       </c>
       <c r="AF164" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG164" t="n">
         <v>1</v>
@@ -13507,7 +13507,7 @@
         <v>0.875</v>
       </c>
       <c r="AF165" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="AG165" t="n">
         <v>1</v>
@@ -13587,7 +13587,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AF166" t="n">
-        <v>0.3636363636363636</v>
+        <v>1</v>
       </c>
       <c r="AG166" t="n">
         <v>1</v>
@@ -13667,7 +13667,7 @@
         <v>1</v>
       </c>
       <c r="AF167" t="n">
-        <v>0.6363636363636364</v>
+        <v>1</v>
       </c>
       <c r="AG167" t="n">
         <v>1</v>
@@ -13747,7 +13747,7 @@
         <v>1</v>
       </c>
       <c r="AF168" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AG168" t="n">
         <v>1</v>
@@ -13827,7 +13827,7 @@
         <v>1</v>
       </c>
       <c r="AF169" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AG169" t="n">
         <v>1</v>
@@ -13907,7 +13907,7 @@
         <v>0.8</v>
       </c>
       <c r="AF170" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AG170" t="n">
         <v>1</v>
@@ -13987,7 +13987,7 @@
         <v>0.875</v>
       </c>
       <c r="AF171" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG171" t="n">
         <v>1</v>
@@ -14067,7 +14067,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AF172" t="n">
-        <v>0.7272727272727273</v>
+        <v>1</v>
       </c>
       <c r="AG172" t="n">
         <v>1</v>
@@ -14147,7 +14147,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF173" t="n">
-        <v>0.5454545454545454</v>
+        <v>1</v>
       </c>
       <c r="AG173" t="n">
         <v>1</v>
@@ -14227,7 +14227,7 @@
         <v>0.9</v>
       </c>
       <c r="AF174" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="AG174" t="n">
         <v>1</v>
@@ -14307,7 +14307,7 @@
         <v>1</v>
       </c>
       <c r="AF175" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AG175" t="n">
         <v>1</v>
@@ -14387,7 +14387,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="AF176" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="AG176" t="n">
         <v>1</v>
@@ -14467,7 +14467,7 @@
         <v>0.75</v>
       </c>
       <c r="AF177" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="AG177" t="n">
         <v>1</v>
@@ -14547,7 +14547,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AF178" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AG178" t="n">
         <v>1</v>
@@ -14627,7 +14627,7 @@
         <v>0.6</v>
       </c>
       <c r="AF179" t="n">
-        <v>0.5833333333333334</v>
+        <v>1</v>
       </c>
       <c r="AG179" t="n">
         <v>1</v>
@@ -14707,7 +14707,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF180" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AG180" t="n">
         <v>1</v>
@@ -14784,7 +14784,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AF181" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="AG181" t="n">
         <v>1</v>
@@ -14864,7 +14864,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AF182" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG182" t="n">
         <v>1</v>
@@ -14944,7 +14944,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AF183" t="n">
-        <v>0.5454545454545454</v>
+        <v>1</v>
       </c>
       <c r="AG183" t="n">
         <v>1</v>
@@ -15024,7 +15024,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AF184" t="n">
-        <v>0.5454545454545454</v>
+        <v>1</v>
       </c>
       <c r="AG184" t="n">
         <v>1</v>
@@ -15104,7 +15104,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AF185" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AG185" t="n">
         <v>1</v>
@@ -15184,7 +15184,7 @@
         <v>0.75</v>
       </c>
       <c r="AF186" t="n">
-        <v>0.8181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AG186" t="n">
         <v>1</v>
@@ -15264,7 +15264,7 @@
         <v>0.9</v>
       </c>
       <c r="AF187" t="n">
-        <v>0.4444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AG187" t="n">
         <v>1</v>
@@ -15344,7 +15344,7 @@
         <v>0.8</v>
       </c>
       <c r="AF188" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AG188" t="n">
         <v>1</v>
@@ -15424,7 +15424,7 @@
         <v>0.75</v>
       </c>
       <c r="AF189" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG189" t="n">
         <v>1</v>
@@ -15504,7 +15504,7 @@
         <v>1</v>
       </c>
       <c r="AF190" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AG190" t="n">
         <v>1</v>
@@ -15584,7 +15584,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AF191" t="n">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="AG191" t="n">
         <v>1</v>
@@ -15664,7 +15664,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="AF192" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG192" t="n">
         <v>1</v>
@@ -15744,7 +15744,7 @@
         <v>0.75</v>
       </c>
       <c r="AF193" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AG193" t="n">
         <v>1</v>
@@ -15824,7 +15824,7 @@
         <v>1</v>
       </c>
       <c r="AF194" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="AG194" t="n">
         <v>1</v>
@@ -15904,7 +15904,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="AF195" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="AG195" t="n">
         <v>1</v>
@@ -15984,7 +15984,7 @@
         <v>0.75</v>
       </c>
       <c r="AF196" t="n">
-        <v>0.5454545454545454</v>
+        <v>1</v>
       </c>
       <c r="AG196" t="n">
         <v>1</v>
@@ -16064,7 +16064,7 @@
         <v>0.75</v>
       </c>
       <c r="AF197" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="AG197" t="n">
         <v>1</v>
@@ -16144,7 +16144,7 @@
         <v>1</v>
       </c>
       <c r="AF198" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="AG198" t="n">
         <v>1</v>
@@ -16224,7 +16224,7 @@
         <v>1</v>
       </c>
       <c r="AF199" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AG199" t="n">
         <v>1</v>
@@ -16304,7 +16304,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AF200" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="AG200" t="n">
         <v>1</v>
@@ -16384,7 +16384,7 @@
         <v>0.875</v>
       </c>
       <c r="AF201" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AG201" t="n">
         <v>1</v>
@@ -16464,7 +16464,7 @@
         <v>1</v>
       </c>
       <c r="AF202" t="n">
-        <v>0.4444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AG202" t="n">
         <v>1</v>
@@ -16544,7 +16544,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AF203" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AG203" t="n">
         <v>1</v>
@@ -16624,7 +16624,7 @@
         <v>0.75</v>
       </c>
       <c r="AF204" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="AG204" t="n">
         <v>1</v>
@@ -16704,7 +16704,7 @@
         <v>1</v>
       </c>
       <c r="AF205" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AG205" t="n">
         <v>1</v>
@@ -16784,7 +16784,7 @@
         <v>1</v>
       </c>
       <c r="AF206" t="n">
-        <v>0.6153846153846154</v>
+        <v>1</v>
       </c>
       <c r="AG206" t="n">
         <v>1</v>
@@ -16864,7 +16864,7 @@
         <v>0.8</v>
       </c>
       <c r="AF207" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AG207" t="n">
         <v>1</v>
@@ -32547,7 +32547,7 @@
         <v>0.21082</v>
       </c>
       <c r="AF418" t="n">
-        <v>0.2085666666666667</v>
+        <v>0.127675</v>
       </c>
       <c r="AG418" t="n">
         <v>0.150375</v>
@@ -32606,7 +32606,7 @@
         <v>0.1962333333333333</v>
       </c>
       <c r="AF419" t="n">
-        <v>0.11385</v>
+        <v>0.2235625</v>
       </c>
       <c r="AG419" t="n">
         <v>0.1805142857142857</v>
@@ -32665,7 +32665,7 @@
         <v>0.2886142857142857</v>
       </c>
       <c r="AF420" t="n">
-        <v>0.2421666666666666</v>
+        <v>0.20874</v>
       </c>
       <c r="AG420" t="n">
         <v>0.21036</v>
@@ -32724,7 +32724,7 @@
         <v>0.2237625</v>
       </c>
       <c r="AF421" t="n">
-        <v>0.2618</v>
+        <v>0.28896</v>
       </c>
       <c r="AG421" t="n">
         <v>0.252225</v>
@@ -32783,7 +32783,7 @@
         <v>0.32965</v>
       </c>
       <c r="AF422" t="n">
-        <v>0.2596</v>
+        <v>0.32118</v>
       </c>
       <c r="AG422" t="n">
         <v>0.2460166666666667</v>
@@ -32842,7 +32842,7 @@
         <v>0.3196</v>
       </c>
       <c r="AF423" t="n">
-        <v>0.3299454545454546</v>
+        <v>0.2702</v>
       </c>
       <c r="AG423" t="n">
         <v>0.30364</v>
@@ -32901,7 +32901,7 @@
         <v>0.3729444444444444</v>
       </c>
       <c r="AF424" t="n">
-        <v>0.3415666666666666</v>
+        <v>0.3475</v>
       </c>
       <c r="AG424" t="n">
         <v>0.35805</v>
@@ -32960,7 +32960,7 @@
         <v>0.4001899999999999</v>
       </c>
       <c r="AF425" t="n">
-        <v>0.40175</v>
+        <v>0.343825</v>
       </c>
       <c r="AG425" t="n">
         <v>0.3969</v>
@@ -33019,7 +33019,7 @@
         <v>0.4868000000000001</v>
       </c>
       <c r="AF426" t="n">
-        <v>0.3984199999999999</v>
+        <v>0.4042000000000001</v>
       </c>
       <c r="AG426" t="n">
         <v>0.4283750000000001</v>
@@ -33078,7 +33078,7 @@
         <v>0.4753583333333333</v>
       </c>
       <c r="AF427" t="n">
-        <v>0.3904</v>
+        <v>0.4777749999999999</v>
       </c>
       <c r="AG427" t="n">
         <v>0.4914125</v>
@@ -33125,7 +33125,7 @@
         <v>0.5105272727272728</v>
       </c>
       <c r="AF428" t="n">
-        <v>0.4098555555555555</v>
+        <v>0.4502</v>
       </c>
       <c r="AG428" t="n">
         <v>0.5786777777777778</v>
@@ -33175,7 +33175,7 @@
         <v>0.6239444444444444</v>
       </c>
       <c r="AF429" t="n">
-        <v>0.4232625</v>
+        <v>0.5307857142857143</v>
       </c>
       <c r="AG429" t="n">
         <v>0.5446749999999999</v>
@@ -33225,7 +33225,7 @@
         <v>0.6690888888888888</v>
       </c>
       <c r="AF430" t="n">
-        <v>0.4967714285714285</v>
+        <v>0.5082142857142856</v>
       </c>
       <c r="AG430" t="n">
         <v>0.6261636363636364</v>
@@ -33275,7 +33275,7 @@
         <v>0.5965857142857143</v>
       </c>
       <c r="AF431" t="n">
-        <v>0.4821428571428572</v>
+        <v>0.5713333333333335</v>
       </c>
       <c r="AG431" t="n">
         <v>0.6130666666666666</v>
@@ -33325,7 +33325,7 @@
         <v>0.6135181818181817</v>
       </c>
       <c r="AF432" t="n">
-        <v>0.5716555555555556</v>
+        <v>0.593657142857143</v>
       </c>
       <c r="AG432" t="n">
         <v>0.539988888888889</v>
@@ -33375,7 +33375,7 @@
         <v>0.6650999999999999</v>
       </c>
       <c r="AF433" t="n">
-        <v>0.5208</v>
+        <v>0.6260100000000001</v>
       </c>
       <c r="AG433" t="n">
         <v>0.6403624999999999</v>
@@ -33425,7 +33425,7 @@
         <v>0.6131714285714286</v>
       </c>
       <c r="AF434" t="n">
-        <v>0.61748</v>
+        <v>0.6938428571428571</v>
       </c>
       <c r="AG434" t="n">
         <v>0.6644099999999999</v>
@@ -33475,7 +33475,7 @@
         <v>0.7117333333333333</v>
       </c>
       <c r="AF435" t="n">
-        <v>0.6697636363636364</v>
+        <v>0.5471125</v>
       </c>
       <c r="AG435" t="n">
         <v>0.6553249999999999</v>
@@ -33525,7 +33525,7 @@
         <v>0.7179666666666668</v>
       </c>
       <c r="AF436" t="n">
-        <v>0.6910749999999999</v>
+        <v>0.67948</v>
       </c>
       <c r="AG436" t="n">
         <v>0.6570666666666667</v>
@@ -33575,7 +33575,7 @@
         <v>0.73512</v>
       </c>
       <c r="AF437" t="n">
-        <v>0.6272090909090908</v>
+        <v>0.6447272727272727</v>
       </c>
       <c r="AG437" t="n">
         <v>0.6755555555555556</v>
@@ -33622,7 +33622,7 @@
         <v>0.7061166666666666</v>
       </c>
       <c r="AF438" t="n">
-        <v>0.7179285714285714</v>
+        <v>0.68631</v>
       </c>
       <c r="AG438" t="n">
         <v>0.7323125</v>
@@ -33672,7 +33672,7 @@
         <v>0.7557666666666667</v>
       </c>
       <c r="AF439" t="n">
-        <v>0.7194199999999999</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="AG439" t="n">
         <v>0.6723000000000001</v>
@@ -33722,7 +33722,7 @@
         <v>0.7010000000000001</v>
       </c>
       <c r="AF440" t="n">
-        <v>0.7299</v>
+        <v>0.7237222222222223</v>
       </c>
       <c r="AG440" t="n">
         <v>0.8287636363636363</v>
@@ -33772,7 +33772,7 @@
         <v>0.7742875</v>
       </c>
       <c r="AF441" t="n">
-        <v>0.7723749999999999</v>
+        <v>0.779342857142857</v>
       </c>
       <c r="AG441" t="n">
         <v>0.6786749999999999</v>
@@ -33822,7 +33822,7 @@
         <v>0.7402375</v>
       </c>
       <c r="AF442" t="n">
-        <v>0.6776599999999999</v>
+        <v>0.6892800000000001</v>
       </c>
       <c r="AG442" t="n">
         <v>0.7175777777777778</v>
@@ -33872,7 +33872,7 @@
         <v>0.7714909090909091</v>
       </c>
       <c r="AF443" t="n">
-        <v>0.6970250000000001</v>
+        <v>0.6907</v>
       </c>
       <c r="AG443" t="n">
         <v>0.7514000000000001</v>
@@ -33922,7 +33922,7 @@
         <v>0.763975</v>
       </c>
       <c r="AF444" t="n">
-        <v>0.7830454545454544</v>
+        <v>0.7421800000000001</v>
       </c>
       <c r="AG444" t="n">
         <v>0.6881</v>
@@ -33972,7 +33972,7 @@
         <v>0.7619333333333334</v>
       </c>
       <c r="AF445" t="n">
-        <v>0.8399333333333332</v>
+        <v>0.7452000000000001</v>
       </c>
       <c r="AG445" t="n">
         <v>0.6619375</v>
@@ -34022,7 +34022,7 @@
         <v>0.7169375000000001</v>
       </c>
       <c r="AF446" t="n">
-        <v>0.70085</v>
+        <v>0.6826125</v>
       </c>
       <c r="AG446" t="n">
         <v>0.7056571428571428</v>
@@ -34072,7 +34072,7 @@
         <v>0.8429111111111109</v>
       </c>
       <c r="AF447" t="n">
-        <v>0.8234249999999999</v>
+        <v>0.68691</v>
       </c>
       <c r="AG447" t="n">
         <v>0.70548</v>
@@ -34122,7 +34122,7 @@
         <v>0.7176666666666667</v>
       </c>
       <c r="AF448" t="n">
-        <v>0.8590750000000001</v>
+        <v>0.7094818181818181</v>
       </c>
       <c r="AG448" t="n">
         <v>0.6137875</v>
@@ -34172,7 +34172,7 @@
         <v>0.7721375</v>
       </c>
       <c r="AF449" t="n">
-        <v>0.6913888888888888</v>
+        <v>0.7185888888888888</v>
       </c>
       <c r="AG449" t="n">
         <v>0.6373571428571428</v>
@@ -34219,7 +34219,7 @@
         <v>0.7523</v>
       </c>
       <c r="AF450" t="n">
-        <v>0.8122874999999999</v>
+        <v>0.66425</v>
       </c>
       <c r="AG450" t="n">
         <v>0.7039375000000001</v>
@@ -34269,7 +34269,7 @@
         <v>0.79535</v>
       </c>
       <c r="AF451" t="n">
-        <v>0.756</v>
+        <v>0.6785181818181819</v>
       </c>
       <c r="AG451" t="n">
         <v>0.6523</v>
@@ -34319,7 +34319,7 @@
         <v>0.7827375000000001</v>
       </c>
       <c r="AF452" t="n">
-        <v>0.8365</v>
+        <v>0.767675</v>
       </c>
       <c r="AG452" t="n">
         <v>0.7395875</v>
@@ -34366,7 +34366,7 @@
         <v>0.8176000000000001</v>
       </c>
       <c r="AF453" t="n">
-        <v>0.8086428571428571</v>
+        <v>0.73316</v>
       </c>
       <c r="AG453" t="n">
         <v>0.7404299999999999</v>
@@ -34416,7 +34416,7 @@
         <v>0.7852600000000001</v>
       </c>
       <c r="AF454" t="n">
-        <v>0.765475</v>
+        <v>0.7338571428571428</v>
       </c>
       <c r="AG454" t="n">
         <v>0.6936199999999999</v>
@@ -34466,7 +34466,7 @@
         <v>0.8203571428571428</v>
       </c>
       <c r="AF455" t="n">
-        <v>0.8568363636363638</v>
+        <v>0.6692999999999999</v>
       </c>
       <c r="AG455" t="n">
         <v>0.66187</v>
@@ -34516,7 +34516,7 @@
         <v>0.7939833333333333</v>
       </c>
       <c r="AF456" t="n">
-        <v>0.7533</v>
+        <v>0.73602</v>
       </c>
       <c r="AG456" t="n">
         <v>0.7350857142857142</v>
@@ -34566,7 +34566,7 @@
         <v>0.7228090909090908</v>
       </c>
       <c r="AF457" t="n">
-        <v>0.7226666666666667</v>
+        <v>0.767875</v>
       </c>
       <c r="AG457" t="n">
         <v>0.7047857142857143</v>
@@ -34616,7 +34616,7 @@
         <v>0.7877571428571429</v>
       </c>
       <c r="AF458" t="n">
-        <v>0.73442</v>
+        <v>0.7299888888888888</v>
       </c>
       <c r="AG458" t="n">
         <v>0.6754875</v>
@@ -34666,7 +34666,7 @@
         <v>0.7976300000000001</v>
       </c>
       <c r="AF459" t="n">
-        <v>0.8531625000000002</v>
+        <v>0.7054454545454546</v>
       </c>
       <c r="AG459" t="n">
         <v>0.7225428571428572</v>
@@ -34716,7 +34716,7 @@
         <v>0.7648111111111111</v>
       </c>
       <c r="AF460" t="n">
-        <v>0.8057333333333333</v>
+        <v>0.7394222222222222</v>
       </c>
       <c r="AG460" t="n">
         <v>0.71025</v>
@@ -34766,7 +34766,7 @@
         <v>0.7052333333333335</v>
       </c>
       <c r="AF461" t="n">
-        <v>0.8199916666666668</v>
+        <v>0.7619333333333334</v>
       </c>
       <c r="AG461" t="n">
         <v>0.7363333333333333</v>
@@ -34816,7 +34816,7 @@
         <v>0.8264363636363636</v>
       </c>
       <c r="AF462" t="n">
-        <v>0.862511111111111</v>
+        <v>0.6142</v>
       </c>
       <c r="AG462" t="n">
         <v>0.7300749999999999</v>
@@ -34866,7 +34866,7 @@
         <v>0.8513875000000001</v>
       </c>
       <c r="AF463" t="n">
-        <v>0.77951</v>
+        <v>0.725325</v>
       </c>
       <c r="AG463" t="n">
         <v>0.7068000000000001</v>
@@ -34913,7 +34913,7 @@
         <v>0.807988888888889</v>
       </c>
       <c r="AF464" t="n">
-        <v>0.8257666666666666</v>
+        <v>0.7359</v>
       </c>
       <c r="AG464" t="n">
         <v>0.65405</v>
@@ -34963,7 +34963,7 @@
         <v>0.822725</v>
       </c>
       <c r="AF465" t="n">
-        <v>0.8161999999999999</v>
+        <v>0.7050555555555555</v>
       </c>
       <c r="AG465" t="n">
         <v>0.7337300000000001</v>
@@ -35013,7 +35013,7 @@
         <v>0.8486111111111111</v>
       </c>
       <c r="AF466" t="n">
-        <v>0.7726714285714286</v>
+        <v>0.7466428571428573</v>
       </c>
       <c r="AG466" t="n">
         <v>0.6647545454545455</v>
@@ -35063,7 +35063,7 @@
         <v>0.7753777777777777</v>
       </c>
       <c r="AF467" t="n">
-        <v>0.9099600000000002</v>
+        <v>0.7173777777777777</v>
       </c>
       <c r="AG467" t="n">
         <v>0.6775</v>
@@ -35113,7 +35113,7 @@
         <v>0.800625</v>
       </c>
       <c r="AF468" t="n">
-        <v>0.7612666666666666</v>
+        <v>0.7905299999999998</v>
       </c>
       <c r="AG468" t="n">
         <v>0.6735899999999999</v>
@@ -35163,7 +35163,7 @@
         <v>0.8267200000000001</v>
       </c>
       <c r="AF469" t="n">
-        <v>0.8188249999999999</v>
+        <v>0.7068727272727273</v>
       </c>
       <c r="AG469" t="n">
         <v>0.7087625</v>
@@ -35213,7 +35213,7 @@
         <v>0.82225</v>
       </c>
       <c r="AF470" t="n">
-        <v>0.8237</v>
+        <v>0.78025</v>
       </c>
       <c r="AG470" t="n">
         <v>0.6691666666666666</v>
@@ -35263,7 +35263,7 @@
         <v>0.8405875</v>
       </c>
       <c r="AF471" t="n">
-        <v>0.8376833333333332</v>
+        <v>0.7529428571428571</v>
       </c>
       <c r="AG471" t="n">
         <v>0.7505285714285713</v>
@@ -35313,7 +35313,7 @@
         <v>0.7876727272727272</v>
       </c>
       <c r="AF472" t="n">
-        <v>0.8511555555555554</v>
+        <v>0.673488888888889</v>
       </c>
       <c r="AG472" t="n">
         <v>0.76529</v>
@@ -35363,7 +35363,7 @@
         <v>0.7727083333333336</v>
       </c>
       <c r="AF473" t="n">
-        <v>0.8157000000000001</v>
+        <v>0.6740999999999999</v>
       </c>
       <c r="AG473" t="n">
         <v>0.7139499999999999</v>
@@ -35413,7 +35413,7 @@
         <v>0.7641777777777778</v>
       </c>
       <c r="AF474" t="n">
-        <v>0.87422</v>
+        <v>0.6760555555555554</v>
       </c>
       <c r="AG474" t="n">
         <v>0.6641666666666667</v>
@@ -35463,7 +35463,7 @@
         <v>0.832225</v>
       </c>
       <c r="AF475" t="n">
-        <v>0.856275</v>
+        <v>0.7688916666666668</v>
       </c>
       <c r="AG475" t="n">
         <v>0.7051555555555555</v>
@@ -35513,7 +35513,7 @@
         <v>0.7699199999999999</v>
       </c>
       <c r="AF476" t="n">
-        <v>0.8098727272727273</v>
+        <v>0.710011111111111</v>
       </c>
       <c r="AG476" t="n">
         <v>0.7401555555555556</v>
@@ -35563,7 +35563,7 @@
         <v>0.8388142857142858</v>
       </c>
       <c r="AF477" t="n">
-        <v>0.9137624999999999</v>
+        <v>0.588925</v>
       </c>
       <c r="AG477" t="n">
         <v>0.6803</v>
@@ -35613,7 +35613,7 @@
         <v>0.7797499999999999</v>
       </c>
       <c r="AF478" t="n">
-        <v>0.7263333333333333</v>
+        <v>0.7249166666666667</v>
       </c>
       <c r="AG478" t="n">
         <v>0.7415666666666668</v>
@@ -35663,7 +35663,7 @@
         <v>0.8019428571428573</v>
       </c>
       <c r="AF479" t="n">
-        <v>0.7894111111111112</v>
+        <v>0.6528333333333334</v>
       </c>
       <c r="AG479" t="n">
         <v>0.7402444444444444</v>
@@ -35713,7 +35713,7 @@
         <v>0.8722000000000001</v>
       </c>
       <c r="AF480" t="n">
-        <v>0.8367666666666665</v>
+        <v>0.6684875</v>
       </c>
       <c r="AG480" t="n">
         <v>0.6899555555555554</v>
@@ -35763,7 +35763,7 @@
         <v>0.866125</v>
       </c>
       <c r="AF481" t="n">
-        <v>0.8291600000000001</v>
+        <v>0.6694142857142857</v>
       </c>
       <c r="AG481" t="n">
         <v>0.7259625</v>
@@ -35813,7 +35813,7 @@
         <v>0.7880230769230768</v>
       </c>
       <c r="AF482" t="n">
-        <v>0.7949857142857143</v>
+        <v>0.7333636363636363</v>
       </c>
       <c r="AG482" t="n">
         <v>0.6759777777777779</v>
@@ -35863,7 +35863,7 @@
         <v>0.7295666666666666</v>
       </c>
       <c r="AF483" t="n">
-        <v>0.8379</v>
+        <v>0.6685800000000001</v>
       </c>
       <c r="AG483" t="n">
         <v>0.6821142857142857</v>
@@ -35913,7 +35913,7 @@
         <v>0.8381000000000002</v>
       </c>
       <c r="AF484" t="n">
-        <v>0.75573</v>
+        <v>0.7099555555555556</v>
       </c>
       <c r="AG484" t="n">
         <v>0.616275</v>
@@ -35963,7 +35963,7 @@
         <v>0.8558888888888889</v>
       </c>
       <c r="AF485" t="n">
-        <v>0.8803000000000001</v>
+        <v>0.6718428571428571</v>
       </c>
       <c r="AG485" t="n">
         <v>0.6479444444444445</v>
@@ -36013,7 +36013,7 @@
         <v>0.8108875</v>
       </c>
       <c r="AF486" t="n">
-        <v>0.79813</v>
+        <v>0.7307875</v>
       </c>
       <c r="AG486" t="n">
         <v>0.5654125</v>
@@ -36063,7 +36063,7 @@
         <v>0.7681888888888889</v>
       </c>
       <c r="AF487" t="n">
-        <v>0.87492</v>
+        <v>0.7039090909090909</v>
       </c>
       <c r="AG487" t="n">
         <v>0.6277888888888888</v>
@@ -36113,7 +36113,7 @@
         <v>0.7734599999999999</v>
       </c>
       <c r="AF488" t="n">
-        <v>0.838225</v>
+        <v>0.687911111111111</v>
       </c>
       <c r="AG488" t="n">
         <v>0.7060166666666667</v>
@@ -36163,7 +36163,7 @@
         <v>0.7183916666666667</v>
       </c>
       <c r="AF489" t="n">
-        <v>0.8140500000000001</v>
+        <v>0.6904222222222223</v>
       </c>
       <c r="AG489" t="n">
         <v>0.6575571428571428</v>
@@ -36213,7 +36213,7 @@
         <v>0.7553222222222223</v>
       </c>
       <c r="AF490" t="n">
-        <v>0.8540111111111112</v>
+        <v>0.7409111111111111</v>
       </c>
       <c r="AG490" t="n">
         <v>0.6117</v>
@@ -36260,7 +36260,7 @@
         <v>0.8608222222222222</v>
       </c>
       <c r="AF491" t="n">
-        <v>0.8558666666666666</v>
+        <v>0.720375</v>
       </c>
       <c r="AG491" t="n">
         <v>0.60181</v>
@@ -36310,7 +36310,7 @@
         <v>0.7385571428571429</v>
       </c>
       <c r="AF492" t="n">
-        <v>0.8560416666666667</v>
+        <v>0.7021375</v>
       </c>
       <c r="AG492" t="n">
         <v>0.6725333333333333</v>
@@ -36360,7 +36360,7 @@
         <v>0.7979700000000001</v>
       </c>
       <c r="AF493" t="n">
-        <v>0.861488888888889</v>
+        <v>0.7608375000000001</v>
       </c>
       <c r="AG493" t="n">
         <v>0.569925</v>
@@ -36410,7 +36410,7 @@
         <v>0.8495909090909091</v>
       </c>
       <c r="AF494" t="n">
-        <v>0.8537333333333333</v>
+        <v>0.7120555555555554</v>
       </c>
       <c r="AG494" t="n">
         <v>0.6724636363636363</v>
@@ -36460,7 +36460,7 @@
         <v>0.9012428571428571</v>
       </c>
       <c r="AF495" t="n">
-        <v>0.7909555555555555</v>
+        <v>0.71375</v>
       </c>
       <c r="AG495" t="n">
         <v>0.6555363636363636</v>
@@ -36510,7 +36510,7 @@
         <v>0.7677083333333333</v>
       </c>
       <c r="AF496" t="n">
-        <v>0.7771333333333333</v>
+        <v>0.6716444444444445</v>
       </c>
       <c r="AG496" t="n">
         <v>0.6922799999999999</v>
@@ -36560,7 +36560,7 @@
         <v>0.7753166666666668</v>
       </c>
       <c r="AF497" t="n">
-        <v>0.7729363636363636</v>
+        <v>0.76569</v>
       </c>
       <c r="AG497" t="n">
         <v>0.6037777777777777</v>
@@ -36610,7 +36610,7 @@
         <v>0.8414857142857143</v>
       </c>
       <c r="AF498" t="n">
-        <v>0.8871909090909091</v>
+        <v>0.7934000000000001</v>
       </c>
       <c r="AG498" t="n">
         <v>0.6193875000000001</v>
@@ -36660,7 +36660,7 @@
         <v>0.7575</v>
       </c>
       <c r="AF499" t="n">
-        <v>0.7679333333333334</v>
+        <v>0.7559777777777779</v>
       </c>
       <c r="AG499" t="n">
         <v>0.6744375</v>
@@ -36710,7 +36710,7 @@
         <v>0.8749272727272728</v>
       </c>
       <c r="AF500" t="n">
-        <v>0.852809090909091</v>
+        <v>0.7145</v>
       </c>
       <c r="AG500" t="n">
         <v>0.70008</v>
@@ -36760,7 +36760,7 @@
         <v>0.8337818181818182</v>
       </c>
       <c r="AF501" t="n">
-        <v>0.853925</v>
+        <v>0.7110000000000001</v>
       </c>
       <c r="AG501" t="n">
         <v>0.6196545454545456</v>
@@ -36810,7 +36810,7 @@
         <v>0.8487</v>
       </c>
       <c r="AF502" t="n">
-        <v>0.8632727272727273</v>
+        <v>0.68355</v>
       </c>
       <c r="AG502" t="n">
         <v>0.7309099999999999</v>
@@ -36860,7 +36860,7 @@
         <v>0.7620749999999999</v>
       </c>
       <c r="AF503" t="n">
-        <v>0.8147714285714286</v>
+        <v>0.7368428571428571</v>
       </c>
       <c r="AG503" t="n">
         <v>0.6705666666666666</v>
@@ -36910,7 +36910,7 @@
         <v>0.8278</v>
       </c>
       <c r="AF504" t="n">
-        <v>0.8250300000000002</v>
+        <v>0.7388666666666668</v>
       </c>
       <c r="AG504" t="n">
         <v>0.6718666666666667</v>
@@ -36960,7 +36960,7 @@
         <v>0.7441</v>
       </c>
       <c r="AF505" t="n">
-        <v>0.8677300000000001</v>
+        <v>0.7291909090909091</v>
       </c>
       <c r="AG505" t="n">
         <v>0.7518636363636362</v>
@@ -37010,7 +37010,7 @@
         <v>0.7855666666666666</v>
       </c>
       <c r="AF506" t="n">
-        <v>0.8842111111111112</v>
+        <v>0.6873600000000001</v>
       </c>
       <c r="AG506" t="n">
         <v>0.7943874999999999</v>
@@ -37060,7 +37060,7 @@
         <v>0.7847333333333332</v>
       </c>
       <c r="AF507" t="n">
-        <v>0.8440090909090909</v>
+        <v>0.8076571428571429</v>
       </c>
       <c r="AG507" t="n">
         <v>0.69035</v>
@@ -37110,7 +37110,7 @@
         <v>0.8195666666666668</v>
       </c>
       <c r="AF508" t="n">
-        <v>0.7984000000000001</v>
+        <v>0.762625</v>
       </c>
       <c r="AG508" t="n">
         <v>0.6579166666666666</v>
@@ -37160,7 +37160,7 @@
         <v>0.8851142857142857</v>
       </c>
       <c r="AF509" t="n">
-        <v>0.8212833333333333</v>
+        <v>0.6557363636363637</v>
       </c>
       <c r="AG509" t="n">
         <v>0.5816000000000001</v>
@@ -37210,7 +37210,7 @@
         <v>0.7951400000000001</v>
       </c>
       <c r="AF510" t="n">
-        <v>0.82751</v>
+        <v>0.7307666666666667</v>
       </c>
       <c r="AG510" t="n">
         <v>0.7370444444444444</v>
@@ -37260,7 +37260,7 @@
         <v>0.80325</v>
       </c>
       <c r="AF511" t="n">
-        <v>0.7893250000000001</v>
+        <v>0.7172714285714286</v>
       </c>
       <c r="AG511" t="n">
         <v>0.6631375</v>
@@ -37310,7 +37310,7 @@
         <v>0.8198555555555554</v>
       </c>
       <c r="AF512" t="n">
-        <v>0.8581727272727271</v>
+        <v>0.7119000000000001</v>
       </c>
       <c r="AG512" t="n">
         <v>0.6413454545454546</v>
@@ -37360,7 +37360,7 @@
         <v>0.8551571428571428</v>
       </c>
       <c r="AF513" t="n">
-        <v>0.7951555555555555</v>
+        <v>0.70216</v>
       </c>
       <c r="AG513" t="n">
         <v>0.6904888888888889</v>
@@ -37410,7 +37410,7 @@
         <v>0.8432222222222223</v>
       </c>
       <c r="AF514" t="n">
-        <v>0.7638400000000001</v>
+        <v>0.7360000000000001</v>
       </c>
       <c r="AG514" t="n">
         <v>0.6874714285714286</v>
@@ -37460,7 +37460,7 @@
         <v>0.7709111111111111</v>
       </c>
       <c r="AF515" t="n">
-        <v>0.8126333333333334</v>
+        <v>0.722577777777778</v>
       </c>
       <c r="AG515" t="n">
         <v>0.6931666666666666</v>
@@ -37510,7 +37510,7 @@
         <v>0.8068363636363636</v>
       </c>
       <c r="AF516" t="n">
-        <v>0.8659000000000001</v>
+        <v>0.703875</v>
       </c>
       <c r="AG516" t="n">
         <v>0.6112299999999999</v>
@@ -37560,7 +37560,7 @@
         <v>0.7667818181818181</v>
       </c>
       <c r="AF517" t="n">
-        <v>0.783588888888889</v>
+        <v>0.72719</v>
       </c>
       <c r="AG517" t="n">
         <v>0.6666818181818182</v>
@@ -37618,7 +37618,7 @@
         <v>0.1409777777777778</v>
       </c>
       <c r="AF520" t="n">
-        <v>0.136831506849315</v>
+        <v>0.09271029411764704</v>
       </c>
       <c r="AG520" t="n">
         <v>0.1444220588235294</v>
@@ -37662,7 +37662,7 @@
         <v>0.16495</v>
       </c>
       <c r="AF521" t="n">
-        <v>0.02614615384615384</v>
+        <v>0.2269</v>
       </c>
       <c r="AG521" t="n">
         <v>0.1429</v>
@@ -37706,7 +37706,7 @@
         <v>0.1847148148148148</v>
       </c>
       <c r="AF522" t="n">
-        <v>0.1229172413793103</v>
+        <v>0.2955076923076923</v>
       </c>
       <c r="AG522" t="n">
         <v>0.2835</v>
@@ -37750,7 +37750,7 @@
         <v>0.3985833333333333</v>
       </c>
       <c r="AF523" t="n">
-        <v>0.165432</v>
+        <v>0.3077892857142857</v>
       </c>
       <c r="AG523" t="n">
         <v>0.3022452380952381</v>
@@ -37794,7 +37794,7 @@
         <v>0.3459789473684211</v>
       </c>
       <c r="AF524" t="n">
-        <v>0.2831285714285715</v>
+        <v>0.3081952380952381</v>
       </c>
       <c r="AG524" t="n">
         <v>0.3887216216216217</v>
@@ -37838,7 +37838,7 @@
         <v>0.3869058823529412</v>
       </c>
       <c r="AF525" t="n">
-        <v>0.2694428571428572</v>
+        <v>0.35515</v>
       </c>
       <c r="AG525" t="n">
         <v>0.4646130434782609</v>
@@ -37882,7 +37882,7 @@
         <v>0.5496242424242423</v>
       </c>
       <c r="AF526" t="n">
-        <v>0.3458558823529412</v>
+        <v>0.3844571428571428</v>
       </c>
       <c r="AG526" t="n">
         <v>0.41598</v>
@@ -37926,7 +37926,7 @@
         <v>0.504332</v>
       </c>
       <c r="AF527" t="n">
-        <v>0.5026571428571428</v>
+        <v>0.4671076923076923</v>
       </c>
       <c r="AG527" t="n">
         <v>0.5046870967741935</v>
@@ -37970,7 +37970,7 @@
         <v>0.5666724137931035</v>
       </c>
       <c r="AF528" t="n">
-        <v>0.461745</v>
+        <v>0.4264857142857143</v>
       </c>
       <c r="AG528" t="n">
         <v>0.579425</v>
@@ -38014,7 +38014,7 @@
         <v>0.515228947368421</v>
       </c>
       <c r="AF529" t="n">
-        <v>0.493104347826087</v>
+        <v>0.4824560000000001</v>
       </c>
       <c r="AG529" t="n">
         <v>0.5007578947368421</v>
@@ -38049,7 +38049,7 @@
         <v>0.633141935483871</v>
       </c>
       <c r="AF530" t="n">
-        <v>0.5617090909090909</v>
+        <v>0.505825</v>
       </c>
       <c r="AG530" t="n">
         <v>0.5682999999999999</v>
@@ -38084,7 +38084,7 @@
         <v>0.5638625</v>
       </c>
       <c r="AF531" t="n">
-        <v>0.5871416666666667</v>
+        <v>0.515978787878788</v>
       </c>
       <c r="AG531" t="n">
         <v>0.4866378378378379</v>
@@ -38119,7 +38119,7 @@
         <v>0.5691249999999999</v>
       </c>
       <c r="AF532" t="n">
-        <v>0.7263055555555555</v>
+        <v>0.5913904761904761</v>
       </c>
       <c r="AG532" t="n">
         <v>0.3932771428571429</v>
@@ -38154,7 +38154,7 @@
         <v>0.5765804878048779</v>
       </c>
       <c r="AF533" t="n">
-        <v>0.6344974999999999</v>
+        <v>0.4756315789473685</v>
       </c>
       <c r="AG533" t="n">
         <v>0.5558023809523809</v>
@@ -38189,7 +38189,7 @@
         <v>0.6972346153846154</v>
       </c>
       <c r="AF534" t="n">
-        <v>0.7973315789473684</v>
+        <v>0.5617508474576272</v>
       </c>
       <c r="AG534" t="n">
         <v>0.6494636363636364</v>
@@ -38224,7 +38224,7 @@
         <v>0.7347864864864865</v>
       </c>
       <c r="AF535" t="n">
-        <v>0.7573774193548386</v>
+        <v>0.522462962962963</v>
       </c>
       <c r="AG535" t="n">
         <v>0.4816966666666668</v>
@@ -38259,7 +38259,7 @@
         <v>0.6253411764705883</v>
       </c>
       <c r="AF536" t="n">
-        <v>0.7032583333333333</v>
+        <v>0.5531326923076924</v>
       </c>
       <c r="AG536" t="n">
         <v>0.4411063829787234</v>
@@ -38294,7 +38294,7 @@
         <v>0.6301266666666667</v>
       </c>
       <c r="AF537" t="n">
-        <v>0.69116</v>
+        <v>0.5193473684210526</v>
       </c>
       <c r="AG537" t="n">
         <v>0.54195</v>
@@ -38329,7 +38329,7 @@
         <v>0.7928615384615385</v>
       </c>
       <c r="AF538" t="n">
-        <v>0.7289473684210527</v>
+        <v>0.4871146341463415</v>
       </c>
       <c r="AG538" t="n">
         <v>0.6228867647058824</v>
@@ -38364,7 +38364,7 @@
         <v>0.7814558139534883</v>
       </c>
       <c r="AF539" t="n">
-        <v>0.8590499999999999</v>
+        <v>0.4822359999999999</v>
       </c>
       <c r="AG539" t="n">
         <v>0.5045277777777778</v>
@@ -38399,7 +38399,7 @@
         <v>0.6841424999999999</v>
       </c>
       <c r="AF540" t="n">
-        <v>0.71055</v>
+        <v>0.6775771428571428</v>
       </c>
       <c r="AG540" t="n">
         <v>0.6734275000000001</v>
@@ -38434,7 +38434,7 @@
         <v>0.6000631578947369</v>
       </c>
       <c r="AF541" t="n">
-        <v>0.7131897435897435</v>
+        <v>0.5170784615384615</v>
       </c>
       <c r="AG541" t="n">
         <v>0.4816444444444445</v>
@@ -38469,7 +38469,7 @@
         <v>0.7363255319148937</v>
       </c>
       <c r="AF542" t="n">
-        <v>0.737990909090909</v>
+        <v>0.6747689655172413</v>
       </c>
       <c r="AG542" t="n">
         <v>0.5161395348837209</v>
@@ -38504,7 +38504,7 @@
         <v>0.7519740740740741</v>
       </c>
       <c r="AF543" t="n">
-        <v>0.6332833333333333</v>
+        <v>0.6066640000000001</v>
       </c>
       <c r="AG543" t="n">
         <v>0.4877159090909091</v>
@@ -38539,7 +38539,7 @@
         <v>0.68443</v>
       </c>
       <c r="AF544" t="n">
-        <v>0.7209125</v>
+        <v>0.5390875000000001</v>
       </c>
       <c r="AG544" t="n">
         <v>0.6173763157894737</v>
@@ -38574,7 +38574,7 @@
         <v>0.7553343749999999</v>
       </c>
       <c r="AF545" t="n">
-        <v>0.7447952380952381</v>
+        <v>0.5784195121951219</v>
       </c>
       <c r="AG545" t="n">
         <v>0.4667423076923077</v>
@@ -38609,7 +38609,7 @@
         <v>0.746855</v>
       </c>
       <c r="AF546" t="n">
-        <v>0.6713432432432432</v>
+        <v>0.53055</v>
       </c>
       <c r="AG546" t="n">
         <v>0.5142375</v>
@@ -38644,7 +38644,7 @@
         <v>0.6878399999999999</v>
       </c>
       <c r="AF547" t="n">
-        <v>0.61053125</v>
+        <v>0.688172340425532</v>
       </c>
       <c r="AG547" t="n">
         <v>0.4867585365853659</v>
@@ -38679,7 +38679,7 @@
         <v>0.703125</v>
       </c>
       <c r="AF548" t="n">
-        <v>0.6718214285714286</v>
+        <v>0.7637390243902439</v>
       </c>
       <c r="AG548" t="n">
         <v>0.5193512195121951</v>
@@ -38714,7 +38714,7 @@
         <v>0.6480318181818182</v>
       </c>
       <c r="AF549" t="n">
-        <v>0.814084</v>
+        <v>0.5896945945945946</v>
       </c>
       <c r="AG549" t="n">
         <v>0.5403441860465117</v>
@@ -38749,7 +38749,7 @@
         <v>0.7345029411764705</v>
       </c>
       <c r="AF550" t="n">
-        <v>0.5715625</v>
+        <v>0.5314666666666668</v>
       </c>
       <c r="AG550" t="n">
         <v>0.442425</v>
@@ -38784,7 +38784,7 @@
         <v>0.7372044444444444</v>
       </c>
       <c r="AF551" t="n">
-        <v>0.736153846153846</v>
+        <v>0.5198444444444443</v>
       </c>
       <c r="AG551" t="n">
         <v>0.499976923076923</v>
@@ -38819,7 +38819,7 @@
         <v>0.8470444444444445</v>
       </c>
       <c r="AF552" t="n">
-        <v>0.85438</v>
+        <v>0.6647923076923076</v>
       </c>
       <c r="AG552" t="n">
         <v>0.5988116666666666</v>
@@ -38854,7 +38854,7 @@
         <v>0.7875636363636364</v>
       </c>
       <c r="AF553" t="n">
-        <v>0.6457472222222221</v>
+        <v>0.6015377777777778</v>
       </c>
       <c r="AG553" t="n">
         <v>0.5693342857142857</v>
@@ -38889,7 +38889,7 @@
         <v>0.7744452380952382</v>
       </c>
       <c r="AF554" t="n">
-        <v>0.7196106382978723</v>
+        <v>0.6437911764705883</v>
       </c>
       <c r="AG554" t="n">
         <v>0.4613942307692307</v>
@@ -38924,7 +38924,7 @@
         <v>0.8044606060606062</v>
       </c>
       <c r="AF555" t="n">
-        <v>0.7562777777777777</v>
+        <v>0.7171111111111111</v>
       </c>
       <c r="AG555" t="n">
         <v>0.5178790697674418</v>
@@ -38959,7 +38959,7 @@
         <v>0.7770958333333334</v>
       </c>
       <c r="AF556" t="n">
-        <v>0.7659095238095238</v>
+        <v>0.5588411764705882</v>
       </c>
       <c r="AG556" t="n">
         <v>0.5133842105263158</v>
@@ -38994,7 +38994,7 @@
         <v>0.7485594594594595</v>
       </c>
       <c r="AF557" t="n">
-        <v>0.844675</v>
+        <v>0.5420320000000001</v>
       </c>
       <c r="AG557" t="n">
         <v>0.6144459459459459</v>
@@ -39029,7 +39029,7 @@
         <v>0.6971044444444445</v>
       </c>
       <c r="AF558" t="n">
-        <v>0.8064136363636364</v>
+        <v>0.6593375000000001</v>
       </c>
       <c r="AG558" t="n">
         <v>0.6063604651162789</v>
@@ -39064,7 +39064,7 @@
         <v>0.684585</v>
       </c>
       <c r="AF559" t="n">
-        <v>0.6768302325581396</v>
+        <v>0.7288735294117646</v>
       </c>
       <c r="AG559" t="n">
         <v>0.5964913043478262</v>
@@ -39099,7 +39099,7 @@
         <v>0.7710264705882351</v>
       </c>
       <c r="AF560" t="n">
-        <v>0.6789857142857143</v>
+        <v>0.6662875</v>
       </c>
       <c r="AG560" t="n">
         <v>0.4655409090909091</v>
@@ -39134,7 +39134,7 @@
         <v>0.7394885714285715</v>
       </c>
       <c r="AF561" t="n">
-        <v>0.7579411764705883</v>
+        <v>0.6439069767441861</v>
       </c>
       <c r="AG561" t="n">
         <v>0.5085512195121952</v>
@@ -39169,7 +39169,7 @@
         <v>0.7903105263157894</v>
       </c>
       <c r="AF562" t="n">
-        <v>0.7340083333333333</v>
+        <v>0.5752938775510203</v>
       </c>
       <c r="AG562" t="n">
         <v>0.5657425531914894</v>
@@ -39204,7 +39204,7 @@
         <v>0.7869628571428571</v>
       </c>
       <c r="AF563" t="n">
-        <v>0.7832630434782609</v>
+        <v>0.6547447368421053</v>
       </c>
       <c r="AG563" t="n">
         <v>0.5546979591836736</v>
@@ -39239,7 +39239,7 @@
         <v>0.6856972222222222</v>
       </c>
       <c r="AF564" t="n">
-        <v>0.6610627450980392</v>
+        <v>0.5952846153846153</v>
       </c>
       <c r="AG564" t="n">
         <v>0.5413347826086957</v>
@@ -39274,7 +39274,7 @@
         <v>0.6693722222222223</v>
       </c>
       <c r="AF565" t="n">
-        <v>0.8073222222222223</v>
+        <v>0.6559579999999999</v>
       </c>
       <c r="AG565" t="n">
         <v>0.6386893617021278</v>
@@ -39309,7 +39309,7 @@
         <v>0.7567666666666667</v>
       </c>
       <c r="AF566" t="n">
-        <v>0.770428</v>
+        <v>0.5904058823529411</v>
       </c>
       <c r="AG566" t="n">
         <v>0.5430470588235295</v>
@@ -39344,7 +39344,7 @@
         <v>0.7825666666666667</v>
       </c>
       <c r="AF567" t="n">
-        <v>0.8293692307692309</v>
+        <v>0.6746322580645161</v>
       </c>
       <c r="AG567" t="n">
         <v>0.6642942307692307</v>
@@ -39379,7 +39379,7 @@
         <v>0.7070041666666667</v>
       </c>
       <c r="AF568" t="n">
-        <v>0.7189634146341464</v>
+        <v>0.6218959183673468</v>
       </c>
       <c r="AG568" t="n">
         <v>0.5320285714285714</v>
@@ -39414,7 +39414,7 @@
         <v>0.7627861111111111</v>
       </c>
       <c r="AF569" t="n">
-        <v>0.8308378378378379</v>
+        <v>0.6945333333333334</v>
       </c>
       <c r="AG569" t="n">
         <v>0.6177075000000001</v>
@@ -39449,7 +39449,7 @@
         <v>0.8022387096774193</v>
       </c>
       <c r="AF570" t="n">
-        <v>0.7310076923076922</v>
+        <v>0.6131027777777778</v>
       </c>
       <c r="AG570" t="n">
         <v>0.5955615384615386</v>
@@ -39484,7 +39484,7 @@
         <v>0.7100853658536584</v>
       </c>
       <c r="AF571" t="n">
-        <v>0.7974440000000002</v>
+        <v>0.5981777777777778</v>
       </c>
       <c r="AG571" t="n">
         <v>0.5553441860465116</v>
@@ -39519,7 +39519,7 @@
         <v>0.7779638888888889</v>
       </c>
       <c r="AF572" t="n">
-        <v>0.8205107142857144</v>
+        <v>0.5134024390243904</v>
       </c>
       <c r="AG572" t="n">
         <v>0.4775645833333333</v>
@@ -39554,7 +39554,7 @@
         <v>0.7921697674418604</v>
       </c>
       <c r="AF573" t="n">
-        <v>0.7170222222222222</v>
+        <v>0.5509815789473684</v>
       </c>
       <c r="AG573" t="n">
         <v>0.4887617647058824</v>
@@ -39589,7 +39589,7 @@
         <v>0.7715212121212123</v>
       </c>
       <c r="AF574" t="n">
-        <v>0.7901172413793105</v>
+        <v>0.5951111111111111</v>
       </c>
       <c r="AG574" t="n">
         <v>0.5916138888888889</v>
@@ -39624,7 +39624,7 @@
         <v>0.7590916666666666</v>
       </c>
       <c r="AF575" t="n">
-        <v>0.8535115384615385</v>
+        <v>0.6182808510638298</v>
       </c>
       <c r="AG575" t="n">
         <v>0.5611488888888888</v>
@@ -39659,7 +39659,7 @@
         <v>0.7393531249999999</v>
       </c>
       <c r="AF576" t="n">
-        <v>0.7951052631578946</v>
+        <v>0.6673478260869565</v>
       </c>
       <c r="AG576" t="n">
         <v>0.5429072727272727</v>
@@ -39694,7 +39694,7 @@
         <v>0.7178054054054054</v>
       </c>
       <c r="AF577" t="n">
-        <v>0.714855</v>
+        <v>0.6079242424242425</v>
       </c>
       <c r="AG577" t="n">
         <v>0.6382439024390244</v>
@@ -39729,7 +39729,7 @@
         <v>0.7656941176470587</v>
       </c>
       <c r="AF578" t="n">
-        <v>0.8714857142857143</v>
+        <v>0.5568466666666667</v>
       </c>
       <c r="AG578" t="n">
         <v>0.6048185185185184</v>
@@ -39764,7 +39764,7 @@
         <v>0.7927666666666666</v>
       </c>
       <c r="AF579" t="n">
-        <v>0.8457357142857143</v>
+        <v>0.6483422222222223</v>
       </c>
       <c r="AG579" t="n">
         <v>0.5165086956521739</v>
@@ -39799,7 +39799,7 @@
         <v>0.647942857142857</v>
       </c>
       <c r="AF580" t="n">
-        <v>0.9195</v>
+        <v>0.7033914285714287</v>
       </c>
       <c r="AG580" t="n">
         <v>0.6554473684210527</v>
@@ -39834,7 +39834,7 @@
         <v>0.7226864864864865</v>
       </c>
       <c r="AF581" t="n">
-        <v>0.734874074074074</v>
+        <v>0.6762511627906976</v>
       </c>
       <c r="AG581" t="n">
         <v>0.61</v>
@@ -39869,7 +39869,7 @@
         <v>0.6328379310344827</v>
       </c>
       <c r="AF582" t="n">
-        <v>0.8707457142857143</v>
+        <v>0.76098</v>
       </c>
       <c r="AG582" t="n">
         <v>0.5082950000000001</v>
@@ -39904,7 +39904,7 @@
         <v>0.8009969696969697</v>
       </c>
       <c r="AF583" t="n">
-        <v>0.7515081081081081</v>
+        <v>0.5908757575757575</v>
       </c>
       <c r="AG583" t="n">
         <v>0.5488657142857143</v>
@@ -39939,7 +39939,7 @@
         <v>0.845920588235294</v>
       </c>
       <c r="AF584" t="n">
-        <v>0.8834705882352941</v>
+        <v>0.6519071428571428</v>
       </c>
       <c r="AG584" t="n">
         <v>0.4263096153846154</v>
@@ -39974,7 +39974,7 @@
         <v>0.6767216216216216</v>
       </c>
       <c r="AF585" t="n">
-        <v>0.8111781250000001</v>
+        <v>0.6854818181818181</v>
       </c>
       <c r="AG585" t="n">
         <v>0.542578</v>
@@ -40009,7 +40009,7 @@
         <v>0.8328636363636364</v>
       </c>
       <c r="AF586" t="n">
-        <v>0.8330000000000001</v>
+        <v>0.5532833333333333</v>
       </c>
       <c r="AG586" t="n">
         <v>0.6687906250000001</v>
@@ -40044,7 +40044,7 @@
         <v>0.7467864864864865</v>
       </c>
       <c r="AF587" t="n">
-        <v>0.6783750000000001</v>
+        <v>0.6112058823529412</v>
       </c>
       <c r="AG587" t="n">
         <v>0.5851883333333333</v>
@@ -40079,7 +40079,7 @@
         <v>0.7588148148148148</v>
       </c>
       <c r="AF588" t="n">
-        <v>0.893804347826087</v>
+        <v>0.549446511627907</v>
       </c>
       <c r="AG588" t="n">
         <v>0.5338622641509434</v>
@@ -40114,7 +40114,7 @@
         <v>0.6893111111111112</v>
       </c>
       <c r="AF589" t="n">
-        <v>0.968</v>
+        <v>0.5089073170731707</v>
       </c>
       <c r="AG589" t="n">
         <v>0.6660233333333333</v>
@@ -40149,7 +40149,7 @@
         <v>0.7934965517241379</v>
       </c>
       <c r="AF590" t="n">
-        <v>0.86465</v>
+        <v>0.5749883720930232</v>
       </c>
       <c r="AG590" t="n">
         <v>0.622885</v>
@@ -40184,7 +40184,7 @@
         <v>0.6970499999999999</v>
       </c>
       <c r="AF591" t="n">
-        <v>0.77676</v>
+        <v>0.59409</v>
       </c>
       <c r="AG591" t="n">
         <v>0.477947619047619</v>
@@ -40219,7 +40219,7 @@
         <v>0.7083263157894738</v>
       </c>
       <c r="AF592" t="n">
-        <v>0.7865782608695653</v>
+        <v>0.6903645161290322</v>
       </c>
       <c r="AG592" t="n">
         <v>0.4996968750000001</v>
@@ -40254,7 +40254,7 @@
         <v>0.6933194444444444</v>
       </c>
       <c r="AF593" t="n">
-        <v>0.7292272727272727</v>
+        <v>0.586853125</v>
       </c>
       <c r="AG593" t="n">
         <v>0.5798840000000002</v>
@@ -40289,7 +40289,7 @@
         <v>0.64825</v>
       </c>
       <c r="AF594" t="n">
-        <v>0.7837212121212122</v>
+        <v>0.7116055555555555</v>
       </c>
       <c r="AG594" t="n">
         <v>0.446626923076923</v>
@@ -40324,7 +40324,7 @@
         <v>0.7274636363636364</v>
       </c>
       <c r="AF595" t="n">
-        <v>0.8800653846153847</v>
+        <v>0.6357674418604652</v>
       </c>
       <c r="AG595" t="n">
         <v>0.5939585365853658</v>
@@ -40359,7 +40359,7 @@
         <v>0.7105781249999999</v>
       </c>
       <c r="AF596" t="n">
-        <v>0.7243535714285715</v>
+        <v>0.5699708333333333</v>
       </c>
       <c r="AG596" t="n">
         <v>0.6019325581395348</v>
@@ -40394,7 +40394,7 @@
         <v>0.6553857142857142</v>
       </c>
       <c r="AF597" t="n">
-        <v>0.6785035714285714</v>
+        <v>0.5887975609756096</v>
       </c>
       <c r="AG597" t="n">
         <v>0.5208736842105263</v>
@@ -40429,7 +40429,7 @@
         <v>0.780425</v>
       </c>
       <c r="AF598" t="n">
-        <v>0.9159333333333334</v>
+        <v>0.6133777777777777</v>
       </c>
       <c r="AG598" t="n">
         <v>0.4400714285714286</v>
@@ -40464,7 +40464,7 @@
         <v>0.8202</v>
       </c>
       <c r="AF599" t="n">
-        <v>0.8608500000000001</v>
+        <v>0.7008708333333334</v>
       </c>
       <c r="AG599" t="n">
         <v>0.4712206896551724</v>
@@ -40499,7 +40499,7 @@
         <v>0.7503111111111109</v>
       </c>
       <c r="AF600" t="n">
-        <v>0.7267305555555557</v>
+        <v>0.7054342857142858</v>
       </c>
       <c r="AG600" t="n">
         <v>0.6081968750000001</v>
@@ -40534,7 +40534,7 @@
         <v>0.8163709677419355</v>
       </c>
       <c r="AF601" t="n">
-        <v>0.9213650000000001</v>
+        <v>0.6908190476190477</v>
       </c>
       <c r="AG601" t="n">
         <v>0.4639152173913043</v>
@@ -40569,7 +40569,7 @@
         <v>0.7530135135135136</v>
       </c>
       <c r="AF602" t="n">
-        <v>0.8507416666666666</v>
+        <v>0.6233533333333334</v>
       </c>
       <c r="AG602" t="n">
         <v>0.6336108108108109</v>
@@ -40604,7 +40604,7 @@
         <v>0.7216</v>
       </c>
       <c r="AF603" t="n">
-        <v>0.7035791666666666</v>
+        <v>0.6619605263157894</v>
       </c>
       <c r="AG603" t="n">
         <v>0.46076</v>
@@ -40639,7 +40639,7 @@
         <v>0.6770939393939396</v>
       </c>
       <c r="AF604" t="n">
-        <v>0.6684433333333334</v>
+        <v>0.7052863636363637</v>
       </c>
       <c r="AG604" t="n">
         <v>0.6705846153846153</v>
@@ -40674,7 +40674,7 @@
         <v>0.7611307692307693</v>
       </c>
       <c r="AF605" t="n">
-        <v>0.6809564102564102</v>
+        <v>0.5884229166666667</v>
       </c>
       <c r="AG605" t="n">
         <v>0.6011774193548388</v>
@@ -40709,7 +40709,7 @@
         <v>0.7701256410256411</v>
       </c>
       <c r="AF606" t="n">
-        <v>0.89698125</v>
+        <v>0.5175733333333333</v>
       </c>
       <c r="AG606" t="n">
         <v>0.5838275000000001</v>
@@ -40744,7 +40744,7 @@
         <v>0.6821361111111111</v>
       </c>
       <c r="AF607" t="n">
-        <v>0.7692310344827586</v>
+        <v>0.6401740740740741</v>
       </c>
       <c r="AG607" t="n">
         <v>0.5910333333333333</v>
@@ -40779,7 +40779,7 @@
         <v>0.693939024390244</v>
       </c>
       <c r="AF608" t="n">
-        <v>0.826870588235294</v>
+        <v>0.6017536585365852</v>
       </c>
       <c r="AG608" t="n">
         <v>0.541629268292683</v>
@@ -40814,7 +40814,7 @@
         <v>0.7293433333333332</v>
       </c>
       <c r="AF609" t="n">
-        <v>0.6976925</v>
+        <v>0.5587136363636364</v>
       </c>
       <c r="AG609" t="n">
         <v>0.6393599999999999</v>
@@ -40849,7 +40849,7 @@
         <v>0.7142740740740742</v>
       </c>
       <c r="AF610" t="n">
-        <v>0.8650954545454546</v>
+        <v>0.5843684210526316</v>
       </c>
       <c r="AG610" t="n">
         <v>0.5253106382978723</v>
@@ -40884,7 +40884,7 @@
         <v>0.7648051282051282</v>
       </c>
       <c r="AF611" t="n">
-        <v>0.6639594594594594</v>
+        <v>0.5476088235294118</v>
       </c>
       <c r="AG611" t="n">
         <v>0.52815</v>
@@ -40919,7 +40919,7 @@
         <v>0.7327692307692308</v>
       </c>
       <c r="AF612" t="n">
-        <v>0.8358833333333333</v>
+        <v>0.6326857142857143</v>
       </c>
       <c r="AG612" t="n">
         <v>0.5162054054054054</v>
@@ -40954,7 +40954,7 @@
         <v>0.727274</v>
       </c>
       <c r="AF613" t="n">
-        <v>0.7622173913043477</v>
+        <v>0.6768555555555555</v>
       </c>
       <c r="AG613" t="n">
         <v>0.6759567567567568</v>
@@ -40989,7 +40989,7 @@
         <v>0.8466314285714285</v>
       </c>
       <c r="AF614" t="n">
-        <v>0.8382153846153847</v>
+        <v>0.6681384615384615</v>
       </c>
       <c r="AG614" t="n">
         <v>0.4732853658536585</v>
@@ -41024,7 +41024,7 @@
         <v>0.728475</v>
       </c>
       <c r="AF615" t="n">
-        <v>0.8087074074074073</v>
+        <v>0.6469694444444444</v>
       </c>
       <c r="AG615" t="n">
         <v>0.681017142857143</v>
@@ -41059,7 +41059,7 @@
         <v>0.7491272727272728</v>
       </c>
       <c r="AF616" t="n">
-        <v>0.8023727272727272</v>
+        <v>0.5806384615384615</v>
       </c>
       <c r="AG616" t="n">
         <v>0.5610877551020409</v>
@@ -41094,7 +41094,7 @@
         <v>0.7956783783783784</v>
       </c>
       <c r="AF617" t="n">
-        <v>0.652753488372093</v>
+        <v>0.5995257142857143</v>
       </c>
       <c r="AG617" t="n">
         <v>0.4817318181818181</v>
@@ -41129,7 +41129,7 @@
         <v>0.741693023255814</v>
       </c>
       <c r="AF618" t="n">
-        <v>0.7811695652173912</v>
+        <v>0.6805558139534884</v>
       </c>
       <c r="AG618" t="n">
         <v>0.631939393939394</v>
@@ -41164,7 +41164,7 @@
         <v>0.756125</v>
       </c>
       <c r="AF619" t="n">
-        <v>0.8658374999999999</v>
+        <v>0.6411065217391304</v>
       </c>
       <c r="AG619" t="n">
         <v>0.515921212121212</v>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI619"/>
+  <dimension ref="A1:AK619"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="14.33203125" customWidth="1" style="8" min="1" max="1"/>
@@ -778,6 +778,9 @@
       <c r="AI5" t="n">
         <v>0.1300313432835821</v>
       </c>
+      <c r="AK5" t="n">
+        <v>0.1076042857142857</v>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1" s="8">
       <c r="A6" s="5" t="n">
@@ -867,6 +870,9 @@
       <c r="AI6" t="n">
         <v>0.1945</v>
       </c>
+      <c r="AK6" t="n">
+        <v>0.3162</v>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1" s="8">
       <c r="A7" s="5" t="n">
@@ -956,6 +962,9 @@
       <c r="AI7" t="n">
         <v>0.2252636363636364</v>
       </c>
+      <c r="AK7" t="n">
+        <v>0.4410916666666667</v>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1" s="8">
       <c r="A8" s="5" t="n">
@@ -1045,6 +1054,9 @@
       <c r="AI8" t="n">
         <v>0.3551473684210526</v>
       </c>
+      <c r="AK8" t="n">
+        <v>0.26645</v>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1" s="8">
       <c r="A9" s="5" t="n">
@@ -1134,6 +1146,9 @@
       <c r="AI9" t="n">
         <v>0.4464521739130435</v>
       </c>
+      <c r="AK9" t="n">
+        <v>0.4295166666666667</v>
+      </c>
     </row>
     <row r="10" ht="16" customHeight="1" s="8">
       <c r="A10" s="5" t="n">
@@ -1223,6 +1238,9 @@
       <c r="AI10" t="n">
         <v>0.4737409090909091</v>
       </c>
+      <c r="AK10" t="n">
+        <v>0.4001428571428571</v>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1" s="8">
       <c r="A11" s="5" t="n">
@@ -1312,6 +1330,9 @@
       <c r="AI11" t="n">
         <v>0.5550304347826086</v>
       </c>
+      <c r="AK11" t="n">
+        <v>0.5890636363636365</v>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="8">
       <c r="A12" s="5" t="n">
@@ -1401,6 +1422,9 @@
       <c r="AI12" t="n">
         <v>0.5381</v>
       </c>
+      <c r="AK12" t="n">
+        <v>0.5923035714285714</v>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1" s="8">
       <c r="A13" s="5" t="n">
@@ -1490,6 +1514,9 @@
       <c r="AI13" t="n">
         <v>0.6533703703703705</v>
       </c>
+      <c r="AK13" t="n">
+        <v>0.6001526315789473</v>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="8">
       <c r="A14" s="5" t="n">
@@ -1579,6 +1606,9 @@
       <c r="AI14" t="n">
         <v>0.64605</v>
       </c>
+      <c r="AK14" t="n">
+        <v>0.6262190476190477</v>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="8">
       <c r="A15" s="5" t="n">
@@ -1659,6 +1689,9 @@
       <c r="AI15" t="n">
         <v>0.6991238095238095</v>
       </c>
+      <c r="AK15" t="n">
+        <v>0.730988888888889</v>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="8">
       <c r="A16" s="5" t="n">
@@ -1739,6 +1772,9 @@
       <c r="AI16" t="n">
         <v>0.7390000000000001</v>
       </c>
+      <c r="AK16" t="n">
+        <v>0.7302958333333334</v>
+      </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="8">
       <c r="A17" s="5" t="n">
@@ -1819,6 +1855,9 @@
       <c r="AI17" t="n">
         <v>0.7603636363636365</v>
       </c>
+      <c r="AK17" t="n">
+        <v>0.6901060606060606</v>
+      </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="8">
       <c r="A18" s="5" t="n">
@@ -1899,6 +1938,9 @@
       <c r="AI18" t="n">
         <v>0.81838</v>
       </c>
+      <c r="AK18" t="n">
+        <v>0.8058157894736842</v>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="8">
       <c r="A19" s="5" t="n">
@@ -1979,6 +2021,9 @@
       <c r="AI19" t="n">
         <v>0.8034599999999998</v>
       </c>
+      <c r="AK19" t="n">
+        <v>0.6688</v>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="8">
       <c r="A20" s="5" t="n">
@@ -2059,6 +2104,9 @@
       <c r="AI20" t="n">
         <v>0.6894499999999999</v>
       </c>
+      <c r="AK20" t="n">
+        <v>0.679668</v>
+      </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="8">
       <c r="A21" s="5" t="n">
@@ -2139,6 +2187,9 @@
       <c r="AI21" t="n">
         <v>0.7377157894736841</v>
       </c>
+      <c r="AK21" t="n">
+        <v>0.6233576923076924</v>
+      </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="8">
       <c r="A22" s="5" t="n">
@@ -2219,6 +2270,9 @@
       <c r="AI22" t="n">
         <v>0.3317</v>
       </c>
+      <c r="AK22" t="n">
+        <v>0.7100040000000001</v>
+      </c>
     </row>
     <row r="23" ht="16" customHeight="1" s="8">
       <c r="A23" s="5" t="n">
@@ -2299,6 +2353,9 @@
       <c r="AI23" t="n">
         <v>0.7929571428571428</v>
       </c>
+      <c r="AK23" t="n">
+        <v>0.6269258064516129</v>
+      </c>
     </row>
     <row r="24" ht="16" customHeight="1" s="8">
       <c r="A24" s="5" t="n">
@@ -2379,6 +2436,9 @@
       <c r="AI24" t="n">
         <v>0.7378400000000001</v>
       </c>
+      <c r="AK24" t="n">
+        <v>0.6684225806451614</v>
+      </c>
     </row>
     <row r="25" ht="16" customHeight="1" s="8">
       <c r="A25" s="5" t="n">
@@ -2459,6 +2519,9 @@
       <c r="AI25" t="n">
         <v>0.74299</v>
       </c>
+      <c r="AK25" t="n">
+        <v>0.7556035714285715</v>
+      </c>
     </row>
     <row r="26" ht="16" customHeight="1" s="8">
       <c r="A26" s="5" t="n">
@@ -2539,6 +2602,9 @@
       <c r="AI26" t="n">
         <v>0.8164666666666666</v>
       </c>
+      <c r="AK26" t="n">
+        <v>0.7703</v>
+      </c>
     </row>
     <row r="27" ht="16" customHeight="1" s="8">
       <c r="A27" s="5" t="n">
@@ -2619,6 +2685,9 @@
       <c r="AI27" t="n">
         <v>0.69924</v>
       </c>
+      <c r="AK27" t="n">
+        <v>0.7475999999999999</v>
+      </c>
     </row>
     <row r="28" ht="16" customHeight="1" s="8">
       <c r="A28" s="5" t="n">
@@ -2699,6 +2768,9 @@
       <c r="AI28" t="n">
         <v>0.7915764705882352</v>
       </c>
+      <c r="AK28" t="n">
+        <v>0.7310136363636363</v>
+      </c>
     </row>
     <row r="29" ht="16" customHeight="1" s="8">
       <c r="A29" s="5" t="n">
@@ -2779,6 +2851,9 @@
       <c r="AI29" t="n">
         <v>0.7888333333333333</v>
       </c>
+      <c r="AK29" t="n">
+        <v>0.7748511111111113</v>
+      </c>
     </row>
     <row r="30" ht="16" customHeight="1" s="8">
       <c r="A30" s="5" t="n">
@@ -2859,6 +2934,9 @@
       <c r="AI30" t="n">
         <v>0.7172551724137931</v>
       </c>
+      <c r="AK30" t="n">
+        <v>0.7331675000000001</v>
+      </c>
     </row>
     <row r="31" ht="16" customHeight="1" s="8">
       <c r="A31" s="5" t="n">
@@ -2939,6 +3017,9 @@
       <c r="AI31" t="n">
         <v>0.80762</v>
       </c>
+      <c r="AK31" t="n">
+        <v>0.7144923076923076</v>
+      </c>
     </row>
     <row r="32" ht="16" customHeight="1" s="8">
       <c r="A32" s="5" t="n">
@@ -3019,6 +3100,9 @@
       <c r="AI32" t="n">
         <v>0.7754629629629629</v>
       </c>
+      <c r="AK32" t="n">
+        <v>0.7305833333333334</v>
+      </c>
     </row>
     <row r="33" ht="16" customHeight="1" s="8">
       <c r="A33" s="5" t="n">
@@ -3099,6 +3183,9 @@
       <c r="AI33" t="n">
         <v>0.861742105263158</v>
       </c>
+      <c r="AK33" t="n">
+        <v>0.801578125</v>
+      </c>
     </row>
     <row r="34" ht="16" customHeight="1" s="8">
       <c r="A34" s="5" t="n">
@@ -3179,6 +3266,9 @@
       <c r="AI34" t="n">
         <v>0.8034428571428572</v>
       </c>
+      <c r="AK34" t="n">
+        <v>0.6722800000000001</v>
+      </c>
     </row>
     <row r="35" ht="16" customHeight="1" s="8">
       <c r="A35" s="5" t="n">
@@ -3259,6 +3349,9 @@
       <c r="AI35" t="n">
         <v>0.7826291666666667</v>
       </c>
+      <c r="AK35" t="n">
+        <v>0.7807580645161289</v>
+      </c>
     </row>
     <row r="36" ht="16" customHeight="1" s="8">
       <c r="A36" s="5" t="n">
@@ -3339,6 +3432,9 @@
       <c r="AI36" t="n">
         <v>0.8525666666666667</v>
       </c>
+      <c r="AK36" t="n">
+        <v>0.8938047619047619</v>
+      </c>
     </row>
     <row r="37" ht="16" customHeight="1" s="8">
       <c r="A37" s="5" t="n">
@@ -3419,6 +3515,9 @@
       <c r="AI37" t="n">
         <v>0.7153318181818181</v>
       </c>
+      <c r="AK37" t="n">
+        <v>0.7297782608695651</v>
+      </c>
     </row>
     <row r="38" ht="16" customHeight="1" s="8">
       <c r="A38" s="5" t="n">
@@ -3499,6 +3598,9 @@
       <c r="AI38" t="n">
         <v>0.648242857142857</v>
       </c>
+      <c r="AK38" t="n">
+        <v>0.729685</v>
+      </c>
     </row>
     <row r="39" ht="16" customHeight="1" s="8">
       <c r="A39" s="5" t="n">
@@ -3579,6 +3681,9 @@
       <c r="AI39" t="n">
         <v>0.7635384615384615</v>
       </c>
+      <c r="AK39" t="n">
+        <v>0.4983157894736842</v>
+      </c>
     </row>
     <row r="40" ht="16" customHeight="1" s="8">
       <c r="A40" s="5" t="n">
@@ -3659,6 +3764,9 @@
       <c r="AI40" t="n">
         <v>0.8502416666666667</v>
       </c>
+      <c r="AK40" t="n">
+        <v>0.7272853658536587</v>
+      </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="8">
       <c r="A41" s="5" t="n">
@@ -3739,6 +3847,9 @@
       <c r="AI41" t="n">
         <v>0.7248052631578947</v>
       </c>
+      <c r="AK41" t="n">
+        <v>0.721609090909091</v>
+      </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="8">
       <c r="A42" s="5" t="n">
@@ -3819,6 +3930,9 @@
       <c r="AI42" t="n">
         <v>0.8111619047619049</v>
       </c>
+      <c r="AK42" t="n">
+        <v>0.7616073170731706</v>
+      </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="8">
       <c r="A43" s="5" t="n">
@@ -3899,6 +4013,9 @@
       <c r="AI43" t="n">
         <v>0.9117714285714287</v>
       </c>
+      <c r="AK43" t="n">
+        <v>0.791764</v>
+      </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="8">
       <c r="A44" s="5" t="n">
@@ -3979,6 +4096,9 @@
       <c r="AI44" t="n">
         <v>0.8577357142857143</v>
       </c>
+      <c r="AK44" t="n">
+        <v>0.7365206896551724</v>
+      </c>
     </row>
     <row r="45" ht="16" customHeight="1" s="8">
       <c r="A45" s="5" t="n">
@@ -4059,6 +4179,9 @@
       <c r="AI45" t="n">
         <v>0.7950076923076922</v>
       </c>
+      <c r="AK45" t="n">
+        <v>0.735924</v>
+      </c>
     </row>
     <row r="46" ht="16" customHeight="1" s="8">
       <c r="A46" s="5" t="n">
@@ -4139,6 +4262,9 @@
       <c r="AI46" t="n">
         <v>0.8558136363636364</v>
       </c>
+      <c r="AK46" t="n">
+        <v>0.7898666666666667</v>
+      </c>
     </row>
     <row r="47" ht="16" customHeight="1" s="8">
       <c r="A47" s="5" t="n">
@@ -4219,6 +4345,9 @@
       <c r="AI47" t="n">
         <v>0.7612833333333332</v>
       </c>
+      <c r="AK47" t="n">
+        <v>0.686258064516129</v>
+      </c>
     </row>
     <row r="48" ht="16" customHeight="1" s="8">
       <c r="A48" s="5" t="n">
@@ -4299,6 +4428,9 @@
       <c r="AI48" t="n">
         <v>0.7560608695652175</v>
       </c>
+      <c r="AK48" t="n">
+        <v>0.7090642857142857</v>
+      </c>
     </row>
     <row r="49" ht="16" customHeight="1" s="8">
       <c r="A49" s="5" t="n">
@@ -4379,6 +4511,9 @@
       <c r="AI49" t="n">
         <v>0.7343642857142857</v>
       </c>
+      <c r="AK49" t="n">
+        <v>0.7792814814814814</v>
+      </c>
     </row>
     <row r="50" ht="16" customHeight="1" s="8">
       <c r="A50" s="5" t="n">
@@ -4459,6 +4594,9 @@
       <c r="AI50" t="n">
         <v>0.8132285714285714</v>
       </c>
+      <c r="AK50" t="n">
+        <v>0.7479083333333333</v>
+      </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="8">
       <c r="A51" s="5" t="n">
@@ -4539,6 +4677,9 @@
       <c r="AI51" t="n">
         <v>0.8495578947368422</v>
       </c>
+      <c r="AK51" t="n">
+        <v>0.826735294117647</v>
+      </c>
     </row>
     <row r="52" ht="16" customHeight="1" s="8">
       <c r="A52" s="5" t="n">
@@ -4619,6 +4760,9 @@
       <c r="AI52" t="n">
         <v>0.8635695652173914</v>
       </c>
+      <c r="AK52" t="n">
+        <v>0.8034413793103449</v>
+      </c>
     </row>
     <row r="53" ht="16" customHeight="1" s="8">
       <c r="A53" s="5" t="n">
@@ -4699,6 +4843,9 @@
       <c r="AI53" t="n">
         <v>0.8532714285714286</v>
       </c>
+      <c r="AK53" t="n">
+        <v>0.7177458333333333</v>
+      </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="8">
       <c r="A54" s="5" t="n">
@@ -4779,6 +4926,9 @@
       <c r="AI54" t="n">
         <v>0.7911</v>
       </c>
+      <c r="AK54" t="n">
+        <v>0.7923249999999999</v>
+      </c>
     </row>
     <row r="55" ht="16" customHeight="1" s="8">
       <c r="A55" s="5" t="n">
@@ -4859,6 +5009,9 @@
       <c r="AI55" t="n">
         <v>0.82185</v>
       </c>
+      <c r="AK55" t="n">
+        <v>0.775551282051282</v>
+      </c>
     </row>
     <row r="56" ht="16" customHeight="1" s="8">
       <c r="A56" s="5" t="n">
@@ -4939,6 +5092,9 @@
       <c r="AI56" t="n">
         <v>0.7447764705882354</v>
       </c>
+      <c r="AK56" t="n">
+        <v>0.754015625</v>
+      </c>
     </row>
     <row r="57" ht="16" customHeight="1" s="8">
       <c r="A57" s="5" t="n">
@@ -5019,6 +5175,9 @@
       <c r="AI57" t="n">
         <v>0.7757166666666667</v>
       </c>
+      <c r="AK57" t="n">
+        <v>0.7059259259259258</v>
+      </c>
     </row>
     <row r="58" ht="16" customHeight="1" s="8">
       <c r="A58" s="5" t="n">
@@ -5099,6 +5258,9 @@
       <c r="AI58" t="n">
         <v>0.8056529411764707</v>
       </c>
+      <c r="AK58" t="n">
+        <v>0.7525571428571428</v>
+      </c>
     </row>
     <row r="59" ht="16" customHeight="1" s="8">
       <c r="A59" s="5" t="n">
@@ -5179,6 +5341,9 @@
       <c r="AI59" t="n">
         <v>0.8226588235294118</v>
       </c>
+      <c r="AK59" t="n">
+        <v>0.8449352941176471</v>
+      </c>
     </row>
     <row r="60" ht="16" customHeight="1" s="8">
       <c r="A60" s="5" t="n">
@@ -5259,6 +5424,9 @@
       <c r="AI60" t="n">
         <v>0.74572</v>
       </c>
+      <c r="AK60" t="n">
+        <v>0.8321055555555557</v>
+      </c>
     </row>
     <row r="61" ht="16" customHeight="1" s="8">
       <c r="A61" s="5" t="n">
@@ -5339,6 +5507,9 @@
       <c r="AI61" t="n">
         <v>0.7422347826086957</v>
       </c>
+      <c r="AK61" t="n">
+        <v>0.7114888888888888</v>
+      </c>
     </row>
     <row r="62" ht="16" customHeight="1" s="8">
       <c r="A62" s="5" t="n">
@@ -5419,6 +5590,9 @@
       <c r="AI62" t="n">
         <v>0.9042545454545454</v>
       </c>
+      <c r="AK62" t="n">
+        <v>0.805626923076923</v>
+      </c>
     </row>
     <row r="63" ht="16" customHeight="1" s="8">
       <c r="A63" s="5" t="n">
@@ -5499,6 +5673,9 @@
       <c r="AI63" t="n">
         <v>0.8332333333333333</v>
       </c>
+      <c r="AK63" t="n">
+        <v>0.7705181818181819</v>
+      </c>
     </row>
     <row r="64" ht="16" customHeight="1" s="8">
       <c r="A64" s="5" t="n">
@@ -5579,6 +5756,9 @@
       <c r="AI64" t="n">
         <v>0.89825</v>
       </c>
+      <c r="AK64" t="n">
+        <v>0.7391384615384615</v>
+      </c>
     </row>
     <row r="65" ht="16" customHeight="1" s="8">
       <c r="A65" s="5" t="n">
@@ -5659,6 +5839,9 @@
       <c r="AI65" t="n">
         <v>0.8747909090909091</v>
       </c>
+      <c r="AK65" t="n">
+        <v>0.7253972222222224</v>
+      </c>
     </row>
     <row r="66" ht="16" customHeight="1" s="8">
       <c r="A66" s="5" t="n">
@@ -5739,6 +5922,9 @@
       <c r="AI66" t="n">
         <v>0.8047294117647058</v>
       </c>
+      <c r="AK66" t="n">
+        <v>0.7957</v>
+      </c>
     </row>
     <row r="67" ht="16" customHeight="1" s="8">
       <c r="A67" s="5" t="n">
@@ -5819,6 +6005,9 @@
       <c r="AI67" t="n">
         <v>0.8612222222222222</v>
       </c>
+      <c r="AK67" t="n">
+        <v>0.7579310344827586</v>
+      </c>
     </row>
     <row r="68" ht="16" customHeight="1" s="8">
       <c r="A68" s="5" t="n">
@@ -5899,6 +6088,9 @@
       <c r="AI68" t="n">
         <v>0.8662904761904762</v>
       </c>
+      <c r="AK68" t="n">
+        <v>0.8633625</v>
+      </c>
     </row>
     <row r="69" ht="16" customHeight="1" s="8">
       <c r="A69" s="5" t="n">
@@ -5979,6 +6171,9 @@
       <c r="AI69" t="n">
         <v>0.830925</v>
       </c>
+      <c r="AK69" t="n">
+        <v>0.7835000000000001</v>
+      </c>
     </row>
     <row r="70" ht="16" customHeight="1" s="8">
       <c r="A70" s="5" t="n">
@@ -6059,6 +6254,9 @@
       <c r="AI70" t="n">
         <v>0.8072952380952382</v>
       </c>
+      <c r="AK70" t="n">
+        <v>0.72416875</v>
+      </c>
     </row>
     <row r="71" ht="16" customHeight="1" s="8">
       <c r="A71" s="5" t="n">
@@ -6139,6 +6337,9 @@
       <c r="AI71" t="n">
         <v>0.8981545454545454</v>
       </c>
+      <c r="AK71" t="n">
+        <v>0.7145826086956523</v>
+      </c>
     </row>
     <row r="72" ht="16" customHeight="1" s="8">
       <c r="A72" s="5" t="n">
@@ -6219,6 +6420,9 @@
       <c r="AI72" t="n">
         <v>0.8337</v>
       </c>
+      <c r="AK72" t="n">
+        <v>0.6706642857142857</v>
+      </c>
     </row>
     <row r="73" ht="16" customHeight="1" s="8">
       <c r="A73" s="5" t="n">
@@ -6299,6 +6503,9 @@
       <c r="AI73" t="n">
         <v>0.8648571428571429</v>
       </c>
+      <c r="AK73" t="n">
+        <v>0.8174600000000001</v>
+      </c>
     </row>
     <row r="74" ht="16" customHeight="1" s="8">
       <c r="A74" s="5" t="n">
@@ -6379,6 +6586,9 @@
       <c r="AI74" t="n">
         <v>0.8498</v>
       </c>
+      <c r="AK74" t="n">
+        <v>0.8018326530612245</v>
+      </c>
     </row>
     <row r="75" ht="16" customHeight="1" s="8">
       <c r="A75" s="5" t="n">
@@ -6459,6 +6669,9 @@
       <c r="AI75" t="n">
         <v>0.8002600000000001</v>
       </c>
+      <c r="AK75" t="n">
+        <v>0.7108098039215687</v>
+      </c>
     </row>
     <row r="76" ht="16" customHeight="1" s="8">
       <c r="A76" s="5" t="n">
@@ -6539,6 +6752,9 @@
       <c r="AI76" t="n">
         <v>0.7300083333333335</v>
       </c>
+      <c r="AK76" t="n">
+        <v>0.8203848484848485</v>
+      </c>
     </row>
     <row r="77" ht="16" customHeight="1" s="8">
       <c r="A77" s="5" t="n">
@@ -6619,6 +6835,9 @@
       <c r="AI77" t="n">
         <v>0.79581875</v>
       </c>
+      <c r="AK77" t="n">
+        <v>0.6724558823529412</v>
+      </c>
     </row>
     <row r="78" ht="16" customHeight="1" s="8">
       <c r="A78" s="5" t="n">
@@ -6699,6 +6918,9 @@
       <c r="AI78" t="n">
         <v>0.8825818181818181</v>
       </c>
+      <c r="AK78" t="n">
+        <v>0.772625</v>
+      </c>
     </row>
     <row r="79" ht="16" customHeight="1" s="8">
       <c r="A79" s="5" t="n">
@@ -6779,6 +7001,9 @@
       <c r="AI79" t="n">
         <v>0.7831111111111112</v>
       </c>
+      <c r="AK79" t="n">
+        <v>0.6749999999999999</v>
+      </c>
     </row>
     <row r="80" ht="16" customHeight="1" s="8">
       <c r="A80" s="5" t="n">
@@ -6859,6 +7084,9 @@
       <c r="AI80" t="n">
         <v>0.7742857142857144</v>
       </c>
+      <c r="AK80" t="n">
+        <v>0.7852472222222221</v>
+      </c>
     </row>
     <row r="81" ht="16" customHeight="1" s="8">
       <c r="A81" s="5" t="n">
@@ -6939,6 +7167,9 @@
       <c r="AI81" t="n">
         <v>0.7648411764705882</v>
       </c>
+      <c r="AK81" t="n">
+        <v>0.7730242424242424</v>
+      </c>
     </row>
     <row r="82" ht="16" customHeight="1" s="8">
       <c r="A82" s="5" t="n">
@@ -7019,6 +7250,9 @@
       <c r="AI82" t="n">
         <v>0.82875</v>
       </c>
+      <c r="AK82" t="n">
+        <v>0.778074074074074</v>
+      </c>
     </row>
     <row r="83" ht="16" customHeight="1" s="8">
       <c r="A83" s="5" t="n">
@@ -7099,6 +7333,9 @@
       <c r="AI83" t="n">
         <v>0.7655000000000001</v>
       </c>
+      <c r="AK83" t="n">
+        <v>0.779445238095238</v>
+      </c>
     </row>
     <row r="84" ht="16" customHeight="1" s="8">
       <c r="A84" s="5" t="n">
@@ -7179,6 +7416,9 @@
       <c r="AI84" t="n">
         <v>0.8789187500000001</v>
       </c>
+      <c r="AK84" t="n">
+        <v>0.8345975000000001</v>
+      </c>
     </row>
     <row r="85" ht="16" customHeight="1" s="8">
       <c r="A85" s="5" t="n">
@@ -7259,6 +7499,9 @@
       <c r="AI85" t="n">
         <v>0.8657625000000001</v>
       </c>
+      <c r="AK85" t="n">
+        <v>0.8136054054054053</v>
+      </c>
     </row>
     <row r="86" ht="16" customHeight="1" s="8">
       <c r="A86" s="5" t="n">
@@ -7339,6 +7582,9 @@
       <c r="AI86" t="n">
         <v>0.7613666666666666</v>
       </c>
+      <c r="AK86" t="n">
+        <v>0.7687878787878787</v>
+      </c>
     </row>
     <row r="87" ht="16" customHeight="1" s="8">
       <c r="A87" s="5" t="n">
@@ -7419,6 +7665,9 @@
       <c r="AI87" t="n">
         <v>0.7791842105263158</v>
       </c>
+      <c r="AK87" t="n">
+        <v>0.7309857142857145</v>
+      </c>
     </row>
     <row r="88" ht="16" customHeight="1" s="8">
       <c r="A88" s="5" t="n">
@@ -7499,6 +7748,9 @@
       <c r="AI88" t="n">
         <v>0.801004761904762</v>
       </c>
+      <c r="AK88" t="n">
+        <v>0.7019410256410256</v>
+      </c>
     </row>
     <row r="89" ht="16" customHeight="1" s="8">
       <c r="A89" s="5" t="n">
@@ -7579,6 +7831,9 @@
       <c r="AI89" t="n">
         <v>0.8487666666666667</v>
       </c>
+      <c r="AK89" t="n">
+        <v>0.7019606060606061</v>
+      </c>
     </row>
     <row r="90" ht="16" customHeight="1" s="8">
       <c r="A90" s="5" t="n">
@@ -7659,6 +7914,9 @@
       <c r="AI90" t="n">
         <v>0.8916153846153846</v>
       </c>
+      <c r="AK90" t="n">
+        <v>0.7504681818181819</v>
+      </c>
     </row>
     <row r="91" ht="16" customHeight="1" s="8">
       <c r="A91" s="5" t="n">
@@ -7739,6 +7997,9 @@
       <c r="AI91" t="n">
         <v>0.7642</v>
       </c>
+      <c r="AK91" t="n">
+        <v>0.7130521739130435</v>
+      </c>
     </row>
     <row r="92" ht="16" customHeight="1" s="8">
       <c r="A92" s="5" t="n">
@@ -7819,6 +8080,9 @@
       <c r="AI92" t="n">
         <v>0.8095</v>
       </c>
+      <c r="AK92" t="n">
+        <v>0.6936685714285715</v>
+      </c>
     </row>
     <row r="93" ht="16" customHeight="1" s="8">
       <c r="A93" s="5" t="n">
@@ -7899,6 +8163,9 @@
       <c r="AI93" t="n">
         <v>0.8826357142857143</v>
       </c>
+      <c r="AK93" t="n">
+        <v>0.8333793103448277</v>
+      </c>
     </row>
     <row r="94" ht="16" customHeight="1" s="8">
       <c r="A94" s="5" t="n">
@@ -7979,6 +8246,9 @@
       <c r="AI94" t="n">
         <v>0.838004761904762</v>
       </c>
+      <c r="AK94" t="n">
+        <v>0.7823138888888889</v>
+      </c>
     </row>
     <row r="95" ht="16" customHeight="1" s="8">
       <c r="A95" s="5" t="n">
@@ -8059,6 +8329,9 @@
       <c r="AI95" t="n">
         <v>0.7770615384615385</v>
       </c>
+      <c r="AK95" t="n">
+        <v>0.8426967741935483</v>
+      </c>
     </row>
     <row r="96" ht="16" customHeight="1" s="8">
       <c r="A96" s="5" t="n">
@@ -8139,6 +8412,9 @@
       <c r="AI96" t="n">
         <v>0.8062428571428571</v>
       </c>
+      <c r="AK96" t="n">
+        <v>0.849252</v>
+      </c>
     </row>
     <row r="97" ht="16" customHeight="1" s="8">
       <c r="A97" s="5" t="n">
@@ -8219,6 +8495,9 @@
       <c r="AI97" t="n">
         <v>0.8111068965517242</v>
       </c>
+      <c r="AK97" t="n">
+        <v>0.7201833333333334</v>
+      </c>
     </row>
     <row r="98" ht="16" customHeight="1" s="8">
       <c r="A98" s="5" t="n">
@@ -8299,6 +8578,9 @@
       <c r="AI98" t="n">
         <v>0.8417523809523809</v>
       </c>
+      <c r="AK98" t="n">
+        <v>0.8378731707317072</v>
+      </c>
     </row>
     <row r="99" ht="16" customHeight="1" s="8">
       <c r="A99" s="5" t="n">
@@ -8379,6 +8661,9 @@
       <c r="AI99" t="n">
         <v>0.8653090909090909</v>
       </c>
+      <c r="AK99" t="n">
+        <v>0.8208909090909091</v>
+      </c>
     </row>
     <row r="100" ht="16" customHeight="1" s="8">
       <c r="A100" s="5" t="n">
@@ -8459,6 +8744,9 @@
       <c r="AI100" t="n">
         <v>0.8858357142857144</v>
       </c>
+      <c r="AK100" t="n">
+        <v>0.7361451612903227</v>
+      </c>
     </row>
     <row r="101" ht="16" customHeight="1" s="8">
       <c r="A101" s="5" t="n">
@@ -8539,6 +8827,9 @@
       <c r="AI101" t="n">
         <v>0.8938117647058824</v>
       </c>
+      <c r="AK101" t="n">
+        <v>0.7283241379310346</v>
+      </c>
     </row>
     <row r="102" ht="16" customHeight="1" s="8">
       <c r="A102" s="5" t="n">
@@ -8619,6 +8910,9 @@
       <c r="AI102" t="n">
         <v>0.8413999999999999</v>
       </c>
+      <c r="AK102" t="n">
+        <v>0.753552380952381</v>
+      </c>
     </row>
     <row r="103" ht="16" customHeight="1" s="8">
       <c r="A103" s="5" t="n">
@@ -8699,6 +8993,9 @@
       <c r="AI103" t="n">
         <v>0.8463416666666667</v>
       </c>
+      <c r="AK103" t="n">
+        <v>0.8401074074074074</v>
+      </c>
     </row>
     <row r="104" ht="16" customHeight="1" s="8">
       <c r="A104" s="5" t="n">
@@ -8778,6 +9075,9 @@
       </c>
       <c r="AI104" t="n">
         <v>0.851348</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>0.7382137931034483</v>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1" s="8">
@@ -8892,6 +9192,9 @@
       <c r="AI108" t="n">
         <v>1</v>
       </c>
+      <c r="AK108" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="109" ht="16" customHeight="1" s="8">
       <c r="A109" s="5" t="n">
@@ -8981,6 +9284,9 @@
       <c r="AI109" t="n">
         <v>0.8</v>
       </c>
+      <c r="AK109" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="110" ht="16" customHeight="1" s="8">
       <c r="A110" s="5" t="n">
@@ -9070,6 +9376,9 @@
       <c r="AI110" t="n">
         <v>0.8461538461538461</v>
       </c>
+      <c r="AK110" t="n">
+        <v>0.6363636363636364</v>
+      </c>
     </row>
     <row r="111" ht="16" customHeight="1" s="8">
       <c r="A111" s="5" t="n">
@@ -9159,6 +9468,9 @@
       <c r="AI111" t="n">
         <v>1</v>
       </c>
+      <c r="AK111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112" ht="16" customHeight="1" s="8">
       <c r="A112" s="5" t="n">
@@ -9248,6 +9560,9 @@
       <c r="AI112" t="n">
         <v>0.75</v>
       </c>
+      <c r="AK112" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="113" ht="16" customHeight="1" s="8">
       <c r="A113" s="5" t="n">
@@ -9337,6 +9652,9 @@
       <c r="AI113" t="n">
         <v>1</v>
       </c>
+      <c r="AK113" t="n">
+        <v>0.6363636363636364</v>
+      </c>
     </row>
     <row r="114" ht="16" customHeight="1" s="8">
       <c r="A114" s="5" t="n">
@@ -9426,6 +9744,9 @@
       <c r="AI114" t="n">
         <v>1</v>
       </c>
+      <c r="AK114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115" ht="16" customHeight="1" s="8">
       <c r="A115" s="5" t="n">
@@ -9515,6 +9836,9 @@
       <c r="AI115" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AK115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116" ht="16" customHeight="1" s="8">
       <c r="A116" s="5" t="n">
@@ -9604,6 +9928,9 @@
       <c r="AI116" t="n">
         <v>1</v>
       </c>
+      <c r="AK116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117" ht="16" customHeight="1" s="8">
       <c r="A117" s="5" t="n">
@@ -9693,6 +10020,9 @@
       <c r="AI117" t="n">
         <v>1</v>
       </c>
+      <c r="AK117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118" ht="16" customHeight="1" s="8">
       <c r="A118" s="5" t="n">
@@ -9770,6 +10100,9 @@
       <c r="AI118" t="n">
         <v>1</v>
       </c>
+      <c r="AK118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119" ht="16" customHeight="1" s="8">
       <c r="A119" s="5" t="n">
@@ -9850,6 +10183,9 @@
       <c r="AI119" t="n">
         <v>1</v>
       </c>
+      <c r="AK119" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="120" ht="16" customHeight="1" s="8">
       <c r="A120" s="5" t="n">
@@ -9930,6 +10266,9 @@
       <c r="AI120" t="n">
         <v>1</v>
       </c>
+      <c r="AK120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121" ht="16" customHeight="1" s="8">
       <c r="A121" s="5" t="n">
@@ -10010,6 +10349,9 @@
       <c r="AI121" t="n">
         <v>1</v>
       </c>
+      <c r="AK121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122" ht="16" customHeight="1" s="8">
       <c r="A122" s="5" t="n">
@@ -10090,6 +10432,9 @@
       <c r="AI122" t="n">
         <v>1</v>
       </c>
+      <c r="AK122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123" ht="16" customHeight="1" s="8">
       <c r="A123" s="5" t="n">
@@ -10170,6 +10515,9 @@
       <c r="AI123" t="n">
         <v>1</v>
       </c>
+      <c r="AK123" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="124" ht="16" customHeight="1" s="8">
       <c r="A124" s="5" t="n">
@@ -10250,6 +10598,9 @@
       <c r="AI124" t="n">
         <v>1</v>
       </c>
+      <c r="AK124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125" ht="16" customHeight="1" s="8">
       <c r="A125" s="5" t="n">
@@ -10330,6 +10681,9 @@
       <c r="AI125" t="n">
         <v>1</v>
       </c>
+      <c r="AK125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126" ht="16" customHeight="1" s="8">
       <c r="A126" s="5" t="n">
@@ -10410,6 +10764,9 @@
       <c r="AI126" t="n">
         <v>1</v>
       </c>
+      <c r="AK126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127" ht="16" customHeight="1" s="8">
       <c r="A127" s="5" t="n">
@@ -10487,6 +10844,9 @@
       <c r="AH127" t="n">
         <v>1</v>
       </c>
+      <c r="AK127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128" ht="16" customHeight="1" s="8">
       <c r="A128" s="5" t="n">
@@ -10567,6 +10927,9 @@
       <c r="AI128" t="n">
         <v>1</v>
       </c>
+      <c r="AK128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129" ht="16" customHeight="1" s="8">
       <c r="A129" s="5" t="n">
@@ -10647,6 +11010,9 @@
       <c r="AI129" t="n">
         <v>1</v>
       </c>
+      <c r="AK129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130" ht="16" customHeight="1" s="8">
       <c r="A130" s="5" t="n">
@@ -10727,6 +11093,9 @@
       <c r="AI130" t="n">
         <v>1</v>
       </c>
+      <c r="AK130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131" ht="16" customHeight="1" s="8">
       <c r="A131" s="5" t="n">
@@ -10807,6 +11176,9 @@
       <c r="AI131" t="n">
         <v>1</v>
       </c>
+      <c r="AK131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132" ht="16" customHeight="1" s="8">
       <c r="A132" s="5" t="n">
@@ -10887,6 +11259,9 @@
       <c r="AI132" t="n">
         <v>1</v>
       </c>
+      <c r="AK132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133" ht="16" customHeight="1" s="8">
       <c r="A133" s="5" t="n">
@@ -10967,6 +11342,9 @@
       <c r="AI133" t="n">
         <v>1</v>
       </c>
+      <c r="AK133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134" ht="16" customHeight="1" s="8">
       <c r="A134" s="5" t="n">
@@ -11047,6 +11425,9 @@
       <c r="AI134" t="n">
         <v>1</v>
       </c>
+      <c r="AK134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135" ht="16" customHeight="1" s="8">
       <c r="A135" s="5" t="n">
@@ -11127,6 +11508,9 @@
       <c r="AI135" t="n">
         <v>1</v>
       </c>
+      <c r="AK135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136" ht="16" customHeight="1" s="8">
       <c r="A136" s="5" t="n">
@@ -11207,6 +11591,9 @@
       <c r="AI136" t="n">
         <v>1</v>
       </c>
+      <c r="AK136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137" ht="16" customHeight="1" s="8">
       <c r="A137" s="5" t="n">
@@ -11287,6 +11674,9 @@
       <c r="AI137" t="n">
         <v>1</v>
       </c>
+      <c r="AK137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138" ht="16" customHeight="1" s="8">
       <c r="A138" s="5" t="n">
@@ -11367,6 +11757,9 @@
       <c r="AI138" t="n">
         <v>1</v>
       </c>
+      <c r="AK138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139" ht="16" customHeight="1" s="8">
       <c r="A139" s="5" t="n">
@@ -11447,6 +11840,9 @@
       <c r="AI139" t="n">
         <v>1</v>
       </c>
+      <c r="AK139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140" ht="16" customHeight="1" s="8">
       <c r="A140" s="5" t="n">
@@ -11524,6 +11920,9 @@
       <c r="AI140" t="n">
         <v>1</v>
       </c>
+      <c r="AK140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141" ht="16" customHeight="1" s="8">
       <c r="A141" s="5" t="n">
@@ -11604,6 +12003,9 @@
       <c r="AI141" t="n">
         <v>1</v>
       </c>
+      <c r="AK141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" ht="16" customHeight="1" s="8">
       <c r="A142" s="5" t="n">
@@ -11684,6 +12086,9 @@
       <c r="AI142" t="n">
         <v>1</v>
       </c>
+      <c r="AK142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143" ht="16" customHeight="1" s="8">
       <c r="A143" s="5" t="n">
@@ -11761,6 +12166,9 @@
       <c r="AI143" t="n">
         <v>1</v>
       </c>
+      <c r="AK143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144" ht="16" customHeight="1" s="8">
       <c r="A144" s="5" t="n">
@@ -11841,6 +12249,9 @@
       <c r="AI144" t="n">
         <v>1</v>
       </c>
+      <c r="AK144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145" ht="16" customHeight="1" s="8">
       <c r="A145" s="5" t="n">
@@ -11921,6 +12332,9 @@
       <c r="AI145" t="n">
         <v>1</v>
       </c>
+      <c r="AK145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146" ht="16" customHeight="1" s="8">
       <c r="A146" s="5" t="n">
@@ -12001,6 +12415,9 @@
       <c r="AI146" t="n">
         <v>1</v>
       </c>
+      <c r="AK146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147" ht="16" customHeight="1" s="8">
       <c r="A147" s="5" t="n">
@@ -12081,6 +12498,9 @@
       <c r="AI147" t="n">
         <v>1</v>
       </c>
+      <c r="AK147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148" ht="16" customHeight="1" s="8">
       <c r="A148" s="5" t="n">
@@ -12161,6 +12581,9 @@
       <c r="AI148" t="n">
         <v>1</v>
       </c>
+      <c r="AK148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149" ht="16" customHeight="1" s="8">
       <c r="A149" s="5" t="n">
@@ -12241,6 +12664,9 @@
       <c r="AI149" t="n">
         <v>1</v>
       </c>
+      <c r="AK149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150" ht="16" customHeight="1" s="8">
       <c r="A150" s="5" t="n">
@@ -12321,6 +12747,9 @@
       <c r="AI150" t="n">
         <v>1</v>
       </c>
+      <c r="AK150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151" ht="16" customHeight="1" s="8">
       <c r="A151" s="5" t="n">
@@ -12401,6 +12830,9 @@
       <c r="AI151" t="n">
         <v>1</v>
       </c>
+      <c r="AK151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152" ht="16" customHeight="1" s="8">
       <c r="A152" s="5" t="n">
@@ -12481,6 +12913,9 @@
       <c r="AI152" t="n">
         <v>1</v>
       </c>
+      <c r="AK152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153" ht="16" customHeight="1" s="8">
       <c r="A153" s="5" t="n">
@@ -12558,6 +12993,9 @@
       <c r="AH153" t="n">
         <v>1</v>
       </c>
+      <c r="AK153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" ht="16" customHeight="1" s="8">
       <c r="A154" s="5" t="n">
@@ -12638,6 +13076,9 @@
       <c r="AI154" t="n">
         <v>1</v>
       </c>
+      <c r="AK154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" ht="16" customHeight="1" s="8">
       <c r="A155" s="5" t="n">
@@ -12718,6 +13159,9 @@
       <c r="AI155" t="n">
         <v>1</v>
       </c>
+      <c r="AK155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156" ht="16" customHeight="1" s="8">
       <c r="A156" s="5" t="n">
@@ -12798,6 +13242,9 @@
       <c r="AI156" t="n">
         <v>1</v>
       </c>
+      <c r="AK156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157" ht="16" customHeight="1" s="8">
       <c r="A157" s="5" t="n">
@@ -12878,6 +13325,9 @@
       <c r="AI157" t="n">
         <v>1</v>
       </c>
+      <c r="AK157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158" ht="16" customHeight="1" s="8">
       <c r="A158" s="5" t="n">
@@ -12958,6 +13408,9 @@
       <c r="AI158" t="n">
         <v>1</v>
       </c>
+      <c r="AK158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159" ht="16" customHeight="1" s="8">
       <c r="A159" s="5" t="n">
@@ -13038,6 +13491,9 @@
       <c r="AI159" t="n">
         <v>1</v>
       </c>
+      <c r="AK159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160" ht="16" customHeight="1" s="8">
       <c r="A160" s="5" t="n">
@@ -13118,6 +13574,9 @@
       <c r="AI160" t="n">
         <v>1</v>
       </c>
+      <c r="AK160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161" ht="16" customHeight="1" s="8">
       <c r="A161" s="5" t="n">
@@ -13198,6 +13657,9 @@
       <c r="AI161" t="n">
         <v>1</v>
       </c>
+      <c r="AK161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162" ht="16" customHeight="1" s="8">
       <c r="A162" s="5" t="n">
@@ -13278,6 +13740,9 @@
       <c r="AI162" t="n">
         <v>1</v>
       </c>
+      <c r="AK162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163" ht="16" customHeight="1" s="8">
       <c r="A163" s="5" t="n">
@@ -13358,6 +13823,9 @@
       <c r="AI163" t="n">
         <v>1</v>
       </c>
+      <c r="AK163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164" ht="16" customHeight="1" s="8">
       <c r="A164" s="5" t="n">
@@ -13438,6 +13906,9 @@
       <c r="AI164" t="n">
         <v>1</v>
       </c>
+      <c r="AK164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165" ht="16" customHeight="1" s="8">
       <c r="A165" s="5" t="n">
@@ -13518,6 +13989,9 @@
       <c r="AI165" t="n">
         <v>1</v>
       </c>
+      <c r="AK165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166" ht="16" customHeight="1" s="8">
       <c r="A166" s="5" t="n">
@@ -13598,6 +14072,9 @@
       <c r="AI166" t="n">
         <v>1</v>
       </c>
+      <c r="AK166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167" ht="16" customHeight="1" s="8">
       <c r="A167" s="5" t="n">
@@ -13678,6 +14155,9 @@
       <c r="AI167" t="n">
         <v>1</v>
       </c>
+      <c r="AK167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168" ht="16" customHeight="1" s="8">
       <c r="A168" s="5" t="n">
@@ -13758,6 +14238,9 @@
       <c r="AI168" t="n">
         <v>1</v>
       </c>
+      <c r="AK168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169" ht="16" customHeight="1" s="8">
       <c r="A169" s="5" t="n">
@@ -13838,6 +14321,9 @@
       <c r="AI169" t="n">
         <v>1</v>
       </c>
+      <c r="AK169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170" ht="16" customHeight="1" s="8">
       <c r="A170" s="5" t="n">
@@ -13918,6 +14404,9 @@
       <c r="AI170" t="n">
         <v>1</v>
       </c>
+      <c r="AK170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171" ht="16" customHeight="1" s="8">
       <c r="A171" s="5" t="n">
@@ -13998,6 +14487,9 @@
       <c r="AI171" t="n">
         <v>1</v>
       </c>
+      <c r="AK171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172" ht="16" customHeight="1" s="8">
       <c r="A172" s="5" t="n">
@@ -14078,6 +14570,9 @@
       <c r="AI172" t="n">
         <v>1</v>
       </c>
+      <c r="AK172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173" ht="16" customHeight="1" s="8">
       <c r="A173" s="5" t="n">
@@ -14158,6 +14653,9 @@
       <c r="AI173" t="n">
         <v>1</v>
       </c>
+      <c r="AK173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174" ht="16" customHeight="1" s="8">
       <c r="A174" s="5" t="n">
@@ -14238,6 +14736,9 @@
       <c r="AI174" t="n">
         <v>1</v>
       </c>
+      <c r="AK174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175" ht="16" customHeight="1" s="8">
       <c r="A175" s="5" t="n">
@@ -14318,6 +14819,9 @@
       <c r="AI175" t="n">
         <v>1</v>
       </c>
+      <c r="AK175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176" ht="16" customHeight="1" s="8">
       <c r="A176" s="5" t="n">
@@ -14398,6 +14902,9 @@
       <c r="AI176" t="n">
         <v>1</v>
       </c>
+      <c r="AK176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177" ht="16" customHeight="1" s="8">
       <c r="A177" s="5" t="n">
@@ -14478,6 +14985,9 @@
       <c r="AI177" t="n">
         <v>1</v>
       </c>
+      <c r="AK177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178" ht="16" customHeight="1" s="8">
       <c r="A178" s="5" t="n">
@@ -14558,6 +15068,9 @@
       <c r="AI178" t="n">
         <v>1</v>
       </c>
+      <c r="AK178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179" ht="16" customHeight="1" s="8">
       <c r="A179" s="5" t="n">
@@ -14638,6 +15151,9 @@
       <c r="AI179" t="n">
         <v>1</v>
       </c>
+      <c r="AK179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180" ht="16" customHeight="1" s="8">
       <c r="A180" s="5" t="n">
@@ -14718,6 +15234,9 @@
       <c r="AI180" t="n">
         <v>1</v>
       </c>
+      <c r="AK180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181" ht="16" customHeight="1" s="8">
       <c r="A181" s="5" t="n">
@@ -14795,6 +15314,9 @@
       <c r="AI181" t="n">
         <v>1</v>
       </c>
+      <c r="AK181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182" ht="16" customHeight="1" s="8">
       <c r="A182" s="5" t="n">
@@ -14875,6 +15397,9 @@
       <c r="AI182" t="n">
         <v>1</v>
       </c>
+      <c r="AK182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183" ht="16" customHeight="1" s="8">
       <c r="A183" s="5" t="n">
@@ -14955,6 +15480,9 @@
       <c r="AI183" t="n">
         <v>1</v>
       </c>
+      <c r="AK183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184" ht="16" customHeight="1" s="8">
       <c r="A184" s="5" t="n">
@@ -15035,6 +15563,9 @@
       <c r="AI184" t="n">
         <v>1</v>
       </c>
+      <c r="AK184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185" ht="16" customHeight="1" s="8">
       <c r="A185" s="5" t="n">
@@ -15115,6 +15646,9 @@
       <c r="AI185" t="n">
         <v>1</v>
       </c>
+      <c r="AK185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186" ht="16" customHeight="1" s="8">
       <c r="A186" s="5" t="n">
@@ -15195,6 +15729,9 @@
       <c r="AI186" t="n">
         <v>1</v>
       </c>
+      <c r="AK186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187" ht="16" customHeight="1" s="8">
       <c r="A187" s="5" t="n">
@@ -15275,6 +15812,9 @@
       <c r="AI187" t="n">
         <v>1</v>
       </c>
+      <c r="AK187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188" ht="16" customHeight="1" s="8">
       <c r="A188" s="5" t="n">
@@ -15355,6 +15895,9 @@
       <c r="AI188" t="n">
         <v>1</v>
       </c>
+      <c r="AK188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189" ht="16" customHeight="1" s="8">
       <c r="A189" s="5" t="n">
@@ -15435,6 +15978,9 @@
       <c r="AI189" t="n">
         <v>1</v>
       </c>
+      <c r="AK189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190" ht="16" customHeight="1" s="8">
       <c r="A190" s="5" t="n">
@@ -15515,6 +16061,9 @@
       <c r="AI190" t="n">
         <v>1</v>
       </c>
+      <c r="AK190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191" ht="16" customHeight="1" s="8">
       <c r="A191" s="5" t="n">
@@ -15595,6 +16144,9 @@
       <c r="AI191" t="n">
         <v>1</v>
       </c>
+      <c r="AK191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192" ht="16" customHeight="1" s="8">
       <c r="A192" s="5" t="n">
@@ -15675,6 +16227,9 @@
       <c r="AI192" t="n">
         <v>1</v>
       </c>
+      <c r="AK192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193" ht="16" customHeight="1" s="8">
       <c r="A193" s="5" t="n">
@@ -15755,6 +16310,9 @@
       <c r="AI193" t="n">
         <v>1</v>
       </c>
+      <c r="AK193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194" ht="16" customHeight="1" s="8">
       <c r="A194" s="5" t="n">
@@ -15835,6 +16393,9 @@
       <c r="AI194" t="n">
         <v>1</v>
       </c>
+      <c r="AK194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195" ht="16" customHeight="1" s="8">
       <c r="A195" s="5" t="n">
@@ -15915,6 +16476,9 @@
       <c r="AI195" t="n">
         <v>1</v>
       </c>
+      <c r="AK195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196" ht="16" customHeight="1" s="8">
       <c r="A196" s="5" t="n">
@@ -15995,6 +16559,9 @@
       <c r="AI196" t="n">
         <v>1</v>
       </c>
+      <c r="AK196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197" ht="16" customHeight="1" s="8">
       <c r="A197" s="5" t="n">
@@ -16075,6 +16642,9 @@
       <c r="AI197" t="n">
         <v>1</v>
       </c>
+      <c r="AK197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198" ht="16" customHeight="1" s="8">
       <c r="A198" s="5" t="n">
@@ -16155,6 +16725,9 @@
       <c r="AI198" t="n">
         <v>1</v>
       </c>
+      <c r="AK198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199" ht="16" customHeight="1" s="8">
       <c r="A199" s="5" t="n">
@@ -16235,6 +16808,9 @@
       <c r="AI199" t="n">
         <v>1</v>
       </c>
+      <c r="AK199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200" ht="16" customHeight="1" s="8">
       <c r="A200" s="5" t="n">
@@ -16315,6 +16891,9 @@
       <c r="AI200" t="n">
         <v>1</v>
       </c>
+      <c r="AK200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201" ht="16" customHeight="1" s="8">
       <c r="A201" s="5" t="n">
@@ -16395,6 +16974,9 @@
       <c r="AI201" t="n">
         <v>1</v>
       </c>
+      <c r="AK201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202" ht="16" customHeight="1" s="8">
       <c r="A202" s="5" t="n">
@@ -16475,6 +17057,9 @@
       <c r="AI202" t="n">
         <v>1</v>
       </c>
+      <c r="AK202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203" ht="16" customHeight="1" s="8">
       <c r="A203" s="5" t="n">
@@ -16555,6 +17140,9 @@
       <c r="AI203" t="n">
         <v>1</v>
       </c>
+      <c r="AK203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204" ht="16" customHeight="1" s="8">
       <c r="A204" s="5" t="n">
@@ -16635,6 +17223,9 @@
       <c r="AI204" t="n">
         <v>1</v>
       </c>
+      <c r="AK204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205" ht="16" customHeight="1" s="8">
       <c r="A205" s="5" t="n">
@@ -16715,6 +17306,9 @@
       <c r="AI205" t="n">
         <v>1</v>
       </c>
+      <c r="AK205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206" ht="16" customHeight="1" s="8">
       <c r="A206" s="5" t="n">
@@ -16795,6 +17389,9 @@
       <c r="AI206" t="n">
         <v>1</v>
       </c>
+      <c r="AK206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207" ht="16" customHeight="1" s="8">
       <c r="A207" s="5" t="n">
@@ -16873,6 +17470,9 @@
         <v>1</v>
       </c>
       <c r="AI207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32558,6 +33158,9 @@
       <c r="AI418" t="n">
         <v>0.11844</v>
       </c>
+      <c r="AK418" t="n">
+        <v>0.1154</v>
+      </c>
     </row>
     <row r="419">
       <c r="H419" s="5" t="n">
@@ -32617,6 +33220,9 @@
       <c r="AI419" t="n">
         <v>0.1168142857142857</v>
       </c>
+      <c r="AK419" t="n">
+        <v>0.1561166666666667</v>
+      </c>
     </row>
     <row r="420">
       <c r="H420" s="5" t="n">
@@ -32676,6 +33282,9 @@
       <c r="AI420" t="n">
         <v>0.2085875</v>
       </c>
+      <c r="AK420" t="n">
+        <v>0.2090714285714286</v>
+      </c>
     </row>
     <row r="421">
       <c r="H421" s="5" t="n">
@@ -32735,6 +33344,9 @@
       <c r="AI421" t="n">
         <v>0.28051</v>
       </c>
+      <c r="AK421" t="n">
+        <v>0.2737142857142857</v>
+      </c>
     </row>
     <row r="422">
       <c r="H422" s="5" t="n">
@@ -32794,6 +33406,9 @@
       <c r="AI422" t="n">
         <v>0.29418</v>
       </c>
+      <c r="AK422" t="n">
+        <v>0.2562142857142857</v>
+      </c>
     </row>
     <row r="423">
       <c r="H423" s="5" t="n">
@@ -32853,6 +33468,9 @@
       <c r="AI423" t="n">
         <v>0.30703</v>
       </c>
+      <c r="AK423" t="n">
+        <v>0.3206833333333333</v>
+      </c>
     </row>
     <row r="424">
       <c r="H424" s="5" t="n">
@@ -32912,6 +33530,9 @@
       <c r="AI424" t="n">
         <v>0.32345</v>
       </c>
+      <c r="AK424" t="n">
+        <v>0.2893</v>
+      </c>
     </row>
     <row r="425">
       <c r="H425" s="5" t="n">
@@ -32971,6 +33592,9 @@
       <c r="AI425" t="n">
         <v>0.4134384615384615</v>
       </c>
+      <c r="AK425" t="n">
+        <v>0.4477222222222223</v>
+      </c>
     </row>
     <row r="426">
       <c r="H426" s="5" t="n">
@@ -33030,6 +33654,9 @@
       <c r="AI426" t="n">
         <v>0.41214</v>
       </c>
+      <c r="AK426" t="n">
+        <v>0.4328571428571428</v>
+      </c>
     </row>
     <row r="427">
       <c r="H427" s="5" t="n">
@@ -33089,6 +33716,9 @@
       <c r="AI427" t="n">
         <v>0.45495</v>
       </c>
+      <c r="AK427" t="n">
+        <v>0.4906083333333333</v>
+      </c>
     </row>
     <row r="428">
       <c r="H428" s="5" t="n">
@@ -33136,6 +33766,9 @@
       <c r="AI428" t="n">
         <v>0.47021</v>
       </c>
+      <c r="AK428" t="n">
+        <v>0.5032222222222222</v>
+      </c>
     </row>
     <row r="429">
       <c r="H429" s="5" t="n">
@@ -33186,6 +33819,9 @@
       <c r="AI429" t="n">
         <v>0.5647</v>
       </c>
+      <c r="AK429" t="n">
+        <v>0.5067125</v>
+      </c>
     </row>
     <row r="430">
       <c r="H430" s="5" t="n">
@@ -33236,6 +33872,9 @@
       <c r="AI430" t="n">
         <v>0.4968555555555556</v>
       </c>
+      <c r="AK430" t="n">
+        <v>0.5874666666666667</v>
+      </c>
     </row>
     <row r="431">
       <c r="H431" s="5" t="n">
@@ -33286,6 +33925,9 @@
       <c r="AI431" t="n">
         <v>0.5662363636363636</v>
       </c>
+      <c r="AK431" t="n">
+        <v>0.59495</v>
+      </c>
     </row>
     <row r="432">
       <c r="H432" s="5" t="n">
@@ -33336,6 +33978,9 @@
       <c r="AI432" t="n">
         <v>0.6087</v>
       </c>
+      <c r="AK432" t="n">
+        <v>0.5515</v>
+      </c>
     </row>
     <row r="433">
       <c r="H433" s="5" t="n">
@@ -33386,6 +34031,9 @@
       <c r="AI433" t="n">
         <v>0.5527083333333334</v>
       </c>
+      <c r="AK433" t="n">
+        <v>0.5979000000000001</v>
+      </c>
     </row>
     <row r="434">
       <c r="H434" s="5" t="n">
@@ -33436,6 +34084,9 @@
       <c r="AI434" t="n">
         <v>0.5567333333333333</v>
       </c>
+      <c r="AK434" t="n">
+        <v>0.6830916666666665</v>
+      </c>
     </row>
     <row r="435">
       <c r="H435" s="5" t="n">
@@ -33486,6 +34137,9 @@
       <c r="AI435" t="n">
         <v>0.4903428571428572</v>
       </c>
+      <c r="AK435" t="n">
+        <v>0.6390125</v>
+      </c>
     </row>
     <row r="436">
       <c r="H436" s="5" t="n">
@@ -33536,6 +34190,9 @@
       <c r="AI436" t="n">
         <v>0.4620100000000001</v>
       </c>
+      <c r="AK436" t="n">
+        <v>0.6901785714285713</v>
+      </c>
     </row>
     <row r="437">
       <c r="H437" s="5" t="n">
@@ -33583,6 +34240,9 @@
       <c r="AH437" t="n">
         <v>0.5641555555555555</v>
       </c>
+      <c r="AK437" t="n">
+        <v>0.5763</v>
+      </c>
     </row>
     <row r="438">
       <c r="H438" s="5" t="n">
@@ -33633,6 +34293,9 @@
       <c r="AI438" t="n">
         <v>0.5260916666666667</v>
       </c>
+      <c r="AK438" t="n">
+        <v>0.6813307692307693</v>
+      </c>
     </row>
     <row r="439">
       <c r="H439" s="5" t="n">
@@ -33683,6 +34346,9 @@
       <c r="AI439" t="n">
         <v>0.5456</v>
       </c>
+      <c r="AK439" t="n">
+        <v>0.63507</v>
+      </c>
     </row>
     <row r="440">
       <c r="H440" s="5" t="n">
@@ -33733,6 +34399,9 @@
       <c r="AI440" t="n">
         <v>0.5898333333333333</v>
       </c>
+      <c r="AK440" t="n">
+        <v>0.67281</v>
+      </c>
     </row>
     <row r="441">
       <c r="H441" s="5" t="n">
@@ -33783,6 +34452,9 @@
       <c r="AI441" t="n">
         <v>0.5843999999999998</v>
       </c>
+      <c r="AK441" t="n">
+        <v>0.7234583333333333</v>
+      </c>
     </row>
     <row r="442">
       <c r="H442" s="5" t="n">
@@ -33833,6 +34505,9 @@
       <c r="AI442" t="n">
         <v>0.5954928571428572</v>
       </c>
+      <c r="AK442" t="n">
+        <v>0.7293875</v>
+      </c>
     </row>
     <row r="443">
       <c r="H443" s="5" t="n">
@@ -33883,6 +34558,9 @@
       <c r="AI443" t="n">
         <v>0.5881416666666667</v>
       </c>
+      <c r="AK443" t="n">
+        <v>0.6389083333333334</v>
+      </c>
     </row>
     <row r="444">
       <c r="H444" s="5" t="n">
@@ -33933,6 +34611,9 @@
       <c r="AI444" t="n">
         <v>0.6613625000000001</v>
       </c>
+      <c r="AK444" t="n">
+        <v>0.6833272727272728</v>
+      </c>
     </row>
     <row r="445">
       <c r="H445" s="5" t="n">
@@ -33983,6 +34664,9 @@
       <c r="AI445" t="n">
         <v>0.57875</v>
       </c>
+      <c r="AK445" t="n">
+        <v>0.72964</v>
+      </c>
     </row>
     <row r="446">
       <c r="H446" s="5" t="n">
@@ -34033,6 +34717,9 @@
       <c r="AI446" t="n">
         <v>0.6669777777777778</v>
       </c>
+      <c r="AK446" t="n">
+        <v>0.6105181818181818</v>
+      </c>
     </row>
     <row r="447">
       <c r="H447" s="5" t="n">
@@ -34083,6 +34770,9 @@
       <c r="AI447" t="n">
         <v>0.5179363636363636</v>
       </c>
+      <c r="AK447" t="n">
+        <v>0.7170916666666667</v>
+      </c>
     </row>
     <row r="448">
       <c r="H448" s="5" t="n">
@@ -34133,6 +34823,9 @@
       <c r="AI448" t="n">
         <v>0.6869727272727273</v>
       </c>
+      <c r="AK448" t="n">
+        <v>0.6460363636363636</v>
+      </c>
     </row>
     <row r="449">
       <c r="H449" s="5" t="n">
@@ -34183,6 +34876,9 @@
       <c r="AI449" t="n">
         <v>0.5404214285714286</v>
       </c>
+      <c r="AK449" t="n">
+        <v>0.70265</v>
+      </c>
     </row>
     <row r="450">
       <c r="H450" s="5" t="n">
@@ -34230,6 +34926,9 @@
       <c r="AI450" t="n">
         <v>0.6353583333333334</v>
       </c>
+      <c r="AK450" t="n">
+        <v>0.7515363636363636</v>
+      </c>
     </row>
     <row r="451">
       <c r="H451" s="5" t="n">
@@ -34280,6 +34979,9 @@
       <c r="AI451" t="n">
         <v>0.6264909090909091</v>
       </c>
+      <c r="AK451" t="n">
+        <v>0.7492300000000001</v>
+      </c>
     </row>
     <row r="452">
       <c r="H452" s="5" t="n">
@@ -34330,6 +35032,9 @@
       <c r="AI452" t="n">
         <v>0.6068666666666667</v>
       </c>
+      <c r="AK452" t="n">
+        <v>0.6980454545454546</v>
+      </c>
     </row>
     <row r="453">
       <c r="H453" s="5" t="n">
@@ -34377,6 +35082,9 @@
       <c r="AI453" t="n">
         <v>0.5649916666666667</v>
       </c>
+      <c r="AK453" t="n">
+        <v>0.6796555555555555</v>
+      </c>
     </row>
     <row r="454">
       <c r="H454" s="5" t="n">
@@ -34427,6 +35135,9 @@
       <c r="AI454" t="n">
         <v>0.5550153846153846</v>
       </c>
+      <c r="AK454" t="n">
+        <v>0.64325</v>
+      </c>
     </row>
     <row r="455">
       <c r="H455" s="5" t="n">
@@ -34477,6 +35188,9 @@
       <c r="AI455" t="n">
         <v>0.6625272727272727</v>
       </c>
+      <c r="AK455" t="n">
+        <v>0.6793454545454546</v>
+      </c>
     </row>
     <row r="456">
       <c r="H456" s="5" t="n">
@@ -34527,6 +35241,9 @@
       <c r="AI456" t="n">
         <v>0.5782636363636363</v>
       </c>
+      <c r="AK456" t="n">
+        <v>0.755925</v>
+      </c>
     </row>
     <row r="457">
       <c r="H457" s="5" t="n">
@@ -34577,6 +35294,9 @@
       <c r="AI457" t="n">
         <v>0.5540833333333334</v>
       </c>
+      <c r="AK457" t="n">
+        <v>0.7241555555555554</v>
+      </c>
     </row>
     <row r="458">
       <c r="H458" s="5" t="n">
@@ -34627,6 +35347,9 @@
       <c r="AI458" t="n">
         <v>0.6508307692307691</v>
       </c>
+      <c r="AK458" t="n">
+        <v>0.7234083333333333</v>
+      </c>
     </row>
     <row r="459">
       <c r="H459" s="5" t="n">
@@ -34677,6 +35400,9 @@
       <c r="AI459" t="n">
         <v>0.6123333333333334</v>
       </c>
+      <c r="AK459" t="n">
+        <v>0.6602818181818182</v>
+      </c>
     </row>
     <row r="460">
       <c r="H460" s="5" t="n">
@@ -34727,6 +35453,9 @@
       <c r="AI460" t="n">
         <v>0.6267272727272727</v>
       </c>
+      <c r="AK460" t="n">
+        <v>0.7216111111111112</v>
+      </c>
     </row>
     <row r="461">
       <c r="H461" s="5" t="n">
@@ -34777,6 +35506,9 @@
       <c r="AI461" t="n">
         <v>0.5632166666666667</v>
       </c>
+      <c r="AK461" t="n">
+        <v>0.7169909090909091</v>
+      </c>
     </row>
     <row r="462">
       <c r="H462" s="5" t="n">
@@ -34827,6 +35559,9 @@
       <c r="AI462" t="n">
         <v>0.588290909090909</v>
       </c>
+      <c r="AK462" t="n">
+        <v>0.6768799999999999</v>
+      </c>
     </row>
     <row r="463">
       <c r="H463" s="5" t="n">
@@ -34874,6 +35609,9 @@
       <c r="AH463" t="n">
         <v>0.5842799999999999</v>
       </c>
+      <c r="AK463" t="n">
+        <v>0.7065181818181819</v>
+      </c>
     </row>
     <row r="464">
       <c r="H464" s="5" t="n">
@@ -34924,6 +35662,9 @@
       <c r="AI464" t="n">
         <v>0.5247090909090909</v>
       </c>
+      <c r="AK464" t="n">
+        <v>0.6657777777777779</v>
+      </c>
     </row>
     <row r="465">
       <c r="H465" s="5" t="n">
@@ -34974,6 +35715,9 @@
       <c r="AI465" t="n">
         <v>0.5759461538461538</v>
       </c>
+      <c r="AK465" t="n">
+        <v>0.6732900000000001</v>
+      </c>
     </row>
     <row r="466">
       <c r="H466" s="5" t="n">
@@ -35024,6 +35768,9 @@
       <c r="AI466" t="n">
         <v>0.6231818181818182</v>
       </c>
+      <c r="AK466" t="n">
+        <v>0.7497666666666666</v>
+      </c>
     </row>
     <row r="467">
       <c r="H467" s="5" t="n">
@@ -35074,6 +35821,9 @@
       <c r="AI467" t="n">
         <v>0.566625</v>
       </c>
+      <c r="AK467" t="n">
+        <v>0.70185</v>
+      </c>
     </row>
     <row r="468">
       <c r="H468" s="5" t="n">
@@ -35124,6 +35874,9 @@
       <c r="AI468" t="n">
         <v>0.5158727272727273</v>
       </c>
+      <c r="AK468" t="n">
+        <v>0.6235899999999999</v>
+      </c>
     </row>
     <row r="469">
       <c r="H469" s="5" t="n">
@@ -35174,6 +35927,9 @@
       <c r="AI469" t="n">
         <v>0.5371222222222223</v>
       </c>
+      <c r="AK469" t="n">
+        <v>0.7743777777777777</v>
+      </c>
     </row>
     <row r="470">
       <c r="H470" s="5" t="n">
@@ -35224,6 +35980,9 @@
       <c r="AI470" t="n">
         <v>0.6442727272727272</v>
       </c>
+      <c r="AK470" t="n">
+        <v>0.7041666666666667</v>
+      </c>
     </row>
     <row r="471">
       <c r="H471" s="5" t="n">
@@ -35274,6 +36033,9 @@
       <c r="AI471" t="n">
         <v>0.5924461538461538</v>
       </c>
+      <c r="AK471" t="n">
+        <v>0.6762499999999998</v>
+      </c>
     </row>
     <row r="472">
       <c r="H472" s="5" t="n">
@@ -35324,6 +36086,9 @@
       <c r="AI472" t="n">
         <v>0.5593545454545454</v>
       </c>
+      <c r="AK472" t="n">
+        <v>0.7589666666666668</v>
+      </c>
     </row>
     <row r="473">
       <c r="H473" s="5" t="n">
@@ -35374,6 +36139,9 @@
       <c r="AI473" t="n">
         <v>0.5250272727272728</v>
       </c>
+      <c r="AK473" t="n">
+        <v>0.6874</v>
+      </c>
     </row>
     <row r="474">
       <c r="H474" s="5" t="n">
@@ -35424,6 +36192,9 @@
       <c r="AI474" t="n">
         <v>0.6432600000000001</v>
       </c>
+      <c r="AK474" t="n">
+        <v>0.7427727272727274</v>
+      </c>
     </row>
     <row r="475">
       <c r="H475" s="5" t="n">
@@ -35474,6 +36245,9 @@
       <c r="AI475" t="n">
         <v>0.54559</v>
       </c>
+      <c r="AK475" t="n">
+        <v>0.6383909090909091</v>
+      </c>
     </row>
     <row r="476">
       <c r="H476" s="5" t="n">
@@ -35524,6 +36298,9 @@
       <c r="AI476" t="n">
         <v>0.6434</v>
       </c>
+      <c r="AK476" t="n">
+        <v>0.672190909090909</v>
+      </c>
     </row>
     <row r="477">
       <c r="H477" s="5" t="n">
@@ -35574,6 +36351,9 @@
       <c r="AI477" t="n">
         <v>0.6002181818181819</v>
       </c>
+      <c r="AK477" t="n">
+        <v>0.7016625</v>
+      </c>
     </row>
     <row r="478">
       <c r="H478" s="5" t="n">
@@ -35624,6 +36404,9 @@
       <c r="AI478" t="n">
         <v>0.5306615384615383</v>
       </c>
+      <c r="AK478" t="n">
+        <v>0.7417111111111111</v>
+      </c>
     </row>
     <row r="479">
       <c r="H479" s="5" t="n">
@@ -35674,6 +36457,9 @@
       <c r="AI479" t="n">
         <v>0.5950222222222222</v>
       </c>
+      <c r="AK479" t="n">
+        <v>0.7144444444444444</v>
+      </c>
     </row>
     <row r="480">
       <c r="H480" s="5" t="n">
@@ -35724,6 +36510,9 @@
       <c r="AI480" t="n">
         <v>0.473225</v>
       </c>
+      <c r="AK480" t="n">
+        <v>0.68855</v>
+      </c>
     </row>
     <row r="481">
       <c r="H481" s="5" t="n">
@@ -35774,6 +36563,9 @@
       <c r="AI481" t="n">
         <v>0.58578</v>
       </c>
+      <c r="AK481" t="n">
+        <v>0.72773</v>
+      </c>
     </row>
     <row r="482">
       <c r="H482" s="5" t="n">
@@ -35824,6 +36616,9 @@
       <c r="AI482" t="n">
         <v>0.5609749999999999</v>
       </c>
+      <c r="AK482" t="n">
+        <v>0.592</v>
+      </c>
     </row>
     <row r="483">
       <c r="H483" s="5" t="n">
@@ -35874,6 +36669,9 @@
       <c r="AI483" t="n">
         <v>0.5564600000000001</v>
       </c>
+      <c r="AK483" t="n">
+        <v>0.712025</v>
+      </c>
     </row>
     <row r="484">
       <c r="H484" s="5" t="n">
@@ -35924,6 +36722,9 @@
       <c r="AI484" t="n">
         <v>0.6442125000000001</v>
       </c>
+      <c r="AK484" t="n">
+        <v>0.7299900000000001</v>
+      </c>
     </row>
     <row r="485">
       <c r="H485" s="5" t="n">
@@ -35974,6 +36775,9 @@
       <c r="AI485" t="n">
         <v>0.562275</v>
       </c>
+      <c r="AK485" t="n">
+        <v>0.6671916666666667</v>
+      </c>
     </row>
     <row r="486">
       <c r="H486" s="5" t="n">
@@ -36024,6 +36828,9 @@
       <c r="AI486" t="n">
         <v>0.5865250000000001</v>
       </c>
+      <c r="AK486" t="n">
+        <v>0.6914363636363636</v>
+      </c>
     </row>
     <row r="487">
       <c r="H487" s="5" t="n">
@@ -36074,6 +36881,9 @@
       <c r="AI487" t="n">
         <v>0.6254666666666667</v>
       </c>
+      <c r="AK487" t="n">
+        <v>0.75117</v>
+      </c>
     </row>
     <row r="488">
       <c r="H488" s="5" t="n">
@@ -36124,6 +36934,9 @@
       <c r="AI488" t="n">
         <v>0.5931272727272727</v>
       </c>
+      <c r="AK488" t="n">
+        <v>0.7481818181818182</v>
+      </c>
     </row>
     <row r="489">
       <c r="H489" s="5" t="n">
@@ -36174,6 +36987,9 @@
       <c r="AI489" t="n">
         <v>0.7043928571428573</v>
       </c>
+      <c r="AK489" t="n">
+        <v>0.6937888888888888</v>
+      </c>
     </row>
     <row r="490">
       <c r="H490" s="5" t="n">
@@ -36224,6 +37040,9 @@
       <c r="AI490" t="n">
         <v>0.6163777777777777</v>
       </c>
+      <c r="AK490" t="n">
+        <v>0.7202545454545454</v>
+      </c>
     </row>
     <row r="491">
       <c r="H491" s="5" t="n">
@@ -36271,6 +37090,9 @@
       <c r="AI491" t="n">
         <v>0.5878583333333333</v>
       </c>
+      <c r="AK491" t="n">
+        <v>0.6682444444444444</v>
+      </c>
     </row>
     <row r="492">
       <c r="H492" s="5" t="n">
@@ -36321,6 +37143,9 @@
       <c r="AI492" t="n">
         <v>0.5871583333333334</v>
       </c>
+      <c r="AK492" t="n">
+        <v>0.7022727272727273</v>
+      </c>
     </row>
     <row r="493">
       <c r="H493" s="5" t="n">
@@ -36371,6 +37196,9 @@
       <c r="AI493" t="n">
         <v>0.5515666666666666</v>
       </c>
+      <c r="AK493" t="n">
+        <v>0.6867090909090909</v>
+      </c>
     </row>
     <row r="494">
       <c r="H494" s="5" t="n">
@@ -36421,6 +37249,9 @@
       <c r="AI494" t="n">
         <v>0.583290909090909</v>
       </c>
+      <c r="AK494" t="n">
+        <v>0.7472000000000001</v>
+      </c>
     </row>
     <row r="495">
       <c r="H495" s="5" t="n">
@@ -36471,6 +37302,9 @@
       <c r="AI495" t="n">
         <v>0.5609166666666667</v>
       </c>
+      <c r="AK495" t="n">
+        <v>0.7337875</v>
+      </c>
     </row>
     <row r="496">
       <c r="H496" s="5" t="n">
@@ -36521,6 +37355,9 @@
       <c r="AI496" t="n">
         <v>0.6091666666666665</v>
       </c>
+      <c r="AK496" t="n">
+        <v>0.7358727272727275</v>
+      </c>
     </row>
     <row r="497">
       <c r="H497" s="5" t="n">
@@ -36571,6 +37408,9 @@
       <c r="AI497" t="n">
         <v>0.5709799999999999</v>
       </c>
+      <c r="AK497" t="n">
+        <v>0.7271000000000001</v>
+      </c>
     </row>
     <row r="498">
       <c r="H498" s="5" t="n">
@@ -36621,6 +37461,9 @@
       <c r="AI498" t="n">
         <v>0.5998222222222221</v>
       </c>
+      <c r="AK498" t="n">
+        <v>0.6508545454545455</v>
+      </c>
     </row>
     <row r="499">
       <c r="H499" s="5" t="n">
@@ -36671,6 +37514,9 @@
       <c r="AI499" t="n">
         <v>0.5218636363636363</v>
       </c>
+      <c r="AK499" t="n">
+        <v>0.7436615384615385</v>
+      </c>
     </row>
     <row r="500">
       <c r="H500" s="5" t="n">
@@ -36721,6 +37567,9 @@
       <c r="AI500" t="n">
         <v>0.6140090909090909</v>
       </c>
+      <c r="AK500" t="n">
+        <v>0.6861999999999999</v>
+      </c>
     </row>
     <row r="501">
       <c r="H501" s="5" t="n">
@@ -36771,6 +37620,9 @@
       <c r="AI501" t="n">
         <v>0.6233333333333334</v>
       </c>
+      <c r="AK501" t="n">
+        <v>0.71231</v>
+      </c>
     </row>
     <row r="502">
       <c r="H502" s="5" t="n">
@@ -36821,6 +37673,9 @@
       <c r="AI502" t="n">
         <v>0.6382636363636365</v>
       </c>
+      <c r="AK502" t="n">
+        <v>0.7150300000000001</v>
+      </c>
     </row>
     <row r="503">
       <c r="H503" s="5" t="n">
@@ -36871,6 +37726,9 @@
       <c r="AI503" t="n">
         <v>0.5552083333333334</v>
       </c>
+      <c r="AK503" t="n">
+        <v>0.6585272727272726</v>
+      </c>
     </row>
     <row r="504">
       <c r="H504" s="5" t="n">
@@ -36921,6 +37779,9 @@
       <c r="AI504" t="n">
         <v>0.5549090909090908</v>
       </c>
+      <c r="AK504" t="n">
+        <v>0.7268214285714286</v>
+      </c>
     </row>
     <row r="505">
       <c r="H505" s="5" t="n">
@@ -36971,6 +37832,9 @@
       <c r="AI505" t="n">
         <v>0.61391</v>
       </c>
+      <c r="AK505" t="n">
+        <v>0.6921</v>
+      </c>
     </row>
     <row r="506">
       <c r="H506" s="5" t="n">
@@ -37021,6 +37885,9 @@
       <c r="AI506" t="n">
         <v>0.5387916666666667</v>
       </c>
+      <c r="AK506" t="n">
+        <v>0.62569</v>
+      </c>
     </row>
     <row r="507">
       <c r="H507" s="5" t="n">
@@ -37071,6 +37938,9 @@
       <c r="AI507" t="n">
         <v>0.5796749999999999</v>
       </c>
+      <c r="AK507" t="n">
+        <v>0.7069777777777779</v>
+      </c>
     </row>
     <row r="508">
       <c r="H508" s="5" t="n">
@@ -37121,6 +37991,9 @@
       <c r="AI508" t="n">
         <v>0.5518545454545455</v>
       </c>
+      <c r="AK508" t="n">
+        <v>0.6854222222222223</v>
+      </c>
     </row>
     <row r="509">
       <c r="H509" s="5" t="n">
@@ -37171,6 +38044,9 @@
       <c r="AI509" t="n">
         <v>0.5947818181818182</v>
       </c>
+      <c r="AK509" t="n">
+        <v>0.65493</v>
+      </c>
     </row>
     <row r="510">
       <c r="H510" s="5" t="n">
@@ -37221,6 +38097,9 @@
       <c r="AI510" t="n">
         <v>0.59485</v>
       </c>
+      <c r="AK510" t="n">
+        <v>0.7499888888888889</v>
+      </c>
     </row>
     <row r="511">
       <c r="H511" s="5" t="n">
@@ -37271,6 +38150,9 @@
       <c r="AI511" t="n">
         <v>0.5214846153846153</v>
       </c>
+      <c r="AK511" t="n">
+        <v>0.7476222222222222</v>
+      </c>
     </row>
     <row r="512">
       <c r="H512" s="5" t="n">
@@ -37321,6 +38203,9 @@
       <c r="AI512" t="n">
         <v>0.6764363636363636</v>
       </c>
+      <c r="AK512" t="n">
+        <v>0.69515</v>
+      </c>
     </row>
     <row r="513">
       <c r="H513" s="5" t="n">
@@ -37371,6 +38256,9 @@
       <c r="AI513" t="n">
         <v>0.5963499999999999</v>
       </c>
+      <c r="AK513" t="n">
+        <v>0.7080538461538463</v>
+      </c>
     </row>
     <row r="514">
       <c r="H514" s="5" t="n">
@@ -37421,6 +38309,9 @@
       <c r="AI514" t="n">
         <v>0.5021545454545454</v>
       </c>
+      <c r="AK514" t="n">
+        <v>0.7440111111111111</v>
+      </c>
     </row>
     <row r="515">
       <c r="H515" s="5" t="n">
@@ -37471,6 +38362,9 @@
       <c r="AI515" t="n">
         <v>0.5428000000000001</v>
       </c>
+      <c r="AK515" t="n">
+        <v>0.6927500000000001</v>
+      </c>
     </row>
     <row r="516">
       <c r="H516" s="5" t="n">
@@ -37521,6 +38415,9 @@
       <c r="AI516" t="n">
         <v>0.49555</v>
       </c>
+      <c r="AK516" t="n">
+        <v>0.6953222222222222</v>
+      </c>
     </row>
     <row r="517">
       <c r="H517" s="5" t="n">
@@ -37570,6 +38467,9 @@
       </c>
       <c r="AI517" t="n">
         <v>0.52064</v>
+      </c>
+      <c r="AK517" t="n">
+        <v>0.7168571428571429</v>
       </c>
     </row>
     <row r="518">
@@ -37629,6 +38529,9 @@
       <c r="AI520" t="n">
         <v>0.1300313432835821</v>
       </c>
+      <c r="AK520" t="n">
+        <v>0.1076042857142857</v>
+      </c>
     </row>
     <row r="521">
       <c r="H521" s="5" t="n">
@@ -37673,6 +38576,9 @@
       <c r="AI521" t="n">
         <v>0.16574375</v>
       </c>
+      <c r="AK521" t="n">
+        <v>0.1369625</v>
+      </c>
     </row>
     <row r="522">
       <c r="H522" s="5" t="n">
@@ -37717,6 +38623,9 @@
       <c r="AI522" t="n">
         <v>0.3067285714285714</v>
       </c>
+      <c r="AK522" t="n">
+        <v>0.2091555555555556</v>
+      </c>
     </row>
     <row r="523">
       <c r="H523" s="5" t="n">
@@ -37761,6 +38670,9 @@
       <c r="AI523" t="n">
         <v>0.31178</v>
       </c>
+      <c r="AK523" t="n">
+        <v>0.2502863636363636</v>
+      </c>
     </row>
     <row r="524">
       <c r="H524" s="5" t="n">
@@ -37805,6 +38717,9 @@
       <c r="AI524" t="n">
         <v>0.3213083333333334</v>
       </c>
+      <c r="AK524" t="n">
+        <v>0.3474</v>
+      </c>
     </row>
     <row r="525">
       <c r="H525" s="5" t="n">
@@ -37849,6 +38764,9 @@
       <c r="AI525" t="n">
         <v>0.3844896551724138</v>
       </c>
+      <c r="AK525" t="n">
+        <v>0.2954864864864865</v>
+      </c>
     </row>
     <row r="526">
       <c r="H526" s="5" t="n">
@@ -37893,6 +38811,9 @@
       <c r="AI526" t="n">
         <v>0.31800625</v>
       </c>
+      <c r="AK526" t="n">
+        <v>0.4344476190476191</v>
+      </c>
     </row>
     <row r="527">
       <c r="H527" s="5" t="n">
@@ -37937,6 +38858,9 @@
       <c r="AI527" t="n">
         <v>0.2846541666666667</v>
       </c>
+      <c r="AK527" t="n">
+        <v>0.5678839999999999</v>
+      </c>
     </row>
     <row r="528">
       <c r="H528" s="5" t="n">
@@ -37981,6 +38905,9 @@
       <c r="AI528" t="n">
         <v>0.5116583333333334</v>
       </c>
+      <c r="AK528" t="n">
+        <v>0.4499207547169811</v>
+      </c>
     </row>
     <row r="529">
       <c r="H529" s="5" t="n">
@@ -38025,6 +38952,9 @@
       <c r="AI529" t="n">
         <v>0.4508945454545455</v>
       </c>
+      <c r="AK529" t="n">
+        <v>0.4131</v>
+      </c>
     </row>
     <row r="530">
       <c r="H530" s="5" t="n">
@@ -38060,6 +38990,9 @@
       <c r="AI530" t="n">
         <v>0.4951224137931035</v>
       </c>
+      <c r="AK530" t="n">
+        <v>0.4914228571428571</v>
+      </c>
     </row>
     <row r="531">
       <c r="H531" s="5" t="n">
@@ -38095,6 +39028,9 @@
       <c r="AI531" t="n">
         <v>0.3783961538461539</v>
       </c>
+      <c r="AK531" t="n">
+        <v>0.507194</v>
+      </c>
     </row>
     <row r="532">
       <c r="H532" s="5" t="n">
@@ -38130,6 +39066,9 @@
       <c r="AI532" t="n">
         <v>0.5010883333333334</v>
       </c>
+      <c r="AK532" t="n">
+        <v>0.4965846153846153</v>
+      </c>
     </row>
     <row r="533">
       <c r="H533" s="5" t="n">
@@ -38165,6 +39104,9 @@
       <c r="AI533" t="n">
         <v>0.4608</v>
       </c>
+      <c r="AK533" t="n">
+        <v>0.4295621621621623</v>
+      </c>
     </row>
     <row r="534">
       <c r="H534" s="5" t="n">
@@ -38200,6 +39142,9 @@
       <c r="AI534" t="n">
         <v>0.4022145833333333</v>
       </c>
+      <c r="AK534" t="n">
+        <v>0.5316</v>
+      </c>
     </row>
     <row r="535">
       <c r="H535" s="5" t="n">
@@ -38235,6 +39180,9 @@
       <c r="AI535" t="n">
         <v>0.465167213114754</v>
       </c>
+      <c r="AK535" t="n">
+        <v>0.4506295454545455</v>
+      </c>
     </row>
     <row r="536">
       <c r="H536" s="5" t="n">
@@ -38270,6 +39218,9 @@
       <c r="AI536" t="n">
         <v>0.3577081081081081</v>
       </c>
+      <c r="AK536" t="n">
+        <v>0.5153283018867925</v>
+      </c>
     </row>
     <row r="537">
       <c r="H537" s="5" t="n">
@@ -38305,6 +39256,9 @@
       <c r="AI537" t="n">
         <v>0.297085</v>
       </c>
+      <c r="AK537" t="n">
+        <v>0.5490267857142858</v>
+      </c>
     </row>
     <row r="538">
       <c r="H538" s="5" t="n">
@@ -38340,6 +39294,9 @@
       <c r="AI538" t="n">
         <v>0.4526016666666667</v>
       </c>
+      <c r="AK538" t="n">
+        <v>0.40654</v>
+      </c>
     </row>
     <row r="539">
       <c r="H539" s="5" t="n">
@@ -38375,6 +39332,9 @@
       <c r="AI539" t="n">
         <v>0.3811</v>
       </c>
+      <c r="AK539" t="n">
+        <v>0.5892018181818183</v>
+      </c>
     </row>
     <row r="540">
       <c r="H540" s="5" t="n">
@@ -38410,6 +39370,9 @@
       <c r="AI540" t="n">
         <v>0.4125803571428571</v>
       </c>
+      <c r="AK540" t="n">
+        <v>0.5236938775510205</v>
+      </c>
     </row>
     <row r="541">
       <c r="H541" s="5" t="n">
@@ -38445,6 +39408,9 @@
       <c r="AI541" t="n">
         <v>0.5831545454545455</v>
       </c>
+      <c r="AK541" t="n">
+        <v>0.4193055555555555</v>
+      </c>
     </row>
     <row r="542">
       <c r="H542" s="5" t="n">
@@ -38480,6 +39446,9 @@
       <c r="AI542" t="n">
         <v>0.4331245901639345</v>
       </c>
+      <c r="AK542" t="n">
+        <v>0.576088888888889</v>
+      </c>
     </row>
     <row r="543">
       <c r="H543" s="5" t="n">
@@ -38515,6 +39484,9 @@
       <c r="AI543" t="n">
         <v>0.4620406779661017</v>
       </c>
+      <c r="AK543" t="n">
+        <v>0.501808</v>
+      </c>
     </row>
     <row r="544">
       <c r="H544" s="5" t="n">
@@ -38550,6 +39522,9 @@
       <c r="AI544" t="n">
         <v>0.4957734374999999</v>
       </c>
+      <c r="AK544" t="n">
+        <v>0.4478823529411765</v>
+      </c>
     </row>
     <row r="545">
       <c r="H545" s="5" t="n">
@@ -38585,6 +39560,9 @@
       <c r="AI545" t="n">
         <v>0.575545945945946</v>
       </c>
+      <c r="AK545" t="n">
+        <v>0.45632</v>
+      </c>
     </row>
     <row r="546">
       <c r="H546" s="5" t="n">
@@ -38620,6 +39598,9 @@
       <c r="AI546" t="n">
         <v>0.482527868852459</v>
       </c>
+      <c r="AK546" t="n">
+        <v>0.5348583333333333</v>
+      </c>
     </row>
     <row r="547">
       <c r="H547" s="5" t="n">
@@ -38655,6 +39636,9 @@
       <c r="AI547" t="n">
         <v>0.4267274509803923</v>
       </c>
+      <c r="AK547" t="n">
+        <v>0.5198714285714287</v>
+      </c>
     </row>
     <row r="548">
       <c r="H548" s="5" t="n">
@@ -38690,6 +39674,9 @@
       <c r="AI548" t="n">
         <v>0.5417542372881355</v>
       </c>
+      <c r="AK548" t="n">
+        <v>0.5644189189189188</v>
+      </c>
     </row>
     <row r="549">
       <c r="H549" s="5" t="n">
@@ -38725,6 +39712,9 @@
       <c r="AI549" t="n">
         <v>0.4767525423728814</v>
       </c>
+      <c r="AK549" t="n">
+        <v>0.5141245283018868</v>
+      </c>
     </row>
     <row r="550">
       <c r="H550" s="5" t="n">
@@ -38760,6 +39750,9 @@
       <c r="AI550" t="n">
         <v>0.4262102564102564</v>
       </c>
+      <c r="AK550" t="n">
+        <v>0.6430943396226414</v>
+      </c>
     </row>
     <row r="551">
       <c r="H551" s="5" t="n">
@@ -38795,6 +39788,9 @@
       <c r="AI551" t="n">
         <v>0.4427032786885246</v>
       </c>
+      <c r="AK551" t="n">
+        <v>0.4812937499999999</v>
+      </c>
     </row>
     <row r="552">
       <c r="H552" s="5" t="n">
@@ -38830,6 +39826,9 @@
       <c r="AI552" t="n">
         <v>0.3574173913043478</v>
       </c>
+      <c r="AK552" t="n">
+        <v>0.5290714285714285</v>
+      </c>
     </row>
     <row r="553">
       <c r="H553" s="5" t="n">
@@ -38865,6 +39864,9 @@
       <c r="AI553" t="n">
         <v>0.4145642857142858</v>
       </c>
+      <c r="AK553" t="n">
+        <v>0.5432341463414634</v>
+      </c>
     </row>
     <row r="554">
       <c r="H554" s="5" t="n">
@@ -38900,6 +39902,9 @@
       <c r="AI554" t="n">
         <v>0.4851067796610169</v>
       </c>
+      <c r="AK554" t="n">
+        <v>0.5158648148148148</v>
+      </c>
     </row>
     <row r="555">
       <c r="H555" s="5" t="n">
@@ -38935,6 +39940,9 @@
       <c r="AI555" t="n">
         <v>0.4232666666666667</v>
       </c>
+      <c r="AK555" t="n">
+        <v>0.5753929824561405</v>
+      </c>
     </row>
     <row r="556">
       <c r="H556" s="5" t="n">
@@ -38970,6 +39978,9 @@
       <c r="AI556" t="n">
         <v>0.444435</v>
       </c>
+      <c r="AK556" t="n">
+        <v>0.5955347826086956</v>
+      </c>
     </row>
     <row r="557">
       <c r="H557" s="5" t="n">
@@ -39005,6 +40016,9 @@
       <c r="AI557" t="n">
         <v>0.41788</v>
       </c>
+      <c r="AK557" t="n">
+        <v>0.4795121212121212</v>
+      </c>
     </row>
     <row r="558">
       <c r="H558" s="5" t="n">
@@ -39040,6 +40054,9 @@
       <c r="AI558" t="n">
         <v>0.4011245901639344</v>
       </c>
+      <c r="AK558" t="n">
+        <v>0.4850000000000002</v>
+      </c>
     </row>
     <row r="559">
       <c r="H559" s="5" t="n">
@@ -39075,6 +40092,9 @@
       <c r="AI559" t="n">
         <v>0.4532693548387098</v>
       </c>
+      <c r="AK559" t="n">
+        <v>0.5440425531914894</v>
+      </c>
     </row>
     <row r="560">
       <c r="H560" s="5" t="n">
@@ -39110,6 +40130,9 @@
       <c r="AI560" t="n">
         <v>0.4451980392156863</v>
       </c>
+      <c r="AK560" t="n">
+        <v>0.6080282051282052</v>
+      </c>
     </row>
     <row r="561">
       <c r="H561" s="5" t="n">
@@ -39145,6 +40168,9 @@
       <c r="AI561" t="n">
         <v>0.5603049999999999</v>
       </c>
+      <c r="AK561" t="n">
+        <v>0.4930116279069768</v>
+      </c>
     </row>
     <row r="562">
       <c r="H562" s="5" t="n">
@@ -39180,6 +40206,9 @@
       <c r="AI562" t="n">
         <v>0.5377527272727273</v>
       </c>
+      <c r="AK562" t="n">
+        <v>0.435880487804878</v>
+      </c>
     </row>
     <row r="563">
       <c r="H563" s="5" t="n">
@@ -39215,6 +40244,9 @@
       <c r="AI563" t="n">
         <v>0.4258238095238095</v>
       </c>
+      <c r="AK563" t="n">
+        <v>0.5299351851851851</v>
+      </c>
     </row>
     <row r="564">
       <c r="H564" s="5" t="n">
@@ -39250,6 +40282,9 @@
       <c r="AI564" t="n">
         <v>0.3946571428571428</v>
       </c>
+      <c r="AK564" t="n">
+        <v>0.6445163636363634</v>
+      </c>
     </row>
     <row r="565">
       <c r="H565" s="5" t="n">
@@ -39285,6 +40320,9 @@
       <c r="AI565" t="n">
         <v>0.397948076923077</v>
       </c>
+      <c r="AK565" t="n">
+        <v>0.4598976744186046</v>
+      </c>
     </row>
     <row r="566">
       <c r="H566" s="5" t="n">
@@ -39320,6 +40358,9 @@
       <c r="AI566" t="n">
         <v>0.4954880952380952</v>
       </c>
+      <c r="AK566" t="n">
+        <v>0.520248</v>
+      </c>
     </row>
     <row r="567">
       <c r="H567" s="5" t="n">
@@ -39355,6 +40396,9 @@
       <c r="AI567" t="n">
         <v>0.3712135135135136</v>
       </c>
+      <c r="AK567" t="n">
+        <v>0.5084170212765958</v>
+      </c>
     </row>
     <row r="568">
       <c r="H568" s="5" t="n">
@@ -39390,6 +40434,9 @@
       <c r="AI568" t="n">
         <v>0.5167102040816326</v>
       </c>
+      <c r="AK568" t="n">
+        <v>0.5476808510638299</v>
+      </c>
     </row>
     <row r="569">
       <c r="H569" s="5" t="n">
@@ -39425,6 +40472,9 @@
       <c r="AI569" t="n">
         <v>0.4900320754716981</v>
       </c>
+      <c r="AK569" t="n">
+        <v>0.6343551020408164</v>
+      </c>
     </row>
     <row r="570">
       <c r="H570" s="5" t="n">
@@ -39460,6 +40510,9 @@
       <c r="AI570" t="n">
         <v>0.5515588235294117</v>
       </c>
+      <c r="AK570" t="n">
+        <v>0.4590404761904762</v>
+      </c>
     </row>
     <row r="571">
       <c r="H571" s="5" t="n">
@@ -39495,6 +40548,9 @@
       <c r="AI571" t="n">
         <v>0.4389015873015872</v>
       </c>
+      <c r="AK571" t="n">
+        <v>0.6639212765957446</v>
+      </c>
     </row>
     <row r="572">
       <c r="H572" s="5" t="n">
@@ -39530,6 +40586,9 @@
       <c r="AI572" t="n">
         <v>0.5389327868852459</v>
       </c>
+      <c r="AK572" t="n">
+        <v>0.4782488372093024</v>
+      </c>
     </row>
     <row r="573">
       <c r="H573" s="5" t="n">
@@ -39565,6 +40624,9 @@
       <c r="AI573" t="n">
         <v>0.4695723404255319</v>
       </c>
+      <c r="AK573" t="n">
+        <v>0.5320480769230769</v>
+      </c>
     </row>
     <row r="574">
       <c r="H574" s="5" t="n">
@@ -39600,6 +40662,9 @@
       <c r="AI574" t="n">
         <v>0.5264584615384615</v>
       </c>
+      <c r="AK574" t="n">
+        <v>0.5420148936170213</v>
+      </c>
     </row>
     <row r="575">
       <c r="H575" s="5" t="n">
@@ -39635,6 +40700,9 @@
       <c r="AI575" t="n">
         <v>0.4963703703703704</v>
       </c>
+      <c r="AK575" t="n">
+        <v>0.6320883720930233</v>
+      </c>
     </row>
     <row r="576">
       <c r="H576" s="5" t="n">
@@ -39670,6 +40738,9 @@
       <c r="AI576" t="n">
         <v>0.4018028571428571</v>
       </c>
+      <c r="AK576" t="n">
+        <v>0.5172867924528303</v>
+      </c>
     </row>
     <row r="577">
       <c r="H577" s="5" t="n">
@@ -39705,6 +40776,9 @@
       <c r="AI577" t="n">
         <v>0.4824263157894737</v>
       </c>
+      <c r="AK577" t="n">
+        <v>0.6090300000000001</v>
+      </c>
     </row>
     <row r="578">
       <c r="H578" s="5" t="n">
@@ -39740,6 +40814,9 @@
       <c r="AI578" t="n">
         <v>0.4637245901639344</v>
       </c>
+      <c r="AK578" t="n">
+        <v>0.4818205128205128</v>
+      </c>
     </row>
     <row r="579">
       <c r="H579" s="5" t="n">
@@ -39775,6 +40852,9 @@
       <c r="AI579" t="n">
         <v>0.4540272727272727</v>
       </c>
+      <c r="AK579" t="n">
+        <v>0.5494477272727273</v>
+      </c>
     </row>
     <row r="580">
       <c r="H580" s="5" t="n">
@@ -39810,6 +40890,9 @@
       <c r="AI580" t="n">
         <v>0.4959056603773584</v>
       </c>
+      <c r="AK580" t="n">
+        <v>0.5358682926829268</v>
+      </c>
     </row>
     <row r="581">
       <c r="H581" s="5" t="n">
@@ -39845,6 +40928,9 @@
       <c r="AI581" t="n">
         <v>0.4562163636363637</v>
       </c>
+      <c r="AK581" t="n">
+        <v>0.6102235294117647</v>
+      </c>
     </row>
     <row r="582">
       <c r="H582" s="5" t="n">
@@ -39880,6 +40966,9 @@
       <c r="AI582" t="n">
         <v>0.5284689655172413</v>
       </c>
+      <c r="AK582" t="n">
+        <v>0.5973909090909092</v>
+      </c>
     </row>
     <row r="583">
       <c r="H583" s="5" t="n">
@@ -39915,6 +41004,9 @@
       <c r="AI583" t="n">
         <v>0.4816906976744186</v>
       </c>
+      <c r="AK583" t="n">
+        <v>0.6986892857142858</v>
+      </c>
     </row>
     <row r="584">
       <c r="H584" s="5" t="n">
@@ -39950,6 +41042,9 @@
       <c r="AI584" t="n">
         <v>0.5130322580645161</v>
       </c>
+      <c r="AK584" t="n">
+        <v>0.5769675675675676</v>
+      </c>
     </row>
     <row r="585">
       <c r="H585" s="5" t="n">
@@ -39985,6 +41080,9 @@
       <c r="AI585" t="n">
         <v>0.4921869565217391</v>
       </c>
+      <c r="AK585" t="n">
+        <v>0.6178622641509434</v>
+      </c>
     </row>
     <row r="586">
       <c r="H586" s="5" t="n">
@@ -40020,6 +41118,9 @@
       <c r="AI586" t="n">
         <v>0.4462366666666667</v>
       </c>
+      <c r="AK586" t="n">
+        <v>0.5800833333333334</v>
+      </c>
     </row>
     <row r="587">
       <c r="H587" s="5" t="n">
@@ -40055,6 +41156,9 @@
       <c r="AI587" t="n">
         <v>0.4618345454545454</v>
       </c>
+      <c r="AK587" t="n">
+        <v>0.4852018867924528</v>
+      </c>
     </row>
     <row r="588">
       <c r="H588" s="5" t="n">
@@ -40090,6 +41194,9 @@
       <c r="AI588" t="n">
         <v>0.5012519999999999</v>
       </c>
+      <c r="AK588" t="n">
+        <v>0.5582600000000001</v>
+      </c>
     </row>
     <row r="589">
       <c r="H589" s="5" t="n">
@@ -40125,6 +41232,9 @@
       <c r="AI589" t="n">
         <v>0.5026981132075472</v>
       </c>
+      <c r="AK589" t="n">
+        <v>0.650254054054054</v>
+      </c>
     </row>
     <row r="590">
       <c r="H590" s="5" t="n">
@@ -40160,6 +41270,9 @@
       <c r="AI590" t="n">
         <v>0.4446111111111111</v>
       </c>
+      <c r="AK590" t="n">
+        <v>0.599292</v>
+      </c>
     </row>
     <row r="591">
       <c r="H591" s="5" t="n">
@@ -40195,6 +41308,9 @@
       <c r="AI591" t="n">
         <v>0.4232176470588236</v>
       </c>
+      <c r="AK591" t="n">
+        <v>0.7191604651162792</v>
+      </c>
     </row>
     <row r="592">
       <c r="H592" s="5" t="n">
@@ -40230,6 +41346,9 @@
       <c r="AI592" t="n">
         <v>0.5659461538461539</v>
       </c>
+      <c r="AK592" t="n">
+        <v>0.6756881355932205</v>
+      </c>
     </row>
     <row r="593">
       <c r="H593" s="5" t="n">
@@ -40265,6 +41384,9 @@
       <c r="AI593" t="n">
         <v>0.4670844827586206</v>
       </c>
+      <c r="AK593" t="n">
+        <v>0.5045954545454545</v>
+      </c>
     </row>
     <row r="594">
       <c r="H594" s="5" t="n">
@@ -40300,6 +41422,9 @@
       <c r="AI594" t="n">
         <v>0.5047617021276595</v>
       </c>
+      <c r="AK594" t="n">
+        <v>0.5366160714285714</v>
+      </c>
     </row>
     <row r="595">
       <c r="H595" s="5" t="n">
@@ -40335,6 +41460,9 @@
       <c r="AI595" t="n">
         <v>0.5065603773584906</v>
       </c>
+      <c r="AK595" t="n">
+        <v>0.5389342857142857</v>
+      </c>
     </row>
     <row r="596">
       <c r="H596" s="5" t="n">
@@ -40370,6 +41498,9 @@
       <c r="AI596" t="n">
         <v>0.4321127659574467</v>
       </c>
+      <c r="AK596" t="n">
+        <v>0.5825416666666666</v>
+      </c>
     </row>
     <row r="597">
       <c r="H597" s="5" t="n">
@@ -40405,6 +41536,9 @@
       <c r="AI597" t="n">
         <v>0.4917372549019607</v>
       </c>
+      <c r="AK597" t="n">
+        <v>0.4837243243243242</v>
+      </c>
     </row>
     <row r="598">
       <c r="H598" s="5" t="n">
@@ -40440,6 +41574,9 @@
       <c r="AI598" t="n">
         <v>0.4583737704918033</v>
       </c>
+      <c r="AK598" t="n">
+        <v>0.489695652173913</v>
+      </c>
     </row>
     <row r="599">
       <c r="H599" s="5" t="n">
@@ -40475,6 +41612,9 @@
       <c r="AI599" t="n">
         <v>0.442138775510204</v>
       </c>
+      <c r="AK599" t="n">
+        <v>0.6250102040816327</v>
+      </c>
     </row>
     <row r="600">
       <c r="H600" s="5" t="n">
@@ -40510,6 +41650,9 @@
       <c r="AI600" t="n">
         <v>0.5020217391304347</v>
       </c>
+      <c r="AK600" t="n">
+        <v>0.6073306122448979</v>
+      </c>
     </row>
     <row r="601">
       <c r="H601" s="5" t="n">
@@ -40545,6 +41688,9 @@
       <c r="AI601" t="n">
         <v>0.48162</v>
       </c>
+      <c r="AK601" t="n">
+        <v>0.6676574468085107</v>
+      </c>
     </row>
     <row r="602">
       <c r="H602" s="5" t="n">
@@ -40580,6 +41726,9 @@
       <c r="AI602" t="n">
         <v>0.5103782608695653</v>
       </c>
+      <c r="AK602" t="n">
+        <v>0.4650875</v>
+      </c>
     </row>
     <row r="603">
       <c r="H603" s="5" t="n">
@@ -40615,6 +41764,9 @@
       <c r="AI603" t="n">
         <v>0.567101923076923</v>
       </c>
+      <c r="AK603" t="n">
+        <v>0.5735384615384616</v>
+      </c>
     </row>
     <row r="604">
       <c r="H604" s="5" t="n">
@@ -40650,6 +41802,9 @@
       <c r="AI604" t="n">
         <v>0.4864060606060606</v>
       </c>
+      <c r="AK604" t="n">
+        <v>0.5157</v>
+      </c>
     </row>
     <row r="605">
       <c r="H605" s="5" t="n">
@@ -40685,6 +41840,9 @@
       <c r="AI605" t="n">
         <v>0.4698021739130435</v>
       </c>
+      <c r="AK605" t="n">
+        <v>0.5193767857142857</v>
+      </c>
     </row>
     <row r="606">
       <c r="H606" s="5" t="n">
@@ -40720,6 +41878,9 @@
       <c r="AI606" t="n">
         <v>0.4769766666666667</v>
       </c>
+      <c r="AK606" t="n">
+        <v>0.5569755102040816</v>
+      </c>
     </row>
     <row r="607">
       <c r="H607" s="5" t="n">
@@ -40755,6 +41916,9 @@
       <c r="AI607" t="n">
         <v>0.5219344262295083</v>
       </c>
+      <c r="AK607" t="n">
+        <v>0.5292907407407408</v>
+      </c>
     </row>
     <row r="608">
       <c r="H608" s="5" t="n">
@@ -40790,6 +41954,9 @@
       <c r="AI608" t="n">
         <v>0.467019696969697</v>
       </c>
+      <c r="AK608" t="n">
+        <v>0.5290255813953487</v>
+      </c>
     </row>
     <row r="609">
       <c r="H609" s="5" t="n">
@@ -40825,6 +41992,9 @@
       <c r="AI609" t="n">
         <v>0.4993666666666666</v>
       </c>
+      <c r="AK609" t="n">
+        <v>0.6392583333333333</v>
+      </c>
     </row>
     <row r="610">
       <c r="H610" s="5" t="n">
@@ -40860,6 +42030,9 @@
       <c r="AI610" t="n">
         <v>0.4155879999999999</v>
       </c>
+      <c r="AK610" t="n">
+        <v>0.531641935483871</v>
+      </c>
     </row>
     <row r="611">
       <c r="H611" s="5" t="n">
@@ -40895,6 +42068,9 @@
       <c r="AI611" t="n">
         <v>0.535139534883721</v>
       </c>
+      <c r="AK611" t="n">
+        <v>0.6348782608695653</v>
+      </c>
     </row>
     <row r="612">
       <c r="H612" s="5" t="n">
@@ -40930,6 +42106,9 @@
       <c r="AI612" t="n">
         <v>0.4739463414634146</v>
       </c>
+      <c r="AK612" t="n">
+        <v>0.507827868852459</v>
+      </c>
     </row>
     <row r="613">
       <c r="H613" s="5" t="n">
@@ -40965,6 +42144,9 @@
       <c r="AI613" t="n">
         <v>0.5428290909090909</v>
       </c>
+      <c r="AK613" t="n">
+        <v>0.649142105263158</v>
+      </c>
     </row>
     <row r="614">
       <c r="H614" s="5" t="n">
@@ -41000,6 +42182,9 @@
       <c r="AI614" t="n">
         <v>0.4532660377358492</v>
       </c>
+      <c r="AK614" t="n">
+        <v>0.7028416666666666</v>
+      </c>
     </row>
     <row r="615">
       <c r="H615" s="5" t="n">
@@ -41035,6 +42220,9 @@
       <c r="AI615" t="n">
         <v>0.4543424242424242</v>
       </c>
+      <c r="AK615" t="n">
+        <v>0.6299983050847457</v>
+      </c>
     </row>
     <row r="616">
       <c r="H616" s="5" t="n">
@@ -41070,6 +42258,9 @@
       <c r="AI616" t="n">
         <v>0.4755127659574467</v>
       </c>
+      <c r="AK616" t="n">
+        <v>0.58445</v>
+      </c>
     </row>
     <row r="617">
       <c r="H617" s="5" t="n">
@@ -41105,6 +42296,9 @@
       <c r="AI617" t="n">
         <v>0.377054</v>
       </c>
+      <c r="AK617" t="n">
+        <v>0.5412575000000001</v>
+      </c>
     </row>
     <row r="618">
       <c r="H618" s="5" t="n">
@@ -41140,6 +42334,9 @@
       <c r="AI618" t="n">
         <v>0.4300561403508771</v>
       </c>
+      <c r="AK618" t="n">
+        <v>0.5855422222222223</v>
+      </c>
     </row>
     <row r="619">
       <c r="H619" s="5" t="n">
@@ -41174,6 +42371,9 @@
       </c>
       <c r="AI619" t="n">
         <v>0.5009944444444445</v>
+      </c>
+      <c r="AK619" t="n">
+        <v>0.6634146341463415</v>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1187,6 +1187,9 @@
       <c r="AL9" t="n">
         <v>0.4001217391304348</v>
       </c>
+      <c r="AM9" t="n">
+        <v>0.4167333333333333</v>
+      </c>
     </row>
     <row r="10" ht="16" customHeight="1" s="8">
       <c r="A10" s="5" t="n">
@@ -1282,6 +1285,9 @@
       <c r="AL10" t="n">
         <v>0.45545</v>
       </c>
+      <c r="AM10" t="n">
+        <v>0.4759459459459459</v>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1" s="8">
       <c r="A11" s="5" t="n">
@@ -1377,6 +1383,9 @@
       <c r="AL11" t="n">
         <v>0.5509526315789474</v>
       </c>
+      <c r="AM11" t="n">
+        <v>0.5322153846153846</v>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="8">
       <c r="A12" s="5" t="n">
@@ -1472,6 +1481,9 @@
       <c r="AL12" t="n">
         <v>0.6627942857142858</v>
       </c>
+      <c r="AM12" t="n">
+        <v>0.6109027027027027</v>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1" s="8">
       <c r="A13" s="5" t="n">
@@ -1567,6 +1579,9 @@
       <c r="AL13" t="n">
         <v>0.7023480000000001</v>
       </c>
+      <c r="AM13" t="n">
+        <v>0.6654416666666667</v>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="8">
       <c r="A14" s="5" t="n">
@@ -1662,6 +1677,9 @@
       <c r="AL14" t="n">
         <v>0.6224999999999999</v>
       </c>
+      <c r="AM14" t="n">
+        <v>0.7221019607843137</v>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="8">
       <c r="A15" s="5" t="n">
@@ -1748,6 +1766,9 @@
       <c r="AL15" t="n">
         <v>0.6213695652173914</v>
       </c>
+      <c r="AM15" t="n">
+        <v>0.6269193548387096</v>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="8">
       <c r="A16" s="5" t="n">
@@ -1834,6 +1855,9 @@
       <c r="AL16" t="n">
         <v>0.6800666666666667</v>
       </c>
+      <c r="AM16" t="n">
+        <v>0.7214510638297873</v>
+      </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="8">
       <c r="A17" s="5" t="n">
@@ -1920,6 +1944,9 @@
       <c r="AL17" t="n">
         <v>0.76598</v>
       </c>
+      <c r="AM17" t="n">
+        <v>0.6934854166666667</v>
+      </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="8">
       <c r="A18" s="5" t="n">
@@ -2006,6 +2033,9 @@
       <c r="AL18" t="n">
         <v>0.7580375</v>
       </c>
+      <c r="AM18" t="n">
+        <v>0.771375</v>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="8">
       <c r="A19" s="5" t="n">
@@ -2092,6 +2122,9 @@
       <c r="AL19" t="n">
         <v>0.6613347826086957</v>
       </c>
+      <c r="AM19" t="n">
+        <v>0.7245118644067797</v>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="8">
       <c r="A20" s="5" t="n">
@@ -2178,6 +2211,9 @@
       <c r="AL20" t="n">
         <v>0.7499533333333334</v>
       </c>
+      <c r="AM20" t="n">
+        <v>0.8111357142857144</v>
+      </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="8">
       <c r="A21" s="5" t="n">
@@ -2264,6 +2300,9 @@
       <c r="AL21" t="n">
         <v>0.7329918918918918</v>
       </c>
+      <c r="AM21" t="n">
+        <v>0.6833214285714285</v>
+      </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="8">
       <c r="A22" s="5" t="n">
@@ -2350,6 +2389,9 @@
       <c r="AL22" t="n">
         <v>0.7339372093023256</v>
       </c>
+      <c r="AM22" t="n">
+        <v>0.7418333333333332</v>
+      </c>
     </row>
     <row r="23" ht="